--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="227">
   <si>
     <t>Ticker</t>
   </si>
@@ -352,7 +352,7 @@
     <t>2027-07-20</t>
   </si>
   <si>
-    <t>2026-08-13</t>
+    <t>2027-08-13</t>
   </si>
   <si>
     <t>2026-09-03</t>
@@ -370,7 +370,7 @@
     <t>2026-09-30</t>
   </si>
   <si>
-    <t>2027-07-09</t>
+    <t>2026-10-08</t>
   </si>
   <si>
     <t>2026-08-20</t>
@@ -421,7 +421,7 @@
     <t>_date_</t>
   </si>
   <si>
-    <t>2026-09-11</t>
+    <t>2026-09-14</t>
   </si>
   <si>
     <t>Criteria</t>
@@ -682,31 +682,25 @@
     <t>Momentum Breakout, Market Leader, Institutional Buying</t>
   </si>
   <si>
-    <t>Momentum Breakout, Market Leader, Volume Spike</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Stable Uptrend, Institutional Buying</t>
-  </si>
-  <si>
     <t>Momentum Breakout, Market Leader</t>
   </si>
   <si>
+    <t>Institutional Buying</t>
+  </si>
+  <si>
+    <t>Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
     <t>Momentum Breakout, Institutional Buying</t>
   </si>
   <si>
-    <t>Volume Spike, Institutional Buying</t>
+    <t>Volume Spike</t>
+  </si>
+  <si>
+    <t>Momentum Breakout</t>
   </si>
   <si>
     <t>Momentum Breakout, Market Leader, Volume Spike, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Institutional Buying</t>
-  </si>
-  <si>
-    <t>Volume Spike</t>
-  </si>
-  <si>
-    <t>Momentum Breakout</t>
   </si>
 </sst>
 </file>
@@ -1388,10 +1382,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="B2">
-        <v>63.01204819277108</v>
+        <v>62.7710843373494</v>
       </c>
       <c r="C2" t="s">
         <v>219</v>
@@ -1399,32 +1393,32 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>122</v>
       </c>
       <c r="B3">
-        <v>62.65060240963855</v>
+        <v>61.26506024096387</v>
       </c>
       <c r="C3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>122</v>
+        <v>13</v>
       </c>
       <c r="B4">
-        <v>60.903614457831324</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="B5">
-        <v>60.18072289156626</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
         <v>221</v>
@@ -1432,24 +1426,24 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="B6">
-        <v>60.12048192771084</v>
+        <v>59.81927710843374</v>
       </c>
       <c r="C6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="B7">
-        <v>58.67469879518071</v>
+        <v>59.75903614457832</v>
       </c>
       <c r="C7" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1457,54 +1451,54 @@
         <v>32</v>
       </c>
       <c r="B8">
-        <v>57.710843373493965</v>
+        <v>59.63855421686747</v>
       </c>
       <c r="C8" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B9">
-        <v>57.168674698795186</v>
+        <v>58.91566265060241</v>
       </c>
       <c r="C9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="B10">
-        <v>56.86746987951808</v>
+        <v>58.13253012048192</v>
       </c>
       <c r="C10" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="B11">
-        <v>56.26506024096385</v>
+        <v>57.349397590361455</v>
       </c>
       <c r="C11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="B12">
-        <v>56.144578313253014</v>
+        <v>57.168674698795186</v>
       </c>
       <c r="C12" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -1512,65 +1506,65 @@
         <v>36</v>
       </c>
       <c r="B13">
-        <v>56.08433734939759</v>
+        <v>56.44578313253012</v>
       </c>
       <c r="C13" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>125</v>
       </c>
       <c r="B14">
-        <v>55.60240963855423</v>
+        <v>55.78313253012049</v>
       </c>
       <c r="C14" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>3</v>
+        <v>124</v>
       </c>
       <c r="B15">
-        <v>54.879518072289166</v>
+        <v>55.42168674698795</v>
       </c>
       <c r="C15" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="B16">
-        <v>54.39759036144578</v>
+        <v>54.879518072289166</v>
       </c>
       <c r="C16" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>125</v>
+        <v>6</v>
       </c>
       <c r="B17">
-        <v>53.975903614457835</v>
+        <v>54.63855421686748</v>
       </c>
       <c r="C17" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B18">
-        <v>53.55421686746989</v>
+        <v>54.39759036144578</v>
       </c>
       <c r="C18" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -1578,10 +1572,10 @@
         <v>43</v>
       </c>
       <c r="B19">
-        <v>52.71084337349398</v>
+        <v>53.6144578313253</v>
       </c>
       <c r="C19" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -1589,40 +1583,40 @@
         <v>126</v>
       </c>
       <c r="B20">
-        <v>52.71084337349397</v>
+        <v>52.46987951807228</v>
       </c>
       <c r="C20" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>58</v>
+        <v>123</v>
       </c>
       <c r="B21">
-        <v>52.168674698795186</v>
+        <v>52.108433734939766</v>
       </c>
       <c r="C21" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B22">
-        <v>51.38554216867469</v>
+        <v>51.9277108433735</v>
       </c>
       <c r="C22" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="B23">
-        <v>51.144578313253014</v>
+        <v>51.506024096385545</v>
       </c>
       <c r="C23" t="s">
         <v>222</v>
@@ -1630,35 +1624,35 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B24">
-        <v>51.02409638554217</v>
+        <v>51.144578313253014</v>
       </c>
       <c r="C24" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>127</v>
+        <v>59</v>
       </c>
       <c r="B25">
-        <v>50.72289156626506</v>
+        <v>51.144578313253</v>
       </c>
       <c r="C25" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="B26">
-        <v>50.66265060240964</v>
+        <v>48.73493975903615</v>
       </c>
       <c r="C26" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -1666,32 +1660,32 @@
         <v>2</v>
       </c>
       <c r="B27">
-        <v>49.096385542168676</v>
+        <v>46.566265060240966</v>
       </c>
       <c r="C27" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B28">
-        <v>46.3855421686747</v>
+        <v>46.506024096385545</v>
       </c>
       <c r="C28" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="B29">
-        <v>46.20481927710843</v>
+        <v>46.20481927710844</v>
       </c>
       <c r="C29" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1702,26 +1696,26 @@
         <v>46.02409638554217</v>
       </c>
       <c r="C30" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B31">
-        <v>45.78313253012048</v>
+        <v>45.06024096385543</v>
       </c>
       <c r="C31" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="B32">
-        <v>44.81927710843374</v>
+        <v>44.87951807228916</v>
       </c>
       <c r="C32" t="s">
         <v>222</v>
@@ -1729,24 +1723,24 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>131</v>
+        <v>39</v>
       </c>
       <c r="B33">
-        <v>44.397590361445786</v>
+        <v>44.81927710843374</v>
       </c>
       <c r="C33" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="B34">
-        <v>43.67469879518072</v>
+        <v>44.1566265060241</v>
       </c>
       <c r="C34" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -1754,65 +1748,65 @@
         <v>53</v>
       </c>
       <c r="B35">
-        <v>41.74698795180723</v>
+        <v>43.43373493975904</v>
       </c>
       <c r="C35" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B36">
-        <v>41.686746987951814</v>
+        <v>41.626506024096386</v>
       </c>
       <c r="C36" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B37">
-        <v>41.144578313253014</v>
+        <v>41.325301204819276</v>
       </c>
       <c r="C37" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B38">
-        <v>41.08433734939759</v>
+        <v>40.36144578313253</v>
       </c>
       <c r="C38" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="B39">
-        <v>39.75903614457831</v>
+        <v>40.361445783132524</v>
       </c>
       <c r="C39" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="B40">
-        <v>39.397590361445786</v>
+        <v>40.12048192771084</v>
       </c>
       <c r="C40" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -1820,120 +1814,120 @@
         <v>21</v>
       </c>
       <c r="B41">
-        <v>38.855421686746986</v>
+        <v>39.45783132530121</v>
       </c>
       <c r="C41" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="B42">
-        <v>38.3132530120482</v>
+        <v>39.03614457831326</v>
       </c>
       <c r="C42" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="B43">
-        <v>37.95180722891566</v>
+        <v>38.91566265060241</v>
       </c>
       <c r="C43" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="B44">
-        <v>37.83132530120482</v>
+        <v>37.048192771084345</v>
       </c>
       <c r="C44" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B45">
-        <v>37.7710843373494</v>
+        <v>36.325301204819276</v>
       </c>
       <c r="C45" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="B46">
-        <v>36.084337349397586</v>
+        <v>33.85542168674699</v>
       </c>
       <c r="C46" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B47">
-        <v>34.27710843373494</v>
+        <v>33.674698795180724</v>
       </c>
       <c r="C47" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="B48">
-        <v>34.21686746987952</v>
+        <v>33.25301204819277</v>
       </c>
       <c r="C48" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>45</v>
+        <v>129</v>
       </c>
       <c r="B49">
-        <v>33.795180722891565</v>
+        <v>32.53012048192771</v>
       </c>
       <c r="C49" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="B50">
-        <v>32.168674698795186</v>
+        <v>32.5301204819277</v>
       </c>
       <c r="C50" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="B51">
-        <v>31.566265060240962</v>
+        <v>32.22891566265061</v>
       </c>
       <c r="C51" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -2164,52 +2158,52 @@
         <v>-1.9922779922779925</v>
       </c>
       <c r="E2" s="1">
-        <v>-2.09</v>
+        <v>-2.08</v>
       </c>
       <c r="F2" s="1">
-        <v>0.07701510805748597</v>
+        <v>0.11407702165707825</v>
       </c>
       <c r="G2" s="1">
         <v>0.21</v>
       </c>
       <c r="H2" s="1">
-        <v>60.43</v>
+        <v>65.99</v>
       </c>
       <c r="I2" s="1">
-        <v>13.62</v>
+        <v>15.94</v>
       </c>
       <c r="J2" s="1">
-        <v>0.016844303538731193</v>
+        <v>0.017365364677044127</v>
       </c>
       <c r="K2" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>-458</v>
+        <v>-457</v>
       </c>
       <c r="M2" s="1">
-        <v>0.04227779366790063</v>
+        <v>0.08609734927746793</v>
       </c>
       <c r="N2" s="1">
-        <v>9.699907770535036</v>
+        <v>13.226465608710125</v>
       </c>
       <c r="O2" s="1">
-        <v>55.42168674698795</v>
+        <v>66.26506024096386</v>
       </c>
       <c r="P2" s="1">
         <v>16.29652721982991</v>
       </c>
       <c r="Q2" s="1">
-        <v>54.21686746987952</v>
+        <v>56.144578313253014</v>
       </c>
       <c r="R2" s="1">
-        <v>41.024096385542165</v>
+        <v>44.518072289156635</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>93</v>
       </c>
       <c r="T2" s="1">
-        <v>21.21</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -2223,55 +2217,55 @@
         <v>54.21686746987952</v>
       </c>
       <c r="D3" s="1">
-        <v>26.320512820512818</v>
+        <v>26.664102564102564</v>
       </c>
       <c r="E3" s="1">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="F3" s="1">
-        <v>-0.0066245737634683804</v>
+        <v>-0.041915882124413245</v>
       </c>
       <c r="G3" s="1">
         <v>2.48</v>
       </c>
       <c r="H3" s="1">
-        <v>55.09</v>
+        <v>50.71</v>
       </c>
       <c r="I3" s="1">
-        <v>45.82</v>
+        <v>40.72</v>
       </c>
       <c r="J3" s="1">
-        <v>-0.009174593363194986</v>
+        <v>-0.007645872041769857</v>
       </c>
       <c r="K3" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L3" s="1">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="M3" s="1">
-        <v>0.058452926611957334</v>
+        <v>0.010501731953844073</v>
       </c>
       <c r="N3" s="1">
-        <v>11.317421064940719</v>
+        <v>5.666903876347738</v>
       </c>
       <c r="O3" s="1">
-        <v>61.44578313253012</v>
+        <v>51.80722891566265</v>
       </c>
       <c r="P3" s="1">
         <v>26.053946839070953</v>
       </c>
       <c r="Q3" s="1">
-        <v>62.89156626506024</v>
+        <v>61.80722891566265</v>
       </c>
       <c r="R3" s="1">
-        <v>49.096385542168676</v>
+        <v>46.566265060240966</v>
       </c>
       <c r="S3" s="1" t="s">
         <v>94</v>
       </c>
       <c r="T3" s="1">
-        <v>-17.98</v>
+        <v>-20.51</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -2288,34 +2282,34 @@
         <v>12.41640378548896</v>
       </c>
       <c r="E4" s="2">
-        <v>6.37</v>
+        <v>6.35</v>
       </c>
       <c r="F4" s="2">
-        <v>0.30429480910639095</v>
+        <v>0.30965016967214226</v>
       </c>
       <c r="G4" s="2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="H4" s="2">
-        <v>54.07</v>
+        <v>54.67</v>
       </c>
       <c r="I4" s="2">
-        <v>49.76</v>
+        <v>49.81</v>
       </c>
       <c r="J4" s="2">
-        <v>0.03297200042696196</v>
+        <v>0.028429868129135224</v>
       </c>
       <c r="K4" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="2">
         <v>179</v>
       </c>
       <c r="M4" s="2">
-        <v>0.3196847585194984</v>
+        <v>0.32240040012361026</v>
       </c>
       <c r="N4" s="2">
-        <v>37.44060425569482</v>
+        <v>36.856770693324364</v>
       </c>
       <c r="O4" s="2">
         <v>93.97590361445783</v>
@@ -2324,7 +2318,7 @@
         <v>19.349659482175007</v>
       </c>
       <c r="Q4" s="2">
-        <v>60.24096385542169</v>
+        <v>61.20481927710844</v>
       </c>
       <c r="R4" s="2">
         <v>54.879518072289166</v>
@@ -2350,114 +2344,114 @@
         <v>29.574074074074076</v>
       </c>
       <c r="E5" s="1">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="F5" s="1">
-        <v>-0.14198481563773874</v>
+        <v>-0.16285150162971704</v>
       </c>
       <c r="G5" s="1">
         <v>1.91</v>
       </c>
       <c r="H5" s="1">
-        <v>53.74</v>
+        <v>51.36</v>
       </c>
       <c r="I5" s="1">
-        <v>-8.89</v>
+        <v>-10.03</v>
       </c>
       <c r="J5" s="1">
-        <v>-0.007412827718672451</v>
+        <v>-0.010800052780961076</v>
       </c>
       <c r="K5" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="1">
         <v>140</v>
       </c>
       <c r="M5" s="1">
-        <v>-0.1019709471636594</v>
+        <v>-0.1306217524329507</v>
       </c>
       <c r="N5" s="1">
-        <v>-4.724966312620957</v>
+        <v>-8.445444562331742</v>
       </c>
       <c r="O5" s="1">
-        <v>26.506024096385545</v>
+        <v>22.89156626506024</v>
       </c>
       <c r="P5" s="1">
         <v>33.002444654975626</v>
       </c>
       <c r="Q5" s="1">
-        <v>51.6867469879518</v>
+        <v>50.24096385542168</v>
       </c>
       <c r="R5" s="1">
-        <v>34.21686746987952</v>
+        <v>32.5301204819277</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T5" s="1">
-        <v>-11.76</v>
+        <v>-13.45</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="1">
         <v>3.17</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="1">
         <v>49.39759036144578</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="1">
         <v>0.8864353312302841</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="1">
         <v>-1.87</v>
       </c>
-      <c r="F6" s="3">
-        <v>-0.15415280889613353</v>
-      </c>
-      <c r="G6" s="3">
+      <c r="F6" s="1">
+        <v>-0.11503668040004339</v>
+      </c>
+      <c r="G6" s="1">
         <v>1.6</v>
       </c>
-      <c r="H6" s="3">
-        <v>43.6</v>
-      </c>
-      <c r="I6" s="3">
-        <v>-12</v>
-      </c>
-      <c r="J6" s="3">
-        <v>0.007459048533648636</v>
-      </c>
-      <c r="K6" s="3" t="b">
+      <c r="H6" s="1">
+        <v>50.17</v>
+      </c>
+      <c r="I6" s="1">
+        <v>-9.29</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0.005413502775150525</v>
+      </c>
+      <c r="K6" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L6" s="3">
-        <v>-207</v>
-      </c>
-      <c r="M6" s="3">
-        <v>-0.12777003847366364</v>
-      </c>
-      <c r="N6" s="3">
-        <v>-7.30487544362138</v>
-      </c>
-      <c r="O6" s="3">
-        <v>19.27710843373494</v>
-      </c>
-      <c r="P6" s="3">
-        <v>37.28546442160462</v>
-      </c>
-      <c r="Q6" s="3">
-        <v>44.6987951807229</v>
-      </c>
-      <c r="R6" s="3">
-        <v>26.98795180722892</v>
-      </c>
-      <c r="S6" s="3" t="s">
+      <c r="L6" s="1">
+        <v>-206</v>
+      </c>
+      <c r="M6" s="1">
+        <v>-0.09378629631426338</v>
+      </c>
+      <c r="N6" s="1">
+        <v>-4.7618989504630065</v>
+      </c>
+      <c r="O6" s="1">
+        <v>34.93975903614458</v>
+      </c>
+      <c r="P6" s="1">
+        <v>30.53129157318417</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>46.626506024096386</v>
+      </c>
+      <c r="R6" s="1">
+        <v>32.40963855421687</v>
+      </c>
+      <c r="S6" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="T6" s="3">
-        <v>7.9</v>
+      <c r="T6" s="1">
+        <v>13.32</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -2474,52 +2468,52 @@
         <v>7.797724399494312</v>
       </c>
       <c r="E7" s="2">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="F7" s="2">
-        <v>-0.01885421281586945</v>
+        <v>-0.023871474132499473</v>
       </c>
       <c r="G7" s="2">
         <v>2.22</v>
       </c>
       <c r="H7" s="2">
-        <v>49.81</v>
+        <v>45.45</v>
       </c>
       <c r="I7" s="2">
-        <v>10.69</v>
+        <v>7.81</v>
       </c>
       <c r="J7" s="2">
-        <v>0.013784073435239356</v>
+        <v>0.012912507978848907</v>
       </c>
       <c r="K7" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L7" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M7" s="2">
-        <v>0.03479075370981932</v>
+        <v>0.01933764017525319</v>
       </c>
       <c r="N7" s="2">
-        <v>8.951203774726917</v>
+        <v>6.550494698488644</v>
       </c>
       <c r="O7" s="2">
-        <v>53.01204819277109</v>
+        <v>56.62650602409639</v>
       </c>
       <c r="P7" s="2">
         <v>19.398494070050486</v>
       </c>
       <c r="Q7" s="2">
-        <v>66.98795180722892</v>
+        <v>65.18072289156628</v>
       </c>
       <c r="R7" s="2">
-        <v>53.55421686746989</v>
+        <v>54.63855421686748</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>98</v>
       </c>
       <c r="T7" s="2">
-        <v>5.14</v>
+        <v>6.22</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -2536,52 +2530,52 @@
         <v>-0.1254019292604502</v>
       </c>
       <c r="E8" s="1">
-        <v>2.96</v>
+        <v>2.66</v>
       </c>
       <c r="F8" s="1">
-        <v>-0.08464457151201868</v>
+        <v>-0.09759926742763378</v>
       </c>
       <c r="G8" s="1">
         <v>0.61</v>
       </c>
       <c r="H8" s="1">
-        <v>40.81</v>
+        <v>36.54</v>
       </c>
       <c r="I8" s="1">
-        <v>10.08</v>
+        <v>7.6</v>
       </c>
       <c r="J8" s="1">
-        <v>-0.005065945795589619</v>
+        <v>-0.007134084901922103</v>
       </c>
       <c r="K8" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L8" s="1">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M8" s="1">
-        <v>-0.1017933722866241</v>
+        <v>-0.11141201708339077</v>
       </c>
       <c r="N8" s="1">
-        <v>-4.707208824917432</v>
+        <v>-6.524471027375747</v>
       </c>
       <c r="O8" s="1">
-        <v>27.710843373493976</v>
+        <v>26.506024096385545</v>
       </c>
       <c r="P8" s="1">
-        <v>11.802451994874641</v>
+        <v>13.122495465725093</v>
       </c>
       <c r="Q8" s="1">
-        <v>47.83132530120482</v>
+        <v>45.78313253012048</v>
       </c>
       <c r="R8" s="1">
-        <v>37.7710843373494</v>
+        <v>37.048192771084345</v>
       </c>
       <c r="S8" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T8" s="1">
-        <v>-21.99</v>
+        <v>-22.71</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -2595,55 +2589,55 @@
         <v>40.963855421686745</v>
       </c>
       <c r="D9" s="2">
-        <v>35.863247863247864</v>
+        <v>35.8974358974359</v>
       </c>
       <c r="E9" s="2">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="F9" s="2">
-        <v>0.19224466721552796</v>
+        <v>0.20801386529729005</v>
       </c>
       <c r="G9" s="2">
         <v>1.61</v>
       </c>
       <c r="H9" s="2">
-        <v>48.09</v>
+        <v>49.98</v>
       </c>
       <c r="I9" s="2">
-        <v>9.51</v>
+        <v>11.01</v>
       </c>
       <c r="J9" s="2">
-        <v>0.040291588452608745</v>
+        <v>0.036210567407572024</v>
       </c>
       <c r="K9" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L9" s="2">
-        <v>-114</v>
+        <v>-113</v>
       </c>
       <c r="M9" s="2">
-        <v>0.21906715047837233</v>
+        <v>0.22961842245116637</v>
       </c>
       <c r="N9" s="2">
-        <v>27.378843451582203</v>
+        <v>27.57857292607997</v>
       </c>
       <c r="O9" s="2">
-        <v>85.54216867469879</v>
+        <v>86.74698795180723</v>
       </c>
       <c r="P9" s="2">
         <v>33.227512780245505</v>
       </c>
       <c r="Q9" s="2">
-        <v>66.50602409638553</v>
+        <v>67.59036144578313</v>
       </c>
       <c r="R9" s="2">
-        <v>58.67469879518071</v>
+        <v>58.91566265060241</v>
       </c>
       <c r="S9" s="2" t="s">
         <v>99</v>
       </c>
       <c r="T9" s="2">
-        <v>31.3</v>
+        <v>31.54</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -2657,25 +2651,25 @@
         <v>59.036144578313255</v>
       </c>
       <c r="D10" s="1">
-        <v>0.752577319587629</v>
+        <v>0.7319587628865981</v>
       </c>
       <c r="E10" s="1">
-        <v>0.07</v>
+        <v>0.08</v>
       </c>
       <c r="F10" s="1">
-        <v>-0.00007291626649179317</v>
+        <v>0.0008470689437733714</v>
       </c>
       <c r="G10" s="1">
         <v>1.42</v>
       </c>
       <c r="H10" s="1">
-        <v>52</v>
+        <v>54.83</v>
       </c>
       <c r="I10" s="1">
-        <v>1.78</v>
+        <v>2.78</v>
       </c>
       <c r="J10" s="1">
-        <v>0.006873130313200099</v>
+        <v>0.007814803125732838</v>
       </c>
       <c r="K10" s="1" t="b">
         <v>0</v>
@@ -2684,28 +2678,28 @@
         <v>-51</v>
       </c>
       <c r="M10" s="1">
-        <v>0.018395023029237123</v>
+        <v>0.015722337803819375</v>
       </c>
       <c r="N10" s="1">
-        <v>7.3116307066687</v>
+        <v>6.188964461345262</v>
       </c>
       <c r="O10" s="1">
-        <v>48.19277108433735</v>
+        <v>54.21686746987952</v>
       </c>
       <c r="P10" s="1">
         <v>14.568379622257217</v>
       </c>
       <c r="Q10" s="1">
-        <v>51.44578313253012</v>
+        <v>54.6987951807229</v>
       </c>
       <c r="R10" s="1">
-        <v>42.4698795180723</v>
+        <v>45.12048192771084</v>
       </c>
       <c r="S10" s="1" t="s">
         <v>100</v>
       </c>
       <c r="T10" s="1">
-        <v>6.92</v>
+        <v>9.57</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -2722,22 +2716,22 @@
         <v>46.702970297029694</v>
       </c>
       <c r="E11" s="2">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="F11" s="2">
-        <v>0.29656945602907425</v>
+        <v>0.3014712260383675</v>
       </c>
       <c r="G11" s="2">
         <v>0.73</v>
       </c>
       <c r="H11" s="2">
-        <v>46.03</v>
+        <v>50.37</v>
       </c>
       <c r="I11" s="2">
-        <v>23.22</v>
+        <v>26.74</v>
       </c>
       <c r="J11" s="2">
-        <v>0.019020742801384657</v>
+        <v>0.01637532525447152</v>
       </c>
       <c r="K11" s="2" t="b">
         <v>0</v>
@@ -2746,19 +2740,19 @@
         <v>40</v>
       </c>
       <c r="M11" s="2">
-        <v>0.2846972093389628</v>
+        <v>0.2919085531997665</v>
       </c>
       <c r="N11" s="2">
-        <v>33.941849337641266</v>
+        <v>33.80758600093998</v>
       </c>
       <c r="O11" s="2">
-        <v>91.56626506024097</v>
+        <v>92.7710843373494</v>
       </c>
       <c r="P11" s="2">
         <v>21.2185970476566</v>
       </c>
       <c r="Q11" s="2">
-        <v>60.00000000000001</v>
+        <v>60.8433734939759</v>
       </c>
       <c r="R11" s="2">
         <v>57.168674698795186</v>
@@ -2784,22 +2778,22 @@
         <v>65.06451612903226</v>
       </c>
       <c r="E12" s="2">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="F12" s="2">
-        <v>0.6047853827604924</v>
+        <v>0.6087644123724786</v>
       </c>
       <c r="G12" s="2">
         <v>0.99</v>
       </c>
       <c r="H12" s="2">
-        <v>62.57</v>
+        <v>63.75</v>
       </c>
       <c r="I12" s="2">
-        <v>49.51</v>
+        <v>51.44</v>
       </c>
       <c r="J12" s="2">
-        <v>0.052019457098429873</v>
+        <v>0.04839537541924725</v>
       </c>
       <c r="K12" s="2" t="b">
         <v>0</v>
@@ -2808,10 +2802,10 @@
         <v>28</v>
       </c>
       <c r="M12" s="2">
-        <v>0.604345669920118</v>
+        <v>0.6084102393043822</v>
       </c>
       <c r="N12" s="2">
-        <v>65.90669539575677</v>
+        <v>65.45775461140155</v>
       </c>
       <c r="O12" s="2">
         <v>100</v>
@@ -2820,16 +2814,16 @@
         <v>23.557267760130397</v>
       </c>
       <c r="Q12" s="2">
-        <v>71.80722891566265</v>
+        <v>72.16867469879517</v>
       </c>
       <c r="R12" s="2">
-        <v>62.65060240963855</v>
+        <v>62.7710843373494</v>
       </c>
       <c r="S12" s="2" t="s">
         <v>102</v>
       </c>
       <c r="T12" s="2">
-        <v>9.91</v>
+        <v>10.03</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -2846,22 +2840,22 @@
         <v>-4558.5</v>
       </c>
       <c r="E13" s="1">
-        <v>-1.08</v>
+        <v>-1.09</v>
       </c>
       <c r="F13" s="1">
-        <v>0.533558044760853</v>
+        <v>0.4049285995752488</v>
       </c>
       <c r="G13" s="1">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="H13" s="1">
-        <v>60.52</v>
+        <v>51.04</v>
       </c>
       <c r="I13" s="1">
-        <v>20.61</v>
+        <v>12.6</v>
       </c>
       <c r="J13" s="1">
-        <v>0.053367666966704835</v>
+        <v>0.05236163758426345</v>
       </c>
       <c r="K13" s="1" t="b">
         <v>1</v>
@@ -2870,28 +2864,28 @@
         <v>5</v>
       </c>
       <c r="M13" s="1">
-        <v>0.5581819638218248</v>
+        <v>0.4251164644567398</v>
       </c>
       <c r="N13" s="1">
-        <v>61.29032478592747</v>
+        <v>47.12837712663732</v>
       </c>
       <c r="O13" s="1">
-        <v>98.79518072289156</v>
+        <v>97.59036144578313</v>
       </c>
       <c r="P13" s="1">
         <v>40.13761891809808</v>
       </c>
       <c r="Q13" s="1">
-        <v>46.144578313253014</v>
+        <v>42.7710843373494</v>
       </c>
       <c r="R13" s="1">
-        <v>39.397590361445786</v>
+        <v>39.03614457831326</v>
       </c>
       <c r="S13" s="1" t="s">
         <v>103</v>
       </c>
       <c r="T13" s="1">
-        <v>38.6</v>
+        <v>38.24</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -2908,22 +2902,22 @@
         <v>5.385542168674699</v>
       </c>
       <c r="E14" s="2">
-        <v>-1.76</v>
+        <v>-1.74</v>
       </c>
       <c r="F14" s="2">
-        <v>0.4447806871379631</v>
+        <v>0.3793541234204233</v>
       </c>
       <c r="G14" s="2">
         <v>0.76</v>
       </c>
       <c r="H14" s="2">
-        <v>62.05</v>
+        <v>61.02</v>
       </c>
       <c r="I14" s="2">
-        <v>65.79</v>
+        <v>64.82</v>
       </c>
       <c r="J14" s="2">
-        <v>0.030940583859687086</v>
+        <v>0.02715853073823938</v>
       </c>
       <c r="K14" s="2" t="b">
         <v>0</v>
@@ -2932,10 +2926,10 @@
         <v>100</v>
       </c>
       <c r="M14" s="2">
-        <v>0.4342275789689751</v>
+        <v>0.3708539697861113</v>
       </c>
       <c r="N14" s="2">
-        <v>48.8948863006425</v>
+        <v>41.702127659574465</v>
       </c>
       <c r="O14" s="2">
         <v>96.3855421686747</v>
@@ -2944,16 +2938,16 @@
         <v>19.142997204429033</v>
       </c>
       <c r="Q14" s="2">
-        <v>67.95180722891567</v>
+        <v>67.10843373493977</v>
       </c>
       <c r="R14" s="2">
-        <v>60.12048192771084</v>
+        <v>60</v>
       </c>
       <c r="S14" s="2" t="s">
         <v>98</v>
       </c>
       <c r="T14" s="2">
-        <v>4.21</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -2970,52 +2964,52 @@
         <v>19.13679245283019</v>
       </c>
       <c r="E15" s="3">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="F15" s="3">
-        <v>-0.17246566900976712</v>
+        <v>-0.2106631266661964</v>
       </c>
       <c r="G15" s="3">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="H15" s="3">
-        <v>54.8</v>
+        <v>50.11</v>
       </c>
       <c r="I15" s="3">
-        <v>33.41</v>
+        <v>27.88</v>
       </c>
       <c r="J15" s="3">
-        <v>-0.032441227898441435</v>
+        <v>-0.029559479351052936</v>
       </c>
       <c r="K15" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L15" s="3">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="M15" s="3">
-        <v>-0.11750156396295486</v>
+        <v>-0.16603732008605843</v>
       </c>
       <c r="N15" s="3">
-        <v>-6.278027992550507</v>
+        <v>-11.987001327642512</v>
       </c>
       <c r="O15" s="3">
-        <v>22.89156626506024</v>
+        <v>18.072289156626507</v>
       </c>
       <c r="P15" s="3">
         <v>41.90435941885386</v>
       </c>
       <c r="Q15" s="3">
-        <v>45.18072289156626</v>
+        <v>43.614457831325296</v>
       </c>
       <c r="R15" s="3">
-        <v>22.048192771084338</v>
+        <v>20.662650602409645</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>104</v>
       </c>
       <c r="T15" s="3">
-        <v>-36.37</v>
+        <v>-37.75</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -3032,22 +3026,22 @@
         <v>6.092261904761904</v>
       </c>
       <c r="E16" s="3">
-        <v>28.8</v>
+        <v>28.81</v>
       </c>
       <c r="F16" s="3">
-        <v>-0.11202941850597757</v>
+        <v>-0.12389391270347115</v>
       </c>
       <c r="G16" s="3">
         <v>1.8</v>
       </c>
       <c r="H16" s="3">
-        <v>42.82</v>
+        <v>41.03</v>
       </c>
       <c r="I16" s="3">
-        <v>-5.4</v>
+        <v>-7.08</v>
       </c>
       <c r="J16" s="3">
-        <v>-0.02980886657616657</v>
+        <v>-0.034065623540480816</v>
       </c>
       <c r="K16" s="3" t="b">
         <v>0</v>
@@ -3056,28 +3050,28 @@
         <v>27</v>
       </c>
       <c r="M16" s="3">
-        <v>-0.07685239127601773</v>
+        <v>-0.09556006725576449</v>
       </c>
       <c r="N16" s="3">
-        <v>-2.2131107238567966</v>
+        <v>-4.9392760446131145</v>
       </c>
       <c r="O16" s="3">
-        <v>30.120481927710845</v>
+        <v>33.734939759036145</v>
       </c>
       <c r="P16" s="3">
         <v>40.1905830435425</v>
       </c>
       <c r="Q16" s="3">
-        <v>28.55421686746988</v>
+        <v>26.626506024096386</v>
       </c>
       <c r="R16" s="3">
-        <v>19.036144578313255</v>
+        <v>19.879518072289155</v>
       </c>
       <c r="S16" s="3" t="s">
         <v>105</v>
       </c>
       <c r="T16" s="3">
-        <v>-24.2</v>
+        <v>-23.35</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -3094,22 +3088,22 @@
         <v>6.40546218487395</v>
       </c>
       <c r="E17" s="3">
-        <v>-1.43</v>
+        <v>-1.42</v>
       </c>
       <c r="F17" s="3">
-        <v>-0.03110062954274151</v>
+        <v>-0.04377505168642326</v>
       </c>
       <c r="G17" s="3">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="H17" s="3">
-        <v>40.7</v>
+        <v>39.09</v>
       </c>
       <c r="I17" s="3">
-        <v>-1.9</v>
+        <v>-3.1</v>
       </c>
       <c r="J17" s="3">
-        <v>-0.00021242702639545717</v>
+        <v>-0.0027585473256991613</v>
       </c>
       <c r="K17" s="3" t="b">
         <v>0</v>
@@ -3118,28 +3112,28 @@
         <v>31</v>
       </c>
       <c r="M17" s="3">
-        <v>0.0023175463257203432</v>
+        <v>-0.0165037254430056</v>
       </c>
       <c r="N17" s="3">
-        <v>5.7038830363170145</v>
+        <v>2.966358136662765</v>
       </c>
       <c r="O17" s="3">
-        <v>40.963855421686745</v>
+        <v>43.373493975903614</v>
       </c>
       <c r="P17" s="3">
         <v>24.80206596461608</v>
       </c>
       <c r="Q17" s="3">
-        <v>34.81927710843373</v>
+        <v>33.25301204819277</v>
       </c>
       <c r="R17" s="3">
-        <v>28.31325301204819</v>
+        <v>28.67469879518072</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>99</v>
       </c>
       <c r="T17" s="3">
-        <v>-4.86</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -3156,22 +3150,22 @@
         <v>730.8947368421053</v>
       </c>
       <c r="E18" s="3">
-        <v>10.85</v>
+        <v>11.06</v>
       </c>
       <c r="F18" s="3">
-        <v>-0.4380561042540274</v>
+        <v>-0.4266853319927678</v>
       </c>
       <c r="G18" s="3">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="H18" s="3">
-        <v>32.45</v>
+        <v>32.17</v>
       </c>
       <c r="I18" s="3">
-        <v>-32.25</v>
+        <v>-32.62</v>
       </c>
       <c r="J18" s="3">
-        <v>-0.05501292024424782</v>
+        <v>-0.05926794055986035</v>
       </c>
       <c r="K18" s="3" t="b">
         <v>0</v>
@@ -3180,19 +3174,19 @@
         <v>31</v>
       </c>
       <c r="M18" s="3">
-        <v>-0.43409868869065693</v>
+        <v>-0.4231436013118045</v>
       </c>
       <c r="N18" s="3">
-        <v>-37.937740465320715</v>
+        <v>-37.69762945021712</v>
       </c>
       <c r="O18" s="3">
         <v>1.2048192771084338</v>
       </c>
       <c r="P18" s="3">
-        <v>48.045600544184595</v>
+        <v>48.6563520729564</v>
       </c>
       <c r="Q18" s="3">
-        <v>40.48192771084337</v>
+        <v>40.602409638554214</v>
       </c>
       <c r="R18" s="3">
         <v>24.397590361445783</v>
@@ -3221,19 +3215,19 @@
         <v>3.12</v>
       </c>
       <c r="F19" s="2">
-        <v>0.09394464766379086</v>
+        <v>0.0716753957715537</v>
       </c>
       <c r="G19" s="2">
         <v>0.1</v>
       </c>
       <c r="H19" s="2">
-        <v>51.35</v>
+        <v>51.42</v>
       </c>
       <c r="I19" s="2">
-        <v>12.37</v>
+        <v>12.27</v>
       </c>
       <c r="J19" s="2">
-        <v>0.0032331451222560735</v>
+        <v>0.0015510400889843102</v>
       </c>
       <c r="K19" s="2" t="b">
         <v>0</v>
@@ -3242,28 +3236,28 @@
         <v>-58</v>
       </c>
       <c r="M19" s="2">
-        <v>0.05437049203008604</v>
+        <v>0.039799819642883705</v>
       </c>
       <c r="N19" s="2">
-        <v>10.909177606753586</v>
+        <v>8.59671264525171</v>
       </c>
       <c r="O19" s="2">
-        <v>60.24096385542169</v>
+        <v>59.036144578313255</v>
       </c>
       <c r="P19" s="2">
         <v>11.392700631623551</v>
       </c>
       <c r="Q19" s="2">
-        <v>58.674698795180724</v>
+        <v>59.39759036144578</v>
       </c>
       <c r="R19" s="2">
-        <v>51.68674698795181</v>
+        <v>51.32530120481928</v>
       </c>
       <c r="S19" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T19" s="2">
-        <v>3.27</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -3280,22 +3274,22 @@
         <v>-0.11030303030303032</v>
       </c>
       <c r="E20" s="2">
-        <v>-5.87</v>
+        <v>-5.68</v>
       </c>
       <c r="F20" s="2">
-        <v>0.20933926986055534</v>
+        <v>0.2142450295217468</v>
       </c>
       <c r="G20" s="2">
         <v>1.07</v>
       </c>
       <c r="H20" s="2">
-        <v>51.32</v>
+        <v>51.79</v>
       </c>
       <c r="I20" s="2">
-        <v>21.68</v>
+        <v>21.76</v>
       </c>
       <c r="J20" s="2">
-        <v>0.025990026683256926</v>
+        <v>0.02369231525888492</v>
       </c>
       <c r="K20" s="2" t="b">
         <v>0</v>
@@ -3304,10 +3298,10 @@
         <v>9</v>
       </c>
       <c r="M20" s="2">
-        <v>0.21241725974317682</v>
+        <v>0.21672424099842114</v>
       </c>
       <c r="N20" s="2">
-        <v>26.713854378062663</v>
+        <v>26.28915478080544</v>
       </c>
       <c r="O20" s="2">
         <v>83.13253012048193</v>
@@ -3316,7 +3310,7 @@
         <v>20.924527727345563</v>
       </c>
       <c r="Q20" s="2">
-        <v>61.20481927710843</v>
+        <v>62.168674698795186</v>
       </c>
       <c r="R20" s="2">
         <v>54.39759036144578</v>
@@ -3342,52 +3336,52 @@
         <v>12.821782178217823</v>
       </c>
       <c r="E21" s="3">
-        <v>-3.44</v>
+        <v>-3.45</v>
       </c>
       <c r="F21" s="3">
-        <v>-0.3530928170441423</v>
+        <v>-0.40637474862507716</v>
       </c>
       <c r="G21" s="3">
         <v>1.62</v>
       </c>
       <c r="H21" s="3">
-        <v>44.96</v>
+        <v>41.43</v>
       </c>
       <c r="I21" s="3">
-        <v>-9.88</v>
+        <v>-12.98</v>
       </c>
       <c r="J21" s="3">
-        <v>-0.02700477285862282</v>
+        <v>-0.026655232596393102</v>
       </c>
       <c r="K21" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" s="3">
         <v>55</v>
       </c>
       <c r="M21" s="3">
-        <v>-0.3258306209409234</v>
+        <v>-0.38441601840310446</v>
       </c>
       <c r="N21" s="3">
-        <v>-27.11093369034736</v>
+        <v>-33.82487115934712</v>
       </c>
       <c r="O21" s="3">
-        <v>6.024096385542169</v>
+        <v>3.614457831325301</v>
       </c>
       <c r="P21" s="3">
         <v>51.51389629888408</v>
       </c>
       <c r="Q21" s="3">
-        <v>42.5301204819277</v>
+        <v>40.120481927710834</v>
       </c>
       <c r="R21" s="3">
-        <v>21.626506024096386</v>
+        <v>20.903614457831324</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T21" s="3">
-        <v>-29.59</v>
+        <v>-30.32</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -3404,52 +3398,52 @@
         <v>0.7641509433962265</v>
       </c>
       <c r="E22" s="1">
-        <v>-0.22</v>
+        <v>-0.24</v>
       </c>
       <c r="F22" s="1">
-        <v>-0.054361555218965185</v>
+        <v>-0.08697293784029955</v>
       </c>
       <c r="G22" s="1">
         <v>1.38</v>
       </c>
       <c r="H22" s="1">
-        <v>34.93</v>
+        <v>33.8</v>
       </c>
       <c r="I22" s="1">
-        <v>0.73</v>
+        <v>-0.04</v>
       </c>
       <c r="J22" s="1">
-        <v>-0.01107803181961188</v>
+        <v>-0.012153134656444237</v>
       </c>
       <c r="K22" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L22" s="1">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M22" s="1">
-        <v>-0.03765246728473426</v>
+        <v>-0.07351436125263888</v>
       </c>
       <c r="N22" s="1">
-        <v>1.7068816752715494</v>
+        <v>-2.734705444300561</v>
       </c>
       <c r="O22" s="1">
-        <v>34.93975903614458</v>
+        <v>37.34939759036144</v>
       </c>
       <c r="P22" s="1">
-        <v>14.970360196599103</v>
+        <v>15.098892338880725</v>
       </c>
       <c r="Q22" s="1">
-        <v>43.6144578313253</v>
+        <v>43.012048192771076</v>
       </c>
       <c r="R22" s="1">
-        <v>38.855421686746986</v>
+        <v>39.45783132530121</v>
       </c>
       <c r="S22" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T22" s="1">
-        <v>-14.25</v>
+        <v>-13.65</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -3466,52 +3460,52 @@
         <v>-0.7145009416195857</v>
       </c>
       <c r="E23" s="2">
-        <v>0.08</v>
+        <v>0.07</v>
       </c>
       <c r="F23" s="2">
-        <v>0.06503541877680424</v>
+        <v>0.08678413084281295</v>
       </c>
       <c r="G23" s="2">
         <v>1.2</v>
       </c>
       <c r="H23" s="2">
-        <v>66.38</v>
+        <v>63.36</v>
       </c>
       <c r="I23" s="2">
-        <v>3.44</v>
+        <v>2.57</v>
       </c>
       <c r="J23" s="2">
-        <v>0.01222086159053441</v>
+        <v>0.011596708144805314</v>
       </c>
       <c r="K23" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L23" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M23" s="2">
-        <v>0.07382967558429421</v>
+        <v>0.09386759220473961</v>
       </c>
       <c r="N23" s="2">
-        <v>12.855095962174406</v>
+        <v>14.003489901437288</v>
       </c>
       <c r="O23" s="2">
-        <v>66.26506024096386</v>
+        <v>69.87951807228916</v>
       </c>
       <c r="P23" s="2">
         <v>21.71519296301999</v>
       </c>
       <c r="Q23" s="2">
-        <v>62.048192771084345</v>
+        <v>60.96385542168675</v>
       </c>
       <c r="R23" s="2">
-        <v>50.66265060240964</v>
+        <v>51.506024096385545</v>
       </c>
       <c r="S23" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T23" s="2">
-        <v>14.87</v>
+        <v>15.71</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -3528,22 +3522,22 @@
         <v>2.6266844974796832</v>
       </c>
       <c r="E24" s="1">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="F24" s="1">
-        <v>-0.05408589314292456</v>
+        <v>-0.04784403608734464</v>
       </c>
       <c r="G24" s="1">
         <v>3.59</v>
       </c>
       <c r="H24" s="1">
-        <v>55.61</v>
+        <v>57.13</v>
       </c>
       <c r="I24" s="1">
-        <v>-6.99</v>
+        <v>-4.75</v>
       </c>
       <c r="J24" s="1">
-        <v>0.04815934157803873</v>
+        <v>0.04512058415482685</v>
       </c>
       <c r="K24" s="1" t="b">
         <v>0</v>
@@ -3552,28 +3546,28 @@
         <v>-68</v>
       </c>
       <c r="M24" s="1">
-        <v>0.05979973251407045</v>
+        <v>0.043886788549605704</v>
       </c>
       <c r="N24" s="1">
-        <v>11.452101655152024</v>
+        <v>9.005409535923906</v>
       </c>
       <c r="O24" s="1">
-        <v>62.65060240963856</v>
+        <v>60.24096385542169</v>
       </c>
       <c r="P24" s="1">
         <v>57.99224429263358</v>
       </c>
       <c r="Q24" s="1">
-        <v>45.66265060240963</v>
+        <v>46.38554216867469</v>
       </c>
       <c r="R24" s="1">
-        <v>31.265060240963855</v>
+        <v>30.542168674698793</v>
       </c>
       <c r="S24" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T24" s="1">
-        <v>34.98</v>
+        <v>34.26</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -3587,55 +3581,55 @@
         <v>14.457831325301203</v>
       </c>
       <c r="D25" s="3">
-        <v>-7.491228070175438</v>
+        <v>-7.74561403508772</v>
       </c>
       <c r="E25" s="3">
-        <v>15.42</v>
+        <v>15.52</v>
       </c>
       <c r="F25" s="3">
-        <v>-0.01417186682645219</v>
+        <v>-0.194648330879535</v>
       </c>
       <c r="G25" s="3">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="H25" s="3">
-        <v>55.18</v>
+        <v>41.79</v>
       </c>
       <c r="I25" s="3">
-        <v>-20.65</v>
+        <v>-34.09</v>
       </c>
       <c r="J25" s="3">
-        <v>0.002148511361824104</v>
+        <v>-0.00021945580560811366</v>
       </c>
       <c r="K25" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="3">
         <v>33</v>
       </c>
       <c r="M25" s="3">
-        <v>0.04430994094335605</v>
+        <v>-0.1464807936184337</v>
       </c>
       <c r="N25" s="3">
-        <v>9.90312249808059</v>
+        <v>-10.031348680880035</v>
       </c>
       <c r="O25" s="3">
-        <v>56.62650602409639</v>
+        <v>20.481927710843372</v>
       </c>
       <c r="P25" s="3">
         <v>45.59139601172712</v>
       </c>
       <c r="Q25" s="3">
-        <v>24.819277108433738</v>
+        <v>18.072289156626507</v>
       </c>
       <c r="R25" s="3">
-        <v>17.7710843373494</v>
+        <v>6.80722891566265</v>
       </c>
       <c r="S25" s="3" t="s">
         <v>100</v>
       </c>
       <c r="T25" s="3">
-        <v>16.37</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -3652,34 +3646,34 @@
         <v>-0.7362637362637364</v>
       </c>
       <c r="E26" s="3">
-        <v>-0.61</v>
+        <v>-0.88</v>
       </c>
       <c r="F26" s="3">
-        <v>-0.5088343658325996</v>
+        <v>-0.4967305619190379</v>
       </c>
       <c r="G26" s="3">
         <v>3.38</v>
       </c>
       <c r="H26" s="3">
-        <v>41.24</v>
+        <v>38.93</v>
       </c>
       <c r="I26" s="3">
-        <v>-16.47</v>
+        <v>-18.96</v>
       </c>
       <c r="J26" s="3">
-        <v>-0.031932587392804836</v>
+        <v>-0.03219111090318241</v>
       </c>
       <c r="K26" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="3">
         <v>158</v>
       </c>
       <c r="M26" s="3">
-        <v>-0.40418270982346904</v>
+        <v>-0.4124373717121106</v>
       </c>
       <c r="N26" s="3">
-        <v>-34.94614257860192</v>
+        <v>-36.62700649024772</v>
       </c>
       <c r="O26" s="3">
         <v>2.4096385542168677</v>
@@ -3688,16 +3682,16 @@
         <v>55.61259899184437</v>
       </c>
       <c r="Q26" s="3">
-        <v>11.325301204819278</v>
+        <v>10.361445783132531</v>
       </c>
       <c r="R26" s="3">
-        <v>-3.2530120481927716</v>
+        <v>-3.1325301204819285</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>100</v>
       </c>
       <c r="T26" s="3">
-        <v>-32.09</v>
+        <v>-31.97</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -3717,19 +3711,19 @@
         <v>6.6</v>
       </c>
       <c r="F27" s="3">
-        <v>-0.4150842653075435</v>
+        <v>-0.42226771764467136</v>
       </c>
       <c r="G27" s="3">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="H27" s="3">
-        <v>31.62</v>
+        <v>31.87</v>
       </c>
       <c r="I27" s="3">
-        <v>-38.42</v>
+        <v>-38.58</v>
       </c>
       <c r="J27" s="3">
-        <v>-0.029180378232809837</v>
+        <v>-0.02946578800091318</v>
       </c>
       <c r="K27" s="3" t="b">
         <v>0</v>
@@ -3738,10 +3732,10 @@
         <v>7</v>
       </c>
       <c r="M27" s="3">
-        <v>-0.3425316466457513</v>
+        <v>-0.36347498834068004</v>
       </c>
       <c r="N27" s="3">
-        <v>-28.78103626083015</v>
+        <v>-31.73076815310467</v>
       </c>
       <c r="O27" s="3">
         <v>4.819277108433735</v>
@@ -3776,22 +3770,22 @@
         <v>8.555555555555555</v>
       </c>
       <c r="E28" s="1">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="F28" s="1">
-        <v>-0.0748885437001901</v>
+        <v>-0.07338028380418915</v>
       </c>
       <c r="G28" s="1">
         <v>3.26</v>
       </c>
       <c r="H28" s="1">
-        <v>44</v>
+        <v>44.96</v>
       </c>
       <c r="I28" s="1">
-        <v>-15.08</v>
+        <v>-14.38</v>
       </c>
       <c r="J28" s="1">
-        <v>0.015388628484536194</v>
+        <v>0.01516221309373249</v>
       </c>
       <c r="K28" s="1" t="b">
         <v>0</v>
@@ -3800,10 +3794,10 @@
         <v>3</v>
       </c>
       <c r="M28" s="1">
-        <v>0.024486558224446453</v>
+        <v>0.006662829585582175</v>
       </c>
       <c r="N28" s="1">
-        <v>7.920784226189633</v>
+        <v>5.283013639521558</v>
       </c>
       <c r="O28" s="1">
         <v>49.39759036144578</v>
@@ -3812,16 +3806,16 @@
         <v>35.08771990976345</v>
       </c>
       <c r="Q28" s="1">
-        <v>45.66265060240963</v>
+        <v>46.26506024096385</v>
       </c>
       <c r="R28" s="1">
-        <v>36.084337349397586</v>
+        <v>36.325301204819276</v>
       </c>
       <c r="S28" s="1" t="s">
         <v>108</v>
       </c>
       <c r="T28" s="1">
-        <v>19.07</v>
+        <v>19.31</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -3838,22 +3832,22 @@
         <v>83.17021276595746</v>
       </c>
       <c r="E29" s="1">
-        <v>-4.8</v>
+        <v>-4.82</v>
       </c>
       <c r="F29" s="1">
-        <v>-0.02832738598789758</v>
+        <v>-0.05392597330072449</v>
       </c>
       <c r="G29" s="1">
         <v>2.32</v>
       </c>
       <c r="H29" s="1">
-        <v>44.32</v>
+        <v>43.13</v>
       </c>
       <c r="I29" s="1">
-        <v>-13.27</v>
+        <v>-13.83</v>
       </c>
       <c r="J29" s="1">
-        <v>0.0007511716917709449</v>
+        <v>-0.0018474164526615137</v>
       </c>
       <c r="K29" s="1" t="b">
         <v>0</v>
@@ -3862,28 +3856,28 @@
         <v>10</v>
       </c>
       <c r="M29" s="1">
-        <v>0.02971470894153616</v>
+        <v>-0.007175128312008505</v>
       </c>
       <c r="N29" s="1">
-        <v>8.443599297898594</v>
+        <v>3.8992178497624854</v>
       </c>
       <c r="O29" s="1">
-        <v>50.602409638554214</v>
+        <v>46.98795180722892</v>
       </c>
       <c r="P29" s="1">
         <v>21.89743824494191</v>
       </c>
       <c r="Q29" s="1">
-        <v>52.40963855421687</v>
+        <v>51.08433734939759</v>
       </c>
       <c r="R29" s="1">
-        <v>46.3855421686747</v>
+        <v>45.06024096385543</v>
       </c>
       <c r="S29" s="1" t="s">
         <v>107</v>
       </c>
       <c r="T29" s="1">
-        <v>6.14</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -3900,52 +3894,52 @@
         <v>226.42272727272726</v>
       </c>
       <c r="E30" s="1">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="F30" s="1">
-        <v>-0.08537007138463008</v>
+        <v>-0.10511192955128379</v>
       </c>
       <c r="G30" s="1">
         <v>1.24</v>
       </c>
       <c r="H30" s="1">
-        <v>35.91</v>
+        <v>44.71</v>
       </c>
       <c r="I30" s="1">
-        <v>-7.16</v>
+        <v>-4.8</v>
       </c>
       <c r="J30" s="1">
-        <v>-0.0038293676551343627</v>
+        <v>-0.003686087424677485</v>
       </c>
       <c r="K30" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L30" s="1">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M30" s="1">
-        <v>-0.07481696321564213</v>
+        <v>-0.09661177591697179</v>
       </c>
       <c r="N30" s="1">
-        <v>-2.0095679178192287</v>
+        <v>-5.044446910733848</v>
       </c>
       <c r="O30" s="1">
-        <v>31.32530120481928</v>
+        <v>32.53012048192771</v>
       </c>
       <c r="P30" s="1">
         <v>14.879468887608937</v>
       </c>
       <c r="Q30" s="1">
-        <v>52.04819277108433</v>
+        <v>56.626506024096386</v>
       </c>
       <c r="R30" s="1">
-        <v>45.78313253012048</v>
+        <v>46.506024096385545</v>
       </c>
       <c r="S30" s="1" t="s">
         <v>103</v>
       </c>
       <c r="T30" s="1">
-        <v>-2.69</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -3959,55 +3953,55 @@
         <v>68.67469879518072</v>
       </c>
       <c r="D31" s="1">
-        <v>7.403575989782886</v>
+        <v>7.35249042145594</v>
       </c>
       <c r="E31" s="1">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="F31" s="1">
-        <v>-0.10567539663580133</v>
+        <v>-0.12396969445810029</v>
       </c>
       <c r="G31" s="1">
         <v>1.47</v>
       </c>
       <c r="H31" s="1">
-        <v>41.4</v>
+        <v>36.58</v>
       </c>
       <c r="I31" s="1">
-        <v>-2.5</v>
+        <v>-5.32</v>
       </c>
       <c r="J31" s="1">
-        <v>-0.003503563660864547</v>
+        <v>-0.002593719779779743</v>
       </c>
       <c r="K31" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="1">
         <v>208</v>
       </c>
       <c r="M31" s="1">
-        <v>-0.08500889313819993</v>
+        <v>-0.10732356025757261</v>
       </c>
       <c r="N31" s="1">
-        <v>-3.028760910075008</v>
+        <v>-6.1156253447939335</v>
       </c>
       <c r="O31" s="1">
-        <v>28.915662650602407</v>
+        <v>27.710843373493976</v>
       </c>
       <c r="P31" s="1">
         <v>26.160269342004856</v>
       </c>
       <c r="Q31" s="1">
-        <v>53.493975903614455</v>
+        <v>51.92771084337348</v>
       </c>
       <c r="R31" s="1">
-        <v>39.75903614457831</v>
+        <v>40.12048192771084</v>
       </c>
       <c r="S31" s="1" t="s">
         <v>95</v>
       </c>
       <c r="T31" s="1">
-        <v>-8.29</v>
+        <v>-7.93</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -4027,49 +4021,49 @@
         <v>3.57</v>
       </c>
       <c r="F32" s="1">
-        <v>0.005854538131604567</v>
+        <v>-0.03624028571413286</v>
       </c>
       <c r="G32" s="1">
         <v>1.61</v>
       </c>
       <c r="H32" s="1">
-        <v>49.79</v>
+        <v>48.27</v>
       </c>
       <c r="I32" s="1">
-        <v>-1.6</v>
+        <v>-2.51</v>
       </c>
       <c r="J32" s="1">
-        <v>0.0007106434503142066</v>
+        <v>-0.0022256869683246927</v>
       </c>
       <c r="K32" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L32" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M32" s="1">
-        <v>0.032677021394448946</v>
+        <v>-0.014635728560256522</v>
       </c>
       <c r="N32" s="1">
-        <v>8.73983054318988</v>
+        <v>3.1531578249376753</v>
       </c>
       <c r="O32" s="1">
-        <v>51.80722891566265</v>
+        <v>45.78313253012048</v>
       </c>
       <c r="P32" s="1">
         <v>27.28297753683016</v>
       </c>
       <c r="Q32" s="1">
-        <v>43.01204819277108</v>
+        <v>41.9277108433735</v>
       </c>
       <c r="R32" s="1">
-        <v>34.27710843373494</v>
+        <v>32.22891566265061</v>
       </c>
       <c r="S32" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T32" s="1">
-        <v>2.39</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -4086,37 +4080,37 @@
         <v>0.06016713091922016</v>
       </c>
       <c r="E33" s="2">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="F33" s="2">
-        <v>0.1801608823919831</v>
+        <v>0.22003018865260257</v>
       </c>
       <c r="G33" s="2">
         <v>1.1</v>
       </c>
       <c r="H33" s="2">
-        <v>55.02</v>
+        <v>54.37</v>
       </c>
       <c r="I33" s="2">
-        <v>14.22</v>
+        <v>14.11</v>
       </c>
       <c r="J33" s="2">
-        <v>0.029885826146028093</v>
+        <v>0.028180009587628892</v>
       </c>
       <c r="K33" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L33" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M33" s="2">
-        <v>0.1845580107957281</v>
+        <v>0.2235719193335659</v>
       </c>
       <c r="N33" s="2">
-        <v>23.927929483317783</v>
+        <v>26.973922614319935</v>
       </c>
       <c r="O33" s="2">
-        <v>79.51807228915662</v>
+        <v>85.54216867469879</v>
       </c>
       <c r="P33" s="2">
         <v>23.38443607454554</v>
@@ -4125,13 +4119,13 @@
         <v>68.91566265060241</v>
       </c>
       <c r="R33" s="2">
-        <v>57.710843373493965</v>
+        <v>59.63855421686747</v>
       </c>
       <c r="S33" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T33" s="2">
-        <v>21.92</v>
+        <v>23.85</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -4145,55 +4139,55 @@
         <v>92.7710843373494</v>
       </c>
       <c r="D34" s="1">
-        <v>-2.3370165745856353</v>
+        <v>-2.3350075339025613</v>
       </c>
       <c r="E34" s="1">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="F34" s="1">
-        <v>-0.13112149004969065</v>
+        <v>-0.10746633153345066</v>
       </c>
       <c r="G34" s="1">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="H34" s="1">
-        <v>41.29</v>
+        <v>45.16</v>
       </c>
       <c r="I34" s="1">
-        <v>-1.19</v>
+        <v>-0.15</v>
       </c>
       <c r="J34" s="1">
-        <v>-0.0031462691295237703</v>
+        <v>-0.004288241982899922</v>
       </c>
       <c r="K34" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L34" s="1">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M34" s="1">
-        <v>-0.12144780756145168</v>
+        <v>-0.10002869710342766</v>
       </c>
       <c r="N34" s="1">
-        <v>-6.672652352400182</v>
+        <v>-5.386139029379429</v>
       </c>
       <c r="O34" s="1">
-        <v>20.481927710843372</v>
+        <v>30.120481927710845</v>
       </c>
       <c r="P34" s="1">
         <v>21.09433056126816</v>
       </c>
       <c r="Q34" s="1">
-        <v>44.69879518072288</v>
+        <v>45.542168674698786</v>
       </c>
       <c r="R34" s="1">
-        <v>31.02409638554217</v>
+        <v>33.674698795180724</v>
       </c>
       <c r="S34" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T34" s="1">
-        <v>-15.81</v>
+        <v>-13.15</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -4207,25 +4201,25 @@
         <v>86.74698795180723</v>
       </c>
       <c r="D35" s="1">
-        <v>-0.44387755102040816</v>
+        <v>-0.45464852607709755</v>
       </c>
       <c r="E35" s="1">
-        <v>-0.32</v>
+        <v>-0.33</v>
       </c>
       <c r="F35" s="1">
-        <v>-0.04404539582641072</v>
+        <v>-0.046510076393472474</v>
       </c>
       <c r="G35" s="1">
-        <v>0.94</v>
+        <v>0.95</v>
       </c>
       <c r="H35" s="1">
-        <v>37.16</v>
+        <v>39.22</v>
       </c>
       <c r="I35" s="1">
-        <v>-12.71</v>
+        <v>-12.41</v>
       </c>
       <c r="J35" s="1">
-        <v>0.01212768145531331</v>
+        <v>0.008957876535317839</v>
       </c>
       <c r="K35" s="1" t="b">
         <v>0</v>
@@ -4234,90 +4228,90 @@
         <v>-56</v>
       </c>
       <c r="M35" s="1">
-        <v>-0.04668367286865771</v>
+        <v>-0.04828094173395414</v>
       </c>
       <c r="N35" s="1">
-        <v>0.803761116879216</v>
+        <v>-0.21136349243207872</v>
       </c>
       <c r="O35" s="1">
-        <v>33.734939759036145</v>
+        <v>39.75903614457831</v>
       </c>
       <c r="P35" s="1">
         <v>23.996351232323672</v>
       </c>
       <c r="Q35" s="1">
-        <v>48.674698795180724</v>
+        <v>48.433734939759034</v>
       </c>
       <c r="R35" s="1">
-        <v>38.433734939759034</v>
+        <v>40.12048192771084</v>
       </c>
       <c r="S35" s="1" t="s">
         <v>109</v>
       </c>
       <c r="T35" s="1">
-        <v>15.93</v>
+        <v>17.62</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B36" s="1">
         <v>10.27</v>
       </c>
-      <c r="C36" s="2">
+      <c r="C36" s="1">
         <v>78.3132530120482</v>
       </c>
-      <c r="D36" s="2">
+      <c r="D36" s="1">
         <v>-0.01265822784810117</v>
       </c>
-      <c r="E36" s="2">
-        <v>-1.28</v>
-      </c>
-      <c r="F36" s="2">
-        <v>0.12067298333965898</v>
-      </c>
-      <c r="G36" s="2">
+      <c r="E36" s="1">
+        <v>-1.31</v>
+      </c>
+      <c r="F36" s="1">
+        <v>0.10412588696847526</v>
+      </c>
+      <c r="G36" s="1">
         <v>1.11</v>
       </c>
-      <c r="H36" s="2">
-        <v>54.7</v>
-      </c>
-      <c r="I36" s="2">
-        <v>-3.24</v>
-      </c>
-      <c r="J36" s="2">
-        <v>0.01164454478056378</v>
-      </c>
-      <c r="K36" s="2" t="b">
+      <c r="H36" s="1">
+        <v>49.49</v>
+      </c>
+      <c r="I36" s="1">
+        <v>-5.22</v>
+      </c>
+      <c r="J36" s="1">
+        <v>0.013974834602639702</v>
+      </c>
+      <c r="K36" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L36" s="2">
+      <c r="L36" s="1">
         <v>-22</v>
       </c>
-      <c r="M36" s="2">
-        <v>0.12550982458377846</v>
-      </c>
-      <c r="N36" s="2">
-        <v>18.02311086212283</v>
-      </c>
-      <c r="O36" s="2">
-        <v>74.69879518072288</v>
-      </c>
-      <c r="P36" s="2">
+      <c r="M36" s="1">
+        <v>0.10802179071753493</v>
+      </c>
+      <c r="N36" s="1">
+        <v>15.41890975271683</v>
+      </c>
+      <c r="O36" s="1">
+        <v>72.28915662650603</v>
+      </c>
+      <c r="P36" s="1">
         <v>26.730280409441182</v>
       </c>
-      <c r="Q36" s="2">
-        <v>56.50602409638554</v>
-      </c>
-      <c r="R36" s="2">
-        <v>50.06024096385542</v>
-      </c>
-      <c r="S36" s="2" t="s">
+      <c r="Q36" s="1">
+        <v>54.819277108433745</v>
+      </c>
+      <c r="R36" s="1">
+        <v>49.75903614457832</v>
+      </c>
+      <c r="S36" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="T36" s="2">
-        <v>23.11</v>
+      <c r="T36" s="1">
+        <v>22.81</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -4334,22 +4328,22 @@
         <v>0.4196597353497164</v>
       </c>
       <c r="E37" s="2">
-        <v>-3.19</v>
+        <v>-3.25</v>
       </c>
       <c r="F37" s="2">
-        <v>0.24279477544856418</v>
+        <v>0.2465346405499334</v>
       </c>
       <c r="G37" s="2">
         <v>1.28</v>
       </c>
       <c r="H37" s="2">
-        <v>41.26</v>
+        <v>43.06</v>
       </c>
       <c r="I37" s="2">
-        <v>4.69</v>
+        <v>5.88</v>
       </c>
       <c r="J37" s="2">
-        <v>0.01972282170033136</v>
+        <v>0.017906991362600627</v>
       </c>
       <c r="K37" s="2" t="b">
         <v>0</v>
@@ -4358,28 +4352,28 @@
         <v>-105</v>
       </c>
       <c r="M37" s="2">
-        <v>0.2551067349790501</v>
+        <v>0.25645148645663074</v>
       </c>
       <c r="N37" s="2">
-        <v>30.98280190164998</v>
+        <v>30.261879326626413</v>
       </c>
       <c r="O37" s="2">
-        <v>90.36144578313254</v>
+        <v>91.56626506024097</v>
       </c>
       <c r="P37" s="2">
         <v>20.90944133883571</v>
       </c>
       <c r="Q37" s="2">
-        <v>53.85542168674699</v>
+        <v>54.57831325301205</v>
       </c>
       <c r="R37" s="2">
-        <v>56.08433734939759</v>
+        <v>56.44578313253012</v>
       </c>
       <c r="S37" s="2" t="s">
         <v>103</v>
       </c>
       <c r="T37" s="2">
-        <v>26.27</v>
+        <v>26.63</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -4393,55 +4387,55 @@
         <v>31.32530120481928</v>
       </c>
       <c r="D38" s="2">
-        <v>683.25</v>
+        <v>686</v>
       </c>
       <c r="E38" s="2">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="F38" s="2">
-        <v>0.22494210612947918</v>
+        <v>0.1415277996894257</v>
       </c>
       <c r="G38" s="2">
         <v>1.23</v>
       </c>
       <c r="H38" s="2">
-        <v>51.1</v>
+        <v>54.73</v>
       </c>
       <c r="I38" s="2">
-        <v>45.34</v>
+        <v>49.41</v>
       </c>
       <c r="J38" s="2">
-        <v>0.01658680920959054</v>
+        <v>0.013192389071912046</v>
       </c>
       <c r="K38" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L38" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M38" s="2">
-        <v>0.23505550145809262</v>
+        <v>0.14967378025564138</v>
       </c>
       <c r="N38" s="2">
-        <v>28.97767854955425</v>
+        <v>19.584108706527466</v>
       </c>
       <c r="O38" s="2">
-        <v>87.95180722891565</v>
+        <v>79.51807228915662</v>
       </c>
       <c r="P38" s="2">
         <v>17.802507034008837</v>
       </c>
       <c r="Q38" s="2">
-        <v>68.67469879518072</v>
+        <v>70.36144578313252</v>
       </c>
       <c r="R38" s="2">
-        <v>63.01204819277108</v>
+        <v>60</v>
       </c>
       <c r="S38" s="2" t="s">
         <v>98</v>
       </c>
       <c r="T38" s="2">
-        <v>-1.07</v>
+        <v>-4.09</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -4458,22 +4452,22 @@
         <v>38.714285714285715</v>
       </c>
       <c r="E39" s="1">
-        <v>-1.33</v>
+        <v>-1.29</v>
       </c>
       <c r="F39" s="1">
-        <v>0.08747649440605555</v>
+        <v>0.06082796966166876</v>
       </c>
       <c r="G39" s="1">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="H39" s="1">
-        <v>40.82</v>
+        <v>44.04</v>
       </c>
       <c r="I39" s="1">
-        <v>-3.78</v>
+        <v>-2.59</v>
       </c>
       <c r="J39" s="1">
-        <v>-0.0013233072451686672</v>
+        <v>-0.0027080927066651856</v>
       </c>
       <c r="K39" s="1" t="b">
         <v>0</v>
@@ -4482,28 +4476,28 @@
         <v>-1</v>
       </c>
       <c r="M39" s="1">
-        <v>0.09319276133092402</v>
+        <v>0.06507804647882476</v>
       </c>
       <c r="N39" s="1">
-        <v>14.791404536837389</v>
+        <v>11.124535328845798</v>
       </c>
       <c r="O39" s="1">
-        <v>71.08433734939759</v>
+        <v>62.65060240963856</v>
       </c>
       <c r="P39" s="1">
         <v>30.28933322215756</v>
       </c>
       <c r="Q39" s="1">
-        <v>45.42168674698796</v>
+        <v>47.34939759036144</v>
       </c>
       <c r="R39" s="1">
-        <v>45.54216867469879</v>
+        <v>43.13253012048193</v>
       </c>
       <c r="S39" s="1" t="s">
         <v>108</v>
       </c>
       <c r="T39" s="1">
-        <v>19.75</v>
+        <v>17.34</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -4520,22 +4514,22 @@
         <v>10.77984665936473</v>
       </c>
       <c r="E40" s="1">
-        <v>3.1</v>
+        <v>3.93</v>
       </c>
       <c r="F40" s="1">
-        <v>0.2561147014726967</v>
+        <v>0.24190292855170817</v>
       </c>
       <c r="G40" s="1">
-        <v>0.71</v>
+        <v>0.69</v>
       </c>
       <c r="H40" s="1">
-        <v>62.04</v>
+        <v>64.36</v>
       </c>
       <c r="I40" s="1">
-        <v>-0.39</v>
+        <v>2.85</v>
       </c>
       <c r="J40" s="1">
-        <v>0.04692431854309367</v>
+        <v>0.04425563961017143</v>
       </c>
       <c r="K40" s="1" t="b">
         <v>0</v>
@@ -4544,10 +4538,10 @@
         <v>-21</v>
       </c>
       <c r="M40" s="1">
-        <v>0.24336302910183627</v>
+        <v>0.23092356344072185</v>
       </c>
       <c r="N40" s="1">
-        <v>29.808431313928608</v>
+        <v>27.70908702503551</v>
       </c>
       <c r="O40" s="1">
         <v>89.1566265060241</v>
@@ -4556,7 +4550,7 @@
         <v>51.940889187924654</v>
       </c>
       <c r="Q40" s="1">
-        <v>54.216867469879524</v>
+        <v>55.18072289156627</v>
       </c>
       <c r="R40" s="1">
         <v>44.81927710843374</v>
@@ -4582,22 +4576,22 @@
         <v>1.5533199195171026</v>
       </c>
       <c r="E41" s="3">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F41" s="3">
-        <v>-0.16570583029827854</v>
+        <v>-0.19243583208496018</v>
       </c>
       <c r="G41" s="3">
         <v>1.21</v>
       </c>
       <c r="H41" s="3">
-        <v>42.54</v>
+        <v>41.16</v>
       </c>
       <c r="I41" s="3">
-        <v>-10.79</v>
+        <v>-11.48</v>
       </c>
       <c r="J41" s="3">
-        <v>0.0006157365050628964</v>
+        <v>-0.003826616292049831</v>
       </c>
       <c r="K41" s="3" t="b">
         <v>0</v>
@@ -4606,10 +4600,10 @@
         <v>3</v>
       </c>
       <c r="M41" s="3">
-        <v>-0.15647186065041407</v>
+        <v>-0.1849981976549372</v>
       </c>
       <c r="N41" s="3">
-        <v>-10.175057661296423</v>
+        <v>-13.883089084530386</v>
       </c>
       <c r="O41" s="3">
         <v>14.457831325301203</v>
@@ -4618,78 +4612,78 @@
         <v>30.769232468942608</v>
       </c>
       <c r="Q41" s="3">
-        <v>29.397590361445783</v>
+        <v>26.867469879518072</v>
       </c>
       <c r="R41" s="3">
-        <v>15.060240963855426</v>
+        <v>14.09638554216868</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>104</v>
       </c>
       <c r="T41" s="3">
-        <v>-21.59</v>
+        <v>-22.55</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="3">
+      <c r="B42" s="1">
         <v>3.33</v>
       </c>
-      <c r="C42" s="3">
+      <c r="C42" s="1">
         <v>51.80722891566265</v>
       </c>
-      <c r="D42" s="3">
+      <c r="D42" s="1">
         <v>1.2342342342342343</v>
       </c>
-      <c r="E42" s="3">
+      <c r="E42" s="1">
         <v>4.37</v>
       </c>
-      <c r="F42" s="3">
-        <v>-0.10306335848358113</v>
-      </c>
-      <c r="G42" s="3">
+      <c r="F42" s="1">
+        <v>-0.09997228985541207</v>
+      </c>
+      <c r="G42" s="1">
         <v>0.31</v>
       </c>
-      <c r="H42" s="3">
-        <v>34.25</v>
-      </c>
-      <c r="I42" s="3">
-        <v>-7.86</v>
-      </c>
-      <c r="J42" s="3">
-        <v>-0.012419728400992461</v>
-      </c>
-      <c r="K42" s="3" t="b">
+      <c r="H42" s="1">
+        <v>36.76</v>
+      </c>
+      <c r="I42" s="1">
+        <v>-7.8</v>
+      </c>
+      <c r="J42" s="1">
+        <v>-0.012686672734253735</v>
+      </c>
+      <c r="K42" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L42" s="3">
+      <c r="L42" s="1">
         <v>15</v>
       </c>
-      <c r="M42" s="3">
-        <v>-0.1334035444694215</v>
-      </c>
-      <c r="N42" s="3">
-        <v>-7.868226043197163</v>
-      </c>
-      <c r="O42" s="3">
-        <v>16.867469879518072</v>
-      </c>
-      <c r="P42" s="3">
-        <v>14.133467943136715</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>36.14457831325301</v>
-      </c>
-      <c r="R42" s="3">
-        <v>29.578313253012045</v>
-      </c>
-      <c r="S42" s="3" t="s">
+      <c r="M42" s="1">
+        <v>-0.12441023155405906</v>
+      </c>
+      <c r="N42" s="1">
+        <v>-7.824292474442575</v>
+      </c>
+      <c r="O42" s="1">
+        <v>25.301204819277107</v>
+      </c>
+      <c r="P42" s="1">
+        <v>14.795072191248144</v>
+      </c>
+      <c r="Q42" s="1">
+        <v>36.024096385542165</v>
+      </c>
+      <c r="R42" s="1">
+        <v>31.746987951807228</v>
+      </c>
+      <c r="S42" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="T42" s="3">
-        <v>-5.91</v>
+      <c r="T42" s="1">
+        <v>-3.74</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -4706,22 +4700,22 @@
         <v>149.86666666666667</v>
       </c>
       <c r="E43" s="2">
-        <v>8.94</v>
+        <v>8.86</v>
       </c>
       <c r="F43" s="2">
-        <v>0.10758482492927159</v>
+        <v>0.13114534829930147</v>
       </c>
       <c r="G43" s="2">
         <v>1.35</v>
       </c>
       <c r="H43" s="2">
-        <v>48.14</v>
+        <v>50.35</v>
       </c>
       <c r="I43" s="2">
-        <v>14.07</v>
+        <v>15.72</v>
       </c>
       <c r="J43" s="2">
-        <v>0.021632940492551427</v>
+        <v>0.019776415536176463</v>
       </c>
       <c r="K43" s="2" t="b">
         <v>1</v>
@@ -4730,28 +4724,28 @@
         <v>17</v>
       </c>
       <c r="M43" s="2">
-        <v>0.12297477434237902</v>
+        <v>0.14354140568267315</v>
       </c>
       <c r="N43" s="2">
-        <v>17.769605837982887</v>
+        <v>18.970871249230644</v>
       </c>
       <c r="O43" s="2">
-        <v>73.49397590361446</v>
+        <v>78.3132530120482</v>
       </c>
       <c r="P43" s="2">
         <v>24.82490242340647</v>
       </c>
       <c r="Q43" s="2">
-        <v>66.98795180722891</v>
+        <v>67.59036144578315</v>
       </c>
       <c r="R43" s="2">
-        <v>56.144578313253014</v>
+        <v>57.349397590361455</v>
       </c>
       <c r="S43" s="2" t="s">
         <v>111</v>
       </c>
       <c r="T43" s="2">
-        <v>3.77</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -4765,55 +4759,55 @@
         <v>42.168674698795186</v>
       </c>
       <c r="D44" s="2">
-        <v>19.135135135135137</v>
+        <v>19.14189189189189</v>
       </c>
       <c r="E44" s="2">
-        <v>-0.69</v>
+        <v>-0.68</v>
       </c>
       <c r="F44" s="2">
-        <v>0.04322128190496813</v>
+        <v>0.061585115155112516</v>
       </c>
       <c r="G44" s="2">
         <v>2.64</v>
       </c>
       <c r="H44" s="2">
-        <v>36.77</v>
+        <v>40.7</v>
       </c>
       <c r="I44" s="2">
-        <v>-3.42</v>
+        <v>-0.69</v>
       </c>
       <c r="J44" s="2">
-        <v>0.016172012552438247</v>
+        <v>0.012416747713801086</v>
       </c>
       <c r="K44" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L44" s="2">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="M44" s="2">
-        <v>0.11533418772638582</v>
+        <v>0.11966949832291118</v>
       </c>
       <c r="N44" s="2">
-        <v>17.00554717638357</v>
+        <v>16.583680513254443</v>
       </c>
       <c r="O44" s="2">
-        <v>72.28915662650603</v>
+        <v>75.90361445783132</v>
       </c>
       <c r="P44" s="2">
         <v>29.40653991657008</v>
       </c>
       <c r="Q44" s="2">
-        <v>54.93975903614458</v>
+        <v>56.26506024096386</v>
       </c>
       <c r="R44" s="2">
-        <v>52.71084337349398</v>
+        <v>53.6144578313253</v>
       </c>
       <c r="S44" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T44" s="2">
-        <v>17.89</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
@@ -4830,22 +4824,22 @@
         <v>-2.3531777956556716</v>
       </c>
       <c r="E45" s="1">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="F45" s="1">
-        <v>-0.016147019880989544</v>
+        <v>0.0011221198160171614</v>
       </c>
       <c r="G45" s="1">
         <v>1.45</v>
       </c>
       <c r="H45" s="1">
-        <v>43.62</v>
+        <v>46.22</v>
       </c>
       <c r="I45" s="1">
-        <v>5.12</v>
+        <v>5.84</v>
       </c>
       <c r="J45" s="1">
-        <v>0.00840259035101518</v>
+        <v>0.0076322629666575196</v>
       </c>
       <c r="K45" s="1" t="b">
         <v>0</v>
@@ -4854,152 +4848,152 @@
         <v>196</v>
       </c>
       <c r="M45" s="1">
-        <v>0.0036400579358628615</v>
+        <v>0.017059907880352165</v>
       </c>
       <c r="N45" s="1">
-        <v>5.836134197331276</v>
+        <v>6.322721468998552</v>
       </c>
       <c r="O45" s="1">
-        <v>43.373493975903614</v>
+        <v>55.42168674698795</v>
       </c>
       <c r="P45" s="1">
         <v>17.57882034058413</v>
       </c>
       <c r="Q45" s="1">
-        <v>47.71084337349397</v>
+        <v>47.46987951807229</v>
       </c>
       <c r="R45" s="1">
-        <v>37.95180722891566</v>
+        <v>41.325301204819276</v>
       </c>
       <c r="S45" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T45" s="1">
-        <v>-6.38</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B46" s="3">
         <v>-0.34</v>
       </c>
-      <c r="C46" s="1">
+      <c r="C46" s="3">
         <v>24.096385542168676</v>
       </c>
-      <c r="D46" s="1">
+      <c r="D46" s="3">
         <v>473.05882352941177</v>
       </c>
-      <c r="E46" s="1">
-        <v>6.45</v>
-      </c>
-      <c r="F46" s="1">
-        <v>-0.0920824693286085</v>
-      </c>
-      <c r="G46" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="H46" s="1">
-        <v>44.1</v>
-      </c>
-      <c r="I46" s="1">
-        <v>-21.57</v>
-      </c>
-      <c r="J46" s="1">
-        <v>-0.0022731283684411232</v>
-      </c>
-      <c r="K46" s="1" t="b">
+      <c r="E46" s="3">
+        <v>4.53</v>
+      </c>
+      <c r="F46" s="3">
+        <v>-0.2143311526386142</v>
+      </c>
+      <c r="G46" s="3">
+        <v>1.76</v>
+      </c>
+      <c r="H46" s="3">
+        <v>37.74</v>
+      </c>
+      <c r="I46" s="3">
+        <v>-26.97</v>
+      </c>
+      <c r="J46" s="3">
+        <v>-0.0031471632843369803</v>
+      </c>
+      <c r="K46" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L46" s="1">
+      <c r="L46" s="3">
         <v>17</v>
       </c>
-      <c r="M46" s="1">
-        <v>-0.05910400630052115</v>
-      </c>
-      <c r="N46" s="1">
-        <v>-0.43827222630713125</v>
-      </c>
-      <c r="O46" s="1">
-        <v>32.53012048192771</v>
-      </c>
-      <c r="P46" s="1">
+      <c r="M46" s="3">
+        <v>-0.18741399946329285</v>
+      </c>
+      <c r="N46" s="3">
+        <v>-14.124669265365952</v>
+      </c>
+      <c r="O46" s="3">
+        <v>13.253012048192772</v>
+      </c>
+      <c r="P46" s="3">
         <v>54.33673655574689</v>
       </c>
-      <c r="Q46" s="1">
-        <v>48.915662650602414</v>
-      </c>
-      <c r="R46" s="1">
-        <v>33.795180722891565</v>
-      </c>
-      <c r="S46" s="1" t="s">
+      <c r="Q46" s="3">
+        <v>45.66265060240964</v>
+      </c>
+      <c r="R46" s="3">
+        <v>28.012048192771083</v>
+      </c>
+      <c r="S46" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="T46" s="1">
-        <v>12.76</v>
+      <c r="T46" s="3">
+        <v>6.98</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B47" s="2">
+      <c r="B47" s="1">
         <v>8.67</v>
       </c>
-      <c r="C47" s="2">
+      <c r="C47" s="1">
         <v>74.69879518072288</v>
       </c>
-      <c r="D47" s="2">
+      <c r="D47" s="1">
         <v>-0.7716262975778546</v>
       </c>
-      <c r="E47" s="2">
-        <v>2.61</v>
-      </c>
-      <c r="F47" s="2">
-        <v>0.2916709433875051</v>
-      </c>
-      <c r="G47" s="2">
+      <c r="E47" s="1">
+        <v>2.59</v>
+      </c>
+      <c r="F47" s="1">
+        <v>0.20487221421397078</v>
+      </c>
+      <c r="G47" s="1">
         <v>1.41</v>
       </c>
-      <c r="H47" s="2">
-        <v>61.49</v>
-      </c>
-      <c r="I47" s="2">
-        <v>8.58</v>
-      </c>
-      <c r="J47" s="2">
-        <v>0.02104819069499104</v>
-      </c>
-      <c r="K47" s="2" t="b">
+      <c r="H47" s="1">
+        <v>63.38</v>
+      </c>
+      <c r="I47" s="1">
+        <v>9.7</v>
+      </c>
+      <c r="J47" s="1">
+        <v>0.021359255911393687</v>
+      </c>
+      <c r="K47" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L47" s="2">
+      <c r="L47" s="1">
         <v>-54</v>
       </c>
-      <c r="M47" s="2">
-        <v>0.3096991698428595</v>
-      </c>
-      <c r="N47" s="2">
-        <v>36.44204538803093</v>
-      </c>
-      <c r="O47" s="2">
-        <v>92.7710843373494</v>
-      </c>
-      <c r="P47" s="2">
+      <c r="M47" s="1">
+        <v>0.21939331000592044</v>
+      </c>
+      <c r="N47" s="1">
+        <v>26.556061681555377</v>
+      </c>
+      <c r="O47" s="1">
+        <v>84.33734939759037</v>
+      </c>
+      <c r="P47" s="1">
         <v>33.3731909304046</v>
       </c>
-      <c r="Q47" s="2">
-        <v>58.07228915662651</v>
-      </c>
-      <c r="R47" s="2">
-        <v>51.144578313253014</v>
-      </c>
-      <c r="S47" s="2" t="s">
+      <c r="Q47" s="1">
+        <v>59.1566265060241</v>
+      </c>
+      <c r="R47" s="1">
+        <v>48.73493975903615</v>
+      </c>
+      <c r="S47" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="T47" s="2">
-        <v>25.29</v>
+      <c r="T47" s="1">
+        <v>22.88</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
@@ -5016,22 +5010,22 @@
         <v>7.583596214511041</v>
       </c>
       <c r="E48" s="2">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="F48" s="2">
-        <v>0.16377787433070318</v>
+        <v>0.20837905756396924</v>
       </c>
       <c r="G48" s="2">
         <v>1.61</v>
       </c>
       <c r="H48" s="2">
-        <v>48.84</v>
+        <v>49.06</v>
       </c>
       <c r="I48" s="2">
-        <v>23.53</v>
+        <v>23.33</v>
       </c>
       <c r="J48" s="2">
-        <v>0.015770408197091683</v>
+        <v>0.016077663016155867</v>
       </c>
       <c r="K48" s="2" t="b">
         <v>0</v>
@@ -5040,90 +5034,90 @@
         <v>241</v>
       </c>
       <c r="M48" s="2">
-        <v>0.19060035759354754</v>
+        <v>0.22998361471784556</v>
       </c>
       <c r="N48" s="2">
-        <v>24.53216416309973</v>
+        <v>27.6150921527479</v>
       </c>
       <c r="O48" s="2">
-        <v>80.72289156626506</v>
+        <v>87.95180722891565</v>
       </c>
       <c r="P48" s="2">
         <v>23.23749735248456</v>
       </c>
       <c r="Q48" s="2">
-        <v>62.65060240963855</v>
+        <v>63.253012048192765</v>
       </c>
       <c r="R48" s="2">
-        <v>55.60240963855423</v>
+        <v>58.13253012048192</v>
       </c>
       <c r="S48" s="2" t="s">
         <v>94</v>
       </c>
       <c r="T48" s="2">
-        <v>6.33</v>
+        <v>8.86</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B49" s="1">
+      <c r="B49" s="2">
         <v>-0.19</v>
       </c>
-      <c r="C49" s="1">
+      <c r="C49" s="2">
         <v>27.710843373493976</v>
       </c>
-      <c r="D49" s="1">
+      <c r="D49" s="2">
         <v>2010.578947368421</v>
       </c>
-      <c r="E49" s="1">
+      <c r="E49" s="2">
         <v>-11.05</v>
       </c>
-      <c r="F49" s="1">
-        <v>-0.0322167072980699</v>
-      </c>
-      <c r="G49" s="1">
-        <v>1.08</v>
-      </c>
-      <c r="H49" s="1">
-        <v>54.11</v>
-      </c>
-      <c r="I49" s="1">
-        <v>-4.82</v>
-      </c>
-      <c r="J49" s="1">
-        <v>0.021348718750445847</v>
-      </c>
-      <c r="K49" s="1" t="b">
+      <c r="F49" s="2">
+        <v>0.017019506036860935</v>
+      </c>
+      <c r="G49" s="2">
+        <v>1.07</v>
+      </c>
+      <c r="H49" s="2">
+        <v>57.62</v>
+      </c>
+      <c r="I49" s="2">
+        <v>-1.38</v>
+      </c>
+      <c r="J49" s="2">
+        <v>0.020284380043506824</v>
+      </c>
+      <c r="K49" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L49" s="1">
+      <c r="L49" s="2">
         <v>-8</v>
       </c>
-      <c r="M49" s="1">
-        <v>-0.028699004575073905</v>
-      </c>
-      <c r="N49" s="1">
-        <v>2.6022279462375866</v>
-      </c>
-      <c r="O49" s="1">
-        <v>36.144578313253014</v>
-      </c>
-      <c r="P49" s="1">
+      <c r="M49" s="2">
+        <v>0.01949871751353527</v>
+      </c>
+      <c r="N49" s="2">
+        <v>6.566602432316857</v>
+      </c>
+      <c r="O49" s="2">
+        <v>57.831325301204814</v>
+      </c>
+      <c r="P49" s="2">
         <v>31.00158698078384</v>
       </c>
-      <c r="Q49" s="1">
-        <v>65.90361445783132</v>
-      </c>
-      <c r="R49" s="1">
-        <v>44.81927710843374</v>
-      </c>
-      <c r="S49" s="1" t="s">
+      <c r="Q49" s="2">
+        <v>68.07228915662651</v>
+      </c>
+      <c r="R49" s="2">
+        <v>51.20481927710843</v>
+      </c>
+      <c r="S49" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="T49" s="1">
-        <v>13.72</v>
+      <c r="T49" s="2">
+        <v>20.11</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
@@ -5140,22 +5134,22 @@
         <v>15.862068965517242</v>
       </c>
       <c r="E50" s="3">
-        <v>13.34</v>
+        <v>12.9</v>
       </c>
       <c r="F50" s="3">
-        <v>-0.3205392932245849</v>
+        <v>-0.30135975488395794</v>
       </c>
       <c r="G50" s="3">
         <v>3.84</v>
       </c>
       <c r="H50" s="3">
-        <v>51.27</v>
+        <v>52.54</v>
       </c>
       <c r="I50" s="3">
-        <v>1.83</v>
+        <v>4.06</v>
       </c>
       <c r="J50" s="3">
-        <v>-0.020491369190329484</v>
+        <v>-0.014966319166082306</v>
       </c>
       <c r="K50" s="3" t="b">
         <v>0</v>
@@ -5164,22 +5158,22 @@
         <v>69</v>
       </c>
       <c r="M50" s="3">
-        <v>-0.19566084655822746</v>
+        <v>-0.2007746035445993</v>
       </c>
       <c r="N50" s="3">
-        <v>-14.09395625207776</v>
+        <v>-15.460729673496596</v>
       </c>
       <c r="O50" s="3">
-        <v>9.63855421686747</v>
+        <v>12.048192771084338</v>
       </c>
       <c r="P50" s="3">
         <v>41.201484669672254</v>
       </c>
       <c r="Q50" s="3">
-        <v>38.915662650602414</v>
+        <v>41.445783132530124</v>
       </c>
       <c r="R50" s="3">
-        <v>16.987951807228914</v>
+        <v>18.192771084337352</v>
       </c>
       <c r="S50" s="3" t="s">
         <v>105</v>
@@ -5200,22 +5194,22 @@
         <v>5.305980528511822</v>
       </c>
       <c r="E51" s="1">
-        <v>14.25</v>
+        <v>14.41</v>
       </c>
       <c r="F51" s="1">
-        <v>0.3093716311878997</v>
+        <v>0.3048778350044126</v>
       </c>
       <c r="G51" s="1">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="H51" s="1">
-        <v>67.99</v>
+        <v>66.99</v>
       </c>
       <c r="I51" s="1">
-        <v>37.47</v>
+        <v>37.05</v>
       </c>
       <c r="J51" s="1">
-        <v>0.061507045332971855</v>
+        <v>0.05940289609896233</v>
       </c>
       <c r="K51" s="1" t="b">
         <v>1</v>
@@ -5224,10 +5218,10 @@
         <v>14</v>
       </c>
       <c r="M51" s="1">
-        <v>0.34059124285448905</v>
+        <v>0.33073246897544495</v>
       </c>
       <c r="N51" s="1">
-        <v>39.5312526891939</v>
+        <v>37.689977578507836</v>
       </c>
       <c r="O51" s="1">
         <v>95.18072289156626</v>
@@ -5236,7 +5230,7 @@
         <v>38.38748944617691</v>
       </c>
       <c r="Q51" s="1">
-        <v>56.746987951807235</v>
+        <v>56.86746987951808</v>
       </c>
       <c r="R51" s="1">
         <v>46.02409638554217</v>
@@ -5260,52 +5254,52 @@
         <v>0.7761989342806395</v>
       </c>
       <c r="E52" s="1">
-        <v>-1.33</v>
+        <v>-1.38</v>
       </c>
       <c r="F52" s="1">
-        <v>-0.015525031624353994</v>
+        <v>-0.0007499657088120004</v>
       </c>
       <c r="G52" s="1">
         <v>0.98</v>
       </c>
       <c r="H52" s="1">
-        <v>25.95</v>
+        <v>31.21</v>
       </c>
       <c r="I52" s="1">
-        <v>1.24</v>
+        <v>1.86</v>
       </c>
       <c r="J52" s="1">
-        <v>0.0010982257259865473</v>
+        <v>0.001402119012330762</v>
       </c>
       <c r="K52" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L52" s="1">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M52" s="1">
-        <v>-0.016404457305102982</v>
+        <v>-0.0014583118450046673</v>
       </c>
       <c r="N52" s="1">
-        <v>3.8316826732346745</v>
+        <v>4.470899496462871</v>
       </c>
       <c r="O52" s="1">
-        <v>38.55421686746988</v>
+        <v>48.19277108433735</v>
       </c>
       <c r="P52" s="1">
         <v>11.383174615246535</v>
       </c>
       <c r="Q52" s="1">
-        <v>45.060240963855414</v>
+        <v>45.3012048192771</v>
       </c>
       <c r="R52" s="1">
-        <v>41.144578313253014</v>
+        <v>44.1566265060241</v>
       </c>
       <c r="S52" s="1" t="s">
         <v>112</v>
       </c>
       <c r="T52" s="1">
-        <v>0.72</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.25">
@@ -5322,52 +5316,52 @@
         <v>-0.1840860215053764</v>
       </c>
       <c r="E53" s="1">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="F53" s="1">
-        <v>-0.13997978523273547</v>
+        <v>-0.15478572046918285</v>
       </c>
       <c r="G53" s="1">
         <v>1.58</v>
       </c>
       <c r="H53" s="1">
-        <v>43.37</v>
+        <v>41.82</v>
       </c>
       <c r="I53" s="1">
-        <v>3.58</v>
+        <v>2</v>
       </c>
       <c r="J53" s="1">
-        <v>-0.02473000892959882</v>
+        <v>-0.0243502086491039</v>
       </c>
       <c r="K53" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L53" s="1">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M53" s="1">
-        <v>-0.11447644049101457</v>
+        <v>-0.1342436825195955</v>
       </c>
       <c r="N53" s="1">
-        <v>-5.975515645356474</v>
+        <v>-8.807637570996214</v>
       </c>
       <c r="O53" s="1">
-        <v>24.096385542168676</v>
+        <v>21.686746987951807</v>
       </c>
       <c r="P53" s="1">
         <v>26.83257063748809</v>
       </c>
       <c r="Q53" s="1">
-        <v>46.626506024096386</v>
+        <v>45.42168674698795</v>
       </c>
       <c r="R53" s="1">
-        <v>32.168674698795186</v>
+        <v>31.445783132530117</v>
       </c>
       <c r="S53" s="1" t="s">
         <v>94</v>
       </c>
       <c r="T53" s="1">
-        <v>-26.43</v>
+        <v>-27.15</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
@@ -5381,25 +5375,25 @@
         <v>37.34939759036144</v>
       </c>
       <c r="D54" s="1">
-        <v>112.91780821917807</v>
+        <v>112.9041095890411</v>
       </c>
       <c r="E54" s="1">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="F54" s="1">
-        <v>-0.07294835163385194</v>
+        <v>-0.03666376420352385</v>
       </c>
       <c r="G54" s="1">
-        <v>3.77</v>
+        <v>3.78</v>
       </c>
       <c r="H54" s="1">
-        <v>60.49</v>
+        <v>57.27</v>
       </c>
       <c r="I54" s="1">
-        <v>33.42</v>
+        <v>31.4</v>
       </c>
       <c r="J54" s="1">
-        <v>-0.014967494352183867</v>
+        <v>-0.008330246091713334</v>
       </c>
       <c r="K54" s="1" t="b">
         <v>1</v>
@@ -5408,28 +5402,28 @@
         <v>321</v>
       </c>
       <c r="M54" s="1">
-        <v>0.04885210514988403</v>
+        <v>0.06179634872725681</v>
       </c>
       <c r="N54" s="1">
-        <v>10.35733891873338</v>
+        <v>10.796365553689013</v>
       </c>
       <c r="O54" s="1">
-        <v>59.036144578313255</v>
+        <v>61.44578313253012</v>
       </c>
       <c r="P54" s="1">
         <v>52.65288503392759</v>
       </c>
       <c r="Q54" s="1">
-        <v>59.397590361445786</v>
+        <v>61.204819277108435</v>
       </c>
       <c r="R54" s="1">
-        <v>41.74698795180723</v>
+        <v>43.43373493975904</v>
       </c>
       <c r="S54" s="1" t="s">
         <v>103</v>
       </c>
       <c r="T54" s="1">
-        <v>-18.25</v>
+        <v>-16.57</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
@@ -5446,22 +5440,22 @@
         <v>7.147058823529411</v>
       </c>
       <c r="E55" s="3">
-        <v>-1.4</v>
+        <v>-1.32</v>
       </c>
       <c r="F55" s="3">
-        <v>-0.21736367233368295</v>
+        <v>-0.22003637590340908</v>
       </c>
       <c r="G55" s="3">
         <v>2.04</v>
       </c>
       <c r="H55" s="3">
-        <v>41.21</v>
+        <v>40.19</v>
       </c>
       <c r="I55" s="3">
-        <v>-4.17</v>
+        <v>-6.92</v>
       </c>
       <c r="J55" s="3">
-        <v>-0.016624824932654922</v>
+        <v>-0.017157363306274934</v>
       </c>
       <c r="K55" s="3" t="b">
         <v>1</v>
@@ -5470,28 +5464,28 @@
         <v>249</v>
       </c>
       <c r="M55" s="3">
-        <v>-0.17163353693473515</v>
+        <v>-0.1832023768213904</v>
       </c>
       <c r="N55" s="3">
-        <v>-11.691225289728541</v>
+        <v>-13.703507001175709</v>
       </c>
       <c r="O55" s="3">
-        <v>13.253012048192772</v>
+        <v>15.66265060240964</v>
       </c>
       <c r="P55" s="3">
         <v>40.717118046641446</v>
       </c>
       <c r="Q55" s="3">
-        <v>44.93975903614458</v>
+        <v>43.6144578313253</v>
       </c>
       <c r="R55" s="3">
-        <v>27.28915662650602</v>
+        <v>27.89156626506025</v>
       </c>
       <c r="S55" s="3" t="s">
         <v>107</v>
       </c>
       <c r="T55" s="3">
-        <v>-21.67</v>
+        <v>-21.07</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
@@ -5508,10 +5502,10 @@
         <v>316.79999999999995</v>
       </c>
       <c r="E56" s="1">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="F56" s="1">
-        <v>-0.018642785546903823</v>
+        <v>-0.06013873910642718</v>
       </c>
       <c r="G56" s="1">
         <v>1.64</v>
@@ -5520,10 +5514,10 @@
         <v>36.78</v>
       </c>
       <c r="I56" s="1">
-        <v>-21</v>
+        <v>-20.92</v>
       </c>
       <c r="J56" s="1">
-        <v>0.007067255987827987</v>
+        <v>0.003353509077609767</v>
       </c>
       <c r="K56" s="1" t="b">
         <v>0</v>
@@ -5532,28 +5526,28 @@
         <v>3</v>
       </c>
       <c r="M56" s="1">
-        <v>0.009498836237064046</v>
+        <v>-0.03747166274826186</v>
       </c>
       <c r="N56" s="1">
-        <v>6.422012027451383</v>
+        <v>0.8695644061371431</v>
       </c>
       <c r="O56" s="1">
-        <v>44.57831325301205</v>
+        <v>40.963855421686745</v>
       </c>
       <c r="P56" s="1">
         <v>39.61783553142854</v>
       </c>
       <c r="Q56" s="1">
-        <v>50</v>
+        <v>49.51807228915663</v>
       </c>
       <c r="R56" s="1">
-        <v>41.686746987951814</v>
+        <v>40.36144578313253</v>
       </c>
       <c r="S56" s="1" t="s">
         <v>100</v>
       </c>
       <c r="T56" s="1">
-        <v>19.74</v>
+        <v>18.41</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
@@ -5570,52 +5564,52 @@
         <v>3.3177083333333335</v>
       </c>
       <c r="E57" s="3">
-        <v>1.01</v>
+        <v>0.97</v>
       </c>
       <c r="F57" s="3">
-        <v>-0.1664644283649183</v>
+        <v>-0.25434985987659464</v>
       </c>
       <c r="G57" s="3">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H57" s="3">
-        <v>45.07</v>
+        <v>39.37</v>
       </c>
       <c r="I57" s="3">
-        <v>13.14</v>
+        <v>6.14</v>
       </c>
       <c r="J57" s="3">
-        <v>-0.02860206911111978</v>
+        <v>-0.029420521253828977</v>
       </c>
       <c r="K57" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L57" s="3">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="M57" s="3">
-        <v>-0.12864912409271145</v>
+        <v>-0.22353680295221368</v>
       </c>
       <c r="N57" s="3">
-        <v>-7.392784005526167</v>
+        <v>-17.736949614258034</v>
       </c>
       <c r="O57" s="3">
-        <v>18.072289156626507</v>
+        <v>10.843373493975903</v>
       </c>
       <c r="P57" s="3">
         <v>41.76493344029593</v>
       </c>
       <c r="Q57" s="3">
-        <v>49.036144578313255</v>
+        <v>44.57831325301205</v>
       </c>
       <c r="R57" s="3">
-        <v>27.349397590361445</v>
+        <v>25.180722891566266</v>
       </c>
       <c r="S57" s="3" t="s">
         <v>107</v>
       </c>
       <c r="T57" s="3">
-        <v>-31.86</v>
+        <v>-34.03</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
@@ -5632,22 +5626,22 @@
         <v>2.417910447761194</v>
       </c>
       <c r="E58" s="3">
-        <v>-4.36</v>
+        <v>-4.45</v>
       </c>
       <c r="F58" s="3">
-        <v>-0.3947490455086623</v>
+        <v>-0.3803363216790769</v>
       </c>
       <c r="G58" s="3">
         <v>2.82</v>
       </c>
       <c r="H58" s="3">
-        <v>36.85</v>
+        <v>37.94</v>
       </c>
       <c r="I58" s="3">
-        <v>-34.48</v>
+        <v>-33.94</v>
       </c>
       <c r="J58" s="3">
-        <v>-0.03170896282234871</v>
+        <v>-0.03406704321764206</v>
       </c>
       <c r="K58" s="3" t="b">
         <v>0</v>
@@ -5656,10 +5650,10 @@
         <v>21</v>
       </c>
       <c r="M58" s="3">
-        <v>-0.3147213085605036</v>
+        <v>-0.31587682328554423</v>
       </c>
       <c r="N58" s="3">
-        <v>-26.000002452305388</v>
+        <v>-26.97095164759109</v>
       </c>
       <c r="O58" s="3">
         <v>7.228915662650602</v>
@@ -5668,16 +5662,16 @@
         <v>46.90217032437056</v>
       </c>
       <c r="Q58" s="3">
-        <v>23.855421686746986</v>
+        <v>23.6144578313253</v>
       </c>
       <c r="R58" s="3">
-        <v>11.626506024096383</v>
+        <v>11.385542168674696</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>96</v>
       </c>
       <c r="T58" s="3">
-        <v>-15.26</v>
+        <v>-15.5</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
@@ -5694,22 +5688,22 @@
         <v>2.1172413793103453</v>
       </c>
       <c r="E59" s="2">
-        <v>-0.51</v>
+        <v>-0.53</v>
       </c>
       <c r="F59" s="2">
-        <v>0.08353250321698108</v>
+        <v>0.08326117526801474</v>
       </c>
       <c r="G59" s="2">
         <v>1.2</v>
       </c>
       <c r="H59" s="2">
-        <v>51.85</v>
+        <v>53.72</v>
       </c>
       <c r="I59" s="2">
-        <v>13.67</v>
+        <v>13.88</v>
       </c>
       <c r="J59" s="2">
-        <v>0.008035973159646846</v>
+        <v>0.007703558276093762</v>
       </c>
       <c r="K59" s="2" t="b">
         <v>0</v>
@@ -5718,28 +5712,28 @@
         <v>170</v>
       </c>
       <c r="M59" s="2">
-        <v>0.09232676002447104</v>
+        <v>0.09034463662994141</v>
       </c>
       <c r="N59" s="2">
-        <v>14.70480440619209</v>
+        <v>13.651194343957476</v>
       </c>
       <c r="O59" s="2">
-        <v>69.87951807228916</v>
+        <v>68.67469879518072</v>
       </c>
       <c r="P59" s="2">
-        <v>8.376287302325013</v>
+        <v>7.747915191962705</v>
       </c>
       <c r="Q59" s="2">
-        <v>56.987951807228924</v>
+        <v>58.07228915662651</v>
       </c>
       <c r="R59" s="2">
-        <v>52.168674698795186</v>
+        <v>51.9277108433735</v>
       </c>
       <c r="S59" s="2" t="s">
         <v>113</v>
       </c>
       <c r="T59" s="2">
-        <v>4.97</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.25">
@@ -5756,52 +5750,52 @@
         <v>0.23638470451911922</v>
       </c>
       <c r="E60" s="2">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="F60" s="2">
-        <v>0.09727405829439849</v>
+        <v>0.09614956412598455</v>
       </c>
       <c r="G60" s="2">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="H60" s="2">
-        <v>49.48</v>
+        <v>52.67</v>
       </c>
       <c r="I60" s="2">
-        <v>12.48</v>
+        <v>13.25</v>
       </c>
       <c r="J60" s="2">
-        <v>0.007925107525405272</v>
+        <v>0.005924303532618246</v>
       </c>
       <c r="K60" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L60" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M60" s="2">
-        <v>0.062097031064438646</v>
+        <v>0.06816989174637422</v>
       </c>
       <c r="N60" s="2">
-        <v>11.681831510188852</v>
+        <v>11.433719855600753</v>
       </c>
       <c r="O60" s="2">
         <v>63.85542168674698</v>
       </c>
       <c r="P60" s="2">
-        <v>7.821740234025714</v>
+        <v>7.56622762341097</v>
       </c>
       <c r="Q60" s="2">
-        <v>56.26506024096386</v>
+        <v>57.95180722891566</v>
       </c>
       <c r="R60" s="2">
-        <v>51.38554216867469</v>
+        <v>51.144578313253</v>
       </c>
       <c r="S60" s="2" t="s">
         <v>114</v>
       </c>
       <c r="T60" s="2">
-        <v>5.41</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
@@ -5815,25 +5809,25 @@
         <v>98.79518072289156</v>
       </c>
       <c r="D61" s="1">
-        <v>1.5311297260584105</v>
+        <v>1.5376952682816392</v>
       </c>
       <c r="E61" s="1">
-        <v>-1.02</v>
+        <v>-1.07</v>
       </c>
       <c r="F61" s="1">
-        <v>-0.012907448139728273</v>
+        <v>-0.11078022494646482</v>
       </c>
       <c r="G61" s="1">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="H61" s="1">
-        <v>53.29</v>
+        <v>46.72</v>
       </c>
       <c r="I61" s="1">
-        <v>58.1</v>
+        <v>48.14</v>
       </c>
       <c r="J61" s="1">
-        <v>-0.015122042969679313</v>
+        <v>-0.014443565039999856</v>
       </c>
       <c r="K61" s="1" t="b">
         <v>0</v>
@@ -5842,28 +5836,28 @@
         <v>934</v>
       </c>
       <c r="M61" s="1">
-        <v>0.04117723122633499</v>
+        <v>-0.06686276450251949</v>
       </c>
       <c r="N61" s="1">
-        <v>9.589851526378467</v>
+        <v>-2.0695457692886157</v>
       </c>
       <c r="O61" s="1">
-        <v>54.21686746987952</v>
+        <v>38.55421686746988</v>
       </c>
       <c r="P61" s="1">
         <v>39.10478556320163</v>
       </c>
       <c r="Q61" s="1">
-        <v>63.614457831325296</v>
+        <v>60.84337349397589</v>
       </c>
       <c r="R61" s="1">
-        <v>46.20481927710843</v>
+        <v>41.626506024096386</v>
       </c>
       <c r="S61" s="1" t="s">
         <v>115</v>
       </c>
       <c r="T61" s="1">
-        <v>-21.9</v>
+        <v>-26.48</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
@@ -5877,55 +5871,55 @@
         <v>97.59036144578313</v>
       </c>
       <c r="D62" s="1">
-        <v>-1.559404523332379</v>
+        <v>-1.5596908101918123</v>
       </c>
       <c r="E62" s="1">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="F62" s="1">
-        <v>0.01212732031679127</v>
+        <v>0.010918330562610656</v>
       </c>
       <c r="G62" s="1">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="H62" s="1">
-        <v>42.38</v>
+        <v>41.84</v>
       </c>
       <c r="I62" s="1">
-        <v>3.6</v>
+        <v>1.73</v>
       </c>
       <c r="J62" s="1">
-        <v>-0.014415481262844898</v>
+        <v>-0.015651687538323376</v>
       </c>
       <c r="K62" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L62" s="1">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="M62" s="1">
-        <v>0.010808181795667782</v>
+        <v>0.009501638290225323</v>
       </c>
       <c r="N62" s="1">
-        <v>6.552946583311764</v>
+        <v>5.566894509985867</v>
       </c>
       <c r="O62" s="1">
-        <v>45.78313253012048</v>
+        <v>50.602409638554214</v>
       </c>
       <c r="P62" s="1">
         <v>24.570041255395854</v>
       </c>
       <c r="Q62" s="1">
-        <v>45.06024096385542</v>
+        <v>43.373493975903614</v>
       </c>
       <c r="R62" s="1">
-        <v>37.83132530120482</v>
+        <v>38.91566265060241</v>
       </c>
       <c r="S62" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T62" s="1">
-        <v>-6.92</v>
+        <v>-5.84</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
@@ -5942,52 +5936,52 @@
         <v>-0.3740157480314961</v>
       </c>
       <c r="E63" s="1">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="F63" s="1">
-        <v>-0.07972553973742277</v>
+        <v>-0.07505515025656574</v>
       </c>
       <c r="G63" s="1">
         <v>0.36</v>
       </c>
       <c r="H63" s="1">
-        <v>40.29</v>
+        <v>43.09</v>
       </c>
       <c r="I63" s="1">
-        <v>-8.06</v>
+        <v>-7.59</v>
       </c>
       <c r="J63" s="1">
-        <v>-0.0011193067865662395</v>
+        <v>-0.0014905033552541922</v>
       </c>
       <c r="K63" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L63" s="1">
-        <v>-102</v>
+        <v>-100</v>
       </c>
       <c r="M63" s="1">
-        <v>-0.10786716152139064</v>
+        <v>-0.09772222661473107</v>
       </c>
       <c r="N63" s="1">
-        <v>-5.314587748394085</v>
+        <v>-5.155491980509771</v>
       </c>
       <c r="O63" s="1">
-        <v>25.301204819277107</v>
+        <v>31.32530120481928</v>
       </c>
       <c r="P63" s="1">
         <v>14.852676969550105</v>
       </c>
       <c r="Q63" s="1">
-        <v>38.554216867469876</v>
+        <v>41.204819277108435</v>
       </c>
       <c r="R63" s="1">
-        <v>31.566265060240962</v>
+        <v>33.85542168674699</v>
       </c>
       <c r="S63" s="1" t="s">
         <v>116</v>
       </c>
       <c r="T63" s="1">
-        <v>5.53</v>
+        <v>7.82</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.25">
@@ -6004,114 +5998,114 @@
         <v>0.32573652028904965</v>
       </c>
       <c r="E64" s="2">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="F64" s="2">
-        <v>0.16149407621481182</v>
+        <v>0.14678101459185267</v>
       </c>
       <c r="G64" s="2">
         <v>0.87</v>
       </c>
       <c r="H64" s="2">
-        <v>61.81</v>
+        <v>61.44</v>
       </c>
       <c r="I64" s="2">
-        <v>18.68</v>
+        <v>18.26</v>
       </c>
       <c r="J64" s="2">
-        <v>0.010333537189443664</v>
+        <v>0.00882702794679454</v>
       </c>
       <c r="K64" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L64" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M64" s="2">
-        <v>0.15577780928994334</v>
+        <v>0.14217676470660034</v>
       </c>
       <c r="N64" s="2">
-        <v>21.04990933273931</v>
+        <v>18.834407151623374</v>
       </c>
       <c r="O64" s="2">
-        <v>78.3132530120482</v>
+        <v>77.10843373493977</v>
       </c>
       <c r="P64" s="2">
-        <v>11.227431947037326</v>
+        <v>11.000474713303552</v>
       </c>
       <c r="Q64" s="2">
         <v>67.10843373493975</v>
       </c>
       <c r="R64" s="2">
-        <v>60.18072289156626</v>
+        <v>59.81927710843374</v>
       </c>
       <c r="S64" s="2" t="s">
         <v>117</v>
       </c>
       <c r="T64" s="2">
-        <v>16.58</v>
+        <v>16.22</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
+      <c r="A65" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B65" s="1">
+      <c r="B65" s="3">
         <v>72.89</v>
       </c>
-      <c r="C65" s="1">
+      <c r="C65" s="3">
         <v>100</v>
       </c>
-      <c r="D65" s="1">
+      <c r="D65" s="3">
         <v>-0.6841816435725065</v>
       </c>
-      <c r="E65" s="1">
+      <c r="E65" s="3">
         <v>1.65</v>
       </c>
-      <c r="F65" s="1">
-        <v>-0.20980199841197136</v>
-      </c>
-      <c r="G65" s="1">
-        <v>5.21</v>
-      </c>
-      <c r="H65" s="1">
-        <v>57.34</v>
-      </c>
-      <c r="I65" s="1">
-        <v>64.89</v>
-      </c>
-      <c r="J65" s="1">
-        <v>-0.02771292158766348</v>
-      </c>
-      <c r="K65" s="1" t="b">
+      <c r="F65" s="3">
+        <v>-0.32929328817874015</v>
+      </c>
+      <c r="G65" s="3">
+        <v>5.27</v>
+      </c>
+      <c r="H65" s="3">
+        <v>48.34</v>
+      </c>
+      <c r="I65" s="3">
+        <v>48.29</v>
+      </c>
+      <c r="J65" s="3">
+        <v>-0.02834489635136885</v>
+      </c>
+      <c r="K65" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L65" s="1">
+      <c r="L65" s="3">
         <v>667</v>
       </c>
-      <c r="M65" s="1">
-        <v>-0.024682892614307672</v>
-      </c>
-      <c r="N65" s="1">
-        <v>3.003839142314212</v>
-      </c>
-      <c r="O65" s="1">
-        <v>37.34939759036144</v>
-      </c>
-      <c r="P65" s="1">
+      <c r="M65" s="3">
+        <v>-0.17806138810160588</v>
+      </c>
+      <c r="N65" s="3">
+        <v>-13.189408129197261</v>
+      </c>
+      <c r="O65" s="3">
+        <v>16.867469879518072</v>
+      </c>
+      <c r="P65" s="3">
         <v>56.49293299150161</v>
       </c>
-      <c r="Q65" s="1">
-        <v>55.42168674698796</v>
-      </c>
-      <c r="R65" s="1">
-        <v>31.506024096385538</v>
-      </c>
-      <c r="S65" s="1" t="s">
+      <c r="Q65" s="3">
+        <v>51.807228915662655</v>
+      </c>
+      <c r="R65" s="3">
+        <v>25.361445783132524</v>
+      </c>
+      <c r="S65" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="T65" s="1">
-        <v>-37.88</v>
+      <c r="T65" s="3">
+        <v>-44.03</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
@@ -6128,22 +6122,22 @@
         <v>3.0958904109589045</v>
       </c>
       <c r="E66" s="1">
-        <v>-2.47</v>
+        <v>-2.42</v>
       </c>
       <c r="F66" s="1">
-        <v>-0.04586003840602697</v>
+        <v>-0.1288085002658646</v>
       </c>
       <c r="G66" s="1">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="H66" s="1">
-        <v>51.34</v>
+        <v>42.85</v>
       </c>
       <c r="I66" s="1">
-        <v>43.03</v>
+        <v>29.98</v>
       </c>
       <c r="J66" s="1">
-        <v>-0.012812069899449795</v>
+        <v>-0.010312173073726555</v>
       </c>
       <c r="K66" s="1" t="b">
         <v>0</v>
@@ -6152,90 +6146,90 @@
         <v>516</v>
       </c>
       <c r="M66" s="1">
-        <v>0.0020686611947933198</v>
+        <v>-0.08984946277526795</v>
       </c>
       <c r="N66" s="1">
-        <v>5.678994523224311</v>
+        <v>-4.368215596563458</v>
       </c>
       <c r="O66" s="1">
-        <v>39.75903614457831</v>
+        <v>36.144578313253014</v>
       </c>
       <c r="P66" s="1">
         <v>31.85898471566022</v>
       </c>
       <c r="Q66" s="1">
-        <v>60.24096385542168</v>
+        <v>57.71084337349398</v>
       </c>
       <c r="R66" s="1">
-        <v>41.08433734939759</v>
+        <v>40.361445783132524</v>
       </c>
       <c r="S66" s="1" t="s">
         <v>103</v>
       </c>
       <c r="T66" s="1">
-        <v>-24.95</v>
+        <v>-25.68</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
+      <c r="A67" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B67" s="1">
+      <c r="B67" s="2">
         <v>16.5</v>
       </c>
-      <c r="C67" s="1">
+      <c r="C67" s="2">
         <v>85.54216867469879</v>
       </c>
-      <c r="D67" s="1">
+      <c r="D67" s="2">
         <v>-0.19636363636363638</v>
       </c>
-      <c r="E67" s="1">
-        <v>-1.67</v>
-      </c>
-      <c r="F67" s="1">
-        <v>0.045729027940415</v>
-      </c>
-      <c r="G67" s="1">
-        <v>1</v>
-      </c>
-      <c r="H67" s="1">
-        <v>38.5</v>
-      </c>
-      <c r="I67" s="1">
-        <v>-25.94</v>
-      </c>
-      <c r="J67" s="1">
-        <v>0.019854061986545244</v>
-      </c>
-      <c r="K67" s="1" t="b">
+      <c r="E67" s="2">
+        <v>-1.75</v>
+      </c>
+      <c r="F67" s="2">
+        <v>0.11546671556504247</v>
+      </c>
+      <c r="G67" s="2">
+        <v>0.99</v>
+      </c>
+      <c r="H67" s="2">
+        <v>47.68</v>
+      </c>
+      <c r="I67" s="2">
+        <v>-21.53</v>
+      </c>
+      <c r="J67" s="2">
+        <v>0.017995018226023292</v>
+      </c>
+      <c r="K67" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L67" s="1">
+      <c r="L67" s="2">
         <v>-251</v>
       </c>
-      <c r="M67" s="1">
-        <v>0.045729027940415</v>
-      </c>
-      <c r="N67" s="1">
-        <v>10.045031197786482</v>
-      </c>
-      <c r="O67" s="1">
-        <v>57.831325301204814</v>
-      </c>
-      <c r="P67" s="1">
+      <c r="M67" s="2">
+        <v>0.11511254249694614</v>
+      </c>
+      <c r="N67" s="2">
+        <v>16.12798493065795</v>
+      </c>
+      <c r="O67" s="2">
+        <v>74.69879518072288</v>
+      </c>
+      <c r="P67" s="2">
         <v>37.5868621181625</v>
       </c>
-      <c r="Q67" s="1">
-        <v>51.68674698795181</v>
-      </c>
-      <c r="R67" s="1">
-        <v>45.30120481927711</v>
-      </c>
-      <c r="S67" s="1" t="s">
+      <c r="Q67" s="2">
+        <v>55.18072289156626</v>
+      </c>
+      <c r="R67" s="2">
+        <v>50.36144578313253</v>
+      </c>
+      <c r="S67" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="T67" s="1">
-        <v>27.56</v>
+      <c r="T67" s="2">
+        <v>32.62</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
@@ -6249,25 +6243,25 @@
         <v>57.831325301204814</v>
       </c>
       <c r="D68" s="1">
-        <v>6.043956043956044</v>
+        <v>6.048351648351648</v>
       </c>
       <c r="E68" s="1">
-        <v>-0.26</v>
+        <v>-0.51</v>
       </c>
       <c r="F68" s="1">
-        <v>-0.008582080340135509</v>
+        <v>-0.02489421025857011</v>
       </c>
       <c r="G68" s="1">
         <v>1.26</v>
       </c>
       <c r="H68" s="1">
-        <v>43.39</v>
+        <v>42.92</v>
       </c>
       <c r="I68" s="1">
-        <v>-4.64</v>
+        <v>-5.03</v>
       </c>
       <c r="J68" s="1">
-        <v>-0.00039742007549923463</v>
+        <v>-0.001234813392897378</v>
       </c>
       <c r="K68" s="1" t="b">
         <v>1</v>
@@ -6276,28 +6270,28 @@
         <v>4</v>
       </c>
       <c r="M68" s="1">
-        <v>0.002850453509601447</v>
+        <v>-0.01568571048806544</v>
       </c>
       <c r="N68" s="1">
-        <v>5.757173754705127</v>
+        <v>3.048159632156794</v>
       </c>
       <c r="O68" s="1">
-        <v>42.168674698795186</v>
+        <v>44.57831325301205</v>
       </c>
       <c r="P68" s="1">
         <v>16.710870321490763</v>
       </c>
       <c r="Q68" s="1">
-        <v>50.361445783132524</v>
+        <v>50.8433734939759</v>
       </c>
       <c r="R68" s="1">
-        <v>43.67469879518072</v>
+        <v>44.87951807228916</v>
       </c>
       <c r="S68" s="1" t="s">
         <v>100</v>
       </c>
       <c r="T68" s="1">
-        <v>1.97</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
@@ -6314,52 +6308,52 @@
         <v>882.7368421052631</v>
       </c>
       <c r="E69" s="2">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F69" s="2">
-        <v>0.1663477841464612</v>
+        <v>0.11902108211532893</v>
       </c>
       <c r="G69" s="2">
         <v>0.34</v>
       </c>
       <c r="H69" s="2">
-        <v>52.84</v>
+        <v>51.2</v>
       </c>
       <c r="I69" s="2">
-        <v>7.55</v>
+        <v>6.84</v>
       </c>
       <c r="J69" s="2">
-        <v>0.016197455902645312</v>
+        <v>0.014913898788446851</v>
       </c>
       <c r="K69" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L69" s="2">
-        <v>-81</v>
+        <v>-80</v>
       </c>
       <c r="M69" s="2">
-        <v>0.13732673668174433</v>
+        <v>0.09564565962097094</v>
       </c>
       <c r="N69" s="2">
-        <v>19.204802071919413</v>
+        <v>14.181296643060417</v>
       </c>
       <c r="O69" s="2">
-        <v>75.90361445783132</v>
+        <v>71.08433734939759</v>
       </c>
       <c r="P69" s="2">
-        <v>13.506581704162873</v>
+        <v>11.74077020079542</v>
       </c>
       <c r="Q69" s="2">
-        <v>60.843373493975896</v>
+        <v>60.361445783132524</v>
       </c>
       <c r="R69" s="2">
-        <v>56.50602409638554</v>
+        <v>55.18072289156626</v>
       </c>
       <c r="S69" s="2" t="s">
         <v>94</v>
       </c>
       <c r="T69" s="2">
-        <v>8.46</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
@@ -6376,52 +6370,52 @@
         <v>0.3596792668957616</v>
       </c>
       <c r="E70" s="3">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="F70" s="3">
-        <v>-0.20096705411897683</v>
+        <v>-0.16912547469030736</v>
       </c>
       <c r="G70" s="3">
         <v>1.48</v>
       </c>
       <c r="H70" s="3">
-        <v>42.57</v>
+        <v>48.12</v>
       </c>
       <c r="I70" s="3">
-        <v>-21.78</v>
+        <v>-19.54</v>
       </c>
       <c r="J70" s="3">
-        <v>-0.010958532071617065</v>
+        <v>-0.01104136108363604</v>
       </c>
       <c r="K70" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="3">
         <v>-41</v>
       </c>
       <c r="M70" s="3">
-        <v>-0.17986083778100093</v>
+        <v>-0.15212516742168336</v>
       </c>
       <c r="N70" s="3">
-        <v>-12.513955374355115</v>
+        <v>-10.595786061205004</v>
       </c>
       <c r="O70" s="3">
-        <v>12.048192771084338</v>
+        <v>19.27710843373494</v>
       </c>
       <c r="P70" s="3">
         <v>31.34692685044607</v>
       </c>
       <c r="Q70" s="3">
-        <v>43.373493975903614</v>
+        <v>45.18072289156627</v>
       </c>
       <c r="R70" s="3">
-        <v>27.83132530120482</v>
+        <v>29.759036144578317</v>
       </c>
       <c r="S70" s="3" t="s">
         <v>97</v>
       </c>
       <c r="T70" s="3">
-        <v>-1.62</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.25">
@@ -6438,22 +6432,22 @@
         <v>-0.5072619688004303</v>
       </c>
       <c r="E71" s="2">
-        <v>-0.38</v>
+        <v>-0.35</v>
       </c>
       <c r="F71" s="2">
-        <v>0.2014224653127636</v>
+        <v>0.2397788063941012</v>
       </c>
       <c r="G71" s="2">
         <v>0.89</v>
       </c>
       <c r="H71" s="2">
-        <v>51.48</v>
+        <v>51.22</v>
       </c>
       <c r="I71" s="2">
-        <v>12.42</v>
+        <v>12.45</v>
       </c>
       <c r="J71" s="2">
-        <v>0.018561663413334335</v>
+        <v>0.01743311779074454</v>
       </c>
       <c r="K71" s="2" t="b">
         <v>0</v>
@@ -6462,28 +6456,28 @@
         <v>48</v>
       </c>
       <c r="M71" s="2">
-        <v>0.1965856240686441</v>
+        <v>0.23588290264504153</v>
       </c>
       <c r="N71" s="2">
-        <v>25.130690810609384</v>
+        <v>28.205020945467492</v>
       </c>
       <c r="O71" s="2">
-        <v>81.92771084337349</v>
+        <v>90.36144578313254</v>
       </c>
       <c r="P71" s="2">
-        <v>17.55411995640854</v>
+        <v>16.760346247612663</v>
       </c>
       <c r="Q71" s="2">
-        <v>61.566265060240966</v>
+        <v>62.40963855421687</v>
       </c>
       <c r="R71" s="2">
-        <v>56.86746987951808</v>
+        <v>59.75903614457832</v>
       </c>
       <c r="S71" s="2" t="s">
         <v>104</v>
       </c>
       <c r="T71" s="2">
-        <v>16.99</v>
+        <v>19.88</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.25">
@@ -6497,25 +6491,25 @@
         <v>44.57831325301205</v>
       </c>
       <c r="D72" s="3">
-        <v>11.338095238095237</v>
+        <v>11.128571428571426</v>
       </c>
       <c r="E72" s="3">
-        <v>0.37</v>
+        <v>0.45</v>
       </c>
       <c r="F72" s="3">
-        <v>-0.22564867925171816</v>
+        <v>-0.24901278052541245</v>
       </c>
       <c r="G72" s="3">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="H72" s="3">
-        <v>32.77</v>
+        <v>33.98</v>
       </c>
       <c r="I72" s="3">
-        <v>-28.26</v>
+        <v>-27.62</v>
       </c>
       <c r="J72" s="3">
-        <v>-0.00805432449229552</v>
+        <v>-0.009611037102184099</v>
       </c>
       <c r="K72" s="3" t="b">
         <v>0</v>
@@ -6524,10 +6518,10 @@
         <v>-164</v>
       </c>
       <c r="M72" s="3">
-        <v>-0.22169126368834768</v>
+        <v>-0.24547104984444912</v>
       </c>
       <c r="N72" s="3">
-        <v>-16.696997965089793</v>
+        <v>-19.930374303481585</v>
       </c>
       <c r="O72" s="3">
         <v>8.433734939759036</v>
@@ -6536,7 +6530,7 @@
         <v>22.69368849988335</v>
       </c>
       <c r="Q72" s="3">
-        <v>41.32530120481927</v>
+        <v>41.56626506024096</v>
       </c>
       <c r="R72" s="3">
         <v>29.879518072289155</v>
@@ -6565,19 +6559,19 @@
         <v>-3.73</v>
       </c>
       <c r="F73" s="3">
-        <v>-0.19929860518961134</v>
+        <v>-0.23410140879719693</v>
       </c>
       <c r="G73" s="3">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="H73" s="3">
-        <v>43.57</v>
+        <v>42.02</v>
       </c>
       <c r="I73" s="3">
-        <v>-1.37</v>
+        <v>-2.57</v>
       </c>
       <c r="J73" s="3">
-        <v>-0.017669355794578977</v>
+        <v>-0.019370875625452002</v>
       </c>
       <c r="K73" s="3" t="b">
         <v>0</v>
@@ -6586,28 +6580,28 @@
         <v>32</v>
       </c>
       <c r="M73" s="3">
-        <v>-0.18874549702062338</v>
+        <v>-0.2252470820947886</v>
       </c>
       <c r="N73" s="3">
-        <v>-13.402421298317357</v>
+        <v>-17.907977528515527</v>
       </c>
       <c r="O73" s="3">
-        <v>10.843373493975903</v>
+        <v>9.63855421686747</v>
       </c>
       <c r="P73" s="3">
         <v>27.09638457523498</v>
       </c>
       <c r="Q73" s="3">
-        <v>48.07228915662651</v>
+        <v>46.506024096385545</v>
       </c>
       <c r="R73" s="3">
-        <v>29.638554216867476</v>
+        <v>29.15662650602409</v>
       </c>
       <c r="S73" s="3" t="s">
         <v>100</v>
       </c>
       <c r="T73" s="3">
-        <v>-28.96</v>
+        <v>-29.44</v>
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.25">
@@ -6624,22 +6618,22 @@
         <v>162.09090909090907</v>
       </c>
       <c r="E74" s="3">
-        <v>-0.01</v>
+        <v>-0.07</v>
       </c>
       <c r="F74" s="3">
-        <v>-0.45260386192658736</v>
+        <v>-0.4326195374414126</v>
       </c>
       <c r="G74" s="3">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="H74" s="3">
-        <v>39.01</v>
+        <v>40.28</v>
       </c>
       <c r="I74" s="3">
-        <v>-33.64</v>
+        <v>-32.91</v>
       </c>
       <c r="J74" s="3">
-        <v>-0.020456283782932308</v>
+        <v>-0.021997699890366984</v>
       </c>
       <c r="K74" s="3" t="b">
         <v>0</v>
@@ -6648,90 +6642,90 @@
         <v>10</v>
       </c>
       <c r="M74" s="3">
-        <v>-0.3532287600019508</v>
+        <v>-0.3529305971197376</v>
       </c>
       <c r="N74" s="3">
-        <v>-29.8507475964501</v>
+        <v>-30.676329031010425</v>
       </c>
       <c r="O74" s="3">
-        <v>3.614457831325301</v>
+        <v>6.024096385542169</v>
       </c>
       <c r="P74" s="3">
         <v>51.49813033405746</v>
       </c>
       <c r="Q74" s="3">
-        <v>40.60240963855422</v>
+        <v>40.722891566265055</v>
       </c>
       <c r="R74" s="3">
-        <v>22.89156626506024</v>
+        <v>23.493975903614462</v>
       </c>
       <c r="S74" s="3" t="s">
         <v>106</v>
       </c>
       <c r="T74" s="3">
-        <v>-2.84</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
+      <c r="A75" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B75" s="1">
+      <c r="B75" s="3">
         <v>3.5</v>
       </c>
-      <c r="C75" s="1">
+      <c r="C75" s="3">
         <v>53.01204819277109</v>
       </c>
-      <c r="D75" s="1">
+      <c r="D75" s="3">
         <v>-22.482857142857142</v>
       </c>
-      <c r="E75" s="1">
-        <v>12.88</v>
-      </c>
-      <c r="F75" s="1">
-        <v>0.2285732150240099</v>
-      </c>
-      <c r="G75" s="1">
+      <c r="E75" s="3">
+        <v>12.84</v>
+      </c>
+      <c r="F75" s="3">
+        <v>-0.03283081248773884</v>
+      </c>
+      <c r="G75" s="3">
         <v>0.88</v>
       </c>
-      <c r="H75" s="1">
-        <v>37.13</v>
-      </c>
-      <c r="I75" s="1">
-        <v>51.7</v>
-      </c>
-      <c r="J75" s="1">
-        <v>-0.0052961048391376156</v>
-      </c>
-      <c r="K75" s="1" t="b">
+      <c r="H75" s="3">
+        <v>36.33</v>
+      </c>
+      <c r="I75" s="3">
+        <v>49.73</v>
+      </c>
+      <c r="J75" s="3">
+        <v>-0.012369235507545288</v>
+      </c>
+      <c r="K75" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L75" s="1">
+      <c r="L75" s="3">
         <v>42</v>
       </c>
-      <c r="M75" s="1">
-        <v>0.22329666093951595</v>
-      </c>
-      <c r="N75" s="1">
-        <v>27.80179449769658</v>
-      </c>
-      <c r="O75" s="1">
-        <v>86.74698795180723</v>
-      </c>
-      <c r="P75" s="1">
-        <v>23.487824486347613</v>
-      </c>
-      <c r="Q75" s="1">
-        <v>33.975903614457835</v>
-      </c>
-      <c r="R75" s="1">
-        <v>38.3132530120482</v>
-      </c>
-      <c r="S75" s="1" t="s">
+      <c r="M75" s="3">
+        <v>-0.03708088930489484</v>
+      </c>
+      <c r="N75" s="3">
+        <v>0.9086417504738393</v>
+      </c>
+      <c r="O75" s="3">
+        <v>42.168674698795186</v>
+      </c>
+      <c r="P75" s="3">
+        <v>24.0515697846509</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>31.325301204819276</v>
+      </c>
+      <c r="R75" s="3">
+        <v>23.734939759036145</v>
+      </c>
+      <c r="S75" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="T75" s="1">
-        <v>-35.41</v>
+      <c r="T75" s="3">
+        <v>-49.98</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
@@ -6748,52 +6742,52 @@
         <v>3.3878504672897196</v>
       </c>
       <c r="E76" s="2">
-        <v>-9.2</v>
+        <v>-9.21</v>
       </c>
       <c r="F76" s="2">
-        <v>0.5466045481756238</v>
+        <v>0.5636196169909476</v>
       </c>
       <c r="G76" s="2">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="H76" s="2">
-        <v>70.9</v>
+        <v>69.22</v>
       </c>
       <c r="I76" s="2">
-        <v>37.84</v>
+        <v>37.55</v>
       </c>
       <c r="J76" s="2">
-        <v>0.049651124253833445</v>
+        <v>0.047704556731006584</v>
       </c>
       <c r="K76" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L76" s="2">
         <v>-5</v>
       </c>
       <c r="M76" s="2">
-        <v>0.5426471326122533</v>
+        <v>0.560786232446177</v>
       </c>
       <c r="N76" s="2">
-        <v>59.73684166497032</v>
+        <v>60.69535392558103</v>
       </c>
       <c r="O76" s="2">
-        <v>97.59036144578313</v>
+        <v>98.79518072289156</v>
       </c>
       <c r="P76" s="2">
         <v>18.71809072120826</v>
       </c>
       <c r="Q76" s="2">
-        <v>68.19277108433735</v>
+        <v>68.3132530120482</v>
       </c>
       <c r="R76" s="2">
-        <v>60.903614457831324</v>
+        <v>61.26506024096387</v>
       </c>
       <c r="S76" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T76" s="2">
-        <v>12.31</v>
+        <v>12.67</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
@@ -6807,25 +6801,25 @@
         <v>20.481927710843372</v>
       </c>
       <c r="D77" s="2">
-        <v>15.619565217391303</v>
+        <v>15.521739130434781</v>
       </c>
       <c r="E77" s="2">
-        <v>-3.22</v>
+        <v>-3.54</v>
       </c>
       <c r="F77" s="2">
-        <v>0.1472074421521147</v>
+        <v>0.1790578903959238</v>
       </c>
       <c r="G77" s="2">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="H77" s="2">
-        <v>52.45</v>
+        <v>53.34</v>
       </c>
       <c r="I77" s="2">
-        <v>27.25</v>
+        <v>27.23</v>
       </c>
       <c r="J77" s="2">
-        <v>0.009958231834577187</v>
+        <v>0.008481528448144898</v>
       </c>
       <c r="K77" s="2" t="b">
         <v>0</v>
@@ -6834,28 +6828,28 @@
         <v>-2</v>
       </c>
       <c r="M77" s="2">
-        <v>0.1524839962366087</v>
+        <v>0.18295379414498347</v>
       </c>
       <c r="N77" s="2">
-        <v>20.72052802740585</v>
+        <v>22.912110095461667</v>
       </c>
       <c r="O77" s="2">
-        <v>77.10843373493977</v>
+        <v>80.72289156626506</v>
       </c>
       <c r="P77" s="2">
         <v>16.006637557486414</v>
       </c>
       <c r="Q77" s="2">
-        <v>56.506024096385545</v>
+        <v>57.34939759036145</v>
       </c>
       <c r="R77" s="2">
-        <v>51.02409638554217</v>
+        <v>52.108433734939766</v>
       </c>
       <c r="S77" s="2" t="s">
         <v>105</v>
       </c>
       <c r="T77" s="2">
-        <v>2.85</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
@@ -6872,22 +6866,22 @@
         <v>0.1824561403508772</v>
       </c>
       <c r="E78" s="2">
-        <v>0.9</v>
+        <v>0.32</v>
       </c>
       <c r="F78" s="2">
-        <v>0.22527682467135035</v>
+        <v>0.21869872829688078</v>
       </c>
       <c r="G78" s="2">
         <v>0.82</v>
       </c>
       <c r="H78" s="2">
-        <v>54.64</v>
+        <v>49.8</v>
       </c>
       <c r="I78" s="2">
-        <v>12.06</v>
+        <v>10.68</v>
       </c>
       <c r="J78" s="2">
-        <v>0.018585920400149204</v>
+        <v>0.017342721837614285</v>
       </c>
       <c r="K78" s="2" t="b">
         <v>0</v>
@@ -6896,28 +6890,28 @@
         <v>6</v>
       </c>
       <c r="M78" s="2">
-        <v>0.2173619935446094</v>
+        <v>0.21232361307114678</v>
       </c>
       <c r="N78" s="2">
-        <v>27.208327758205918</v>
+        <v>25.849091988078005</v>
       </c>
       <c r="O78" s="2">
-        <v>84.33734939759037</v>
+        <v>81.92771084337349</v>
       </c>
       <c r="P78" s="2">
         <v>11.616065285425229</v>
       </c>
       <c r="Q78" s="2">
-        <v>59.036144578313255</v>
+        <v>56.506024096385545</v>
       </c>
       <c r="R78" s="2">
-        <v>56.26506024096385</v>
+        <v>55.42168674698795</v>
       </c>
       <c r="S78" s="2" t="s">
         <v>99</v>
       </c>
       <c r="T78" s="2">
-        <v>16.39</v>
+        <v>15.54</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.25">
@@ -6934,52 +6928,52 @@
         <v>0.16652360515021455</v>
       </c>
       <c r="E79" s="2">
-        <v>1.05</v>
+        <v>0.86</v>
       </c>
       <c r="F79" s="2">
-        <v>0.09240598660319256</v>
+        <v>0.12308203179029567</v>
       </c>
       <c r="G79" s="2">
         <v>0.77</v>
       </c>
       <c r="H79" s="2">
-        <v>46.8</v>
+        <v>52.91</v>
       </c>
       <c r="I79" s="2">
-        <v>9.7</v>
+        <v>11.17</v>
       </c>
       <c r="J79" s="2">
-        <v>0.009593455670335713</v>
+        <v>0.008070070989143285</v>
       </c>
       <c r="K79" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L79" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M79" s="2">
-        <v>0.08229259127457911</v>
+        <v>0.11493605122408002</v>
       </c>
       <c r="N79" s="2">
-        <v>13.70138753120289</v>
+        <v>16.110335803371328</v>
       </c>
       <c r="O79" s="2">
-        <v>67.46987951807229</v>
+        <v>73.49397590361446</v>
       </c>
       <c r="P79" s="2">
         <v>6.707278396222185</v>
       </c>
       <c r="Q79" s="2">
-        <v>56.626506024096386</v>
+        <v>59.638554216867476</v>
       </c>
       <c r="R79" s="2">
-        <v>53.975903614457835</v>
+        <v>55.78313253012049</v>
       </c>
       <c r="S79" s="2" t="s">
         <v>103</v>
       </c>
       <c r="T79" s="2">
-        <v>3.55</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.25">
@@ -6996,22 +6990,22 @@
         <v>-0.9297343616109682</v>
       </c>
       <c r="E80" s="2">
-        <v>-0.75</v>
+        <v>-1.2</v>
       </c>
       <c r="F80" s="2">
-        <v>0.08852788455239721</v>
+        <v>0.08981467784137125</v>
       </c>
       <c r="G80" s="2">
         <v>1.01</v>
       </c>
       <c r="H80" s="2">
-        <v>48.18</v>
+        <v>52.62</v>
       </c>
       <c r="I80" s="2">
-        <v>10.78</v>
+        <v>11.6</v>
       </c>
       <c r="J80" s="2">
-        <v>0.007348897971501634</v>
+        <v>0.006967555741556304</v>
       </c>
       <c r="K80" s="2" t="b">
         <v>0</v>
@@ -7020,28 +7014,28 @@
         <v>111</v>
       </c>
       <c r="M80" s="2">
-        <v>0.08896759739277171</v>
+        <v>0.09016885090946758</v>
       </c>
       <c r="N80" s="2">
-        <v>14.368888143022144</v>
+        <v>13.633615771910081</v>
       </c>
       <c r="O80" s="2">
-        <v>68.67469879518072</v>
+        <v>67.46987951807229</v>
       </c>
       <c r="P80" s="2">
         <v>6.716293473999743</v>
       </c>
       <c r="Q80" s="2">
-        <v>55.06024096385542</v>
+        <v>57.59036144578313</v>
       </c>
       <c r="R80" s="2">
-        <v>52.71084337349397</v>
+        <v>52.46987951807228</v>
       </c>
       <c r="S80" s="2" t="s">
         <v>113</v>
       </c>
       <c r="T80" s="2">
-        <v>7.41</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.25">
@@ -7055,37 +7049,37 @@
         <v>75.90361445783132</v>
       </c>
       <c r="D81" s="2">
-        <v>-0.02293577981651388</v>
+        <v>-0.012614678899082707</v>
       </c>
       <c r="E81" s="2">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="F81" s="2">
-        <v>0.061762461772720836</v>
+        <v>0.07529213315532597</v>
       </c>
       <c r="G81" s="2">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="H81" s="2">
-        <v>58.94</v>
+        <v>61.4</v>
       </c>
       <c r="I81" s="2">
-        <v>14.73</v>
+        <v>16.04</v>
       </c>
       <c r="J81" s="2">
-        <v>0.011685449904914111</v>
+        <v>0.011834976203009067</v>
       </c>
       <c r="K81" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L81" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M81" s="2">
-        <v>0.06528016449571683</v>
+        <v>0.0777713446320003</v>
       </c>
       <c r="N81" s="2">
-        <v>12.000144853316655</v>
+        <v>12.393865144163373</v>
       </c>
       <c r="O81" s="2">
         <v>65.06024096385542</v>
@@ -7094,16 +7088,16 @@
         <v>12.706223591210087</v>
       </c>
       <c r="Q81" s="2">
-        <v>60.72289156626506</v>
+        <v>61.807228915662655</v>
       </c>
       <c r="R81" s="2">
-        <v>50.72289156626506</v>
+        <v>51.144578313253014</v>
       </c>
       <c r="S81" s="2" t="s">
         <v>106</v>
       </c>
       <c r="T81" s="2">
-        <v>-1.41</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.25">
@@ -7117,25 +7111,25 @@
         <v>92.7710843373494</v>
       </c>
       <c r="D82" s="1">
-        <v>-2.3390256152687092</v>
+        <v>-2.3370165745856353</v>
       </c>
       <c r="E82" s="1">
-        <v>2.43</v>
+        <v>2.31</v>
       </c>
       <c r="F82" s="1">
-        <v>-0.12841419419162076</v>
+        <v>-0.11245534943727947</v>
       </c>
       <c r="G82" s="1">
         <v>1.2</v>
       </c>
       <c r="H82" s="1">
-        <v>41</v>
+        <v>44.09</v>
       </c>
       <c r="I82" s="1">
-        <v>-1.5</v>
+        <v>-0.81</v>
       </c>
       <c r="J82" s="1">
-        <v>-0.0033444154604389876</v>
+        <v>-0.004296330421879677</v>
       </c>
       <c r="K82" s="1" t="b">
         <v>0</v>
@@ -7144,90 +7138,90 @@
         <v>177</v>
       </c>
       <c r="M82" s="1">
-        <v>-0.11961993738413079</v>
+        <v>-0.1053718880753528</v>
       </c>
       <c r="N82" s="1">
-        <v>-6.489865334668096</v>
+        <v>-5.920458126571948</v>
       </c>
       <c r="O82" s="1">
-        <v>21.686746987951807</v>
+        <v>28.915662650602407</v>
       </c>
       <c r="P82" s="1">
         <v>20.22353911360907</v>
       </c>
       <c r="Q82" s="1">
-        <v>43.373493975903614</v>
+        <v>44.33734939759036</v>
       </c>
       <c r="R82" s="1">
-        <v>31.325301204819272</v>
+        <v>33.25301204819277</v>
       </c>
       <c r="S82" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T82" s="1">
-        <v>-15.44</v>
+        <v>-13.52</v>
       </c>
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A83" s="3" t="s">
+      <c r="A83" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B83" s="3">
+      <c r="B83" s="1">
         <v>3.33</v>
       </c>
-      <c r="C83" s="3">
+      <c r="C83" s="1">
         <v>51.80722891566265</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="1">
         <v>1.7717717717717718</v>
       </c>
-      <c r="E83" s="3">
-        <v>0.26</v>
-      </c>
-      <c r="F83" s="3">
-        <v>-0.14946475666085596</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0.98</v>
-      </c>
-      <c r="H83" s="3">
-        <v>37.15</v>
-      </c>
-      <c r="I83" s="3">
-        <v>12.82</v>
-      </c>
-      <c r="J83" s="3">
-        <v>-0.007633760614858054</v>
-      </c>
-      <c r="K83" s="3" t="b">
+      <c r="E83" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="F83" s="1">
+        <v>-0.12472396540924859</v>
+      </c>
+      <c r="G83" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="H83" s="1">
+        <v>47.25</v>
+      </c>
+      <c r="I83" s="1">
+        <v>15.69</v>
+      </c>
+      <c r="J83" s="1">
+        <v>-0.00655843117640546</v>
+      </c>
+      <c r="K83" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L83" s="3">
-        <v>374</v>
-      </c>
-      <c r="M83" s="3">
-        <v>-0.15034418234160496</v>
-      </c>
-      <c r="N83" s="3">
-        <v>-9.56228983041552</v>
-      </c>
-      <c r="O83" s="3">
-        <v>15.66265060240964</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="L83" s="1">
+        <v>375</v>
+      </c>
+      <c r="M83" s="1">
+        <v>-0.12578648461353759</v>
+      </c>
+      <c r="N83" s="1">
+        <v>-7.96191778039042</v>
+      </c>
+      <c r="O83" s="1">
+        <v>24.096385542168676</v>
+      </c>
+      <c r="P83" s="1">
         <v>17.353844275841347</v>
       </c>
-      <c r="Q83" s="3">
-        <v>43.975903614457835</v>
-      </c>
-      <c r="R83" s="3">
-        <v>29.75903614457831</v>
-      </c>
-      <c r="S83" s="3" t="s">
+      <c r="Q83" s="1">
+        <v>48.43373493975904</v>
+      </c>
+      <c r="R83" s="1">
+        <v>32.53012048192771</v>
+      </c>
+      <c r="S83" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="T83" s="3">
-        <v>-26.89</v>
+      <c r="T83" s="1">
+        <v>-24.12</v>
       </c>
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.25">
@@ -7244,52 +7238,52 @@
         <v>-0.31902834008097164</v>
       </c>
       <c r="E84" s="1">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="F84" s="1">
-        <v>0.017694110055123793</v>
+        <v>0.015690017419081617</v>
       </c>
       <c r="G84" s="1">
         <v>0.95</v>
       </c>
       <c r="H84" s="1">
-        <v>36.77</v>
+        <v>47.51</v>
       </c>
       <c r="I84" s="1">
-        <v>9.39</v>
+        <v>11.5</v>
       </c>
       <c r="J84" s="1">
-        <v>0.006631107241643684</v>
+        <v>0.005081454781607029</v>
       </c>
       <c r="K84" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L84" s="1">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M84" s="1">
-        <v>0.015495545853251302</v>
+        <v>0.01391915207859995</v>
       </c>
       <c r="N84" s="1">
-        <v>7.021682989070106</v>
+        <v>6.008645888823329</v>
       </c>
       <c r="O84" s="1">
-        <v>46.98795180722892</v>
+        <v>53.01204819277109</v>
       </c>
       <c r="P84" s="1">
-        <v>8.331725352403268</v>
+        <v>8.441182677506358</v>
       </c>
       <c r="Q84" s="1">
-        <v>47.95180722891566</v>
+        <v>52.7710843373494</v>
       </c>
       <c r="R84" s="1">
-        <v>44.397590361445786</v>
+        <v>46.20481927710844</v>
       </c>
       <c r="S84" s="1" t="s">
         <v>104</v>
       </c>
       <c r="T84" s="1">
-        <v>-2.37</v>
+        <v>-0.56</v>
       </c>
     </row>
   </sheetData>
@@ -7316,7 +7310,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>41.024096385542165</v>
+        <v>44.518072289156635</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -7324,7 +7318,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>49.096385542168676</v>
+        <v>46.566265060240966</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7340,7 +7334,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>34.21686746987952</v>
+        <v>32.5301204819277</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -7348,7 +7342,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>26.98795180722892</v>
+        <v>32.40963855421687</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7356,7 +7350,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>53.55421686746989</v>
+        <v>54.63855421686748</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -7364,7 +7358,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>37.7710843373494</v>
+        <v>37.048192771084345</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -7372,7 +7366,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>58.67469879518071</v>
+        <v>58.91566265060241</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -7380,7 +7374,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>42.4698795180723</v>
+        <v>45.12048192771084</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -7396,7 +7390,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>62.65060240963855</v>
+        <v>62.7710843373494</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -7404,7 +7398,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>39.397590361445786</v>
+        <v>39.03614457831326</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -7412,7 +7406,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>60.12048192771084</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -7420,7 +7414,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>22.048192771084338</v>
+        <v>20.662650602409645</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -7428,7 +7422,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>19.036144578313255</v>
+        <v>19.879518072289155</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -7436,7 +7430,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>28.31325301204819</v>
+        <v>28.67469879518072</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -7452,7 +7446,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>51.68674698795181</v>
+        <v>51.32530120481928</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -7468,7 +7462,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>21.626506024096386</v>
+        <v>20.903614457831324</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -7476,7 +7470,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>38.855421686746986</v>
+        <v>39.45783132530121</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -7484,7 +7478,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>50.66265060240964</v>
+        <v>51.506024096385545</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -7492,7 +7486,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>31.265060240963855</v>
+        <v>30.542168674698793</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -7500,7 +7494,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>17.7710843373494</v>
+        <v>6.80722891566265</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -7508,7 +7502,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>-3.2530120481927716</v>
+        <v>-3.1325301204819285</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -7524,7 +7518,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>36.084337349397586</v>
+        <v>36.325301204819276</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -7532,7 +7526,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>46.3855421686747</v>
+        <v>45.06024096385543</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -7540,7 +7534,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>45.78313253012048</v>
+        <v>46.506024096385545</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -7548,7 +7542,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>39.75903614457831</v>
+        <v>40.12048192771084</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -7556,7 +7550,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>34.27710843373494</v>
+        <v>32.22891566265061</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -7564,7 +7558,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>57.710843373493965</v>
+        <v>59.63855421686747</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -7572,7 +7566,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>31.02409638554217</v>
+        <v>33.674698795180724</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -7580,7 +7574,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>38.433734939759034</v>
+        <v>40.12048192771084</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -7588,7 +7582,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>50.06024096385542</v>
+        <v>49.75903614457832</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -7596,7 +7590,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>56.08433734939759</v>
+        <v>56.44578313253012</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -7604,7 +7598,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>63.01204819277108</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -7612,7 +7606,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>45.54216867469879</v>
+        <v>43.13253012048193</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -7628,7 +7622,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>15.060240963855426</v>
+        <v>14.09638554216868</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -7636,7 +7630,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>29.578313253012045</v>
+        <v>31.746987951807228</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -7644,7 +7638,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>56.144578313253014</v>
+        <v>57.349397590361455</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -7652,7 +7646,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>52.71084337349398</v>
+        <v>53.6144578313253</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -7660,7 +7654,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>37.95180722891566</v>
+        <v>41.325301204819276</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -7668,7 +7662,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>33.795180722891565</v>
+        <v>28.012048192771083</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -7676,7 +7670,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>51.144578313253014</v>
+        <v>48.73493975903615</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -7684,7 +7678,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>55.60240963855423</v>
+        <v>58.13253012048192</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -7692,7 +7686,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>44.81927710843374</v>
+        <v>51.20481927710843</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -7700,7 +7694,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>16.987951807228914</v>
+        <v>18.192771084337352</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -7716,7 +7710,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>41.144578313253014</v>
+        <v>44.1566265060241</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -7724,7 +7718,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>32.168674698795186</v>
+        <v>31.445783132530117</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -7732,7 +7726,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>41.74698795180723</v>
+        <v>43.43373493975904</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -7740,7 +7734,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>27.28915662650602</v>
+        <v>27.89156626506025</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -7748,7 +7742,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>41.686746987951814</v>
+        <v>40.36144578313253</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -7756,7 +7750,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>27.349397590361445</v>
+        <v>25.180722891566266</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -7764,7 +7758,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>11.626506024096383</v>
+        <v>11.385542168674696</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -7772,7 +7766,7 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>52.168674698795186</v>
+        <v>51.9277108433735</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -7780,7 +7774,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>51.38554216867469</v>
+        <v>51.144578313253</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -7788,7 +7782,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>46.20481927710843</v>
+        <v>41.626506024096386</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -7796,7 +7790,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>37.83132530120482</v>
+        <v>38.91566265060241</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -7804,7 +7798,7 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>31.566265060240962</v>
+        <v>33.85542168674699</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -7812,7 +7806,7 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>60.18072289156626</v>
+        <v>59.81927710843374</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -7820,7 +7814,7 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>31.506024096385538</v>
+        <v>25.361445783132524</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -7828,7 +7822,7 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>41.08433734939759</v>
+        <v>40.361445783132524</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -7836,7 +7830,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>45.30120481927711</v>
+        <v>50.36144578313253</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -7844,7 +7838,7 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>43.67469879518072</v>
+        <v>44.87951807228916</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -7852,7 +7846,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>56.50602409638554</v>
+        <v>55.18072289156626</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -7860,7 +7854,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>27.83132530120482</v>
+        <v>29.759036144578317</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -7868,7 +7862,7 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>56.86746987951808</v>
+        <v>59.75903614457832</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -7884,7 +7878,7 @@
         <v>72</v>
       </c>
       <c r="B73">
-        <v>29.638554216867476</v>
+        <v>29.15662650602409</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -7892,7 +7886,7 @@
         <v>73</v>
       </c>
       <c r="B74">
-        <v>22.89156626506024</v>
+        <v>23.493975903614462</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -7900,7 +7894,7 @@
         <v>120</v>
       </c>
       <c r="B75">
-        <v>38.3132530120482</v>
+        <v>23.734939759036145</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -7908,7 +7902,7 @@
         <v>122</v>
       </c>
       <c r="B76">
-        <v>60.903614457831324</v>
+        <v>61.26506024096387</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -7916,7 +7910,7 @@
         <v>123</v>
       </c>
       <c r="B77">
-        <v>51.02409638554217</v>
+        <v>52.108433734939766</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -7924,7 +7918,7 @@
         <v>124</v>
       </c>
       <c r="B78">
-        <v>56.26506024096385</v>
+        <v>55.42168674698795</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -7932,7 +7926,7 @@
         <v>125</v>
       </c>
       <c r="B79">
-        <v>53.975903614457835</v>
+        <v>55.78313253012049</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -7940,7 +7934,7 @@
         <v>126</v>
       </c>
       <c r="B80">
-        <v>52.71084337349397</v>
+        <v>52.46987951807228</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -7948,7 +7942,7 @@
         <v>127</v>
       </c>
       <c r="B81">
-        <v>50.72289156626506</v>
+        <v>51.144578313253014</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -7956,7 +7950,7 @@
         <v>128</v>
       </c>
       <c r="B82">
-        <v>31.325301204819272</v>
+        <v>33.25301204819277</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -7964,7 +7958,7 @@
         <v>129</v>
       </c>
       <c r="B83">
-        <v>29.75903614457831</v>
+        <v>32.53012048192771</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -7972,7 +7966,7 @@
         <v>131</v>
       </c>
       <c r="B84">
-        <v>44.397590361445786</v>
+        <v>46.20481927710844</v>
       </c>
     </row>
   </sheetData>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="232">
   <si>
     <t>Ticker</t>
   </si>
@@ -175,6 +175,9 @@
     <t>CHPT</t>
   </si>
   <si>
+    <t>LULU</t>
+  </si>
+  <si>
     <t>MMM</t>
   </si>
   <si>
@@ -331,21 +334,24 @@
     <t>2026-09-01</t>
   </si>
   <si>
+    <t>2026-09-14</t>
+  </si>
+  <si>
+    <t>2027-07-23</t>
+  </si>
+  <si>
+    <t>2027-08-06</t>
+  </si>
+  <si>
+    <t>2027-07-30</t>
+  </si>
+  <si>
+    <t>2027-07-29</t>
+  </si>
+  <si>
     <t>2027-07-28</t>
   </si>
   <si>
-    <t>2027-07-23</t>
-  </si>
-  <si>
-    <t>2027-08-06</t>
-  </si>
-  <si>
-    <t>2027-07-30</t>
-  </si>
-  <si>
-    <t>2027-07-29</t>
-  </si>
-  <si>
     <t>2027-08-10</t>
   </si>
   <si>
@@ -421,7 +427,7 @@
     <t>_date_</t>
   </si>
   <si>
-    <t>2026-09-14</t>
+    <t>2026-09-15</t>
   </si>
   <si>
     <t>Criteria</t>
@@ -682,22 +688,31 @@
     <t>Momentum Breakout, Market Leader, Institutional Buying</t>
   </si>
   <si>
+    <t>Momentum Breakout, Market Leader, Volume Spike</t>
+  </si>
+  <si>
     <t>Momentum Breakout, Market Leader</t>
   </si>
   <si>
     <t>Institutional Buying</t>
   </si>
   <si>
+    <t>Momentum Breakout, Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Institutional Buying</t>
+  </si>
+  <si>
     <t>Volume Spike, Institutional Buying</t>
   </si>
   <si>
-    <t>Momentum Breakout, Institutional Buying</t>
+    <t>Momentum Breakout, Volume Spike</t>
+  </si>
+  <si>
+    <t>Momentum Breakout</t>
   </si>
   <si>
     <t>Volume Spike</t>
-  </si>
-  <si>
-    <t>Momentum Breakout</t>
   </si>
   <si>
     <t>Momentum Breakout, Market Leader, Volume Spike, Institutional Buying</t>
@@ -1095,7 +1110,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A52"/>
+  <dimension ref="A1:A53"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -1356,6 +1371,11 @@
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1374,51 +1394,51 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="B2">
-        <v>62.7710843373494</v>
+        <v>63.63095238095239</v>
       </c>
       <c r="C2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>122</v>
+        <v>11</v>
       </c>
       <c r="B3">
-        <v>61.26506024096387</v>
+        <v>62.67857142857142</v>
       </c>
       <c r="C3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>124</v>
       </c>
       <c r="B4">
-        <v>60</v>
+        <v>61.07142857142858</v>
       </c>
       <c r="C4" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="B5">
-        <v>60</v>
+        <v>60.892857142857146</v>
       </c>
       <c r="C5" t="s">
         <v>221</v>
@@ -1426,10 +1446,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="B6">
-        <v>59.81927710843374</v>
+        <v>60.476190476190474</v>
       </c>
       <c r="C6" t="s">
         <v>221</v>
@@ -1437,87 +1457,87 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="B7">
-        <v>59.75903614457832</v>
+        <v>60.05952380952382</v>
       </c>
       <c r="C7" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="B8">
-        <v>59.63855421686747</v>
+        <v>60.00000000000001</v>
       </c>
       <c r="C8" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="B9">
-        <v>58.91566265060241</v>
+        <v>59.82142857142858</v>
       </c>
       <c r="C9" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B10">
-        <v>58.13253012048192</v>
+        <v>59.34523809523809</v>
       </c>
       <c r="C10" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="B11">
-        <v>57.349397590361455</v>
+        <v>58.45238095238095</v>
       </c>
       <c r="C11" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>127</v>
       </c>
       <c r="B12">
-        <v>57.168674698795186</v>
+        <v>55.59523809523809</v>
       </c>
       <c r="C12" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>126</v>
       </c>
       <c r="B13">
-        <v>56.44578313253012</v>
+        <v>55.35714285714287</v>
       </c>
       <c r="C13" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>125</v>
+        <v>19</v>
       </c>
       <c r="B14">
-        <v>55.78313253012049</v>
+        <v>55.11904761904761</v>
       </c>
       <c r="C14" t="s">
         <v>221</v>
@@ -1525,10 +1545,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="B15">
-        <v>55.42168674698795</v>
+        <v>55</v>
       </c>
       <c r="C15" t="s">
         <v>223</v>
@@ -1539,40 +1559,40 @@
         <v>3</v>
       </c>
       <c r="B16">
-        <v>54.879518072289166</v>
+        <v>54.76190476190476</v>
       </c>
       <c r="C16" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B17">
-        <v>54.63855421686748</v>
+        <v>54.22619047619048</v>
       </c>
       <c r="C17" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="B18">
-        <v>54.39759036144578</v>
+        <v>54.16666666666668</v>
       </c>
       <c r="C18" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B19">
-        <v>53.6144578313253</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="C19" t="s">
         <v>224</v>
@@ -1580,266 +1600,266 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B20">
-        <v>52.46987951807228</v>
+        <v>52.73809523809524</v>
       </c>
       <c r="C20" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B21">
-        <v>52.108433734939766</v>
+        <v>52.738095238095234</v>
       </c>
       <c r="C21" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="B22">
-        <v>51.9277108433735</v>
+        <v>52.5</v>
       </c>
       <c r="C22" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>128</v>
       </c>
       <c r="B23">
-        <v>51.506024096385545</v>
+        <v>52.32142857142857</v>
       </c>
       <c r="C23" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>127</v>
+        <v>60</v>
       </c>
       <c r="B24">
-        <v>51.144578313253014</v>
+        <v>51.904761904761905</v>
       </c>
       <c r="C24" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="B25">
-        <v>51.144578313253</v>
+        <v>51.785714285714285</v>
       </c>
       <c r="C25" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="B26">
-        <v>48.73493975903615</v>
+        <v>48.392857142857146</v>
       </c>
       <c r="C26" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="B27">
-        <v>46.566265060240966</v>
+        <v>48.392857142857146</v>
       </c>
       <c r="C27" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="B28">
-        <v>46.506024096385545</v>
+        <v>47.91666666666667</v>
       </c>
       <c r="C28" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>131</v>
+        <v>68</v>
       </c>
       <c r="B29">
-        <v>46.20481927710844</v>
+        <v>47.261904761904766</v>
       </c>
       <c r="C29" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B30">
-        <v>46.02409638554217</v>
+        <v>46.785714285714285</v>
       </c>
       <c r="C30" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>28</v>
+        <v>133</v>
       </c>
       <c r="B31">
-        <v>45.06024096385543</v>
+        <v>46.36904761904763</v>
       </c>
       <c r="C31" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="B32">
-        <v>44.87951807228916</v>
+        <v>46.13095238095238</v>
       </c>
       <c r="C32" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B33">
-        <v>44.81927710843374</v>
+        <v>44.28571428571429</v>
       </c>
       <c r="C33" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="B34">
-        <v>44.1566265060241</v>
+        <v>43.214285714285715</v>
       </c>
       <c r="C34" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B35">
-        <v>43.43373493975904</v>
+        <v>42.55952380952381</v>
       </c>
       <c r="C35" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="B36">
-        <v>41.626506024096386</v>
+        <v>41.8452380952381</v>
       </c>
       <c r="C36" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B37">
-        <v>41.325301204819276</v>
+        <v>41.84523809523809</v>
       </c>
       <c r="C37" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B38">
-        <v>40.36144578313253</v>
+        <v>41.488095238095234</v>
       </c>
       <c r="C38" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B39">
-        <v>40.361445783132524</v>
+        <v>40.89285714285714</v>
       </c>
       <c r="C39" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B40">
-        <v>40.12048192771084</v>
+        <v>39.88095238095238</v>
       </c>
       <c r="C40" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B41">
-        <v>39.45783132530121</v>
+        <v>39.3452380952381</v>
       </c>
       <c r="C41" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="B42">
-        <v>39.03614457831326</v>
+        <v>39.285714285714285</v>
       </c>
       <c r="C42" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="B43">
-        <v>38.91566265060241</v>
+        <v>38.69047619047619</v>
       </c>
       <c r="C43" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -1847,87 +1867,87 @@
         <v>7</v>
       </c>
       <c r="B44">
-        <v>37.048192771084345</v>
+        <v>38.51190476190476</v>
       </c>
       <c r="C44" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B45">
-        <v>36.325301204819276</v>
+        <v>38.33333333333333</v>
       </c>
       <c r="C45" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="B46">
-        <v>33.85542168674699</v>
+        <v>37.738095238095234</v>
       </c>
       <c r="C46" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="B47">
-        <v>33.674698795180724</v>
+        <v>37.67857142857143</v>
       </c>
       <c r="C47" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>128</v>
+        <v>66</v>
       </c>
       <c r="B48">
-        <v>33.25301204819277</v>
+        <v>36.78571428571429</v>
       </c>
       <c r="C48" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>129</v>
+        <v>63</v>
       </c>
       <c r="B49">
-        <v>32.53012048192771</v>
+        <v>35.05952380952382</v>
       </c>
       <c r="C49" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>4</v>
+        <v>131</v>
       </c>
       <c r="B50">
-        <v>32.5301204819277</v>
+        <v>33.988095238095234</v>
       </c>
       <c r="C50" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="B51">
-        <v>32.22891566265061</v>
+        <v>32.97619047619047</v>
       </c>
       <c r="C51" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -1948,127 +1968,127 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -2079,7 +2099,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T84"/>
+  <dimension ref="A1:T85"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -2087,61 +2107,61 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="R1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="S1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
@@ -2152,28 +2172,28 @@
         <v>7.77</v>
       </c>
       <c r="C2" s="1">
-        <v>67.46987951807229</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="D2" s="1">
-        <v>-1.9922779922779925</v>
+        <v>-1.9909909909909909</v>
       </c>
       <c r="E2" s="1">
         <v>-2.08</v>
       </c>
       <c r="F2" s="1">
-        <v>0.11407702165707825</v>
+        <v>0.10627341897372927</v>
       </c>
       <c r="G2" s="1">
         <v>0.21</v>
       </c>
       <c r="H2" s="1">
-        <v>65.99</v>
+        <v>61.46</v>
       </c>
       <c r="I2" s="1">
-        <v>15.94</v>
+        <v>13.81</v>
       </c>
       <c r="J2" s="1">
-        <v>0.017365364677044127</v>
+        <v>0.018109264215455927</v>
       </c>
       <c r="K2" s="1" t="b">
         <v>0</v>
@@ -2182,28 +2202,28 @@
         <v>-457</v>
       </c>
       <c r="M2" s="1">
-        <v>0.08609734927746793</v>
+        <v>0.08410284460030737</v>
       </c>
       <c r="N2" s="1">
-        <v>13.226465608710125</v>
+        <v>12.291686279451223</v>
       </c>
       <c r="O2" s="1">
-        <v>66.26506024096386</v>
+        <v>69.04761904761905</v>
       </c>
       <c r="P2" s="1">
         <v>16.29652721982991</v>
       </c>
       <c r="Q2" s="1">
-        <v>56.144578313253014</v>
+        <v>56.07142857142857</v>
       </c>
       <c r="R2" s="1">
-        <v>44.518072289156635</v>
+        <v>46.07142857142856</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T2" s="1">
-        <v>24.7</v>
+        <v>26.25</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -2214,58 +2234,58 @@
         <v>3.9</v>
       </c>
       <c r="C3" s="1">
-        <v>54.21686746987952</v>
+        <v>53.57142857142857</v>
       </c>
       <c r="D3" s="1">
-        <v>26.664102564102564</v>
+        <v>26.710256410256406</v>
       </c>
       <c r="E3" s="1">
         <v>3.63</v>
       </c>
       <c r="F3" s="1">
-        <v>-0.041915882124413245</v>
+        <v>-0.11584733501843623</v>
       </c>
       <c r="G3" s="1">
         <v>2.48</v>
       </c>
       <c r="H3" s="1">
-        <v>50.71</v>
+        <v>50.65</v>
       </c>
       <c r="I3" s="1">
-        <v>40.72</v>
+        <v>40.14</v>
       </c>
       <c r="J3" s="1">
-        <v>-0.007645872041769857</v>
+        <v>-0.006437339770132733</v>
       </c>
       <c r="K3" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="1">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="M3" s="1">
-        <v>0.010501731953844073</v>
+        <v>-0.07431258809101293</v>
       </c>
       <c r="N3" s="1">
-        <v>5.666903876347738</v>
+        <v>-3.549856989680803</v>
       </c>
       <c r="O3" s="1">
-        <v>51.80722891566265</v>
+        <v>39.285714285714285</v>
       </c>
       <c r="P3" s="1">
         <v>26.053946839070953</v>
       </c>
       <c r="Q3" s="1">
-        <v>61.80722891566265</v>
+        <v>62.26190476190476</v>
       </c>
       <c r="R3" s="1">
-        <v>46.566265060240966</v>
+        <v>43.214285714285715</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="T3" s="1">
-        <v>-20.51</v>
+        <v>-23.86</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -2276,7 +2296,7 @@
         <v>-3.17</v>
       </c>
       <c r="C4" s="2">
-        <v>10.843373493975903</v>
+        <v>10.714285714285714</v>
       </c>
       <c r="D4" s="2">
         <v>12.41640378548896</v>
@@ -2285,19 +2305,19 @@
         <v>6.35</v>
       </c>
       <c r="F4" s="2">
-        <v>0.30965016967214226</v>
+        <v>0.3791065423867275</v>
       </c>
       <c r="G4" s="2">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="H4" s="2">
-        <v>54.67</v>
+        <v>53.13</v>
       </c>
       <c r="I4" s="2">
-        <v>49.81</v>
+        <v>48.32</v>
       </c>
       <c r="J4" s="2">
-        <v>0.028429868129135224</v>
+        <v>0.02566850265165403</v>
       </c>
       <c r="K4" s="2" t="b">
         <v>0</v>
@@ -2306,28 +2326,28 @@
         <v>179</v>
       </c>
       <c r="M4" s="2">
-        <v>0.32240040012361026</v>
+        <v>0.3889289487546992</v>
       </c>
       <c r="N4" s="2">
-        <v>36.856770693324364</v>
+        <v>42.774296694890424</v>
       </c>
       <c r="O4" s="2">
-        <v>93.97590361445783</v>
+        <v>94.04761904761905</v>
       </c>
       <c r="P4" s="2">
         <v>19.349659482175007</v>
       </c>
       <c r="Q4" s="2">
-        <v>61.20481927710844</v>
+        <v>59.642857142857146</v>
       </c>
       <c r="R4" s="2">
-        <v>54.879518072289166</v>
+        <v>54.76190476190476</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T4" s="2">
-        <v>6.53</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -2338,7 +2358,7 @@
         <v>1.08</v>
       </c>
       <c r="C5" s="1">
-        <v>39.75903614457831</v>
+        <v>39.285714285714285</v>
       </c>
       <c r="D5" s="1">
         <v>29.574074074074076</v>
@@ -2347,19 +2367,19 @@
         <v>1.69</v>
       </c>
       <c r="F5" s="1">
-        <v>-0.16285150162971704</v>
+        <v>-0.18112513184895096</v>
       </c>
       <c r="G5" s="1">
         <v>1.91</v>
       </c>
       <c r="H5" s="1">
-        <v>51.36</v>
+        <v>50.65</v>
       </c>
       <c r="I5" s="1">
-        <v>-10.03</v>
+        <v>-10.35</v>
       </c>
       <c r="J5" s="1">
-        <v>-0.010800052780961076</v>
+        <v>-0.011563696848779472</v>
       </c>
       <c r="K5" s="1" t="b">
         <v>0</v>
@@ -2368,28 +2388,28 @@
         <v>140</v>
       </c>
       <c r="M5" s="1">
-        <v>-0.1306217524329507</v>
+        <v>-0.15558687529222448</v>
       </c>
       <c r="N5" s="1">
-        <v>-8.445444562331742</v>
+        <v>-11.677285709801952</v>
       </c>
       <c r="O5" s="1">
-        <v>22.89156626506024</v>
+        <v>23.809523809523807</v>
       </c>
       <c r="P5" s="1">
         <v>33.002444654975626</v>
       </c>
       <c r="Q5" s="1">
-        <v>50.24096385542168</v>
+        <v>49.642857142857146</v>
       </c>
       <c r="R5" s="1">
-        <v>32.5301204819277</v>
+        <v>32.797619047619044</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="T5" s="1">
-        <v>-13.45</v>
+        <v>-13.18</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -2400,7 +2420,7 @@
         <v>3.17</v>
       </c>
       <c r="C6" s="1">
-        <v>49.39759036144578</v>
+        <v>48.80952380952381</v>
       </c>
       <c r="D6" s="1">
         <v>0.8864353312302841</v>
@@ -2409,49 +2429,49 @@
         <v>-1.87</v>
       </c>
       <c r="F6" s="1">
-        <v>-0.11503668040004339</v>
+        <v>-0.05562068915255862</v>
       </c>
       <c r="G6" s="1">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H6" s="1">
-        <v>50.17</v>
+        <v>53.97</v>
       </c>
       <c r="I6" s="1">
-        <v>-9.29</v>
+        <v>-7.33</v>
       </c>
       <c r="J6" s="1">
-        <v>0.005413502775150525</v>
+        <v>0.004162236323503007</v>
       </c>
       <c r="K6" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L6" s="1">
-        <v>-206</v>
+        <v>-205</v>
       </c>
       <c r="M6" s="1">
-        <v>-0.09378629631426338</v>
+        <v>-0.03906291841797771</v>
       </c>
       <c r="N6" s="1">
-        <v>-4.7618989504630065</v>
+        <v>-0.024890022377279178</v>
       </c>
       <c r="O6" s="1">
-        <v>34.93975903614458</v>
+        <v>46.42857142857143</v>
       </c>
       <c r="P6" s="1">
-        <v>30.53129157318417</v>
+        <v>28.714544797168166</v>
       </c>
       <c r="Q6" s="1">
-        <v>46.626506024096386</v>
+        <v>48.92857142857143</v>
       </c>
       <c r="R6" s="1">
-        <v>32.40963855421687</v>
+        <v>36.36904761904762</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="T6" s="1">
-        <v>13.32</v>
+        <v>17.28</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -2462,28 +2482,28 @@
         <v>7.91</v>
       </c>
       <c r="C7" s="2">
-        <v>69.87951807228916</v>
+        <v>69.04761904761905</v>
       </c>
       <c r="D7" s="2">
-        <v>7.797724399494312</v>
+        <v>7.79646017699115</v>
       </c>
       <c r="E7" s="2">
         <v>0.51</v>
       </c>
       <c r="F7" s="2">
-        <v>-0.023871474132499473</v>
+        <v>-0.045212461319663694</v>
       </c>
       <c r="G7" s="2">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="H7" s="2">
-        <v>45.45</v>
+        <v>44.26</v>
       </c>
       <c r="I7" s="2">
-        <v>7.81</v>
+        <v>6.84</v>
       </c>
       <c r="J7" s="2">
-        <v>0.012912507978848907</v>
+        <v>0.011113833428752447</v>
       </c>
       <c r="K7" s="2" t="b">
         <v>0</v>
@@ -2492,28 +2512,28 @@
         <v>178</v>
       </c>
       <c r="M7" s="2">
-        <v>0.01933764017525319</v>
+        <v>-0.01069371894079163</v>
       </c>
       <c r="N7" s="2">
-        <v>6.550494698488644</v>
+        <v>2.8120299253413243</v>
       </c>
       <c r="O7" s="2">
-        <v>56.62650602409639</v>
+        <v>50</v>
       </c>
       <c r="P7" s="2">
         <v>19.398494070050486</v>
       </c>
       <c r="Q7" s="2">
-        <v>65.18072289156628</v>
+        <v>65</v>
       </c>
       <c r="R7" s="2">
-        <v>54.63855421686748</v>
+        <v>52.5</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T7" s="2">
-        <v>6.22</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -2524,28 +2544,28 @@
         <v>15.55</v>
       </c>
       <c r="C8" s="1">
-        <v>84.33734939759037</v>
+        <v>84.52380952380952</v>
       </c>
       <c r="D8" s="1">
-        <v>-0.1254019292604502</v>
+        <v>-0.1209003215434084</v>
       </c>
       <c r="E8" s="1">
         <v>2.66</v>
       </c>
       <c r="F8" s="1">
-        <v>-0.09759926742763378</v>
+        <v>-0.08899213415981173</v>
       </c>
       <c r="G8" s="1">
         <v>0.61</v>
       </c>
       <c r="H8" s="1">
-        <v>36.54</v>
+        <v>38.71</v>
       </c>
       <c r="I8" s="1">
-        <v>7.6</v>
+        <v>8.04</v>
       </c>
       <c r="J8" s="1">
-        <v>-0.007134084901922103</v>
+        <v>-0.008278073861432799</v>
       </c>
       <c r="K8" s="1" t="b">
         <v>1</v>
@@ -2554,28 +2574,28 @@
         <v>361</v>
       </c>
       <c r="M8" s="1">
-        <v>-0.11141201708339077</v>
+        <v>-0.09993710125555166</v>
       </c>
       <c r="N8" s="1">
-        <v>-6.524471027375747</v>
+        <v>-6.112308306134675</v>
       </c>
       <c r="O8" s="1">
-        <v>26.506024096385545</v>
+        <v>30.952380952380953</v>
       </c>
       <c r="P8" s="1">
         <v>13.122495465725093</v>
       </c>
       <c r="Q8" s="1">
-        <v>45.78313253012048</v>
+        <v>47.619047619047606</v>
       </c>
       <c r="R8" s="1">
-        <v>37.048192771084345</v>
+        <v>38.51190476190476</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="T8" s="1">
-        <v>-22.71</v>
+        <v>-21.24</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -2586,28 +2606,28 @@
         <v>1.17</v>
       </c>
       <c r="C9" s="2">
-        <v>40.963855421686745</v>
+        <v>40.476190476190474</v>
       </c>
       <c r="D9" s="2">
-        <v>35.8974358974359</v>
+        <v>35.82905982905983</v>
       </c>
       <c r="E9" s="2">
         <v>2.97</v>
       </c>
       <c r="F9" s="2">
-        <v>0.20801386529729005</v>
+        <v>0.2981570975269442</v>
       </c>
       <c r="G9" s="2">
         <v>1.61</v>
       </c>
       <c r="H9" s="2">
-        <v>49.98</v>
+        <v>51.52</v>
       </c>
       <c r="I9" s="2">
-        <v>11.01</v>
+        <v>12.54</v>
       </c>
       <c r="J9" s="2">
-        <v>0.036210567407572024</v>
+        <v>0.03281094613323919</v>
       </c>
       <c r="K9" s="2" t="b">
         <v>0</v>
@@ -2616,28 +2636,28 @@
         <v>-113</v>
       </c>
       <c r="M9" s="2">
-        <v>0.22961842245116637</v>
+        <v>0.3152761486254092</v>
       </c>
       <c r="N9" s="2">
-        <v>27.57857292607997</v>
+        <v>35.40901668196142</v>
       </c>
       <c r="O9" s="2">
-        <v>86.74698795180723</v>
+        <v>90.47619047619048</v>
       </c>
       <c r="P9" s="2">
         <v>33.227512780245505</v>
       </c>
       <c r="Q9" s="2">
-        <v>67.59036144578313</v>
+        <v>69.28571428571429</v>
       </c>
       <c r="R9" s="2">
-        <v>58.91566265060241</v>
+        <v>60.05952380952382</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T9" s="2">
-        <v>31.54</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -2648,28 +2668,28 @@
         <v>4.85</v>
       </c>
       <c r="C10" s="1">
-        <v>59.036144578313255</v>
+        <v>58.333333333333336</v>
       </c>
       <c r="D10" s="1">
-        <v>0.7319587628865981</v>
+        <v>0.7463917525773198</v>
       </c>
       <c r="E10" s="1">
         <v>0.08</v>
       </c>
       <c r="F10" s="1">
-        <v>0.0008470689437733714</v>
+        <v>0.03514550148048769</v>
       </c>
       <c r="G10" s="1">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="H10" s="1">
-        <v>54.83</v>
+        <v>55.82</v>
       </c>
       <c r="I10" s="1">
-        <v>2.78</v>
+        <v>3.46</v>
       </c>
       <c r="J10" s="1">
-        <v>0.007814803125732838</v>
+        <v>0.008165217096187226</v>
       </c>
       <c r="K10" s="1" t="b">
         <v>0</v>
@@ -2678,28 +2698,28 @@
         <v>-51</v>
       </c>
       <c r="M10" s="1">
-        <v>0.015722337803819375</v>
+        <v>0.046651748940111704</v>
       </c>
       <c r="N10" s="1">
-        <v>6.188964461345262</v>
+        <v>8.54657671343166</v>
       </c>
       <c r="O10" s="1">
-        <v>54.21686746987952</v>
+        <v>61.904761904761905</v>
       </c>
       <c r="P10" s="1">
         <v>14.568379622257217</v>
       </c>
       <c r="Q10" s="1">
-        <v>54.6987951807229</v>
+        <v>55</v>
       </c>
       <c r="R10" s="1">
-        <v>45.12048192771084</v>
+        <v>47.857142857142854</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T10" s="1">
-        <v>9.57</v>
+        <v>12.31</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -2710,28 +2730,28 @@
         <v>-1.01</v>
       </c>
       <c r="C11" s="2">
-        <v>18.072289156626507</v>
+        <v>17.857142857142858</v>
       </c>
       <c r="D11" s="2">
-        <v>46.702970297029694</v>
+        <v>46.61386138613861</v>
       </c>
       <c r="E11" s="2">
         <v>2.19</v>
       </c>
       <c r="F11" s="2">
-        <v>0.3014712260383675</v>
+        <v>0.4918834716303588</v>
       </c>
       <c r="G11" s="2">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="H11" s="2">
-        <v>50.37</v>
+        <v>58.63</v>
       </c>
       <c r="I11" s="2">
-        <v>26.74</v>
+        <v>37.45</v>
       </c>
       <c r="J11" s="2">
-        <v>0.01637532525447152</v>
+        <v>0.016475646770997953</v>
       </c>
       <c r="K11" s="2" t="b">
         <v>0</v>
@@ -2740,28 +2760,28 @@
         <v>40</v>
       </c>
       <c r="M11" s="2">
-        <v>0.2919085531997665</v>
+        <v>0.48374490635403933</v>
       </c>
       <c r="N11" s="2">
-        <v>33.80758600093998</v>
+        <v>52.25589245482441</v>
       </c>
       <c r="O11" s="2">
-        <v>92.7710843373494</v>
+        <v>96.42857142857143</v>
       </c>
       <c r="P11" s="2">
         <v>21.2185970476566</v>
       </c>
       <c r="Q11" s="2">
-        <v>60.8433734939759</v>
+        <v>64.16666666666667</v>
       </c>
       <c r="R11" s="2">
-        <v>57.168674698795186</v>
+        <v>58.45238095238095</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T11" s="2">
-        <v>5.52</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -2772,28 +2792,28 @@
         <v>-0.31</v>
       </c>
       <c r="C12" s="2">
-        <v>25.301204819277107</v>
+        <v>25</v>
       </c>
       <c r="D12" s="2">
-        <v>65.06451612903226</v>
+        <v>65.16129032258064</v>
       </c>
       <c r="E12" s="2">
         <v>1.36</v>
       </c>
       <c r="F12" s="2">
-        <v>0.6087644123724786</v>
+        <v>0.733967426886627</v>
       </c>
       <c r="G12" s="2">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="H12" s="2">
-        <v>63.75</v>
+        <v>64.15</v>
       </c>
       <c r="I12" s="2">
-        <v>51.44</v>
+        <v>53.43</v>
       </c>
       <c r="J12" s="2">
-        <v>0.04839537541924725</v>
+        <v>0.045047197379191106</v>
       </c>
       <c r="K12" s="2" t="b">
         <v>0</v>
@@ -2802,10 +2822,10 @@
         <v>28</v>
       </c>
       <c r="M12" s="2">
-        <v>0.6084102393043822</v>
+        <v>0.7334061465227428</v>
       </c>
       <c r="N12" s="2">
-        <v>65.45775461140155</v>
+        <v>77.22201647169479</v>
       </c>
       <c r="O12" s="2">
         <v>100</v>
@@ -2814,16 +2834,16 @@
         <v>23.557267760130397</v>
       </c>
       <c r="Q12" s="2">
-        <v>72.16867469879517</v>
+        <v>71.66666666666667</v>
       </c>
       <c r="R12" s="2">
-        <v>62.7710843373494</v>
+        <v>62.67857142857142</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T12" s="2">
-        <v>10.03</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -2834,28 +2854,28 @@
         <v>0.02</v>
       </c>
       <c r="C13" s="1">
-        <v>30.120481927710845</v>
+        <v>29.761904761904763</v>
       </c>
       <c r="D13" s="1">
-        <v>-4558.5</v>
+        <v>-4529.499999999999</v>
       </c>
       <c r="E13" s="1">
         <v>-1.09</v>
       </c>
       <c r="F13" s="1">
-        <v>0.4049285995752488</v>
+        <v>0.3824775262089728</v>
       </c>
       <c r="G13" s="1">
         <v>1.57</v>
       </c>
       <c r="H13" s="1">
-        <v>51.04</v>
+        <v>50.07</v>
       </c>
       <c r="I13" s="1">
-        <v>12.6</v>
+        <v>11.72</v>
       </c>
       <c r="J13" s="1">
-        <v>0.05236163758426345</v>
+        <v>0.05024102119441429</v>
       </c>
       <c r="K13" s="1" t="b">
         <v>1</v>
@@ -2864,28 +2884,28 @@
         <v>5</v>
       </c>
       <c r="M13" s="1">
-        <v>0.4251164644567398</v>
+        <v>0.39847401657966963</v>
       </c>
       <c r="N13" s="1">
-        <v>47.12837712663732</v>
+        <v>43.72880347738745</v>
       </c>
       <c r="O13" s="1">
-        <v>97.59036144578313</v>
+        <v>95.23809523809523</v>
       </c>
       <c r="P13" s="1">
         <v>40.13761891809808</v>
       </c>
       <c r="Q13" s="1">
-        <v>42.7710843373494</v>
+        <v>41.54761904761905</v>
       </c>
       <c r="R13" s="1">
-        <v>39.03614457831326</v>
+        <v>38.33333333333333</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T13" s="1">
-        <v>38.24</v>
+        <v>37.54</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -2896,7 +2916,7 @@
         <v>1.66</v>
       </c>
       <c r="C14" s="2">
-        <v>43.373493975903614</v>
+        <v>42.857142857142854</v>
       </c>
       <c r="D14" s="2">
         <v>5.385542168674699</v>
@@ -2905,19 +2925,19 @@
         <v>-1.74</v>
       </c>
       <c r="F14" s="2">
-        <v>0.3793541234204233</v>
+        <v>0.5715212354760213</v>
       </c>
       <c r="G14" s="2">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="H14" s="2">
-        <v>61.02</v>
+        <v>65.11</v>
       </c>
       <c r="I14" s="2">
-        <v>64.82</v>
+        <v>74.94</v>
       </c>
       <c r="J14" s="2">
-        <v>0.02715853073823938</v>
+        <v>0.026102728768634946</v>
       </c>
       <c r="K14" s="2" t="b">
         <v>0</v>
@@ -2926,28 +2946,28 @@
         <v>100</v>
       </c>
       <c r="M14" s="2">
-        <v>0.3708539697861113</v>
+        <v>0.5645052309274701</v>
       </c>
       <c r="N14" s="2">
-        <v>41.702127659574465</v>
+        <v>60.33192491216749</v>
       </c>
       <c r="O14" s="2">
-        <v>96.3855421686747</v>
+        <v>98.80952380952381</v>
       </c>
       <c r="P14" s="2">
         <v>19.142997204429033</v>
       </c>
       <c r="Q14" s="2">
-        <v>67.10843373493977</v>
+        <v>67.97619047619048</v>
       </c>
       <c r="R14" s="2">
-        <v>60</v>
+        <v>60.892857142857146</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T14" s="2">
-        <v>4.09</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -2958,7 +2978,7 @@
         <v>-2.12</v>
       </c>
       <c r="C15" s="3">
-        <v>15.66265060240964</v>
+        <v>15.476190476190476</v>
       </c>
       <c r="D15" s="3">
         <v>19.13679245283019</v>
@@ -2967,49 +2987,49 @@
         <v>1.51</v>
       </c>
       <c r="F15" s="3">
-        <v>-0.2106631266661964</v>
+        <v>-0.293970758187976</v>
       </c>
       <c r="G15" s="3">
         <v>2.26</v>
       </c>
       <c r="H15" s="3">
-        <v>50.11</v>
+        <v>50.17</v>
       </c>
       <c r="I15" s="3">
-        <v>27.88</v>
+        <v>27.45</v>
       </c>
       <c r="J15" s="3">
-        <v>-0.029559479351052936</v>
+        <v>-0.027012091624370158</v>
       </c>
       <c r="K15" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L15" s="3">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="M15" s="3">
-        <v>-0.16603732008605843</v>
+        <v>-0.25861009526327783</v>
       </c>
       <c r="N15" s="3">
-        <v>-11.987001327642512</v>
+        <v>-21.979607706907288</v>
       </c>
       <c r="O15" s="3">
-        <v>18.072289156626507</v>
+        <v>10.714285714285714</v>
       </c>
       <c r="P15" s="3">
         <v>41.90435941885386</v>
       </c>
       <c r="Q15" s="3">
-        <v>43.614457831325296</v>
+        <v>44.166666666666664</v>
       </c>
       <c r="R15" s="3">
-        <v>20.662650602409645</v>
+        <v>19.107142857142858</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T15" s="3">
-        <v>-37.75</v>
+        <v>-39.31</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -3020,7 +3040,7 @@
         <v>-3.36</v>
       </c>
       <c r="C16" s="3">
-        <v>9.63855421686747</v>
+        <v>9.523809523809524</v>
       </c>
       <c r="D16" s="3">
         <v>6.092261904761904</v>
@@ -3029,19 +3049,19 @@
         <v>28.81</v>
       </c>
       <c r="F16" s="3">
-        <v>-0.12389391270347115</v>
+        <v>-0.08108354636825113</v>
       </c>
       <c r="G16" s="3">
         <v>1.8</v>
       </c>
       <c r="H16" s="3">
-        <v>41.03</v>
+        <v>41.38</v>
       </c>
       <c r="I16" s="3">
-        <v>-7.08</v>
+        <v>-7.26</v>
       </c>
       <c r="J16" s="3">
-        <v>-0.034065623540480816</v>
+        <v>-0.03795401302739081</v>
       </c>
       <c r="K16" s="3" t="b">
         <v>0</v>
@@ -3050,90 +3070,90 @@
         <v>27</v>
       </c>
       <c r="M16" s="3">
-        <v>-0.09556006725576449</v>
+        <v>-0.058632331812887184</v>
       </c>
       <c r="N16" s="3">
-        <v>-4.9392760446131145</v>
+        <v>-1.9818313618682253</v>
       </c>
       <c r="O16" s="3">
-        <v>33.734939759036145</v>
+        <v>42.857142857142854</v>
       </c>
       <c r="P16" s="3">
         <v>40.1905830435425</v>
       </c>
       <c r="Q16" s="3">
-        <v>26.626506024096386</v>
+        <v>27.380952380952376</v>
       </c>
       <c r="R16" s="3">
-        <v>19.879518072289155</v>
+        <v>22.678571428571423</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T16" s="3">
-        <v>-23.35</v>
+        <v>-20.55</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="1">
         <v>-4.76</v>
       </c>
-      <c r="C17" s="3">
-        <v>6.024096385542169</v>
-      </c>
-      <c r="D17" s="3">
+      <c r="C17" s="1">
+        <v>5.952380952380952</v>
+      </c>
+      <c r="D17" s="1">
         <v>6.40546218487395</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="1">
         <v>-1.42</v>
       </c>
-      <c r="F17" s="3">
-        <v>-0.04377505168642326</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1.77</v>
-      </c>
-      <c r="H17" s="3">
-        <v>39.09</v>
-      </c>
-      <c r="I17" s="3">
-        <v>-3.1</v>
-      </c>
-      <c r="J17" s="3">
-        <v>-0.0027585473256991613</v>
-      </c>
-      <c r="K17" s="3" t="b">
+      <c r="F17" s="1">
+        <v>0.0033111411473464164</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1.76</v>
+      </c>
+      <c r="H17" s="1">
+        <v>42.88</v>
+      </c>
+      <c r="I17" s="1">
+        <v>-1.33</v>
+      </c>
+      <c r="J17" s="1">
+        <v>-0.006078857794570694</v>
+      </c>
+      <c r="K17" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="1">
         <v>31</v>
       </c>
-      <c r="M17" s="3">
-        <v>-0.0165037254430056</v>
-      </c>
-      <c r="N17" s="3">
-        <v>2.966358136662765</v>
-      </c>
-      <c r="O17" s="3">
-        <v>43.373493975903614</v>
-      </c>
-      <c r="P17" s="3">
+      <c r="M17" s="1">
+        <v>0.024639794974942175</v>
+      </c>
+      <c r="N17" s="1">
+        <v>6.345381316914713</v>
+      </c>
+      <c r="O17" s="1">
+        <v>57.14285714285714</v>
+      </c>
+      <c r="P17" s="1">
         <v>24.80206596461608</v>
       </c>
-      <c r="Q17" s="3">
-        <v>33.25301204819277</v>
-      </c>
-      <c r="R17" s="3">
-        <v>28.67469879518072</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="T17" s="3">
-        <v>-4.5</v>
+      <c r="Q17" s="1">
+        <v>35.357142857142854</v>
+      </c>
+      <c r="R17" s="1">
+        <v>32.67857142857143</v>
+      </c>
+      <c r="S17" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="T17" s="1">
+        <v>-0.49</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -3144,7 +3164,7 @@
         <v>0.19</v>
       </c>
       <c r="C18" s="3">
-        <v>33.734939759036145</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="D18" s="3">
         <v>730.8947368421053</v>
@@ -3153,19 +3173,19 @@
         <v>11.06</v>
       </c>
       <c r="F18" s="3">
-        <v>-0.4266853319927678</v>
+        <v>-0.38614992766037703</v>
       </c>
       <c r="G18" s="3">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="H18" s="3">
-        <v>32.17</v>
+        <v>36.56</v>
       </c>
       <c r="I18" s="3">
-        <v>-32.62</v>
+        <v>-31.02</v>
       </c>
       <c r="J18" s="3">
-        <v>-0.05926794055986035</v>
+        <v>-0.061861656245620386</v>
       </c>
       <c r="K18" s="3" t="b">
         <v>0</v>
@@ -3174,28 +3194,28 @@
         <v>31</v>
       </c>
       <c r="M18" s="3">
-        <v>-0.4231436013118045</v>
+        <v>-0.3836241660228986</v>
       </c>
       <c r="N18" s="3">
-        <v>-37.69762945021712</v>
+        <v>-34.481014782869366</v>
       </c>
       <c r="O18" s="3">
-        <v>1.2048192771084338</v>
+        <v>2.380952380952381</v>
       </c>
       <c r="P18" s="3">
         <v>48.6563520729564</v>
       </c>
       <c r="Q18" s="3">
-        <v>40.602409638554214</v>
+        <v>41.54761904761905</v>
       </c>
       <c r="R18" s="3">
-        <v>24.397590361445783</v>
+        <v>24.642857142857146</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T18" s="3">
-        <v>-9.87</v>
+        <v>-9.63</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -3206,7 +3226,7 @@
         <v>5.65</v>
       </c>
       <c r="C19" s="2">
-        <v>62.65060240963856</v>
+        <v>61.904761904761905</v>
       </c>
       <c r="D19" s="2">
         <v>4.892035398230088</v>
@@ -3215,19 +3235,19 @@
         <v>3.12</v>
       </c>
       <c r="F19" s="2">
-        <v>0.0716753957715537</v>
+        <v>0.07297195256463443</v>
       </c>
       <c r="G19" s="2">
         <v>0.1</v>
       </c>
       <c r="H19" s="2">
-        <v>51.42</v>
+        <v>53.41</v>
       </c>
       <c r="I19" s="2">
-        <v>12.27</v>
+        <v>13.13</v>
       </c>
       <c r="J19" s="2">
-        <v>0.0015510400889843102</v>
+        <v>-0.0001345906658455575</v>
       </c>
       <c r="K19" s="2" t="b">
         <v>0</v>
@@ -3236,28 +3256,28 @@
         <v>-58</v>
       </c>
       <c r="M19" s="2">
-        <v>0.039799819642883705</v>
+        <v>0.04771433618984999</v>
       </c>
       <c r="N19" s="2">
-        <v>8.59671264525171</v>
+        <v>8.652835438405484</v>
       </c>
       <c r="O19" s="2">
-        <v>59.036144578313255</v>
+        <v>63.095238095238095</v>
       </c>
       <c r="P19" s="2">
         <v>11.392700631623551</v>
       </c>
       <c r="Q19" s="2">
-        <v>59.39759036144578</v>
+        <v>59.88095238095238</v>
       </c>
       <c r="R19" s="2">
-        <v>51.32530120481928</v>
+        <v>52.4404761904762</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T19" s="2">
-        <v>2.91</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -3268,7 +3288,7 @@
         <v>8.25</v>
       </c>
       <c r="C20" s="2">
-        <v>71.08433734939759</v>
+        <v>70.23809523809523</v>
       </c>
       <c r="D20" s="2">
         <v>-0.11030303030303032</v>
@@ -3277,19 +3297,19 @@
         <v>-5.68</v>
       </c>
       <c r="F20" s="2">
-        <v>0.2142450295217468</v>
+        <v>0.24812821049311512</v>
       </c>
       <c r="G20" s="2">
         <v>1.07</v>
       </c>
       <c r="H20" s="2">
-        <v>51.79</v>
+        <v>51.07</v>
       </c>
       <c r="I20" s="2">
-        <v>21.76</v>
+        <v>21.42</v>
       </c>
       <c r="J20" s="2">
-        <v>0.02369231525888492</v>
+        <v>0.022609001575628982</v>
       </c>
       <c r="K20" s="2" t="b">
         <v>0</v>
@@ -3298,28 +3318,28 @@
         <v>9</v>
       </c>
       <c r="M20" s="2">
-        <v>0.21672424099842114</v>
+        <v>0.25009269176670945</v>
       </c>
       <c r="N20" s="2">
-        <v>26.28915478080544</v>
+        <v>28.890670996091437</v>
       </c>
       <c r="O20" s="2">
-        <v>83.13253012048193</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="P20" s="2">
         <v>20.924527727345563</v>
       </c>
       <c r="Q20" s="2">
-        <v>62.168674698795186</v>
+        <v>61.42857142857143</v>
       </c>
       <c r="R20" s="2">
-        <v>54.39759036144578</v>
+        <v>55.11904761904761</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="T20" s="2">
-        <v>18.54</v>
+        <v>19.27</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -3330,7 +3350,7 @@
         <v>1.01</v>
       </c>
       <c r="C21" s="3">
-        <v>38.55421686746988</v>
+        <v>38.095238095238095</v>
       </c>
       <c r="D21" s="3">
         <v>12.821782178217823</v>
@@ -3339,49 +3359,49 @@
         <v>-3.45</v>
       </c>
       <c r="F21" s="3">
-        <v>-0.40637474862507716</v>
+        <v>-0.38466214792594977</v>
       </c>
       <c r="G21" s="3">
         <v>1.62</v>
       </c>
       <c r="H21" s="3">
-        <v>41.43</v>
+        <v>42.85</v>
       </c>
       <c r="I21" s="3">
-        <v>-12.98</v>
+        <v>-12.04</v>
       </c>
       <c r="J21" s="3">
-        <v>-0.026655232596393102</v>
+        <v>-0.024603202857270873</v>
       </c>
       <c r="K21" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="3">
         <v>55</v>
       </c>
       <c r="M21" s="3">
-        <v>-0.38441601840310446</v>
+        <v>-0.3672624566455427</v>
       </c>
       <c r="N21" s="3">
-        <v>-33.82487115934712</v>
+        <v>-32.844843845133774</v>
       </c>
       <c r="O21" s="3">
-        <v>3.614457831325301</v>
+        <v>3.571428571428571</v>
       </c>
       <c r="P21" s="3">
         <v>51.51389629888408</v>
       </c>
       <c r="Q21" s="3">
-        <v>40.120481927710834</v>
+        <v>40.95238095238095</v>
       </c>
       <c r="R21" s="3">
-        <v>20.903614457831324</v>
+        <v>20.714285714285715</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="T21" s="3">
-        <v>-30.32</v>
+        <v>-30.51</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -3392,58 +3412,58 @@
         <v>8.48</v>
       </c>
       <c r="C22" s="1">
-        <v>72.28915662650603</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="D22" s="1">
-        <v>0.7641509433962265</v>
+        <v>0.7594339622641508</v>
       </c>
       <c r="E22" s="1">
         <v>-0.24</v>
       </c>
       <c r="F22" s="1">
-        <v>-0.08697293784029955</v>
+        <v>-0.10266680181312518</v>
       </c>
       <c r="G22" s="1">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="H22" s="1">
-        <v>33.8</v>
+        <v>30.94</v>
       </c>
       <c r="I22" s="1">
-        <v>-0.04</v>
+        <v>-1.92</v>
       </c>
       <c r="J22" s="1">
-        <v>-0.012153134656444237</v>
+        <v>-0.013616463667740084</v>
       </c>
       <c r="K22" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L22" s="1">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M22" s="1">
-        <v>-0.07351436125263888</v>
+        <v>-0.09172183471738526</v>
       </c>
       <c r="N22" s="1">
-        <v>-2.734705444300561</v>
+        <v>-5.290781652318034</v>
       </c>
       <c r="O22" s="1">
-        <v>37.34939759036144</v>
+        <v>36.904761904761905</v>
       </c>
       <c r="P22" s="1">
-        <v>15.098892338880725</v>
+        <v>16.69901984635222</v>
       </c>
       <c r="Q22" s="1">
-        <v>43.012048192771076</v>
+        <v>42.023809523809526</v>
       </c>
       <c r="R22" s="1">
-        <v>39.45783132530121</v>
+        <v>38.69047619047619</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="T22" s="1">
-        <v>-13.65</v>
+        <v>-14.42</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -3454,7 +3474,7 @@
         <v>26.55</v>
       </c>
       <c r="C23" s="2">
-        <v>96.3855421686747</v>
+        <v>96.42857142857143</v>
       </c>
       <c r="D23" s="2">
         <v>-0.7145009416195857</v>
@@ -3463,49 +3483,49 @@
         <v>0.07</v>
       </c>
       <c r="F23" s="2">
-        <v>0.08678413084281295</v>
+        <v>0.1297929317469627</v>
       </c>
       <c r="G23" s="2">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="H23" s="2">
-        <v>63.36</v>
+        <v>67.74</v>
       </c>
       <c r="I23" s="2">
-        <v>2.57</v>
+        <v>5.67</v>
       </c>
       <c r="J23" s="2">
-        <v>0.011596708144805314</v>
+        <v>0.011863476972555707</v>
       </c>
       <c r="K23" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L23" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M23" s="2">
-        <v>0.09386759220473961</v>
+        <v>0.13512509520386162</v>
       </c>
       <c r="N23" s="2">
-        <v>14.003489901437288</v>
+        <v>17.39391133980666</v>
       </c>
       <c r="O23" s="2">
-        <v>69.87951807228916</v>
+        <v>75</v>
       </c>
       <c r="P23" s="2">
-        <v>21.71519296301999</v>
+        <v>20.883293768118005</v>
       </c>
       <c r="Q23" s="2">
-        <v>60.96385542168675</v>
+        <v>63.33333333333332</v>
       </c>
       <c r="R23" s="2">
-        <v>51.506024096385545</v>
+        <v>54.22619047619048</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T23" s="2">
-        <v>15.71</v>
+        <v>18.43</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -3516,28 +3536,28 @@
         <v>-97.21</v>
       </c>
       <c r="C24" s="1">
-        <v>1.2048192771084338</v>
+        <v>1.1904761904761905</v>
       </c>
       <c r="D24" s="1">
-        <v>2.6266844974796832</v>
+        <v>2.6552823783561363</v>
       </c>
       <c r="E24" s="1">
         <v>1.55</v>
       </c>
       <c r="F24" s="1">
-        <v>-0.04784403608734464</v>
+        <v>-0.006597090330134586</v>
       </c>
       <c r="G24" s="1">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="H24" s="1">
-        <v>57.13</v>
+        <v>55.01</v>
       </c>
       <c r="I24" s="1">
-        <v>-4.75</v>
+        <v>-5.53</v>
       </c>
       <c r="J24" s="1">
-        <v>0.04512058415482685</v>
+        <v>0.040503645035753016</v>
       </c>
       <c r="K24" s="1" t="b">
         <v>0</v>
@@ -3546,28 +3566,28 @@
         <v>-68</v>
       </c>
       <c r="M24" s="1">
-        <v>0.043886788549605704</v>
+        <v>0.06580807661091415</v>
       </c>
       <c r="N24" s="1">
-        <v>9.005409535923906</v>
+        <v>10.462209480511904</v>
       </c>
       <c r="O24" s="1">
-        <v>60.24096385542169</v>
+        <v>65.47619047619048</v>
       </c>
       <c r="P24" s="1">
         <v>57.99224429263358</v>
       </c>
       <c r="Q24" s="1">
-        <v>46.38554216867469</v>
+        <v>45.47619047619048</v>
       </c>
       <c r="R24" s="1">
-        <v>30.542168674698793</v>
+        <v>32.142857142857146</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T24" s="1">
-        <v>34.26</v>
+        <v>35.86</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -3578,7 +3598,7 @@
         <v>-2.28</v>
       </c>
       <c r="C25" s="3">
-        <v>14.457831325301203</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="D25" s="3">
         <v>-7.74561403508772</v>
@@ -3587,49 +3607,49 @@
         <v>15.52</v>
       </c>
       <c r="F25" s="3">
-        <v>-0.194648330879535</v>
+        <v>-0.21651597338679843</v>
       </c>
       <c r="G25" s="3">
         <v>2.36</v>
       </c>
       <c r="H25" s="3">
-        <v>41.79</v>
+        <v>41.93</v>
       </c>
       <c r="I25" s="3">
-        <v>-34.09</v>
+        <v>-33.59</v>
       </c>
       <c r="J25" s="3">
-        <v>-0.00021945580560811366</v>
+        <v>-0.0021524259468810357</v>
       </c>
       <c r="K25" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L25" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M25" s="3">
-        <v>-0.1464807936184337</v>
+        <v>-0.17834890864267972</v>
       </c>
       <c r="N25" s="3">
-        <v>-10.031348680880035</v>
+        <v>-13.953489044847473</v>
       </c>
       <c r="O25" s="3">
-        <v>20.481927710843372</v>
+        <v>19.047619047619047</v>
       </c>
       <c r="P25" s="3">
         <v>45.59139601172712</v>
       </c>
       <c r="Q25" s="3">
-        <v>18.072289156626507</v>
+        <v>18.928571428571427</v>
       </c>
       <c r="R25" s="3">
-        <v>6.80722891566265</v>
+        <v>6.369047619047619</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T25" s="3">
-        <v>5.4</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -3640,7 +3660,7 @@
         <v>-4.55</v>
       </c>
       <c r="C26" s="3">
-        <v>7.228915662650602</v>
+        <v>7.142857142857142</v>
       </c>
       <c r="D26" s="3">
         <v>-0.7362637362637364</v>
@@ -3649,49 +3669,49 @@
         <v>-0.88</v>
       </c>
       <c r="F26" s="3">
-        <v>-0.4967305619190379</v>
+        <v>-0.4573781880803759</v>
       </c>
       <c r="G26" s="3">
         <v>3.38</v>
       </c>
       <c r="H26" s="3">
-        <v>38.93</v>
+        <v>42.39</v>
       </c>
       <c r="I26" s="3">
-        <v>-18.96</v>
+        <v>-15.61</v>
       </c>
       <c r="J26" s="3">
-        <v>-0.03219111090318241</v>
+        <v>-0.0326450394752859</v>
       </c>
       <c r="K26" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L26" s="3">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M26" s="3">
-        <v>-0.4124373717121106</v>
+        <v>-0.39058582477816817</v>
       </c>
       <c r="N26" s="3">
-        <v>-36.62700649024772</v>
+        <v>-35.177180658396324</v>
       </c>
       <c r="O26" s="3">
-        <v>2.4096385542168677</v>
+        <v>1.1904761904761905</v>
       </c>
       <c r="P26" s="3">
         <v>55.61259899184437</v>
       </c>
       <c r="Q26" s="3">
-        <v>10.361445783132531</v>
+        <v>12.738095238095237</v>
       </c>
       <c r="R26" s="3">
-        <v>-3.1325301204819285</v>
+        <v>-3.2738095238095246</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T26" s="3">
-        <v>-31.97</v>
+        <v>-32.12</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -3702,7 +3722,7 @@
         <v>-0.98</v>
       </c>
       <c r="C27" s="3">
-        <v>19.27710843373494</v>
+        <v>19.047619047619047</v>
       </c>
       <c r="D27" s="3">
         <v>-1.7653061224489797</v>
@@ -3711,49 +3731,49 @@
         <v>6.6</v>
       </c>
       <c r="F27" s="3">
-        <v>-0.42226771764467136</v>
+        <v>-0.3968756486822497</v>
       </c>
       <c r="G27" s="3">
         <v>2.66</v>
       </c>
       <c r="H27" s="3">
-        <v>31.87</v>
+        <v>31.83</v>
       </c>
       <c r="I27" s="3">
-        <v>-38.58</v>
+        <v>-38.35</v>
       </c>
       <c r="J27" s="3">
-        <v>-0.02946578800091318</v>
+        <v>-0.029785130381341725</v>
       </c>
       <c r="K27" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="3">
         <v>7</v>
       </c>
       <c r="M27" s="3">
-        <v>-0.36347498834068004</v>
+        <v>-0.3502893784798695</v>
       </c>
       <c r="N27" s="3">
-        <v>-31.73076815310467</v>
+        <v>-31.147536028566456</v>
       </c>
       <c r="O27" s="3">
-        <v>4.819277108433735</v>
+        <v>4.761904761904762</v>
       </c>
       <c r="P27" s="3">
-        <v>48.69918825259344</v>
+        <v>48.780487048443945</v>
       </c>
       <c r="Q27" s="3">
-        <v>10.481927710843372</v>
+        <v>10.833333333333332</v>
       </c>
       <c r="R27" s="3">
-        <v>0.36144578313253106</v>
+        <v>0.4166666666666643</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T27" s="3">
-        <v>-15.8</v>
+        <v>-15.74</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -3764,7 +3784,7 @@
         <v>-1.08</v>
       </c>
       <c r="C28" s="1">
-        <v>16.867469879518072</v>
+        <v>16.666666666666664</v>
       </c>
       <c r="D28" s="1">
         <v>8.555555555555555</v>
@@ -3773,19 +3793,19 @@
         <v>1.72</v>
       </c>
       <c r="F28" s="1">
-        <v>-0.07338028380418915</v>
+        <v>-0.017592968676545417</v>
       </c>
       <c r="G28" s="1">
         <v>3.26</v>
       </c>
       <c r="H28" s="1">
-        <v>44.96</v>
+        <v>43.77</v>
       </c>
       <c r="I28" s="1">
-        <v>-14.38</v>
+        <v>-15.19</v>
       </c>
       <c r="J28" s="1">
-        <v>0.01516221309373249</v>
+        <v>0.013666160712908892</v>
       </c>
       <c r="K28" s="1" t="b">
         <v>0</v>
@@ -3794,28 +3814,28 @@
         <v>3</v>
       </c>
       <c r="M28" s="1">
-        <v>0.006662829585582175</v>
+        <v>0.04583171244235773</v>
       </c>
       <c r="N28" s="1">
-        <v>5.283013639521558</v>
+        <v>8.46457306365626</v>
       </c>
       <c r="O28" s="1">
-        <v>49.39759036144578</v>
+        <v>60.71428571428571</v>
       </c>
       <c r="P28" s="1">
         <v>35.08771990976345</v>
       </c>
       <c r="Q28" s="1">
-        <v>46.26506024096385</v>
+        <v>46.66666666666667</v>
       </c>
       <c r="R28" s="1">
-        <v>36.325301204819276</v>
+        <v>39.88095238095238</v>
       </c>
       <c r="S28" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="T28" s="1">
-        <v>19.31</v>
+        <v>22.87</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -3826,7 +3846,7 @@
         <v>0.47</v>
       </c>
       <c r="C29" s="1">
-        <v>36.144578313253014</v>
+        <v>35.714285714285715</v>
       </c>
       <c r="D29" s="1">
         <v>83.17021276595746</v>
@@ -3835,19 +3855,19 @@
         <v>-4.82</v>
       </c>
       <c r="F29" s="1">
-        <v>-0.05392597330072449</v>
+        <v>-0.01132295527763083</v>
       </c>
       <c r="G29" s="1">
         <v>2.32</v>
       </c>
       <c r="H29" s="1">
-        <v>43.13</v>
+        <v>46.35</v>
       </c>
       <c r="I29" s="1">
-        <v>-13.83</v>
+        <v>-11.53</v>
       </c>
       <c r="J29" s="1">
-        <v>-0.0018474164526615137</v>
+        <v>-0.0035344403769208797</v>
       </c>
       <c r="K29" s="1" t="b">
         <v>0</v>
@@ -3856,28 +3876,28 @@
         <v>10</v>
       </c>
       <c r="M29" s="1">
-        <v>-0.007175128312008505</v>
+        <v>0.02572154873871968</v>
       </c>
       <c r="N29" s="1">
-        <v>3.8992178497624854</v>
+        <v>6.453556693292471</v>
       </c>
       <c r="O29" s="1">
-        <v>46.98795180722892</v>
+        <v>58.333333333333336</v>
       </c>
       <c r="P29" s="1">
         <v>21.89743824494191</v>
       </c>
       <c r="Q29" s="1">
-        <v>51.08433734939759</v>
+        <v>52.5</v>
       </c>
       <c r="R29" s="1">
-        <v>45.06024096385543</v>
+        <v>48.392857142857146</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T29" s="1">
-        <v>4.82</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -3888,7 +3908,7 @@
         <v>2.2</v>
       </c>
       <c r="C30" s="1">
-        <v>46.98795180722892</v>
+        <v>46.42857142857143</v>
       </c>
       <c r="D30" s="1">
         <v>226.42272727272726</v>
@@ -3897,49 +3917,49 @@
         <v>1.75</v>
       </c>
       <c r="F30" s="1">
-        <v>-0.10511192955128379</v>
+        <v>-0.0856315494495418</v>
       </c>
       <c r="G30" s="1">
         <v>1.24</v>
       </c>
       <c r="H30" s="1">
-        <v>44.71</v>
+        <v>43.12</v>
       </c>
       <c r="I30" s="1">
-        <v>-4.8</v>
+        <v>-5.44</v>
       </c>
       <c r="J30" s="1">
-        <v>-0.003686087424677485</v>
+        <v>-0.004631496078572336</v>
       </c>
       <c r="K30" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L30" s="1">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M30" s="1">
-        <v>-0.09661177591697179</v>
+        <v>-0.07889618508293261</v>
       </c>
       <c r="N30" s="1">
-        <v>-5.044446910733848</v>
+        <v>-4.008216688872772</v>
       </c>
       <c r="O30" s="1">
-        <v>32.53012048192771</v>
+        <v>38.095238095238095</v>
       </c>
       <c r="P30" s="1">
         <v>14.879468887608937</v>
       </c>
       <c r="Q30" s="1">
-        <v>56.626506024096386</v>
+        <v>57.14285714285714</v>
       </c>
       <c r="R30" s="1">
-        <v>46.506024096385545</v>
+        <v>48.392857142857146</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="T30" s="1">
-        <v>-1.97</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -3950,28 +3970,28 @@
         <v>7.83</v>
       </c>
       <c r="C31" s="1">
-        <v>68.67469879518072</v>
+        <v>67.85714285714286</v>
       </c>
       <c r="D31" s="1">
-        <v>7.35249042145594</v>
+        <v>7.31162196679438</v>
       </c>
       <c r="E31" s="1">
         <v>0.38</v>
       </c>
       <c r="F31" s="1">
-        <v>-0.12396969445810029</v>
+        <v>-0.15004171656000947</v>
       </c>
       <c r="G31" s="1">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="H31" s="1">
-        <v>36.58</v>
+        <v>33.86</v>
       </c>
       <c r="I31" s="1">
-        <v>-5.32</v>
+        <v>-7.11</v>
       </c>
       <c r="J31" s="1">
-        <v>-0.002593719779779743</v>
+        <v>-0.0023213180223429575</v>
       </c>
       <c r="K31" s="1" t="b">
         <v>0</v>
@@ -3980,90 +4000,90 @@
         <v>208</v>
       </c>
       <c r="M31" s="1">
-        <v>-0.10732356025757261</v>
+        <v>-0.1365709878267911</v>
       </c>
       <c r="N31" s="1">
-        <v>-6.1156253447939335</v>
+        <v>-9.775696963258616</v>
       </c>
       <c r="O31" s="1">
-        <v>27.710843373493976</v>
+        <v>25</v>
       </c>
       <c r="P31" s="1">
-        <v>26.160269342004856</v>
+        <v>28.417468700740923</v>
       </c>
       <c r="Q31" s="1">
-        <v>51.92771084337348</v>
+        <v>52.97619047619048</v>
       </c>
       <c r="R31" s="1">
-        <v>40.12048192771084</v>
+        <v>39.3452380952381</v>
       </c>
       <c r="S31" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T31" s="1">
-        <v>-7.93</v>
+        <v>-8.7</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32" s="3">
         <v>-2.58</v>
       </c>
-      <c r="C32" s="1">
-        <v>13.253012048192772</v>
-      </c>
-      <c r="D32" s="1">
-        <v>7.817829457364342</v>
-      </c>
-      <c r="E32" s="1">
+      <c r="C32" s="3">
+        <v>13.095238095238097</v>
+      </c>
+      <c r="D32" s="3">
+        <v>8.267441860465116</v>
+      </c>
+      <c r="E32" s="3">
         <v>3.57</v>
       </c>
-      <c r="F32" s="1">
-        <v>-0.03624028571413286</v>
-      </c>
-      <c r="G32" s="1">
+      <c r="F32" s="3">
+        <v>-0.10963238670996056</v>
+      </c>
+      <c r="G32" s="3">
         <v>1.61</v>
       </c>
-      <c r="H32" s="1">
-        <v>48.27</v>
-      </c>
-      <c r="I32" s="1">
-        <v>-2.51</v>
-      </c>
-      <c r="J32" s="1">
-        <v>-0.0022256869683246927</v>
-      </c>
-      <c r="K32" s="1" t="b">
+      <c r="H32" s="3">
+        <v>46.11</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-3.74</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-0.006645706526291285</v>
+      </c>
+      <c r="K32" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L32" s="1">
-        <v>22</v>
-      </c>
-      <c r="M32" s="1">
-        <v>-0.014635728560256522</v>
-      </c>
-      <c r="N32" s="1">
-        <v>3.1531578249376753</v>
-      </c>
-      <c r="O32" s="1">
-        <v>45.78313253012048</v>
-      </c>
-      <c r="P32" s="1">
+      <c r="L32" s="3">
+        <v>21</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-0.09251333561149555</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-5.369931741729066</v>
+      </c>
+      <c r="O32" s="3">
+        <v>35.714285714285715</v>
+      </c>
+      <c r="P32" s="3">
         <v>27.28297753683016</v>
       </c>
-      <c r="Q32" s="1">
-        <v>41.9277108433735</v>
-      </c>
-      <c r="R32" s="1">
-        <v>32.22891566265061</v>
-      </c>
-      <c r="S32" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="T32" s="1">
-        <v>0.34</v>
+      <c r="Q32" s="3">
+        <v>39.166666666666664</v>
+      </c>
+      <c r="R32" s="3">
+        <v>28.452380952380956</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="T32" s="3">
+        <v>-3.44</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -4074,28 +4094,28 @@
         <v>17.95</v>
       </c>
       <c r="C33" s="2">
-        <v>87.95180722891565</v>
+        <v>88.09523809523809</v>
       </c>
       <c r="D33" s="2">
-        <v>0.06016713091922016</v>
+        <v>0.06295264623955427</v>
       </c>
       <c r="E33" s="2">
         <v>0.24</v>
       </c>
       <c r="F33" s="2">
-        <v>0.22003018865260257</v>
+        <v>0.25184842447027966</v>
       </c>
       <c r="G33" s="2">
         <v>1.1</v>
       </c>
       <c r="H33" s="2">
-        <v>54.37</v>
+        <v>57.29</v>
       </c>
       <c r="I33" s="2">
-        <v>14.11</v>
+        <v>15.73</v>
       </c>
       <c r="J33" s="2">
-        <v>0.028180009587628892</v>
+        <v>0.026555017703357508</v>
       </c>
       <c r="K33" s="2" t="b">
         <v>0</v>
@@ -4104,28 +4124,28 @@
         <v>82</v>
       </c>
       <c r="M33" s="2">
-        <v>0.2235719193335659</v>
+        <v>0.25465482628970015</v>
       </c>
       <c r="N33" s="2">
-        <v>26.973922614319935</v>
+        <v>29.346884448390504</v>
       </c>
       <c r="O33" s="2">
-        <v>85.54216867469879</v>
+        <v>86.90476190476191</v>
       </c>
       <c r="P33" s="2">
         <v>23.38443607454554</v>
       </c>
       <c r="Q33" s="2">
-        <v>68.91566265060241</v>
+        <v>69.99999999999999</v>
       </c>
       <c r="R33" s="2">
-        <v>59.63855421686747</v>
+        <v>60.476190476190474</v>
       </c>
       <c r="S33" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T33" s="2">
-        <v>23.85</v>
+        <v>24.68</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -4136,7 +4156,7 @@
         <v>19.91</v>
       </c>
       <c r="C34" s="1">
-        <v>92.7710843373494</v>
+        <v>92.85714285714286</v>
       </c>
       <c r="D34" s="1">
         <v>-2.3350075339025613</v>
@@ -4145,49 +4165,49 @@
         <v>2.34</v>
       </c>
       <c r="F34" s="1">
-        <v>-0.10746633153345066</v>
+        <v>-0.07331616485328905</v>
       </c>
       <c r="G34" s="1">
         <v>1.21</v>
       </c>
       <c r="H34" s="1">
-        <v>45.16</v>
+        <v>51.88</v>
       </c>
       <c r="I34" s="1">
-        <v>-0.15</v>
+        <v>2.45</v>
       </c>
       <c r="J34" s="1">
-        <v>-0.004288241982899922</v>
+        <v>-0.00459191191504251</v>
       </c>
       <c r="K34" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="1">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M34" s="1">
-        <v>-0.10002869710342766</v>
+        <v>-0.06742272103250602</v>
       </c>
       <c r="N34" s="1">
-        <v>-5.386139029379429</v>
+        <v>-2.860870283830112</v>
       </c>
       <c r="O34" s="1">
-        <v>30.120481927710845</v>
+        <v>41.66666666666667</v>
       </c>
       <c r="P34" s="1">
         <v>21.09433056126816</v>
       </c>
       <c r="Q34" s="1">
-        <v>45.542168674698786</v>
+        <v>50.11904761904762</v>
       </c>
       <c r="R34" s="1">
-        <v>33.674698795180724</v>
+        <v>37.738095238095234</v>
       </c>
       <c r="S34" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="T34" s="1">
-        <v>-13.15</v>
+        <v>-9.09</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -4198,7 +4218,7 @@
         <v>17.64</v>
       </c>
       <c r="C35" s="1">
-        <v>86.74698795180723</v>
+        <v>86.90476190476191</v>
       </c>
       <c r="D35" s="1">
         <v>-0.45464852607709755</v>
@@ -4207,19 +4227,19 @@
         <v>-0.33</v>
       </c>
       <c r="F35" s="1">
-        <v>-0.046510076393472474</v>
+        <v>-0.037469858056862995</v>
       </c>
       <c r="G35" s="1">
-        <v>0.95</v>
+        <v>0.94</v>
       </c>
       <c r="H35" s="1">
-        <v>39.22</v>
+        <v>41.86</v>
       </c>
       <c r="I35" s="1">
-        <v>-12.41</v>
+        <v>-11.36</v>
       </c>
       <c r="J35" s="1">
-        <v>0.008957876535317839</v>
+        <v>0.00631900789595127</v>
       </c>
       <c r="K35" s="1" t="b">
         <v>0</v>
@@ -4228,28 +4248,28 @@
         <v>-56</v>
       </c>
       <c r="M35" s="1">
-        <v>-0.04828094173395414</v>
+        <v>-0.0391536991485153</v>
       </c>
       <c r="N35" s="1">
-        <v>-0.21136349243207872</v>
+        <v>-0.03396809543103205</v>
       </c>
       <c r="O35" s="1">
-        <v>39.75903614457831</v>
+        <v>45.23809523809524</v>
       </c>
       <c r="P35" s="1">
         <v>23.996351232323672</v>
       </c>
       <c r="Q35" s="1">
-        <v>48.433734939759034</v>
+        <v>49.04761904761905</v>
       </c>
       <c r="R35" s="1">
-        <v>40.12048192771084</v>
+        <v>41.42857142857144</v>
       </c>
       <c r="S35" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="T35" s="1">
-        <v>17.62</v>
+        <v>18.93</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -4260,7 +4280,7 @@
         <v>10.27</v>
       </c>
       <c r="C36" s="1">
-        <v>78.3132530120482</v>
+        <v>77.38095238095238</v>
       </c>
       <c r="D36" s="1">
         <v>-0.01265822784810117</v>
@@ -4269,19 +4289,19 @@
         <v>-1.31</v>
       </c>
       <c r="F36" s="1">
-        <v>0.10412588696847526</v>
+        <v>0.00013701730383681998</v>
       </c>
       <c r="G36" s="1">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="H36" s="1">
-        <v>49.49</v>
+        <v>40.14</v>
       </c>
       <c r="I36" s="1">
-        <v>-5.22</v>
+        <v>-10.34</v>
       </c>
       <c r="J36" s="1">
-        <v>0.013974834602639702</v>
+        <v>0.01357148485754007</v>
       </c>
       <c r="K36" s="1" t="b">
         <v>0</v>
@@ -4290,28 +4310,28 @@
         <v>-22</v>
       </c>
       <c r="M36" s="1">
-        <v>0.10802179071753493</v>
+        <v>0.003785339669083454</v>
       </c>
       <c r="N36" s="1">
-        <v>15.41890975271683</v>
+        <v>4.259935786328843</v>
       </c>
       <c r="O36" s="1">
-        <v>72.28915662650603</v>
+        <v>51.19047619047619</v>
       </c>
       <c r="P36" s="1">
         <v>26.730280409441182</v>
       </c>
       <c r="Q36" s="1">
-        <v>54.819277108433745</v>
+        <v>51.42857142857143</v>
       </c>
       <c r="R36" s="1">
-        <v>49.75903614457832</v>
+        <v>43.86904761904762</v>
       </c>
       <c r="S36" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T36" s="1">
-        <v>22.81</v>
+        <v>16.92</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -4322,28 +4342,28 @@
         <v>5.29</v>
       </c>
       <c r="C37" s="2">
-        <v>60.24096385542169</v>
+        <v>59.523809523809526</v>
       </c>
       <c r="D37" s="2">
-        <v>0.4196597353497164</v>
+        <v>0.42155009451795833</v>
       </c>
       <c r="E37" s="2">
         <v>-3.25</v>
       </c>
       <c r="F37" s="2">
-        <v>0.2465346405499334</v>
+        <v>0.25459594388146645</v>
       </c>
       <c r="G37" s="2">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="H37" s="2">
-        <v>43.06</v>
+        <v>42.71</v>
       </c>
       <c r="I37" s="2">
-        <v>5.88</v>
+        <v>5.62</v>
       </c>
       <c r="J37" s="2">
-        <v>0.017906991362600627</v>
+        <v>0.016363915997029486</v>
       </c>
       <c r="K37" s="2" t="b">
         <v>0</v>
@@ -4352,28 +4372,28 @@
         <v>-105</v>
       </c>
       <c r="M37" s="2">
-        <v>0.25645148645663074</v>
+        <v>0.2621732287939018</v>
       </c>
       <c r="N37" s="2">
-        <v>30.261879326626413</v>
+        <v>30.098724698810674</v>
       </c>
       <c r="O37" s="2">
-        <v>91.56626506024097</v>
+        <v>88.09523809523809</v>
       </c>
       <c r="P37" s="2">
         <v>20.90944133883571</v>
       </c>
       <c r="Q37" s="2">
-        <v>54.57831325301205</v>
+        <v>54.04761904761905</v>
       </c>
       <c r="R37" s="2">
-        <v>56.44578313253012</v>
+        <v>55</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="T37" s="2">
-        <v>26.63</v>
+        <v>25.18</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -4384,58 +4404,58 @@
         <v>0.04</v>
       </c>
       <c r="C38" s="2">
-        <v>31.32530120481928</v>
+        <v>30.952380952380953</v>
       </c>
       <c r="D38" s="2">
-        <v>686</v>
+        <v>686.5</v>
       </c>
       <c r="E38" s="2">
         <v>3.14</v>
       </c>
       <c r="F38" s="2">
-        <v>0.1415277996894257</v>
+        <v>0.3342029603102209</v>
       </c>
       <c r="G38" s="2">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="H38" s="2">
-        <v>54.73</v>
+        <v>60.02</v>
       </c>
       <c r="I38" s="2">
-        <v>49.41</v>
+        <v>59.34</v>
       </c>
       <c r="J38" s="2">
-        <v>0.013192389071912046</v>
+        <v>0.012932393209592455</v>
       </c>
       <c r="K38" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L38" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="M38" s="2">
-        <v>0.14967378025564138</v>
+        <v>0.34009640413100395</v>
       </c>
       <c r="N38" s="2">
-        <v>19.584108706527466</v>
+        <v>37.89104223252089</v>
       </c>
       <c r="O38" s="2">
-        <v>79.51807228915662</v>
+        <v>91.66666666666666</v>
       </c>
       <c r="P38" s="2">
         <v>17.802507034008837</v>
       </c>
       <c r="Q38" s="2">
-        <v>70.36144578313252</v>
+        <v>71.07142857142857</v>
       </c>
       <c r="R38" s="2">
-        <v>60</v>
+        <v>63.63095238095239</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T38" s="2">
-        <v>-4.09</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -4446,7 +4466,7 @@
         <v>-0.35</v>
       </c>
       <c r="C39" s="1">
-        <v>22.89156626506024</v>
+        <v>22.61904761904762</v>
       </c>
       <c r="D39" s="1">
         <v>38.714285714285715</v>
@@ -4455,49 +4475,49 @@
         <v>-1.29</v>
       </c>
       <c r="F39" s="1">
-        <v>0.06082796966166876</v>
+        <v>0.0338278408960873</v>
       </c>
       <c r="G39" s="1">
         <v>1.12</v>
       </c>
       <c r="H39" s="1">
-        <v>44.04</v>
+        <v>41.19</v>
       </c>
       <c r="I39" s="1">
-        <v>-2.59</v>
+        <v>-3.93</v>
       </c>
       <c r="J39" s="1">
-        <v>-0.0027080927066651856</v>
+        <v>-0.0046964101108271745</v>
       </c>
       <c r="K39" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="1">
         <v>-1</v>
       </c>
       <c r="M39" s="1">
-        <v>0.06507804647882476</v>
+        <v>0.03719552307939189</v>
       </c>
       <c r="N39" s="1">
-        <v>11.124535328845798</v>
+        <v>7.600954127359692</v>
       </c>
       <c r="O39" s="1">
-        <v>62.65060240963856</v>
+        <v>59.523809523809526</v>
       </c>
       <c r="P39" s="1">
         <v>30.28933322215756</v>
       </c>
       <c r="Q39" s="1">
-        <v>47.34939759036144</v>
+        <v>45.83333333333333</v>
       </c>
       <c r="R39" s="1">
-        <v>43.13253012048193</v>
+        <v>41.8452380952381</v>
       </c>
       <c r="S39" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="T39" s="1">
-        <v>17.34</v>
+        <v>16.05</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -4508,28 +4528,28 @@
         <v>-9.13</v>
       </c>
       <c r="C40" s="1">
-        <v>2.4096385542168677</v>
+        <v>2.380952380952381</v>
       </c>
       <c r="D40" s="1">
-        <v>10.77984665936473</v>
+        <v>10.75575027382256</v>
       </c>
       <c r="E40" s="1">
         <v>3.93</v>
       </c>
       <c r="F40" s="1">
-        <v>0.24190292855170817</v>
+        <v>0.35583345074192746</v>
       </c>
       <c r="G40" s="1">
-        <v>0.69</v>
+        <v>0.57</v>
       </c>
       <c r="H40" s="1">
-        <v>64.36</v>
+        <v>65.74</v>
       </c>
       <c r="I40" s="1">
-        <v>2.85</v>
+        <v>7.49</v>
       </c>
       <c r="J40" s="1">
-        <v>0.04425563961017143</v>
+        <v>0.04219847071029511</v>
       </c>
       <c r="K40" s="1" t="b">
         <v>0</v>
@@ -4538,28 +4558,28 @@
         <v>-21</v>
       </c>
       <c r="M40" s="1">
-        <v>0.23092356344072185</v>
+        <v>0.34376592291841934</v>
       </c>
       <c r="N40" s="1">
-        <v>27.70908702503551</v>
+        <v>38.25799411126243</v>
       </c>
       <c r="O40" s="1">
-        <v>89.1566265060241</v>
+        <v>92.85714285714286</v>
       </c>
       <c r="P40" s="1">
         <v>51.940889187924654</v>
       </c>
       <c r="Q40" s="1">
-        <v>55.18072289156627</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="R40" s="1">
-        <v>44.81927710843374</v>
+        <v>46.13095238095238</v>
       </c>
       <c r="S40" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="T40" s="1">
-        <v>36.34</v>
+        <v>37.66</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -4570,7 +4590,7 @@
         <v>-4.97</v>
       </c>
       <c r="C41" s="3">
-        <v>4.819277108433735</v>
+        <v>4.761904761904762</v>
       </c>
       <c r="D41" s="3">
         <v>1.5533199195171026</v>
@@ -4579,19 +4599,19 @@
         <v>0.01</v>
       </c>
       <c r="F41" s="3">
-        <v>-0.19243583208496018</v>
+        <v>-0.1710458223895145</v>
       </c>
       <c r="G41" s="3">
         <v>1.21</v>
       </c>
       <c r="H41" s="3">
-        <v>41.16</v>
+        <v>40.93</v>
       </c>
       <c r="I41" s="3">
-        <v>-11.48</v>
+        <v>-11.44</v>
       </c>
       <c r="J41" s="3">
-        <v>-0.003826616292049831</v>
+        <v>-0.008618924068727829</v>
       </c>
       <c r="K41" s="3" t="b">
         <v>0</v>
@@ -4600,28 +4620,28 @@
         <v>3</v>
       </c>
       <c r="M41" s="3">
-        <v>-0.1849981976549372</v>
+        <v>-0.16515237856873144</v>
       </c>
       <c r="N41" s="3">
-        <v>-13.883089084530386</v>
+        <v>-12.633836037452648</v>
       </c>
       <c r="O41" s="3">
-        <v>14.457831325301203</v>
+        <v>22.61904761904762</v>
       </c>
       <c r="P41" s="3">
         <v>30.769232468942608</v>
       </c>
       <c r="Q41" s="3">
-        <v>26.867469879518072</v>
+        <v>25.714285714285715</v>
       </c>
       <c r="R41" s="3">
-        <v>14.09638554216868</v>
+        <v>16.011904761904763</v>
       </c>
       <c r="S41" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T41" s="3">
-        <v>-22.55</v>
+        <v>-20.63</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -4632,7 +4652,7 @@
         <v>3.33</v>
       </c>
       <c r="C42" s="1">
-        <v>51.80722891566265</v>
+        <v>51.19047619047619</v>
       </c>
       <c r="D42" s="1">
         <v>1.2342342342342343</v>
@@ -4641,19 +4661,19 @@
         <v>4.37</v>
       </c>
       <c r="F42" s="1">
-        <v>-0.09997228985541207</v>
+        <v>-0.11119920037718439</v>
       </c>
       <c r="G42" s="1">
         <v>0.31</v>
       </c>
       <c r="H42" s="1">
-        <v>36.76</v>
+        <v>29.9</v>
       </c>
       <c r="I42" s="1">
-        <v>-7.8</v>
+        <v>-8.94</v>
       </c>
       <c r="J42" s="1">
-        <v>-0.012686672734253735</v>
+        <v>-0.01334438891230663</v>
       </c>
       <c r="K42" s="1" t="b">
         <v>0</v>
@@ -4662,28 +4682,28 @@
         <v>15</v>
       </c>
       <c r="M42" s="1">
-        <v>-0.12441023155405906</v>
+        <v>-0.1305633729311858</v>
       </c>
       <c r="N42" s="1">
-        <v>-7.824292474442575</v>
+        <v>-9.174935473698085</v>
       </c>
       <c r="O42" s="1">
-        <v>25.301204819277107</v>
+        <v>26.190476190476193</v>
       </c>
       <c r="P42" s="1">
-        <v>14.795072191248144</v>
+        <v>15.213803115341037</v>
       </c>
       <c r="Q42" s="1">
-        <v>36.024096385542165</v>
+        <v>35.595238095238095</v>
       </c>
       <c r="R42" s="1">
-        <v>31.746987951807228</v>
+        <v>31.904761904761912</v>
       </c>
       <c r="S42" s="1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="T42" s="1">
-        <v>-3.74</v>
+        <v>-3.58</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -4694,28 +4714,28 @@
         <v>0.15</v>
       </c>
       <c r="C43" s="2">
-        <v>32.53012048192771</v>
+        <v>32.142857142857146</v>
       </c>
       <c r="D43" s="2">
-        <v>149.86666666666667</v>
+        <v>150.40000000000003</v>
       </c>
       <c r="E43" s="2">
         <v>8.86</v>
       </c>
       <c r="F43" s="2">
-        <v>0.13114534829930147</v>
+        <v>0.22645110931947438</v>
       </c>
       <c r="G43" s="2">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="H43" s="2">
-        <v>50.35</v>
+        <v>60.98</v>
       </c>
       <c r="I43" s="2">
-        <v>15.72</v>
+        <v>26.84</v>
       </c>
       <c r="J43" s="2">
-        <v>0.019776415536176463</v>
+        <v>0.017405124119254923</v>
       </c>
       <c r="K43" s="2" t="b">
         <v>1</v>
@@ -4724,28 +4744,28 @@
         <v>17</v>
       </c>
       <c r="M43" s="2">
-        <v>0.14354140568267315</v>
+        <v>0.23599287550550407</v>
       </c>
       <c r="N43" s="2">
-        <v>18.970871249230644</v>
+        <v>27.480689369970897</v>
       </c>
       <c r="O43" s="2">
-        <v>78.3132530120482</v>
+        <v>84.52380952380952</v>
       </c>
       <c r="P43" s="2">
         <v>24.82490242340647</v>
       </c>
       <c r="Q43" s="2">
-        <v>67.59036144578315</v>
+        <v>70.59523809523809</v>
       </c>
       <c r="R43" s="2">
-        <v>57.349397590361455</v>
+        <v>59.34523809523809</v>
       </c>
       <c r="S43" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="T43" s="2">
-        <v>4.97</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -4756,58 +4776,58 @@
         <v>1.48</v>
       </c>
       <c r="C44" s="2">
-        <v>42.168674698795186</v>
+        <v>41.66666666666667</v>
       </c>
       <c r="D44" s="2">
-        <v>19.14189189189189</v>
+        <v>18.986486486486484</v>
       </c>
       <c r="E44" s="2">
         <v>-0.68</v>
       </c>
       <c r="F44" s="2">
-        <v>0.061585115155112516</v>
+        <v>0.15213440320259755</v>
       </c>
       <c r="G44" s="2">
         <v>2.64</v>
       </c>
       <c r="H44" s="2">
-        <v>40.7</v>
+        <v>43.29</v>
       </c>
       <c r="I44" s="2">
-        <v>-0.69</v>
+        <v>0.94</v>
       </c>
       <c r="J44" s="2">
-        <v>0.012416747713801086</v>
+        <v>0.009516185097174473</v>
       </c>
       <c r="K44" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L44" s="2">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="M44" s="2">
-        <v>0.11966949832291118</v>
+        <v>0.19815939304109365</v>
       </c>
       <c r="N44" s="2">
-        <v>16.583680513254443</v>
+        <v>23.697341123529867</v>
       </c>
       <c r="O44" s="2">
-        <v>75.90361445783132</v>
+        <v>79.76190476190477</v>
       </c>
       <c r="P44" s="2">
         <v>29.40653991657008</v>
       </c>
       <c r="Q44" s="2">
-        <v>56.26506024096386</v>
+        <v>57.85714285714286</v>
       </c>
       <c r="R44" s="2">
-        <v>53.6144578313253</v>
+        <v>54.16666666666668</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T44" s="2">
-        <v>18.8</v>
+        <v>19.35</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
@@ -4818,7 +4838,7 @@
         <v>12.43</v>
       </c>
       <c r="C45" s="1">
-        <v>81.92771084337349</v>
+        <v>82.14285714285714</v>
       </c>
       <c r="D45" s="1">
         <v>-2.3531777956556716</v>
@@ -4827,19 +4847,19 @@
         <v>1.03</v>
       </c>
       <c r="F45" s="1">
-        <v>0.0011221198160171614</v>
+        <v>0.011395111336318639</v>
       </c>
       <c r="G45" s="1">
         <v>1.45</v>
       </c>
       <c r="H45" s="1">
-        <v>46.22</v>
+        <v>44.33</v>
       </c>
       <c r="I45" s="1">
-        <v>5.84</v>
+        <v>4.94</v>
       </c>
       <c r="J45" s="1">
-        <v>0.0076322629666575196</v>
+        <v>0.005988594063351231</v>
       </c>
       <c r="K45" s="1" t="b">
         <v>0</v>
@@ -4848,28 +4868,28 @@
         <v>196</v>
       </c>
       <c r="M45" s="1">
-        <v>0.017059907880352165</v>
+        <v>0.024023919523710857</v>
       </c>
       <c r="N45" s="1">
-        <v>6.322721468998552</v>
+        <v>6.283793771791587</v>
       </c>
       <c r="O45" s="1">
-        <v>55.42168674698795</v>
+        <v>55.952380952380956</v>
       </c>
       <c r="P45" s="1">
         <v>17.57882034058413</v>
       </c>
       <c r="Q45" s="1">
-        <v>47.46987951807229</v>
+        <v>47.5</v>
       </c>
       <c r="R45" s="1">
-        <v>41.325301204819276</v>
+        <v>41.488095238095234</v>
       </c>
       <c r="S45" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T45" s="1">
-        <v>-3</v>
+        <v>-2.84</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
@@ -4880,7 +4900,7 @@
         <v>-0.34</v>
       </c>
       <c r="C46" s="3">
-        <v>24.096385542168676</v>
+        <v>23.809523809523807</v>
       </c>
       <c r="D46" s="3">
         <v>473.05882352941177</v>
@@ -4889,19 +4909,19 @@
         <v>4.53</v>
       </c>
       <c r="F46" s="3">
-        <v>-0.2143311526386142</v>
+        <v>-0.23994457657298007</v>
       </c>
       <c r="G46" s="3">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="H46" s="3">
-        <v>37.74</v>
+        <v>35.37</v>
       </c>
       <c r="I46" s="3">
-        <v>-26.97</v>
+        <v>-29.28</v>
       </c>
       <c r="J46" s="3">
-        <v>-0.0031471632843369803</v>
+        <v>-0.005392628447964363</v>
       </c>
       <c r="K46" s="3" t="b">
         <v>0</v>
@@ -4910,28 +4930,28 @@
         <v>17</v>
       </c>
       <c r="M46" s="3">
-        <v>-0.18741399946329285</v>
+        <v>-0.21833528256344226</v>
       </c>
       <c r="N46" s="3">
-        <v>-14.124669265365952</v>
+        <v>-17.95212643692373</v>
       </c>
       <c r="O46" s="3">
-        <v>13.253012048192772</v>
+        <v>15.476190476190476</v>
       </c>
       <c r="P46" s="3">
         <v>54.33673655574689</v>
       </c>
       <c r="Q46" s="3">
-        <v>45.66265060240964</v>
+        <v>44.76190476190476</v>
       </c>
       <c r="R46" s="3">
-        <v>28.012048192771083</v>
+        <v>28.33333333333333</v>
       </c>
       <c r="S46" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T46" s="3">
-        <v>6.98</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
@@ -4942,7 +4962,7 @@
         <v>8.67</v>
       </c>
       <c r="C47" s="1">
-        <v>74.69879518072288</v>
+        <v>73.80952380952381</v>
       </c>
       <c r="D47" s="1">
         <v>-0.7716262975778546</v>
@@ -4951,49 +4971,49 @@
         <v>2.59</v>
       </c>
       <c r="F47" s="1">
-        <v>0.20487221421397078</v>
+        <v>0.1493413552637205</v>
       </c>
       <c r="G47" s="1">
         <v>1.41</v>
       </c>
       <c r="H47" s="1">
-        <v>63.38</v>
+        <v>55.62</v>
       </c>
       <c r="I47" s="1">
-        <v>9.7</v>
+        <v>6.66</v>
       </c>
       <c r="J47" s="1">
-        <v>0.021359255911393687</v>
+        <v>0.02088932491538467</v>
       </c>
       <c r="K47" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="1">
         <v>-54</v>
       </c>
       <c r="M47" s="1">
-        <v>0.21939331000592044</v>
+        <v>0.16084760272334453</v>
       </c>
       <c r="N47" s="1">
-        <v>26.556061681555377</v>
+        <v>19.966162091754942</v>
       </c>
       <c r="O47" s="1">
-        <v>84.33734939759037</v>
+        <v>77.38095238095238</v>
       </c>
       <c r="P47" s="1">
         <v>33.3731909304046</v>
       </c>
       <c r="Q47" s="1">
-        <v>59.1566265060241</v>
+        <v>57.261904761904766</v>
       </c>
       <c r="R47" s="1">
-        <v>48.73493975903615</v>
+        <v>46.785714285714285</v>
       </c>
       <c r="S47" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T47" s="1">
-        <v>22.88</v>
+        <v>20.93</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
@@ -5004,7 +5024,7 @@
         <v>3.17</v>
       </c>
       <c r="C48" s="2">
-        <v>49.39759036144578</v>
+        <v>48.80952380952381</v>
       </c>
       <c r="D48" s="2">
         <v>7.583596214511041</v>
@@ -5013,49 +5033,49 @@
         <v>0.65</v>
       </c>
       <c r="F48" s="2">
-        <v>0.20837905756396924</v>
+        <v>0.09430081661353241</v>
       </c>
       <c r="G48" s="2">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="H48" s="2">
-        <v>49.06</v>
+        <v>47.7</v>
       </c>
       <c r="I48" s="2">
-        <v>23.33</v>
+        <v>21.78</v>
       </c>
       <c r="J48" s="2">
-        <v>0.016077663016155867</v>
+        <v>0.015972105415578995</v>
       </c>
       <c r="K48" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L48" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M48" s="2">
-        <v>0.22998361471784556</v>
+        <v>0.11170050789393948</v>
       </c>
       <c r="N48" s="2">
-        <v>27.6150921527479</v>
+        <v>15.051452608814447</v>
       </c>
       <c r="O48" s="2">
-        <v>87.95180722891565</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="P48" s="2">
         <v>23.23749735248456</v>
       </c>
       <c r="Q48" s="2">
-        <v>63.253012048192765</v>
+        <v>63.214285714285715</v>
       </c>
       <c r="R48" s="2">
-        <v>58.13253012048192</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="S48" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="T48" s="2">
-        <v>8.86</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
@@ -5066,7 +5086,7 @@
         <v>-0.19</v>
       </c>
       <c r="C49" s="2">
-        <v>27.710843373493976</v>
+        <v>27.380952380952383</v>
       </c>
       <c r="D49" s="2">
         <v>2010.578947368421</v>
@@ -5075,49 +5095,49 @@
         <v>-11.05</v>
       </c>
       <c r="F49" s="2">
-        <v>0.017019506036860935</v>
+        <v>0.06976828110732493</v>
       </c>
       <c r="G49" s="2">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H49" s="2">
-        <v>57.62</v>
+        <v>57.77</v>
       </c>
       <c r="I49" s="2">
-        <v>-1.38</v>
+        <v>-0.37</v>
       </c>
       <c r="J49" s="2">
-        <v>0.020284380043506824</v>
+        <v>0.01967291624853963</v>
       </c>
       <c r="K49" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L49" s="2">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="M49" s="2">
-        <v>0.01949871751353527</v>
+        <v>0.07145212219897723</v>
       </c>
       <c r="N49" s="2">
-        <v>6.566602432316857</v>
+        <v>11.026614039318213</v>
       </c>
       <c r="O49" s="2">
-        <v>57.831325301204814</v>
+        <v>67.85714285714286</v>
       </c>
       <c r="P49" s="2">
         <v>31.00158698078384</v>
       </c>
       <c r="Q49" s="2">
-        <v>68.07228915662651</v>
+        <v>67.97619047619048</v>
       </c>
       <c r="R49" s="2">
-        <v>51.20481927710843</v>
+        <v>54.226190476190474</v>
       </c>
       <c r="S49" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T49" s="2">
-        <v>20.11</v>
+        <v>23.13</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
@@ -5128,7 +5148,7 @@
         <v>-3.77</v>
       </c>
       <c r="C50" s="3">
-        <v>8.433734939759036</v>
+        <v>8.333333333333332</v>
       </c>
       <c r="D50" s="3">
         <v>15.862068965517242</v>
@@ -5137,19 +5157,19 @@
         <v>12.9</v>
       </c>
       <c r="F50" s="3">
-        <v>-0.30135975488395794</v>
+        <v>-0.3130166929384501</v>
       </c>
       <c r="G50" s="3">
-        <v>3.84</v>
+        <v>3.83</v>
       </c>
       <c r="H50" s="3">
-        <v>52.54</v>
+        <v>52.06</v>
       </c>
       <c r="I50" s="3">
-        <v>4.06</v>
+        <v>3.53</v>
       </c>
       <c r="J50" s="3">
-        <v>-0.014966319166082306</v>
+        <v>-0.009173609071791338</v>
       </c>
       <c r="K50" s="3" t="b">
         <v>0</v>
@@ -5158,25 +5178,25 @@
         <v>69</v>
       </c>
       <c r="M50" s="3">
-        <v>-0.2007746035445993</v>
+        <v>-0.2335955214488501</v>
       </c>
       <c r="N50" s="3">
-        <v>-15.460729673496596</v>
+        <v>-19.478150325464515</v>
       </c>
       <c r="O50" s="3">
-        <v>12.048192771084338</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="P50" s="3">
         <v>41.201484669672254</v>
       </c>
       <c r="Q50" s="3">
-        <v>41.445783132530124</v>
+        <v>43.0952380952381</v>
       </c>
       <c r="R50" s="3">
-        <v>18.192771084337352</v>
+        <v>19.94047619047619</v>
       </c>
       <c r="S50" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T50" s="3"/>
     </row>
@@ -5188,7 +5208,7 @@
         <v>-7.19</v>
       </c>
       <c r="C51" s="1">
-        <v>3.614457831325301</v>
+        <v>3.571428571428571</v>
       </c>
       <c r="D51" s="1">
         <v>5.305980528511822</v>
@@ -5197,171 +5217,169 @@
         <v>14.41</v>
       </c>
       <c r="F51" s="1">
-        <v>0.3048778350044126</v>
+        <v>0.17963645168770112</v>
       </c>
       <c r="G51" s="1">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="H51" s="1">
-        <v>66.99</v>
+        <v>65.43</v>
       </c>
       <c r="I51" s="1">
-        <v>37.05</v>
+        <v>34.96</v>
       </c>
       <c r="J51" s="1">
-        <v>0.05940289609896233</v>
+        <v>0.05269183044390552</v>
       </c>
       <c r="K51" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" s="1">
         <v>14</v>
       </c>
       <c r="M51" s="1">
-        <v>0.33073246897544495</v>
+        <v>0.19928126442364458</v>
       </c>
       <c r="N51" s="1">
-        <v>37.689977578507836</v>
+        <v>23.80952826178494</v>
       </c>
       <c r="O51" s="1">
-        <v>95.18072289156626</v>
+        <v>80.95238095238095</v>
       </c>
       <c r="P51" s="1">
         <v>38.38748944617691</v>
       </c>
       <c r="Q51" s="1">
-        <v>56.86746987951808</v>
+        <v>56.66666666666667</v>
       </c>
       <c r="R51" s="1">
-        <v>46.02409638554217</v>
+        <v>41.84523809523809</v>
       </c>
       <c r="S51" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T51" s="1"/>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
+      <c r="A52" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B52" s="1">
-        <v>5.63</v>
-      </c>
-      <c r="C52" s="1">
-        <v>61.44578313253012</v>
-      </c>
-      <c r="D52" s="1">
-        <v>0.7761989342806395</v>
-      </c>
-      <c r="E52" s="1">
-        <v>-1.38</v>
-      </c>
-      <c r="F52" s="1">
-        <v>-0.0007499657088120004</v>
-      </c>
-      <c r="G52" s="1">
-        <v>0.98</v>
-      </c>
-      <c r="H52" s="1">
-        <v>31.21</v>
-      </c>
-      <c r="I52" s="1">
-        <v>1.86</v>
-      </c>
-      <c r="J52" s="1">
-        <v>0.001402119012330762</v>
-      </c>
-      <c r="K52" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L52" s="1">
-        <v>84</v>
-      </c>
-      <c r="M52" s="1">
-        <v>-0.0014583118450046673</v>
-      </c>
-      <c r="N52" s="1">
-        <v>4.470899496462871</v>
-      </c>
-      <c r="O52" s="1">
-        <v>48.19277108433735</v>
-      </c>
-      <c r="P52" s="1">
-        <v>11.383174615246535</v>
-      </c>
-      <c r="Q52" s="1">
-        <v>45.3012048192771</v>
-      </c>
-      <c r="R52" s="1">
-        <v>44.1566265060241</v>
-      </c>
-      <c r="S52" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="T52" s="1">
-        <v>3.73</v>
-      </c>
+      <c r="B52" s="3">
+        <v>12.2</v>
+      </c>
+      <c r="C52" s="3">
+        <v>79.76190476190477</v>
+      </c>
+      <c r="D52" s="3">
+        <v>-1.9934426229508198</v>
+      </c>
+      <c r="E52" s="3">
+        <v>-5.11</v>
+      </c>
+      <c r="F52" s="3">
+        <v>-0.19207949801295793</v>
+      </c>
+      <c r="G52" s="3">
+        <v>0.92</v>
+      </c>
+      <c r="H52" s="3">
+        <v>35.49</v>
+      </c>
+      <c r="I52" s="3">
+        <v>-33.72</v>
+      </c>
+      <c r="J52" s="3">
+        <v>-0.013819046212626454</v>
+      </c>
+      <c r="K52" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L52" s="3">
+        <v>-106</v>
+      </c>
+      <c r="M52" s="3">
+        <v>-0.19432461946849433</v>
+      </c>
+      <c r="N52" s="3">
+        <v>-15.551060127428942</v>
+      </c>
+      <c r="O52" s="3">
+        <v>17.857142857142858</v>
+      </c>
+      <c r="P52" s="3">
+        <v>41.9219479219836</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>31.78571428571429</v>
+      </c>
+      <c r="R52" s="3">
+        <v>20.714285714285715</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="T52" s="3"/>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>52</v>
       </c>
       <c r="B53" s="1">
-        <v>23.25</v>
+        <v>5.63</v>
       </c>
       <c r="C53" s="1">
-        <v>93.97590361445783</v>
+        <v>60.71428571428571</v>
       </c>
       <c r="D53" s="1">
-        <v>-0.1840860215053764</v>
+        <v>0.7761989342806395</v>
       </c>
       <c r="E53" s="1">
-        <v>0.68</v>
+        <v>-1.38</v>
       </c>
       <c r="F53" s="1">
-        <v>-0.15478572046918285</v>
+        <v>-0.01488236910196998</v>
       </c>
       <c r="G53" s="1">
-        <v>1.58</v>
+        <v>0.98</v>
       </c>
       <c r="H53" s="1">
-        <v>41.82</v>
+        <v>28.75</v>
       </c>
       <c r="I53" s="1">
-        <v>2</v>
+        <v>0.73</v>
       </c>
       <c r="J53" s="1">
-        <v>-0.0243502086491039</v>
+        <v>0.0015174016725078593</v>
       </c>
       <c r="K53" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L53" s="1">
-        <v>350</v>
+        <v>83</v>
       </c>
       <c r="M53" s="1">
-        <v>-0.1342436825195955</v>
+        <v>-0.015443649465854081</v>
       </c>
       <c r="N53" s="1">
-        <v>-8.807637570996214</v>
+        <v>2.3370368728350774</v>
       </c>
       <c r="O53" s="1">
-        <v>21.686746987951807</v>
+        <v>48.80952380952381</v>
       </c>
       <c r="P53" s="1">
-        <v>26.83257063748809</v>
+        <v>11.84024085938085</v>
       </c>
       <c r="Q53" s="1">
-        <v>45.42168674698795</v>
+        <v>45.714285714285715</v>
       </c>
       <c r="R53" s="1">
-        <v>31.445783132530117</v>
+        <v>44.28571428571429</v>
       </c>
       <c r="S53" s="1" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="T53" s="1">
-        <v>-27.15</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
@@ -5369,247 +5387,247 @@
         <v>53</v>
       </c>
       <c r="B54" s="1">
+        <v>23.25</v>
+      </c>
+      <c r="C54" s="1">
+        <v>94.04761904761905</v>
+      </c>
+      <c r="D54" s="1">
+        <v>-0.1840860215053764</v>
+      </c>
+      <c r="E54" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="F54" s="1">
+        <v>-0.19409200129650622</v>
+      </c>
+      <c r="G54" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="H54" s="1">
+        <v>38.96</v>
+      </c>
+      <c r="I54" s="1">
+        <v>0.11</v>
+      </c>
+      <c r="J54" s="1">
+        <v>-0.02302966946456977</v>
+      </c>
+      <c r="K54" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L54" s="1">
+        <v>349</v>
+      </c>
+      <c r="M54" s="1">
+        <v>-0.17781487074386737</v>
+      </c>
+      <c r="N54" s="1">
+        <v>-13.90008525496624</v>
+      </c>
+      <c r="O54" s="1">
+        <v>20.238095238095237</v>
+      </c>
+      <c r="P54" s="1">
+        <v>26.83257063748809</v>
+      </c>
+      <c r="Q54" s="1">
+        <v>45</v>
+      </c>
+      <c r="R54" s="1">
+        <v>31.666666666666668</v>
+      </c>
+      <c r="S54" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="T54" s="1">
+        <v>-26.93</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B55" s="1">
         <v>0.73</v>
       </c>
-      <c r="C54" s="1">
-        <v>37.34939759036144</v>
-      </c>
-      <c r="D54" s="1">
-        <v>112.9041095890411</v>
-      </c>
-      <c r="E54" s="1">
+      <c r="C55" s="1">
+        <v>36.904761904761905</v>
+      </c>
+      <c r="D55" s="1">
+        <v>113.35616438356165</v>
+      </c>
+      <c r="E55" s="1">
         <v>1.71</v>
       </c>
-      <c r="F54" s="1">
-        <v>-0.03666376420352385</v>
-      </c>
-      <c r="G54" s="1">
+      <c r="F55" s="1">
+        <v>-0.12901404016470144</v>
+      </c>
+      <c r="G55" s="1">
         <v>3.78</v>
       </c>
-      <c r="H54" s="1">
-        <v>57.27</v>
-      </c>
-      <c r="I54" s="1">
-        <v>31.4</v>
-      </c>
-      <c r="J54" s="1">
-        <v>-0.008330246091713334</v>
-      </c>
-      <c r="K54" s="1" t="b">
+      <c r="H55" s="1">
+        <v>55.91</v>
+      </c>
+      <c r="I55" s="1">
+        <v>29.06</v>
+      </c>
+      <c r="J55" s="1">
+        <v>-0.004621200860634374</v>
+      </c>
+      <c r="K55" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L54" s="1">
+      <c r="L55" s="1">
         <v>321</v>
       </c>
-      <c r="M54" s="1">
-        <v>0.06179634872725681</v>
-      </c>
-      <c r="N54" s="1">
-        <v>10.796365553689013</v>
-      </c>
-      <c r="O54" s="1">
-        <v>61.44578313253012</v>
-      </c>
-      <c r="P54" s="1">
+      <c r="M55" s="1">
+        <v>-0.05099606958481173</v>
+      </c>
+      <c r="N55" s="1">
+        <v>-1.218205139060682</v>
+      </c>
+      <c r="O55" s="1">
+        <v>44.047619047619044</v>
+      </c>
+      <c r="P55" s="1">
         <v>52.65288503392759</v>
       </c>
-      <c r="Q54" s="1">
-        <v>61.204819277108435</v>
-      </c>
-      <c r="R54" s="1">
-        <v>43.43373493975904</v>
-      </c>
-      <c r="S54" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="T54" s="1">
-        <v>-16.57</v>
-      </c>
-    </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A55" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B55" s="3">
+      <c r="Q55" s="1">
+        <v>62.5</v>
+      </c>
+      <c r="R55" s="1">
+        <v>39.285714285714285</v>
+      </c>
+      <c r="S55" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="T55" s="1">
+        <v>-20.71</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B56" s="3">
         <v>4.42</v>
       </c>
-      <c r="C55" s="3">
-        <v>56.62650602409639</v>
-      </c>
-      <c r="D55" s="3">
+      <c r="C56" s="3">
+        <v>55.952380952380956</v>
+      </c>
+      <c r="D56" s="3">
         <v>7.147058823529411</v>
       </c>
-      <c r="E55" s="3">
+      <c r="E56" s="3">
         <v>-1.32</v>
       </c>
-      <c r="F55" s="3">
-        <v>-0.22003637590340908</v>
-      </c>
-      <c r="G55" s="3">
-        <v>2.04</v>
-      </c>
-      <c r="H55" s="3">
-        <v>40.19</v>
-      </c>
-      <c r="I55" s="3">
-        <v>-6.92</v>
-      </c>
-      <c r="J55" s="3">
-        <v>-0.017157363306274934</v>
-      </c>
-      <c r="K55" s="3" t="b">
+      <c r="F56" s="3">
+        <v>-0.28447959561421315</v>
+      </c>
+      <c r="G56" s="3">
+        <v>2.05</v>
+      </c>
+      <c r="H56" s="3">
+        <v>38.57</v>
+      </c>
+      <c r="I56" s="3">
+        <v>-9.25</v>
+      </c>
+      <c r="J56" s="3">
+        <v>-0.018492553887907257</v>
+      </c>
+      <c r="K56" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L55" s="3">
+      <c r="L56" s="3">
         <v>249</v>
       </c>
-      <c r="M55" s="3">
-        <v>-0.1832023768213904</v>
-      </c>
-      <c r="N55" s="3">
-        <v>-13.703507001175709</v>
-      </c>
-      <c r="O55" s="3">
-        <v>15.66265060240964</v>
-      </c>
-      <c r="P55" s="3">
+      <c r="M56" s="3">
+        <v>-0.25501237651029796</v>
+      </c>
+      <c r="N56" s="3">
+        <v>-21.619835831609308</v>
+      </c>
+      <c r="O56" s="3">
+        <v>13.095238095238097</v>
+      </c>
+      <c r="P56" s="3">
         <v>40.717118046641446</v>
       </c>
-      <c r="Q55" s="3">
-        <v>43.6144578313253</v>
-      </c>
-      <c r="R55" s="3">
-        <v>27.89156626506025</v>
-      </c>
-      <c r="S55" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="T55" s="3">
-        <v>-21.07</v>
-      </c>
-    </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B56" s="1">
+      <c r="Q56" s="3">
+        <v>43.57142857142857</v>
+      </c>
+      <c r="R56" s="3">
+        <v>27.26190476190476</v>
+      </c>
+      <c r="S56" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="T56" s="3">
+        <v>-21.7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B57" s="1">
         <v>-0.1</v>
       </c>
-      <c r="C56" s="1">
-        <v>28.915662650602407</v>
-      </c>
-      <c r="D56" s="1">
+      <c r="C57" s="1">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="D57" s="1">
         <v>316.79999999999995</v>
       </c>
-      <c r="E56" s="1">
+      <c r="E57" s="1">
         <v>1.24</v>
       </c>
-      <c r="F56" s="1">
-        <v>-0.06013873910642718</v>
-      </c>
-      <c r="G56" s="1">
-        <v>1.64</v>
-      </c>
-      <c r="H56" s="1">
+      <c r="F57" s="1">
+        <v>-0.03951178688229742</v>
+      </c>
+      <c r="G57" s="1">
+        <v>1.65</v>
+      </c>
+      <c r="H57" s="1">
         <v>36.78</v>
       </c>
-      <c r="I56" s="1">
-        <v>-20.92</v>
-      </c>
-      <c r="J56" s="1">
-        <v>0.003353509077609767</v>
-      </c>
-      <c r="K56" s="1" t="b">
+      <c r="I57" s="1">
+        <v>-20.78</v>
+      </c>
+      <c r="J57" s="1">
+        <v>0.00033428373596081193</v>
+      </c>
+      <c r="K57" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L56" s="1">
+      <c r="L57" s="1">
         <v>3</v>
       </c>
-      <c r="M56" s="1">
-        <v>-0.03747166274826186</v>
-      </c>
-      <c r="N56" s="1">
-        <v>0.8695644061371431</v>
-      </c>
-      <c r="O56" s="1">
-        <v>40.963855421686745</v>
-      </c>
-      <c r="P56" s="1">
-        <v>39.61783553142854</v>
-      </c>
-      <c r="Q56" s="1">
-        <v>49.51807228915663</v>
-      </c>
-      <c r="R56" s="1">
-        <v>40.36144578313253</v>
-      </c>
-      <c r="S56" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="T56" s="1">
-        <v>18.41</v>
-      </c>
-    </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A57" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B57" s="3">
-        <v>5.76</v>
-      </c>
-      <c r="C57" s="3">
-        <v>65.06024096385542</v>
-      </c>
-      <c r="D57" s="3">
-        <v>3.3177083333333335</v>
-      </c>
-      <c r="E57" s="3">
-        <v>0.97</v>
-      </c>
-      <c r="F57" s="3">
-        <v>-0.25434985987659464</v>
-      </c>
-      <c r="G57" s="3">
-        <v>1.87</v>
-      </c>
-      <c r="H57" s="3">
-        <v>39.37</v>
-      </c>
-      <c r="I57" s="3">
-        <v>6.14</v>
-      </c>
-      <c r="J57" s="3">
-        <v>-0.029420521253828977</v>
-      </c>
-      <c r="K57" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L57" s="3">
-        <v>518</v>
-      </c>
-      <c r="M57" s="3">
-        <v>-0.22353680295221368</v>
-      </c>
-      <c r="N57" s="3">
-        <v>-17.736949614258034</v>
-      </c>
-      <c r="O57" s="3">
-        <v>10.843373493975903</v>
-      </c>
-      <c r="P57" s="3">
-        <v>41.76493344029593</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>44.57831325301205</v>
-      </c>
-      <c r="R57" s="3">
-        <v>25.180722891566266</v>
-      </c>
-      <c r="S57" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="T57" s="3">
-        <v>-34.03</v>
+      <c r="M57" s="1">
+        <v>-0.02127017505606421</v>
+      </c>
+      <c r="N57" s="1">
+        <v>1.754384313814067</v>
+      </c>
+      <c r="O57" s="1">
+        <v>47.61904761904761</v>
+      </c>
+      <c r="P57" s="1">
+        <v>37.631577254992756</v>
+      </c>
+      <c r="Q57" s="1">
+        <v>49.642857142857146</v>
+      </c>
+      <c r="R57" s="1">
+        <v>42.55952380952381</v>
+      </c>
+      <c r="S57" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="T57" s="1">
+        <v>20.61</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
@@ -5617,247 +5635,247 @@
         <v>57</v>
       </c>
       <c r="B58" s="3">
+        <v>5.76</v>
+      </c>
+      <c r="C58" s="3">
+        <v>64.28571428571429</v>
+      </c>
+      <c r="D58" s="3">
+        <v>3.3177083333333335</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0.97</v>
+      </c>
+      <c r="F58" s="3">
+        <v>-0.317920015733788</v>
+      </c>
+      <c r="G58" s="3">
+        <v>1.88</v>
+      </c>
+      <c r="H58" s="3">
+        <v>37.83</v>
+      </c>
+      <c r="I58" s="3">
+        <v>3.51</v>
+      </c>
+      <c r="J58" s="3">
+        <v>-0.0285829849042525</v>
+      </c>
+      <c r="K58" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L58" s="3">
+        <v>518</v>
+      </c>
+      <c r="M58" s="3">
+        <v>-0.29322367972288765</v>
+      </c>
+      <c r="N58" s="3">
+        <v>-25.440966152868267</v>
+      </c>
+      <c r="O58" s="3">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="P58" s="3">
+        <v>41.76493344029593</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>43.6904761904762</v>
+      </c>
+      <c r="R58" s="3">
+        <v>24.345238095238095</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="T58" s="3">
+        <v>-34.86</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B59" s="3">
         <v>-0.67</v>
       </c>
-      <c r="C58" s="3">
-        <v>21.686746987951807</v>
-      </c>
-      <c r="D58" s="3">
+      <c r="C59" s="3">
+        <v>21.428571428571427</v>
+      </c>
+      <c r="D59" s="3">
         <v>2.417910447761194</v>
       </c>
-      <c r="E58" s="3">
+      <c r="E59" s="3">
         <v>-4.45</v>
       </c>
-      <c r="F58" s="3">
-        <v>-0.3803363216790769</v>
-      </c>
-      <c r="G58" s="3">
+      <c r="F59" s="3">
+        <v>-0.35646321151174687</v>
+      </c>
+      <c r="G59" s="3">
         <v>2.82</v>
       </c>
-      <c r="H58" s="3">
-        <v>37.94</v>
-      </c>
-      <c r="I58" s="3">
-        <v>-33.94</v>
-      </c>
-      <c r="J58" s="3">
-        <v>-0.03406704321764206</v>
-      </c>
-      <c r="K58" s="3" t="b">
+      <c r="H59" s="3">
+        <v>37.31</v>
+      </c>
+      <c r="I59" s="3">
+        <v>-34.04</v>
+      </c>
+      <c r="J59" s="3">
+        <v>-0.034985618157129354</v>
+      </c>
+      <c r="K59" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L58" s="3">
+      <c r="L59" s="3">
         <v>21</v>
       </c>
-      <c r="M58" s="3">
-        <v>-0.31587682328554423</v>
-      </c>
-      <c r="N58" s="3">
-        <v>-26.97095164759109</v>
-      </c>
-      <c r="O58" s="3">
-        <v>7.228915662650602</v>
-      </c>
-      <c r="P58" s="3">
+      <c r="M59" s="3">
+        <v>-0.3053866983982939</v>
+      </c>
+      <c r="N59" s="3">
+        <v>-26.657268020408896</v>
+      </c>
+      <c r="O59" s="3">
+        <v>7.142857142857142</v>
+      </c>
+      <c r="P59" s="3">
         <v>46.90217032437056</v>
       </c>
-      <c r="Q58" s="3">
-        <v>23.6144578313253</v>
-      </c>
-      <c r="R58" s="3">
-        <v>11.385542168674696</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="T58" s="3">
-        <v>-15.5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B59" s="2">
+      <c r="Q59" s="3">
+        <v>24.047619047619047</v>
+      </c>
+      <c r="R59" s="3">
+        <v>11.54761904761905</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="T59" s="3">
+        <v>-15.34</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B60" s="1">
         <v>4.35</v>
       </c>
-      <c r="C59" s="2">
-        <v>55.42168674698795</v>
-      </c>
-      <c r="D59" s="2">
-        <v>2.1172413793103453</v>
-      </c>
-      <c r="E59" s="2">
+      <c r="C60" s="1">
+        <v>54.761904761904766</v>
+      </c>
+      <c r="D60" s="1">
+        <v>2.124137931034483</v>
+      </c>
+      <c r="E60" s="1">
         <v>-0.53</v>
       </c>
-      <c r="F59" s="2">
-        <v>0.08326117526801474</v>
-      </c>
-      <c r="G59" s="2">
+      <c r="F60" s="1">
+        <v>0.017158339444140802</v>
+      </c>
+      <c r="G60" s="1">
         <v>1.2</v>
       </c>
-      <c r="H59" s="2">
-        <v>53.72</v>
-      </c>
-      <c r="I59" s="2">
-        <v>13.88</v>
-      </c>
-      <c r="J59" s="2">
-        <v>0.007703558276093762</v>
-      </c>
-      <c r="K59" s="2" t="b">
+      <c r="H60" s="1">
+        <v>32.67</v>
+      </c>
+      <c r="I60" s="1">
+        <v>7.18</v>
+      </c>
+      <c r="J60" s="1">
+        <v>0.006475190445758139</v>
+      </c>
+      <c r="K60" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L60" s="1">
+        <v>170</v>
+      </c>
+      <c r="M60" s="1">
+        <v>0.022771143082981782</v>
+      </c>
+      <c r="N60" s="1">
+        <v>6.158516127718678</v>
+      </c>
+      <c r="O60" s="1">
+        <v>54.761904761904766</v>
+      </c>
+      <c r="P60" s="1">
+        <v>8.239463877564281</v>
+      </c>
+      <c r="Q60" s="1">
+        <v>49.88095238095238</v>
+      </c>
+      <c r="R60" s="1">
+        <v>47.91666666666667</v>
+      </c>
+      <c r="S60" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="T60" s="1">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2">
+        <v>8.63</v>
+      </c>
+      <c r="C61" s="2">
+        <v>72.61904761904762</v>
+      </c>
+      <c r="D61" s="2">
+        <v>0.21089223638470433</v>
+      </c>
+      <c r="E61" s="2">
+        <v>0.11</v>
+      </c>
+      <c r="F61" s="2">
+        <v>0.08901526304575452</v>
+      </c>
+      <c r="G61" s="2">
+        <v>0.21</v>
+      </c>
+      <c r="H61" s="2">
+        <v>50.1</v>
+      </c>
+      <c r="I61" s="2">
+        <v>12.2</v>
+      </c>
+      <c r="J61" s="2">
+        <v>0.003842324958567833</v>
+      </c>
+      <c r="K61" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L59" s="2">
-        <v>170</v>
-      </c>
-      <c r="M59" s="2">
-        <v>0.09034463662994141</v>
-      </c>
-      <c r="N59" s="2">
-        <v>13.651194343957476</v>
-      </c>
-      <c r="O59" s="2">
-        <v>68.67469879518072</v>
-      </c>
-      <c r="P59" s="2">
-        <v>7.747915191962705</v>
-      </c>
-      <c r="Q59" s="2">
-        <v>58.07228915662651</v>
-      </c>
-      <c r="R59" s="2">
-        <v>51.9277108433735</v>
-      </c>
-      <c r="S59" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="T59" s="2">
-        <v>4.73</v>
-      </c>
-    </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B60" s="2">
-        <v>8.63</v>
-      </c>
-      <c r="C60" s="2">
-        <v>73.49397590361446</v>
-      </c>
-      <c r="D60" s="2">
-        <v>0.23638470451911922</v>
-      </c>
-      <c r="E60" s="2">
-        <v>0.11</v>
-      </c>
-      <c r="F60" s="2">
-        <v>0.09614956412598455</v>
-      </c>
-      <c r="G60" s="2">
-        <v>0.21</v>
-      </c>
-      <c r="H60" s="2">
-        <v>52.67</v>
-      </c>
-      <c r="I60" s="2">
-        <v>13.25</v>
-      </c>
-      <c r="J60" s="2">
-        <v>0.005924303532618246</v>
-      </c>
-      <c r="K60" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L60" s="2">
-        <v>94</v>
-      </c>
-      <c r="M60" s="2">
-        <v>0.06816989174637422</v>
-      </c>
-      <c r="N60" s="2">
-        <v>11.433719855600753</v>
-      </c>
-      <c r="O60" s="2">
-        <v>63.85542168674698</v>
-      </c>
-      <c r="P60" s="2">
+      <c r="L61" s="2">
+        <v>93</v>
+      </c>
+      <c r="M61" s="2">
+        <v>0.06684468867233262</v>
+      </c>
+      <c r="N61" s="2">
+        <v>10.565870686653756</v>
+      </c>
+      <c r="O61" s="2">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="P61" s="2">
         <v>7.56622762341097</v>
       </c>
-      <c r="Q60" s="2">
-        <v>57.95180722891566</v>
-      </c>
-      <c r="R60" s="2">
-        <v>51.144578313253</v>
-      </c>
-      <c r="S60" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="T60" s="2">
-        <v>5.17</v>
-      </c>
-    </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B61" s="1">
-        <v>44.17</v>
-      </c>
-      <c r="C61" s="1">
-        <v>98.79518072289156</v>
-      </c>
-      <c r="D61" s="1">
-        <v>1.5376952682816392</v>
-      </c>
-      <c r="E61" s="1">
-        <v>-1.07</v>
-      </c>
-      <c r="F61" s="1">
-        <v>-0.11078022494646482</v>
-      </c>
-      <c r="G61" s="1">
-        <v>2.24</v>
-      </c>
-      <c r="H61" s="1">
-        <v>46.72</v>
-      </c>
-      <c r="I61" s="1">
-        <v>48.14</v>
-      </c>
-      <c r="J61" s="1">
-        <v>-0.014443565039999856</v>
-      </c>
-      <c r="K61" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L61" s="1">
-        <v>934</v>
-      </c>
-      <c r="M61" s="1">
-        <v>-0.06686276450251949</v>
-      </c>
-      <c r="N61" s="1">
-        <v>-2.0695457692886157</v>
-      </c>
-      <c r="O61" s="1">
-        <v>38.55421686746988</v>
-      </c>
-      <c r="P61" s="1">
-        <v>39.10478556320163</v>
-      </c>
-      <c r="Q61" s="1">
-        <v>60.84337349397589</v>
-      </c>
-      <c r="R61" s="1">
-        <v>41.626506024096386</v>
-      </c>
-      <c r="S61" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="T61" s="1">
-        <v>-26.48</v>
+      <c r="Q61" s="2">
+        <v>55.833333333333336</v>
+      </c>
+      <c r="R61" s="2">
+        <v>51.904761904761905</v>
+      </c>
+      <c r="S61" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="T61" s="2">
+        <v>5.93</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
@@ -5865,61 +5883,61 @@
         <v>61</v>
       </c>
       <c r="B62" s="1">
-        <v>34.93</v>
+        <v>44.17</v>
       </c>
       <c r="C62" s="1">
-        <v>97.59036144578313</v>
+        <v>98.80952380952381</v>
       </c>
       <c r="D62" s="1">
-        <v>-1.5596908101918123</v>
+        <v>1.5390536563278243</v>
       </c>
       <c r="E62" s="1">
-        <v>1.52</v>
+        <v>-1.07</v>
       </c>
       <c r="F62" s="1">
-        <v>0.010918330562610656</v>
+        <v>-0.13255273116418548</v>
       </c>
       <c r="G62" s="1">
-        <v>0.96</v>
+        <v>2.25</v>
       </c>
       <c r="H62" s="1">
-        <v>41.84</v>
+        <v>47</v>
       </c>
       <c r="I62" s="1">
-        <v>1.73</v>
+        <v>47.56</v>
       </c>
       <c r="J62" s="1">
-        <v>-0.015651687538323376</v>
+        <v>-0.011404063520089628</v>
       </c>
       <c r="K62" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L62" s="1">
-        <v>367</v>
+        <v>933</v>
       </c>
       <c r="M62" s="1">
-        <v>0.009501638290225323</v>
+        <v>-0.0974727084214293</v>
       </c>
       <c r="N62" s="1">
-        <v>5.566894509985867</v>
+        <v>-5.865869022722432</v>
       </c>
       <c r="O62" s="1">
-        <v>50.602409638554214</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="P62" s="1">
-        <v>24.570041255395854</v>
+        <v>39.10478556320163</v>
       </c>
       <c r="Q62" s="1">
-        <v>43.373493975903614</v>
+        <v>63.0952380952381</v>
       </c>
       <c r="R62" s="1">
-        <v>38.91566265060241</v>
+        <v>40.89285714285714</v>
       </c>
       <c r="S62" s="1" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="T62" s="1">
-        <v>-5.84</v>
+        <v>-27.22</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
@@ -5927,681 +5945,681 @@
         <v>62</v>
       </c>
       <c r="B63" s="1">
+        <v>34.93</v>
+      </c>
+      <c r="C63" s="1">
+        <v>97.61904761904762</v>
+      </c>
+      <c r="D63" s="1">
+        <v>-1.5714285714285714</v>
+      </c>
+      <c r="E63" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="F63" s="1">
+        <v>-0.10943245551206178</v>
+      </c>
+      <c r="G63" s="1">
+        <v>1.02</v>
+      </c>
+      <c r="H63" s="1">
+        <v>37.54</v>
+      </c>
+      <c r="I63" s="1">
+        <v>-2.59</v>
+      </c>
+      <c r="J63" s="1">
+        <v>-0.017563774443349688</v>
+      </c>
+      <c r="K63" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L63" s="1">
+        <v>366</v>
+      </c>
+      <c r="M63" s="1">
+        <v>-0.10887117514817768</v>
+      </c>
+      <c r="N63" s="1">
+        <v>-7.005715695397279</v>
+      </c>
+      <c r="O63" s="1">
+        <v>29.761904761904763</v>
+      </c>
+      <c r="P63" s="1">
+        <v>25.543467249515373</v>
+      </c>
+      <c r="Q63" s="1">
+        <v>42.02380952380952</v>
+      </c>
+      <c r="R63" s="1">
+        <v>32.97619047619047</v>
+      </c>
+      <c r="S63" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="T63" s="1">
+        <v>-11.78</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B64" s="1">
         <v>7.62</v>
       </c>
-      <c r="C63" s="1">
-        <v>66.26506024096386</v>
-      </c>
-      <c r="D63" s="1">
+      <c r="C64" s="1">
+        <v>65.47619047619048</v>
+      </c>
+      <c r="D64" s="1">
         <v>-0.3740157480314961</v>
       </c>
-      <c r="E63" s="1">
+      <c r="E64" s="1">
         <v>0.39</v>
       </c>
-      <c r="F63" s="1">
-        <v>-0.07505515025656574</v>
-      </c>
-      <c r="G63" s="1">
+      <c r="F64" s="1">
+        <v>-0.07581948239747988</v>
+      </c>
+      <c r="G64" s="1">
         <v>0.36</v>
       </c>
-      <c r="H63" s="1">
-        <v>43.09</v>
-      </c>
-      <c r="I63" s="1">
-        <v>-7.59</v>
-      </c>
-      <c r="J63" s="1">
-        <v>-0.0014905033552541922</v>
-      </c>
-      <c r="K63" s="1" t="b">
+      <c r="H64" s="1">
+        <v>39.52</v>
+      </c>
+      <c r="I64" s="1">
+        <v>-8.18</v>
+      </c>
+      <c r="J64" s="1">
+        <v>-0.0023487886477502927</v>
+      </c>
+      <c r="K64" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L63" s="1">
-        <v>-100</v>
-      </c>
-      <c r="M63" s="1">
-        <v>-0.09772222661473107</v>
-      </c>
-      <c r="N63" s="1">
-        <v>-5.155491980509771</v>
-      </c>
-      <c r="O63" s="1">
-        <v>31.32530120481928</v>
-      </c>
-      <c r="P63" s="1">
+      <c r="L64" s="1">
+        <v>-99</v>
+      </c>
+      <c r="M64" s="1">
+        <v>-0.09378045404177104</v>
+      </c>
+      <c r="N64" s="1">
+        <v>-5.496643584756611</v>
+      </c>
+      <c r="O64" s="1">
+        <v>34.523809523809526</v>
+      </c>
+      <c r="P64" s="1">
         <v>14.852676969550105</v>
       </c>
-      <c r="Q63" s="1">
-        <v>41.204819277108435</v>
-      </c>
-      <c r="R63" s="1">
-        <v>33.85542168674699</v>
-      </c>
-      <c r="S63" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="T63" s="1">
-        <v>7.82</v>
-      </c>
-    </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B64" s="2">
+      <c r="Q64" s="1">
+        <v>40.476190476190474</v>
+      </c>
+      <c r="R64" s="1">
+        <v>35.05952380952382</v>
+      </c>
+      <c r="S64" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="T64" s="1">
+        <v>9.02</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2">
         <v>17.99</v>
       </c>
-      <c r="C64" s="2">
-        <v>89.1566265060241</v>
-      </c>
-      <c r="D64" s="2">
-        <v>0.32573652028904965</v>
-      </c>
-      <c r="E64" s="2">
+      <c r="C65" s="2">
+        <v>89.28571428571429</v>
+      </c>
+      <c r="D65" s="2">
+        <v>0.3379655364091163</v>
+      </c>
+      <c r="E65" s="2">
         <v>2.09</v>
       </c>
-      <c r="F64" s="2">
-        <v>0.14678101459185267</v>
-      </c>
-      <c r="G64" s="2">
+      <c r="F65" s="2">
+        <v>0.14489256596481664</v>
+      </c>
+      <c r="G65" s="2">
         <v>0.87</v>
       </c>
-      <c r="H64" s="2">
-        <v>61.44</v>
-      </c>
-      <c r="I64" s="2">
-        <v>18.26</v>
-      </c>
-      <c r="J64" s="2">
-        <v>0.00882702794679454</v>
-      </c>
-      <c r="K64" s="2" t="b">
+      <c r="H65" s="2">
+        <v>62.91</v>
+      </c>
+      <c r="I65" s="2">
+        <v>18.95</v>
+      </c>
+      <c r="J65" s="2">
+        <v>0.008725734380038465</v>
+      </c>
+      <c r="K65" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L64" s="2">
-        <v>81</v>
-      </c>
-      <c r="M64" s="2">
-        <v>0.14217676470660034</v>
-      </c>
-      <c r="N64" s="2">
-        <v>18.834407151623374</v>
-      </c>
-      <c r="O64" s="2">
-        <v>77.10843373493977</v>
-      </c>
-      <c r="P64" s="2">
+      <c r="L65" s="2">
+        <v>80</v>
+      </c>
+      <c r="M65" s="2">
+        <v>0.14124424359957</v>
+      </c>
+      <c r="N65" s="2">
+        <v>18.0058261793775</v>
+      </c>
+      <c r="O65" s="2">
+        <v>76.19047619047619</v>
+      </c>
+      <c r="P65" s="2">
         <v>11.000474713303552</v>
       </c>
-      <c r="Q64" s="2">
-        <v>67.10843373493975</v>
-      </c>
-      <c r="R64" s="2">
-        <v>59.81927710843374</v>
-      </c>
-      <c r="S64" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="T64" s="2">
+      <c r="Q65" s="2">
+        <v>67.61904761904762</v>
+      </c>
+      <c r="R65" s="2">
+        <v>59.82142857142858</v>
+      </c>
+      <c r="S65" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="T65" s="2">
         <v>16.22</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A65" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B65" s="3">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B66" s="3">
         <v>72.89</v>
       </c>
-      <c r="C65" s="3">
+      <c r="C66" s="3">
         <v>100</v>
       </c>
-      <c r="D65" s="3">
-        <v>-0.6841816435725065</v>
-      </c>
-      <c r="E65" s="3">
+      <c r="D66" s="3">
+        <v>-0.682809713266566</v>
+      </c>
+      <c r="E66" s="3">
         <v>1.65</v>
       </c>
-      <c r="F65" s="3">
-        <v>-0.32929328817874015</v>
-      </c>
-      <c r="G65" s="3">
-        <v>5.27</v>
-      </c>
-      <c r="H65" s="3">
-        <v>48.34</v>
-      </c>
-      <c r="I65" s="3">
-        <v>48.29</v>
-      </c>
-      <c r="J65" s="3">
-        <v>-0.02834489635136885</v>
-      </c>
-      <c r="K65" s="3" t="b">
+      <c r="F66" s="3">
+        <v>-0.37625682427058826</v>
+      </c>
+      <c r="G66" s="3">
+        <v>5.32</v>
+      </c>
+      <c r="H66" s="3">
+        <v>49.11</v>
+      </c>
+      <c r="I66" s="3">
+        <v>48.67</v>
+      </c>
+      <c r="J66" s="3">
+        <v>-0.023376347664004333</v>
+      </c>
+      <c r="K66" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L65" s="3">
+      <c r="L66" s="3">
         <v>667</v>
       </c>
-      <c r="M65" s="3">
-        <v>-0.17806138810160588</v>
-      </c>
-      <c r="N65" s="3">
-        <v>-13.189408129197261</v>
-      </c>
-      <c r="O65" s="3">
-        <v>16.867469879518072</v>
-      </c>
-      <c r="P65" s="3">
+      <c r="M66" s="3">
+        <v>-0.25502026567162295</v>
+      </c>
+      <c r="N66" s="3">
+        <v>-21.620624747741797</v>
+      </c>
+      <c r="O66" s="3">
+        <v>11.904761904761903</v>
+      </c>
+      <c r="P66" s="3">
         <v>56.49293299150161</v>
       </c>
-      <c r="Q65" s="3">
-        <v>51.807228915662655</v>
-      </c>
-      <c r="R65" s="3">
-        <v>25.361445783132524</v>
-      </c>
-      <c r="S65" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="T65" s="3">
-        <v>-44.03</v>
-      </c>
-    </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B66" s="1">
+      <c r="Q66" s="3">
+        <v>52.61904761904762</v>
+      </c>
+      <c r="R66" s="3">
+        <v>24.226190476190474</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="T66" s="3">
+        <v>-45.16</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B67" s="1">
         <v>13.87</v>
       </c>
-      <c r="C66" s="1">
-        <v>83.13253012048193</v>
-      </c>
-      <c r="D66" s="1">
+      <c r="C67" s="1">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="D67" s="1">
         <v>3.0958904109589045</v>
       </c>
-      <c r="E66" s="1">
+      <c r="E67" s="1">
         <v>-2.42</v>
       </c>
-      <c r="F66" s="1">
-        <v>-0.1288085002658646</v>
-      </c>
-      <c r="G66" s="1">
+      <c r="F67" s="1">
+        <v>-0.2044691877308949</v>
+      </c>
+      <c r="G67" s="1">
         <v>2.1</v>
       </c>
-      <c r="H66" s="1">
-        <v>42.85</v>
-      </c>
-      <c r="I66" s="1">
-        <v>29.98</v>
-      </c>
-      <c r="J66" s="1">
-        <v>-0.010312173073726555</v>
-      </c>
-      <c r="K66" s="1" t="b">
+      <c r="H67" s="1">
+        <v>44.26</v>
+      </c>
+      <c r="I67" s="1">
+        <v>31.58</v>
+      </c>
+      <c r="J67" s="1">
+        <v>-0.006571112690586851</v>
+      </c>
+      <c r="K67" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L66" s="1">
+      <c r="L67" s="1">
         <v>516</v>
       </c>
-      <c r="M66" s="1">
-        <v>-0.08984946277526795</v>
-      </c>
-      <c r="N66" s="1">
-        <v>-4.368215596563458</v>
-      </c>
-      <c r="O66" s="1">
-        <v>36.144578313253014</v>
-      </c>
-      <c r="P66" s="1">
+      <c r="M67" s="1">
+        <v>-0.17359876771726945</v>
+      </c>
+      <c r="N67" s="1">
+        <v>-13.478474952306449</v>
+      </c>
+      <c r="O67" s="1">
+        <v>21.428571428571427</v>
+      </c>
+      <c r="P67" s="1">
         <v>31.85898471566022</v>
       </c>
-      <c r="Q66" s="1">
-        <v>57.71084337349398</v>
-      </c>
-      <c r="R66" s="1">
-        <v>40.361445783132524</v>
-      </c>
-      <c r="S66" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="T66" s="1">
-        <v>-25.68</v>
-      </c>
-    </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A67" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B67" s="2">
+      <c r="Q67" s="1">
+        <v>60.47619047619049</v>
+      </c>
+      <c r="R67" s="1">
+        <v>36.78571428571429</v>
+      </c>
+      <c r="S67" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="T67" s="1">
+        <v>-29.25</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2">
         <v>16.5</v>
       </c>
-      <c r="C67" s="2">
-        <v>85.54216867469879</v>
-      </c>
-      <c r="D67" s="2">
-        <v>-0.19636363636363638</v>
-      </c>
-      <c r="E67" s="2">
+      <c r="C68" s="2">
+        <v>85.71428571428571</v>
+      </c>
+      <c r="D68" s="2">
+        <v>-0.19939393939393935</v>
+      </c>
+      <c r="E68" s="2">
         <v>-1.75</v>
       </c>
-      <c r="F67" s="2">
-        <v>0.11546671556504247</v>
-      </c>
-      <c r="G67" s="2">
+      <c r="F68" s="2">
+        <v>0.18702937424462948</v>
+      </c>
+      <c r="G68" s="2">
         <v>0.99</v>
       </c>
-      <c r="H67" s="2">
-        <v>47.68</v>
-      </c>
-      <c r="I67" s="2">
-        <v>-21.53</v>
-      </c>
-      <c r="J67" s="2">
-        <v>0.017995018226023292</v>
-      </c>
-      <c r="K67" s="2" t="b">
+      <c r="H68" s="2">
+        <v>49.63</v>
+      </c>
+      <c r="I68" s="2">
+        <v>-20.21</v>
+      </c>
+      <c r="J68" s="2">
+        <v>0.017030321227002713</v>
+      </c>
+      <c r="K68" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L67" s="2">
-        <v>-251</v>
-      </c>
-      <c r="M67" s="2">
-        <v>0.11511254249694614</v>
-      </c>
-      <c r="N67" s="2">
-        <v>16.12798493065795</v>
-      </c>
-      <c r="O67" s="2">
-        <v>74.69879518072288</v>
-      </c>
-      <c r="P67" s="2">
+      <c r="L68" s="2">
+        <v>-252</v>
+      </c>
+      <c r="M68" s="2">
+        <v>0.18674873406268744</v>
+      </c>
+      <c r="N68" s="2">
+        <v>22.556275225689244</v>
+      </c>
+      <c r="O68" s="2">
+        <v>78.57142857142857</v>
+      </c>
+      <c r="P68" s="2">
         <v>37.5868621181625</v>
       </c>
-      <c r="Q67" s="2">
-        <v>55.18072289156626</v>
-      </c>
-      <c r="R67" s="2">
-        <v>50.36144578313253</v>
-      </c>
-      <c r="S67" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="T67" s="2">
-        <v>32.62</v>
-      </c>
-    </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B68" s="1">
+      <c r="Q68" s="2">
+        <v>56.07142857142856</v>
+      </c>
+      <c r="R68" s="2">
+        <v>51.785714285714285</v>
+      </c>
+      <c r="S68" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="T68" s="2">
+        <v>34.04</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B69" s="1">
         <v>4.55</v>
       </c>
-      <c r="C68" s="1">
-        <v>57.831325301204814</v>
-      </c>
-      <c r="D68" s="1">
+      <c r="C69" s="1">
+        <v>57.14285714285714</v>
+      </c>
+      <c r="D69" s="1">
         <v>6.048351648351648</v>
       </c>
-      <c r="E68" s="1">
+      <c r="E69" s="1">
         <v>-0.51</v>
       </c>
-      <c r="F68" s="1">
-        <v>-0.02489421025857011</v>
-      </c>
-      <c r="G68" s="1">
+      <c r="F69" s="1">
+        <v>0.008791281346479565</v>
+      </c>
+      <c r="G69" s="1">
         <v>1.26</v>
       </c>
-      <c r="H68" s="1">
-        <v>42.92</v>
-      </c>
-      <c r="I68" s="1">
-        <v>-5.03</v>
-      </c>
-      <c r="J68" s="1">
-        <v>-0.001234813392897378</v>
-      </c>
-      <c r="K68" s="1" t="b">
+      <c r="H69" s="1">
+        <v>42.87</v>
+      </c>
+      <c r="I69" s="1">
+        <v>-5.13</v>
+      </c>
+      <c r="J69" s="1">
+        <v>-0.0026670443633801297</v>
+      </c>
+      <c r="K69" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L68" s="1">
-        <v>4</v>
-      </c>
-      <c r="M68" s="1">
-        <v>-0.01568571048806544</v>
-      </c>
-      <c r="N68" s="1">
-        <v>3.048159632156794</v>
-      </c>
-      <c r="O68" s="1">
-        <v>44.57831325301205</v>
-      </c>
-      <c r="P68" s="1">
+      <c r="L69" s="1">
+        <v>3</v>
+      </c>
+      <c r="M69" s="1">
+        <v>0.016087926076972847</v>
+      </c>
+      <c r="N69" s="1">
+        <v>5.490194427117783</v>
+      </c>
+      <c r="O69" s="1">
+        <v>53.57142857142857</v>
+      </c>
+      <c r="P69" s="1">
         <v>16.710870321490763</v>
       </c>
-      <c r="Q68" s="1">
-        <v>50.8433734939759</v>
-      </c>
-      <c r="R68" s="1">
-        <v>44.87951807228916</v>
-      </c>
-      <c r="S68" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="T68" s="1">
-        <v>3.17</v>
-      </c>
-    </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A69" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B69" s="2">
+      <c r="Q69" s="1">
+        <v>51.42857142857143</v>
+      </c>
+      <c r="R69" s="1">
+        <v>47.261904761904766</v>
+      </c>
+      <c r="S69" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="T69" s="1">
+        <v>5.55</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2">
         <v>-2.66</v>
       </c>
-      <c r="C69" s="2">
-        <v>12.048192771084338</v>
-      </c>
-      <c r="D69" s="2">
-        <v>882.7368421052631</v>
-      </c>
-      <c r="E69" s="2">
+      <c r="C70" s="2">
+        <v>11.904761904761903</v>
+      </c>
+      <c r="D70" s="2">
+        <v>886.3947368421052</v>
+      </c>
+      <c r="E70" s="2">
         <v>0.14</v>
       </c>
-      <c r="F69" s="2">
-        <v>0.11902108211532893</v>
-      </c>
-      <c r="G69" s="2">
-        <v>0.34</v>
-      </c>
-      <c r="H69" s="2">
-        <v>51.2</v>
-      </c>
-      <c r="I69" s="2">
-        <v>6.84</v>
-      </c>
-      <c r="J69" s="2">
-        <v>0.014913898788446851</v>
-      </c>
-      <c r="K69" s="2" t="b">
+      <c r="F70" s="2">
+        <v>0.145766467206474</v>
+      </c>
+      <c r="G70" s="2">
+        <v>0.33</v>
+      </c>
+      <c r="H70" s="2">
+        <v>50.57</v>
+      </c>
+      <c r="I70" s="2">
+        <v>6.73</v>
+      </c>
+      <c r="J70" s="2">
+        <v>0.013094764996098374</v>
+      </c>
+      <c r="K70" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L69" s="2">
-        <v>-80</v>
-      </c>
-      <c r="M69" s="2">
-        <v>0.09564565962097094</v>
-      </c>
-      <c r="N69" s="2">
-        <v>14.181296643060417</v>
-      </c>
-      <c r="O69" s="2">
-        <v>71.08433734939759</v>
-      </c>
-      <c r="P69" s="2">
-        <v>11.74077020079542</v>
-      </c>
-      <c r="Q69" s="2">
-        <v>60.361445783132524</v>
-      </c>
-      <c r="R69" s="2">
-        <v>55.18072289156626</v>
-      </c>
-      <c r="S69" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="T69" s="2">
-        <v>7.13</v>
-      </c>
-    </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A70" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B70" s="3">
+      <c r="L70" s="2">
+        <v>-79</v>
+      </c>
+      <c r="M70" s="2">
+        <v>0.1269635750163567</v>
+      </c>
+      <c r="N70" s="2">
+        <v>16.577759321056156</v>
+      </c>
+      <c r="O70" s="2">
+        <v>73.80952380952381</v>
+      </c>
+      <c r="P70" s="2">
+        <v>10.873073633899006</v>
+      </c>
+      <c r="Q70" s="2">
+        <v>59.523809523809526</v>
+      </c>
+      <c r="R70" s="2">
+        <v>56.36904761904761</v>
+      </c>
+      <c r="S70" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="T70" s="2">
+        <v>8.32</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B71" s="1">
         <v>8.73</v>
       </c>
-      <c r="C70" s="3">
-        <v>77.10843373493977</v>
-      </c>
-      <c r="D70" s="3">
+      <c r="C71" s="1">
+        <v>76.19047619047619</v>
+      </c>
+      <c r="D71" s="1">
         <v>0.3596792668957616</v>
       </c>
-      <c r="E70" s="3">
+      <c r="E71" s="1">
         <v>0.12</v>
       </c>
-      <c r="F70" s="3">
-        <v>-0.16912547469030736</v>
-      </c>
-      <c r="G70" s="3">
-        <v>1.48</v>
-      </c>
-      <c r="H70" s="3">
-        <v>48.12</v>
-      </c>
-      <c r="I70" s="3">
-        <v>-19.54</v>
-      </c>
-      <c r="J70" s="3">
-        <v>-0.01104136108363604</v>
-      </c>
-      <c r="K70" s="3" t="b">
+      <c r="F71" s="1">
+        <v>-0.13257627458934082</v>
+      </c>
+      <c r="G71" s="1">
+        <v>1.47</v>
+      </c>
+      <c r="H71" s="1">
+        <v>51.21</v>
+      </c>
+      <c r="I71" s="1">
+        <v>-18.13</v>
+      </c>
+      <c r="J71" s="1">
+        <v>-0.011852053783059556</v>
+      </c>
+      <c r="K71" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L70" s="3">
-        <v>-41</v>
-      </c>
-      <c r="M70" s="3">
-        <v>-0.15212516742168336</v>
-      </c>
-      <c r="N70" s="3">
-        <v>-10.595786061205004</v>
-      </c>
-      <c r="O70" s="3">
-        <v>19.27710843373494</v>
-      </c>
-      <c r="P70" s="3">
+      <c r="L71" s="1">
+        <v>-42</v>
+      </c>
+      <c r="M71" s="1">
+        <v>-0.1193861860380645</v>
+      </c>
+      <c r="N71" s="1">
+        <v>-8.057216784385952</v>
+      </c>
+      <c r="O71" s="1">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="P71" s="1">
         <v>31.34692685044607</v>
       </c>
-      <c r="Q70" s="3">
-        <v>45.18072289156627</v>
-      </c>
-      <c r="R70" s="3">
-        <v>29.759036144578317</v>
-      </c>
-      <c r="S70" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="T70" s="3">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A71" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B71" s="2">
+      <c r="Q71" s="1">
+        <v>46.42857142857143</v>
+      </c>
+      <c r="R71" s="1">
+        <v>32.44047619047619</v>
+      </c>
+      <c r="S71" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="T71" s="1">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2">
         <v>18.59</v>
       </c>
-      <c r="C71" s="2">
-        <v>90.36144578313254</v>
-      </c>
-      <c r="D71" s="2">
+      <c r="C72" s="2">
+        <v>90.47619047619048</v>
+      </c>
+      <c r="D72" s="2">
         <v>-0.5072619688004303</v>
       </c>
-      <c r="E71" s="2">
+      <c r="E72" s="2">
         <v>-0.35</v>
       </c>
-      <c r="F71" s="2">
-        <v>0.2397788063941012</v>
-      </c>
-      <c r="G71" s="2">
+      <c r="F72" s="2">
+        <v>0.2716834297070755</v>
+      </c>
+      <c r="G72" s="2">
         <v>0.89</v>
       </c>
-      <c r="H71" s="2">
-        <v>51.22</v>
-      </c>
-      <c r="I71" s="2">
-        <v>12.45</v>
-      </c>
-      <c r="J71" s="2">
-        <v>0.01743311779074454</v>
-      </c>
-      <c r="K71" s="2" t="b">
+      <c r="H72" s="2">
+        <v>57.18</v>
+      </c>
+      <c r="I72" s="2">
+        <v>14.48</v>
+      </c>
+      <c r="J72" s="2">
+        <v>0.016741609992840023</v>
+      </c>
+      <c r="K72" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L71" s="2">
-        <v>48</v>
-      </c>
-      <c r="M71" s="2">
-        <v>0.23588290264504153</v>
-      </c>
-      <c r="N71" s="2">
-        <v>28.205020945467492</v>
-      </c>
-      <c r="O71" s="2">
-        <v>90.36144578313254</v>
-      </c>
-      <c r="P71" s="2">
-        <v>16.760346247612663</v>
-      </c>
-      <c r="Q71" s="2">
-        <v>62.40963855421687</v>
-      </c>
-      <c r="R71" s="2">
-        <v>59.75903614457832</v>
-      </c>
-      <c r="S71" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="T71" s="2">
-        <v>19.88</v>
-      </c>
-    </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A72" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B72" s="3">
+      <c r="L72" s="2">
+        <v>49</v>
+      </c>
+      <c r="M72" s="2">
+        <v>0.2685963877057129</v>
+      </c>
+      <c r="N72" s="2">
+        <v>30.741040589991776</v>
+      </c>
+      <c r="O72" s="2">
+        <v>89.28571428571429</v>
+      </c>
+      <c r="P72" s="2">
+        <v>16.66857152537527</v>
+      </c>
+      <c r="Q72" s="2">
+        <v>64.76190476190476</v>
+      </c>
+      <c r="R72" s="2">
+        <v>60.00000000000001</v>
+      </c>
+      <c r="S72" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="T72" s="2">
+        <v>20.12</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B73" s="1">
         <v>2.1</v>
       </c>
-      <c r="C72" s="3">
-        <v>44.57831325301205</v>
-      </c>
-      <c r="D72" s="3">
-        <v>11.128571428571426</v>
-      </c>
-      <c r="E72" s="3">
+      <c r="C73" s="1">
+        <v>44.047619047619044</v>
+      </c>
+      <c r="D73" s="1">
+        <v>11.171428571428569</v>
+      </c>
+      <c r="E73" s="1">
         <v>0.45</v>
       </c>
-      <c r="F72" s="3">
-        <v>-0.24901278052541245</v>
-      </c>
-      <c r="G72" s="3">
-        <v>1.1</v>
-      </c>
-      <c r="H72" s="3">
-        <v>33.98</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-27.62</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-0.009611037102184099</v>
-      </c>
-      <c r="K72" s="3" t="b">
+      <c r="F73" s="1">
+        <v>-0.21672373297195272</v>
+      </c>
+      <c r="G73" s="1">
+        <v>1.09</v>
+      </c>
+      <c r="H73" s="1">
+        <v>35.29</v>
+      </c>
+      <c r="I73" s="1">
+        <v>-27.22</v>
+      </c>
+      <c r="J73" s="1">
+        <v>-0.011810229769209929</v>
+      </c>
+      <c r="K73" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L72" s="3">
-        <v>-164</v>
-      </c>
-      <c r="M72" s="3">
-        <v>-0.24547104984444912</v>
-      </c>
-      <c r="N72" s="3">
-        <v>-19.930374303481585</v>
-      </c>
-      <c r="O72" s="3">
-        <v>8.433734939759036</v>
-      </c>
-      <c r="P72" s="3">
+      <c r="L73" s="1">
+        <v>-165</v>
+      </c>
+      <c r="M73" s="1">
+        <v>-0.21419797133447427</v>
+      </c>
+      <c r="N73" s="1">
+        <v>-17.538395314026932</v>
+      </c>
+      <c r="O73" s="1">
+        <v>16.666666666666664</v>
+      </c>
+      <c r="P73" s="1">
         <v>22.69368849988335</v>
       </c>
-      <c r="Q72" s="3">
-        <v>41.56626506024096</v>
-      </c>
-      <c r="R72" s="3">
-        <v>29.879518072289155</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="T72" s="3">
-        <v>-2.13</v>
-      </c>
-    </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A73" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B73" s="3">
-        <v>0.42</v>
-      </c>
-      <c r="C73" s="3">
-        <v>34.93975903614458</v>
-      </c>
-      <c r="D73" s="3">
-        <v>97.42857142857143</v>
-      </c>
-      <c r="E73" s="3">
-        <v>-3.73</v>
-      </c>
-      <c r="F73" s="3">
-        <v>-0.23410140879719693</v>
-      </c>
-      <c r="G73" s="3">
-        <v>1.25</v>
-      </c>
-      <c r="H73" s="3">
-        <v>42.02</v>
-      </c>
-      <c r="I73" s="3">
-        <v>-2.57</v>
-      </c>
-      <c r="J73" s="3">
-        <v>-0.019370875625452002</v>
-      </c>
-      <c r="K73" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L73" s="3">
-        <v>32</v>
-      </c>
-      <c r="M73" s="3">
-        <v>-0.2252470820947886</v>
-      </c>
-      <c r="N73" s="3">
-        <v>-17.907977528515527</v>
-      </c>
-      <c r="O73" s="3">
-        <v>9.63855421686747</v>
-      </c>
-      <c r="P73" s="3">
-        <v>27.09638457523498</v>
-      </c>
-      <c r="Q73" s="3">
-        <v>46.506024096385545</v>
-      </c>
-      <c r="R73" s="3">
-        <v>29.15662650602409</v>
-      </c>
-      <c r="S73" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="T73" s="3">
-        <v>-29.44</v>
+      <c r="Q73" s="1">
+        <v>41.309523809523796</v>
+      </c>
+      <c r="R73" s="1">
+        <v>31.964285714285715</v>
+      </c>
+      <c r="S73" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="T73" s="1">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.25">
@@ -6609,619 +6627,619 @@
         <v>73</v>
       </c>
       <c r="B74" s="3">
-        <v>-0.22</v>
+        <v>0.42</v>
       </c>
       <c r="C74" s="3">
-        <v>26.506024096385545</v>
+        <v>34.523809523809526</v>
       </c>
       <c r="D74" s="3">
-        <v>162.09090909090907</v>
+        <v>97.42857142857143</v>
       </c>
       <c r="E74" s="3">
-        <v>-0.07</v>
+        <v>-3.73</v>
       </c>
       <c r="F74" s="3">
-        <v>-0.4326195374414126</v>
+        <v>-0.281049343590817</v>
       </c>
       <c r="G74" s="3">
-        <v>3.25</v>
+        <v>1.25</v>
       </c>
       <c r="H74" s="3">
-        <v>40.28</v>
+        <v>38.01</v>
       </c>
       <c r="I74" s="3">
-        <v>-32.91</v>
+        <v>-5.59</v>
       </c>
       <c r="J74" s="3">
-        <v>-0.021997699890366984</v>
+        <v>-0.020583768933837104</v>
       </c>
       <c r="K74" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L74" s="3">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="M74" s="3">
-        <v>-0.3529305971197376</v>
+        <v>-0.2740333390422658</v>
       </c>
       <c r="N74" s="3">
-        <v>-30.676329031010425</v>
+        <v>-23.52193208480608</v>
       </c>
       <c r="O74" s="3">
-        <v>6.024096385542169</v>
+        <v>9.523809523809524</v>
       </c>
       <c r="P74" s="3">
-        <v>51.49813033405746</v>
+        <v>28.20053515048475</v>
       </c>
       <c r="Q74" s="3">
-        <v>40.722891566265055</v>
+        <v>44.76190476190476</v>
       </c>
       <c r="R74" s="3">
-        <v>23.493975903614462</v>
+        <v>29.226190476190474</v>
       </c>
       <c r="S74" s="3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="T74" s="3">
-        <v>-2.24</v>
+        <v>-29.37</v>
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="B75" s="3">
-        <v>3.5</v>
+        <v>-0.22</v>
       </c>
       <c r="C75" s="3">
-        <v>53.01204819277109</v>
+        <v>26.190476190476193</v>
       </c>
       <c r="D75" s="3">
-        <v>-22.482857142857142</v>
+        <v>162.09090909090907</v>
       </c>
       <c r="E75" s="3">
-        <v>12.84</v>
+        <v>-0.07</v>
       </c>
       <c r="F75" s="3">
-        <v>-0.03283081248773884</v>
+        <v>-0.3855401168163636</v>
       </c>
       <c r="G75" s="3">
-        <v>0.88</v>
+        <v>3.25</v>
       </c>
       <c r="H75" s="3">
-        <v>36.33</v>
+        <v>41.59</v>
       </c>
       <c r="I75" s="3">
-        <v>49.73</v>
+        <v>-31.93</v>
       </c>
       <c r="J75" s="3">
-        <v>-0.012369235507545288</v>
+        <v>-0.023093207756405974</v>
       </c>
       <c r="K75" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L75" s="3">
+        <v>10</v>
+      </c>
+      <c r="M75" s="3">
+        <v>-0.32239607587940244</v>
+      </c>
+      <c r="N75" s="3">
+        <v>-28.358205768519756</v>
+      </c>
+      <c r="O75" s="3">
+        <v>5.952380952380952</v>
+      </c>
+      <c r="P75" s="3">
+        <v>51.49813033405746</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>41.42857142857142</v>
+      </c>
+      <c r="R75" s="3">
+        <v>23.273809523809526</v>
+      </c>
+      <c r="S75" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="T75" s="3">
+        <v>-2.46</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B76" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="C76" s="3">
+        <v>52.38095238095239</v>
+      </c>
+      <c r="D76" s="3">
+        <v>-22.482857142857142</v>
+      </c>
+      <c r="E76" s="3">
+        <v>12.84</v>
+      </c>
+      <c r="F76" s="3">
+        <v>-0.09524217209719844</v>
+      </c>
+      <c r="G76" s="3">
+        <v>0.89</v>
+      </c>
+      <c r="H76" s="3">
+        <v>30.93</v>
+      </c>
+      <c r="I76" s="3">
+        <v>40.63</v>
+      </c>
+      <c r="J76" s="3">
+        <v>-0.01917734748256924</v>
+      </c>
+      <c r="K76" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L76" s="3">
         <v>42</v>
       </c>
-      <c r="M75" s="3">
-        <v>-0.03708088930489484</v>
-      </c>
-      <c r="N75" s="3">
-        <v>0.9086417504738393</v>
-      </c>
-      <c r="O75" s="3">
-        <v>42.168674698795186</v>
-      </c>
-      <c r="P75" s="3">
-        <v>24.0515697846509</v>
-      </c>
-      <c r="Q75" s="3">
-        <v>31.325301204819276</v>
-      </c>
-      <c r="R75" s="3">
-        <v>23.734939759036145</v>
-      </c>
-      <c r="S75" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="T75" s="3">
-        <v>-49.98</v>
-      </c>
-    </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A76" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B76" s="2">
-        <v>2.14</v>
-      </c>
-      <c r="C76" s="2">
-        <v>45.78313253012048</v>
-      </c>
-      <c r="D76" s="2">
-        <v>3.3878504672897196</v>
-      </c>
-      <c r="E76" s="2">
-        <v>-9.21</v>
-      </c>
-      <c r="F76" s="2">
-        <v>0.5636196169909476</v>
-      </c>
-      <c r="G76" s="2">
-        <v>0.92</v>
-      </c>
-      <c r="H76" s="2">
-        <v>69.22</v>
-      </c>
-      <c r="I76" s="2">
-        <v>37.55</v>
-      </c>
-      <c r="J76" s="2">
-        <v>0.047704556731006584</v>
-      </c>
-      <c r="K76" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L76" s="2">
-        <v>-5</v>
-      </c>
-      <c r="M76" s="2">
-        <v>0.560786232446177</v>
-      </c>
-      <c r="N76" s="2">
-        <v>60.69535392558103</v>
-      </c>
-      <c r="O76" s="2">
-        <v>98.79518072289156</v>
-      </c>
-      <c r="P76" s="2">
-        <v>18.71809072120826</v>
-      </c>
-      <c r="Q76" s="2">
-        <v>68.3132530120482</v>
-      </c>
-      <c r="R76" s="2">
-        <v>61.26506024096387</v>
-      </c>
-      <c r="S76" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="T76" s="2">
-        <v>12.67</v>
+      <c r="M76" s="3">
+        <v>-0.09832921409856099</v>
+      </c>
+      <c r="N76" s="3">
+        <v>-5.951519590435606</v>
+      </c>
+      <c r="O76" s="3">
+        <v>32.142857142857146</v>
+      </c>
+      <c r="P76" s="3">
+        <v>28.293521533287937</v>
+      </c>
+      <c r="Q76" s="3">
+        <v>29.16666666666667</v>
+      </c>
+      <c r="R76" s="3">
+        <v>19.04761904761905</v>
+      </c>
+      <c r="S76" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="T76" s="3">
+        <v>-54.67</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B77" s="2">
-        <v>-0.92</v>
+        <v>2.14</v>
       </c>
       <c r="C77" s="2">
-        <v>20.481927710843372</v>
+        <v>45.23809523809524</v>
       </c>
       <c r="D77" s="2">
-        <v>15.521739130434781</v>
+        <v>3.3878504672897196</v>
       </c>
       <c r="E77" s="2">
-        <v>-3.54</v>
+        <v>-9.21</v>
       </c>
       <c r="F77" s="2">
-        <v>0.1790578903959238</v>
+        <v>0.5122086541982861</v>
       </c>
       <c r="G77" s="2">
-        <v>1.11</v>
+        <v>0.91</v>
       </c>
       <c r="H77" s="2">
-        <v>53.34</v>
+        <v>69.74</v>
       </c>
       <c r="I77" s="2">
-        <v>27.23</v>
+        <v>37.63</v>
       </c>
       <c r="J77" s="2">
-        <v>0.008481528448144898</v>
+        <v>0.045132353905019885</v>
       </c>
       <c r="K77" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="2">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="M77" s="2">
-        <v>0.18295379414498347</v>
+        <v>0.5096828925608077</v>
       </c>
       <c r="N77" s="2">
-        <v>22.912110095461667</v>
+        <v>54.84969107550126</v>
       </c>
       <c r="O77" s="2">
-        <v>80.72289156626506</v>
+        <v>97.61904761904762</v>
       </c>
       <c r="P77" s="2">
-        <v>16.006637557486414</v>
+        <v>18.71809072120826</v>
       </c>
       <c r="Q77" s="2">
-        <v>57.34939759036145</v>
+        <v>68.57142857142857</v>
       </c>
       <c r="R77" s="2">
-        <v>52.108433734939766</v>
+        <v>61.07142857142858</v>
       </c>
       <c r="S77" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="T77" s="2">
-        <v>3.94</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B78" s="2">
-        <v>5.7</v>
+        <v>-0.92</v>
       </c>
       <c r="C78" s="2">
-        <v>63.85542168674698</v>
+        <v>20.238095238095237</v>
       </c>
       <c r="D78" s="2">
-        <v>0.1824561403508772</v>
+        <v>15.521739130434781</v>
       </c>
       <c r="E78" s="2">
-        <v>0.32</v>
+        <v>-3.54</v>
       </c>
       <c r="F78" s="2">
-        <v>0.21869872829688078</v>
+        <v>0.19783090164987194</v>
       </c>
       <c r="G78" s="2">
-        <v>0.82</v>
+        <v>1.11</v>
       </c>
       <c r="H78" s="2">
-        <v>49.8</v>
+        <v>63.04</v>
       </c>
       <c r="I78" s="2">
-        <v>10.68</v>
+        <v>31.25</v>
       </c>
       <c r="J78" s="2">
-        <v>0.017342721837614285</v>
+        <v>0.007629812933399693</v>
       </c>
       <c r="K78" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L78" s="2">
-        <v>6</v>
+        <v>-2</v>
       </c>
       <c r="M78" s="2">
-        <v>0.21232361307114678</v>
+        <v>0.2009179436512345</v>
       </c>
       <c r="N78" s="2">
-        <v>25.849091988078005</v>
+        <v>23.973196184543944</v>
       </c>
       <c r="O78" s="2">
-        <v>81.92771084337349</v>
+        <v>82.14285714285714</v>
       </c>
       <c r="P78" s="2">
-        <v>11.616065285425229</v>
+        <v>16.006637557486414</v>
       </c>
       <c r="Q78" s="2">
-        <v>56.506024096385545</v>
+        <v>59.047619047619044</v>
       </c>
       <c r="R78" s="2">
-        <v>55.42168674698795</v>
+        <v>52.73809523809524</v>
       </c>
       <c r="S78" s="2" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="T78" s="2">
-        <v>15.54</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B79" s="2">
-        <v>11.65</v>
+        <v>5.7</v>
       </c>
       <c r="C79" s="2">
-        <v>79.51807228915662</v>
+        <v>63.095238095238095</v>
       </c>
       <c r="D79" s="2">
-        <v>0.16652360515021455</v>
+        <v>0.15087719298245603</v>
       </c>
       <c r="E79" s="2">
-        <v>0.86</v>
+        <v>0.32</v>
       </c>
       <c r="F79" s="2">
-        <v>0.12308203179029567</v>
+        <v>0.2240634416854555</v>
       </c>
       <c r="G79" s="2">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="H79" s="2">
-        <v>52.91</v>
+        <v>50.59</v>
       </c>
       <c r="I79" s="2">
-        <v>11.17</v>
+        <v>10.9</v>
       </c>
       <c r="J79" s="2">
-        <v>0.008070070989143285</v>
+        <v>0.015564912992595579</v>
       </c>
       <c r="K79" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L79" s="2">
-        <v>159</v>
+        <v>6</v>
       </c>
       <c r="M79" s="2">
-        <v>0.11493605122408002</v>
+        <v>0.2190119184104986</v>
       </c>
       <c r="N79" s="2">
-        <v>16.110335803371328</v>
+        <v>25.782593660470347</v>
       </c>
       <c r="O79" s="2">
-        <v>73.49397590361446</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="P79" s="2">
-        <v>6.707278396222185</v>
+        <v>11.616065285425229</v>
       </c>
       <c r="Q79" s="2">
-        <v>59.638554216867476</v>
+        <v>56.54761904761905</v>
       </c>
       <c r="R79" s="2">
-        <v>55.78313253012049</v>
+        <v>55.35714285714287</v>
       </c>
       <c r="S79" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="T79" s="2">
-        <v>5.36</v>
+        <v>15.48</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B80" s="2">
-        <v>23.34</v>
+        <v>11.65</v>
       </c>
       <c r="C80" s="2">
-        <v>95.18072289156626</v>
+        <v>78.57142857142857</v>
       </c>
       <c r="D80" s="2">
-        <v>-0.9297343616109682</v>
+        <v>0.16652360515021455</v>
       </c>
       <c r="E80" s="2">
-        <v>-1.2</v>
+        <v>0.86</v>
       </c>
       <c r="F80" s="2">
-        <v>0.08981467784137125</v>
+        <v>0.13197724656539647</v>
       </c>
       <c r="G80" s="2">
-        <v>1.01</v>
+        <v>0.76</v>
       </c>
       <c r="H80" s="2">
-        <v>52.62</v>
+        <v>54.77</v>
       </c>
       <c r="I80" s="2">
-        <v>11.6</v>
+        <v>11.71</v>
       </c>
       <c r="J80" s="2">
-        <v>0.006967555741556304</v>
+        <v>0.006321162644489269</v>
       </c>
       <c r="K80" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L80" s="2">
-        <v>111</v>
+        <v>158</v>
       </c>
       <c r="M80" s="2">
-        <v>0.09016885090946758</v>
+        <v>0.1252418821987873</v>
       </c>
       <c r="N80" s="2">
-        <v>13.633615771910081</v>
+        <v>16.405590039299227</v>
       </c>
       <c r="O80" s="2">
-        <v>67.46987951807229</v>
+        <v>72.61904761904762</v>
       </c>
       <c r="P80" s="2">
-        <v>6.716293473999743</v>
+        <v>6.707278396222185</v>
       </c>
       <c r="Q80" s="2">
-        <v>57.59036144578313</v>
+        <v>59.76190476190476</v>
       </c>
       <c r="R80" s="2">
-        <v>52.46987951807228</v>
+        <v>55.59523809523809</v>
       </c>
       <c r="S80" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="T80" s="2">
-        <v>7.17</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B81" s="2">
+        <v>23.34</v>
+      </c>
+      <c r="C81" s="2">
+        <v>95.23809523809523</v>
+      </c>
+      <c r="D81" s="2">
+        <v>-0.9297343616109682</v>
+      </c>
+      <c r="E81" s="2">
+        <v>-1.2</v>
+      </c>
+      <c r="F81" s="2">
+        <v>0.052605277861602316</v>
+      </c>
+      <c r="G81" s="2">
+        <v>1.01</v>
+      </c>
+      <c r="H81" s="2">
+        <v>42.31</v>
+      </c>
+      <c r="I81" s="2">
+        <v>8.92</v>
+      </c>
+      <c r="J81" s="2">
+        <v>0.006508752891852481</v>
+      </c>
+      <c r="K81" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L81" s="2">
+        <v>111</v>
+      </c>
+      <c r="M81" s="2">
+        <v>0.05288591804354437</v>
+      </c>
+      <c r="N81" s="2">
+        <v>9.169993623774937</v>
+      </c>
+      <c r="O81" s="2">
+        <v>64.28571428571429</v>
+      </c>
+      <c r="P81" s="2">
+        <v>6.716293473999743</v>
+      </c>
+      <c r="Q81" s="2">
+        <v>54.76190476190476</v>
+      </c>
+      <c r="R81" s="2">
+        <v>52.32142857142857</v>
+      </c>
+      <c r="S81" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="T81" s="2">
+        <v>7.02</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B82" s="2">
         <v>8.72</v>
       </c>
-      <c r="C81" s="2">
-        <v>75.90361445783132</v>
-      </c>
-      <c r="D81" s="2">
-        <v>-0.012614678899082707</v>
-      </c>
-      <c r="E81" s="2">
+      <c r="C82" s="2">
+        <v>75</v>
+      </c>
+      <c r="D82" s="2">
+        <v>-0.008027522935779848</v>
+      </c>
+      <c r="E82" s="2">
         <v>0.23</v>
       </c>
-      <c r="F81" s="2">
-        <v>0.07529213315532597</v>
-      </c>
-      <c r="G81" s="2">
+      <c r="F82" s="2">
+        <v>0.10331513906437166</v>
+      </c>
+      <c r="G82" s="2">
         <v>1.07</v>
       </c>
-      <c r="H81" s="2">
-        <v>61.4</v>
-      </c>
-      <c r="I81" s="2">
-        <v>16.04</v>
-      </c>
-      <c r="J81" s="2">
-        <v>0.011834976203009067</v>
-      </c>
-      <c r="K81" s="2" t="b">
+      <c r="H82" s="2">
+        <v>60.79</v>
+      </c>
+      <c r="I82" s="2">
+        <v>15.89</v>
+      </c>
+      <c r="J82" s="2">
+        <v>0.01050859977659108</v>
+      </c>
+      <c r="K82" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="L81" s="2">
+      <c r="L82" s="2">
         <v>91</v>
       </c>
-      <c r="M81" s="2">
-        <v>0.0777713446320003</v>
-      </c>
-      <c r="N81" s="2">
-        <v>12.393865144163373</v>
-      </c>
-      <c r="O81" s="2">
-        <v>65.06024096385542</v>
-      </c>
-      <c r="P81" s="2">
+      <c r="M82" s="2">
+        <v>0.105279620337966</v>
+      </c>
+      <c r="N82" s="2">
+        <v>14.409363853217085</v>
+      </c>
+      <c r="O82" s="2">
+        <v>70.23809523809523</v>
+      </c>
+      <c r="P82" s="2">
         <v>12.706223591210087</v>
       </c>
-      <c r="Q81" s="2">
-        <v>61.807228915662655</v>
-      </c>
-      <c r="R81" s="2">
-        <v>51.144578313253014</v>
-      </c>
-      <c r="S81" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="T81" s="2">
-        <v>-0.99</v>
-      </c>
-    </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B82" s="1">
-        <v>19.91</v>
-      </c>
-      <c r="C82" s="1">
-        <v>92.7710843373494</v>
-      </c>
-      <c r="D82" s="1">
-        <v>-2.3370165745856353</v>
-      </c>
-      <c r="E82" s="1">
-        <v>2.31</v>
-      </c>
-      <c r="F82" s="1">
-        <v>-0.11245534943727947</v>
-      </c>
-      <c r="G82" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="H82" s="1">
-        <v>44.09</v>
-      </c>
-      <c r="I82" s="1">
-        <v>-0.81</v>
-      </c>
-      <c r="J82" s="1">
-        <v>-0.004296330421879677</v>
-      </c>
-      <c r="K82" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L82" s="1">
-        <v>177</v>
-      </c>
-      <c r="M82" s="1">
-        <v>-0.1053718880753528</v>
-      </c>
-      <c r="N82" s="1">
-        <v>-5.920458126571948</v>
-      </c>
-      <c r="O82" s="1">
-        <v>28.915662650602407</v>
-      </c>
-      <c r="P82" s="1">
-        <v>20.22353911360907</v>
-      </c>
-      <c r="Q82" s="1">
-        <v>44.33734939759036</v>
-      </c>
-      <c r="R82" s="1">
-        <v>33.25301204819277</v>
-      </c>
-      <c r="S82" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="T82" s="1">
-        <v>-13.52</v>
+      <c r="Q82" s="2">
+        <v>61.54761904761905</v>
+      </c>
+      <c r="R82" s="2">
+        <v>52.738095238095234</v>
+      </c>
+      <c r="S82" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="T82" s="2">
+        <v>0.6</v>
       </c>
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B83" s="1">
-        <v>3.33</v>
+        <v>19.91</v>
       </c>
       <c r="C83" s="1">
-        <v>51.80722891566265</v>
+        <v>92.85714285714286</v>
       </c>
       <c r="D83" s="1">
-        <v>1.7717717717717718</v>
+        <v>-2.3370165745856353</v>
       </c>
       <c r="E83" s="1">
-        <v>0.25</v>
+        <v>2.31</v>
       </c>
       <c r="F83" s="1">
-        <v>-0.12472396540924859</v>
+        <v>-0.07890721604839149</v>
       </c>
       <c r="G83" s="1">
-        <v>0.97</v>
+        <v>1.19</v>
       </c>
       <c r="H83" s="1">
-        <v>47.25</v>
+        <v>51.37</v>
       </c>
       <c r="I83" s="1">
-        <v>15.69</v>
+        <v>1.78</v>
       </c>
       <c r="J83" s="1">
-        <v>-0.00655843117640546</v>
+        <v>-0.004505233144730778</v>
       </c>
       <c r="K83" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L83" s="1">
-        <v>375</v>
+        <v>177</v>
       </c>
       <c r="M83" s="1">
-        <v>-0.12578648461353759</v>
+        <v>-0.07357505259149255</v>
       </c>
       <c r="N83" s="1">
-        <v>-7.96191778039042</v>
+        <v>-3.476103439728764</v>
       </c>
       <c r="O83" s="1">
-        <v>24.096385542168676</v>
+        <v>40.476190476190474</v>
       </c>
       <c r="P83" s="1">
-        <v>17.353844275841347</v>
+        <v>20.22353911360907</v>
       </c>
       <c r="Q83" s="1">
-        <v>48.43373493975904</v>
+        <v>49.642857142857146</v>
       </c>
       <c r="R83" s="1">
-        <v>32.53012048192771</v>
+        <v>37.67857142857143</v>
       </c>
       <c r="S83" s="1" t="s">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="T83" s="1">
-        <v>-24.12</v>
+        <v>-9.09</v>
       </c>
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.25">
@@ -7229,61 +7247,123 @@
         <v>131</v>
       </c>
       <c r="B84" s="1">
-        <v>12.35</v>
+        <v>3.33</v>
       </c>
       <c r="C84" s="1">
-        <v>80.72289156626506</v>
+        <v>51.19047619047619</v>
       </c>
       <c r="D84" s="1">
-        <v>-0.31902834008097164</v>
+        <v>1.7717717717717718</v>
       </c>
       <c r="E84" s="1">
-        <v>0.61</v>
+        <v>0.25</v>
       </c>
       <c r="F84" s="1">
-        <v>0.015690017419081617</v>
+        <v>-0.12941707354157667</v>
       </c>
       <c r="G84" s="1">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="H84" s="1">
-        <v>47.51</v>
+        <v>44.81</v>
       </c>
       <c r="I84" s="1">
-        <v>11.5</v>
+        <v>14.33</v>
       </c>
       <c r="J84" s="1">
-        <v>0.005081454781607029</v>
+        <v>-0.005320117320406684</v>
       </c>
       <c r="K84" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L84" s="1">
+        <v>376</v>
+      </c>
+      <c r="M84" s="1">
+        <v>-0.12997835390546075</v>
+      </c>
+      <c r="N84" s="1">
+        <v>-9.116433571125583</v>
+      </c>
+      <c r="O84" s="1">
+        <v>27.380952380952383</v>
+      </c>
+      <c r="P84" s="1">
+        <v>17.353844275841347</v>
+      </c>
+      <c r="Q84" s="1">
+        <v>49.28571428571428</v>
+      </c>
+      <c r="R84" s="1">
+        <v>33.988095238095234</v>
+      </c>
+      <c r="S84" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="T84" s="1">
+        <v>-22.66</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B85" s="1">
+        <v>12.35</v>
+      </c>
+      <c r="C85" s="1">
+        <v>80.95238095238095</v>
+      </c>
+      <c r="D85" s="1">
+        <v>-0.31902834008097164</v>
+      </c>
+      <c r="E85" s="1">
+        <v>0.61</v>
+      </c>
+      <c r="F85" s="1">
+        <v>0.007986959800442284</v>
+      </c>
+      <c r="G85" s="1">
+        <v>0.95</v>
+      </c>
+      <c r="H85" s="1">
+        <v>36.65</v>
+      </c>
+      <c r="I85" s="1">
+        <v>8.75</v>
+      </c>
+      <c r="J85" s="1">
+        <v>0.0037754325789410813</v>
+      </c>
+      <c r="K85" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L85" s="1">
         <v>134</v>
       </c>
-      <c r="M84" s="1">
-        <v>0.01391915207859995</v>
-      </c>
-      <c r="N84" s="1">
-        <v>6.008645888823329</v>
-      </c>
-      <c r="O84" s="1">
-        <v>53.01204819277109</v>
-      </c>
-      <c r="P84" s="1">
+      <c r="M85" s="1">
+        <v>0.006583758890732039</v>
+      </c>
+      <c r="N85" s="1">
+        <v>4.5397777084936894</v>
+      </c>
+      <c r="O85" s="1">
+        <v>52.38095238095239</v>
+      </c>
+      <c r="P85" s="1">
         <v>8.441182677506358</v>
       </c>
-      <c r="Q84" s="1">
-        <v>52.7710843373494</v>
-      </c>
-      <c r="R84" s="1">
-        <v>46.20481927710844</v>
-      </c>
-      <c r="S84" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="T84" s="1">
-        <v>-0.56</v>
+      <c r="Q85" s="1">
+        <v>49.523809523809526</v>
+      </c>
+      <c r="R85" s="1">
+        <v>46.36904761904763</v>
+      </c>
+      <c r="S85" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="T85" s="1">
+        <v>-0.4</v>
       </c>
     </row>
   </sheetData>
@@ -7294,15 +7374,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B84"/>
+  <dimension ref="A1:B85"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -7310,7 +7390,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>44.518072289156635</v>
+        <v>46.07142857142856</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -7318,7 +7398,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>46.566265060240966</v>
+        <v>43.214285714285715</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7326,7 +7406,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>54.879518072289166</v>
+        <v>54.76190476190476</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -7334,7 +7414,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>32.5301204819277</v>
+        <v>32.797619047619044</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -7342,7 +7422,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>32.40963855421687</v>
+        <v>36.36904761904762</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7350,7 +7430,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>54.63855421686748</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -7358,7 +7438,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>37.048192771084345</v>
+        <v>38.51190476190476</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -7366,7 +7446,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>58.91566265060241</v>
+        <v>60.05952380952382</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -7374,7 +7454,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>45.12048192771084</v>
+        <v>47.857142857142854</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -7382,7 +7462,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>57.168674698795186</v>
+        <v>58.45238095238095</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -7390,7 +7470,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>62.7710843373494</v>
+        <v>62.67857142857142</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -7398,7 +7478,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>39.03614457831326</v>
+        <v>38.33333333333333</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -7406,7 +7486,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>60</v>
+        <v>60.892857142857146</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -7414,7 +7494,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>20.662650602409645</v>
+        <v>19.107142857142858</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -7422,7 +7502,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>19.879518072289155</v>
+        <v>22.678571428571423</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -7430,7 +7510,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>28.67469879518072</v>
+        <v>32.67857142857143</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -7438,7 +7518,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>24.397590361445783</v>
+        <v>24.642857142857146</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -7446,7 +7526,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>51.32530120481928</v>
+        <v>52.4404761904762</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -7454,7 +7534,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>54.39759036144578</v>
+        <v>55.11904761904761</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -7462,7 +7542,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>20.903614457831324</v>
+        <v>20.714285714285715</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -7470,7 +7550,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>39.45783132530121</v>
+        <v>38.69047619047619</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -7478,7 +7558,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>51.506024096385545</v>
+        <v>54.22619047619048</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -7486,7 +7566,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>30.542168674698793</v>
+        <v>32.142857142857146</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -7494,7 +7574,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>6.80722891566265</v>
+        <v>6.369047619047619</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -7502,7 +7582,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>-3.1325301204819285</v>
+        <v>-3.2738095238095246</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -7510,7 +7590,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>0.36144578313253106</v>
+        <v>0.4166666666666643</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -7518,7 +7598,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>36.325301204819276</v>
+        <v>39.88095238095238</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -7526,7 +7606,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>45.06024096385543</v>
+        <v>48.392857142857146</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -7534,7 +7614,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>46.506024096385545</v>
+        <v>48.392857142857146</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -7542,7 +7622,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>40.12048192771084</v>
+        <v>39.3452380952381</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -7550,7 +7630,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>32.22891566265061</v>
+        <v>28.452380952380956</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -7558,7 +7638,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>59.63855421686747</v>
+        <v>60.476190476190474</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -7566,7 +7646,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>33.674698795180724</v>
+        <v>37.738095238095234</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -7574,7 +7654,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>40.12048192771084</v>
+        <v>41.42857142857144</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -7582,7 +7662,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>49.75903614457832</v>
+        <v>43.86904761904762</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -7590,7 +7670,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>56.44578313253012</v>
+        <v>55</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -7598,7 +7678,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>60</v>
+        <v>63.63095238095239</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -7606,7 +7686,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>43.13253012048193</v>
+        <v>41.8452380952381</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -7614,7 +7694,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>44.81927710843374</v>
+        <v>46.13095238095238</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -7622,7 +7702,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>14.09638554216868</v>
+        <v>16.011904761904763</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -7630,7 +7710,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>31.746987951807228</v>
+        <v>31.904761904761912</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -7638,7 +7718,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>57.349397590361455</v>
+        <v>59.34523809523809</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -7646,7 +7726,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>53.6144578313253</v>
+        <v>54.16666666666668</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -7654,7 +7734,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>41.325301204819276</v>
+        <v>41.488095238095234</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -7662,7 +7742,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>28.012048192771083</v>
+        <v>28.33333333333333</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -7670,7 +7750,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>48.73493975903615</v>
+        <v>46.785714285714285</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -7678,7 +7758,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>58.13253012048192</v>
+        <v>53.33333333333334</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -7686,7 +7766,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>51.20481927710843</v>
+        <v>54.226190476190474</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -7694,7 +7774,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>18.192771084337352</v>
+        <v>19.94047619047619</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -7702,7 +7782,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>46.02409638554217</v>
+        <v>41.84523809523809</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -7710,7 +7790,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>44.1566265060241</v>
+        <v>20.714285714285715</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -7718,7 +7798,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>31.445783132530117</v>
+        <v>44.28571428571429</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -7726,7 +7806,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>43.43373493975904</v>
+        <v>31.666666666666668</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -7734,7 +7814,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>27.89156626506025</v>
+        <v>39.285714285714285</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -7742,7 +7822,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>40.36144578313253</v>
+        <v>27.26190476190476</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -7750,7 +7830,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>25.180722891566266</v>
+        <v>42.55952380952381</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -7758,7 +7838,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>11.385542168674696</v>
+        <v>24.345238095238095</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -7766,7 +7846,7 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>51.9277108433735</v>
+        <v>11.54761904761905</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -7774,7 +7854,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>51.144578313253</v>
+        <v>47.91666666666667</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -7782,7 +7862,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>41.626506024096386</v>
+        <v>51.904761904761905</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -7790,7 +7870,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>38.91566265060241</v>
+        <v>40.89285714285714</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -7798,7 +7878,7 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>33.85542168674699</v>
+        <v>32.97619047619047</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -7806,7 +7886,7 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>59.81927710843374</v>
+        <v>35.05952380952382</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -7814,7 +7894,7 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>25.361445783132524</v>
+        <v>59.82142857142858</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -7822,7 +7902,7 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>40.361445783132524</v>
+        <v>24.226190476190474</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -7830,7 +7910,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>50.36144578313253</v>
+        <v>36.78571428571429</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -7838,7 +7918,7 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>44.87951807228916</v>
+        <v>51.785714285714285</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -7846,7 +7926,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>55.18072289156626</v>
+        <v>47.261904761904766</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -7854,7 +7934,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>29.759036144578317</v>
+        <v>56.36904761904761</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -7862,7 +7942,7 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>59.75903614457832</v>
+        <v>32.44047619047619</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -7870,7 +7950,7 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>29.879518072289155</v>
+        <v>60.00000000000001</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -7878,7 +7958,7 @@
         <v>72</v>
       </c>
       <c r="B73">
-        <v>29.15662650602409</v>
+        <v>31.964285714285715</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -7886,15 +7966,15 @@
         <v>73</v>
       </c>
       <c r="B74">
-        <v>23.493975903614462</v>
+        <v>29.226190476190474</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="B75">
-        <v>23.734939759036145</v>
+        <v>23.273809523809526</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -7902,63 +7982,63 @@
         <v>122</v>
       </c>
       <c r="B76">
-        <v>61.26506024096387</v>
+        <v>19.04761904761905</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B77">
-        <v>52.108433734939766</v>
+        <v>61.07142857142858</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B78">
-        <v>55.42168674698795</v>
+        <v>52.73809523809524</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B79">
-        <v>55.78313253012049</v>
+        <v>55.35714285714287</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B80">
-        <v>52.46987951807228</v>
+        <v>55.59523809523809</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B81">
-        <v>51.144578313253014</v>
+        <v>52.32142857142857</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B82">
-        <v>33.25301204819277</v>
+        <v>52.738095238095234</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B83">
-        <v>32.53012048192771</v>
+        <v>37.67857142857143</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -7966,7 +8046,15 @@
         <v>131</v>
       </c>
       <c r="B84">
-        <v>46.20481927710844</v>
+        <v>33.988095238095234</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>133</v>
+      </c>
+      <c r="B85">
+        <v>46.36904761904763</v>
       </c>
     </row>
   </sheetData>
@@ -7985,137 +8073,137 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D7" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D8" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D9" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D10" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D11" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D12" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D13" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D14" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D15" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -8134,120 +8222,120 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D7" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D8" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D9" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D10" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D11" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D12" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D13" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D14" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -8266,123 +8354,123 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D7" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D8" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D11" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D12" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D13" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D14" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -8401,125 +8489,125 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D7" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D8" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D9" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D10" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D11" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D12" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D13" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D14" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D15" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -8535,212 +8623,212 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D3" t="s">
         <v>189</v>
-      </c>
-      <c r="D3" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D6" t="s">
         <v>199</v>
-      </c>
-      <c r="D6" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B7" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C7" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D7" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B8" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C8" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D8" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C9" t="s">
         <v>206</v>
       </c>
-      <c r="C9" t="s">
-        <v>204</v>
-      </c>
       <c r="D9" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B10" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C10" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D10" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B11" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C11" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D11" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B12" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B13" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C13" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D13" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B14" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C14" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D14" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B15" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C15" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D15" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -427,7 +427,7 @@
     <t>_date_</t>
   </si>
   <si>
-    <t>2026-09-15</t>
+    <t>2026-09-16</t>
   </si>
   <si>
     <t>Criteria</t>
@@ -685,37 +685,37 @@
     <t>Triggers</t>
   </si>
   <si>
+    <t>Momentum Breakout, Market Leader, Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
     <t>Momentum Breakout, Market Leader, Institutional Buying</t>
   </si>
   <si>
     <t>Momentum Breakout, Market Leader, Volume Spike</t>
   </si>
   <si>
+    <t>Stable Uptrend, Institutional Buying</t>
+  </si>
+  <si>
     <t>Momentum Breakout, Market Leader</t>
   </si>
   <si>
+    <t>Momentum Breakout, Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
     <t>Institutional Buying</t>
   </si>
   <si>
-    <t>Momentum Breakout, Volume Spike, Institutional Buying</t>
-  </si>
-  <si>
     <t>Momentum Breakout, Institutional Buying</t>
   </si>
   <si>
     <t>Volume Spike, Institutional Buying</t>
   </si>
   <si>
-    <t>Momentum Breakout, Volume Spike</t>
+    <t>Volume Spike</t>
   </si>
   <si>
     <t>Momentum Breakout</t>
-  </si>
-  <si>
-    <t>Volume Spike</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Market Leader, Volume Spike, Institutional Buying</t>
   </si>
 </sst>
 </file>
@@ -1405,7 +1405,7 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>63.63095238095239</v>
+        <v>64.94047619047619</v>
       </c>
       <c r="C2" t="s">
         <v>221</v>
@@ -1416,10 +1416,10 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>62.67857142857142</v>
+        <v>62.797619047619044</v>
       </c>
       <c r="C3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1427,120 +1427,120 @@
         <v>124</v>
       </c>
       <c r="B4">
-        <v>61.07142857142858</v>
+        <v>61.42857142857142</v>
       </c>
       <c r="C4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="B5">
-        <v>60.892857142857146</v>
+        <v>61.1904761904762</v>
       </c>
       <c r="C5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="B6">
-        <v>60.476190476190474</v>
+        <v>60.654761904761905</v>
       </c>
       <c r="C6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="B7">
-        <v>60.05952380952382</v>
+        <v>60.416666666666664</v>
       </c>
       <c r="C7" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="B8">
-        <v>60.00000000000001</v>
+        <v>60.238095238095234</v>
       </c>
       <c r="C8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="B9">
-        <v>59.82142857142858</v>
+        <v>59.345238095238095</v>
       </c>
       <c r="C9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="B10">
-        <v>59.34523809523809</v>
+        <v>58.80952380952381</v>
       </c>
       <c r="C10" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="B11">
-        <v>58.45238095238095</v>
+        <v>58.51190476190476</v>
       </c>
       <c r="C11" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>127</v>
+        <v>19</v>
       </c>
       <c r="B12">
-        <v>55.59523809523809</v>
+        <v>56.54761904761905</v>
       </c>
       <c r="C12" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B13">
-        <v>55.35714285714287</v>
+        <v>56.42857142857142</v>
       </c>
       <c r="C13" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>125</v>
       </c>
       <c r="B14">
-        <v>55.11904761904761</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="C14" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -1548,43 +1548,43 @@
         <v>36</v>
       </c>
       <c r="B15">
-        <v>55</v>
+        <v>54.76190476190477</v>
       </c>
       <c r="C15" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>3</v>
+        <v>126</v>
       </c>
       <c r="B16">
-        <v>54.76190476190476</v>
+        <v>54.523809523809526</v>
       </c>
       <c r="C16" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="B17">
-        <v>54.22619047619048</v>
+        <v>54.166666666666664</v>
       </c>
       <c r="C17" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="B18">
-        <v>54.16666666666668</v>
+        <v>53.92857142857143</v>
       </c>
       <c r="C18" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -1592,73 +1592,73 @@
         <v>47</v>
       </c>
       <c r="B19">
-        <v>53.33333333333334</v>
+        <v>53.80952380952382</v>
       </c>
       <c r="C19" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>125</v>
+        <v>60</v>
       </c>
       <c r="B20">
-        <v>52.73809523809524</v>
+        <v>53.333333333333336</v>
       </c>
       <c r="C20" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>129</v>
+        <v>22</v>
       </c>
       <c r="B21">
-        <v>52.738095238095234</v>
+        <v>53.03571428571429</v>
       </c>
       <c r="C21" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="B22">
-        <v>52.5</v>
+        <v>53.03571428571428</v>
       </c>
       <c r="C22" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>128</v>
+        <v>43</v>
       </c>
       <c r="B23">
-        <v>52.32142857142857</v>
+        <v>52.5</v>
       </c>
       <c r="C23" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="B24">
-        <v>51.904761904761905</v>
+        <v>52.14285714285714</v>
       </c>
       <c r="C24" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B25">
-        <v>51.785714285714285</v>
+        <v>50.65476190476192</v>
       </c>
       <c r="C25" t="s">
         <v>229</v>
@@ -1666,32 +1666,32 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>133</v>
       </c>
       <c r="B26">
-        <v>48.392857142857146</v>
+        <v>49.583333333333336</v>
       </c>
       <c r="C26" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="B27">
-        <v>48.392857142857146</v>
+        <v>49.404761904761905</v>
       </c>
       <c r="C27" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="B28">
-        <v>47.91666666666667</v>
+        <v>47.55952380952381</v>
       </c>
       <c r="C28" t="s">
         <v>227</v>
@@ -1699,90 +1699,90 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="B29">
-        <v>47.261904761904766</v>
+        <v>47.5</v>
       </c>
       <c r="C29" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="B30">
-        <v>46.785714285714285</v>
+        <v>46.8452380952381</v>
       </c>
       <c r="C30" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>133</v>
+        <v>56</v>
       </c>
       <c r="B31">
-        <v>46.36904761904763</v>
+        <v>45.654761904761905</v>
       </c>
       <c r="C31" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="B32">
-        <v>46.13095238095238</v>
+        <v>45.595238095238095</v>
       </c>
       <c r="C32" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B33">
-        <v>44.28571428571429</v>
+        <v>44.166666666666664</v>
       </c>
       <c r="C33" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="B34">
-        <v>43.214285714285715</v>
+        <v>43.273809523809526</v>
       </c>
       <c r="C34" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="B35">
-        <v>42.55952380952381</v>
+        <v>43.095238095238095</v>
       </c>
       <c r="C35" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36">
-        <v>41.8452380952381</v>
+        <v>43.035714285714285</v>
       </c>
       <c r="C36" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -1790,10 +1790,10 @@
         <v>50</v>
       </c>
       <c r="B37">
-        <v>41.84523809523809</v>
+        <v>42.91666666666666</v>
       </c>
       <c r="C37" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -1801,95 +1801,95 @@
         <v>44</v>
       </c>
       <c r="B38">
-        <v>41.488095238095234</v>
+        <v>41.726190476190474</v>
       </c>
       <c r="C38" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="B39">
-        <v>40.89285714285714</v>
+        <v>39.46428571428573</v>
       </c>
       <c r="C39" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B40">
-        <v>39.88095238095238</v>
+        <v>39.464285714285715</v>
       </c>
       <c r="C40" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="B41">
-        <v>39.3452380952381</v>
+        <v>39.047619047619044</v>
       </c>
       <c r="C41" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="B42">
-        <v>39.285714285714285</v>
+        <v>38.33333333333333</v>
       </c>
       <c r="C42" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="B43">
-        <v>38.69047619047619</v>
+        <v>38.214285714285715</v>
       </c>
       <c r="C43" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B44">
-        <v>38.51190476190476</v>
+        <v>38.09523809523809</v>
       </c>
       <c r="C44" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>12</v>
+        <v>131</v>
       </c>
       <c r="B45">
-        <v>38.33333333333333</v>
+        <v>37.67857142857142</v>
       </c>
       <c r="C45" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="B46">
-        <v>37.738095238095234</v>
+        <v>37.440476190476204</v>
       </c>
       <c r="C46" t="s">
         <v>227</v>
@@ -1897,57 +1897,57 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>130</v>
+        <v>63</v>
       </c>
       <c r="B47">
-        <v>37.67857142857143</v>
+        <v>36.60714285714286</v>
       </c>
       <c r="C47" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="B48">
-        <v>36.78571428571429</v>
+        <v>35.89285714285714</v>
       </c>
       <c r="C48" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="B49">
-        <v>35.05952380952382</v>
+        <v>35.476190476190474</v>
       </c>
       <c r="C49" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>131</v>
+        <v>66</v>
       </c>
       <c r="B50">
-        <v>33.988095238095234</v>
+        <v>34.40476190476191</v>
       </c>
       <c r="C50" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="B51">
-        <v>32.97619047619047</v>
+        <v>33.511904761904766</v>
       </c>
       <c r="C51" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -2181,49 +2181,49 @@
         <v>-2.08</v>
       </c>
       <c r="F2" s="1">
-        <v>0.10627341897372927</v>
+        <v>0.18997200578729737</v>
       </c>
       <c r="G2" s="1">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="H2" s="1">
-        <v>61.46</v>
+        <v>64.77</v>
       </c>
       <c r="I2" s="1">
-        <v>13.81</v>
+        <v>15.4</v>
       </c>
       <c r="J2" s="1">
-        <v>0.018109264215455927</v>
+        <v>0.01919412435012669</v>
       </c>
       <c r="K2" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>-457</v>
+        <v>-458</v>
       </c>
       <c r="M2" s="1">
-        <v>0.08410284460030737</v>
+        <v>0.18672862035598436</v>
       </c>
       <c r="N2" s="1">
-        <v>12.291686279451223</v>
+        <v>20.153285214512568</v>
       </c>
       <c r="O2" s="1">
-        <v>69.04761904761905</v>
+        <v>79.76190476190477</v>
       </c>
       <c r="P2" s="1">
         <v>16.29652721982991</v>
       </c>
       <c r="Q2" s="1">
-        <v>56.07142857142857</v>
+        <v>56.785714285714285</v>
       </c>
       <c r="R2" s="1">
-        <v>46.07142857142856</v>
+        <v>49.404761904761905</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>94</v>
       </c>
       <c r="T2" s="1">
-        <v>26.25</v>
+        <v>29.59</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -2243,49 +2243,49 @@
         <v>3.63</v>
       </c>
       <c r="F3" s="1">
-        <v>-0.11584733501843623</v>
+        <v>-0.09944683961161421</v>
       </c>
       <c r="G3" s="1">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="H3" s="1">
-        <v>50.65</v>
+        <v>55.74</v>
       </c>
       <c r="I3" s="1">
-        <v>40.14</v>
+        <v>45.47</v>
       </c>
       <c r="J3" s="1">
-        <v>-0.006437339770132733</v>
+        <v>-0.007724499379480425</v>
       </c>
       <c r="K3" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="1">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="M3" s="1">
-        <v>-0.07431258809101293</v>
+        <v>-0.09348711888157657</v>
       </c>
       <c r="N3" s="1">
-        <v>-3.549856989680803</v>
+        <v>-7.868288709243537</v>
       </c>
       <c r="O3" s="1">
-        <v>39.285714285714285</v>
+        <v>38.095238095238095</v>
       </c>
       <c r="P3" s="1">
         <v>26.053946839070953</v>
       </c>
       <c r="Q3" s="1">
-        <v>62.26190476190476</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="R3" s="1">
-        <v>43.214285714285715</v>
+        <v>43.095238095238095</v>
       </c>
       <c r="S3" s="1" t="s">
         <v>95</v>
       </c>
       <c r="T3" s="1">
-        <v>-23.86</v>
+        <v>-23.98</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -2305,49 +2305,49 @@
         <v>6.35</v>
       </c>
       <c r="F4" s="2">
-        <v>0.3791065423867275</v>
+        <v>0.3251267781323619</v>
       </c>
       <c r="G4" s="2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="H4" s="2">
-        <v>53.13</v>
+        <v>50.5</v>
       </c>
       <c r="I4" s="2">
-        <v>48.32</v>
+        <v>45.61</v>
       </c>
       <c r="J4" s="2">
-        <v>0.02566850265165403</v>
+        <v>0.023804526247211924</v>
       </c>
       <c r="K4" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L4" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M4" s="2">
-        <v>0.3889289487546992</v>
+        <v>0.32658630157645274</v>
       </c>
       <c r="N4" s="2">
-        <v>42.774296694890424</v>
+        <v>34.13905333655941</v>
       </c>
       <c r="O4" s="2">
-        <v>94.04761904761905</v>
+        <v>91.66666666666666</v>
       </c>
       <c r="P4" s="2">
         <v>19.349659482175007</v>
       </c>
       <c r="Q4" s="2">
-        <v>59.642857142857146</v>
+        <v>58.452380952380956</v>
       </c>
       <c r="R4" s="2">
-        <v>54.76190476190476</v>
+        <v>54.166666666666664</v>
       </c>
       <c r="S4" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T4" s="2">
-        <v>6.41</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -2361,55 +2361,55 @@
         <v>39.285714285714285</v>
       </c>
       <c r="D5" s="1">
-        <v>29.574074074074076</v>
+        <v>30.814814814814813</v>
       </c>
       <c r="E5" s="1">
         <v>1.69</v>
       </c>
       <c r="F5" s="1">
-        <v>-0.18112513184895096</v>
+        <v>-0.15121888524507135</v>
       </c>
       <c r="G5" s="1">
         <v>1.91</v>
       </c>
       <c r="H5" s="1">
-        <v>50.65</v>
+        <v>50.75</v>
       </c>
       <c r="I5" s="1">
-        <v>-10.35</v>
+        <v>-10.22</v>
       </c>
       <c r="J5" s="1">
-        <v>-0.011563696848779472</v>
+        <v>-0.014458365222932316</v>
       </c>
       <c r="K5" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L5" s="1">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M5" s="1">
-        <v>-0.15558687529222448</v>
+        <v>-0.14752953431695282</v>
       </c>
       <c r="N5" s="1">
-        <v>-11.677285709801952</v>
+        <v>-13.272530252781154</v>
       </c>
       <c r="O5" s="1">
-        <v>23.809523809523807</v>
+        <v>27.380952380952383</v>
       </c>
       <c r="P5" s="1">
         <v>33.002444654975626</v>
       </c>
       <c r="Q5" s="1">
-        <v>49.642857142857146</v>
+        <v>48.80952380952381</v>
       </c>
       <c r="R5" s="1">
-        <v>32.797619047619044</v>
+        <v>33.511904761904766</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T5" s="1">
-        <v>-13.18</v>
+        <v>-12.46</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -2429,19 +2429,19 @@
         <v>-1.87</v>
       </c>
       <c r="F6" s="1">
-        <v>-0.05562068915255862</v>
+        <v>-0.06339811196205472</v>
       </c>
       <c r="G6" s="1">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="H6" s="1">
-        <v>53.97</v>
+        <v>48.93</v>
       </c>
       <c r="I6" s="1">
-        <v>-7.33</v>
+        <v>-9.39</v>
       </c>
       <c r="J6" s="1">
-        <v>0.004162236323503007</v>
+        <v>0.0038728792097678113</v>
       </c>
       <c r="K6" s="1" t="b">
         <v>0</v>
@@ -2450,28 +2450,28 @@
         <v>-205</v>
       </c>
       <c r="M6" s="1">
-        <v>-0.03906291841797771</v>
+        <v>-0.06096557288856996</v>
       </c>
       <c r="N6" s="1">
-        <v>-0.024890022377279178</v>
+        <v>-4.616134109942875</v>
       </c>
       <c r="O6" s="1">
-        <v>46.42857142857143</v>
+        <v>45.23809523809524</v>
       </c>
       <c r="P6" s="1">
         <v>28.714544797168166</v>
       </c>
       <c r="Q6" s="1">
-        <v>48.92857142857143</v>
+        <v>47.023809523809526</v>
       </c>
       <c r="R6" s="1">
-        <v>36.36904761904762</v>
+        <v>36.25</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T6" s="1">
-        <v>17.28</v>
+        <v>17.16</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -2491,19 +2491,19 @@
         <v>0.51</v>
       </c>
       <c r="F7" s="2">
-        <v>-0.045212461319663694</v>
+        <v>-0.02110888832927165</v>
       </c>
       <c r="G7" s="2">
         <v>2.23</v>
       </c>
       <c r="H7" s="2">
-        <v>44.26</v>
+        <v>46.43</v>
       </c>
       <c r="I7" s="2">
-        <v>6.84</v>
+        <v>7.89</v>
       </c>
       <c r="J7" s="2">
-        <v>0.011113833428752447</v>
+        <v>0.009509047270217452</v>
       </c>
       <c r="K7" s="2" t="b">
         <v>0</v>
@@ -2512,28 +2512,28 @@
         <v>178</v>
       </c>
       <c r="M7" s="2">
-        <v>-0.01069371894079163</v>
+        <v>-0.016122183228627907</v>
       </c>
       <c r="N7" s="2">
-        <v>2.8120299253413243</v>
+        <v>-0.13179514394866726</v>
       </c>
       <c r="O7" s="2">
-        <v>50</v>
+        <v>54.761904761904766</v>
       </c>
       <c r="P7" s="2">
         <v>19.398494070050486</v>
       </c>
       <c r="Q7" s="2">
-        <v>65</v>
+        <v>65.23809523809523</v>
       </c>
       <c r="R7" s="2">
-        <v>52.5</v>
+        <v>53.92857142857143</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>99</v>
       </c>
       <c r="T7" s="2">
-        <v>4.09</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -2553,19 +2553,19 @@
         <v>2.66</v>
       </c>
       <c r="F8" s="1">
-        <v>-0.08899213415981173</v>
+        <v>-0.09864059584071115</v>
       </c>
       <c r="G8" s="1">
         <v>0.61</v>
       </c>
       <c r="H8" s="1">
-        <v>38.71</v>
+        <v>35.76</v>
       </c>
       <c r="I8" s="1">
-        <v>8.04</v>
+        <v>6.35</v>
       </c>
       <c r="J8" s="1">
-        <v>-0.008278073861432799</v>
+        <v>-0.009019027055515196</v>
       </c>
       <c r="K8" s="1" t="b">
         <v>1</v>
@@ -2574,28 +2574,28 @@
         <v>361</v>
       </c>
       <c r="M8" s="1">
-        <v>-0.09993710125555166</v>
+        <v>-0.10022174623847624</v>
       </c>
       <c r="N8" s="1">
-        <v>-6.112308306134675</v>
+        <v>-8.541751444933494</v>
       </c>
       <c r="O8" s="1">
-        <v>30.952380952380953</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="P8" s="1">
-        <v>13.122495465725093</v>
+        <v>13.846685592437208</v>
       </c>
       <c r="Q8" s="1">
-        <v>47.619047619047606</v>
+        <v>46.547619047619044</v>
       </c>
       <c r="R8" s="1">
-        <v>38.51190476190476</v>
+        <v>39.464285714285715</v>
       </c>
       <c r="S8" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T8" s="1">
-        <v>-21.24</v>
+        <v>-20.29</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -2609,25 +2609,25 @@
         <v>40.476190476190474</v>
       </c>
       <c r="D9" s="2">
-        <v>35.82905982905983</v>
+        <v>36.18803418803419</v>
       </c>
       <c r="E9" s="2">
         <v>2.97</v>
       </c>
       <c r="F9" s="2">
-        <v>0.2981570975269442</v>
+        <v>0.2636560065630964</v>
       </c>
       <c r="G9" s="2">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="H9" s="2">
-        <v>51.52</v>
+        <v>52.4</v>
       </c>
       <c r="I9" s="2">
-        <v>12.54</v>
+        <v>13.28</v>
       </c>
       <c r="J9" s="2">
-        <v>0.03281094613323919</v>
+        <v>0.03026422724404011</v>
       </c>
       <c r="K9" s="2" t="b">
         <v>0</v>
@@ -2636,28 +2636,28 @@
         <v>-113</v>
       </c>
       <c r="M9" s="2">
-        <v>0.3152761486254092</v>
+        <v>0.26616963027236396</v>
       </c>
       <c r="N9" s="2">
-        <v>35.40901668196142</v>
+        <v>28.09738620615052</v>
       </c>
       <c r="O9" s="2">
-        <v>90.47619047619048</v>
+        <v>88.09523809523809</v>
       </c>
       <c r="P9" s="2">
         <v>33.227512780245505</v>
       </c>
       <c r="Q9" s="2">
-        <v>69.28571428571429</v>
+        <v>69.16666666666667</v>
       </c>
       <c r="R9" s="2">
-        <v>60.05952380952382</v>
+        <v>59.345238095238095</v>
       </c>
       <c r="S9" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T9" s="2">
-        <v>32.68</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -2677,49 +2677,49 @@
         <v>0.08</v>
       </c>
       <c r="F10" s="1">
-        <v>0.03514550148048769</v>
+        <v>0.030047404885244697</v>
       </c>
       <c r="G10" s="1">
         <v>1.41</v>
       </c>
       <c r="H10" s="1">
-        <v>55.82</v>
+        <v>52.47</v>
       </c>
       <c r="I10" s="1">
-        <v>3.46</v>
+        <v>2.3</v>
       </c>
       <c r="J10" s="1">
-        <v>0.008165217096187226</v>
+        <v>0.008695891919290369</v>
       </c>
       <c r="K10" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L10" s="1">
-        <v>-51</v>
+        <v>-50</v>
       </c>
       <c r="M10" s="1">
-        <v>0.046651748940111704</v>
+        <v>0.03170963991879261</v>
       </c>
       <c r="N10" s="1">
-        <v>8.54657671343166</v>
+        <v>4.651387170793397</v>
       </c>
       <c r="O10" s="1">
-        <v>61.904761904761905</v>
+        <v>60.71428571428571</v>
       </c>
       <c r="P10" s="1">
         <v>14.568379622257217</v>
       </c>
       <c r="Q10" s="1">
-        <v>55</v>
+        <v>54.404761904761905</v>
       </c>
       <c r="R10" s="1">
-        <v>47.857142857142854</v>
+        <v>47.738095238095234</v>
       </c>
       <c r="S10" s="1" t="s">
         <v>101</v>
       </c>
       <c r="T10" s="1">
-        <v>12.31</v>
+        <v>12.19</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -2739,19 +2739,19 @@
         <v>2.19</v>
       </c>
       <c r="F11" s="2">
-        <v>0.4918834716303588</v>
+        <v>0.5321658356975969</v>
       </c>
       <c r="G11" s="2">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="H11" s="2">
-        <v>58.63</v>
+        <v>64.54</v>
       </c>
       <c r="I11" s="2">
-        <v>37.45</v>
+        <v>45.07</v>
       </c>
       <c r="J11" s="2">
-        <v>0.016475646770997953</v>
+        <v>0.018237022494593438</v>
       </c>
       <c r="K11" s="2" t="b">
         <v>0</v>
@@ -2760,10 +2760,10 @@
         <v>40</v>
       </c>
       <c r="M11" s="2">
-        <v>0.48374490635403933</v>
+        <v>0.5309495661608545</v>
       </c>
       <c r="N11" s="2">
-        <v>52.25589245482441</v>
+        <v>54.57537979499957</v>
       </c>
       <c r="O11" s="2">
         <v>96.42857142857143</v>
@@ -2772,16 +2772,16 @@
         <v>21.2185970476566</v>
       </c>
       <c r="Q11" s="2">
-        <v>64.16666666666667</v>
+        <v>65.83333333333333</v>
       </c>
       <c r="R11" s="2">
-        <v>58.45238095238095</v>
+        <v>58.80952380952381</v>
       </c>
       <c r="S11" s="2" t="s">
         <v>102</v>
       </c>
       <c r="T11" s="2">
-        <v>6.81</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -2801,31 +2801,31 @@
         <v>1.36</v>
       </c>
       <c r="F12" s="2">
-        <v>0.733967426886627</v>
+        <v>0.7196463124147912</v>
       </c>
       <c r="G12" s="2">
         <v>0.98</v>
       </c>
       <c r="H12" s="2">
-        <v>64.15</v>
+        <v>64.56</v>
       </c>
       <c r="I12" s="2">
-        <v>53.43</v>
+        <v>53.63</v>
       </c>
       <c r="J12" s="2">
-        <v>0.045047197379191106</v>
+        <v>0.043642160393446656</v>
       </c>
       <c r="K12" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L12" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M12" s="2">
-        <v>0.7334061465227428</v>
+        <v>0.7195652277790083</v>
       </c>
       <c r="N12" s="2">
-        <v>77.22201647169479</v>
+        <v>73.43694595681495</v>
       </c>
       <c r="O12" s="2">
         <v>100</v>
@@ -2834,16 +2834,16 @@
         <v>23.557267760130397</v>
       </c>
       <c r="Q12" s="2">
-        <v>71.66666666666667</v>
+        <v>71.9047619047619</v>
       </c>
       <c r="R12" s="2">
-        <v>62.67857142857142</v>
+        <v>62.797619047619044</v>
       </c>
       <c r="S12" s="2" t="s">
         <v>103</v>
       </c>
       <c r="T12" s="2">
-        <v>9.93</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -2863,19 +2863,19 @@
         <v>-1.09</v>
       </c>
       <c r="F13" s="1">
-        <v>0.3824775262089728</v>
+        <v>0.3954261927978079</v>
       </c>
       <c r="G13" s="1">
         <v>1.57</v>
       </c>
       <c r="H13" s="1">
-        <v>50.07</v>
+        <v>54.25</v>
       </c>
       <c r="I13" s="1">
-        <v>11.72</v>
+        <v>15.34</v>
       </c>
       <c r="J13" s="1">
-        <v>0.05024102119441429</v>
+        <v>0.04631047830695267</v>
       </c>
       <c r="K13" s="1" t="b">
         <v>1</v>
@@ -2884,10 +2884,10 @@
         <v>5</v>
       </c>
       <c r="M13" s="1">
-        <v>0.39847401657966963</v>
+        <v>0.3977371049176184</v>
       </c>
       <c r="N13" s="1">
-        <v>43.72880347738745</v>
+        <v>41.254133670675955</v>
       </c>
       <c r="O13" s="1">
         <v>95.23809523809523</v>
@@ -2896,7 +2896,7 @@
         <v>40.13761891809808</v>
       </c>
       <c r="Q13" s="1">
-        <v>41.54761904761905</v>
+        <v>43.80952380952381</v>
       </c>
       <c r="R13" s="1">
         <v>38.33333333333333</v>
@@ -2925,49 +2925,49 @@
         <v>-1.74</v>
       </c>
       <c r="F14" s="2">
-        <v>0.5715212354760213</v>
+        <v>0.5985931847629387</v>
       </c>
       <c r="G14" s="2">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="H14" s="2">
-        <v>65.11</v>
+        <v>68.68</v>
       </c>
       <c r="I14" s="2">
-        <v>74.94</v>
+        <v>80.16</v>
       </c>
       <c r="J14" s="2">
-        <v>0.026102728768634946</v>
+        <v>0.025749119233567475</v>
       </c>
       <c r="K14" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L14" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M14" s="2">
-        <v>0.5645052309274701</v>
+        <v>0.5975390844977619</v>
       </c>
       <c r="N14" s="2">
-        <v>60.33192491216749</v>
+        <v>61.23433162869032</v>
       </c>
       <c r="O14" s="2">
-        <v>98.80952380952381</v>
+        <v>97.61904761904762</v>
       </c>
       <c r="P14" s="2">
         <v>19.142997204429033</v>
       </c>
       <c r="Q14" s="2">
-        <v>67.97619047619048</v>
+        <v>68.0952380952381</v>
       </c>
       <c r="R14" s="2">
-        <v>60.892857142857146</v>
+        <v>60.654761904761905</v>
       </c>
       <c r="S14" s="2" t="s">
         <v>99</v>
       </c>
       <c r="T14" s="2">
-        <v>4.98</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -2981,55 +2981,55 @@
         <v>15.476190476190476</v>
       </c>
       <c r="D15" s="3">
-        <v>19.13679245283019</v>
+        <v>19.396226415094336</v>
       </c>
       <c r="E15" s="3">
         <v>1.51</v>
       </c>
       <c r="F15" s="3">
-        <v>-0.293970758187976</v>
+        <v>-0.26013481734958127</v>
       </c>
       <c r="G15" s="3">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="H15" s="3">
-        <v>50.17</v>
+        <v>55.59</v>
       </c>
       <c r="I15" s="3">
-        <v>27.45</v>
+        <v>33.23</v>
       </c>
       <c r="J15" s="3">
-        <v>-0.027012091624370158</v>
+        <v>-0.027382456892013598</v>
       </c>
       <c r="K15" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L15" s="3">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="M15" s="3">
-        <v>-0.25861009526327783</v>
+        <v>-0.2550670276131547</v>
       </c>
       <c r="N15" s="3">
-        <v>-21.979607706907288</v>
+        <v>-24.02627958240134</v>
       </c>
       <c r="O15" s="3">
-        <v>10.714285714285714</v>
+        <v>15.476190476190476</v>
       </c>
       <c r="P15" s="3">
         <v>41.90435941885386</v>
       </c>
       <c r="Q15" s="3">
-        <v>44.166666666666664</v>
+        <v>46.19047619047619</v>
       </c>
       <c r="R15" s="3">
-        <v>19.107142857142858</v>
+        <v>20.535714285714285</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>105</v>
       </c>
       <c r="T15" s="3">
-        <v>-39.31</v>
+        <v>-37.88</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -3049,19 +3049,19 @@
         <v>28.81</v>
       </c>
       <c r="F16" s="3">
-        <v>-0.08108354636825113</v>
+        <v>-0.2566940845659939</v>
       </c>
       <c r="G16" s="3">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="H16" s="3">
-        <v>41.38</v>
+        <v>39.79</v>
       </c>
       <c r="I16" s="3">
-        <v>-7.26</v>
+        <v>-9.27</v>
       </c>
       <c r="J16" s="3">
-        <v>-0.03795401302739081</v>
+        <v>-0.042142640718164474</v>
       </c>
       <c r="K16" s="3" t="b">
         <v>0</v>
@@ -3070,90 +3070,90 @@
         <v>27</v>
       </c>
       <c r="M16" s="3">
-        <v>-0.058632331812887184</v>
+        <v>-0.25341015681678947</v>
       </c>
       <c r="N16" s="3">
-        <v>-1.9818313618682253</v>
+        <v>-23.860592502764824</v>
       </c>
       <c r="O16" s="3">
-        <v>42.857142857142854</v>
+        <v>16.666666666666664</v>
       </c>
       <c r="P16" s="3">
         <v>40.1905830435425</v>
       </c>
       <c r="Q16" s="3">
-        <v>27.380952380952376</v>
+        <v>26.785714285714285</v>
       </c>
       <c r="R16" s="3">
-        <v>22.678571428571423</v>
+        <v>14.821428571428566</v>
       </c>
       <c r="S16" s="3" t="s">
         <v>106</v>
       </c>
       <c r="T16" s="3">
-        <v>-20.55</v>
+        <v>-28.41</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="3">
         <v>-4.76</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="3">
         <v>5.952380952380952</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" s="3">
         <v>6.40546218487395</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" s="3">
         <v>-1.42</v>
       </c>
-      <c r="F17" s="1">
-        <v>0.0033111411473464164</v>
-      </c>
-      <c r="G17" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="H17" s="1">
-        <v>42.88</v>
-      </c>
-      <c r="I17" s="1">
-        <v>-1.33</v>
-      </c>
-      <c r="J17" s="1">
-        <v>-0.006078857794570694</v>
-      </c>
-      <c r="K17" s="1" t="b">
+      <c r="F17" s="3">
+        <v>-0.032752045584167805</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1.77</v>
+      </c>
+      <c r="H17" s="3">
+        <v>41.14</v>
+      </c>
+      <c r="I17" s="3">
+        <v>-2.6</v>
+      </c>
+      <c r="J17" s="3">
+        <v>-0.009769835280095828</v>
+      </c>
+      <c r="K17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L17" s="1">
+      <c r="L17" s="3">
         <v>31</v>
       </c>
-      <c r="M17" s="1">
-        <v>0.024639794974942175</v>
-      </c>
-      <c r="N17" s="1">
-        <v>6.345381316914713</v>
-      </c>
-      <c r="O17" s="1">
-        <v>57.14285714285714</v>
-      </c>
-      <c r="P17" s="1">
+      <c r="M17" s="3">
+        <v>-0.02963028710652904</v>
+      </c>
+      <c r="N17" s="3">
+        <v>-1.4826055317387739</v>
+      </c>
+      <c r="O17" s="3">
+        <v>48.80952380952381</v>
+      </c>
+      <c r="P17" s="3">
         <v>24.80206596461608</v>
       </c>
-      <c r="Q17" s="1">
-        <v>35.357142857142854</v>
-      </c>
-      <c r="R17" s="1">
-        <v>32.67857142857143</v>
-      </c>
-      <c r="S17" s="1" t="s">
+      <c r="Q17" s="3">
+        <v>33.45238095238095</v>
+      </c>
+      <c r="R17" s="3">
+        <v>29.821428571428577</v>
+      </c>
+      <c r="S17" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="T17" s="1">
-        <v>-0.49</v>
+      <c r="T17" s="3">
+        <v>-3.35</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -3173,49 +3173,49 @@
         <v>11.06</v>
       </c>
       <c r="F18" s="3">
-        <v>-0.38614992766037703</v>
+        <v>-0.49106436960759603</v>
       </c>
       <c r="G18" s="3">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="H18" s="3">
-        <v>36.56</v>
+        <v>22.21</v>
       </c>
       <c r="I18" s="3">
-        <v>-31.02</v>
+        <v>-44.66</v>
       </c>
       <c r="J18" s="3">
-        <v>-0.061861656245620386</v>
+        <v>-0.06780716033684732</v>
       </c>
       <c r="K18" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="3">
         <v>31</v>
       </c>
       <c r="M18" s="3">
-        <v>-0.3836241660228986</v>
+        <v>-0.49053731947500767</v>
       </c>
       <c r="N18" s="3">
-        <v>-34.481014782869366</v>
+        <v>-47.57330876858664</v>
       </c>
       <c r="O18" s="3">
-        <v>2.380952380952381</v>
+        <v>1.1904761904761905</v>
       </c>
       <c r="P18" s="3">
-        <v>48.6563520729564</v>
+        <v>57.77687251199141</v>
       </c>
       <c r="Q18" s="3">
-        <v>41.54761904761905</v>
+        <v>39.761904761904766</v>
       </c>
       <c r="R18" s="3">
-        <v>24.642857142857146</v>
+        <v>23.333333333333343</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>107</v>
       </c>
       <c r="T18" s="3">
-        <v>-9.63</v>
+        <v>-10.93</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -3235,19 +3235,19 @@
         <v>3.12</v>
       </c>
       <c r="F19" s="2">
-        <v>0.07297195256463443</v>
+        <v>0.07709467163159969</v>
       </c>
       <c r="G19" s="2">
         <v>0.1</v>
       </c>
       <c r="H19" s="2">
-        <v>53.41</v>
+        <v>51.86</v>
       </c>
       <c r="I19" s="2">
-        <v>13.13</v>
+        <v>12.41</v>
       </c>
       <c r="J19" s="2">
-        <v>-0.0001345906658455575</v>
+        <v>0.0009386174230938178</v>
       </c>
       <c r="K19" s="2" t="b">
         <v>0</v>
@@ -3256,28 +3256,28 @@
         <v>-58</v>
       </c>
       <c r="M19" s="2">
-        <v>0.04771433618984999</v>
+        <v>0.07344586302137257</v>
       </c>
       <c r="N19" s="2">
-        <v>8.652835438405484</v>
+        <v>8.825009481051378</v>
       </c>
       <c r="O19" s="2">
-        <v>63.095238095238095</v>
+        <v>65.47619047619048</v>
       </c>
       <c r="P19" s="2">
         <v>11.392700631623551</v>
       </c>
       <c r="Q19" s="2">
-        <v>59.88095238095238</v>
+        <v>59.166666666666664</v>
       </c>
       <c r="R19" s="2">
-        <v>52.4404761904762</v>
+        <v>53.27380952380953</v>
       </c>
       <c r="S19" s="2" t="s">
         <v>108</v>
       </c>
       <c r="T19" s="2">
-        <v>4.03</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -3297,49 +3297,49 @@
         <v>-5.68</v>
       </c>
       <c r="F20" s="2">
-        <v>0.24812821049311512</v>
+        <v>0.29160445537570323</v>
       </c>
       <c r="G20" s="2">
         <v>1.07</v>
       </c>
       <c r="H20" s="2">
-        <v>51.07</v>
+        <v>58.62</v>
       </c>
       <c r="I20" s="2">
-        <v>21.42</v>
+        <v>24.44</v>
       </c>
       <c r="J20" s="2">
-        <v>0.022609001575628982</v>
+        <v>0.02271122205930087</v>
       </c>
       <c r="K20" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M20" s="2">
-        <v>0.25009269176670945</v>
+        <v>0.2918882516009431</v>
       </c>
       <c r="N20" s="2">
-        <v>28.890670996091437</v>
+        <v>30.66924833900843</v>
       </c>
       <c r="O20" s="2">
-        <v>85.71428571428571</v>
+        <v>90.47619047619048</v>
       </c>
       <c r="P20" s="2">
         <v>20.924527727345563</v>
       </c>
       <c r="Q20" s="2">
-        <v>61.42857142857143</v>
+        <v>63.21428571428571</v>
       </c>
       <c r="R20" s="2">
-        <v>55.11904761904761</v>
+        <v>56.54761904761905</v>
       </c>
       <c r="S20" s="2" t="s">
         <v>95</v>
       </c>
       <c r="T20" s="2">
-        <v>19.27</v>
+        <v>20.69</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -3359,49 +3359,49 @@
         <v>-3.45</v>
       </c>
       <c r="F21" s="3">
-        <v>-0.38466214792594977</v>
+        <v>-0.3165139515121378</v>
       </c>
       <c r="G21" s="3">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H21" s="3">
-        <v>42.85</v>
+        <v>46.12</v>
       </c>
       <c r="I21" s="3">
-        <v>-12.04</v>
+        <v>-9.95</v>
       </c>
       <c r="J21" s="3">
-        <v>-0.024603202857270873</v>
+        <v>-0.024252468286811893</v>
       </c>
       <c r="K21" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" s="3">
         <v>55</v>
       </c>
       <c r="M21" s="3">
-        <v>-0.3672624566455427</v>
+        <v>-0.31404087012076165</v>
       </c>
       <c r="N21" s="3">
-        <v>-32.844843845133774</v>
+        <v>-29.923663833162035</v>
       </c>
       <c r="O21" s="3">
-        <v>3.571428571428571</v>
+        <v>8.333333333333332</v>
       </c>
       <c r="P21" s="3">
         <v>51.51389629888408</v>
       </c>
       <c r="Q21" s="3">
-        <v>40.95238095238095</v>
+        <v>43.21428571428571</v>
       </c>
       <c r="R21" s="3">
-        <v>20.714285714285715</v>
+        <v>22.5</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>109</v>
       </c>
       <c r="T21" s="3">
-        <v>-30.51</v>
+        <v>-28.72</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -3421,49 +3421,49 @@
         <v>-0.24</v>
       </c>
       <c r="F22" s="1">
-        <v>-0.10266680181312518</v>
+        <v>-0.11926045075471127</v>
       </c>
       <c r="G22" s="1">
         <v>1.39</v>
       </c>
       <c r="H22" s="1">
-        <v>30.94</v>
+        <v>29.8</v>
       </c>
       <c r="I22" s="1">
-        <v>-1.92</v>
+        <v>-3.92</v>
       </c>
       <c r="J22" s="1">
-        <v>-0.013616463667740084</v>
+        <v>-0.015748340097914405</v>
       </c>
       <c r="K22" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="1">
         <v>243</v>
       </c>
       <c r="M22" s="1">
-        <v>-0.09172183471738526</v>
+        <v>-0.11767930035694618</v>
       </c>
       <c r="N22" s="1">
-        <v>-5.290781652318034</v>
+        <v>-10.28750685678049</v>
       </c>
       <c r="O22" s="1">
-        <v>36.904761904761905</v>
+        <v>29.761904761904763</v>
       </c>
       <c r="P22" s="1">
-        <v>16.69901984635222</v>
+        <v>19.455960650079966</v>
       </c>
       <c r="Q22" s="1">
-        <v>42.023809523809526</v>
+        <v>41.42857142857142</v>
       </c>
       <c r="R22" s="1">
-        <v>38.69047619047619</v>
+        <v>35.476190476190474</v>
       </c>
       <c r="S22" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T22" s="1">
-        <v>-14.42</v>
+        <v>-17.63</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -3483,19 +3483,19 @@
         <v>0.07</v>
       </c>
       <c r="F23" s="2">
-        <v>0.1297929317469627</v>
+        <v>0.11380484232451815</v>
       </c>
       <c r="G23" s="2">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="H23" s="2">
-        <v>67.74</v>
+        <v>71.92</v>
       </c>
       <c r="I23" s="2">
-        <v>5.67</v>
+        <v>7.66</v>
       </c>
       <c r="J23" s="2">
-        <v>0.011863476972555707</v>
+        <v>0.012063555475983053</v>
       </c>
       <c r="K23" s="2" t="b">
         <v>1</v>
@@ -3504,90 +3504,90 @@
         <v>45</v>
       </c>
       <c r="M23" s="2">
-        <v>0.13512509520386162</v>
+        <v>0.11453460404656357</v>
       </c>
       <c r="N23" s="2">
-        <v>17.39391133980666</v>
+        <v>12.933883583570488</v>
       </c>
       <c r="O23" s="2">
-        <v>75</v>
+        <v>70.23809523809523</v>
       </c>
       <c r="P23" s="2">
         <v>20.883293768118005</v>
       </c>
       <c r="Q23" s="2">
-        <v>63.33333333333332</v>
+        <v>64.28571428571428</v>
       </c>
       <c r="R23" s="2">
-        <v>54.22619047619048</v>
+        <v>53.03571428571429</v>
       </c>
       <c r="S23" s="2" t="s">
         <v>108</v>
       </c>
       <c r="T23" s="2">
-        <v>18.43</v>
+        <v>17.24</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" s="3">
         <v>-97.21</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24" s="3">
         <v>1.1904761904761905</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D24" s="3">
         <v>2.6552823783561363</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E24" s="3">
         <v>1.55</v>
       </c>
-      <c r="F24" s="1">
-        <v>-0.006597090330134586</v>
-      </c>
-      <c r="G24" s="1">
-        <v>3.58</v>
-      </c>
-      <c r="H24" s="1">
-        <v>55.01</v>
-      </c>
-      <c r="I24" s="1">
-        <v>-5.53</v>
-      </c>
-      <c r="J24" s="1">
-        <v>0.040503645035753016</v>
-      </c>
-      <c r="K24" s="1" t="b">
+      <c r="F24" s="3">
+        <v>-0.037047816214066706</v>
+      </c>
+      <c r="G24" s="3">
+        <v>3.59</v>
+      </c>
+      <c r="H24" s="3">
+        <v>53.4</v>
+      </c>
+      <c r="I24" s="3">
+        <v>-7.02</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0.03523033883671116</v>
+      </c>
+      <c r="K24" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L24" s="1">
+      <c r="L24" s="3">
         <v>-68</v>
       </c>
-      <c r="M24" s="1">
-        <v>0.06580807661091415</v>
-      </c>
-      <c r="N24" s="1">
-        <v>10.462209480511904</v>
-      </c>
-      <c r="O24" s="1">
-        <v>65.47619047619048</v>
-      </c>
-      <c r="P24" s="1">
+      <c r="M24" s="3">
+        <v>-0.02654735588019086</v>
+      </c>
+      <c r="N24" s="3">
+        <v>-1.1743124091049617</v>
+      </c>
+      <c r="O24" s="3">
+        <v>51.19047619047619</v>
+      </c>
+      <c r="P24" s="3">
         <v>57.99224429263358</v>
       </c>
-      <c r="Q24" s="1">
-        <v>45.47619047619048</v>
-      </c>
-      <c r="R24" s="1">
-        <v>32.142857142857146</v>
-      </c>
-      <c r="S24" s="1" t="s">
+      <c r="Q24" s="3">
+        <v>44.88095238095239</v>
+      </c>
+      <c r="R24" s="3">
+        <v>27.85714285714286</v>
+      </c>
+      <c r="S24" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="T24" s="1">
-        <v>35.86</v>
+      <c r="T24" s="3">
+        <v>31.58</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -3607,19 +3607,19 @@
         <v>15.52</v>
       </c>
       <c r="F25" s="3">
-        <v>-0.21651597338679843</v>
+        <v>-0.22806529314068907</v>
       </c>
       <c r="G25" s="3">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="H25" s="3">
-        <v>41.93</v>
+        <v>42.06</v>
       </c>
       <c r="I25" s="3">
-        <v>-33.59</v>
+        <v>-33.23</v>
       </c>
       <c r="J25" s="3">
-        <v>-0.0021524259468810357</v>
+        <v>-0.007099344383079003</v>
       </c>
       <c r="K25" s="3" t="b">
         <v>1</v>
@@ -3628,10 +3628,10 @@
         <v>34</v>
       </c>
       <c r="M25" s="3">
-        <v>-0.17834890864267972</v>
+        <v>-0.22251099558956555</v>
       </c>
       <c r="N25" s="3">
-        <v>-13.953489044847473</v>
+        <v>-20.77067638004243</v>
       </c>
       <c r="O25" s="3">
         <v>19.047619047619047</v>
@@ -3640,16 +3640,16 @@
         <v>45.59139601172712</v>
       </c>
       <c r="Q25" s="3">
-        <v>18.928571428571427</v>
+        <v>17.142857142857142</v>
       </c>
       <c r="R25" s="3">
-        <v>6.369047619047619</v>
+        <v>5.178571428571429</v>
       </c>
       <c r="S25" s="3" t="s">
         <v>101</v>
       </c>
       <c r="T25" s="3">
-        <v>4.97</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -3669,49 +3669,49 @@
         <v>-0.88</v>
       </c>
       <c r="F26" s="3">
-        <v>-0.4573781880803759</v>
+        <v>-0.418863256826684</v>
       </c>
       <c r="G26" s="3">
         <v>3.38</v>
       </c>
       <c r="H26" s="3">
-        <v>42.39</v>
+        <v>42.26</v>
       </c>
       <c r="I26" s="3">
-        <v>-15.61</v>
+        <v>-15.66</v>
       </c>
       <c r="J26" s="3">
-        <v>-0.0326450394752859</v>
+        <v>-0.03423806305110756</v>
       </c>
       <c r="K26" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" s="3">
         <v>159</v>
       </c>
       <c r="M26" s="3">
-        <v>-0.39058582477816817</v>
+        <v>-0.4092141851685278</v>
       </c>
       <c r="N26" s="3">
-        <v>-35.177180658396324</v>
+        <v>-39.44099533793866</v>
       </c>
       <c r="O26" s="3">
-        <v>1.1904761904761905</v>
+        <v>2.380952380952381</v>
       </c>
       <c r="P26" s="3">
         <v>55.61259899184437</v>
       </c>
       <c r="Q26" s="3">
-        <v>12.738095238095237</v>
+        <v>13.095238095238095</v>
       </c>
       <c r="R26" s="3">
-        <v>-3.2738095238095246</v>
+        <v>-2.7976190476190483</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>101</v>
       </c>
       <c r="T26" s="3">
-        <v>-32.12</v>
+        <v>-31.64</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -3731,19 +3731,19 @@
         <v>6.6</v>
       </c>
       <c r="F27" s="3">
-        <v>-0.3968756486822497</v>
+        <v>-0.38761491156669486</v>
       </c>
       <c r="G27" s="3">
         <v>2.66</v>
       </c>
       <c r="H27" s="3">
-        <v>31.83</v>
+        <v>30.88</v>
       </c>
       <c r="I27" s="3">
-        <v>-38.35</v>
+        <v>-39.09</v>
       </c>
       <c r="J27" s="3">
-        <v>-0.029785130381341725</v>
+        <v>-0.032032005871659296</v>
       </c>
       <c r="K27" s="3" t="b">
         <v>1</v>
@@ -3752,28 +3752,28 @@
         <v>7</v>
       </c>
       <c r="M27" s="3">
-        <v>-0.3502893784798695</v>
+        <v>-0.3808848867967204</v>
       </c>
       <c r="N27" s="3">
-        <v>-31.147536028566456</v>
+        <v>-36.60806550075791</v>
       </c>
       <c r="O27" s="3">
-        <v>4.761904761904762</v>
+        <v>3.571428571428571</v>
       </c>
       <c r="P27" s="3">
-        <v>48.780487048443945</v>
+        <v>50.16260146842582</v>
       </c>
       <c r="Q27" s="3">
-        <v>10.833333333333332</v>
+        <v>10.95238095238095</v>
       </c>
       <c r="R27" s="3">
-        <v>0.4166666666666643</v>
+        <v>0.17857142857142705</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>101</v>
       </c>
       <c r="T27" s="3">
-        <v>-15.74</v>
+        <v>-15.98</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -3793,19 +3793,19 @@
         <v>1.72</v>
       </c>
       <c r="F28" s="1">
-        <v>-0.017592968676545417</v>
+        <v>-0.0383812817215857</v>
       </c>
       <c r="G28" s="1">
         <v>3.26</v>
       </c>
       <c r="H28" s="1">
-        <v>43.77</v>
+        <v>44.98</v>
       </c>
       <c r="I28" s="1">
-        <v>-15.19</v>
+        <v>-14.12</v>
       </c>
       <c r="J28" s="1">
-        <v>0.013666160712908892</v>
+        <v>0.010443960294191939</v>
       </c>
       <c r="K28" s="1" t="b">
         <v>0</v>
@@ -3814,28 +3814,28 @@
         <v>3</v>
       </c>
       <c r="M28" s="1">
-        <v>0.04583171244235773</v>
+        <v>-0.029218717878126466</v>
       </c>
       <c r="N28" s="1">
-        <v>8.46457306365626</v>
+        <v>-1.4414486088985201</v>
       </c>
       <c r="O28" s="1">
-        <v>60.71428571428571</v>
+        <v>50</v>
       </c>
       <c r="P28" s="1">
         <v>35.08771990976345</v>
       </c>
       <c r="Q28" s="1">
-        <v>46.66666666666667</v>
+        <v>45.35714285714286</v>
       </c>
       <c r="R28" s="1">
-        <v>39.88095238095238</v>
+        <v>35.89285714285714</v>
       </c>
       <c r="S28" s="1" t="s">
         <v>110</v>
       </c>
       <c r="T28" s="1">
-        <v>22.87</v>
+        <v>18.88</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -3855,19 +3855,19 @@
         <v>-4.82</v>
       </c>
       <c r="F29" s="1">
-        <v>-0.01132295527763083</v>
+        <v>-0.023658413715891106</v>
       </c>
       <c r="G29" s="1">
         <v>2.32</v>
       </c>
       <c r="H29" s="1">
-        <v>46.35</v>
+        <v>44.44</v>
       </c>
       <c r="I29" s="1">
-        <v>-11.53</v>
+        <v>-12.74</v>
       </c>
       <c r="J29" s="1">
-        <v>-0.0035344403769208797</v>
+        <v>-0.005401540775250435</v>
       </c>
       <c r="K29" s="1" t="b">
         <v>0</v>
@@ -3876,28 +3876,28 @@
         <v>10</v>
       </c>
       <c r="M29" s="1">
-        <v>0.02572154873871968</v>
+        <v>-0.018306827754224653</v>
       </c>
       <c r="N29" s="1">
-        <v>6.453556693292471</v>
+        <v>-0.35025959650833816</v>
       </c>
       <c r="O29" s="1">
-        <v>58.333333333333336</v>
+        <v>53.57142857142857</v>
       </c>
       <c r="P29" s="1">
         <v>21.89743824494191</v>
       </c>
       <c r="Q29" s="1">
-        <v>52.5</v>
+        <v>51.42857142857142</v>
       </c>
       <c r="R29" s="1">
-        <v>48.392857142857146</v>
+        <v>46.8452380952381</v>
       </c>
       <c r="S29" s="1" t="s">
         <v>108</v>
       </c>
       <c r="T29" s="1">
-        <v>8.15</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -3917,19 +3917,19 @@
         <v>1.75</v>
       </c>
       <c r="F30" s="1">
-        <v>-0.0856315494495418</v>
+        <v>-0.09990039554502307</v>
       </c>
       <c r="G30" s="1">
         <v>1.24</v>
       </c>
       <c r="H30" s="1">
-        <v>43.12</v>
+        <v>45.23</v>
       </c>
       <c r="I30" s="1">
-        <v>-5.44</v>
+        <v>-4.84</v>
       </c>
       <c r="J30" s="1">
-        <v>-0.004631496078572336</v>
+        <v>-0.006306081131863606</v>
       </c>
       <c r="K30" s="1" t="b">
         <v>0</v>
@@ -3938,28 +3938,28 @@
         <v>136</v>
       </c>
       <c r="M30" s="1">
-        <v>-0.07889618508293261</v>
+        <v>-0.09892737991562917</v>
       </c>
       <c r="N30" s="1">
-        <v>-4.008216688872772</v>
+        <v>-8.412314812648793</v>
       </c>
       <c r="O30" s="1">
-        <v>38.095238095238095</v>
+        <v>35.714285714285715</v>
       </c>
       <c r="P30" s="1">
         <v>14.879468887608937</v>
       </c>
       <c r="Q30" s="1">
-        <v>57.14285714285714</v>
+        <v>57.38095238095238</v>
       </c>
       <c r="R30" s="1">
-        <v>48.392857142857146</v>
+        <v>47.55952380952381</v>
       </c>
       <c r="S30" s="1" t="s">
         <v>109</v>
       </c>
       <c r="T30" s="1">
-        <v>-0.08</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -3973,25 +3973,25 @@
         <v>67.85714285714286</v>
       </c>
       <c r="D31" s="1">
-        <v>7.31162196679438</v>
+        <v>7.2899106002554275</v>
       </c>
       <c r="E31" s="1">
         <v>0.38</v>
       </c>
       <c r="F31" s="1">
-        <v>-0.15004171656000947</v>
+        <v>-0.15552777507748197</v>
       </c>
       <c r="G31" s="1">
         <v>1.48</v>
       </c>
       <c r="H31" s="1">
-        <v>33.86</v>
+        <v>33.8</v>
       </c>
       <c r="I31" s="1">
-        <v>-7.11</v>
+        <v>-7.66</v>
       </c>
       <c r="J31" s="1">
-        <v>-0.0023213180223429575</v>
+        <v>-0.004310297631664881</v>
       </c>
       <c r="K31" s="1" t="b">
         <v>0</v>
@@ -4000,90 +4000,90 @@
         <v>208</v>
       </c>
       <c r="M31" s="1">
-        <v>-0.1365709878267911</v>
+        <v>-0.15358174381869416</v>
       </c>
       <c r="N31" s="1">
-        <v>-9.775696963258616</v>
+        <v>-13.877751202955297</v>
       </c>
       <c r="O31" s="1">
-        <v>25</v>
+        <v>26.190476190476193</v>
       </c>
       <c r="P31" s="1">
-        <v>28.417468700740923</v>
+        <v>29.54918623383928</v>
       </c>
       <c r="Q31" s="1">
-        <v>52.97619047619048</v>
+        <v>52.73809523809524</v>
       </c>
       <c r="R31" s="1">
-        <v>39.3452380952381</v>
+        <v>39.46428571428573</v>
       </c>
       <c r="S31" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T31" s="1">
-        <v>-8.7</v>
+        <v>-8.58</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="1">
         <v>-2.58</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="1">
         <v>13.095238095238097</v>
       </c>
-      <c r="D32" s="3">
-        <v>8.267441860465116</v>
-      </c>
-      <c r="E32" s="3">
+      <c r="D32" s="1">
+        <v>8.755813953488373</v>
+      </c>
+      <c r="E32" s="1">
         <v>3.57</v>
       </c>
-      <c r="F32" s="3">
-        <v>-0.10963238670996056</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="F32" s="1">
+        <v>-0.08562265625398327</v>
+      </c>
+      <c r="G32" s="1">
         <v>1.61</v>
       </c>
-      <c r="H32" s="3">
-        <v>46.11</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-3.74</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-0.006645706526291285</v>
-      </c>
-      <c r="K32" s="3" t="b">
+      <c r="H32" s="1">
+        <v>44.66</v>
+      </c>
+      <c r="I32" s="1">
+        <v>-4.63</v>
+      </c>
+      <c r="J32" s="1">
+        <v>-0.012864987356518672</v>
+      </c>
+      <c r="K32" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L32" s="3">
-        <v>21</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-0.09251333561149555</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-5.369931741729066</v>
-      </c>
-      <c r="O32" s="3">
-        <v>35.714285714285715</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="L32" s="1">
+        <v>20</v>
+      </c>
+      <c r="M32" s="1">
+        <v>-0.0831495748626071</v>
+      </c>
+      <c r="N32" s="1">
+        <v>-6.834534307346585</v>
+      </c>
+      <c r="O32" s="1">
+        <v>41.66666666666667</v>
+      </c>
+      <c r="P32" s="1">
         <v>27.28297753683016</v>
       </c>
-      <c r="Q32" s="3">
-        <v>39.166666666666664</v>
-      </c>
-      <c r="R32" s="3">
-        <v>28.452380952380956</v>
-      </c>
-      <c r="S32" s="3" t="s">
+      <c r="Q32" s="1">
+        <v>37.73809523809524</v>
+      </c>
+      <c r="R32" s="1">
+        <v>30.05952380952381</v>
+      </c>
+      <c r="S32" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="T32" s="3">
-        <v>-3.44</v>
+      <c r="T32" s="1">
+        <v>-1.83</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -4103,49 +4103,49 @@
         <v>0.24</v>
       </c>
       <c r="F33" s="2">
-        <v>0.25184842447027966</v>
+        <v>0.22833643011595184</v>
       </c>
       <c r="G33" s="2">
         <v>1.1</v>
       </c>
       <c r="H33" s="2">
-        <v>57.29</v>
+        <v>55.13</v>
       </c>
       <c r="I33" s="2">
-        <v>15.73</v>
+        <v>14.93</v>
       </c>
       <c r="J33" s="2">
-        <v>0.026555017703357508</v>
+        <v>0.025936437941787623</v>
       </c>
       <c r="K33" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L33" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M33" s="2">
-        <v>0.25465482628970015</v>
+        <v>0.22874185329486596</v>
       </c>
       <c r="N33" s="2">
-        <v>29.346884448390504</v>
+        <v>24.354608508400734</v>
       </c>
       <c r="O33" s="2">
-        <v>86.90476190476191</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="P33" s="2">
         <v>23.38443607454554</v>
       </c>
       <c r="Q33" s="2">
-        <v>69.99999999999999</v>
+        <v>68.8095238095238</v>
       </c>
       <c r="R33" s="2">
-        <v>60.476190476190474</v>
+        <v>60.238095238095234</v>
       </c>
       <c r="S33" s="2" t="s">
         <v>108</v>
       </c>
       <c r="T33" s="2">
-        <v>24.68</v>
+        <v>24.45</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -4159,25 +4159,25 @@
         <v>92.85714285714286</v>
       </c>
       <c r="D34" s="1">
-        <v>-2.3350075339025613</v>
+        <v>-2.3395278754394777</v>
       </c>
       <c r="E34" s="1">
         <v>2.34</v>
       </c>
       <c r="F34" s="1">
-        <v>-0.07331616485328905</v>
+        <v>-0.0816363831952599</v>
       </c>
       <c r="G34" s="1">
         <v>1.21</v>
       </c>
       <c r="H34" s="1">
-        <v>51.88</v>
+        <v>51.65</v>
       </c>
       <c r="I34" s="1">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="J34" s="1">
-        <v>-0.00459191191504251</v>
+        <v>-0.005879704137087581</v>
       </c>
       <c r="K34" s="1" t="b">
         <v>1</v>
@@ -4186,28 +4186,28 @@
         <v>213</v>
       </c>
       <c r="M34" s="1">
-        <v>-0.06742272103250602</v>
+        <v>-0.08078499451954024</v>
       </c>
       <c r="N34" s="1">
-        <v>-2.860870283830112</v>
+        <v>-6.598076273039903</v>
       </c>
       <c r="O34" s="1">
-        <v>41.66666666666667</v>
+        <v>42.857142857142854</v>
       </c>
       <c r="P34" s="1">
         <v>21.09433056126816</v>
       </c>
       <c r="Q34" s="1">
-        <v>50.11904761904762</v>
+        <v>49.88095238095239</v>
       </c>
       <c r="R34" s="1">
-        <v>37.738095238095234</v>
+        <v>38.09523809523809</v>
       </c>
       <c r="S34" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T34" s="1">
-        <v>-9.09</v>
+        <v>-8.73</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -4221,25 +4221,25 @@
         <v>86.90476190476191</v>
       </c>
       <c r="D35" s="1">
-        <v>-0.45464852607709755</v>
+        <v>-0.4552154195011338</v>
       </c>
       <c r="E35" s="1">
         <v>-0.33</v>
       </c>
       <c r="F35" s="1">
-        <v>-0.037469858056862995</v>
+        <v>-0.03260980368034272</v>
       </c>
       <c r="G35" s="1">
-        <v>0.94</v>
+        <v>0.95</v>
       </c>
       <c r="H35" s="1">
-        <v>41.86</v>
+        <v>37.62</v>
       </c>
       <c r="I35" s="1">
-        <v>-11.36</v>
+        <v>-14.04</v>
       </c>
       <c r="J35" s="1">
-        <v>0.00631900789595127</v>
+        <v>0.004372133480899242</v>
       </c>
       <c r="K35" s="1" t="b">
         <v>0</v>
@@ -4248,28 +4248,28 @@
         <v>-56</v>
       </c>
       <c r="M35" s="1">
-        <v>-0.0391536991485153</v>
+        <v>-0.03281251526979978</v>
       </c>
       <c r="N35" s="1">
-        <v>-0.03396809543103205</v>
+        <v>-1.8008283480658522</v>
       </c>
       <c r="O35" s="1">
-        <v>45.23809523809524</v>
+        <v>47.61904761904761</v>
       </c>
       <c r="P35" s="1">
         <v>23.996351232323672</v>
       </c>
       <c r="Q35" s="1">
-        <v>49.04761904761905</v>
+        <v>47.142857142857146</v>
       </c>
       <c r="R35" s="1">
-        <v>41.42857142857144</v>
+        <v>42.023809523809526</v>
       </c>
       <c r="S35" s="1" t="s">
         <v>111</v>
       </c>
       <c r="T35" s="1">
-        <v>18.93</v>
+        <v>19.52</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -4289,49 +4289,49 @@
         <v>-1.31</v>
       </c>
       <c r="F36" s="1">
-        <v>0.00013701730383681998</v>
+        <v>-0.024708035868163617</v>
       </c>
       <c r="G36" s="1">
         <v>1.13</v>
       </c>
       <c r="H36" s="1">
-        <v>40.14</v>
+        <v>39.03</v>
       </c>
       <c r="I36" s="1">
-        <v>-10.34</v>
+        <v>-11.19</v>
       </c>
       <c r="J36" s="1">
-        <v>0.01357148485754007</v>
+        <v>0.011962812460977914</v>
       </c>
       <c r="K36" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L36" s="1">
-        <v>-22</v>
+        <v>-21</v>
       </c>
       <c r="M36" s="1">
-        <v>0.003785339669083454</v>
+        <v>-0.024180985735575256</v>
       </c>
       <c r="N36" s="1">
-        <v>4.259935786328843</v>
+        <v>-0.9376753946434004</v>
       </c>
       <c r="O36" s="1">
-        <v>51.19047619047619</v>
+        <v>52.38095238095239</v>
       </c>
       <c r="P36" s="1">
         <v>26.730280409441182</v>
       </c>
       <c r="Q36" s="1">
-        <v>51.42857142857143</v>
+        <v>50.357142857142854</v>
       </c>
       <c r="R36" s="1">
-        <v>43.86904761904762</v>
+        <v>43.98809523809524</v>
       </c>
       <c r="S36" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T36" s="1">
-        <v>16.92</v>
+        <v>17.04</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -4351,49 +4351,49 @@
         <v>-3.25</v>
       </c>
       <c r="F37" s="2">
-        <v>0.25459594388146645</v>
+        <v>0.25051673512777806</v>
       </c>
       <c r="G37" s="2">
         <v>1.27</v>
       </c>
       <c r="H37" s="2">
-        <v>42.71</v>
+        <v>43.18</v>
       </c>
       <c r="I37" s="2">
-        <v>5.62</v>
+        <v>6.02</v>
       </c>
       <c r="J37" s="2">
-        <v>0.016363915997029486</v>
+        <v>0.01624961674252208</v>
       </c>
       <c r="K37" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L37" s="2">
-        <v>-105</v>
+        <v>-107</v>
       </c>
       <c r="M37" s="2">
-        <v>0.2621732287939018</v>
+        <v>0.2516113777108462</v>
       </c>
       <c r="N37" s="2">
-        <v>30.098724698810674</v>
+        <v>26.641560949998738</v>
       </c>
       <c r="O37" s="2">
-        <v>88.09523809523809</v>
+        <v>86.90476190476191</v>
       </c>
       <c r="P37" s="2">
         <v>20.90944133883571</v>
       </c>
       <c r="Q37" s="2">
-        <v>54.04761904761905</v>
+        <v>54.88095238095239</v>
       </c>
       <c r="R37" s="2">
-        <v>55</v>
+        <v>54.76190476190477</v>
       </c>
       <c r="S37" s="2" t="s">
         <v>109</v>
       </c>
       <c r="T37" s="2">
-        <v>25.18</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -4413,49 +4413,49 @@
         <v>3.14</v>
       </c>
       <c r="F38" s="2">
-        <v>0.3342029603102209</v>
+        <v>0.38422048428667477</v>
       </c>
       <c r="G38" s="2">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="H38" s="2">
-        <v>60.02</v>
+        <v>62.57</v>
       </c>
       <c r="I38" s="2">
-        <v>59.34</v>
+        <v>63.94</v>
       </c>
       <c r="J38" s="2">
-        <v>0.012932393209592455</v>
+        <v>0.013717782691271281</v>
       </c>
       <c r="K38" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M38" s="2">
-        <v>0.34009640413100395</v>
+        <v>0.385031330644503</v>
       </c>
       <c r="N38" s="2">
-        <v>37.89104223252089</v>
+        <v>39.983556243364426</v>
       </c>
       <c r="O38" s="2">
-        <v>91.66666666666666</v>
+        <v>94.04761904761905</v>
       </c>
       <c r="P38" s="2">
         <v>17.802507034008837</v>
       </c>
       <c r="Q38" s="2">
-        <v>71.07142857142857</v>
+        <v>72.14285714285714</v>
       </c>
       <c r="R38" s="2">
-        <v>63.63095238095239</v>
+        <v>64.94047619047619</v>
       </c>
       <c r="S38" s="2" t="s">
         <v>99</v>
       </c>
       <c r="T38" s="2">
-        <v>-0.45</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -4475,19 +4475,19 @@
         <v>-1.29</v>
       </c>
       <c r="F39" s="1">
-        <v>0.0338278408960873</v>
+        <v>0.04074342820752774</v>
       </c>
       <c r="G39" s="1">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="H39" s="1">
-        <v>41.19</v>
+        <v>41.43</v>
       </c>
       <c r="I39" s="1">
-        <v>-3.93</v>
+        <v>-3.84</v>
       </c>
       <c r="J39" s="1">
-        <v>-0.0046964101108271745</v>
+        <v>-0.004615158293231361</v>
       </c>
       <c r="K39" s="1" t="b">
         <v>1</v>
@@ -4496,28 +4496,28 @@
         <v>-1</v>
       </c>
       <c r="M39" s="1">
-        <v>0.03719552307939189</v>
+        <v>0.0412704783401161</v>
       </c>
       <c r="N39" s="1">
-        <v>7.600954127359692</v>
+        <v>5.60747101292574</v>
       </c>
       <c r="O39" s="1">
-        <v>59.523809523809526</v>
+        <v>61.904761904761905</v>
       </c>
       <c r="P39" s="1">
         <v>30.28933322215756</v>
       </c>
       <c r="Q39" s="1">
-        <v>45.83333333333333</v>
+        <v>47.85714285714286</v>
       </c>
       <c r="R39" s="1">
-        <v>41.8452380952381</v>
+        <v>43.273809523809526</v>
       </c>
       <c r="S39" s="1" t="s">
         <v>110</v>
       </c>
       <c r="T39" s="1">
-        <v>16.05</v>
+        <v>17.48</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -4537,19 +4537,19 @@
         <v>3.93</v>
       </c>
       <c r="F40" s="1">
-        <v>0.35583345074192746</v>
+        <v>0.22655592528415458</v>
       </c>
       <c r="G40" s="1">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="H40" s="1">
-        <v>65.74</v>
+        <v>60.85</v>
       </c>
       <c r="I40" s="1">
-        <v>7.49</v>
+        <v>3.88</v>
       </c>
       <c r="J40" s="1">
-        <v>0.04219847071029511</v>
+        <v>0.03927426054044417</v>
       </c>
       <c r="K40" s="1" t="b">
         <v>0</v>
@@ -4558,28 +4558,28 @@
         <v>-21</v>
       </c>
       <c r="M40" s="1">
-        <v>0.34376592291841934</v>
+        <v>0.22505585952217233</v>
       </c>
       <c r="N40" s="1">
-        <v>38.25799411126243</v>
+        <v>23.98600913113135</v>
       </c>
       <c r="O40" s="1">
-        <v>92.85714285714286</v>
+        <v>82.14285714285714</v>
       </c>
       <c r="P40" s="1">
         <v>51.940889187924654</v>
       </c>
       <c r="Q40" s="1">
-        <v>56.66666666666666</v>
+        <v>54.88095238095237</v>
       </c>
       <c r="R40" s="1">
-        <v>46.13095238095238</v>
+        <v>43.035714285714285</v>
       </c>
       <c r="S40" s="1" t="s">
         <v>112</v>
       </c>
       <c r="T40" s="1">
-        <v>37.66</v>
+        <v>34.56</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -4599,49 +4599,49 @@
         <v>0.01</v>
       </c>
       <c r="F41" s="3">
-        <v>-0.1710458223895145</v>
+        <v>-0.184636320368181</v>
       </c>
       <c r="G41" s="3">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="H41" s="3">
-        <v>40.93</v>
+        <v>38.33</v>
       </c>
       <c r="I41" s="3">
-        <v>-11.44</v>
+        <v>-13.12</v>
       </c>
       <c r="J41" s="3">
-        <v>-0.008618924068727829</v>
+        <v>-0.014939605641185334</v>
       </c>
       <c r="K41" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M41" s="3">
-        <v>-0.16515237856873144</v>
+        <v>-0.18374438937456994</v>
       </c>
       <c r="N41" s="3">
-        <v>-12.633836037452648</v>
+        <v>-16.894015758542867</v>
       </c>
       <c r="O41" s="3">
-        <v>22.61904761904762</v>
+        <v>21.428571428571427</v>
       </c>
       <c r="P41" s="3">
         <v>30.769232468942608</v>
       </c>
       <c r="Q41" s="3">
-        <v>25.714285714285715</v>
+        <v>22.857142857142854</v>
       </c>
       <c r="R41" s="3">
-        <v>16.011904761904763</v>
+        <v>14.523809523809518</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>105</v>
       </c>
       <c r="T41" s="3">
-        <v>-20.63</v>
+        <v>-22.12</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -4655,55 +4655,55 @@
         <v>51.19047619047619</v>
       </c>
       <c r="D42" s="1">
-        <v>1.2342342342342343</v>
+        <v>1.231231231231231</v>
       </c>
       <c r="E42" s="1">
         <v>4.37</v>
       </c>
       <c r="F42" s="1">
-        <v>-0.11119920037718439</v>
+        <v>-0.11696272762902046</v>
       </c>
       <c r="G42" s="1">
         <v>0.31</v>
       </c>
       <c r="H42" s="1">
-        <v>29.9</v>
+        <v>26.01</v>
       </c>
       <c r="I42" s="1">
-        <v>-8.94</v>
+        <v>-10.11</v>
       </c>
       <c r="J42" s="1">
-        <v>-0.01334438891230663</v>
+        <v>-0.013478457515303063</v>
       </c>
       <c r="K42" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L42" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M42" s="1">
-        <v>-0.1305633729311858</v>
+        <v>-0.11976014756352793</v>
       </c>
       <c r="N42" s="1">
-        <v>-9.174935473698085</v>
+        <v>-10.495591577438663</v>
       </c>
       <c r="O42" s="1">
-        <v>26.190476190476193</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="P42" s="1">
-        <v>15.213803115341037</v>
+        <v>16.35579214434687</v>
       </c>
       <c r="Q42" s="1">
-        <v>35.595238095238095</v>
+        <v>36.07142857142857</v>
       </c>
       <c r="R42" s="1">
-        <v>31.904761904761912</v>
+        <v>32.738095238095234</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>109</v>
       </c>
       <c r="T42" s="1">
-        <v>-3.58</v>
+        <v>-2.75</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -4723,49 +4723,49 @@
         <v>8.86</v>
       </c>
       <c r="F43" s="2">
-        <v>0.22645110931947438</v>
+        <v>0.22561817582402588</v>
       </c>
       <c r="G43" s="2">
         <v>1.34</v>
       </c>
       <c r="H43" s="2">
-        <v>60.98</v>
+        <v>56.12</v>
       </c>
       <c r="I43" s="2">
-        <v>26.84</v>
+        <v>22.61</v>
       </c>
       <c r="J43" s="2">
-        <v>0.017405124119254923</v>
+        <v>0.014746331798322916</v>
       </c>
       <c r="K43" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L43" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M43" s="2">
-        <v>0.23599287550550407</v>
+        <v>0.2269966146323339</v>
       </c>
       <c r="N43" s="2">
-        <v>27.480689369970897</v>
+        <v>24.180084642147513</v>
       </c>
       <c r="O43" s="2">
-        <v>84.52380952380952</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="P43" s="2">
         <v>24.82490242340647</v>
       </c>
       <c r="Q43" s="2">
-        <v>70.59523809523809</v>
+        <v>68.45238095238096</v>
       </c>
       <c r="R43" s="2">
-        <v>59.34523809523809</v>
+        <v>58.51190476190476</v>
       </c>
       <c r="S43" s="2" t="s">
         <v>113</v>
       </c>
       <c r="T43" s="2">
-        <v>6.97</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -4779,25 +4779,25 @@
         <v>41.66666666666667</v>
       </c>
       <c r="D44" s="2">
-        <v>18.986486486486484</v>
+        <v>19.054054054054053</v>
       </c>
       <c r="E44" s="2">
         <v>-0.68</v>
       </c>
       <c r="F44" s="2">
-        <v>0.15213440320259755</v>
+        <v>0.13296058108978287</v>
       </c>
       <c r="G44" s="2">
         <v>2.64</v>
       </c>
       <c r="H44" s="2">
-        <v>43.29</v>
+        <v>41.79</v>
       </c>
       <c r="I44" s="2">
-        <v>0.94</v>
+        <v>-0.47</v>
       </c>
       <c r="J44" s="2">
-        <v>0.009516185097174473</v>
+        <v>0.008373532667441874</v>
       </c>
       <c r="K44" s="2" t="b">
         <v>1</v>
@@ -4806,28 +4806,28 @@
         <v>-8</v>
       </c>
       <c r="M44" s="2">
-        <v>0.19815939304109365</v>
+        <v>0.13960952122397452</v>
       </c>
       <c r="N44" s="2">
-        <v>23.697341123529867</v>
+        <v>15.44137530131158</v>
       </c>
       <c r="O44" s="2">
-        <v>79.76190476190477</v>
+        <v>73.80952380952381</v>
       </c>
       <c r="P44" s="2">
         <v>29.40653991657008</v>
       </c>
       <c r="Q44" s="2">
-        <v>57.85714285714286</v>
+        <v>56.42857142857142</v>
       </c>
       <c r="R44" s="2">
-        <v>54.16666666666668</v>
+        <v>52.5</v>
       </c>
       <c r="S44" s="2" t="s">
         <v>101</v>
       </c>
       <c r="T44" s="2">
-        <v>19.35</v>
+        <v>17.68</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
@@ -4841,37 +4841,37 @@
         <v>82.14285714285714</v>
       </c>
       <c r="D45" s="1">
-        <v>-2.3531777956556716</v>
+        <v>-2.3580048270313756</v>
       </c>
       <c r="E45" s="1">
         <v>1.03</v>
       </c>
       <c r="F45" s="1">
-        <v>0.011395111336318639</v>
+        <v>-0.006913898943788705</v>
       </c>
       <c r="G45" s="1">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="H45" s="1">
-        <v>44.33</v>
+        <v>41.37</v>
       </c>
       <c r="I45" s="1">
-        <v>4.94</v>
+        <v>3.43</v>
       </c>
       <c r="J45" s="1">
-        <v>0.005988594063351231</v>
+        <v>0.0044034813722999225</v>
       </c>
       <c r="K45" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L45" s="1">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M45" s="1">
-        <v>0.024023919523710857</v>
+        <v>-0.005048952320783728</v>
       </c>
       <c r="N45" s="1">
-        <v>6.283793771791587</v>
+        <v>0.975527946835755</v>
       </c>
       <c r="O45" s="1">
         <v>55.952380952380956</v>
@@ -4880,16 +4880,16 @@
         <v>17.57882034058413</v>
       </c>
       <c r="Q45" s="1">
-        <v>47.5</v>
+        <v>46.19047619047619</v>
       </c>
       <c r="R45" s="1">
-        <v>41.488095238095234</v>
+        <v>41.726190476190474</v>
       </c>
       <c r="S45" s="1" t="s">
         <v>107</v>
       </c>
       <c r="T45" s="1">
-        <v>-2.84</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
@@ -4909,19 +4909,19 @@
         <v>4.53</v>
       </c>
       <c r="F46" s="3">
-        <v>-0.23994457657298007</v>
+        <v>-0.25965455072204424</v>
       </c>
       <c r="G46" s="3">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="H46" s="3">
-        <v>35.37</v>
+        <v>34.21</v>
       </c>
       <c r="I46" s="3">
-        <v>-29.28</v>
+        <v>-31.05</v>
       </c>
       <c r="J46" s="3">
-        <v>-0.005392628447964363</v>
+        <v>-0.00821452517149062</v>
       </c>
       <c r="K46" s="3" t="b">
         <v>0</v>
@@ -4930,28 +4930,28 @@
         <v>17</v>
       </c>
       <c r="M46" s="3">
-        <v>-0.21833528256344226</v>
+        <v>-0.2564922499265141</v>
       </c>
       <c r="N46" s="3">
-        <v>-17.95212643692373</v>
+        <v>-24.168801813737286</v>
       </c>
       <c r="O46" s="3">
-        <v>15.476190476190476</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="P46" s="3">
         <v>54.33673655574689</v>
       </c>
       <c r="Q46" s="3">
-        <v>44.76190476190476</v>
+        <v>44.52380952380952</v>
       </c>
       <c r="R46" s="3">
-        <v>28.33333333333333</v>
+        <v>27.976190476190474</v>
       </c>
       <c r="S46" s="3" t="s">
         <v>101</v>
       </c>
       <c r="T46" s="3">
-        <v>7.3</v>
+        <v>6.94</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
@@ -4971,49 +4971,49 @@
         <v>2.59</v>
       </c>
       <c r="F47" s="1">
-        <v>0.1493413552637205</v>
+        <v>0.1123052319507205</v>
       </c>
       <c r="G47" s="1">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="H47" s="1">
-        <v>55.62</v>
+        <v>46.61</v>
       </c>
       <c r="I47" s="1">
-        <v>6.66</v>
+        <v>2.22</v>
       </c>
       <c r="J47" s="1">
-        <v>0.02088932491538467</v>
+        <v>0.019366235203556553</v>
       </c>
       <c r="K47" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L47" s="1">
-        <v>-54</v>
+        <v>-56</v>
       </c>
       <c r="M47" s="1">
-        <v>0.16084760272334453</v>
+        <v>0.11400800930215982</v>
       </c>
       <c r="N47" s="1">
-        <v>19.966162091754942</v>
+        <v>12.88122410913011</v>
       </c>
       <c r="O47" s="1">
-        <v>77.38095238095238</v>
+        <v>69.04761904761905</v>
       </c>
       <c r="P47" s="1">
         <v>33.3731909304046</v>
       </c>
       <c r="Q47" s="1">
-        <v>57.261904761904766</v>
+        <v>53.45238095238095</v>
       </c>
       <c r="R47" s="1">
-        <v>46.785714285714285</v>
+        <v>44.166666666666664</v>
       </c>
       <c r="S47" s="1" t="s">
         <v>107</v>
       </c>
       <c r="T47" s="1">
-        <v>20.93</v>
+        <v>18.31</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
@@ -5033,19 +5033,19 @@
         <v>0.65</v>
       </c>
       <c r="F48" s="2">
-        <v>0.09430081661353241</v>
+        <v>0.12318043425795686</v>
       </c>
       <c r="G48" s="2">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H48" s="2">
-        <v>47.7</v>
+        <v>52.86</v>
       </c>
       <c r="I48" s="2">
-        <v>21.78</v>
+        <v>26.2</v>
       </c>
       <c r="J48" s="2">
-        <v>0.015972105415578995</v>
+        <v>0.013968962881582982</v>
       </c>
       <c r="K48" s="2" t="b">
         <v>0</v>
@@ -5054,28 +5054,28 @@
         <v>242</v>
       </c>
       <c r="M48" s="2">
-        <v>0.11170050789393948</v>
+        <v>0.12565351564933303</v>
       </c>
       <c r="N48" s="2">
-        <v>15.051452608814447</v>
+        <v>14.045774743847439</v>
       </c>
       <c r="O48" s="2">
-        <v>71.42857142857143</v>
+        <v>72.61904761904762</v>
       </c>
       <c r="P48" s="2">
         <v>23.23749735248456</v>
       </c>
       <c r="Q48" s="2">
-        <v>63.214285714285715</v>
+        <v>65</v>
       </c>
       <c r="R48" s="2">
-        <v>53.33333333333334</v>
+        <v>53.80952380952382</v>
       </c>
       <c r="S48" s="2" t="s">
         <v>95</v>
       </c>
       <c r="T48" s="2">
-        <v>4.07</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
@@ -5089,25 +5089,25 @@
         <v>27.380952380952383</v>
       </c>
       <c r="D49" s="2">
-        <v>2010.578947368421</v>
+        <v>2104.736842105263</v>
       </c>
       <c r="E49" s="2">
         <v>-11.05</v>
       </c>
       <c r="F49" s="2">
-        <v>0.06976828110732493</v>
+        <v>0.005968255942283559</v>
       </c>
       <c r="G49" s="2">
         <v>1.06</v>
       </c>
       <c r="H49" s="2">
-        <v>57.77</v>
+        <v>60.08</v>
       </c>
       <c r="I49" s="2">
-        <v>-0.37</v>
+        <v>1.34</v>
       </c>
       <c r="J49" s="2">
-        <v>0.01967291624853963</v>
+        <v>0.019831944438526</v>
       </c>
       <c r="K49" s="2" t="b">
         <v>0</v>
@@ -5116,28 +5116,28 @@
         <v>-7</v>
       </c>
       <c r="M49" s="2">
-        <v>0.07145212219897723</v>
+        <v>0.006211509849632035</v>
       </c>
       <c r="N49" s="2">
-        <v>11.026614039318213</v>
+        <v>2.101574163877322</v>
       </c>
       <c r="O49" s="2">
-        <v>67.85714285714286</v>
+        <v>57.14285714285714</v>
       </c>
       <c r="P49" s="2">
         <v>31.00158698078384</v>
       </c>
       <c r="Q49" s="2">
-        <v>67.97619047619048</v>
+        <v>68.57142857142857</v>
       </c>
       <c r="R49" s="2">
-        <v>54.226190476190474</v>
+        <v>51.13095238095238</v>
       </c>
       <c r="S49" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T49" s="2">
-        <v>23.13</v>
+        <v>20.03</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
@@ -5157,19 +5157,19 @@
         <v>12.9</v>
       </c>
       <c r="F50" s="3">
-        <v>-0.3130166929384501</v>
+        <v>-0.2899883066465494</v>
       </c>
       <c r="G50" s="3">
         <v>3.83</v>
       </c>
       <c r="H50" s="3">
-        <v>52.06</v>
+        <v>49.43</v>
       </c>
       <c r="I50" s="3">
-        <v>3.53</v>
+        <v>0.25</v>
       </c>
       <c r="J50" s="3">
-        <v>-0.009173609071791338</v>
+        <v>-0.006198950548386034</v>
       </c>
       <c r="K50" s="3" t="b">
         <v>0</v>
@@ -5178,22 +5178,22 @@
         <v>69</v>
       </c>
       <c r="M50" s="3">
-        <v>-0.2335955214488501</v>
+        <v>-0.27851483068327965</v>
       </c>
       <c r="N50" s="3">
-        <v>-19.478150325464515</v>
+        <v>-26.371059889413832</v>
       </c>
       <c r="O50" s="3">
-        <v>14.285714285714285</v>
+        <v>10.714285714285714</v>
       </c>
       <c r="P50" s="3">
         <v>41.201484669672254</v>
       </c>
       <c r="Q50" s="3">
-        <v>43.0952380952381</v>
+        <v>43.452380952380956</v>
       </c>
       <c r="R50" s="3">
-        <v>19.94047619047619</v>
+        <v>20.05952380952381</v>
       </c>
       <c r="S50" s="3" t="s">
         <v>106</v>
@@ -5217,19 +5217,19 @@
         <v>14.41</v>
       </c>
       <c r="F51" s="1">
-        <v>0.17963645168770112</v>
+        <v>0.2246923854244884</v>
       </c>
       <c r="G51" s="1">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="H51" s="1">
-        <v>65.43</v>
+        <v>63.24</v>
       </c>
       <c r="I51" s="1">
-        <v>34.96</v>
+        <v>32.27</v>
       </c>
       <c r="J51" s="1">
-        <v>0.05269183044390552</v>
+        <v>0.047903993640471966</v>
       </c>
       <c r="K51" s="1" t="b">
         <v>0</v>
@@ -5238,22 +5238,22 @@
         <v>14</v>
       </c>
       <c r="M51" s="1">
-        <v>0.19928126442364458</v>
+        <v>0.22744926304110447</v>
       </c>
       <c r="N51" s="1">
-        <v>23.80952826178494</v>
+        <v>24.225349483024562</v>
       </c>
       <c r="O51" s="1">
-        <v>80.95238095238095</v>
+        <v>84.52380952380952</v>
       </c>
       <c r="P51" s="1">
         <v>38.38748944617691</v>
       </c>
       <c r="Q51" s="1">
-        <v>56.66666666666667</v>
+        <v>55.5952380952381</v>
       </c>
       <c r="R51" s="1">
-        <v>41.84523809523809</v>
+        <v>42.91666666666666</v>
       </c>
       <c r="S51" s="1" t="s">
         <v>96</v>
@@ -5277,43 +5277,43 @@
         <v>-5.11</v>
       </c>
       <c r="F52" s="3">
-        <v>-0.19207949801295793</v>
+        <v>-0.16803559328215234</v>
       </c>
       <c r="G52" s="3">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="H52" s="3">
-        <v>35.49</v>
+        <v>34.18</v>
       </c>
       <c r="I52" s="3">
-        <v>-33.72</v>
+        <v>-34.64</v>
       </c>
       <c r="J52" s="3">
-        <v>-0.013819046212626454</v>
+        <v>-0.014342051443960092</v>
       </c>
       <c r="K52" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" s="3">
         <v>-106</v>
       </c>
       <c r="M52" s="3">
-        <v>-0.19432461946849433</v>
+        <v>-0.16831938950739223</v>
       </c>
       <c r="N52" s="3">
-        <v>-15.551060127428942</v>
+        <v>-15.3515157718251</v>
       </c>
       <c r="O52" s="3">
-        <v>17.857142857142858</v>
+        <v>23.809523809523807</v>
       </c>
       <c r="P52" s="3">
         <v>41.9219479219836</v>
       </c>
       <c r="Q52" s="3">
-        <v>31.78571428571429</v>
+        <v>32.261904761904766</v>
       </c>
       <c r="R52" s="3">
-        <v>20.714285714285715</v>
+        <v>22.85714285714286</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>113</v>
@@ -5331,55 +5331,55 @@
         <v>60.71428571428571</v>
       </c>
       <c r="D53" s="1">
-        <v>0.7761989342806395</v>
+        <v>0.788632326820604</v>
       </c>
       <c r="E53" s="1">
         <v>-1.38</v>
       </c>
       <c r="F53" s="1">
-        <v>-0.01488236910196998</v>
+        <v>0.025977115851738786</v>
       </c>
       <c r="G53" s="1">
         <v>0.98</v>
       </c>
       <c r="H53" s="1">
-        <v>28.75</v>
+        <v>39.1</v>
       </c>
       <c r="I53" s="1">
-        <v>0.73</v>
+        <v>3.05</v>
       </c>
       <c r="J53" s="1">
-        <v>0.0015174016725078593</v>
+        <v>0.001750937952638683</v>
       </c>
       <c r="K53" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="1">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="M53" s="1">
-        <v>-0.015443649465854081</v>
+        <v>0.02589603121595596</v>
       </c>
       <c r="N53" s="1">
-        <v>2.3370368728350774</v>
+        <v>4.070026300509722</v>
       </c>
       <c r="O53" s="1">
-        <v>48.80952380952381</v>
+        <v>59.523809523809526</v>
       </c>
       <c r="P53" s="1">
         <v>11.84024085938085</v>
       </c>
       <c r="Q53" s="1">
-        <v>45.714285714285715</v>
+        <v>48.69047619047619</v>
       </c>
       <c r="R53" s="1">
-        <v>44.28571428571429</v>
+        <v>47.5</v>
       </c>
       <c r="S53" s="1" t="s">
         <v>114</v>
       </c>
       <c r="T53" s="1">
-        <v>3.86</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
@@ -5399,19 +5399,19 @@
         <v>0.68</v>
       </c>
       <c r="F54" s="1">
-        <v>-0.19409200129650622</v>
+        <v>-0.1781849023649378</v>
       </c>
       <c r="G54" s="1">
         <v>1.58</v>
       </c>
       <c r="H54" s="1">
-        <v>38.96</v>
+        <v>41.53</v>
       </c>
       <c r="I54" s="1">
-        <v>0.11</v>
+        <v>1.04</v>
       </c>
       <c r="J54" s="1">
-        <v>-0.02302966946456977</v>
+        <v>-0.023384481286201516</v>
       </c>
       <c r="K54" s="1" t="b">
         <v>0</v>
@@ -5420,28 +5420,28 @@
         <v>349</v>
       </c>
       <c r="M54" s="1">
-        <v>-0.17781487074386737</v>
+        <v>-0.17583344792723588</v>
       </c>
       <c r="N54" s="1">
-        <v>-13.90008525496624</v>
+        <v>-16.102921613809464</v>
       </c>
       <c r="O54" s="1">
-        <v>20.238095238095237</v>
+        <v>22.61904761904762</v>
       </c>
       <c r="P54" s="1">
         <v>26.83257063748809</v>
       </c>
       <c r="Q54" s="1">
-        <v>45</v>
+        <v>46.30952380952381</v>
       </c>
       <c r="R54" s="1">
-        <v>31.666666666666668</v>
+        <v>32.5</v>
       </c>
       <c r="S54" s="1" t="s">
         <v>95</v>
       </c>
       <c r="T54" s="1">
-        <v>-26.93</v>
+        <v>-26.1</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
@@ -5461,31 +5461,31 @@
         <v>1.71</v>
       </c>
       <c r="F55" s="1">
-        <v>-0.12901404016470144</v>
+        <v>-0.08118514612274264</v>
       </c>
       <c r="G55" s="1">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="H55" s="1">
-        <v>55.91</v>
+        <v>59.93</v>
       </c>
       <c r="I55" s="1">
-        <v>29.06</v>
+        <v>34.96</v>
       </c>
       <c r="J55" s="1">
-        <v>-0.004621200860634374</v>
+        <v>-0.009976997406942507</v>
       </c>
       <c r="K55" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" s="1">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="M55" s="1">
-        <v>-0.05099606958481173</v>
+        <v>-0.06999546638471277</v>
       </c>
       <c r="N55" s="1">
-        <v>-1.218205139060682</v>
+        <v>-5.519123459557149</v>
       </c>
       <c r="O55" s="1">
         <v>44.047619047619044</v>
@@ -5494,16 +5494,16 @@
         <v>52.65288503392759</v>
       </c>
       <c r="Q55" s="1">
-        <v>62.5</v>
+        <v>60.5952380952381</v>
       </c>
       <c r="R55" s="1">
-        <v>39.285714285714285</v>
+        <v>38.214285714285715</v>
       </c>
       <c r="S55" s="1" t="s">
         <v>109</v>
       </c>
       <c r="T55" s="1">
-        <v>-20.71</v>
+        <v>-21.79</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
@@ -5517,25 +5517,25 @@
         <v>55.952380952380956</v>
       </c>
       <c r="D56" s="3">
-        <v>7.147058823529411</v>
+        <v>7.153846153846153</v>
       </c>
       <c r="E56" s="3">
         <v>-1.32</v>
       </c>
       <c r="F56" s="3">
-        <v>-0.28447959561421315</v>
+        <v>-0.26697782392274355</v>
       </c>
       <c r="G56" s="3">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H56" s="3">
-        <v>38.57</v>
+        <v>39.66</v>
       </c>
       <c r="I56" s="3">
-        <v>-9.25</v>
+        <v>-8.7</v>
       </c>
       <c r="J56" s="3">
-        <v>-0.018492553887907257</v>
+        <v>-0.023519023530335328</v>
       </c>
       <c r="K56" s="3" t="b">
         <v>1</v>
@@ -5544,28 +5544,28 @@
         <v>249</v>
       </c>
       <c r="M56" s="3">
-        <v>-0.25501237651029796</v>
+        <v>-0.2626803382262538</v>
       </c>
       <c r="N56" s="3">
-        <v>-21.619835831609308</v>
+        <v>-24.787610643711254</v>
       </c>
       <c r="O56" s="3">
-        <v>13.095238095238097</v>
+        <v>11.904761904761903</v>
       </c>
       <c r="P56" s="3">
         <v>40.717118046641446</v>
       </c>
       <c r="Q56" s="3">
-        <v>43.57142857142857</v>
+        <v>43.69047619047618</v>
       </c>
       <c r="R56" s="3">
-        <v>27.26190476190476</v>
+        <v>26.54761904761905</v>
       </c>
       <c r="S56" s="3" t="s">
         <v>108</v>
       </c>
       <c r="T56" s="3">
-        <v>-21.7</v>
+        <v>-22.42</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
@@ -5585,7 +5585,7 @@
         <v>1.24</v>
       </c>
       <c r="F57" s="1">
-        <v>-0.03951178688229742</v>
+        <v>0.009109164907531307</v>
       </c>
       <c r="G57" s="1">
         <v>1.65</v>
@@ -5594,10 +5594,10 @@
         <v>36.78</v>
       </c>
       <c r="I57" s="1">
-        <v>-20.78</v>
+        <v>-20.62</v>
       </c>
       <c r="J57" s="1">
-        <v>0.00033428373596081193</v>
+        <v>-0.0003338970613827449</v>
       </c>
       <c r="K57" s="1" t="b">
         <v>0</v>
@@ -5606,28 +5606,28 @@
         <v>3</v>
       </c>
       <c r="M57" s="1">
-        <v>-0.02127017505606421</v>
+        <v>0.011744415570473121</v>
       </c>
       <c r="N57" s="1">
-        <v>1.754384313814067</v>
+        <v>2.6548647359614446</v>
       </c>
       <c r="O57" s="1">
-        <v>47.61904761904761</v>
+        <v>58.333333333333336</v>
       </c>
       <c r="P57" s="1">
         <v>37.631577254992756</v>
       </c>
       <c r="Q57" s="1">
-        <v>49.642857142857146</v>
+        <v>49.404761904761905</v>
       </c>
       <c r="R57" s="1">
-        <v>42.55952380952381</v>
+        <v>45.654761904761905</v>
       </c>
       <c r="S57" s="1" t="s">
         <v>101</v>
       </c>
       <c r="T57" s="1">
-        <v>20.61</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
@@ -5647,49 +5647,49 @@
         <v>0.97</v>
       </c>
       <c r="F58" s="3">
-        <v>-0.317920015733788</v>
+        <v>-0.3219048525927221</v>
       </c>
       <c r="G58" s="3">
         <v>1.88</v>
       </c>
       <c r="H58" s="3">
-        <v>37.83</v>
+        <v>38.55</v>
       </c>
       <c r="I58" s="3">
-        <v>3.51</v>
+        <v>3.39</v>
       </c>
       <c r="J58" s="3">
-        <v>-0.0285829849042525</v>
+        <v>-0.02997595485040001</v>
       </c>
       <c r="K58" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L58" s="3">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M58" s="3">
-        <v>-0.29322367972288765</v>
+        <v>-0.3183371286182778</v>
       </c>
       <c r="N58" s="3">
-        <v>-25.440966152868267</v>
+        <v>-30.353289682913648</v>
       </c>
       <c r="O58" s="3">
-        <v>8.333333333333332</v>
+        <v>5.952380952380952</v>
       </c>
       <c r="P58" s="3">
         <v>41.76493344029593</v>
       </c>
       <c r="Q58" s="3">
-        <v>43.6904761904762</v>
+        <v>44.16666666666668</v>
       </c>
       <c r="R58" s="3">
-        <v>24.345238095238095</v>
+        <v>23.63095238095238</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>108</v>
       </c>
       <c r="T58" s="3">
-        <v>-34.86</v>
+        <v>-35.58</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
@@ -5709,19 +5709,19 @@
         <v>-4.45</v>
       </c>
       <c r="F59" s="3">
-        <v>-0.35646321151174687</v>
+        <v>-0.32374488987579514</v>
       </c>
       <c r="G59" s="3">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="H59" s="3">
-        <v>37.31</v>
+        <v>37.47</v>
       </c>
       <c r="I59" s="3">
-        <v>-34.04</v>
+        <v>-34.26</v>
       </c>
       <c r="J59" s="3">
-        <v>-0.034985618157129354</v>
+        <v>-0.03724195679252611</v>
       </c>
       <c r="K59" s="3" t="b">
         <v>0</v>
@@ -5730,10 +5730,10 @@
         <v>21</v>
       </c>
       <c r="M59" s="3">
-        <v>-0.3053866983982939</v>
+        <v>-0.31632564570166666</v>
       </c>
       <c r="N59" s="3">
-        <v>-26.657268020408896</v>
+        <v>-30.152141391252542</v>
       </c>
       <c r="O59" s="3">
         <v>7.142857142857142</v>
@@ -5742,7 +5742,7 @@
         <v>46.90217032437056</v>
       </c>
       <c r="Q59" s="3">
-        <v>24.047619047619047</v>
+        <v>24.4047619047619</v>
       </c>
       <c r="R59" s="3">
         <v>11.54761904761905</v>
@@ -5755,65 +5755,65 @@
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
+      <c r="A60" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="1">
+      <c r="B60" s="2">
         <v>4.35</v>
       </c>
-      <c r="C60" s="1">
+      <c r="C60" s="2">
         <v>54.761904761904766</v>
       </c>
-      <c r="D60" s="1">
-        <v>2.124137931034483</v>
-      </c>
-      <c r="E60" s="1">
+      <c r="D60" s="2">
+        <v>2.1310344827586207</v>
+      </c>
+      <c r="E60" s="2">
         <v>-0.53</v>
       </c>
-      <c r="F60" s="1">
-        <v>0.017158339444140802</v>
-      </c>
-      <c r="G60" s="1">
+      <c r="F60" s="2">
+        <v>0.04971518130638918</v>
+      </c>
+      <c r="G60" s="2">
         <v>1.2</v>
       </c>
-      <c r="H60" s="1">
-        <v>32.67</v>
-      </c>
-      <c r="I60" s="1">
-        <v>7.18</v>
-      </c>
-      <c r="J60" s="1">
-        <v>0.006475190445758139</v>
-      </c>
-      <c r="K60" s="1" t="b">
+      <c r="H60" s="2">
+        <v>36.67</v>
+      </c>
+      <c r="I60" s="2">
+        <v>8.33</v>
+      </c>
+      <c r="J60" s="2">
+        <v>0.004880893733414715</v>
+      </c>
+      <c r="K60" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="L60" s="1">
-        <v>170</v>
-      </c>
-      <c r="M60" s="1">
-        <v>0.022771143082981782</v>
-      </c>
-      <c r="N60" s="1">
-        <v>6.158516127718678</v>
-      </c>
-      <c r="O60" s="1">
-        <v>54.761904761904766</v>
-      </c>
-      <c r="P60" s="1">
+      <c r="L60" s="2">
+        <v>169</v>
+      </c>
+      <c r="M60" s="2">
+        <v>0.05052602766421743</v>
+      </c>
+      <c r="N60" s="2">
+        <v>6.533025945335871</v>
+      </c>
+      <c r="O60" s="2">
+        <v>64.28571428571429</v>
+      </c>
+      <c r="P60" s="2">
         <v>8.239463877564281</v>
       </c>
-      <c r="Q60" s="1">
-        <v>49.88095238095238</v>
-      </c>
-      <c r="R60" s="1">
-        <v>47.91666666666667</v>
-      </c>
-      <c r="S60" s="1" t="s">
+      <c r="Q60" s="2">
+        <v>50.47619047619048</v>
+      </c>
+      <c r="R60" s="2">
+        <v>50.65476190476192</v>
+      </c>
+      <c r="S60" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="T60" s="1">
-        <v>0.72</v>
+      <c r="T60" s="2">
+        <v>3.46</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
@@ -5833,49 +5833,49 @@
         <v>0.11</v>
       </c>
       <c r="F61" s="2">
-        <v>0.08901526304575452</v>
+        <v>0.12227607146783773</v>
       </c>
       <c r="G61" s="2">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="H61" s="2">
-        <v>50.1</v>
+        <v>49.68</v>
       </c>
       <c r="I61" s="2">
-        <v>12.2</v>
+        <v>11.96</v>
       </c>
       <c r="J61" s="2">
-        <v>0.003842324958567833</v>
+        <v>0.0033351444135746124</v>
       </c>
       <c r="K61" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L61" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M61" s="2">
-        <v>0.06684468867233262</v>
+        <v>0.11903268603652473</v>
       </c>
       <c r="N61" s="2">
-        <v>10.565870686653756</v>
+        <v>13.383691782566597</v>
       </c>
       <c r="O61" s="2">
-        <v>66.66666666666666</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="P61" s="2">
         <v>7.56622762341097</v>
       </c>
       <c r="Q61" s="2">
-        <v>55.833333333333336</v>
+        <v>55.83333333333333</v>
       </c>
       <c r="R61" s="2">
-        <v>51.904761904761905</v>
+        <v>53.333333333333336</v>
       </c>
       <c r="S61" s="2" t="s">
         <v>116</v>
       </c>
       <c r="T61" s="2">
-        <v>5.93</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
@@ -5889,55 +5889,55 @@
         <v>98.80952380952381</v>
       </c>
       <c r="D62" s="1">
-        <v>1.5390536563278243</v>
+        <v>1.5592030790129048</v>
       </c>
       <c r="E62" s="1">
         <v>-1.07</v>
       </c>
       <c r="F62" s="1">
-        <v>-0.13255273116418548</v>
+        <v>-0.16729067067498354</v>
       </c>
       <c r="G62" s="1">
         <v>2.25</v>
       </c>
       <c r="H62" s="1">
-        <v>47</v>
+        <v>47.66</v>
       </c>
       <c r="I62" s="1">
-        <v>47.56</v>
+        <v>47.45</v>
       </c>
       <c r="J62" s="1">
-        <v>-0.011404063520089628</v>
+        <v>-0.009834786261477414</v>
       </c>
       <c r="K62" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L62" s="1">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="M62" s="1">
-        <v>-0.0974727084214293</v>
+        <v>-0.16222288093855697</v>
       </c>
       <c r="N62" s="1">
-        <v>-5.865869022722432</v>
+        <v>-14.741864914941566</v>
       </c>
       <c r="O62" s="1">
-        <v>33.33333333333333</v>
+        <v>25</v>
       </c>
       <c r="P62" s="1">
         <v>39.10478556320163</v>
       </c>
       <c r="Q62" s="1">
-        <v>63.0952380952381</v>
+        <v>64.64285714285714</v>
       </c>
       <c r="R62" s="1">
-        <v>40.89285714285714</v>
+        <v>39.047619047619044</v>
       </c>
       <c r="S62" s="1" t="s">
         <v>117</v>
       </c>
       <c r="T62" s="1">
-        <v>-27.22</v>
+        <v>-29.06</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
@@ -5951,55 +5951,55 @@
         <v>97.61904761904762</v>
       </c>
       <c r="D63" s="1">
-        <v>-1.5714285714285714</v>
+        <v>-1.571142284569138</v>
       </c>
       <c r="E63" s="1">
         <v>1.52</v>
       </c>
       <c r="F63" s="1">
-        <v>-0.10943245551206178</v>
+        <v>-0.11320311703726427</v>
       </c>
       <c r="G63" s="1">
         <v>1.02</v>
       </c>
       <c r="H63" s="1">
-        <v>37.54</v>
+        <v>40.31</v>
       </c>
       <c r="I63" s="1">
-        <v>-2.59</v>
+        <v>-1.02</v>
       </c>
       <c r="J63" s="1">
-        <v>-0.017563774443349688</v>
+        <v>-0.02144312061000298</v>
       </c>
       <c r="K63" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L63" s="1">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="M63" s="1">
-        <v>-0.10887117514817768</v>
+        <v>-0.11312203240148144</v>
       </c>
       <c r="N63" s="1">
-        <v>-7.005715695397279</v>
+        <v>-9.83178006123402</v>
       </c>
       <c r="O63" s="1">
-        <v>29.761904761904763</v>
+        <v>30.952380952380953</v>
       </c>
       <c r="P63" s="1">
         <v>25.543467249515373</v>
       </c>
       <c r="Q63" s="1">
-        <v>42.02380952380952</v>
+        <v>42.97619047619048</v>
       </c>
       <c r="R63" s="1">
-        <v>32.97619047619047</v>
+        <v>33.21428571428571</v>
       </c>
       <c r="S63" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T63" s="1">
-        <v>-11.78</v>
+        <v>-11.54</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.25">
@@ -6019,49 +6019,49 @@
         <v>0.39</v>
       </c>
       <c r="F64" s="1">
-        <v>-0.07581948239747988</v>
+        <v>-0.08571379694836431</v>
       </c>
       <c r="G64" s="1">
         <v>0.36</v>
       </c>
       <c r="H64" s="1">
-        <v>39.52</v>
+        <v>37.33</v>
       </c>
       <c r="I64" s="1">
-        <v>-8.18</v>
+        <v>-8.7</v>
       </c>
       <c r="J64" s="1">
-        <v>-0.0023487886477502927</v>
+        <v>-0.0030446808769919544</v>
       </c>
       <c r="K64" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L64" s="1">
-        <v>-99</v>
+        <v>-100</v>
       </c>
       <c r="M64" s="1">
-        <v>-0.09378045404177104</v>
+        <v>-0.08830850529341472</v>
       </c>
       <c r="N64" s="1">
-        <v>-5.496643584756611</v>
+        <v>-7.350427350427351</v>
       </c>
       <c r="O64" s="1">
-        <v>34.523809523809526</v>
+        <v>39.285714285714285</v>
       </c>
       <c r="P64" s="1">
         <v>14.852676969550105</v>
       </c>
       <c r="Q64" s="1">
-        <v>40.476190476190474</v>
+        <v>40</v>
       </c>
       <c r="R64" s="1">
-        <v>35.05952380952382</v>
+        <v>36.60714285714286</v>
       </c>
       <c r="S64" s="1" t="s">
         <v>118</v>
       </c>
       <c r="T64" s="1">
-        <v>9.02</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.25">
@@ -6081,49 +6081,49 @@
         <v>2.09</v>
       </c>
       <c r="F65" s="2">
-        <v>0.14489256596481664</v>
+        <v>0.17438602033740158</v>
       </c>
       <c r="G65" s="2">
         <v>0.87</v>
       </c>
       <c r="H65" s="2">
-        <v>62.91</v>
+        <v>63.99</v>
       </c>
       <c r="I65" s="2">
-        <v>18.95</v>
+        <v>19.35</v>
       </c>
       <c r="J65" s="2">
-        <v>0.008725734380038465</v>
+        <v>0.00810399776588151</v>
       </c>
       <c r="K65" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L65" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M65" s="2">
-        <v>0.14124424359957</v>
+        <v>0.17385897020481322</v>
       </c>
       <c r="N65" s="2">
-        <v>18.0058261793775</v>
+        <v>18.86632019939545</v>
       </c>
       <c r="O65" s="2">
-        <v>76.19047619047619</v>
+        <v>78.57142857142857</v>
       </c>
       <c r="P65" s="2">
         <v>11.000474713303552</v>
       </c>
       <c r="Q65" s="2">
-        <v>67.61904761904762</v>
+        <v>67.38095238095238</v>
       </c>
       <c r="R65" s="2">
-        <v>59.82142857142858</v>
+        <v>60.416666666666664</v>
       </c>
       <c r="S65" s="2" t="s">
         <v>119</v>
       </c>
       <c r="T65" s="2">
-        <v>16.22</v>
+        <v>16.82</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
@@ -6143,49 +6143,49 @@
         <v>1.65</v>
       </c>
       <c r="F66" s="3">
-        <v>-0.37625682427058826</v>
+        <v>-0.30612036596776043</v>
       </c>
       <c r="G66" s="3">
-        <v>5.32</v>
+        <v>5.34</v>
       </c>
       <c r="H66" s="3">
-        <v>49.11</v>
+        <v>48.38</v>
       </c>
       <c r="I66" s="3">
-        <v>48.67</v>
+        <v>46.39</v>
       </c>
       <c r="J66" s="3">
-        <v>-0.023376347664004333</v>
+        <v>-0.021679354986217498</v>
       </c>
       <c r="K66" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L66" s="3">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="M66" s="3">
-        <v>-0.25502026567162295</v>
+        <v>-0.2885250000028874</v>
       </c>
       <c r="N66" s="3">
-        <v>-21.620624747741797</v>
+        <v>-27.37207682137461</v>
       </c>
       <c r="O66" s="3">
-        <v>11.904761904761903</v>
+        <v>9.523809523809524</v>
       </c>
       <c r="P66" s="3">
         <v>56.49293299150161</v>
       </c>
       <c r="Q66" s="3">
-        <v>52.61904761904762</v>
+        <v>53.69047619047619</v>
       </c>
       <c r="R66" s="3">
-        <v>24.226190476190474</v>
+        <v>24.107142857142858</v>
       </c>
       <c r="S66" s="3" t="s">
         <v>101</v>
       </c>
       <c r="T66" s="3">
-        <v>-45.16</v>
+        <v>-45.28</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
@@ -6205,49 +6205,49 @@
         <v>-2.42</v>
       </c>
       <c r="F67" s="1">
-        <v>-0.2044691877308949</v>
+        <v>-0.2617366956570995</v>
       </c>
       <c r="G67" s="1">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="H67" s="1">
-        <v>44.26</v>
+        <v>41.98</v>
       </c>
       <c r="I67" s="1">
-        <v>31.58</v>
+        <v>27.09</v>
       </c>
       <c r="J67" s="1">
-        <v>-0.006571112690586851</v>
+        <v>-0.008935193532327766</v>
       </c>
       <c r="K67" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L67" s="1">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="M67" s="1">
-        <v>-0.17359876771726945</v>
+        <v>-0.2572364983711527</v>
       </c>
       <c r="N67" s="1">
-        <v>-13.478474952306449</v>
+        <v>-24.243226658201145</v>
       </c>
       <c r="O67" s="1">
-        <v>21.428571428571427</v>
+        <v>13.095238095238097</v>
       </c>
       <c r="P67" s="1">
         <v>31.85898471566022</v>
       </c>
       <c r="Q67" s="1">
-        <v>60.47619047619049</v>
+        <v>59.28571428571429</v>
       </c>
       <c r="R67" s="1">
-        <v>36.78571428571429</v>
+        <v>34.40476190476191</v>
       </c>
       <c r="S67" s="1" t="s">
         <v>109</v>
       </c>
       <c r="T67" s="1">
-        <v>-29.25</v>
+        <v>-31.63</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
@@ -6261,55 +6261,55 @@
         <v>85.71428571428571</v>
       </c>
       <c r="D68" s="2">
-        <v>-0.19939393939393935</v>
+        <v>-0.19272727272727272</v>
       </c>
       <c r="E68" s="2">
         <v>-1.75</v>
       </c>
       <c r="F68" s="2">
-        <v>0.18702937424462948</v>
+        <v>0.1538135254630747</v>
       </c>
       <c r="G68" s="2">
         <v>0.99</v>
       </c>
       <c r="H68" s="2">
-        <v>49.63</v>
+        <v>46.03</v>
       </c>
       <c r="I68" s="2">
-        <v>-20.21</v>
+        <v>-21.92</v>
       </c>
       <c r="J68" s="2">
-        <v>0.017030321227002713</v>
+        <v>0.0173490916462733</v>
       </c>
       <c r="K68" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L68" s="2">
-        <v>-252</v>
+        <v>-253</v>
       </c>
       <c r="M68" s="2">
-        <v>0.18674873406268744</v>
+        <v>0.15377298314518328</v>
       </c>
       <c r="N68" s="2">
-        <v>22.556275225689244</v>
+        <v>16.857721493432447</v>
       </c>
       <c r="O68" s="2">
-        <v>78.57142857142857</v>
+        <v>76.19047619047619</v>
       </c>
       <c r="P68" s="2">
         <v>37.5868621181625</v>
       </c>
       <c r="Q68" s="2">
-        <v>56.07142857142856</v>
+        <v>54.88095238095237</v>
       </c>
       <c r="R68" s="2">
-        <v>51.785714285714285</v>
+        <v>50.952380952380956</v>
       </c>
       <c r="S68" s="2" t="s">
         <v>120</v>
       </c>
       <c r="T68" s="2">
-        <v>34.04</v>
+        <v>33.21</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
@@ -6323,25 +6323,25 @@
         <v>57.14285714285714</v>
       </c>
       <c r="D69" s="1">
-        <v>6.048351648351648</v>
+        <v>5.90989010989011</v>
       </c>
       <c r="E69" s="1">
         <v>-0.51</v>
       </c>
       <c r="F69" s="1">
-        <v>0.008791281346479565</v>
+        <v>-0.03535041439732235</v>
       </c>
       <c r="G69" s="1">
         <v>1.26</v>
       </c>
       <c r="H69" s="1">
-        <v>42.87</v>
+        <v>42.04</v>
       </c>
       <c r="I69" s="1">
-        <v>-5.13</v>
+        <v>-5.62</v>
       </c>
       <c r="J69" s="1">
-        <v>-0.0026670443633801297</v>
+        <v>-0.002107307937633244</v>
       </c>
       <c r="K69" s="1" t="b">
         <v>1</v>
@@ -6350,28 +6350,28 @@
         <v>3</v>
       </c>
       <c r="M69" s="1">
-        <v>0.016087926076972847</v>
+        <v>-0.03429631413214562</v>
       </c>
       <c r="N69" s="1">
-        <v>5.490194427117783</v>
+        <v>-1.9492082343004389</v>
       </c>
       <c r="O69" s="1">
-        <v>53.57142857142857</v>
+        <v>46.42857142857143</v>
       </c>
       <c r="P69" s="1">
         <v>16.710870321490763</v>
       </c>
       <c r="Q69" s="1">
-        <v>51.42857142857143</v>
+        <v>51.785714285714285</v>
       </c>
       <c r="R69" s="1">
-        <v>47.261904761904766</v>
+        <v>45.595238095238095</v>
       </c>
       <c r="S69" s="1" t="s">
         <v>101</v>
       </c>
       <c r="T69" s="1">
-        <v>5.55</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
@@ -6391,49 +6391,49 @@
         <v>0.14</v>
       </c>
       <c r="F70" s="2">
-        <v>0.145766467206474</v>
+        <v>0.16490324960665417</v>
       </c>
       <c r="G70" s="2">
         <v>0.33</v>
       </c>
       <c r="H70" s="2">
-        <v>50.57</v>
+        <v>55.1</v>
       </c>
       <c r="I70" s="2">
-        <v>6.73</v>
+        <v>8.24</v>
       </c>
       <c r="J70" s="2">
-        <v>0.013094764996098374</v>
+        <v>0.012756661965465627</v>
       </c>
       <c r="K70" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L70" s="2">
-        <v>-79</v>
+        <v>-80</v>
       </c>
       <c r="M70" s="2">
-        <v>0.1269635750163567</v>
+        <v>0.16218691430792953</v>
       </c>
       <c r="N70" s="2">
-        <v>16.577759321056156</v>
+        <v>17.69911460970707</v>
       </c>
       <c r="O70" s="2">
-        <v>73.80952380952381</v>
+        <v>77.38095238095238</v>
       </c>
       <c r="P70" s="2">
         <v>10.873073633899006</v>
       </c>
       <c r="Q70" s="2">
-        <v>59.523809523809526</v>
+        <v>61.54761904761905</v>
       </c>
       <c r="R70" s="2">
-        <v>56.36904761904761</v>
+        <v>57.55952380952381</v>
       </c>
       <c r="S70" s="2" t="s">
         <v>95</v>
       </c>
       <c r="T70" s="2">
-        <v>8.32</v>
+        <v>9.51</v>
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.25">
@@ -6453,49 +6453,49 @@
         <v>0.12</v>
       </c>
       <c r="F71" s="1">
-        <v>-0.13257627458934082</v>
+        <v>-0.11127216289829135</v>
       </c>
       <c r="G71" s="1">
         <v>1.47</v>
       </c>
       <c r="H71" s="1">
-        <v>51.21</v>
+        <v>53.22</v>
       </c>
       <c r="I71" s="1">
-        <v>-18.13</v>
+        <v>-17.21</v>
       </c>
       <c r="J71" s="1">
-        <v>-0.011852053783059556</v>
+        <v>-0.011945566606133252</v>
       </c>
       <c r="K71" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L71" s="1">
         <v>-42</v>
       </c>
       <c r="M71" s="1">
-        <v>-0.1193861860380645</v>
+        <v>-0.10936667395739497</v>
       </c>
       <c r="N71" s="1">
-        <v>-8.057216784385952</v>
+        <v>-9.456244216825366</v>
       </c>
       <c r="O71" s="1">
-        <v>28.57142857142857</v>
+        <v>32.142857142857146</v>
       </c>
       <c r="P71" s="1">
         <v>31.34692685044607</v>
       </c>
       <c r="Q71" s="1">
-        <v>46.42857142857143</v>
+        <v>47.85714285714286</v>
       </c>
       <c r="R71" s="1">
-        <v>32.44047619047619</v>
+        <v>33.98809523809525</v>
       </c>
       <c r="S71" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T71" s="1">
-        <v>2.99</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.25">
@@ -6515,19 +6515,19 @@
         <v>-0.35</v>
       </c>
       <c r="F72" s="2">
-        <v>0.2716834297070755</v>
+        <v>0.3396255610793315</v>
       </c>
       <c r="G72" s="2">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="H72" s="2">
-        <v>57.18</v>
+        <v>63.84</v>
       </c>
       <c r="I72" s="2">
-        <v>14.48</v>
+        <v>18.34</v>
       </c>
       <c r="J72" s="2">
-        <v>0.016741609992840023</v>
+        <v>0.017869700383916123</v>
       </c>
       <c r="K72" s="2" t="b">
         <v>0</v>
@@ -6536,28 +6536,28 @@
         <v>49</v>
       </c>
       <c r="M72" s="2">
-        <v>0.2685963877057129</v>
+        <v>0.33913905326463456</v>
       </c>
       <c r="N72" s="2">
-        <v>30.741040589991776</v>
+        <v>35.39432850537759</v>
       </c>
       <c r="O72" s="2">
-        <v>89.28571428571429</v>
+        <v>92.85714285714286</v>
       </c>
       <c r="P72" s="2">
         <v>16.66857152537527</v>
       </c>
       <c r="Q72" s="2">
-        <v>64.76190476190476</v>
+        <v>66.07142857142857</v>
       </c>
       <c r="R72" s="2">
-        <v>60.00000000000001</v>
+        <v>61.1904761904762</v>
       </c>
       <c r="S72" s="2" t="s">
         <v>105</v>
       </c>
       <c r="T72" s="2">
-        <v>20.12</v>
+        <v>21.31</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.25">
@@ -6571,25 +6571,25 @@
         <v>44.047619047619044</v>
       </c>
       <c r="D73" s="1">
-        <v>11.171428571428569</v>
+        <v>11.228571428571428</v>
       </c>
       <c r="E73" s="1">
         <v>0.45</v>
       </c>
       <c r="F73" s="1">
-        <v>-0.21672373297195272</v>
+        <v>-0.21388220785878986</v>
       </c>
       <c r="G73" s="1">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="H73" s="1">
-        <v>35.29</v>
+        <v>33.22</v>
       </c>
       <c r="I73" s="1">
-        <v>-27.22</v>
+        <v>-28.16</v>
       </c>
       <c r="J73" s="1">
-        <v>-0.011810229769209929</v>
+        <v>-0.013981966974583135</v>
       </c>
       <c r="K73" s="1" t="b">
         <v>0</v>
@@ -6598,90 +6598,90 @@
         <v>-165</v>
       </c>
       <c r="M73" s="1">
-        <v>-0.21419797133447427</v>
+        <v>-0.21347678467987574</v>
       </c>
       <c r="N73" s="1">
-        <v>-17.538395314026932</v>
+        <v>-19.867255289073448</v>
       </c>
       <c r="O73" s="1">
-        <v>16.666666666666664</v>
+        <v>20.238095238095237</v>
       </c>
       <c r="P73" s="1">
-        <v>22.69368849988335</v>
+        <v>23.53809998436916</v>
       </c>
       <c r="Q73" s="1">
-        <v>41.309523809523796</v>
+        <v>41.07142857142856</v>
       </c>
       <c r="R73" s="1">
-        <v>31.964285714285715</v>
+        <v>32.79761904761905</v>
       </c>
       <c r="S73" s="1" t="s">
         <v>121</v>
       </c>
       <c r="T73" s="1">
-        <v>-0.05</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A74" s="3" t="s">
+      <c r="A74" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B74" s="3">
+      <c r="B74" s="1">
         <v>0.42</v>
       </c>
-      <c r="C74" s="3">
+      <c r="C74" s="1">
         <v>34.523809523809526</v>
       </c>
-      <c r="D74" s="3">
+      <c r="D74" s="1">
         <v>97.42857142857143</v>
       </c>
-      <c r="E74" s="3">
+      <c r="E74" s="1">
         <v>-3.73</v>
       </c>
-      <c r="F74" s="3">
-        <v>-0.281049343590817</v>
-      </c>
-      <c r="G74" s="3">
+      <c r="F74" s="1">
+        <v>-0.2458692580788271</v>
+      </c>
+      <c r="G74" s="1">
         <v>1.25</v>
       </c>
-      <c r="H74" s="3">
-        <v>38.01</v>
-      </c>
-      <c r="I74" s="3">
-        <v>-5.59</v>
-      </c>
-      <c r="J74" s="3">
-        <v>-0.020583768933837104</v>
-      </c>
-      <c r="K74" s="3" t="b">
+      <c r="H74" s="1">
+        <v>37.34</v>
+      </c>
+      <c r="I74" s="1">
+        <v>-6.2</v>
+      </c>
+      <c r="J74" s="1">
+        <v>-0.021065123362163558</v>
+      </c>
+      <c r="K74" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L74" s="3">
+      <c r="L74" s="1">
         <v>32</v>
       </c>
-      <c r="M74" s="3">
-        <v>-0.2740333390422658</v>
-      </c>
-      <c r="N74" s="3">
-        <v>-23.52193208480608</v>
-      </c>
-      <c r="O74" s="3">
-        <v>9.523809523809524</v>
-      </c>
-      <c r="P74" s="3">
-        <v>28.20053515048475</v>
-      </c>
-      <c r="Q74" s="3">
-        <v>44.76190476190476</v>
-      </c>
-      <c r="R74" s="3">
-        <v>29.226190476190474</v>
-      </c>
-      <c r="S74" s="3" t="s">
+      <c r="M74" s="1">
+        <v>-0.2448557001315418</v>
+      </c>
+      <c r="N74" s="1">
+        <v>-23.00514683424005</v>
+      </c>
+      <c r="O74" s="1">
+        <v>17.857142857142858</v>
+      </c>
+      <c r="P74" s="1">
+        <v>28.58847656283351</v>
+      </c>
+      <c r="Q74" s="1">
+        <v>45.238095238095234</v>
+      </c>
+      <c r="R74" s="1">
+        <v>32.08333333333333</v>
+      </c>
+      <c r="S74" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="T74" s="3">
-        <v>-29.37</v>
+      <c r="T74" s="1">
+        <v>-26.51</v>
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
@@ -6701,19 +6701,19 @@
         <v>-0.07</v>
       </c>
       <c r="F75" s="3">
-        <v>-0.3855401168163636</v>
+        <v>-0.32767054861165523</v>
       </c>
       <c r="G75" s="3">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="H75" s="3">
-        <v>41.59</v>
+        <v>41</v>
       </c>
       <c r="I75" s="3">
-        <v>-31.93</v>
+        <v>-32.23</v>
       </c>
       <c r="J75" s="3">
-        <v>-0.023093207756405974</v>
+        <v>-0.024464045607845736</v>
       </c>
       <c r="K75" s="3" t="b">
         <v>0</v>
@@ -6722,28 +6722,28 @@
         <v>10</v>
       </c>
       <c r="M75" s="3">
-        <v>-0.32239607587940244</v>
+        <v>-0.318507984768196</v>
       </c>
       <c r="N75" s="3">
-        <v>-28.358205768519756</v>
+        <v>-30.370375297905472</v>
       </c>
       <c r="O75" s="3">
-        <v>5.952380952380952</v>
+        <v>4.761904761904762</v>
       </c>
       <c r="P75" s="3">
         <v>51.49813033405746</v>
       </c>
       <c r="Q75" s="3">
-        <v>41.42857142857142</v>
+        <v>41.07142857142857</v>
       </c>
       <c r="R75" s="3">
-        <v>23.273809523809526</v>
+        <v>22.916666666666664</v>
       </c>
       <c r="S75" s="3" t="s">
         <v>107</v>
       </c>
       <c r="T75" s="3">
-        <v>-2.46</v>
+        <v>-2.82</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
@@ -6763,19 +6763,19 @@
         <v>12.84</v>
       </c>
       <c r="F76" s="3">
-        <v>-0.09524217209719844</v>
+        <v>-0.09932836975139925</v>
       </c>
       <c r="G76" s="3">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="H76" s="3">
-        <v>30.93</v>
+        <v>30.36</v>
       </c>
       <c r="I76" s="3">
-        <v>40.63</v>
+        <v>37.09</v>
       </c>
       <c r="J76" s="3">
-        <v>-0.01917734748256924</v>
+        <v>-0.0245718939217082</v>
       </c>
       <c r="K76" s="3" t="b">
         <v>0</v>
@@ -6784,28 +6784,28 @@
         <v>42</v>
       </c>
       <c r="M76" s="3">
-        <v>-0.09832921409856099</v>
+        <v>-0.09973379293031337</v>
       </c>
       <c r="N76" s="3">
-        <v>-5.951519590435606</v>
+        <v>-8.49295611411721</v>
       </c>
       <c r="O76" s="3">
-        <v>32.142857142857146</v>
+        <v>34.523809523809526</v>
       </c>
       <c r="P76" s="3">
-        <v>28.293521533287937</v>
+        <v>29.799918858582526</v>
       </c>
       <c r="Q76" s="3">
-        <v>29.16666666666667</v>
+        <v>27.73809523809524</v>
       </c>
       <c r="R76" s="3">
-        <v>19.04761904761905</v>
+        <v>18.80952380952381</v>
       </c>
       <c r="S76" s="3" t="s">
         <v>123</v>
       </c>
       <c r="T76" s="3">
-        <v>-54.67</v>
+        <v>-54.91</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
@@ -6825,19 +6825,19 @@
         <v>-9.21</v>
       </c>
       <c r="F77" s="2">
-        <v>0.5122086541982861</v>
+        <v>0.5985399365044687</v>
       </c>
       <c r="G77" s="2">
         <v>0.91</v>
       </c>
       <c r="H77" s="2">
-        <v>69.74</v>
+        <v>70.44</v>
       </c>
       <c r="I77" s="2">
-        <v>37.63</v>
+        <v>37.73</v>
       </c>
       <c r="J77" s="2">
-        <v>0.045132353905019885</v>
+        <v>0.04313458390643316</v>
       </c>
       <c r="K77" s="2" t="b">
         <v>1</v>
@@ -6846,28 +6846,28 @@
         <v>-5</v>
       </c>
       <c r="M77" s="2">
-        <v>0.5096828925608077</v>
+        <v>0.598175055643446</v>
       </c>
       <c r="N77" s="2">
-        <v>54.84969107550126</v>
+        <v>61.29792874325874</v>
       </c>
       <c r="O77" s="2">
-        <v>97.61904761904762</v>
+        <v>98.80952380952381</v>
       </c>
       <c r="P77" s="2">
         <v>18.71809072120826</v>
       </c>
       <c r="Q77" s="2">
-        <v>68.57142857142857</v>
+        <v>68.21428571428572</v>
       </c>
       <c r="R77" s="2">
-        <v>61.07142857142858</v>
+        <v>61.42857142857142</v>
       </c>
       <c r="S77" s="2" t="s">
         <v>108</v>
       </c>
       <c r="T77" s="2">
-        <v>12.47</v>
+        <v>12.83</v>
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
@@ -6887,49 +6887,49 @@
         <v>-3.54</v>
       </c>
       <c r="F78" s="2">
-        <v>0.19783090164987194</v>
+        <v>0.27617531896803516</v>
       </c>
       <c r="G78" s="2">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="H78" s="2">
-        <v>63.04</v>
+        <v>69.8</v>
       </c>
       <c r="I78" s="2">
-        <v>31.25</v>
+        <v>35.1</v>
       </c>
       <c r="J78" s="2">
-        <v>0.007629812933399693</v>
+        <v>0.007659308923559309</v>
       </c>
       <c r="K78" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="2">
         <v>-2</v>
       </c>
       <c r="M78" s="2">
-        <v>0.2009179436512345</v>
+        <v>0.2765807421469493</v>
       </c>
       <c r="N78" s="2">
-        <v>23.973196184543944</v>
+        <v>29.138497393609047</v>
       </c>
       <c r="O78" s="2">
-        <v>82.14285714285714</v>
+        <v>89.28571428571429</v>
       </c>
       <c r="P78" s="2">
         <v>16.006637557486414</v>
       </c>
       <c r="Q78" s="2">
-        <v>59.047619047619044</v>
+        <v>59.76190476190476</v>
       </c>
       <c r="R78" s="2">
-        <v>52.73809523809524</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="S78" s="2" t="s">
         <v>106</v>
       </c>
       <c r="T78" s="2">
-        <v>4.57</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.25">
@@ -6949,19 +6949,19 @@
         <v>0.32</v>
       </c>
       <c r="F79" s="2">
-        <v>0.2240634416854555</v>
+        <v>0.2079016452541409</v>
       </c>
       <c r="G79" s="2">
         <v>0.82</v>
       </c>
       <c r="H79" s="2">
-        <v>50.59</v>
+        <v>45.88</v>
       </c>
       <c r="I79" s="2">
-        <v>10.9</v>
+        <v>9.56</v>
       </c>
       <c r="J79" s="2">
-        <v>0.015564912992595579</v>
+        <v>0.013365622745193617</v>
       </c>
       <c r="K79" s="2" t="b">
         <v>0</v>
@@ -6970,28 +6970,28 @@
         <v>6</v>
       </c>
       <c r="M79" s="2">
-        <v>0.2190119184104986</v>
+        <v>0.20717188353209548</v>
       </c>
       <c r="N79" s="2">
-        <v>25.782593660470347</v>
+        <v>22.197611532123666</v>
       </c>
       <c r="O79" s="2">
-        <v>83.33333333333334</v>
+        <v>80.95238095238095</v>
       </c>
       <c r="P79" s="2">
         <v>11.616065285425229</v>
       </c>
       <c r="Q79" s="2">
-        <v>56.54761904761905</v>
+        <v>54.523809523809526</v>
       </c>
       <c r="R79" s="2">
-        <v>55.35714285714287</v>
+        <v>54.523809523809526</v>
       </c>
       <c r="S79" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T79" s="2">
-        <v>15.48</v>
+        <v>14.65</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.25">
@@ -7005,25 +7005,25 @@
         <v>78.57142857142857</v>
       </c>
       <c r="D80" s="2">
-        <v>0.16652360515021455</v>
+        <v>0.17339055793991412</v>
       </c>
       <c r="E80" s="2">
         <v>0.86</v>
       </c>
       <c r="F80" s="2">
-        <v>0.13197724656539647</v>
+        <v>0.14613415540886288</v>
       </c>
       <c r="G80" s="2">
         <v>0.76</v>
       </c>
       <c r="H80" s="2">
-        <v>54.77</v>
+        <v>56.55</v>
       </c>
       <c r="I80" s="2">
-        <v>11.71</v>
+        <v>12.12</v>
       </c>
       <c r="J80" s="2">
-        <v>0.006321162644489269</v>
+        <v>0.0055381350409172215</v>
       </c>
       <c r="K80" s="2" t="b">
         <v>0</v>
@@ -7032,28 +7032,28 @@
         <v>158</v>
       </c>
       <c r="M80" s="2">
-        <v>0.1252418821987873</v>
+        <v>0.14516113977946898</v>
       </c>
       <c r="N80" s="2">
-        <v>16.405590039299227</v>
+        <v>15.996537156861027</v>
       </c>
       <c r="O80" s="2">
-        <v>72.61904761904762</v>
+        <v>75</v>
       </c>
       <c r="P80" s="2">
         <v>6.707278396222185</v>
       </c>
       <c r="Q80" s="2">
-        <v>59.76190476190476</v>
+        <v>60.59523809523809</v>
       </c>
       <c r="R80" s="2">
-        <v>55.59523809523809</v>
+        <v>56.42857142857142</v>
       </c>
       <c r="S80" s="2" t="s">
         <v>109</v>
       </c>
       <c r="T80" s="2">
-        <v>5.17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.25">
@@ -7067,55 +7067,55 @@
         <v>95.23809523809523</v>
       </c>
       <c r="D81" s="2">
-        <v>-0.9297343616109682</v>
+        <v>-0.9305912596401028</v>
       </c>
       <c r="E81" s="2">
         <v>-1.2</v>
       </c>
       <c r="F81" s="2">
-        <v>0.052605277861602316</v>
+        <v>0.08875571734637322</v>
       </c>
       <c r="G81" s="2">
         <v>1.01</v>
       </c>
       <c r="H81" s="2">
-        <v>42.31</v>
+        <v>48.12</v>
       </c>
       <c r="I81" s="2">
-        <v>8.92</v>
+        <v>10.26</v>
       </c>
       <c r="J81" s="2">
-        <v>0.006508752891852481</v>
+        <v>0.005946364182234916</v>
       </c>
       <c r="K81" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" s="2">
         <v>111</v>
       </c>
       <c r="M81" s="2">
-        <v>0.05288591804354437</v>
+        <v>0.08879625966426463</v>
       </c>
       <c r="N81" s="2">
-        <v>9.169993623774937</v>
+        <v>10.36004914534059</v>
       </c>
       <c r="O81" s="2">
-        <v>64.28571428571429</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="P81" s="2">
         <v>6.716293473999743</v>
       </c>
       <c r="Q81" s="2">
-        <v>54.76190476190476</v>
+        <v>56.9047619047619</v>
       </c>
       <c r="R81" s="2">
-        <v>52.32142857142857</v>
+        <v>53.03571428571428</v>
       </c>
       <c r="S81" s="2" t="s">
         <v>115</v>
       </c>
       <c r="T81" s="2">
-        <v>7.02</v>
+        <v>7.73</v>
       </c>
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.25">
@@ -7135,19 +7135,19 @@
         <v>0.23</v>
       </c>
       <c r="F82" s="2">
-        <v>0.10331513906437166</v>
+        <v>0.10275826738458416</v>
       </c>
       <c r="G82" s="2">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H82" s="2">
-        <v>60.79</v>
+        <v>61.05</v>
       </c>
       <c r="I82" s="2">
-        <v>15.89</v>
+        <v>15.87</v>
       </c>
       <c r="J82" s="2">
-        <v>0.01050859977659108</v>
+        <v>0.009615572553266824</v>
       </c>
       <c r="K82" s="2" t="b">
         <v>1</v>
@@ -7156,13 +7156,13 @@
         <v>91</v>
       </c>
       <c r="M82" s="2">
-        <v>0.105279620337966</v>
+        <v>0.10300152129193263</v>
       </c>
       <c r="N82" s="2">
-        <v>14.409363853217085</v>
+        <v>11.780575308107379</v>
       </c>
       <c r="O82" s="2">
-        <v>70.23809523809523</v>
+        <v>67.85714285714286</v>
       </c>
       <c r="P82" s="2">
         <v>12.706223591210087</v>
@@ -7171,13 +7171,13 @@
         <v>61.54761904761905</v>
       </c>
       <c r="R82" s="2">
-        <v>52.738095238095234</v>
+        <v>52.14285714285714</v>
       </c>
       <c r="S82" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T82" s="2">
-        <v>0.6</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.25">
@@ -7191,37 +7191,37 @@
         <v>92.85714285714286</v>
       </c>
       <c r="D83" s="1">
-        <v>-2.3370165745856353</v>
+        <v>-2.3420391762933197</v>
       </c>
       <c r="E83" s="1">
         <v>2.31</v>
       </c>
       <c r="F83" s="1">
-        <v>-0.07890721604839149</v>
+        <v>-0.08552630423763508</v>
       </c>
       <c r="G83" s="1">
         <v>1.19</v>
       </c>
       <c r="H83" s="1">
-        <v>51.37</v>
+        <v>51.07</v>
       </c>
       <c r="I83" s="1">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="J83" s="1">
-        <v>-0.004505233144730778</v>
+        <v>-0.005899393486030319</v>
       </c>
       <c r="K83" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L83" s="1">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M83" s="1">
-        <v>-0.07357505259149255</v>
+        <v>-0.08475600019769824</v>
       </c>
       <c r="N83" s="1">
-        <v>-3.476103439728764</v>
+        <v>-6.995176840855699</v>
       </c>
       <c r="O83" s="1">
         <v>40.476190476190474</v>
@@ -7230,16 +7230,16 @@
         <v>20.22353911360907</v>
       </c>
       <c r="Q83" s="1">
-        <v>49.642857142857146</v>
+        <v>48.80952380952382</v>
       </c>
       <c r="R83" s="1">
-        <v>37.67857142857143</v>
+        <v>37.440476190476204</v>
       </c>
       <c r="S83" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T83" s="1">
-        <v>-9.09</v>
+        <v>-9.33</v>
       </c>
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.25">
@@ -7253,25 +7253,25 @@
         <v>51.19047619047619</v>
       </c>
       <c r="D84" s="1">
-        <v>1.7717717717717718</v>
+        <v>1.768768768768769</v>
       </c>
       <c r="E84" s="1">
         <v>0.25</v>
       </c>
       <c r="F84" s="1">
-        <v>-0.12941707354157667</v>
+        <v>-0.09873019265286587</v>
       </c>
       <c r="G84" s="1">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="H84" s="1">
-        <v>44.81</v>
+        <v>46.94</v>
       </c>
       <c r="I84" s="1">
-        <v>14.33</v>
+        <v>15.05</v>
       </c>
       <c r="J84" s="1">
-        <v>-0.005320117320406684</v>
+        <v>-0.005203554523688541</v>
       </c>
       <c r="K84" s="1" t="b">
         <v>0</v>
@@ -7280,28 +7280,28 @@
         <v>376</v>
       </c>
       <c r="M84" s="1">
-        <v>-0.12997835390546075</v>
+        <v>-0.0988518196065401</v>
       </c>
       <c r="N84" s="1">
-        <v>-9.116433571125583</v>
+        <v>-8.404758781739888</v>
       </c>
       <c r="O84" s="1">
-        <v>27.380952380952383</v>
+        <v>36.904761904761905</v>
       </c>
       <c r="P84" s="1">
         <v>17.353844275841347</v>
       </c>
       <c r="Q84" s="1">
-        <v>49.28571428571428</v>
+        <v>50.95238095238095</v>
       </c>
       <c r="R84" s="1">
-        <v>33.988095238095234</v>
+        <v>37.67857142857142</v>
       </c>
       <c r="S84" s="1" t="s">
         <v>132</v>
       </c>
       <c r="T84" s="1">
-        <v>-22.66</v>
+        <v>-18.97</v>
       </c>
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.25">
@@ -7321,49 +7321,49 @@
         <v>0.61</v>
       </c>
       <c r="F85" s="1">
-        <v>0.007986959800442284</v>
+        <v>0.04775813285066943</v>
       </c>
       <c r="G85" s="1">
         <v>0.95</v>
       </c>
       <c r="H85" s="1">
-        <v>36.65</v>
+        <v>46.97</v>
       </c>
       <c r="I85" s="1">
-        <v>8.75</v>
+        <v>10.69</v>
       </c>
       <c r="J85" s="1">
-        <v>0.0037754325789410813</v>
+        <v>0.00249809106312259</v>
       </c>
       <c r="K85" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L85" s="1">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="M85" s="1">
-        <v>0.006583758890732039</v>
+        <v>0.04755542126121237</v>
       </c>
       <c r="N85" s="1">
-        <v>4.5397777084936894</v>
+        <v>6.2359653050353545</v>
       </c>
       <c r="O85" s="1">
-        <v>52.38095238095239</v>
+        <v>63.095238095238095</v>
       </c>
       <c r="P85" s="1">
-        <v>8.441182677506358</v>
+        <v>8.573177934912337</v>
       </c>
       <c r="Q85" s="1">
-        <v>49.523809523809526</v>
+        <v>53.69047619047619</v>
       </c>
       <c r="R85" s="1">
-        <v>46.36904761904763</v>
+        <v>49.583333333333336</v>
       </c>
       <c r="S85" s="1" t="s">
         <v>105</v>
       </c>
       <c r="T85" s="1">
-        <v>-0.4</v>
+        <v>2.82</v>
       </c>
     </row>
   </sheetData>
@@ -7390,7 +7390,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>46.07142857142856</v>
+        <v>49.404761904761905</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -7398,7 +7398,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>43.214285714285715</v>
+        <v>43.095238095238095</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7406,7 +7406,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>54.76190476190476</v>
+        <v>54.166666666666664</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -7414,7 +7414,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>32.797619047619044</v>
+        <v>33.511904761904766</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -7422,7 +7422,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>36.36904761904762</v>
+        <v>36.25</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7430,7 +7430,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>52.5</v>
+        <v>53.92857142857143</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -7438,7 +7438,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>38.51190476190476</v>
+        <v>39.464285714285715</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -7446,7 +7446,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>60.05952380952382</v>
+        <v>59.345238095238095</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -7454,7 +7454,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>47.857142857142854</v>
+        <v>47.738095238095234</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -7462,7 +7462,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>58.45238095238095</v>
+        <v>58.80952380952381</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -7470,7 +7470,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>62.67857142857142</v>
+        <v>62.797619047619044</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -7486,7 +7486,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>60.892857142857146</v>
+        <v>60.654761904761905</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -7494,7 +7494,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>19.107142857142858</v>
+        <v>20.535714285714285</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -7502,7 +7502,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>22.678571428571423</v>
+        <v>14.821428571428566</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -7510,7 +7510,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>32.67857142857143</v>
+        <v>29.821428571428577</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -7518,7 +7518,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>24.642857142857146</v>
+        <v>23.333333333333343</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -7526,7 +7526,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>52.4404761904762</v>
+        <v>53.27380952380953</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -7534,7 +7534,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>55.11904761904761</v>
+        <v>56.54761904761905</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -7542,7 +7542,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>20.714285714285715</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -7550,7 +7550,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>38.69047619047619</v>
+        <v>35.476190476190474</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -7558,7 +7558,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>54.22619047619048</v>
+        <v>53.03571428571429</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -7566,7 +7566,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>32.142857142857146</v>
+        <v>27.85714285714286</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -7574,7 +7574,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>6.369047619047619</v>
+        <v>5.178571428571429</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -7582,7 +7582,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>-3.2738095238095246</v>
+        <v>-2.7976190476190483</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -7590,7 +7590,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>0.4166666666666643</v>
+        <v>0.17857142857142705</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -7598,7 +7598,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>39.88095238095238</v>
+        <v>35.89285714285714</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -7606,7 +7606,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>48.392857142857146</v>
+        <v>46.8452380952381</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -7614,7 +7614,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>48.392857142857146</v>
+        <v>47.55952380952381</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -7622,7 +7622,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>39.3452380952381</v>
+        <v>39.46428571428573</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -7630,7 +7630,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>28.452380952380956</v>
+        <v>30.05952380952381</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -7638,7 +7638,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>60.476190476190474</v>
+        <v>60.238095238095234</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -7646,7 +7646,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>37.738095238095234</v>
+        <v>38.09523809523809</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -7654,7 +7654,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>41.42857142857144</v>
+        <v>42.023809523809526</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -7662,7 +7662,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>43.86904761904762</v>
+        <v>43.98809523809524</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -7670,7 +7670,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>55</v>
+        <v>54.76190476190477</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -7678,7 +7678,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>63.63095238095239</v>
+        <v>64.94047619047619</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -7686,7 +7686,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>41.8452380952381</v>
+        <v>43.273809523809526</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -7694,7 +7694,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>46.13095238095238</v>
+        <v>43.035714285714285</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -7702,7 +7702,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>16.011904761904763</v>
+        <v>14.523809523809518</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -7710,7 +7710,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>31.904761904761912</v>
+        <v>32.738095238095234</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -7718,7 +7718,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>59.34523809523809</v>
+        <v>58.51190476190476</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -7726,7 +7726,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>54.16666666666668</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -7734,7 +7734,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>41.488095238095234</v>
+        <v>41.726190476190474</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -7742,7 +7742,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>28.33333333333333</v>
+        <v>27.976190476190474</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -7750,7 +7750,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>46.785714285714285</v>
+        <v>44.166666666666664</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -7758,7 +7758,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>53.33333333333334</v>
+        <v>53.80952380952382</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -7766,7 +7766,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>54.226190476190474</v>
+        <v>51.13095238095238</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -7774,7 +7774,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>19.94047619047619</v>
+        <v>20.05952380952381</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -7782,7 +7782,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>41.84523809523809</v>
+        <v>42.91666666666666</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -7790,7 +7790,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>20.714285714285715</v>
+        <v>22.85714285714286</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -7798,7 +7798,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>44.28571428571429</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -7806,7 +7806,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>31.666666666666668</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -7814,7 +7814,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>39.285714285714285</v>
+        <v>38.214285714285715</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -7822,7 +7822,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>27.26190476190476</v>
+        <v>26.54761904761905</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -7830,7 +7830,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>42.55952380952381</v>
+        <v>45.654761904761905</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -7838,7 +7838,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>24.345238095238095</v>
+        <v>23.63095238095238</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -7854,7 +7854,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>47.91666666666667</v>
+        <v>50.65476190476192</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -7862,7 +7862,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>51.904761904761905</v>
+        <v>53.333333333333336</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -7870,7 +7870,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>40.89285714285714</v>
+        <v>39.047619047619044</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -7878,7 +7878,7 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>32.97619047619047</v>
+        <v>33.21428571428571</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -7886,7 +7886,7 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>35.05952380952382</v>
+        <v>36.60714285714286</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -7894,7 +7894,7 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>59.82142857142858</v>
+        <v>60.416666666666664</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -7902,7 +7902,7 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>24.226190476190474</v>
+        <v>24.107142857142858</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -7910,7 +7910,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>36.78571428571429</v>
+        <v>34.40476190476191</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -7918,7 +7918,7 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>51.785714285714285</v>
+        <v>50.952380952380956</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -7926,7 +7926,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>47.261904761904766</v>
+        <v>45.595238095238095</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -7934,7 +7934,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>56.36904761904761</v>
+        <v>57.55952380952381</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -7942,7 +7942,7 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>32.44047619047619</v>
+        <v>33.98809523809525</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -7950,7 +7950,7 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>60.00000000000001</v>
+        <v>61.1904761904762</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -7958,7 +7958,7 @@
         <v>72</v>
       </c>
       <c r="B73">
-        <v>31.964285714285715</v>
+        <v>32.79761904761905</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -7966,7 +7966,7 @@
         <v>73</v>
       </c>
       <c r="B74">
-        <v>29.226190476190474</v>
+        <v>32.08333333333333</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -7974,7 +7974,7 @@
         <v>74</v>
       </c>
       <c r="B75">
-        <v>23.273809523809526</v>
+        <v>22.916666666666664</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -7982,7 +7982,7 @@
         <v>122</v>
       </c>
       <c r="B76">
-        <v>19.04761904761905</v>
+        <v>18.80952380952381</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -7990,7 +7990,7 @@
         <v>124</v>
       </c>
       <c r="B77">
-        <v>61.07142857142858</v>
+        <v>61.42857142857142</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -7998,7 +7998,7 @@
         <v>125</v>
       </c>
       <c r="B78">
-        <v>52.73809523809524</v>
+        <v>55.00000000000001</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -8006,7 +8006,7 @@
         <v>126</v>
       </c>
       <c r="B79">
-        <v>55.35714285714287</v>
+        <v>54.523809523809526</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -8014,7 +8014,7 @@
         <v>127</v>
       </c>
       <c r="B80">
-        <v>55.59523809523809</v>
+        <v>56.42857142857142</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -8022,7 +8022,7 @@
         <v>128</v>
       </c>
       <c r="B81">
-        <v>52.32142857142857</v>
+        <v>53.03571428571428</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -8030,7 +8030,7 @@
         <v>129</v>
       </c>
       <c r="B82">
-        <v>52.738095238095234</v>
+        <v>52.14285714285714</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -8038,7 +8038,7 @@
         <v>130</v>
       </c>
       <c r="B83">
-        <v>37.67857142857143</v>
+        <v>37.440476190476204</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -8046,7 +8046,7 @@
         <v>131</v>
       </c>
       <c r="B84">
-        <v>33.988095238095234</v>
+        <v>37.67857142857142</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -8054,7 +8054,7 @@
         <v>133</v>
       </c>
       <c r="B85">
-        <v>46.36904761904763</v>
+        <v>49.583333333333336</v>
       </c>
     </row>
   </sheetData>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="230">
   <si>
     <t>Ticker</t>
   </si>
@@ -427,7 +427,7 @@
     <t>_date_</t>
   </si>
   <si>
-    <t>2026-09-16</t>
+    <t>2026-09-17</t>
   </si>
   <si>
     <t>Criteria</t>
@@ -694,28 +694,22 @@
     <t>Momentum Breakout, Market Leader, Volume Spike</t>
   </si>
   <si>
-    <t>Stable Uptrend, Institutional Buying</t>
-  </si>
-  <si>
     <t>Momentum Breakout, Market Leader</t>
   </si>
   <si>
-    <t>Momentum Breakout, Volume Spike, Institutional Buying</t>
+    <t>Momentum Breakout, Institutional Buying</t>
   </si>
   <si>
     <t>Institutional Buying</t>
   </si>
   <si>
-    <t>Momentum Breakout, Institutional Buying</t>
+    <t>Momentum Breakout</t>
   </si>
   <si>
     <t>Volume Spike, Institutional Buying</t>
   </si>
   <si>
     <t>Volume Spike</t>
-  </si>
-  <si>
-    <t>Momentum Breakout</t>
   </si>
 </sst>
 </file>
@@ -1405,7 +1399,7 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>64.94047619047619</v>
+        <v>65.6547619047619</v>
       </c>
       <c r="C2" t="s">
         <v>221</v>
@@ -1416,7 +1410,7 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>62.797619047619044</v>
+        <v>62.916666666666664</v>
       </c>
       <c r="C3" t="s">
         <v>222</v>
@@ -1424,13 +1418,13 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>124</v>
+        <v>13</v>
       </c>
       <c r="B4">
-        <v>61.42857142857142</v>
+        <v>61.13095238095239</v>
       </c>
       <c r="C4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1438,29 +1432,29 @@
         <v>71</v>
       </c>
       <c r="B5">
-        <v>61.1904761904762</v>
+        <v>61.07142857142857</v>
       </c>
       <c r="C5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>124</v>
       </c>
       <c r="B6">
-        <v>60.654761904761905</v>
+        <v>60.17857142857143</v>
       </c>
       <c r="C6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="B7">
-        <v>60.416666666666664</v>
+        <v>60.05952380952382</v>
       </c>
       <c r="C7" t="s">
         <v>224</v>
@@ -1471,21 +1465,21 @@
         <v>32</v>
       </c>
       <c r="B8">
-        <v>60.238095238095234</v>
+        <v>59.761904761904766</v>
       </c>
       <c r="C8" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="B9">
-        <v>59.345238095238095</v>
+        <v>59.34523809523809</v>
       </c>
       <c r="C9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1493,7 +1487,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>58.80952380952381</v>
+        <v>59.16666666666667</v>
       </c>
       <c r="C10" t="s">
         <v>222</v>
@@ -1504,197 +1498,197 @@
         <v>42</v>
       </c>
       <c r="B11">
-        <v>58.51190476190476</v>
+        <v>58.98809523809524</v>
       </c>
       <c r="C11" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>126</v>
       </c>
       <c r="B12">
-        <v>56.54761904761905</v>
+        <v>56.30952380952381</v>
       </c>
       <c r="C12" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>127</v>
+        <v>19</v>
       </c>
       <c r="B13">
-        <v>56.42857142857142</v>
+        <v>56.19047619047619</v>
       </c>
       <c r="C13" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>125</v>
+        <v>47</v>
       </c>
       <c r="B14">
-        <v>55.00000000000001</v>
+        <v>55.95238095238097</v>
       </c>
       <c r="C14" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>125</v>
       </c>
       <c r="B15">
-        <v>54.76190476190477</v>
+        <v>55.11904761904762</v>
       </c>
       <c r="C15" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>126</v>
+        <v>6</v>
       </c>
       <c r="B16">
-        <v>54.523809523809526</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="C16" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>3</v>
+        <v>127</v>
       </c>
       <c r="B17">
-        <v>54.166666666666664</v>
+        <v>54.76190476190476</v>
       </c>
       <c r="C17" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B18">
-        <v>53.92857142857143</v>
+        <v>54.523809523809526</v>
       </c>
       <c r="C18" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B19">
-        <v>53.80952380952382</v>
+        <v>53.80952380952381</v>
       </c>
       <c r="C19" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="B20">
-        <v>53.333333333333336</v>
+        <v>53.03571428571429</v>
       </c>
       <c r="C20" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B21">
-        <v>53.03571428571429</v>
+        <v>52.85714285714286</v>
       </c>
       <c r="C21" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B22">
-        <v>53.03571428571428</v>
+        <v>52.14285714285714</v>
       </c>
       <c r="C22" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>43</v>
+        <v>128</v>
       </c>
       <c r="B23">
-        <v>52.5</v>
+        <v>51.488095238095234</v>
       </c>
       <c r="C23" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B24">
-        <v>52.14285714285714</v>
+        <v>48.75</v>
       </c>
       <c r="C24" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="B25">
-        <v>50.65476190476192</v>
+        <v>48.69047619047619</v>
       </c>
       <c r="C25" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>133</v>
+        <v>59</v>
       </c>
       <c r="B26">
-        <v>49.583333333333336</v>
+        <v>48.15476190476191</v>
       </c>
       <c r="C26" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="B27">
-        <v>49.404761904761905</v>
+        <v>47.083333333333336</v>
       </c>
       <c r="C27" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="B28">
-        <v>47.55952380952381</v>
+        <v>45.95238095238095</v>
       </c>
       <c r="C28" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -1702,172 +1696,172 @@
         <v>52</v>
       </c>
       <c r="B29">
-        <v>47.5</v>
+        <v>45.83333333333334</v>
       </c>
       <c r="C29" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="B30">
-        <v>46.8452380952381</v>
+        <v>45.714285714285715</v>
       </c>
       <c r="C30" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="B31">
-        <v>45.654761904761905</v>
+        <v>44.226190476190474</v>
       </c>
       <c r="C31" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="B32">
-        <v>45.595238095238095</v>
+        <v>43.273809523809526</v>
       </c>
       <c r="C32" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B33">
-        <v>44.166666666666664</v>
+        <v>43.035714285714285</v>
       </c>
       <c r="C33" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B34">
-        <v>43.273809523809526</v>
+        <v>42.55952380952381</v>
       </c>
       <c r="C34" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="B35">
-        <v>43.095238095238095</v>
+        <v>41.904761904761905</v>
       </c>
       <c r="C35" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36">
-        <v>43.035714285714285</v>
+        <v>41.13095238095239</v>
       </c>
       <c r="C36" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="B37">
-        <v>42.91666666666666</v>
+        <v>40.6547619047619</v>
       </c>
       <c r="C37" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="B38">
-        <v>41.726190476190474</v>
+        <v>40.41666666666667</v>
       </c>
       <c r="C38" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="B39">
-        <v>39.46428571428573</v>
+        <v>40.41666666666667</v>
       </c>
       <c r="C39" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="B40">
-        <v>39.464285714285715</v>
+        <v>39.04761904761906</v>
       </c>
       <c r="C40" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="B41">
-        <v>39.047619047619044</v>
+        <v>37.97619047619047</v>
       </c>
       <c r="C41" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="B42">
-        <v>38.33333333333333</v>
+        <v>35.95238095238095</v>
       </c>
       <c r="C42" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="B43">
-        <v>38.214285714285715</v>
+        <v>35.83333333333333</v>
       </c>
       <c r="C43" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="B44">
-        <v>38.09523809523809</v>
+        <v>35.77380952380953</v>
       </c>
       <c r="C44" t="s">
         <v>229</v>
@@ -1878,10 +1872,10 @@
         <v>131</v>
       </c>
       <c r="B45">
-        <v>37.67857142857142</v>
+        <v>35.535714285714285</v>
       </c>
       <c r="C45" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -1889,54 +1883,54 @@
         <v>130</v>
       </c>
       <c r="B46">
-        <v>37.440476190476204</v>
+        <v>35.17857142857143</v>
       </c>
       <c r="C46" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="B47">
-        <v>36.60714285714286</v>
+        <v>34.88095238095238</v>
       </c>
       <c r="C47" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="B48">
-        <v>35.89285714285714</v>
+        <v>34.82142857142857</v>
       </c>
       <c r="C48" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="B49">
-        <v>35.476190476190474</v>
+        <v>34.22619047619048</v>
       </c>
       <c r="C49" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="B50">
-        <v>34.40476190476191</v>
+        <v>33.63095238095238</v>
       </c>
       <c r="C50" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -1944,10 +1938,10 @@
         <v>4</v>
       </c>
       <c r="B51">
-        <v>33.511904761904766</v>
+        <v>33.035714285714285</v>
       </c>
       <c r="C51" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -2181,49 +2175,49 @@
         <v>-2.08</v>
       </c>
       <c r="F2" s="1">
-        <v>0.18997200578729737</v>
+        <v>0.13917432403740498</v>
       </c>
       <c r="G2" s="1">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="H2" s="1">
-        <v>64.77</v>
+        <v>53.83</v>
       </c>
       <c r="I2" s="1">
-        <v>15.4</v>
+        <v>11.62</v>
       </c>
       <c r="J2" s="1">
-        <v>0.01919412435012669</v>
+        <v>0.018274591018596964</v>
       </c>
       <c r="K2" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>-458</v>
+        <v>-460</v>
       </c>
       <c r="M2" s="1">
-        <v>0.18672862035598436</v>
+        <v>0.1340896264906748</v>
       </c>
       <c r="N2" s="1">
-        <v>20.153285214512568</v>
+        <v>15.127595249919409</v>
       </c>
       <c r="O2" s="1">
-        <v>79.76190476190477</v>
+        <v>77.38095238095238</v>
       </c>
       <c r="P2" s="1">
         <v>16.29652721982991</v>
       </c>
       <c r="Q2" s="1">
-        <v>56.785714285714285</v>
+        <v>52.97619047619047</v>
       </c>
       <c r="R2" s="1">
-        <v>49.404761904761905</v>
+        <v>48.45238095238095</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>94</v>
       </c>
       <c r="T2" s="1">
-        <v>29.59</v>
+        <v>28.64</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -2243,49 +2237,49 @@
         <v>3.63</v>
       </c>
       <c r="F3" s="1">
-        <v>-0.09944683961161421</v>
+        <v>-0.016313119383390345</v>
       </c>
       <c r="G3" s="1">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="H3" s="1">
-        <v>55.74</v>
+        <v>57.83</v>
       </c>
       <c r="I3" s="1">
-        <v>45.47</v>
+        <v>47.4</v>
       </c>
       <c r="J3" s="1">
-        <v>-0.007724499379480425</v>
+        <v>-0.007137324520773477</v>
       </c>
       <c r="K3" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L3" s="1">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="M3" s="1">
-        <v>-0.09348711888157657</v>
+        <v>-0.0069160834109522895</v>
       </c>
       <c r="N3" s="1">
-        <v>-7.868288709243537</v>
+        <v>1.0270242597566883</v>
       </c>
       <c r="O3" s="1">
-        <v>38.095238095238095</v>
+        <v>55.952380952380956</v>
       </c>
       <c r="P3" s="1">
         <v>26.053946839070953</v>
       </c>
       <c r="Q3" s="1">
-        <v>64.28571428571429</v>
+        <v>65.35714285714286</v>
       </c>
       <c r="R3" s="1">
-        <v>43.095238095238095</v>
+        <v>48.69047619047619</v>
       </c>
       <c r="S3" s="1" t="s">
         <v>95</v>
       </c>
       <c r="T3" s="1">
-        <v>-23.98</v>
+        <v>-18.38</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -2299,25 +2293,25 @@
         <v>10.714285714285714</v>
       </c>
       <c r="D4" s="2">
-        <v>12.41640378548896</v>
+        <v>12.511041009463725</v>
       </c>
       <c r="E4" s="2">
         <v>6.35</v>
       </c>
       <c r="F4" s="2">
-        <v>0.3251267781323619</v>
+        <v>0.36953368077022036</v>
       </c>
       <c r="G4" s="2">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="H4" s="2">
-        <v>50.5</v>
+        <v>55.35</v>
       </c>
       <c r="I4" s="2">
-        <v>45.61</v>
+        <v>50.24</v>
       </c>
       <c r="J4" s="2">
-        <v>0.023804526247211924</v>
+        <v>0.022909772955587993</v>
       </c>
       <c r="K4" s="2" t="b">
         <v>0</v>
@@ -2326,28 +2320,28 @@
         <v>180</v>
       </c>
       <c r="M4" s="2">
-        <v>0.32658630157645274</v>
+        <v>0.3717863948732021</v>
       </c>
       <c r="N4" s="2">
-        <v>34.13905333655941</v>
+        <v>38.89727208817214</v>
       </c>
       <c r="O4" s="2">
-        <v>91.66666666666666</v>
+        <v>92.85714285714286</v>
       </c>
       <c r="P4" s="2">
         <v>19.349659482175007</v>
       </c>
       <c r="Q4" s="2">
-        <v>58.452380952380956</v>
+        <v>60.00000000000001</v>
       </c>
       <c r="R4" s="2">
-        <v>54.166666666666664</v>
+        <v>54.523809523809526</v>
       </c>
       <c r="S4" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T4" s="2">
-        <v>5.81</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -2367,49 +2361,49 @@
         <v>1.69</v>
       </c>
       <c r="F5" s="1">
-        <v>-0.15121888524507135</v>
+        <v>-0.13815240424574216</v>
       </c>
       <c r="G5" s="1">
         <v>1.91</v>
       </c>
       <c r="H5" s="1">
-        <v>50.75</v>
+        <v>53.19</v>
       </c>
       <c r="I5" s="1">
-        <v>-10.22</v>
+        <v>-8.84</v>
       </c>
       <c r="J5" s="1">
-        <v>-0.014458365222932316</v>
+        <v>-0.014538324058561328</v>
       </c>
       <c r="K5" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L5" s="1">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="M5" s="1">
-        <v>-0.14752953431695282</v>
+        <v>-0.13229534757798966</v>
       </c>
       <c r="N5" s="1">
-        <v>-13.272530252781154</v>
+        <v>-11.510902156947047</v>
       </c>
       <c r="O5" s="1">
-        <v>27.380952380952383</v>
+        <v>25</v>
       </c>
       <c r="P5" s="1">
         <v>33.002444654975626</v>
       </c>
       <c r="Q5" s="1">
-        <v>48.80952380952381</v>
+        <v>50</v>
       </c>
       <c r="R5" s="1">
-        <v>33.511904761904766</v>
+        <v>33.035714285714285</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T5" s="1">
-        <v>-12.46</v>
+        <v>-12.94</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -2429,49 +2423,49 @@
         <v>-1.87</v>
       </c>
       <c r="F6" s="1">
-        <v>-0.06339811196205472</v>
+        <v>-0.0503926023399119</v>
       </c>
       <c r="G6" s="1">
         <v>1.6</v>
       </c>
       <c r="H6" s="1">
-        <v>48.93</v>
+        <v>46.58</v>
       </c>
       <c r="I6" s="1">
-        <v>-9.39</v>
+        <v>-10.43</v>
       </c>
       <c r="J6" s="1">
-        <v>0.0038728792097678113</v>
+        <v>0.0033357882717431897</v>
       </c>
       <c r="K6" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L6" s="1">
-        <v>-205</v>
+        <v>-207</v>
       </c>
       <c r="M6" s="1">
-        <v>-0.06096557288856996</v>
+        <v>-0.04653080673480037</v>
       </c>
       <c r="N6" s="1">
-        <v>-4.616134109942875</v>
+        <v>-2.934448072628113</v>
       </c>
       <c r="O6" s="1">
-        <v>45.23809523809524</v>
+        <v>48.80952380952381</v>
       </c>
       <c r="P6" s="1">
         <v>28.714544797168166</v>
       </c>
       <c r="Q6" s="1">
-        <v>47.023809523809526</v>
+        <v>46.42857142857144</v>
       </c>
       <c r="R6" s="1">
-        <v>36.25</v>
+        <v>37.67857142857143</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T6" s="1">
-        <v>17.16</v>
+        <v>18.59</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -2485,55 +2479,55 @@
         <v>69.04761904761905</v>
       </c>
       <c r="D7" s="2">
-        <v>7.79646017699115</v>
+        <v>7.798988621997471</v>
       </c>
       <c r="E7" s="2">
         <v>0.51</v>
       </c>
       <c r="F7" s="2">
-        <v>-0.02110888832927165</v>
+        <v>0.006251988920001082</v>
       </c>
       <c r="G7" s="2">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="H7" s="2">
-        <v>46.43</v>
+        <v>49.06</v>
       </c>
       <c r="I7" s="2">
-        <v>7.89</v>
+        <v>9.16</v>
       </c>
       <c r="J7" s="2">
-        <v>0.009509047270217452</v>
+        <v>0.008375651987741858</v>
       </c>
       <c r="K7" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L7" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="M7" s="2">
-        <v>-0.016122183228627907</v>
+        <v>0.014104306650394527</v>
       </c>
       <c r="N7" s="2">
-        <v>-0.13179514394866726</v>
+        <v>3.1290632658913653</v>
       </c>
       <c r="O7" s="2">
-        <v>54.761904761904766</v>
+        <v>59.523809523809526</v>
       </c>
       <c r="P7" s="2">
         <v>19.398494070050486</v>
       </c>
       <c r="Q7" s="2">
-        <v>65.23809523809523</v>
+        <v>65.47619047619048</v>
       </c>
       <c r="R7" s="2">
-        <v>53.92857142857143</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>99</v>
       </c>
       <c r="T7" s="2">
-        <v>5.51</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -2547,55 +2541,55 @@
         <v>84.52380952380952</v>
       </c>
       <c r="D8" s="1">
-        <v>-0.1209003215434084</v>
+        <v>-0.11961414790996792</v>
       </c>
       <c r="E8" s="1">
         <v>2.66</v>
       </c>
       <c r="F8" s="1">
-        <v>-0.09864059584071115</v>
+        <v>-0.09413153631108542</v>
       </c>
       <c r="G8" s="1">
         <v>0.61</v>
       </c>
       <c r="H8" s="1">
-        <v>35.76</v>
+        <v>36.89</v>
       </c>
       <c r="I8" s="1">
-        <v>6.35</v>
+        <v>6.5</v>
       </c>
       <c r="J8" s="1">
-        <v>-0.009019027055515196</v>
+        <v>-0.010305307227373635</v>
       </c>
       <c r="K8" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="1">
         <v>361</v>
       </c>
       <c r="M8" s="1">
-        <v>-0.10022174623847624</v>
+        <v>-0.09664170345440792</v>
       </c>
       <c r="N8" s="1">
-        <v>-8.541751444933494</v>
+        <v>-7.945537744588867</v>
       </c>
       <c r="O8" s="1">
-        <v>33.33333333333333</v>
+        <v>38.095238095238095</v>
       </c>
       <c r="P8" s="1">
-        <v>13.846685592437208</v>
+        <v>14.000228138738285</v>
       </c>
       <c r="Q8" s="1">
-        <v>46.547619047619044</v>
+        <v>46.9047619047619</v>
       </c>
       <c r="R8" s="1">
-        <v>39.464285714285715</v>
+        <v>40.6547619047619</v>
       </c>
       <c r="S8" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T8" s="1">
-        <v>-20.29</v>
+        <v>-19.1</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -2609,25 +2603,25 @@
         <v>40.476190476190474</v>
       </c>
       <c r="D9" s="2">
-        <v>36.18803418803419</v>
+        <v>36.13675213675214</v>
       </c>
       <c r="E9" s="2">
         <v>2.97</v>
       </c>
       <c r="F9" s="2">
-        <v>0.2636560065630964</v>
+        <v>0.28719085421434615</v>
       </c>
       <c r="G9" s="2">
         <v>1.62</v>
       </c>
       <c r="H9" s="2">
-        <v>52.4</v>
+        <v>55.26</v>
       </c>
       <c r="I9" s="2">
-        <v>13.28</v>
+        <v>15.6</v>
       </c>
       <c r="J9" s="2">
-        <v>0.03026422724404011</v>
+        <v>0.028227698598507878</v>
       </c>
       <c r="K9" s="2" t="b">
         <v>0</v>
@@ -2636,28 +2630,28 @@
         <v>-113</v>
       </c>
       <c r="M9" s="2">
-        <v>0.26616963027236396</v>
+        <v>0.29118137633962804</v>
       </c>
       <c r="N9" s="2">
-        <v>28.09738620615052</v>
+        <v>30.836770234814725</v>
       </c>
       <c r="O9" s="2">
-        <v>88.09523809523809</v>
+        <v>90.47619047619048</v>
       </c>
       <c r="P9" s="2">
         <v>33.227512780245505</v>
       </c>
       <c r="Q9" s="2">
-        <v>69.16666666666667</v>
+        <v>70.11904761904762</v>
       </c>
       <c r="R9" s="2">
-        <v>59.345238095238095</v>
+        <v>60.05952380952382</v>
       </c>
       <c r="S9" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T9" s="2">
-        <v>31.97</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -2677,49 +2671,49 @@
         <v>0.08</v>
       </c>
       <c r="F10" s="1">
-        <v>0.030047404885244697</v>
+        <v>0.036553128997951295</v>
       </c>
       <c r="G10" s="1">
         <v>1.41</v>
       </c>
       <c r="H10" s="1">
-        <v>52.47</v>
+        <v>53.74</v>
       </c>
       <c r="I10" s="1">
-        <v>2.3</v>
+        <v>2.79</v>
       </c>
       <c r="J10" s="1">
-        <v>0.008695891919290369</v>
+        <v>0.009467084769635965</v>
       </c>
       <c r="K10" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L10" s="1">
-        <v>-50</v>
+        <v>-51</v>
       </c>
       <c r="M10" s="1">
-        <v>0.03170963991879261</v>
+        <v>0.03919202266144417</v>
       </c>
       <c r="N10" s="1">
-        <v>4.651387170793397</v>
+        <v>5.63783486699633</v>
       </c>
       <c r="O10" s="1">
-        <v>60.71428571428571</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="P10" s="1">
         <v>14.568379622257217</v>
       </c>
       <c r="Q10" s="1">
-        <v>54.404761904761905</v>
+        <v>55.11904761904761</v>
       </c>
       <c r="R10" s="1">
-        <v>47.738095238095234</v>
+        <v>49.16666666666667</v>
       </c>
       <c r="S10" s="1" t="s">
         <v>101</v>
       </c>
       <c r="T10" s="1">
-        <v>12.19</v>
+        <v>13.62</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -2733,25 +2727,25 @@
         <v>17.857142857142858</v>
       </c>
       <c r="D11" s="2">
-        <v>46.61386138613861</v>
+        <v>46.68316831683168</v>
       </c>
       <c r="E11" s="2">
         <v>2.19</v>
       </c>
       <c r="F11" s="2">
-        <v>0.5321658356975969</v>
+        <v>0.5263281039258502</v>
       </c>
       <c r="G11" s="2">
         <v>0.7</v>
       </c>
       <c r="H11" s="2">
-        <v>64.54</v>
+        <v>62.18</v>
       </c>
       <c r="I11" s="2">
-        <v>45.07</v>
+        <v>42.5</v>
       </c>
       <c r="J11" s="2">
-        <v>0.018237022494593438</v>
+        <v>0.02049348878682897</v>
       </c>
       <c r="K11" s="2" t="b">
         <v>0</v>
@@ -2760,10 +2754,10 @@
         <v>40</v>
       </c>
       <c r="M11" s="2">
-        <v>0.5309495661608545</v>
+        <v>0.5243972061232944</v>
       </c>
       <c r="N11" s="2">
-        <v>54.57537979499957</v>
+        <v>54.158353213181364</v>
       </c>
       <c r="O11" s="2">
         <v>96.42857142857143</v>
@@ -2772,16 +2766,16 @@
         <v>21.2185970476566</v>
       </c>
       <c r="Q11" s="2">
-        <v>65.83333333333333</v>
+        <v>66.07142857142857</v>
       </c>
       <c r="R11" s="2">
-        <v>58.80952380952381</v>
+        <v>59.16666666666667</v>
       </c>
       <c r="S11" s="2" t="s">
         <v>102</v>
       </c>
       <c r="T11" s="2">
-        <v>7.16</v>
+        <v>7.52</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -2801,19 +2795,19 @@
         <v>1.36</v>
       </c>
       <c r="F12" s="2">
-        <v>0.7196463124147912</v>
+        <v>0.7366925384690726</v>
       </c>
       <c r="G12" s="2">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="H12" s="2">
-        <v>64.56</v>
+        <v>64.93</v>
       </c>
       <c r="I12" s="2">
-        <v>53.63</v>
+        <v>54.07</v>
       </c>
       <c r="J12" s="2">
-        <v>0.043642160393446656</v>
+        <v>0.04310533256031088</v>
       </c>
       <c r="K12" s="2" t="b">
         <v>0</v>
@@ -2822,10 +2816,10 @@
         <v>29</v>
       </c>
       <c r="M12" s="2">
-        <v>0.7195652277790083</v>
+        <v>0.736499448688817</v>
       </c>
       <c r="N12" s="2">
-        <v>73.43694595681495</v>
+        <v>75.36857746973361</v>
       </c>
       <c r="O12" s="2">
         <v>100</v>
@@ -2834,16 +2828,16 @@
         <v>23.557267760130397</v>
       </c>
       <c r="Q12" s="2">
-        <v>71.9047619047619</v>
+        <v>71.78571428571428</v>
       </c>
       <c r="R12" s="2">
-        <v>62.797619047619044</v>
+        <v>62.916666666666664</v>
       </c>
       <c r="S12" s="2" t="s">
         <v>103</v>
       </c>
       <c r="T12" s="2">
-        <v>10.05</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -2863,19 +2857,19 @@
         <v>-1.09</v>
       </c>
       <c r="F13" s="1">
-        <v>0.3954261927978079</v>
+        <v>0.3953383641809631</v>
       </c>
       <c r="G13" s="1">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H13" s="1">
-        <v>54.25</v>
+        <v>57.55</v>
       </c>
       <c r="I13" s="1">
-        <v>15.34</v>
+        <v>18.42</v>
       </c>
       <c r="J13" s="1">
-        <v>0.04631047830695267</v>
+        <v>0.04445005290715395</v>
       </c>
       <c r="K13" s="1" t="b">
         <v>1</v>
@@ -2884,28 +2878,28 @@
         <v>5</v>
       </c>
       <c r="M13" s="1">
-        <v>0.3977371049176184</v>
+        <v>0.39894270674573384</v>
       </c>
       <c r="N13" s="1">
-        <v>41.254133670675955</v>
+        <v>41.6129032754253</v>
       </c>
       <c r="O13" s="1">
-        <v>95.23809523809523</v>
+        <v>94.04761904761905</v>
       </c>
       <c r="P13" s="1">
         <v>40.13761891809808</v>
       </c>
       <c r="Q13" s="1">
-        <v>43.80952380952381</v>
+        <v>44.88095238095239</v>
       </c>
       <c r="R13" s="1">
-        <v>38.33333333333333</v>
+        <v>37.97619047619047</v>
       </c>
       <c r="S13" s="1" t="s">
         <v>104</v>
       </c>
       <c r="T13" s="1">
-        <v>37.54</v>
+        <v>37.18</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -2925,19 +2919,19 @@
         <v>-1.74</v>
       </c>
       <c r="F14" s="2">
-        <v>0.5985931847629387</v>
+        <v>0.6024453242113869</v>
       </c>
       <c r="G14" s="2">
         <v>0.74</v>
       </c>
       <c r="H14" s="2">
-        <v>68.68</v>
+        <v>65.5</v>
       </c>
       <c r="I14" s="2">
-        <v>80.16</v>
+        <v>75.85</v>
       </c>
       <c r="J14" s="2">
-        <v>0.025749119233567475</v>
+        <v>0.025363471923827274</v>
       </c>
       <c r="K14" s="2" t="b">
         <v>0</v>
@@ -2946,28 +2940,28 @@
         <v>101</v>
       </c>
       <c r="M14" s="2">
-        <v>0.5975390844977619</v>
+        <v>0.6007718794491719</v>
       </c>
       <c r="N14" s="2">
-        <v>61.23433162869032</v>
+        <v>61.79582054576912</v>
       </c>
       <c r="O14" s="2">
-        <v>97.61904761904762</v>
+        <v>98.80952380952381</v>
       </c>
       <c r="P14" s="2">
         <v>19.142997204429033</v>
       </c>
       <c r="Q14" s="2">
-        <v>68.0952380952381</v>
+        <v>68.21428571428572</v>
       </c>
       <c r="R14" s="2">
-        <v>60.654761904761905</v>
+        <v>61.13095238095239</v>
       </c>
       <c r="S14" s="2" t="s">
         <v>99</v>
       </c>
       <c r="T14" s="2">
-        <v>4.74</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -2987,49 +2981,49 @@
         <v>1.51</v>
       </c>
       <c r="F15" s="3">
-        <v>-0.26013481734958127</v>
+        <v>-0.16186108732737764</v>
       </c>
       <c r="G15" s="3">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="H15" s="3">
-        <v>55.59</v>
+        <v>56.2</v>
       </c>
       <c r="I15" s="3">
-        <v>33.23</v>
+        <v>33.37</v>
       </c>
       <c r="J15" s="3">
-        <v>-0.027382456892013598</v>
+        <v>-0.024282221805917426</v>
       </c>
       <c r="K15" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L15" s="3">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="M15" s="3">
-        <v>-0.2550670276131547</v>
+        <v>-0.1538800430768138</v>
       </c>
       <c r="N15" s="3">
-        <v>-24.02627958240134</v>
+        <v>-13.669371706829459</v>
       </c>
       <c r="O15" s="3">
-        <v>15.476190476190476</v>
+        <v>23.809523809523807</v>
       </c>
       <c r="P15" s="3">
         <v>41.90435941885386</v>
       </c>
       <c r="Q15" s="3">
-        <v>46.19047619047619</v>
+        <v>46.42857142857143</v>
       </c>
       <c r="R15" s="3">
-        <v>20.535714285714285</v>
+        <v>23.273809523809526</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>105</v>
       </c>
       <c r="T15" s="3">
-        <v>-37.88</v>
+        <v>-35.14</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -3049,19 +3043,19 @@
         <v>28.81</v>
       </c>
       <c r="F16" s="3">
-        <v>-0.2566940845659939</v>
+        <v>-0.23270905450864193</v>
       </c>
       <c r="G16" s="3">
         <v>1.81</v>
       </c>
       <c r="H16" s="3">
-        <v>39.79</v>
+        <v>41.34</v>
       </c>
       <c r="I16" s="3">
-        <v>-9.27</v>
+        <v>-8.58</v>
       </c>
       <c r="J16" s="3">
-        <v>-0.042142640718164474</v>
+        <v>-0.044848323753694776</v>
       </c>
       <c r="K16" s="3" t="b">
         <v>0</v>
@@ -3070,90 +3064,90 @@
         <v>27</v>
       </c>
       <c r="M16" s="3">
-        <v>-0.25341015681678947</v>
+        <v>-0.22749563044174137</v>
       </c>
       <c r="N16" s="3">
-        <v>-23.860592502764824</v>
+        <v>-21.03093044332222</v>
       </c>
       <c r="O16" s="3">
-        <v>16.666666666666664</v>
+        <v>15.476190476190476</v>
       </c>
       <c r="P16" s="3">
         <v>40.1905830435425</v>
       </c>
       <c r="Q16" s="3">
-        <v>26.785714285714285</v>
+        <v>27.499999999999996</v>
       </c>
       <c r="R16" s="3">
-        <v>14.821428571428566</v>
+        <v>14.464285714285708</v>
       </c>
       <c r="S16" s="3" t="s">
         <v>106</v>
       </c>
       <c r="T16" s="3">
-        <v>-28.41</v>
+        <v>-28.77</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="1">
         <v>-4.76</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="1">
         <v>5.952380952380952</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="1">
         <v>6.40546218487395</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="1">
         <v>-1.42</v>
       </c>
-      <c r="F17" s="3">
-        <v>-0.032752045584167805</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="F17" s="1">
+        <v>-0.01848988209780404</v>
+      </c>
+      <c r="G17" s="1">
         <v>1.77</v>
       </c>
-      <c r="H17" s="3">
-        <v>41.14</v>
-      </c>
-      <c r="I17" s="3">
-        <v>-2.6</v>
-      </c>
-      <c r="J17" s="3">
-        <v>-0.009769835280095828</v>
-      </c>
-      <c r="K17" s="3" t="b">
+      <c r="H17" s="1">
+        <v>43.27</v>
+      </c>
+      <c r="I17" s="1">
+        <v>-1.56</v>
+      </c>
+      <c r="J17" s="1">
+        <v>-0.01188842384778865</v>
+      </c>
+      <c r="K17" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="1">
         <v>31</v>
       </c>
-      <c r="M17" s="3">
-        <v>-0.02963028710652904</v>
-      </c>
-      <c r="N17" s="3">
-        <v>-1.4826055317387739</v>
-      </c>
-      <c r="O17" s="3">
-        <v>48.80952380952381</v>
-      </c>
-      <c r="P17" s="3">
+      <c r="M17" s="1">
+        <v>-0.013533911071244242</v>
+      </c>
+      <c r="N17" s="1">
+        <v>0.3652414937274923</v>
+      </c>
+      <c r="O17" s="1">
+        <v>52.38095238095239</v>
+      </c>
+      <c r="P17" s="1">
         <v>24.80206596461608</v>
       </c>
-      <c r="Q17" s="3">
-        <v>33.45238095238095</v>
-      </c>
-      <c r="R17" s="3">
-        <v>29.821428571428577</v>
-      </c>
-      <c r="S17" s="3" t="s">
+      <c r="Q17" s="1">
+        <v>34.166666666666664</v>
+      </c>
+      <c r="R17" s="1">
+        <v>30.535714285714292</v>
+      </c>
+      <c r="S17" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="T17" s="3">
-        <v>-3.35</v>
+      <c r="T17" s="1">
+        <v>-2.64</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -3167,25 +3161,25 @@
         <v>33.33333333333333</v>
       </c>
       <c r="D18" s="3">
-        <v>730.8947368421053</v>
+        <v>729.8947368421053</v>
       </c>
       <c r="E18" s="3">
         <v>11.06</v>
       </c>
       <c r="F18" s="3">
-        <v>-0.49106436960759603</v>
+        <v>-0.5954649734272661</v>
       </c>
       <c r="G18" s="3">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="H18" s="3">
-        <v>22.21</v>
+        <v>19.42</v>
       </c>
       <c r="I18" s="3">
-        <v>-44.66</v>
+        <v>-52.36</v>
       </c>
       <c r="J18" s="3">
-        <v>-0.06780716033684732</v>
+        <v>-0.07470679947091596</v>
       </c>
       <c r="K18" s="3" t="b">
         <v>1</v>
@@ -3194,28 +3188,28 @@
         <v>31</v>
       </c>
       <c r="M18" s="3">
-        <v>-0.49053731947500767</v>
+        <v>-0.5943707980058178</v>
       </c>
       <c r="N18" s="3">
-        <v>-47.57330876858664</v>
+        <v>-57.71844719972986</v>
       </c>
       <c r="O18" s="3">
         <v>1.1904761904761905</v>
       </c>
       <c r="P18" s="3">
-        <v>57.77687251199141</v>
+        <v>64.53582969240198</v>
       </c>
       <c r="Q18" s="3">
         <v>39.761904761904766</v>
       </c>
       <c r="R18" s="3">
-        <v>23.333333333333343</v>
+        <v>23.214285714285722</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>107</v>
       </c>
       <c r="T18" s="3">
-        <v>-10.93</v>
+        <v>-11.05</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -3235,31 +3229,31 @@
         <v>3.12</v>
       </c>
       <c r="F19" s="2">
-        <v>0.07709467163159969</v>
+        <v>0.09289548264290536</v>
       </c>
       <c r="G19" s="2">
         <v>0.1</v>
       </c>
       <c r="H19" s="2">
-        <v>51.86</v>
+        <v>51.64</v>
       </c>
       <c r="I19" s="2">
-        <v>12.41</v>
+        <v>12.23</v>
       </c>
       <c r="J19" s="2">
-        <v>0.0009386174230938178</v>
+        <v>0.0024878357788022908</v>
       </c>
       <c r="K19" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L19" s="2">
-        <v>-58</v>
+        <v>-59</v>
       </c>
       <c r="M19" s="2">
-        <v>0.07344586302137257</v>
+        <v>0.08710278923523807</v>
       </c>
       <c r="N19" s="2">
-        <v>8.825009481051378</v>
+        <v>10.428911524375723</v>
       </c>
       <c r="O19" s="2">
         <v>65.47619047619048</v>
@@ -3268,16 +3262,16 @@
         <v>11.392700631623551</v>
       </c>
       <c r="Q19" s="2">
-        <v>59.166666666666664</v>
+        <v>59.285714285714285</v>
       </c>
       <c r="R19" s="2">
-        <v>53.27380952380953</v>
+        <v>53.63095238095239</v>
       </c>
       <c r="S19" s="2" t="s">
         <v>108</v>
       </c>
       <c r="T19" s="2">
-        <v>4.86</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -3297,19 +3291,19 @@
         <v>-5.68</v>
       </c>
       <c r="F20" s="2">
-        <v>0.29160445537570323</v>
+        <v>0.2896528188729648</v>
       </c>
       <c r="G20" s="2">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H20" s="2">
-        <v>58.62</v>
+        <v>59.35</v>
       </c>
       <c r="I20" s="2">
-        <v>24.44</v>
+        <v>24.67</v>
       </c>
       <c r="J20" s="2">
-        <v>0.02271122205930087</v>
+        <v>0.02288829696965994</v>
       </c>
       <c r="K20" s="2" t="b">
         <v>1</v>
@@ -3318,28 +3312,28 @@
         <v>8</v>
       </c>
       <c r="M20" s="2">
-        <v>0.2918882516009431</v>
+        <v>0.2900389984334759</v>
       </c>
       <c r="N20" s="2">
-        <v>30.66924833900843</v>
+        <v>30.722532444199512</v>
       </c>
       <c r="O20" s="2">
-        <v>90.47619047619048</v>
+        <v>89.28571428571429</v>
       </c>
       <c r="P20" s="2">
         <v>20.924527727345563</v>
       </c>
       <c r="Q20" s="2">
-        <v>63.21428571428571</v>
+        <v>63.33333333333333</v>
       </c>
       <c r="R20" s="2">
-        <v>56.54761904761905</v>
+        <v>56.19047619047619</v>
       </c>
       <c r="S20" s="2" t="s">
         <v>95</v>
       </c>
       <c r="T20" s="2">
-        <v>20.69</v>
+        <v>20.34</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -3359,19 +3353,19 @@
         <v>-3.45</v>
       </c>
       <c r="F21" s="3">
-        <v>-0.3165139515121378</v>
+        <v>-0.3136559058170199</v>
       </c>
       <c r="G21" s="3">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="H21" s="3">
-        <v>46.12</v>
+        <v>43.06</v>
       </c>
       <c r="I21" s="3">
-        <v>-9.95</v>
+        <v>-12.44</v>
       </c>
       <c r="J21" s="3">
-        <v>-0.024252468286811893</v>
+        <v>-0.02229608683853931</v>
       </c>
       <c r="K21" s="3" t="b">
         <v>0</v>
@@ -3380,28 +3374,28 @@
         <v>55</v>
       </c>
       <c r="M21" s="3">
-        <v>-0.31404087012076165</v>
+        <v>-0.309665383691738</v>
       </c>
       <c r="N21" s="3">
-        <v>-29.923663833162035</v>
+        <v>-29.247905768321875</v>
       </c>
       <c r="O21" s="3">
-        <v>8.333333333333332</v>
+        <v>5.952380952380952</v>
       </c>
       <c r="P21" s="3">
         <v>51.51389629888408</v>
       </c>
       <c r="Q21" s="3">
-        <v>43.21428571428571</v>
+        <v>42.261904761904766</v>
       </c>
       <c r="R21" s="3">
-        <v>22.5</v>
+        <v>21.904761904761905</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>109</v>
       </c>
       <c r="T21" s="3">
-        <v>-28.72</v>
+        <v>-29.31</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -3421,49 +3415,49 @@
         <v>-0.24</v>
       </c>
       <c r="F22" s="1">
-        <v>-0.11926045075471127</v>
+        <v>-0.1300937179463819</v>
       </c>
       <c r="G22" s="1">
         <v>1.39</v>
       </c>
       <c r="H22" s="1">
-        <v>29.8</v>
+        <v>36.31</v>
       </c>
       <c r="I22" s="1">
-        <v>-3.92</v>
+        <v>-1.75</v>
       </c>
       <c r="J22" s="1">
-        <v>-0.015748340097914405</v>
+        <v>-0.016116795327733746</v>
       </c>
       <c r="K22" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L22" s="1">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M22" s="1">
-        <v>-0.11767930035694618</v>
+        <v>-0.1275835508030594</v>
       </c>
       <c r="N22" s="1">
-        <v>-10.28750685678049</v>
+        <v>-11.039722479454017</v>
       </c>
       <c r="O22" s="1">
-        <v>29.761904761904763</v>
+        <v>27.380952380952383</v>
       </c>
       <c r="P22" s="1">
         <v>19.455960650079966</v>
       </c>
       <c r="Q22" s="1">
-        <v>41.42857142857142</v>
+        <v>43.333333333333336</v>
       </c>
       <c r="R22" s="1">
-        <v>35.476190476190474</v>
+        <v>34.88095238095238</v>
       </c>
       <c r="S22" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T22" s="1">
-        <v>-17.63</v>
+        <v>-18.23</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -3477,37 +3471,37 @@
         <v>96.42857142857143</v>
       </c>
       <c r="D23" s="2">
-        <v>-0.7145009416195857</v>
+        <v>-0.7043314500941621</v>
       </c>
       <c r="E23" s="2">
         <v>0.07</v>
       </c>
       <c r="F23" s="2">
-        <v>0.11380484232451815</v>
+        <v>0.10351016002164629</v>
       </c>
       <c r="G23" s="2">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="H23" s="2">
-        <v>71.92</v>
+        <v>73.69</v>
       </c>
       <c r="I23" s="2">
-        <v>7.66</v>
+        <v>9.09</v>
       </c>
       <c r="J23" s="2">
-        <v>0.012063555475983053</v>
+        <v>0.010912196213464802</v>
       </c>
       <c r="K23" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" s="2">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M23" s="2">
-        <v>0.11453460404656357</v>
+        <v>0.10460433544309455</v>
       </c>
       <c r="N23" s="2">
-        <v>12.933883583570488</v>
+        <v>12.179066145161386</v>
       </c>
       <c r="O23" s="2">
         <v>70.23809523809523</v>
@@ -3516,7 +3510,7 @@
         <v>20.883293768118005</v>
       </c>
       <c r="Q23" s="2">
-        <v>64.28571428571428</v>
+        <v>64.52380952380952</v>
       </c>
       <c r="R23" s="2">
         <v>53.03571428571429</v>
@@ -3529,65 +3523,65 @@
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="1">
         <v>-97.21</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="1">
         <v>1.1904761904761905</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="1">
         <v>2.6552823783561363</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="1">
         <v>1.55</v>
       </c>
-      <c r="F24" s="3">
-        <v>-0.037047816214066706</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="F24" s="1">
+        <v>-0.006415625307672729</v>
+      </c>
+      <c r="G24" s="1">
         <v>3.59</v>
       </c>
-      <c r="H24" s="3">
-        <v>53.4</v>
-      </c>
-      <c r="I24" s="3">
-        <v>-7.02</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0.03523033883671116</v>
-      </c>
-      <c r="K24" s="3" t="b">
+      <c r="H24" s="1">
+        <v>54.44</v>
+      </c>
+      <c r="I24" s="1">
+        <v>-5.54</v>
+      </c>
+      <c r="J24" s="1">
+        <v>0.03283725680886844</v>
+      </c>
+      <c r="K24" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="1">
         <v>-68</v>
       </c>
-      <c r="M24" s="3">
-        <v>-0.02654735588019086</v>
-      </c>
-      <c r="N24" s="3">
-        <v>-1.1743124091049617</v>
-      </c>
-      <c r="O24" s="3">
-        <v>51.19047619047619</v>
-      </c>
-      <c r="P24" s="3">
+      <c r="M24" s="1">
+        <v>0.01025445905439204</v>
+      </c>
+      <c r="N24" s="1">
+        <v>2.744078506291129</v>
+      </c>
+      <c r="O24" s="1">
+        <v>58.333333333333336</v>
+      </c>
+      <c r="P24" s="1">
         <v>57.99224429263358</v>
       </c>
-      <c r="Q24" s="3">
-        <v>44.88095238095239</v>
-      </c>
-      <c r="R24" s="3">
-        <v>27.85714285714286</v>
-      </c>
-      <c r="S24" s="3" t="s">
+      <c r="Q24" s="1">
+        <v>45.71428571428571</v>
+      </c>
+      <c r="R24" s="1">
+        <v>30.41666666666667</v>
+      </c>
+      <c r="S24" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="T24" s="3">
-        <v>31.58</v>
+      <c r="T24" s="1">
+        <v>34.14</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -3607,19 +3601,19 @@
         <v>15.52</v>
       </c>
       <c r="F25" s="3">
-        <v>-0.22806529314068907</v>
+        <v>-0.1867725554705666</v>
       </c>
       <c r="G25" s="3">
         <v>2.37</v>
       </c>
       <c r="H25" s="3">
-        <v>42.06</v>
+        <v>42</v>
       </c>
       <c r="I25" s="3">
-        <v>-33.23</v>
+        <v>-33.32</v>
       </c>
       <c r="J25" s="3">
-        <v>-0.007099344383079003</v>
+        <v>-0.00973890708744834</v>
       </c>
       <c r="K25" s="3" t="b">
         <v>1</v>
@@ -3628,28 +3622,28 @@
         <v>34</v>
       </c>
       <c r="M25" s="3">
-        <v>-0.22251099558956555</v>
+        <v>-0.17795478883889526</v>
       </c>
       <c r="N25" s="3">
-        <v>-20.77067638004243</v>
+        <v>-16.076846283037604</v>
       </c>
       <c r="O25" s="3">
-        <v>19.047619047619047</v>
+        <v>22.61904761904762</v>
       </c>
       <c r="P25" s="3">
         <v>45.59139601172712</v>
       </c>
       <c r="Q25" s="3">
-        <v>17.142857142857142</v>
+        <v>15.833333333333334</v>
       </c>
       <c r="R25" s="3">
-        <v>5.178571428571429</v>
+        <v>5.773809523809524</v>
       </c>
       <c r="S25" s="3" t="s">
         <v>101</v>
       </c>
       <c r="T25" s="3">
-        <v>3.78</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -3669,19 +3663,19 @@
         <v>-0.88</v>
       </c>
       <c r="F26" s="3">
-        <v>-0.418863256826684</v>
+        <v>-0.37535174498183227</v>
       </c>
       <c r="G26" s="3">
         <v>3.38</v>
       </c>
       <c r="H26" s="3">
-        <v>42.26</v>
+        <v>44.13</v>
       </c>
       <c r="I26" s="3">
-        <v>-15.66</v>
+        <v>-14.4</v>
       </c>
       <c r="J26" s="3">
-        <v>-0.03423806305110756</v>
+        <v>-0.030956695479958874</v>
       </c>
       <c r="K26" s="3" t="b">
         <v>0</v>
@@ -3690,28 +3684,28 @@
         <v>159</v>
       </c>
       <c r="M26" s="3">
-        <v>-0.4092141851685278</v>
+        <v>-0.3600332890815565</v>
       </c>
       <c r="N26" s="3">
-        <v>-39.44099533793866</v>
+        <v>-34.28469630730373</v>
       </c>
       <c r="O26" s="3">
-        <v>2.380952380952381</v>
+        <v>3.571428571428571</v>
       </c>
       <c r="P26" s="3">
         <v>55.61259899184437</v>
       </c>
       <c r="Q26" s="3">
-        <v>13.095238095238095</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="R26" s="3">
-        <v>-2.7976190476190483</v>
+        <v>-2.321428571428573</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>101</v>
       </c>
       <c r="T26" s="3">
-        <v>-31.64</v>
+        <v>-31.16</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -3731,19 +3725,19 @@
         <v>6.6</v>
       </c>
       <c r="F27" s="3">
-        <v>-0.38761491156669486</v>
+        <v>-0.37690704855558455</v>
       </c>
       <c r="G27" s="3">
         <v>2.66</v>
       </c>
       <c r="H27" s="3">
-        <v>30.88</v>
+        <v>32.13</v>
       </c>
       <c r="I27" s="3">
-        <v>-39.09</v>
+        <v>-38.74</v>
       </c>
       <c r="J27" s="3">
-        <v>-0.032032005871659296</v>
+        <v>-0.031771079717984034</v>
       </c>
       <c r="K27" s="3" t="b">
         <v>1</v>
@@ -3752,28 +3746,28 @@
         <v>7</v>
       </c>
       <c r="M27" s="3">
-        <v>-0.3808848867967204</v>
+        <v>-0.36622274738144267</v>
       </c>
       <c r="N27" s="3">
-        <v>-36.60806550075791</v>
+        <v>-34.90364213729234</v>
       </c>
       <c r="O27" s="3">
-        <v>3.571428571428571</v>
+        <v>2.380952380952381</v>
       </c>
       <c r="P27" s="3">
-        <v>50.16260146842582</v>
+        <v>50.56910707785277</v>
       </c>
       <c r="Q27" s="3">
-        <v>10.95238095238095</v>
+        <v>10.833333333333332</v>
       </c>
       <c r="R27" s="3">
-        <v>0.17857142857142705</v>
+        <v>-0.2976190476190492</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>101</v>
       </c>
       <c r="T27" s="3">
-        <v>-15.98</v>
+        <v>-16.46</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -3793,19 +3787,19 @@
         <v>1.72</v>
       </c>
       <c r="F28" s="1">
-        <v>-0.0383812817215857</v>
+        <v>-0.07217364791915923</v>
       </c>
       <c r="G28" s="1">
         <v>3.26</v>
       </c>
       <c r="H28" s="1">
-        <v>44.98</v>
+        <v>41.08</v>
       </c>
       <c r="I28" s="1">
-        <v>-14.12</v>
+        <v>-17.38</v>
       </c>
       <c r="J28" s="1">
-        <v>0.010443960294191939</v>
+        <v>0.008462414769437203</v>
       </c>
       <c r="K28" s="1" t="b">
         <v>0</v>
@@ -3814,28 +3808,28 @@
         <v>3</v>
       </c>
       <c r="M28" s="1">
-        <v>-0.029218717878126466</v>
+        <v>-0.05762755113990581</v>
       </c>
       <c r="N28" s="1">
-        <v>-1.4414486088985201</v>
+        <v>-4.044122513138661</v>
       </c>
       <c r="O28" s="1">
-        <v>50</v>
+        <v>44.047619047619044</v>
       </c>
       <c r="P28" s="1">
         <v>35.08771990976345</v>
       </c>
       <c r="Q28" s="1">
-        <v>45.35714285714286</v>
+        <v>42.73809523809524</v>
       </c>
       <c r="R28" s="1">
-        <v>35.89285714285714</v>
+        <v>33.63095238095238</v>
       </c>
       <c r="S28" s="1" t="s">
         <v>110</v>
       </c>
       <c r="T28" s="1">
-        <v>18.88</v>
+        <v>16.62</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -3855,19 +3849,19 @@
         <v>-4.82</v>
       </c>
       <c r="F29" s="1">
-        <v>-0.023658413715891106</v>
+        <v>-0.07480700682309602</v>
       </c>
       <c r="G29" s="1">
         <v>2.32</v>
       </c>
       <c r="H29" s="1">
-        <v>44.44</v>
+        <v>44.21</v>
       </c>
       <c r="I29" s="1">
-        <v>-12.74</v>
+        <v>-12.91</v>
       </c>
       <c r="J29" s="1">
-        <v>-0.005401540775250435</v>
+        <v>-0.005462710293284703</v>
       </c>
       <c r="K29" s="1" t="b">
         <v>0</v>
@@ -3876,28 +3870,28 @@
         <v>10</v>
       </c>
       <c r="M29" s="1">
-        <v>-0.018306827754224653</v>
+        <v>-0.06631105649185065</v>
       </c>
       <c r="N29" s="1">
-        <v>-0.35025959650833816</v>
+        <v>-4.912473048333143</v>
       </c>
       <c r="O29" s="1">
-        <v>53.57142857142857</v>
+        <v>41.66666666666667</v>
       </c>
       <c r="P29" s="1">
         <v>21.89743824494191</v>
       </c>
       <c r="Q29" s="1">
-        <v>51.42857142857142</v>
+        <v>51.9047619047619</v>
       </c>
       <c r="R29" s="1">
-        <v>46.8452380952381</v>
+        <v>43.273809523809526</v>
       </c>
       <c r="S29" s="1" t="s">
         <v>108</v>
       </c>
       <c r="T29" s="1">
-        <v>6.6</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -3917,49 +3911,49 @@
         <v>1.75</v>
       </c>
       <c r="F30" s="1">
-        <v>-0.09990039554502307</v>
+        <v>-0.1310201126090189</v>
       </c>
       <c r="G30" s="1">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="H30" s="1">
-        <v>45.23</v>
+        <v>38.56</v>
       </c>
       <c r="I30" s="1">
-        <v>-4.84</v>
+        <v>-7.87</v>
       </c>
       <c r="J30" s="1">
-        <v>-0.006306081131863606</v>
+        <v>-0.008268715647729552</v>
       </c>
       <c r="K30" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L30" s="1">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M30" s="1">
-        <v>-0.09892737991562917</v>
+        <v>-0.12941103110688912</v>
       </c>
       <c r="N30" s="1">
-        <v>-8.412314812648793</v>
+        <v>-11.222470509836985</v>
       </c>
       <c r="O30" s="1">
-        <v>35.714285714285715</v>
+        <v>26.190476190476193</v>
       </c>
       <c r="P30" s="1">
-        <v>14.879468887608937</v>
+        <v>16.059849712981297</v>
       </c>
       <c r="Q30" s="1">
-        <v>57.38095238095238</v>
+        <v>54.047619047619044</v>
       </c>
       <c r="R30" s="1">
-        <v>47.55952380952381</v>
+        <v>44.226190476190474</v>
       </c>
       <c r="S30" s="1" t="s">
         <v>109</v>
       </c>
       <c r="T30" s="1">
-        <v>-0.92</v>
+        <v>-4.25</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -3979,49 +3973,49 @@
         <v>0.38</v>
       </c>
       <c r="F31" s="1">
-        <v>-0.15552777507748197</v>
+        <v>-0.1190897807479452</v>
       </c>
       <c r="G31" s="1">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="H31" s="1">
-        <v>33.8</v>
+        <v>35.64</v>
       </c>
       <c r="I31" s="1">
-        <v>-7.66</v>
+        <v>-6.99</v>
       </c>
       <c r="J31" s="1">
-        <v>-0.004310297631664881</v>
+        <v>-0.005521795155601717</v>
       </c>
       <c r="K31" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L31" s="1">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M31" s="1">
-        <v>-0.15358174381869416</v>
+        <v>-0.11593598100377078</v>
       </c>
       <c r="N31" s="1">
-        <v>-13.877751202955297</v>
+        <v>-9.874965499525155</v>
       </c>
       <c r="O31" s="1">
-        <v>26.190476190476193</v>
+        <v>30.952380952380953</v>
       </c>
       <c r="P31" s="1">
         <v>29.54918623383928</v>
       </c>
       <c r="Q31" s="1">
-        <v>52.73809523809524</v>
+        <v>52.50000000000001</v>
       </c>
       <c r="R31" s="1">
-        <v>39.46428571428573</v>
+        <v>40.41666666666667</v>
       </c>
       <c r="S31" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T31" s="1">
-        <v>-8.58</v>
+        <v>-7.63</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -4041,19 +4035,19 @@
         <v>3.57</v>
       </c>
       <c r="F32" s="1">
-        <v>-0.08562265625398327</v>
+        <v>-0.06511914251731207</v>
       </c>
       <c r="G32" s="1">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="H32" s="1">
-        <v>44.66</v>
+        <v>42.46</v>
       </c>
       <c r="I32" s="1">
-        <v>-4.63</v>
+        <v>-6.11</v>
       </c>
       <c r="J32" s="1">
-        <v>-0.012864987356518672</v>
+        <v>-0.013429000841589598</v>
       </c>
       <c r="K32" s="1" t="b">
         <v>0</v>
@@ -4062,28 +4056,28 @@
         <v>20</v>
       </c>
       <c r="M32" s="1">
-        <v>-0.0831495748626071</v>
+        <v>-0.06112862039203015</v>
       </c>
       <c r="N32" s="1">
-        <v>-6.834534307346585</v>
+        <v>-4.394229438351093</v>
       </c>
       <c r="O32" s="1">
-        <v>41.66666666666667</v>
+        <v>42.857142857142854</v>
       </c>
       <c r="P32" s="1">
         <v>27.28297753683016</v>
       </c>
       <c r="Q32" s="1">
-        <v>37.73809523809524</v>
+        <v>36.66666666666668</v>
       </c>
       <c r="R32" s="1">
-        <v>30.05952380952381</v>
+        <v>30.41666666666667</v>
       </c>
       <c r="S32" s="1" t="s">
         <v>107</v>
       </c>
       <c r="T32" s="1">
-        <v>-1.83</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -4103,49 +4097,49 @@
         <v>0.24</v>
       </c>
       <c r="F33" s="2">
-        <v>0.22833643011595184</v>
+        <v>0.22712345913400184</v>
       </c>
       <c r="G33" s="2">
         <v>1.1</v>
       </c>
       <c r="H33" s="2">
-        <v>55.13</v>
+        <v>53.68</v>
       </c>
       <c r="I33" s="2">
-        <v>14.93</v>
+        <v>14.45</v>
       </c>
       <c r="J33" s="2">
-        <v>0.025936437941787623</v>
+        <v>0.02483134658279094</v>
       </c>
       <c r="K33" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L33" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="M33" s="2">
-        <v>0.22874185329486596</v>
+        <v>0.22776709173485377</v>
       </c>
       <c r="N33" s="2">
-        <v>24.354608508400734</v>
+        <v>24.49534177433729</v>
       </c>
       <c r="O33" s="2">
-        <v>85.71428571428571</v>
+        <v>84.52380952380952</v>
       </c>
       <c r="P33" s="2">
         <v>23.38443607454554</v>
       </c>
       <c r="Q33" s="2">
-        <v>68.8095238095238</v>
+        <v>67.85714285714286</v>
       </c>
       <c r="R33" s="2">
-        <v>60.238095238095234</v>
+        <v>59.761904761904766</v>
       </c>
       <c r="S33" s="2" t="s">
         <v>108</v>
       </c>
       <c r="T33" s="2">
-        <v>24.45</v>
+        <v>23.97</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -4159,55 +4153,55 @@
         <v>92.85714285714286</v>
       </c>
       <c r="D34" s="1">
-        <v>-2.3395278754394777</v>
+        <v>-2.3390256152687092</v>
       </c>
       <c r="E34" s="1">
         <v>2.34</v>
       </c>
       <c r="F34" s="1">
-        <v>-0.0816363831952599</v>
+        <v>-0.09993113567007382</v>
       </c>
       <c r="G34" s="1">
         <v>1.21</v>
       </c>
       <c r="H34" s="1">
-        <v>51.65</v>
+        <v>53.26</v>
       </c>
       <c r="I34" s="1">
-        <v>2.32</v>
+        <v>2.93</v>
       </c>
       <c r="J34" s="1">
-        <v>-0.005879704137087581</v>
+        <v>-0.005954115496555359</v>
       </c>
       <c r="K34" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" s="1">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M34" s="1">
-        <v>-0.08078499451954024</v>
+        <v>-0.09857950720828479</v>
       </c>
       <c r="N34" s="1">
-        <v>-6.598076273039903</v>
+        <v>-8.139318119976558</v>
       </c>
       <c r="O34" s="1">
-        <v>42.857142857142854</v>
+        <v>35.714285714285715</v>
       </c>
       <c r="P34" s="1">
         <v>21.09433056126816</v>
       </c>
       <c r="Q34" s="1">
-        <v>49.88095238095239</v>
+        <v>49.76190476190476</v>
       </c>
       <c r="R34" s="1">
-        <v>38.09523809523809</v>
+        <v>35.83333333333333</v>
       </c>
       <c r="S34" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T34" s="1">
-        <v>-8.73</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -4227,19 +4221,19 @@
         <v>-0.33</v>
       </c>
       <c r="F35" s="1">
-        <v>-0.03260980368034272</v>
+        <v>-0.0768646671316858</v>
       </c>
       <c r="G35" s="1">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="H35" s="1">
-        <v>37.62</v>
+        <v>36.12</v>
       </c>
       <c r="I35" s="1">
-        <v>-14.04</v>
+        <v>-15.71</v>
       </c>
       <c r="J35" s="1">
-        <v>0.004372133480899242</v>
+        <v>0.0020215839801205754</v>
       </c>
       <c r="K35" s="1" t="b">
         <v>0</v>
@@ -4248,28 +4242,28 @@
         <v>-56</v>
       </c>
       <c r="M35" s="1">
-        <v>-0.03281251526979978</v>
+        <v>-0.07712212017202658</v>
       </c>
       <c r="N35" s="1">
-        <v>-1.8008283480658522</v>
+        <v>-5.993579416350741</v>
       </c>
       <c r="O35" s="1">
-        <v>47.61904761904761</v>
+        <v>39.285714285714285</v>
       </c>
       <c r="P35" s="1">
         <v>23.996351232323672</v>
       </c>
       <c r="Q35" s="1">
-        <v>47.142857142857146</v>
+        <v>45.71428571428572</v>
       </c>
       <c r="R35" s="1">
-        <v>42.023809523809526</v>
+        <v>39.16666666666667</v>
       </c>
       <c r="S35" s="1" t="s">
         <v>111</v>
       </c>
       <c r="T35" s="1">
-        <v>19.52</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -4289,19 +4283,19 @@
         <v>-1.31</v>
       </c>
       <c r="F36" s="1">
-        <v>-0.024708035868163617</v>
+        <v>-0.049627530556429385</v>
       </c>
       <c r="G36" s="1">
         <v>1.13</v>
       </c>
       <c r="H36" s="1">
-        <v>39.03</v>
+        <v>41</v>
       </c>
       <c r="I36" s="1">
-        <v>-11.19</v>
+        <v>-10.3</v>
       </c>
       <c r="J36" s="1">
-        <v>0.011962812460977914</v>
+        <v>0.01082927262830012</v>
       </c>
       <c r="K36" s="1" t="b">
         <v>0</v>
@@ -4310,28 +4304,28 @@
         <v>-21</v>
       </c>
       <c r="M36" s="1">
-        <v>-0.024180985735575256</v>
+        <v>-0.04879080817532189</v>
       </c>
       <c r="N36" s="1">
-        <v>-0.9376753946434004</v>
+        <v>-3.1604482166802708</v>
       </c>
       <c r="O36" s="1">
-        <v>52.38095238095239</v>
+        <v>46.42857142857143</v>
       </c>
       <c r="P36" s="1">
         <v>26.730280409441182</v>
       </c>
       <c r="Q36" s="1">
-        <v>50.357142857142854</v>
+        <v>51.19047619047618</v>
       </c>
       <c r="R36" s="1">
-        <v>43.98809523809524</v>
+        <v>42.20238095238096</v>
       </c>
       <c r="S36" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T36" s="1">
-        <v>17.04</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -4351,19 +4345,19 @@
         <v>-3.25</v>
       </c>
       <c r="F37" s="2">
-        <v>0.25051673512777806</v>
+        <v>0.1886359402391052</v>
       </c>
       <c r="G37" s="2">
         <v>1.27</v>
       </c>
       <c r="H37" s="2">
-        <v>43.18</v>
+        <v>41.23</v>
       </c>
       <c r="I37" s="2">
-        <v>6.02</v>
+        <v>4.49</v>
       </c>
       <c r="J37" s="2">
-        <v>0.01624961674252208</v>
+        <v>0.015940140989749038</v>
       </c>
       <c r="K37" s="2" t="b">
         <v>0</v>
@@ -4372,28 +4366,28 @@
         <v>-107</v>
       </c>
       <c r="M37" s="2">
-        <v>0.2516113777108462</v>
+        <v>0.1903737482614054</v>
       </c>
       <c r="N37" s="2">
-        <v>26.641560949998738</v>
+        <v>20.756007426992465</v>
       </c>
       <c r="O37" s="2">
-        <v>86.90476190476191</v>
+        <v>80.95238095238095</v>
       </c>
       <c r="P37" s="2">
         <v>20.90944133883571</v>
       </c>
       <c r="Q37" s="2">
-        <v>54.88095238095239</v>
+        <v>53.57142857142857</v>
       </c>
       <c r="R37" s="2">
-        <v>54.76190476190477</v>
+        <v>52.85714285714286</v>
       </c>
       <c r="S37" s="2" t="s">
         <v>109</v>
       </c>
       <c r="T37" s="2">
-        <v>24.94</v>
+        <v>23.04</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -4407,25 +4401,25 @@
         <v>30.952380952380953</v>
       </c>
       <c r="D38" s="2">
-        <v>686.5</v>
+        <v>686.25</v>
       </c>
       <c r="E38" s="2">
         <v>3.14</v>
       </c>
       <c r="F38" s="2">
-        <v>0.38422048428667477</v>
+        <v>0.40235676143176236</v>
       </c>
       <c r="G38" s="2">
         <v>1.2</v>
       </c>
       <c r="H38" s="2">
-        <v>62.57</v>
+        <v>63.64</v>
       </c>
       <c r="I38" s="2">
-        <v>63.94</v>
+        <v>64.58</v>
       </c>
       <c r="J38" s="2">
-        <v>0.013717782691271281</v>
+        <v>0.016130727470549343</v>
       </c>
       <c r="K38" s="2" t="b">
         <v>1</v>
@@ -4434,28 +4428,28 @@
         <v>391</v>
       </c>
       <c r="M38" s="2">
-        <v>0.385031330644503</v>
+        <v>0.4036440266334662</v>
       </c>
       <c r="N38" s="2">
-        <v>39.983556243364426</v>
+        <v>42.08303526419854</v>
       </c>
       <c r="O38" s="2">
-        <v>94.04761904761905</v>
+        <v>95.23809523809523</v>
       </c>
       <c r="P38" s="2">
         <v>17.802507034008837</v>
       </c>
       <c r="Q38" s="2">
-        <v>72.14285714285714</v>
+        <v>73.0952380952381</v>
       </c>
       <c r="R38" s="2">
-        <v>64.94047619047619</v>
+        <v>65.6547619047619</v>
       </c>
       <c r="S38" s="2" t="s">
         <v>99</v>
       </c>
       <c r="T38" s="2">
-        <v>0.86</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -4475,19 +4469,19 @@
         <v>-1.29</v>
       </c>
       <c r="F39" s="1">
-        <v>0.04074342820752774</v>
+        <v>-0.008753068940589755</v>
       </c>
       <c r="G39" s="1">
         <v>1.13</v>
       </c>
       <c r="H39" s="1">
-        <v>41.43</v>
+        <v>34.29</v>
       </c>
       <c r="I39" s="1">
-        <v>-3.84</v>
+        <v>-7.54</v>
       </c>
       <c r="J39" s="1">
-        <v>-0.004615158293231361</v>
+        <v>-0.004369013442851532</v>
       </c>
       <c r="K39" s="1" t="b">
         <v>1</v>
@@ -4496,28 +4490,28 @@
         <v>-1</v>
       </c>
       <c r="M39" s="1">
-        <v>0.0412704783401161</v>
+        <v>-0.007916346559482257</v>
       </c>
       <c r="N39" s="1">
-        <v>5.60747101292574</v>
+        <v>0.9269979449037048</v>
       </c>
       <c r="O39" s="1">
-        <v>61.904761904761905</v>
+        <v>54.761904761904766</v>
       </c>
       <c r="P39" s="1">
         <v>30.28933322215756</v>
       </c>
       <c r="Q39" s="1">
-        <v>47.85714285714286</v>
+        <v>44.76190476190476</v>
       </c>
       <c r="R39" s="1">
-        <v>43.273809523809526</v>
+        <v>41.13095238095239</v>
       </c>
       <c r="S39" s="1" t="s">
         <v>110</v>
       </c>
       <c r="T39" s="1">
-        <v>17.48</v>
+        <v>15.34</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -4537,19 +4531,19 @@
         <v>3.93</v>
       </c>
       <c r="F40" s="1">
-        <v>0.22655592528415458</v>
+        <v>0.21997708337187738</v>
       </c>
       <c r="G40" s="1">
-        <v>0.63</v>
+        <v>0.78</v>
       </c>
       <c r="H40" s="1">
-        <v>60.85</v>
+        <v>51.81</v>
       </c>
       <c r="I40" s="1">
-        <v>3.88</v>
+        <v>-4.2</v>
       </c>
       <c r="J40" s="1">
-        <v>0.03927426054044417</v>
+        <v>0.03570437173223505</v>
       </c>
       <c r="K40" s="1" t="b">
         <v>0</v>
@@ -4558,10 +4552,10 @@
         <v>-21</v>
       </c>
       <c r="M40" s="1">
-        <v>0.22505585952217233</v>
+        <v>0.21856109165000315</v>
       </c>
       <c r="N40" s="1">
-        <v>23.98600913113135</v>
+        <v>23.574741765852227</v>
       </c>
       <c r="O40" s="1">
         <v>82.14285714285714</v>
@@ -4570,7 +4564,7 @@
         <v>51.940889187924654</v>
       </c>
       <c r="Q40" s="1">
-        <v>54.88095238095237</v>
+        <v>50.83333333333333</v>
       </c>
       <c r="R40" s="1">
         <v>43.035714285714285</v>
@@ -4599,19 +4593,19 @@
         <v>0.01</v>
       </c>
       <c r="F41" s="3">
-        <v>-0.184636320368181</v>
+        <v>-0.20571247732610687</v>
       </c>
       <c r="G41" s="3">
         <v>1.22</v>
       </c>
       <c r="H41" s="3">
-        <v>38.33</v>
+        <v>39.71</v>
       </c>
       <c r="I41" s="3">
-        <v>-13.12</v>
+        <v>-12.83</v>
       </c>
       <c r="J41" s="3">
-        <v>-0.014939605641185334</v>
+        <v>-0.018308195349763592</v>
       </c>
       <c r="K41" s="3" t="b">
         <v>1</v>
@@ -4620,28 +4614,28 @@
         <v>4</v>
       </c>
       <c r="M41" s="3">
-        <v>-0.18374438937456994</v>
+        <v>-0.20429648560423264</v>
       </c>
       <c r="N41" s="3">
-        <v>-16.894015758542867</v>
+        <v>-18.711015959571345</v>
       </c>
       <c r="O41" s="3">
-        <v>21.428571428571427</v>
+        <v>19.047619047619047</v>
       </c>
       <c r="P41" s="3">
         <v>30.769232468942608</v>
       </c>
       <c r="Q41" s="3">
-        <v>22.857142857142854</v>
+        <v>23.452380952380953</v>
       </c>
       <c r="R41" s="3">
-        <v>14.523809523809518</v>
+        <v>13.69047619047619</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>105</v>
       </c>
       <c r="T41" s="3">
-        <v>-22.12</v>
+        <v>-22.96</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -4661,19 +4655,19 @@
         <v>4.37</v>
       </c>
       <c r="F42" s="1">
-        <v>-0.11696272762902046</v>
+        <v>-0.12134989496918369</v>
       </c>
       <c r="G42" s="1">
         <v>0.31</v>
       </c>
       <c r="H42" s="1">
-        <v>26.01</v>
+        <v>31.62</v>
       </c>
       <c r="I42" s="1">
-        <v>-10.11</v>
+        <v>-9.32</v>
       </c>
       <c r="J42" s="1">
-        <v>-0.013478457515303063</v>
+        <v>-0.013867968558443513</v>
       </c>
       <c r="K42" s="1" t="b">
         <v>0</v>
@@ -4682,10 +4676,10 @@
         <v>16</v>
       </c>
       <c r="M42" s="1">
-        <v>-0.11976014756352793</v>
+        <v>-0.12579095991506195</v>
       </c>
       <c r="N42" s="1">
-        <v>-10.495591577438663</v>
+        <v>-10.860463390654274</v>
       </c>
       <c r="O42" s="1">
         <v>28.57142857142857</v>
@@ -4694,7 +4688,7 @@
         <v>16.35579214434687</v>
       </c>
       <c r="Q42" s="1">
-        <v>36.07142857142857</v>
+        <v>36.42857142857142</v>
       </c>
       <c r="R42" s="1">
         <v>32.738095238095234</v>
@@ -4717,55 +4711,55 @@
         <v>32.142857142857146</v>
       </c>
       <c r="D43" s="2">
-        <v>150.40000000000003</v>
+        <v>150.8</v>
       </c>
       <c r="E43" s="2">
         <v>8.86</v>
       </c>
       <c r="F43" s="2">
-        <v>0.22561817582402588</v>
+        <v>0.22595450989255267</v>
       </c>
       <c r="G43" s="2">
         <v>1.34</v>
       </c>
       <c r="H43" s="2">
-        <v>56.12</v>
+        <v>57.66</v>
       </c>
       <c r="I43" s="2">
-        <v>22.61</v>
+        <v>24.8</v>
       </c>
       <c r="J43" s="2">
-        <v>0.014746331798322916</v>
+        <v>0.013519996080484386</v>
       </c>
       <c r="K43" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" s="2">
         <v>18</v>
       </c>
       <c r="M43" s="2">
-        <v>0.2269966146323339</v>
+        <v>0.2281428607354492</v>
       </c>
       <c r="N43" s="2">
-        <v>24.180084642147513</v>
+        <v>24.53291867439685</v>
       </c>
       <c r="O43" s="2">
-        <v>83.33333333333334</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="P43" s="2">
         <v>24.82490242340647</v>
       </c>
       <c r="Q43" s="2">
-        <v>68.45238095238096</v>
+        <v>68.33333333333334</v>
       </c>
       <c r="R43" s="2">
-        <v>58.51190476190476</v>
+        <v>58.98809523809524</v>
       </c>
       <c r="S43" s="2" t="s">
         <v>113</v>
       </c>
       <c r="T43" s="2">
-        <v>6.13</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -4785,49 +4779,49 @@
         <v>-0.68</v>
       </c>
       <c r="F44" s="2">
-        <v>0.13296058108978287</v>
+        <v>0.12001048705223726</v>
       </c>
       <c r="G44" s="2">
         <v>2.64</v>
       </c>
       <c r="H44" s="2">
-        <v>41.79</v>
+        <v>42.93</v>
       </c>
       <c r="I44" s="2">
-        <v>-0.47</v>
+        <v>0.37</v>
       </c>
       <c r="J44" s="2">
-        <v>0.008373532667441874</v>
+        <v>0.007689979303030582</v>
       </c>
       <c r="K44" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="2">
         <v>-8</v>
       </c>
       <c r="M44" s="2">
-        <v>0.13960952122397452</v>
+        <v>0.13056606170620877</v>
       </c>
       <c r="N44" s="2">
-        <v>15.44137530131158</v>
+        <v>14.77523877147279</v>
       </c>
       <c r="O44" s="2">
-        <v>73.80952380952381</v>
+        <v>76.19047619047619</v>
       </c>
       <c r="P44" s="2">
         <v>29.40653991657008</v>
       </c>
       <c r="Q44" s="2">
-        <v>56.42857142857142</v>
+        <v>56.42857142857143</v>
       </c>
       <c r="R44" s="2">
-        <v>52.5</v>
+        <v>52.97619047619048</v>
       </c>
       <c r="S44" s="2" t="s">
         <v>101</v>
       </c>
       <c r="T44" s="2">
-        <v>17.68</v>
+        <v>18.16</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
@@ -4847,49 +4841,49 @@
         <v>1.03</v>
       </c>
       <c r="F45" s="1">
-        <v>-0.006913898943788705</v>
+        <v>-0.020309610306311288</v>
       </c>
       <c r="G45" s="1">
         <v>1.46</v>
       </c>
       <c r="H45" s="1">
-        <v>41.37</v>
+        <v>42.64</v>
       </c>
       <c r="I45" s="1">
-        <v>3.43</v>
+        <v>3.51</v>
       </c>
       <c r="J45" s="1">
-        <v>0.0044034813722999225</v>
+        <v>0.0034348964400732775</v>
       </c>
       <c r="K45" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L45" s="1">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="M45" s="1">
-        <v>-0.005048952320783728</v>
+        <v>-0.017348900342392448</v>
       </c>
       <c r="N45" s="1">
-        <v>0.975527946835755</v>
+        <v>-0.016257433387322155</v>
       </c>
       <c r="O45" s="1">
-        <v>55.952380952380956</v>
+        <v>51.19047619047619</v>
       </c>
       <c r="P45" s="1">
         <v>17.57882034058413</v>
       </c>
       <c r="Q45" s="1">
-        <v>46.19047619047619</v>
+        <v>46.785714285714285</v>
       </c>
       <c r="R45" s="1">
-        <v>41.726190476190474</v>
+        <v>40.41666666666667</v>
       </c>
       <c r="S45" s="1" t="s">
         <v>107</v>
       </c>
       <c r="T45" s="1">
-        <v>-2.6</v>
+        <v>-3.91</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
@@ -4909,19 +4903,19 @@
         <v>4.53</v>
       </c>
       <c r="F46" s="3">
-        <v>-0.25965455072204424</v>
+        <v>-0.257603525148644</v>
       </c>
       <c r="G46" s="3">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="H46" s="3">
-        <v>34.21</v>
+        <v>34.52</v>
       </c>
       <c r="I46" s="3">
-        <v>-31.05</v>
+        <v>-31.26</v>
       </c>
       <c r="J46" s="3">
-        <v>-0.00821452517149062</v>
+        <v>-0.009825507176882218</v>
       </c>
       <c r="K46" s="3" t="b">
         <v>0</v>
@@ -4930,28 +4924,28 @@
         <v>17</v>
       </c>
       <c r="M46" s="3">
-        <v>-0.2564922499265141</v>
+        <v>-0.2525188276019138</v>
       </c>
       <c r="N46" s="3">
-        <v>-24.168801813737286</v>
+        <v>-23.533250159339456</v>
       </c>
       <c r="O46" s="3">
-        <v>14.285714285714285</v>
+        <v>13.095238095238097</v>
       </c>
       <c r="P46" s="3">
         <v>54.33673655574689</v>
       </c>
       <c r="Q46" s="3">
-        <v>44.52380952380952</v>
+        <v>43.8095238095238</v>
       </c>
       <c r="R46" s="3">
-        <v>27.976190476190474</v>
+        <v>27.26190476190476</v>
       </c>
       <c r="S46" s="3" t="s">
         <v>101</v>
       </c>
       <c r="T46" s="3">
-        <v>6.94</v>
+        <v>6.23</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
@@ -4971,19 +4965,19 @@
         <v>2.59</v>
       </c>
       <c r="F47" s="1">
-        <v>0.1123052319507205</v>
+        <v>0.1248779887475471</v>
       </c>
       <c r="G47" s="1">
         <v>1.42</v>
       </c>
       <c r="H47" s="1">
-        <v>46.61</v>
+        <v>48.27</v>
       </c>
       <c r="I47" s="1">
-        <v>2.22</v>
+        <v>3.1</v>
       </c>
       <c r="J47" s="1">
-        <v>0.019366235203556553</v>
+        <v>0.018663167015806774</v>
       </c>
       <c r="K47" s="1" t="b">
         <v>1</v>
@@ -4992,28 +4986,28 @@
         <v>-56</v>
       </c>
       <c r="M47" s="1">
-        <v>0.11400800930215982</v>
+        <v>0.12758124567112517</v>
       </c>
       <c r="N47" s="1">
-        <v>12.88122410913011</v>
+        <v>14.476757167964438</v>
       </c>
       <c r="O47" s="1">
-        <v>69.04761904761905</v>
+        <v>75</v>
       </c>
       <c r="P47" s="1">
         <v>33.3731909304046</v>
       </c>
       <c r="Q47" s="1">
-        <v>53.45238095238095</v>
+        <v>53.57142857142857</v>
       </c>
       <c r="R47" s="1">
-        <v>44.166666666666664</v>
+        <v>45.714285714285715</v>
       </c>
       <c r="S47" s="1" t="s">
         <v>107</v>
       </c>
       <c r="T47" s="1">
-        <v>18.31</v>
+        <v>19.86</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
@@ -5033,19 +5027,19 @@
         <v>0.65</v>
       </c>
       <c r="F48" s="2">
-        <v>0.12318043425795686</v>
+        <v>0.15471522428717138</v>
       </c>
       <c r="G48" s="2">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H48" s="2">
-        <v>52.86</v>
+        <v>56.53</v>
       </c>
       <c r="I48" s="2">
-        <v>26.2</v>
+        <v>29.55</v>
       </c>
       <c r="J48" s="2">
-        <v>0.013968962881582982</v>
+        <v>0.01416947553790085</v>
       </c>
       <c r="K48" s="2" t="b">
         <v>0</v>
@@ -5054,28 +5048,28 @@
         <v>242</v>
       </c>
       <c r="M48" s="2">
-        <v>0.12565351564933303</v>
+        <v>0.1585770198922829</v>
       </c>
       <c r="N48" s="2">
-        <v>14.045774743847439</v>
+        <v>17.576334590080215</v>
       </c>
       <c r="O48" s="2">
-        <v>72.61904761904762</v>
+        <v>79.76190476190477</v>
       </c>
       <c r="P48" s="2">
         <v>23.23749735248456</v>
       </c>
       <c r="Q48" s="2">
-        <v>65</v>
+        <v>65.95238095238095</v>
       </c>
       <c r="R48" s="2">
-        <v>53.80952380952382</v>
+        <v>55.95238095238097</v>
       </c>
       <c r="S48" s="2" t="s">
         <v>95</v>
       </c>
       <c r="T48" s="2">
-        <v>4.54</v>
+        <v>6.68</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
@@ -5095,19 +5089,19 @@
         <v>-11.05</v>
       </c>
       <c r="F49" s="2">
-        <v>0.005968255942283559</v>
+        <v>0.09095461833396687</v>
       </c>
       <c r="G49" s="2">
         <v>1.06</v>
       </c>
       <c r="H49" s="2">
-        <v>60.08</v>
+        <v>60.21</v>
       </c>
       <c r="I49" s="2">
-        <v>1.34</v>
+        <v>2.38</v>
       </c>
       <c r="J49" s="2">
-        <v>0.019831944438526</v>
+        <v>0.02047618809470788</v>
       </c>
       <c r="K49" s="2" t="b">
         <v>0</v>
@@ -5116,13 +5110,13 @@
         <v>-7</v>
       </c>
       <c r="M49" s="2">
-        <v>0.006211509849632035</v>
+        <v>0.09134079789447802</v>
       </c>
       <c r="N49" s="2">
-        <v>2.101574163877322</v>
+        <v>10.852712390299727</v>
       </c>
       <c r="O49" s="2">
-        <v>57.14285714285714</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="P49" s="2">
         <v>31.00158698078384</v>
@@ -5131,13 +5125,13 @@
         <v>68.57142857142857</v>
       </c>
       <c r="R49" s="2">
-        <v>51.13095238095238</v>
+        <v>53.86904761904761</v>
       </c>
       <c r="S49" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T49" s="2">
-        <v>20.03</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
@@ -5157,19 +5151,19 @@
         <v>12.9</v>
       </c>
       <c r="F50" s="3">
-        <v>-0.2899883066465494</v>
+        <v>-0.2943170786638365</v>
       </c>
       <c r="G50" s="3">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="H50" s="3">
-        <v>49.43</v>
+        <v>52.84</v>
       </c>
       <c r="I50" s="3">
-        <v>0.25</v>
+        <v>4.53</v>
       </c>
       <c r="J50" s="3">
-        <v>-0.006198950548386034</v>
+        <v>-0.0025153531749216936</v>
       </c>
       <c r="K50" s="3" t="b">
         <v>0</v>
@@ -5178,22 +5172,22 @@
         <v>69</v>
       </c>
       <c r="M50" s="3">
-        <v>-0.27851483068327965</v>
+        <v>-0.27616663931981233</v>
       </c>
       <c r="N50" s="3">
-        <v>-26.371059889413832</v>
+        <v>-25.89803133112931</v>
       </c>
       <c r="O50" s="3">
-        <v>10.714285714285714</v>
+        <v>9.523809523809524</v>
       </c>
       <c r="P50" s="3">
         <v>41.201484669672254</v>
       </c>
       <c r="Q50" s="3">
-        <v>43.452380952380956</v>
+        <v>46.904761904761905</v>
       </c>
       <c r="R50" s="3">
-        <v>20.05952380952381</v>
+        <v>20.535714285714285</v>
       </c>
       <c r="S50" s="3" t="s">
         <v>106</v>
@@ -5217,19 +5211,19 @@
         <v>14.41</v>
       </c>
       <c r="F51" s="1">
-        <v>0.2246923854244884</v>
+        <v>0.21613007367573558</v>
       </c>
       <c r="G51" s="1">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="H51" s="1">
-        <v>63.24</v>
+        <v>65.16</v>
       </c>
       <c r="I51" s="1">
-        <v>32.27</v>
+        <v>35.25</v>
       </c>
       <c r="J51" s="1">
-        <v>0.047903993640471966</v>
+        <v>0.04821181700151261</v>
       </c>
       <c r="K51" s="1" t="b">
         <v>0</v>
@@ -5238,22 +5232,22 @@
         <v>14</v>
       </c>
       <c r="M51" s="1">
-        <v>0.22744926304110447</v>
+        <v>0.22031368558127307</v>
       </c>
       <c r="N51" s="1">
-        <v>24.225349483024562</v>
+        <v>23.750001158979234</v>
       </c>
       <c r="O51" s="1">
-        <v>84.52380952380952</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="P51" s="1">
         <v>38.38748944617691</v>
       </c>
       <c r="Q51" s="1">
-        <v>55.5952380952381</v>
+        <v>56.30952380952381</v>
       </c>
       <c r="R51" s="1">
-        <v>42.91666666666666</v>
+        <v>42.55952380952381</v>
       </c>
       <c r="S51" s="1" t="s">
         <v>96</v>
@@ -5277,19 +5271,19 @@
         <v>-5.11</v>
       </c>
       <c r="F52" s="3">
-        <v>-0.16803559328215234</v>
+        <v>-0.18580444638797697</v>
       </c>
       <c r="G52" s="3">
-        <v>0.93</v>
+        <v>0.94</v>
       </c>
       <c r="H52" s="3">
-        <v>34.18</v>
+        <v>33.92</v>
       </c>
       <c r="I52" s="3">
-        <v>-34.64</v>
+        <v>-35.33</v>
       </c>
       <c r="J52" s="3">
-        <v>-0.014342051443960092</v>
+        <v>-0.015144775587393204</v>
       </c>
       <c r="K52" s="3" t="b">
         <v>0</v>
@@ -5298,22 +5292,22 @@
         <v>-106</v>
       </c>
       <c r="M52" s="3">
-        <v>-0.16831938950739223</v>
+        <v>-0.18619062594848812</v>
       </c>
       <c r="N52" s="3">
-        <v>-15.3515157718251</v>
+        <v>-16.900429993996887</v>
       </c>
       <c r="O52" s="3">
-        <v>23.809523809523807</v>
+        <v>21.428571428571427</v>
       </c>
       <c r="P52" s="3">
-        <v>41.9219479219836</v>
+        <v>42.461480269958265</v>
       </c>
       <c r="Q52" s="3">
-        <v>32.261904761904766</v>
+        <v>32.142857142857146</v>
       </c>
       <c r="R52" s="3">
-        <v>22.85714285714286</v>
+        <v>22.142857142857146</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>113</v>
@@ -5337,49 +5331,49 @@
         <v>-1.38</v>
       </c>
       <c r="F53" s="1">
-        <v>0.025977115851738786</v>
+        <v>-0.010746958005590768</v>
       </c>
       <c r="G53" s="1">
         <v>0.98</v>
       </c>
       <c r="H53" s="1">
-        <v>39.1</v>
+        <v>37.1</v>
       </c>
       <c r="I53" s="1">
-        <v>3.05</v>
+        <v>2.03</v>
       </c>
       <c r="J53" s="1">
-        <v>0.001750937952638683</v>
+        <v>0.0020615095187688</v>
       </c>
       <c r="K53" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L53" s="1">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="M53" s="1">
-        <v>0.02589603121595596</v>
+        <v>-0.010875684525761153</v>
       </c>
       <c r="N53" s="1">
-        <v>4.070026300509722</v>
+        <v>0.6310641482758126</v>
       </c>
       <c r="O53" s="1">
-        <v>59.523809523809526</v>
+        <v>53.57142857142857</v>
       </c>
       <c r="P53" s="1">
         <v>11.84024085938085</v>
       </c>
       <c r="Q53" s="1">
-        <v>48.69047619047619</v>
+        <v>48.095238095238095</v>
       </c>
       <c r="R53" s="1">
-        <v>47.5</v>
+        <v>45.83333333333334</v>
       </c>
       <c r="S53" s="1" t="s">
         <v>114</v>
       </c>
       <c r="T53" s="1">
-        <v>7.07</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
@@ -5399,49 +5393,49 @@
         <v>0.68</v>
       </c>
       <c r="F54" s="1">
-        <v>-0.1781849023649378</v>
+        <v>-0.19304729842879337</v>
       </c>
       <c r="G54" s="1">
         <v>1.58</v>
       </c>
       <c r="H54" s="1">
-        <v>41.53</v>
+        <v>42.82</v>
       </c>
       <c r="I54" s="1">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="J54" s="1">
-        <v>-0.023384481286201516</v>
+        <v>-0.022109313461793265</v>
       </c>
       <c r="K54" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L54" s="1">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="M54" s="1">
-        <v>-0.17583344792723588</v>
+        <v>-0.18931422934385223</v>
       </c>
       <c r="N54" s="1">
-        <v>-16.102921613809464</v>
+        <v>-17.212790333533306</v>
       </c>
       <c r="O54" s="1">
-        <v>22.61904761904762</v>
+        <v>20.238095238095237</v>
       </c>
       <c r="P54" s="1">
         <v>26.83257063748809</v>
       </c>
       <c r="Q54" s="1">
-        <v>46.30952380952381</v>
+        <v>46.3095238095238</v>
       </c>
       <c r="R54" s="1">
-        <v>32.5</v>
+        <v>31.488095238095237</v>
       </c>
       <c r="S54" s="1" t="s">
         <v>95</v>
       </c>
       <c r="T54" s="1">
-        <v>-26.1</v>
+        <v>-27.11</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
@@ -5461,49 +5455,49 @@
         <v>1.71</v>
       </c>
       <c r="F55" s="1">
-        <v>-0.08118514612274264</v>
+        <v>-0.07348611333178189</v>
       </c>
       <c r="G55" s="1">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="H55" s="1">
-        <v>59.93</v>
+        <v>63.9</v>
       </c>
       <c r="I55" s="1">
-        <v>34.96</v>
+        <v>41.96</v>
       </c>
       <c r="J55" s="1">
-        <v>-0.009976997406942507</v>
+        <v>-0.0094372266902849</v>
       </c>
       <c r="K55" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L55" s="1">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M55" s="1">
-        <v>-0.06999546638471277</v>
+        <v>-0.05585058006843924</v>
       </c>
       <c r="N55" s="1">
-        <v>-5.519123459557149</v>
+        <v>-3.8664254059919974</v>
       </c>
       <c r="O55" s="1">
-        <v>44.047619047619044</v>
+        <v>45.23809523809524</v>
       </c>
       <c r="P55" s="1">
         <v>52.65288503392759</v>
       </c>
       <c r="Q55" s="1">
-        <v>60.5952380952381</v>
+        <v>62.73809523809524</v>
       </c>
       <c r="R55" s="1">
-        <v>38.214285714285715</v>
+        <v>39.04761904761906</v>
       </c>
       <c r="S55" s="1" t="s">
         <v>109</v>
       </c>
       <c r="T55" s="1">
-        <v>-21.79</v>
+        <v>-20.95</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
@@ -5523,19 +5517,19 @@
         <v>-1.32</v>
       </c>
       <c r="F56" s="3">
-        <v>-0.26697782392274355</v>
+        <v>-0.22484567397568406</v>
       </c>
       <c r="G56" s="3">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="H56" s="3">
-        <v>39.66</v>
+        <v>43.19</v>
       </c>
       <c r="I56" s="3">
-        <v>-8.7</v>
+        <v>-5.91</v>
       </c>
       <c r="J56" s="3">
-        <v>-0.023519023530335328</v>
+        <v>-0.02516181656273842</v>
       </c>
       <c r="K56" s="3" t="b">
         <v>1</v>
@@ -5544,28 +5538,28 @@
         <v>249</v>
       </c>
       <c r="M56" s="3">
-        <v>-0.2626803382262538</v>
+        <v>-0.2180875316667389</v>
       </c>
       <c r="N56" s="3">
-        <v>-24.787610643711254</v>
+        <v>-20.090120565821966</v>
       </c>
       <c r="O56" s="3">
-        <v>11.904761904761903</v>
+        <v>17.857142857142858</v>
       </c>
       <c r="P56" s="3">
         <v>40.717118046641446</v>
       </c>
       <c r="Q56" s="3">
-        <v>43.69047619047618</v>
+        <v>45.23809523809523</v>
       </c>
       <c r="R56" s="3">
-        <v>26.54761904761905</v>
+        <v>27.976190476190474</v>
       </c>
       <c r="S56" s="3" t="s">
         <v>108</v>
       </c>
       <c r="T56" s="3">
-        <v>-22.42</v>
+        <v>-20.99</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
@@ -5585,19 +5579,19 @@
         <v>1.24</v>
       </c>
       <c r="F57" s="1">
-        <v>0.009109164907531307</v>
+        <v>0.03418556245201523</v>
       </c>
       <c r="G57" s="1">
         <v>1.65</v>
       </c>
       <c r="H57" s="1">
-        <v>36.78</v>
+        <v>35.01</v>
       </c>
       <c r="I57" s="1">
-        <v>-20.62</v>
+        <v>-21.83</v>
       </c>
       <c r="J57" s="1">
-        <v>-0.0003338970613827449</v>
+        <v>0.0011690210894471037</v>
       </c>
       <c r="K57" s="1" t="b">
         <v>0</v>
@@ -5606,28 +5600,28 @@
         <v>3</v>
       </c>
       <c r="M57" s="1">
-        <v>0.011744415570473121</v>
+        <v>0.038369174357552716</v>
       </c>
       <c r="N57" s="1">
-        <v>2.6548647359614446</v>
+        <v>5.555550036607185</v>
       </c>
       <c r="O57" s="1">
-        <v>58.333333333333336</v>
+        <v>63.095238095238095</v>
       </c>
       <c r="P57" s="1">
         <v>37.631577254992756</v>
       </c>
       <c r="Q57" s="1">
-        <v>49.404761904761905</v>
+        <v>49.166666666666664</v>
       </c>
       <c r="R57" s="1">
-        <v>45.654761904761905</v>
+        <v>47.083333333333336</v>
       </c>
       <c r="S57" s="1" t="s">
         <v>101</v>
       </c>
       <c r="T57" s="1">
-        <v>23.7</v>
+        <v>25.13</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
@@ -5647,19 +5641,19 @@
         <v>0.97</v>
       </c>
       <c r="F58" s="3">
-        <v>-0.3219048525927221</v>
+        <v>-0.2939656832427451</v>
       </c>
       <c r="G58" s="3">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="H58" s="3">
-        <v>38.55</v>
+        <v>38.21</v>
       </c>
       <c r="I58" s="3">
-        <v>3.39</v>
+        <v>2.55</v>
       </c>
       <c r="J58" s="3">
-        <v>-0.02997595485040001</v>
+        <v>-0.027760195620194616</v>
       </c>
       <c r="K58" s="3" t="b">
         <v>1</v>
@@ -5668,28 +5662,28 @@
         <v>519</v>
       </c>
       <c r="M58" s="3">
-        <v>-0.3183371286182778</v>
+        <v>-0.28823735309516296</v>
       </c>
       <c r="N58" s="3">
-        <v>-30.353289682913648</v>
+        <v>-27.105102708664376</v>
       </c>
       <c r="O58" s="3">
-        <v>5.952380952380952</v>
+        <v>8.333333333333332</v>
       </c>
       <c r="P58" s="3">
         <v>41.76493344029593</v>
       </c>
       <c r="Q58" s="3">
-        <v>44.16666666666668</v>
+        <v>44.28571428571429</v>
       </c>
       <c r="R58" s="3">
-        <v>23.63095238095238</v>
+        <v>24.642857142857146</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>108</v>
       </c>
       <c r="T58" s="3">
-        <v>-35.58</v>
+        <v>-34.56</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
@@ -5709,19 +5703,19 @@
         <v>-4.45</v>
       </c>
       <c r="F59" s="3">
-        <v>-0.32374488987579514</v>
+        <v>-0.30642145796909237</v>
       </c>
       <c r="G59" s="3">
         <v>2.83</v>
       </c>
       <c r="H59" s="3">
-        <v>37.47</v>
+        <v>37</v>
       </c>
       <c r="I59" s="3">
-        <v>-34.26</v>
+        <v>-34.47</v>
       </c>
       <c r="J59" s="3">
-        <v>-0.03724195679252611</v>
+        <v>-0.035584909904490813</v>
       </c>
       <c r="K59" s="3" t="b">
         <v>0</v>
@@ -5730,10 +5724,10 @@
         <v>21</v>
       </c>
       <c r="M59" s="3">
-        <v>-0.31632564570166666</v>
+        <v>-0.2946429813735022</v>
       </c>
       <c r="N59" s="3">
-        <v>-30.152141391252542</v>
+        <v>-27.745665536498297</v>
       </c>
       <c r="O59" s="3">
         <v>7.142857142857142</v>
@@ -5742,7 +5736,7 @@
         <v>46.90217032437056</v>
       </c>
       <c r="Q59" s="3">
-        <v>24.4047619047619</v>
+        <v>24.64285714285714</v>
       </c>
       <c r="R59" s="3">
         <v>11.54761904761905</v>
@@ -5755,65 +5749,65 @@
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
+      <c r="A60" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="2">
+      <c r="B60" s="1">
         <v>4.35</v>
       </c>
-      <c r="C60" s="2">
+      <c r="C60" s="1">
         <v>54.761904761904766</v>
       </c>
-      <c r="D60" s="2">
+      <c r="D60" s="1">
         <v>2.1310344827586207</v>
       </c>
-      <c r="E60" s="2">
+      <c r="E60" s="1">
         <v>-0.53</v>
       </c>
-      <c r="F60" s="2">
-        <v>0.04971518130638918</v>
-      </c>
-      <c r="G60" s="2">
-        <v>1.2</v>
-      </c>
-      <c r="H60" s="2">
-        <v>36.67</v>
-      </c>
-      <c r="I60" s="2">
-        <v>8.33</v>
-      </c>
-      <c r="J60" s="2">
-        <v>0.004880893733414715</v>
-      </c>
-      <c r="K60" s="2" t="b">
+      <c r="F60" s="1">
+        <v>0.00011090848615603541</v>
+      </c>
+      <c r="G60" s="1">
+        <v>1.21</v>
+      </c>
+      <c r="H60" s="1">
+        <v>30.34</v>
+      </c>
+      <c r="I60" s="1">
+        <v>5.28</v>
+      </c>
+      <c r="J60" s="1">
+        <v>0.0026890684731403847</v>
+      </c>
+      <c r="K60" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L60" s="2">
-        <v>169</v>
-      </c>
-      <c r="M60" s="2">
-        <v>0.05052602766421743</v>
-      </c>
-      <c r="N60" s="2">
-        <v>6.533025945335871</v>
-      </c>
-      <c r="O60" s="2">
-        <v>64.28571428571429</v>
-      </c>
-      <c r="P60" s="2">
-        <v>8.239463877564281</v>
-      </c>
-      <c r="Q60" s="2">
-        <v>50.47619047619048</v>
-      </c>
-      <c r="R60" s="2">
-        <v>50.65476190476192</v>
-      </c>
-      <c r="S60" s="2" t="s">
+      <c r="L60" s="1">
+        <v>168</v>
+      </c>
+      <c r="M60" s="1">
+        <v>0.00146253694794507</v>
+      </c>
+      <c r="N60" s="1">
+        <v>1.8648862956464198</v>
+      </c>
+      <c r="O60" s="1">
+        <v>57.14285714285714</v>
+      </c>
+      <c r="P60" s="1">
+        <v>10.661929166819702</v>
+      </c>
+      <c r="Q60" s="1">
+        <v>48.57142857142857</v>
+      </c>
+      <c r="R60" s="1">
+        <v>48.15476190476191</v>
+      </c>
+      <c r="S60" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="T60" s="2">
-        <v>3.46</v>
+      <c r="T60" s="1">
+        <v>0.96</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
@@ -5833,49 +5827,49 @@
         <v>0.11</v>
       </c>
       <c r="F61" s="2">
-        <v>0.12227607146783773</v>
+        <v>0.12445396323271768</v>
       </c>
       <c r="G61" s="2">
         <v>0.2</v>
       </c>
       <c r="H61" s="2">
-        <v>49.68</v>
+        <v>51.61</v>
       </c>
       <c r="I61" s="2">
-        <v>11.96</v>
+        <v>12.36</v>
       </c>
       <c r="J61" s="2">
-        <v>0.0033351444135746124</v>
+        <v>0.002682390492088862</v>
       </c>
       <c r="K61" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L61" s="2">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="M61" s="2">
-        <v>0.11903268603652473</v>
+        <v>0.1193049024259023</v>
       </c>
       <c r="N61" s="2">
-        <v>13.383691782566597</v>
+        <v>13.649122843442147</v>
       </c>
       <c r="O61" s="2">
-        <v>71.42857142857143</v>
+        <v>72.61904761904762</v>
       </c>
       <c r="P61" s="2">
         <v>7.56622762341097</v>
       </c>
       <c r="Q61" s="2">
-        <v>55.83333333333333</v>
+        <v>56.3095238095238</v>
       </c>
       <c r="R61" s="2">
-        <v>53.333333333333336</v>
+        <v>53.80952380952381</v>
       </c>
       <c r="S61" s="2" t="s">
         <v>116</v>
       </c>
       <c r="T61" s="2">
-        <v>7.36</v>
+        <v>7.83</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
@@ -5889,55 +5883,55 @@
         <v>98.80952380952381</v>
       </c>
       <c r="D62" s="1">
-        <v>1.5592030790129048</v>
+        <v>1.5630518451437625</v>
       </c>
       <c r="E62" s="1">
         <v>-1.07</v>
       </c>
       <c r="F62" s="1">
-        <v>-0.16729067067498354</v>
+        <v>-0.11746136793860389</v>
       </c>
       <c r="G62" s="1">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="H62" s="1">
-        <v>47.66</v>
+        <v>48.48</v>
       </c>
       <c r="I62" s="1">
-        <v>47.45</v>
+        <v>47.41</v>
       </c>
       <c r="J62" s="1">
-        <v>-0.009834786261477414</v>
+        <v>-0.007594870900274268</v>
       </c>
       <c r="K62" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L62" s="1">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="M62" s="1">
-        <v>-0.16222288093855697</v>
+        <v>-0.10948032368804006</v>
       </c>
       <c r="N62" s="1">
-        <v>-14.741864914941566</v>
+        <v>-9.229399767952083</v>
       </c>
       <c r="O62" s="1">
-        <v>25</v>
+        <v>32.142857142857146</v>
       </c>
       <c r="P62" s="1">
         <v>39.10478556320163</v>
       </c>
       <c r="Q62" s="1">
-        <v>64.64285714285714</v>
+        <v>65.95238095238095</v>
       </c>
       <c r="R62" s="1">
-        <v>39.047619047619044</v>
+        <v>41.904761904761905</v>
       </c>
       <c r="S62" s="1" t="s">
         <v>117</v>
       </c>
       <c r="T62" s="1">
-        <v>-29.06</v>
+        <v>-26.2</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
@@ -5957,49 +5951,49 @@
         <v>1.52</v>
       </c>
       <c r="F63" s="1">
-        <v>-0.11320311703726427</v>
+        <v>-0.07534634601813338</v>
       </c>
       <c r="G63" s="1">
-        <v>1.02</v>
+        <v>0.98</v>
       </c>
       <c r="H63" s="1">
-        <v>40.31</v>
+        <v>48.54</v>
       </c>
       <c r="I63" s="1">
-        <v>-1.02</v>
+        <v>4.46</v>
       </c>
       <c r="J63" s="1">
-        <v>-0.02144312061000298</v>
+        <v>-0.021517666542102794</v>
       </c>
       <c r="K63" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L63" s="1">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="M63" s="1">
-        <v>-0.11312203240148144</v>
+        <v>-0.07547507253830377</v>
       </c>
       <c r="N63" s="1">
-        <v>-9.83178006123402</v>
+        <v>-5.828874652978454</v>
       </c>
       <c r="O63" s="1">
-        <v>30.952380952380953</v>
+        <v>40.476190476190474</v>
       </c>
       <c r="P63" s="1">
         <v>25.543467249515373</v>
       </c>
       <c r="Q63" s="1">
-        <v>42.97619047619048</v>
+        <v>46.9047619047619</v>
       </c>
       <c r="R63" s="1">
-        <v>33.21428571428571</v>
+        <v>35.95238095238095</v>
       </c>
       <c r="S63" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T63" s="1">
-        <v>-11.54</v>
+        <v>-8.8</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.25">
@@ -6019,49 +6013,49 @@
         <v>0.39</v>
       </c>
       <c r="F64" s="1">
-        <v>-0.08571379694836431</v>
+        <v>-0.0936857412895841</v>
       </c>
       <c r="G64" s="1">
         <v>0.36</v>
       </c>
       <c r="H64" s="1">
-        <v>37.33</v>
+        <v>36.13</v>
       </c>
       <c r="I64" s="1">
-        <v>-8.7</v>
+        <v>-9.18</v>
       </c>
       <c r="J64" s="1">
-        <v>-0.0030446808769919544</v>
+        <v>-0.004285269128497558</v>
       </c>
       <c r="K64" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L64" s="1">
-        <v>-100</v>
+        <v>-102</v>
       </c>
       <c r="M64" s="1">
-        <v>-0.08830850529341472</v>
+        <v>-0.09780498993503639</v>
       </c>
       <c r="N64" s="1">
-        <v>-7.350427350427351</v>
+        <v>-8.061866392651721</v>
       </c>
       <c r="O64" s="1">
-        <v>39.285714285714285</v>
+        <v>36.904761904761905</v>
       </c>
       <c r="P64" s="1">
-        <v>14.852676969550105</v>
+        <v>15.23755966827515</v>
       </c>
       <c r="Q64" s="1">
-        <v>40</v>
+        <v>39.52380952380952</v>
       </c>
       <c r="R64" s="1">
-        <v>36.60714285714286</v>
+        <v>35.77380952380953</v>
       </c>
       <c r="S64" s="1" t="s">
         <v>118</v>
       </c>
       <c r="T64" s="1">
-        <v>10.57</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.25">
@@ -6081,19 +6075,19 @@
         <v>2.09</v>
       </c>
       <c r="F65" s="2">
-        <v>0.17438602033740158</v>
+        <v>0.1274765267285201</v>
       </c>
       <c r="G65" s="2">
         <v>0.87</v>
       </c>
       <c r="H65" s="2">
-        <v>63.99</v>
+        <v>57.54</v>
       </c>
       <c r="I65" s="2">
-        <v>19.35</v>
+        <v>16.82</v>
       </c>
       <c r="J65" s="2">
-        <v>0.00810399776588151</v>
+        <v>0.008582770334031393</v>
       </c>
       <c r="K65" s="2" t="b">
         <v>0</v>
@@ -6102,28 +6096,28 @@
         <v>79</v>
       </c>
       <c r="M65" s="2">
-        <v>0.17385897020481322</v>
+        <v>0.12663980434741262</v>
       </c>
       <c r="N65" s="2">
-        <v>18.86632019939545</v>
+        <v>14.38261303559319</v>
       </c>
       <c r="O65" s="2">
-        <v>78.57142857142857</v>
+        <v>73.80952380952381</v>
       </c>
       <c r="P65" s="2">
         <v>11.000474713303552</v>
       </c>
       <c r="Q65" s="2">
-        <v>67.38095238095238</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="R65" s="2">
-        <v>60.416666666666664</v>
+        <v>59.34523809523809</v>
       </c>
       <c r="S65" s="2" t="s">
         <v>119</v>
       </c>
       <c r="T65" s="2">
-        <v>16.82</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
@@ -6143,19 +6137,19 @@
         <v>1.65</v>
       </c>
       <c r="F66" s="3">
-        <v>-0.30612036596776043</v>
+        <v>-0.28197481717561235</v>
       </c>
       <c r="G66" s="3">
-        <v>5.34</v>
+        <v>5.35</v>
       </c>
       <c r="H66" s="3">
-        <v>48.38</v>
+        <v>48.25</v>
       </c>
       <c r="I66" s="3">
-        <v>46.39</v>
+        <v>45.1</v>
       </c>
       <c r="J66" s="3">
-        <v>-0.021679354986217498</v>
+        <v>-0.01930812701154623</v>
       </c>
       <c r="K66" s="3" t="b">
         <v>0</v>
@@ -6164,28 +6158,28 @@
         <v>669</v>
       </c>
       <c r="M66" s="3">
-        <v>-0.2885250000028874</v>
+        <v>-0.25397679903855375</v>
       </c>
       <c r="N66" s="3">
-        <v>-27.37207682137461</v>
+        <v>-23.679047303003447</v>
       </c>
       <c r="O66" s="3">
-        <v>9.523809523809524</v>
+        <v>11.904761904761903</v>
       </c>
       <c r="P66" s="3">
         <v>56.49293299150161</v>
       </c>
       <c r="Q66" s="3">
-        <v>53.69047619047619</v>
+        <v>53.45238095238095</v>
       </c>
       <c r="R66" s="3">
-        <v>24.107142857142858</v>
+        <v>25.059523809523807</v>
       </c>
       <c r="S66" s="3" t="s">
         <v>101</v>
       </c>
       <c r="T66" s="3">
-        <v>-45.28</v>
+        <v>-44.33</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
@@ -6205,19 +6199,19 @@
         <v>-2.42</v>
       </c>
       <c r="F67" s="1">
-        <v>-0.2617366956570995</v>
+        <v>-0.2648852670764519</v>
       </c>
       <c r="G67" s="1">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H67" s="1">
-        <v>41.98</v>
+        <v>44.07</v>
       </c>
       <c r="I67" s="1">
-        <v>27.09</v>
+        <v>28.77</v>
       </c>
       <c r="J67" s="1">
-        <v>-0.008935193532327766</v>
+        <v>-0.00805694021004898</v>
       </c>
       <c r="K67" s="1" t="b">
         <v>0</v>
@@ -6226,90 +6220,90 @@
         <v>515</v>
       </c>
       <c r="M67" s="1">
-        <v>-0.2572364983711527</v>
+        <v>-0.2578053084670807</v>
       </c>
       <c r="N67" s="1">
-        <v>-24.243226658201145</v>
+        <v>-24.061898245856156</v>
       </c>
       <c r="O67" s="1">
-        <v>13.095238095238097</v>
+        <v>10.714285714285714</v>
       </c>
       <c r="P67" s="1">
         <v>31.85898471566022</v>
       </c>
       <c r="Q67" s="1">
-        <v>59.28571428571429</v>
+        <v>60.833333333333336</v>
       </c>
       <c r="R67" s="1">
-        <v>34.40476190476191</v>
+        <v>34.22619047619048</v>
       </c>
       <c r="S67" s="1" t="s">
         <v>109</v>
       </c>
       <c r="T67" s="1">
-        <v>-31.63</v>
+        <v>-31.81</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A68" s="2" t="s">
+      <c r="A68" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B68" s="2">
+      <c r="B68" s="1">
         <v>16.5</v>
       </c>
-      <c r="C68" s="2">
+      <c r="C68" s="1">
         <v>85.71428571428571</v>
       </c>
-      <c r="D68" s="2">
-        <v>-0.19272727272727272</v>
-      </c>
-      <c r="E68" s="2">
+      <c r="D68" s="1">
+        <v>-0.16666666666666666</v>
+      </c>
+      <c r="E68" s="1">
         <v>-1.75</v>
       </c>
-      <c r="F68" s="2">
-        <v>0.1538135254630747</v>
-      </c>
-      <c r="G68" s="2">
-        <v>0.99</v>
-      </c>
-      <c r="H68" s="2">
-        <v>46.03</v>
-      </c>
-      <c r="I68" s="2">
-        <v>-21.92</v>
-      </c>
-      <c r="J68" s="2">
-        <v>0.0173490916462733</v>
-      </c>
-      <c r="K68" s="2" t="b">
+      <c r="F68" s="1">
+        <v>0.11498925297726181</v>
+      </c>
+      <c r="G68" s="1">
+        <v>1</v>
+      </c>
+      <c r="H68" s="1">
+        <v>44.69</v>
+      </c>
+      <c r="I68" s="1">
+        <v>-22.62</v>
+      </c>
+      <c r="J68" s="1">
+        <v>0.0166310390803228</v>
+      </c>
+      <c r="K68" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L68" s="2">
+      <c r="L68" s="1">
         <v>-253</v>
       </c>
-      <c r="M68" s="2">
-        <v>0.15377298314518328</v>
-      </c>
-      <c r="N68" s="2">
-        <v>16.857721493432447</v>
-      </c>
-      <c r="O68" s="2">
-        <v>76.19047619047619</v>
-      </c>
-      <c r="P68" s="2">
+      <c r="M68" s="1">
+        <v>0.11498925297726181</v>
+      </c>
+      <c r="N68" s="1">
+        <v>13.217557898578114</v>
+      </c>
+      <c r="O68" s="1">
+        <v>71.42857142857143</v>
+      </c>
+      <c r="P68" s="1">
         <v>37.5868621181625</v>
       </c>
-      <c r="Q68" s="2">
-        <v>54.88095238095237</v>
-      </c>
-      <c r="R68" s="2">
-        <v>50.952380952380956</v>
-      </c>
-      <c r="S68" s="2" t="s">
+      <c r="Q68" s="1">
+        <v>55.35714285714285</v>
+      </c>
+      <c r="R68" s="1">
+        <v>49.82142857142858</v>
+      </c>
+      <c r="S68" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="T68" s="2">
-        <v>33.21</v>
+      <c r="T68" s="1">
+        <v>32.08</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
@@ -6329,19 +6323,19 @@
         <v>-0.51</v>
       </c>
       <c r="F69" s="1">
-        <v>-0.03535041439732235</v>
+        <v>-0.04998603396932634</v>
       </c>
       <c r="G69" s="1">
         <v>1.26</v>
       </c>
       <c r="H69" s="1">
-        <v>42.04</v>
+        <v>42.65</v>
       </c>
       <c r="I69" s="1">
-        <v>-5.62</v>
+        <v>-5.49</v>
       </c>
       <c r="J69" s="1">
-        <v>-0.002107307937633244</v>
+        <v>-0.0018231082887820442</v>
       </c>
       <c r="K69" s="1" t="b">
         <v>1</v>
@@ -6350,28 +6344,28 @@
         <v>3</v>
       </c>
       <c r="M69" s="1">
-        <v>-0.03429631413214562</v>
+        <v>-0.048312589207111345</v>
       </c>
       <c r="N69" s="1">
-        <v>-1.9492082343004389</v>
+        <v>-3.1126263198592152</v>
       </c>
       <c r="O69" s="1">
-        <v>46.42857142857143</v>
+        <v>47.61904761904761</v>
       </c>
       <c r="P69" s="1">
         <v>16.710870321490763</v>
       </c>
       <c r="Q69" s="1">
-        <v>51.785714285714285</v>
+        <v>52.14285714285714</v>
       </c>
       <c r="R69" s="1">
-        <v>45.595238095238095</v>
+        <v>45.95238095238095</v>
       </c>
       <c r="S69" s="1" t="s">
         <v>101</v>
       </c>
       <c r="T69" s="1">
-        <v>3.89</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
@@ -6391,49 +6385,49 @@
         <v>0.14</v>
       </c>
       <c r="F70" s="2">
-        <v>0.16490324960665417</v>
+        <v>0.14785845586039803</v>
       </c>
       <c r="G70" s="2">
         <v>0.33</v>
       </c>
       <c r="H70" s="2">
-        <v>55.1</v>
+        <v>60.63</v>
       </c>
       <c r="I70" s="2">
-        <v>8.24</v>
+        <v>10.31</v>
       </c>
       <c r="J70" s="2">
-        <v>0.012756661965465627</v>
+        <v>0.011556005234894402</v>
       </c>
       <c r="K70" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L70" s="2">
-        <v>-80</v>
+        <v>-81</v>
       </c>
       <c r="M70" s="2">
-        <v>0.16218691430792953</v>
+        <v>0.14354611743469015</v>
       </c>
       <c r="N70" s="2">
-        <v>17.69911460970707</v>
+        <v>16.073244344320926</v>
       </c>
       <c r="O70" s="2">
-        <v>77.38095238095238</v>
+        <v>78.57142857142857</v>
       </c>
       <c r="P70" s="2">
         <v>10.873073633899006</v>
       </c>
       <c r="Q70" s="2">
-        <v>61.54761904761905</v>
+        <v>63.0952380952381</v>
       </c>
       <c r="R70" s="2">
-        <v>57.55952380952381</v>
+        <v>57.916666666666664</v>
       </c>
       <c r="S70" s="2" t="s">
         <v>95</v>
       </c>
       <c r="T70" s="2">
-        <v>9.51</v>
+        <v>9.87</v>
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.25">
@@ -6453,49 +6447,49 @@
         <v>0.12</v>
       </c>
       <c r="F71" s="1">
-        <v>-0.11127216289829135</v>
+        <v>-0.10353830882476733</v>
       </c>
       <c r="G71" s="1">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="H71" s="1">
-        <v>53.22</v>
+        <v>56.52</v>
       </c>
       <c r="I71" s="1">
-        <v>-17.21</v>
+        <v>-15.71</v>
       </c>
       <c r="J71" s="1">
-        <v>-0.011945566606133252</v>
+        <v>-0.0115712870718021</v>
       </c>
       <c r="K71" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="1">
         <v>-42</v>
       </c>
       <c r="M71" s="1">
-        <v>-0.10936667395739497</v>
+        <v>-0.1005775988608485</v>
       </c>
       <c r="N71" s="1">
-        <v>-9.456244216825366</v>
+        <v>-8.339127285232923</v>
       </c>
       <c r="O71" s="1">
-        <v>32.142857142857146</v>
+        <v>34.523809523809526</v>
       </c>
       <c r="P71" s="1">
         <v>31.34692685044607</v>
       </c>
       <c r="Q71" s="1">
-        <v>47.85714285714286</v>
+        <v>48.92857142857144</v>
       </c>
       <c r="R71" s="1">
-        <v>33.98809523809525</v>
+        <v>34.82142857142857</v>
       </c>
       <c r="S71" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T71" s="1">
-        <v>4.54</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.25">
@@ -6515,49 +6509,49 @@
         <v>-0.35</v>
       </c>
       <c r="F72" s="2">
-        <v>0.3396255610793315</v>
+        <v>0.355611520246977</v>
       </c>
       <c r="G72" s="2">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="H72" s="2">
-        <v>63.84</v>
+        <v>70.34</v>
       </c>
       <c r="I72" s="2">
-        <v>18.34</v>
+        <v>21.31</v>
       </c>
       <c r="J72" s="2">
-        <v>0.017869700383916123</v>
+        <v>0.018940721330516136</v>
       </c>
       <c r="K72" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M72" s="2">
-        <v>0.33913905326463456</v>
+        <v>0.3547747978658695</v>
       </c>
       <c r="N72" s="2">
-        <v>35.39432850537759</v>
+        <v>37.196112387438866</v>
       </c>
       <c r="O72" s="2">
-        <v>92.85714285714286</v>
+        <v>91.66666666666666</v>
       </c>
       <c r="P72" s="2">
         <v>16.66857152537527</v>
       </c>
       <c r="Q72" s="2">
-        <v>66.07142857142857</v>
+        <v>67.5</v>
       </c>
       <c r="R72" s="2">
-        <v>61.1904761904762</v>
+        <v>61.07142857142857</v>
       </c>
       <c r="S72" s="2" t="s">
         <v>105</v>
       </c>
       <c r="T72" s="2">
-        <v>21.31</v>
+        <v>21.19</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.25">
@@ -6577,49 +6571,49 @@
         <v>0.45</v>
       </c>
       <c r="F73" s="1">
-        <v>-0.21388220785878986</v>
+        <v>-0.223425028502856</v>
       </c>
       <c r="G73" s="1">
         <v>1.1</v>
       </c>
       <c r="H73" s="1">
-        <v>33.22</v>
+        <v>35.3</v>
       </c>
       <c r="I73" s="1">
-        <v>-28.16</v>
+        <v>-27.91</v>
       </c>
       <c r="J73" s="1">
-        <v>-0.013981966974583135</v>
+        <v>-0.015605210804864569</v>
       </c>
       <c r="K73" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L73" s="1">
-        <v>-165</v>
+        <v>-168</v>
       </c>
       <c r="M73" s="1">
-        <v>-0.21347678467987574</v>
+        <v>-0.22278139590200408</v>
       </c>
       <c r="N73" s="1">
-        <v>-19.867255289073448</v>
+        <v>-20.559506989348492</v>
       </c>
       <c r="O73" s="1">
-        <v>20.238095238095237</v>
+        <v>16.666666666666664</v>
       </c>
       <c r="P73" s="1">
-        <v>23.53809998436916</v>
+        <v>24.466963086179547</v>
       </c>
       <c r="Q73" s="1">
-        <v>41.07142857142856</v>
+        <v>41.19047619047618</v>
       </c>
       <c r="R73" s="1">
-        <v>32.79761904761905</v>
+        <v>31.250000000000004</v>
       </c>
       <c r="S73" s="1" t="s">
         <v>121</v>
       </c>
       <c r="T73" s="1">
-        <v>0.79</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.25">
@@ -6639,19 +6633,19 @@
         <v>-3.73</v>
       </c>
       <c r="F74" s="1">
-        <v>-0.2458692580788271</v>
+        <v>-0.25077736060496936</v>
       </c>
       <c r="G74" s="1">
         <v>1.25</v>
       </c>
       <c r="H74" s="1">
-        <v>37.34</v>
+        <v>37.02</v>
       </c>
       <c r="I74" s="1">
-        <v>-6.2</v>
+        <v>-6.54</v>
       </c>
       <c r="J74" s="1">
-        <v>-0.021065123362163558</v>
+        <v>-0.020688608993560825</v>
       </c>
       <c r="K74" s="1" t="b">
         <v>0</v>
@@ -6660,28 +6654,28 @@
         <v>32</v>
       </c>
       <c r="M74" s="1">
-        <v>-0.2448557001315418</v>
+        <v>-0.24916827910283956</v>
       </c>
       <c r="N74" s="1">
-        <v>-23.00514683424005</v>
+        <v>-23.19819530943203</v>
       </c>
       <c r="O74" s="1">
-        <v>17.857142857142858</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="P74" s="1">
-        <v>28.58847656283351</v>
+        <v>28.76752600761915</v>
       </c>
       <c r="Q74" s="1">
-        <v>45.238095238095234</v>
+        <v>45.47619047619048</v>
       </c>
       <c r="R74" s="1">
-        <v>32.08333333333333</v>
+        <v>30.77380952380952</v>
       </c>
       <c r="S74" s="1" t="s">
         <v>101</v>
       </c>
       <c r="T74" s="1">
-        <v>-26.51</v>
+        <v>-27.82</v>
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
@@ -6701,19 +6695,19 @@
         <v>-0.07</v>
       </c>
       <c r="F75" s="3">
-        <v>-0.32767054861165523</v>
+        <v>-0.34233848521827903</v>
       </c>
       <c r="G75" s="3">
         <v>3.26</v>
       </c>
       <c r="H75" s="3">
-        <v>41</v>
+        <v>38.92</v>
       </c>
       <c r="I75" s="3">
-        <v>-32.23</v>
+        <v>-33.56</v>
       </c>
       <c r="J75" s="3">
-        <v>-0.024464045607845736</v>
+        <v>-0.02413302452368327</v>
       </c>
       <c r="K75" s="3" t="b">
         <v>0</v>
@@ -6722,10 +6716,10 @@
         <v>10</v>
       </c>
       <c r="M75" s="3">
-        <v>-0.318507984768196</v>
+        <v>-0.3277923884390256</v>
       </c>
       <c r="N75" s="3">
-        <v>-30.370375297905472</v>
+        <v>-31.060606243050643</v>
       </c>
       <c r="O75" s="3">
         <v>4.761904761904762</v>
@@ -6734,16 +6728,16 @@
         <v>51.49813033405746</v>
       </c>
       <c r="Q75" s="3">
-        <v>41.07142857142857</v>
+        <v>40.95238095238095</v>
       </c>
       <c r="R75" s="3">
-        <v>22.916666666666664</v>
+        <v>23.035714285714278</v>
       </c>
       <c r="S75" s="3" t="s">
         <v>107</v>
       </c>
       <c r="T75" s="3">
-        <v>-2.82</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
@@ -6763,19 +6757,19 @@
         <v>12.84</v>
       </c>
       <c r="F76" s="3">
-        <v>-0.09932836975139925</v>
+        <v>-0.03477008748832573</v>
       </c>
       <c r="G76" s="3">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="H76" s="3">
-        <v>30.36</v>
+        <v>29.92</v>
       </c>
       <c r="I76" s="3">
-        <v>37.09</v>
+        <v>36.77</v>
       </c>
       <c r="J76" s="3">
-        <v>-0.0245718939217082</v>
+        <v>-0.026809012666337013</v>
       </c>
       <c r="K76" s="3" t="b">
         <v>0</v>
@@ -6784,28 +6778,28 @@
         <v>42</v>
       </c>
       <c r="M76" s="3">
-        <v>-0.09973379293031337</v>
+        <v>-0.03534935682909246</v>
       </c>
       <c r="N76" s="3">
-        <v>-8.49295611411721</v>
+        <v>-1.8163030820573203</v>
       </c>
       <c r="O76" s="3">
-        <v>34.523809523809526</v>
+        <v>50</v>
       </c>
       <c r="P76" s="3">
         <v>29.799918858582526</v>
       </c>
       <c r="Q76" s="3">
-        <v>27.73809523809524</v>
+        <v>27.142857142857146</v>
       </c>
       <c r="R76" s="3">
-        <v>18.80952380952381</v>
+        <v>23.333333333333332</v>
       </c>
       <c r="S76" s="3" t="s">
         <v>123</v>
       </c>
       <c r="T76" s="3">
-        <v>-54.91</v>
+        <v>-50.39</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
@@ -6819,25 +6813,25 @@
         <v>45.23809523809524</v>
       </c>
       <c r="D77" s="2">
-        <v>3.3878504672897196</v>
+        <v>2.5327102803738315</v>
       </c>
       <c r="E77" s="2">
         <v>-9.21</v>
       </c>
       <c r="F77" s="2">
-        <v>0.5985399365044687</v>
+        <v>0.5855054885366315</v>
       </c>
       <c r="G77" s="2">
         <v>0.91</v>
       </c>
       <c r="H77" s="2">
-        <v>70.44</v>
+        <v>68.71</v>
       </c>
       <c r="I77" s="2">
-        <v>37.73</v>
+        <v>37.43</v>
       </c>
       <c r="J77" s="2">
-        <v>0.04313458390643316</v>
+        <v>0.0408141427825861</v>
       </c>
       <c r="K77" s="2" t="b">
         <v>1</v>
@@ -6846,28 +6840,28 @@
         <v>-5</v>
       </c>
       <c r="M77" s="2">
-        <v>0.598175055643446</v>
+        <v>0.5849262191958648</v>
       </c>
       <c r="N77" s="2">
-        <v>61.29792874325874</v>
+        <v>60.21125452043841</v>
       </c>
       <c r="O77" s="2">
-        <v>98.80952380952381</v>
+        <v>97.61904761904762</v>
       </c>
       <c r="P77" s="2">
         <v>18.71809072120826</v>
       </c>
       <c r="Q77" s="2">
-        <v>68.21428571428572</v>
+        <v>66.90476190476191</v>
       </c>
       <c r="R77" s="2">
-        <v>61.42857142857142</v>
+        <v>60.17857142857143</v>
       </c>
       <c r="S77" s="2" t="s">
         <v>108</v>
       </c>
       <c r="T77" s="2">
-        <v>12.83</v>
+        <v>11.58</v>
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
@@ -6887,19 +6881,19 @@
         <v>-3.54</v>
       </c>
       <c r="F78" s="2">
-        <v>0.27617531896803516</v>
+        <v>0.26017740358189306</v>
       </c>
       <c r="G78" s="2">
         <v>1.1</v>
       </c>
       <c r="H78" s="2">
-        <v>69.8</v>
+        <v>66.56</v>
       </c>
       <c r="I78" s="2">
-        <v>35.1</v>
+        <v>33.66</v>
       </c>
       <c r="J78" s="2">
-        <v>0.007659308923559309</v>
+        <v>0.008528919767391452</v>
       </c>
       <c r="K78" s="2" t="b">
         <v>1</v>
@@ -6908,28 +6902,28 @@
         <v>-2</v>
       </c>
       <c r="M78" s="2">
-        <v>0.2765807421469493</v>
+        <v>0.260821036182745</v>
       </c>
       <c r="N78" s="2">
-        <v>29.138497393609047</v>
+        <v>27.800736219126428</v>
       </c>
       <c r="O78" s="2">
-        <v>89.28571428571429</v>
+        <v>88.09523809523809</v>
       </c>
       <c r="P78" s="2">
         <v>16.006637557486414</v>
       </c>
       <c r="Q78" s="2">
-        <v>59.76190476190476</v>
+        <v>60.11904761904761</v>
       </c>
       <c r="R78" s="2">
-        <v>55.00000000000001</v>
+        <v>55.11904761904762</v>
       </c>
       <c r="S78" s="2" t="s">
         <v>106</v>
       </c>
       <c r="T78" s="2">
-        <v>6.83</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.25">
@@ -6949,19 +6943,19 @@
         <v>0.32</v>
       </c>
       <c r="F79" s="2">
-        <v>0.2079016452541409</v>
+        <v>0.23526566934943535</v>
       </c>
       <c r="G79" s="2">
         <v>0.82</v>
       </c>
       <c r="H79" s="2">
-        <v>45.88</v>
+        <v>54.21</v>
       </c>
       <c r="I79" s="2">
-        <v>9.56</v>
+        <v>12.06</v>
       </c>
       <c r="J79" s="2">
-        <v>0.013365622745193617</v>
+        <v>0.011809951162798203</v>
       </c>
       <c r="K79" s="2" t="b">
         <v>0</v>
@@ -6970,28 +6964,28 @@
         <v>6</v>
       </c>
       <c r="M79" s="2">
-        <v>0.20717188353209548</v>
+        <v>0.2341071306679019</v>
       </c>
       <c r="N79" s="2">
-        <v>22.197611532123666</v>
+        <v>25.129345667642113</v>
       </c>
       <c r="O79" s="2">
-        <v>80.95238095238095</v>
+        <v>86.90476190476191</v>
       </c>
       <c r="P79" s="2">
         <v>11.616065285425229</v>
       </c>
       <c r="Q79" s="2">
-        <v>54.523809523809526</v>
+        <v>57.5</v>
       </c>
       <c r="R79" s="2">
-        <v>54.523809523809526</v>
+        <v>56.30952380952381</v>
       </c>
       <c r="S79" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T79" s="2">
-        <v>14.65</v>
+        <v>16.43</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.25">
@@ -7011,49 +7005,49 @@
         <v>0.86</v>
       </c>
       <c r="F80" s="2">
-        <v>0.14613415540886288</v>
+        <v>0.09779666499891404</v>
       </c>
       <c r="G80" s="2">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="H80" s="2">
-        <v>56.55</v>
+        <v>51.46</v>
       </c>
       <c r="I80" s="2">
-        <v>12.12</v>
+        <v>10.81</v>
       </c>
       <c r="J80" s="2">
-        <v>0.0055381350409172215</v>
+        <v>0.005145519256080646</v>
       </c>
       <c r="K80" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L80" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="M80" s="2">
-        <v>0.14516113977946898</v>
+        <v>0.09631631001695462</v>
       </c>
       <c r="N80" s="2">
-        <v>15.996537156861027</v>
+        <v>11.350263602547383</v>
       </c>
       <c r="O80" s="2">
-        <v>75</v>
+        <v>69.04761904761905</v>
       </c>
       <c r="P80" s="2">
         <v>6.707278396222185</v>
       </c>
       <c r="Q80" s="2">
-        <v>60.59523809523809</v>
+        <v>58.333333333333336</v>
       </c>
       <c r="R80" s="2">
-        <v>56.42857142857142</v>
+        <v>54.76190476190476</v>
       </c>
       <c r="S80" s="2" t="s">
         <v>109</v>
       </c>
       <c r="T80" s="2">
-        <v>6</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.25">
@@ -7073,49 +7067,49 @@
         <v>-1.2</v>
       </c>
       <c r="F81" s="2">
-        <v>0.08875571734637322</v>
+        <v>0.03644260659650999</v>
       </c>
       <c r="G81" s="2">
         <v>1.01</v>
       </c>
       <c r="H81" s="2">
-        <v>48.12</v>
+        <v>45.95</v>
       </c>
       <c r="I81" s="2">
-        <v>10.26</v>
+        <v>9.51</v>
       </c>
       <c r="J81" s="2">
-        <v>0.005946364182234916</v>
+        <v>0.005047171522951603</v>
       </c>
       <c r="K81" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L81" s="2">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="M81" s="2">
-        <v>0.08879625966426463</v>
+        <v>0.036506969856595184</v>
       </c>
       <c r="N81" s="2">
-        <v>10.36004914534059</v>
+        <v>5.369329586511442</v>
       </c>
       <c r="O81" s="2">
-        <v>66.66666666666666</v>
+        <v>61.904761904761905</v>
       </c>
       <c r="P81" s="2">
         <v>6.716293473999743</v>
       </c>
       <c r="Q81" s="2">
-        <v>56.9047619047619</v>
+        <v>55.95238095238095</v>
       </c>
       <c r="R81" s="2">
-        <v>53.03571428571428</v>
+        <v>51.488095238095234</v>
       </c>
       <c r="S81" s="2" t="s">
         <v>115</v>
       </c>
       <c r="T81" s="2">
-        <v>7.73</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.25">
@@ -7129,37 +7123,37 @@
         <v>75</v>
       </c>
       <c r="D82" s="2">
-        <v>-0.008027522935779848</v>
+        <v>-0.006880733944954185</v>
       </c>
       <c r="E82" s="2">
         <v>0.23</v>
       </c>
       <c r="F82" s="2">
-        <v>0.10275826738458416</v>
+        <v>0.09327502320462885</v>
       </c>
       <c r="G82" s="2">
         <v>1.06</v>
       </c>
       <c r="H82" s="2">
-        <v>61.05</v>
+        <v>63.09</v>
       </c>
       <c r="I82" s="2">
-        <v>15.87</v>
+        <v>16.65</v>
       </c>
       <c r="J82" s="2">
-        <v>0.009615572553266824</v>
+        <v>0.008846273422963275</v>
       </c>
       <c r="K82" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" s="2">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="M82" s="2">
-        <v>0.10300152129193263</v>
+        <v>0.09366120276514</v>
       </c>
       <c r="N82" s="2">
-        <v>11.780575308107379</v>
+        <v>11.084752877365919</v>
       </c>
       <c r="O82" s="2">
         <v>67.85714285714286</v>
@@ -7168,7 +7162,7 @@
         <v>12.706223591210087</v>
       </c>
       <c r="Q82" s="2">
-        <v>61.54761904761905</v>
+        <v>61.66666666666667</v>
       </c>
       <c r="R82" s="2">
         <v>52.14285714285714</v>
@@ -7191,55 +7185,55 @@
         <v>92.85714285714286</v>
       </c>
       <c r="D83" s="1">
-        <v>-2.3420391762933197</v>
+        <v>-2.3415369161225517</v>
       </c>
       <c r="E83" s="1">
         <v>2.31</v>
       </c>
       <c r="F83" s="1">
-        <v>-0.08552630423763508</v>
+        <v>-0.10393878933499942</v>
       </c>
       <c r="G83" s="1">
         <v>1.19</v>
       </c>
       <c r="H83" s="1">
-        <v>51.07</v>
+        <v>52.82</v>
       </c>
       <c r="I83" s="1">
-        <v>1.64</v>
+        <v>2.24</v>
       </c>
       <c r="J83" s="1">
-        <v>-0.005899393486030319</v>
+        <v>-0.005985794666373905</v>
       </c>
       <c r="K83" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L83" s="1">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="M83" s="1">
-        <v>-0.08475600019769824</v>
+        <v>-0.10271588739338078</v>
       </c>
       <c r="N83" s="1">
-        <v>-6.995176840855699</v>
+        <v>-8.552956138486152</v>
       </c>
       <c r="O83" s="1">
-        <v>40.476190476190474</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="P83" s="1">
         <v>20.22353911360907</v>
       </c>
       <c r="Q83" s="1">
-        <v>48.80952380952382</v>
+        <v>48.333333333333336</v>
       </c>
       <c r="R83" s="1">
-        <v>37.440476190476204</v>
+        <v>35.17857142857143</v>
       </c>
       <c r="S83" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T83" s="1">
-        <v>-9.33</v>
+        <v>-11.59</v>
       </c>
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.25">
@@ -7259,49 +7253,49 @@
         <v>0.25</v>
       </c>
       <c r="F84" s="1">
-        <v>-0.09873019265286587</v>
+        <v>-0.11599547572192025</v>
       </c>
       <c r="G84" s="1">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="H84" s="1">
-        <v>46.94</v>
+        <v>44.08</v>
       </c>
       <c r="I84" s="1">
-        <v>15.05</v>
+        <v>13.25</v>
       </c>
       <c r="J84" s="1">
-        <v>-0.005203554523688541</v>
+        <v>-0.004470920292175302</v>
       </c>
       <c r="K84" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L84" s="1">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="M84" s="1">
-        <v>-0.0988518196065401</v>
+        <v>-0.11612420224209064</v>
       </c>
       <c r="N84" s="1">
-        <v>-8.404758781739888</v>
+        <v>-9.89378762335714</v>
       </c>
       <c r="O84" s="1">
-        <v>36.904761904761905</v>
+        <v>29.761904761904763</v>
       </c>
       <c r="P84" s="1">
         <v>17.353844275841347</v>
       </c>
       <c r="Q84" s="1">
-        <v>50.95238095238095</v>
+        <v>50.11904761904762</v>
       </c>
       <c r="R84" s="1">
-        <v>37.67857142857142</v>
+        <v>35.535714285714285</v>
       </c>
       <c r="S84" s="1" t="s">
         <v>132</v>
       </c>
       <c r="T84" s="1">
-        <v>-18.97</v>
+        <v>-21.11</v>
       </c>
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.25">
@@ -7315,55 +7309,55 @@
         <v>80.95238095238095</v>
       </c>
       <c r="D85" s="1">
-        <v>-0.31902834008097164</v>
+        <v>-0.32145748987854245</v>
       </c>
       <c r="E85" s="1">
         <v>0.61</v>
       </c>
       <c r="F85" s="1">
-        <v>0.04775813285066943</v>
+        <v>0.03350004667964804</v>
       </c>
       <c r="G85" s="1">
         <v>0.95</v>
       </c>
       <c r="H85" s="1">
-        <v>46.97</v>
+        <v>32.1</v>
       </c>
       <c r="I85" s="1">
-        <v>10.69</v>
+        <v>6.97</v>
       </c>
       <c r="J85" s="1">
-        <v>0.00249809106312259</v>
+        <v>0.0015280819620693672</v>
       </c>
       <c r="K85" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L85" s="1">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="M85" s="1">
-        <v>0.04755542126121237</v>
+        <v>0.03317823037922207</v>
       </c>
       <c r="N85" s="1">
-        <v>6.2359653050353545</v>
+        <v>5.036455638774131</v>
       </c>
       <c r="O85" s="1">
-        <v>63.095238095238095</v>
+        <v>60.71428571428571</v>
       </c>
       <c r="P85" s="1">
-        <v>8.573177934912337</v>
+        <v>9.561516372520778</v>
       </c>
       <c r="Q85" s="1">
-        <v>53.69047619047619</v>
+        <v>47.85714285714286</v>
       </c>
       <c r="R85" s="1">
-        <v>49.583333333333336</v>
+        <v>48.75</v>
       </c>
       <c r="S85" s="1" t="s">
         <v>105</v>
       </c>
       <c r="T85" s="1">
-        <v>2.82</v>
+        <v>1.98</v>
       </c>
     </row>
   </sheetData>
@@ -7390,7 +7384,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>49.404761904761905</v>
+        <v>48.45238095238095</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -7398,7 +7392,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>43.095238095238095</v>
+        <v>48.69047619047619</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7406,7 +7400,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>54.166666666666664</v>
+        <v>54.523809523809526</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -7414,7 +7408,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>33.511904761904766</v>
+        <v>33.035714285714285</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -7422,7 +7416,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>36.25</v>
+        <v>37.67857142857143</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7430,7 +7424,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>53.92857142857143</v>
+        <v>55.00000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -7438,7 +7432,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>39.464285714285715</v>
+        <v>40.6547619047619</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -7446,7 +7440,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>59.345238095238095</v>
+        <v>60.05952380952382</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -7454,7 +7448,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>47.738095238095234</v>
+        <v>49.16666666666667</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -7462,7 +7456,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>58.80952380952381</v>
+        <v>59.16666666666667</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -7470,7 +7464,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>62.797619047619044</v>
+        <v>62.916666666666664</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -7478,7 +7472,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>38.33333333333333</v>
+        <v>37.97619047619047</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -7486,7 +7480,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>60.654761904761905</v>
+        <v>61.13095238095239</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -7494,7 +7488,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>20.535714285714285</v>
+        <v>23.273809523809526</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -7502,7 +7496,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>14.821428571428566</v>
+        <v>14.464285714285708</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -7510,7 +7504,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>29.821428571428577</v>
+        <v>30.535714285714292</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -7518,7 +7512,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>23.333333333333343</v>
+        <v>23.214285714285722</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -7526,7 +7520,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>53.27380952380953</v>
+        <v>53.63095238095239</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -7534,7 +7528,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>56.54761904761905</v>
+        <v>56.19047619047619</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -7542,7 +7536,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>22.5</v>
+        <v>21.904761904761905</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -7550,7 +7544,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>35.476190476190474</v>
+        <v>34.88095238095238</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -7566,7 +7560,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>27.85714285714286</v>
+        <v>30.41666666666667</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -7574,7 +7568,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>5.178571428571429</v>
+        <v>5.773809523809524</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -7582,7 +7576,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>-2.7976190476190483</v>
+        <v>-2.321428571428573</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -7590,7 +7584,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>0.17857142857142705</v>
+        <v>-0.2976190476190492</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -7598,7 +7592,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>35.89285714285714</v>
+        <v>33.63095238095238</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -7606,7 +7600,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>46.8452380952381</v>
+        <v>43.273809523809526</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -7614,7 +7608,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>47.55952380952381</v>
+        <v>44.226190476190474</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -7622,7 +7616,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>39.46428571428573</v>
+        <v>40.41666666666667</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -7630,7 +7624,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>30.05952380952381</v>
+        <v>30.41666666666667</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -7638,7 +7632,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>60.238095238095234</v>
+        <v>59.761904761904766</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -7646,7 +7640,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>38.09523809523809</v>
+        <v>35.83333333333333</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -7654,7 +7648,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>42.023809523809526</v>
+        <v>39.16666666666667</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -7662,7 +7656,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>43.98809523809524</v>
+        <v>42.20238095238096</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -7670,7 +7664,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>54.76190476190477</v>
+        <v>52.85714285714286</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -7678,7 +7672,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>64.94047619047619</v>
+        <v>65.6547619047619</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -7686,7 +7680,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>43.273809523809526</v>
+        <v>41.13095238095239</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -7702,7 +7696,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>14.523809523809518</v>
+        <v>13.69047619047619</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -7718,7 +7712,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>58.51190476190476</v>
+        <v>58.98809523809524</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -7726,7 +7720,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>52.5</v>
+        <v>52.97619047619048</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -7734,7 +7728,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>41.726190476190474</v>
+        <v>40.41666666666667</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -7742,7 +7736,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>27.976190476190474</v>
+        <v>27.26190476190476</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -7750,7 +7744,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>44.166666666666664</v>
+        <v>45.714285714285715</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -7758,7 +7752,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>53.80952380952382</v>
+        <v>55.95238095238097</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -7766,7 +7760,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>51.13095238095238</v>
+        <v>53.86904761904761</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -7774,7 +7768,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>20.05952380952381</v>
+        <v>20.535714285714285</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -7782,7 +7776,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>42.91666666666666</v>
+        <v>42.55952380952381</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -7790,7 +7784,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>22.85714285714286</v>
+        <v>22.142857142857146</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -7798,7 +7792,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>47.5</v>
+        <v>45.83333333333334</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -7806,7 +7800,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>32.5</v>
+        <v>31.488095238095237</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -7814,7 +7808,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>38.214285714285715</v>
+        <v>39.04761904761906</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -7822,7 +7816,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>26.54761904761905</v>
+        <v>27.976190476190474</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -7830,7 +7824,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>45.654761904761905</v>
+        <v>47.083333333333336</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -7838,7 +7832,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>23.63095238095238</v>
+        <v>24.642857142857146</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -7854,7 +7848,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>50.65476190476192</v>
+        <v>48.15476190476191</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -7862,7 +7856,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>53.333333333333336</v>
+        <v>53.80952380952381</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -7870,7 +7864,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>39.047619047619044</v>
+        <v>41.904761904761905</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -7878,7 +7872,7 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>33.21428571428571</v>
+        <v>35.95238095238095</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -7886,7 +7880,7 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>36.60714285714286</v>
+        <v>35.77380952380953</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -7894,7 +7888,7 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>60.416666666666664</v>
+        <v>59.34523809523809</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -7902,7 +7896,7 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>24.107142857142858</v>
+        <v>25.059523809523807</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -7910,7 +7904,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>34.40476190476191</v>
+        <v>34.22619047619048</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -7918,7 +7912,7 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>50.952380952380956</v>
+        <v>49.82142857142858</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -7926,7 +7920,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>45.595238095238095</v>
+        <v>45.95238095238095</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -7934,7 +7928,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>57.55952380952381</v>
+        <v>57.916666666666664</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -7942,7 +7936,7 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>33.98809523809525</v>
+        <v>34.82142857142857</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -7950,7 +7944,7 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>61.1904761904762</v>
+        <v>61.07142857142857</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -7958,7 +7952,7 @@
         <v>72</v>
       </c>
       <c r="B73">
-        <v>32.79761904761905</v>
+        <v>31.250000000000004</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -7966,7 +7960,7 @@
         <v>73</v>
       </c>
       <c r="B74">
-        <v>32.08333333333333</v>
+        <v>30.77380952380952</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -7974,7 +7968,7 @@
         <v>74</v>
       </c>
       <c r="B75">
-        <v>22.916666666666664</v>
+        <v>23.035714285714278</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -7982,7 +7976,7 @@
         <v>122</v>
       </c>
       <c r="B76">
-        <v>18.80952380952381</v>
+        <v>23.333333333333332</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -7990,7 +7984,7 @@
         <v>124</v>
       </c>
       <c r="B77">
-        <v>61.42857142857142</v>
+        <v>60.17857142857143</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -7998,7 +7992,7 @@
         <v>125</v>
       </c>
       <c r="B78">
-        <v>55.00000000000001</v>
+        <v>55.11904761904762</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -8006,7 +8000,7 @@
         <v>126</v>
       </c>
       <c r="B79">
-        <v>54.523809523809526</v>
+        <v>56.30952380952381</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -8014,7 +8008,7 @@
         <v>127</v>
       </c>
       <c r="B80">
-        <v>56.42857142857142</v>
+        <v>54.76190476190476</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -8022,7 +8016,7 @@
         <v>128</v>
       </c>
       <c r="B81">
-        <v>53.03571428571428</v>
+        <v>51.488095238095234</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -8038,7 +8032,7 @@
         <v>130</v>
       </c>
       <c r="B83">
-        <v>37.440476190476204</v>
+        <v>35.17857142857143</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -8046,7 +8040,7 @@
         <v>131</v>
       </c>
       <c r="B84">
-        <v>37.67857142857142</v>
+        <v>35.535714285714285</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -8054,7 +8048,7 @@
         <v>133</v>
       </c>
       <c r="B85">
-        <v>49.583333333333336</v>
+        <v>48.75</v>
       </c>
     </row>
   </sheetData>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -427,7 +427,7 @@
     <t>_date_</t>
   </si>
   <si>
-    <t>2026-09-17</t>
+    <t>2026-09-18</t>
   </si>
   <si>
     <t>Criteria</t>
@@ -694,13 +694,13 @@
     <t>Momentum Breakout, Market Leader, Volume Spike</t>
   </si>
   <si>
+    <t>Institutional Buying</t>
+  </si>
+  <si>
     <t>Momentum Breakout, Market Leader</t>
   </si>
   <si>
     <t>Momentum Breakout, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Institutional Buying</t>
   </si>
   <si>
     <t>Momentum Breakout</t>
@@ -1399,7 +1399,7 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>65.6547619047619</v>
+        <v>65.35714285714286</v>
       </c>
       <c r="C2" t="s">
         <v>221</v>
@@ -1432,7 +1432,7 @@
         <v>71</v>
       </c>
       <c r="B5">
-        <v>61.07142857142857</v>
+        <v>60.952380952380956</v>
       </c>
       <c r="C5" t="s">
         <v>221</v>
@@ -1451,35 +1451,35 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="B7">
-        <v>60.05952380952382</v>
+        <v>60.11904761904761</v>
       </c>
       <c r="C7" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="B8">
-        <v>59.761904761904766</v>
+        <v>59.82142857142857</v>
       </c>
       <c r="C8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="B9">
-        <v>59.34523809523809</v>
+        <v>59.702380952380956</v>
       </c>
       <c r="C9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1490,7 +1490,7 @@
         <v>59.16666666666667</v>
       </c>
       <c r="C10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1498,73 +1498,73 @@
         <v>42</v>
       </c>
       <c r="B11">
-        <v>58.98809523809524</v>
+        <v>58.273809523809526</v>
       </c>
       <c r="C11" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>126</v>
+        <v>69</v>
       </c>
       <c r="B12">
-        <v>56.30952380952381</v>
+        <v>57.916666666666664</v>
       </c>
       <c r="C12" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="B13">
-        <v>56.19047619047619</v>
+        <v>55.95238095238097</v>
       </c>
       <c r="C13" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="B14">
-        <v>55.95238095238097</v>
+        <v>55.83333333333333</v>
       </c>
       <c r="C14" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>125</v>
+        <v>6</v>
       </c>
       <c r="B15">
-        <v>55.11904761904762</v>
+        <v>55.23809523809524</v>
       </c>
       <c r="C15" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>6</v>
+        <v>125</v>
       </c>
       <c r="B16">
-        <v>55.00000000000001</v>
+        <v>55.23809523809524</v>
       </c>
       <c r="C16" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>127</v>
+        <v>22</v>
       </c>
       <c r="B17">
-        <v>54.76190476190476</v>
+        <v>55.05952380952381</v>
       </c>
       <c r="C17" t="s">
         <v>226</v>
@@ -1575,7 +1575,7 @@
         <v>3</v>
       </c>
       <c r="B18">
-        <v>54.523809523809526</v>
+        <v>54.58333333333333</v>
       </c>
       <c r="C18" t="s">
         <v>222</v>
@@ -1583,10 +1583,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>60</v>
+        <v>126</v>
       </c>
       <c r="B19">
-        <v>53.80952380952381</v>
+        <v>54.28571428571429</v>
       </c>
       <c r="C19" t="s">
         <v>226</v>
@@ -1594,13 +1594,13 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>127</v>
       </c>
       <c r="B20">
-        <v>53.03571428571429</v>
+        <v>53.57142857142857</v>
       </c>
       <c r="C20" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -1608,7 +1608,7 @@
         <v>36</v>
       </c>
       <c r="B21">
-        <v>52.85714285714286</v>
+        <v>53.21428571428571</v>
       </c>
       <c r="C21" t="s">
         <v>227</v>
@@ -1616,57 +1616,57 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>129</v>
+        <v>60</v>
       </c>
       <c r="B22">
-        <v>52.14285714285714</v>
+        <v>52.976190476190474</v>
       </c>
       <c r="C22" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B23">
-        <v>51.488095238095234</v>
+        <v>51.845238095238095</v>
       </c>
       <c r="C23" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>133</v>
+        <v>2</v>
       </c>
       <c r="B24">
-        <v>48.75</v>
+        <v>50.23809523809524</v>
       </c>
       <c r="C24" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="B25">
-        <v>48.69047619047619</v>
+        <v>49.82142857142857</v>
       </c>
       <c r="C25" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>59</v>
+        <v>133</v>
       </c>
       <c r="B26">
-        <v>48.15476190476191</v>
+        <v>49.345238095238095</v>
       </c>
       <c r="C26" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -1674,54 +1674,54 @@
         <v>56</v>
       </c>
       <c r="B27">
-        <v>47.083333333333336</v>
+        <v>47.67857142857143</v>
       </c>
       <c r="C27" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="B28">
-        <v>45.95238095238095</v>
+        <v>46.607142857142854</v>
       </c>
       <c r="C28" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="B29">
-        <v>45.83333333333334</v>
+        <v>46.30952380952381</v>
       </c>
       <c r="C29" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B30">
-        <v>45.714285714285715</v>
+        <v>45.833333333333336</v>
       </c>
       <c r="C30" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="B31">
-        <v>44.226190476190474</v>
+        <v>45.65476190476191</v>
       </c>
       <c r="C31" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -1729,21 +1729,21 @@
         <v>28</v>
       </c>
       <c r="B32">
-        <v>43.273809523809526</v>
+        <v>43.75</v>
       </c>
       <c r="C32" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B33">
-        <v>43.035714285714285</v>
+        <v>43.095238095238095</v>
       </c>
       <c r="C33" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -1751,10 +1751,10 @@
         <v>50</v>
       </c>
       <c r="B34">
-        <v>42.55952380952381</v>
+        <v>42.91666666666666</v>
       </c>
       <c r="C34" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -1762,65 +1762,65 @@
         <v>61</v>
       </c>
       <c r="B35">
-        <v>41.904761904761905</v>
+        <v>42.73809523809524</v>
       </c>
       <c r="C35" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B36">
-        <v>41.13095238095239</v>
+        <v>41.964285714285715</v>
       </c>
       <c r="C36" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="B37">
-        <v>40.6547619047619</v>
+        <v>41.36904761904762</v>
       </c>
       <c r="C37" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="B38">
-        <v>40.41666666666667</v>
+        <v>40.833333333333336</v>
       </c>
       <c r="C38" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B39">
-        <v>40.41666666666667</v>
+        <v>40.773809523809526</v>
       </c>
       <c r="C39" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="B40">
-        <v>39.04761904761906</v>
+        <v>39.107142857142854</v>
       </c>
       <c r="C40" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -1828,21 +1828,21 @@
         <v>12</v>
       </c>
       <c r="B41">
-        <v>37.97619047619047</v>
+        <v>38.33333333333333</v>
       </c>
       <c r="C41" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="B42">
-        <v>35.95238095238095</v>
+        <v>38.03571428571429</v>
       </c>
       <c r="C42" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -1850,62 +1850,62 @@
         <v>33</v>
       </c>
       <c r="B43">
-        <v>35.83333333333333</v>
+        <v>37.5</v>
       </c>
       <c r="C43" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>63</v>
+        <v>131</v>
       </c>
       <c r="B44">
-        <v>35.77380952380953</v>
+        <v>36.964285714285715</v>
       </c>
       <c r="C44" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B45">
-        <v>35.535714285714285</v>
+        <v>36.8452380952381</v>
       </c>
       <c r="C45" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>130</v>
+        <v>27</v>
       </c>
       <c r="B46">
-        <v>35.17857142857143</v>
+        <v>35.29761904761905</v>
       </c>
       <c r="C46" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B47">
-        <v>34.88095238095238</v>
+        <v>35.05952380952381</v>
       </c>
       <c r="C47" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B48">
-        <v>34.82142857142857</v>
+        <v>34.583333333333336</v>
       </c>
       <c r="C48" t="s">
         <v>229</v>
@@ -1913,35 +1913,35 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="B49">
-        <v>34.22619047619048</v>
+        <v>33.45238095238095</v>
       </c>
       <c r="C49" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="B50">
-        <v>33.63095238095238</v>
+        <v>33.392857142857146</v>
       </c>
       <c r="C50" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B51">
-        <v>33.035714285714285</v>
+        <v>33.03571428571429</v>
       </c>
       <c r="C51" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>
@@ -2175,111 +2175,111 @@
         <v>-2.08</v>
       </c>
       <c r="F2" s="1">
-        <v>0.13917432403740498</v>
+        <v>0.14261768239983702</v>
       </c>
       <c r="G2" s="1">
         <v>0.21</v>
       </c>
       <c r="H2" s="1">
-        <v>53.83</v>
+        <v>53.14</v>
       </c>
       <c r="I2" s="1">
-        <v>11.62</v>
+        <v>11.32</v>
       </c>
       <c r="J2" s="1">
-        <v>0.018274591018596964</v>
+        <v>0.01738299261332833</v>
       </c>
       <c r="K2" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>-460</v>
+        <v>-461</v>
       </c>
       <c r="M2" s="1">
-        <v>0.1340896264906748</v>
+        <v>0.1173575295885716</v>
       </c>
       <c r="N2" s="1">
-        <v>15.127595249919409</v>
+        <v>16.008240656485683</v>
       </c>
       <c r="O2" s="1">
-        <v>77.38095238095238</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="P2" s="1">
         <v>16.29652721982991</v>
       </c>
       <c r="Q2" s="1">
-        <v>52.97619047619047</v>
+        <v>51.785714285714285</v>
       </c>
       <c r="R2" s="1">
-        <v>48.45238095238095</v>
+        <v>46.666666666666664</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>94</v>
       </c>
       <c r="T2" s="1">
-        <v>28.64</v>
+        <v>26.85</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="2">
         <v>3.9</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="2">
         <v>53.57142857142857</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="2">
         <v>26.710256410256406</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="2">
         <v>3.63</v>
       </c>
-      <c r="F3" s="1">
-        <v>-0.016313119383390345</v>
-      </c>
-      <c r="G3" s="1">
-        <v>2.46</v>
-      </c>
-      <c r="H3" s="1">
-        <v>57.83</v>
-      </c>
-      <c r="I3" s="1">
-        <v>47.4</v>
-      </c>
-      <c r="J3" s="1">
-        <v>-0.007137324520773477</v>
-      </c>
-      <c r="K3" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" s="1">
+      <c r="F3" s="2">
+        <v>-0.026096101709148514</v>
+      </c>
+      <c r="G3" s="2">
+        <v>2.47</v>
+      </c>
+      <c r="H3" s="2">
+        <v>62.78</v>
+      </c>
+      <c r="I3" s="2">
+        <v>54.45</v>
+      </c>
+      <c r="J3" s="2">
+        <v>-0.002934949024288785</v>
+      </c>
+      <c r="K3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" s="2">
         <v>858</v>
       </c>
-      <c r="M3" s="1">
-        <v>-0.0069160834109522895</v>
-      </c>
-      <c r="N3" s="1">
-        <v>1.0270242597566883</v>
-      </c>
-      <c r="O3" s="1">
-        <v>55.952380952380956</v>
-      </c>
-      <c r="P3" s="1">
+      <c r="M3" s="2">
+        <v>0.020906967445990965</v>
+      </c>
+      <c r="N3" s="2">
+        <v>6.36318444222764</v>
+      </c>
+      <c r="O3" s="2">
+        <v>58.333333333333336</v>
+      </c>
+      <c r="P3" s="2">
         <v>26.053946839070953</v>
       </c>
-      <c r="Q3" s="1">
-        <v>65.35714285714286</v>
-      </c>
-      <c r="R3" s="1">
-        <v>48.69047619047619</v>
-      </c>
-      <c r="S3" s="1" t="s">
+      <c r="Q3" s="2">
+        <v>67.61904761904762</v>
+      </c>
+      <c r="R3" s="2">
+        <v>50.23809523809524</v>
+      </c>
+      <c r="S3" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="T3" s="1">
-        <v>-18.38</v>
+      <c r="T3" s="2">
+        <v>-16.84</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -2299,31 +2299,31 @@
         <v>6.35</v>
       </c>
       <c r="F4" s="2">
-        <v>0.36953368077022036</v>
+        <v>0.3889886085759751</v>
       </c>
       <c r="G4" s="2">
         <v>1.35</v>
       </c>
       <c r="H4" s="2">
-        <v>55.35</v>
+        <v>57.13</v>
       </c>
       <c r="I4" s="2">
-        <v>50.24</v>
+        <v>52.22</v>
       </c>
       <c r="J4" s="2">
-        <v>0.022909772955587993</v>
+        <v>0.022918824167334283</v>
       </c>
       <c r="K4" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L4" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M4" s="2">
-        <v>0.3717863948732021</v>
+        <v>0.400179815517675</v>
       </c>
       <c r="N4" s="2">
-        <v>38.89727208817214</v>
+        <v>44.29046924939603</v>
       </c>
       <c r="O4" s="2">
         <v>92.85714285714286</v>
@@ -2332,16 +2332,16 @@
         <v>19.349659482175007</v>
       </c>
       <c r="Q4" s="2">
-        <v>60.00000000000001</v>
+        <v>59.761904761904766</v>
       </c>
       <c r="R4" s="2">
-        <v>54.523809523809526</v>
+        <v>54.58333333333333</v>
       </c>
       <c r="S4" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T4" s="2">
-        <v>6.17</v>
+        <v>6.23</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -2355,25 +2355,25 @@
         <v>39.285714285714285</v>
       </c>
       <c r="D5" s="1">
-        <v>30.814814814814813</v>
+        <v>30.824074074074073</v>
       </c>
       <c r="E5" s="1">
         <v>1.69</v>
       </c>
       <c r="F5" s="1">
-        <v>-0.13815240424574216</v>
+        <v>-0.1479610540882516</v>
       </c>
       <c r="G5" s="1">
         <v>1.91</v>
       </c>
       <c r="H5" s="1">
-        <v>53.19</v>
+        <v>54.82</v>
       </c>
       <c r="I5" s="1">
-        <v>-8.84</v>
+        <v>-7.91</v>
       </c>
       <c r="J5" s="1">
-        <v>-0.014538324058561328</v>
+        <v>-0.01294422094788631</v>
       </c>
       <c r="K5" s="1" t="b">
         <v>0</v>
@@ -2382,28 +2382,28 @@
         <v>140</v>
       </c>
       <c r="M5" s="1">
-        <v>-0.13229534757798966</v>
+        <v>-0.11886391603983193</v>
       </c>
       <c r="N5" s="1">
-        <v>-11.510902156947047</v>
+        <v>-7.613903906354659</v>
       </c>
       <c r="O5" s="1">
-        <v>25</v>
+        <v>30.952380952380953</v>
       </c>
       <c r="P5" s="1">
         <v>33.002444654975626</v>
       </c>
       <c r="Q5" s="1">
-        <v>50</v>
+        <v>50.714285714285715</v>
       </c>
       <c r="R5" s="1">
-        <v>33.035714285714285</v>
+        <v>35.05952380952381</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T5" s="1">
-        <v>-12.94</v>
+        <v>-10.92</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -2423,49 +2423,49 @@
         <v>-1.87</v>
       </c>
       <c r="F6" s="1">
-        <v>-0.0503926023399119</v>
+        <v>-0.08334953218372448</v>
       </c>
       <c r="G6" s="1">
         <v>1.6</v>
       </c>
       <c r="H6" s="1">
-        <v>46.58</v>
+        <v>43.15</v>
       </c>
       <c r="I6" s="1">
-        <v>-10.43</v>
+        <v>-12.09</v>
       </c>
       <c r="J6" s="1">
-        <v>0.0033357882717431897</v>
+        <v>0.002038697338800449</v>
       </c>
       <c r="K6" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L6" s="1">
-        <v>-207</v>
+        <v>-206</v>
       </c>
       <c r="M6" s="1">
-        <v>-0.04653080673480037</v>
+        <v>-0.06416460599795326</v>
       </c>
       <c r="N6" s="1">
-        <v>-2.934448072628113</v>
+        <v>-2.1439729021667935</v>
       </c>
       <c r="O6" s="1">
-        <v>48.80952380952381</v>
+        <v>45.23809523809524</v>
       </c>
       <c r="P6" s="1">
-        <v>28.714544797168166</v>
+        <v>27.785495103772316</v>
       </c>
       <c r="Q6" s="1">
-        <v>46.42857142857144</v>
+        <v>43.92857142857143</v>
       </c>
       <c r="R6" s="1">
-        <v>37.67857142857143</v>
+        <v>36.011904761904766</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T6" s="1">
-        <v>18.59</v>
+        <v>16.93</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -2485,31 +2485,31 @@
         <v>0.51</v>
       </c>
       <c r="F7" s="2">
-        <v>0.006251988920001082</v>
+        <v>-0.00995312315159319</v>
       </c>
       <c r="G7" s="2">
         <v>2.22</v>
       </c>
       <c r="H7" s="2">
-        <v>49.06</v>
+        <v>51.72</v>
       </c>
       <c r="I7" s="2">
-        <v>9.16</v>
+        <v>10.68</v>
       </c>
       <c r="J7" s="2">
-        <v>0.008375651987741858</v>
+        <v>0.008073721528561052</v>
       </c>
       <c r="K7" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L7" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="M7" s="2">
-        <v>0.014104306650394527</v>
+        <v>0.029056226759474946</v>
       </c>
       <c r="N7" s="2">
-        <v>3.1290632658913653</v>
+        <v>7.178110373576027</v>
       </c>
       <c r="O7" s="2">
         <v>59.523809523809526</v>
@@ -2518,16 +2518,16 @@
         <v>19.398494070050486</v>
       </c>
       <c r="Q7" s="2">
-        <v>65.47619047619048</v>
+        <v>66.07142857142856</v>
       </c>
       <c r="R7" s="2">
-        <v>55.00000000000001</v>
+        <v>55.23809523809524</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>99</v>
       </c>
       <c r="T7" s="2">
-        <v>6.59</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -2547,19 +2547,19 @@
         <v>2.66</v>
       </c>
       <c r="F8" s="1">
-        <v>-0.09413153631108542</v>
+        <v>-0.09112621751435272</v>
       </c>
       <c r="G8" s="1">
         <v>0.61</v>
       </c>
       <c r="H8" s="1">
-        <v>36.89</v>
+        <v>35.04</v>
       </c>
       <c r="I8" s="1">
-        <v>6.5</v>
+        <v>5.98</v>
       </c>
       <c r="J8" s="1">
-        <v>-0.010305307227373635</v>
+        <v>-0.011442639316187131</v>
       </c>
       <c r="K8" s="1" t="b">
         <v>0</v>
@@ -2568,28 +2568,28 @@
         <v>361</v>
       </c>
       <c r="M8" s="1">
-        <v>-0.09664170345440792</v>
+        <v>-0.10359641953510401</v>
       </c>
       <c r="N8" s="1">
-        <v>-7.945537744588867</v>
+        <v>-6.087154255881869</v>
       </c>
       <c r="O8" s="1">
-        <v>38.095238095238095</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="P8" s="1">
-        <v>14.000228138738285</v>
+        <v>14.011691026293512</v>
       </c>
       <c r="Q8" s="1">
-        <v>46.9047619047619</v>
+        <v>45.71428571428571</v>
       </c>
       <c r="R8" s="1">
-        <v>40.6547619047619</v>
+        <v>39.107142857142854</v>
       </c>
       <c r="S8" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T8" s="1">
-        <v>-19.1</v>
+        <v>-20.65</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -2609,19 +2609,19 @@
         <v>2.97</v>
       </c>
       <c r="F9" s="2">
-        <v>0.28719085421434615</v>
+        <v>0.28692453905415327</v>
       </c>
       <c r="G9" s="2">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H9" s="2">
-        <v>55.26</v>
+        <v>55.93</v>
       </c>
       <c r="I9" s="2">
-        <v>15.6</v>
+        <v>16.18</v>
       </c>
       <c r="J9" s="2">
-        <v>0.028227698598507878</v>
+        <v>0.027370917952379985</v>
       </c>
       <c r="K9" s="2" t="b">
         <v>0</v>
@@ -2630,13 +2630,13 @@
         <v>-113</v>
       </c>
       <c r="M9" s="2">
-        <v>0.29118137633962804</v>
+        <v>0.30642921400968737</v>
       </c>
       <c r="N9" s="2">
-        <v>30.836770234814725</v>
+        <v>34.91540909859726</v>
       </c>
       <c r="O9" s="2">
-        <v>90.47619047619048</v>
+        <v>89.28571428571429</v>
       </c>
       <c r="P9" s="2">
         <v>33.227512780245505</v>
@@ -2645,13 +2645,13 @@
         <v>70.11904761904762</v>
       </c>
       <c r="R9" s="2">
-        <v>60.05952380952382</v>
+        <v>59.702380952380956</v>
       </c>
       <c r="S9" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T9" s="2">
-        <v>32.68</v>
+        <v>32.32</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -2671,19 +2671,19 @@
         <v>0.08</v>
       </c>
       <c r="F10" s="1">
-        <v>0.036553128997951295</v>
+        <v>-0.011637194267276788</v>
       </c>
       <c r="G10" s="1">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="H10" s="1">
-        <v>53.74</v>
+        <v>49.27</v>
       </c>
       <c r="I10" s="1">
-        <v>2.79</v>
+        <v>1.25</v>
       </c>
       <c r="J10" s="1">
-        <v>0.009467084769635965</v>
+        <v>0.009268221718603961</v>
       </c>
       <c r="K10" s="1" t="b">
         <v>0</v>
@@ -2692,28 +2692,28 @@
         <v>-51</v>
       </c>
       <c r="M10" s="1">
-        <v>0.03919202266144417</v>
+        <v>0.0017922540627630656</v>
       </c>
       <c r="N10" s="1">
-        <v>5.63783486699633</v>
+        <v>4.451713103904849</v>
       </c>
       <c r="O10" s="1">
-        <v>64.28571428571429</v>
+        <v>53.57142857142857</v>
       </c>
       <c r="P10" s="1">
         <v>14.568379622257217</v>
       </c>
       <c r="Q10" s="1">
-        <v>55.11904761904761</v>
+        <v>52.50000000000001</v>
       </c>
       <c r="R10" s="1">
-        <v>49.16666666666667</v>
+        <v>45.714285714285715</v>
       </c>
       <c r="S10" s="1" t="s">
         <v>101</v>
       </c>
       <c r="T10" s="1">
-        <v>13.62</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -2733,31 +2733,31 @@
         <v>2.19</v>
       </c>
       <c r="F11" s="2">
-        <v>0.5263281039258502</v>
+        <v>0.5334397451303984</v>
       </c>
       <c r="G11" s="2">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="H11" s="2">
-        <v>62.18</v>
+        <v>62.47</v>
       </c>
       <c r="I11" s="2">
-        <v>42.5</v>
+        <v>42.8</v>
       </c>
       <c r="J11" s="2">
-        <v>0.02049348878682897</v>
+        <v>0.022974717537993104</v>
       </c>
       <c r="K11" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="2">
         <v>40</v>
       </c>
       <c r="M11" s="2">
-        <v>0.5243972061232944</v>
+        <v>0.5241670308072757</v>
       </c>
       <c r="N11" s="2">
-        <v>54.158353213181364</v>
+        <v>56.6891907783561</v>
       </c>
       <c r="O11" s="2">
         <v>96.42857142857143</v>
@@ -2766,7 +2766,7 @@
         <v>21.2185970476566</v>
       </c>
       <c r="Q11" s="2">
-        <v>66.07142857142857</v>
+        <v>65.95238095238095</v>
       </c>
       <c r="R11" s="2">
         <v>59.16666666666667</v>
@@ -2795,19 +2795,19 @@
         <v>1.36</v>
       </c>
       <c r="F12" s="2">
-        <v>0.7366925384690726</v>
+        <v>0.8570457789234048</v>
       </c>
       <c r="G12" s="2">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="H12" s="2">
-        <v>64.93</v>
+        <v>67.58</v>
       </c>
       <c r="I12" s="2">
-        <v>54.07</v>
+        <v>57.94</v>
       </c>
       <c r="J12" s="2">
-        <v>0.04310533256031088</v>
+        <v>0.04364680656389421</v>
       </c>
       <c r="K12" s="2" t="b">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>29</v>
       </c>
       <c r="M12" s="2">
-        <v>0.736499448688817</v>
+        <v>0.8564062813838791</v>
       </c>
       <c r="N12" s="2">
-        <v>75.36857746973361</v>
+        <v>89.91311583601643</v>
       </c>
       <c r="O12" s="2">
         <v>100</v>
@@ -2857,49 +2857,49 @@
         <v>-1.09</v>
       </c>
       <c r="F13" s="1">
-        <v>0.3953383641809631</v>
+        <v>0.4323827828383941</v>
       </c>
       <c r="G13" s="1">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="H13" s="1">
-        <v>57.55</v>
+        <v>58.59</v>
       </c>
       <c r="I13" s="1">
-        <v>18.42</v>
+        <v>19.48</v>
       </c>
       <c r="J13" s="1">
-        <v>0.04445005290715395</v>
+        <v>0.044580855708661694</v>
       </c>
       <c r="K13" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
       </c>
       <c r="M13" s="1">
-        <v>0.39894270674573384</v>
+        <v>0.45060846271487676</v>
       </c>
       <c r="N13" s="1">
-        <v>41.6129032754253</v>
+        <v>49.33333396911621</v>
       </c>
       <c r="O13" s="1">
-        <v>94.04761904761905</v>
+        <v>95.23809523809523</v>
       </c>
       <c r="P13" s="1">
         <v>40.13761891809808</v>
       </c>
       <c r="Q13" s="1">
-        <v>44.88095238095239</v>
+        <v>45</v>
       </c>
       <c r="R13" s="1">
-        <v>37.97619047619047</v>
+        <v>38.33333333333333</v>
       </c>
       <c r="S13" s="1" t="s">
         <v>104</v>
       </c>
       <c r="T13" s="1">
-        <v>37.18</v>
+        <v>37.54</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -2919,19 +2919,19 @@
         <v>-1.74</v>
       </c>
       <c r="F14" s="2">
-        <v>0.6024453242113869</v>
+        <v>0.6464154964714657</v>
       </c>
       <c r="G14" s="2">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="H14" s="2">
-        <v>65.5</v>
+        <v>68.16</v>
       </c>
       <c r="I14" s="2">
-        <v>75.85</v>
+        <v>79.57</v>
       </c>
       <c r="J14" s="2">
-        <v>0.025363471923827274</v>
+        <v>0.026403162056311824</v>
       </c>
       <c r="K14" s="2" t="b">
         <v>0</v>
@@ -2940,10 +2940,10 @@
         <v>101</v>
       </c>
       <c r="M14" s="2">
-        <v>0.6007718794491719</v>
+        <v>0.6384217772273943</v>
       </c>
       <c r="N14" s="2">
-        <v>61.79582054576912</v>
+        <v>68.11466542036797</v>
       </c>
       <c r="O14" s="2">
         <v>98.80952380952381</v>
@@ -2975,25 +2975,25 @@
         <v>15.476190476190476</v>
       </c>
       <c r="D15" s="3">
-        <v>19.396226415094336</v>
+        <v>19.344339622641506</v>
       </c>
       <c r="E15" s="3">
         <v>1.51</v>
       </c>
       <c r="F15" s="3">
-        <v>-0.16186108732737764</v>
+        <v>-0.183942639186129</v>
       </c>
       <c r="G15" s="3">
         <v>2.24</v>
       </c>
       <c r="H15" s="3">
-        <v>56.2</v>
+        <v>62.01</v>
       </c>
       <c r="I15" s="3">
-        <v>33.37</v>
+        <v>41.64</v>
       </c>
       <c r="J15" s="3">
-        <v>-0.024282221805917426</v>
+        <v>-0.01681202405057133</v>
       </c>
       <c r="K15" s="3" t="b">
         <v>0</v>
@@ -3002,28 +3002,28 @@
         <v>1027</v>
       </c>
       <c r="M15" s="3">
-        <v>-0.1538800430768138</v>
+        <v>-0.14429379173553514</v>
       </c>
       <c r="N15" s="3">
-        <v>-13.669371706829459</v>
+        <v>-10.156891475924976</v>
       </c>
       <c r="O15" s="3">
-        <v>23.809523809523807</v>
+        <v>27.380952380952383</v>
       </c>
       <c r="P15" s="3">
         <v>41.90435941885386</v>
       </c>
       <c r="Q15" s="3">
-        <v>46.42857142857143</v>
+        <v>49.04761904761905</v>
       </c>
       <c r="R15" s="3">
-        <v>23.273809523809526</v>
+        <v>25.059523809523814</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>105</v>
       </c>
       <c r="T15" s="3">
-        <v>-35.14</v>
+        <v>-33.36</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -3043,19 +3043,19 @@
         <v>28.81</v>
       </c>
       <c r="F16" s="3">
-        <v>-0.23270905450864193</v>
+        <v>-0.2617258060096448</v>
       </c>
       <c r="G16" s="3">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H16" s="3">
-        <v>41.34</v>
+        <v>49.84</v>
       </c>
       <c r="I16" s="3">
-        <v>-8.58</v>
+        <v>-3.4</v>
       </c>
       <c r="J16" s="3">
-        <v>-0.044848323753694776</v>
+        <v>-0.04455402581301085</v>
       </c>
       <c r="K16" s="3" t="b">
         <v>0</v>
@@ -3064,10 +3064,10 @@
         <v>27</v>
       </c>
       <c r="M16" s="3">
-        <v>-0.22749563044174137</v>
+        <v>-0.2361459044286165</v>
       </c>
       <c r="N16" s="3">
-        <v>-21.03093044332222</v>
+        <v>-19.34210274523312</v>
       </c>
       <c r="O16" s="3">
         <v>15.476190476190476</v>
@@ -3076,7 +3076,7 @@
         <v>40.1905830435425</v>
       </c>
       <c r="Q16" s="3">
-        <v>27.499999999999996</v>
+        <v>30.59523809523809</v>
       </c>
       <c r="R16" s="3">
         <v>14.464285714285708</v>
@@ -3105,49 +3105,49 @@
         <v>-1.42</v>
       </c>
       <c r="F17" s="1">
-        <v>-0.01848988209780404</v>
+        <v>0.013064178103322027</v>
       </c>
       <c r="G17" s="1">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="H17" s="1">
-        <v>43.27</v>
+        <v>57.58</v>
       </c>
       <c r="I17" s="1">
-        <v>-1.56</v>
+        <v>7.56</v>
       </c>
       <c r="J17" s="1">
-        <v>-0.01188842384778865</v>
+        <v>-0.011747558648710344</v>
       </c>
       <c r="K17" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="1">
         <v>31</v>
       </c>
       <c r="M17" s="1">
-        <v>-0.013533911071244242</v>
+        <v>0.03704533583553604</v>
       </c>
       <c r="N17" s="1">
-        <v>0.3652414937274923</v>
+        <v>7.977021281182132</v>
       </c>
       <c r="O17" s="1">
-        <v>52.38095238095239</v>
+        <v>60.71428571428571</v>
       </c>
       <c r="P17" s="1">
         <v>24.80206596461608</v>
       </c>
       <c r="Q17" s="1">
-        <v>34.166666666666664</v>
+        <v>39.64285714285714</v>
       </c>
       <c r="R17" s="1">
-        <v>30.535714285714292</v>
+        <v>33.03571428571429</v>
       </c>
       <c r="S17" s="1" t="s">
         <v>100</v>
       </c>
       <c r="T17" s="1">
-        <v>-2.64</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -3161,25 +3161,25 @@
         <v>33.33333333333333</v>
       </c>
       <c r="D18" s="3">
-        <v>729.8947368421053</v>
+        <v>664</v>
       </c>
       <c r="E18" s="3">
         <v>11.06</v>
       </c>
       <c r="F18" s="3">
-        <v>-0.5954649734272661</v>
+        <v>-0.641038905118166</v>
       </c>
       <c r="G18" s="3">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="H18" s="3">
-        <v>19.42</v>
+        <v>17.5</v>
       </c>
       <c r="I18" s="3">
-        <v>-52.36</v>
+        <v>-53.33</v>
       </c>
       <c r="J18" s="3">
-        <v>-0.07470679947091596</v>
+        <v>-0.0760385728134037</v>
       </c>
       <c r="K18" s="3" t="b">
         <v>1</v>
@@ -3188,28 +3188,28 @@
         <v>31</v>
       </c>
       <c r="M18" s="3">
-        <v>-0.5943707980058178</v>
+        <v>-0.6365624223414861</v>
       </c>
       <c r="N18" s="3">
-        <v>-57.71844719972986</v>
+        <v>-59.38375453652007</v>
       </c>
       <c r="O18" s="3">
         <v>1.1904761904761905</v>
       </c>
       <c r="P18" s="3">
-        <v>64.53582969240198</v>
+        <v>64.57654723759453</v>
       </c>
       <c r="Q18" s="3">
-        <v>39.761904761904766</v>
+        <v>39.404761904761905</v>
       </c>
       <c r="R18" s="3">
-        <v>23.214285714285722</v>
+        <v>22.91666666666667</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>107</v>
       </c>
       <c r="T18" s="3">
-        <v>-11.05</v>
+        <v>-11.35</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -3229,49 +3229,49 @@
         <v>3.12</v>
       </c>
       <c r="F19" s="2">
-        <v>0.09289548264290536</v>
+        <v>0.08863470926540619</v>
       </c>
       <c r="G19" s="2">
         <v>0.1</v>
       </c>
       <c r="H19" s="2">
-        <v>51.64</v>
+        <v>55.47</v>
       </c>
       <c r="I19" s="2">
-        <v>12.23</v>
+        <v>13.7</v>
       </c>
       <c r="J19" s="2">
-        <v>0.0024878357788022908</v>
+        <v>0.004333912536991641</v>
       </c>
       <c r="K19" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L19" s="2">
-        <v>-59</v>
+        <v>-60</v>
       </c>
       <c r="M19" s="2">
-        <v>0.08710278923523807</v>
+        <v>0.05985731998674937</v>
       </c>
       <c r="N19" s="2">
-        <v>10.428911524375723</v>
+        <v>10.258219696303476</v>
       </c>
       <c r="O19" s="2">
-        <v>65.47619047619048</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="P19" s="2">
         <v>11.392700631623551</v>
       </c>
       <c r="Q19" s="2">
-        <v>59.285714285714285</v>
+        <v>61.30952380952381</v>
       </c>
       <c r="R19" s="2">
-        <v>53.63095238095239</v>
+        <v>53.750000000000014</v>
       </c>
       <c r="S19" s="2" t="s">
         <v>108</v>
       </c>
       <c r="T19" s="2">
-        <v>5.22</v>
+        <v>5.34</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -3291,19 +3291,19 @@
         <v>-5.68</v>
       </c>
       <c r="F20" s="2">
-        <v>0.2896528188729648</v>
+        <v>0.29838175683835083</v>
       </c>
       <c r="G20" s="2">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H20" s="2">
-        <v>59.35</v>
+        <v>61.76</v>
       </c>
       <c r="I20" s="2">
-        <v>24.67</v>
+        <v>25.66</v>
       </c>
       <c r="J20" s="2">
-        <v>0.02288829696965994</v>
+        <v>0.024160727212878624</v>
       </c>
       <c r="K20" s="2" t="b">
         <v>1</v>
@@ -3312,28 +3312,28 @@
         <v>8</v>
       </c>
       <c r="M20" s="2">
-        <v>0.2900389984334759</v>
+        <v>0.30061999822669083</v>
       </c>
       <c r="N20" s="2">
-        <v>30.722532444199512</v>
+        <v>34.334487520297614</v>
       </c>
       <c r="O20" s="2">
-        <v>89.28571428571429</v>
+        <v>88.09523809523809</v>
       </c>
       <c r="P20" s="2">
         <v>20.924527727345563</v>
       </c>
       <c r="Q20" s="2">
-        <v>63.33333333333333</v>
+        <v>63.57142857142857</v>
       </c>
       <c r="R20" s="2">
-        <v>56.19047619047619</v>
+        <v>55.83333333333333</v>
       </c>
       <c r="S20" s="2" t="s">
         <v>95</v>
       </c>
       <c r="T20" s="2">
-        <v>20.34</v>
+        <v>19.98</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -3347,25 +3347,25 @@
         <v>38.095238095238095</v>
       </c>
       <c r="D21" s="3">
-        <v>12.821782178217823</v>
+        <v>11.871287128712872</v>
       </c>
       <c r="E21" s="3">
         <v>-3.45</v>
       </c>
       <c r="F21" s="3">
-        <v>-0.3136559058170199</v>
+        <v>-0.3086773589264147</v>
       </c>
       <c r="G21" s="3">
         <v>1.62</v>
       </c>
       <c r="H21" s="3">
-        <v>43.06</v>
+        <v>43.15</v>
       </c>
       <c r="I21" s="3">
-        <v>-12.44</v>
+        <v>-12.39</v>
       </c>
       <c r="J21" s="3">
-        <v>-0.02229608683853931</v>
+        <v>-0.01972517720233169</v>
       </c>
       <c r="K21" s="3" t="b">
         <v>0</v>
@@ -3374,28 +3374,28 @@
         <v>55</v>
       </c>
       <c r="M21" s="3">
-        <v>-0.309665383691738</v>
+        <v>-0.28885293520111777</v>
       </c>
       <c r="N21" s="3">
-        <v>-29.247905768321875</v>
+        <v>-24.612805822483242</v>
       </c>
       <c r="O21" s="3">
-        <v>5.952380952380952</v>
+        <v>9.523809523809524</v>
       </c>
       <c r="P21" s="3">
         <v>51.51389629888408</v>
       </c>
       <c r="Q21" s="3">
-        <v>42.261904761904766</v>
+        <v>41.42857142857143</v>
       </c>
       <c r="R21" s="3">
-        <v>21.904761904761905</v>
+        <v>22.67857142857143</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>109</v>
       </c>
       <c r="T21" s="3">
-        <v>-29.31</v>
+        <v>-28.54</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -3415,49 +3415,49 @@
         <v>-0.24</v>
       </c>
       <c r="F22" s="1">
-        <v>-0.1300937179463819</v>
+        <v>-0.17720162664717115</v>
       </c>
       <c r="G22" s="1">
         <v>1.39</v>
       </c>
       <c r="H22" s="1">
-        <v>36.31</v>
+        <v>33.39</v>
       </c>
       <c r="I22" s="1">
-        <v>-1.75</v>
+        <v>-2.75</v>
       </c>
       <c r="J22" s="1">
-        <v>-0.016116795327733746</v>
+        <v>-0.01576589966346</v>
       </c>
       <c r="K22" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L22" s="1">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M22" s="1">
-        <v>-0.1275835508030594</v>
+        <v>-0.16473142462641988</v>
       </c>
       <c r="N22" s="1">
-        <v>-11.039722479454017</v>
+        <v>-12.20065476501345</v>
       </c>
       <c r="O22" s="1">
-        <v>27.380952380952383</v>
+        <v>22.61904761904762</v>
       </c>
       <c r="P22" s="1">
         <v>19.455960650079966</v>
       </c>
       <c r="Q22" s="1">
-        <v>43.333333333333336</v>
+        <v>42.5</v>
       </c>
       <c r="R22" s="1">
-        <v>34.88095238095238</v>
+        <v>33.45238095238095</v>
       </c>
       <c r="S22" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T22" s="1">
-        <v>-18.23</v>
+        <v>-19.66</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -3477,19 +3477,19 @@
         <v>0.07</v>
       </c>
       <c r="F23" s="2">
-        <v>0.10351016002164629</v>
+        <v>0.15333876142910308</v>
       </c>
       <c r="G23" s="2">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="H23" s="2">
-        <v>73.69</v>
+        <v>73.97</v>
       </c>
       <c r="I23" s="2">
-        <v>9.09</v>
+        <v>9.34</v>
       </c>
       <c r="J23" s="2">
-        <v>0.010912196213464802</v>
+        <v>0.010819397291640383</v>
       </c>
       <c r="K23" s="2" t="b">
         <v>0</v>
@@ -3498,28 +3498,28 @@
         <v>43</v>
       </c>
       <c r="M23" s="2">
-        <v>0.10460433544309455</v>
+        <v>0.15941398805459728</v>
       </c>
       <c r="N23" s="2">
-        <v>12.179066145161386</v>
+        <v>20.213886503088265</v>
       </c>
       <c r="O23" s="2">
-        <v>70.23809523809523</v>
+        <v>77.38095238095238</v>
       </c>
       <c r="P23" s="2">
         <v>20.883293768118005</v>
       </c>
       <c r="Q23" s="2">
-        <v>64.52380952380952</v>
+        <v>64.88095238095238</v>
       </c>
       <c r="R23" s="2">
-        <v>53.03571428571429</v>
+        <v>55.05952380952381</v>
       </c>
       <c r="S23" s="2" t="s">
         <v>108</v>
       </c>
       <c r="T23" s="2">
-        <v>17.24</v>
+        <v>19.27</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -3539,49 +3539,49 @@
         <v>1.55</v>
       </c>
       <c r="F24" s="1">
-        <v>-0.006415625307672729</v>
+        <v>0.009069000595089555</v>
       </c>
       <c r="G24" s="1">
         <v>3.59</v>
       </c>
       <c r="H24" s="1">
-        <v>54.44</v>
+        <v>56.02</v>
       </c>
       <c r="I24" s="1">
-        <v>-5.54</v>
+        <v>-3.56</v>
       </c>
       <c r="J24" s="1">
-        <v>0.03283725680886844</v>
+        <v>0.03196791800631613</v>
       </c>
       <c r="K24" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L24" s="1">
-        <v>-68</v>
+        <v>-69</v>
       </c>
       <c r="M24" s="1">
-        <v>0.01025445905439204</v>
+        <v>0.09188393196366862</v>
       </c>
       <c r="N24" s="1">
-        <v>2.744078506291129</v>
+        <v>13.4608808939954</v>
       </c>
       <c r="O24" s="1">
-        <v>58.333333333333336</v>
+        <v>67.85714285714286</v>
       </c>
       <c r="P24" s="1">
         <v>57.99224429263358</v>
       </c>
       <c r="Q24" s="1">
-        <v>45.71428571428571</v>
+        <v>45.95238095238095</v>
       </c>
       <c r="R24" s="1">
-        <v>30.41666666666667</v>
+        <v>33.273809523809526</v>
       </c>
       <c r="S24" s="1" t="s">
         <v>107</v>
       </c>
       <c r="T24" s="1">
-        <v>34.14</v>
+        <v>36.99</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -3595,25 +3595,25 @@
         <v>14.285714285714285</v>
       </c>
       <c r="D25" s="3">
-        <v>-7.74561403508772</v>
+        <v>-7.855263157894737</v>
       </c>
       <c r="E25" s="3">
         <v>15.52</v>
       </c>
       <c r="F25" s="3">
-        <v>-0.1867725554705666</v>
+        <v>-0.21161631597654293</v>
       </c>
       <c r="G25" s="3">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="H25" s="3">
-        <v>42</v>
+        <v>47.79</v>
       </c>
       <c r="I25" s="3">
-        <v>-33.32</v>
+        <v>-28.26</v>
       </c>
       <c r="J25" s="3">
-        <v>-0.00973890708744834</v>
+        <v>-0.009516307640798203</v>
       </c>
       <c r="K25" s="3" t="b">
         <v>1</v>
@@ -3622,28 +3622,28 @@
         <v>34</v>
       </c>
       <c r="M25" s="3">
-        <v>-0.17795478883889526</v>
+        <v>-0.1684502320585577</v>
       </c>
       <c r="N25" s="3">
-        <v>-16.076846283037604</v>
+        <v>-12.57253550822724</v>
       </c>
       <c r="O25" s="3">
-        <v>22.61904761904762</v>
+        <v>21.428571428571427</v>
       </c>
       <c r="P25" s="3">
         <v>45.59139601172712</v>
       </c>
       <c r="Q25" s="3">
-        <v>15.833333333333334</v>
+        <v>17.857142857142854</v>
       </c>
       <c r="R25" s="3">
-        <v>5.773809523809524</v>
+        <v>5.535714285714283</v>
       </c>
       <c r="S25" s="3" t="s">
         <v>101</v>
       </c>
       <c r="T25" s="3">
-        <v>4.37</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -3663,19 +3663,19 @@
         <v>-0.88</v>
       </c>
       <c r="F26" s="3">
-        <v>-0.37535174498183227</v>
+        <v>-0.38089331921802017</v>
       </c>
       <c r="G26" s="3">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="H26" s="3">
-        <v>44.13</v>
+        <v>51.77</v>
       </c>
       <c r="I26" s="3">
-        <v>-14.4</v>
+        <v>-8.09</v>
       </c>
       <c r="J26" s="3">
-        <v>-0.030956695479958874</v>
+        <v>-0.02542519862129914</v>
       </c>
       <c r="K26" s="3" t="b">
         <v>0</v>
@@ -3684,28 +3684,28 @@
         <v>159</v>
       </c>
       <c r="M26" s="3">
-        <v>-0.3600332890815565</v>
+        <v>-0.30511286078422384</v>
       </c>
       <c r="N26" s="3">
-        <v>-34.28469630730373</v>
+        <v>-26.23879838079385</v>
       </c>
       <c r="O26" s="3">
-        <v>3.571428571428571</v>
+        <v>5.952380952380952</v>
       </c>
       <c r="P26" s="3">
         <v>55.61259899184437</v>
       </c>
       <c r="Q26" s="3">
-        <v>14.285714285714285</v>
+        <v>16.547619047619047</v>
       </c>
       <c r="R26" s="3">
-        <v>-2.321428571428573</v>
+        <v>-1.488095238095239</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>101</v>
       </c>
       <c r="T26" s="3">
-        <v>-31.16</v>
+        <v>-30.33</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -3725,31 +3725,31 @@
         <v>6.6</v>
       </c>
       <c r="F27" s="3">
-        <v>-0.37690704855558455</v>
+        <v>-0.43659126318311603</v>
       </c>
       <c r="G27" s="3">
         <v>2.66</v>
       </c>
       <c r="H27" s="3">
-        <v>32.13</v>
+        <v>33.02</v>
       </c>
       <c r="I27" s="3">
-        <v>-38.74</v>
+        <v>-38.44</v>
       </c>
       <c r="J27" s="3">
-        <v>-0.031771079717984034</v>
+        <v>-0.029686712670485314</v>
       </c>
       <c r="K27" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="3">
         <v>7</v>
       </c>
       <c r="M27" s="3">
-        <v>-0.36622274738144267</v>
+        <v>-0.3835129674024823</v>
       </c>
       <c r="N27" s="3">
-        <v>-34.90364213729234</v>
+        <v>-34.078809042619696</v>
       </c>
       <c r="O27" s="3">
         <v>2.380952380952381</v>
@@ -3758,7 +3758,7 @@
         <v>50.56910707785277</v>
       </c>
       <c r="Q27" s="3">
-        <v>10.833333333333332</v>
+        <v>11.071428571428571</v>
       </c>
       <c r="R27" s="3">
         <v>-0.2976190476190492</v>
@@ -3787,19 +3787,19 @@
         <v>1.72</v>
       </c>
       <c r="F28" s="1">
-        <v>-0.07217364791915923</v>
+        <v>-0.10752541967838937</v>
       </c>
       <c r="G28" s="1">
         <v>3.26</v>
       </c>
       <c r="H28" s="1">
-        <v>41.08</v>
+        <v>44.54</v>
       </c>
       <c r="I28" s="1">
-        <v>-17.38</v>
+        <v>-15.19</v>
       </c>
       <c r="J28" s="1">
-        <v>0.008462414769437203</v>
+        <v>0.007852922331981196</v>
       </c>
       <c r="K28" s="1" t="b">
         <v>0</v>
@@ -3808,28 +3808,28 @@
         <v>3</v>
       </c>
       <c r="M28" s="1">
-        <v>-0.05762755113990581</v>
+        <v>-0.035262197711984467</v>
       </c>
       <c r="N28" s="1">
-        <v>-4.044122513138661</v>
+        <v>0.7462679264300778</v>
       </c>
       <c r="O28" s="1">
-        <v>44.047619047619044</v>
+        <v>50</v>
       </c>
       <c r="P28" s="1">
         <v>35.08771990976345</v>
       </c>
       <c r="Q28" s="1">
-        <v>42.73809523809524</v>
+        <v>44.04761904761905</v>
       </c>
       <c r="R28" s="1">
-        <v>33.63095238095238</v>
+        <v>35.29761904761905</v>
       </c>
       <c r="S28" s="1" t="s">
         <v>110</v>
       </c>
       <c r="T28" s="1">
-        <v>16.62</v>
+        <v>18.29</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -3849,49 +3849,49 @@
         <v>-4.82</v>
       </c>
       <c r="F29" s="1">
-        <v>-0.07480700682309602</v>
+        <v>-0.12454138915648824</v>
       </c>
       <c r="G29" s="1">
         <v>2.32</v>
       </c>
       <c r="H29" s="1">
-        <v>44.21</v>
+        <v>41.43</v>
       </c>
       <c r="I29" s="1">
-        <v>-12.91</v>
+        <v>-14.54</v>
       </c>
       <c r="J29" s="1">
-        <v>-0.005462710293284703</v>
+        <v>-0.0057808021121030975</v>
       </c>
       <c r="K29" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L29" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M29" s="1">
-        <v>-0.06631105649185065</v>
+        <v>-0.08233455154779157</v>
       </c>
       <c r="N29" s="1">
-        <v>-4.912473048333143</v>
+        <v>-3.960967457150625</v>
       </c>
       <c r="O29" s="1">
-        <v>41.66666666666667</v>
+        <v>42.857142857142854</v>
       </c>
       <c r="P29" s="1">
-        <v>21.89743824494191</v>
+        <v>20.094438777659683</v>
       </c>
       <c r="Q29" s="1">
-        <v>51.9047619047619</v>
+        <v>49.047619047619044</v>
       </c>
       <c r="R29" s="1">
-        <v>43.273809523809526</v>
+        <v>43.75</v>
       </c>
       <c r="S29" s="1" t="s">
         <v>108</v>
       </c>
       <c r="T29" s="1">
-        <v>3.03</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -3911,49 +3911,49 @@
         <v>1.75</v>
       </c>
       <c r="F30" s="1">
-        <v>-0.1310201126090189</v>
+        <v>-0.17760776992614247</v>
       </c>
       <c r="G30" s="1">
         <v>1.25</v>
       </c>
       <c r="H30" s="1">
-        <v>38.56</v>
+        <v>31.46</v>
       </c>
       <c r="I30" s="1">
-        <v>-7.87</v>
+        <v>-10.92</v>
       </c>
       <c r="J30" s="1">
-        <v>-0.008268715647729552</v>
+        <v>-0.009765094945169386</v>
       </c>
       <c r="K30" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="1">
         <v>135</v>
       </c>
       <c r="M30" s="1">
-        <v>-0.12941103110688912</v>
+        <v>-0.16961405068207114</v>
       </c>
       <c r="N30" s="1">
-        <v>-11.222470509836985</v>
+        <v>-12.688917370578585</v>
       </c>
       <c r="O30" s="1">
-        <v>26.190476190476193</v>
+        <v>20.238095238095237</v>
       </c>
       <c r="P30" s="1">
-        <v>16.059849712981297</v>
+        <v>18.121365335609003</v>
       </c>
       <c r="Q30" s="1">
-        <v>54.047619047619044</v>
+        <v>50.833333333333336</v>
       </c>
       <c r="R30" s="1">
-        <v>44.226190476190474</v>
+        <v>41.36904761904762</v>
       </c>
       <c r="S30" s="1" t="s">
         <v>109</v>
       </c>
       <c r="T30" s="1">
-        <v>-4.25</v>
+        <v>-7.11</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -3973,19 +3973,19 @@
         <v>0.38</v>
       </c>
       <c r="F31" s="1">
-        <v>-0.1190897807479452</v>
+        <v>-0.17413290143696686</v>
       </c>
       <c r="G31" s="1">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H31" s="1">
-        <v>35.64</v>
+        <v>38.54</v>
       </c>
       <c r="I31" s="1">
-        <v>-6.99</v>
+        <v>-5.94</v>
       </c>
       <c r="J31" s="1">
-        <v>-0.005521795155601717</v>
+        <v>-0.00680370228467923</v>
       </c>
       <c r="K31" s="1" t="b">
         <v>0</v>
@@ -3994,90 +3994,90 @@
         <v>207</v>
       </c>
       <c r="M31" s="1">
-        <v>-0.11593598100377078</v>
+        <v>-0.1587849604883499</v>
       </c>
       <c r="N31" s="1">
-        <v>-9.874965499525155</v>
+        <v>-11.606008351206453</v>
       </c>
       <c r="O31" s="1">
-        <v>30.952380952380953</v>
+        <v>25</v>
       </c>
       <c r="P31" s="1">
         <v>29.54918623383928</v>
       </c>
       <c r="Q31" s="1">
-        <v>52.50000000000001</v>
+        <v>52.38095238095239</v>
       </c>
       <c r="R31" s="1">
-        <v>40.41666666666667</v>
+        <v>38.03571428571429</v>
       </c>
       <c r="S31" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T31" s="1">
-        <v>-7.63</v>
+        <v>-10.01</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32" s="3">
         <v>-2.58</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C32" s="3">
         <v>13.095238095238097</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D32" s="3">
         <v>8.755813953488373</v>
       </c>
-      <c r="E32" s="1">
+      <c r="E32" s="3">
         <v>3.57</v>
       </c>
-      <c r="F32" s="1">
-        <v>-0.06511914251731207</v>
-      </c>
-      <c r="G32" s="1">
+      <c r="F32" s="3">
+        <v>-0.11543986639936045</v>
+      </c>
+      <c r="G32" s="3">
         <v>1.62</v>
       </c>
-      <c r="H32" s="1">
-        <v>42.46</v>
-      </c>
-      <c r="I32" s="1">
-        <v>-6.11</v>
-      </c>
-      <c r="J32" s="1">
-        <v>-0.013429000841589598</v>
-      </c>
-      <c r="K32" s="1" t="b">
+      <c r="H32" s="3">
+        <v>43.64</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-5.56</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-0.013401635283696658</v>
+      </c>
+      <c r="K32" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L32" s="1">
+      <c r="L32" s="3">
         <v>20</v>
       </c>
-      <c r="M32" s="1">
-        <v>-0.06112862039203015</v>
-      </c>
-      <c r="N32" s="1">
-        <v>-4.394229438351093</v>
-      </c>
-      <c r="O32" s="1">
-        <v>42.857142857142854</v>
-      </c>
-      <c r="P32" s="1">
+      <c r="M32" s="3">
+        <v>-0.09561544267406352</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-5.289056569777815</v>
+      </c>
+      <c r="O32" s="3">
+        <v>38.095238095238095</v>
+      </c>
+      <c r="P32" s="3">
         <v>27.28297753683016</v>
       </c>
-      <c r="Q32" s="1">
-        <v>36.66666666666668</v>
-      </c>
-      <c r="R32" s="1">
-        <v>30.41666666666667</v>
-      </c>
-      <c r="S32" s="1" t="s">
+      <c r="Q32" s="3">
+        <v>36.78571428571429</v>
+      </c>
+      <c r="R32" s="3">
+        <v>28.750000000000007</v>
+      </c>
+      <c r="S32" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="T32" s="1">
-        <v>-1.47</v>
+      <c r="T32" s="3">
+        <v>-3.14</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -4097,49 +4097,49 @@
         <v>0.24</v>
       </c>
       <c r="F33" s="2">
-        <v>0.22712345913400184</v>
+        <v>0.2677141062276712</v>
       </c>
       <c r="G33" s="2">
         <v>1.1</v>
       </c>
       <c r="H33" s="2">
-        <v>53.68</v>
+        <v>55.58</v>
       </c>
       <c r="I33" s="2">
-        <v>14.45</v>
+        <v>15.34</v>
       </c>
       <c r="J33" s="2">
-        <v>0.02483134658279094</v>
+        <v>0.024478017780715046</v>
       </c>
       <c r="K33" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L33" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M33" s="2">
-        <v>0.22776709173485377</v>
+        <v>0.27091159392529973</v>
       </c>
       <c r="N33" s="2">
-        <v>24.49534177433729</v>
+        <v>31.363647090158498</v>
       </c>
       <c r="O33" s="2">
-        <v>84.52380952380952</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="P33" s="2">
         <v>23.38443607454554</v>
       </c>
       <c r="Q33" s="2">
-        <v>67.85714285714286</v>
+        <v>68.21428571428572</v>
       </c>
       <c r="R33" s="2">
-        <v>59.761904761904766</v>
+        <v>60.11904761904761</v>
       </c>
       <c r="S33" s="2" t="s">
         <v>108</v>
       </c>
       <c r="T33" s="2">
-        <v>23.97</v>
+        <v>24.33</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -4153,55 +4153,55 @@
         <v>92.85714285714286</v>
       </c>
       <c r="D34" s="1">
-        <v>-2.3390256152687092</v>
+        <v>-2.3345052737317933</v>
       </c>
       <c r="E34" s="1">
         <v>2.34</v>
       </c>
       <c r="F34" s="1">
-        <v>-0.09993113567007382</v>
+        <v>-0.0946855440919999</v>
       </c>
       <c r="G34" s="1">
         <v>1.21</v>
       </c>
       <c r="H34" s="1">
-        <v>53.26</v>
+        <v>53.36</v>
       </c>
       <c r="I34" s="1">
-        <v>2.93</v>
+        <v>2.97</v>
       </c>
       <c r="J34" s="1">
-        <v>-0.005954115496555359</v>
+        <v>-0.005376928216629924</v>
       </c>
       <c r="K34" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L34" s="1">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="M34" s="1">
-        <v>-0.09857950720828479</v>
+        <v>-0.08797081992697997</v>
       </c>
       <c r="N34" s="1">
-        <v>-8.139318119976558</v>
+        <v>-4.5245942950694635</v>
       </c>
       <c r="O34" s="1">
-        <v>35.714285714285715</v>
+        <v>41.66666666666667</v>
       </c>
       <c r="P34" s="1">
         <v>21.09433056126816</v>
       </c>
       <c r="Q34" s="1">
-        <v>49.76190476190476</v>
+        <v>49.404761904761905</v>
       </c>
       <c r="R34" s="1">
-        <v>35.83333333333333</v>
+        <v>37.5</v>
       </c>
       <c r="S34" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T34" s="1">
-        <v>-11</v>
+        <v>-9.33</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -4221,19 +4221,19 @@
         <v>-0.33</v>
       </c>
       <c r="F35" s="1">
-        <v>-0.0768646671316858</v>
+        <v>-0.09428172618550805</v>
       </c>
       <c r="G35" s="1">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="H35" s="1">
-        <v>36.12</v>
+        <v>32.88</v>
       </c>
       <c r="I35" s="1">
-        <v>-15.71</v>
+        <v>-17.53</v>
       </c>
       <c r="J35" s="1">
-        <v>0.0020215839801205754</v>
+        <v>0.00047106364207268763</v>
       </c>
       <c r="K35" s="1" t="b">
         <v>0</v>
@@ -4242,28 +4242,28 @@
         <v>-56</v>
       </c>
       <c r="M35" s="1">
-        <v>-0.07712212017202658</v>
+        <v>-0.09588047003432232</v>
       </c>
       <c r="N35" s="1">
-        <v>-5.993579416350741</v>
+        <v>-5.315559305803698</v>
       </c>
       <c r="O35" s="1">
-        <v>39.285714285714285</v>
+        <v>36.904761904761905</v>
       </c>
       <c r="P35" s="1">
         <v>23.996351232323672</v>
       </c>
       <c r="Q35" s="1">
-        <v>45.71428571428572</v>
+        <v>43.92857142857144</v>
       </c>
       <c r="R35" s="1">
-        <v>39.16666666666667</v>
+        <v>38.095238095238095</v>
       </c>
       <c r="S35" s="1" t="s">
         <v>111</v>
       </c>
       <c r="T35" s="1">
-        <v>16.67</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -4277,37 +4277,37 @@
         <v>77.38095238095238</v>
       </c>
       <c r="D36" s="1">
-        <v>-0.01265822784810117</v>
+        <v>-0.0029211295034079223</v>
       </c>
       <c r="E36" s="1">
         <v>-1.31</v>
       </c>
       <c r="F36" s="1">
-        <v>-0.049627530556429385</v>
+        <v>-0.06323833297718343</v>
       </c>
       <c r="G36" s="1">
         <v>1.13</v>
       </c>
       <c r="H36" s="1">
-        <v>41</v>
+        <v>40.72</v>
       </c>
       <c r="I36" s="1">
-        <v>-10.3</v>
+        <v>-10.42</v>
       </c>
       <c r="J36" s="1">
-        <v>0.01082927262830012</v>
+        <v>0.00936018056564004</v>
       </c>
       <c r="K36" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L36" s="1">
-        <v>-21</v>
+        <v>-20</v>
       </c>
       <c r="M36" s="1">
-        <v>-0.04879080817532189</v>
+        <v>-0.059081598970266325</v>
       </c>
       <c r="N36" s="1">
-        <v>-3.1604482166802708</v>
+        <v>-1.635672199398101</v>
       </c>
       <c r="O36" s="1">
         <v>46.42857142857143</v>
@@ -4316,16 +4316,16 @@
         <v>26.730280409441182</v>
       </c>
       <c r="Q36" s="1">
-        <v>51.19047619047618</v>
+        <v>51.07142857142856</v>
       </c>
       <c r="R36" s="1">
-        <v>42.20238095238096</v>
+        <v>42.26190476190476</v>
       </c>
       <c r="S36" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T36" s="1">
-        <v>15.25</v>
+        <v>15.31</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -4345,19 +4345,19 @@
         <v>-3.25</v>
       </c>
       <c r="F37" s="2">
-        <v>0.1886359402391052</v>
+        <v>0.20640191800020602</v>
       </c>
       <c r="G37" s="2">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="H37" s="2">
-        <v>41.23</v>
+        <v>40.99</v>
       </c>
       <c r="I37" s="2">
-        <v>4.49</v>
+        <v>4.37</v>
       </c>
       <c r="J37" s="2">
-        <v>0.015940140989749038</v>
+        <v>0.01526286056327369</v>
       </c>
       <c r="K37" s="2" t="b">
         <v>0</v>
@@ -4366,28 +4366,28 @@
         <v>-107</v>
       </c>
       <c r="M37" s="2">
-        <v>0.1903737482614054</v>
+        <v>0.2153548835535659</v>
       </c>
       <c r="N37" s="2">
-        <v>20.756007426992465</v>
+        <v>25.807976052985126</v>
       </c>
       <c r="O37" s="2">
-        <v>80.95238095238095</v>
+        <v>82.14285714285714</v>
       </c>
       <c r="P37" s="2">
-        <v>20.90944133883571</v>
+        <v>20.538852415160598</v>
       </c>
       <c r="Q37" s="2">
-        <v>53.57142857142857</v>
+        <v>53.214285714285715</v>
       </c>
       <c r="R37" s="2">
-        <v>52.85714285714286</v>
+        <v>53.21428571428571</v>
       </c>
       <c r="S37" s="2" t="s">
         <v>109</v>
       </c>
       <c r="T37" s="2">
-        <v>23.04</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -4407,19 +4407,19 @@
         <v>3.14</v>
       </c>
       <c r="F38" s="2">
-        <v>0.40235676143176236</v>
+        <v>0.38959043893960177</v>
       </c>
       <c r="G38" s="2">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="H38" s="2">
-        <v>63.64</v>
+        <v>65.41</v>
       </c>
       <c r="I38" s="2">
-        <v>64.58</v>
+        <v>67.81</v>
       </c>
       <c r="J38" s="2">
-        <v>0.016130727470549343</v>
+        <v>0.01971069619730847</v>
       </c>
       <c r="K38" s="2" t="b">
         <v>1</v>
@@ -4428,28 +4428,28 @@
         <v>391</v>
       </c>
       <c r="M38" s="2">
-        <v>0.4036440266334662</v>
+        <v>0.3963051631046217</v>
       </c>
       <c r="N38" s="2">
-        <v>42.08303526419854</v>
+        <v>43.90300400809071</v>
       </c>
       <c r="O38" s="2">
-        <v>95.23809523809523</v>
+        <v>91.66666666666666</v>
       </c>
       <c r="P38" s="2">
         <v>17.802507034008837</v>
       </c>
       <c r="Q38" s="2">
-        <v>73.0952380952381</v>
+        <v>74.28571428571429</v>
       </c>
       <c r="R38" s="2">
-        <v>65.6547619047619</v>
+        <v>65.35714285714286</v>
       </c>
       <c r="S38" s="2" t="s">
         <v>99</v>
       </c>
       <c r="T38" s="2">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -4469,19 +4469,19 @@
         <v>-1.29</v>
       </c>
       <c r="F39" s="1">
-        <v>-0.008753068940589755</v>
+        <v>-0.0019111822236348719</v>
       </c>
       <c r="G39" s="1">
         <v>1.13</v>
       </c>
       <c r="H39" s="1">
-        <v>34.29</v>
+        <v>38.13</v>
       </c>
       <c r="I39" s="1">
-        <v>-7.54</v>
+        <v>-6.2</v>
       </c>
       <c r="J39" s="1">
-        <v>-0.004369013442851532</v>
+        <v>-0.00389104937391255</v>
       </c>
       <c r="K39" s="1" t="b">
         <v>1</v>
@@ -4490,10 +4490,10 @@
         <v>-1</v>
       </c>
       <c r="M39" s="1">
-        <v>-0.007916346559482257</v>
+        <v>0.002245551783282229</v>
       </c>
       <c r="N39" s="1">
-        <v>0.9269979449037048</v>
+        <v>4.4970428759567636</v>
       </c>
       <c r="O39" s="1">
         <v>54.761904761904766</v>
@@ -4502,16 +4502,16 @@
         <v>30.28933322215756</v>
       </c>
       <c r="Q39" s="1">
-        <v>44.76190476190476</v>
+        <v>45.35714285714286</v>
       </c>
       <c r="R39" s="1">
-        <v>41.13095238095239</v>
+        <v>40.773809523809526</v>
       </c>
       <c r="S39" s="1" t="s">
         <v>110</v>
       </c>
       <c r="T39" s="1">
-        <v>15.34</v>
+        <v>14.98</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -4531,19 +4531,19 @@
         <v>3.93</v>
       </c>
       <c r="F40" s="1">
-        <v>0.21997708337187738</v>
+        <v>0.43030548050227524</v>
       </c>
       <c r="G40" s="1">
-        <v>0.78</v>
+        <v>0.69</v>
       </c>
       <c r="H40" s="1">
-        <v>51.81</v>
+        <v>57.6</v>
       </c>
       <c r="I40" s="1">
-        <v>-4.2</v>
+        <v>3.12</v>
       </c>
       <c r="J40" s="1">
-        <v>0.03570437173223505</v>
+        <v>0.034652432816401194</v>
       </c>
       <c r="K40" s="1" t="b">
         <v>0</v>
@@ -4552,28 +4552,28 @@
         <v>-21</v>
       </c>
       <c r="M40" s="1">
-        <v>0.21856109165000315</v>
+        <v>0.4203932686396268</v>
       </c>
       <c r="N40" s="1">
-        <v>23.574741765852227</v>
+        <v>46.31181456159121</v>
       </c>
       <c r="O40" s="1">
-        <v>82.14285714285714</v>
+        <v>94.04761904761905</v>
       </c>
       <c r="P40" s="1">
         <v>51.940889187924654</v>
       </c>
       <c r="Q40" s="1">
-        <v>50.83333333333333</v>
+        <v>53.92857142857143</v>
       </c>
       <c r="R40" s="1">
-        <v>43.035714285714285</v>
+        <v>46.607142857142854</v>
       </c>
       <c r="S40" s="1" t="s">
         <v>112</v>
       </c>
       <c r="T40" s="1">
-        <v>34.56</v>
+        <v>38.13</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -4593,19 +4593,19 @@
         <v>0.01</v>
       </c>
       <c r="F41" s="3">
-        <v>-0.20571247732610687</v>
+        <v>-0.12879710667669408</v>
       </c>
       <c r="G41" s="3">
         <v>1.22</v>
       </c>
       <c r="H41" s="3">
-        <v>39.71</v>
+        <v>41.94</v>
       </c>
       <c r="I41" s="3">
-        <v>-12.83</v>
+        <v>-11.84</v>
       </c>
       <c r="J41" s="3">
-        <v>-0.018308195349763592</v>
+        <v>-0.01752626670200881</v>
       </c>
       <c r="K41" s="3" t="b">
         <v>1</v>
@@ -4614,28 +4614,28 @@
         <v>4</v>
       </c>
       <c r="M41" s="3">
-        <v>-0.20429648560423264</v>
+        <v>-0.12176263374191132</v>
       </c>
       <c r="N41" s="3">
-        <v>-18.711015959571345</v>
+        <v>-7.903775676562595</v>
       </c>
       <c r="O41" s="3">
-        <v>19.047619047619047</v>
+        <v>29.761904761904763</v>
       </c>
       <c r="P41" s="3">
         <v>30.769232468942608</v>
       </c>
       <c r="Q41" s="3">
-        <v>23.452380952380953</v>
+        <v>23.80952380952381</v>
       </c>
       <c r="R41" s="3">
-        <v>13.69047619047619</v>
+        <v>16.666666666666668</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>105</v>
       </c>
       <c r="T41" s="3">
-        <v>-22.96</v>
+        <v>-19.98</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -4655,19 +4655,19 @@
         <v>4.37</v>
       </c>
       <c r="F42" s="1">
-        <v>-0.12134989496918369</v>
+        <v>-0.11764762786499958</v>
       </c>
       <c r="G42" s="1">
         <v>0.31</v>
       </c>
       <c r="H42" s="1">
-        <v>31.62</v>
+        <v>29.27</v>
       </c>
       <c r="I42" s="1">
-        <v>-9.32</v>
+        <v>-9.61</v>
       </c>
       <c r="J42" s="1">
-        <v>-0.013867968558443513</v>
+        <v>-0.014228006805639215</v>
       </c>
       <c r="K42" s="1" t="b">
         <v>0</v>
@@ -4676,10 +4676,10 @@
         <v>16</v>
       </c>
       <c r="M42" s="1">
-        <v>-0.12579095991506195</v>
+        <v>-0.13971029297863646</v>
       </c>
       <c r="N42" s="1">
-        <v>-10.860463390654274</v>
+        <v>-9.698541600235115</v>
       </c>
       <c r="O42" s="1">
         <v>28.57142857142857</v>
@@ -4688,16 +4688,16 @@
         <v>16.35579214434687</v>
       </c>
       <c r="Q42" s="1">
-        <v>36.42857142857142</v>
+        <v>35.833333333333336</v>
       </c>
       <c r="R42" s="1">
-        <v>32.738095238095234</v>
+        <v>32.61904761904761</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>109</v>
       </c>
       <c r="T42" s="1">
-        <v>-2.75</v>
+        <v>-2.87</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -4717,19 +4717,19 @@
         <v>8.86</v>
       </c>
       <c r="F43" s="2">
-        <v>0.22595450989255267</v>
+        <v>0.21190668561134812</v>
       </c>
       <c r="G43" s="2">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="H43" s="2">
-        <v>57.66</v>
+        <v>51.57</v>
       </c>
       <c r="I43" s="2">
-        <v>24.8</v>
+        <v>18.39</v>
       </c>
       <c r="J43" s="2">
-        <v>0.013519996080484386</v>
+        <v>0.012189998135815248</v>
       </c>
       <c r="K43" s="2" t="b">
         <v>0</v>
@@ -4738,28 +4738,28 @@
         <v>18</v>
       </c>
       <c r="M43" s="2">
-        <v>0.2281428607354492</v>
+        <v>0.22309789255304802</v>
       </c>
       <c r="N43" s="2">
-        <v>24.53291867439685</v>
+        <v>26.582276952933338</v>
       </c>
       <c r="O43" s="2">
-        <v>85.71428571428571</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="P43" s="2">
         <v>24.82490242340647</v>
       </c>
       <c r="Q43" s="2">
-        <v>68.33333333333334</v>
+        <v>65.11904761904762</v>
       </c>
       <c r="R43" s="2">
-        <v>58.98809523809524</v>
+        <v>58.273809523809526</v>
       </c>
       <c r="S43" s="2" t="s">
         <v>113</v>
       </c>
       <c r="T43" s="2">
-        <v>6.61</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -4779,19 +4779,19 @@
         <v>-0.68</v>
       </c>
       <c r="F44" s="2">
-        <v>0.12001048705223726</v>
+        <v>0.09458570456341873</v>
       </c>
       <c r="G44" s="2">
         <v>2.64</v>
       </c>
       <c r="H44" s="2">
-        <v>42.93</v>
+        <v>40.6</v>
       </c>
       <c r="I44" s="2">
-        <v>0.37</v>
+        <v>-1.42</v>
       </c>
       <c r="J44" s="2">
-        <v>0.007689979303030582</v>
+        <v>0.007225443850806593</v>
       </c>
       <c r="K44" s="2" t="b">
         <v>0</v>
@@ -4800,28 +4800,28 @@
         <v>-8</v>
       </c>
       <c r="M44" s="2">
-        <v>0.13056606170620877</v>
+        <v>0.14702450280452672</v>
       </c>
       <c r="N44" s="2">
-        <v>14.77523877147279</v>
+        <v>18.974937978081215</v>
       </c>
       <c r="O44" s="2">
-        <v>76.19047619047619</v>
+        <v>75</v>
       </c>
       <c r="P44" s="2">
-        <v>29.40653991657008</v>
+        <v>27.705367784091152</v>
       </c>
       <c r="Q44" s="2">
-        <v>56.42857142857143</v>
+        <v>55.11904761904762</v>
       </c>
       <c r="R44" s="2">
-        <v>52.97619047619048</v>
+        <v>52.857142857142854</v>
       </c>
       <c r="S44" s="2" t="s">
         <v>101</v>
       </c>
       <c r="T44" s="2">
-        <v>18.16</v>
+        <v>18.04</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
@@ -4835,55 +4835,55 @@
         <v>82.14285714285714</v>
       </c>
       <c r="D45" s="1">
-        <v>-2.3580048270313756</v>
+        <v>-2.353982300884956</v>
       </c>
       <c r="E45" s="1">
         <v>1.03</v>
       </c>
       <c r="F45" s="1">
-        <v>-0.020309610306311288</v>
+        <v>0.0005285439271493358</v>
       </c>
       <c r="G45" s="1">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H45" s="1">
-        <v>42.64</v>
+        <v>45.39</v>
       </c>
       <c r="I45" s="1">
-        <v>3.51</v>
+        <v>4.57</v>
       </c>
       <c r="J45" s="1">
-        <v>0.0034348964400732775</v>
+        <v>0.002962136272608495</v>
       </c>
       <c r="K45" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L45" s="1">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="M45" s="1">
-        <v>-0.017348900342392448</v>
+        <v>0.014917238566477753</v>
       </c>
       <c r="N45" s="1">
-        <v>-0.016257433387322155</v>
+        <v>5.764211554276315</v>
       </c>
       <c r="O45" s="1">
-        <v>51.19047619047619</v>
+        <v>57.14285714285714</v>
       </c>
       <c r="P45" s="1">
         <v>17.57882034058413</v>
       </c>
       <c r="Q45" s="1">
-        <v>46.785714285714285</v>
+        <v>47.14285714285714</v>
       </c>
       <c r="R45" s="1">
-        <v>40.41666666666667</v>
+        <v>41.964285714285715</v>
       </c>
       <c r="S45" s="1" t="s">
         <v>107</v>
       </c>
       <c r="T45" s="1">
-        <v>-3.91</v>
+        <v>-2.36</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
@@ -4903,31 +4903,31 @@
         <v>4.53</v>
       </c>
       <c r="F46" s="3">
-        <v>-0.257603525148644</v>
+        <v>-0.28433903598072496</v>
       </c>
       <c r="G46" s="3">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="H46" s="3">
-        <v>34.52</v>
+        <v>35.24</v>
       </c>
       <c r="I46" s="3">
-        <v>-31.26</v>
+        <v>-30.88</v>
       </c>
       <c r="J46" s="3">
-        <v>-0.009825507176882218</v>
+        <v>-0.010267187067093893</v>
       </c>
       <c r="K46" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="3">
         <v>17</v>
       </c>
       <c r="M46" s="3">
-        <v>-0.2525188276019138</v>
+        <v>-0.25971838070898523</v>
       </c>
       <c r="N46" s="3">
-        <v>-23.533250159339456</v>
+        <v>-21.699350373269993</v>
       </c>
       <c r="O46" s="3">
         <v>13.095238095238097</v>
@@ -4936,7 +4936,7 @@
         <v>54.33673655574689</v>
       </c>
       <c r="Q46" s="3">
-        <v>43.8095238095238</v>
+        <v>43.92857142857142</v>
       </c>
       <c r="R46" s="3">
         <v>27.26190476190476</v>
@@ -4965,19 +4965,19 @@
         <v>2.59</v>
       </c>
       <c r="F47" s="1">
-        <v>0.1248779887475471</v>
+        <v>0.06911654352729206</v>
       </c>
       <c r="G47" s="1">
         <v>1.42</v>
       </c>
       <c r="H47" s="1">
-        <v>48.27</v>
+        <v>44.44</v>
       </c>
       <c r="I47" s="1">
-        <v>3.1</v>
+        <v>1.03</v>
       </c>
       <c r="J47" s="1">
-        <v>0.018663167015806774</v>
+        <v>0.017993162101325254</v>
       </c>
       <c r="K47" s="1" t="b">
         <v>1</v>
@@ -4986,28 +4986,28 @@
         <v>-56</v>
       </c>
       <c r="M47" s="1">
-        <v>0.12758124567112517</v>
+        <v>0.08254599185733191</v>
       </c>
       <c r="N47" s="1">
-        <v>14.476757167964438</v>
+        <v>12.527086883361735</v>
       </c>
       <c r="O47" s="1">
-        <v>75</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="P47" s="1">
         <v>33.3731909304046</v>
       </c>
       <c r="Q47" s="1">
-        <v>53.57142857142857</v>
+        <v>51.19047619047618</v>
       </c>
       <c r="R47" s="1">
-        <v>45.714285714285715</v>
+        <v>43.095238095238095</v>
       </c>
       <c r="S47" s="1" t="s">
         <v>107</v>
       </c>
       <c r="T47" s="1">
-        <v>19.86</v>
+        <v>17.24</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
@@ -5021,25 +5021,25 @@
         <v>48.80952380952381</v>
       </c>
       <c r="D48" s="2">
-        <v>7.583596214511041</v>
+        <v>7.596214511041009</v>
       </c>
       <c r="E48" s="2">
         <v>0.65</v>
       </c>
       <c r="F48" s="2">
-        <v>0.15471522428717138</v>
+        <v>0.1475564641964429</v>
       </c>
       <c r="G48" s="2">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="H48" s="2">
-        <v>56.53</v>
+        <v>55.92</v>
       </c>
       <c r="I48" s="2">
-        <v>29.55</v>
+        <v>28.93</v>
       </c>
       <c r="J48" s="2">
-        <v>0.01416947553790085</v>
+        <v>0.014071902287302821</v>
       </c>
       <c r="K48" s="2" t="b">
         <v>0</v>
@@ -5048,10 +5048,10 @@
         <v>242</v>
       </c>
       <c r="M48" s="2">
-        <v>0.1585770198922829</v>
+        <v>0.16706113915197696</v>
       </c>
       <c r="N48" s="2">
-        <v>17.576334590080215</v>
+        <v>20.97860161282623</v>
       </c>
       <c r="O48" s="2">
         <v>79.76190476190477</v>
@@ -5060,7 +5060,7 @@
         <v>23.23749735248456</v>
       </c>
       <c r="Q48" s="2">
-        <v>65.95238095238095</v>
+        <v>65.23809523809523</v>
       </c>
       <c r="R48" s="2">
         <v>55.95238095238097</v>
@@ -5089,19 +5089,19 @@
         <v>-11.05</v>
       </c>
       <c r="F49" s="2">
-        <v>0.09095461833396687</v>
+        <v>0.14702008167561414</v>
       </c>
       <c r="G49" s="2">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H49" s="2">
-        <v>60.21</v>
+        <v>54.87</v>
       </c>
       <c r="I49" s="2">
-        <v>2.38</v>
+        <v>-1.77</v>
       </c>
       <c r="J49" s="2">
-        <v>0.02047618809470788</v>
+        <v>0.02015172853706399</v>
       </c>
       <c r="K49" s="2" t="b">
         <v>0</v>
@@ -5110,28 +5110,28 @@
         <v>-7</v>
       </c>
       <c r="M49" s="2">
-        <v>0.09134079789447802</v>
+        <v>0.14925832306395415</v>
       </c>
       <c r="N49" s="2">
-        <v>10.852712390299727</v>
+        <v>19.19832000402394</v>
       </c>
       <c r="O49" s="2">
-        <v>66.66666666666666</v>
+        <v>76.19047619047619</v>
       </c>
       <c r="P49" s="2">
         <v>31.00158698078384</v>
       </c>
       <c r="Q49" s="2">
-        <v>68.57142857142857</v>
+        <v>65.83333333333333</v>
       </c>
       <c r="R49" s="2">
-        <v>53.86904761904761</v>
+        <v>56.60714285714286</v>
       </c>
       <c r="S49" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T49" s="2">
-        <v>22.77</v>
+        <v>25.51</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
@@ -5151,19 +5151,19 @@
         <v>12.9</v>
       </c>
       <c r="F50" s="3">
-        <v>-0.2943170786638365</v>
+        <v>-0.33794354933020865</v>
       </c>
       <c r="G50" s="3">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="H50" s="3">
-        <v>52.84</v>
+        <v>53.98</v>
       </c>
       <c r="I50" s="3">
-        <v>4.53</v>
+        <v>6.03</v>
       </c>
       <c r="J50" s="3">
-        <v>-0.0025153531749216936</v>
+        <v>0.0016556572401208354</v>
       </c>
       <c r="K50" s="3" t="b">
         <v>0</v>
@@ -5172,22 +5172,22 @@
         <v>69</v>
       </c>
       <c r="M50" s="3">
-        <v>-0.27616663931981233</v>
+        <v>-0.24713489871755823</v>
       </c>
       <c r="N50" s="3">
-        <v>-25.89803133112931</v>
+        <v>-20.44100217412728</v>
       </c>
       <c r="O50" s="3">
-        <v>9.523809523809524</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="P50" s="3">
         <v>41.201484669672254</v>
       </c>
       <c r="Q50" s="3">
-        <v>46.904761904761905</v>
+        <v>48.0952380952381</v>
       </c>
       <c r="R50" s="3">
-        <v>20.535714285714285</v>
+        <v>22.44047619047619</v>
       </c>
       <c r="S50" s="3" t="s">
         <v>106</v>
@@ -5211,19 +5211,19 @@
         <v>14.41</v>
       </c>
       <c r="F51" s="1">
-        <v>0.21613007367573558</v>
+        <v>0.22519945433144278</v>
       </c>
       <c r="G51" s="1">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="H51" s="1">
-        <v>65.16</v>
+        <v>72.38</v>
       </c>
       <c r="I51" s="1">
-        <v>35.25</v>
+        <v>51.99</v>
       </c>
       <c r="J51" s="1">
-        <v>0.04821181700151261</v>
+        <v>0.05178035769740061</v>
       </c>
       <c r="K51" s="1" t="b">
         <v>0</v>
@@ -5232,22 +5232,22 @@
         <v>14</v>
       </c>
       <c r="M51" s="1">
-        <v>0.22031368558127307</v>
+        <v>0.2472621194450797</v>
       </c>
       <c r="N51" s="1">
-        <v>23.750001158979234</v>
+        <v>28.998699642136504</v>
       </c>
       <c r="O51" s="1">
-        <v>83.33333333333334</v>
+        <v>84.52380952380952</v>
       </c>
       <c r="P51" s="1">
         <v>38.38748944617691</v>
       </c>
       <c r="Q51" s="1">
-        <v>56.30952380952381</v>
+        <v>57.26190476190476</v>
       </c>
       <c r="R51" s="1">
-        <v>42.55952380952381</v>
+        <v>42.91666666666666</v>
       </c>
       <c r="S51" s="1" t="s">
         <v>96</v>
@@ -5271,19 +5271,19 @@
         <v>-5.11</v>
       </c>
       <c r="F52" s="3">
-        <v>-0.18580444638797697</v>
+        <v>-0.1508505170090942</v>
       </c>
       <c r="G52" s="3">
-        <v>0.94</v>
+        <v>0.92</v>
       </c>
       <c r="H52" s="3">
-        <v>33.92</v>
+        <v>37.62</v>
       </c>
       <c r="I52" s="3">
-        <v>-35.33</v>
+        <v>-33.68</v>
       </c>
       <c r="J52" s="3">
-        <v>-0.015144775587393204</v>
+        <v>-0.01466672459830375</v>
       </c>
       <c r="K52" s="3" t="b">
         <v>0</v>
@@ -5292,22 +5292,22 @@
         <v>-106</v>
       </c>
       <c r="M52" s="3">
-        <v>-0.18619062594848812</v>
+        <v>-0.153408507167197</v>
       </c>
       <c r="N52" s="3">
-        <v>-16.900429993996887</v>
+        <v>-11.068363019091167</v>
       </c>
       <c r="O52" s="3">
-        <v>21.428571428571427</v>
+        <v>26.190476190476193</v>
       </c>
       <c r="P52" s="3">
-        <v>42.461480269958265</v>
+        <v>42.42351222913704</v>
       </c>
       <c r="Q52" s="3">
-        <v>32.142857142857146</v>
+        <v>32.976190476190474</v>
       </c>
       <c r="R52" s="3">
-        <v>22.142857142857146</v>
+        <v>23.452380952380963</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>113</v>
@@ -5331,43 +5331,43 @@
         <v>-1.38</v>
       </c>
       <c r="F53" s="1">
-        <v>-0.010746958005590768</v>
+        <v>-0.007669684320463485</v>
       </c>
       <c r="G53" s="1">
         <v>0.98</v>
       </c>
       <c r="H53" s="1">
-        <v>37.1</v>
+        <v>38.94</v>
       </c>
       <c r="I53" s="1">
-        <v>2.03</v>
+        <v>2.49</v>
       </c>
       <c r="J53" s="1">
-        <v>0.0020615095187688</v>
+        <v>0.003116379726557908</v>
       </c>
       <c r="K53" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" s="1">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M53" s="1">
-        <v>-0.010875684525761153</v>
+        <v>-0.00830918185998919</v>
       </c>
       <c r="N53" s="1">
-        <v>0.6310641482758126</v>
+        <v>3.4415695116296163</v>
       </c>
       <c r="O53" s="1">
-        <v>53.57142857142857</v>
+        <v>52.38095238095239</v>
       </c>
       <c r="P53" s="1">
         <v>11.84024085938085</v>
       </c>
       <c r="Q53" s="1">
-        <v>48.095238095238095</v>
+        <v>49.285714285714285</v>
       </c>
       <c r="R53" s="1">
-        <v>45.83333333333334</v>
+        <v>45.833333333333336</v>
       </c>
       <c r="S53" s="1" t="s">
         <v>114</v>
@@ -5393,19 +5393,19 @@
         <v>0.68</v>
       </c>
       <c r="F54" s="1">
-        <v>-0.19304729842879337</v>
+        <v>-0.22587610778068734</v>
       </c>
       <c r="G54" s="1">
         <v>1.58</v>
       </c>
       <c r="H54" s="1">
-        <v>42.82</v>
+        <v>44.6</v>
       </c>
       <c r="I54" s="1">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J54" s="1">
-        <v>-0.022109313461793265</v>
+        <v>-0.019674720900480898</v>
       </c>
       <c r="K54" s="1" t="b">
         <v>0</v>
@@ -5414,28 +5414,28 @@
         <v>348</v>
       </c>
       <c r="M54" s="1">
-        <v>-0.18931422934385223</v>
+        <v>-0.2073306791344418</v>
       </c>
       <c r="N54" s="1">
-        <v>-17.212790333533306</v>
+        <v>-16.46058021581565</v>
       </c>
       <c r="O54" s="1">
-        <v>20.238095238095237</v>
+        <v>19.047619047619047</v>
       </c>
       <c r="P54" s="1">
         <v>26.83257063748809</v>
       </c>
       <c r="Q54" s="1">
-        <v>46.3095238095238</v>
+        <v>47.14285714285714</v>
       </c>
       <c r="R54" s="1">
-        <v>31.488095238095237</v>
+        <v>31.130952380952383</v>
       </c>
       <c r="S54" s="1" t="s">
         <v>95</v>
       </c>
       <c r="T54" s="1">
-        <v>-27.11</v>
+        <v>-27.47</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
@@ -5455,19 +5455,19 @@
         <v>1.71</v>
       </c>
       <c r="F55" s="1">
-        <v>-0.07348611333178189</v>
+        <v>-0.14613784423314732</v>
       </c>
       <c r="G55" s="1">
-        <v>3.74</v>
+        <v>3.77</v>
       </c>
       <c r="H55" s="1">
-        <v>63.9</v>
+        <v>63.81</v>
       </c>
       <c r="I55" s="1">
-        <v>41.96</v>
+        <v>41.79</v>
       </c>
       <c r="J55" s="1">
-        <v>-0.0094372266902849</v>
+        <v>-0.003218821411904941</v>
       </c>
       <c r="K55" s="1" t="b">
         <v>0</v>
@@ -5476,28 +5476,28 @@
         <v>321</v>
       </c>
       <c r="M55" s="1">
-        <v>-0.05585058006843924</v>
+        <v>-0.057567435008836876</v>
       </c>
       <c r="N55" s="1">
-        <v>-3.8664254059919974</v>
+        <v>-1.4842558032551514</v>
       </c>
       <c r="O55" s="1">
-        <v>45.23809523809524</v>
+        <v>47.61904761904761</v>
       </c>
       <c r="P55" s="1">
         <v>52.65288503392759</v>
       </c>
       <c r="Q55" s="1">
-        <v>62.73809523809524</v>
+        <v>64.52380952380953</v>
       </c>
       <c r="R55" s="1">
-        <v>39.04761904761906</v>
+        <v>40.833333333333336</v>
       </c>
       <c r="S55" s="1" t="s">
         <v>109</v>
       </c>
       <c r="T55" s="1">
-        <v>-20.95</v>
+        <v>-19.17</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
@@ -5517,19 +5517,19 @@
         <v>-1.32</v>
       </c>
       <c r="F56" s="3">
-        <v>-0.22484567397568406</v>
+        <v>-0.31589162172699237</v>
       </c>
       <c r="G56" s="3">
         <v>2.05</v>
       </c>
       <c r="H56" s="3">
-        <v>43.19</v>
+        <v>41.42</v>
       </c>
       <c r="I56" s="3">
-        <v>-5.91</v>
+        <v>-7.38</v>
       </c>
       <c r="J56" s="3">
-        <v>-0.02516181656273842</v>
+        <v>-0.024576530428492824</v>
       </c>
       <c r="K56" s="3" t="b">
         <v>1</v>
@@ -5538,28 +5538,28 @@
         <v>249</v>
       </c>
       <c r="M56" s="3">
-        <v>-0.2180875316667389</v>
+        <v>-0.28231800090189274</v>
       </c>
       <c r="N56" s="3">
-        <v>-20.090120565821966</v>
+        <v>-23.959312392560737</v>
       </c>
       <c r="O56" s="3">
-        <v>17.857142857142858</v>
+        <v>10.714285714285714</v>
       </c>
       <c r="P56" s="3">
         <v>40.717118046641446</v>
       </c>
       <c r="Q56" s="3">
-        <v>45.23809523809523</v>
+        <v>43.33333333333332</v>
       </c>
       <c r="R56" s="3">
-        <v>27.976190476190474</v>
+        <v>25.714285714285715</v>
       </c>
       <c r="S56" s="3" t="s">
         <v>108</v>
       </c>
       <c r="T56" s="3">
-        <v>-20.99</v>
+        <v>-23.25</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
@@ -5579,19 +5579,19 @@
         <v>1.24</v>
       </c>
       <c r="F57" s="1">
-        <v>0.03418556245201523</v>
+        <v>0.0206035181830152</v>
       </c>
       <c r="G57" s="1">
         <v>1.65</v>
       </c>
       <c r="H57" s="1">
-        <v>35.01</v>
+        <v>38.21</v>
       </c>
       <c r="I57" s="1">
-        <v>-21.83</v>
+        <v>-20.31</v>
       </c>
       <c r="J57" s="1">
-        <v>0.0011690210894471037</v>
+        <v>0.0035088291968071706</v>
       </c>
       <c r="K57" s="1" t="b">
         <v>0</v>
@@ -5600,28 +5600,28 @@
         <v>3</v>
       </c>
       <c r="M57" s="1">
-        <v>0.038369174357552716</v>
+        <v>0.04138718821760068</v>
       </c>
       <c r="N57" s="1">
-        <v>5.555550036607185</v>
+        <v>8.41120651938861</v>
       </c>
       <c r="O57" s="1">
-        <v>63.095238095238095</v>
+        <v>61.904761904761905</v>
       </c>
       <c r="P57" s="1">
-        <v>37.631577254992756</v>
+        <v>35.9459458370989</v>
       </c>
       <c r="Q57" s="1">
-        <v>49.166666666666664</v>
+        <v>51.785714285714285</v>
       </c>
       <c r="R57" s="1">
-        <v>47.083333333333336</v>
+        <v>47.67857142857143</v>
       </c>
       <c r="S57" s="1" t="s">
         <v>101</v>
       </c>
       <c r="T57" s="1">
-        <v>25.13</v>
+        <v>25.73</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
@@ -5641,19 +5641,19 @@
         <v>0.97</v>
       </c>
       <c r="F58" s="3">
-        <v>-0.2939656832427451</v>
+        <v>-0.3511289432034123</v>
       </c>
       <c r="G58" s="3">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="H58" s="3">
-        <v>38.21</v>
+        <v>36.08</v>
       </c>
       <c r="I58" s="3">
-        <v>2.55</v>
+        <v>1.04</v>
       </c>
       <c r="J58" s="3">
-        <v>-0.027760195620194616</v>
+        <v>-0.02347529119863297</v>
       </c>
       <c r="K58" s="3" t="b">
         <v>1</v>
@@ -5662,28 +5662,28 @@
         <v>519</v>
       </c>
       <c r="M58" s="3">
-        <v>-0.28823735309516296</v>
+        <v>-0.3229910514642812</v>
       </c>
       <c r="N58" s="3">
-        <v>-27.105102708664376</v>
+        <v>-28.02661744879958</v>
       </c>
       <c r="O58" s="3">
-        <v>8.333333333333332</v>
+        <v>3.571428571428571</v>
       </c>
       <c r="P58" s="3">
         <v>41.76493344029593</v>
       </c>
       <c r="Q58" s="3">
-        <v>44.28571428571429</v>
+        <v>43.57142857142858</v>
       </c>
       <c r="R58" s="3">
-        <v>24.642857142857146</v>
+        <v>23.452380952380956</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>108</v>
       </c>
       <c r="T58" s="3">
-        <v>-34.56</v>
+        <v>-35.75</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
@@ -5703,19 +5703,19 @@
         <v>-4.45</v>
       </c>
       <c r="F59" s="3">
-        <v>-0.30642145796909237</v>
+        <v>-0.35196353882296316</v>
       </c>
       <c r="G59" s="3">
         <v>2.83</v>
       </c>
       <c r="H59" s="3">
-        <v>37</v>
+        <v>40.26</v>
       </c>
       <c r="I59" s="3">
-        <v>-34.47</v>
+        <v>-33.18</v>
       </c>
       <c r="J59" s="3">
-        <v>-0.035584909904490813</v>
+        <v>-0.03274734561863475</v>
       </c>
       <c r="K59" s="3" t="b">
         <v>0</v>
@@ -5724,10 +5724,10 @@
         <v>21</v>
       </c>
       <c r="M59" s="3">
-        <v>-0.2946429813735022</v>
+        <v>-0.293449513956361</v>
       </c>
       <c r="N59" s="3">
-        <v>-27.745665536498297</v>
+        <v>-25.072463698007557</v>
       </c>
       <c r="O59" s="3">
         <v>7.142857142857142</v>
@@ -5736,7 +5736,7 @@
         <v>46.90217032437056</v>
       </c>
       <c r="Q59" s="3">
-        <v>24.64285714285714</v>
+        <v>25.238095238095237</v>
       </c>
       <c r="R59" s="3">
         <v>11.54761904761905</v>
@@ -5759,25 +5759,25 @@
         <v>54.761904761904766</v>
       </c>
       <c r="D60" s="1">
-        <v>2.1310344827586207</v>
+        <v>2.142528735632184</v>
       </c>
       <c r="E60" s="1">
         <v>-0.53</v>
       </c>
       <c r="F60" s="1">
-        <v>0.00011090848615603541</v>
+        <v>-0.020251531770902317</v>
       </c>
       <c r="G60" s="1">
         <v>1.21</v>
       </c>
       <c r="H60" s="1">
-        <v>30.34</v>
+        <v>30.72</v>
       </c>
       <c r="I60" s="1">
-        <v>5.28</v>
+        <v>5.37</v>
       </c>
       <c r="J60" s="1">
-        <v>0.0026890684731403847</v>
+        <v>0.0008430588561212438</v>
       </c>
       <c r="K60" s="1" t="b">
         <v>1</v>
@@ -5786,28 +5786,28 @@
         <v>168</v>
       </c>
       <c r="M60" s="1">
-        <v>0.00146253694794507</v>
+        <v>-0.013536807605882384</v>
       </c>
       <c r="N60" s="1">
-        <v>1.8648862956464198</v>
+        <v>2.9188069370402863</v>
       </c>
       <c r="O60" s="1">
-        <v>57.14285714285714</v>
+        <v>51.19047619047619</v>
       </c>
       <c r="P60" s="1">
         <v>10.661929166819702</v>
       </c>
       <c r="Q60" s="1">
-        <v>48.57142857142857</v>
+        <v>47.14285714285714</v>
       </c>
       <c r="R60" s="1">
-        <v>48.15476190476191</v>
+        <v>45.65476190476191</v>
       </c>
       <c r="S60" s="1" t="s">
         <v>115</v>
       </c>
       <c r="T60" s="1">
-        <v>0.96</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
@@ -5827,19 +5827,19 @@
         <v>0.11</v>
       </c>
       <c r="F61" s="2">
-        <v>0.12445396323271768</v>
+        <v>0.13665521564582694</v>
       </c>
       <c r="G61" s="2">
         <v>0.2</v>
       </c>
       <c r="H61" s="2">
-        <v>51.61</v>
+        <v>55.02</v>
       </c>
       <c r="I61" s="2">
-        <v>12.36</v>
+        <v>13.38</v>
       </c>
       <c r="J61" s="2">
-        <v>0.002682390492088862</v>
+        <v>0.0022562035036327002</v>
       </c>
       <c r="K61" s="2" t="b">
         <v>0</v>
@@ -5848,28 +5848,28 @@
         <v>92</v>
       </c>
       <c r="M61" s="2">
-        <v>0.1193049024259023</v>
+        <v>0.11107531406479865</v>
       </c>
       <c r="N61" s="2">
-        <v>13.649122843442147</v>
+        <v>15.3800191041084</v>
       </c>
       <c r="O61" s="2">
-        <v>72.61904761904762</v>
+        <v>70.23809523809523</v>
       </c>
       <c r="P61" s="2">
         <v>7.56622762341097</v>
       </c>
       <c r="Q61" s="2">
-        <v>56.3095238095238</v>
+        <v>56.904761904761905</v>
       </c>
       <c r="R61" s="2">
-        <v>53.80952380952381</v>
+        <v>52.976190476190474</v>
       </c>
       <c r="S61" s="2" t="s">
         <v>116</v>
       </c>
       <c r="T61" s="2">
-        <v>7.83</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
@@ -5889,19 +5889,19 @@
         <v>-1.07</v>
       </c>
       <c r="F62" s="1">
-        <v>-0.11746136793860389</v>
+        <v>-0.14534398401134</v>
       </c>
       <c r="G62" s="1">
         <v>2.24</v>
       </c>
       <c r="H62" s="1">
-        <v>48.48</v>
+        <v>53.81</v>
       </c>
       <c r="I62" s="1">
-        <v>47.41</v>
+        <v>53.63</v>
       </c>
       <c r="J62" s="1">
-        <v>-0.007594870900274268</v>
+        <v>-0.003201504761632868</v>
       </c>
       <c r="K62" s="1" t="b">
         <v>0</v>
@@ -5910,10 +5910,10 @@
         <v>936</v>
       </c>
       <c r="M62" s="1">
-        <v>-0.10948032368804006</v>
+        <v>-0.10569513656074614</v>
       </c>
       <c r="N62" s="1">
-        <v>-9.229399767952083</v>
+        <v>-6.297025958446079</v>
       </c>
       <c r="O62" s="1">
         <v>32.142857142857146</v>
@@ -5922,16 +5922,16 @@
         <v>39.10478556320163</v>
       </c>
       <c r="Q62" s="1">
-        <v>65.95238095238095</v>
+        <v>68.57142857142857</v>
       </c>
       <c r="R62" s="1">
-        <v>41.904761904761905</v>
+        <v>42.73809523809524</v>
       </c>
       <c r="S62" s="1" t="s">
         <v>117</v>
       </c>
       <c r="T62" s="1">
-        <v>-26.2</v>
+        <v>-25.37</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
@@ -5945,55 +5945,55 @@
         <v>97.61904761904762</v>
       </c>
       <c r="D63" s="1">
-        <v>-1.571142284569138</v>
+        <v>-1.5714285714285714</v>
       </c>
       <c r="E63" s="1">
         <v>1.52</v>
       </c>
       <c r="F63" s="1">
-        <v>-0.07534634601813338</v>
+        <v>-0.160242230119019</v>
       </c>
       <c r="G63" s="1">
         <v>0.98</v>
       </c>
       <c r="H63" s="1">
-        <v>48.54</v>
+        <v>46.19</v>
       </c>
       <c r="I63" s="1">
-        <v>4.46</v>
+        <v>2.75</v>
       </c>
       <c r="J63" s="1">
-        <v>-0.021517666542102794</v>
+        <v>-0.019539477769417283</v>
       </c>
       <c r="K63" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="1">
         <v>364</v>
       </c>
       <c r="M63" s="1">
-        <v>-0.07547507253830377</v>
+        <v>-0.1608817276585447</v>
       </c>
       <c r="N63" s="1">
-        <v>-5.828874652978454</v>
+        <v>-11.81568506822593</v>
       </c>
       <c r="O63" s="1">
-        <v>40.476190476190474</v>
+        <v>23.809523809523807</v>
       </c>
       <c r="P63" s="1">
         <v>25.543467249515373</v>
       </c>
       <c r="Q63" s="1">
-        <v>46.9047619047619</v>
+        <v>45.59523809523809</v>
       </c>
       <c r="R63" s="1">
-        <v>35.95238095238095</v>
+        <v>30.95238095238095</v>
       </c>
       <c r="S63" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T63" s="1">
-        <v>-8.8</v>
+        <v>-13.8</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.25">
@@ -6013,19 +6013,19 @@
         <v>0.39</v>
       </c>
       <c r="F64" s="1">
-        <v>-0.0936857412895841</v>
+        <v>-0.07826768557150945</v>
       </c>
       <c r="G64" s="1">
         <v>0.36</v>
       </c>
       <c r="H64" s="1">
-        <v>36.13</v>
+        <v>32.74</v>
       </c>
       <c r="I64" s="1">
-        <v>-9.18</v>
+        <v>-9.9</v>
       </c>
       <c r="J64" s="1">
-        <v>-0.004285269128497558</v>
+        <v>-0.005731773645318966</v>
       </c>
       <c r="K64" s="1" t="b">
         <v>1</v>
@@ -6034,28 +6034,28 @@
         <v>-102</v>
       </c>
       <c r="M64" s="1">
-        <v>-0.09780498993503639</v>
+        <v>-0.09873160683633209</v>
       </c>
       <c r="N64" s="1">
-        <v>-8.061866392651721</v>
+        <v>-5.6006729860046764</v>
       </c>
       <c r="O64" s="1">
-        <v>36.904761904761905</v>
+        <v>35.714285714285715</v>
       </c>
       <c r="P64" s="1">
-        <v>15.23755966827515</v>
+        <v>15.66660418352099</v>
       </c>
       <c r="Q64" s="1">
-        <v>39.52380952380952</v>
+        <v>36.666666666666664</v>
       </c>
       <c r="R64" s="1">
-        <v>35.77380952380953</v>
+        <v>34.583333333333336</v>
       </c>
       <c r="S64" s="1" t="s">
         <v>118</v>
       </c>
       <c r="T64" s="1">
-        <v>9.74</v>
+        <v>8.55</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.25">
@@ -6075,19 +6075,19 @@
         <v>2.09</v>
       </c>
       <c r="F65" s="2">
-        <v>0.1274765267285201</v>
+        <v>0.12653804598976784</v>
       </c>
       <c r="G65" s="2">
         <v>0.87</v>
       </c>
       <c r="H65" s="2">
-        <v>57.54</v>
+        <v>61.38</v>
       </c>
       <c r="I65" s="2">
-        <v>16.82</v>
+        <v>18.99</v>
       </c>
       <c r="J65" s="2">
-        <v>0.008582770334031393</v>
+        <v>0.010026576004527079</v>
       </c>
       <c r="K65" s="2" t="b">
         <v>0</v>
@@ -6096,28 +6096,28 @@
         <v>79</v>
       </c>
       <c r="M65" s="2">
-        <v>0.12663980434741262</v>
+        <v>0.12238131198285074</v>
       </c>
       <c r="N65" s="2">
-        <v>14.38261303559319</v>
+        <v>16.51061889591362</v>
       </c>
       <c r="O65" s="2">
         <v>73.80952380952381</v>
       </c>
       <c r="P65" s="2">
-        <v>11.000474713303552</v>
+        <v>10.614074802632032</v>
       </c>
       <c r="Q65" s="2">
-        <v>66.66666666666667</v>
+        <v>67.5</v>
       </c>
       <c r="R65" s="2">
-        <v>59.34523809523809</v>
+        <v>59.82142857142857</v>
       </c>
       <c r="S65" s="2" t="s">
         <v>119</v>
       </c>
       <c r="T65" s="2">
-        <v>15.75</v>
+        <v>16.22</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
@@ -6131,25 +6131,25 @@
         <v>100</v>
       </c>
       <c r="D66" s="3">
-        <v>-0.682809713266566</v>
+        <v>-0.6829469062971602</v>
       </c>
       <c r="E66" s="3">
         <v>1.65</v>
       </c>
       <c r="F66" s="3">
-        <v>-0.28197481717561235</v>
+        <v>-0.35540440046254984</v>
       </c>
       <c r="G66" s="3">
-        <v>5.35</v>
+        <v>5.28</v>
       </c>
       <c r="H66" s="3">
-        <v>48.25</v>
+        <v>52.85</v>
       </c>
       <c r="I66" s="3">
-        <v>45.1</v>
+        <v>52.25</v>
       </c>
       <c r="J66" s="3">
-        <v>-0.01930812701154623</v>
+        <v>-0.013316325042583134</v>
       </c>
       <c r="K66" s="3" t="b">
         <v>0</v>
@@ -6158,28 +6158,28 @@
         <v>669</v>
       </c>
       <c r="M66" s="3">
-        <v>-0.25397679903855375</v>
+        <v>-0.21855192700404846</v>
       </c>
       <c r="N66" s="3">
-        <v>-23.679047303003447</v>
+        <v>-17.582705002776308</v>
       </c>
       <c r="O66" s="3">
-        <v>11.904761904761903</v>
+        <v>17.857142857142858</v>
       </c>
       <c r="P66" s="3">
         <v>56.49293299150161</v>
       </c>
       <c r="Q66" s="3">
-        <v>53.45238095238095</v>
+        <v>55.714285714285715</v>
       </c>
       <c r="R66" s="3">
-        <v>25.059523809523807</v>
+        <v>27.559523809523807</v>
       </c>
       <c r="S66" s="3" t="s">
         <v>101</v>
       </c>
       <c r="T66" s="3">
-        <v>-44.33</v>
+        <v>-41.83</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
@@ -6199,19 +6199,19 @@
         <v>-2.42</v>
       </c>
       <c r="F67" s="1">
-        <v>-0.2648852670764519</v>
+        <v>-0.3245414157229523</v>
       </c>
       <c r="G67" s="1">
         <v>2.1</v>
       </c>
       <c r="H67" s="1">
-        <v>44.07</v>
+        <v>45.45</v>
       </c>
       <c r="I67" s="1">
-        <v>28.77</v>
+        <v>30.3</v>
       </c>
       <c r="J67" s="1">
-        <v>-0.00805694021004898</v>
+        <v>-0.006999113410551259</v>
       </c>
       <c r="K67" s="1" t="b">
         <v>0</v>
@@ -6220,28 +6220,28 @@
         <v>515</v>
       </c>
       <c r="M67" s="1">
-        <v>-0.2578053084670807</v>
+        <v>-0.28936905104903843</v>
       </c>
       <c r="N67" s="1">
-        <v>-24.061898245856156</v>
+        <v>-24.6644174072753</v>
       </c>
       <c r="O67" s="1">
-        <v>10.714285714285714</v>
+        <v>8.333333333333332</v>
       </c>
       <c r="P67" s="1">
         <v>31.85898471566022</v>
       </c>
       <c r="Q67" s="1">
-        <v>60.833333333333336</v>
+        <v>60.952380952380956</v>
       </c>
       <c r="R67" s="1">
-        <v>34.22619047619048</v>
+        <v>33.392857142857146</v>
       </c>
       <c r="S67" s="1" t="s">
         <v>109</v>
       </c>
       <c r="T67" s="1">
-        <v>-31.81</v>
+        <v>-32.64</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
@@ -6261,19 +6261,19 @@
         <v>-1.75</v>
       </c>
       <c r="F68" s="1">
-        <v>0.11498925297726181</v>
+        <v>0.12098116029422168</v>
       </c>
       <c r="G68" s="1">
         <v>1</v>
       </c>
       <c r="H68" s="1">
-        <v>44.69</v>
+        <v>41.55</v>
       </c>
       <c r="I68" s="1">
-        <v>-22.62</v>
+        <v>-24.41</v>
       </c>
       <c r="J68" s="1">
-        <v>0.0166310390803228</v>
+        <v>0.015903007530378665</v>
       </c>
       <c r="K68" s="1" t="b">
         <v>0</v>
@@ -6282,28 +6282,28 @@
         <v>-253</v>
       </c>
       <c r="M68" s="1">
-        <v>0.11498925297726181</v>
+        <v>0.12098116029422168</v>
       </c>
       <c r="N68" s="1">
-        <v>13.217557898578114</v>
+        <v>16.370603727050714</v>
       </c>
       <c r="O68" s="1">
-        <v>71.42857142857143</v>
+        <v>72.61904761904762</v>
       </c>
       <c r="P68" s="1">
         <v>37.5868621181625</v>
       </c>
       <c r="Q68" s="1">
-        <v>55.35714285714285</v>
+        <v>53.57142857142857</v>
       </c>
       <c r="R68" s="1">
-        <v>49.82142857142858</v>
+        <v>49.94047619047619</v>
       </c>
       <c r="S68" s="1" t="s">
         <v>120</v>
       </c>
       <c r="T68" s="1">
-        <v>32.08</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
@@ -6323,49 +6323,49 @@
         <v>-0.51</v>
       </c>
       <c r="F69" s="1">
-        <v>-0.04998603396932634</v>
+        <v>-0.05160245320421514</v>
       </c>
       <c r="G69" s="1">
         <v>1.26</v>
       </c>
       <c r="H69" s="1">
-        <v>42.65</v>
+        <v>40.26</v>
       </c>
       <c r="I69" s="1">
-        <v>-5.49</v>
+        <v>-6.45</v>
       </c>
       <c r="J69" s="1">
-        <v>-0.0018231082887820442</v>
+        <v>-0.0026694513557431114</v>
       </c>
       <c r="K69" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" s="1">
         <v>3</v>
       </c>
       <c r="M69" s="1">
-        <v>-0.048312589207111345</v>
+        <v>-0.043288985190380935</v>
       </c>
       <c r="N69" s="1">
-        <v>-3.1126263198592152</v>
+        <v>-0.056410821409558276</v>
       </c>
       <c r="O69" s="1">
-        <v>47.61904761904761</v>
+        <v>48.80952380952381</v>
       </c>
       <c r="P69" s="1">
         <v>16.710870321490763</v>
       </c>
       <c r="Q69" s="1">
-        <v>52.14285714285714</v>
+        <v>50.23809523809524</v>
       </c>
       <c r="R69" s="1">
-        <v>45.95238095238095</v>
+        <v>46.30952380952381</v>
       </c>
       <c r="S69" s="1" t="s">
         <v>101</v>
       </c>
       <c r="T69" s="1">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
@@ -6385,19 +6385,19 @@
         <v>0.14</v>
       </c>
       <c r="F70" s="2">
-        <v>0.14785845586039803</v>
+        <v>0.18148827115001517</v>
       </c>
       <c r="G70" s="2">
         <v>0.33</v>
       </c>
       <c r="H70" s="2">
-        <v>60.63</v>
+        <v>63.49</v>
       </c>
       <c r="I70" s="2">
-        <v>10.31</v>
+        <v>11.64</v>
       </c>
       <c r="J70" s="2">
-        <v>0.011556005234894402</v>
+        <v>0.011031310227524998</v>
       </c>
       <c r="K70" s="2" t="b">
         <v>0</v>
@@ -6406,10 +6406,10 @@
         <v>-81</v>
       </c>
       <c r="M70" s="2">
-        <v>0.14354611743469015</v>
+        <v>0.16006510357590398</v>
       </c>
       <c r="N70" s="2">
-        <v>16.073244344320926</v>
+        <v>20.27899805521894</v>
       </c>
       <c r="O70" s="2">
         <v>78.57142857142857</v>
@@ -6418,7 +6418,7 @@
         <v>10.873073633899006</v>
       </c>
       <c r="Q70" s="2">
-        <v>63.0952380952381</v>
+        <v>63.80952380952381</v>
       </c>
       <c r="R70" s="2">
         <v>57.916666666666664</v>
@@ -6447,49 +6447,49 @@
         <v>0.12</v>
       </c>
       <c r="F71" s="1">
-        <v>-0.10353830882476733</v>
+        <v>-0.10410043717522413</v>
       </c>
       <c r="G71" s="1">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="H71" s="1">
-        <v>56.52</v>
+        <v>56.09</v>
       </c>
       <c r="I71" s="1">
-        <v>-15.71</v>
+        <v>-15.89</v>
       </c>
       <c r="J71" s="1">
-        <v>-0.0115712870718021</v>
+        <v>-0.011294694481653683</v>
       </c>
       <c r="K71" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L71" s="1">
         <v>-42</v>
       </c>
       <c r="M71" s="1">
-        <v>-0.1005775988608485</v>
+        <v>-0.08907224499637001</v>
       </c>
       <c r="N71" s="1">
-        <v>-8.339127285232923</v>
+        <v>-4.6347368020084625</v>
       </c>
       <c r="O71" s="1">
-        <v>34.523809523809526</v>
+        <v>40.476190476190474</v>
       </c>
       <c r="P71" s="1">
         <v>31.34692685044607</v>
       </c>
       <c r="Q71" s="1">
-        <v>48.92857142857144</v>
+        <v>48.92857142857143</v>
       </c>
       <c r="R71" s="1">
-        <v>34.82142857142857</v>
+        <v>36.72619047619048</v>
       </c>
       <c r="S71" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T71" s="1">
-        <v>5.37</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.25">
@@ -6509,19 +6509,19 @@
         <v>-0.35</v>
       </c>
       <c r="F72" s="2">
-        <v>0.355611520246977</v>
+        <v>0.38700394876648403</v>
       </c>
       <c r="G72" s="2">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="H72" s="2">
-        <v>70.34</v>
+        <v>71.95</v>
       </c>
       <c r="I72" s="2">
-        <v>21.31</v>
+        <v>22.46</v>
       </c>
       <c r="J72" s="2">
-        <v>0.018940721330516136</v>
+        <v>0.020482341301313448</v>
       </c>
       <c r="K72" s="2" t="b">
         <v>1</v>
@@ -6530,28 +6530,28 @@
         <v>48</v>
       </c>
       <c r="M72" s="2">
-        <v>0.3547747978658695</v>
+        <v>0.3831669635293298</v>
       </c>
       <c r="N72" s="2">
-        <v>37.196112387438866</v>
+        <v>42.58918405056152</v>
       </c>
       <c r="O72" s="2">
-        <v>91.66666666666666</v>
+        <v>90.47619047619048</v>
       </c>
       <c r="P72" s="2">
-        <v>16.66857152537527</v>
+        <v>16.43822745912965</v>
       </c>
       <c r="Q72" s="2">
-        <v>67.5</v>
+        <v>67.73809523809524</v>
       </c>
       <c r="R72" s="2">
-        <v>61.07142857142857</v>
+        <v>60.952380952380956</v>
       </c>
       <c r="S72" s="2" t="s">
         <v>105</v>
       </c>
       <c r="T72" s="2">
-        <v>21.19</v>
+        <v>21.07</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.25">
@@ -6565,25 +6565,25 @@
         <v>44.047619047619044</v>
       </c>
       <c r="D73" s="1">
-        <v>11.228571428571428</v>
+        <v>11.242857142857142</v>
       </c>
       <c r="E73" s="1">
         <v>0.45</v>
       </c>
       <c r="F73" s="1">
-        <v>-0.223425028502856</v>
+        <v>-0.22311173466010972</v>
       </c>
       <c r="G73" s="1">
         <v>1.1</v>
       </c>
       <c r="H73" s="1">
-        <v>35.3</v>
+        <v>35.69</v>
       </c>
       <c r="I73" s="1">
-        <v>-27.91</v>
+        <v>-27.82</v>
       </c>
       <c r="J73" s="1">
-        <v>-0.015605210804864569</v>
+        <v>-0.01665608966991251</v>
       </c>
       <c r="K73" s="1" t="b">
         <v>0</v>
@@ -6592,10 +6592,10 @@
         <v>-168</v>
       </c>
       <c r="M73" s="1">
-        <v>-0.22278139590200408</v>
+        <v>-0.21991424696248119</v>
       </c>
       <c r="N73" s="1">
-        <v>-20.559506989348492</v>
+        <v>-17.71893699861958</v>
       </c>
       <c r="O73" s="1">
         <v>16.666666666666664</v>
@@ -6604,78 +6604,78 @@
         <v>24.466963086179547</v>
       </c>
       <c r="Q73" s="1">
-        <v>41.19047619047618</v>
+        <v>40.95238095238095</v>
       </c>
       <c r="R73" s="1">
-        <v>31.250000000000004</v>
+        <v>31.011904761904763</v>
       </c>
       <c r="S73" s="1" t="s">
         <v>121</v>
       </c>
       <c r="T73" s="1">
-        <v>-0.76</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
+      <c r="A74" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B74" s="1">
+      <c r="B74" s="3">
         <v>0.42</v>
       </c>
-      <c r="C74" s="1">
+      <c r="C74" s="3">
         <v>34.523809523809526</v>
       </c>
-      <c r="D74" s="1">
+      <c r="D74" s="3">
         <v>97.42857142857143</v>
       </c>
-      <c r="E74" s="1">
+      <c r="E74" s="3">
         <v>-3.73</v>
       </c>
-      <c r="F74" s="1">
-        <v>-0.25077736060496936</v>
-      </c>
-      <c r="G74" s="1">
+      <c r="F74" s="3">
+        <v>-0.28198268431201057</v>
+      </c>
+      <c r="G74" s="3">
         <v>1.25</v>
       </c>
-      <c r="H74" s="1">
-        <v>37.02</v>
-      </c>
-      <c r="I74" s="1">
-        <v>-6.54</v>
-      </c>
-      <c r="J74" s="1">
-        <v>-0.020688608993560825</v>
-      </c>
-      <c r="K74" s="1" t="b">
+      <c r="H74" s="3">
+        <v>37.31</v>
+      </c>
+      <c r="I74" s="3">
+        <v>-6.51</v>
+      </c>
+      <c r="J74" s="3">
+        <v>-0.020148539678220282</v>
+      </c>
+      <c r="K74" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L74" s="1">
+      <c r="L74" s="3">
         <v>32</v>
       </c>
-      <c r="M74" s="1">
-        <v>-0.24916827910283956</v>
-      </c>
-      <c r="N74" s="1">
-        <v>-23.19819530943203</v>
-      </c>
-      <c r="O74" s="1">
-        <v>14.285714285714285</v>
-      </c>
-      <c r="P74" s="1">
+      <c r="M74" s="3">
+        <v>-0.27398896506793924</v>
+      </c>
+      <c r="N74" s="3">
+        <v>-23.126408809165383</v>
+      </c>
+      <c r="O74" s="3">
+        <v>11.904761904761903</v>
+      </c>
+      <c r="P74" s="3">
         <v>28.76752600761915</v>
       </c>
-      <c r="Q74" s="1">
-        <v>45.47619047619048</v>
-      </c>
-      <c r="R74" s="1">
-        <v>30.77380952380952</v>
-      </c>
-      <c r="S74" s="1" t="s">
+      <c r="Q74" s="3">
+        <v>43.92857142857142</v>
+      </c>
+      <c r="R74" s="3">
+        <v>29.46428571428571</v>
+      </c>
+      <c r="S74" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="T74" s="1">
-        <v>-27.82</v>
+      <c r="T74" s="3">
+        <v>-29.13</v>
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
@@ -6695,19 +6695,19 @@
         <v>-0.07</v>
       </c>
       <c r="F75" s="3">
-        <v>-0.34233848521827903</v>
+        <v>-0.3827096309968233</v>
       </c>
       <c r="G75" s="3">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="H75" s="3">
-        <v>38.92</v>
+        <v>42.99</v>
       </c>
       <c r="I75" s="3">
-        <v>-33.56</v>
+        <v>-31.88</v>
       </c>
       <c r="J75" s="3">
-        <v>-0.02413302452368327</v>
+        <v>-0.021794288971493467</v>
       </c>
       <c r="K75" s="3" t="b">
         <v>0</v>
@@ -6716,10 +6716,10 @@
         <v>10</v>
       </c>
       <c r="M75" s="3">
-        <v>-0.3277923884390256</v>
+        <v>-0.31076615780018124</v>
       </c>
       <c r="N75" s="3">
-        <v>-31.060606243050643</v>
+        <v>-26.804128082389596</v>
       </c>
       <c r="O75" s="3">
         <v>4.761904761904762</v>
@@ -6728,16 +6728,16 @@
         <v>51.49813033405746</v>
       </c>
       <c r="Q75" s="3">
-        <v>40.95238095238095</v>
+        <v>41.666666666666664</v>
       </c>
       <c r="R75" s="3">
-        <v>23.035714285714278</v>
+        <v>22.916666666666664</v>
       </c>
       <c r="S75" s="3" t="s">
         <v>107</v>
       </c>
       <c r="T75" s="3">
-        <v>-2.7</v>
+        <v>-2.82</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
@@ -6757,19 +6757,19 @@
         <v>12.84</v>
       </c>
       <c r="F76" s="3">
-        <v>-0.03477008748832573</v>
+        <v>-0.0611885072682134</v>
       </c>
       <c r="G76" s="3">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="H76" s="3">
-        <v>29.92</v>
+        <v>32.97</v>
       </c>
       <c r="I76" s="3">
-        <v>36.77</v>
+        <v>38.22</v>
       </c>
       <c r="J76" s="3">
-        <v>-0.026809012666337013</v>
+        <v>-0.028462291768440205</v>
       </c>
       <c r="K76" s="3" t="b">
         <v>0</v>
@@ -6778,13 +6778,13 @@
         <v>42</v>
       </c>
       <c r="M76" s="3">
-        <v>-0.03534935682909246</v>
+        <v>-0.06470574373560478</v>
       </c>
       <c r="N76" s="3">
-        <v>-1.8163030820573203</v>
+        <v>-2.1980866759319406</v>
       </c>
       <c r="O76" s="3">
-        <v>50</v>
+        <v>44.047619047619044</v>
       </c>
       <c r="P76" s="3">
         <v>29.799918858582526</v>
@@ -6793,13 +6793,13 @@
         <v>27.142857142857146</v>
       </c>
       <c r="R76" s="3">
-        <v>23.333333333333332</v>
+        <v>21.30952380952381</v>
       </c>
       <c r="S76" s="3" t="s">
         <v>123</v>
       </c>
       <c r="T76" s="3">
-        <v>-50.39</v>
+        <v>-52.41</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
@@ -6819,7 +6819,7 @@
         <v>-9.21</v>
       </c>
       <c r="F77" s="2">
-        <v>0.5855054885366315</v>
+        <v>0.6232657291118143</v>
       </c>
       <c r="G77" s="2">
         <v>0.91</v>
@@ -6828,10 +6828,10 @@
         <v>68.71</v>
       </c>
       <c r="I77" s="2">
-        <v>37.43</v>
+        <v>37.33</v>
       </c>
       <c r="J77" s="2">
-        <v>0.0408141427825861</v>
+        <v>0.038466396827951506</v>
       </c>
       <c r="K77" s="2" t="b">
         <v>1</v>
@@ -6840,10 +6840,10 @@
         <v>-5</v>
       </c>
       <c r="M77" s="2">
-        <v>0.5849262191958648</v>
+        <v>0.6203879901839486</v>
       </c>
       <c r="N77" s="2">
-        <v>60.21125452043841</v>
+        <v>66.3112867160234</v>
       </c>
       <c r="O77" s="2">
         <v>97.61904761904762</v>
@@ -6852,7 +6852,7 @@
         <v>18.71809072120826</v>
       </c>
       <c r="Q77" s="2">
-        <v>66.90476190476191</v>
+        <v>66.42857142857143</v>
       </c>
       <c r="R77" s="2">
         <v>60.17857142857143</v>
@@ -6881,19 +6881,19 @@
         <v>-3.54</v>
       </c>
       <c r="F78" s="2">
-        <v>0.26017740358189306</v>
+        <v>0.28791856966256796</v>
       </c>
       <c r="G78" s="2">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="H78" s="2">
-        <v>66.56</v>
+        <v>67.88</v>
       </c>
       <c r="I78" s="2">
-        <v>33.66</v>
+        <v>34.12</v>
       </c>
       <c r="J78" s="2">
-        <v>0.008528919767391452</v>
+        <v>0.010085901055516088</v>
       </c>
       <c r="K78" s="2" t="b">
         <v>1</v>
@@ -6902,28 +6902,28 @@
         <v>-2</v>
       </c>
       <c r="M78" s="2">
-        <v>0.260821036182745</v>
+        <v>0.29143580612995934</v>
       </c>
       <c r="N78" s="2">
-        <v>27.800736219126428</v>
+        <v>33.41606831062446</v>
       </c>
       <c r="O78" s="2">
-        <v>88.09523809523809</v>
+        <v>86.90476190476191</v>
       </c>
       <c r="P78" s="2">
         <v>16.006637557486414</v>
       </c>
       <c r="Q78" s="2">
-        <v>60.11904761904761</v>
+        <v>60.71428571428571</v>
       </c>
       <c r="R78" s="2">
-        <v>55.11904761904762</v>
+        <v>55.23809523809524</v>
       </c>
       <c r="S78" s="2" t="s">
         <v>106</v>
       </c>
       <c r="T78" s="2">
-        <v>6.95</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.25">
@@ -6943,19 +6943,19 @@
         <v>0.32</v>
       </c>
       <c r="F79" s="2">
-        <v>0.23526566934943535</v>
+        <v>0.22072735281538344</v>
       </c>
       <c r="G79" s="2">
         <v>0.82</v>
       </c>
       <c r="H79" s="2">
-        <v>54.21</v>
+        <v>52.71</v>
       </c>
       <c r="I79" s="2">
-        <v>12.06</v>
+        <v>11.64</v>
       </c>
       <c r="J79" s="2">
-        <v>0.011809951162798203</v>
+        <v>0.0106762542842756</v>
       </c>
       <c r="K79" s="2" t="b">
         <v>0</v>
@@ -6964,28 +6964,28 @@
         <v>6</v>
       </c>
       <c r="M79" s="2">
-        <v>0.2341071306679019</v>
+        <v>0.2149718749596521</v>
       </c>
       <c r="N79" s="2">
-        <v>25.129345667642113</v>
+        <v>25.76967519359375</v>
       </c>
       <c r="O79" s="2">
-        <v>86.90476190476191</v>
+        <v>80.95238095238095</v>
       </c>
       <c r="P79" s="2">
         <v>11.616065285425229</v>
       </c>
       <c r="Q79" s="2">
-        <v>57.5</v>
+        <v>55.714285714285715</v>
       </c>
       <c r="R79" s="2">
-        <v>56.30952380952381</v>
+        <v>54.28571428571429</v>
       </c>
       <c r="S79" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T79" s="2">
-        <v>16.43</v>
+        <v>14.41</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.25">
@@ -7005,19 +7005,19 @@
         <v>0.86</v>
       </c>
       <c r="F80" s="2">
-        <v>0.09779666499891404</v>
+        <v>0.0843399422476147</v>
       </c>
       <c r="G80" s="2">
         <v>0.77</v>
       </c>
       <c r="H80" s="2">
-        <v>51.46</v>
+        <v>49.05</v>
       </c>
       <c r="I80" s="2">
-        <v>10.81</v>
+        <v>10.18</v>
       </c>
       <c r="J80" s="2">
-        <v>0.005145519256080646</v>
+        <v>0.0050444272596201515</v>
       </c>
       <c r="K80" s="2" t="b">
         <v>0</v>
@@ -7026,90 +7026,90 @@
         <v>156</v>
       </c>
       <c r="M80" s="2">
-        <v>0.09631631001695462</v>
+        <v>0.07698572054306907</v>
       </c>
       <c r="N80" s="2">
-        <v>11.350263602547383</v>
+        <v>11.971059751935451</v>
       </c>
       <c r="O80" s="2">
-        <v>69.04761904761905</v>
+        <v>65.47619047619048</v>
       </c>
       <c r="P80" s="2">
         <v>6.707278396222185</v>
       </c>
       <c r="Q80" s="2">
-        <v>58.333333333333336</v>
+        <v>57.38095238095238</v>
       </c>
       <c r="R80" s="2">
-        <v>54.76190476190476</v>
+        <v>53.57142857142857</v>
       </c>
       <c r="S80" s="2" t="s">
         <v>109</v>
       </c>
       <c r="T80" s="2">
-        <v>4.34</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A81" s="2" t="s">
+      <c r="A81" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B81" s="2">
+      <c r="B81" s="1">
         <v>23.34</v>
       </c>
-      <c r="C81" s="2">
+      <c r="C81" s="1">
         <v>95.23809523809523</v>
       </c>
-      <c r="D81" s="2">
+      <c r="D81" s="1">
         <v>-0.9305912596401028</v>
       </c>
-      <c r="E81" s="2">
+      <c r="E81" s="1">
         <v>-1.2</v>
       </c>
-      <c r="F81" s="2">
-        <v>0.03644260659650999</v>
-      </c>
-      <c r="G81" s="2">
+      <c r="F81" s="1">
+        <v>0.0044873316391628865</v>
+      </c>
+      <c r="G81" s="1">
         <v>1.01</v>
       </c>
-      <c r="H81" s="2">
-        <v>45.95</v>
-      </c>
-      <c r="I81" s="2">
-        <v>9.51</v>
-      </c>
-      <c r="J81" s="2">
-        <v>0.005047171522951603</v>
-      </c>
-      <c r="K81" s="2" t="b">
+      <c r="H81" s="1">
+        <v>43.87</v>
+      </c>
+      <c r="I81" s="1">
+        <v>9.05</v>
+      </c>
+      <c r="J81" s="1">
+        <v>0.004610365580476141</v>
+      </c>
+      <c r="K81" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L81" s="2">
+      <c r="L81" s="1">
         <v>109</v>
       </c>
-      <c r="M81" s="2">
-        <v>0.036506969856595184</v>
-      </c>
-      <c r="N81" s="2">
-        <v>5.369329586511442</v>
-      </c>
-      <c r="O81" s="2">
-        <v>61.904761904761905</v>
-      </c>
-      <c r="P81" s="2">
-        <v>6.716293473999743</v>
-      </c>
-      <c r="Q81" s="2">
-        <v>55.95238095238095</v>
-      </c>
-      <c r="R81" s="2">
-        <v>51.488095238095234</v>
-      </c>
-      <c r="S81" s="2" t="s">
+      <c r="M81" s="1">
+        <v>0.004807080408925746</v>
+      </c>
+      <c r="N81" s="1">
+        <v>4.753195738521108</v>
+      </c>
+      <c r="O81" s="1">
+        <v>55.952380952380956</v>
+      </c>
+      <c r="P81" s="1">
+        <v>6.0971680093981355</v>
+      </c>
+      <c r="Q81" s="1">
+        <v>54.76190476190476</v>
+      </c>
+      <c r="R81" s="1">
+        <v>49.82142857142857</v>
+      </c>
+      <c r="S81" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="T81" s="2">
-        <v>6.18</v>
+      <c r="T81" s="1">
+        <v>4.52</v>
       </c>
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.25">
@@ -7129,49 +7129,49 @@
         <v>0.23</v>
       </c>
       <c r="F82" s="2">
-        <v>0.09327502320462885</v>
+        <v>0.09374269714401647</v>
       </c>
       <c r="G82" s="2">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H82" s="2">
-        <v>63.09</v>
+        <v>65.39</v>
       </c>
       <c r="I82" s="2">
-        <v>16.65</v>
+        <v>17.8</v>
       </c>
       <c r="J82" s="2">
-        <v>0.008846273422963275</v>
+        <v>0.007968058636898694</v>
       </c>
       <c r="K82" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L82" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M82" s="2">
-        <v>0.09366120276514</v>
+        <v>0.09598093853235645</v>
       </c>
       <c r="N82" s="2">
-        <v>11.084752877365919</v>
+        <v>13.870581550864175</v>
       </c>
       <c r="O82" s="2">
-        <v>67.85714285714286</v>
+        <v>69.04761904761905</v>
       </c>
       <c r="P82" s="2">
         <v>12.706223591210087</v>
       </c>
       <c r="Q82" s="2">
-        <v>61.66666666666667</v>
+        <v>60.714285714285715</v>
       </c>
       <c r="R82" s="2">
-        <v>52.14285714285714</v>
+        <v>51.845238095238095</v>
       </c>
       <c r="S82" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T82" s="2">
-        <v>0.01</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.25">
@@ -7185,25 +7185,25 @@
         <v>92.85714285714286</v>
       </c>
       <c r="D83" s="1">
-        <v>-2.3415369161225517</v>
+        <v>-2.336514314414867</v>
       </c>
       <c r="E83" s="1">
         <v>2.31</v>
       </c>
       <c r="F83" s="1">
-        <v>-0.10393878933499942</v>
+        <v>-0.09998981403199197</v>
       </c>
       <c r="G83" s="1">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="H83" s="1">
-        <v>52.82</v>
+        <v>52.91</v>
       </c>
       <c r="I83" s="1">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="J83" s="1">
-        <v>-0.005985794666373905</v>
+        <v>-0.00553602339977182</v>
       </c>
       <c r="K83" s="1" t="b">
         <v>0</v>
@@ -7212,28 +7212,28 @@
         <v>174</v>
       </c>
       <c r="M83" s="1">
-        <v>-0.10271588739338078</v>
+        <v>-0.0935948386367349</v>
       </c>
       <c r="N83" s="1">
-        <v>-8.552956138486152</v>
+        <v>-5.086996166044951</v>
       </c>
       <c r="O83" s="1">
-        <v>33.33333333333333</v>
+        <v>39.285714285714285</v>
       </c>
       <c r="P83" s="1">
         <v>20.22353911360907</v>
       </c>
       <c r="Q83" s="1">
-        <v>48.333333333333336</v>
+        <v>48.214285714285715</v>
       </c>
       <c r="R83" s="1">
-        <v>35.17857142857143</v>
+        <v>36.8452380952381</v>
       </c>
       <c r="S83" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T83" s="1">
-        <v>-11.59</v>
+        <v>-9.92</v>
       </c>
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.25">
@@ -7247,25 +7247,25 @@
         <v>51.19047619047619</v>
       </c>
       <c r="D84" s="1">
-        <v>1.768768768768769</v>
+        <v>1.765765765765766</v>
       </c>
       <c r="E84" s="1">
         <v>0.25</v>
       </c>
       <c r="F84" s="1">
-        <v>-0.11599547572192025</v>
+        <v>-0.10251326537077814</v>
       </c>
       <c r="G84" s="1">
         <v>0.98</v>
       </c>
       <c r="H84" s="1">
-        <v>44.08</v>
+        <v>47.72</v>
       </c>
       <c r="I84" s="1">
-        <v>13.25</v>
+        <v>14.75</v>
       </c>
       <c r="J84" s="1">
-        <v>-0.004470920292175302</v>
+        <v>-0.0033472350322131072</v>
       </c>
       <c r="K84" s="1" t="b">
         <v>0</v>
@@ -7274,28 +7274,28 @@
         <v>374</v>
       </c>
       <c r="M84" s="1">
-        <v>-0.11612420224209064</v>
+        <v>-0.10315276291030384</v>
       </c>
       <c r="N84" s="1">
-        <v>-9.89378762335714</v>
+        <v>-6.042788593401852</v>
       </c>
       <c r="O84" s="1">
-        <v>29.761904761904763</v>
+        <v>34.523809523809526</v>
       </c>
       <c r="P84" s="1">
         <v>17.353844275841347</v>
       </c>
       <c r="Q84" s="1">
-        <v>50.11904761904762</v>
+        <v>50.238095238095234</v>
       </c>
       <c r="R84" s="1">
-        <v>35.535714285714285</v>
+        <v>36.964285714285715</v>
       </c>
       <c r="S84" s="1" t="s">
         <v>132</v>
       </c>
       <c r="T84" s="1">
-        <v>-21.11</v>
+        <v>-19.68</v>
       </c>
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.25">
@@ -7315,19 +7315,19 @@
         <v>0.61</v>
       </c>
       <c r="F85" s="1">
-        <v>0.03350004667964804</v>
+        <v>0.05354553650639611</v>
       </c>
       <c r="G85" s="1">
         <v>0.95</v>
       </c>
       <c r="H85" s="1">
-        <v>32.1</v>
+        <v>35.4</v>
       </c>
       <c r="I85" s="1">
-        <v>6.97</v>
+        <v>7.56</v>
       </c>
       <c r="J85" s="1">
-        <v>0.0015280819620693672</v>
+        <v>0.000695414352035943</v>
       </c>
       <c r="K85" s="1" t="b">
         <v>0</v>
@@ -7336,28 +7336,28 @@
         <v>131</v>
       </c>
       <c r="M85" s="1">
-        <v>0.03317823037922207</v>
+        <v>0.05194679265758184</v>
       </c>
       <c r="N85" s="1">
-        <v>5.036455638774131</v>
+        <v>9.46716696338671</v>
       </c>
       <c r="O85" s="1">
-        <v>60.71428571428571</v>
+        <v>63.095238095238095</v>
       </c>
       <c r="P85" s="1">
         <v>9.561516372520778</v>
       </c>
       <c r="Q85" s="1">
-        <v>47.85714285714286</v>
+        <v>48.45238095238095</v>
       </c>
       <c r="R85" s="1">
-        <v>48.75</v>
+        <v>49.345238095238095</v>
       </c>
       <c r="S85" s="1" t="s">
         <v>105</v>
       </c>
       <c r="T85" s="1">
-        <v>1.98</v>
+        <v>2.58</v>
       </c>
     </row>
   </sheetData>
@@ -7384,7 +7384,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>48.45238095238095</v>
+        <v>46.666666666666664</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -7392,7 +7392,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>48.69047619047619</v>
+        <v>50.23809523809524</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7400,7 +7400,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>54.523809523809526</v>
+        <v>54.58333333333333</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -7408,7 +7408,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>33.035714285714285</v>
+        <v>35.05952380952381</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -7416,7 +7416,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>37.67857142857143</v>
+        <v>36.011904761904766</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7424,7 +7424,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>55.00000000000001</v>
+        <v>55.23809523809524</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -7432,7 +7432,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>40.6547619047619</v>
+        <v>39.107142857142854</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -7440,7 +7440,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>60.05952380952382</v>
+        <v>59.702380952380956</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -7448,7 +7448,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>49.16666666666667</v>
+        <v>45.714285714285715</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -7472,7 +7472,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>37.97619047619047</v>
+        <v>38.33333333333333</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -7488,7 +7488,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>23.273809523809526</v>
+        <v>25.059523809523814</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -7504,7 +7504,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>30.535714285714292</v>
+        <v>33.03571428571429</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -7512,7 +7512,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>23.214285714285722</v>
+        <v>22.91666666666667</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -7520,7 +7520,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>53.63095238095239</v>
+        <v>53.750000000000014</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -7528,7 +7528,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>56.19047619047619</v>
+        <v>55.83333333333333</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -7536,7 +7536,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>21.904761904761905</v>
+        <v>22.67857142857143</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -7544,7 +7544,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>34.88095238095238</v>
+        <v>33.45238095238095</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -7552,7 +7552,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>53.03571428571429</v>
+        <v>55.05952380952381</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -7560,7 +7560,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>30.41666666666667</v>
+        <v>33.273809523809526</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -7568,7 +7568,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>5.773809523809524</v>
+        <v>5.535714285714283</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -7576,7 +7576,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>-2.321428571428573</v>
+        <v>-1.488095238095239</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -7592,7 +7592,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>33.63095238095238</v>
+        <v>35.29761904761905</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -7600,7 +7600,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>43.273809523809526</v>
+        <v>43.75</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -7608,7 +7608,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>44.226190476190474</v>
+        <v>41.36904761904762</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -7616,7 +7616,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>40.41666666666667</v>
+        <v>38.03571428571429</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -7624,7 +7624,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>30.41666666666667</v>
+        <v>28.750000000000007</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -7632,7 +7632,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>59.761904761904766</v>
+        <v>60.11904761904761</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -7640,7 +7640,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>35.83333333333333</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -7648,7 +7648,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>39.16666666666667</v>
+        <v>38.095238095238095</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -7656,7 +7656,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>42.20238095238096</v>
+        <v>42.26190476190476</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -7664,7 +7664,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>52.85714285714286</v>
+        <v>53.21428571428571</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -7672,7 +7672,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>65.6547619047619</v>
+        <v>65.35714285714286</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -7680,7 +7680,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>41.13095238095239</v>
+        <v>40.773809523809526</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -7688,7 +7688,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>43.035714285714285</v>
+        <v>46.607142857142854</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -7696,7 +7696,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>13.69047619047619</v>
+        <v>16.666666666666668</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -7704,7 +7704,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>32.738095238095234</v>
+        <v>32.61904761904761</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -7712,7 +7712,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>58.98809523809524</v>
+        <v>58.273809523809526</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -7720,7 +7720,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>52.97619047619048</v>
+        <v>52.857142857142854</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -7728,7 +7728,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>40.41666666666667</v>
+        <v>41.964285714285715</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -7744,7 +7744,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>45.714285714285715</v>
+        <v>43.095238095238095</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -7760,7 +7760,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>53.86904761904761</v>
+        <v>56.60714285714286</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -7768,7 +7768,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>20.535714285714285</v>
+        <v>22.44047619047619</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -7776,7 +7776,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>42.55952380952381</v>
+        <v>42.91666666666666</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -7784,7 +7784,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>22.142857142857146</v>
+        <v>23.452380952380963</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -7792,7 +7792,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>45.83333333333334</v>
+        <v>45.833333333333336</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -7800,7 +7800,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>31.488095238095237</v>
+        <v>31.130952380952383</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -7808,7 +7808,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>39.04761904761906</v>
+        <v>40.833333333333336</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -7816,7 +7816,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>27.976190476190474</v>
+        <v>25.714285714285715</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -7824,7 +7824,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>47.083333333333336</v>
+        <v>47.67857142857143</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -7832,7 +7832,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>24.642857142857146</v>
+        <v>23.452380952380956</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -7848,7 +7848,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>48.15476190476191</v>
+        <v>45.65476190476191</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -7856,7 +7856,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>53.80952380952381</v>
+        <v>52.976190476190474</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -7864,7 +7864,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>41.904761904761905</v>
+        <v>42.73809523809524</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -7872,7 +7872,7 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>35.95238095238095</v>
+        <v>30.95238095238095</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -7880,7 +7880,7 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>35.77380952380953</v>
+        <v>34.583333333333336</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -7888,7 +7888,7 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>59.34523809523809</v>
+        <v>59.82142857142857</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -7896,7 +7896,7 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>25.059523809523807</v>
+        <v>27.559523809523807</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -7904,7 +7904,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>34.22619047619048</v>
+        <v>33.392857142857146</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -7912,7 +7912,7 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>49.82142857142858</v>
+        <v>49.94047619047619</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -7920,7 +7920,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>45.95238095238095</v>
+        <v>46.30952380952381</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -7936,7 +7936,7 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>34.82142857142857</v>
+        <v>36.72619047619048</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -7944,7 +7944,7 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>61.07142857142857</v>
+        <v>60.952380952380956</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -7952,7 +7952,7 @@
         <v>72</v>
       </c>
       <c r="B73">
-        <v>31.250000000000004</v>
+        <v>31.011904761904763</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -7960,7 +7960,7 @@
         <v>73</v>
       </c>
       <c r="B74">
-        <v>30.77380952380952</v>
+        <v>29.46428571428571</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -7968,7 +7968,7 @@
         <v>74</v>
       </c>
       <c r="B75">
-        <v>23.035714285714278</v>
+        <v>22.916666666666664</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -7976,7 +7976,7 @@
         <v>122</v>
       </c>
       <c r="B76">
-        <v>23.333333333333332</v>
+        <v>21.30952380952381</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -7992,7 +7992,7 @@
         <v>125</v>
       </c>
       <c r="B78">
-        <v>55.11904761904762</v>
+        <v>55.23809523809524</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -8000,7 +8000,7 @@
         <v>126</v>
       </c>
       <c r="B79">
-        <v>56.30952380952381</v>
+        <v>54.28571428571429</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -8008,7 +8008,7 @@
         <v>127</v>
       </c>
       <c r="B80">
-        <v>54.76190476190476</v>
+        <v>53.57142857142857</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -8016,7 +8016,7 @@
         <v>128</v>
       </c>
       <c r="B81">
-        <v>51.488095238095234</v>
+        <v>49.82142857142857</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -8024,7 +8024,7 @@
         <v>129</v>
       </c>
       <c r="B82">
-        <v>52.14285714285714</v>
+        <v>51.845238095238095</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -8032,7 +8032,7 @@
         <v>130</v>
       </c>
       <c r="B83">
-        <v>35.17857142857143</v>
+        <v>36.8452380952381</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -8040,7 +8040,7 @@
         <v>131</v>
       </c>
       <c r="B84">
-        <v>35.535714285714285</v>
+        <v>36.964285714285715</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -8048,7 +8048,7 @@
         <v>133</v>
       </c>
       <c r="B85">
-        <v>48.75</v>
+        <v>49.345238095238095</v>
       </c>
     </row>
   </sheetData>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="233">
   <si>
     <t>Ticker</t>
   </si>
@@ -178,6 +178,9 @@
     <t>LULU</t>
   </si>
   <si>
+    <t>SPCX</t>
+  </si>
+  <si>
     <t>MMM</t>
   </si>
   <si>
@@ -322,6 +325,9 @@
     <t>2026-08-26</t>
   </si>
   <si>
+    <t>2026-10-13</t>
+  </si>
+  <si>
     <t>2027-08-03</t>
   </si>
   <si>
@@ -355,9 +361,6 @@
     <t>2027-08-10</t>
   </si>
   <si>
-    <t>2027-07-20</t>
-  </si>
-  <si>
     <t>2027-08-13</t>
   </si>
   <si>
@@ -367,10 +370,7 @@
     <t>2027-07-21</t>
   </si>
   <si>
-    <t>2027-07-14</t>
-  </si>
-  <si>
-    <t>2027-07-15</t>
+    <t>2026-10-14</t>
   </si>
   <si>
     <t>2026-09-30</t>
@@ -379,7 +379,7 @@
     <t>2026-10-08</t>
   </si>
   <si>
-    <t>2026-08-20</t>
+    <t>2027-08-20</t>
   </si>
   <si>
     <t>2026-08-25</t>
@@ -427,7 +427,7 @@
     <t>_date_</t>
   </si>
   <si>
-    <t>2026-09-18</t>
+    <t>2026-09-21</t>
   </si>
   <si>
     <t>Criteria</t>
@@ -688,28 +688,37 @@
     <t>Momentum Breakout, Market Leader, Volume Spike, Institutional Buying</t>
   </si>
   <si>
+    <t>Momentum Breakout, Market Leader, Stable Uptrend, Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
     <t>Momentum Breakout, Market Leader, Institutional Buying</t>
   </si>
   <si>
+    <t>Momentum Breakout, Market Leader</t>
+  </si>
+  <si>
+    <t>Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Volume Spike</t>
+  </si>
+  <si>
+    <t>Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Volume Spike</t>
+  </si>
+  <si>
+    <t>Momentum Breakout</t>
+  </si>
+  <si>
     <t>Momentum Breakout, Market Leader, Volume Spike</t>
-  </si>
-  <si>
-    <t>Institutional Buying</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Market Leader</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Momentum Breakout</t>
-  </si>
-  <si>
-    <t>Volume Spike, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Volume Spike</t>
   </si>
 </sst>
 </file>
@@ -1104,7 +1113,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A53"/>
+  <dimension ref="A1:A54"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -1370,6 +1379,11 @@
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>51</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1399,7 +1413,7 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>65.35714285714286</v>
+        <v>65.52941176470588</v>
       </c>
       <c r="C2" t="s">
         <v>221</v>
@@ -1407,10 +1421,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="B3">
-        <v>62.916666666666664</v>
+        <v>62.88235294117648</v>
       </c>
       <c r="C3" t="s">
         <v>222</v>
@@ -1418,32 +1432,32 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4">
-        <v>61.13095238095239</v>
+        <v>62.8235294117647</v>
       </c>
       <c r="C4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="B5">
-        <v>60.952380952380956</v>
+        <v>60.76470588235294</v>
       </c>
       <c r="C5" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>124</v>
+        <v>13</v>
       </c>
       <c r="B6">
-        <v>60.17857142857143</v>
+        <v>60.52941176470589</v>
       </c>
       <c r="C6" t="s">
         <v>223</v>
@@ -1454,21 +1468,21 @@
         <v>32</v>
       </c>
       <c r="B7">
-        <v>60.11904761904761</v>
+        <v>60.11764705882352</v>
       </c>
       <c r="C7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B8">
-        <v>59.82142857142857</v>
+        <v>59.941176470588246</v>
       </c>
       <c r="C8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1476,40 +1490,40 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>59.702380952380956</v>
+        <v>59.94117647058823</v>
       </c>
       <c r="C9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="B10">
-        <v>59.16666666666667</v>
+        <v>58.64705882352942</v>
       </c>
       <c r="C10" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="B11">
-        <v>58.273809523809526</v>
+        <v>58.64705882352941</v>
       </c>
       <c r="C11" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B12">
-        <v>57.916666666666664</v>
+        <v>57.76470588235295</v>
       </c>
       <c r="C12" t="s">
         <v>227</v>
@@ -1517,134 +1531,134 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="B13">
-        <v>55.95238095238097</v>
+        <v>57.70588235294118</v>
       </c>
       <c r="C13" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B14">
-        <v>55.83333333333333</v>
+        <v>55.52941176470588</v>
       </c>
       <c r="C14" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="B15">
-        <v>55.23809523809524</v>
+        <v>54.70588235294118</v>
       </c>
       <c r="C15" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B16">
-        <v>55.23809523809524</v>
+        <v>54.705882352941174</v>
       </c>
       <c r="C16" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="B17">
-        <v>55.05952380952381</v>
+        <v>54.64705882352941</v>
       </c>
       <c r="C17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B18">
-        <v>54.58333333333333</v>
+        <v>54.52941176470587</v>
       </c>
       <c r="C18" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>126</v>
+        <v>3</v>
       </c>
       <c r="B19">
-        <v>54.28571428571429</v>
+        <v>54.470588235294116</v>
       </c>
       <c r="C19" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>127</v>
+        <v>47</v>
       </c>
       <c r="B20">
-        <v>53.57142857142857</v>
+        <v>54.23529411764706</v>
       </c>
       <c r="C20" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>127</v>
       </c>
       <c r="B21">
-        <v>53.21428571428571</v>
+        <v>54.11764705882352</v>
       </c>
       <c r="C21" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="B22">
-        <v>52.976190476190474</v>
+        <v>52.94117647058824</v>
       </c>
       <c r="C22" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>129</v>
+        <v>36</v>
       </c>
       <c r="B23">
-        <v>51.845238095238095</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="C23" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>2</v>
+        <v>129</v>
       </c>
       <c r="B24">
-        <v>50.23809523809524</v>
+        <v>51.70588235294118</v>
       </c>
       <c r="C24" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -1652,7 +1666,7 @@
         <v>128</v>
       </c>
       <c r="B25">
-        <v>49.82142857142857</v>
+        <v>51.52941176470588</v>
       </c>
       <c r="C25" t="s">
         <v>228</v>
@@ -1660,65 +1674,65 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>133</v>
+        <v>2</v>
       </c>
       <c r="B26">
-        <v>49.345238095238095</v>
+        <v>50.23529411764706</v>
       </c>
       <c r="C26" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>56</v>
+        <v>133</v>
       </c>
       <c r="B27">
-        <v>47.67857142857143</v>
+        <v>49.529411764705884</v>
       </c>
       <c r="C27" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="B28">
-        <v>46.607142857142854</v>
+        <v>48.52941176470588</v>
       </c>
       <c r="C28" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B29">
-        <v>46.30952380952381</v>
+        <v>48.11764705882352</v>
       </c>
       <c r="C29" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B30">
-        <v>45.833333333333336</v>
+        <v>47.88235294117647</v>
       </c>
       <c r="C30" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B31">
-        <v>45.65476190476191</v>
+        <v>46.470588235294116</v>
       </c>
       <c r="C31" t="s">
         <v>228</v>
@@ -1726,131 +1740,131 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B32">
-        <v>43.75</v>
+        <v>46.470588235294116</v>
       </c>
       <c r="C32" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="B33">
-        <v>43.095238095238095</v>
+        <v>46.05882352941177</v>
       </c>
       <c r="C33" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="B34">
-        <v>42.91666666666666</v>
+        <v>45.1764705882353</v>
       </c>
       <c r="C34" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="B35">
-        <v>42.73809523809524</v>
+        <v>44.76470588235294</v>
       </c>
       <c r="C35" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="B36">
-        <v>41.964285714285715</v>
+        <v>43.82352941176471</v>
       </c>
       <c r="C36" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="B37">
-        <v>41.36904761904762</v>
+        <v>42.882352941176464</v>
       </c>
       <c r="C37" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="B38">
-        <v>40.833333333333336</v>
+        <v>42.8235294117647</v>
       </c>
       <c r="C38" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B39">
-        <v>40.773809523809526</v>
+        <v>41.99999999999999</v>
       </c>
       <c r="C39" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="B40">
-        <v>39.107142857142854</v>
+        <v>41.76470588235294</v>
       </c>
       <c r="C40" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B41">
-        <v>38.33333333333333</v>
+        <v>41.05882352941176</v>
       </c>
       <c r="C41" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B42">
-        <v>38.03571428571429</v>
+        <v>39.76470588235295</v>
       </c>
       <c r="C42" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B43">
-        <v>37.5</v>
+        <v>39.529411764705884</v>
       </c>
       <c r="C43" t="s">
         <v>224</v>
@@ -1858,65 +1872,65 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="B44">
-        <v>36.964285714285715</v>
+        <v>39.411764705882355</v>
       </c>
       <c r="C44" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>130</v>
+        <v>71</v>
       </c>
       <c r="B45">
-        <v>36.8452380952381</v>
+        <v>39.35294117647059</v>
       </c>
       <c r="C45" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B46">
-        <v>35.29761904761905</v>
+        <v>39.23529411764706</v>
       </c>
       <c r="C46" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B47">
-        <v>35.05952380952381</v>
+        <v>38.529411764705884</v>
       </c>
       <c r="C47" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="B48">
-        <v>34.583333333333336</v>
+        <v>38.294117647058826</v>
       </c>
       <c r="C48" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="B49">
-        <v>33.45238095238095</v>
+        <v>37.82352941176471</v>
       </c>
       <c r="C49" t="s">
         <v>228</v>
@@ -1924,21 +1938,21 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>66</v>
+        <v>130</v>
       </c>
       <c r="B50">
-        <v>33.392857142857146</v>
+        <v>36.8235294117647</v>
       </c>
       <c r="C50" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="B51">
-        <v>33.03571428571429</v>
+        <v>36.41176470588236</v>
       </c>
       <c r="C51" t="s">
         <v>228</v>
@@ -1962,127 +1976,127 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -2093,7 +2107,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T85"/>
+  <dimension ref="A1:T86"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -2101,61 +2115,61 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="R1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="S1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
@@ -2166,7 +2180,7 @@
         <v>7.77</v>
       </c>
       <c r="C2" s="1">
-        <v>66.66666666666666</v>
+        <v>67.05882352941175</v>
       </c>
       <c r="D2" s="1">
         <v>-1.9909909909909909</v>
@@ -2175,49 +2189,49 @@
         <v>-2.08</v>
       </c>
       <c r="F2" s="1">
-        <v>0.14261768239983702</v>
+        <v>0.17135440094619037</v>
       </c>
       <c r="G2" s="1">
         <v>0.21</v>
       </c>
       <c r="H2" s="1">
-        <v>53.14</v>
+        <v>51.05</v>
       </c>
       <c r="I2" s="1">
-        <v>11.32</v>
+        <v>10.27</v>
       </c>
       <c r="J2" s="1">
-        <v>0.01738299261332833</v>
+        <v>0.016848552590128983</v>
       </c>
       <c r="K2" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="1">
         <v>-461</v>
       </c>
       <c r="M2" s="1">
-        <v>0.1173575295885716</v>
+        <v>0.15404246822008671</v>
       </c>
       <c r="N2" s="1">
-        <v>16.008240656485683</v>
+        <v>18.670630711388874</v>
       </c>
       <c r="O2" s="1">
-        <v>71.42857142857143</v>
+        <v>77.64705882352942</v>
       </c>
       <c r="P2" s="1">
         <v>16.29652721982991</v>
       </c>
       <c r="Q2" s="1">
-        <v>51.785714285714285</v>
+        <v>50.8235294117647</v>
       </c>
       <c r="R2" s="1">
-        <v>46.666666666666664</v>
+        <v>48.52941176470588</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="T2" s="1">
-        <v>26.85</v>
+        <v>28.71</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -2228,55 +2242,55 @@
         <v>3.9</v>
       </c>
       <c r="C3" s="2">
-        <v>53.57142857142857</v>
+        <v>54.11764705882353</v>
       </c>
       <c r="D3" s="2">
         <v>26.710256410256406</v>
       </c>
       <c r="E3" s="2">
-        <v>3.63</v>
+        <v>3.59</v>
       </c>
       <c r="F3" s="2">
-        <v>-0.026096101709148514</v>
+        <v>-0.023099612774609424</v>
       </c>
       <c r="G3" s="2">
         <v>2.47</v>
       </c>
       <c r="H3" s="2">
-        <v>62.78</v>
+        <v>67.65</v>
       </c>
       <c r="I3" s="2">
-        <v>54.45</v>
+        <v>61.01</v>
       </c>
       <c r="J3" s="2">
-        <v>-0.002934949024288785</v>
+        <v>-0.0014133504791873641</v>
       </c>
       <c r="K3" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L3" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="M3" s="2">
-        <v>0.020906967445990965</v>
+        <v>0.009113730399279651</v>
       </c>
       <c r="N3" s="2">
-        <v>6.36318444222764</v>
+        <v>4.177756929308165</v>
       </c>
       <c r="O3" s="2">
-        <v>58.333333333333336</v>
+        <v>57.647058823529406</v>
       </c>
       <c r="P3" s="2">
         <v>26.053946839070953</v>
       </c>
       <c r="Q3" s="2">
-        <v>67.61904761904762</v>
+        <v>68.82352941176471</v>
       </c>
       <c r="R3" s="2">
-        <v>50.23809523809524</v>
+        <v>50.23529411764706</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T3" s="2">
         <v>-16.84</v>
@@ -2290,28 +2304,28 @@
         <v>-3.17</v>
       </c>
       <c r="C4" s="2">
-        <v>10.714285714285714</v>
+        <v>10.588235294117647</v>
       </c>
       <c r="D4" s="2">
         <v>12.511041009463725</v>
       </c>
       <c r="E4" s="2">
-        <v>6.35</v>
+        <v>6.34</v>
       </c>
       <c r="F4" s="2">
-        <v>0.3889886085759751</v>
+        <v>0.3907653845388289</v>
       </c>
       <c r="G4" s="2">
         <v>1.35</v>
       </c>
       <c r="H4" s="2">
-        <v>57.13</v>
+        <v>54.48</v>
       </c>
       <c r="I4" s="2">
-        <v>52.22</v>
+        <v>49.5</v>
       </c>
       <c r="J4" s="2">
-        <v>0.022918824167334283</v>
+        <v>0.02262796784613889</v>
       </c>
       <c r="K4" s="2" t="b">
         <v>0</v>
@@ -2320,28 +2334,28 @@
         <v>181</v>
       </c>
       <c r="M4" s="2">
-        <v>0.400179815517675</v>
+        <v>0.39843522815165966</v>
       </c>
       <c r="N4" s="2">
-        <v>44.29046924939603</v>
+        <v>43.109906704546184</v>
       </c>
       <c r="O4" s="2">
-        <v>92.85714285714286</v>
+        <v>92.94117647058823</v>
       </c>
       <c r="P4" s="2">
         <v>19.349659482175007</v>
       </c>
       <c r="Q4" s="2">
-        <v>59.761904761904766</v>
+        <v>58.117647058823536</v>
       </c>
       <c r="R4" s="2">
-        <v>54.58333333333333</v>
+        <v>54.470588235294116</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="T4" s="2">
-        <v>6.23</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -2352,58 +2366,58 @@
         <v>1.08</v>
       </c>
       <c r="C5" s="1">
-        <v>39.285714285714285</v>
+        <v>40</v>
       </c>
       <c r="D5" s="1">
-        <v>30.824074074074073</v>
+        <v>30.990740740740737</v>
       </c>
       <c r="E5" s="1">
         <v>1.69</v>
       </c>
       <c r="F5" s="1">
-        <v>-0.1479610540882516</v>
+        <v>-0.14304464950581564</v>
       </c>
       <c r="G5" s="1">
         <v>1.91</v>
       </c>
       <c r="H5" s="1">
-        <v>54.82</v>
+        <v>56.14</v>
       </c>
       <c r="I5" s="1">
-        <v>-7.91</v>
+        <v>-6.97</v>
       </c>
       <c r="J5" s="1">
-        <v>-0.01294422094788631</v>
+        <v>-0.011996112001193106</v>
       </c>
       <c r="K5" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L5" s="1">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M5" s="1">
-        <v>-0.11886391603983193</v>
+        <v>-0.12310305611245576</v>
       </c>
       <c r="N5" s="1">
-        <v>-7.613903906354659</v>
+        <v>-9.043921721865367</v>
       </c>
       <c r="O5" s="1">
-        <v>30.952380952380953</v>
+        <v>34.11764705882353</v>
       </c>
       <c r="P5" s="1">
         <v>33.002444654975626</v>
       </c>
       <c r="Q5" s="1">
-        <v>50.714285714285715</v>
+        <v>50.94117647058823</v>
       </c>
       <c r="R5" s="1">
-        <v>35.05952380952381</v>
+        <v>36.05882352941177</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="T5" s="1">
-        <v>-10.92</v>
+        <v>-9.92</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -2414,58 +2428,58 @@
         <v>3.17</v>
       </c>
       <c r="C6" s="1">
-        <v>48.80952380952381</v>
+        <v>49.411764705882355</v>
       </c>
       <c r="D6" s="1">
-        <v>0.8864353312302841</v>
+        <v>0.8706624605678233</v>
       </c>
       <c r="E6" s="1">
-        <v>-1.87</v>
+        <v>-1.88</v>
       </c>
       <c r="F6" s="1">
-        <v>-0.08334953218372448</v>
+        <v>-0.11827212497552217</v>
       </c>
       <c r="G6" s="1">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="H6" s="1">
-        <v>43.15</v>
+        <v>36.1</v>
       </c>
       <c r="I6" s="1">
-        <v>-12.09</v>
+        <v>-15.95</v>
       </c>
       <c r="J6" s="1">
-        <v>0.002038697338800449</v>
+        <v>0.00021664429675236435</v>
       </c>
       <c r="K6" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="1">
-        <v>-206</v>
+        <v>-205</v>
       </c>
       <c r="M6" s="1">
-        <v>-0.06416460599795326</v>
+        <v>-0.10490468325030289</v>
       </c>
       <c r="N6" s="1">
-        <v>-2.1439729021667935</v>
+        <v>-7.224084435650077</v>
       </c>
       <c r="O6" s="1">
-        <v>45.23809523809524</v>
+        <v>37.64705882352941</v>
       </c>
       <c r="P6" s="1">
         <v>27.785495103772316</v>
       </c>
       <c r="Q6" s="1">
-        <v>43.92857142857143</v>
+        <v>41.1764705882353</v>
       </c>
       <c r="R6" s="1">
-        <v>36.011904761904766</v>
+        <v>34.05882352941177</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T6" s="1">
-        <v>16.93</v>
+        <v>14.97</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -2476,58 +2490,58 @@
         <v>7.91</v>
       </c>
       <c r="C7" s="2">
-        <v>69.04761904761905</v>
+        <v>69.41176470588235</v>
       </c>
       <c r="D7" s="2">
-        <v>7.798988621997471</v>
+        <v>7.814159292035399</v>
       </c>
       <c r="E7" s="2">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="F7" s="2">
-        <v>-0.00995312315159319</v>
+        <v>-0.004436447452838818</v>
       </c>
       <c r="G7" s="2">
         <v>2.22</v>
       </c>
       <c r="H7" s="2">
-        <v>51.72</v>
+        <v>55.64</v>
       </c>
       <c r="I7" s="2">
-        <v>10.68</v>
+        <v>12.79</v>
       </c>
       <c r="J7" s="2">
-        <v>0.008073721528561052</v>
+        <v>0.00794321380736259</v>
       </c>
       <c r="K7" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L7" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M7" s="2">
-        <v>0.029056226759474946</v>
+        <v>0.02229843599759973</v>
       </c>
       <c r="N7" s="2">
-        <v>7.178110373576027</v>
+        <v>5.49622748914018</v>
       </c>
       <c r="O7" s="2">
-        <v>59.523809523809526</v>
+        <v>60</v>
       </c>
       <c r="P7" s="2">
         <v>19.398494070050486</v>
       </c>
       <c r="Q7" s="2">
-        <v>66.07142857142856</v>
+        <v>67.76470588235294</v>
       </c>
       <c r="R7" s="2">
-        <v>55.23809523809524</v>
+        <v>55.52941176470588</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T7" s="2">
-        <v>6.82</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -2538,58 +2552,58 @@
         <v>15.55</v>
       </c>
       <c r="C8" s="1">
-        <v>84.52380952380952</v>
+        <v>84.70588235294117</v>
       </c>
       <c r="D8" s="1">
         <v>-0.11961414790996792</v>
       </c>
       <c r="E8" s="1">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="F8" s="1">
-        <v>-0.09112621751435272</v>
+        <v>-0.0841234225495912</v>
       </c>
       <c r="G8" s="1">
         <v>0.61</v>
       </c>
       <c r="H8" s="1">
-        <v>35.04</v>
+        <v>38.49</v>
       </c>
       <c r="I8" s="1">
-        <v>5.98</v>
+        <v>6.71</v>
       </c>
       <c r="J8" s="1">
-        <v>-0.011442639316187131</v>
+        <v>-0.011827467778737204</v>
       </c>
       <c r="K8" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L8" s="1">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M8" s="1">
-        <v>-0.10359641953510401</v>
+        <v>-0.092669819718174</v>
       </c>
       <c r="N8" s="1">
-        <v>-6.087154255881869</v>
+        <v>-6.000598082437192</v>
       </c>
       <c r="O8" s="1">
-        <v>33.33333333333333</v>
+        <v>41.17647058823529</v>
       </c>
       <c r="P8" s="1">
         <v>14.011691026293512</v>
       </c>
       <c r="Q8" s="1">
-        <v>45.71428571428571</v>
+        <v>45.76470588235294</v>
       </c>
       <c r="R8" s="1">
-        <v>39.107142857142854</v>
+        <v>41.05882352941176</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="T8" s="1">
-        <v>-20.65</v>
+        <v>-18.7</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -2600,58 +2614,58 @@
         <v>1.17</v>
       </c>
       <c r="C9" s="2">
-        <v>40.476190476190474</v>
+        <v>41.17647058823529</v>
       </c>
       <c r="D9" s="2">
         <v>36.13675213675214</v>
       </c>
       <c r="E9" s="2">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="F9" s="2">
-        <v>0.28692453905415327</v>
+        <v>0.3367039704258855</v>
       </c>
       <c r="G9" s="2">
         <v>1.61</v>
       </c>
       <c r="H9" s="2">
-        <v>55.93</v>
+        <v>57.5</v>
       </c>
       <c r="I9" s="2">
-        <v>16.18</v>
+        <v>17.4</v>
       </c>
       <c r="J9" s="2">
-        <v>0.027370917952379985</v>
+        <v>0.02814584744862212</v>
       </c>
       <c r="K9" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L9" s="2">
-        <v>-113</v>
+        <v>-112</v>
       </c>
       <c r="M9" s="2">
-        <v>0.30642921400968737</v>
+        <v>0.3500714121511048</v>
       </c>
       <c r="N9" s="2">
-        <v>34.91540909859726</v>
+        <v>38.273525104490695</v>
       </c>
       <c r="O9" s="2">
-        <v>89.28571428571429</v>
+        <v>89.41176470588236</v>
       </c>
       <c r="P9" s="2">
         <v>33.227512780245505</v>
       </c>
       <c r="Q9" s="2">
-        <v>70.11904761904762</v>
+        <v>70.35294117647058</v>
       </c>
       <c r="R9" s="2">
-        <v>59.702380952380956</v>
+        <v>59.94117647058823</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="T9" s="2">
-        <v>32.32</v>
+        <v>32.56</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -2662,58 +2676,58 @@
         <v>4.85</v>
       </c>
       <c r="C10" s="1">
-        <v>58.333333333333336</v>
+        <v>58.82352941176471</v>
       </c>
       <c r="D10" s="1">
-        <v>0.7463917525773198</v>
+        <v>0.7484536082474229</v>
       </c>
       <c r="E10" s="1">
         <v>0.08</v>
       </c>
       <c r="F10" s="1">
-        <v>-0.011637194267276788</v>
+        <v>-0.05361085296055531</v>
       </c>
       <c r="G10" s="1">
         <v>1.42</v>
       </c>
       <c r="H10" s="1">
-        <v>49.27</v>
+        <v>45.51</v>
       </c>
       <c r="I10" s="1">
-        <v>1.25</v>
+        <v>-0.41</v>
       </c>
       <c r="J10" s="1">
-        <v>0.009268221718603961</v>
+        <v>0.008396296401718037</v>
       </c>
       <c r="K10" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="1">
-        <v>-51</v>
+        <v>-50</v>
       </c>
       <c r="M10" s="1">
-        <v>0.0017922540627630656</v>
+        <v>-0.044407040625158434</v>
       </c>
       <c r="N10" s="1">
-        <v>4.451713103904849</v>
+        <v>-1.1743201731356305</v>
       </c>
       <c r="O10" s="1">
-        <v>53.57142857142857</v>
+        <v>50.588235294117645</v>
       </c>
       <c r="P10" s="1">
         <v>14.568379622257217</v>
       </c>
       <c r="Q10" s="1">
-        <v>52.50000000000001</v>
+        <v>51.294117647058826</v>
       </c>
       <c r="R10" s="1">
-        <v>45.714285714285715</v>
+        <v>45.1764705882353</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="T10" s="1">
-        <v>10.17</v>
+        <v>9.63</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -2724,7 +2738,7 @@
         <v>-1.01</v>
       </c>
       <c r="C11" s="2">
-        <v>17.857142857142858</v>
+        <v>17.647058823529413</v>
       </c>
       <c r="D11" s="2">
         <v>46.68316831683168</v>
@@ -2733,19 +2747,19 @@
         <v>2.19</v>
       </c>
       <c r="F11" s="2">
-        <v>0.5334397451303984</v>
+        <v>0.47235958602627137</v>
       </c>
       <c r="G11" s="2">
         <v>0.71</v>
       </c>
       <c r="H11" s="2">
-        <v>62.47</v>
+        <v>58.36</v>
       </c>
       <c r="I11" s="2">
-        <v>42.8</v>
+        <v>38.76</v>
       </c>
       <c r="J11" s="2">
-        <v>0.022974717537993104</v>
+        <v>0.024411657653181016</v>
       </c>
       <c r="K11" s="2" t="b">
         <v>1</v>
@@ -2754,28 +2768,28 @@
         <v>40</v>
       </c>
       <c r="M11" s="2">
-        <v>0.5241670308072757</v>
+        <v>0.46600457274706875</v>
       </c>
       <c r="N11" s="2">
-        <v>56.6891907783561</v>
+        <v>49.86684116408709</v>
       </c>
       <c r="O11" s="2">
-        <v>96.42857142857143</v>
+        <v>94.11764705882352</v>
       </c>
       <c r="P11" s="2">
         <v>21.2185970476566</v>
       </c>
       <c r="Q11" s="2">
-        <v>65.95238095238095</v>
+        <v>64.94117647058825</v>
       </c>
       <c r="R11" s="2">
-        <v>59.16666666666667</v>
+        <v>58.64705882352941</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="T11" s="2">
-        <v>7.52</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -2786,28 +2800,28 @@
         <v>-0.31</v>
       </c>
       <c r="C12" s="2">
-        <v>25</v>
+        <v>24.705882352941178</v>
       </c>
       <c r="D12" s="2">
         <v>65.16129032258064</v>
       </c>
       <c r="E12" s="2">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="F12" s="2">
-        <v>0.8570457789234048</v>
+        <v>0.8213136145457095</v>
       </c>
       <c r="G12" s="2">
         <v>0.98</v>
       </c>
       <c r="H12" s="2">
-        <v>67.58</v>
+        <v>64.21</v>
       </c>
       <c r="I12" s="2">
-        <v>57.94</v>
+        <v>55.57</v>
       </c>
       <c r="J12" s="2">
-        <v>0.04364680656389421</v>
+        <v>0.04325071796450576</v>
       </c>
       <c r="K12" s="2" t="b">
         <v>0</v>
@@ -2816,10 +2830,10 @@
         <v>29</v>
       </c>
       <c r="M12" s="2">
-        <v>0.8564062813838791</v>
+        <v>0.8208753377678335</v>
       </c>
       <c r="N12" s="2">
-        <v>89.91311583601643</v>
+        <v>85.35391766616357</v>
       </c>
       <c r="O12" s="2">
         <v>100</v>
@@ -2828,16 +2842,16 @@
         <v>23.557267760130397</v>
       </c>
       <c r="Q12" s="2">
-        <v>71.78571428571428</v>
+        <v>71.05882352941177</v>
       </c>
       <c r="R12" s="2">
-        <v>62.916666666666664</v>
+        <v>62.8235294117647</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="T12" s="2">
-        <v>10.17</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -2848,58 +2862,58 @@
         <v>0.02</v>
       </c>
       <c r="C13" s="1">
-        <v>29.761904761904763</v>
+        <v>30.58823529411765</v>
       </c>
       <c r="D13" s="1">
         <v>-4529.499999999999</v>
       </c>
       <c r="E13" s="1">
-        <v>-1.09</v>
+        <v>-1.08</v>
       </c>
       <c r="F13" s="1">
-        <v>0.4323827828383941</v>
+        <v>0.500607940418708</v>
       </c>
       <c r="G13" s="1">
         <v>1.57</v>
       </c>
       <c r="H13" s="1">
-        <v>58.59</v>
+        <v>60.67</v>
       </c>
       <c r="I13" s="1">
-        <v>19.48</v>
+        <v>21.47</v>
       </c>
       <c r="J13" s="1">
-        <v>0.044580855708661694</v>
+        <v>0.04603904305404006</v>
       </c>
       <c r="K13" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
       </c>
       <c r="M13" s="1">
-        <v>0.45060846271487676</v>
+        <v>0.5130988285881752</v>
       </c>
       <c r="N13" s="1">
-        <v>49.33333396911621</v>
+        <v>54.57626674819773</v>
       </c>
       <c r="O13" s="1">
-        <v>95.23809523809523</v>
+        <v>95.29411764705881</v>
       </c>
       <c r="P13" s="1">
         <v>40.13761891809808</v>
       </c>
       <c r="Q13" s="1">
-        <v>45</v>
+        <v>45.411764705882355</v>
       </c>
       <c r="R13" s="1">
-        <v>38.33333333333333</v>
+        <v>38.529411764705884</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="T13" s="1">
-        <v>37.54</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -2910,28 +2924,28 @@
         <v>1.66</v>
       </c>
       <c r="C14" s="2">
-        <v>42.857142857142854</v>
+        <v>43.529411764705884</v>
       </c>
       <c r="D14" s="2">
         <v>5.385542168674699</v>
       </c>
       <c r="E14" s="2">
-        <v>-1.74</v>
+        <v>-1.75</v>
       </c>
       <c r="F14" s="2">
-        <v>0.6464154964714657</v>
+        <v>0.5208156300520135</v>
       </c>
       <c r="G14" s="2">
         <v>0.75</v>
       </c>
       <c r="H14" s="2">
-        <v>68.16</v>
+        <v>61.6</v>
       </c>
       <c r="I14" s="2">
-        <v>79.57</v>
+        <v>70.95</v>
       </c>
       <c r="J14" s="2">
-        <v>0.026403162056311824</v>
+        <v>0.027317155840913813</v>
       </c>
       <c r="K14" s="2" t="b">
         <v>0</v>
@@ -2940,28 +2954,28 @@
         <v>101</v>
       </c>
       <c r="M14" s="2">
-        <v>0.6384217772273943</v>
+        <v>0.515337170328563</v>
       </c>
       <c r="N14" s="2">
-        <v>68.11466542036797</v>
+        <v>54.80010092223652</v>
       </c>
       <c r="O14" s="2">
-        <v>98.80952380952381</v>
+        <v>96.47058823529412</v>
       </c>
       <c r="P14" s="2">
         <v>19.142997204429033</v>
       </c>
       <c r="Q14" s="2">
-        <v>68.21428571428572</v>
+        <v>67.52941176470588</v>
       </c>
       <c r="R14" s="2">
-        <v>61.13095238095239</v>
+        <v>60.52941176470589</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T14" s="2">
-        <v>5.22</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -2972,58 +2986,58 @@
         <v>-2.12</v>
       </c>
       <c r="C15" s="3">
-        <v>15.476190476190476</v>
+        <v>15.294117647058824</v>
       </c>
       <c r="D15" s="3">
-        <v>19.344339622641506</v>
+        <v>19.249999999999996</v>
       </c>
       <c r="E15" s="3">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="F15" s="3">
-        <v>-0.183942639186129</v>
+        <v>-0.24954793524322455</v>
       </c>
       <c r="G15" s="3">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="H15" s="3">
-        <v>62.01</v>
+        <v>66.49</v>
       </c>
       <c r="I15" s="3">
-        <v>41.64</v>
+        <v>47.75</v>
       </c>
       <c r="J15" s="3">
-        <v>-0.01681202405057133</v>
+        <v>-0.012798871678323958</v>
       </c>
       <c r="K15" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="3">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="M15" s="3">
-        <v>-0.14429379173553514</v>
+        <v>-0.22215563662597193</v>
       </c>
       <c r="N15" s="3">
-        <v>-10.156891475924976</v>
+        <v>-18.949179773216983</v>
       </c>
       <c r="O15" s="3">
-        <v>27.380952380952383</v>
+        <v>18.823529411764707</v>
       </c>
       <c r="P15" s="3">
         <v>41.90435941885386</v>
       </c>
       <c r="Q15" s="3">
-        <v>49.04761904761905</v>
+        <v>51.294117647058826</v>
       </c>
       <c r="R15" s="3">
-        <v>25.059523809523814</v>
+        <v>23.058823529411768</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="T15" s="3">
-        <v>-33.36</v>
+        <v>-35.36</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -3034,58 +3048,58 @@
         <v>-3.36</v>
       </c>
       <c r="C16" s="3">
-        <v>9.523809523809524</v>
+        <v>9.411764705882353</v>
       </c>
       <c r="D16" s="3">
         <v>6.092261904761904</v>
       </c>
       <c r="E16" s="3">
-        <v>28.81</v>
+        <v>29.93</v>
       </c>
       <c r="F16" s="3">
-        <v>-0.2617258060096448</v>
+        <v>-0.27546611076087707</v>
       </c>
       <c r="G16" s="3">
         <v>1.8</v>
       </c>
       <c r="H16" s="3">
-        <v>49.84</v>
+        <v>51.58</v>
       </c>
       <c r="I16" s="3">
-        <v>-3.4</v>
+        <v>-2.61</v>
       </c>
       <c r="J16" s="3">
-        <v>-0.04455402581301085</v>
+        <v>-0.04143714625090329</v>
       </c>
       <c r="K16" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="3">
         <v>27</v>
       </c>
       <c r="M16" s="3">
-        <v>-0.2361459044286165</v>
+        <v>-0.2579350396458354</v>
       </c>
       <c r="N16" s="3">
-        <v>-19.34210274523312</v>
+        <v>-22.527120075203335</v>
       </c>
       <c r="O16" s="3">
-        <v>15.476190476190476</v>
+        <v>12.941176470588237</v>
       </c>
       <c r="P16" s="3">
         <v>40.1905830435425</v>
       </c>
       <c r="Q16" s="3">
-        <v>30.59523809523809</v>
+        <v>30.941176470588232</v>
       </c>
       <c r="R16" s="3">
-        <v>14.464285714285708</v>
+        <v>13.764705882352942</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="T16" s="3">
-        <v>-28.77</v>
+        <v>-29.47</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -3096,28 +3110,28 @@
         <v>-4.76</v>
       </c>
       <c r="C17" s="1">
-        <v>5.952380952380952</v>
+        <v>5.88235294117647</v>
       </c>
       <c r="D17" s="1">
-        <v>6.40546218487395</v>
+        <v>6.226890756302521</v>
       </c>
       <c r="E17" s="1">
-        <v>-1.42</v>
+        <v>-1.64</v>
       </c>
       <c r="F17" s="1">
-        <v>0.013064178103322027</v>
+        <v>-0.003653700994869169</v>
       </c>
       <c r="G17" s="1">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="H17" s="1">
-        <v>57.58</v>
+        <v>56.29</v>
       </c>
       <c r="I17" s="1">
-        <v>7.56</v>
+        <v>6.82</v>
       </c>
       <c r="J17" s="1">
-        <v>-0.011747558648710344</v>
+        <v>-0.010226651418576992</v>
       </c>
       <c r="K17" s="1" t="b">
         <v>1</v>
@@ -3126,28 +3140,28 @@
         <v>31</v>
       </c>
       <c r="M17" s="1">
-        <v>0.03704533583553604</v>
+        <v>0.013000816564420425</v>
       </c>
       <c r="N17" s="1">
-        <v>7.977021281182132</v>
+        <v>4.566465545822243</v>
       </c>
       <c r="O17" s="1">
-        <v>60.71428571428571</v>
+        <v>58.82352941176471</v>
       </c>
       <c r="P17" s="1">
         <v>24.80206596461608</v>
       </c>
       <c r="Q17" s="1">
-        <v>39.64285714285714</v>
+        <v>38.8235294117647</v>
       </c>
       <c r="R17" s="1">
-        <v>33.03571428571429</v>
+        <v>33.05882352941177</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="T17" s="1">
-        <v>-0.14</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -3158,28 +3172,28 @@
         <v>0.19</v>
       </c>
       <c r="C18" s="3">
-        <v>33.33333333333333</v>
+        <v>34.11764705882353</v>
       </c>
       <c r="D18" s="3">
         <v>664</v>
       </c>
       <c r="E18" s="3">
-        <v>11.06</v>
+        <v>11.08</v>
       </c>
       <c r="F18" s="3">
-        <v>-0.641038905118166</v>
+        <v>-0.6537555572936488</v>
       </c>
       <c r="G18" s="3">
         <v>1.14</v>
       </c>
       <c r="H18" s="3">
-        <v>17.5</v>
+        <v>17.26</v>
       </c>
       <c r="I18" s="3">
-        <v>-53.33</v>
+        <v>-54.68</v>
       </c>
       <c r="J18" s="3">
-        <v>-0.0760385728134037</v>
+        <v>-0.0786608109751957</v>
       </c>
       <c r="K18" s="3" t="b">
         <v>1</v>
@@ -3188,28 +3202,28 @@
         <v>31</v>
       </c>
       <c r="M18" s="3">
-        <v>-0.6365624223414861</v>
+        <v>-0.6506876198485164</v>
       </c>
       <c r="N18" s="3">
-        <v>-59.38375453652007</v>
+        <v>-61.80237809547143</v>
       </c>
       <c r="O18" s="3">
-        <v>1.1904761904761905</v>
+        <v>1.1764705882352942</v>
       </c>
       <c r="P18" s="3">
-        <v>64.57654723759453</v>
+        <v>66.0016263719844</v>
       </c>
       <c r="Q18" s="3">
-        <v>39.404761904761905</v>
+        <v>39.647058823529406</v>
       </c>
       <c r="R18" s="3">
-        <v>22.91666666666667</v>
+        <v>23.11764705882353</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="T18" s="3">
-        <v>-11.35</v>
+        <v>-11.15</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -3220,58 +3234,58 @@
         <v>5.65</v>
       </c>
       <c r="C19" s="2">
-        <v>61.904761904761905</v>
+        <v>62.35294117647059</v>
       </c>
       <c r="D19" s="2">
         <v>4.892035398230088</v>
       </c>
       <c r="E19" s="2">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="F19" s="2">
-        <v>0.08863470926540619</v>
+        <v>0.08330440913490506</v>
       </c>
       <c r="G19" s="2">
         <v>0.1</v>
       </c>
       <c r="H19" s="2">
-        <v>55.47</v>
+        <v>50.58</v>
       </c>
       <c r="I19" s="2">
-        <v>13.7</v>
+        <v>11.7</v>
       </c>
       <c r="J19" s="2">
-        <v>0.004333912536991641</v>
+        <v>0.005207328208841143</v>
       </c>
       <c r="K19" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="2">
         <v>-60</v>
       </c>
       <c r="M19" s="2">
-        <v>0.05985731998674937</v>
+        <v>0.06358195413048318</v>
       </c>
       <c r="N19" s="2">
-        <v>10.258219696303476</v>
+        <v>9.624579302428529</v>
       </c>
       <c r="O19" s="2">
-        <v>64.28571428571429</v>
+        <v>65.88235294117646</v>
       </c>
       <c r="P19" s="2">
         <v>11.392700631623551</v>
       </c>
       <c r="Q19" s="2">
-        <v>61.30952380952381</v>
+        <v>59.52941176470588</v>
       </c>
       <c r="R19" s="2">
-        <v>53.750000000000014</v>
+        <v>54.52941176470587</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="T19" s="2">
-        <v>5.34</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -3282,28 +3296,28 @@
         <v>8.25</v>
       </c>
       <c r="C20" s="2">
-        <v>70.23809523809523</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="D20" s="2">
         <v>-0.11030303030303032</v>
       </c>
       <c r="E20" s="2">
-        <v>-5.68</v>
+        <v>-5.69</v>
       </c>
       <c r="F20" s="2">
-        <v>0.29838175683835083</v>
+        <v>0.2985100255815787</v>
       </c>
       <c r="G20" s="2">
         <v>1.07</v>
       </c>
       <c r="H20" s="2">
-        <v>61.76</v>
+        <v>55.48</v>
       </c>
       <c r="I20" s="2">
-        <v>25.66</v>
+        <v>23.58</v>
       </c>
       <c r="J20" s="2">
-        <v>0.024160727212878624</v>
+        <v>0.02446185566034033</v>
       </c>
       <c r="K20" s="2" t="b">
         <v>1</v>
@@ -3312,28 +3326,28 @@
         <v>8</v>
       </c>
       <c r="M20" s="2">
-        <v>0.30061999822669083</v>
+        <v>0.30004399430414486</v>
       </c>
       <c r="N20" s="2">
-        <v>34.334487520297614</v>
+        <v>33.270783319794695</v>
       </c>
       <c r="O20" s="2">
-        <v>88.09523809523809</v>
+        <v>87.05882352941177</v>
       </c>
       <c r="P20" s="2">
-        <v>20.924527727345563</v>
+        <v>16.026261190565123</v>
       </c>
       <c r="Q20" s="2">
-        <v>63.57142857142857</v>
+        <v>61.88235294117647</v>
       </c>
       <c r="R20" s="2">
-        <v>55.83333333333333</v>
+        <v>57.70588235294118</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T20" s="2">
-        <v>19.98</v>
+        <v>21.85</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -3344,28 +3358,28 @@
         <v>1.01</v>
       </c>
       <c r="C21" s="3">
-        <v>38.095238095238095</v>
+        <v>38.82352941176471</v>
       </c>
       <c r="D21" s="3">
-        <v>11.871287128712872</v>
+        <v>11.10891089108911</v>
       </c>
       <c r="E21" s="3">
-        <v>-3.45</v>
+        <v>-3.44</v>
       </c>
       <c r="F21" s="3">
-        <v>-0.3086773589264147</v>
+        <v>-0.3838834786197487</v>
       </c>
       <c r="G21" s="3">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="H21" s="3">
-        <v>43.15</v>
+        <v>41.09</v>
       </c>
       <c r="I21" s="3">
-        <v>-12.39</v>
+        <v>-14.66</v>
       </c>
       <c r="J21" s="3">
-        <v>-0.01972517720233169</v>
+        <v>-0.019708423756906745</v>
       </c>
       <c r="K21" s="3" t="b">
         <v>0</v>
@@ -3374,28 +3388,28 @@
         <v>55</v>
       </c>
       <c r="M21" s="3">
-        <v>-0.28885293520111777</v>
+        <v>-0.3700777601166534</v>
       </c>
       <c r="N21" s="3">
-        <v>-24.612805822483242</v>
+        <v>-33.74139212228513</v>
       </c>
       <c r="O21" s="3">
-        <v>9.523809523809524</v>
+        <v>4.705882352941177</v>
       </c>
       <c r="P21" s="3">
-        <v>51.51389629888408</v>
+        <v>52.10839414803409</v>
       </c>
       <c r="Q21" s="3">
-        <v>41.42857142857143</v>
+        <v>40.11764705882352</v>
       </c>
       <c r="R21" s="3">
-        <v>22.67857142857143</v>
+        <v>21.05882352941176</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="T21" s="3">
-        <v>-28.54</v>
+        <v>-30.16</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -3406,7 +3420,7 @@
         <v>8.48</v>
       </c>
       <c r="C22" s="1">
-        <v>71.42857142857143</v>
+        <v>71.76470588235294</v>
       </c>
       <c r="D22" s="1">
         <v>0.7594339622641508</v>
@@ -3415,49 +3429,49 @@
         <v>-0.24</v>
       </c>
       <c r="F22" s="1">
-        <v>-0.17720162664717115</v>
+        <v>-0.16247749883609502</v>
       </c>
       <c r="G22" s="1">
         <v>1.39</v>
       </c>
       <c r="H22" s="1">
-        <v>33.39</v>
+        <v>36.97</v>
       </c>
       <c r="I22" s="1">
-        <v>-2.75</v>
+        <v>-1.74</v>
       </c>
       <c r="J22" s="1">
-        <v>-0.01576589966346</v>
+        <v>-0.015443370621383741</v>
       </c>
       <c r="K22" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L22" s="1">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M22" s="1">
-        <v>-0.16473142462641988</v>
+        <v>-0.15393110166751223</v>
       </c>
       <c r="N22" s="1">
-        <v>-12.20065476501345</v>
+        <v>-12.126726277371016</v>
       </c>
       <c r="O22" s="1">
-        <v>22.61904761904762</v>
+        <v>28.235294117647058</v>
       </c>
       <c r="P22" s="1">
         <v>19.455960650079966</v>
       </c>
       <c r="Q22" s="1">
-        <v>42.5</v>
+        <v>43.17647058823529</v>
       </c>
       <c r="R22" s="1">
-        <v>33.45238095238095</v>
+        <v>35.17647058823529</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T22" s="1">
-        <v>-19.66</v>
+        <v>-17.93</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -3468,58 +3482,58 @@
         <v>26.55</v>
       </c>
       <c r="C23" s="2">
-        <v>96.42857142857143</v>
+        <v>96.47058823529412</v>
       </c>
       <c r="D23" s="2">
-        <v>-0.7043314500941621</v>
+        <v>-0.6975517890772129</v>
       </c>
       <c r="E23" s="2">
-        <v>0.07</v>
+        <v>0.09</v>
       </c>
       <c r="F23" s="2">
-        <v>0.15333876142910308</v>
+        <v>0.1163265158634346</v>
       </c>
       <c r="G23" s="2">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="H23" s="2">
-        <v>73.97</v>
+        <v>69.68</v>
       </c>
       <c r="I23" s="2">
-        <v>9.34</v>
+        <v>9.47</v>
       </c>
       <c r="J23" s="2">
-        <v>0.010819397291640383</v>
+        <v>0.01077845836789855</v>
       </c>
       <c r="K23" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L23" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M23" s="2">
-        <v>0.15941398805459728</v>
+        <v>0.12070928364219502</v>
       </c>
       <c r="N23" s="2">
-        <v>20.213886503088265</v>
+        <v>15.337312253599702</v>
       </c>
       <c r="O23" s="2">
-        <v>77.38095238095238</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="P23" s="2">
         <v>20.883293768118005</v>
       </c>
       <c r="Q23" s="2">
-        <v>64.88095238095238</v>
+        <v>64.35294117647058</v>
       </c>
       <c r="R23" s="2">
-        <v>55.05952380952381</v>
+        <v>52.94117647058824</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="T23" s="2">
-        <v>19.27</v>
+        <v>17.15</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -3530,28 +3544,28 @@
         <v>-97.21</v>
       </c>
       <c r="C24" s="1">
-        <v>1.1904761904761905</v>
+        <v>1.1764705882352942</v>
       </c>
       <c r="D24" s="1">
         <v>2.6552823783561363</v>
       </c>
       <c r="E24" s="1">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="F24" s="1">
-        <v>0.009069000595089555</v>
+        <v>0.27883062135226305</v>
       </c>
       <c r="G24" s="1">
-        <v>3.59</v>
+        <v>3.57</v>
       </c>
       <c r="H24" s="1">
-        <v>56.02</v>
+        <v>67.81</v>
       </c>
       <c r="I24" s="1">
-        <v>-3.56</v>
+        <v>15.85</v>
       </c>
       <c r="J24" s="1">
-        <v>0.03196791800631613</v>
+        <v>0.03594071848343393</v>
       </c>
       <c r="K24" s="1" t="b">
         <v>0</v>
@@ -3560,28 +3574,28 @@
         <v>-69</v>
       </c>
       <c r="M24" s="1">
-        <v>0.09188393196366862</v>
+        <v>0.3351491873093344</v>
       </c>
       <c r="N24" s="1">
-        <v>13.4608808939954</v>
+        <v>36.78130262031365</v>
       </c>
       <c r="O24" s="1">
-        <v>67.85714285714286</v>
+        <v>88.23529411764706</v>
       </c>
       <c r="P24" s="1">
         <v>57.99224429263358</v>
       </c>
       <c r="Q24" s="1">
-        <v>45.95238095238095</v>
+        <v>51.76470588235295</v>
       </c>
       <c r="R24" s="1">
-        <v>33.273809523809526</v>
+        <v>39.529411764705884</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="T24" s="1">
-        <v>36.99</v>
+        <v>43.25</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -3592,28 +3606,28 @@
         <v>-2.28</v>
       </c>
       <c r="C25" s="3">
-        <v>14.285714285714285</v>
+        <v>14.117647058823529</v>
       </c>
       <c r="D25" s="3">
         <v>-7.855263157894737</v>
       </c>
       <c r="E25" s="3">
-        <v>15.52</v>
+        <v>15.51</v>
       </c>
       <c r="F25" s="3">
-        <v>-0.21161631597654293</v>
+        <v>-0.35825644391981387</v>
       </c>
       <c r="G25" s="3">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="H25" s="3">
-        <v>47.79</v>
+        <v>44.11</v>
       </c>
       <c r="I25" s="3">
-        <v>-28.26</v>
+        <v>-32.23</v>
       </c>
       <c r="J25" s="3">
-        <v>-0.009516307640798203</v>
+        <v>-0.007836334056621033</v>
       </c>
       <c r="K25" s="3" t="b">
         <v>1</v>
@@ -3622,28 +3636,28 @@
         <v>34</v>
       </c>
       <c r="M25" s="3">
-        <v>-0.1684502320585577</v>
+        <v>-0.328234484635305</v>
       </c>
       <c r="N25" s="3">
-        <v>-12.57253550822724</v>
+        <v>-29.557064574150292</v>
       </c>
       <c r="O25" s="3">
-        <v>21.428571428571427</v>
+        <v>7.0588235294117645</v>
       </c>
       <c r="P25" s="3">
         <v>45.59139601172712</v>
       </c>
       <c r="Q25" s="3">
-        <v>17.857142857142854</v>
+        <v>15.999999999999998</v>
       </c>
       <c r="R25" s="3">
-        <v>5.535714285714283</v>
+        <v>1.3529411764705888</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="T25" s="3">
-        <v>4.13</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -3654,28 +3668,28 @@
         <v>-4.55</v>
       </c>
       <c r="C26" s="3">
-        <v>7.142857142857142</v>
+        <v>7.0588235294117645</v>
       </c>
       <c r="D26" s="3">
         <v>-0.7362637362637364</v>
       </c>
       <c r="E26" s="3">
-        <v>-0.88</v>
+        <v>-0.85</v>
       </c>
       <c r="F26" s="3">
-        <v>-0.38089331921802017</v>
+        <v>-0.3928647242491275</v>
       </c>
       <c r="G26" s="3">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="H26" s="3">
-        <v>51.77</v>
+        <v>50.87</v>
       </c>
       <c r="I26" s="3">
-        <v>-8.09</v>
+        <v>-8.78</v>
       </c>
       <c r="J26" s="3">
-        <v>-0.02542519862129914</v>
+        <v>-0.021117207118913392</v>
       </c>
       <c r="K26" s="3" t="b">
         <v>0</v>
@@ -3684,28 +3698,28 @@
         <v>159</v>
       </c>
       <c r="M26" s="3">
-        <v>-0.30511286078422384</v>
+        <v>-0.34070978768187854</v>
       </c>
       <c r="N26" s="3">
-        <v>-26.23879838079385</v>
+        <v>-30.804594878807638</v>
       </c>
       <c r="O26" s="3">
-        <v>5.952380952380952</v>
+        <v>5.88235294117647</v>
       </c>
       <c r="P26" s="3">
         <v>55.61259899184437</v>
       </c>
       <c r="Q26" s="3">
-        <v>16.547619047619047</v>
+        <v>16.47058823529412</v>
       </c>
       <c r="R26" s="3">
-        <v>-1.488095238095239</v>
+        <v>-1.3529411764705905</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="T26" s="3">
-        <v>-30.33</v>
+        <v>-30.19</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -3716,28 +3730,28 @@
         <v>-0.98</v>
       </c>
       <c r="C27" s="3">
-        <v>19.047619047619047</v>
+        <v>18.823529411764707</v>
       </c>
       <c r="D27" s="3">
         <v>-1.7653061224489797</v>
       </c>
       <c r="E27" s="3">
-        <v>6.6</v>
+        <v>6.87</v>
       </c>
       <c r="F27" s="3">
-        <v>-0.43659126318311603</v>
+        <v>-0.45704082290160536</v>
       </c>
       <c r="G27" s="3">
         <v>2.66</v>
       </c>
       <c r="H27" s="3">
-        <v>33.02</v>
+        <v>35.76</v>
       </c>
       <c r="I27" s="3">
-        <v>-38.44</v>
+        <v>-37.48</v>
       </c>
       <c r="J27" s="3">
-        <v>-0.029686712670485314</v>
+        <v>-0.02833457505757826</v>
       </c>
       <c r="K27" s="3" t="b">
         <v>0</v>
@@ -3746,28 +3760,28 @@
         <v>7</v>
       </c>
       <c r="M27" s="3">
-        <v>-0.3835129674024823</v>
+        <v>-0.4206638503378939</v>
       </c>
       <c r="N27" s="3">
-        <v>-34.078809042619696</v>
+        <v>-38.80000114440918</v>
       </c>
       <c r="O27" s="3">
-        <v>2.380952380952381</v>
+        <v>2.3529411764705883</v>
       </c>
       <c r="P27" s="3">
         <v>50.56910707785277</v>
       </c>
       <c r="Q27" s="3">
-        <v>11.071428571428571</v>
+        <v>11.411764705882351</v>
       </c>
       <c r="R27" s="3">
-        <v>-0.2976190476190492</v>
+        <v>-0.29411764705882604</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="T27" s="3">
-        <v>-16.46</v>
+        <v>-16.45</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -3778,58 +3792,58 @@
         <v>-1.08</v>
       </c>
       <c r="C28" s="1">
-        <v>16.666666666666664</v>
+        <v>16.470588235294116</v>
       </c>
       <c r="D28" s="1">
         <v>8.555555555555555</v>
       </c>
       <c r="E28" s="1">
-        <v>1.72</v>
+        <v>2.19</v>
       </c>
       <c r="F28" s="1">
-        <v>-0.10752541967838937</v>
+        <v>-0.13784439903538875</v>
       </c>
       <c r="G28" s="1">
         <v>3.26</v>
       </c>
       <c r="H28" s="1">
-        <v>44.54</v>
+        <v>43.94</v>
       </c>
       <c r="I28" s="1">
-        <v>-15.19</v>
+        <v>-15.84</v>
       </c>
       <c r="J28" s="1">
-        <v>0.007852922331981196</v>
+        <v>0.0069187697872931855</v>
       </c>
       <c r="K28" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="1">
         <v>3</v>
       </c>
       <c r="M28" s="1">
-        <v>-0.035262197711984467</v>
+        <v>-0.08831912313539603</v>
       </c>
       <c r="N28" s="1">
-        <v>0.7462679264300778</v>
+        <v>-5.565528424159394</v>
       </c>
       <c r="O28" s="1">
-        <v>50</v>
+        <v>43.529411764705884</v>
       </c>
       <c r="P28" s="1">
         <v>35.08771990976345</v>
       </c>
       <c r="Q28" s="1">
-        <v>44.04761904761905</v>
+        <v>43.294117647058826</v>
       </c>
       <c r="R28" s="1">
-        <v>35.29761904761905</v>
+        <v>33.41176470588235</v>
       </c>
       <c r="S28" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="T28" s="1">
-        <v>18.29</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -3840,28 +3854,28 @@
         <v>0.47</v>
       </c>
       <c r="C29" s="1">
-        <v>35.714285714285715</v>
+        <v>36.470588235294116</v>
       </c>
       <c r="D29" s="1">
         <v>83.17021276595746</v>
       </c>
       <c r="E29" s="1">
-        <v>-4.82</v>
+        <v>-4.83</v>
       </c>
       <c r="F29" s="1">
-        <v>-0.12454138915648824</v>
+        <v>-0.11463314202553478</v>
       </c>
       <c r="G29" s="1">
         <v>2.32</v>
       </c>
       <c r="H29" s="1">
-        <v>41.43</v>
+        <v>47.08</v>
       </c>
       <c r="I29" s="1">
-        <v>-14.54</v>
+        <v>-11.1</v>
       </c>
       <c r="J29" s="1">
-        <v>-0.0057808021121030975</v>
+        <v>-0.006393793195820497</v>
       </c>
       <c r="K29" s="1" t="b">
         <v>0</v>
@@ -3870,28 +3884,28 @@
         <v>9</v>
       </c>
       <c r="M29" s="1">
-        <v>-0.08233455154779157</v>
+        <v>-0.08570687468571603</v>
       </c>
       <c r="N29" s="1">
-        <v>-3.960967457150625</v>
+        <v>-5.304303579191391</v>
       </c>
       <c r="O29" s="1">
-        <v>42.857142857142854</v>
+        <v>44.70588235294118</v>
       </c>
       <c r="P29" s="1">
-        <v>20.094438777659683</v>
+        <v>18.81663456064845</v>
       </c>
       <c r="Q29" s="1">
-        <v>49.047619047619044</v>
+        <v>50.470588235294116</v>
       </c>
       <c r="R29" s="1">
-        <v>43.75</v>
+        <v>44.76470588235294</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="T29" s="1">
-        <v>3.51</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -3902,58 +3916,58 @@
         <v>2.2</v>
       </c>
       <c r="C30" s="1">
-        <v>46.42857142857143</v>
+        <v>47.05882352941176</v>
       </c>
       <c r="D30" s="1">
         <v>226.42272727272726</v>
       </c>
       <c r="E30" s="1">
-        <v>1.75</v>
+        <v>1.22</v>
       </c>
       <c r="F30" s="1">
-        <v>-0.17760776992614247</v>
+        <v>-0.14823570800154484</v>
       </c>
       <c r="G30" s="1">
         <v>1.25</v>
       </c>
       <c r="H30" s="1">
-        <v>31.46</v>
+        <v>36.25</v>
       </c>
       <c r="I30" s="1">
-        <v>-10.92</v>
+        <v>-9.64</v>
       </c>
       <c r="J30" s="1">
-        <v>-0.009765094945169386</v>
+        <v>-0.011306743281542289</v>
       </c>
       <c r="K30" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L30" s="1">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M30" s="1">
-        <v>-0.16961405068207114</v>
+        <v>-0.14275724827809433</v>
       </c>
       <c r="N30" s="1">
-        <v>-12.688917370578585</v>
+        <v>-11.009340938429224</v>
       </c>
       <c r="O30" s="1">
-        <v>20.238095238095237</v>
+        <v>29.411764705882355</v>
       </c>
       <c r="P30" s="1">
         <v>18.121365335609003</v>
       </c>
       <c r="Q30" s="1">
-        <v>50.833333333333336</v>
+        <v>51.29411764705882</v>
       </c>
       <c r="R30" s="1">
-        <v>41.36904761904762</v>
+        <v>43.82352941176471</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="T30" s="1">
-        <v>-7.11</v>
+        <v>-4.65</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -3964,58 +3978,58 @@
         <v>7.83</v>
       </c>
       <c r="C31" s="1">
-        <v>67.85714285714286</v>
+        <v>68.23529411764706</v>
       </c>
       <c r="D31" s="1">
         <v>7.2899106002554275</v>
       </c>
       <c r="E31" s="1">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="F31" s="1">
-        <v>-0.17413290143696686</v>
+        <v>-0.17360639642433562</v>
       </c>
       <c r="G31" s="1">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H31" s="1">
-        <v>38.54</v>
+        <v>48.46</v>
       </c>
       <c r="I31" s="1">
-        <v>-5.94</v>
+        <v>-1.79</v>
       </c>
       <c r="J31" s="1">
-        <v>-0.00680370228467923</v>
+        <v>-0.008693619379437459</v>
       </c>
       <c r="K31" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L31" s="1">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M31" s="1">
-        <v>-0.1587849604883499</v>
+        <v>-0.16330689214424865</v>
       </c>
       <c r="N31" s="1">
-        <v>-11.606008351206453</v>
+        <v>-13.064305325044659</v>
       </c>
       <c r="O31" s="1">
-        <v>25</v>
+        <v>25.882352941176475</v>
       </c>
       <c r="P31" s="1">
         <v>29.54918623383928</v>
       </c>
       <c r="Q31" s="1">
-        <v>52.38095238095239</v>
+        <v>54.941176470588225</v>
       </c>
       <c r="R31" s="1">
-        <v>38.03571428571429</v>
+        <v>38.294117647058826</v>
       </c>
       <c r="S31" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="T31" s="1">
-        <v>-10.01</v>
+        <v>-9.75</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -4026,58 +4040,58 @@
         <v>-2.58</v>
       </c>
       <c r="C32" s="3">
-        <v>13.095238095238097</v>
+        <v>12.941176470588237</v>
       </c>
       <c r="D32" s="3">
-        <v>8.755813953488373</v>
+        <v>8.848837209302324</v>
       </c>
       <c r="E32" s="3">
         <v>3.57</v>
       </c>
       <c r="F32" s="3">
-        <v>-0.11543986639936045</v>
+        <v>-0.13886547011266287</v>
       </c>
       <c r="G32" s="3">
         <v>1.62</v>
       </c>
       <c r="H32" s="3">
-        <v>43.64</v>
+        <v>41.48</v>
       </c>
       <c r="I32" s="3">
-        <v>-5.56</v>
+        <v>-7.16</v>
       </c>
       <c r="J32" s="3">
-        <v>-0.013401635283696658</v>
+        <v>-0.015827286358028467</v>
       </c>
       <c r="K32" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="3">
         <v>20</v>
       </c>
       <c r="M32" s="3">
-        <v>-0.09561544267406352</v>
+        <v>-0.12527888999850556</v>
       </c>
       <c r="N32" s="3">
-        <v>-5.289056569777815</v>
+        <v>-9.26150511047035</v>
       </c>
       <c r="O32" s="3">
-        <v>38.095238095238095</v>
+        <v>32.94117647058823</v>
       </c>
       <c r="P32" s="3">
-        <v>27.28297753683016</v>
+        <v>26.613703173358488</v>
       </c>
       <c r="Q32" s="3">
-        <v>36.78571428571429</v>
+        <v>34.11764705882353</v>
       </c>
       <c r="R32" s="3">
-        <v>28.750000000000007</v>
+        <v>26.941176470588225</v>
       </c>
       <c r="S32" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="T32" s="3">
-        <v>-3.14</v>
+        <v>-4.95</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -4088,58 +4102,58 @@
         <v>17.95</v>
       </c>
       <c r="C33" s="2">
-        <v>88.09523809523809</v>
+        <v>88.23529411764706</v>
       </c>
       <c r="D33" s="2">
-        <v>0.06295264623955427</v>
+        <v>0.06128133704735384</v>
       </c>
       <c r="E33" s="2">
         <v>0.24</v>
       </c>
       <c r="F33" s="2">
-        <v>0.2677141062276712</v>
+        <v>0.2666208096967232</v>
       </c>
       <c r="G33" s="2">
         <v>1.1</v>
       </c>
       <c r="H33" s="2">
-        <v>55.58</v>
+        <v>53.45</v>
       </c>
       <c r="I33" s="2">
-        <v>15.34</v>
+        <v>14.53</v>
       </c>
       <c r="J33" s="2">
-        <v>0.024478017780715046</v>
+        <v>0.024272774655738058</v>
       </c>
       <c r="K33" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L33" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M33" s="2">
-        <v>0.27091159392529973</v>
+        <v>0.2688121935861034</v>
       </c>
       <c r="N33" s="2">
-        <v>31.363647090158498</v>
+        <v>30.147603247990556</v>
       </c>
       <c r="O33" s="2">
-        <v>85.71428571428571</v>
+        <v>85.88235294117646</v>
       </c>
       <c r="P33" s="2">
         <v>23.38443607454554</v>
       </c>
       <c r="Q33" s="2">
-        <v>68.21428571428572</v>
+        <v>66.58823529411765</v>
       </c>
       <c r="R33" s="2">
-        <v>60.11904761904761</v>
+        <v>60.11764705882352</v>
       </c>
       <c r="S33" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="T33" s="2">
-        <v>24.33</v>
+        <v>24.32</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -4150,7 +4164,7 @@
         <v>19.91</v>
       </c>
       <c r="C34" s="1">
-        <v>92.85714285714286</v>
+        <v>92.94117647058823</v>
       </c>
       <c r="D34" s="1">
         <v>-2.3345052737317933</v>
@@ -4159,49 +4173,49 @@
         <v>2.34</v>
       </c>
       <c r="F34" s="1">
-        <v>-0.0946855440919999</v>
+        <v>-0.08750618822022042</v>
       </c>
       <c r="G34" s="1">
         <v>1.21</v>
       </c>
       <c r="H34" s="1">
-        <v>53.36</v>
+        <v>58.02</v>
       </c>
       <c r="I34" s="1">
-        <v>2.97</v>
+        <v>4.77</v>
       </c>
       <c r="J34" s="1">
-        <v>-0.005376928216629924</v>
+        <v>-0.004614332104260911</v>
       </c>
       <c r="K34" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="1">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M34" s="1">
-        <v>-0.08797081992697997</v>
+        <v>-0.08290428205252198</v>
       </c>
       <c r="N34" s="1">
-        <v>-4.5245942950694635</v>
+        <v>-5.0240443158719845</v>
       </c>
       <c r="O34" s="1">
-        <v>41.66666666666667</v>
+        <v>47.05882352941176</v>
       </c>
       <c r="P34" s="1">
         <v>21.09433056126816</v>
       </c>
       <c r="Q34" s="1">
-        <v>49.404761904761905</v>
+        <v>50.35294117647059</v>
       </c>
       <c r="R34" s="1">
-        <v>37.5</v>
+        <v>39.23529411764706</v>
       </c>
       <c r="S34" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="T34" s="1">
-        <v>-9.33</v>
+        <v>-7.59</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -4212,28 +4226,28 @@
         <v>17.64</v>
       </c>
       <c r="C35" s="1">
-        <v>86.90476190476191</v>
+        <v>87.05882352941177</v>
       </c>
       <c r="D35" s="1">
         <v>-0.4552154195011338</v>
       </c>
       <c r="E35" s="1">
-        <v>-0.33</v>
+        <v>-0.47</v>
       </c>
       <c r="F35" s="1">
-        <v>-0.09428172618550805</v>
+        <v>-0.09003772464392384</v>
       </c>
       <c r="G35" s="1">
         <v>0.95</v>
       </c>
       <c r="H35" s="1">
-        <v>32.88</v>
+        <v>32.01</v>
       </c>
       <c r="I35" s="1">
-        <v>-17.53</v>
+        <v>-18.08</v>
       </c>
       <c r="J35" s="1">
-        <v>0.00047106364207268763</v>
+        <v>-0.00036953627848923315</v>
       </c>
       <c r="K35" s="1" t="b">
         <v>0</v>
@@ -4242,28 +4256,28 @@
         <v>-56</v>
       </c>
       <c r="M35" s="1">
-        <v>-0.09588047003432232</v>
+        <v>-0.09113341658861396</v>
       </c>
       <c r="N35" s="1">
-        <v>-5.315559305803698</v>
+        <v>-5.846957769481191</v>
       </c>
       <c r="O35" s="1">
-        <v>36.904761904761905</v>
+        <v>42.35294117647059</v>
       </c>
       <c r="P35" s="1">
-        <v>23.996351232323672</v>
+        <v>23.054125788710962</v>
       </c>
       <c r="Q35" s="1">
-        <v>43.92857142857144</v>
+        <v>44.11764705882353</v>
       </c>
       <c r="R35" s="1">
-        <v>38.095238095238095</v>
+        <v>40.1764705882353</v>
       </c>
       <c r="S35" s="1" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="T35" s="1">
-        <v>15.6</v>
+        <v>17.68</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -4274,58 +4288,58 @@
         <v>10.27</v>
       </c>
       <c r="C36" s="1">
-        <v>77.38095238095238</v>
+        <v>77.64705882352942</v>
       </c>
       <c r="D36" s="1">
-        <v>-0.0029211295034079223</v>
+        <v>0.009737098344693247</v>
       </c>
       <c r="E36" s="1">
-        <v>-1.31</v>
+        <v>-1.3</v>
       </c>
       <c r="F36" s="1">
-        <v>-0.06323833297718343</v>
+        <v>-0.10611758218520727</v>
       </c>
       <c r="G36" s="1">
         <v>1.13</v>
       </c>
       <c r="H36" s="1">
-        <v>40.72</v>
+        <v>38.78</v>
       </c>
       <c r="I36" s="1">
-        <v>-10.42</v>
+        <v>-11.92</v>
       </c>
       <c r="J36" s="1">
-        <v>0.00936018056564004</v>
+        <v>0.00604092659304731</v>
       </c>
       <c r="K36" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="1">
         <v>-20</v>
       </c>
       <c r="M36" s="1">
-        <v>-0.059081598970266325</v>
+        <v>-0.103268783129013</v>
       </c>
       <c r="N36" s="1">
-        <v>-1.635672199398101</v>
+        <v>-7.060494423521095</v>
       </c>
       <c r="O36" s="1">
-        <v>46.42857142857143</v>
+        <v>38.82352941176471</v>
       </c>
       <c r="P36" s="1">
         <v>26.730280409441182</v>
       </c>
       <c r="Q36" s="1">
-        <v>51.07142857142856</v>
+        <v>49.17647058823529</v>
       </c>
       <c r="R36" s="1">
-        <v>42.26190476190476</v>
+        <v>39.411764705882355</v>
       </c>
       <c r="S36" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="T36" s="1">
-        <v>15.31</v>
+        <v>12.46</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -4336,28 +4350,28 @@
         <v>5.29</v>
       </c>
       <c r="C37" s="2">
-        <v>59.523809523809526</v>
+        <v>60</v>
       </c>
       <c r="D37" s="2">
         <v>0.42155009451795833</v>
       </c>
       <c r="E37" s="2">
-        <v>-3.25</v>
+        <v>-3.26</v>
       </c>
       <c r="F37" s="2">
-        <v>0.20640191800020602</v>
+        <v>0.19408671098118957</v>
       </c>
       <c r="G37" s="2">
         <v>1.28</v>
       </c>
       <c r="H37" s="2">
-        <v>40.99</v>
+        <v>39.81</v>
       </c>
       <c r="I37" s="2">
-        <v>4.37</v>
+        <v>3.7</v>
       </c>
       <c r="J37" s="2">
-        <v>0.01526286056327369</v>
+        <v>0.014291683203633186</v>
       </c>
       <c r="K37" s="2" t="b">
         <v>0</v>
@@ -4366,28 +4380,28 @@
         <v>-107</v>
       </c>
       <c r="M37" s="2">
-        <v>0.2153548835535659</v>
+        <v>0.20022258587145414</v>
       </c>
       <c r="N37" s="2">
-        <v>25.807976052985126</v>
+        <v>23.288642476525613</v>
       </c>
       <c r="O37" s="2">
-        <v>82.14285714285714</v>
+        <v>80</v>
       </c>
       <c r="P37" s="2">
-        <v>20.538852415160598</v>
+        <v>20.1020772277769</v>
       </c>
       <c r="Q37" s="2">
-        <v>53.214285714285715</v>
+        <v>52.23529411764706</v>
       </c>
       <c r="R37" s="2">
-        <v>53.21428571428571</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="T37" s="2">
-        <v>23.4</v>
+        <v>23.12</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -4398,58 +4412,58 @@
         <v>0.04</v>
       </c>
       <c r="C38" s="2">
-        <v>30.952380952380953</v>
+        <v>31.76470588235294</v>
       </c>
       <c r="D38" s="2">
-        <v>686.25</v>
+        <v>689</v>
       </c>
       <c r="E38" s="2">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="F38" s="2">
-        <v>0.38959043893960177</v>
+        <v>0.35075515836149834</v>
       </c>
       <c r="G38" s="2">
         <v>1.21</v>
       </c>
       <c r="H38" s="2">
-        <v>65.41</v>
+        <v>59.71</v>
       </c>
       <c r="I38" s="2">
-        <v>67.81</v>
+        <v>60.33</v>
       </c>
       <c r="J38" s="2">
-        <v>0.01971069619730847</v>
+        <v>0.022221061202637803</v>
       </c>
       <c r="K38" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L38" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M38" s="2">
-        <v>0.3963051631046217</v>
+        <v>0.3553570645291968</v>
       </c>
       <c r="N38" s="2">
-        <v>43.90300400809071</v>
+        <v>38.80209034229988</v>
       </c>
       <c r="O38" s="2">
-        <v>91.66666666666666</v>
+        <v>90.58823529411765</v>
       </c>
       <c r="P38" s="2">
         <v>17.802507034008837</v>
       </c>
       <c r="Q38" s="2">
-        <v>74.28571428571429</v>
+        <v>73.41176470588233</v>
       </c>
       <c r="R38" s="2">
-        <v>65.35714285714286</v>
+        <v>65.52941176470588</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T38" s="2">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -4460,7 +4474,7 @@
         <v>-0.35</v>
       </c>
       <c r="C39" s="1">
-        <v>22.61904761904762</v>
+        <v>22.35294117647059</v>
       </c>
       <c r="D39" s="1">
         <v>38.714285714285715</v>
@@ -4469,19 +4483,19 @@
         <v>-1.29</v>
       </c>
       <c r="F39" s="1">
-        <v>-0.0019111822236348719</v>
+        <v>-0.01788636127597297</v>
       </c>
       <c r="G39" s="1">
         <v>1.13</v>
       </c>
       <c r="H39" s="1">
-        <v>38.13</v>
+        <v>35.01</v>
       </c>
       <c r="I39" s="1">
-        <v>-6.2</v>
+        <v>-7.93</v>
       </c>
       <c r="J39" s="1">
-        <v>-0.00389104937391255</v>
+        <v>-0.004630991566639146</v>
       </c>
       <c r="K39" s="1" t="b">
         <v>1</v>
@@ -4490,28 +4504,28 @@
         <v>-1</v>
       </c>
       <c r="M39" s="1">
-        <v>0.002245551783282229</v>
+        <v>-0.0150375622197787</v>
       </c>
       <c r="N39" s="1">
-        <v>4.4970428759567636</v>
+        <v>1.762627667402337</v>
       </c>
       <c r="O39" s="1">
-        <v>54.761904761904766</v>
+        <v>51.76470588235295</v>
       </c>
       <c r="P39" s="1">
         <v>30.28933322215756</v>
       </c>
       <c r="Q39" s="1">
-        <v>45.35714285714286</v>
+        <v>43.529411764705884</v>
       </c>
       <c r="R39" s="1">
-        <v>40.773809523809526</v>
+        <v>39.76470588235295</v>
       </c>
       <c r="S39" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="T39" s="1">
-        <v>14.98</v>
+        <v>13.97</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -4522,58 +4536,58 @@
         <v>-9.13</v>
       </c>
       <c r="C40" s="1">
-        <v>2.380952380952381</v>
+        <v>2.3529411764705883</v>
       </c>
       <c r="D40" s="1">
         <v>10.75575027382256</v>
       </c>
       <c r="E40" s="1">
-        <v>3.93</v>
+        <v>4.43</v>
       </c>
       <c r="F40" s="1">
-        <v>0.43030548050227524</v>
+        <v>0.5674113238863513</v>
       </c>
       <c r="G40" s="1">
-        <v>0.69</v>
+        <v>0.58</v>
       </c>
       <c r="H40" s="1">
-        <v>57.6</v>
+        <v>65.12</v>
       </c>
       <c r="I40" s="1">
-        <v>3.12</v>
+        <v>15.32</v>
       </c>
       <c r="J40" s="1">
-        <v>0.034652432816401194</v>
+        <v>0.03709642901680366</v>
       </c>
       <c r="K40" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="1">
         <v>-21</v>
       </c>
       <c r="M40" s="1">
-        <v>0.4203932686396268</v>
+        <v>0.5582075115509544</v>
       </c>
       <c r="N40" s="1">
-        <v>46.31181456159121</v>
+        <v>59.087135044475644</v>
       </c>
       <c r="O40" s="1">
-        <v>94.04761904761905</v>
+        <v>97.6470588235294</v>
       </c>
       <c r="P40" s="1">
         <v>51.940889187924654</v>
       </c>
       <c r="Q40" s="1">
-        <v>53.92857142857143</v>
+        <v>57.1764705882353</v>
       </c>
       <c r="R40" s="1">
-        <v>46.607142857142854</v>
+        <v>47.88235294117647</v>
       </c>
       <c r="S40" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="T40" s="1">
-        <v>38.13</v>
+        <v>39.41</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -4584,7 +4598,7 @@
         <v>-4.97</v>
       </c>
       <c r="C41" s="3">
-        <v>4.761904761904762</v>
+        <v>4.705882352941177</v>
       </c>
       <c r="D41" s="3">
         <v>1.5533199195171026</v>
@@ -4593,19 +4607,19 @@
         <v>0.01</v>
       </c>
       <c r="F41" s="3">
-        <v>-0.12879710667669408</v>
+        <v>-0.08949428988061581</v>
       </c>
       <c r="G41" s="3">
         <v>1.22</v>
       </c>
       <c r="H41" s="3">
-        <v>41.94</v>
+        <v>44.93</v>
       </c>
       <c r="I41" s="3">
-        <v>-11.84</v>
+        <v>-10.28</v>
       </c>
       <c r="J41" s="3">
-        <v>-0.01752626670200881</v>
+        <v>-0.017788954477799407</v>
       </c>
       <c r="K41" s="3" t="b">
         <v>1</v>
@@ -4614,28 +4628,28 @@
         <v>4</v>
       </c>
       <c r="M41" s="3">
-        <v>-0.12176263374191132</v>
+        <v>-0.08467324532397935</v>
       </c>
       <c r="N41" s="3">
-        <v>-7.903775676562595</v>
+        <v>-5.200940643017723</v>
       </c>
       <c r="O41" s="3">
-        <v>29.761904761904763</v>
+        <v>45.88235294117647</v>
       </c>
       <c r="P41" s="3">
         <v>30.769232468942608</v>
       </c>
       <c r="Q41" s="3">
-        <v>23.80952380952381</v>
+        <v>24.352941176470587</v>
       </c>
       <c r="R41" s="3">
-        <v>16.666666666666668</v>
+        <v>21.70588235294118</v>
       </c>
       <c r="S41" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="T41" s="3">
-        <v>-19.98</v>
+        <v>-14.94</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -4646,28 +4660,28 @@
         <v>3.33</v>
       </c>
       <c r="C42" s="1">
-        <v>51.19047619047619</v>
+        <v>51.76470588235295</v>
       </c>
       <c r="D42" s="1">
-        <v>1.231231231231231</v>
+        <v>1.2252252252252251</v>
       </c>
       <c r="E42" s="1">
-        <v>4.37</v>
+        <v>4.33</v>
       </c>
       <c r="F42" s="1">
-        <v>-0.11764762786499958</v>
+        <v>-0.1271099460459196</v>
       </c>
       <c r="G42" s="1">
         <v>0.31</v>
       </c>
       <c r="H42" s="1">
-        <v>29.27</v>
+        <v>25.48</v>
       </c>
       <c r="I42" s="1">
-        <v>-9.61</v>
+        <v>-10.74</v>
       </c>
       <c r="J42" s="1">
-        <v>-0.014228006805639215</v>
+        <v>-0.014511416874836373</v>
       </c>
       <c r="K42" s="1" t="b">
         <v>0</v>
@@ -4676,28 +4690,28 @@
         <v>16</v>
       </c>
       <c r="M42" s="1">
-        <v>-0.13971029297863646</v>
+        <v>-0.14223049488264305</v>
       </c>
       <c r="N42" s="1">
-        <v>-9.698541600235115</v>
+        <v>-10.956665598884099</v>
       </c>
       <c r="O42" s="1">
-        <v>28.57142857142857</v>
+        <v>30.58823529411765</v>
       </c>
       <c r="P42" s="1">
-        <v>16.35579214434687</v>
+        <v>17.091741705344468</v>
       </c>
       <c r="Q42" s="1">
-        <v>35.833333333333336</v>
+        <v>35.88235294117647</v>
       </c>
       <c r="R42" s="1">
-        <v>32.61904761904761</v>
+        <v>33.294117647058826</v>
       </c>
       <c r="S42" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="T42" s="1">
-        <v>-2.87</v>
+        <v>-2.19</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -4708,28 +4722,28 @@
         <v>0.15</v>
       </c>
       <c r="C43" s="2">
-        <v>32.142857142857146</v>
+        <v>32.94117647058823</v>
       </c>
       <c r="D43" s="2">
         <v>150.8</v>
       </c>
       <c r="E43" s="2">
-        <v>8.86</v>
+        <v>8.78</v>
       </c>
       <c r="F43" s="2">
-        <v>0.21190668561134812</v>
+        <v>0.20769404139812686</v>
       </c>
       <c r="G43" s="2">
         <v>1.35</v>
       </c>
       <c r="H43" s="2">
-        <v>51.57</v>
+        <v>51.49</v>
       </c>
       <c r="I43" s="2">
-        <v>18.39</v>
+        <v>18.22</v>
       </c>
       <c r="J43" s="2">
-        <v>0.012189998135815248</v>
+        <v>0.011303345521781681</v>
       </c>
       <c r="K43" s="2" t="b">
         <v>0</v>
@@ -4738,28 +4752,28 @@
         <v>18</v>
       </c>
       <c r="M43" s="2">
-        <v>0.22309789255304802</v>
+        <v>0.2153638850109576</v>
       </c>
       <c r="N43" s="2">
-        <v>26.582276952933338</v>
+        <v>24.80277239047597</v>
       </c>
       <c r="O43" s="2">
-        <v>83.33333333333334</v>
+        <v>83.52941176470588</v>
       </c>
       <c r="P43" s="2">
         <v>24.82490242340647</v>
       </c>
       <c r="Q43" s="2">
-        <v>65.11904761904762</v>
+        <v>65.52941176470588</v>
       </c>
       <c r="R43" s="2">
-        <v>58.273809523809526</v>
+        <v>58.64705882352942</v>
       </c>
       <c r="S43" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="T43" s="2">
-        <v>5.9</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -4770,28 +4784,28 @@
         <v>1.48</v>
       </c>
       <c r="C44" s="2">
-        <v>41.66666666666667</v>
+        <v>42.35294117647059</v>
       </c>
       <c r="D44" s="2">
         <v>19.054054054054053</v>
       </c>
       <c r="E44" s="2">
-        <v>-0.68</v>
+        <v>-0.69</v>
       </c>
       <c r="F44" s="2">
-        <v>0.09458570456341873</v>
+        <v>0.11192113827705684</v>
       </c>
       <c r="G44" s="2">
         <v>2.64</v>
       </c>
       <c r="H44" s="2">
-        <v>40.6</v>
+        <v>40.81</v>
       </c>
       <c r="I44" s="2">
-        <v>-1.42</v>
+        <v>-1.15</v>
       </c>
       <c r="J44" s="2">
-        <v>0.007225443850806593</v>
+        <v>0.00694695478308402</v>
       </c>
       <c r="K44" s="2" t="b">
         <v>0</v>
@@ -4800,28 +4814,28 @@
         <v>-8</v>
       </c>
       <c r="M44" s="2">
-        <v>0.14702450280452672</v>
+        <v>0.14785983406289227</v>
       </c>
       <c r="N44" s="2">
-        <v>18.974937978081215</v>
+        <v>18.052367295669427</v>
       </c>
       <c r="O44" s="2">
-        <v>75</v>
+        <v>74.11764705882354</v>
       </c>
       <c r="P44" s="2">
-        <v>27.705367784091152</v>
+        <v>25.276100184761987</v>
       </c>
       <c r="Q44" s="2">
-        <v>55.11904761904762</v>
+        <v>55.882352941176464</v>
       </c>
       <c r="R44" s="2">
-        <v>52.857142857142854</v>
+        <v>53.88235294117648</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="T44" s="2">
-        <v>18.04</v>
+        <v>19.07</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
@@ -4832,7 +4846,7 @@
         <v>12.43</v>
       </c>
       <c r="C45" s="1">
-        <v>82.14285714285714</v>
+        <v>82.35294117647058</v>
       </c>
       <c r="D45" s="1">
         <v>-2.353982300884956</v>
@@ -4841,49 +4855,49 @@
         <v>1.03</v>
       </c>
       <c r="F45" s="1">
-        <v>0.0005285439271493358</v>
+        <v>-0.004389269728821227</v>
       </c>
       <c r="G45" s="1">
         <v>1.45</v>
       </c>
       <c r="H45" s="1">
-        <v>45.39</v>
+        <v>50.15</v>
       </c>
       <c r="I45" s="1">
-        <v>4.57</v>
+        <v>6.38</v>
       </c>
       <c r="J45" s="1">
-        <v>0.002962136272608495</v>
+        <v>0.002299682623178883</v>
       </c>
       <c r="K45" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L45" s="1">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M45" s="1">
-        <v>0.014917238566477753</v>
+        <v>0.005471957773389713</v>
       </c>
       <c r="N45" s="1">
-        <v>5.764211554276315</v>
+        <v>3.8135796667191753</v>
       </c>
       <c r="O45" s="1">
-        <v>57.14285714285714</v>
+        <v>56.470588235294116</v>
       </c>
       <c r="P45" s="1">
         <v>17.57882034058413</v>
       </c>
       <c r="Q45" s="1">
-        <v>47.14285714285714</v>
+        <v>47.411764705882355</v>
       </c>
       <c r="R45" s="1">
-        <v>41.964285714285715</v>
+        <v>41.76470588235294</v>
       </c>
       <c r="S45" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="T45" s="1">
-        <v>-2.36</v>
+        <v>-2.56</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
@@ -4894,28 +4908,28 @@
         <v>-0.34</v>
       </c>
       <c r="C46" s="3">
-        <v>23.809523809523807</v>
+        <v>23.52941176470588</v>
       </c>
       <c r="D46" s="3">
         <v>473.05882352941177</v>
       </c>
       <c r="E46" s="3">
-        <v>4.53</v>
+        <v>4.52</v>
       </c>
       <c r="F46" s="3">
-        <v>-0.28433903598072496</v>
+        <v>-0.3430157444441759</v>
       </c>
       <c r="G46" s="3">
         <v>1.77</v>
       </c>
       <c r="H46" s="3">
-        <v>35.24</v>
+        <v>38.3</v>
       </c>
       <c r="I46" s="3">
-        <v>-30.88</v>
+        <v>-29.97</v>
       </c>
       <c r="J46" s="3">
-        <v>-0.010267187067093893</v>
+        <v>-0.011057260488990146</v>
       </c>
       <c r="K46" s="3" t="b">
         <v>1</v>
@@ -4924,28 +4938,28 @@
         <v>17</v>
       </c>
       <c r="M46" s="3">
-        <v>-0.25971838070898523</v>
+        <v>-0.3261420884959483</v>
       </c>
       <c r="N46" s="3">
-        <v>-21.699350373269993</v>
+        <v>-29.34782496021462</v>
       </c>
       <c r="O46" s="3">
-        <v>13.095238095238097</v>
+        <v>8.235294117647058</v>
       </c>
       <c r="P46" s="3">
         <v>54.33673655574689</v>
       </c>
       <c r="Q46" s="3">
-        <v>43.92857142857142</v>
+        <v>43.99999999999999</v>
       </c>
       <c r="R46" s="3">
-        <v>27.26190476190476</v>
+        <v>25.47058823529411</v>
       </c>
       <c r="S46" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="T46" s="3">
-        <v>6.23</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
@@ -4956,28 +4970,28 @@
         <v>8.67</v>
       </c>
       <c r="C47" s="1">
-        <v>73.80952380952381</v>
+        <v>74.11764705882354</v>
       </c>
       <c r="D47" s="1">
         <v>-0.7716262975778546</v>
       </c>
       <c r="E47" s="1">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="F47" s="1">
-        <v>0.06911654352729206</v>
+        <v>0.04936994662389097</v>
       </c>
       <c r="G47" s="1">
         <v>1.42</v>
       </c>
       <c r="H47" s="1">
-        <v>44.44</v>
+        <v>45.21</v>
       </c>
       <c r="I47" s="1">
-        <v>1.03</v>
+        <v>1.43</v>
       </c>
       <c r="J47" s="1">
-        <v>0.017993162101325254</v>
+        <v>0.017196094279245757</v>
       </c>
       <c r="K47" s="1" t="b">
         <v>1</v>
@@ -4986,28 +5000,28 @@
         <v>-56</v>
       </c>
       <c r="M47" s="1">
-        <v>0.08254599185733191</v>
+        <v>0.05857375895928785</v>
       </c>
       <c r="N47" s="1">
-        <v>12.527086883361735</v>
+        <v>9.123759785308987</v>
       </c>
       <c r="O47" s="1">
-        <v>66.66666666666666</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="P47" s="1">
-        <v>33.3731909304046</v>
+        <v>31.953867028493892</v>
       </c>
       <c r="Q47" s="1">
-        <v>51.19047619047618</v>
+        <v>50.705882352941174</v>
       </c>
       <c r="R47" s="1">
-        <v>43.095238095238095</v>
+        <v>42.882352941176464</v>
       </c>
       <c r="S47" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="T47" s="1">
-        <v>17.24</v>
+        <v>17.03</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
@@ -5018,58 +5032,58 @@
         <v>3.17</v>
       </c>
       <c r="C48" s="2">
-        <v>48.80952380952381</v>
+        <v>49.411764705882355</v>
       </c>
       <c r="D48" s="2">
         <v>7.596214511041009</v>
       </c>
       <c r="E48" s="2">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="F48" s="2">
-        <v>0.1475564641964429</v>
+        <v>0.12913228124481538</v>
       </c>
       <c r="G48" s="2">
         <v>1.61</v>
       </c>
       <c r="H48" s="2">
-        <v>55.92</v>
+        <v>57.76</v>
       </c>
       <c r="I48" s="2">
-        <v>28.93</v>
+        <v>30.02</v>
       </c>
       <c r="J48" s="2">
-        <v>0.014071902287302821</v>
+        <v>0.012049853895436924</v>
       </c>
       <c r="K48" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M48" s="2">
-        <v>0.16706113915197696</v>
+        <v>0.14249972297003466</v>
       </c>
       <c r="N48" s="2">
-        <v>20.97860161282623</v>
+        <v>17.51635618638368</v>
       </c>
       <c r="O48" s="2">
-        <v>79.76190476190477</v>
+        <v>72.94117647058823</v>
       </c>
       <c r="P48" s="2">
-        <v>23.23749735248456</v>
+        <v>22.881696991902864</v>
       </c>
       <c r="Q48" s="2">
-        <v>65.23809523809523</v>
+        <v>65.64705882352942</v>
       </c>
       <c r="R48" s="2">
-        <v>55.95238095238097</v>
+        <v>54.23529411764706</v>
       </c>
       <c r="S48" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T48" s="2">
-        <v>6.68</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
@@ -5080,28 +5094,28 @@
         <v>-0.19</v>
       </c>
       <c r="C49" s="2">
-        <v>27.380952380952383</v>
+        <v>27.058823529411764</v>
       </c>
       <c r="D49" s="2">
         <v>2104.736842105263</v>
       </c>
       <c r="E49" s="2">
-        <v>-11.05</v>
+        <v>-11.2</v>
       </c>
       <c r="F49" s="2">
-        <v>0.14702008167561414</v>
+        <v>0.1524975552342094</v>
       </c>
       <c r="G49" s="2">
         <v>1.07</v>
       </c>
       <c r="H49" s="2">
-        <v>54.87</v>
+        <v>48.29</v>
       </c>
       <c r="I49" s="2">
-        <v>-1.77</v>
+        <v>-5.76</v>
       </c>
       <c r="J49" s="2">
-        <v>0.02015172853706399</v>
+        <v>0.01968426452911071</v>
       </c>
       <c r="K49" s="2" t="b">
         <v>0</v>
@@ -5110,28 +5124,28 @@
         <v>-7</v>
       </c>
       <c r="M49" s="2">
-        <v>0.14925832306395415</v>
+        <v>0.15403152395677555</v>
       </c>
       <c r="N49" s="2">
-        <v>19.19832000402394</v>
+        <v>18.669536285057763</v>
       </c>
       <c r="O49" s="2">
-        <v>76.19047619047619</v>
+        <v>76.47058823529412</v>
       </c>
       <c r="P49" s="2">
         <v>31.00158698078384</v>
       </c>
       <c r="Q49" s="2">
-        <v>65.83333333333333</v>
+        <v>62.58823529411765</v>
       </c>
       <c r="R49" s="2">
-        <v>56.60714285714286</v>
+        <v>56.58823529411765</v>
       </c>
       <c r="S49" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="T49" s="2">
-        <v>25.51</v>
+        <v>25.49</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
@@ -5142,28 +5156,28 @@
         <v>-3.77</v>
       </c>
       <c r="C50" s="3">
-        <v>8.333333333333332</v>
+        <v>8.235294117647058</v>
       </c>
       <c r="D50" s="3">
         <v>15.862068965517242</v>
       </c>
       <c r="E50" s="3">
-        <v>12.9</v>
+        <v>12.86</v>
       </c>
       <c r="F50" s="3">
-        <v>-0.33794354933020865</v>
+        <v>-0.2553528301595756</v>
       </c>
       <c r="G50" s="3">
-        <v>3.84</v>
+        <v>3.83</v>
       </c>
       <c r="H50" s="3">
-        <v>53.98</v>
+        <v>61.66</v>
       </c>
       <c r="I50" s="3">
-        <v>6.03</v>
+        <v>17.4</v>
       </c>
       <c r="J50" s="3">
-        <v>0.0016556572401208354</v>
+        <v>0.004022777169526145</v>
       </c>
       <c r="K50" s="3" t="b">
         <v>0</v>
@@ -5172,25 +5186,25 @@
         <v>69</v>
       </c>
       <c r="M50" s="3">
-        <v>-0.24713489871755823</v>
+        <v>-0.19333666609011568</v>
       </c>
       <c r="N50" s="3">
-        <v>-20.44100217412728</v>
+        <v>-16.067282719631365</v>
       </c>
       <c r="O50" s="3">
-        <v>14.285714285714285</v>
+        <v>23.52941176470588</v>
       </c>
       <c r="P50" s="3">
         <v>41.201484669672254</v>
       </c>
       <c r="Q50" s="3">
-        <v>48.0952380952381</v>
+        <v>53.05882352941176</v>
       </c>
       <c r="R50" s="3">
-        <v>22.44047619047619</v>
+        <v>25.764705882352942</v>
       </c>
       <c r="S50" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="T50" s="3"/>
     </row>
@@ -5202,7 +5216,7 @@
         <v>-7.19</v>
       </c>
       <c r="C51" s="1">
-        <v>3.571428571428571</v>
+        <v>3.5294117647058822</v>
       </c>
       <c r="D51" s="1">
         <v>5.305980528511822</v>
@@ -5211,19 +5225,19 @@
         <v>14.41</v>
       </c>
       <c r="F51" s="1">
-        <v>0.22519945433144278</v>
+        <v>0.19409276915417073</v>
       </c>
       <c r="G51" s="1">
         <v>1.69</v>
       </c>
       <c r="H51" s="1">
-        <v>72.38</v>
+        <v>73.35</v>
       </c>
       <c r="I51" s="1">
-        <v>51.99</v>
+        <v>56.44</v>
       </c>
       <c r="J51" s="1">
-        <v>0.05178035769740061</v>
+        <v>0.055910643616748225</v>
       </c>
       <c r="K51" s="1" t="b">
         <v>0</v>
@@ -5232,25 +5246,25 @@
         <v>14</v>
       </c>
       <c r="M51" s="1">
-        <v>0.2472621194450797</v>
+        <v>0.20921331799089415</v>
       </c>
       <c r="N51" s="1">
-        <v>28.998699642136504</v>
+        <v>24.18771568846962</v>
       </c>
       <c r="O51" s="1">
-        <v>84.52380952380952</v>
+        <v>81.17647058823529</v>
       </c>
       <c r="P51" s="1">
         <v>38.38748944617691</v>
       </c>
       <c r="Q51" s="1">
-        <v>57.26190476190476</v>
+        <v>57.76470588235294</v>
       </c>
       <c r="R51" s="1">
-        <v>42.91666666666666</v>
+        <v>41.99999999999999</v>
       </c>
       <c r="S51" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="T51" s="1"/>
     </row>
@@ -5262,28 +5276,28 @@
         <v>12.2</v>
       </c>
       <c r="C52" s="3">
-        <v>79.76190476190477</v>
+        <v>80</v>
       </c>
       <c r="D52" s="3">
         <v>-1.9934426229508198</v>
       </c>
       <c r="E52" s="3">
-        <v>-5.11</v>
+        <v>-5.32</v>
       </c>
       <c r="F52" s="3">
-        <v>-0.1508505170090942</v>
+        <v>-0.15357333799365053</v>
       </c>
       <c r="G52" s="3">
         <v>0.92</v>
       </c>
       <c r="H52" s="3">
-        <v>37.62</v>
+        <v>37.66</v>
       </c>
       <c r="I52" s="3">
         <v>-33.68</v>
       </c>
       <c r="J52" s="3">
-        <v>-0.01466672459830375</v>
+        <v>-0.014884544949434263</v>
       </c>
       <c r="K52" s="3" t="b">
         <v>0</v>
@@ -5292,150 +5306,148 @@
         <v>-106</v>
       </c>
       <c r="M52" s="3">
-        <v>-0.153408507167197</v>
+        <v>-0.1553264451051547</v>
       </c>
       <c r="N52" s="3">
-        <v>-11.068363019091167</v>
+        <v>-12.26626062113526</v>
       </c>
       <c r="O52" s="3">
-        <v>26.190476190476193</v>
+        <v>27.058823529411764</v>
       </c>
       <c r="P52" s="3">
-        <v>42.42351222913704</v>
+        <v>34.68082090497681</v>
       </c>
       <c r="Q52" s="3">
-        <v>32.976190476190474</v>
+        <v>32.8235294117647</v>
       </c>
       <c r="R52" s="3">
-        <v>23.452380952380963</v>
+        <v>25.000000000000004</v>
       </c>
       <c r="S52" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="T52" s="3"/>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B53" s="1">
-        <v>5.63</v>
-      </c>
-      <c r="C53" s="1">
-        <v>60.71428571428571</v>
-      </c>
-      <c r="D53" s="1">
-        <v>0.788632326820604</v>
-      </c>
-      <c r="E53" s="1">
-        <v>-1.38</v>
-      </c>
-      <c r="F53" s="1">
-        <v>-0.007669684320463485</v>
-      </c>
-      <c r="G53" s="1">
-        <v>0.98</v>
-      </c>
-      <c r="H53" s="1">
-        <v>38.94</v>
-      </c>
-      <c r="I53" s="1">
-        <v>2.49</v>
-      </c>
-      <c r="J53" s="1">
-        <v>0.003116379726557908</v>
-      </c>
-      <c r="K53" s="1" t="b">
+      <c r="B53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="1">
-        <v>84</v>
-      </c>
-      <c r="M53" s="1">
-        <v>-0.00830918185998919</v>
-      </c>
-      <c r="N53" s="1">
-        <v>3.4415695116296163</v>
-      </c>
-      <c r="O53" s="1">
-        <v>52.38095238095239</v>
-      </c>
-      <c r="P53" s="1">
-        <v>11.84024085938085</v>
-      </c>
-      <c r="Q53" s="1">
-        <v>49.285714285714285</v>
-      </c>
-      <c r="R53" s="1">
-        <v>45.833333333333336</v>
-      </c>
-      <c r="S53" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="T53" s="1">
-        <v>5.41</v>
-      </c>
+      <c r="C53" s="3">
+        <v>29.411764705882355</v>
+      </c>
+      <c r="D53" s="3">
+        <v>0</v>
+      </c>
+      <c r="E53" s="3">
+        <v>-0.87</v>
+      </c>
+      <c r="F53" s="3">
+        <v>-0.18529050424936652</v>
+      </c>
+      <c r="G53" s="3">
+        <v>0</v>
+      </c>
+      <c r="H53" s="3">
+        <v>59.07</v>
+      </c>
+      <c r="I53" s="3">
+        <v>8</v>
+      </c>
+      <c r="J53" s="3">
+        <v>-0.0033033594136436216</v>
+      </c>
+      <c r="K53" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L53" s="3">
+        <v>1744</v>
+      </c>
+      <c r="M53" s="3">
+        <v>-0.2072043431431686</v>
+      </c>
+      <c r="N53" s="3">
+        <v>-17.454050424936653</v>
+      </c>
+      <c r="O53" s="3">
+        <v>22.35294117647059</v>
+      </c>
+      <c r="P53" s="3">
+        <v>48.781873808753</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>39.52941176470589</v>
+      </c>
+      <c r="R53" s="3">
+        <v>16.764705882352942</v>
+      </c>
+      <c r="S53" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="T53" s="3"/>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B54" s="1">
-        <v>23.25</v>
+        <v>5.63</v>
       </c>
       <c r="C54" s="1">
-        <v>94.04761904761905</v>
+        <v>61.1764705882353</v>
       </c>
       <c r="D54" s="1">
-        <v>-0.1840860215053764</v>
+        <v>0.788632326820604</v>
       </c>
       <c r="E54" s="1">
-        <v>0.68</v>
+        <v>-1.38</v>
       </c>
       <c r="F54" s="1">
-        <v>-0.22587610778068734</v>
+        <v>0.0007133736567358911</v>
       </c>
       <c r="G54" s="1">
-        <v>1.58</v>
+        <v>0.98</v>
       </c>
       <c r="H54" s="1">
-        <v>44.6</v>
+        <v>42.32</v>
       </c>
       <c r="I54" s="1">
-        <v>2</v>
+        <v>3.37</v>
       </c>
       <c r="J54" s="1">
-        <v>-0.019674720900480898</v>
+        <v>0.003759356894933924</v>
       </c>
       <c r="K54" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="1">
-        <v>348</v>
+        <v>84</v>
       </c>
       <c r="M54" s="1">
-        <v>-0.2073306791344418</v>
+        <v>0.00027509687885984846</v>
       </c>
       <c r="N54" s="1">
-        <v>-16.46058021581565</v>
+        <v>3.2938935772661915</v>
       </c>
       <c r="O54" s="1">
-        <v>19.047619047619047</v>
+        <v>54.11764705882353</v>
       </c>
       <c r="P54" s="1">
-        <v>26.83257063748809</v>
+        <v>11.84024085938085</v>
       </c>
       <c r="Q54" s="1">
-        <v>47.14285714285714</v>
+        <v>49.64705882352941</v>
       </c>
       <c r="R54" s="1">
-        <v>31.130952380952383</v>
+        <v>46.470588235294116</v>
       </c>
       <c r="S54" s="1" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="T54" s="1">
-        <v>-27.47</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
@@ -5443,247 +5455,247 @@
         <v>54</v>
       </c>
       <c r="B55" s="1">
+        <v>23.25</v>
+      </c>
+      <c r="C55" s="1">
+        <v>94.11764705882352</v>
+      </c>
+      <c r="D55" s="1">
+        <v>-0.1840860215053764</v>
+      </c>
+      <c r="E55" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="F55" s="1">
+        <v>-0.22474739791865422</v>
+      </c>
+      <c r="G55" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="H55" s="1">
+        <v>51.31</v>
+      </c>
+      <c r="I55" s="1">
+        <v>4.48</v>
+      </c>
+      <c r="J55" s="1">
+        <v>-0.01873942324057018</v>
+      </c>
+      <c r="K55" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L55" s="1">
+        <v>349</v>
+      </c>
+      <c r="M55" s="1">
+        <v>-0.21203737136024903</v>
+      </c>
+      <c r="N55" s="1">
+        <v>-17.937353246644697</v>
+      </c>
+      <c r="O55" s="1">
+        <v>21.176470588235293</v>
+      </c>
+      <c r="P55" s="1">
+        <v>26.83257063748809</v>
+      </c>
+      <c r="Q55" s="1">
+        <v>48.94117647058823</v>
+      </c>
+      <c r="R55" s="1">
+        <v>31.941176470588232</v>
+      </c>
+      <c r="S55" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="T55" s="1">
+        <v>-26.66</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B56" s="1">
         <v>0.73</v>
       </c>
-      <c r="C55" s="1">
-        <v>36.904761904761905</v>
-      </c>
-      <c r="D55" s="1">
+      <c r="C56" s="1">
+        <v>37.64705882352941</v>
+      </c>
+      <c r="D56" s="1">
         <v>113.35616438356165</v>
       </c>
-      <c r="E55" s="1">
-        <v>1.71</v>
-      </c>
-      <c r="F55" s="1">
-        <v>-0.14613784423314732</v>
-      </c>
-      <c r="G55" s="1">
-        <v>3.77</v>
-      </c>
-      <c r="H55" s="1">
-        <v>63.81</v>
-      </c>
-      <c r="I55" s="1">
-        <v>41.79</v>
-      </c>
-      <c r="J55" s="1">
-        <v>-0.003218821411904941</v>
-      </c>
-      <c r="K55" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L55" s="1">
+      <c r="E56" s="1">
+        <v>1.76</v>
+      </c>
+      <c r="F56" s="1">
+        <v>-0.2859773610162384</v>
+      </c>
+      <c r="G56" s="1">
+        <v>3.78</v>
+      </c>
+      <c r="H56" s="1">
+        <v>59.97</v>
+      </c>
+      <c r="I56" s="1">
+        <v>37.39</v>
+      </c>
+      <c r="J56" s="1">
+        <v>-0.0012414242881671764</v>
+      </c>
+      <c r="K56" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L56" s="1">
         <v>321</v>
       </c>
-      <c r="M55" s="1">
-        <v>-0.057567435008836876</v>
-      </c>
-      <c r="N55" s="1">
-        <v>-1.4842558032551514</v>
-      </c>
-      <c r="O55" s="1">
-        <v>47.61904761904761</v>
-      </c>
-      <c r="P55" s="1">
+      <c r="M56" s="1">
+        <v>-0.22505688889146858</v>
+      </c>
+      <c r="N56" s="1">
+        <v>-19.23930499976665</v>
+      </c>
+      <c r="O56" s="1">
+        <v>17.647058823529413</v>
+      </c>
+      <c r="P56" s="1">
         <v>52.65288503392759</v>
       </c>
-      <c r="Q55" s="1">
-        <v>64.52380952380953</v>
-      </c>
-      <c r="R55" s="1">
-        <v>40.833333333333336</v>
-      </c>
-      <c r="S55" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="T55" s="1">
-        <v>-19.17</v>
-      </c>
-    </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A56" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B56" s="3">
+      <c r="Q56" s="1">
+        <v>64.47058823529412</v>
+      </c>
+      <c r="R56" s="1">
+        <v>32.47058823529412</v>
+      </c>
+      <c r="S56" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="T56" s="1">
+        <v>-27.53</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B57" s="3">
         <v>4.42</v>
       </c>
-      <c r="C56" s="3">
-        <v>55.952380952380956</v>
-      </c>
-      <c r="D56" s="3">
+      <c r="C57" s="3">
+        <v>56.470588235294116</v>
+      </c>
+      <c r="D57" s="3">
         <v>7.153846153846153</v>
       </c>
-      <c r="E56" s="3">
-        <v>-1.32</v>
-      </c>
-      <c r="F56" s="3">
-        <v>-0.31589162172699237</v>
-      </c>
-      <c r="G56" s="3">
-        <v>2.05</v>
-      </c>
-      <c r="H56" s="3">
-        <v>41.42</v>
-      </c>
-      <c r="I56" s="3">
-        <v>-7.38</v>
-      </c>
-      <c r="J56" s="3">
-        <v>-0.024576530428492824</v>
-      </c>
-      <c r="K56" s="3" t="b">
+      <c r="E57" s="3">
+        <v>-1.31</v>
+      </c>
+      <c r="F57" s="3">
+        <v>-0.3066477202178408</v>
+      </c>
+      <c r="G57" s="3">
+        <v>2.04</v>
+      </c>
+      <c r="H57" s="3">
+        <v>47.97</v>
+      </c>
+      <c r="I57" s="3">
+        <v>-2.28</v>
+      </c>
+      <c r="J57" s="3">
+        <v>-0.026119656622999848</v>
+      </c>
+      <c r="K57" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L56" s="3">
+      <c r="L57" s="3">
         <v>249</v>
       </c>
-      <c r="M56" s="3">
-        <v>-0.28231800090189274</v>
-      </c>
-      <c r="N56" s="3">
-        <v>-23.959312392560737</v>
-      </c>
-      <c r="O56" s="3">
-        <v>10.714285714285714</v>
-      </c>
-      <c r="P56" s="3">
+      <c r="M57" s="3">
+        <v>-0.28385732776828665</v>
+      </c>
+      <c r="N57" s="3">
+        <v>-25.119348887448457</v>
+      </c>
+      <c r="O57" s="3">
+        <v>11.76470588235294</v>
+      </c>
+      <c r="P57" s="3">
         <v>40.717118046641446</v>
       </c>
-      <c r="Q56" s="3">
-        <v>43.33333333333332</v>
-      </c>
-      <c r="R56" s="3">
-        <v>25.714285714285715</v>
-      </c>
-      <c r="S56" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="T56" s="3">
-        <v>-23.25</v>
-      </c>
-    </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B57" s="1">
+      <c r="Q57" s="3">
+        <v>45.294117647058826</v>
+      </c>
+      <c r="R57" s="3">
+        <v>26.11764705882353</v>
+      </c>
+      <c r="S57" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="T57" s="3">
+        <v>-22.85</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B58" s="1">
         <v>-0.1</v>
       </c>
-      <c r="C57" s="1">
-        <v>28.57142857142857</v>
-      </c>
-      <c r="D57" s="1">
+      <c r="C58" s="1">
+        <v>28.235294117647058</v>
+      </c>
+      <c r="D58" s="1">
         <v>316.79999999999995</v>
       </c>
-      <c r="E57" s="1">
-        <v>1.24</v>
-      </c>
-      <c r="F57" s="1">
-        <v>0.0206035181830152</v>
-      </c>
-      <c r="G57" s="1">
-        <v>1.65</v>
-      </c>
-      <c r="H57" s="1">
-        <v>38.21</v>
-      </c>
-      <c r="I57" s="1">
-        <v>-20.31</v>
-      </c>
-      <c r="J57" s="1">
-        <v>0.0035088291968071706</v>
-      </c>
-      <c r="K57" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L57" s="1">
+      <c r="E58" s="1">
+        <v>1.26</v>
+      </c>
+      <c r="F58" s="1">
+        <v>0.015258253548212003</v>
+      </c>
+      <c r="G58" s="1">
+        <v>1.64</v>
+      </c>
+      <c r="H58" s="1">
+        <v>45.54</v>
+      </c>
+      <c r="I58" s="1">
+        <v>-16.59</v>
+      </c>
+      <c r="J58" s="1">
+        <v>0.006183258478815165</v>
+      </c>
+      <c r="K58" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L58" s="1">
         <v>3</v>
       </c>
-      <c r="M57" s="1">
-        <v>0.04138718821760068</v>
-      </c>
-      <c r="N57" s="1">
-        <v>8.41120651938861</v>
-      </c>
-      <c r="O57" s="1">
-        <v>61.904761904761905</v>
-      </c>
-      <c r="P57" s="1">
-        <v>35.9459458370989</v>
-      </c>
-      <c r="Q57" s="1">
-        <v>51.785714285714285</v>
-      </c>
-      <c r="R57" s="1">
-        <v>47.67857142857143</v>
-      </c>
-      <c r="S57" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="T57" s="1">
-        <v>25.73</v>
-      </c>
-    </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A58" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B58" s="3">
-        <v>5.76</v>
-      </c>
-      <c r="C58" s="3">
-        <v>64.28571428571429</v>
-      </c>
-      <c r="D58" s="3">
-        <v>3.3177083333333335</v>
-      </c>
-      <c r="E58" s="3">
-        <v>0.97</v>
-      </c>
-      <c r="F58" s="3">
-        <v>-0.3511289432034123</v>
-      </c>
-      <c r="G58" s="3">
-        <v>1.88</v>
-      </c>
-      <c r="H58" s="3">
-        <v>36.08</v>
-      </c>
-      <c r="I58" s="3">
-        <v>1.04</v>
-      </c>
-      <c r="J58" s="3">
-        <v>-0.02347529119863297</v>
-      </c>
-      <c r="K58" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L58" s="3">
-        <v>519</v>
-      </c>
-      <c r="M58" s="3">
-        <v>-0.3229910514642812</v>
-      </c>
-      <c r="N58" s="3">
-        <v>-28.02661744879958</v>
-      </c>
-      <c r="O58" s="3">
-        <v>3.571428571428571</v>
-      </c>
-      <c r="P58" s="3">
-        <v>41.76493344029593</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>43.57142857142858</v>
-      </c>
-      <c r="R58" s="3">
-        <v>23.452380952380956</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="T58" s="3">
-        <v>-35.75</v>
+      <c r="M58" s="1">
+        <v>0.02928311044024534</v>
+      </c>
+      <c r="N58" s="1">
+        <v>6.194694933404732</v>
+      </c>
+      <c r="O58" s="1">
+        <v>61.1764705882353</v>
+      </c>
+      <c r="P58" s="1">
+        <v>33.706290307642504</v>
+      </c>
+      <c r="Q58" s="1">
+        <v>54.588235294117645</v>
+      </c>
+      <c r="R58" s="1">
+        <v>48.11764705882352</v>
+      </c>
+      <c r="S58" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="T58" s="1">
+        <v>26.17</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
@@ -5691,247 +5703,247 @@
         <v>58</v>
       </c>
       <c r="B59" s="3">
+        <v>5.76</v>
+      </c>
+      <c r="C59" s="3">
+        <v>64.70588235294117</v>
+      </c>
+      <c r="D59" s="3">
+        <v>3.3177083333333335</v>
+      </c>
+      <c r="E59" s="3">
+        <v>0.97</v>
+      </c>
+      <c r="F59" s="3">
+        <v>-0.3111624099274826</v>
+      </c>
+      <c r="G59" s="3">
+        <v>1.87</v>
+      </c>
+      <c r="H59" s="3">
+        <v>48.41</v>
+      </c>
+      <c r="I59" s="3">
+        <v>10.01</v>
+      </c>
+      <c r="J59" s="3">
+        <v>-0.021833508394369143</v>
+      </c>
+      <c r="K59" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L59" s="3">
+        <v>520</v>
+      </c>
+      <c r="M59" s="3">
+        <v>-0.2920973700898748</v>
+      </c>
+      <c r="N59" s="3">
+        <v>-25.94335311960727</v>
+      </c>
+      <c r="O59" s="3">
+        <v>10.588235294117647</v>
+      </c>
+      <c r="P59" s="3">
+        <v>41.76493344029593</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>48.35294117647059</v>
+      </c>
+      <c r="R59" s="3">
+        <v>25.647058823529413</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="T59" s="3">
+        <v>-33.56</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B60" s="3">
         <v>-0.67</v>
       </c>
-      <c r="C59" s="3">
-        <v>21.428571428571427</v>
-      </c>
-      <c r="D59" s="3">
+      <c r="C60" s="3">
+        <v>21.176470588235293</v>
+      </c>
+      <c r="D60" s="3">
         <v>2.417910447761194</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E60" s="3">
         <v>-4.45</v>
       </c>
-      <c r="F59" s="3">
-        <v>-0.35196353882296316</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="F60" s="3">
+        <v>-0.44776614924243374</v>
+      </c>
+      <c r="G60" s="3">
         <v>2.83</v>
       </c>
-      <c r="H59" s="3">
-        <v>40.26</v>
-      </c>
-      <c r="I59" s="3">
-        <v>-33.18</v>
-      </c>
-      <c r="J59" s="3">
-        <v>-0.03274734561863475</v>
-      </c>
-      <c r="K59" s="3" t="b">
+      <c r="H60" s="3">
+        <v>40.27</v>
+      </c>
+      <c r="I60" s="3">
+        <v>-33.28</v>
+      </c>
+      <c r="J60" s="3">
+        <v>-0.03148487285323178</v>
+      </c>
+      <c r="K60" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L60" s="3">
         <v>21</v>
       </c>
-      <c r="M59" s="3">
-        <v>-0.293449513956361</v>
-      </c>
-      <c r="N59" s="3">
-        <v>-25.072463698007557</v>
-      </c>
-      <c r="O59" s="3">
-        <v>7.142857142857142</v>
-      </c>
-      <c r="P59" s="3">
+      <c r="M60" s="3">
+        <v>-0.4076638240667759</v>
+      </c>
+      <c r="N60" s="3">
+        <v>-37.49999851729739</v>
+      </c>
+      <c r="O60" s="3">
+        <v>3.5294117647058822</v>
+      </c>
+      <c r="P60" s="3">
         <v>46.90217032437056</v>
       </c>
-      <c r="Q59" s="3">
-        <v>25.238095238095237</v>
-      </c>
-      <c r="R59" s="3">
-        <v>11.54761904761905</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="T59" s="3">
-        <v>-15.34</v>
-      </c>
-    </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B60" s="1">
+      <c r="Q60" s="3">
+        <v>25.17647058823529</v>
+      </c>
+      <c r="R60" s="3">
+        <v>10.64705882352941</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="T60" s="3">
+        <v>-16.24</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B61" s="1">
         <v>4.35</v>
       </c>
-      <c r="C60" s="1">
-        <v>54.761904761904766</v>
-      </c>
-      <c r="D60" s="1">
+      <c r="C61" s="1">
+        <v>55.294117647058826</v>
+      </c>
+      <c r="D61" s="1">
         <v>2.142528735632184</v>
       </c>
-      <c r="E60" s="1">
-        <v>-0.53</v>
-      </c>
-      <c r="F60" s="1">
-        <v>-0.020251531770902317</v>
-      </c>
-      <c r="G60" s="1">
+      <c r="E61" s="1">
+        <v>-0.52</v>
+      </c>
+      <c r="F61" s="1">
+        <v>-0.010041567863520548</v>
+      </c>
+      <c r="G61" s="1">
         <v>1.21</v>
       </c>
-      <c r="H60" s="1">
-        <v>30.72</v>
-      </c>
-      <c r="I60" s="1">
-        <v>5.37</v>
-      </c>
-      <c r="J60" s="1">
-        <v>0.0008430588561212438</v>
-      </c>
-      <c r="K60" s="1" t="b">
+      <c r="H61" s="1">
+        <v>31.09</v>
+      </c>
+      <c r="I61" s="1">
+        <v>4.89</v>
+      </c>
+      <c r="J61" s="1">
+        <v>-0.0010450931807364139</v>
+      </c>
+      <c r="K61" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L60" s="1">
-        <v>168</v>
-      </c>
-      <c r="M60" s="1">
-        <v>-0.013536807605882384</v>
-      </c>
-      <c r="N60" s="1">
-        <v>2.9188069370402863</v>
-      </c>
-      <c r="O60" s="1">
-        <v>51.19047619047619</v>
-      </c>
-      <c r="P60" s="1">
-        <v>10.661929166819702</v>
-      </c>
-      <c r="Q60" s="1">
-        <v>47.14285714285714</v>
-      </c>
-      <c r="R60" s="1">
-        <v>45.65476190476191</v>
-      </c>
-      <c r="S60" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="T60" s="1">
-        <v>-1.54</v>
-      </c>
-    </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A61" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B61" s="2">
+      <c r="L61" s="1">
+        <v>169</v>
+      </c>
+      <c r="M61" s="1">
+        <v>-0.005439661695822107</v>
+      </c>
+      <c r="N61" s="1">
+        <v>2.7224177197980004</v>
+      </c>
+      <c r="O61" s="1">
+        <v>52.94117647058824</v>
+      </c>
+      <c r="P61" s="1">
+        <v>10.92423743722024</v>
+      </c>
+      <c r="Q61" s="1">
+        <v>46.705882352941174</v>
+      </c>
+      <c r="R61" s="1">
+        <v>46.05882352941177</v>
+      </c>
+      <c r="S61" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="T61" s="1">
+        <v>-1.14</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2">
         <v>8.63</v>
       </c>
-      <c r="C61" s="2">
-        <v>72.61904761904762</v>
-      </c>
-      <c r="D61" s="2">
-        <v>0.21089223638470433</v>
-      </c>
-      <c r="E61" s="2">
+      <c r="C62" s="2">
+        <v>72.94117647058823</v>
+      </c>
+      <c r="D62" s="2">
+        <v>0.1888760139049825</v>
+      </c>
+      <c r="E62" s="2">
         <v>0.11</v>
       </c>
-      <c r="F61" s="2">
-        <v>0.13665521564582694</v>
-      </c>
-      <c r="G61" s="2">
+      <c r="F62" s="2">
+        <v>0.16701176988006336</v>
+      </c>
+      <c r="G62" s="2">
         <v>0.2</v>
       </c>
-      <c r="H61" s="2">
-        <v>55.02</v>
-      </c>
-      <c r="I61" s="2">
-        <v>13.38</v>
-      </c>
-      <c r="J61" s="2">
-        <v>0.0022562035036327002</v>
-      </c>
-      <c r="K61" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L61" s="2">
-        <v>92</v>
-      </c>
-      <c r="M61" s="2">
-        <v>0.11107531406479865</v>
-      </c>
-      <c r="N61" s="2">
-        <v>15.3800191041084</v>
-      </c>
-      <c r="O61" s="2">
-        <v>70.23809523809523</v>
-      </c>
-      <c r="P61" s="2">
+      <c r="H62" s="2">
+        <v>55.6</v>
+      </c>
+      <c r="I62" s="2">
+        <v>13.25</v>
+      </c>
+      <c r="J62" s="2">
+        <v>0.0022001582385115736</v>
+      </c>
+      <c r="K62" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L62" s="2">
+        <v>93</v>
+      </c>
+      <c r="M62" s="2">
+        <v>0.14948069876502168</v>
+      </c>
+      <c r="N62" s="2">
+        <v>18.21445376588238</v>
+      </c>
+      <c r="O62" s="2">
+        <v>75.29411764705883</v>
+      </c>
+      <c r="P62" s="2">
         <v>7.56622762341097</v>
       </c>
-      <c r="Q61" s="2">
-        <v>56.904761904761905</v>
-      </c>
-      <c r="R61" s="2">
-        <v>52.976190476190474</v>
-      </c>
-      <c r="S61" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="T61" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B62" s="1">
-        <v>44.17</v>
-      </c>
-      <c r="C62" s="1">
-        <v>98.80952380952381</v>
-      </c>
-      <c r="D62" s="1">
-        <v>1.5630518451437625</v>
-      </c>
-      <c r="E62" s="1">
-        <v>-1.07</v>
-      </c>
-      <c r="F62" s="1">
-        <v>-0.14534398401134</v>
-      </c>
-      <c r="G62" s="1">
-        <v>2.24</v>
-      </c>
-      <c r="H62" s="1">
-        <v>53.81</v>
-      </c>
-      <c r="I62" s="1">
-        <v>53.63</v>
-      </c>
-      <c r="J62" s="1">
-        <v>-0.003201504761632868</v>
-      </c>
-      <c r="K62" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L62" s="1">
-        <v>936</v>
-      </c>
-      <c r="M62" s="1">
-        <v>-0.10569513656074614</v>
-      </c>
-      <c r="N62" s="1">
-        <v>-6.297025958446079</v>
-      </c>
-      <c r="O62" s="1">
-        <v>32.142857142857146</v>
-      </c>
-      <c r="P62" s="1">
-        <v>39.10478556320163</v>
-      </c>
-      <c r="Q62" s="1">
-        <v>68.57142857142857</v>
-      </c>
-      <c r="R62" s="1">
-        <v>42.73809523809524</v>
-      </c>
-      <c r="S62" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="T62" s="1">
-        <v>-25.37</v>
+      <c r="Q62" s="2">
+        <v>56.470588235294116</v>
+      </c>
+      <c r="R62" s="2">
+        <v>54.70588235294118</v>
+      </c>
+      <c r="S62" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="T62" s="2">
+        <v>8.73</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
@@ -5939,61 +5951,61 @@
         <v>62</v>
       </c>
       <c r="B63" s="1">
-        <v>34.93</v>
+        <v>44.17</v>
       </c>
       <c r="C63" s="1">
-        <v>97.61904761904762</v>
+        <v>98.82352941176471</v>
       </c>
       <c r="D63" s="1">
-        <v>-1.5714285714285714</v>
+        <v>1.5843332578673308</v>
       </c>
       <c r="E63" s="1">
-        <v>1.52</v>
+        <v>-1.09</v>
       </c>
       <c r="F63" s="1">
-        <v>-0.160242230119019</v>
+        <v>-0.1638427687651962</v>
       </c>
       <c r="G63" s="1">
-        <v>0.98</v>
+        <v>2.23</v>
       </c>
       <c r="H63" s="1">
-        <v>46.19</v>
+        <v>60.5</v>
       </c>
       <c r="I63" s="1">
-        <v>2.75</v>
+        <v>60.91</v>
       </c>
       <c r="J63" s="1">
-        <v>-0.019539477769417283</v>
+        <v>-0.001457016922845972</v>
       </c>
       <c r="K63" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" s="1">
-        <v>364</v>
+        <v>937</v>
       </c>
       <c r="M63" s="1">
-        <v>-0.1608817276585447</v>
+        <v>-0.13688874692581965</v>
       </c>
       <c r="N63" s="1">
-        <v>-11.81568506822593</v>
+        <v>-10.42249080320176</v>
       </c>
       <c r="O63" s="1">
-        <v>23.809523809523807</v>
+        <v>31.76470588235294</v>
       </c>
       <c r="P63" s="1">
-        <v>25.543467249515373</v>
+        <v>39.10478556320163</v>
       </c>
       <c r="Q63" s="1">
-        <v>45.59523809523809</v>
+        <v>70.70588235294119</v>
       </c>
       <c r="R63" s="1">
-        <v>30.95238095238095</v>
+        <v>42.8235294117647</v>
       </c>
       <c r="S63" s="1" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="T63" s="1">
-        <v>-13.8</v>
+        <v>-25.29</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.25">
@@ -6001,247 +6013,247 @@
         <v>63</v>
       </c>
       <c r="B64" s="1">
-        <v>7.62</v>
+        <v>34.93</v>
       </c>
       <c r="C64" s="1">
-        <v>65.47619047619048</v>
+        <v>97.6470588235294</v>
       </c>
       <c r="D64" s="1">
-        <v>-0.3740157480314961</v>
+        <v>-1.5714285714285714</v>
       </c>
       <c r="E64" s="1">
-        <v>0.39</v>
+        <v>1.52</v>
       </c>
       <c r="F64" s="1">
-        <v>-0.07826768557150945</v>
+        <v>-0.18465613704495365</v>
       </c>
       <c r="G64" s="1">
-        <v>0.36</v>
+        <v>0.97</v>
       </c>
       <c r="H64" s="1">
-        <v>32.74</v>
+        <v>51.21</v>
       </c>
       <c r="I64" s="1">
-        <v>-9.9</v>
+        <v>5.78</v>
       </c>
       <c r="J64" s="1">
-        <v>-0.005731773645318966</v>
+        <v>-0.018767477952433345</v>
       </c>
       <c r="K64" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L64" s="1">
-        <v>-102</v>
+        <v>365</v>
       </c>
       <c r="M64" s="1">
-        <v>-0.09873160683633209</v>
+        <v>-0.1853135522117677</v>
       </c>
       <c r="N64" s="1">
-        <v>-5.6006729860046764</v>
+        <v>-15.26497133179656</v>
       </c>
       <c r="O64" s="1">
-        <v>35.714285714285715</v>
+        <v>24.705882352941178</v>
       </c>
       <c r="P64" s="1">
-        <v>15.66660418352099</v>
+        <v>25.543467249515373</v>
       </c>
       <c r="Q64" s="1">
-        <v>36.666666666666664</v>
+        <v>46.23529411764706</v>
       </c>
       <c r="R64" s="1">
-        <v>34.583333333333336</v>
+        <v>31</v>
       </c>
       <c r="S64" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="T64" s="1">
+        <v>-13.76</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B65" s="1">
+        <v>7.62</v>
+      </c>
+      <c r="C65" s="1">
+        <v>65.88235294117646</v>
+      </c>
+      <c r="D65" s="1">
+        <v>-0.3740157480314961</v>
+      </c>
+      <c r="E65" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="F65" s="1">
+        <v>-0.10503529169995265</v>
+      </c>
+      <c r="G65" s="1">
+        <v>0.36</v>
+      </c>
+      <c r="H65" s="1">
+        <v>26.2</v>
+      </c>
+      <c r="I65" s="1">
+        <v>-12.29</v>
+      </c>
+      <c r="J65" s="1">
+        <v>-0.00620465013183804</v>
+      </c>
+      <c r="K65" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L65" s="1">
+        <v>-101</v>
+      </c>
+      <c r="M65" s="1">
+        <v>-0.11906014859198599</v>
+      </c>
+      <c r="N65" s="1">
+        <v>-8.639630969818391</v>
+      </c>
+      <c r="O65" s="1">
+        <v>35.294117647058826</v>
+      </c>
+      <c r="P65" s="1">
+        <v>18.133639028994587</v>
+      </c>
+      <c r="Q65" s="1">
+        <v>35.647058823529406</v>
+      </c>
+      <c r="R65" s="1">
+        <v>33.1764705882353</v>
+      </c>
+      <c r="S65" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="T64" s="1">
-        <v>8.55</v>
-      </c>
-    </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A65" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B65" s="2">
+      <c r="T65" s="1">
+        <v>7.14</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2">
         <v>17.99</v>
       </c>
-      <c r="C65" s="2">
-        <v>89.28571428571429</v>
-      </c>
-      <c r="D65" s="2">
+      <c r="C66" s="2">
+        <v>89.41176470588236</v>
+      </c>
+      <c r="D66" s="2">
         <v>0.3379655364091163</v>
       </c>
-      <c r="E65" s="2">
-        <v>2.09</v>
-      </c>
-      <c r="F65" s="2">
-        <v>0.12653804598976784</v>
-      </c>
-      <c r="G65" s="2">
+      <c r="E66" s="2">
+        <v>2.08</v>
+      </c>
+      <c r="F66" s="2">
+        <v>0.1309853158244585</v>
+      </c>
+      <c r="G66" s="2">
         <v>0.87</v>
       </c>
-      <c r="H65" s="2">
-        <v>61.38</v>
-      </c>
-      <c r="I65" s="2">
-        <v>18.99</v>
-      </c>
-      <c r="J65" s="2">
-        <v>0.010026576004527079</v>
-      </c>
-      <c r="K65" s="2" t="b">
+      <c r="H66" s="2">
+        <v>63.45</v>
+      </c>
+      <c r="I66" s="2">
+        <v>19.9</v>
+      </c>
+      <c r="J66" s="2">
+        <v>0.011390845288298571</v>
+      </c>
+      <c r="K66" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L65" s="2">
-        <v>79</v>
-      </c>
-      <c r="M65" s="2">
-        <v>0.12238131198285074</v>
-      </c>
-      <c r="N65" s="2">
-        <v>16.51061889591362</v>
-      </c>
-      <c r="O65" s="2">
-        <v>73.80952380952381</v>
-      </c>
-      <c r="P65" s="2">
-        <v>10.614074802632032</v>
-      </c>
-      <c r="Q65" s="2">
-        <v>67.5</v>
-      </c>
-      <c r="R65" s="2">
-        <v>59.82142857142857</v>
-      </c>
-      <c r="S65" s="2" t="s">
+      <c r="L66" s="2">
+        <v>80</v>
+      </c>
+      <c r="M66" s="2">
+        <v>0.1281365167682642</v>
+      </c>
+      <c r="N66" s="2">
+        <v>16.080035566206636</v>
+      </c>
+      <c r="O66" s="2">
+        <v>71.76470588235294</v>
+      </c>
+      <c r="P66" s="2">
+        <v>10.56723987277981</v>
+      </c>
+      <c r="Q66" s="2">
+        <v>69.76470588235296</v>
+      </c>
+      <c r="R66" s="2">
+        <v>59.941176470588246</v>
+      </c>
+      <c r="S66" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="T65" s="2">
-        <v>16.22</v>
-      </c>
-    </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A66" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B66" s="3">
+      <c r="T66" s="2">
+        <v>16.34</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B67" s="3">
         <v>72.89</v>
       </c>
-      <c r="C66" s="3">
+      <c r="C67" s="3">
         <v>100</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D67" s="3">
         <v>-0.6829469062971602</v>
       </c>
-      <c r="E66" s="3">
-        <v>1.65</v>
-      </c>
-      <c r="F66" s="3">
-        <v>-0.35540440046254984</v>
-      </c>
-      <c r="G66" s="3">
-        <v>5.28</v>
-      </c>
-      <c r="H66" s="3">
-        <v>52.85</v>
-      </c>
-      <c r="I66" s="3">
-        <v>52.25</v>
-      </c>
-      <c r="J66" s="3">
-        <v>-0.013316325042583134</v>
-      </c>
-      <c r="K66" s="3" t="b">
+      <c r="E67" s="3">
+        <v>1.69</v>
+      </c>
+      <c r="F67" s="3">
+        <v>-0.30455322839306775</v>
+      </c>
+      <c r="G67" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="H67" s="3">
+        <v>62.45</v>
+      </c>
+      <c r="I67" s="3">
+        <v>68.76</v>
+      </c>
+      <c r="J67" s="3">
+        <v>-0.009006231348070728</v>
+      </c>
+      <c r="K67" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L66" s="3">
+      <c r="L67" s="3">
         <v>669</v>
       </c>
-      <c r="M66" s="3">
-        <v>-0.21855192700404846</v>
-      </c>
-      <c r="N66" s="3">
-        <v>-17.582705002776308</v>
-      </c>
-      <c r="O66" s="3">
-        <v>17.857142857142858</v>
-      </c>
-      <c r="P66" s="3">
+      <c r="M67" s="3">
+        <v>-0.21251510503909898</v>
+      </c>
+      <c r="N67" s="3">
+        <v>-17.985126614529694</v>
+      </c>
+      <c r="O67" s="3">
+        <v>20</v>
+      </c>
+      <c r="P67" s="3">
         <v>56.49293299150161</v>
       </c>
-      <c r="Q66" s="3">
-        <v>55.714285714285715</v>
-      </c>
-      <c r="R66" s="3">
-        <v>27.559523809523807</v>
-      </c>
-      <c r="S66" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="T66" s="3">
-        <v>-41.83</v>
-      </c>
-    </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B67" s="1">
-        <v>13.87</v>
-      </c>
-      <c r="C67" s="1">
-        <v>83.33333333333334</v>
-      </c>
-      <c r="D67" s="1">
-        <v>3.0958904109589045</v>
-      </c>
-      <c r="E67" s="1">
-        <v>-2.42</v>
-      </c>
-      <c r="F67" s="1">
-        <v>-0.3245414157229523</v>
-      </c>
-      <c r="G67" s="1">
-        <v>2.1</v>
-      </c>
-      <c r="H67" s="1">
-        <v>45.45</v>
-      </c>
-      <c r="I67" s="1">
-        <v>30.3</v>
-      </c>
-      <c r="J67" s="1">
-        <v>-0.006999113410551259</v>
-      </c>
-      <c r="K67" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L67" s="1">
-        <v>515</v>
-      </c>
-      <c r="M67" s="1">
-        <v>-0.28936905104903843</v>
-      </c>
-      <c r="N67" s="1">
-        <v>-24.6644174072753</v>
-      </c>
-      <c r="O67" s="1">
-        <v>8.333333333333332</v>
-      </c>
-      <c r="P67" s="1">
-        <v>31.85898471566022</v>
-      </c>
-      <c r="Q67" s="1">
-        <v>60.952380952380956</v>
-      </c>
-      <c r="R67" s="1">
-        <v>33.392857142857146</v>
-      </c>
-      <c r="S67" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="T67" s="1">
-        <v>-32.64</v>
+      <c r="Q67" s="3">
+        <v>60.235294117647065</v>
+      </c>
+      <c r="R67" s="3">
+        <v>28.82352941176471</v>
+      </c>
+      <c r="S67" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="T67" s="3">
+        <v>-40.57</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
@@ -6249,61 +6261,61 @@
         <v>67</v>
       </c>
       <c r="B68" s="1">
-        <v>16.5</v>
+        <v>13.87</v>
       </c>
       <c r="C68" s="1">
-        <v>85.71428571428571</v>
+        <v>83.52941176470588</v>
       </c>
       <c r="D68" s="1">
-        <v>-0.16666666666666666</v>
+        <v>3.0958904109589045</v>
       </c>
       <c r="E68" s="1">
-        <v>-1.75</v>
+        <v>-2.41</v>
       </c>
       <c r="F68" s="1">
-        <v>0.12098116029422168</v>
+        <v>-0.2541149385652279</v>
       </c>
       <c r="G68" s="1">
+        <v>2.09</v>
+      </c>
+      <c r="H68" s="1">
+        <v>54.56</v>
+      </c>
+      <c r="I68" s="1">
+        <v>40.29</v>
+      </c>
+      <c r="J68" s="1">
+        <v>-0.005746473878596395</v>
+      </c>
+      <c r="K68" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="H68" s="1">
-        <v>41.55</v>
-      </c>
-      <c r="I68" s="1">
-        <v>-24.41</v>
-      </c>
-      <c r="J68" s="1">
-        <v>0.015903007530378665</v>
-      </c>
-      <c r="K68" s="1" t="b">
-        <v>0</v>
-      </c>
       <c r="L68" s="1">
-        <v>-253</v>
+        <v>515</v>
       </c>
       <c r="M68" s="1">
-        <v>0.12098116029422168</v>
+        <v>-0.2302288541709836</v>
       </c>
       <c r="N68" s="1">
-        <v>16.370603727050714</v>
+        <v>-19.75650152771815</v>
       </c>
       <c r="O68" s="1">
-        <v>72.61904761904762</v>
+        <v>16.470588235294116</v>
       </c>
       <c r="P68" s="1">
-        <v>37.5868621181625</v>
+        <v>31.85898471566022</v>
       </c>
       <c r="Q68" s="1">
-        <v>53.57142857142857</v>
+        <v>64</v>
       </c>
       <c r="R68" s="1">
-        <v>49.94047619047619</v>
+        <v>36.41176470588236</v>
       </c>
       <c r="S68" s="1" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="T68" s="1">
-        <v>32.2</v>
+        <v>-29.62</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
@@ -6311,1053 +6323,1115 @@
         <v>68</v>
       </c>
       <c r="B69" s="1">
-        <v>4.55</v>
+        <v>16.5</v>
       </c>
       <c r="C69" s="1">
-        <v>57.14285714285714</v>
+        <v>85.88235294117646</v>
       </c>
       <c r="D69" s="1">
-        <v>5.90989010989011</v>
+        <v>-0.18969696969696975</v>
       </c>
       <c r="E69" s="1">
-        <v>-0.51</v>
+        <v>-1.74</v>
       </c>
       <c r="F69" s="1">
-        <v>-0.05160245320421514</v>
+        <v>0.10287924141109017</v>
       </c>
       <c r="G69" s="1">
-        <v>1.26</v>
+        <v>1</v>
       </c>
       <c r="H69" s="1">
-        <v>40.26</v>
+        <v>38.46</v>
       </c>
       <c r="I69" s="1">
-        <v>-6.45</v>
+        <v>-26.03</v>
       </c>
       <c r="J69" s="1">
-        <v>-0.0026694513557431114</v>
+        <v>0.014305268913456093</v>
       </c>
       <c r="K69" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L69" s="1">
-        <v>3</v>
+        <v>-252</v>
       </c>
       <c r="M69" s="1">
-        <v>-0.043288985190380935</v>
+        <v>0.10287924141109017</v>
       </c>
       <c r="N69" s="1">
-        <v>-0.056410821409558276</v>
+        <v>13.554308030489231</v>
       </c>
       <c r="O69" s="1">
-        <v>48.80952380952381</v>
+        <v>69.41176470588235</v>
       </c>
       <c r="P69" s="1">
+        <v>37.32769516583675</v>
+      </c>
+      <c r="Q69" s="1">
+        <v>51.88235294117647</v>
+      </c>
+      <c r="R69" s="1">
+        <v>48.647058823529406</v>
+      </c>
+      <c r="S69" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="T69" s="1">
+        <v>30.9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B70" s="1">
+        <v>4.55</v>
+      </c>
+      <c r="C70" s="1">
+        <v>57.647058823529406</v>
+      </c>
+      <c r="D70" s="1">
+        <v>5.90989010989011</v>
+      </c>
+      <c r="E70" s="1">
+        <v>-0.54</v>
+      </c>
+      <c r="F70" s="1">
+        <v>-0.05427432644450578</v>
+      </c>
+      <c r="G70" s="1">
+        <v>1.26</v>
+      </c>
+      <c r="H70" s="1">
+        <v>41.86</v>
+      </c>
+      <c r="I70" s="1">
+        <v>-5.88</v>
+      </c>
+      <c r="J70" s="1">
+        <v>-0.0034438902035923793</v>
+      </c>
+      <c r="K70" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L70" s="1">
+        <v>4</v>
+      </c>
+      <c r="M70" s="1">
+        <v>-0.048576728332117236</v>
+      </c>
+      <c r="N70" s="1">
+        <v>-1.591288943831511</v>
+      </c>
+      <c r="O70" s="1">
+        <v>49.411764705882355</v>
+      </c>
+      <c r="P70" s="1">
         <v>16.710870321490763</v>
       </c>
-      <c r="Q69" s="1">
-        <v>50.23809523809524</v>
-      </c>
-      <c r="R69" s="1">
-        <v>46.30952380952381</v>
-      </c>
-      <c r="S69" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="T69" s="1">
-        <v>4.6</v>
-      </c>
-    </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A70" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B70" s="2">
+      <c r="Q70" s="1">
+        <v>50.11764705882353</v>
+      </c>
+      <c r="R70" s="1">
+        <v>46.470588235294116</v>
+      </c>
+      <c r="S70" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="T70" s="1">
+        <v>4.76</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2">
         <v>-2.66</v>
       </c>
-      <c r="C70" s="2">
-        <v>11.904761904761903</v>
-      </c>
-      <c r="D70" s="2">
+      <c r="C71" s="2">
+        <v>11.76470588235294</v>
+      </c>
+      <c r="D71" s="2">
         <v>886.3947368421052</v>
       </c>
-      <c r="E70" s="2">
+      <c r="E71" s="2">
         <v>0.14</v>
       </c>
-      <c r="F70" s="2">
-        <v>0.18148827115001517</v>
-      </c>
-      <c r="G70" s="2">
+      <c r="F71" s="2">
+        <v>0.194930505072704</v>
+      </c>
+      <c r="G71" s="2">
         <v>0.33</v>
       </c>
-      <c r="H70" s="2">
-        <v>63.49</v>
-      </c>
-      <c r="I70" s="2">
-        <v>11.64</v>
-      </c>
-      <c r="J70" s="2">
-        <v>0.011031310227524998</v>
-      </c>
-      <c r="K70" s="2" t="b">
+      <c r="H71" s="2">
+        <v>58.63</v>
+      </c>
+      <c r="I71" s="2">
+        <v>10.07</v>
+      </c>
+      <c r="J71" s="2">
+        <v>0.010643766218434549</v>
+      </c>
+      <c r="K71" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L71" s="2">
+        <v>-80</v>
+      </c>
+      <c r="M71" s="2">
+        <v>0.18024823301385662</v>
+      </c>
+      <c r="N71" s="2">
+        <v>21.291207190765867</v>
+      </c>
+      <c r="O71" s="2">
+        <v>78.82352941176471</v>
+      </c>
+      <c r="P71" s="2">
+        <v>10.873073633899006</v>
+      </c>
+      <c r="Q71" s="2">
+        <v>61.529411764705884</v>
+      </c>
+      <c r="R71" s="2">
+        <v>57.76470588235295</v>
+      </c>
+      <c r="S71" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="T71" s="2">
+        <v>9.72</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B72" s="1">
+        <v>8.73</v>
+      </c>
+      <c r="C72" s="1">
+        <v>76.47058823529412</v>
+      </c>
+      <c r="D72" s="1">
+        <v>0.3596792668957616</v>
+      </c>
+      <c r="E72" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="F72" s="1">
+        <v>-0.07602792906157597</v>
+      </c>
+      <c r="G72" s="1">
+        <v>1.47</v>
+      </c>
+      <c r="H72" s="1">
+        <v>60.91</v>
+      </c>
+      <c r="I72" s="1">
+        <v>-13.48</v>
+      </c>
+      <c r="J72" s="1">
+        <v>-0.010519264250470662</v>
+      </c>
+      <c r="K72" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L72" s="1">
+        <v>-41</v>
+      </c>
+      <c r="M72" s="1">
+        <v>-0.06572842478148899</v>
+      </c>
+      <c r="N72" s="1">
+        <v>-3.306458588768694</v>
+      </c>
+      <c r="O72" s="1">
+        <v>48.23529411764706</v>
+      </c>
+      <c r="P72" s="1">
+        <v>31.147611427732443</v>
+      </c>
+      <c r="Q72" s="1">
+        <v>50.23529411764706</v>
+      </c>
+      <c r="R72" s="1">
+        <v>39.35294117647059</v>
+      </c>
+      <c r="S72" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="T72" s="1">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2">
+        <v>18.59</v>
+      </c>
+      <c r="C73" s="2">
+        <v>90.58823529411765</v>
+      </c>
+      <c r="D73" s="2">
+        <v>-0.5045723507261969</v>
+      </c>
+      <c r="E73" s="2">
+        <v>-0.34</v>
+      </c>
+      <c r="F73" s="2">
+        <v>0.37210962570846884</v>
+      </c>
+      <c r="G73" s="2">
+        <v>0.88</v>
+      </c>
+      <c r="H73" s="2">
+        <v>69.21</v>
+      </c>
+      <c r="I73" s="2">
+        <v>22.05</v>
+      </c>
+      <c r="J73" s="2">
+        <v>0.021459848374739025</v>
+      </c>
+      <c r="K73" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L73" s="2">
+        <v>49</v>
+      </c>
+      <c r="M73" s="2">
+        <v>0.3694799650412126</v>
+      </c>
+      <c r="N73" s="2">
+        <v>40.21438039350146</v>
+      </c>
+      <c r="O73" s="2">
+        <v>91.76470588235294</v>
+      </c>
+      <c r="P73" s="2">
+        <v>8.480874361506512</v>
+      </c>
+      <c r="Q73" s="2">
+        <v>67.52941176470588</v>
+      </c>
+      <c r="R73" s="2">
+        <v>62.88235294117648</v>
+      </c>
+      <c r="S73" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="T73" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B74" s="1">
+        <v>2.1</v>
+      </c>
+      <c r="C74" s="1">
+        <v>44.70588235294118</v>
+      </c>
+      <c r="D74" s="1">
+        <v>11.28095238095238</v>
+      </c>
+      <c r="E74" s="1">
+        <v>0.44</v>
+      </c>
+      <c r="F74" s="1">
+        <v>-0.2492358041514754</v>
+      </c>
+      <c r="G74" s="1">
+        <v>1.1</v>
+      </c>
+      <c r="H74" s="1">
+        <v>33.01</v>
+      </c>
+      <c r="I74" s="1">
+        <v>-28.89</v>
+      </c>
+      <c r="J74" s="1">
+        <v>-0.017197560372573417</v>
+      </c>
+      <c r="K74" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L74" s="1">
+        <v>-167</v>
+      </c>
+      <c r="M74" s="1">
+        <v>-0.24704442026209517</v>
+      </c>
+      <c r="N74" s="1">
+        <v>-21.43805813682931</v>
+      </c>
+      <c r="O74" s="1">
+        <v>15.294117647058824</v>
+      </c>
+      <c r="P74" s="1">
+        <v>25.03694506602277</v>
+      </c>
+      <c r="Q74" s="1">
+        <v>40.70588235294117</v>
+      </c>
+      <c r="R74" s="1">
+        <v>30.823529411764714</v>
+      </c>
+      <c r="S74" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="T74" s="1">
+        <v>-1.19</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B75" s="1">
+        <v>0.42</v>
+      </c>
+      <c r="C75" s="1">
+        <v>35.294117647058826</v>
+      </c>
+      <c r="D75" s="1">
+        <v>97.42857142857143</v>
+      </c>
+      <c r="E75" s="1">
+        <v>-3.72</v>
+      </c>
+      <c r="F75" s="1">
+        <v>-0.25756672965758654</v>
+      </c>
+      <c r="G75" s="1">
+        <v>1.25</v>
+      </c>
+      <c r="H75" s="1">
+        <v>37.24</v>
+      </c>
+      <c r="I75" s="1">
+        <v>-6.77</v>
+      </c>
+      <c r="J75" s="1">
+        <v>-0.019738950752422973</v>
+      </c>
+      <c r="K75" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L70" s="2">
-        <v>-81</v>
-      </c>
-      <c r="M70" s="2">
-        <v>0.16006510357590398</v>
-      </c>
-      <c r="N70" s="2">
-        <v>20.27899805521894</v>
-      </c>
-      <c r="O70" s="2">
-        <v>78.57142857142857</v>
-      </c>
-      <c r="P70" s="2">
-        <v>10.873073633899006</v>
-      </c>
-      <c r="Q70" s="2">
-        <v>63.80952380952381</v>
-      </c>
-      <c r="R70" s="2">
-        <v>57.916666666666664</v>
-      </c>
-      <c r="S70" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="T70" s="2">
-        <v>9.87</v>
-      </c>
-    </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B71" s="1">
-        <v>8.73</v>
-      </c>
-      <c r="C71" s="1">
-        <v>76.19047619047619</v>
-      </c>
-      <c r="D71" s="1">
-        <v>0.3596792668957616</v>
-      </c>
-      <c r="E71" s="1">
-        <v>0.12</v>
-      </c>
-      <c r="F71" s="1">
-        <v>-0.10410043717522413</v>
-      </c>
-      <c r="G71" s="1">
-        <v>1.47</v>
-      </c>
-      <c r="H71" s="1">
-        <v>56.09</v>
-      </c>
-      <c r="I71" s="1">
-        <v>-15.89</v>
-      </c>
-      <c r="J71" s="1">
-        <v>-0.011294694481653683</v>
-      </c>
-      <c r="K71" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L71" s="1">
-        <v>-42</v>
-      </c>
-      <c r="M71" s="1">
-        <v>-0.08907224499637001</v>
-      </c>
-      <c r="N71" s="1">
-        <v>-4.6347368020084625</v>
-      </c>
-      <c r="O71" s="1">
-        <v>40.476190476190474</v>
-      </c>
-      <c r="P71" s="1">
-        <v>31.34692685044607</v>
-      </c>
-      <c r="Q71" s="1">
-        <v>48.92857142857143</v>
-      </c>
-      <c r="R71" s="1">
-        <v>36.72619047619048</v>
-      </c>
-      <c r="S71" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="T71" s="1">
-        <v>7.27</v>
-      </c>
-    </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A72" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B72" s="2">
-        <v>18.59</v>
-      </c>
-      <c r="C72" s="2">
-        <v>90.47619047619048</v>
-      </c>
-      <c r="D72" s="2">
-        <v>-0.5072619688004303</v>
-      </c>
-      <c r="E72" s="2">
-        <v>-0.35</v>
-      </c>
-      <c r="F72" s="2">
-        <v>0.38700394876648403</v>
-      </c>
-      <c r="G72" s="2">
-        <v>0.88</v>
-      </c>
-      <c r="H72" s="2">
-        <v>71.95</v>
-      </c>
-      <c r="I72" s="2">
-        <v>22.46</v>
-      </c>
-      <c r="J72" s="2">
-        <v>0.020482341301313448</v>
-      </c>
-      <c r="K72" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L72" s="2">
-        <v>48</v>
-      </c>
-      <c r="M72" s="2">
-        <v>0.3831669635293298</v>
-      </c>
-      <c r="N72" s="2">
-        <v>42.58918405056152</v>
-      </c>
-      <c r="O72" s="2">
-        <v>90.47619047619048</v>
-      </c>
-      <c r="P72" s="2">
-        <v>16.43822745912965</v>
-      </c>
-      <c r="Q72" s="2">
-        <v>67.73809523809524</v>
-      </c>
-      <c r="R72" s="2">
-        <v>60.952380952380956</v>
-      </c>
-      <c r="S72" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="T72" s="2">
-        <v>21.07</v>
-      </c>
-    </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B73" s="1">
-        <v>2.1</v>
-      </c>
-      <c r="C73" s="1">
-        <v>44.047619047619044</v>
-      </c>
-      <c r="D73" s="1">
-        <v>11.242857142857142</v>
-      </c>
-      <c r="E73" s="1">
-        <v>0.45</v>
-      </c>
-      <c r="F73" s="1">
-        <v>-0.22311173466010972</v>
-      </c>
-      <c r="G73" s="1">
-        <v>1.1</v>
-      </c>
-      <c r="H73" s="1">
-        <v>35.69</v>
-      </c>
-      <c r="I73" s="1">
-        <v>-27.82</v>
-      </c>
-      <c r="J73" s="1">
-        <v>-0.01665608966991251</v>
-      </c>
-      <c r="K73" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L73" s="1">
-        <v>-168</v>
-      </c>
-      <c r="M73" s="1">
-        <v>-0.21991424696248119</v>
-      </c>
-      <c r="N73" s="1">
-        <v>-17.71893699861958</v>
-      </c>
-      <c r="O73" s="1">
-        <v>16.666666666666664</v>
-      </c>
-      <c r="P73" s="1">
-        <v>24.466963086179547</v>
-      </c>
-      <c r="Q73" s="1">
-        <v>40.95238095238095</v>
-      </c>
-      <c r="R73" s="1">
-        <v>31.011904761904763</v>
-      </c>
-      <c r="S73" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="T73" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A74" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B74" s="3">
-        <v>0.42</v>
-      </c>
-      <c r="C74" s="3">
-        <v>34.523809523809526</v>
-      </c>
-      <c r="D74" s="3">
-        <v>97.42857142857143</v>
-      </c>
-      <c r="E74" s="3">
-        <v>-3.73</v>
-      </c>
-      <c r="F74" s="3">
-        <v>-0.28198268431201057</v>
-      </c>
-      <c r="G74" s="3">
-        <v>1.25</v>
-      </c>
-      <c r="H74" s="3">
-        <v>37.31</v>
-      </c>
-      <c r="I74" s="3">
-        <v>-6.51</v>
-      </c>
-      <c r="J74" s="3">
-        <v>-0.020148539678220282</v>
-      </c>
-      <c r="K74" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L74" s="3">
+      <c r="L75" s="1">
         <v>32</v>
       </c>
-      <c r="M74" s="3">
-        <v>-0.27398896506793924</v>
-      </c>
-      <c r="N74" s="3">
-        <v>-23.126408809165383</v>
-      </c>
-      <c r="O74" s="3">
-        <v>11.904761904761903</v>
-      </c>
-      <c r="P74" s="3">
+      <c r="M75" s="1">
+        <v>-0.252088269934136</v>
+      </c>
+      <c r="N75" s="1">
+        <v>-21.942443104033394</v>
+      </c>
+      <c r="O75" s="1">
+        <v>14.117647058823529</v>
+      </c>
+      <c r="P75" s="1">
         <v>28.76752600761915</v>
       </c>
-      <c r="Q74" s="3">
-        <v>43.92857142857142</v>
-      </c>
-      <c r="R74" s="3">
-        <v>29.46428571428571</v>
-      </c>
-      <c r="S74" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="T74" s="3">
-        <v>-29.13</v>
-      </c>
-    </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A75" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B75" s="3">
-        <v>-0.22</v>
-      </c>
-      <c r="C75" s="3">
-        <v>26.190476190476193</v>
-      </c>
-      <c r="D75" s="3">
-        <v>162.09090909090907</v>
-      </c>
-      <c r="E75" s="3">
-        <v>-0.07</v>
-      </c>
-      <c r="F75" s="3">
-        <v>-0.3827096309968233</v>
-      </c>
-      <c r="G75" s="3">
-        <v>3.25</v>
-      </c>
-      <c r="H75" s="3">
-        <v>42.99</v>
-      </c>
-      <c r="I75" s="3">
-        <v>-31.88</v>
-      </c>
-      <c r="J75" s="3">
-        <v>-0.021794288971493467</v>
-      </c>
-      <c r="K75" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L75" s="3">
-        <v>10</v>
-      </c>
-      <c r="M75" s="3">
-        <v>-0.31076615780018124</v>
-      </c>
-      <c r="N75" s="3">
-        <v>-26.804128082389596</v>
-      </c>
-      <c r="O75" s="3">
-        <v>4.761904761904762</v>
-      </c>
-      <c r="P75" s="3">
-        <v>51.49813033405746</v>
-      </c>
-      <c r="Q75" s="3">
-        <v>41.666666666666664</v>
-      </c>
-      <c r="R75" s="3">
-        <v>22.916666666666664</v>
-      </c>
-      <c r="S75" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="T75" s="3">
-        <v>-2.82</v>
+      <c r="Q75" s="1">
+        <v>44.11764705882353</v>
+      </c>
+      <c r="R75" s="1">
+        <v>30.411764705882355</v>
+      </c>
+      <c r="S75" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="T75" s="1">
+        <v>-28.19</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>122</v>
+        <v>75</v>
       </c>
       <c r="B76" s="3">
-        <v>3.5</v>
+        <v>-0.22</v>
       </c>
       <c r="C76" s="3">
-        <v>52.38095238095239</v>
+        <v>25.882352941176475</v>
       </c>
       <c r="D76" s="3">
-        <v>-22.482857142857142</v>
+        <v>162.09090909090907</v>
       </c>
       <c r="E76" s="3">
-        <v>12.84</v>
+        <v>-0.07</v>
       </c>
       <c r="F76" s="3">
-        <v>-0.0611885072682134</v>
+        <v>-0.3679034265742512</v>
       </c>
       <c r="G76" s="3">
-        <v>0.89</v>
+        <v>3.26</v>
       </c>
       <c r="H76" s="3">
-        <v>32.97</v>
+        <v>44.25</v>
       </c>
       <c r="I76" s="3">
-        <v>38.22</v>
+        <v>-31.13</v>
       </c>
       <c r="J76" s="3">
-        <v>-0.028462291768440205</v>
+        <v>-0.020269386182837294</v>
       </c>
       <c r="K76" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L76" s="3">
+        <v>10</v>
+      </c>
+      <c r="M76" s="3">
+        <v>-0.31837815067425845</v>
+      </c>
+      <c r="N76" s="3">
+        <v>-28.571431178045636</v>
+      </c>
+      <c r="O76" s="3">
+        <v>9.411764705882353</v>
+      </c>
+      <c r="P76" s="3">
+        <v>51.49813033405746</v>
+      </c>
+      <c r="Q76" s="3">
+        <v>41.529411764705884</v>
+      </c>
+      <c r="R76" s="3">
+        <v>24.235294117647058</v>
+      </c>
+      <c r="S76" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="T76" s="3">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B77" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="C77" s="3">
+        <v>52.94117647058824</v>
+      </c>
+      <c r="D77" s="3">
+        <v>-22.482857142857142</v>
+      </c>
+      <c r="E77" s="3">
+        <v>12.83</v>
+      </c>
+      <c r="F77" s="3">
+        <v>0.0027535145231743496</v>
+      </c>
+      <c r="G77" s="3">
+        <v>0.89</v>
+      </c>
+      <c r="H77" s="3">
+        <v>32.42</v>
+      </c>
+      <c r="I77" s="3">
+        <v>36.75</v>
+      </c>
+      <c r="J77" s="3">
+        <v>-0.029428435250407167</v>
+      </c>
+      <c r="K77" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L77" s="3">
         <v>42</v>
       </c>
-      <c r="M76" s="3">
-        <v>-0.06470574373560478</v>
-      </c>
-      <c r="N76" s="3">
-        <v>-2.1980866759319406</v>
-      </c>
-      <c r="O76" s="3">
-        <v>44.047619047619044</v>
-      </c>
-      <c r="P76" s="3">
+      <c r="M77" s="3">
+        <v>0.0003429922448561218</v>
+      </c>
+      <c r="N77" s="3">
+        <v>3.3006831138658232</v>
+      </c>
+      <c r="O77" s="3">
+        <v>55.294117647058826</v>
+      </c>
+      <c r="P77" s="3">
         <v>29.799918858582526</v>
       </c>
-      <c r="Q76" s="3">
-        <v>27.142857142857146</v>
-      </c>
-      <c r="R76" s="3">
-        <v>21.30952380952381</v>
-      </c>
-      <c r="S76" s="3" t="s">
+      <c r="Q77" s="3">
+        <v>26.82352941176471</v>
+      </c>
+      <c r="R77" s="3">
+        <v>24.764705882352942</v>
+      </c>
+      <c r="S77" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="T76" s="3">
-        <v>-52.41</v>
-      </c>
-    </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A77" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B77" s="2">
-        <v>2.14</v>
-      </c>
-      <c r="C77" s="2">
-        <v>45.23809523809524</v>
-      </c>
-      <c r="D77" s="2">
-        <v>2.5327102803738315</v>
-      </c>
-      <c r="E77" s="2">
-        <v>-9.21</v>
-      </c>
-      <c r="F77" s="2">
-        <v>0.6232657291118143</v>
-      </c>
-      <c r="G77" s="2">
-        <v>0.91</v>
-      </c>
-      <c r="H77" s="2">
-        <v>68.71</v>
-      </c>
-      <c r="I77" s="2">
-        <v>37.33</v>
-      </c>
-      <c r="J77" s="2">
-        <v>0.038466396827951506</v>
-      </c>
-      <c r="K77" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L77" s="2">
-        <v>-5</v>
-      </c>
-      <c r="M77" s="2">
-        <v>0.6203879901839486</v>
-      </c>
-      <c r="N77" s="2">
-        <v>66.3112867160234</v>
-      </c>
-      <c r="O77" s="2">
-        <v>97.61904761904762</v>
-      </c>
-      <c r="P77" s="2">
-        <v>18.71809072120826</v>
-      </c>
-      <c r="Q77" s="2">
-        <v>66.42857142857143</v>
-      </c>
-      <c r="R77" s="2">
-        <v>60.17857142857143</v>
-      </c>
-      <c r="S77" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="T77" s="2">
-        <v>11.58</v>
+      <c r="T77" s="3">
+        <v>-48.95</v>
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B78" s="2">
-        <v>-0.92</v>
+        <v>2.14</v>
       </c>
       <c r="C78" s="2">
-        <v>20.238095238095237</v>
+        <v>45.88235294117647</v>
       </c>
       <c r="D78" s="2">
-        <v>15.521739130434781</v>
+        <v>2.5327102803738315</v>
       </c>
       <c r="E78" s="2">
-        <v>-3.54</v>
+        <v>-9.21</v>
       </c>
       <c r="F78" s="2">
-        <v>0.28791856966256796</v>
+        <v>0.725900059276373</v>
       </c>
       <c r="G78" s="2">
-        <v>1.11</v>
+        <v>0.91</v>
       </c>
       <c r="H78" s="2">
-        <v>67.88</v>
+        <v>69.04</v>
       </c>
       <c r="I78" s="2">
-        <v>34.12</v>
+        <v>37.3</v>
       </c>
       <c r="J78" s="2">
-        <v>0.010085901055516088</v>
+        <v>0.03715276494318379</v>
       </c>
       <c r="K78" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L78" s="2">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="M78" s="2">
-        <v>0.29143580612995934</v>
+        <v>0.7239278137759309</v>
       </c>
       <c r="N78" s="2">
-        <v>33.41606831062446</v>
+        <v>75.6591652669733</v>
       </c>
       <c r="O78" s="2">
-        <v>86.90476190476191</v>
+        <v>98.82352941176471</v>
       </c>
       <c r="P78" s="2">
-        <v>16.006637557486414</v>
+        <v>18.71809072120826</v>
       </c>
       <c r="Q78" s="2">
-        <v>60.71428571428571</v>
+        <v>66.82352941176471</v>
       </c>
       <c r="R78" s="2">
-        <v>55.23809523809524</v>
+        <v>60.76470588235294</v>
       </c>
       <c r="S78" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="T78" s="2">
-        <v>7.07</v>
+        <v>12.17</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B79" s="2">
-        <v>5.7</v>
+        <v>-0.92</v>
       </c>
       <c r="C79" s="2">
-        <v>63.095238095238095</v>
+        <v>20</v>
       </c>
       <c r="D79" s="2">
-        <v>0.15087719298245603</v>
+        <v>15.521739130434781</v>
       </c>
       <c r="E79" s="2">
-        <v>0.32</v>
+        <v>-3.59</v>
       </c>
       <c r="F79" s="2">
-        <v>0.22072735281538344</v>
+        <v>0.21389377272069082</v>
       </c>
       <c r="G79" s="2">
-        <v>0.82</v>
+        <v>1.11</v>
       </c>
       <c r="H79" s="2">
-        <v>52.71</v>
+        <v>57.32</v>
       </c>
       <c r="I79" s="2">
-        <v>11.64</v>
+        <v>30.04</v>
       </c>
       <c r="J79" s="2">
-        <v>0.0106762542842756</v>
+        <v>0.010210533127861597</v>
       </c>
       <c r="K79" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="2">
-        <v>6</v>
+        <v>-2</v>
       </c>
       <c r="M79" s="2">
-        <v>0.2149718749596521</v>
+        <v>0.21630429499900905</v>
       </c>
       <c r="N79" s="2">
-        <v>25.76967519359375</v>
+        <v>24.89681338928112</v>
       </c>
       <c r="O79" s="2">
-        <v>80.95238095238095</v>
+        <v>84.70588235294117</v>
       </c>
       <c r="P79" s="2">
-        <v>11.616065285425229</v>
+        <v>16.006637557486414</v>
       </c>
       <c r="Q79" s="2">
-        <v>55.714285714285715</v>
+        <v>58.352941176470594</v>
       </c>
       <c r="R79" s="2">
-        <v>54.28571428571429</v>
+        <v>54.64705882352941</v>
       </c>
       <c r="S79" s="2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="T79" s="2">
-        <v>14.41</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B80" s="2">
+        <v>5.7</v>
+      </c>
+      <c r="C80" s="2">
+        <v>63.52941176470588</v>
+      </c>
+      <c r="D80" s="2">
+        <v>0.15087719298245603</v>
+      </c>
+      <c r="E80" s="2">
+        <v>0.34</v>
+      </c>
+      <c r="F80" s="2">
+        <v>0.213666256736375</v>
+      </c>
+      <c r="G80" s="2">
+        <v>0.82</v>
+      </c>
+      <c r="H80" s="2">
+        <v>49.48</v>
+      </c>
+      <c r="I80" s="2">
+        <v>10.72</v>
+      </c>
+      <c r="J80" s="2">
+        <v>0.009350410735690403</v>
+      </c>
+      <c r="K80" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L80" s="2">
+        <v>6</v>
+      </c>
+      <c r="M80" s="2">
+        <v>0.20972176573549062</v>
+      </c>
+      <c r="N80" s="2">
+        <v>24.238560462929264</v>
+      </c>
+      <c r="O80" s="2">
+        <v>82.35294117647058</v>
+      </c>
+      <c r="P80" s="2">
+        <v>11.616065285425229</v>
+      </c>
+      <c r="Q80" s="2">
+        <v>54.35294117647059</v>
+      </c>
+      <c r="R80" s="2">
+        <v>54.705882352941174</v>
+      </c>
+      <c r="S80" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="T80" s="2">
+        <v>14.83</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B80" s="2">
+      <c r="B81" s="2">
         <v>11.65</v>
       </c>
-      <c r="C80" s="2">
-        <v>78.57142857142857</v>
-      </c>
-      <c r="D80" s="2">
+      <c r="C81" s="2">
+        <v>78.82352941176471</v>
+      </c>
+      <c r="D81" s="2">
         <v>0.17339055793991412</v>
       </c>
-      <c r="E80" s="2">
-        <v>0.86</v>
-      </c>
-      <c r="F80" s="2">
-        <v>0.0843399422476147</v>
-      </c>
-      <c r="G80" s="2">
+      <c r="E81" s="2">
+        <v>0.87</v>
+      </c>
+      <c r="F81" s="2">
+        <v>0.0978195036153274</v>
+      </c>
+      <c r="G81" s="2">
         <v>0.77</v>
       </c>
-      <c r="H80" s="2">
-        <v>49.05</v>
-      </c>
-      <c r="I80" s="2">
-        <v>10.18</v>
-      </c>
-      <c r="J80" s="2">
-        <v>0.0050444272596201515</v>
-      </c>
-      <c r="K80" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L80" s="2">
-        <v>156</v>
-      </c>
-      <c r="M80" s="2">
-        <v>0.07698572054306907</v>
-      </c>
-      <c r="N80" s="2">
-        <v>11.971059751935451</v>
-      </c>
-      <c r="O80" s="2">
-        <v>65.47619047619048</v>
-      </c>
-      <c r="P80" s="2">
+      <c r="H81" s="2">
+        <v>48.36</v>
+      </c>
+      <c r="I81" s="2">
+        <v>9.84</v>
+      </c>
+      <c r="J81" s="2">
+        <v>0.005078502637170659</v>
+      </c>
+      <c r="K81" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L81" s="2">
+        <v>157</v>
+      </c>
+      <c r="M81" s="2">
+        <v>0.09277932066975292</v>
+      </c>
+      <c r="N81" s="2">
+        <v>12.544315956355497</v>
+      </c>
+      <c r="O81" s="2">
+        <v>67.05882352941175</v>
+      </c>
+      <c r="P81" s="2">
         <v>6.707278396222185</v>
       </c>
-      <c r="Q80" s="2">
-        <v>57.38095238095238</v>
-      </c>
-      <c r="R80" s="2">
-        <v>53.57142857142857</v>
-      </c>
-      <c r="S80" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="T80" s="2">
-        <v>3.14</v>
-      </c>
-    </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B81" s="1">
-        <v>23.34</v>
-      </c>
-      <c r="C81" s="1">
-        <v>95.23809523809523</v>
-      </c>
-      <c r="D81" s="1">
-        <v>-0.9305912596401028</v>
-      </c>
-      <c r="E81" s="1">
-        <v>-1.2</v>
-      </c>
-      <c r="F81" s="1">
-        <v>0.0044873316391628865</v>
-      </c>
-      <c r="G81" s="1">
-        <v>1.01</v>
-      </c>
-      <c r="H81" s="1">
-        <v>43.87</v>
-      </c>
-      <c r="I81" s="1">
-        <v>9.05</v>
-      </c>
-      <c r="J81" s="1">
-        <v>0.004610365580476141</v>
-      </c>
-      <c r="K81" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L81" s="1">
-        <v>109</v>
-      </c>
-      <c r="M81" s="1">
-        <v>0.004807080408925746</v>
-      </c>
-      <c r="N81" s="1">
-        <v>4.753195738521108</v>
-      </c>
-      <c r="O81" s="1">
-        <v>55.952380952380956</v>
-      </c>
-      <c r="P81" s="1">
-        <v>6.0971680093981355</v>
-      </c>
-      <c r="Q81" s="1">
-        <v>54.76190476190476</v>
-      </c>
-      <c r="R81" s="1">
-        <v>49.82142857142857</v>
-      </c>
-      <c r="S81" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="T81" s="1">
-        <v>4.52</v>
+      <c r="Q81" s="2">
+        <v>56.35294117647059</v>
+      </c>
+      <c r="R81" s="2">
+        <v>54.11764705882352</v>
+      </c>
+      <c r="S81" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="T81" s="2">
+        <v>3.69</v>
       </c>
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B82" s="2">
+        <v>23.34</v>
+      </c>
+      <c r="C82" s="2">
+        <v>95.29411764705881</v>
+      </c>
+      <c r="D82" s="2">
+        <v>-0.9305912596401028</v>
+      </c>
+      <c r="E82" s="2">
+        <v>-1.14</v>
+      </c>
+      <c r="F82" s="2">
+        <v>0.04229693820603323</v>
+      </c>
+      <c r="G82" s="2">
+        <v>1.01</v>
+      </c>
+      <c r="H82" s="2">
+        <v>46.64</v>
+      </c>
+      <c r="I82" s="2">
+        <v>9.45</v>
+      </c>
+      <c r="J82" s="2">
+        <v>0.004151948041054371</v>
+      </c>
+      <c r="K82" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L82" s="2">
+        <v>110</v>
+      </c>
+      <c r="M82" s="2">
+        <v>0.04251607659497125</v>
+      </c>
+      <c r="N82" s="2">
+        <v>7.517991548877342</v>
+      </c>
+      <c r="O82" s="2">
+        <v>62.35294117647059</v>
+      </c>
+      <c r="P82" s="2">
+        <v>6.0971680093981355</v>
+      </c>
+      <c r="Q82" s="2">
+        <v>53.88235294117647</v>
+      </c>
+      <c r="R82" s="2">
+        <v>51.52941176470588</v>
+      </c>
+      <c r="S82" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="T82" s="2">
+        <v>6.22</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B82" s="2">
+      <c r="B83" s="2">
         <v>8.72</v>
       </c>
-      <c r="C82" s="2">
-        <v>75</v>
-      </c>
-      <c r="D82" s="2">
-        <v>-0.006880733944954185</v>
-      </c>
-      <c r="E82" s="2">
+      <c r="C83" s="2">
+        <v>75.29411764705883</v>
+      </c>
+      <c r="D83" s="2">
+        <v>0.0045871559633026545</v>
+      </c>
+      <c r="E83" s="2">
         <v>0.23</v>
       </c>
-      <c r="F82" s="2">
-        <v>0.09374269714401647</v>
-      </c>
-      <c r="G82" s="2">
+      <c r="F83" s="2">
+        <v>0.09371734243905319</v>
+      </c>
+      <c r="G83" s="2">
         <v>1.07</v>
       </c>
-      <c r="H82" s="2">
-        <v>65.39</v>
-      </c>
-      <c r="I82" s="2">
-        <v>17.8</v>
-      </c>
-      <c r="J82" s="2">
-        <v>0.007968058636898694</v>
-      </c>
-      <c r="K82" s="2" t="b">
+      <c r="H83" s="2">
+        <v>62.99</v>
+      </c>
+      <c r="I83" s="2">
+        <v>16.96</v>
+      </c>
+      <c r="J83" s="2">
+        <v>0.006818160934891378</v>
+      </c>
+      <c r="K83" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L82" s="2">
-        <v>88</v>
-      </c>
-      <c r="M82" s="2">
-        <v>0.09598093853235645</v>
-      </c>
-      <c r="N82" s="2">
-        <v>13.870581550864175</v>
-      </c>
-      <c r="O82" s="2">
-        <v>69.04761904761905</v>
-      </c>
-      <c r="P82" s="2">
+      <c r="L83" s="2">
+        <v>89</v>
+      </c>
+      <c r="M83" s="2">
+        <v>0.09525131116161933</v>
+      </c>
+      <c r="N83" s="2">
+        <v>12.791515005542134</v>
+      </c>
+      <c r="O83" s="2">
+        <v>68.23529411764706</v>
+      </c>
+      <c r="P83" s="2">
         <v>12.706223591210087</v>
       </c>
-      <c r="Q82" s="2">
-        <v>60.714285714285715</v>
-      </c>
-      <c r="R82" s="2">
-        <v>51.845238095238095</v>
-      </c>
-      <c r="S82" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="T82" s="2">
-        <v>-0.29</v>
-      </c>
-    </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B83" s="1">
-        <v>19.91</v>
-      </c>
-      <c r="C83" s="1">
-        <v>92.85714285714286</v>
-      </c>
-      <c r="D83" s="1">
-        <v>-2.336514314414867</v>
-      </c>
-      <c r="E83" s="1">
-        <v>2.31</v>
-      </c>
-      <c r="F83" s="1">
-        <v>-0.09998981403199197</v>
-      </c>
-      <c r="G83" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="H83" s="1">
-        <v>52.91</v>
-      </c>
-      <c r="I83" s="1">
-        <v>2.28</v>
-      </c>
-      <c r="J83" s="1">
-        <v>-0.00553602339977182</v>
-      </c>
-      <c r="K83" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L83" s="1">
-        <v>174</v>
-      </c>
-      <c r="M83" s="1">
-        <v>-0.0935948386367349</v>
-      </c>
-      <c r="N83" s="1">
-        <v>-5.086996166044951</v>
-      </c>
-      <c r="O83" s="1">
-        <v>39.285714285714285</v>
-      </c>
-      <c r="P83" s="1">
-        <v>20.22353911360907</v>
-      </c>
-      <c r="Q83" s="1">
-        <v>48.214285714285715</v>
-      </c>
-      <c r="R83" s="1">
-        <v>36.8452380952381</v>
-      </c>
-      <c r="S83" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="T83" s="1">
-        <v>-9.92</v>
+      <c r="Q83" s="2">
+        <v>60.47058823529413</v>
+      </c>
+      <c r="R83" s="2">
+        <v>51.70588235294118</v>
+      </c>
+      <c r="S83" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="T83" s="2">
+        <v>-0.43</v>
       </c>
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B84" s="1">
-        <v>3.33</v>
+        <v>19.91</v>
       </c>
       <c r="C84" s="1">
-        <v>51.19047619047619</v>
+        <v>92.94117647058823</v>
       </c>
       <c r="D84" s="1">
-        <v>1.765765765765766</v>
+        <v>-2.336514314414867</v>
       </c>
       <c r="E84" s="1">
-        <v>0.25</v>
+        <v>2.31</v>
       </c>
       <c r="F84" s="1">
-        <v>-0.10251326537077814</v>
+        <v>-0.09977449087485286</v>
       </c>
       <c r="G84" s="1">
-        <v>0.98</v>
+        <v>1.2</v>
       </c>
       <c r="H84" s="1">
-        <v>47.72</v>
+        <v>56.92</v>
       </c>
       <c r="I84" s="1">
-        <v>14.75</v>
+        <v>3.66</v>
       </c>
       <c r="J84" s="1">
-        <v>-0.0033472350322131072</v>
+        <v>-0.004928465830562718</v>
       </c>
       <c r="K84" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="1">
-        <v>374</v>
+        <v>174</v>
       </c>
       <c r="M84" s="1">
-        <v>-0.10315276291030384</v>
+        <v>-0.09539172309609245</v>
       </c>
       <c r="N84" s="1">
-        <v>-6.042788593401852</v>
+        <v>-6.272788420229038</v>
       </c>
       <c r="O84" s="1">
-        <v>34.523809523809526</v>
+        <v>40</v>
       </c>
       <c r="P84" s="1">
-        <v>17.353844275841347</v>
+        <v>20.22353911360907</v>
       </c>
       <c r="Q84" s="1">
-        <v>50.238095238095234</v>
+        <v>48.70588235294117</v>
       </c>
       <c r="R84" s="1">
-        <v>36.964285714285715</v>
+        <v>36.8235294117647</v>
       </c>
       <c r="S84" s="1" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="T84" s="1">
-        <v>-19.68</v>
+        <v>-9.94</v>
       </c>
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B85" s="1">
+        <v>3.33</v>
+      </c>
+      <c r="C85" s="1">
+        <v>51.76470588235295</v>
+      </c>
+      <c r="D85" s="1">
+        <v>1.765765765765766</v>
+      </c>
+      <c r="E85" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="F85" s="1">
+        <v>-0.11613052030966527</v>
+      </c>
+      <c r="G85" s="1">
+        <v>0.98</v>
+      </c>
+      <c r="H85" s="1">
+        <v>46.97</v>
+      </c>
+      <c r="I85" s="1">
+        <v>13.94</v>
+      </c>
+      <c r="J85" s="1">
+        <v>-0.004039471243333974</v>
+      </c>
+      <c r="K85" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L85" s="1">
+        <v>375</v>
+      </c>
+      <c r="M85" s="1">
+        <v>-0.11656879708754131</v>
+      </c>
+      <c r="N85" s="1">
+        <v>-8.390495819373927</v>
+      </c>
+      <c r="O85" s="1">
+        <v>36.470588235294116</v>
+      </c>
+      <c r="P85" s="1">
+        <v>17.353844275841347</v>
+      </c>
+      <c r="Q85" s="1">
+        <v>49.41176470588235</v>
+      </c>
+      <c r="R85" s="1">
+        <v>37.82352941176471</v>
+      </c>
+      <c r="S85" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="T85" s="1">
+        <v>-18.82</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B85" s="1">
+      <c r="B86" s="1">
         <v>12.35</v>
       </c>
-      <c r="C85" s="1">
-        <v>80.95238095238095</v>
-      </c>
-      <c r="D85" s="1">
-        <v>-0.32145748987854245</v>
-      </c>
-      <c r="E85" s="1">
-        <v>0.61</v>
-      </c>
-      <c r="F85" s="1">
-        <v>0.05354553650639611</v>
-      </c>
-      <c r="G85" s="1">
+      <c r="C86" s="1">
+        <v>81.17647058823529</v>
+      </c>
+      <c r="D86" s="1">
+        <v>-0.3206477732793522</v>
+      </c>
+      <c r="E86" s="1">
+        <v>0.62</v>
+      </c>
+      <c r="F86" s="1">
+        <v>0.055982420657871894</v>
+      </c>
+      <c r="G86" s="1">
         <v>0.95</v>
       </c>
-      <c r="H85" s="1">
-        <v>35.4</v>
-      </c>
-      <c r="I85" s="1">
-        <v>7.56</v>
-      </c>
-      <c r="J85" s="1">
-        <v>0.000695414352035943</v>
-      </c>
-      <c r="K85" s="1" t="b">
+      <c r="H86" s="1">
+        <v>30.88</v>
+      </c>
+      <c r="I86" s="1">
+        <v>5.74</v>
+      </c>
+      <c r="J86" s="1">
+        <v>-0.00014255025102466516</v>
+      </c>
+      <c r="K86" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L85" s="1">
-        <v>131</v>
-      </c>
-      <c r="M85" s="1">
-        <v>0.05194679265758184</v>
-      </c>
-      <c r="N85" s="1">
-        <v>9.46716696338671</v>
-      </c>
-      <c r="O85" s="1">
-        <v>63.095238095238095</v>
-      </c>
-      <c r="P85" s="1">
-        <v>9.561516372520778</v>
-      </c>
-      <c r="Q85" s="1">
-        <v>48.45238095238095</v>
-      </c>
-      <c r="R85" s="1">
-        <v>49.345238095238095</v>
-      </c>
-      <c r="S85" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="T85" s="1">
-        <v>2.58</v>
+      <c r="L86" s="1">
+        <v>132</v>
+      </c>
+      <c r="M86" s="1">
+        <v>0.05488672871318179</v>
+      </c>
+      <c r="N86" s="1">
+        <v>8.755056760698379</v>
+      </c>
+      <c r="O86" s="1">
+        <v>63.52941176470588</v>
+      </c>
+      <c r="P86" s="1">
+        <v>10.0605242712113</v>
+      </c>
+      <c r="Q86" s="1">
+        <v>46.82352941176471</v>
+      </c>
+      <c r="R86" s="1">
+        <v>49.529411764705884</v>
+      </c>
+      <c r="S86" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="T86" s="1">
+        <v>2.76</v>
       </c>
     </row>
   </sheetData>
@@ -7368,7 +7442,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B85"/>
+  <dimension ref="A1:B86"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -7384,7 +7458,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>46.666666666666664</v>
+        <v>48.52941176470588</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -7392,7 +7466,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>50.23809523809524</v>
+        <v>50.23529411764706</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7400,7 +7474,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>54.58333333333333</v>
+        <v>54.470588235294116</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -7408,7 +7482,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>35.05952380952381</v>
+        <v>36.05882352941177</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -7416,7 +7490,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>36.011904761904766</v>
+        <v>34.05882352941177</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7424,7 +7498,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>55.23809523809524</v>
+        <v>55.52941176470588</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -7432,7 +7506,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>39.107142857142854</v>
+        <v>41.05882352941176</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -7440,7 +7514,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>59.702380952380956</v>
+        <v>59.94117647058823</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -7448,7 +7522,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>45.714285714285715</v>
+        <v>45.1764705882353</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -7456,7 +7530,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>59.16666666666667</v>
+        <v>58.64705882352941</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -7464,7 +7538,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>62.916666666666664</v>
+        <v>62.8235294117647</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -7472,7 +7546,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>38.33333333333333</v>
+        <v>38.529411764705884</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -7480,7 +7554,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>61.13095238095239</v>
+        <v>60.52941176470589</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -7488,7 +7562,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>25.059523809523814</v>
+        <v>23.058823529411768</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -7496,7 +7570,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>14.464285714285708</v>
+        <v>13.764705882352942</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -7504,7 +7578,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>33.03571428571429</v>
+        <v>33.05882352941177</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -7512,7 +7586,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>22.91666666666667</v>
+        <v>23.11764705882353</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -7520,7 +7594,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>53.750000000000014</v>
+        <v>54.52941176470587</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -7528,7 +7602,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>55.83333333333333</v>
+        <v>57.70588235294118</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -7536,7 +7610,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>22.67857142857143</v>
+        <v>21.05882352941176</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -7544,7 +7618,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>33.45238095238095</v>
+        <v>35.17647058823529</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -7552,7 +7626,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>55.05952380952381</v>
+        <v>52.94117647058824</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -7560,7 +7634,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>33.273809523809526</v>
+        <v>39.529411764705884</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -7568,7 +7642,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>5.535714285714283</v>
+        <v>1.3529411764705888</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -7576,7 +7650,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>-1.488095238095239</v>
+        <v>-1.3529411764705905</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -7584,7 +7658,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>-0.2976190476190492</v>
+        <v>-0.29411764705882604</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -7592,7 +7666,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>35.29761904761905</v>
+        <v>33.41176470588235</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -7600,7 +7674,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>43.75</v>
+        <v>44.76470588235294</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -7608,7 +7682,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>41.36904761904762</v>
+        <v>43.82352941176471</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -7616,7 +7690,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>38.03571428571429</v>
+        <v>38.294117647058826</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -7624,7 +7698,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>28.750000000000007</v>
+        <v>26.941176470588225</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -7632,7 +7706,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>60.11904761904761</v>
+        <v>60.11764705882352</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -7640,7 +7714,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>37.5</v>
+        <v>39.23529411764706</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -7648,7 +7722,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>38.095238095238095</v>
+        <v>40.1764705882353</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -7656,7 +7730,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>42.26190476190476</v>
+        <v>39.411764705882355</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -7664,7 +7738,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>53.21428571428571</v>
+        <v>52.94117647058823</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -7672,7 +7746,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>65.35714285714286</v>
+        <v>65.52941176470588</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -7680,7 +7754,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>40.773809523809526</v>
+        <v>39.76470588235295</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -7688,7 +7762,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>46.607142857142854</v>
+        <v>47.88235294117647</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -7696,7 +7770,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>16.666666666666668</v>
+        <v>21.70588235294118</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -7704,7 +7778,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>32.61904761904761</v>
+        <v>33.294117647058826</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -7712,7 +7786,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>58.273809523809526</v>
+        <v>58.64705882352942</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -7720,7 +7794,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>52.857142857142854</v>
+        <v>53.88235294117648</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -7728,7 +7802,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>41.964285714285715</v>
+        <v>41.76470588235294</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -7736,7 +7810,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>27.26190476190476</v>
+        <v>25.47058823529411</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -7744,7 +7818,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>43.095238095238095</v>
+        <v>42.882352941176464</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -7752,7 +7826,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>55.95238095238097</v>
+        <v>54.23529411764706</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -7760,7 +7834,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>56.60714285714286</v>
+        <v>56.58823529411765</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -7768,7 +7842,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>22.44047619047619</v>
+        <v>25.764705882352942</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -7776,7 +7850,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>42.91666666666666</v>
+        <v>41.99999999999999</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -7784,7 +7858,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>23.452380952380963</v>
+        <v>25.000000000000004</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -7792,7 +7866,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>45.833333333333336</v>
+        <v>16.764705882352942</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -7800,7 +7874,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>31.130952380952383</v>
+        <v>46.470588235294116</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -7808,7 +7882,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>40.833333333333336</v>
+        <v>31.941176470588232</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -7816,7 +7890,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>25.714285714285715</v>
+        <v>32.47058823529412</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -7824,7 +7898,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>47.67857142857143</v>
+        <v>26.11764705882353</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -7832,7 +7906,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>23.452380952380956</v>
+        <v>48.11764705882352</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -7840,7 +7914,7 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>11.54761904761905</v>
+        <v>25.647058823529413</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -7848,7 +7922,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>45.65476190476191</v>
+        <v>10.64705882352941</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -7856,7 +7930,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>52.976190476190474</v>
+        <v>46.05882352941177</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -7864,7 +7938,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>42.73809523809524</v>
+        <v>54.70588235294118</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -7872,7 +7946,7 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>30.95238095238095</v>
+        <v>42.8235294117647</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -7880,7 +7954,7 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>34.583333333333336</v>
+        <v>31</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -7888,7 +7962,7 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>59.82142857142857</v>
+        <v>33.1764705882353</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -7896,7 +7970,7 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>27.559523809523807</v>
+        <v>59.941176470588246</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -7904,7 +7978,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>33.392857142857146</v>
+        <v>28.82352941176471</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -7912,7 +7986,7 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>49.94047619047619</v>
+        <v>36.41176470588236</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -7920,7 +7994,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>46.30952380952381</v>
+        <v>48.647058823529406</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -7928,7 +8002,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>57.916666666666664</v>
+        <v>46.470588235294116</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -7936,7 +8010,7 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>36.72619047619048</v>
+        <v>57.76470588235295</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -7944,7 +8018,7 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>60.952380952380956</v>
+        <v>39.35294117647059</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -7952,7 +8026,7 @@
         <v>72</v>
       </c>
       <c r="B73">
-        <v>31.011904761904763</v>
+        <v>62.88235294117648</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -7960,7 +8034,7 @@
         <v>73</v>
       </c>
       <c r="B74">
-        <v>29.46428571428571</v>
+        <v>30.823529411764714</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -7968,87 +8042,95 @@
         <v>74</v>
       </c>
       <c r="B75">
-        <v>22.916666666666664</v>
+        <v>30.411764705882355</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>122</v>
+        <v>75</v>
       </c>
       <c r="B76">
-        <v>21.30952380952381</v>
+        <v>24.235294117647058</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B77">
-        <v>60.17857142857143</v>
+        <v>24.764705882352942</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B78">
-        <v>55.23809523809524</v>
+        <v>60.76470588235294</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B79">
-        <v>54.28571428571429</v>
+        <v>54.64705882352941</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B80">
-        <v>53.57142857142857</v>
+        <v>54.705882352941174</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B81">
-        <v>49.82142857142857</v>
+        <v>54.11764705882352</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B82">
-        <v>51.845238095238095</v>
+        <v>51.52941176470588</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B83">
-        <v>36.8452380952381</v>
+        <v>51.70588235294118</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B84">
-        <v>36.964285714285715</v>
+        <v>36.8235294117647</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>131</v>
+      </c>
+      <c r="B85">
+        <v>37.82352941176471</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
         <v>133</v>
       </c>
-      <c r="B85">
-        <v>49.345238095238095</v>
+      <c r="B86">
+        <v>49.529411764705884</v>
       </c>
     </row>
   </sheetData>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -427,7 +427,7 @@
     <t>_date_</t>
   </si>
   <si>
-    <t>2026-09-21</t>
+    <t>2026-09-22</t>
   </si>
   <si>
     <t>Criteria</t>
@@ -688,34 +688,34 @@
     <t>Momentum Breakout, Market Leader, Volume Spike, Institutional Buying</t>
   </si>
   <si>
+    <t>Momentum Breakout, Market Leader, Institutional Buying</t>
+  </si>
+  <si>
     <t>Momentum Breakout, Market Leader, Stable Uptrend, Volume Spike, Institutional Buying</t>
   </si>
   <si>
-    <t>Momentum Breakout, Market Leader, Institutional Buying</t>
-  </si>
-  <si>
     <t>Momentum Breakout, Market Leader</t>
   </si>
   <si>
     <t>Institutional Buying</t>
   </si>
   <si>
+    <t>Momentum Breakout, Volume Spike</t>
+  </si>
+  <si>
+    <t>Momentum Breakout</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
     <t>Momentum Breakout, Institutional Buying</t>
   </si>
   <si>
-    <t>Momentum Breakout, Volume Spike</t>
+    <t>Volume Spike</t>
   </si>
   <si>
     <t>Volume Spike, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Volume Spike, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Volume Spike</t>
-  </si>
-  <si>
-    <t>Momentum Breakout</t>
   </si>
   <si>
     <t>Momentum Breakout, Market Leader, Volume Spike</t>
@@ -1413,7 +1413,7 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>65.52941176470588</v>
+        <v>65.76470588235294</v>
       </c>
       <c r="C2" t="s">
         <v>221</v>
@@ -1421,10 +1421,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="B3">
-        <v>62.88235294117648</v>
+        <v>62.8235294117647</v>
       </c>
       <c r="C3" t="s">
         <v>222</v>
@@ -1432,10 +1432,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="B4">
-        <v>62.8235294117647</v>
+        <v>61.82352941176471</v>
       </c>
       <c r="C4" t="s">
         <v>223</v>
@@ -1443,10 +1443,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>124</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>60.76470588235294</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
         <v>224</v>
@@ -1457,73 +1457,73 @@
         <v>13</v>
       </c>
       <c r="B6">
-        <v>60.52941176470589</v>
+        <v>60.88235294117647</v>
       </c>
       <c r="C6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>124</v>
       </c>
       <c r="B7">
-        <v>60.11764705882352</v>
+        <v>60.529411764705884</v>
       </c>
       <c r="C7" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="B8">
-        <v>59.941176470588246</v>
+        <v>60.47058823529413</v>
       </c>
       <c r="C8" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="B9">
-        <v>59.94117647058823</v>
+        <v>59.941176470588246</v>
       </c>
       <c r="C9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="B10">
-        <v>58.64705882352942</v>
+        <v>59.235294117647065</v>
       </c>
       <c r="C10" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="B11">
-        <v>58.64705882352941</v>
+        <v>57.52941176470589</v>
       </c>
       <c r="C11" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="B12">
-        <v>57.76470588235295</v>
+        <v>57.41176470588236</v>
       </c>
       <c r="C12" t="s">
         <v>227</v>
@@ -1534,7 +1534,7 @@
         <v>19</v>
       </c>
       <c r="B13">
-        <v>57.70588235294118</v>
+        <v>57.352941176470594</v>
       </c>
       <c r="C13" t="s">
         <v>221</v>
@@ -1542,46 +1542,46 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B14">
-        <v>55.52941176470588</v>
+        <v>57.05882352941176</v>
       </c>
       <c r="C14" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="B15">
-        <v>54.70588235294118</v>
+        <v>56.76470588235294</v>
       </c>
       <c r="C15" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>126</v>
+        <v>43</v>
       </c>
       <c r="B16">
-        <v>54.705882352941174</v>
+        <v>56.470588235294116</v>
       </c>
       <c r="C16" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>125</v>
+        <v>6</v>
       </c>
       <c r="B17">
-        <v>54.64705882352941</v>
+        <v>55.76470588235293</v>
       </c>
       <c r="C17" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -1589,7 +1589,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>54.52941176470587</v>
+        <v>54.17647058823529</v>
       </c>
       <c r="C18" t="s">
         <v>230</v>
@@ -1597,54 +1597,54 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="B19">
-        <v>54.470588235294116</v>
+        <v>54.11764705882353</v>
       </c>
       <c r="C19" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>127</v>
       </c>
       <c r="B20">
-        <v>54.23529411764706</v>
+        <v>54.11764705882352</v>
       </c>
       <c r="C20" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>127</v>
+        <v>3</v>
       </c>
       <c r="B21">
-        <v>54.11764705882352</v>
+        <v>54</v>
       </c>
       <c r="C21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="B22">
-        <v>52.94117647058824</v>
+        <v>53.94117647058824</v>
       </c>
       <c r="C22" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="B23">
-        <v>52.94117647058823</v>
+        <v>53.76470588235295</v>
       </c>
       <c r="C23" t="s">
         <v>231</v>
@@ -1652,24 +1652,24 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B24">
-        <v>51.70588235294118</v>
+        <v>53.529411764705884</v>
       </c>
       <c r="C24" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>128</v>
+        <v>36</v>
       </c>
       <c r="B25">
-        <v>51.52941176470588</v>
+        <v>53.29411764705882</v>
       </c>
       <c r="C25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -1677,18 +1677,18 @@
         <v>2</v>
       </c>
       <c r="B26">
-        <v>50.23529411764706</v>
+        <v>53.17647058823529</v>
       </c>
       <c r="C26" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B27">
-        <v>49.529411764705884</v>
+        <v>51.58823529411765</v>
       </c>
       <c r="C27" t="s">
         <v>225</v>
@@ -1696,230 +1696,230 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1</v>
+        <v>128</v>
       </c>
       <c r="B28">
-        <v>48.52941176470588</v>
+        <v>49.88235294117647</v>
       </c>
       <c r="C28" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="B29">
-        <v>48.11764705882352</v>
+        <v>47.47058823529412</v>
       </c>
       <c r="C29" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B30">
-        <v>47.88235294117647</v>
+        <v>47.1764705882353</v>
       </c>
       <c r="C30" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="B31">
-        <v>46.470588235294116</v>
+        <v>45.88235294117647</v>
       </c>
       <c r="C31" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="B32">
-        <v>46.470588235294116</v>
+        <v>45.764705882352935</v>
       </c>
       <c r="C32" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>60</v>
+        <v>133</v>
       </c>
       <c r="B33">
-        <v>46.05882352941177</v>
+        <v>45.64705882352941</v>
       </c>
       <c r="C33" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="B34">
-        <v>45.1764705882353</v>
+        <v>45.29411764705882</v>
       </c>
       <c r="C34" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="B35">
-        <v>44.76470588235294</v>
+        <v>44.29411764705883</v>
       </c>
       <c r="C35" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="B36">
-        <v>43.82352941176471</v>
+        <v>44.11764705882353</v>
       </c>
       <c r="C36" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="B37">
-        <v>42.882352941176464</v>
+        <v>43.647058823529406</v>
       </c>
       <c r="C37" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="B38">
-        <v>42.8235294117647</v>
+        <v>43.35294117647059</v>
       </c>
       <c r="C38" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="B39">
-        <v>41.99999999999999</v>
+        <v>43.35294117647059</v>
       </c>
       <c r="C39" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B40">
-        <v>41.76470588235294</v>
+        <v>42.411764705882355</v>
       </c>
       <c r="C40" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="B41">
-        <v>41.05882352941176</v>
+        <v>41.52941176470589</v>
       </c>
       <c r="C41" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="B42">
-        <v>39.76470588235295</v>
+        <v>40.823529411764696</v>
       </c>
       <c r="C42" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="B43">
-        <v>39.529411764705884</v>
+        <v>40.352941176470594</v>
       </c>
       <c r="C43" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="B44">
-        <v>39.411764705882355</v>
+        <v>40.23529411764706</v>
       </c>
       <c r="C44" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="B45">
-        <v>39.35294117647059</v>
+        <v>40.17647058823529</v>
       </c>
       <c r="C45" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B46">
-        <v>39.23529411764706</v>
+        <v>39.588235294117645</v>
       </c>
       <c r="C46" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B47">
-        <v>38.529411764705884</v>
+        <v>38.705882352941174</v>
       </c>
       <c r="C47" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="B48">
-        <v>38.294117647058826</v>
+        <v>38.705882352941174</v>
       </c>
       <c r="C48" t="s">
         <v>225</v>
@@ -1927,35 +1927,35 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>131</v>
+        <v>71</v>
       </c>
       <c r="B49">
-        <v>37.82352941176471</v>
+        <v>38.411764705882355</v>
       </c>
       <c r="C49" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>130</v>
+        <v>35</v>
       </c>
       <c r="B50">
-        <v>36.8235294117647</v>
+        <v>38.00000000000001</v>
       </c>
       <c r="C50" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="B51">
-        <v>36.41176470588236</v>
+        <v>36.76470588235295</v>
       </c>
       <c r="C51" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -2183,55 +2183,55 @@
         <v>67.05882352941175</v>
       </c>
       <c r="D2" s="1">
-        <v>-1.9909909909909909</v>
+        <v>-2.0978120978120978</v>
       </c>
       <c r="E2" s="1">
         <v>-2.08</v>
       </c>
       <c r="F2" s="1">
-        <v>0.17135440094619037</v>
+        <v>0.12235458909482223</v>
       </c>
       <c r="G2" s="1">
         <v>0.21</v>
       </c>
       <c r="H2" s="1">
-        <v>51.05</v>
+        <v>46.1</v>
       </c>
       <c r="I2" s="1">
-        <v>10.27</v>
+        <v>8.01</v>
       </c>
       <c r="J2" s="1">
-        <v>0.016848552590128983</v>
+        <v>0.015687366545096053</v>
       </c>
       <c r="K2" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L2" s="1">
-        <v>-461</v>
+        <v>-460</v>
       </c>
       <c r="M2" s="1">
-        <v>0.15404246822008671</v>
+        <v>0.08434679399457945</v>
       </c>
       <c r="N2" s="1">
-        <v>18.670630711388874</v>
+        <v>14.320792703286145</v>
       </c>
       <c r="O2" s="1">
-        <v>77.64705882352942</v>
+        <v>69.41176470588235</v>
       </c>
       <c r="P2" s="1">
         <v>16.29652721982991</v>
       </c>
       <c r="Q2" s="1">
-        <v>50.8235294117647</v>
+        <v>48.11764705882352</v>
       </c>
       <c r="R2" s="1">
-        <v>48.52941176470588</v>
+        <v>45.764705882352935</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>95</v>
       </c>
       <c r="T2" s="1">
-        <v>28.71</v>
+        <v>25.95</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -2251,49 +2251,49 @@
         <v>3.59</v>
       </c>
       <c r="F3" s="2">
-        <v>-0.023099612774609424</v>
+        <v>-0.014726308882188316</v>
       </c>
       <c r="G3" s="2">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="H3" s="2">
-        <v>67.65</v>
+        <v>70.85</v>
       </c>
       <c r="I3" s="2">
-        <v>61.01</v>
+        <v>69.7</v>
       </c>
       <c r="J3" s="2">
-        <v>-0.0014133504791873641</v>
+        <v>0.001892919301467904</v>
       </c>
       <c r="K3" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L3" s="2">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="M3" s="2">
-        <v>0.009113730399279651</v>
+        <v>0.0569592793448519</v>
       </c>
       <c r="N3" s="2">
-        <v>4.177756929308165</v>
+        <v>11.582041238313389</v>
       </c>
       <c r="O3" s="2">
-        <v>57.647058823529406</v>
+        <v>65.88235294117646</v>
       </c>
       <c r="P3" s="2">
         <v>26.053946839070953</v>
       </c>
       <c r="Q3" s="2">
-        <v>68.82352941176471</v>
+        <v>70.3529411764706</v>
       </c>
       <c r="R3" s="2">
-        <v>50.23529411764706</v>
+        <v>53.17647058823529</v>
       </c>
       <c r="S3" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T3" s="2">
-        <v>-16.84</v>
+        <v>-13.9</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -2313,19 +2313,19 @@
         <v>6.34</v>
       </c>
       <c r="F4" s="2">
-        <v>0.3907653845388289</v>
+        <v>0.4216343854971777</v>
       </c>
       <c r="G4" s="2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="H4" s="2">
-        <v>54.48</v>
+        <v>57.79</v>
       </c>
       <c r="I4" s="2">
-        <v>49.5</v>
+        <v>52.73</v>
       </c>
       <c r="J4" s="2">
-        <v>0.02262796784613889</v>
+        <v>0.022897271333209533</v>
       </c>
       <c r="K4" s="2" t="b">
         <v>0</v>
@@ -2334,28 +2334,28 @@
         <v>181</v>
       </c>
       <c r="M4" s="2">
-        <v>0.39843522815165966</v>
+        <v>0.4389543933909592</v>
       </c>
       <c r="N4" s="2">
-        <v>43.109906704546184</v>
+        <v>49.781552642924126</v>
       </c>
       <c r="O4" s="2">
-        <v>92.94117647058823</v>
+        <v>91.76470588235294</v>
       </c>
       <c r="P4" s="2">
         <v>19.349659482175007</v>
       </c>
       <c r="Q4" s="2">
-        <v>58.117647058823536</v>
+        <v>58.58823529411766</v>
       </c>
       <c r="R4" s="2">
-        <v>54.470588235294116</v>
+        <v>54</v>
       </c>
       <c r="S4" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T4" s="2">
-        <v>6.12</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -2369,55 +2369,55 @@
         <v>40</v>
       </c>
       <c r="D5" s="1">
-        <v>30.990740740740737</v>
+        <v>30.98148148148148</v>
       </c>
       <c r="E5" s="1">
         <v>1.69</v>
       </c>
       <c r="F5" s="1">
-        <v>-0.14304464950581564</v>
+        <v>-0.17608998882001448</v>
       </c>
       <c r="G5" s="1">
         <v>1.91</v>
       </c>
       <c r="H5" s="1">
-        <v>56.14</v>
+        <v>58.85</v>
       </c>
       <c r="I5" s="1">
-        <v>-6.97</v>
+        <v>-5.25</v>
       </c>
       <c r="J5" s="1">
-        <v>-0.011996112001193106</v>
+        <v>-0.01190530793671953</v>
       </c>
       <c r="K5" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L5" s="1">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="M5" s="1">
-        <v>-0.12310305611245576</v>
+        <v>-0.13230885775517787</v>
       </c>
       <c r="N5" s="1">
-        <v>-9.043921721865367</v>
+        <v>-7.344772471689587</v>
       </c>
       <c r="O5" s="1">
-        <v>34.11764705882353</v>
+        <v>32.94117647058823</v>
       </c>
       <c r="P5" s="1">
         <v>33.002444654975626</v>
       </c>
       <c r="Q5" s="1">
-        <v>50.94117647058823</v>
+        <v>51.88235294117648</v>
       </c>
       <c r="R5" s="1">
-        <v>36.05882352941177</v>
+        <v>35.705882352941174</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T5" s="1">
-        <v>-9.92</v>
+        <v>-10.27</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -2437,49 +2437,49 @@
         <v>-1.88</v>
       </c>
       <c r="F6" s="1">
-        <v>-0.11827212497552217</v>
+        <v>-0.08114159750692664</v>
       </c>
       <c r="G6" s="1">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H6" s="1">
-        <v>36.1</v>
+        <v>42.7</v>
       </c>
       <c r="I6" s="1">
-        <v>-15.95</v>
+        <v>-13.05</v>
       </c>
       <c r="J6" s="1">
-        <v>0.00021664429675236435</v>
+        <v>-0.000491060031693518</v>
       </c>
       <c r="K6" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L6" s="1">
-        <v>-205</v>
+        <v>-204</v>
       </c>
       <c r="M6" s="1">
-        <v>-0.10490468325030289</v>
+        <v>-0.05227491768395742</v>
       </c>
       <c r="N6" s="1">
-        <v>-7.224084435650077</v>
+        <v>0.6586215354324567</v>
       </c>
       <c r="O6" s="1">
-        <v>37.64705882352941</v>
+        <v>47.05882352941176</v>
       </c>
       <c r="P6" s="1">
         <v>27.785495103772316</v>
       </c>
       <c r="Q6" s="1">
-        <v>41.1764705882353</v>
+        <v>42</v>
       </c>
       <c r="R6" s="1">
-        <v>34.05882352941177</v>
+        <v>36.41176470588235</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T6" s="1">
-        <v>14.97</v>
+        <v>17.33</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -2493,25 +2493,25 @@
         <v>69.41176470588235</v>
       </c>
       <c r="D7" s="2">
-        <v>7.814159292035399</v>
+        <v>7.841972187104931</v>
       </c>
       <c r="E7" s="2">
         <v>0.5</v>
       </c>
       <c r="F7" s="2">
-        <v>-0.004436447452838818</v>
+        <v>-0.027789106745771536</v>
       </c>
       <c r="G7" s="2">
         <v>2.22</v>
       </c>
       <c r="H7" s="2">
-        <v>55.64</v>
+        <v>56.92</v>
       </c>
       <c r="I7" s="2">
-        <v>12.79</v>
+        <v>13.73</v>
       </c>
       <c r="J7" s="2">
-        <v>0.00794321380736259</v>
+        <v>0.007958419461773562</v>
       </c>
       <c r="K7" s="2" t="b">
         <v>0</v>
@@ -2520,28 +2520,28 @@
         <v>176</v>
       </c>
       <c r="M7" s="2">
-        <v>0.02229843599759973</v>
+        <v>0.03090647556093251</v>
       </c>
       <c r="N7" s="2">
-        <v>5.49622748914018</v>
+        <v>8.97676085992146</v>
       </c>
       <c r="O7" s="2">
-        <v>60</v>
+        <v>61.1764705882353</v>
       </c>
       <c r="P7" s="2">
         <v>19.398494070050486</v>
       </c>
       <c r="Q7" s="2">
-        <v>67.76470588235294</v>
+        <v>67.6470588235294</v>
       </c>
       <c r="R7" s="2">
-        <v>55.52941176470588</v>
+        <v>55.76470588235293</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T7" s="2">
-        <v>7.11</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -2561,49 +2561,49 @@
         <v>2.63</v>
       </c>
       <c r="F8" s="1">
-        <v>-0.0841234225495912</v>
+        <v>-0.11170199013444851</v>
       </c>
       <c r="G8" s="1">
         <v>0.61</v>
       </c>
       <c r="H8" s="1">
-        <v>38.49</v>
+        <v>37.47</v>
       </c>
       <c r="I8" s="1">
-        <v>6.71</v>
+        <v>6.37</v>
       </c>
       <c r="J8" s="1">
-        <v>-0.011827467778737204</v>
+        <v>-0.0121088336555875</v>
       </c>
       <c r="K8" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L8" s="1">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="M8" s="1">
-        <v>-0.092669819718174</v>
+        <v>-0.1304653320193785</v>
       </c>
       <c r="N8" s="1">
-        <v>-6.000598082437192</v>
+        <v>-7.160419898109647</v>
       </c>
       <c r="O8" s="1">
-        <v>41.17647058823529</v>
+        <v>34.11764705882353</v>
       </c>
       <c r="P8" s="1">
         <v>14.011691026293512</v>
       </c>
       <c r="Q8" s="1">
-        <v>45.76470588235294</v>
+        <v>44</v>
       </c>
       <c r="R8" s="1">
-        <v>41.05882352941176</v>
+        <v>38.705882352941174</v>
       </c>
       <c r="S8" s="1" t="s">
         <v>101</v>
       </c>
       <c r="T8" s="1">
-        <v>-18.7</v>
+        <v>-21.05</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -2623,19 +2623,19 @@
         <v>2.96</v>
       </c>
       <c r="F9" s="2">
-        <v>0.3367039704258855</v>
+        <v>0.4444060477068711</v>
       </c>
       <c r="G9" s="2">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H9" s="2">
-        <v>57.5</v>
+        <v>61.86</v>
       </c>
       <c r="I9" s="2">
-        <v>17.4</v>
+        <v>21.23</v>
       </c>
       <c r="J9" s="2">
-        <v>0.02814584744862212</v>
+        <v>0.029573599732622087</v>
       </c>
       <c r="K9" s="2" t="b">
         <v>0</v>
@@ -2644,28 +2644,28 @@
         <v>-112</v>
       </c>
       <c r="M9" s="2">
-        <v>0.3500714121511048</v>
+        <v>0.4732727275298403</v>
       </c>
       <c r="N9" s="2">
-        <v>38.273525104490695</v>
+        <v>53.21338605681224</v>
       </c>
       <c r="O9" s="2">
-        <v>89.41176470588236</v>
+        <v>92.94117647058823</v>
       </c>
       <c r="P9" s="2">
         <v>33.227512780245505</v>
       </c>
       <c r="Q9" s="2">
-        <v>70.35294117647058</v>
+        <v>71.88235294117646</v>
       </c>
       <c r="R9" s="2">
-        <v>59.94117647058823</v>
+        <v>61</v>
       </c>
       <c r="S9" s="2" t="s">
         <v>102</v>
       </c>
       <c r="T9" s="2">
-        <v>32.56</v>
+        <v>33.62</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -2685,34 +2685,34 @@
         <v>0.08</v>
       </c>
       <c r="F10" s="1">
-        <v>-0.05361085296055531</v>
+        <v>-0.061693416901536235</v>
       </c>
       <c r="G10" s="1">
         <v>1.42</v>
       </c>
       <c r="H10" s="1">
-        <v>45.51</v>
+        <v>46.91</v>
       </c>
       <c r="I10" s="1">
-        <v>-0.41</v>
+        <v>0.1</v>
       </c>
       <c r="J10" s="1">
-        <v>0.008396296401718037</v>
+        <v>0.008287253135108447</v>
       </c>
       <c r="K10" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L10" s="1">
-        <v>-50</v>
+        <v>-49</v>
       </c>
       <c r="M10" s="1">
-        <v>-0.044407040625158434</v>
+        <v>-0.041486741025457796</v>
       </c>
       <c r="N10" s="1">
-        <v>-1.1743201731356305</v>
+        <v>1.7374392012824234</v>
       </c>
       <c r="O10" s="1">
-        <v>50.588235294117645</v>
+        <v>52.94117647058824</v>
       </c>
       <c r="P10" s="1">
         <v>14.568379622257217</v>
@@ -2721,13 +2721,13 @@
         <v>51.294117647058826</v>
       </c>
       <c r="R10" s="1">
-        <v>45.1764705882353</v>
+        <v>45.88235294117647</v>
       </c>
       <c r="S10" s="1" t="s">
         <v>103</v>
       </c>
       <c r="T10" s="1">
-        <v>9.63</v>
+        <v>10.33</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -2747,19 +2747,19 @@
         <v>2.19</v>
       </c>
       <c r="F11" s="2">
-        <v>0.47235958602627137</v>
+        <v>0.5692639602385912</v>
       </c>
       <c r="G11" s="2">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="H11" s="2">
-        <v>58.36</v>
+        <v>63.87</v>
       </c>
       <c r="I11" s="2">
-        <v>38.76</v>
+        <v>46.37</v>
       </c>
       <c r="J11" s="2">
-        <v>0.024411657653181016</v>
+        <v>0.025101987323489144</v>
       </c>
       <c r="K11" s="2" t="b">
         <v>1</v>
@@ -2768,28 +2768,28 @@
         <v>40</v>
       </c>
       <c r="M11" s="2">
-        <v>0.46600457274706875</v>
+        <v>0.5557928429878722</v>
       </c>
       <c r="N11" s="2">
-        <v>49.86684116408709</v>
+        <v>61.465397602615425</v>
       </c>
       <c r="O11" s="2">
-        <v>94.11764705882352</v>
+        <v>96.47058823529412</v>
       </c>
       <c r="P11" s="2">
         <v>21.2185970476566</v>
       </c>
       <c r="Q11" s="2">
-        <v>64.94117647058825</v>
+        <v>66.3529411764706</v>
       </c>
       <c r="R11" s="2">
-        <v>58.64705882352941</v>
+        <v>59.235294117647065</v>
       </c>
       <c r="S11" s="2" t="s">
         <v>104</v>
       </c>
       <c r="T11" s="2">
-        <v>7</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -2809,31 +2809,31 @@
         <v>1.33</v>
       </c>
       <c r="F12" s="2">
-        <v>0.8213136145457095</v>
+        <v>0.8692235811798992</v>
       </c>
       <c r="G12" s="2">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="H12" s="2">
-        <v>64.21</v>
+        <v>65.08</v>
       </c>
       <c r="I12" s="2">
-        <v>55.57</v>
+        <v>56.43</v>
       </c>
       <c r="J12" s="2">
-        <v>0.04325071796450576</v>
+        <v>0.04296681619528336</v>
       </c>
       <c r="K12" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L12" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M12" s="2">
-        <v>0.8208753377678335</v>
+        <v>0.8687424698495163</v>
       </c>
       <c r="N12" s="2">
-        <v>85.35391766616357</v>
+        <v>92.76036028877982</v>
       </c>
       <c r="O12" s="2">
         <v>100</v>
@@ -2842,7 +2842,7 @@
         <v>23.557267760130397</v>
       </c>
       <c r="Q12" s="2">
-        <v>71.05882352941177</v>
+        <v>71.17647058823529</v>
       </c>
       <c r="R12" s="2">
         <v>62.8235294117647</v>
@@ -2871,19 +2871,19 @@
         <v>-1.08</v>
       </c>
       <c r="F13" s="1">
-        <v>0.500607940418708</v>
+        <v>0.3554111746281361</v>
       </c>
       <c r="G13" s="1">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="H13" s="1">
-        <v>60.67</v>
+        <v>50.77</v>
       </c>
       <c r="I13" s="1">
-        <v>21.47</v>
+        <v>13.59</v>
       </c>
       <c r="J13" s="1">
-        <v>0.04603904305404006</v>
+        <v>0.04600715560834621</v>
       </c>
       <c r="K13" s="1" t="b">
         <v>1</v>
@@ -2892,28 +2892,28 @@
         <v>5</v>
       </c>
       <c r="M13" s="1">
-        <v>0.5130988285881752</v>
+        <v>0.3833156317903397</v>
       </c>
       <c r="N13" s="1">
-        <v>54.57626674819773</v>
+        <v>44.21767648286217</v>
       </c>
       <c r="O13" s="1">
-        <v>95.29411764705881</v>
+        <v>89.41176470588236</v>
       </c>
       <c r="P13" s="1">
         <v>40.13761891809808</v>
       </c>
       <c r="Q13" s="1">
-        <v>45.411764705882355</v>
+        <v>41.529411764705884</v>
       </c>
       <c r="R13" s="1">
-        <v>38.529411764705884</v>
+        <v>36.76470588235295</v>
       </c>
       <c r="S13" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T13" s="1">
-        <v>37.74</v>
+        <v>35.97</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -2933,49 +2933,49 @@
         <v>-1.75</v>
       </c>
       <c r="F14" s="2">
-        <v>0.5208156300520135</v>
+        <v>0.6029356493111555</v>
       </c>
       <c r="G14" s="2">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="H14" s="2">
-        <v>61.6</v>
+        <v>66.04</v>
       </c>
       <c r="I14" s="2">
-        <v>70.95</v>
+        <v>78.82</v>
       </c>
       <c r="J14" s="2">
-        <v>0.027317155840913813</v>
+        <v>0.02817723147779358</v>
       </c>
       <c r="K14" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L14" s="2">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="M14" s="2">
-        <v>0.515337170328563</v>
+        <v>0.5913889773819678</v>
       </c>
       <c r="N14" s="2">
-        <v>54.80010092223652</v>
+        <v>65.02501104202497</v>
       </c>
       <c r="O14" s="2">
-        <v>96.47058823529412</v>
+        <v>97.6470588235294</v>
       </c>
       <c r="P14" s="2">
         <v>19.142997204429033</v>
       </c>
       <c r="Q14" s="2">
-        <v>67.52941176470588</v>
+        <v>68.23529411764707</v>
       </c>
       <c r="R14" s="2">
-        <v>60.52941176470589</v>
+        <v>60.88235294117647</v>
       </c>
       <c r="S14" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T14" s="2">
-        <v>4.61</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -2989,55 +2989,55 @@
         <v>15.294117647058824</v>
       </c>
       <c r="D15" s="3">
-        <v>19.249999999999996</v>
+        <v>19.245283018867923</v>
       </c>
       <c r="E15" s="3">
         <v>1.49</v>
       </c>
       <c r="F15" s="3">
-        <v>-0.24954793524322455</v>
+        <v>-0.25590666911775917</v>
       </c>
       <c r="G15" s="3">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="H15" s="3">
-        <v>66.49</v>
+        <v>68.81</v>
       </c>
       <c r="I15" s="3">
-        <v>47.75</v>
+        <v>54.27</v>
       </c>
       <c r="J15" s="3">
-        <v>-0.012798871678323958</v>
+        <v>-0.005688061350404316</v>
       </c>
       <c r="K15" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L15" s="3">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="M15" s="3">
-        <v>-0.22215563662597193</v>
+        <v>-0.19480553015914104</v>
       </c>
       <c r="N15" s="3">
-        <v>-18.949179773216983</v>
+        <v>-13.594439712085904</v>
       </c>
       <c r="O15" s="3">
-        <v>18.823529411764707</v>
+        <v>24.705882352941178</v>
       </c>
       <c r="P15" s="3">
         <v>41.90435941885386</v>
       </c>
       <c r="Q15" s="3">
-        <v>51.294117647058826</v>
+        <v>54.352941176470594</v>
       </c>
       <c r="R15" s="3">
-        <v>23.058823529411768</v>
+        <v>26.117647058823536</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>107</v>
       </c>
       <c r="T15" s="3">
-        <v>-35.36</v>
+        <v>-32.3</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -3057,19 +3057,19 @@
         <v>29.93</v>
       </c>
       <c r="F16" s="3">
-        <v>-0.27546611076087707</v>
+        <v>-0.32147700664168166</v>
       </c>
       <c r="G16" s="3">
         <v>1.8</v>
       </c>
       <c r="H16" s="3">
-        <v>51.58</v>
+        <v>49.47</v>
       </c>
       <c r="I16" s="3">
-        <v>-2.61</v>
+        <v>-4.13</v>
       </c>
       <c r="J16" s="3">
-        <v>-0.04143714625090329</v>
+        <v>-0.03587144521515425</v>
       </c>
       <c r="K16" s="3" t="b">
         <v>1</v>
@@ -3078,28 +3078,28 @@
         <v>27</v>
       </c>
       <c r="M16" s="3">
-        <v>-0.2579350396458354</v>
+        <v>-0.282988100211056</v>
       </c>
       <c r="N16" s="3">
-        <v>-22.527120075203335</v>
+        <v>-22.412696717277406</v>
       </c>
       <c r="O16" s="3">
-        <v>12.941176470588237</v>
+        <v>11.76470588235294</v>
       </c>
       <c r="P16" s="3">
         <v>40.1905830435425</v>
       </c>
       <c r="Q16" s="3">
-        <v>30.941176470588232</v>
+        <v>30.11764705882353</v>
       </c>
       <c r="R16" s="3">
-        <v>13.764705882352942</v>
+        <v>13.411764705882351</v>
       </c>
       <c r="S16" s="3" t="s">
         <v>108</v>
       </c>
       <c r="T16" s="3">
-        <v>-29.47</v>
+        <v>-29.82</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -3113,25 +3113,25 @@
         <v>5.88235294117647</v>
       </c>
       <c r="D17" s="1">
-        <v>6.226890756302521</v>
+        <v>6.40546218487395</v>
       </c>
       <c r="E17" s="1">
         <v>-1.64</v>
       </c>
       <c r="F17" s="1">
-        <v>-0.003653700994869169</v>
+        <v>-0.0223939315990294</v>
       </c>
       <c r="G17" s="1">
         <v>1.76</v>
       </c>
       <c r="H17" s="1">
-        <v>56.29</v>
+        <v>59.23</v>
       </c>
       <c r="I17" s="1">
-        <v>6.82</v>
+        <v>9.23</v>
       </c>
       <c r="J17" s="1">
-        <v>-0.010226651418576992</v>
+        <v>-0.005724892285899171</v>
       </c>
       <c r="K17" s="1" t="b">
         <v>1</v>
@@ -3140,10 +3140,10 @@
         <v>31</v>
       </c>
       <c r="M17" s="1">
-        <v>0.013000816564420425</v>
+        <v>0.014170529510064922</v>
       </c>
       <c r="N17" s="1">
-        <v>4.566465545822243</v>
+        <v>7.303166254834687</v>
       </c>
       <c r="O17" s="1">
         <v>58.82352941176471</v>
@@ -3152,16 +3152,16 @@
         <v>24.80206596461608</v>
       </c>
       <c r="Q17" s="1">
-        <v>38.8235294117647</v>
+        <v>40.94117647058823</v>
       </c>
       <c r="R17" s="1">
-        <v>33.05882352941177</v>
+        <v>33.529411764705884</v>
       </c>
       <c r="S17" s="1" t="s">
         <v>102</v>
       </c>
       <c r="T17" s="1">
-        <v>-0.11</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -3181,19 +3181,19 @@
         <v>11.08</v>
       </c>
       <c r="F18" s="3">
-        <v>-0.6537555572936488</v>
+        <v>-0.671927651428184</v>
       </c>
       <c r="G18" s="3">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="H18" s="3">
-        <v>17.26</v>
+        <v>16.58</v>
       </c>
       <c r="I18" s="3">
-        <v>-54.68</v>
+        <v>-55.05</v>
       </c>
       <c r="J18" s="3">
-        <v>-0.0786608109751957</v>
+        <v>-0.08051049341946842</v>
       </c>
       <c r="K18" s="3" t="b">
         <v>1</v>
@@ -3202,16 +3202,16 @@
         <v>31</v>
       </c>
       <c r="M18" s="3">
-        <v>-0.6506876198485164</v>
+        <v>-0.6675976494547387</v>
       </c>
       <c r="N18" s="3">
-        <v>-61.80237809547143</v>
+        <v>-60.873651641645665</v>
       </c>
       <c r="O18" s="3">
         <v>1.1764705882352942</v>
       </c>
       <c r="P18" s="3">
-        <v>66.0016263719844</v>
+        <v>66.08306146236951</v>
       </c>
       <c r="Q18" s="3">
         <v>39.647058823529406</v>
@@ -3243,19 +3243,19 @@
         <v>3.1</v>
       </c>
       <c r="F19" s="2">
-        <v>0.08330440913490506</v>
+        <v>0.08137945031094068</v>
       </c>
       <c r="G19" s="2">
         <v>0.1</v>
       </c>
       <c r="H19" s="2">
-        <v>50.58</v>
+        <v>51.72</v>
       </c>
       <c r="I19" s="2">
-        <v>11.7</v>
+        <v>12.21</v>
       </c>
       <c r="J19" s="2">
-        <v>0.005207328208841143</v>
+        <v>0.0069900163072013745</v>
       </c>
       <c r="K19" s="2" t="b">
         <v>1</v>
@@ -3264,28 +3264,28 @@
         <v>-60</v>
       </c>
       <c r="M19" s="2">
-        <v>0.06358195413048318</v>
+        <v>0.03807943057648688</v>
       </c>
       <c r="N19" s="2">
-        <v>9.624579302428529</v>
+        <v>9.694056361476889</v>
       </c>
       <c r="O19" s="2">
-        <v>65.88235294117646</v>
+        <v>63.52941176470588</v>
       </c>
       <c r="P19" s="2">
         <v>11.392700631623551</v>
       </c>
       <c r="Q19" s="2">
-        <v>59.52941176470588</v>
+        <v>60.58823529411764</v>
       </c>
       <c r="R19" s="2">
-        <v>54.52941176470587</v>
+        <v>54.17647058823529</v>
       </c>
       <c r="S19" s="2" t="s">
         <v>110</v>
       </c>
       <c r="T19" s="2">
-        <v>6.11</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -3305,19 +3305,19 @@
         <v>-5.69</v>
       </c>
       <c r="F20" s="2">
-        <v>0.2985100255815787</v>
+        <v>0.2800570477168324</v>
       </c>
       <c r="G20" s="2">
         <v>1.07</v>
       </c>
       <c r="H20" s="2">
-        <v>55.48</v>
+        <v>56.22</v>
       </c>
       <c r="I20" s="2">
-        <v>23.58</v>
+        <v>23.64</v>
       </c>
       <c r="J20" s="2">
-        <v>0.02446185566034033</v>
+        <v>0.024914226042989283</v>
       </c>
       <c r="K20" s="2" t="b">
         <v>1</v>
@@ -3326,28 +3326,28 @@
         <v>8</v>
       </c>
       <c r="M20" s="2">
-        <v>0.30004399430414486</v>
+        <v>0.2834248270295121</v>
       </c>
       <c r="N20" s="2">
-        <v>33.270783319794695</v>
+        <v>34.22859600677942</v>
       </c>
       <c r="O20" s="2">
-        <v>87.05882352941177</v>
+        <v>85.88235294117646</v>
       </c>
       <c r="P20" s="2">
-        <v>16.026261190565123</v>
+        <v>15.865501923269152</v>
       </c>
       <c r="Q20" s="2">
-        <v>61.88235294117647</v>
+        <v>61.529411764705884</v>
       </c>
       <c r="R20" s="2">
-        <v>57.70588235294118</v>
+        <v>57.352941176470594</v>
       </c>
       <c r="S20" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T20" s="2">
-        <v>21.85</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -3361,25 +3361,25 @@
         <v>38.82352941176471</v>
       </c>
       <c r="D21" s="3">
-        <v>11.10891089108911</v>
+        <v>10.05940594059406</v>
       </c>
       <c r="E21" s="3">
         <v>-3.44</v>
       </c>
       <c r="F21" s="3">
-        <v>-0.3838834786197487</v>
+        <v>-0.42545785802279146</v>
       </c>
       <c r="G21" s="3">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H21" s="3">
-        <v>41.09</v>
+        <v>38.66</v>
       </c>
       <c r="I21" s="3">
-        <v>-14.66</v>
+        <v>-16.12</v>
       </c>
       <c r="J21" s="3">
-        <v>-0.019708423756906745</v>
+        <v>-0.021632002869338838</v>
       </c>
       <c r="K21" s="3" t="b">
         <v>0</v>
@@ -3388,28 +3388,28 @@
         <v>55</v>
       </c>
       <c r="M21" s="3">
-        <v>-0.3700777601166534</v>
+        <v>-0.39562895553905664</v>
       </c>
       <c r="N21" s="3">
-        <v>-33.74139212228513</v>
+        <v>-33.676782250077466</v>
       </c>
       <c r="O21" s="3">
-        <v>4.705882352941177</v>
+        <v>3.5294117647058822</v>
       </c>
       <c r="P21" s="3">
         <v>52.10839414803409</v>
       </c>
       <c r="Q21" s="3">
-        <v>40.11764705882352</v>
+        <v>37.176470588235304</v>
       </c>
       <c r="R21" s="3">
-        <v>21.05882352941176</v>
+        <v>19.94117647058824</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>111</v>
       </c>
       <c r="T21" s="3">
-        <v>-30.16</v>
+        <v>-31.28</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -3429,49 +3429,49 @@
         <v>-0.24</v>
       </c>
       <c r="F22" s="1">
-        <v>-0.16247749883609502</v>
+        <v>-0.17882726156553108</v>
       </c>
       <c r="G22" s="1">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="H22" s="1">
-        <v>36.97</v>
+        <v>38.89</v>
       </c>
       <c r="I22" s="1">
-        <v>-1.74</v>
+        <v>-1.16</v>
       </c>
       <c r="J22" s="1">
-        <v>-0.015443370621383741</v>
+        <v>-0.014377725904286806</v>
       </c>
       <c r="K22" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L22" s="1">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M22" s="1">
-        <v>-0.15393110166751223</v>
+        <v>-0.16054503101098394</v>
       </c>
       <c r="N22" s="1">
-        <v>-12.126726277371016</v>
+        <v>-10.168389797270192</v>
       </c>
       <c r="O22" s="1">
-        <v>28.235294117647058</v>
+        <v>27.058823529411764</v>
       </c>
       <c r="P22" s="1">
         <v>19.455960650079966</v>
       </c>
       <c r="Q22" s="1">
-        <v>43.17647058823529</v>
+        <v>43.41176470588235</v>
       </c>
       <c r="R22" s="1">
-        <v>35.17647058823529</v>
+        <v>35.05882352941176</v>
       </c>
       <c r="S22" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T22" s="1">
-        <v>-17.93</v>
+        <v>-18.05</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -3491,49 +3491,49 @@
         <v>0.09</v>
       </c>
       <c r="F23" s="2">
-        <v>0.1163265158634346</v>
+        <v>0.24517715795272965</v>
       </c>
       <c r="G23" s="2">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="H23" s="2">
-        <v>69.68</v>
+        <v>78.3</v>
       </c>
       <c r="I23" s="2">
-        <v>9.47</v>
+        <v>19.29</v>
       </c>
       <c r="J23" s="2">
-        <v>0.01077845836789855</v>
+        <v>0.010395046789147466</v>
       </c>
       <c r="K23" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M23" s="2">
-        <v>0.12070928364219502</v>
+        <v>0.2557616072211517</v>
       </c>
       <c r="N23" s="2">
-        <v>15.337312253599702</v>
+        <v>31.462274025943383</v>
       </c>
       <c r="O23" s="2">
-        <v>70.58823529411765</v>
+        <v>84.70588235294117</v>
       </c>
       <c r="P23" s="2">
         <v>20.883293768118005</v>
       </c>
       <c r="Q23" s="2">
-        <v>64.35294117647058</v>
+        <v>66.35294117647058</v>
       </c>
       <c r="R23" s="2">
-        <v>52.94117647058824</v>
+        <v>57.05882352941176</v>
       </c>
       <c r="S23" s="2" t="s">
         <v>110</v>
       </c>
       <c r="T23" s="2">
-        <v>17.15</v>
+        <v>21.27</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -3553,19 +3553,19 @@
         <v>1.58</v>
       </c>
       <c r="F24" s="1">
-        <v>0.27883062135226305</v>
+        <v>0.3559061594649231</v>
       </c>
       <c r="G24" s="1">
-        <v>3.57</v>
+        <v>3.59</v>
       </c>
       <c r="H24" s="1">
-        <v>67.81</v>
+        <v>67.26</v>
       </c>
       <c r="I24" s="1">
-        <v>15.85</v>
+        <v>19.35</v>
       </c>
       <c r="J24" s="1">
-        <v>0.03594071848343393</v>
+        <v>0.042698758631470726</v>
       </c>
       <c r="K24" s="1" t="b">
         <v>0</v>
@@ -3574,28 +3574,28 @@
         <v>-69</v>
       </c>
       <c r="M24" s="1">
-        <v>0.3351491873093344</v>
+        <v>0.48051399403407347</v>
       </c>
       <c r="N24" s="1">
-        <v>36.78130262031365</v>
+        <v>53.937512707235534</v>
       </c>
       <c r="O24" s="1">
-        <v>88.23529411764706</v>
+        <v>94.11764705882352</v>
       </c>
       <c r="P24" s="1">
         <v>57.99224429263358</v>
       </c>
       <c r="Q24" s="1">
-        <v>51.76470588235295</v>
+        <v>52.70588235294118</v>
       </c>
       <c r="R24" s="1">
-        <v>39.529411764705884</v>
+        <v>41.52941176470589</v>
       </c>
       <c r="S24" s="1" t="s">
         <v>109</v>
       </c>
       <c r="T24" s="1">
-        <v>43.25</v>
+        <v>45.25</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -3615,19 +3615,19 @@
         <v>15.51</v>
       </c>
       <c r="F25" s="3">
-        <v>-0.35825644391981387</v>
+        <v>-0.34178268035836645</v>
       </c>
       <c r="G25" s="3">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="H25" s="3">
-        <v>44.11</v>
+        <v>45.62</v>
       </c>
       <c r="I25" s="3">
-        <v>-32.23</v>
+        <v>-30.61</v>
       </c>
       <c r="J25" s="3">
-        <v>-0.007836334056621033</v>
+        <v>-0.005656802949248415</v>
       </c>
       <c r="K25" s="3" t="b">
         <v>1</v>
@@ -3636,28 +3636,28 @@
         <v>34</v>
       </c>
       <c r="M25" s="3">
-        <v>-0.328234484635305</v>
+        <v>-0.2768326507566857</v>
       </c>
       <c r="N25" s="3">
-        <v>-29.557064574150292</v>
+        <v>-21.797151771840372</v>
       </c>
       <c r="O25" s="3">
-        <v>7.0588235294117645</v>
+        <v>14.117647058823529</v>
       </c>
       <c r="P25" s="3">
         <v>45.59139601172712</v>
       </c>
       <c r="Q25" s="3">
-        <v>15.999999999999998</v>
+        <v>17.058823529411768</v>
       </c>
       <c r="R25" s="3">
-        <v>1.3529411764705888</v>
+        <v>3.8235294117647083</v>
       </c>
       <c r="S25" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T25" s="3">
-        <v>-0.05</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -3677,19 +3677,19 @@
         <v>-0.85</v>
       </c>
       <c r="F26" s="3">
-        <v>-0.3928647242491275</v>
+        <v>-0.47826863127602764</v>
       </c>
       <c r="G26" s="3">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="H26" s="3">
-        <v>50.87</v>
+        <v>50.17</v>
       </c>
       <c r="I26" s="3">
-        <v>-8.78</v>
+        <v>-9.17</v>
       </c>
       <c r="J26" s="3">
-        <v>-0.021117207118913392</v>
+        <v>-0.016589914410062075</v>
       </c>
       <c r="K26" s="3" t="b">
         <v>0</v>
@@ -3698,10 +3698,10 @@
         <v>159</v>
       </c>
       <c r="M26" s="3">
-        <v>-0.34070978768187854</v>
+        <v>-0.3642452459752993</v>
       </c>
       <c r="N26" s="3">
-        <v>-30.804594878807638</v>
+        <v>-30.538411293701735</v>
       </c>
       <c r="O26" s="3">
         <v>5.88235294117647</v>
@@ -3710,16 +3710,16 @@
         <v>55.61259899184437</v>
       </c>
       <c r="Q26" s="3">
-        <v>16.47058823529412</v>
+        <v>18.11764705882353</v>
       </c>
       <c r="R26" s="3">
-        <v>-1.3529411764705905</v>
+        <v>-0.529411764705884</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T26" s="3">
-        <v>-30.19</v>
+        <v>-29.37</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -3739,19 +3739,19 @@
         <v>6.87</v>
       </c>
       <c r="F27" s="3">
-        <v>-0.45704082290160536</v>
+        <v>-0.4881430755122261</v>
       </c>
       <c r="G27" s="3">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="H27" s="3">
-        <v>35.76</v>
+        <v>39.53</v>
       </c>
       <c r="I27" s="3">
-        <v>-37.48</v>
+        <v>-36.02</v>
       </c>
       <c r="J27" s="3">
-        <v>-0.02833457505757826</v>
+        <v>-0.02614151145842167</v>
       </c>
       <c r="K27" s="3" t="b">
         <v>0</v>
@@ -3760,10 +3760,10 @@
         <v>7</v>
       </c>
       <c r="M27" s="3">
-        <v>-0.4206638503378939</v>
+        <v>-0.40875970599906075</v>
       </c>
       <c r="N27" s="3">
-        <v>-38.80000114440918</v>
+        <v>-34.98985729607787</v>
       </c>
       <c r="O27" s="3">
         <v>2.3529411764705883</v>
@@ -3772,16 +3772,16 @@
         <v>50.56910707785277</v>
       </c>
       <c r="Q27" s="3">
-        <v>11.411764705882351</v>
+        <v>12.117647058823529</v>
       </c>
       <c r="R27" s="3">
-        <v>-0.29411764705882604</v>
+        <v>-0.17647058823529704</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T27" s="3">
-        <v>-16.45</v>
+        <v>-16.34</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -3801,31 +3801,31 @@
         <v>2.19</v>
       </c>
       <c r="F28" s="1">
-        <v>-0.13784439903538875</v>
+        <v>-0.16759229370479933</v>
       </c>
       <c r="G28" s="1">
         <v>3.26</v>
       </c>
       <c r="H28" s="1">
-        <v>43.94</v>
+        <v>45.06</v>
       </c>
       <c r="I28" s="1">
-        <v>-15.84</v>
+        <v>-15.01</v>
       </c>
       <c r="J28" s="1">
-        <v>0.0069187697872931855</v>
+        <v>0.00752648863948191</v>
       </c>
       <c r="K28" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" s="1">
         <v>3</v>
       </c>
       <c r="M28" s="1">
-        <v>-0.08831912313539603</v>
+        <v>-0.058861133038282</v>
       </c>
       <c r="N28" s="1">
-        <v>-5.565528424159394</v>
+        <v>0</v>
       </c>
       <c r="O28" s="1">
         <v>43.529411764705884</v>
@@ -3834,7 +3834,7 @@
         <v>35.08771990976345</v>
       </c>
       <c r="Q28" s="1">
-        <v>43.294117647058826</v>
+        <v>43.64705882352941</v>
       </c>
       <c r="R28" s="1">
         <v>33.41176470588235</v>
@@ -3857,55 +3857,55 @@
         <v>36.470588235294116</v>
       </c>
       <c r="D29" s="1">
-        <v>83.17021276595746</v>
+        <v>81.95744680851065</v>
       </c>
       <c r="E29" s="1">
         <v>-4.83</v>
       </c>
       <c r="F29" s="1">
-        <v>-0.11463314202553478</v>
+        <v>-0.12997023012338427</v>
       </c>
       <c r="G29" s="1">
         <v>2.32</v>
       </c>
       <c r="H29" s="1">
-        <v>47.08</v>
+        <v>43.52</v>
       </c>
       <c r="I29" s="1">
-        <v>-11.1</v>
+        <v>-12.7</v>
       </c>
       <c r="J29" s="1">
-        <v>-0.006393793195820497</v>
+        <v>-0.0077674306022950355</v>
       </c>
       <c r="K29" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M29" s="1">
-        <v>-0.08570687468571603</v>
+        <v>-0.06646353451285203</v>
       </c>
       <c r="N29" s="1">
-        <v>-5.304303579191391</v>
+        <v>-0.760240147457008</v>
       </c>
       <c r="O29" s="1">
-        <v>44.70588235294118</v>
+        <v>41.17647058823529</v>
       </c>
       <c r="P29" s="1">
         <v>18.81663456064845</v>
       </c>
       <c r="Q29" s="1">
-        <v>50.470588235294116</v>
+        <v>48.23529411764706</v>
       </c>
       <c r="R29" s="1">
-        <v>44.76470588235294</v>
+        <v>43.35294117647059</v>
       </c>
       <c r="S29" s="1" t="s">
         <v>110</v>
       </c>
       <c r="T29" s="1">
-        <v>4.52</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -3919,55 +3919,55 @@
         <v>47.05882352941176</v>
       </c>
       <c r="D30" s="1">
-        <v>226.42272727272726</v>
+        <v>224.99545454545452</v>
       </c>
       <c r="E30" s="1">
         <v>1.22</v>
       </c>
       <c r="F30" s="1">
-        <v>-0.14823570800154484</v>
+        <v>-0.16000727780394192</v>
       </c>
       <c r="G30" s="1">
         <v>1.25</v>
       </c>
       <c r="H30" s="1">
-        <v>36.25</v>
+        <v>38.06</v>
       </c>
       <c r="I30" s="1">
-        <v>-9.64</v>
+        <v>-9.15</v>
       </c>
       <c r="J30" s="1">
-        <v>-0.011306743281542289</v>
+        <v>-0.01177318330114735</v>
       </c>
       <c r="K30" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L30" s="1">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M30" s="1">
-        <v>-0.14275724827809433</v>
+        <v>-0.14797949454437143</v>
       </c>
       <c r="N30" s="1">
-        <v>-11.009340938429224</v>
+        <v>-8.911836150608938</v>
       </c>
       <c r="O30" s="1">
-        <v>29.411764705882355</v>
+        <v>28.235294117647058</v>
       </c>
       <c r="P30" s="1">
         <v>18.121365335609003</v>
       </c>
       <c r="Q30" s="1">
-        <v>51.29411764705882</v>
+        <v>50.94117647058823</v>
       </c>
       <c r="R30" s="1">
-        <v>43.82352941176471</v>
+        <v>43.35294117647059</v>
       </c>
       <c r="S30" s="1" t="s">
         <v>111</v>
       </c>
       <c r="T30" s="1">
-        <v>-4.65</v>
+        <v>-5.12</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -3987,111 +3987,111 @@
         <v>0.39</v>
       </c>
       <c r="F31" s="1">
-        <v>-0.17360639642433562</v>
+        <v>-0.1566270157683553</v>
       </c>
       <c r="G31" s="1">
         <v>1.47</v>
       </c>
       <c r="H31" s="1">
-        <v>48.46</v>
+        <v>47.87</v>
       </c>
       <c r="I31" s="1">
-        <v>-1.79</v>
+        <v>-2.04</v>
       </c>
       <c r="J31" s="1">
-        <v>-0.008693619379437459</v>
+        <v>-0.009828331118262638</v>
       </c>
       <c r="K31" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L31" s="1">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="M31" s="1">
-        <v>-0.16330689214424865</v>
+        <v>-0.13401478324036276</v>
       </c>
       <c r="N31" s="1">
-        <v>-13.064305325044659</v>
+        <v>-7.51536502020808</v>
       </c>
       <c r="O31" s="1">
-        <v>25.882352941176475</v>
+        <v>31.76470588235294</v>
       </c>
       <c r="P31" s="1">
         <v>29.54918623383928</v>
       </c>
       <c r="Q31" s="1">
-        <v>54.941176470588225</v>
+        <v>53.882352941176464</v>
       </c>
       <c r="R31" s="1">
-        <v>38.294117647058826</v>
+        <v>39.588235294117645</v>
       </c>
       <c r="S31" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T31" s="1">
-        <v>-9.75</v>
+        <v>-8.46</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="1">
         <v>-2.58</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="1">
         <v>12.941176470588237</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="1">
         <v>8.848837209302324</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="1">
         <v>3.57</v>
       </c>
-      <c r="F32" s="3">
-        <v>-0.13886547011266287</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="F32" s="1">
+        <v>-0.07147154091015032</v>
+      </c>
+      <c r="G32" s="1">
         <v>1.62</v>
       </c>
-      <c r="H32" s="3">
-        <v>41.48</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-7.16</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-0.015827286358028467</v>
-      </c>
-      <c r="K32" s="3" t="b">
+      <c r="H32" s="1">
+        <v>44.16</v>
+      </c>
+      <c r="I32" s="1">
+        <v>-5.87</v>
+      </c>
+      <c r="J32" s="1">
+        <v>-0.015087942996531436</v>
+      </c>
+      <c r="K32" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="1">
         <v>20</v>
       </c>
-      <c r="M32" s="3">
-        <v>-0.12527888999850556</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-9.26150511047035</v>
-      </c>
-      <c r="O32" s="3">
-        <v>32.94117647058823</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="M32" s="1">
+        <v>-0.04164263842641547</v>
+      </c>
+      <c r="N32" s="1">
+        <v>1.7218494611866562</v>
+      </c>
+      <c r="O32" s="1">
+        <v>51.76470588235295</v>
+      </c>
+      <c r="P32" s="1">
         <v>26.613703173358488</v>
       </c>
-      <c r="Q32" s="3">
-        <v>34.11764705882353</v>
-      </c>
-      <c r="R32" s="3">
-        <v>26.941176470588225</v>
-      </c>
-      <c r="S32" s="3" t="s">
+      <c r="Q32" s="1">
+        <v>34.705882352941174</v>
+      </c>
+      <c r="R32" s="1">
+        <v>32.588235294117645</v>
+      </c>
+      <c r="S32" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="T32" s="3">
-        <v>-4.95</v>
+      <c r="T32" s="1">
+        <v>0.7</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -4111,19 +4111,19 @@
         <v>0.24</v>
       </c>
       <c r="F33" s="2">
-        <v>0.2666208096967232</v>
+        <v>0.30184740943249877</v>
       </c>
       <c r="G33" s="2">
         <v>1.1</v>
       </c>
       <c r="H33" s="2">
-        <v>53.45</v>
+        <v>58.36</v>
       </c>
       <c r="I33" s="2">
-        <v>14.53</v>
+        <v>16.75</v>
       </c>
       <c r="J33" s="2">
-        <v>0.024272774655738058</v>
+        <v>0.024220162899023054</v>
       </c>
       <c r="K33" s="2" t="b">
         <v>0</v>
@@ -4132,28 +4132,28 @@
         <v>81</v>
       </c>
       <c r="M33" s="2">
-        <v>0.2688121935861034</v>
+        <v>0.306658522736327</v>
       </c>
       <c r="N33" s="2">
-        <v>30.147603247990556</v>
+        <v>36.55196557746089</v>
       </c>
       <c r="O33" s="2">
-        <v>85.88235294117646</v>
+        <v>87.05882352941177</v>
       </c>
       <c r="P33" s="2">
         <v>23.38443607454554</v>
       </c>
       <c r="Q33" s="2">
-        <v>66.58823529411765</v>
+        <v>68.11764705882354</v>
       </c>
       <c r="R33" s="2">
-        <v>60.11764705882352</v>
+        <v>60.47058823529413</v>
       </c>
       <c r="S33" s="2" t="s">
         <v>110</v>
       </c>
       <c r="T33" s="2">
-        <v>24.32</v>
+        <v>24.68</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -4173,49 +4173,49 @@
         <v>2.34</v>
       </c>
       <c r="F34" s="1">
-        <v>-0.08750618822022042</v>
+        <v>-0.0538363290873837</v>
       </c>
       <c r="G34" s="1">
         <v>1.21</v>
       </c>
       <c r="H34" s="1">
-        <v>58.02</v>
+        <v>60.46</v>
       </c>
       <c r="I34" s="1">
-        <v>4.77</v>
+        <v>5.8</v>
       </c>
       <c r="J34" s="1">
-        <v>-0.004614332104260911</v>
+        <v>-0.004138124741324778</v>
       </c>
       <c r="K34" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" s="1">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M34" s="1">
-        <v>-0.08290428205252198</v>
+        <v>-0.04373299114934448</v>
       </c>
       <c r="N34" s="1">
-        <v>-5.0240443158719845</v>
+        <v>1.5128141888937587</v>
       </c>
       <c r="O34" s="1">
-        <v>47.05882352941176</v>
+        <v>50.588235294117645</v>
       </c>
       <c r="P34" s="1">
         <v>21.09433056126816</v>
       </c>
       <c r="Q34" s="1">
-        <v>50.35294117647059</v>
+        <v>51.41176470588235</v>
       </c>
       <c r="R34" s="1">
-        <v>39.23529411764706</v>
+        <v>40.17647058823529</v>
       </c>
       <c r="S34" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T34" s="1">
-        <v>-7.59</v>
+        <v>-6.65</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -4235,49 +4235,49 @@
         <v>-0.47</v>
       </c>
       <c r="F35" s="1">
-        <v>-0.09003772464392384</v>
+        <v>-0.05316189641702512</v>
       </c>
       <c r="G35" s="1">
-        <v>0.95</v>
+        <v>0.94</v>
       </c>
       <c r="H35" s="1">
-        <v>32.01</v>
+        <v>33.06</v>
       </c>
       <c r="I35" s="1">
-        <v>-18.08</v>
+        <v>-17.53</v>
       </c>
       <c r="J35" s="1">
-        <v>-0.00036953627848923315</v>
+        <v>-0.0013001789228728464</v>
       </c>
       <c r="K35" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L35" s="1">
-        <v>-56</v>
+        <v>-57</v>
       </c>
       <c r="M35" s="1">
-        <v>-0.09113341658861396</v>
+        <v>-0.05604856439932204</v>
       </c>
       <c r="N35" s="1">
-        <v>-5.846957769481191</v>
+        <v>0.2812568638960001</v>
       </c>
       <c r="O35" s="1">
-        <v>42.35294117647059</v>
+        <v>44.70588235294118</v>
       </c>
       <c r="P35" s="1">
-        <v>23.054125788710962</v>
+        <v>19.973884530776573</v>
       </c>
       <c r="Q35" s="1">
-        <v>44.11764705882353</v>
+        <v>43.529411764705884</v>
       </c>
       <c r="R35" s="1">
-        <v>40.1764705882353</v>
+        <v>41.23529411764706</v>
       </c>
       <c r="S35" s="1" t="s">
         <v>101</v>
       </c>
       <c r="T35" s="1">
-        <v>17.68</v>
+        <v>18.74</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -4297,49 +4297,49 @@
         <v>-1.3</v>
       </c>
       <c r="F36" s="1">
-        <v>-0.10611758218520727</v>
+        <v>-0.11334064795685607</v>
       </c>
       <c r="G36" s="1">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="H36" s="1">
-        <v>38.78</v>
+        <v>43.04</v>
       </c>
       <c r="I36" s="1">
-        <v>-11.92</v>
+        <v>-9.91</v>
       </c>
       <c r="J36" s="1">
-        <v>0.00604092659304731</v>
+        <v>0.004948993697604279</v>
       </c>
       <c r="K36" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L36" s="1">
-        <v>-20</v>
+        <v>-18</v>
       </c>
       <c r="M36" s="1">
-        <v>-0.103268783129013</v>
+        <v>-0.10756731199226222</v>
       </c>
       <c r="N36" s="1">
-        <v>-7.060494423521095</v>
+        <v>-4.870617895398018</v>
       </c>
       <c r="O36" s="1">
-        <v>38.82352941176471</v>
+        <v>35.294117647058826</v>
       </c>
       <c r="P36" s="1">
         <v>26.730280409441182</v>
       </c>
       <c r="Q36" s="1">
-        <v>49.17647058823529</v>
+        <v>49.52941176470588</v>
       </c>
       <c r="R36" s="1">
-        <v>39.411764705882355</v>
+        <v>38.00000000000001</v>
       </c>
       <c r="S36" s="1" t="s">
         <v>108</v>
       </c>
       <c r="T36" s="1">
-        <v>12.46</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -4359,19 +4359,19 @@
         <v>-3.26</v>
       </c>
       <c r="F37" s="2">
-        <v>0.19408671098118957</v>
+        <v>0.17046413001919664</v>
       </c>
       <c r="G37" s="2">
         <v>1.28</v>
       </c>
       <c r="H37" s="2">
-        <v>39.81</v>
+        <v>40.4</v>
       </c>
       <c r="I37" s="2">
-        <v>3.7</v>
+        <v>4.04</v>
       </c>
       <c r="J37" s="2">
-        <v>0.014291683203633186</v>
+        <v>0.01343969144514559</v>
       </c>
       <c r="K37" s="2" t="b">
         <v>0</v>
@@ -4380,13 +4380,13 @@
         <v>-107</v>
       </c>
       <c r="M37" s="2">
-        <v>0.20022258587145414</v>
+        <v>0.1839352472699156</v>
       </c>
       <c r="N37" s="2">
-        <v>23.288642476525613</v>
+        <v>24.27963803081976</v>
       </c>
       <c r="O37" s="2">
-        <v>80</v>
+        <v>81.17647058823529</v>
       </c>
       <c r="P37" s="2">
         <v>20.1020772277769</v>
@@ -4395,13 +4395,13 @@
         <v>52.23529411764706</v>
       </c>
       <c r="R37" s="2">
-        <v>52.94117647058823</v>
+        <v>53.29411764705882</v>
       </c>
       <c r="S37" s="2" t="s">
         <v>111</v>
       </c>
       <c r="T37" s="2">
-        <v>23.12</v>
+        <v>23.48</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -4421,31 +4421,31 @@
         <v>3.13</v>
       </c>
       <c r="F38" s="2">
-        <v>0.35075515836149834</v>
+        <v>0.40770262130266477</v>
       </c>
       <c r="G38" s="2">
         <v>1.21</v>
       </c>
       <c r="H38" s="2">
-        <v>59.71</v>
+        <v>65.03</v>
       </c>
       <c r="I38" s="2">
-        <v>60.33</v>
+        <v>69.06</v>
       </c>
       <c r="J38" s="2">
-        <v>0.022221061202637803</v>
+        <v>0.024172783695703096</v>
       </c>
       <c r="K38" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L38" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="M38" s="2">
-        <v>0.3553570645291968</v>
+        <v>0.41780595924070396</v>
       </c>
       <c r="N38" s="2">
-        <v>38.80209034229988</v>
+        <v>47.66670922789859</v>
       </c>
       <c r="O38" s="2">
         <v>90.58823529411765</v>
@@ -4454,16 +4454,16 @@
         <v>17.802507034008837</v>
       </c>
       <c r="Q38" s="2">
-        <v>73.41176470588233</v>
+        <v>74.94117647058823</v>
       </c>
       <c r="R38" s="2">
-        <v>65.52941176470588</v>
+        <v>65.76470588235294</v>
       </c>
       <c r="S38" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T38" s="2">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -4483,19 +4483,19 @@
         <v>-1.29</v>
       </c>
       <c r="F39" s="1">
-        <v>-0.01788636127597297</v>
+        <v>-0.04491288216402424</v>
       </c>
       <c r="G39" s="1">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="H39" s="1">
-        <v>35.01</v>
+        <v>39.12</v>
       </c>
       <c r="I39" s="1">
-        <v>-7.93</v>
+        <v>-6.48</v>
       </c>
       <c r="J39" s="1">
-        <v>-0.004630991566639146</v>
+        <v>-0.005118805496403966</v>
       </c>
       <c r="K39" s="1" t="b">
         <v>1</v>
@@ -4504,28 +4504,28 @@
         <v>-1</v>
       </c>
       <c r="M39" s="1">
-        <v>-0.0150375622197787</v>
+        <v>-0.039139546199430386</v>
       </c>
       <c r="N39" s="1">
-        <v>1.762627667402337</v>
+        <v>1.972158683885172</v>
       </c>
       <c r="O39" s="1">
-        <v>51.76470588235295</v>
+        <v>54.11764705882353</v>
       </c>
       <c r="P39" s="1">
         <v>30.28933322215756</v>
       </c>
       <c r="Q39" s="1">
-        <v>43.529411764705884</v>
+        <v>44.11764705882353</v>
       </c>
       <c r="R39" s="1">
-        <v>39.76470588235295</v>
+        <v>40.352941176470594</v>
       </c>
       <c r="S39" s="1" t="s">
         <v>112</v>
       </c>
       <c r="T39" s="1">
-        <v>13.97</v>
+        <v>14.56</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -4545,19 +4545,19 @@
         <v>4.43</v>
       </c>
       <c r="F40" s="1">
-        <v>0.5674113238863513</v>
+        <v>0.5549316354205458</v>
       </c>
       <c r="G40" s="1">
-        <v>0.58</v>
+        <v>0.71</v>
       </c>
       <c r="H40" s="1">
-        <v>65.12</v>
+        <v>64.25</v>
       </c>
       <c r="I40" s="1">
-        <v>15.32</v>
+        <v>16.25</v>
       </c>
       <c r="J40" s="1">
-        <v>0.03709642901680366</v>
+        <v>0.039596274222561394</v>
       </c>
       <c r="K40" s="1" t="b">
         <v>1</v>
@@ -4566,13 +4566,13 @@
         <v>-21</v>
       </c>
       <c r="M40" s="1">
-        <v>0.5582075115509544</v>
+        <v>0.540979406839444</v>
       </c>
       <c r="N40" s="1">
-        <v>59.087135044475644</v>
+        <v>59.9840539877726</v>
       </c>
       <c r="O40" s="1">
-        <v>97.6470588235294</v>
+        <v>95.29411764705881</v>
       </c>
       <c r="P40" s="1">
         <v>51.940889187924654</v>
@@ -4581,13 +4581,13 @@
         <v>57.1764705882353</v>
       </c>
       <c r="R40" s="1">
-        <v>47.88235294117647</v>
+        <v>47.47058823529412</v>
       </c>
       <c r="S40" s="1" t="s">
         <v>113</v>
       </c>
       <c r="T40" s="1">
-        <v>39.41</v>
+        <v>38.99</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -4607,19 +4607,19 @@
         <v>0.01</v>
       </c>
       <c r="F41" s="3">
-        <v>-0.08949428988061581</v>
+        <v>-0.11093094280679497</v>
       </c>
       <c r="G41" s="3">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="H41" s="3">
-        <v>44.93</v>
+        <v>41.3</v>
       </c>
       <c r="I41" s="3">
-        <v>-10.28</v>
+        <v>-11.73</v>
       </c>
       <c r="J41" s="3">
-        <v>-0.017788954477799407</v>
+        <v>-0.018190576248909927</v>
       </c>
       <c r="K41" s="3" t="b">
         <v>1</v>
@@ -4628,28 +4628,28 @@
         <v>4</v>
       </c>
       <c r="M41" s="3">
-        <v>-0.08467324532397935</v>
+        <v>-0.10082760486875575</v>
       </c>
       <c r="N41" s="3">
-        <v>-5.200940643017723</v>
+        <v>-4.196647183047376</v>
       </c>
       <c r="O41" s="3">
-        <v>45.88235294117647</v>
+        <v>36.470588235294116</v>
       </c>
       <c r="P41" s="3">
         <v>30.769232468942608</v>
       </c>
       <c r="Q41" s="3">
-        <v>24.352941176470587</v>
+        <v>22.11764705882353</v>
       </c>
       <c r="R41" s="3">
-        <v>21.70588235294118</v>
+        <v>18.411764705882355</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>107</v>
       </c>
       <c r="T41" s="3">
-        <v>-14.94</v>
+        <v>-18.23</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -4669,19 +4669,19 @@
         <v>4.33</v>
       </c>
       <c r="F42" s="1">
-        <v>-0.1271099460459196</v>
+        <v>-0.14897076190873235</v>
       </c>
       <c r="G42" s="1">
         <v>0.31</v>
       </c>
       <c r="H42" s="1">
-        <v>25.48</v>
+        <v>23.09</v>
       </c>
       <c r="I42" s="1">
-        <v>-10.74</v>
+        <v>-11.52</v>
       </c>
       <c r="J42" s="1">
-        <v>-0.014511416874836373</v>
+        <v>-0.014496939696363138</v>
       </c>
       <c r="K42" s="1" t="b">
         <v>0</v>
@@ -4690,28 +4690,28 @@
         <v>16</v>
       </c>
       <c r="M42" s="1">
-        <v>-0.14223049488264305</v>
+        <v>-0.18216744370514693</v>
       </c>
       <c r="N42" s="1">
-        <v>-10.956665598884099</v>
+        <v>-12.330631066686488</v>
       </c>
       <c r="O42" s="1">
-        <v>30.58823529411765</v>
+        <v>25.882352941176475</v>
       </c>
       <c r="P42" s="1">
-        <v>17.091741705344468</v>
+        <v>17.903820641360944</v>
       </c>
       <c r="Q42" s="1">
-        <v>35.88235294117647</v>
+        <v>35.529411764705884</v>
       </c>
       <c r="R42" s="1">
-        <v>33.294117647058826</v>
+        <v>31.41176470588236</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>111</v>
       </c>
       <c r="T42" s="1">
-        <v>-2.19</v>
+        <v>-4.08</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -4731,19 +4731,19 @@
         <v>8.78</v>
       </c>
       <c r="F43" s="2">
-        <v>0.20769404139812686</v>
+        <v>0.1466821730212451</v>
       </c>
       <c r="G43" s="2">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="H43" s="2">
-        <v>51.49</v>
+        <v>46.42</v>
       </c>
       <c r="I43" s="2">
-        <v>18.22</v>
+        <v>13.33</v>
       </c>
       <c r="J43" s="2">
-        <v>0.011303345521781681</v>
+        <v>0.008310784566949897</v>
       </c>
       <c r="K43" s="2" t="b">
         <v>0</v>
@@ -4752,28 +4752,28 @@
         <v>18</v>
       </c>
       <c r="M43" s="2">
-        <v>0.2153638850109576</v>
+        <v>0.16303995825426099</v>
       </c>
       <c r="N43" s="2">
-        <v>24.80277239047597</v>
+        <v>22.190109129254292</v>
       </c>
       <c r="O43" s="2">
-        <v>83.52941176470588</v>
+        <v>78.82352941176471</v>
       </c>
       <c r="P43" s="2">
         <v>24.82490242340647</v>
       </c>
       <c r="Q43" s="2">
-        <v>65.52941176470588</v>
+        <v>61.647058823529406</v>
       </c>
       <c r="R43" s="2">
-        <v>58.64705882352942</v>
+        <v>56.76470588235294</v>
       </c>
       <c r="S43" s="2" t="s">
         <v>114</v>
       </c>
       <c r="T43" s="2">
-        <v>6.27</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -4793,49 +4793,49 @@
         <v>-0.69</v>
       </c>
       <c r="F44" s="2">
-        <v>0.11192113827705684</v>
+        <v>0.1399912326229593</v>
       </c>
       <c r="G44" s="2">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="H44" s="2">
-        <v>40.81</v>
+        <v>52.16</v>
       </c>
       <c r="I44" s="2">
-        <v>-1.15</v>
+        <v>6.67</v>
       </c>
       <c r="J44" s="2">
-        <v>0.00694695478308402</v>
+        <v>0.007072447098323006</v>
       </c>
       <c r="K44" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="M44" s="2">
-        <v>0.14785983406289227</v>
+        <v>0.21841237947535896</v>
       </c>
       <c r="N44" s="2">
-        <v>18.052367295669427</v>
+        <v>27.727351251364098</v>
       </c>
       <c r="O44" s="2">
-        <v>74.11764705882354</v>
+        <v>83.52941176470588</v>
       </c>
       <c r="P44" s="2">
         <v>25.276100184761987</v>
       </c>
       <c r="Q44" s="2">
-        <v>55.882352941176464</v>
+        <v>60.11764705882353</v>
       </c>
       <c r="R44" s="2">
-        <v>53.88235294117648</v>
+        <v>56.470588235294116</v>
       </c>
       <c r="S44" s="2" t="s">
         <v>103</v>
       </c>
       <c r="T44" s="2">
-        <v>19.07</v>
+        <v>21.65</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
@@ -4855,49 +4855,49 @@
         <v>1.03</v>
       </c>
       <c r="F45" s="1">
-        <v>-0.004389269728821227</v>
+        <v>0.029717044134122655</v>
       </c>
       <c r="G45" s="1">
         <v>1.45</v>
       </c>
       <c r="H45" s="1">
-        <v>50.15</v>
+        <v>53.77</v>
       </c>
       <c r="I45" s="1">
-        <v>6.38</v>
+        <v>7.92</v>
       </c>
       <c r="J45" s="1">
-        <v>0.002299682623178883</v>
+        <v>0.0024730901845549935</v>
       </c>
       <c r="K45" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="1">
         <v>195</v>
       </c>
       <c r="M45" s="1">
-        <v>0.005471957773389713</v>
+        <v>0.051367054001349555</v>
       </c>
       <c r="N45" s="1">
-        <v>3.8135796667191753</v>
+        <v>11.022818703963162</v>
       </c>
       <c r="O45" s="1">
-        <v>56.470588235294116</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="P45" s="1">
         <v>17.57882034058413</v>
       </c>
       <c r="Q45" s="1">
-        <v>47.411764705882355</v>
+        <v>48.23529411764706</v>
       </c>
       <c r="R45" s="1">
-        <v>41.76470588235294</v>
+        <v>44.11764705882353</v>
       </c>
       <c r="S45" s="1" t="s">
         <v>109</v>
       </c>
       <c r="T45" s="1">
-        <v>-2.56</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
@@ -4917,19 +4917,19 @@
         <v>4.52</v>
       </c>
       <c r="F46" s="3">
-        <v>-0.3430157444441759</v>
+        <v>-0.33191721542388575</v>
       </c>
       <c r="G46" s="3">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="H46" s="3">
-        <v>38.3</v>
+        <v>39.66</v>
       </c>
       <c r="I46" s="3">
-        <v>-29.97</v>
+        <v>-29.26</v>
       </c>
       <c r="J46" s="3">
-        <v>-0.011057260488990146</v>
+        <v>-0.010799170236480702</v>
       </c>
       <c r="K46" s="3" t="b">
         <v>1</v>
@@ -4938,28 +4938,28 @@
         <v>17</v>
       </c>
       <c r="M46" s="3">
-        <v>-0.3261420884959483</v>
+        <v>-0.2958338656451742</v>
       </c>
       <c r="N46" s="3">
-        <v>-29.34782496021462</v>
+        <v>-23.69727326068923</v>
       </c>
       <c r="O46" s="3">
-        <v>8.235294117647058</v>
+        <v>10.588235294117647</v>
       </c>
       <c r="P46" s="3">
         <v>54.33673655574689</v>
       </c>
       <c r="Q46" s="3">
-        <v>43.99999999999999</v>
+        <v>43.647058823529406</v>
       </c>
       <c r="R46" s="3">
-        <v>25.47058823529411</v>
+        <v>26.05882352941176</v>
       </c>
       <c r="S46" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T46" s="3">
-        <v>4.43</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
@@ -4979,19 +4979,19 @@
         <v>2.57</v>
       </c>
       <c r="F47" s="1">
-        <v>0.04936994662389097</v>
+        <v>0.01831102006304998</v>
       </c>
       <c r="G47" s="1">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="H47" s="1">
-        <v>45.21</v>
+        <v>47.76</v>
       </c>
       <c r="I47" s="1">
-        <v>1.43</v>
+        <v>2.59</v>
       </c>
       <c r="J47" s="1">
-        <v>0.017196094279245757</v>
+        <v>0.017313755813952298</v>
       </c>
       <c r="K47" s="1" t="b">
         <v>1</v>
@@ -5000,28 +5000,28 @@
         <v>-56</v>
       </c>
       <c r="M47" s="1">
-        <v>0.05857375895928785</v>
+        <v>0.038036584608745594</v>
       </c>
       <c r="N47" s="1">
-        <v>9.123759785308987</v>
+        <v>9.689771764702748</v>
       </c>
       <c r="O47" s="1">
-        <v>64.70588235294117</v>
+        <v>62.35294117647059</v>
       </c>
       <c r="P47" s="1">
-        <v>31.953867028493892</v>
+        <v>30.777935412994907</v>
       </c>
       <c r="Q47" s="1">
-        <v>50.705882352941174</v>
+        <v>51.41176470588235</v>
       </c>
       <c r="R47" s="1">
-        <v>42.882352941176464</v>
+        <v>42.411764705882355</v>
       </c>
       <c r="S47" s="1" t="s">
         <v>109</v>
       </c>
       <c r="T47" s="1">
-        <v>17.03</v>
+        <v>16.56</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
@@ -5041,19 +5041,19 @@
         <v>0.66</v>
       </c>
       <c r="F48" s="2">
-        <v>0.12913228124481538</v>
+        <v>0.08857843283151749</v>
       </c>
       <c r="G48" s="2">
         <v>1.61</v>
       </c>
       <c r="H48" s="2">
-        <v>57.76</v>
+        <v>57.81</v>
       </c>
       <c r="I48" s="2">
-        <v>30.02</v>
+        <v>30.4</v>
       </c>
       <c r="J48" s="2">
-        <v>0.012049853895436924</v>
+        <v>0.011006532885688187</v>
       </c>
       <c r="K48" s="2" t="b">
         <v>1</v>
@@ -5062,28 +5062,28 @@
         <v>243</v>
       </c>
       <c r="M48" s="2">
-        <v>0.14249972297003466</v>
+        <v>0.11792622398486952</v>
       </c>
       <c r="N48" s="2">
-        <v>17.51635618638368</v>
+        <v>17.678735702315144</v>
       </c>
       <c r="O48" s="2">
         <v>72.94117647058823</v>
       </c>
       <c r="P48" s="2">
-        <v>22.881696991902864</v>
+        <v>21.006318468965095</v>
       </c>
       <c r="Q48" s="2">
-        <v>65.64705882352942</v>
+        <v>64.94117647058825</v>
       </c>
       <c r="R48" s="2">
-        <v>54.23529411764706</v>
+        <v>54.11764705882353</v>
       </c>
       <c r="S48" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T48" s="2">
-        <v>4.97</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
@@ -5103,19 +5103,19 @@
         <v>-11.2</v>
       </c>
       <c r="F49" s="2">
-        <v>0.1524975552342094</v>
+        <v>0.16839141657281478</v>
       </c>
       <c r="G49" s="2">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H49" s="2">
-        <v>48.29</v>
+        <v>56.3</v>
       </c>
       <c r="I49" s="2">
-        <v>-5.76</v>
+        <v>0.13</v>
       </c>
       <c r="J49" s="2">
-        <v>0.01968426452911071</v>
+        <v>0.01968550258408668</v>
       </c>
       <c r="K49" s="2" t="b">
         <v>0</v>
@@ -5124,28 +5124,28 @@
         <v>-7</v>
       </c>
       <c r="M49" s="2">
-        <v>0.15403152395677555</v>
+        <v>0.17224030721587735</v>
       </c>
       <c r="N49" s="2">
-        <v>18.669536285057763</v>
+        <v>23.110144025415934</v>
       </c>
       <c r="O49" s="2">
-        <v>76.47058823529412</v>
+        <v>80</v>
       </c>
       <c r="P49" s="2">
         <v>31.00158698078384</v>
       </c>
       <c r="Q49" s="2">
-        <v>62.58823529411765</v>
+        <v>65.05882352941177</v>
       </c>
       <c r="R49" s="2">
-        <v>56.58823529411765</v>
+        <v>57.41176470588236</v>
       </c>
       <c r="S49" s="2" t="s">
         <v>102</v>
       </c>
       <c r="T49" s="2">
-        <v>25.49</v>
+        <v>26.31</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
@@ -5165,19 +5165,19 @@
         <v>12.86</v>
       </c>
       <c r="F50" s="3">
-        <v>-0.2553528301595756</v>
+        <v>-0.35061372518661527</v>
       </c>
       <c r="G50" s="3">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="H50" s="3">
-        <v>61.66</v>
+        <v>59.46</v>
       </c>
       <c r="I50" s="3">
-        <v>17.4</v>
+        <v>15.1</v>
       </c>
       <c r="J50" s="3">
-        <v>0.004022777169526145</v>
+        <v>0.005966274501828959</v>
       </c>
       <c r="K50" s="3" t="b">
         <v>0</v>
@@ -5186,19 +5186,19 @@
         <v>69</v>
       </c>
       <c r="M50" s="3">
-        <v>-0.19333666609011568</v>
+        <v>-0.21301588469712873</v>
       </c>
       <c r="N50" s="3">
-        <v>-16.067282719631365</v>
+        <v>-15.41547516588467</v>
       </c>
       <c r="O50" s="3">
-        <v>23.52941176470588</v>
+        <v>22.35294117647059</v>
       </c>
       <c r="P50" s="3">
         <v>41.201484669672254</v>
       </c>
       <c r="Q50" s="3">
-        <v>53.05882352941176</v>
+        <v>52.47058823529412</v>
       </c>
       <c r="R50" s="3">
         <v>25.764705882352942</v>
@@ -5225,19 +5225,19 @@
         <v>14.41</v>
       </c>
       <c r="F51" s="1">
-        <v>0.19409276915417073</v>
+        <v>0.08880189473805797</v>
       </c>
       <c r="G51" s="1">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="H51" s="1">
-        <v>73.35</v>
+        <v>63.45</v>
       </c>
       <c r="I51" s="1">
-        <v>56.44</v>
+        <v>43.75</v>
       </c>
       <c r="J51" s="1">
-        <v>0.055910643616748225</v>
+        <v>0.05712275038086046</v>
       </c>
       <c r="K51" s="1" t="b">
         <v>0</v>
@@ -5246,22 +5246,22 @@
         <v>14</v>
       </c>
       <c r="M51" s="1">
-        <v>0.20921331799089415</v>
+        <v>0.1277719124990664</v>
       </c>
       <c r="N51" s="1">
-        <v>24.18771568846962</v>
+        <v>18.66330455373483</v>
       </c>
       <c r="O51" s="1">
-        <v>81.17647058823529</v>
+        <v>75.29411764705883</v>
       </c>
       <c r="P51" s="1">
         <v>38.38748944617691</v>
       </c>
       <c r="Q51" s="1">
-        <v>57.76470588235294</v>
+        <v>55.647058823529406</v>
       </c>
       <c r="R51" s="1">
-        <v>41.99999999999999</v>
+        <v>40.23529411764706</v>
       </c>
       <c r="S51" s="1" t="s">
         <v>97</v>
@@ -5285,19 +5285,19 @@
         <v>-5.32</v>
       </c>
       <c r="F52" s="3">
-        <v>-0.15357333799365053</v>
+        <v>-0.09322290450599283</v>
       </c>
       <c r="G52" s="3">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="H52" s="3">
-        <v>37.66</v>
+        <v>41.69</v>
       </c>
       <c r="I52" s="3">
-        <v>-33.68</v>
+        <v>-31.64</v>
       </c>
       <c r="J52" s="3">
-        <v>-0.014884544949434263</v>
+        <v>-0.014901649060531279</v>
       </c>
       <c r="K52" s="3" t="b">
         <v>0</v>
@@ -5306,22 +5306,22 @@
         <v>-106</v>
       </c>
       <c r="M52" s="3">
-        <v>-0.1553264451051547</v>
+        <v>-0.09803401780982102</v>
       </c>
       <c r="N52" s="3">
-        <v>-12.26626062113526</v>
+        <v>-3.917288477153896</v>
       </c>
       <c r="O52" s="3">
-        <v>27.058823529411764</v>
+        <v>37.64705882352941</v>
       </c>
       <c r="P52" s="3">
         <v>34.68082090497681</v>
       </c>
       <c r="Q52" s="3">
-        <v>32.8235294117647</v>
+        <v>33.88235294117647</v>
       </c>
       <c r="R52" s="3">
-        <v>25.000000000000004</v>
+        <v>28.35294117647059</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>114</v>
@@ -5345,43 +5345,43 @@
         <v>-0.87</v>
       </c>
       <c r="F53" s="3">
-        <v>-0.18529050424936652</v>
+        <v>-0.02853783888377522</v>
       </c>
       <c r="G53" s="3">
         <v>0</v>
       </c>
       <c r="H53" s="3">
-        <v>59.07</v>
+        <v>57.24</v>
       </c>
       <c r="I53" s="3">
-        <v>8</v>
+        <v>6.47</v>
       </c>
       <c r="J53" s="3">
-        <v>-0.0033033594136436216</v>
+        <v>-0.00028338611462836165</v>
       </c>
       <c r="K53" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L53" s="3">
-        <v>1744</v>
+        <v>1747</v>
       </c>
       <c r="M53" s="3">
-        <v>-0.2072043431431686</v>
+        <v>-0.07664897192205722</v>
       </c>
       <c r="N53" s="3">
-        <v>-17.454050424936653</v>
+        <v>-1.7787838883775209</v>
       </c>
       <c r="O53" s="3">
-        <v>22.35294117647059</v>
+        <v>38.82352941176471</v>
       </c>
       <c r="P53" s="3">
         <v>48.781873808753</v>
       </c>
       <c r="Q53" s="3">
-        <v>39.52941176470589</v>
+        <v>39.05882352941177</v>
       </c>
       <c r="R53" s="3">
-        <v>16.764705882352942</v>
+        <v>22.176470588235297</v>
       </c>
       <c r="S53" s="3" t="s">
         <v>96</v>
@@ -5405,49 +5405,49 @@
         <v>-1.38</v>
       </c>
       <c r="F54" s="1">
-        <v>0.0007133736567358911</v>
+        <v>-0.04717718517893808</v>
       </c>
       <c r="G54" s="1">
         <v>0.98</v>
       </c>
       <c r="H54" s="1">
-        <v>42.32</v>
+        <v>42.09</v>
       </c>
       <c r="I54" s="1">
-        <v>3.37</v>
+        <v>3.15</v>
       </c>
       <c r="J54" s="1">
-        <v>0.003759356894933924</v>
+        <v>0.004441741139798914</v>
       </c>
       <c r="K54" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L54" s="1">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M54" s="1">
-        <v>0.00027509687885984846</v>
+        <v>-0.04813940783970372</v>
       </c>
       <c r="N54" s="1">
-        <v>3.2938935772661915</v>
+        <v>1.072172519857834</v>
       </c>
       <c r="O54" s="1">
-        <v>54.11764705882353</v>
+        <v>49.411764705882355</v>
       </c>
       <c r="P54" s="1">
         <v>11.84024085938085</v>
       </c>
       <c r="Q54" s="1">
-        <v>49.64705882352941</v>
+        <v>49.647058823529406</v>
       </c>
       <c r="R54" s="1">
-        <v>46.470588235294116</v>
+        <v>45.29411764705882</v>
       </c>
       <c r="S54" s="1" t="s">
         <v>115</v>
       </c>
       <c r="T54" s="1">
-        <v>6.04</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
@@ -5467,49 +5467,49 @@
         <v>0.67</v>
       </c>
       <c r="F55" s="1">
-        <v>-0.22474739791865422</v>
+        <v>-0.288060757277564</v>
       </c>
       <c r="G55" s="1">
         <v>1.58</v>
       </c>
       <c r="H55" s="1">
-        <v>51.31</v>
+        <v>47.79</v>
       </c>
       <c r="I55" s="1">
-        <v>4.48</v>
+        <v>2.83</v>
       </c>
       <c r="J55" s="1">
-        <v>-0.01873942324057018</v>
+        <v>-0.01779511032282079</v>
       </c>
       <c r="K55" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" s="1">
         <v>349</v>
       </c>
       <c r="M55" s="1">
-        <v>-0.21203737136024903</v>
+        <v>-0.2601563001153604</v>
       </c>
       <c r="N55" s="1">
-        <v>-17.937353246644697</v>
+        <v>-20.129516707707833</v>
       </c>
       <c r="O55" s="1">
-        <v>21.176470588235293</v>
+        <v>16.470588235294116</v>
       </c>
       <c r="P55" s="1">
         <v>26.83257063748809</v>
       </c>
       <c r="Q55" s="1">
-        <v>48.94117647058823</v>
+        <v>47.647058823529406</v>
       </c>
       <c r="R55" s="1">
-        <v>31.941176470588232</v>
+        <v>30.529411764705884</v>
       </c>
       <c r="S55" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T55" s="1">
-        <v>-26.66</v>
+        <v>-28.07</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
@@ -5529,19 +5529,19 @@
         <v>1.76</v>
       </c>
       <c r="F56" s="1">
-        <v>-0.2859773610162384</v>
+        <v>-0.40501189646957925</v>
       </c>
       <c r="G56" s="1">
-        <v>3.78</v>
+        <v>3.81</v>
       </c>
       <c r="H56" s="1">
-        <v>59.97</v>
+        <v>58.16</v>
       </c>
       <c r="I56" s="1">
-        <v>37.39</v>
+        <v>34.4</v>
       </c>
       <c r="J56" s="1">
-        <v>-0.0012414242881671764</v>
+        <v>0.002493886963514102</v>
       </c>
       <c r="K56" s="1" t="b">
         <v>1</v>
@@ -5550,13 +5550,13 @@
         <v>321</v>
       </c>
       <c r="M56" s="1">
-        <v>-0.22505688889146858</v>
+        <v>-0.2698196126320068</v>
       </c>
       <c r="N56" s="1">
-        <v>-19.23930499976665</v>
+        <v>-21.095847959372488</v>
       </c>
       <c r="O56" s="1">
-        <v>17.647058823529413</v>
+        <v>15.294117647058824</v>
       </c>
       <c r="P56" s="1">
         <v>52.65288503392759</v>
@@ -5565,13 +5565,13 @@
         <v>64.47058823529412</v>
       </c>
       <c r="R56" s="1">
-        <v>32.47058823529412</v>
+        <v>32.352941176470594</v>
       </c>
       <c r="S56" s="1" t="s">
         <v>111</v>
       </c>
       <c r="T56" s="1">
-        <v>-27.53</v>
+        <v>-27.65</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
@@ -5591,49 +5591,49 @@
         <v>-1.31</v>
       </c>
       <c r="F57" s="3">
-        <v>-0.3066477202178408</v>
+        <v>-0.4080921337953689</v>
       </c>
       <c r="G57" s="3">
         <v>2.04</v>
       </c>
       <c r="H57" s="3">
-        <v>47.97</v>
+        <v>44.9</v>
       </c>
       <c r="I57" s="3">
-        <v>-2.28</v>
+        <v>-5.08</v>
       </c>
       <c r="J57" s="3">
-        <v>-0.026119656622999848</v>
+        <v>-0.02658883780766918</v>
       </c>
       <c r="K57" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" s="3">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M57" s="3">
-        <v>-0.28385732776828665</v>
+        <v>-0.3580565554355556</v>
       </c>
       <c r="N57" s="3">
-        <v>-25.119348887448457</v>
+        <v>-29.919542239727363</v>
       </c>
       <c r="O57" s="3">
-        <v>11.76470588235294</v>
+        <v>7.0588235294117645</v>
       </c>
       <c r="P57" s="3">
         <v>40.717118046641446</v>
       </c>
       <c r="Q57" s="3">
-        <v>45.294117647058826</v>
+        <v>43.88235294117648</v>
       </c>
       <c r="R57" s="3">
-        <v>26.11764705882353</v>
+        <v>24.588235294117645</v>
       </c>
       <c r="S57" s="3" t="s">
         <v>110</v>
       </c>
       <c r="T57" s="3">
-        <v>-22.85</v>
+        <v>-24.38</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
@@ -5653,19 +5653,19 @@
         <v>1.26</v>
       </c>
       <c r="F58" s="1">
-        <v>0.015258253548212003</v>
+        <v>-0.03510685683816665</v>
       </c>
       <c r="G58" s="1">
         <v>1.64</v>
       </c>
       <c r="H58" s="1">
-        <v>45.54</v>
+        <v>40</v>
       </c>
       <c r="I58" s="1">
-        <v>-16.59</v>
+        <v>-20.02</v>
       </c>
       <c r="J58" s="1">
-        <v>0.006183258478815165</v>
+        <v>0.008187271445607172</v>
       </c>
       <c r="K58" s="1" t="b">
         <v>1</v>
@@ -5674,28 +5674,28 @@
         <v>3</v>
       </c>
       <c r="M58" s="1">
-        <v>0.02928311044024534</v>
+        <v>-0.004315731693666169</v>
       </c>
       <c r="N58" s="1">
-        <v>6.194694933404732</v>
+        <v>5.454540134461573</v>
       </c>
       <c r="O58" s="1">
-        <v>61.1764705882353</v>
+        <v>56.470588235294116</v>
       </c>
       <c r="P58" s="1">
         <v>33.706290307642504</v>
       </c>
       <c r="Q58" s="1">
-        <v>54.588235294117645</v>
+        <v>53.529411764705884</v>
       </c>
       <c r="R58" s="1">
-        <v>48.11764705882352</v>
+        <v>47.1764705882353</v>
       </c>
       <c r="S58" s="1" t="s">
         <v>103</v>
       </c>
       <c r="T58" s="1">
-        <v>26.17</v>
+        <v>25.23</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
@@ -5709,25 +5709,25 @@
         <v>64.70588235294117</v>
       </c>
       <c r="D59" s="3">
-        <v>3.3177083333333335</v>
+        <v>3.416666666666667</v>
       </c>
       <c r="E59" s="3">
         <v>0.97</v>
       </c>
       <c r="F59" s="3">
-        <v>-0.3111624099274826</v>
+        <v>-0.36214032499205284</v>
       </c>
       <c r="G59" s="3">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H59" s="3">
-        <v>48.41</v>
+        <v>49.65</v>
       </c>
       <c r="I59" s="3">
-        <v>10.01</v>
+        <v>10.96</v>
       </c>
       <c r="J59" s="3">
-        <v>-0.021833508394369143</v>
+        <v>-0.020031765263886687</v>
       </c>
       <c r="K59" s="3" t="b">
         <v>1</v>
@@ -5736,28 +5736,28 @@
         <v>520</v>
       </c>
       <c r="M59" s="3">
-        <v>-0.2920973700898748</v>
+        <v>-0.32076475057913034</v>
       </c>
       <c r="N59" s="3">
-        <v>-25.94335311960727</v>
+        <v>-26.19036175408484</v>
       </c>
       <c r="O59" s="3">
-        <v>10.588235294117647</v>
+        <v>8.235294117647058</v>
       </c>
       <c r="P59" s="3">
         <v>41.76493344029593</v>
       </c>
       <c r="Q59" s="3">
-        <v>48.35294117647059</v>
+        <v>49.411764705882355</v>
       </c>
       <c r="R59" s="3">
-        <v>25.647058823529413</v>
+        <v>25.176470588235297</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>110</v>
       </c>
       <c r="T59" s="3">
-        <v>-33.56</v>
+        <v>-34.03</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.25">
@@ -5777,19 +5777,19 @@
         <v>-4.45</v>
       </c>
       <c r="F60" s="3">
-        <v>-0.44776614924243374</v>
+        <v>-0.4762525915996093</v>
       </c>
       <c r="G60" s="3">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="H60" s="3">
-        <v>40.27</v>
+        <v>39.76</v>
       </c>
       <c r="I60" s="3">
-        <v>-33.28</v>
+        <v>-33.17</v>
       </c>
       <c r="J60" s="3">
-        <v>-0.03148487285323178</v>
+        <v>-0.03034375587208709</v>
       </c>
       <c r="K60" s="3" t="b">
         <v>0</v>
@@ -5798,28 +5798,28 @@
         <v>21</v>
       </c>
       <c r="M60" s="3">
-        <v>-0.4076638240667759</v>
+        <v>-0.3886903294699361</v>
       </c>
       <c r="N60" s="3">
-        <v>-37.49999851729739</v>
+        <v>-32.9829196431654</v>
       </c>
       <c r="O60" s="3">
-        <v>3.5294117647058822</v>
+        <v>4.705882352941177</v>
       </c>
       <c r="P60" s="3">
         <v>46.90217032437056</v>
       </c>
       <c r="Q60" s="3">
-        <v>25.17647058823529</v>
+        <v>24.470588235294116</v>
       </c>
       <c r="R60" s="3">
-        <v>10.64705882352941</v>
+        <v>10.999999999999996</v>
       </c>
       <c r="S60" s="3" t="s">
         <v>98</v>
       </c>
       <c r="T60" s="3">
-        <v>-16.24</v>
+        <v>-15.89</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
@@ -5839,49 +5839,49 @@
         <v>-0.52</v>
       </c>
       <c r="F61" s="1">
-        <v>-0.010041567863520548</v>
+        <v>-0.05819923617421936</v>
       </c>
       <c r="G61" s="1">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="H61" s="1">
-        <v>31.09</v>
+        <v>30.89</v>
       </c>
       <c r="I61" s="1">
-        <v>4.89</v>
+        <v>4.76</v>
       </c>
       <c r="J61" s="1">
-        <v>-0.0010450931807364139</v>
+        <v>-0.0018349270383264532</v>
       </c>
       <c r="K61" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L61" s="1">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M61" s="1">
-        <v>-0.005439661695822107</v>
+        <v>-0.04857700956656297</v>
       </c>
       <c r="N61" s="1">
-        <v>2.7224177197980004</v>
+        <v>1.028412347171901</v>
       </c>
       <c r="O61" s="1">
-        <v>52.94117647058824</v>
+        <v>48.23529411764706</v>
       </c>
       <c r="P61" s="1">
         <v>10.92423743722024</v>
       </c>
       <c r="Q61" s="1">
-        <v>46.705882352941174</v>
+        <v>45.64705882352941</v>
       </c>
       <c r="R61" s="1">
-        <v>46.05882352941177</v>
+        <v>44.29411764705883</v>
       </c>
       <c r="S61" s="1" t="s">
         <v>116</v>
       </c>
       <c r="T61" s="1">
-        <v>-1.14</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
@@ -5901,19 +5901,19 @@
         <v>0.11</v>
       </c>
       <c r="F62" s="2">
-        <v>0.16701176988006336</v>
+        <v>0.1447019618261561</v>
       </c>
       <c r="G62" s="2">
         <v>0.2</v>
       </c>
       <c r="H62" s="2">
-        <v>55.6</v>
+        <v>51.06</v>
       </c>
       <c r="I62" s="2">
-        <v>13.25</v>
+        <v>12</v>
       </c>
       <c r="J62" s="2">
-        <v>0.0022001582385115736</v>
+        <v>0.002900590394848981</v>
       </c>
       <c r="K62" s="2" t="b">
         <v>1</v>
@@ -5922,28 +5922,28 @@
         <v>93</v>
       </c>
       <c r="M62" s="2">
-        <v>0.14948069876502168</v>
+        <v>0.1062130553955305</v>
       </c>
       <c r="N62" s="2">
-        <v>18.21445376588238</v>
+        <v>16.50741884338125</v>
       </c>
       <c r="O62" s="2">
-        <v>75.29411764705883</v>
+        <v>71.76470588235294</v>
       </c>
       <c r="P62" s="2">
         <v>7.56622762341097</v>
       </c>
       <c r="Q62" s="2">
-        <v>56.470588235294116</v>
+        <v>55.529411764705884</v>
       </c>
       <c r="R62" s="2">
-        <v>54.70588235294118</v>
+        <v>53.76470588235295</v>
       </c>
       <c r="S62" s="2" t="s">
         <v>101</v>
       </c>
       <c r="T62" s="2">
-        <v>8.73</v>
+        <v>7.79</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
@@ -5963,19 +5963,19 @@
         <v>-1.09</v>
       </c>
       <c r="F63" s="1">
-        <v>-0.1638427687651962</v>
+        <v>-0.25672498670267446</v>
       </c>
       <c r="G63" s="1">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="H63" s="1">
-        <v>60.5</v>
+        <v>58.84</v>
       </c>
       <c r="I63" s="1">
-        <v>60.91</v>
+        <v>58.75</v>
       </c>
       <c r="J63" s="1">
-        <v>-0.001457016922845972</v>
+        <v>0.0010465932475691904</v>
       </c>
       <c r="K63" s="1" t="b">
         <v>0</v>
@@ -5984,28 +5984,28 @@
         <v>937</v>
       </c>
       <c r="M63" s="1">
-        <v>-0.13688874692581965</v>
+        <v>-0.19706718173520477</v>
       </c>
       <c r="N63" s="1">
-        <v>-10.42249080320176</v>
+        <v>-13.820604869692273</v>
       </c>
       <c r="O63" s="1">
-        <v>31.76470588235294</v>
+        <v>23.52941176470588</v>
       </c>
       <c r="P63" s="1">
         <v>39.10478556320163</v>
       </c>
       <c r="Q63" s="1">
-        <v>70.70588235294119</v>
+        <v>70.70588235294117</v>
       </c>
       <c r="R63" s="1">
-        <v>42.8235294117647</v>
+        <v>40.823529411764696</v>
       </c>
       <c r="S63" s="1" t="s">
         <v>117</v>
       </c>
       <c r="T63" s="1">
-        <v>-25.29</v>
+        <v>-27.29</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.25">
@@ -6025,49 +6025,49 @@
         <v>1.52</v>
       </c>
       <c r="F64" s="1">
-        <v>-0.18465613704495365</v>
+        <v>-0.21826527074775506</v>
       </c>
       <c r="G64" s="1">
         <v>0.97</v>
       </c>
       <c r="H64" s="1">
-        <v>51.21</v>
+        <v>49.13</v>
       </c>
       <c r="I64" s="1">
-        <v>5.78</v>
+        <v>4.15</v>
       </c>
       <c r="J64" s="1">
-        <v>-0.018767477952433345</v>
+        <v>-0.016992616469964354</v>
       </c>
       <c r="K64" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L64" s="1">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="M64" s="1">
-        <v>-0.1853135522117677</v>
+        <v>-0.21970860473890352</v>
       </c>
       <c r="N64" s="1">
-        <v>-15.26497133179656</v>
+        <v>-16.08474717006215</v>
       </c>
       <c r="O64" s="1">
-        <v>24.705882352941178</v>
+        <v>21.176470588235293</v>
       </c>
       <c r="P64" s="1">
         <v>25.543467249515373</v>
       </c>
       <c r="Q64" s="1">
-        <v>46.23529411764706</v>
+        <v>45.64705882352941</v>
       </c>
       <c r="R64" s="1">
-        <v>31</v>
+        <v>30.17647058823529</v>
       </c>
       <c r="S64" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T64" s="1">
-        <v>-13.76</v>
+        <v>-14.58</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.25">
@@ -6087,19 +6087,19 @@
         <v>0.4</v>
       </c>
       <c r="F65" s="1">
-        <v>-0.10503529169995265</v>
+        <v>-0.10661675418115169</v>
       </c>
       <c r="G65" s="1">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="H65" s="1">
-        <v>26.2</v>
+        <v>26.56</v>
       </c>
       <c r="I65" s="1">
-        <v>-12.29</v>
+        <v>-12.27</v>
       </c>
       <c r="J65" s="1">
-        <v>-0.00620465013183804</v>
+        <v>-0.006198749451862429</v>
       </c>
       <c r="K65" s="1" t="b">
         <v>1</v>
@@ -6108,28 +6108,28 @@
         <v>-101</v>
       </c>
       <c r="M65" s="1">
-        <v>-0.11906014859198599</v>
+        <v>-0.137888990656035</v>
       </c>
       <c r="N65" s="1">
-        <v>-8.639630969818391</v>
+        <v>-7.902785761775298</v>
       </c>
       <c r="O65" s="1">
-        <v>35.294117647058826</v>
+        <v>30.58823529411765</v>
       </c>
       <c r="P65" s="1">
-        <v>18.133639028994587</v>
+        <v>18.234594077618315</v>
       </c>
       <c r="Q65" s="1">
-        <v>35.647058823529406</v>
+        <v>35.05882352941176</v>
       </c>
       <c r="R65" s="1">
-        <v>33.1764705882353</v>
+        <v>31.41176470588235</v>
       </c>
       <c r="S65" s="1" t="s">
         <v>118</v>
       </c>
       <c r="T65" s="1">
-        <v>7.14</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
@@ -6149,19 +6149,19 @@
         <v>2.08</v>
       </c>
       <c r="F66" s="2">
-        <v>0.1309853158244585</v>
+        <v>0.09081696202461209</v>
       </c>
       <c r="G66" s="2">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="H66" s="2">
-        <v>63.45</v>
+        <v>60.94</v>
       </c>
       <c r="I66" s="2">
-        <v>19.9</v>
+        <v>18.23</v>
       </c>
       <c r="J66" s="2">
-        <v>0.011390845288298571</v>
+        <v>0.012576158300945956</v>
       </c>
       <c r="K66" s="2" t="b">
         <v>0</v>
@@ -6170,19 +6170,19 @@
         <v>80</v>
       </c>
       <c r="M66" s="2">
-        <v>0.1281365167682642</v>
+        <v>0.08504362606001825</v>
       </c>
       <c r="N66" s="2">
-        <v>16.080035566206636</v>
+        <v>14.390475909830016</v>
       </c>
       <c r="O66" s="2">
-        <v>71.76470588235294</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="P66" s="2">
         <v>10.56723987277981</v>
       </c>
       <c r="Q66" s="2">
-        <v>69.76470588235296</v>
+        <v>69.05882352941177</v>
       </c>
       <c r="R66" s="2">
         <v>59.941176470588246</v>
@@ -6205,25 +6205,25 @@
         <v>100</v>
       </c>
       <c r="D67" s="3">
-        <v>-0.6829469062971602</v>
+        <v>-0.6876114693373577</v>
       </c>
       <c r="E67" s="3">
         <v>1.69</v>
       </c>
       <c r="F67" s="3">
-        <v>-0.30455322839306775</v>
+        <v>-0.483467970397213</v>
       </c>
       <c r="G67" s="3">
-        <v>5.2</v>
+        <v>5.19</v>
       </c>
       <c r="H67" s="3">
-        <v>62.45</v>
+        <v>59.01</v>
       </c>
       <c r="I67" s="3">
-        <v>68.76</v>
+        <v>61.97</v>
       </c>
       <c r="J67" s="3">
-        <v>-0.009006231348070728</v>
+        <v>-0.008451523664449314</v>
       </c>
       <c r="K67" s="3" t="b">
         <v>0</v>
@@ -6232,28 +6232,28 @@
         <v>669</v>
       </c>
       <c r="M67" s="3">
-        <v>-0.21251510503909898</v>
+        <v>-0.28188232296681137</v>
       </c>
       <c r="N67" s="3">
-        <v>-17.985126614529694</v>
+        <v>-22.302118992852936</v>
       </c>
       <c r="O67" s="3">
-        <v>20</v>
+        <v>12.941176470588237</v>
       </c>
       <c r="P67" s="3">
         <v>56.49293299150161</v>
       </c>
       <c r="Q67" s="3">
-        <v>60.235294117647065</v>
+        <v>58.352941176470594</v>
       </c>
       <c r="R67" s="3">
-        <v>28.82352941176471</v>
+        <v>26.470588235294116</v>
       </c>
       <c r="S67" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T67" s="3">
-        <v>-40.57</v>
+        <v>-42.92</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
@@ -6273,49 +6273,49 @@
         <v>-2.41</v>
       </c>
       <c r="F68" s="1">
-        <v>-0.2541149385652279</v>
+        <v>-0.3093846180875441</v>
       </c>
       <c r="G68" s="1">
         <v>2.09</v>
       </c>
       <c r="H68" s="1">
-        <v>54.56</v>
+        <v>52.59</v>
       </c>
       <c r="I68" s="1">
-        <v>40.29</v>
+        <v>37.52</v>
       </c>
       <c r="J68" s="1">
-        <v>-0.005746473878596395</v>
+        <v>-0.0061824604096929</v>
       </c>
       <c r="K68" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L68" s="1">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M68" s="1">
-        <v>-0.2302288541709836</v>
+        <v>-0.2569434830758167</v>
       </c>
       <c r="N68" s="1">
-        <v>-19.75650152771815</v>
+        <v>-19.80823500375347</v>
       </c>
       <c r="O68" s="1">
-        <v>16.470588235294116</v>
+        <v>17.647058823529413</v>
       </c>
       <c r="P68" s="1">
         <v>31.85898471566022</v>
       </c>
       <c r="Q68" s="1">
-        <v>64</v>
+        <v>62.82352941176471</v>
       </c>
       <c r="R68" s="1">
-        <v>36.41176470588236</v>
+        <v>36.294117647058826</v>
       </c>
       <c r="S68" s="1" t="s">
         <v>111</v>
       </c>
       <c r="T68" s="1">
-        <v>-29.62</v>
+        <v>-29.74</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
@@ -6335,49 +6335,49 @@
         <v>-1.74</v>
       </c>
       <c r="F69" s="1">
-        <v>0.10287924141109017</v>
+        <v>0.12191258079284352</v>
       </c>
       <c r="G69" s="1">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="H69" s="1">
-        <v>38.46</v>
+        <v>40.46</v>
       </c>
       <c r="I69" s="1">
-        <v>-26.03</v>
+        <v>-24.89</v>
       </c>
       <c r="J69" s="1">
-        <v>0.014305268913456093</v>
+        <v>0.012090565256253636</v>
       </c>
       <c r="K69" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L69" s="1">
-        <v>-252</v>
+        <v>-251</v>
       </c>
       <c r="M69" s="1">
-        <v>0.10287924141109017</v>
+        <v>0.12095035813207788</v>
       </c>
       <c r="N69" s="1">
-        <v>13.554308030489231</v>
+        <v>17.98114911703599</v>
       </c>
       <c r="O69" s="1">
-        <v>69.41176470588235</v>
+        <v>74.11764705882354</v>
       </c>
       <c r="P69" s="1">
         <v>37.32769516583675</v>
       </c>
       <c r="Q69" s="1">
-        <v>51.88235294117647</v>
+        <v>51.64705882352941</v>
       </c>
       <c r="R69" s="1">
-        <v>48.647058823529406</v>
+        <v>49.82352941176471</v>
       </c>
       <c r="S69" s="1" t="s">
         <v>120</v>
       </c>
       <c r="T69" s="1">
-        <v>30.9</v>
+        <v>32.08</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
@@ -6397,19 +6397,19 @@
         <v>-0.54</v>
       </c>
       <c r="F70" s="1">
-        <v>-0.05427432644450578</v>
+        <v>-0.07914880660674846</v>
       </c>
       <c r="G70" s="1">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="H70" s="1">
-        <v>41.86</v>
+        <v>41.35</v>
       </c>
       <c r="I70" s="1">
-        <v>-5.88</v>
+        <v>-5.95</v>
       </c>
       <c r="J70" s="1">
-        <v>-0.0034438902035923793</v>
+        <v>-0.003959832536586201</v>
       </c>
       <c r="K70" s="1" t="b">
         <v>0</v>
@@ -6418,28 +6418,28 @@
         <v>4</v>
       </c>
       <c r="M70" s="1">
-        <v>-0.048576728332117236</v>
+        <v>-0.06712102334717795</v>
       </c>
       <c r="N70" s="1">
-        <v>-1.591288943831511</v>
+        <v>-0.8259890308895951</v>
       </c>
       <c r="O70" s="1">
-        <v>49.411764705882355</v>
+        <v>40</v>
       </c>
       <c r="P70" s="1">
         <v>16.710870321490763</v>
       </c>
       <c r="Q70" s="1">
-        <v>50.11764705882353</v>
+        <v>49.41176470588235</v>
       </c>
       <c r="R70" s="1">
-        <v>46.470588235294116</v>
+        <v>43.647058823529406</v>
       </c>
       <c r="S70" s="1" t="s">
         <v>103</v>
       </c>
       <c r="T70" s="1">
-        <v>4.76</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.25">
@@ -6459,49 +6459,49 @@
         <v>0.14</v>
       </c>
       <c r="F71" s="2">
-        <v>0.194930505072704</v>
+        <v>0.17910724334687944</v>
       </c>
       <c r="G71" s="2">
         <v>0.33</v>
       </c>
       <c r="H71" s="2">
-        <v>58.63</v>
+        <v>61.78</v>
       </c>
       <c r="I71" s="2">
-        <v>10.07</v>
+        <v>10.97</v>
       </c>
       <c r="J71" s="2">
-        <v>0.010643766218434549</v>
+        <v>0.011428321756449769</v>
       </c>
       <c r="K71" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L71" s="2">
-        <v>-80</v>
+        <v>-79</v>
       </c>
       <c r="M71" s="2">
-        <v>0.18024823301385662</v>
+        <v>0.1468727842112305</v>
       </c>
       <c r="N71" s="2">
-        <v>21.291207190765867</v>
+        <v>20.57339172495126</v>
       </c>
       <c r="O71" s="2">
-        <v>78.82352941176471</v>
+        <v>76.47058823529412</v>
       </c>
       <c r="P71" s="2">
         <v>10.873073633899006</v>
       </c>
       <c r="Q71" s="2">
-        <v>61.529411764705884</v>
+        <v>62.94117647058824</v>
       </c>
       <c r="R71" s="2">
-        <v>57.76470588235295</v>
+        <v>57.52941176470589</v>
       </c>
       <c r="S71" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T71" s="2">
-        <v>9.72</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.25">
@@ -6521,19 +6521,19 @@
         <v>0.2</v>
       </c>
       <c r="F72" s="1">
-        <v>-0.07602792906157597</v>
+        <v>-0.08518072896555895</v>
       </c>
       <c r="G72" s="1">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="H72" s="1">
-        <v>60.91</v>
+        <v>64.68</v>
       </c>
       <c r="I72" s="1">
-        <v>-13.48</v>
+        <v>-11.48</v>
       </c>
       <c r="J72" s="1">
-        <v>-0.010519264250470662</v>
+        <v>-0.008265106383773379</v>
       </c>
       <c r="K72" s="1" t="b">
         <v>1</v>
@@ -6542,28 +6542,28 @@
         <v>-41</v>
       </c>
       <c r="M72" s="1">
-        <v>-0.06572842478148899</v>
+        <v>-0.06208738510718359</v>
       </c>
       <c r="N72" s="1">
-        <v>-3.306458588768694</v>
+        <v>-0.32262520689016383</v>
       </c>
       <c r="O72" s="1">
-        <v>48.23529411764706</v>
+        <v>42.35294117647059</v>
       </c>
       <c r="P72" s="1">
-        <v>31.147611427732443</v>
+        <v>29.505935179545663</v>
       </c>
       <c r="Q72" s="1">
-        <v>50.23529411764706</v>
+        <v>51.41176470588235</v>
       </c>
       <c r="R72" s="1">
-        <v>39.35294117647059</v>
+        <v>38.411764705882355</v>
       </c>
       <c r="S72" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T72" s="1">
-        <v>9.9</v>
+        <v>8.96</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.25">
@@ -6583,19 +6583,19 @@
         <v>-0.34</v>
       </c>
       <c r="F73" s="2">
-        <v>0.37210962570846884</v>
+        <v>0.3661418648578458</v>
       </c>
       <c r="G73" s="2">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="H73" s="2">
-        <v>69.21</v>
+        <v>70.01</v>
       </c>
       <c r="I73" s="2">
-        <v>22.05</v>
+        <v>22.49</v>
       </c>
       <c r="J73" s="2">
-        <v>0.021459848374739025</v>
+        <v>0.022824506586912218</v>
       </c>
       <c r="K73" s="2" t="b">
         <v>1</v>
@@ -6604,13 +6604,13 @@
         <v>49</v>
       </c>
       <c r="M73" s="2">
-        <v>0.3694799650412126</v>
+        <v>0.36084964022363475</v>
       </c>
       <c r="N73" s="2">
-        <v>40.21438039350146</v>
+        <v>41.971077326191676</v>
       </c>
       <c r="O73" s="2">
-        <v>91.76470588235294</v>
+        <v>88.23529411764706</v>
       </c>
       <c r="P73" s="2">
         <v>8.480874361506512</v>
@@ -6619,13 +6619,13 @@
         <v>67.52941176470588</v>
       </c>
       <c r="R73" s="2">
-        <v>62.88235294117648</v>
+        <v>61.82352941176471</v>
       </c>
       <c r="S73" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T73" s="2">
-        <v>23</v>
+        <v>21.95</v>
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.25">
@@ -6645,19 +6645,19 @@
         <v>0.44</v>
       </c>
       <c r="F74" s="1">
-        <v>-0.2492358041514754</v>
+        <v>-0.22734951375738882</v>
       </c>
       <c r="G74" s="1">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="H74" s="1">
-        <v>33.01</v>
+        <v>37.15</v>
       </c>
       <c r="I74" s="1">
-        <v>-28.89</v>
+        <v>-27.61</v>
       </c>
       <c r="J74" s="1">
-        <v>-0.017197560372573417</v>
+        <v>-0.017856358794734354</v>
       </c>
       <c r="K74" s="1" t="b">
         <v>1</v>
@@ -6666,28 +6666,28 @@
         <v>-167</v>
       </c>
       <c r="M74" s="1">
-        <v>-0.24704442026209517</v>
+        <v>-0.2230195117839434</v>
       </c>
       <c r="N74" s="1">
-        <v>-21.43805813682931</v>
+        <v>-16.415837874566144</v>
       </c>
       <c r="O74" s="1">
-        <v>15.294117647058824</v>
+        <v>20</v>
       </c>
       <c r="P74" s="1">
         <v>25.03694506602277</v>
       </c>
       <c r="Q74" s="1">
-        <v>40.70588235294117</v>
+        <v>39.999999999999986</v>
       </c>
       <c r="R74" s="1">
-        <v>30.823529411764714</v>
+        <v>31.882352941176475</v>
       </c>
       <c r="S74" s="1" t="s">
         <v>121</v>
       </c>
       <c r="T74" s="1">
-        <v>-1.19</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
@@ -6707,19 +6707,19 @@
         <v>-3.72</v>
       </c>
       <c r="F75" s="1">
-        <v>-0.25756672965758654</v>
+        <v>-0.25447052316800706</v>
       </c>
       <c r="G75" s="1">
         <v>1.25</v>
       </c>
       <c r="H75" s="1">
-        <v>37.24</v>
+        <v>35.22</v>
       </c>
       <c r="I75" s="1">
-        <v>-6.77</v>
+        <v>-7.97</v>
       </c>
       <c r="J75" s="1">
-        <v>-0.019738950752422973</v>
+        <v>-0.02010197248908249</v>
       </c>
       <c r="K75" s="1" t="b">
         <v>0</v>
@@ -6728,28 +6728,28 @@
         <v>32</v>
       </c>
       <c r="M75" s="1">
-        <v>-0.252088269934136</v>
+        <v>-0.24244273990843657</v>
       </c>
       <c r="N75" s="1">
-        <v>-21.942443104033394</v>
+        <v>-18.358160687015463</v>
       </c>
       <c r="O75" s="1">
-        <v>14.117647058823529</v>
+        <v>18.823529411764707</v>
       </c>
       <c r="P75" s="1">
-        <v>28.76752600761915</v>
+        <v>29.662784615305803</v>
       </c>
       <c r="Q75" s="1">
-        <v>44.11764705882353</v>
+        <v>42.47058823529411</v>
       </c>
       <c r="R75" s="1">
-        <v>30.411764705882355</v>
+        <v>31.352941176470587</v>
       </c>
       <c r="S75" s="1" t="s">
         <v>103</v>
       </c>
       <c r="T75" s="1">
-        <v>-28.19</v>
+        <v>-27.24</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
@@ -6769,19 +6769,19 @@
         <v>-0.07</v>
       </c>
       <c r="F76" s="3">
-        <v>-0.3679034265742512</v>
+        <v>-0.40944987440285974</v>
       </c>
       <c r="G76" s="3">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="H76" s="3">
-        <v>44.25</v>
+        <v>46.92</v>
       </c>
       <c r="I76" s="3">
-        <v>-31.13</v>
+        <v>-29.66</v>
       </c>
       <c r="J76" s="3">
-        <v>-0.020269386182837294</v>
+        <v>-0.01851730216819086</v>
       </c>
       <c r="K76" s="3" t="b">
         <v>0</v>
@@ -6790,10 +6790,10 @@
         <v>10</v>
       </c>
       <c r="M76" s="3">
-        <v>-0.31837815067425845</v>
+        <v>-0.301680936397108</v>
       </c>
       <c r="N76" s="3">
-        <v>-28.571431178045636</v>
+        <v>-24.281980335882608</v>
       </c>
       <c r="O76" s="3">
         <v>9.411764705882353</v>
@@ -6802,16 +6802,16 @@
         <v>51.49813033405746</v>
       </c>
       <c r="Q76" s="3">
-        <v>41.529411764705884</v>
+        <v>42.470588235294116</v>
       </c>
       <c r="R76" s="3">
-        <v>24.235294117647058</v>
+        <v>24.352941176470587</v>
       </c>
       <c r="S76" s="3" t="s">
         <v>109</v>
       </c>
       <c r="T76" s="3">
-        <v>-1.5</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
@@ -6831,19 +6831,19 @@
         <v>12.83</v>
       </c>
       <c r="F77" s="3">
-        <v>0.0027535145231743496</v>
+        <v>0.03308542528212116</v>
       </c>
       <c r="G77" s="3">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="H77" s="3">
-        <v>32.42</v>
+        <v>46.96</v>
       </c>
       <c r="I77" s="3">
-        <v>36.75</v>
+        <v>47.7</v>
       </c>
       <c r="J77" s="3">
-        <v>-0.029428435250407167</v>
+        <v>-0.027436595398920918</v>
       </c>
       <c r="K77" s="3" t="b">
         <v>1</v>
@@ -6852,28 +6852,28 @@
         <v>42</v>
       </c>
       <c r="M77" s="3">
-        <v>0.0003429922448561218</v>
+        <v>0.02683097798714451</v>
       </c>
       <c r="N77" s="3">
-        <v>3.3006831138658232</v>
+        <v>8.569211102542653</v>
       </c>
       <c r="O77" s="3">
-        <v>55.294117647058826</v>
+        <v>60</v>
       </c>
       <c r="P77" s="3">
         <v>29.799918858582526</v>
       </c>
       <c r="Q77" s="3">
-        <v>26.82352941176471</v>
+        <v>30.82352941176471</v>
       </c>
       <c r="R77" s="3">
-        <v>24.764705882352942</v>
+        <v>26.058823529411768</v>
       </c>
       <c r="S77" s="3" t="s">
         <v>123</v>
       </c>
       <c r="T77" s="3">
-        <v>-48.95</v>
+        <v>-47.66</v>
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
@@ -6893,19 +6893,19 @@
         <v>-9.21</v>
       </c>
       <c r="F78" s="2">
-        <v>0.725900059276373</v>
+        <v>0.8533544445212071</v>
       </c>
       <c r="G78" s="2">
         <v>0.91</v>
       </c>
       <c r="H78" s="2">
-        <v>69.04</v>
+        <v>69.62</v>
       </c>
       <c r="I78" s="2">
-        <v>37.3</v>
+        <v>37.34</v>
       </c>
       <c r="J78" s="2">
-        <v>0.03715276494318379</v>
+        <v>0.035823719334485506</v>
       </c>
       <c r="K78" s="2" t="b">
         <v>0</v>
@@ -6914,10 +6914,10 @@
         <v>-5</v>
       </c>
       <c r="M78" s="2">
-        <v>0.7239278137759309</v>
+        <v>0.8490244425477618</v>
       </c>
       <c r="N78" s="2">
-        <v>75.6591652669733</v>
+        <v>90.78855755860438</v>
       </c>
       <c r="O78" s="2">
         <v>98.82352941176471</v>
@@ -6926,16 +6926,16 @@
         <v>18.71809072120826</v>
       </c>
       <c r="Q78" s="2">
-        <v>66.82352941176471</v>
+        <v>66.3529411764706</v>
       </c>
       <c r="R78" s="2">
-        <v>60.76470588235294</v>
+        <v>60.529411764705884</v>
       </c>
       <c r="S78" s="2" t="s">
         <v>110</v>
       </c>
       <c r="T78" s="2">
-        <v>12.17</v>
+        <v>11.93</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.25">
@@ -6955,19 +6955,19 @@
         <v>-3.59</v>
       </c>
       <c r="F79" s="2">
-        <v>0.21389377272069082</v>
+        <v>0.20345912339991712</v>
       </c>
       <c r="G79" s="2">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="H79" s="2">
-        <v>57.32</v>
+        <v>57.2</v>
       </c>
       <c r="I79" s="2">
-        <v>30.04</v>
+        <v>29.64</v>
       </c>
       <c r="J79" s="2">
-        <v>0.010210533127861597</v>
+        <v>0.010328529615366816</v>
       </c>
       <c r="K79" s="2" t="b">
         <v>1</v>
@@ -6976,28 +6976,28 @@
         <v>-2</v>
       </c>
       <c r="M79" s="2">
-        <v>0.21630429499900905</v>
+        <v>0.20923245936451096</v>
       </c>
       <c r="N79" s="2">
-        <v>24.89681338928112</v>
+        <v>26.809359240279296</v>
       </c>
       <c r="O79" s="2">
-        <v>84.70588235294117</v>
+        <v>82.35294117647058</v>
       </c>
       <c r="P79" s="2">
         <v>16.006637557486414</v>
       </c>
       <c r="Q79" s="2">
-        <v>58.352941176470594</v>
+        <v>58</v>
       </c>
       <c r="R79" s="2">
-        <v>54.64705882352941</v>
+        <v>53.94117647058824</v>
       </c>
       <c r="S79" s="2" t="s">
         <v>108</v>
       </c>
       <c r="T79" s="2">
-        <v>6.48</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.25">
@@ -7017,19 +7017,19 @@
         <v>0.34</v>
       </c>
       <c r="F80" s="2">
-        <v>0.213666256736375</v>
+        <v>0.16325022398107458</v>
       </c>
       <c r="G80" s="2">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="H80" s="2">
-        <v>49.48</v>
+        <v>44.42</v>
       </c>
       <c r="I80" s="2">
-        <v>10.72</v>
+        <v>9.13</v>
       </c>
       <c r="J80" s="2">
-        <v>0.009350410735690403</v>
+        <v>0.008464093374121217</v>
       </c>
       <c r="K80" s="2" t="b">
         <v>1</v>
@@ -7038,28 +7038,28 @@
         <v>6</v>
       </c>
       <c r="M80" s="2">
-        <v>0.20972176573549062</v>
+        <v>0.15507133136456663</v>
       </c>
       <c r="N80" s="2">
-        <v>24.238560462929264</v>
+        <v>21.393246440284873</v>
       </c>
       <c r="O80" s="2">
-        <v>82.35294117647058</v>
+        <v>77.64705882352942</v>
       </c>
       <c r="P80" s="2">
         <v>11.616065285425229</v>
       </c>
       <c r="Q80" s="2">
-        <v>54.35294117647059</v>
+        <v>52.23529411764706</v>
       </c>
       <c r="R80" s="2">
-        <v>54.705882352941174</v>
+        <v>53.529411764705884</v>
       </c>
       <c r="S80" s="2" t="s">
         <v>102</v>
       </c>
       <c r="T80" s="2">
-        <v>14.83</v>
+        <v>13.65</v>
       </c>
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.25">
@@ -7073,37 +7073,37 @@
         <v>78.82352941176471</v>
       </c>
       <c r="D81" s="2">
-        <v>0.17339055793991412</v>
+        <v>0.16652360515021455</v>
       </c>
       <c r="E81" s="2">
         <v>0.87</v>
       </c>
       <c r="F81" s="2">
-        <v>0.0978195036153274</v>
+        <v>0.08541672472491912</v>
       </c>
       <c r="G81" s="2">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="H81" s="2">
-        <v>48.36</v>
+        <v>47.78</v>
       </c>
       <c r="I81" s="2">
-        <v>9.84</v>
+        <v>9.64</v>
       </c>
       <c r="J81" s="2">
-        <v>0.005078502637170659</v>
+        <v>0.005503316692849597</v>
       </c>
       <c r="K81" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L81" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M81" s="2">
-        <v>0.09277932066975292</v>
+        <v>0.07387005279573144</v>
       </c>
       <c r="N81" s="2">
-        <v>12.544315956355497</v>
+        <v>13.273118583401333</v>
       </c>
       <c r="O81" s="2">
         <v>67.05882352941175</v>
@@ -7112,7 +7112,7 @@
         <v>6.707278396222185</v>
       </c>
       <c r="Q81" s="2">
-        <v>56.35294117647059</v>
+        <v>56.470588235294116</v>
       </c>
       <c r="R81" s="2">
         <v>54.11764705882352</v>
@@ -7125,65 +7125,65 @@
       </c>
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A82" s="2" t="s">
+      <c r="A82" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B82" s="2">
+      <c r="B82" s="1">
         <v>23.34</v>
       </c>
-      <c r="C82" s="2">
+      <c r="C82" s="1">
         <v>95.29411764705881</v>
       </c>
-      <c r="D82" s="2">
+      <c r="D82" s="1">
         <v>-0.9305912596401028</v>
       </c>
-      <c r="E82" s="2">
+      <c r="E82" s="1">
         <v>-1.14</v>
       </c>
-      <c r="F82" s="2">
-        <v>0.04229693820603323</v>
-      </c>
-      <c r="G82" s="2">
+      <c r="F82" s="1">
+        <v>0.002682604422117138</v>
+      </c>
+      <c r="G82" s="1">
         <v>1.01</v>
       </c>
-      <c r="H82" s="2">
-        <v>46.64</v>
-      </c>
-      <c r="I82" s="2">
-        <v>9.45</v>
-      </c>
-      <c r="J82" s="2">
-        <v>0.004151948041054371</v>
-      </c>
-      <c r="K82" s="2" t="b">
+      <c r="H82" s="1">
+        <v>47.21</v>
+      </c>
+      <c r="I82" s="1">
+        <v>9.49</v>
+      </c>
+      <c r="J82" s="1">
+        <v>0.004143141617712615</v>
+      </c>
+      <c r="K82" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L82" s="2">
-        <v>110</v>
-      </c>
-      <c r="M82" s="2">
-        <v>0.04251607659497125</v>
-      </c>
-      <c r="N82" s="2">
-        <v>7.517991548877342</v>
-      </c>
-      <c r="O82" s="2">
-        <v>62.35294117647059</v>
-      </c>
-      <c r="P82" s="2">
+      <c r="L82" s="1">
+        <v>111</v>
+      </c>
+      <c r="M82" s="1">
+        <v>0.0031637157524999626</v>
+      </c>
+      <c r="N82" s="1">
+        <v>6.202484879078198</v>
+      </c>
+      <c r="O82" s="1">
+        <v>57.647058823529406</v>
+      </c>
+      <c r="P82" s="1">
         <v>6.0971680093981355</v>
       </c>
-      <c r="Q82" s="2">
-        <v>53.88235294117647</v>
-      </c>
-      <c r="R82" s="2">
-        <v>51.52941176470588</v>
-      </c>
-      <c r="S82" s="2" t="s">
+      <c r="Q82" s="1">
+        <v>54</v>
+      </c>
+      <c r="R82" s="1">
+        <v>49.88235294117647</v>
+      </c>
+      <c r="S82" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="T82" s="2">
-        <v>6.22</v>
+      <c r="T82" s="1">
+        <v>4.58</v>
       </c>
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.25">
@@ -7203,31 +7203,31 @@
         <v>0.23</v>
       </c>
       <c r="F83" s="2">
-        <v>0.09371734243905319</v>
+        <v>0.07859834923787892</v>
       </c>
       <c r="G83" s="2">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H83" s="2">
-        <v>62.99</v>
+        <v>66.87</v>
       </c>
       <c r="I83" s="2">
-        <v>16.96</v>
+        <v>18.42</v>
       </c>
       <c r="J83" s="2">
-        <v>0.006818160934891378</v>
+        <v>0.006758079773930283</v>
       </c>
       <c r="K83" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L83" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M83" s="2">
-        <v>0.09525131116161933</v>
+        <v>0.08244723988094149</v>
       </c>
       <c r="N83" s="2">
-        <v>12.791515005542134</v>
+        <v>14.13083729192234</v>
       </c>
       <c r="O83" s="2">
         <v>68.23529411764706</v>
@@ -7236,16 +7236,16 @@
         <v>12.706223591210087</v>
       </c>
       <c r="Q83" s="2">
-        <v>60.47058823529413</v>
+        <v>60.70588235294118</v>
       </c>
       <c r="R83" s="2">
-        <v>51.70588235294118</v>
+        <v>51.58823529411765</v>
       </c>
       <c r="S83" s="2" t="s">
         <v>109</v>
       </c>
       <c r="T83" s="2">
-        <v>-0.43</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.25">
@@ -7265,49 +7265,49 @@
         <v>2.31</v>
       </c>
       <c r="F84" s="1">
-        <v>-0.09977449087485286</v>
+        <v>-0.062491054051565256</v>
       </c>
       <c r="G84" s="1">
         <v>1.2</v>
       </c>
       <c r="H84" s="1">
-        <v>56.92</v>
+        <v>60.38</v>
       </c>
       <c r="I84" s="1">
-        <v>3.66</v>
+        <v>5.05</v>
       </c>
       <c r="J84" s="1">
-        <v>-0.004928465830562718</v>
+        <v>-0.004565627632875225</v>
       </c>
       <c r="K84" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L84" s="1">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M84" s="1">
-        <v>-0.09539172309609245</v>
+        <v>-0.05286882744390886</v>
       </c>
       <c r="N84" s="1">
-        <v>-6.272788420229038</v>
+        <v>0.5992305594373104</v>
       </c>
       <c r="O84" s="1">
-        <v>40</v>
+        <v>45.88235294117647</v>
       </c>
       <c r="P84" s="1">
         <v>20.22353911360907</v>
       </c>
       <c r="Q84" s="1">
-        <v>48.70588235294117</v>
+        <v>50.58823529411764</v>
       </c>
       <c r="R84" s="1">
-        <v>36.8235294117647</v>
+        <v>38.705882352941174</v>
       </c>
       <c r="S84" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T84" s="1">
-        <v>-9.94</v>
+        <v>-8.06</v>
       </c>
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.25">
@@ -7321,55 +7321,55 @@
         <v>51.76470588235295</v>
       </c>
       <c r="D85" s="1">
-        <v>1.765765765765766</v>
+        <v>1.7867867867867866</v>
       </c>
       <c r="E85" s="1">
         <v>0.23</v>
       </c>
       <c r="F85" s="1">
-        <v>-0.11613052030966527</v>
+        <v>-0.14075910782647483</v>
       </c>
       <c r="G85" s="1">
         <v>0.98</v>
       </c>
       <c r="H85" s="1">
-        <v>46.97</v>
+        <v>50.17</v>
       </c>
       <c r="I85" s="1">
-        <v>13.94</v>
+        <v>15.1</v>
       </c>
       <c r="J85" s="1">
-        <v>-0.004039471243333974</v>
+        <v>-0.005311625140946857</v>
       </c>
       <c r="K85" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L85" s="1">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="M85" s="1">
-        <v>-0.11656879708754131</v>
+        <v>-0.14172133048724045</v>
       </c>
       <c r="N85" s="1">
-        <v>-8.390495819373927</v>
+        <v>-8.286019744895846</v>
       </c>
       <c r="O85" s="1">
-        <v>36.470588235294116</v>
+        <v>29.411764705882355</v>
       </c>
       <c r="P85" s="1">
         <v>17.353844275841347</v>
       </c>
       <c r="Q85" s="1">
-        <v>49.41176470588235</v>
+        <v>50.235294117647065</v>
       </c>
       <c r="R85" s="1">
-        <v>37.82352941176471</v>
+        <v>35.47058823529412</v>
       </c>
       <c r="S85" s="1" t="s">
         <v>132</v>
       </c>
       <c r="T85" s="1">
-        <v>-18.82</v>
+        <v>-21.18</v>
       </c>
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.25">
@@ -7389,49 +7389,49 @@
         <v>0.62</v>
       </c>
       <c r="F86" s="1">
-        <v>0.055982420657871894</v>
+        <v>-0.01857690019218944</v>
       </c>
       <c r="G86" s="1">
-        <v>0.95</v>
+        <v>0.94</v>
       </c>
       <c r="H86" s="1">
-        <v>30.88</v>
+        <v>26.16</v>
       </c>
       <c r="I86" s="1">
-        <v>5.74</v>
+        <v>2.79</v>
       </c>
       <c r="J86" s="1">
-        <v>-0.00014255025102466516</v>
+        <v>-0.001510736645017923</v>
       </c>
       <c r="K86" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="1">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="M86" s="1">
-        <v>0.05488672871318179</v>
+        <v>-0.021463568174486358</v>
       </c>
       <c r="N86" s="1">
-        <v>8.755056760698379</v>
+        <v>3.7397564863795743</v>
       </c>
       <c r="O86" s="1">
-        <v>63.52941176470588</v>
+        <v>55.294117647058826</v>
       </c>
       <c r="P86" s="1">
-        <v>10.0605242712113</v>
+        <v>13.196185332148602</v>
       </c>
       <c r="Q86" s="1">
-        <v>46.82352941176471</v>
+        <v>44.705882352941174</v>
       </c>
       <c r="R86" s="1">
-        <v>49.529411764705884</v>
+        <v>45.64705882352941</v>
       </c>
       <c r="S86" s="1" t="s">
         <v>107</v>
       </c>
       <c r="T86" s="1">
-        <v>2.76</v>
+        <v>-1.12</v>
       </c>
     </row>
   </sheetData>
@@ -7458,7 +7458,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>48.52941176470588</v>
+        <v>45.764705882352935</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -7466,7 +7466,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>50.23529411764706</v>
+        <v>53.17647058823529</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7474,7 +7474,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>54.470588235294116</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -7482,7 +7482,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>36.05882352941177</v>
+        <v>35.705882352941174</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -7490,7 +7490,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>34.05882352941177</v>
+        <v>36.41176470588235</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7498,7 +7498,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>55.52941176470588</v>
+        <v>55.76470588235293</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -7506,7 +7506,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>41.05882352941176</v>
+        <v>38.705882352941174</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -7514,7 +7514,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>59.94117647058823</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -7522,7 +7522,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>45.1764705882353</v>
+        <v>45.88235294117647</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -7530,7 +7530,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>58.64705882352941</v>
+        <v>59.235294117647065</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -7546,7 +7546,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>38.529411764705884</v>
+        <v>36.76470588235295</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -7554,7 +7554,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>60.52941176470589</v>
+        <v>60.88235294117647</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -7562,7 +7562,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>23.058823529411768</v>
+        <v>26.117647058823536</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -7570,7 +7570,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>13.764705882352942</v>
+        <v>13.411764705882351</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -7578,7 +7578,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>33.05882352941177</v>
+        <v>33.529411764705884</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -7594,7 +7594,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>54.52941176470587</v>
+        <v>54.17647058823529</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -7602,7 +7602,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>57.70588235294118</v>
+        <v>57.352941176470594</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -7610,7 +7610,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>21.05882352941176</v>
+        <v>19.94117647058824</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -7618,7 +7618,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>35.17647058823529</v>
+        <v>35.05882352941176</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -7626,7 +7626,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>52.94117647058824</v>
+        <v>57.05882352941176</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -7634,7 +7634,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>39.529411764705884</v>
+        <v>41.52941176470589</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -7642,7 +7642,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>1.3529411764705888</v>
+        <v>3.8235294117647083</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -7650,7 +7650,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>-1.3529411764705905</v>
+        <v>-0.529411764705884</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -7658,7 +7658,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>-0.29411764705882604</v>
+        <v>-0.17647058823529704</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -7674,7 +7674,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>44.76470588235294</v>
+        <v>43.35294117647059</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -7682,7 +7682,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>43.82352941176471</v>
+        <v>43.35294117647059</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -7690,7 +7690,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>38.294117647058826</v>
+        <v>39.588235294117645</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -7698,7 +7698,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>26.941176470588225</v>
+        <v>32.588235294117645</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -7706,7 +7706,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>60.11764705882352</v>
+        <v>60.47058823529413</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -7714,7 +7714,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>39.23529411764706</v>
+        <v>40.17647058823529</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -7722,7 +7722,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>40.1764705882353</v>
+        <v>41.23529411764706</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -7730,7 +7730,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>39.411764705882355</v>
+        <v>38.00000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -7738,7 +7738,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>52.94117647058823</v>
+        <v>53.29411764705882</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -7746,7 +7746,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>65.52941176470588</v>
+        <v>65.76470588235294</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -7754,7 +7754,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>39.76470588235295</v>
+        <v>40.352941176470594</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -7762,7 +7762,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>47.88235294117647</v>
+        <v>47.47058823529412</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -7770,7 +7770,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>21.70588235294118</v>
+        <v>18.411764705882355</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -7778,7 +7778,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>33.294117647058826</v>
+        <v>31.41176470588236</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -7786,7 +7786,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>58.64705882352942</v>
+        <v>56.76470588235294</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -7794,7 +7794,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>53.88235294117648</v>
+        <v>56.470588235294116</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -7802,7 +7802,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>41.76470588235294</v>
+        <v>44.11764705882353</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -7810,7 +7810,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>25.47058823529411</v>
+        <v>26.05882352941176</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -7818,7 +7818,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>42.882352941176464</v>
+        <v>42.411764705882355</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -7826,7 +7826,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>54.23529411764706</v>
+        <v>54.11764705882353</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -7834,7 +7834,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>56.58823529411765</v>
+        <v>57.41176470588236</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -7850,7 +7850,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>41.99999999999999</v>
+        <v>40.23529411764706</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -7858,7 +7858,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>25.000000000000004</v>
+        <v>28.35294117647059</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -7866,7 +7866,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>16.764705882352942</v>
+        <v>22.176470588235297</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -7874,7 +7874,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>46.470588235294116</v>
+        <v>45.29411764705882</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -7882,7 +7882,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>31.941176470588232</v>
+        <v>30.529411764705884</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -7890,7 +7890,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>32.47058823529412</v>
+        <v>32.352941176470594</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -7898,7 +7898,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>26.11764705882353</v>
+        <v>24.588235294117645</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -7906,7 +7906,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>48.11764705882352</v>
+        <v>47.1764705882353</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -7914,7 +7914,7 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>25.647058823529413</v>
+        <v>25.176470588235297</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -7922,7 +7922,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>10.64705882352941</v>
+        <v>10.999999999999996</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -7930,7 +7930,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>46.05882352941177</v>
+        <v>44.29411764705883</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -7938,7 +7938,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>54.70588235294118</v>
+        <v>53.76470588235295</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -7946,7 +7946,7 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>42.8235294117647</v>
+        <v>40.823529411764696</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -7954,7 +7954,7 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>31</v>
+        <v>30.17647058823529</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -7962,7 +7962,7 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>33.1764705882353</v>
+        <v>31.41176470588235</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -7978,7 +7978,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>28.82352941176471</v>
+        <v>26.470588235294116</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -7986,7 +7986,7 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>36.41176470588236</v>
+        <v>36.294117647058826</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -7994,7 +7994,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>48.647058823529406</v>
+        <v>49.82352941176471</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -8002,7 +8002,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>46.470588235294116</v>
+        <v>43.647058823529406</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -8010,7 +8010,7 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>57.76470588235295</v>
+        <v>57.52941176470589</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -8018,7 +8018,7 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>39.35294117647059</v>
+        <v>38.411764705882355</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -8026,7 +8026,7 @@
         <v>72</v>
       </c>
       <c r="B73">
-        <v>62.88235294117648</v>
+        <v>61.82352941176471</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -8034,7 +8034,7 @@
         <v>73</v>
       </c>
       <c r="B74">
-        <v>30.823529411764714</v>
+        <v>31.882352941176475</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -8042,7 +8042,7 @@
         <v>74</v>
       </c>
       <c r="B75">
-        <v>30.411764705882355</v>
+        <v>31.352941176470587</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -8050,7 +8050,7 @@
         <v>75</v>
       </c>
       <c r="B76">
-        <v>24.235294117647058</v>
+        <v>24.352941176470587</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -8058,7 +8058,7 @@
         <v>122</v>
       </c>
       <c r="B77">
-        <v>24.764705882352942</v>
+        <v>26.058823529411768</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -8066,7 +8066,7 @@
         <v>124</v>
       </c>
       <c r="B78">
-        <v>60.76470588235294</v>
+        <v>60.529411764705884</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -8074,7 +8074,7 @@
         <v>125</v>
       </c>
       <c r="B79">
-        <v>54.64705882352941</v>
+        <v>53.94117647058824</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -8082,7 +8082,7 @@
         <v>126</v>
       </c>
       <c r="B80">
-        <v>54.705882352941174</v>
+        <v>53.529411764705884</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -8098,7 +8098,7 @@
         <v>128</v>
       </c>
       <c r="B82">
-        <v>51.52941176470588</v>
+        <v>49.88235294117647</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -8106,7 +8106,7 @@
         <v>129</v>
       </c>
       <c r="B83">
-        <v>51.70588235294118</v>
+        <v>51.58823529411765</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -8114,7 +8114,7 @@
         <v>130</v>
       </c>
       <c r="B84">
-        <v>36.8235294117647</v>
+        <v>38.705882352941174</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -8122,7 +8122,7 @@
         <v>131</v>
       </c>
       <c r="B85">
-        <v>37.82352941176471</v>
+        <v>35.47058823529412</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
@@ -8130,7 +8130,7 @@
         <v>133</v>
       </c>
       <c r="B86">
-        <v>49.529411764705884</v>
+        <v>45.64705882352941</v>
       </c>
     </row>
   </sheetData>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="234">
   <si>
     <t>Ticker</t>
   </si>
@@ -382,7 +382,7 @@
     <t>2027-08-20</t>
   </si>
   <si>
-    <t>2026-08-25</t>
+    <t>2027-08-25</t>
   </si>
   <si>
     <t>2026-10-01</t>
@@ -427,7 +427,7 @@
     <t>_date_</t>
   </si>
   <si>
-    <t>2026-09-22</t>
+    <t>2026-09-24</t>
   </si>
   <si>
     <t>Criteria</t>
@@ -685,25 +685,28 @@
     <t>Triggers</t>
   </si>
   <si>
+    <t>Momentum Breakout, Market Leader, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Market Leader, Stable Uptrend, Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Market Leader</t>
+  </si>
+  <si>
+    <t>Stable Uptrend, Institutional Buying</t>
+  </si>
+  <si>
     <t>Momentum Breakout, Market Leader, Volume Spike, Institutional Buying</t>
   </si>
   <si>
-    <t>Momentum Breakout, Market Leader, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Market Leader, Stable Uptrend, Volume Spike, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Market Leader</t>
+    <t>Momentum Breakout, Volume Spike</t>
   </si>
   <si>
     <t>Institutional Buying</t>
   </si>
   <si>
-    <t>Momentum Breakout, Volume Spike</t>
-  </si>
-  <si>
-    <t>Momentum Breakout</t>
+    <t>Volume Spike, Institutional Buying</t>
   </si>
   <si>
     <t>Momentum Breakout, Volume Spike, Institutional Buying</t>
@@ -715,7 +718,7 @@
     <t>Volume Spike</t>
   </si>
   <si>
-    <t>Volume Spike, Institutional Buying</t>
+    <t>Earnings Upcoming, Institutional Buying</t>
   </si>
   <si>
     <t>Momentum Breakout, Market Leader, Volume Spike</t>
@@ -1413,7 +1416,7 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>65.76470588235294</v>
+        <v>66.58823529411764</v>
       </c>
       <c r="C2" t="s">
         <v>221</v>
@@ -1424,10 +1427,10 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>62.8235294117647</v>
+        <v>62.588235294117645</v>
       </c>
       <c r="C3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1435,10 +1438,10 @@
         <v>72</v>
       </c>
       <c r="B4">
-        <v>61.82352941176471</v>
+        <v>61.94117647058824</v>
       </c>
       <c r="C4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1446,51 +1449,51 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>61</v>
+        <v>61.705882352941174</v>
       </c>
       <c r="C5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="B6">
-        <v>60.88235294117647</v>
+        <v>61.58823529411765</v>
       </c>
       <c r="C6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>124</v>
+        <v>13</v>
       </c>
       <c r="B7">
-        <v>60.529411764705884</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>124</v>
       </c>
       <c r="B8">
-        <v>60.47058823529413</v>
+        <v>60.64705882352942</v>
       </c>
       <c r="C8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="B9">
-        <v>59.941176470588246</v>
+        <v>60</v>
       </c>
       <c r="C9" t="s">
         <v>225</v>
@@ -1501,7 +1504,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>59.235294117647065</v>
+        <v>58.05882352941177</v>
       </c>
       <c r="C10" t="s">
         <v>221</v>
@@ -1509,43 +1512,43 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="B11">
-        <v>57.52941176470589</v>
+        <v>57.58823529411765</v>
       </c>
       <c r="C11" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="B12">
         <v>57.41176470588236</v>
       </c>
       <c r="C12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B13">
-        <v>57.352941176470594</v>
+        <v>57.05882352941175</v>
       </c>
       <c r="C13" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="B14">
-        <v>57.05882352941176</v>
+        <v>56.94117647058823</v>
       </c>
       <c r="C14" t="s">
         <v>228</v>
@@ -1553,10 +1556,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B15">
-        <v>56.76470588235294</v>
+        <v>56.588235294117645</v>
       </c>
       <c r="C15" t="s">
         <v>229</v>
@@ -1564,43 +1567,43 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="B16">
-        <v>56.470588235294116</v>
+        <v>56.411764705882355</v>
       </c>
       <c r="C16" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="B17">
-        <v>55.76470588235293</v>
+        <v>56.17647058823529</v>
       </c>
       <c r="C17" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="B18">
-        <v>54.17647058823529</v>
+        <v>56.17647058823529</v>
       </c>
       <c r="C18" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="B19">
-        <v>54.11764705882353</v>
+        <v>55.88235294117647</v>
       </c>
       <c r="C19" t="s">
         <v>231</v>
@@ -1608,32 +1611,32 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>127</v>
+        <v>3</v>
       </c>
       <c r="B20">
-        <v>54.11764705882352</v>
+        <v>53.294117647058826</v>
       </c>
       <c r="C20" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>3</v>
+        <v>125</v>
       </c>
       <c r="B21">
-        <v>54</v>
+        <v>51.94117647058824</v>
       </c>
       <c r="C21" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>125</v>
+        <v>36</v>
       </c>
       <c r="B22">
-        <v>53.94117647058824</v>
+        <v>51.88235294117647</v>
       </c>
       <c r="C22" t="s">
         <v>226</v>
@@ -1641,13 +1644,13 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>61</v>
+        <v>127</v>
       </c>
       <c r="B23">
-        <v>53.76470588235295</v>
+        <v>51.76470588235294</v>
       </c>
       <c r="C23" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -1655,7 +1658,7 @@
         <v>126</v>
       </c>
       <c r="B24">
-        <v>53.529411764705884</v>
+        <v>51.29411764705883</v>
       </c>
       <c r="C24" t="s">
         <v>228</v>
@@ -1663,10 +1666,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="B25">
-        <v>53.29411764705882</v>
+        <v>51.05882352941176</v>
       </c>
       <c r="C25" t="s">
         <v>227</v>
@@ -1674,35 +1677,35 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="B26">
-        <v>53.17647058823529</v>
+        <v>50.94117647058823</v>
       </c>
       <c r="C26" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
       <c r="B27">
-        <v>51.58823529411765</v>
+        <v>49.882352941176464</v>
       </c>
       <c r="C27" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>128</v>
+        <v>53</v>
       </c>
       <c r="B28">
-        <v>49.88235294117647</v>
+        <v>47.529411764705884</v>
       </c>
       <c r="C28" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -1710,51 +1713,51 @@
         <v>39</v>
       </c>
       <c r="B29">
-        <v>47.47058823529412</v>
+        <v>47.235294117647065</v>
       </c>
       <c r="C29" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>57</v>
+        <v>133</v>
       </c>
       <c r="B30">
-        <v>47.1764705882353</v>
+        <v>46.588235294117645</v>
       </c>
       <c r="C30" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="B31">
-        <v>45.88235294117647</v>
+        <v>46.35294117647059</v>
       </c>
       <c r="C31" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1</v>
+        <v>128</v>
       </c>
       <c r="B32">
-        <v>45.764705882352935</v>
+        <v>46.35294117647059</v>
       </c>
       <c r="C32" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>133</v>
+        <v>1</v>
       </c>
       <c r="B33">
-        <v>45.64705882352941</v>
+        <v>45.647058823529406</v>
       </c>
       <c r="C33" t="s">
         <v>231</v>
@@ -1762,10 +1765,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B34">
-        <v>45.29411764705882</v>
+        <v>45.352941176470594</v>
       </c>
       <c r="C34" t="s">
         <v>231</v>
@@ -1773,10 +1776,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="B35">
-        <v>44.29411764705883</v>
+        <v>43.94117647058824</v>
       </c>
       <c r="C35" t="s">
         <v>231</v>
@@ -1784,10 +1787,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="B36">
-        <v>44.11764705882353</v>
+        <v>43.41176470588235</v>
       </c>
       <c r="C36" t="s">
         <v>231</v>
@@ -1795,101 +1798,101 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="B37">
-        <v>43.647058823529406</v>
+        <v>43.11764705882353</v>
       </c>
       <c r="C37" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="B38">
-        <v>43.35294117647059</v>
+        <v>42.76470588235294</v>
       </c>
       <c r="C38" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B39">
-        <v>43.35294117647059</v>
+        <v>42.47058823529412</v>
       </c>
       <c r="C39" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B40">
-        <v>42.411764705882355</v>
+        <v>42.117647058823536</v>
       </c>
       <c r="C40" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B41">
-        <v>41.52941176470589</v>
+        <v>41.23529411764706</v>
       </c>
       <c r="C41" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="B42">
-        <v>40.823529411764696</v>
+        <v>41.05882352941176</v>
       </c>
       <c r="C42" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="B43">
-        <v>40.352941176470594</v>
+        <v>40.76470588235294</v>
       </c>
       <c r="C43" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="B44">
-        <v>40.23529411764706</v>
+        <v>40.58823529411765</v>
       </c>
       <c r="C44" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="B45">
-        <v>40.17647058823529</v>
+        <v>39.70588235294118</v>
       </c>
       <c r="C45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -1897,54 +1900,54 @@
         <v>30</v>
       </c>
       <c r="B46">
-        <v>39.588235294117645</v>
+        <v>39</v>
       </c>
       <c r="C46" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>7</v>
+        <v>71</v>
       </c>
       <c r="B47">
-        <v>38.705882352941174</v>
+        <v>39</v>
       </c>
       <c r="C47" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>130</v>
+        <v>35</v>
       </c>
       <c r="B48">
-        <v>38.705882352941174</v>
+        <v>38.411764705882355</v>
       </c>
       <c r="C48" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B49">
-        <v>38.411764705882355</v>
+        <v>38.05882352941177</v>
       </c>
       <c r="C49" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B50">
-        <v>38.00000000000001</v>
+        <v>37.35294117647059</v>
       </c>
       <c r="C50" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -1952,10 +1955,10 @@
         <v>12</v>
       </c>
       <c r="B51">
-        <v>36.76470588235295</v>
+        <v>37.00000000000001</v>
       </c>
       <c r="C51" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -2183,37 +2186,37 @@
         <v>67.05882352941175</v>
       </c>
       <c r="D2" s="1">
-        <v>-2.0978120978120978</v>
+        <v>-2.047619047619048</v>
       </c>
       <c r="E2" s="1">
         <v>-2.08</v>
       </c>
       <c r="F2" s="1">
-        <v>0.12235458909482223</v>
+        <v>0.13172893774885863</v>
       </c>
       <c r="G2" s="1">
         <v>0.21</v>
       </c>
       <c r="H2" s="1">
-        <v>46.1</v>
+        <v>50.62</v>
       </c>
       <c r="I2" s="1">
-        <v>8.01</v>
+        <v>9.36</v>
       </c>
       <c r="J2" s="1">
-        <v>0.015687366545096053</v>
+        <v>0.013554747128503516</v>
       </c>
       <c r="K2" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L2" s="1">
-        <v>-460</v>
+        <v>-457</v>
       </c>
       <c r="M2" s="1">
-        <v>0.08434679399457945</v>
+        <v>0.08888369669755436</v>
       </c>
       <c r="N2" s="1">
-        <v>14.320792703286145</v>
+        <v>15.38681790409775</v>
       </c>
       <c r="O2" s="1">
         <v>69.41176470588235</v>
@@ -2222,16 +2225,16 @@
         <v>16.29652721982991</v>
       </c>
       <c r="Q2" s="1">
-        <v>48.11764705882352</v>
+        <v>50.11764705882352</v>
       </c>
       <c r="R2" s="1">
-        <v>45.764705882352935</v>
+        <v>45.647058823529406</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>95</v>
       </c>
       <c r="T2" s="1">
-        <v>25.95</v>
+        <v>25.83</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -2245,55 +2248,55 @@
         <v>54.11764705882353</v>
       </c>
       <c r="D3" s="2">
-        <v>26.710256410256406</v>
+        <v>26.676923076923075</v>
       </c>
       <c r="E3" s="2">
         <v>3.59</v>
       </c>
       <c r="F3" s="2">
-        <v>-0.014726308882188316</v>
+        <v>0.037824397126275</v>
       </c>
       <c r="G3" s="2">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="H3" s="2">
-        <v>70.85</v>
+        <v>69.23</v>
       </c>
       <c r="I3" s="2">
-        <v>69.7</v>
+        <v>67.95</v>
       </c>
       <c r="J3" s="2">
-        <v>0.001892919301467904</v>
+        <v>0.010272886926532632</v>
       </c>
       <c r="K3" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L3" s="2">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="M3" s="2">
-        <v>0.0569592793448519</v>
+        <v>0.11754908617110704</v>
       </c>
       <c r="N3" s="2">
-        <v>11.582041238313389</v>
+        <v>18.253356851453013</v>
       </c>
       <c r="O3" s="2">
-        <v>65.88235294117646</v>
+        <v>72.94117647058823</v>
       </c>
       <c r="P3" s="2">
         <v>26.053946839070953</v>
       </c>
       <c r="Q3" s="2">
-        <v>70.3529411764706</v>
+        <v>73.29411764705883</v>
       </c>
       <c r="R3" s="2">
-        <v>53.17647058823529</v>
+        <v>56.94117647058823</v>
       </c>
       <c r="S3" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T3" s="2">
-        <v>-13.9</v>
+        <v>-10.13</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -2313,19 +2316,19 @@
         <v>6.34</v>
       </c>
       <c r="F4" s="2">
-        <v>0.4216343854971777</v>
+        <v>0.3691387491148527</v>
       </c>
       <c r="G4" s="2">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="H4" s="2">
-        <v>57.79</v>
+        <v>53.7</v>
       </c>
       <c r="I4" s="2">
-        <v>52.73</v>
+        <v>48.61</v>
       </c>
       <c r="J4" s="2">
-        <v>0.022897271333209533</v>
+        <v>0.023150448238343307</v>
       </c>
       <c r="K4" s="2" t="b">
         <v>0</v>
@@ -2334,28 +2337,28 @@
         <v>181</v>
       </c>
       <c r="M4" s="2">
-        <v>0.4389543933909592</v>
+        <v>0.3881208179350508</v>
       </c>
       <c r="N4" s="2">
-        <v>49.781552642924126</v>
+        <v>45.310530027847406</v>
       </c>
       <c r="O4" s="2">
-        <v>91.76470588235294</v>
+        <v>89.41176470588236</v>
       </c>
       <c r="P4" s="2">
         <v>19.349659482175007</v>
       </c>
       <c r="Q4" s="2">
-        <v>58.58823529411766</v>
+        <v>58.117647058823536</v>
       </c>
       <c r="R4" s="2">
-        <v>54</v>
+        <v>53.294117647058826</v>
       </c>
       <c r="S4" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T4" s="2">
-        <v>5.65</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -2375,19 +2378,19 @@
         <v>1.69</v>
       </c>
       <c r="F5" s="1">
-        <v>-0.17608998882001448</v>
+        <v>-0.10211514577301976</v>
       </c>
       <c r="G5" s="1">
         <v>1.91</v>
       </c>
       <c r="H5" s="1">
-        <v>58.85</v>
+        <v>60.31</v>
       </c>
       <c r="I5" s="1">
-        <v>-5.25</v>
+        <v>-4.11</v>
       </c>
       <c r="J5" s="1">
-        <v>-0.01190530793671953</v>
+        <v>-0.007650825092846842</v>
       </c>
       <c r="K5" s="1" t="b">
         <v>0</v>
@@ -2396,28 +2399,28 @@
         <v>143</v>
       </c>
       <c r="M5" s="1">
-        <v>-0.13230885775517787</v>
+        <v>-0.05276176684050471</v>
       </c>
       <c r="N5" s="1">
-        <v>-7.344772471689587</v>
+        <v>1.222271550291836</v>
       </c>
       <c r="O5" s="1">
-        <v>32.94117647058823</v>
+        <v>48.23529411764706</v>
       </c>
       <c r="P5" s="1">
         <v>33.002444654975626</v>
       </c>
       <c r="Q5" s="1">
-        <v>51.88235294117648</v>
+        <v>54</v>
       </c>
       <c r="R5" s="1">
-        <v>35.705882352941174</v>
+        <v>40.76470588235294</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T5" s="1">
-        <v>-10.27</v>
+        <v>-5.21</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -2431,25 +2434,25 @@
         <v>49.411764705882355</v>
       </c>
       <c r="D6" s="1">
-        <v>0.8706624605678233</v>
+        <v>0.8264984227129338</v>
       </c>
       <c r="E6" s="1">
         <v>-1.88</v>
       </c>
       <c r="F6" s="1">
-        <v>-0.08114159750692664</v>
+        <v>-0.10420662709478996</v>
       </c>
       <c r="G6" s="1">
         <v>1.6</v>
       </c>
       <c r="H6" s="1">
-        <v>42.7</v>
+        <v>37.18</v>
       </c>
       <c r="I6" s="1">
-        <v>-13.05</v>
+        <v>-15.85</v>
       </c>
       <c r="J6" s="1">
-        <v>-0.000491060031693518</v>
+        <v>-0.0020607832537343487</v>
       </c>
       <c r="K6" s="1" t="b">
         <v>1</v>
@@ -2458,28 +2461,28 @@
         <v>-204</v>
       </c>
       <c r="M6" s="1">
-        <v>-0.05227491768395742</v>
+        <v>-0.07166593768873608</v>
       </c>
       <c r="N6" s="1">
-        <v>0.6586215354324567</v>
+        <v>-0.6681455345312957</v>
       </c>
       <c r="O6" s="1">
-        <v>47.05882352941176</v>
+        <v>45.88235294117647</v>
       </c>
       <c r="P6" s="1">
         <v>27.785495103772316</v>
       </c>
       <c r="Q6" s="1">
-        <v>42</v>
+        <v>40.117647058823536</v>
       </c>
       <c r="R6" s="1">
-        <v>36.41176470588235</v>
+        <v>35.588235294117645</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T6" s="1">
-        <v>17.33</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -2493,55 +2496,55 @@
         <v>69.41176470588235</v>
       </c>
       <c r="D7" s="2">
-        <v>7.841972187104931</v>
+        <v>7.8103666245259165</v>
       </c>
       <c r="E7" s="2">
         <v>0.5</v>
       </c>
       <c r="F7" s="2">
-        <v>-0.027789106745771536</v>
+        <v>0.0020655019957711296</v>
       </c>
       <c r="G7" s="2">
         <v>2.22</v>
       </c>
       <c r="H7" s="2">
-        <v>56.92</v>
+        <v>54.23</v>
       </c>
       <c r="I7" s="2">
-        <v>13.73</v>
+        <v>12.47</v>
       </c>
       <c r="J7" s="2">
-        <v>0.007958419461773562</v>
+        <v>0.00844467352025804</v>
       </c>
       <c r="K7" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L7" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M7" s="2">
-        <v>0.03090647556093251</v>
+        <v>0.06823157045474737</v>
       </c>
       <c r="N7" s="2">
-        <v>8.97676085992146</v>
+        <v>13.321605279817053</v>
       </c>
       <c r="O7" s="2">
-        <v>61.1764705882353</v>
+        <v>65.88235294117646</v>
       </c>
       <c r="P7" s="2">
         <v>19.398494070050486</v>
       </c>
       <c r="Q7" s="2">
-        <v>67.6470588235294</v>
+        <v>67.29411764705883</v>
       </c>
       <c r="R7" s="2">
-        <v>55.76470588235293</v>
+        <v>57.05882352941175</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T7" s="2">
-        <v>7.35</v>
+        <v>8.64</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -2561,49 +2564,49 @@
         <v>2.63</v>
       </c>
       <c r="F8" s="1">
-        <v>-0.11170199013444851</v>
+        <v>-0.13658805305680174</v>
       </c>
       <c r="G8" s="1">
         <v>0.61</v>
       </c>
       <c r="H8" s="1">
-        <v>37.47</v>
+        <v>33.1</v>
       </c>
       <c r="I8" s="1">
-        <v>6.37</v>
+        <v>4.37</v>
       </c>
       <c r="J8" s="1">
-        <v>-0.0121088336555875</v>
+        <v>-0.012906366634134737</v>
       </c>
       <c r="K8" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L8" s="1">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="M8" s="1">
-        <v>-0.1304653320193785</v>
+        <v>-0.15773950117073676</v>
       </c>
       <c r="N8" s="1">
-        <v>-7.160419898109647</v>
+        <v>-9.275501882731369</v>
       </c>
       <c r="O8" s="1">
-        <v>34.11764705882353</v>
+        <v>25.882352941176475</v>
       </c>
       <c r="P8" s="1">
-        <v>14.011691026293512</v>
+        <v>14.910048504309984</v>
       </c>
       <c r="Q8" s="1">
-        <v>44</v>
+        <v>42.823529411764696</v>
       </c>
       <c r="R8" s="1">
-        <v>38.705882352941174</v>
+        <v>35.76470588235294</v>
       </c>
       <c r="S8" s="1" t="s">
         <v>101</v>
       </c>
       <c r="T8" s="1">
-        <v>-21.05</v>
+        <v>-23.99</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -2617,25 +2620,25 @@
         <v>41.17647058823529</v>
       </c>
       <c r="D9" s="2">
-        <v>36.13675213675214</v>
+        <v>36.128205128205124</v>
       </c>
       <c r="E9" s="2">
         <v>2.96</v>
       </c>
       <c r="F9" s="2">
-        <v>0.4444060477068711</v>
+        <v>0.5922545047803275</v>
       </c>
       <c r="G9" s="2">
         <v>1.6</v>
       </c>
       <c r="H9" s="2">
-        <v>61.86</v>
+        <v>65.07</v>
       </c>
       <c r="I9" s="2">
-        <v>21.23</v>
+        <v>25.21</v>
       </c>
       <c r="J9" s="2">
-        <v>0.029573599732622087</v>
+        <v>0.033494708858078245</v>
       </c>
       <c r="K9" s="2" t="b">
         <v>0</v>
@@ -2644,28 +2647,28 @@
         <v>-112</v>
       </c>
       <c r="M9" s="2">
-        <v>0.4732727275298403</v>
+        <v>0.6247951941863814</v>
       </c>
       <c r="N9" s="2">
-        <v>53.21338605681224</v>
+        <v>68.97796765298045</v>
       </c>
       <c r="O9" s="2">
-        <v>92.94117647058823</v>
+        <v>95.29411764705881</v>
       </c>
       <c r="P9" s="2">
         <v>33.227512780245505</v>
       </c>
       <c r="Q9" s="2">
-        <v>71.88235294117646</v>
+        <v>72.58823529411765</v>
       </c>
       <c r="R9" s="2">
-        <v>61</v>
+        <v>61.705882352941174</v>
       </c>
       <c r="S9" s="2" t="s">
         <v>102</v>
       </c>
       <c r="T9" s="2">
-        <v>33.62</v>
+        <v>34.33</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -2685,19 +2688,19 @@
         <v>0.08</v>
       </c>
       <c r="F10" s="1">
-        <v>-0.061693416901536235</v>
+        <v>-0.08843909450990346</v>
       </c>
       <c r="G10" s="1">
         <v>1.42</v>
       </c>
       <c r="H10" s="1">
-        <v>46.91</v>
+        <v>44.57</v>
       </c>
       <c r="I10" s="1">
-        <v>0.1</v>
+        <v>-0.79</v>
       </c>
       <c r="J10" s="1">
-        <v>0.008287253135108447</v>
+        <v>0.007969366079722411</v>
       </c>
       <c r="K10" s="1" t="b">
         <v>1</v>
@@ -2706,28 +2709,28 @@
         <v>-49</v>
       </c>
       <c r="M10" s="1">
-        <v>-0.041486741025457796</v>
+        <v>-0.06566061192566575</v>
       </c>
       <c r="N10" s="1">
-        <v>1.7374392012824234</v>
+        <v>-0.067612958224256</v>
       </c>
       <c r="O10" s="1">
-        <v>52.94117647058824</v>
+        <v>47.05882352941176</v>
       </c>
       <c r="P10" s="1">
         <v>14.568379622257217</v>
       </c>
       <c r="Q10" s="1">
-        <v>51.294117647058826</v>
+        <v>49.88235294117647</v>
       </c>
       <c r="R10" s="1">
-        <v>45.88235294117647</v>
+        <v>43.41176470588235</v>
       </c>
       <c r="S10" s="1" t="s">
         <v>103</v>
       </c>
       <c r="T10" s="1">
-        <v>10.33</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -2747,49 +2750,49 @@
         <v>2.19</v>
       </c>
       <c r="F11" s="2">
-        <v>0.5692639602385912</v>
+        <v>0.5436053945474817</v>
       </c>
       <c r="G11" s="2">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="H11" s="2">
-        <v>63.87</v>
+        <v>63.53</v>
       </c>
       <c r="I11" s="2">
-        <v>46.37</v>
+        <v>45.88</v>
       </c>
       <c r="J11" s="2">
-        <v>0.025101987323489144</v>
+        <v>0.025187103761932495</v>
       </c>
       <c r="K11" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="2">
         <v>40</v>
       </c>
       <c r="M11" s="2">
-        <v>0.5557928429878722</v>
+        <v>0.527877394667889</v>
       </c>
       <c r="N11" s="2">
-        <v>61.465397602615425</v>
+        <v>59.2861877011312</v>
       </c>
       <c r="O11" s="2">
-        <v>96.47058823529412</v>
+        <v>92.94117647058823</v>
       </c>
       <c r="P11" s="2">
         <v>21.2185970476566</v>
       </c>
       <c r="Q11" s="2">
-        <v>66.3529411764706</v>
+        <v>66.11764705882354</v>
       </c>
       <c r="R11" s="2">
-        <v>59.235294117647065</v>
+        <v>58.05882352941177</v>
       </c>
       <c r="S11" s="2" t="s">
         <v>104</v>
       </c>
       <c r="T11" s="2">
-        <v>7.59</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -2809,19 +2812,19 @@
         <v>1.33</v>
       </c>
       <c r="F12" s="2">
-        <v>0.8692235811798992</v>
+        <v>0.7507429854997593</v>
       </c>
       <c r="G12" s="2">
         <v>0.99</v>
       </c>
       <c r="H12" s="2">
-        <v>65.08</v>
+        <v>60.07</v>
       </c>
       <c r="I12" s="2">
-        <v>56.43</v>
+        <v>52.13</v>
       </c>
       <c r="J12" s="2">
-        <v>0.04296681619528336</v>
+        <v>0.04224989986338375</v>
       </c>
       <c r="K12" s="2" t="b">
         <v>0</v>
@@ -2830,10 +2833,10 @@
         <v>30</v>
       </c>
       <c r="M12" s="2">
-        <v>0.8687424698495163</v>
+        <v>0.7502006406763251</v>
       </c>
       <c r="N12" s="2">
-        <v>92.76036028877982</v>
+        <v>81.51851230197482</v>
       </c>
       <c r="O12" s="2">
         <v>100</v>
@@ -2842,16 +2845,16 @@
         <v>23.557267760130397</v>
       </c>
       <c r="Q12" s="2">
-        <v>71.17647058823529</v>
+        <v>69.52941176470588</v>
       </c>
       <c r="R12" s="2">
-        <v>62.8235294117647</v>
+        <v>62.588235294117645</v>
       </c>
       <c r="S12" s="2" t="s">
         <v>105</v>
       </c>
       <c r="T12" s="2">
-        <v>10.08</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -2871,19 +2874,19 @@
         <v>-1.08</v>
       </c>
       <c r="F13" s="1">
-        <v>0.3554111746281361</v>
+        <v>0.4230021877811984</v>
       </c>
       <c r="G13" s="1">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H13" s="1">
-        <v>50.77</v>
+        <v>54.15</v>
       </c>
       <c r="I13" s="1">
-        <v>13.59</v>
+        <v>17.49</v>
       </c>
       <c r="J13" s="1">
-        <v>0.04600715560834621</v>
+        <v>0.0473234816342728</v>
       </c>
       <c r="K13" s="1" t="b">
         <v>1</v>
@@ -2892,28 +2895,28 @@
         <v>5</v>
       </c>
       <c r="M13" s="1">
-        <v>0.3833156317903397</v>
+        <v>0.4539158427169496</v>
       </c>
       <c r="N13" s="1">
-        <v>44.21767648286217</v>
+        <v>51.89003250603727</v>
       </c>
       <c r="O13" s="1">
-        <v>89.41176470588236</v>
+        <v>90.58823529411765</v>
       </c>
       <c r="P13" s="1">
         <v>40.13761891809808</v>
       </c>
       <c r="Q13" s="1">
-        <v>41.529411764705884</v>
+        <v>42.94117647058824</v>
       </c>
       <c r="R13" s="1">
-        <v>36.76470588235295</v>
+        <v>37.00000000000001</v>
       </c>
       <c r="S13" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T13" s="1">
-        <v>35.97</v>
+        <v>36.21</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -2933,31 +2936,31 @@
         <v>-1.75</v>
       </c>
       <c r="F14" s="2">
-        <v>0.6029356493111555</v>
+        <v>0.6865564862931275</v>
       </c>
       <c r="G14" s="2">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="H14" s="2">
-        <v>66.04</v>
+        <v>70.21</v>
       </c>
       <c r="I14" s="2">
-        <v>78.82</v>
+        <v>87.96</v>
       </c>
       <c r="J14" s="2">
-        <v>0.02817723147779358</v>
+        <v>0.03120544454354591</v>
       </c>
       <c r="K14" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L14" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M14" s="2">
-        <v>0.5913889773819678</v>
+        <v>0.6729978657072717</v>
       </c>
       <c r="N14" s="2">
-        <v>65.02501104202497</v>
+        <v>73.7982348050695</v>
       </c>
       <c r="O14" s="2">
         <v>97.6470588235294</v>
@@ -2966,78 +2969,78 @@
         <v>19.142997204429033</v>
       </c>
       <c r="Q14" s="2">
-        <v>68.23529411764707</v>
+        <v>68.82352941176471</v>
       </c>
       <c r="R14" s="2">
-        <v>60.88235294117647</v>
+        <v>61</v>
       </c>
       <c r="S14" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T14" s="2">
-        <v>4.97</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="1">
         <v>-2.12</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="1">
         <v>15.294117647058824</v>
       </c>
-      <c r="D15" s="3">
-        <v>19.245283018867923</v>
-      </c>
-      <c r="E15" s="3">
+      <c r="D15" s="1">
+        <v>18.990566037735846</v>
+      </c>
+      <c r="E15" s="1">
         <v>1.49</v>
       </c>
-      <c r="F15" s="3">
-        <v>-0.25590666911775917</v>
-      </c>
-      <c r="G15" s="3">
-        <v>2.27</v>
-      </c>
-      <c r="H15" s="3">
-        <v>68.81</v>
-      </c>
-      <c r="I15" s="3">
-        <v>54.27</v>
-      </c>
-      <c r="J15" s="3">
-        <v>-0.005688061350404316</v>
-      </c>
-      <c r="K15" s="3" t="b">
+      <c r="F15" s="1">
+        <v>-0.20152043253389712</v>
+      </c>
+      <c r="G15" s="1">
+        <v>2.25</v>
+      </c>
+      <c r="H15" s="1">
+        <v>67.25</v>
+      </c>
+      <c r="I15" s="1">
+        <v>53.01</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0.008670674726406103</v>
+      </c>
+      <c r="K15" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L15" s="3">
-        <v>1030</v>
-      </c>
-      <c r="M15" s="3">
-        <v>-0.19480553015914104</v>
-      </c>
-      <c r="N15" s="3">
-        <v>-13.594439712085904</v>
-      </c>
-      <c r="O15" s="3">
-        <v>24.705882352941178</v>
-      </c>
-      <c r="P15" s="3">
+      <c r="L15" s="1">
+        <v>1031</v>
+      </c>
+      <c r="M15" s="1">
+        <v>-0.1337273296046182</v>
+      </c>
+      <c r="N15" s="1">
+        <v>-6.874284726119502</v>
+      </c>
+      <c r="O15" s="1">
+        <v>31.76470588235294</v>
+      </c>
+      <c r="P15" s="1">
         <v>41.90435941885386</v>
       </c>
-      <c r="Q15" s="3">
-        <v>54.352941176470594</v>
-      </c>
-      <c r="R15" s="3">
-        <v>26.117647058823536</v>
-      </c>
-      <c r="S15" s="3" t="s">
+      <c r="Q15" s="1">
+        <v>59.76470588235295</v>
+      </c>
+      <c r="R15" s="1">
+        <v>30.88235294117647</v>
+      </c>
+      <c r="S15" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="T15" s="3">
-        <v>-32.3</v>
+      <c r="T15" s="1">
+        <v>-27.53</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -3057,19 +3060,19 @@
         <v>29.93</v>
       </c>
       <c r="F16" s="3">
-        <v>-0.32147700664168166</v>
+        <v>-0.2998474830571089</v>
       </c>
       <c r="G16" s="3">
         <v>1.8</v>
       </c>
       <c r="H16" s="3">
-        <v>49.47</v>
+        <v>50.07</v>
       </c>
       <c r="I16" s="3">
-        <v>-4.13</v>
+        <v>-3.72</v>
       </c>
       <c r="J16" s="3">
-        <v>-0.03587144521515425</v>
+        <v>-0.02683543490510299</v>
       </c>
       <c r="K16" s="3" t="b">
         <v>1</v>
@@ -3078,28 +3081,28 @@
         <v>27</v>
       </c>
       <c r="M16" s="3">
-        <v>-0.282988100211056</v>
+        <v>-0.2564598971823704</v>
       </c>
       <c r="N16" s="3">
-        <v>-22.412696717277406</v>
+        <v>-19.147541483894724</v>
       </c>
       <c r="O16" s="3">
-        <v>11.76470588235294</v>
+        <v>10.588235294117647</v>
       </c>
       <c r="P16" s="3">
         <v>40.1905830435425</v>
       </c>
       <c r="Q16" s="3">
-        <v>30.11764705882353</v>
+        <v>30.588235294117645</v>
       </c>
       <c r="R16" s="3">
-        <v>13.411764705882351</v>
+        <v>13.058823529411764</v>
       </c>
       <c r="S16" s="3" t="s">
         <v>108</v>
       </c>
       <c r="T16" s="3">
-        <v>-29.82</v>
+        <v>-30.17</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -3113,25 +3116,25 @@
         <v>5.88235294117647</v>
       </c>
       <c r="D17" s="1">
-        <v>6.40546218487395</v>
+        <v>6.226890756302521</v>
       </c>
       <c r="E17" s="1">
         <v>-1.64</v>
       </c>
       <c r="F17" s="1">
-        <v>-0.0223939315990294</v>
+        <v>-0.07341890325967368</v>
       </c>
       <c r="G17" s="1">
         <v>1.76</v>
       </c>
       <c r="H17" s="1">
-        <v>59.23</v>
+        <v>51.78</v>
       </c>
       <c r="I17" s="1">
-        <v>9.23</v>
+        <v>4.97</v>
       </c>
       <c r="J17" s="1">
-        <v>-0.005724892285899171</v>
+        <v>-0.00003944970876741593</v>
       </c>
       <c r="K17" s="1" t="b">
         <v>1</v>
@@ -3140,28 +3143,28 @@
         <v>31</v>
       </c>
       <c r="M17" s="1">
-        <v>0.014170529510064922</v>
+        <v>-0.03220069667867209</v>
       </c>
       <c r="N17" s="1">
-        <v>7.303166254834687</v>
+        <v>3.2783785664751077</v>
       </c>
       <c r="O17" s="1">
-        <v>58.82352941176471</v>
+        <v>54.11764705882353</v>
       </c>
       <c r="P17" s="1">
         <v>24.80206596461608</v>
       </c>
       <c r="Q17" s="1">
-        <v>40.94117647058823</v>
+        <v>41.05882352941177</v>
       </c>
       <c r="R17" s="1">
-        <v>33.529411764705884</v>
+        <v>33.294117647058826</v>
       </c>
       <c r="S17" s="1" t="s">
         <v>102</v>
       </c>
       <c r="T17" s="1">
-        <v>0.36</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -3181,19 +3184,19 @@
         <v>11.08</v>
       </c>
       <c r="F18" s="3">
-        <v>-0.671927651428184</v>
+        <v>-0.709113646504802</v>
       </c>
       <c r="G18" s="3">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="H18" s="3">
-        <v>16.58</v>
+        <v>19.48</v>
       </c>
       <c r="I18" s="3">
-        <v>-55.05</v>
+        <v>-55.62</v>
       </c>
       <c r="J18" s="3">
-        <v>-0.08051049341946842</v>
+        <v>-0.07868279643766589</v>
       </c>
       <c r="K18" s="3" t="b">
         <v>1</v>
@@ -3202,16 +3205,16 @@
         <v>31</v>
       </c>
       <c r="M18" s="3">
-        <v>-0.6675976494547387</v>
+        <v>-0.7026055086235913</v>
       </c>
       <c r="N18" s="3">
-        <v>-60.873651641645665</v>
+        <v>-63.76210262801681</v>
       </c>
       <c r="O18" s="3">
         <v>1.1764705882352942</v>
       </c>
       <c r="P18" s="3">
-        <v>66.08306146236951</v>
+        <v>67.99674143147296</v>
       </c>
       <c r="Q18" s="3">
         <v>39.647058823529406</v>
@@ -3243,19 +3246,19 @@
         <v>3.1</v>
       </c>
       <c r="F19" s="2">
-        <v>0.08137945031094068</v>
+        <v>0.13823063380827963</v>
       </c>
       <c r="G19" s="2">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H19" s="2">
-        <v>51.72</v>
+        <v>63.77</v>
       </c>
       <c r="I19" s="2">
-        <v>12.21</v>
+        <v>17.67</v>
       </c>
       <c r="J19" s="2">
-        <v>0.0069900163072013745</v>
+        <v>0.008014195843523662</v>
       </c>
       <c r="K19" s="2" t="b">
         <v>1</v>
@@ -3264,28 +3267,28 @@
         <v>-60</v>
       </c>
       <c r="M19" s="2">
-        <v>0.03807943057648688</v>
+        <v>0.08887725487576459</v>
       </c>
       <c r="N19" s="2">
-        <v>9.694056361476889</v>
+        <v>15.386173721918766</v>
       </c>
       <c r="O19" s="2">
-        <v>63.52941176470588</v>
+        <v>68.23529411764706</v>
       </c>
       <c r="P19" s="2">
         <v>11.392700631623551</v>
       </c>
       <c r="Q19" s="2">
-        <v>60.58823529411764</v>
+        <v>64.47058823529412</v>
       </c>
       <c r="R19" s="2">
-        <v>54.17647058823529</v>
+        <v>55.88235294117647</v>
       </c>
       <c r="S19" s="2" t="s">
         <v>110</v>
       </c>
       <c r="T19" s="2">
-        <v>5.76</v>
+        <v>7.47</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -3305,49 +3308,49 @@
         <v>-5.69</v>
       </c>
       <c r="F20" s="2">
-        <v>0.2800570477168324</v>
+        <v>0.3328171899283523</v>
       </c>
       <c r="G20" s="2">
         <v>1.07</v>
       </c>
       <c r="H20" s="2">
-        <v>56.22</v>
+        <v>57.25</v>
       </c>
       <c r="I20" s="2">
-        <v>23.64</v>
+        <v>24.03</v>
       </c>
       <c r="J20" s="2">
-        <v>0.024914226042989283</v>
+        <v>0.024704990513418974</v>
       </c>
       <c r="K20" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" s="2">
         <v>8</v>
       </c>
       <c r="M20" s="2">
-        <v>0.2834248270295121</v>
+        <v>0.3366136036923919</v>
       </c>
       <c r="N20" s="2">
-        <v>34.22859600677942</v>
+        <v>40.1598086035815</v>
       </c>
       <c r="O20" s="2">
-        <v>85.88235294117646</v>
+        <v>87.05882352941177</v>
       </c>
       <c r="P20" s="2">
         <v>15.865501923269152</v>
       </c>
       <c r="Q20" s="2">
-        <v>61.529411764705884</v>
+        <v>62.23529411764706</v>
       </c>
       <c r="R20" s="2">
-        <v>57.352941176470594</v>
+        <v>57.58823529411765</v>
       </c>
       <c r="S20" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T20" s="2">
-        <v>21.5</v>
+        <v>21.73</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -3361,55 +3364,55 @@
         <v>38.82352941176471</v>
       </c>
       <c r="D21" s="3">
-        <v>10.05940594059406</v>
+        <v>9.623762376237623</v>
       </c>
       <c r="E21" s="3">
         <v>-3.44</v>
       </c>
       <c r="F21" s="3">
-        <v>-0.42545785802279146</v>
+        <v>-0.4076005561597832</v>
       </c>
       <c r="G21" s="3">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="H21" s="3">
-        <v>38.66</v>
+        <v>34.18</v>
       </c>
       <c r="I21" s="3">
-        <v>-16.12</v>
+        <v>-19.74</v>
       </c>
       <c r="J21" s="3">
-        <v>-0.021632002869338838</v>
+        <v>-0.024514627176096933</v>
       </c>
       <c r="K21" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="3">
         <v>55</v>
       </c>
       <c r="M21" s="3">
-        <v>-0.39562895553905664</v>
+        <v>-0.3734328322834266</v>
       </c>
       <c r="N21" s="3">
-        <v>-33.676782250077466</v>
+        <v>-30.844834994000347</v>
       </c>
       <c r="O21" s="3">
-        <v>3.5294117647058822</v>
+        <v>4.705882352941177</v>
       </c>
       <c r="P21" s="3">
-        <v>52.10839414803409</v>
+        <v>54.27900061157512</v>
       </c>
       <c r="Q21" s="3">
-        <v>37.176470588235304</v>
+        <v>36.352941176470594</v>
       </c>
       <c r="R21" s="3">
-        <v>19.94117647058824</v>
+        <v>20.058823529411768</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>111</v>
       </c>
       <c r="T21" s="3">
-        <v>-31.28</v>
+        <v>-31.16</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -3423,25 +3426,25 @@
         <v>71.76470588235294</v>
       </c>
       <c r="D22" s="1">
-        <v>0.7594339622641508</v>
+        <v>0.7558962264150944</v>
       </c>
       <c r="E22" s="1">
         <v>-0.24</v>
       </c>
       <c r="F22" s="1">
-        <v>-0.17882726156553108</v>
+        <v>-0.18846342966613092</v>
       </c>
       <c r="G22" s="1">
         <v>1.38</v>
       </c>
       <c r="H22" s="1">
-        <v>38.89</v>
+        <v>38.96</v>
       </c>
       <c r="I22" s="1">
-        <v>-1.16</v>
+        <v>-1.32</v>
       </c>
       <c r="J22" s="1">
-        <v>-0.014377725904286806</v>
+        <v>-0.012270105174911727</v>
       </c>
       <c r="K22" s="1" t="b">
         <v>1</v>
@@ -3450,28 +3453,28 @@
         <v>245</v>
       </c>
       <c r="M22" s="1">
-        <v>-0.16054503101098394</v>
+        <v>-0.16785432637563014</v>
       </c>
       <c r="N22" s="1">
-        <v>-10.168389797270192</v>
+        <v>-10.286984403220702</v>
       </c>
       <c r="O22" s="1">
-        <v>27.058823529411764</v>
+        <v>23.52941176470588</v>
       </c>
       <c r="P22" s="1">
         <v>19.455960650079966</v>
       </c>
       <c r="Q22" s="1">
-        <v>43.41176470588235</v>
+        <v>44.11764705882352</v>
       </c>
       <c r="R22" s="1">
-        <v>35.05882352941176</v>
+        <v>33.99999999999999</v>
       </c>
       <c r="S22" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T22" s="1">
-        <v>-18.05</v>
+        <v>-19.11</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -3485,25 +3488,25 @@
         <v>96.47058823529412</v>
       </c>
       <c r="D23" s="2">
-        <v>-0.6975517890772129</v>
+        <v>-0.688512241054614</v>
       </c>
       <c r="E23" s="2">
         <v>0.09</v>
       </c>
       <c r="F23" s="2">
-        <v>0.24517715795272965</v>
+        <v>0.258470266226973</v>
       </c>
       <c r="G23" s="2">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="H23" s="2">
-        <v>78.3</v>
+        <v>73.89</v>
       </c>
       <c r="I23" s="2">
-        <v>19.29</v>
+        <v>17.68</v>
       </c>
       <c r="J23" s="2">
-        <v>0.010395046789147466</v>
+        <v>0.011516256880881174</v>
       </c>
       <c r="K23" s="2" t="b">
         <v>1</v>
@@ -3512,28 +3515,28 @@
         <v>45</v>
       </c>
       <c r="M23" s="2">
-        <v>0.2557616072211517</v>
+        <v>0.26931716269565764</v>
       </c>
       <c r="N23" s="2">
-        <v>31.462274025943383</v>
+        <v>33.43016450390807</v>
       </c>
       <c r="O23" s="2">
-        <v>84.70588235294117</v>
+        <v>83.52941176470588</v>
       </c>
       <c r="P23" s="2">
         <v>20.883293768118005</v>
       </c>
       <c r="Q23" s="2">
-        <v>66.35294117647058</v>
+        <v>65.76470588235294</v>
       </c>
       <c r="R23" s="2">
-        <v>57.05882352941176</v>
+        <v>56.411764705882355</v>
       </c>
       <c r="S23" s="2" t="s">
         <v>110</v>
       </c>
       <c r="T23" s="2">
-        <v>21.27</v>
+        <v>20.62</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -3547,25 +3550,25 @@
         <v>1.1764705882352942</v>
       </c>
       <c r="D24" s="1">
-        <v>2.6552823783561363</v>
+        <v>2.6549737681308505</v>
       </c>
       <c r="E24" s="1">
         <v>1.58</v>
       </c>
       <c r="F24" s="1">
-        <v>0.3559061594649231</v>
+        <v>0.5182394077841334</v>
       </c>
       <c r="G24" s="1">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="H24" s="1">
-        <v>67.26</v>
+        <v>65.82</v>
       </c>
       <c r="I24" s="1">
-        <v>19.35</v>
+        <v>18.27</v>
       </c>
       <c r="J24" s="1">
-        <v>0.042698758631470726</v>
+        <v>0.05735022450404733</v>
       </c>
       <c r="K24" s="1" t="b">
         <v>0</v>
@@ -3574,28 +3577,28 @@
         <v>-69</v>
       </c>
       <c r="M24" s="1">
-        <v>0.48051399403407347</v>
+        <v>0.6581643722301651</v>
       </c>
       <c r="N24" s="1">
-        <v>53.937512707235534</v>
+        <v>72.31488545735884</v>
       </c>
       <c r="O24" s="1">
-        <v>94.11764705882352</v>
+        <v>96.47058823529412</v>
       </c>
       <c r="P24" s="1">
         <v>57.99224429263358</v>
       </c>
       <c r="Q24" s="1">
-        <v>52.70588235294118</v>
+        <v>52.58823529411765</v>
       </c>
       <c r="R24" s="1">
-        <v>41.52941176470589</v>
+        <v>42.47058823529412</v>
       </c>
       <c r="S24" s="1" t="s">
         <v>109</v>
       </c>
       <c r="T24" s="1">
-        <v>45.25</v>
+        <v>46.19</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -3615,49 +3618,49 @@
         <v>15.51</v>
       </c>
       <c r="F25" s="3">
-        <v>-0.34178268035836645</v>
+        <v>-0.28859643682751596</v>
       </c>
       <c r="G25" s="3">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="H25" s="3">
-        <v>45.62</v>
+        <v>45.17</v>
       </c>
       <c r="I25" s="3">
-        <v>-30.61</v>
+        <v>-30.3</v>
       </c>
       <c r="J25" s="3">
-        <v>-0.005656802949248415</v>
+        <v>-0.00024310390602355666</v>
       </c>
       <c r="K25" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" s="3">
         <v>34</v>
       </c>
       <c r="M25" s="3">
-        <v>-0.2768326507566857</v>
+        <v>-0.21483754084046047</v>
       </c>
       <c r="N25" s="3">
-        <v>-21.797151771840372</v>
+        <v>-14.985305849703732</v>
       </c>
       <c r="O25" s="3">
-        <v>14.117647058823529</v>
+        <v>17.647058823529413</v>
       </c>
       <c r="P25" s="3">
         <v>45.59139601172712</v>
       </c>
       <c r="Q25" s="3">
-        <v>17.058823529411768</v>
+        <v>19.764705882352946</v>
       </c>
       <c r="R25" s="3">
-        <v>3.8235294117647083</v>
+        <v>5.705882352941179</v>
       </c>
       <c r="S25" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T25" s="3">
-        <v>2.42</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -3671,55 +3674,55 @@
         <v>7.0588235294117645</v>
       </c>
       <c r="D26" s="3">
-        <v>-0.7362637362637364</v>
+        <v>-0.6021978021978023</v>
       </c>
       <c r="E26" s="3">
         <v>-0.85</v>
       </c>
       <c r="F26" s="3">
-        <v>-0.47826863127602764</v>
+        <v>-0.3998634494049582</v>
       </c>
       <c r="G26" s="3">
         <v>3.37</v>
       </c>
       <c r="H26" s="3">
-        <v>50.17</v>
+        <v>53.2</v>
       </c>
       <c r="I26" s="3">
-        <v>-9.17</v>
+        <v>-5.63</v>
       </c>
       <c r="J26" s="3">
-        <v>-0.016589914410062075</v>
+        <v>-0.003862061978036462</v>
       </c>
       <c r="K26" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="3">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M26" s="3">
-        <v>-0.3642452459752993</v>
+        <v>-0.2713277262510454</v>
       </c>
       <c r="N26" s="3">
-        <v>-30.538411293701735</v>
+        <v>-20.634324390762227</v>
       </c>
       <c r="O26" s="3">
-        <v>5.88235294117647</v>
+        <v>8.235294117647058</v>
       </c>
       <c r="P26" s="3">
         <v>55.61259899184437</v>
       </c>
       <c r="Q26" s="3">
-        <v>18.11764705882353</v>
+        <v>24.23529411764706</v>
       </c>
       <c r="R26" s="3">
-        <v>-0.529411764705884</v>
+        <v>2.5294117647058822</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T26" s="3">
-        <v>-29.37</v>
+        <v>-26.31</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -3739,19 +3742,19 @@
         <v>6.87</v>
       </c>
       <c r="F27" s="3">
-        <v>-0.4881430755122261</v>
+        <v>-0.48152232434367737</v>
       </c>
       <c r="G27" s="3">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="H27" s="3">
-        <v>39.53</v>
+        <v>37.21</v>
       </c>
       <c r="I27" s="3">
-        <v>-36.02</v>
+        <v>-36.84</v>
       </c>
       <c r="J27" s="3">
-        <v>-0.02614151145842167</v>
+        <v>-0.020644318548790477</v>
       </c>
       <c r="K27" s="3" t="b">
         <v>0</v>
@@ -3760,10 +3763,10 @@
         <v>7</v>
       </c>
       <c r="M27" s="3">
-        <v>-0.40875970599906075</v>
+        <v>-0.3914930836535949</v>
       </c>
       <c r="N27" s="3">
-        <v>-34.98985729607787</v>
+        <v>-32.650860131017176</v>
       </c>
       <c r="O27" s="3">
         <v>2.3529411764705883</v>
@@ -3772,16 +3775,16 @@
         <v>50.56910707785277</v>
       </c>
       <c r="Q27" s="3">
-        <v>12.117647058823529</v>
+        <v>12.823529411764705</v>
       </c>
       <c r="R27" s="3">
-        <v>-0.17647058823529704</v>
+        <v>-0.05882352941176627</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T27" s="3">
-        <v>-16.34</v>
+        <v>-16.22</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -3801,19 +3804,19 @@
         <v>2.19</v>
       </c>
       <c r="F28" s="1">
-        <v>-0.16759229370479933</v>
+        <v>-0.05686137828423446</v>
       </c>
       <c r="G28" s="1">
         <v>3.26</v>
       </c>
       <c r="H28" s="1">
-        <v>45.06</v>
+        <v>51.74</v>
       </c>
       <c r="I28" s="1">
-        <v>-15.01</v>
+        <v>-9.7</v>
       </c>
       <c r="J28" s="1">
-        <v>0.00752648863948191</v>
+        <v>0.013389762757673942</v>
       </c>
       <c r="K28" s="1" t="b">
         <v>0</v>
@@ -3822,28 +3825,28 @@
         <v>3</v>
       </c>
       <c r="M28" s="1">
-        <v>-0.058861133038282</v>
+        <v>0.06570855181190183</v>
       </c>
       <c r="N28" s="1">
-        <v>0</v>
+        <v>13.069303415532502</v>
       </c>
       <c r="O28" s="1">
-        <v>43.529411764705884</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="P28" s="1">
         <v>35.08771990976345</v>
       </c>
       <c r="Q28" s="1">
-        <v>43.64705882352941</v>
+        <v>49.05882352941176</v>
       </c>
       <c r="R28" s="1">
-        <v>33.41176470588235</v>
+        <v>41.05882352941176</v>
       </c>
       <c r="S28" s="1" t="s">
         <v>112</v>
       </c>
       <c r="T28" s="1">
-        <v>16.4</v>
+        <v>24.05</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -3863,19 +3866,19 @@
         <v>-4.83</v>
       </c>
       <c r="F29" s="1">
-        <v>-0.12997023012338427</v>
+        <v>-0.1804792706906862</v>
       </c>
       <c r="G29" s="1">
         <v>2.32</v>
       </c>
       <c r="H29" s="1">
-        <v>43.52</v>
+        <v>40.82</v>
       </c>
       <c r="I29" s="1">
-        <v>-12.7</v>
+        <v>-14.09</v>
       </c>
       <c r="J29" s="1">
-        <v>-0.0077674306022950355</v>
+        <v>-0.008374137523703638</v>
       </c>
       <c r="K29" s="1" t="b">
         <v>1</v>
@@ -3884,28 +3887,28 @@
         <v>11</v>
       </c>
       <c r="M29" s="1">
-        <v>-0.06646353451285203</v>
+        <v>-0.10888975399736767</v>
       </c>
       <c r="N29" s="1">
-        <v>-0.760240147457008</v>
+        <v>-4.390527165394458</v>
       </c>
       <c r="O29" s="1">
-        <v>41.17647058823529</v>
+        <v>35.294117647058826</v>
       </c>
       <c r="P29" s="1">
         <v>18.81663456064845</v>
       </c>
       <c r="Q29" s="1">
-        <v>48.23529411764706</v>
+        <v>47.05882352941176</v>
       </c>
       <c r="R29" s="1">
-        <v>43.35294117647059</v>
+        <v>41.23529411764706</v>
       </c>
       <c r="S29" s="1" t="s">
         <v>110</v>
       </c>
       <c r="T29" s="1">
-        <v>3.11</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -3925,49 +3928,49 @@
         <v>1.22</v>
       </c>
       <c r="F30" s="1">
-        <v>-0.16000727780394192</v>
+        <v>-0.17080193300518698</v>
       </c>
       <c r="G30" s="1">
         <v>1.25</v>
       </c>
       <c r="H30" s="1">
-        <v>38.06</v>
+        <v>40.13</v>
       </c>
       <c r="I30" s="1">
-        <v>-9.15</v>
+        <v>-9.17</v>
       </c>
       <c r="J30" s="1">
-        <v>-0.01177318330114735</v>
+        <v>-0.010028384946304017</v>
       </c>
       <c r="K30" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L30" s="1">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M30" s="1">
-        <v>-0.14797949454437143</v>
+        <v>-0.1572433124193312</v>
       </c>
       <c r="N30" s="1">
-        <v>-8.911836150608938</v>
+        <v>-9.225883007590806</v>
       </c>
       <c r="O30" s="1">
-        <v>28.235294117647058</v>
+        <v>27.058823529411764</v>
       </c>
       <c r="P30" s="1">
         <v>18.121365335609003</v>
       </c>
       <c r="Q30" s="1">
-        <v>50.94117647058823</v>
+        <v>51.882352941176464</v>
       </c>
       <c r="R30" s="1">
-        <v>43.35294117647059</v>
+        <v>43.11764705882353</v>
       </c>
       <c r="S30" s="1" t="s">
         <v>111</v>
       </c>
       <c r="T30" s="1">
-        <v>-5.12</v>
+        <v>-5.36</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -3981,55 +3984,55 @@
         <v>68.23529411764706</v>
       </c>
       <c r="D31" s="1">
-        <v>7.2899106002554275</v>
+        <v>7.286079182630906</v>
       </c>
       <c r="E31" s="1">
         <v>0.39</v>
       </c>
       <c r="F31" s="1">
-        <v>-0.1566270157683553</v>
+        <v>-0.16135179682802436</v>
       </c>
       <c r="G31" s="1">
         <v>1.47</v>
       </c>
       <c r="H31" s="1">
-        <v>47.87</v>
+        <v>42.32</v>
       </c>
       <c r="I31" s="1">
-        <v>-2.04</v>
+        <v>-4.77</v>
       </c>
       <c r="J31" s="1">
-        <v>-0.009828331118262638</v>
+        <v>-0.009218959447684303</v>
       </c>
       <c r="K31" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L31" s="1">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="M31" s="1">
-        <v>-0.13401478324036276</v>
+        <v>-0.13586159012661547</v>
       </c>
       <c r="N31" s="1">
-        <v>-7.51536502020808</v>
+        <v>-7.087710778319237</v>
       </c>
       <c r="O31" s="1">
-        <v>31.76470588235294</v>
+        <v>30.58823529411765</v>
       </c>
       <c r="P31" s="1">
         <v>29.54918623383928</v>
       </c>
       <c r="Q31" s="1">
-        <v>53.882352941176464</v>
+        <v>51.64705882352941</v>
       </c>
       <c r="R31" s="1">
-        <v>39.588235294117645</v>
+        <v>39</v>
       </c>
       <c r="S31" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T31" s="1">
-        <v>-8.46</v>
+        <v>-9.05</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -4049,31 +4052,31 @@
         <v>3.57</v>
       </c>
       <c r="F32" s="1">
-        <v>-0.07147154091015032</v>
+        <v>-0.07265357003503854</v>
       </c>
       <c r="G32" s="1">
         <v>1.62</v>
       </c>
       <c r="H32" s="1">
-        <v>44.16</v>
+        <v>41.06</v>
       </c>
       <c r="I32" s="1">
-        <v>-5.87</v>
+        <v>-7.6</v>
       </c>
       <c r="J32" s="1">
-        <v>-0.015087942996531436</v>
+        <v>-0.013710073635057411</v>
       </c>
       <c r="K32" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M32" s="1">
-        <v>-0.04164263842641547</v>
+        <v>-0.039028190982116184</v>
       </c>
       <c r="N32" s="1">
-        <v>1.7218494611866562</v>
+        <v>2.5956291361306865</v>
       </c>
       <c r="O32" s="1">
         <v>51.76470588235295</v>
@@ -4082,16 +4085,16 @@
         <v>26.613703173358488</v>
       </c>
       <c r="Q32" s="1">
-        <v>34.705882352941174</v>
+        <v>34.23529411764706</v>
       </c>
       <c r="R32" s="1">
-        <v>32.588235294117645</v>
+        <v>32.470588235294116</v>
       </c>
       <c r="S32" s="1" t="s">
         <v>109</v>
       </c>
       <c r="T32" s="1">
-        <v>0.7</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -4105,55 +4108,55 @@
         <v>88.23529411764706</v>
       </c>
       <c r="D33" s="2">
-        <v>0.06128133704735384</v>
+        <v>0.0579387186629526</v>
       </c>
       <c r="E33" s="2">
         <v>0.24</v>
       </c>
       <c r="F33" s="2">
-        <v>0.30184740943249877</v>
+        <v>0.2993452791916342</v>
       </c>
       <c r="G33" s="2">
         <v>1.1</v>
       </c>
       <c r="H33" s="2">
-        <v>58.36</v>
+        <v>54.5</v>
       </c>
       <c r="I33" s="2">
-        <v>16.75</v>
+        <v>15.32</v>
       </c>
       <c r="J33" s="2">
-        <v>0.024220162899023054</v>
+        <v>0.024467845138836035</v>
       </c>
       <c r="K33" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2">
         <v>81</v>
       </c>
       <c r="M33" s="2">
-        <v>0.306658522736327</v>
+        <v>0.3047687274259765</v>
       </c>
       <c r="N33" s="2">
-        <v>36.55196557746089</v>
+        <v>36.97532097693996</v>
       </c>
       <c r="O33" s="2">
-        <v>87.05882352941177</v>
+        <v>85.88235294117646</v>
       </c>
       <c r="P33" s="2">
         <v>23.38443607454554</v>
       </c>
       <c r="Q33" s="2">
-        <v>68.11764705882354</v>
+        <v>67.29411764705883</v>
       </c>
       <c r="R33" s="2">
-        <v>60.47058823529413</v>
+        <v>60</v>
       </c>
       <c r="S33" s="2" t="s">
         <v>110</v>
       </c>
       <c r="T33" s="2">
-        <v>24.68</v>
+        <v>24.21</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -4173,49 +4176,49 @@
         <v>2.34</v>
       </c>
       <c r="F34" s="1">
-        <v>-0.0538363290873837</v>
+        <v>-0.0979788143941577</v>
       </c>
       <c r="G34" s="1">
         <v>1.21</v>
       </c>
       <c r="H34" s="1">
-        <v>60.46</v>
+        <v>45.68</v>
       </c>
       <c r="I34" s="1">
-        <v>5.8</v>
+        <v>0.17</v>
       </c>
       <c r="J34" s="1">
-        <v>-0.004138124741324778</v>
+        <v>-0.0028423176498818294</v>
       </c>
       <c r="K34" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="1">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="M34" s="1">
-        <v>-0.04373299114934448</v>
+        <v>-0.08658957310203885</v>
       </c>
       <c r="N34" s="1">
-        <v>1.5128141888937587</v>
+        <v>-2.1605090758615764</v>
       </c>
       <c r="O34" s="1">
-        <v>50.588235294117645</v>
+        <v>42.35294117647059</v>
       </c>
       <c r="P34" s="1">
         <v>21.09433056126816</v>
       </c>
       <c r="Q34" s="1">
-        <v>51.41176470588235</v>
+        <v>46.470588235294116</v>
       </c>
       <c r="R34" s="1">
-        <v>40.17647058823529</v>
+        <v>37.35294117647059</v>
       </c>
       <c r="S34" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T34" s="1">
-        <v>-6.65</v>
+        <v>-9.48</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -4229,55 +4232,55 @@
         <v>87.05882352941177</v>
       </c>
       <c r="D35" s="1">
-        <v>-0.4552154195011338</v>
+        <v>-0.4631519274376417</v>
       </c>
       <c r="E35" s="1">
         <v>-0.47</v>
       </c>
       <c r="F35" s="1">
-        <v>-0.05316189641702512</v>
+        <v>-0.014927975149269773</v>
       </c>
       <c r="G35" s="1">
-        <v>0.94</v>
+        <v>0.95</v>
       </c>
       <c r="H35" s="1">
-        <v>33.06</v>
+        <v>34.66</v>
       </c>
       <c r="I35" s="1">
-        <v>-17.53</v>
+        <v>-16.81</v>
       </c>
       <c r="J35" s="1">
-        <v>-0.0013001789228728464</v>
+        <v>-0.0023912012811345175</v>
       </c>
       <c r="K35" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="1">
         <v>-57</v>
       </c>
       <c r="M35" s="1">
-        <v>-0.05604856439932204</v>
+        <v>-0.017639699266440934</v>
       </c>
       <c r="N35" s="1">
-        <v>0.2812568638960001</v>
+        <v>4.73447830769823</v>
       </c>
       <c r="O35" s="1">
-        <v>44.70588235294118</v>
+        <v>55.294117647058826</v>
       </c>
       <c r="P35" s="1">
         <v>19.973884530776573</v>
       </c>
       <c r="Q35" s="1">
-        <v>43.529411764705884</v>
+        <v>43.05882352941177</v>
       </c>
       <c r="R35" s="1">
-        <v>41.23529411764706</v>
+        <v>43.94117647058824</v>
       </c>
       <c r="S35" s="1" t="s">
         <v>101</v>
       </c>
       <c r="T35" s="1">
-        <v>18.74</v>
+        <v>21.44</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -4297,19 +4300,19 @@
         <v>-1.3</v>
       </c>
       <c r="F36" s="1">
-        <v>-0.11334064795685607</v>
+        <v>-0.09509953450079849</v>
       </c>
       <c r="G36" s="1">
         <v>1.12</v>
       </c>
       <c r="H36" s="1">
-        <v>43.04</v>
+        <v>44.02</v>
       </c>
       <c r="I36" s="1">
-        <v>-9.91</v>
+        <v>-9.19</v>
       </c>
       <c r="J36" s="1">
-        <v>0.004948993697604279</v>
+        <v>0.004373412843074677</v>
       </c>
       <c r="K36" s="1" t="b">
         <v>1</v>
@@ -4318,28 +4321,28 @@
         <v>-18</v>
       </c>
       <c r="M36" s="1">
-        <v>-0.10756731199226222</v>
+        <v>-0.0885913966195877</v>
       </c>
       <c r="N36" s="1">
-        <v>-4.870617895398018</v>
+        <v>-2.3606914276164535</v>
       </c>
       <c r="O36" s="1">
-        <v>35.294117647058826</v>
+        <v>40</v>
       </c>
       <c r="P36" s="1">
         <v>26.730280409441182</v>
       </c>
       <c r="Q36" s="1">
-        <v>49.52941176470588</v>
+        <v>48.82352941176472</v>
       </c>
       <c r="R36" s="1">
-        <v>38.00000000000001</v>
+        <v>38.411764705882355</v>
       </c>
       <c r="S36" s="1" t="s">
         <v>108</v>
       </c>
       <c r="T36" s="1">
-        <v>11.05</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -4359,49 +4362,49 @@
         <v>-3.26</v>
       </c>
       <c r="F37" s="2">
-        <v>0.17046413001919664</v>
+        <v>0.1559409475199089</v>
       </c>
       <c r="G37" s="2">
         <v>1.28</v>
       </c>
       <c r="H37" s="2">
-        <v>40.4</v>
+        <v>40.33</v>
       </c>
       <c r="I37" s="2">
-        <v>4.04</v>
+        <v>4</v>
       </c>
       <c r="J37" s="2">
-        <v>0.01343969144514559</v>
+        <v>0.011443912733200126</v>
       </c>
       <c r="K37" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="2">
-        <v>-107</v>
+        <v>-108</v>
       </c>
       <c r="M37" s="2">
-        <v>0.1839352472699156</v>
+        <v>0.17112660257606738</v>
       </c>
       <c r="N37" s="2">
-        <v>24.27963803081976</v>
+        <v>23.61110849194904</v>
       </c>
       <c r="O37" s="2">
-        <v>81.17647058823529</v>
+        <v>78.82352941176471</v>
       </c>
       <c r="P37" s="2">
         <v>20.1020772277769</v>
       </c>
       <c r="Q37" s="2">
-        <v>52.23529411764706</v>
+        <v>51.76470588235294</v>
       </c>
       <c r="R37" s="2">
-        <v>53.29411764705882</v>
+        <v>51.88235294117647</v>
       </c>
       <c r="S37" s="2" t="s">
         <v>111</v>
       </c>
       <c r="T37" s="2">
-        <v>23.48</v>
+        <v>22.07</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -4421,49 +4424,49 @@
         <v>3.13</v>
       </c>
       <c r="F38" s="2">
-        <v>0.40770262130266477</v>
+        <v>0.4655988829695965</v>
       </c>
       <c r="G38" s="2">
         <v>1.21</v>
       </c>
       <c r="H38" s="2">
-        <v>65.03</v>
+        <v>67.3</v>
       </c>
       <c r="I38" s="2">
-        <v>69.06</v>
+        <v>73.95</v>
       </c>
       <c r="J38" s="2">
-        <v>0.024172783695703096</v>
+        <v>0.027151927006933585</v>
       </c>
       <c r="K38" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" s="2">
         <v>391</v>
       </c>
       <c r="M38" s="2">
-        <v>0.41780595924070396</v>
+        <v>0.47698812426171533</v>
       </c>
       <c r="N38" s="2">
-        <v>47.66670922789859</v>
+        <v>54.19726066051385</v>
       </c>
       <c r="O38" s="2">
-        <v>90.58823529411765</v>
+        <v>91.76470588235294</v>
       </c>
       <c r="P38" s="2">
         <v>17.802507034008837</v>
       </c>
       <c r="Q38" s="2">
-        <v>74.94117647058823</v>
+        <v>76.23529411764704</v>
       </c>
       <c r="R38" s="2">
-        <v>65.76470588235294</v>
+        <v>66.58823529411764</v>
       </c>
       <c r="S38" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T38" s="2">
-        <v>1.68</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -4483,49 +4486,49 @@
         <v>-1.29</v>
       </c>
       <c r="F39" s="1">
-        <v>-0.04491288216402424</v>
+        <v>-0.08180180735324165</v>
       </c>
       <c r="G39" s="1">
         <v>1.12</v>
       </c>
       <c r="H39" s="1">
-        <v>39.12</v>
+        <v>36.15</v>
       </c>
       <c r="I39" s="1">
-        <v>-6.48</v>
+        <v>-7.93</v>
       </c>
       <c r="J39" s="1">
-        <v>-0.005118805496403966</v>
+        <v>-0.006090746762965525</v>
       </c>
       <c r="K39" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" s="1">
         <v>-1</v>
       </c>
       <c r="M39" s="1">
-        <v>-0.039139546199430386</v>
+        <v>-0.07529366947203087</v>
       </c>
       <c r="N39" s="1">
-        <v>1.972158683885172</v>
+        <v>-1.030918712860774</v>
       </c>
       <c r="O39" s="1">
-        <v>54.11764705882353</v>
+        <v>44.70588235294118</v>
       </c>
       <c r="P39" s="1">
         <v>30.28933322215756</v>
       </c>
       <c r="Q39" s="1">
-        <v>44.11764705882353</v>
+        <v>42.705882352941174</v>
       </c>
       <c r="R39" s="1">
-        <v>40.352941176470594</v>
+        <v>36.82352941176471</v>
       </c>
       <c r="S39" s="1" t="s">
         <v>112</v>
       </c>
       <c r="T39" s="1">
-        <v>14.56</v>
+        <v>11.03</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -4545,19 +4548,19 @@
         <v>4.43</v>
       </c>
       <c r="F40" s="1">
-        <v>0.5549316354205458</v>
+        <v>0.5650719043727077</v>
       </c>
       <c r="G40" s="1">
-        <v>0.71</v>
+        <v>0.61</v>
       </c>
       <c r="H40" s="1">
-        <v>64.25</v>
+        <v>65.42</v>
       </c>
       <c r="I40" s="1">
-        <v>16.25</v>
+        <v>18.61</v>
       </c>
       <c r="J40" s="1">
-        <v>0.039596274222561394</v>
+        <v>0.04541650717500069</v>
       </c>
       <c r="K40" s="1" t="b">
         <v>1</v>
@@ -4566,28 +4569,28 @@
         <v>-21</v>
       </c>
       <c r="M40" s="1">
-        <v>0.540979406839444</v>
+        <v>0.5439204562587727</v>
       </c>
       <c r="N40" s="1">
-        <v>59.9840539877726</v>
+        <v>60.89049386021957</v>
       </c>
       <c r="O40" s="1">
-        <v>95.29411764705881</v>
+        <v>94.11764705882352</v>
       </c>
       <c r="P40" s="1">
         <v>51.940889187924654</v>
       </c>
       <c r="Q40" s="1">
-        <v>57.1764705882353</v>
+        <v>58.117647058823536</v>
       </c>
       <c r="R40" s="1">
-        <v>47.47058823529412</v>
+        <v>47.235294117647065</v>
       </c>
       <c r="S40" s="1" t="s">
         <v>113</v>
       </c>
       <c r="T40" s="1">
-        <v>38.99</v>
+        <v>38.76</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -4601,25 +4604,25 @@
         <v>4.705882352941177</v>
       </c>
       <c r="D41" s="3">
-        <v>1.5533199195171026</v>
+        <v>1.5553319919517103</v>
       </c>
       <c r="E41" s="3">
         <v>0.01</v>
       </c>
       <c r="F41" s="3">
-        <v>-0.11093094280679497</v>
+        <v>-0.10056493821438309</v>
       </c>
       <c r="G41" s="3">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="H41" s="3">
-        <v>41.3</v>
+        <v>35.65</v>
       </c>
       <c r="I41" s="3">
-        <v>-11.73</v>
+        <v>-15.19</v>
       </c>
       <c r="J41" s="3">
-        <v>-0.018190576248909927</v>
+        <v>-0.020176778753364773</v>
       </c>
       <c r="K41" s="3" t="b">
         <v>1</v>
@@ -4628,90 +4631,90 @@
         <v>4</v>
       </c>
       <c r="M41" s="3">
-        <v>-0.10082760486875575</v>
+        <v>-0.08809100727539576</v>
       </c>
       <c r="N41" s="3">
-        <v>-4.196647183047376</v>
+        <v>-2.310652493197266</v>
       </c>
       <c r="O41" s="3">
-        <v>36.470588235294116</v>
+        <v>41.17647058823529</v>
       </c>
       <c r="P41" s="3">
         <v>30.769232468942608</v>
       </c>
       <c r="Q41" s="3">
-        <v>22.11764705882353</v>
+        <v>20.352941176470587</v>
       </c>
       <c r="R41" s="3">
-        <v>18.411764705882355</v>
+        <v>19.588235294117645</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>107</v>
       </c>
       <c r="T41" s="3">
-        <v>-18.23</v>
+        <v>-17.06</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="1">
+      <c r="B42" s="3">
         <v>3.33</v>
       </c>
-      <c r="C42" s="1">
+      <c r="C42" s="3">
         <v>51.76470588235295</v>
       </c>
-      <c r="D42" s="1">
+      <c r="D42" s="3">
         <v>1.2252252252252251</v>
       </c>
-      <c r="E42" s="1">
+      <c r="E42" s="3">
         <v>4.33</v>
       </c>
-      <c r="F42" s="1">
-        <v>-0.14897076190873235</v>
-      </c>
-      <c r="G42" s="1">
+      <c r="F42" s="3">
+        <v>-0.1892512599381852</v>
+      </c>
+      <c r="G42" s="3">
         <v>0.31</v>
       </c>
-      <c r="H42" s="1">
-        <v>23.09</v>
-      </c>
-      <c r="I42" s="1">
-        <v>-11.52</v>
-      </c>
-      <c r="J42" s="1">
-        <v>-0.014496939696363138</v>
-      </c>
-      <c r="K42" s="1" t="b">
+      <c r="H42" s="3">
+        <v>44.75</v>
+      </c>
+      <c r="I42" s="3">
+        <v>-9.07</v>
+      </c>
+      <c r="J42" s="3">
+        <v>-0.015165693555448268</v>
+      </c>
+      <c r="K42" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L42" s="1">
+      <c r="L42" s="3">
         <v>16</v>
       </c>
-      <c r="M42" s="1">
-        <v>-0.18216744370514693</v>
-      </c>
-      <c r="N42" s="1">
-        <v>-12.330631066686488</v>
-      </c>
-      <c r="O42" s="1">
-        <v>25.882352941176475</v>
-      </c>
-      <c r="P42" s="1">
-        <v>17.903820641360944</v>
-      </c>
-      <c r="Q42" s="1">
-        <v>35.529411764705884</v>
-      </c>
-      <c r="R42" s="1">
-        <v>31.41176470588236</v>
-      </c>
-      <c r="S42" s="1" t="s">
+      <c r="M42" s="3">
+        <v>-0.22667305275514715</v>
+      </c>
+      <c r="N42" s="3">
+        <v>-16.168857041172398</v>
+      </c>
+      <c r="O42" s="3">
+        <v>15.294117647058824</v>
+      </c>
+      <c r="P42" s="3">
+        <v>19.870570381723375</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>38.58823529411765</v>
+      </c>
+      <c r="R42" s="3">
+        <v>26.58823529411765</v>
+      </c>
+      <c r="S42" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="T42" s="1">
-        <v>-4.08</v>
+      <c r="T42" s="3">
+        <v>-8.9</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -4725,25 +4728,25 @@
         <v>32.94117647058823</v>
       </c>
       <c r="D43" s="2">
-        <v>150.8</v>
+        <v>150.93333333333334</v>
       </c>
       <c r="E43" s="2">
         <v>8.78</v>
       </c>
       <c r="F43" s="2">
-        <v>0.1466821730212451</v>
+        <v>0.16499480030957842</v>
       </c>
       <c r="G43" s="2">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="H43" s="2">
-        <v>46.42</v>
+        <v>48.26</v>
       </c>
       <c r="I43" s="2">
-        <v>13.33</v>
+        <v>14.98</v>
       </c>
       <c r="J43" s="2">
-        <v>0.008310784566949897</v>
+        <v>0.007307714562346161</v>
       </c>
       <c r="K43" s="2" t="b">
         <v>0</v>
@@ -4752,28 +4755,28 @@
         <v>18</v>
       </c>
       <c r="M43" s="2">
-        <v>0.16303995825426099</v>
+        <v>0.1839768691297765</v>
       </c>
       <c r="N43" s="2">
-        <v>22.190109129254292</v>
+        <v>24.89613514731997</v>
       </c>
       <c r="O43" s="2">
-        <v>78.82352941176471</v>
+        <v>81.17647058823529</v>
       </c>
       <c r="P43" s="2">
         <v>24.82490242340647</v>
       </c>
       <c r="Q43" s="2">
-        <v>61.647058823529406</v>
+        <v>60.470588235294116</v>
       </c>
       <c r="R43" s="2">
-        <v>56.76470588235294</v>
+        <v>56.17647058823529</v>
       </c>
       <c r="S43" s="2" t="s">
         <v>114</v>
       </c>
       <c r="T43" s="2">
-        <v>4.39</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -4793,19 +4796,19 @@
         <v>-0.69</v>
       </c>
       <c r="F44" s="2">
-        <v>0.1399912326229593</v>
+        <v>0.09335062089405227</v>
       </c>
       <c r="G44" s="2">
         <v>2.63</v>
       </c>
       <c r="H44" s="2">
-        <v>52.16</v>
+        <v>52.42</v>
       </c>
       <c r="I44" s="2">
-        <v>6.67</v>
+        <v>8.16</v>
       </c>
       <c r="J44" s="2">
-        <v>0.007072447098323006</v>
+        <v>0.010273746718710872</v>
       </c>
       <c r="K44" s="2" t="b">
         <v>1</v>
@@ -4814,28 +4817,28 @@
         <v>-6</v>
       </c>
       <c r="M44" s="2">
-        <v>0.21841237947535896</v>
+        <v>0.181752827113832</v>
       </c>
       <c r="N44" s="2">
-        <v>27.727351251364098</v>
+        <v>24.673730945725513</v>
       </c>
       <c r="O44" s="2">
-        <v>83.52941176470588</v>
+        <v>80</v>
       </c>
       <c r="P44" s="2">
         <v>25.276100184761987</v>
       </c>
       <c r="Q44" s="2">
-        <v>60.11764705882353</v>
+        <v>62.35294117647059</v>
       </c>
       <c r="R44" s="2">
-        <v>56.470588235294116</v>
+        <v>56.17647058823529</v>
       </c>
       <c r="S44" s="2" t="s">
         <v>103</v>
       </c>
       <c r="T44" s="2">
-        <v>21.65</v>
+        <v>21.36</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
@@ -4849,55 +4852,55 @@
         <v>82.35294117647058</v>
       </c>
       <c r="D45" s="1">
-        <v>-2.353982300884956</v>
+        <v>-2.352373290426388</v>
       </c>
       <c r="E45" s="1">
         <v>1.03</v>
       </c>
       <c r="F45" s="1">
-        <v>0.029717044134122655</v>
+        <v>-0.025361315714862998</v>
       </c>
       <c r="G45" s="1">
         <v>1.45</v>
       </c>
       <c r="H45" s="1">
-        <v>53.77</v>
+        <v>43.13</v>
       </c>
       <c r="I45" s="1">
-        <v>7.92</v>
+        <v>3.09</v>
       </c>
       <c r="J45" s="1">
-        <v>0.0024730901845549935</v>
+        <v>0.002880008894932799</v>
       </c>
       <c r="K45" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L45" s="1">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M45" s="1">
-        <v>0.051367054001349555</v>
+        <v>-0.0009557986603225821</v>
       </c>
       <c r="N45" s="1">
-        <v>11.022818703963162</v>
+        <v>6.402868368310048</v>
       </c>
       <c r="O45" s="1">
-        <v>64.70588235294117</v>
+        <v>58.82352941176471</v>
       </c>
       <c r="P45" s="1">
         <v>17.57882034058413</v>
       </c>
       <c r="Q45" s="1">
-        <v>48.23529411764706</v>
+        <v>44</v>
       </c>
       <c r="R45" s="1">
-        <v>44.11764705882353</v>
+        <v>42.117647058823536</v>
       </c>
       <c r="S45" s="1" t="s">
         <v>109</v>
       </c>
       <c r="T45" s="1">
-        <v>-0.21</v>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
@@ -4917,19 +4920,19 @@
         <v>4.52</v>
       </c>
       <c r="F46" s="3">
-        <v>-0.33191721542388575</v>
+        <v>-0.334412896006272</v>
       </c>
       <c r="G46" s="3">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="H46" s="3">
-        <v>39.66</v>
+        <v>35.14</v>
       </c>
       <c r="I46" s="3">
-        <v>-29.26</v>
+        <v>-33.04</v>
       </c>
       <c r="J46" s="3">
-        <v>-0.010799170236480702</v>
+        <v>-0.010102064440776522</v>
       </c>
       <c r="K46" s="3" t="b">
         <v>1</v>
@@ -4938,28 +4941,28 @@
         <v>17</v>
       </c>
       <c r="M46" s="3">
-        <v>-0.2958338656451742</v>
+        <v>-0.2931946894252704</v>
       </c>
       <c r="N46" s="3">
-        <v>-23.69727326068923</v>
+        <v>-22.82102070818473</v>
       </c>
       <c r="O46" s="3">
-        <v>10.588235294117647</v>
+        <v>5.88235294117647</v>
       </c>
       <c r="P46" s="3">
         <v>54.33673655574689</v>
       </c>
       <c r="Q46" s="3">
-        <v>43.647058823529406</v>
+        <v>42.11764705882352</v>
       </c>
       <c r="R46" s="3">
-        <v>26.05882352941176</v>
+        <v>24.29411764705882</v>
       </c>
       <c r="S46" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T46" s="3">
-        <v>5.02</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
@@ -4979,19 +4982,19 @@
         <v>2.57</v>
       </c>
       <c r="F47" s="1">
-        <v>0.01831102006304998</v>
+        <v>0.08195431159315396</v>
       </c>
       <c r="G47" s="1">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="H47" s="1">
-        <v>47.76</v>
+        <v>47.74</v>
       </c>
       <c r="I47" s="1">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="J47" s="1">
-        <v>0.017313755813952298</v>
+        <v>0.018669269883780492</v>
       </c>
       <c r="K47" s="1" t="b">
         <v>1</v>
@@ -5000,28 +5003,28 @@
         <v>-56</v>
       </c>
       <c r="M47" s="1">
-        <v>0.038036584608745594</v>
+        <v>0.10473279417739167</v>
       </c>
       <c r="N47" s="1">
-        <v>9.689771764702748</v>
+        <v>16.97172765208148</v>
       </c>
       <c r="O47" s="1">
-        <v>62.35294117647059</v>
+        <v>71.76470588235294</v>
       </c>
       <c r="P47" s="1">
         <v>30.777935412994907</v>
       </c>
       <c r="Q47" s="1">
-        <v>51.41176470588235</v>
+        <v>52.58823529411765</v>
       </c>
       <c r="R47" s="1">
-        <v>42.411764705882355</v>
+        <v>45.352941176470594</v>
       </c>
       <c r="S47" s="1" t="s">
         <v>109</v>
       </c>
       <c r="T47" s="1">
-        <v>16.56</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
@@ -5041,19 +5044,19 @@
         <v>0.66</v>
       </c>
       <c r="F48" s="2">
-        <v>0.08857843283151749</v>
+        <v>0.15637147879667657</v>
       </c>
       <c r="G48" s="2">
         <v>1.61</v>
       </c>
       <c r="H48" s="2">
-        <v>57.81</v>
+        <v>57.25</v>
       </c>
       <c r="I48" s="2">
-        <v>30.4</v>
+        <v>29.52</v>
       </c>
       <c r="J48" s="2">
-        <v>0.011006532885688187</v>
+        <v>0.011279799840354104</v>
       </c>
       <c r="K48" s="2" t="b">
         <v>1</v>
@@ -5062,28 +5065,28 @@
         <v>243</v>
       </c>
       <c r="M48" s="2">
-        <v>0.11792622398486952</v>
+        <v>0.18945451302616467</v>
       </c>
       <c r="N48" s="2">
-        <v>17.678735702315144</v>
+        <v>25.443899536958774</v>
       </c>
       <c r="O48" s="2">
-        <v>72.94117647058823</v>
+        <v>82.35294117647058</v>
       </c>
       <c r="P48" s="2">
         <v>21.006318468965095</v>
       </c>
       <c r="Q48" s="2">
-        <v>64.94117647058825</v>
+        <v>64.58823529411765</v>
       </c>
       <c r="R48" s="2">
-        <v>54.11764705882353</v>
+        <v>56.588235294117645</v>
       </c>
       <c r="S48" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T48" s="2">
-        <v>4.85</v>
+        <v>7.32</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
@@ -5103,19 +5106,19 @@
         <v>-11.2</v>
       </c>
       <c r="F49" s="2">
-        <v>0.16839141657281478</v>
+        <v>0.09844711598854143</v>
       </c>
       <c r="G49" s="2">
         <v>1.08</v>
       </c>
       <c r="H49" s="2">
-        <v>56.3</v>
+        <v>43.77</v>
       </c>
       <c r="I49" s="2">
-        <v>0.13</v>
+        <v>-8.35</v>
       </c>
       <c r="J49" s="2">
-        <v>0.01968550258408668</v>
+        <v>0.01726551784734589</v>
       </c>
       <c r="K49" s="2" t="b">
         <v>0</v>
@@ -5124,28 +5127,28 @@
         <v>-7</v>
       </c>
       <c r="M49" s="2">
-        <v>0.17224030721587735</v>
+        <v>0.10278587457601529</v>
       </c>
       <c r="N49" s="2">
-        <v>23.110144025415934</v>
+        <v>16.777035691943844</v>
       </c>
       <c r="O49" s="2">
-        <v>80</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="P49" s="2">
         <v>31.00158698078384</v>
       </c>
       <c r="Q49" s="2">
-        <v>65.05882352941177</v>
+        <v>60.94117647058823</v>
       </c>
       <c r="R49" s="2">
-        <v>57.41176470588236</v>
+        <v>54.47058823529412</v>
       </c>
       <c r="S49" s="2" t="s">
         <v>102</v>
       </c>
       <c r="T49" s="2">
-        <v>26.31</v>
+        <v>23.37</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
@@ -5165,19 +5168,19 @@
         <v>12.86</v>
       </c>
       <c r="F50" s="3">
-        <v>-0.35061372518661527</v>
+        <v>-0.32806768601339753</v>
       </c>
       <c r="G50" s="3">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="H50" s="3">
-        <v>59.46</v>
+        <v>56.63</v>
       </c>
       <c r="I50" s="3">
-        <v>15.1</v>
+        <v>13.32</v>
       </c>
       <c r="J50" s="3">
-        <v>0.005966274501828959</v>
+        <v>0.012732253681764958</v>
       </c>
       <c r="K50" s="3" t="b">
         <v>0</v>
@@ -5186,10 +5189,10 @@
         <v>69</v>
       </c>
       <c r="M50" s="3">
-        <v>-0.21301588469712873</v>
+        <v>-0.17404175615807582</v>
       </c>
       <c r="N50" s="3">
-        <v>-15.41547516588467</v>
+        <v>-10.905727381465272</v>
       </c>
       <c r="O50" s="3">
         <v>22.35294117647059</v>
@@ -5198,10 +5201,10 @@
         <v>41.201484669672254</v>
       </c>
       <c r="Q50" s="3">
-        <v>52.47058823529412</v>
+        <v>54.705882352941174</v>
       </c>
       <c r="R50" s="3">
-        <v>25.764705882352942</v>
+        <v>27.411764705882355</v>
       </c>
       <c r="S50" s="3" t="s">
         <v>108</v>
@@ -5219,25 +5222,25 @@
         <v>3.5294117647058822</v>
       </c>
       <c r="D51" s="1">
-        <v>5.305980528511822</v>
+        <v>4.831710709318498</v>
       </c>
       <c r="E51" s="1">
         <v>14.41</v>
       </c>
       <c r="F51" s="1">
-        <v>0.08880189473805797</v>
+        <v>0.25314923951320245</v>
       </c>
       <c r="G51" s="1">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="H51" s="1">
-        <v>63.45</v>
+        <v>58.76</v>
       </c>
       <c r="I51" s="1">
-        <v>43.75</v>
+        <v>39.64</v>
       </c>
       <c r="J51" s="1">
-        <v>0.05712275038086046</v>
+        <v>0.05856227101337115</v>
       </c>
       <c r="K51" s="1" t="b">
         <v>0</v>
@@ -5246,22 +5249,22 @@
         <v>14</v>
       </c>
       <c r="M51" s="1">
-        <v>0.1277719124990664</v>
+        <v>0.29436744609420407</v>
       </c>
       <c r="N51" s="1">
-        <v>18.66330455373483</v>
+        <v>35.93519284376273</v>
       </c>
       <c r="O51" s="1">
-        <v>75.29411764705883</v>
+        <v>84.70588235294117</v>
       </c>
       <c r="P51" s="1">
         <v>38.38748944617691</v>
       </c>
       <c r="Q51" s="1">
-        <v>55.647058823529406</v>
+        <v>54.470588235294116</v>
       </c>
       <c r="R51" s="1">
-        <v>40.23529411764706</v>
+        <v>42.76470588235294</v>
       </c>
       <c r="S51" s="1" t="s">
         <v>97</v>
@@ -5285,43 +5288,43 @@
         <v>-5.32</v>
       </c>
       <c r="F52" s="3">
-        <v>-0.09322290450599283</v>
+        <v>-0.1556909455488903</v>
       </c>
       <c r="G52" s="3">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="H52" s="3">
-        <v>41.69</v>
+        <v>42.56</v>
       </c>
       <c r="I52" s="3">
-        <v>-31.64</v>
+        <v>-31.08</v>
       </c>
       <c r="J52" s="3">
-        <v>-0.014901649060531279</v>
+        <v>-0.014176342869726724</v>
       </c>
       <c r="K52" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L52" s="3">
-        <v>-106</v>
+        <v>-110</v>
       </c>
       <c r="M52" s="3">
-        <v>-0.09803401780982102</v>
+        <v>-0.16057204895979837</v>
       </c>
       <c r="N52" s="3">
-        <v>-3.917288477153896</v>
+        <v>-9.558756661637522</v>
       </c>
       <c r="O52" s="3">
-        <v>37.64705882352941</v>
+        <v>24.705882352941178</v>
       </c>
       <c r="P52" s="3">
         <v>34.68082090497681</v>
       </c>
       <c r="Q52" s="3">
-        <v>33.88235294117647</v>
+        <v>34</v>
       </c>
       <c r="R52" s="3">
-        <v>28.35294117647059</v>
+        <v>24.117647058823533</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>114</v>
@@ -5345,43 +5348,43 @@
         <v>-0.87</v>
       </c>
       <c r="F53" s="3">
-        <v>-0.02853783888377522</v>
+        <v>-0.05073960103705262</v>
       </c>
       <c r="G53" s="3">
         <v>0</v>
       </c>
       <c r="H53" s="3">
-        <v>57.24</v>
+        <v>52.32</v>
       </c>
       <c r="I53" s="3">
-        <v>6.47</v>
+        <v>3.52</v>
       </c>
       <c r="J53" s="3">
-        <v>-0.00028338611462836165</v>
+        <v>0.00616712984089757</v>
       </c>
       <c r="K53" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L53" s="3">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="M53" s="3">
-        <v>-0.07664897192205722</v>
+        <v>-0.10497408338047576</v>
       </c>
       <c r="N53" s="3">
-        <v>-1.7787838883775209</v>
+        <v>-3.9989601037052673</v>
       </c>
       <c r="O53" s="3">
-        <v>38.82352941176471</v>
+        <v>36.470588235294116</v>
       </c>
       <c r="P53" s="3">
         <v>48.781873808753</v>
       </c>
       <c r="Q53" s="3">
-        <v>39.05882352941177</v>
+        <v>39.294117647058826</v>
       </c>
       <c r="R53" s="3">
-        <v>22.176470588235297</v>
+        <v>22.058823529411768</v>
       </c>
       <c r="S53" s="3" t="s">
         <v>96</v>
@@ -5405,111 +5408,111 @@
         <v>-1.38</v>
       </c>
       <c r="F54" s="1">
-        <v>-0.04717718517893808</v>
+        <v>-0.011625899312348711</v>
       </c>
       <c r="G54" s="1">
         <v>0.98</v>
       </c>
       <c r="H54" s="1">
-        <v>42.09</v>
+        <v>51.46</v>
       </c>
       <c r="I54" s="1">
-        <v>3.15</v>
+        <v>5.85</v>
       </c>
       <c r="J54" s="1">
-        <v>0.004441741139798914</v>
+        <v>0.00526224159782243</v>
       </c>
       <c r="K54" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" s="1">
         <v>85</v>
       </c>
       <c r="M54" s="1">
-        <v>-0.04813940783970372</v>
+        <v>-0.012710588959217173</v>
       </c>
       <c r="N54" s="1">
-        <v>1.072172519857834</v>
+        <v>5.227389338420602</v>
       </c>
       <c r="O54" s="1">
-        <v>49.411764705882355</v>
+        <v>57.647058823529406</v>
       </c>
       <c r="P54" s="1">
         <v>11.84024085938085</v>
       </c>
       <c r="Q54" s="1">
-        <v>49.647058823529406</v>
+        <v>53.05882352941176</v>
       </c>
       <c r="R54" s="1">
-        <v>45.29411764705882</v>
+        <v>47.529411764705884</v>
       </c>
       <c r="S54" s="1" t="s">
         <v>115</v>
       </c>
       <c r="T54" s="1">
-        <v>4.87</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
+      <c r="A55" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B55" s="1">
+      <c r="B55" s="3">
         <v>23.25</v>
       </c>
-      <c r="C55" s="1">
+      <c r="C55" s="3">
         <v>94.11764705882352</v>
       </c>
-      <c r="D55" s="1">
+      <c r="D55" s="3">
         <v>-0.1840860215053764</v>
       </c>
-      <c r="E55" s="1">
+      <c r="E55" s="3">
         <v>0.67</v>
       </c>
-      <c r="F55" s="1">
-        <v>-0.288060757277564</v>
-      </c>
-      <c r="G55" s="1">
+      <c r="F55" s="3">
+        <v>-0.27141810180094517</v>
+      </c>
+      <c r="G55" s="3">
         <v>1.58</v>
       </c>
-      <c r="H55" s="1">
-        <v>47.79</v>
-      </c>
-      <c r="I55" s="1">
-        <v>2.83</v>
-      </c>
-      <c r="J55" s="1">
-        <v>-0.01779511032282079</v>
-      </c>
-      <c r="K55" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L55" s="1">
+      <c r="H55" s="3">
+        <v>47.65</v>
+      </c>
+      <c r="I55" s="3">
+        <v>2.48</v>
+      </c>
+      <c r="J55" s="3">
+        <v>-0.01629632521473801</v>
+      </c>
+      <c r="K55" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L55" s="3">
         <v>349</v>
       </c>
-      <c r="M55" s="1">
-        <v>-0.2601563001153604</v>
-      </c>
-      <c r="N55" s="1">
-        <v>-20.129516707707833</v>
-      </c>
-      <c r="O55" s="1">
-        <v>16.470588235294116</v>
-      </c>
-      <c r="P55" s="1">
+      <c r="M55" s="3">
+        <v>-0.23996210204175972</v>
+      </c>
+      <c r="N55" s="3">
+        <v>-17.49776196983366</v>
+      </c>
+      <c r="O55" s="3">
+        <v>12.941176470588237</v>
+      </c>
+      <c r="P55" s="3">
         <v>26.83257063748809</v>
       </c>
-      <c r="Q55" s="1">
-        <v>47.647058823529406</v>
-      </c>
-      <c r="R55" s="1">
-        <v>30.529411764705884</v>
-      </c>
-      <c r="S55" s="1" t="s">
+      <c r="Q55" s="3">
+        <v>47.29411764705881</v>
+      </c>
+      <c r="R55" s="3">
+        <v>29.235294117647058</v>
+      </c>
+      <c r="S55" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="T55" s="1">
-        <v>-28.07</v>
+      <c r="T55" s="3">
+        <v>-29.36</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
@@ -5529,49 +5532,49 @@
         <v>1.76</v>
       </c>
       <c r="F56" s="1">
-        <v>-0.40501189646957925</v>
+        <v>-0.37319162494732894</v>
       </c>
       <c r="G56" s="1">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="H56" s="1">
-        <v>58.16</v>
+        <v>57.38</v>
       </c>
       <c r="I56" s="1">
-        <v>34.4</v>
+        <v>33.36</v>
       </c>
       <c r="J56" s="1">
-        <v>0.002493886963514102</v>
+        <v>0.01229850390500414</v>
       </c>
       <c r="K56" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L56" s="1">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M56" s="1">
-        <v>-0.2698196126320068</v>
+        <v>-0.22133507438574418</v>
       </c>
       <c r="N56" s="1">
-        <v>-21.095847959372488</v>
+        <v>-15.6350592042321</v>
       </c>
       <c r="O56" s="1">
-        <v>15.294117647058824</v>
+        <v>16.470588235294116</v>
       </c>
       <c r="P56" s="1">
         <v>52.65288503392759</v>
       </c>
       <c r="Q56" s="1">
-        <v>64.47058823529412</v>
+        <v>69.29411764705883</v>
       </c>
       <c r="R56" s="1">
-        <v>32.352941176470594</v>
+        <v>35.05882352941177</v>
       </c>
       <c r="S56" s="1" t="s">
         <v>111</v>
       </c>
       <c r="T56" s="1">
-        <v>-27.65</v>
+        <v>-24.94</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
@@ -5591,19 +5594,19 @@
         <v>-1.31</v>
       </c>
       <c r="F57" s="3">
-        <v>-0.4080921337953689</v>
+        <v>-0.339847777710406</v>
       </c>
       <c r="G57" s="3">
         <v>2.04</v>
       </c>
       <c r="H57" s="3">
-        <v>44.9</v>
+        <v>43.47</v>
       </c>
       <c r="I57" s="3">
-        <v>-5.08</v>
+        <v>-6.61</v>
       </c>
       <c r="J57" s="3">
-        <v>-0.02658883780766918</v>
+        <v>-0.024809220487229364</v>
       </c>
       <c r="K57" s="3" t="b">
         <v>0</v>
@@ -5612,10 +5615,10 @@
         <v>250</v>
       </c>
       <c r="M57" s="3">
-        <v>-0.3580565554355556</v>
+        <v>-0.2834439160732459</v>
       </c>
       <c r="N57" s="3">
-        <v>-29.919542239727363</v>
+        <v>-21.84594337298228</v>
       </c>
       <c r="O57" s="3">
         <v>7.0588235294117645</v>
@@ -5653,19 +5656,19 @@
         <v>1.26</v>
       </c>
       <c r="F58" s="1">
-        <v>-0.03510685683816665</v>
+        <v>-0.07314590368359956</v>
       </c>
       <c r="G58" s="1">
         <v>1.64</v>
       </c>
       <c r="H58" s="1">
-        <v>40</v>
+        <v>41.11</v>
       </c>
       <c r="I58" s="1">
-        <v>-20.02</v>
+        <v>-19.65</v>
       </c>
       <c r="J58" s="1">
-        <v>0.008187271445607172</v>
+        <v>0.010654820733857415</v>
       </c>
       <c r="K58" s="1" t="b">
         <v>1</v>
@@ -5674,28 +5677,28 @@
         <v>3</v>
       </c>
       <c r="M58" s="1">
-        <v>-0.004315731693666169</v>
+        <v>-0.03843583498380876</v>
       </c>
       <c r="N58" s="1">
-        <v>5.454540134461573</v>
+        <v>2.6548647359614446</v>
       </c>
       <c r="O58" s="1">
-        <v>56.470588235294116</v>
+        <v>52.94117647058824</v>
       </c>
       <c r="P58" s="1">
         <v>33.706290307642504</v>
       </c>
       <c r="Q58" s="1">
-        <v>53.529411764705884</v>
+        <v>55.1764705882353</v>
       </c>
       <c r="R58" s="1">
-        <v>47.1764705882353</v>
+        <v>46.35294117647059</v>
       </c>
       <c r="S58" s="1" t="s">
         <v>103</v>
       </c>
       <c r="T58" s="1">
-        <v>25.23</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
@@ -5715,19 +5718,19 @@
         <v>0.97</v>
       </c>
       <c r="F59" s="3">
-        <v>-0.36214032499205284</v>
+        <v>-0.2917755267339034</v>
       </c>
       <c r="G59" s="3">
         <v>1.86</v>
       </c>
       <c r="H59" s="3">
-        <v>49.65</v>
+        <v>50.68</v>
       </c>
       <c r="I59" s="3">
-        <v>10.96</v>
+        <v>11.79</v>
       </c>
       <c r="J59" s="3">
-        <v>-0.020031765263886687</v>
+        <v>-0.015145886610036194</v>
       </c>
       <c r="K59" s="3" t="b">
         <v>1</v>
@@ -5736,28 +5739,28 @@
         <v>520</v>
       </c>
       <c r="M59" s="3">
-        <v>-0.32076475057913034</v>
+        <v>-0.2451338719185595</v>
       </c>
       <c r="N59" s="3">
-        <v>-26.19036175408484</v>
+        <v>-18.014938957513635</v>
       </c>
       <c r="O59" s="3">
-        <v>8.235294117647058</v>
+        <v>11.76470588235294</v>
       </c>
       <c r="P59" s="3">
         <v>41.76493344029593</v>
       </c>
       <c r="Q59" s="3">
-        <v>49.411764705882355</v>
+        <v>50.94117647058824</v>
       </c>
       <c r="R59" s="3">
-        <v>25.176470588235297</v>
+        <v>26.70588235294118</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>110</v>
       </c>
       <c r="T59" s="3">
-        <v>-34.03</v>
+        <v>-32.5</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.25">
@@ -5777,19 +5780,19 @@
         <v>-4.45</v>
       </c>
       <c r="F60" s="3">
-        <v>-0.4762525915996093</v>
+        <v>-0.4746268538055761</v>
       </c>
       <c r="G60" s="3">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="H60" s="3">
-        <v>39.76</v>
+        <v>35.66</v>
       </c>
       <c r="I60" s="3">
-        <v>-33.17</v>
+        <v>-34.99</v>
       </c>
       <c r="J60" s="3">
-        <v>-0.03034375587208709</v>
+        <v>-0.02643302661710694</v>
       </c>
       <c r="K60" s="3" t="b">
         <v>0</v>
@@ -5798,28 +5801,28 @@
         <v>21</v>
       </c>
       <c r="M60" s="3">
-        <v>-0.3886903294699361</v>
+        <v>-0.3753777511171118</v>
       </c>
       <c r="N60" s="3">
-        <v>-32.9829196431654</v>
+        <v>-31.039326877368868</v>
       </c>
       <c r="O60" s="3">
-        <v>4.705882352941177</v>
+        <v>3.5294117647058822</v>
       </c>
       <c r="P60" s="3">
         <v>46.90217032437056</v>
       </c>
       <c r="Q60" s="3">
-        <v>24.470588235294116</v>
+        <v>24.11764705882353</v>
       </c>
       <c r="R60" s="3">
-        <v>10.999999999999996</v>
+        <v>10.64705882352941</v>
       </c>
       <c r="S60" s="3" t="s">
         <v>98</v>
       </c>
       <c r="T60" s="3">
-        <v>-15.89</v>
+        <v>-16.24</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
@@ -5833,55 +5836,55 @@
         <v>55.294117647058826</v>
       </c>
       <c r="D61" s="1">
-        <v>2.142528735632184</v>
+        <v>2.1747126436781614</v>
       </c>
       <c r="E61" s="1">
         <v>-0.52</v>
       </c>
       <c r="F61" s="1">
-        <v>-0.05819923617421936</v>
+        <v>-0.10634080411283578</v>
       </c>
       <c r="G61" s="1">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="H61" s="1">
-        <v>30.89</v>
+        <v>25.28</v>
       </c>
       <c r="I61" s="1">
-        <v>4.76</v>
+        <v>1.37</v>
       </c>
       <c r="J61" s="1">
-        <v>-0.0018349270383264532</v>
+        <v>-0.003637125376053656</v>
       </c>
       <c r="K61" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" s="1">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="M61" s="1">
-        <v>-0.04857700956656297</v>
+        <v>-0.09495156282071693</v>
       </c>
       <c r="N61" s="1">
-        <v>1.028412347171901</v>
+        <v>-2.9967080477293764</v>
       </c>
       <c r="O61" s="1">
-        <v>48.23529411764706</v>
+        <v>37.64705882352941</v>
       </c>
       <c r="P61" s="1">
-        <v>10.92423743722024</v>
+        <v>13.593577982515374</v>
       </c>
       <c r="Q61" s="1">
-        <v>45.64705882352941</v>
+        <v>43.1764705882353</v>
       </c>
       <c r="R61" s="1">
-        <v>44.29411764705883</v>
+        <v>39.70588235294118</v>
       </c>
       <c r="S61" s="1" t="s">
         <v>116</v>
       </c>
       <c r="T61" s="1">
-        <v>-2.9</v>
+        <v>-7.49</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
@@ -5901,19 +5904,19 @@
         <v>0.11</v>
       </c>
       <c r="F62" s="2">
-        <v>0.1447019618261561</v>
+        <v>0.10426060464486614</v>
       </c>
       <c r="G62" s="2">
         <v>0.2</v>
       </c>
       <c r="H62" s="2">
-        <v>51.06</v>
+        <v>52.07</v>
       </c>
       <c r="I62" s="2">
-        <v>12</v>
+        <v>11.96</v>
       </c>
       <c r="J62" s="2">
-        <v>0.002900590394848981</v>
+        <v>0.0031673648005258437</v>
       </c>
       <c r="K62" s="2" t="b">
         <v>1</v>
@@ -5922,28 +5925,28 @@
         <v>93</v>
       </c>
       <c r="M62" s="2">
-        <v>0.1062130553955305</v>
+        <v>0.06087301877012763</v>
       </c>
       <c r="N62" s="2">
-        <v>16.50741884338125</v>
+        <v>12.585750111355079</v>
       </c>
       <c r="O62" s="2">
-        <v>71.76470588235294</v>
+        <v>63.52941176470588</v>
       </c>
       <c r="P62" s="2">
         <v>7.56622762341097</v>
       </c>
       <c r="Q62" s="2">
-        <v>55.529411764705884</v>
+        <v>55.05882352941176</v>
       </c>
       <c r="R62" s="2">
-        <v>53.76470588235295</v>
+        <v>50.94117647058823</v>
       </c>
       <c r="S62" s="2" t="s">
         <v>101</v>
       </c>
       <c r="T62" s="2">
-        <v>7.79</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
@@ -5957,55 +5960,55 @@
         <v>98.82352941176471</v>
       </c>
       <c r="D63" s="1">
-        <v>1.5843332578673308</v>
+        <v>1.5863708399366083</v>
       </c>
       <c r="E63" s="1">
         <v>-1.09</v>
       </c>
       <c r="F63" s="1">
-        <v>-0.25672498670267446</v>
+        <v>-0.10940412880479819</v>
       </c>
       <c r="G63" s="1">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="H63" s="1">
-        <v>58.84</v>
+        <v>59.82</v>
       </c>
       <c r="I63" s="1">
-        <v>58.75</v>
+        <v>60.87</v>
       </c>
       <c r="J63" s="1">
-        <v>0.0010465932475691904</v>
+        <v>0.007891169951779037</v>
       </c>
       <c r="K63" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L63" s="1">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="M63" s="1">
-        <v>-0.19706718173520477</v>
+        <v>-0.04269571552238771</v>
       </c>
       <c r="N63" s="1">
-        <v>-13.820604869692273</v>
+        <v>2.2288766821035337</v>
       </c>
       <c r="O63" s="1">
-        <v>23.52941176470588</v>
+        <v>50.588235294117645</v>
       </c>
       <c r="P63" s="1">
         <v>39.10478556320163</v>
       </c>
       <c r="Q63" s="1">
-        <v>70.70588235294117</v>
+        <v>73.17647058823529</v>
       </c>
       <c r="R63" s="1">
-        <v>40.823529411764696</v>
+        <v>49.882352941176464</v>
       </c>
       <c r="S63" s="1" t="s">
         <v>117</v>
       </c>
       <c r="T63" s="1">
-        <v>-27.29</v>
+        <v>-18.23</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.25">
@@ -6019,55 +6022,55 @@
         <v>97.6470588235294</v>
       </c>
       <c r="D64" s="1">
-        <v>-1.5714285714285714</v>
+        <v>-1.5699971371314059</v>
       </c>
       <c r="E64" s="1">
         <v>1.52</v>
       </c>
       <c r="F64" s="1">
-        <v>-0.21826527074775506</v>
+        <v>-0.1437068021735461</v>
       </c>
       <c r="G64" s="1">
         <v>0.97</v>
       </c>
       <c r="H64" s="1">
-        <v>49.13</v>
+        <v>48.77</v>
       </c>
       <c r="I64" s="1">
-        <v>4.15</v>
+        <v>3.68</v>
       </c>
       <c r="J64" s="1">
-        <v>-0.016992616469964354</v>
+        <v>-0.013487697999865201</v>
       </c>
       <c r="K64" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L64" s="1">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="M64" s="1">
-        <v>-0.21970860473890352</v>
+        <v>-0.1453338366438488</v>
       </c>
       <c r="N64" s="1">
-        <v>-16.08474717006215</v>
+        <v>-8.034935430042568</v>
       </c>
       <c r="O64" s="1">
-        <v>21.176470588235293</v>
+        <v>29.411764705882355</v>
       </c>
       <c r="P64" s="1">
         <v>25.543467249515373</v>
       </c>
       <c r="Q64" s="1">
-        <v>45.64705882352941</v>
+        <v>46.58823529411765</v>
       </c>
       <c r="R64" s="1">
-        <v>30.17647058823529</v>
+        <v>32.882352941176464</v>
       </c>
       <c r="S64" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T64" s="1">
-        <v>-14.58</v>
+        <v>-11.87</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.25">
@@ -6081,25 +6084,25 @@
         <v>65.88235294117646</v>
       </c>
       <c r="D65" s="1">
-        <v>-0.3740157480314961</v>
+        <v>-0.39107611548556437</v>
       </c>
       <c r="E65" s="1">
         <v>0.4</v>
       </c>
       <c r="F65" s="1">
-        <v>-0.10661675418115169</v>
+        <v>-0.11383661090491344</v>
       </c>
       <c r="G65" s="1">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="H65" s="1">
-        <v>26.56</v>
+        <v>30.07</v>
       </c>
       <c r="I65" s="1">
-        <v>-12.27</v>
+        <v>-12.06</v>
       </c>
       <c r="J65" s="1">
-        <v>-0.006198749451862429</v>
+        <v>-0.006280424808417941</v>
       </c>
       <c r="K65" s="1" t="b">
         <v>1</v>
@@ -6108,28 +6111,28 @@
         <v>-101</v>
       </c>
       <c r="M65" s="1">
-        <v>-0.137888990656035</v>
+        <v>-0.14854667960470425</v>
       </c>
       <c r="N65" s="1">
-        <v>-7.902785761775298</v>
+        <v>-8.356219726128106</v>
       </c>
       <c r="O65" s="1">
-        <v>30.58823529411765</v>
+        <v>28.235294117647058</v>
       </c>
       <c r="P65" s="1">
         <v>18.234594077618315</v>
       </c>
       <c r="Q65" s="1">
-        <v>35.05882352941176</v>
+        <v>34.588235294117645</v>
       </c>
       <c r="R65" s="1">
-        <v>31.41176470588235</v>
+        <v>30.58823529411765</v>
       </c>
       <c r="S65" s="1" t="s">
         <v>118</v>
       </c>
       <c r="T65" s="1">
-        <v>5.38</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
@@ -6149,19 +6152,19 @@
         <v>2.08</v>
       </c>
       <c r="F66" s="2">
-        <v>0.09081696202461209</v>
+        <v>0.14063338479640128</v>
       </c>
       <c r="G66" s="2">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="H66" s="2">
-        <v>60.94</v>
+        <v>65.86</v>
       </c>
       <c r="I66" s="2">
-        <v>18.23</v>
+        <v>21.31</v>
       </c>
       <c r="J66" s="2">
-        <v>0.012576158300945956</v>
+        <v>0.014957079449734328</v>
       </c>
       <c r="K66" s="2" t="b">
         <v>0</v>
@@ -6170,90 +6173,90 @@
         <v>80</v>
       </c>
       <c r="M66" s="2">
-        <v>0.08504362606001825</v>
+        <v>0.13358290209175627</v>
       </c>
       <c r="N66" s="2">
-        <v>14.390475909830016</v>
+        <v>19.85673844351794</v>
       </c>
       <c r="O66" s="2">
-        <v>70.58823529411765</v>
+        <v>75.29411764705883</v>
       </c>
       <c r="P66" s="2">
         <v>10.56723987277981</v>
       </c>
       <c r="Q66" s="2">
-        <v>69.05882352941177</v>
+        <v>70.94117647058823</v>
       </c>
       <c r="R66" s="2">
-        <v>59.941176470588246</v>
+        <v>61.58823529411765</v>
       </c>
       <c r="S66" s="2" t="s">
         <v>119</v>
       </c>
       <c r="T66" s="2">
-        <v>16.34</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A67" s="3" t="s">
+      <c r="A67" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B67" s="3">
+      <c r="B67" s="1">
         <v>72.89</v>
       </c>
-      <c r="C67" s="3">
+      <c r="C67" s="1">
         <v>100</v>
       </c>
-      <c r="D67" s="3">
+      <c r="D67" s="1">
         <v>-0.6876114693373577</v>
       </c>
-      <c r="E67" s="3">
+      <c r="E67" s="1">
         <v>1.69</v>
       </c>
-      <c r="F67" s="3">
-        <v>-0.483467970397213</v>
-      </c>
-      <c r="G67" s="3">
-        <v>5.19</v>
-      </c>
-      <c r="H67" s="3">
-        <v>59.01</v>
-      </c>
-      <c r="I67" s="3">
-        <v>61.97</v>
-      </c>
-      <c r="J67" s="3">
-        <v>-0.008451523664449314</v>
-      </c>
-      <c r="K67" s="3" t="b">
+      <c r="F67" s="1">
+        <v>-0.34390122875127477</v>
+      </c>
+      <c r="G67" s="1">
+        <v>5.2</v>
+      </c>
+      <c r="H67" s="1">
+        <v>57.64</v>
+      </c>
+      <c r="I67" s="1">
+        <v>61.62</v>
+      </c>
+      <c r="J67" s="1">
+        <v>-0.0007520970444974813</v>
+      </c>
+      <c r="K67" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L67" s="3">
-        <v>669</v>
-      </c>
-      <c r="M67" s="3">
-        <v>-0.28188232296681137</v>
-      </c>
-      <c r="N67" s="3">
-        <v>-22.302118992852936</v>
-      </c>
-      <c r="O67" s="3">
-        <v>12.941176470588237</v>
-      </c>
-      <c r="P67" s="3">
+      <c r="L67" s="1">
+        <v>667</v>
+      </c>
+      <c r="M67" s="1">
+        <v>-0.11611640290889758</v>
+      </c>
+      <c r="N67" s="1">
+        <v>-5.113192056547441</v>
+      </c>
+      <c r="O67" s="1">
+        <v>34.11764705882353</v>
+      </c>
+      <c r="P67" s="1">
         <v>56.49293299150161</v>
       </c>
-      <c r="Q67" s="3">
-        <v>58.352941176470594</v>
-      </c>
-      <c r="R67" s="3">
-        <v>26.470588235294116</v>
-      </c>
-      <c r="S67" s="3" t="s">
+      <c r="Q67" s="1">
+        <v>61.1764705882353</v>
+      </c>
+      <c r="R67" s="1">
+        <v>34.05882352941176</v>
+      </c>
+      <c r="S67" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="T67" s="3">
-        <v>-42.92</v>
+      <c r="T67" s="1">
+        <v>-35.33</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
@@ -6267,55 +6270,55 @@
         <v>83.52941176470588</v>
       </c>
       <c r="D68" s="1">
-        <v>3.0958904109589045</v>
+        <v>3.1405912040374915</v>
       </c>
       <c r="E68" s="1">
         <v>-2.41</v>
       </c>
       <c r="F68" s="1">
-        <v>-0.3093846180875441</v>
+        <v>-0.2345671284820057</v>
       </c>
       <c r="G68" s="1">
         <v>2.09</v>
       </c>
       <c r="H68" s="1">
-        <v>52.59</v>
+        <v>57.39</v>
       </c>
       <c r="I68" s="1">
-        <v>37.52</v>
+        <v>43.49</v>
       </c>
       <c r="J68" s="1">
-        <v>-0.0061824604096929</v>
+        <v>-0.0024222637003197605</v>
       </c>
       <c r="K68" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L68" s="1">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="M68" s="1">
-        <v>-0.2569434830758167</v>
+        <v>-0.1754515427276745</v>
       </c>
       <c r="N68" s="1">
-        <v>-19.80823500375347</v>
+        <v>-11.046706038425134</v>
       </c>
       <c r="O68" s="1">
-        <v>17.647058823529413</v>
+        <v>21.176470588235293</v>
       </c>
       <c r="P68" s="1">
         <v>31.85898471566022</v>
       </c>
       <c r="Q68" s="1">
-        <v>62.82352941176471</v>
+        <v>65.88235294117648</v>
       </c>
       <c r="R68" s="1">
-        <v>36.294117647058826</v>
+        <v>38.05882352941177</v>
       </c>
       <c r="S68" s="1" t="s">
         <v>111</v>
       </c>
       <c r="T68" s="1">
-        <v>-29.74</v>
+        <v>-27.98</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
@@ -6335,19 +6338,19 @@
         <v>-1.74</v>
       </c>
       <c r="F69" s="1">
-        <v>0.12191258079284352</v>
+        <v>0.04697038470444885</v>
       </c>
       <c r="G69" s="1">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="H69" s="1">
-        <v>40.46</v>
+        <v>32.56</v>
       </c>
       <c r="I69" s="1">
-        <v>-24.89</v>
+        <v>-29.41</v>
       </c>
       <c r="J69" s="1">
-        <v>0.012090565256253636</v>
+        <v>0.008317740820796147</v>
       </c>
       <c r="K69" s="1" t="b">
         <v>0</v>
@@ -6356,28 +6359,28 @@
         <v>-251</v>
       </c>
       <c r="M69" s="1">
-        <v>0.12095035813207788</v>
+        <v>0.04642803988101463</v>
       </c>
       <c r="N69" s="1">
-        <v>17.98114911703599</v>
+        <v>11.141252222443766</v>
       </c>
       <c r="O69" s="1">
-        <v>74.11764705882354</v>
+        <v>62.35294117647059</v>
       </c>
       <c r="P69" s="1">
         <v>37.32769516583675</v>
       </c>
       <c r="Q69" s="1">
-        <v>51.64705882352941</v>
+        <v>46.941176470588225</v>
       </c>
       <c r="R69" s="1">
-        <v>49.82352941176471</v>
+        <v>44.882352941176464</v>
       </c>
       <c r="S69" s="1" t="s">
         <v>120</v>
       </c>
       <c r="T69" s="1">
-        <v>32.08</v>
+        <v>27.14</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
@@ -6391,25 +6394,25 @@
         <v>57.647058823529406</v>
       </c>
       <c r="D70" s="1">
-        <v>5.90989010989011</v>
+        <v>5.923076923076923</v>
       </c>
       <c r="E70" s="1">
         <v>-0.54</v>
       </c>
       <c r="F70" s="1">
-        <v>-0.07914880660674846</v>
+        <v>-0.1390719121631107</v>
       </c>
       <c r="G70" s="1">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="H70" s="1">
-        <v>41.35</v>
+        <v>36.48</v>
       </c>
       <c r="I70" s="1">
-        <v>-5.95</v>
+        <v>-7.97</v>
       </c>
       <c r="J70" s="1">
-        <v>-0.003959832536586201</v>
+        <v>-0.004690740525377768</v>
       </c>
       <c r="K70" s="1" t="b">
         <v>0</v>
@@ -6418,28 +6421,28 @@
         <v>4</v>
       </c>
       <c r="M70" s="1">
-        <v>-0.06712102334717795</v>
+        <v>-0.1249709467538207</v>
       </c>
       <c r="N70" s="1">
-        <v>-0.8259890308895951</v>
+        <v>-5.998646441039758</v>
       </c>
       <c r="O70" s="1">
-        <v>40</v>
+        <v>32.94117647058823</v>
       </c>
       <c r="P70" s="1">
         <v>16.710870321490763</v>
       </c>
       <c r="Q70" s="1">
-        <v>49.41176470588235</v>
+        <v>46.82352941176471</v>
       </c>
       <c r="R70" s="1">
-        <v>43.647058823529406</v>
+        <v>40.58823529411765</v>
       </c>
       <c r="S70" s="1" t="s">
         <v>103</v>
       </c>
       <c r="T70" s="1">
-        <v>1.94</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.25">
@@ -6459,19 +6462,19 @@
         <v>0.14</v>
       </c>
       <c r="F71" s="2">
-        <v>0.17910724334687944</v>
+        <v>0.1818283619151045</v>
       </c>
       <c r="G71" s="2">
         <v>0.33</v>
       </c>
       <c r="H71" s="2">
-        <v>61.78</v>
+        <v>60.3</v>
       </c>
       <c r="I71" s="2">
-        <v>10.97</v>
+        <v>11.01</v>
       </c>
       <c r="J71" s="2">
-        <v>0.011428321756449769</v>
+        <v>0.011873694973868707</v>
       </c>
       <c r="K71" s="2" t="b">
         <v>1</v>
@@ -6480,10 +6483,10 @@
         <v>-79</v>
       </c>
       <c r="M71" s="2">
-        <v>0.1468727842112305</v>
+        <v>0.145491258745011</v>
       </c>
       <c r="N71" s="2">
-        <v>20.57339172495126</v>
+        <v>21.047574108843424</v>
       </c>
       <c r="O71" s="2">
         <v>76.47058823529412</v>
@@ -6492,16 +6495,16 @@
         <v>10.873073633899006</v>
       </c>
       <c r="Q71" s="2">
-        <v>62.94117647058824</v>
+        <v>62.58823529411765</v>
       </c>
       <c r="R71" s="2">
-        <v>57.52941176470589</v>
+        <v>57.41176470588236</v>
       </c>
       <c r="S71" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T71" s="2">
-        <v>9.48</v>
+        <v>9.36</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.25">
@@ -6521,19 +6524,19 @@
         <v>0.2</v>
       </c>
       <c r="F72" s="1">
-        <v>-0.08518072896555895</v>
+        <v>-0.1025784763643005</v>
       </c>
       <c r="G72" s="1">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H72" s="1">
-        <v>64.68</v>
+        <v>60.94</v>
       </c>
       <c r="I72" s="1">
-        <v>-11.48</v>
+        <v>-12.09</v>
       </c>
       <c r="J72" s="1">
-        <v>-0.008265106383773379</v>
+        <v>-0.005793518152722301</v>
       </c>
       <c r="K72" s="1" t="b">
         <v>1</v>
@@ -6542,28 +6545,28 @@
         <v>-41</v>
       </c>
       <c r="M72" s="1">
-        <v>-0.06208738510718359</v>
+        <v>-0.07708826966289162</v>
       </c>
       <c r="N72" s="1">
-        <v>-0.32262520689016383</v>
+        <v>-1.210378731946844</v>
       </c>
       <c r="O72" s="1">
-        <v>42.35294117647059</v>
+        <v>43.529411764705884</v>
       </c>
       <c r="P72" s="1">
         <v>29.505935179545663</v>
       </c>
       <c r="Q72" s="1">
-        <v>51.41176470588235</v>
+        <v>51.17647058823529</v>
       </c>
       <c r="R72" s="1">
-        <v>38.411764705882355</v>
+        <v>39</v>
       </c>
       <c r="S72" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T72" s="1">
-        <v>8.96</v>
+        <v>9.55</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.25">
@@ -6583,19 +6586,19 @@
         <v>-0.34</v>
       </c>
       <c r="F73" s="2">
-        <v>0.3661418648578458</v>
+        <v>0.3584735428253212</v>
       </c>
       <c r="G73" s="2">
         <v>0.89</v>
       </c>
       <c r="H73" s="2">
-        <v>70.01</v>
+        <v>72.47</v>
       </c>
       <c r="I73" s="2">
-        <v>22.49</v>
+        <v>23.9</v>
       </c>
       <c r="J73" s="2">
-        <v>0.022824506586912218</v>
+        <v>0.0231736868851309</v>
       </c>
       <c r="K73" s="2" t="b">
         <v>1</v>
@@ -6604,10 +6607,10 @@
         <v>49</v>
       </c>
       <c r="M73" s="2">
-        <v>0.36084964022363475</v>
+        <v>0.3525077497675446</v>
       </c>
       <c r="N73" s="2">
-        <v>41.971077326191676</v>
+        <v>41.74922321109678</v>
       </c>
       <c r="O73" s="2">
         <v>88.23529411764706</v>
@@ -6616,16 +6619,16 @@
         <v>8.480874361506512</v>
       </c>
       <c r="Q73" s="2">
-        <v>67.52941176470588</v>
+        <v>67.76470588235294</v>
       </c>
       <c r="R73" s="2">
-        <v>61.82352941176471</v>
+        <v>61.94117647058824</v>
       </c>
       <c r="S73" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T73" s="2">
-        <v>21.95</v>
+        <v>22.06</v>
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.25">
@@ -6639,117 +6642,117 @@
         <v>44.70588235294118</v>
       </c>
       <c r="D74" s="1">
-        <v>11.28095238095238</v>
+        <v>11.29047619047619</v>
       </c>
       <c r="E74" s="1">
         <v>0.44</v>
       </c>
       <c r="F74" s="1">
-        <v>-0.22734951375738882</v>
+        <v>-0.20838020460620804</v>
       </c>
       <c r="G74" s="1">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="H74" s="1">
-        <v>37.15</v>
+        <v>36.31</v>
       </c>
       <c r="I74" s="1">
-        <v>-27.61</v>
+        <v>-27.47</v>
       </c>
       <c r="J74" s="1">
-        <v>-0.017856358794734354</v>
+        <v>-0.01794466382043905</v>
       </c>
       <c r="K74" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L74" s="1">
-        <v>-167</v>
+        <v>-169</v>
       </c>
       <c r="M74" s="1">
-        <v>-0.2230195117839434</v>
+        <v>-0.20295675637186572</v>
       </c>
       <c r="N74" s="1">
-        <v>-16.415837874566144</v>
+        <v>-13.797227402844255</v>
       </c>
       <c r="O74" s="1">
-        <v>20</v>
+        <v>18.823529411764707</v>
       </c>
       <c r="P74" s="1">
         <v>25.03694506602277</v>
       </c>
       <c r="Q74" s="1">
-        <v>39.999999999999986</v>
+        <v>40.470588235294116</v>
       </c>
       <c r="R74" s="1">
-        <v>31.882352941176475</v>
+        <v>31.29411764705883</v>
       </c>
       <c r="S74" s="1" t="s">
         <v>121</v>
       </c>
       <c r="T74" s="1">
-        <v>-0.13</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
+      <c r="A75" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B75" s="1">
+      <c r="B75" s="3">
         <v>0.42</v>
       </c>
-      <c r="C75" s="1">
+      <c r="C75" s="3">
         <v>35.294117647058826</v>
       </c>
-      <c r="D75" s="1">
+      <c r="D75" s="3">
         <v>97.42857142857143</v>
       </c>
-      <c r="E75" s="1">
+      <c r="E75" s="3">
         <v>-3.72</v>
       </c>
-      <c r="F75" s="1">
-        <v>-0.25447052316800706</v>
-      </c>
-      <c r="G75" s="1">
+      <c r="F75" s="3">
+        <v>-0.2535075385430039</v>
+      </c>
+      <c r="G75" s="3">
         <v>1.25</v>
       </c>
-      <c r="H75" s="1">
-        <v>35.22</v>
-      </c>
-      <c r="I75" s="1">
-        <v>-7.97</v>
-      </c>
-      <c r="J75" s="1">
-        <v>-0.02010197248908249</v>
-      </c>
-      <c r="K75" s="1" t="b">
+      <c r="H75" s="3">
+        <v>33.98</v>
+      </c>
+      <c r="I75" s="3">
+        <v>-9.54</v>
+      </c>
+      <c r="J75" s="3">
+        <v>-0.020526609964835567</v>
+      </c>
+      <c r="K75" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L75" s="1">
+      <c r="L75" s="3">
         <v>32</v>
       </c>
-      <c r="M75" s="1">
-        <v>-0.24244273990843657</v>
-      </c>
-      <c r="N75" s="1">
-        <v>-18.358160687015463</v>
-      </c>
-      <c r="O75" s="1">
-        <v>18.823529411764707</v>
-      </c>
-      <c r="P75" s="1">
-        <v>29.662784615305803</v>
-      </c>
-      <c r="Q75" s="1">
-        <v>42.47058823529411</v>
-      </c>
-      <c r="R75" s="1">
-        <v>31.352941176470587</v>
-      </c>
-      <c r="S75" s="1" t="s">
+      <c r="M75" s="3">
+        <v>-0.23994891795714812</v>
+      </c>
+      <c r="N75" s="3">
+        <v>-17.4964435613725</v>
+      </c>
+      <c r="O75" s="3">
+        <v>14.117647058823529</v>
+      </c>
+      <c r="P75" s="3">
+        <v>30.766929498676355</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>41.99999999999999</v>
+      </c>
+      <c r="R75" s="3">
+        <v>29.705882352941174</v>
+      </c>
+      <c r="S75" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="T75" s="1">
-        <v>-27.24</v>
+      <c r="T75" s="3">
+        <v>-28.89</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
@@ -6769,19 +6772,19 @@
         <v>-0.07</v>
       </c>
       <c r="F76" s="3">
-        <v>-0.40944987440285974</v>
+        <v>-0.3801939058098336</v>
       </c>
       <c r="G76" s="3">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="H76" s="3">
-        <v>46.92</v>
+        <v>43.99</v>
       </c>
       <c r="I76" s="3">
-        <v>-29.66</v>
+        <v>-30.44</v>
       </c>
       <c r="J76" s="3">
-        <v>-0.01851730216819086</v>
+        <v>-0.012066563046976795</v>
       </c>
       <c r="K76" s="3" t="b">
         <v>0</v>
@@ -6790,10 +6793,10 @@
         <v>10</v>
       </c>
       <c r="M76" s="3">
-        <v>-0.301680936397108</v>
+        <v>-0.2581663205371315</v>
       </c>
       <c r="N76" s="3">
-        <v>-24.281980335882608</v>
+        <v>-19.318183819370834</v>
       </c>
       <c r="O76" s="3">
         <v>9.411764705882353</v>
@@ -6802,16 +6805,16 @@
         <v>51.49813033405746</v>
       </c>
       <c r="Q76" s="3">
-        <v>42.470588235294116</v>
+        <v>44.35294117647059</v>
       </c>
       <c r="R76" s="3">
-        <v>24.352941176470587</v>
+        <v>25.411764705882348</v>
       </c>
       <c r="S76" s="3" t="s">
         <v>109</v>
       </c>
       <c r="T76" s="3">
-        <v>-1.38</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
@@ -6831,19 +6834,19 @@
         <v>12.83</v>
       </c>
       <c r="F77" s="3">
-        <v>0.03308542528212116</v>
+        <v>-0.008463843435563806</v>
       </c>
       <c r="G77" s="3">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="H77" s="3">
-        <v>46.96</v>
+        <v>47.66</v>
       </c>
       <c r="I77" s="3">
-        <v>47.7</v>
+        <v>46.66</v>
       </c>
       <c r="J77" s="3">
-        <v>-0.027436595398920918</v>
+        <v>-0.02532844109852842</v>
       </c>
       <c r="K77" s="3" t="b">
         <v>1</v>
@@ -6852,28 +6855,28 @@
         <v>42</v>
       </c>
       <c r="M77" s="3">
-        <v>0.02683097798714451</v>
+        <v>-0.014971981316774574</v>
       </c>
       <c r="N77" s="3">
-        <v>8.569211102542653</v>
+        <v>5.00125010266486</v>
       </c>
       <c r="O77" s="3">
-        <v>60</v>
+        <v>56.470588235294116</v>
       </c>
       <c r="P77" s="3">
         <v>29.799918858582526</v>
       </c>
       <c r="Q77" s="3">
-        <v>30.82352941176471</v>
+        <v>31.411764705882355</v>
       </c>
       <c r="R77" s="3">
-        <v>26.058823529411768</v>
+        <v>25.11764705882353</v>
       </c>
       <c r="S77" s="3" t="s">
         <v>123</v>
       </c>
       <c r="T77" s="3">
-        <v>-47.66</v>
+        <v>-48.6</v>
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
@@ -6887,25 +6890,25 @@
         <v>45.88235294117647</v>
       </c>
       <c r="D78" s="2">
-        <v>2.5327102803738315</v>
+        <v>2.5233644859813085</v>
       </c>
       <c r="E78" s="2">
         <v>-9.21</v>
       </c>
       <c r="F78" s="2">
-        <v>0.8533544445212071</v>
+        <v>0.737380609576443</v>
       </c>
       <c r="G78" s="2">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="H78" s="2">
-        <v>69.62</v>
+        <v>69.02</v>
       </c>
       <c r="I78" s="2">
-        <v>37.34</v>
+        <v>37.22</v>
       </c>
       <c r="J78" s="2">
-        <v>0.035823719334485506</v>
+        <v>0.03350658862091758</v>
       </c>
       <c r="K78" s="2" t="b">
         <v>0</v>
@@ -6914,10 +6917,10 @@
         <v>-5</v>
       </c>
       <c r="M78" s="2">
-        <v>0.8490244425477618</v>
+        <v>0.7330418509889691</v>
       </c>
       <c r="N78" s="2">
-        <v>90.78855755860438</v>
+        <v>79.80263333323923</v>
       </c>
       <c r="O78" s="2">
         <v>98.82352941176471</v>
@@ -6926,16 +6929,16 @@
         <v>18.71809072120826</v>
       </c>
       <c r="Q78" s="2">
-        <v>66.3529411764706</v>
+        <v>66.23529411764707</v>
       </c>
       <c r="R78" s="2">
-        <v>60.529411764705884</v>
+        <v>60.64705882352942</v>
       </c>
       <c r="S78" s="2" t="s">
         <v>110</v>
       </c>
       <c r="T78" s="2">
-        <v>11.93</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.25">
@@ -6955,19 +6958,19 @@
         <v>-3.59</v>
       </c>
       <c r="F79" s="2">
-        <v>0.20345912339991712</v>
+        <v>0.15156768438222118</v>
       </c>
       <c r="G79" s="2">
         <v>1.12</v>
       </c>
       <c r="H79" s="2">
-        <v>57.2</v>
+        <v>52.1</v>
       </c>
       <c r="I79" s="2">
-        <v>29.64</v>
+        <v>27.39</v>
       </c>
       <c r="J79" s="2">
-        <v>0.010328529615366816</v>
+        <v>0.010105327452156775</v>
       </c>
       <c r="K79" s="2" t="b">
         <v>1</v>
@@ -6976,28 +6979,28 @@
         <v>-2</v>
       </c>
       <c r="M79" s="2">
-        <v>0.20923245936451096</v>
+        <v>0.15807582226343198</v>
       </c>
       <c r="N79" s="2">
-        <v>26.809359240279296</v>
+        <v>22.306030460685516</v>
       </c>
       <c r="O79" s="2">
-        <v>82.35294117647058</v>
+        <v>77.64705882352942</v>
       </c>
       <c r="P79" s="2">
         <v>16.006637557486414</v>
       </c>
       <c r="Q79" s="2">
-        <v>58</v>
+        <v>56.35294117647059</v>
       </c>
       <c r="R79" s="2">
-        <v>53.94117647058824</v>
+        <v>51.94117647058824</v>
       </c>
       <c r="S79" s="2" t="s">
         <v>108</v>
       </c>
       <c r="T79" s="2">
-        <v>5.77</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.25">
@@ -7017,19 +7020,19 @@
         <v>0.34</v>
       </c>
       <c r="F80" s="2">
-        <v>0.16325022398107458</v>
+        <v>0.14030161636326516</v>
       </c>
       <c r="G80" s="2">
         <v>0.83</v>
       </c>
       <c r="H80" s="2">
-        <v>44.42</v>
+        <v>43.93</v>
       </c>
       <c r="I80" s="2">
-        <v>9.13</v>
+        <v>8.74</v>
       </c>
       <c r="J80" s="2">
-        <v>0.008464093374121217</v>
+        <v>0.0077447226379382126</v>
       </c>
       <c r="K80" s="2" t="b">
         <v>1</v>
@@ -7038,28 +7041,28 @@
         <v>6</v>
       </c>
       <c r="M80" s="2">
-        <v>0.15507133136456663</v>
+        <v>0.13108175436488323</v>
       </c>
       <c r="N80" s="2">
-        <v>21.393246440284873</v>
+        <v>19.60662367083064</v>
       </c>
       <c r="O80" s="2">
-        <v>77.64705882352942</v>
+        <v>74.11764705882354</v>
       </c>
       <c r="P80" s="2">
         <v>11.616065285425229</v>
       </c>
       <c r="Q80" s="2">
-        <v>52.23529411764706</v>
+        <v>50.35294117647059</v>
       </c>
       <c r="R80" s="2">
-        <v>53.529411764705884</v>
+        <v>51.29411764705883</v>
       </c>
       <c r="S80" s="2" t="s">
         <v>102</v>
       </c>
       <c r="T80" s="2">
-        <v>13.65</v>
+        <v>11.42</v>
       </c>
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.25">
@@ -7079,19 +7082,19 @@
         <v>0.87</v>
       </c>
       <c r="F81" s="2">
-        <v>0.08541672472491912</v>
+        <v>0.0480738888119855</v>
       </c>
       <c r="G81" s="2">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="H81" s="2">
-        <v>47.78</v>
+        <v>40.52</v>
       </c>
       <c r="I81" s="2">
-        <v>9.64</v>
+        <v>7.43</v>
       </c>
       <c r="J81" s="2">
-        <v>0.005503316692849597</v>
+        <v>0.004699661602189917</v>
       </c>
       <c r="K81" s="2" t="b">
         <v>1</v>
@@ -7100,28 +7103,28 @@
         <v>158</v>
       </c>
       <c r="M81" s="2">
-        <v>0.07387005279573144</v>
+        <v>0.03559995787299819</v>
       </c>
       <c r="N81" s="2">
-        <v>13.273118583401333</v>
+        <v>10.058444021642135</v>
       </c>
       <c r="O81" s="2">
-        <v>67.05882352941175</v>
+        <v>61.1764705882353</v>
       </c>
       <c r="P81" s="2">
         <v>6.707278396222185</v>
       </c>
       <c r="Q81" s="2">
-        <v>56.470588235294116</v>
+        <v>52.8235294117647</v>
       </c>
       <c r="R81" s="2">
-        <v>54.11764705882352</v>
+        <v>51.76470588235294</v>
       </c>
       <c r="S81" s="2" t="s">
         <v>111</v>
       </c>
       <c r="T81" s="2">
-        <v>3.69</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.25">
@@ -7141,19 +7144,19 @@
         <v>-1.14</v>
       </c>
       <c r="F82" s="1">
-        <v>0.002682604422117138</v>
+        <v>-0.053291150385017916</v>
       </c>
       <c r="G82" s="1">
         <v>1.01</v>
       </c>
       <c r="H82" s="1">
-        <v>47.21</v>
+        <v>33.11</v>
       </c>
       <c r="I82" s="1">
-        <v>9.49</v>
+        <v>4.99</v>
       </c>
       <c r="J82" s="1">
-        <v>0.004143141617712615</v>
+        <v>0.002755423044509321</v>
       </c>
       <c r="K82" s="1" t="b">
         <v>1</v>
@@ -7162,28 +7165,28 @@
         <v>111</v>
       </c>
       <c r="M82" s="1">
-        <v>0.0031637157524999626</v>
+        <v>-0.05274880556158368</v>
       </c>
       <c r="N82" s="1">
-        <v>6.202484879078198</v>
+        <v>1.2235676781839364</v>
       </c>
       <c r="O82" s="1">
-        <v>57.647058823529406</v>
+        <v>49.411764705882355</v>
       </c>
       <c r="P82" s="1">
-        <v>6.0971680093981355</v>
+        <v>7.571607002312677</v>
       </c>
       <c r="Q82" s="1">
-        <v>54</v>
+        <v>48.23529411764706</v>
       </c>
       <c r="R82" s="1">
-        <v>49.88235294117647</v>
+        <v>46.35294117647059</v>
       </c>
       <c r="S82" s="1" t="s">
         <v>101</v>
       </c>
       <c r="T82" s="1">
-        <v>4.58</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.25">
@@ -7197,25 +7200,25 @@
         <v>75.29411764705883</v>
       </c>
       <c r="D83" s="2">
-        <v>0.0045871559633026545</v>
+        <v>0.010321100917431176</v>
       </c>
       <c r="E83" s="2">
         <v>0.23</v>
       </c>
       <c r="F83" s="2">
-        <v>0.07859834923787892</v>
+        <v>0.08114405426294356</v>
       </c>
       <c r="G83" s="2">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="H83" s="2">
-        <v>66.87</v>
+        <v>60.86</v>
       </c>
       <c r="I83" s="2">
-        <v>18.42</v>
+        <v>16.75</v>
       </c>
       <c r="J83" s="2">
-        <v>0.006758079773930283</v>
+        <v>0.007002184284276297</v>
       </c>
       <c r="K83" s="2" t="b">
         <v>0</v>
@@ -7224,28 +7227,28 @@
         <v>90</v>
       </c>
       <c r="M83" s="2">
-        <v>0.08244723988094149</v>
+        <v>0.08494046802698318</v>
       </c>
       <c r="N83" s="2">
-        <v>14.13083729192234</v>
+        <v>14.992495037040623</v>
       </c>
       <c r="O83" s="2">
-        <v>68.23529411764706</v>
+        <v>67.05882352941175</v>
       </c>
       <c r="P83" s="2">
         <v>12.706223591210087</v>
       </c>
       <c r="Q83" s="2">
-        <v>60.70588235294118</v>
+        <v>58.47058823529412</v>
       </c>
       <c r="R83" s="2">
-        <v>51.58823529411765</v>
+        <v>51.05882352941176</v>
       </c>
       <c r="S83" s="2" t="s">
         <v>109</v>
       </c>
       <c r="T83" s="2">
-        <v>-0.55</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.25">
@@ -7265,49 +7268,49 @@
         <v>2.31</v>
       </c>
       <c r="F84" s="1">
-        <v>-0.062491054051565256</v>
+        <v>-0.10498741089377293</v>
       </c>
       <c r="G84" s="1">
         <v>1.2</v>
       </c>
       <c r="H84" s="1">
-        <v>60.38</v>
+        <v>44.8</v>
       </c>
       <c r="I84" s="1">
-        <v>5.05</v>
+        <v>-0.55</v>
       </c>
       <c r="J84" s="1">
-        <v>-0.004565627632875225</v>
+        <v>-0.0032923025525219162</v>
       </c>
       <c r="K84" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="1">
         <v>175</v>
       </c>
       <c r="M84" s="1">
-        <v>-0.05286882744390886</v>
+        <v>-0.0941405144250883</v>
       </c>
       <c r="N84" s="1">
-        <v>0.5992305594373104</v>
+        <v>-2.915603208166512</v>
       </c>
       <c r="O84" s="1">
-        <v>45.88235294117647</v>
+        <v>38.82352941176471</v>
       </c>
       <c r="P84" s="1">
         <v>20.22353911360907</v>
       </c>
       <c r="Q84" s="1">
-        <v>50.58823529411764</v>
+        <v>45.52941176470588</v>
       </c>
       <c r="R84" s="1">
-        <v>38.705882352941174</v>
+        <v>36.23529411764706</v>
       </c>
       <c r="S84" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T84" s="1">
-        <v>-8.06</v>
+        <v>-10.53</v>
       </c>
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.25">
@@ -7321,25 +7324,25 @@
         <v>51.76470588235295</v>
       </c>
       <c r="D85" s="1">
-        <v>1.7867867867867866</v>
+        <v>1.6186186186186187</v>
       </c>
       <c r="E85" s="1">
         <v>0.23</v>
       </c>
       <c r="F85" s="1">
-        <v>-0.14075910782647483</v>
+        <v>-0.17498308576310917</v>
       </c>
       <c r="G85" s="1">
         <v>0.98</v>
       </c>
       <c r="H85" s="1">
-        <v>50.17</v>
+        <v>39.58</v>
       </c>
       <c r="I85" s="1">
-        <v>15.1</v>
+        <v>9.22</v>
       </c>
       <c r="J85" s="1">
-        <v>-0.005311625140946857</v>
+        <v>-0.008051726536975383</v>
       </c>
       <c r="K85" s="1" t="b">
         <v>1</v>
@@ -7348,28 +7351,28 @@
         <v>378</v>
       </c>
       <c r="M85" s="1">
-        <v>-0.14172133048724045</v>
+        <v>-0.17606777540997764</v>
       </c>
       <c r="N85" s="1">
-        <v>-8.286019744895846</v>
+        <v>-11.108329306655454</v>
       </c>
       <c r="O85" s="1">
-        <v>29.411764705882355</v>
+        <v>20</v>
       </c>
       <c r="P85" s="1">
-        <v>17.353844275841347</v>
+        <v>18.130768996018627</v>
       </c>
       <c r="Q85" s="1">
-        <v>50.235294117647065</v>
+        <v>44</v>
       </c>
       <c r="R85" s="1">
-        <v>35.47058823529412</v>
+        <v>31.235294117647054</v>
       </c>
       <c r="S85" s="1" t="s">
         <v>132</v>
       </c>
       <c r="T85" s="1">
-        <v>-21.18</v>
+        <v>-25.41</v>
       </c>
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.25">
@@ -7383,25 +7386,25 @@
         <v>81.17647058823529</v>
       </c>
       <c r="D86" s="1">
-        <v>-0.3206477732793522</v>
+        <v>-0.3141700404858299</v>
       </c>
       <c r="E86" s="1">
         <v>0.62</v>
       </c>
       <c r="F86" s="1">
-        <v>-0.01857690019218944</v>
+        <v>0.003154001706210746</v>
       </c>
       <c r="G86" s="1">
-        <v>0.94</v>
+        <v>0.95</v>
       </c>
       <c r="H86" s="1">
-        <v>26.16</v>
+        <v>34.69</v>
       </c>
       <c r="I86" s="1">
-        <v>2.79</v>
+        <v>4.49</v>
       </c>
       <c r="J86" s="1">
-        <v>-0.001510736645017923</v>
+        <v>-0.0025285139555875553</v>
       </c>
       <c r="K86" s="1" t="b">
         <v>1</v>
@@ -7410,28 +7413,28 @@
         <v>131</v>
       </c>
       <c r="M86" s="1">
-        <v>-0.021463568174486358</v>
+        <v>0.0004422775890395858</v>
       </c>
       <c r="N86" s="1">
-        <v>3.7397564863795743</v>
+        <v>6.54267599324627</v>
       </c>
       <c r="O86" s="1">
-        <v>55.294117647058826</v>
+        <v>60</v>
       </c>
       <c r="P86" s="1">
         <v>13.196185332148602</v>
       </c>
       <c r="Q86" s="1">
-        <v>44.705882352941174</v>
+        <v>45.41176470588236</v>
       </c>
       <c r="R86" s="1">
-        <v>45.64705882352941</v>
+        <v>46.588235294117645</v>
       </c>
       <c r="S86" s="1" t="s">
         <v>107</v>
       </c>
       <c r="T86" s="1">
-        <v>-1.12</v>
+        <v>-0.18</v>
       </c>
     </row>
   </sheetData>
@@ -7458,7 +7461,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>45.764705882352935</v>
+        <v>45.647058823529406</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -7466,7 +7469,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>53.17647058823529</v>
+        <v>56.94117647058823</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7474,7 +7477,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>54</v>
+        <v>53.294117647058826</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -7482,7 +7485,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>35.705882352941174</v>
+        <v>40.76470588235294</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -7490,7 +7493,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>36.41176470588235</v>
+        <v>35.588235294117645</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7498,7 +7501,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>55.76470588235293</v>
+        <v>57.05882352941175</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -7506,7 +7509,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>38.705882352941174</v>
+        <v>35.76470588235294</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -7514,7 +7517,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>61</v>
+        <v>61.705882352941174</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -7522,7 +7525,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>45.88235294117647</v>
+        <v>43.41176470588235</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -7530,7 +7533,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>59.235294117647065</v>
+        <v>58.05882352941177</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -7538,7 +7541,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>62.8235294117647</v>
+        <v>62.588235294117645</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -7546,7 +7549,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>36.76470588235295</v>
+        <v>37.00000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -7554,7 +7557,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>60.88235294117647</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -7562,7 +7565,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>26.117647058823536</v>
+        <v>30.88235294117647</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -7570,7 +7573,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>13.411764705882351</v>
+        <v>13.058823529411764</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -7578,7 +7581,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>33.529411764705884</v>
+        <v>33.294117647058826</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -7594,7 +7597,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>54.17647058823529</v>
+        <v>55.88235294117647</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -7602,7 +7605,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>57.352941176470594</v>
+        <v>57.58823529411765</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -7610,7 +7613,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>19.94117647058824</v>
+        <v>20.058823529411768</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -7618,7 +7621,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>35.05882352941176</v>
+        <v>33.99999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -7626,7 +7629,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>57.05882352941176</v>
+        <v>56.411764705882355</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -7634,7 +7637,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>41.52941176470589</v>
+        <v>42.47058823529412</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -7642,7 +7645,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>3.8235294117647083</v>
+        <v>5.705882352941179</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -7650,7 +7653,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>-0.529411764705884</v>
+        <v>2.5294117647058822</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -7658,7 +7661,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>-0.17647058823529704</v>
+        <v>-0.05882352941176627</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -7666,7 +7669,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>33.41176470588235</v>
+        <v>41.05882352941176</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -7674,7 +7677,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>43.35294117647059</v>
+        <v>41.23529411764706</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -7682,7 +7685,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>43.35294117647059</v>
+        <v>43.11764705882353</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -7690,7 +7693,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>39.588235294117645</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -7698,7 +7701,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>32.588235294117645</v>
+        <v>32.470588235294116</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -7706,7 +7709,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>60.47058823529413</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -7714,7 +7717,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>40.17647058823529</v>
+        <v>37.35294117647059</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -7722,7 +7725,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>41.23529411764706</v>
+        <v>43.94117647058824</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -7730,7 +7733,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>38.00000000000001</v>
+        <v>38.411764705882355</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -7738,7 +7741,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>53.29411764705882</v>
+        <v>51.88235294117647</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -7746,7 +7749,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>65.76470588235294</v>
+        <v>66.58823529411764</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -7754,7 +7757,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>40.352941176470594</v>
+        <v>36.82352941176471</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -7762,7 +7765,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>47.47058823529412</v>
+        <v>47.235294117647065</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -7770,7 +7773,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>18.411764705882355</v>
+        <v>19.588235294117645</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -7778,7 +7781,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>31.41176470588236</v>
+        <v>26.58823529411765</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -7786,7 +7789,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>56.76470588235294</v>
+        <v>56.17647058823529</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -7794,7 +7797,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>56.470588235294116</v>
+        <v>56.17647058823529</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -7802,7 +7805,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>44.11764705882353</v>
+        <v>42.117647058823536</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -7810,7 +7813,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>26.05882352941176</v>
+        <v>24.29411764705882</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -7818,7 +7821,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>42.411764705882355</v>
+        <v>45.352941176470594</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -7826,7 +7829,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>54.11764705882353</v>
+        <v>56.588235294117645</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -7834,7 +7837,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>57.41176470588236</v>
+        <v>54.47058823529412</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -7842,7 +7845,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>25.764705882352942</v>
+        <v>27.411764705882355</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -7850,7 +7853,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>40.23529411764706</v>
+        <v>42.76470588235294</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -7858,7 +7861,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>28.35294117647059</v>
+        <v>24.117647058823533</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -7866,7 +7869,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>22.176470588235297</v>
+        <v>22.058823529411768</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -7874,7 +7877,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>45.29411764705882</v>
+        <v>47.529411764705884</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -7882,7 +7885,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>30.529411764705884</v>
+        <v>29.235294117647058</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -7890,7 +7893,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>32.352941176470594</v>
+        <v>35.05882352941177</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -7906,7 +7909,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>47.1764705882353</v>
+        <v>46.35294117647059</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -7914,7 +7917,7 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>25.176470588235297</v>
+        <v>26.70588235294118</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -7922,7 +7925,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>10.999999999999996</v>
+        <v>10.64705882352941</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -7930,7 +7933,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>44.29411764705883</v>
+        <v>39.70588235294118</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -7938,7 +7941,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>53.76470588235295</v>
+        <v>50.94117647058823</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -7946,7 +7949,7 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>40.823529411764696</v>
+        <v>49.882352941176464</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -7954,7 +7957,7 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>30.17647058823529</v>
+        <v>32.882352941176464</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -7962,7 +7965,7 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>31.41176470588235</v>
+        <v>30.58823529411765</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -7970,7 +7973,7 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>59.941176470588246</v>
+        <v>61.58823529411765</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -7978,7 +7981,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>26.470588235294116</v>
+        <v>34.05882352941176</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -7986,7 +7989,7 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>36.294117647058826</v>
+        <v>38.05882352941177</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -7994,7 +7997,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>49.82352941176471</v>
+        <v>44.882352941176464</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -8002,7 +8005,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>43.647058823529406</v>
+        <v>40.58823529411765</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -8010,7 +8013,7 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>57.52941176470589</v>
+        <v>57.41176470588236</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -8018,7 +8021,7 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>38.411764705882355</v>
+        <v>39</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -8026,7 +8029,7 @@
         <v>72</v>
       </c>
       <c r="B73">
-        <v>61.82352941176471</v>
+        <v>61.94117647058824</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -8034,7 +8037,7 @@
         <v>73</v>
       </c>
       <c r="B74">
-        <v>31.882352941176475</v>
+        <v>31.29411764705883</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -8042,7 +8045,7 @@
         <v>74</v>
       </c>
       <c r="B75">
-        <v>31.352941176470587</v>
+        <v>29.705882352941174</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -8050,7 +8053,7 @@
         <v>75</v>
       </c>
       <c r="B76">
-        <v>24.352941176470587</v>
+        <v>25.411764705882348</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -8058,7 +8061,7 @@
         <v>122</v>
       </c>
       <c r="B77">
-        <v>26.058823529411768</v>
+        <v>25.11764705882353</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -8066,7 +8069,7 @@
         <v>124</v>
       </c>
       <c r="B78">
-        <v>60.529411764705884</v>
+        <v>60.64705882352942</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -8074,7 +8077,7 @@
         <v>125</v>
       </c>
       <c r="B79">
-        <v>53.94117647058824</v>
+        <v>51.94117647058824</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -8082,7 +8085,7 @@
         <v>126</v>
       </c>
       <c r="B80">
-        <v>53.529411764705884</v>
+        <v>51.29411764705883</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -8090,7 +8093,7 @@
         <v>127</v>
       </c>
       <c r="B81">
-        <v>54.11764705882352</v>
+        <v>51.76470588235294</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -8098,7 +8101,7 @@
         <v>128</v>
       </c>
       <c r="B82">
-        <v>49.88235294117647</v>
+        <v>46.35294117647059</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -8106,7 +8109,7 @@
         <v>129</v>
       </c>
       <c r="B83">
-        <v>51.58823529411765</v>
+        <v>51.05882352941176</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -8114,7 +8117,7 @@
         <v>130</v>
       </c>
       <c r="B84">
-        <v>38.705882352941174</v>
+        <v>36.23529411764706</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -8122,7 +8125,7 @@
         <v>131</v>
       </c>
       <c r="B85">
-        <v>35.47058823529412</v>
+        <v>31.235294117647054</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
@@ -8130,7 +8133,7 @@
         <v>133</v>
       </c>
       <c r="B86">
-        <v>45.64705882352941</v>
+        <v>46.588235294117645</v>
       </c>
     </row>
   </sheetData>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="233">
   <si>
     <t>Ticker</t>
   </si>
@@ -322,7 +322,7 @@
     <t>2027-07-16</t>
   </si>
   <si>
-    <t>2026-08-26</t>
+    <t>2027-08-26</t>
   </si>
   <si>
     <t>2026-10-13</t>
@@ -427,7 +427,7 @@
     <t>_date_</t>
   </si>
   <si>
-    <t>2026-09-24</t>
+    <t>2026-09-25</t>
   </si>
   <si>
     <t>Criteria</t>
@@ -688,40 +688,37 @@
     <t>Momentum Breakout, Market Leader, Institutional Buying</t>
   </si>
   <si>
-    <t>Momentum Breakout, Market Leader, Stable Uptrend, Volume Spike, Institutional Buying</t>
-  </si>
-  <si>
     <t>Momentum Breakout, Market Leader</t>
   </si>
   <si>
-    <t>Stable Uptrend, Institutional Buying</t>
+    <t>Momentum Breakout, Stable Uptrend, Volume Spike, Institutional Buying</t>
   </si>
   <si>
     <t>Momentum Breakout, Market Leader, Volume Spike, Institutional Buying</t>
   </si>
   <si>
+    <t>Institutional Buying</t>
+  </si>
+  <si>
+    <t>Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
     <t>Momentum Breakout, Volume Spike</t>
   </si>
   <si>
-    <t>Institutional Buying</t>
-  </si>
-  <si>
-    <t>Volume Spike, Institutional Buying</t>
+    <t>Momentum Breakout</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Volume Spike</t>
   </si>
   <si>
     <t>Momentum Breakout, Volume Spike, Institutional Buying</t>
   </si>
   <si>
-    <t>Momentum Breakout, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Volume Spike</t>
-  </si>
-  <si>
     <t>Earnings Upcoming, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Market Leader, Volume Spike</t>
   </si>
 </sst>
 </file>
@@ -1416,7 +1413,7 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>66.58823529411764</v>
+        <v>66.23529411764706</v>
       </c>
       <c r="C2" t="s">
         <v>221</v>
@@ -1424,76 +1421,76 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B3">
-        <v>62.588235294117645</v>
+        <v>62.764705882352935</v>
       </c>
       <c r="C3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="B4">
-        <v>61.94117647058824</v>
+        <v>61.1764705882353</v>
       </c>
       <c r="C4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B5">
-        <v>61.705882352941174</v>
+        <v>60.88235294117648</v>
       </c>
       <c r="C5" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B6">
-        <v>61.58823529411765</v>
+        <v>60.529411764705884</v>
       </c>
       <c r="C6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>124</v>
       </c>
       <c r="B7">
-        <v>61</v>
+        <v>60.176470588235304</v>
       </c>
       <c r="C7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>124</v>
+        <v>32</v>
       </c>
       <c r="B8">
-        <v>60.64705882352942</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="B9">
-        <v>60</v>
+        <v>59.52941176470588</v>
       </c>
       <c r="C9" t="s">
         <v>225</v>
@@ -1504,7 +1501,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>58.05882352941177</v>
+        <v>57.588235294117645</v>
       </c>
       <c r="C10" t="s">
         <v>221</v>
@@ -1512,21 +1509,21 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B11">
-        <v>57.58823529411765</v>
+        <v>57.41176470588236</v>
       </c>
       <c r="C11" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="B12">
-        <v>57.41176470588236</v>
+        <v>57.1764705882353</v>
       </c>
       <c r="C12" t="s">
         <v>226</v>
@@ -1534,10 +1531,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="B13">
-        <v>57.05882352941175</v>
+        <v>57.117647058823536</v>
       </c>
       <c r="C13" t="s">
         <v>227</v>
@@ -1545,10 +1542,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="B14">
-        <v>56.94117647058823</v>
+        <v>56.94117647058824</v>
       </c>
       <c r="C14" t="s">
         <v>228</v>
@@ -1556,21 +1553,21 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="B15">
-        <v>56.588235294117645</v>
+        <v>56.94117647058822</v>
       </c>
       <c r="C15" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B16">
-        <v>56.411764705882355</v>
+        <v>56.88235294117648</v>
       </c>
       <c r="C16" t="s">
         <v>229</v>
@@ -1578,10 +1575,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="B17">
-        <v>56.17647058823529</v>
+        <v>56.70588235294119</v>
       </c>
       <c r="C17" t="s">
         <v>230</v>
@@ -1589,21 +1586,21 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B18">
-        <v>56.17647058823529</v>
+        <v>55.82352941176471</v>
       </c>
       <c r="C18" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="B19">
-        <v>55.88235294117647</v>
+        <v>55.764705882352935</v>
       </c>
       <c r="C19" t="s">
         <v>231</v>
@@ -1611,35 +1608,35 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B20">
-        <v>53.294117647058826</v>
+        <v>55.17647058823529</v>
       </c>
       <c r="C20" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B21">
-        <v>51.94117647058824</v>
+        <v>53.88235294117647</v>
       </c>
       <c r="C21" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="B22">
-        <v>51.88235294117647</v>
+        <v>52.94117647058824</v>
       </c>
       <c r="C22" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1647,29 +1644,29 @@
         <v>127</v>
       </c>
       <c r="B23">
-        <v>51.76470588235294</v>
+        <v>51.88235294117647</v>
       </c>
       <c r="C23" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>126</v>
+        <v>61</v>
       </c>
       <c r="B24">
-        <v>51.29411764705883</v>
+        <v>51.05882352941177</v>
       </c>
       <c r="C24" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>129</v>
+        <v>36</v>
       </c>
       <c r="B25">
-        <v>51.05882352941176</v>
+        <v>50.588235294117645</v>
       </c>
       <c r="C25" t="s">
         <v>227</v>
@@ -1677,35 +1674,35 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>126</v>
       </c>
       <c r="B26">
-        <v>50.94117647058823</v>
+        <v>49.88235294117647</v>
       </c>
       <c r="C26" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>62</v>
+        <v>125</v>
       </c>
       <c r="B27">
-        <v>49.882352941176464</v>
+        <v>49.23529411764706</v>
       </c>
       <c r="C27" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B28">
-        <v>47.529411764705884</v>
+        <v>48.94117647058823</v>
       </c>
       <c r="C28" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -1713,164 +1710,164 @@
         <v>39</v>
       </c>
       <c r="B29">
-        <v>47.235294117647065</v>
+        <v>47.352941176470594</v>
       </c>
       <c r="C29" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>133</v>
+        <v>46</v>
       </c>
       <c r="B30">
-        <v>46.588235294117645</v>
+        <v>47.00000000000001</v>
       </c>
       <c r="C30" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="B31">
-        <v>46.35294117647059</v>
+        <v>46.23529411764706</v>
       </c>
       <c r="C31" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>128</v>
+        <v>1</v>
       </c>
       <c r="B32">
-        <v>46.35294117647059</v>
+        <v>46.05882352941177</v>
       </c>
       <c r="C32" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>1</v>
+        <v>128</v>
       </c>
       <c r="B33">
-        <v>45.647058823529406</v>
+        <v>45.99999999999999</v>
       </c>
       <c r="C33" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="B34">
-        <v>45.352941176470594</v>
+        <v>45.64705882352941</v>
       </c>
       <c r="C34" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="B35">
-        <v>43.94117647058824</v>
+        <v>45.117647058823536</v>
       </c>
       <c r="C35" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="B36">
-        <v>43.41176470588235</v>
+        <v>45.117647058823536</v>
       </c>
       <c r="C36" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B37">
-        <v>43.11764705882353</v>
+        <v>43.64705882352941</v>
       </c>
       <c r="C37" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="B38">
-        <v>42.76470588235294</v>
+        <v>43.64705882352941</v>
       </c>
       <c r="C38" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B39">
-        <v>42.47058823529412</v>
+        <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B40">
-        <v>42.117647058823536</v>
+        <v>42.76470588235294</v>
       </c>
       <c r="C40" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="B41">
-        <v>41.23529411764706</v>
+        <v>42.470588235294116</v>
       </c>
       <c r="C41" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="B42">
-        <v>41.05882352941176</v>
+        <v>42.23529411764706</v>
       </c>
       <c r="C42" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="B43">
-        <v>40.76470588235294</v>
+        <v>41.117647058823536</v>
       </c>
       <c r="C43" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -1878,21 +1875,21 @@
         <v>69</v>
       </c>
       <c r="B44">
-        <v>40.58823529411765</v>
+        <v>40.94117647058824</v>
       </c>
       <c r="C44" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="B45">
-        <v>39.70588235294118</v>
+        <v>40.29411764705881</v>
       </c>
       <c r="C45" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -1900,21 +1897,21 @@
         <v>30</v>
       </c>
       <c r="B46">
-        <v>39</v>
+        <v>39.588235294117645</v>
       </c>
       <c r="C46" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="B47">
-        <v>39</v>
+        <v>39.00000000000001</v>
       </c>
       <c r="C47" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -1922,40 +1919,40 @@
         <v>35</v>
       </c>
       <c r="B48">
-        <v>38.411764705882355</v>
+        <v>38.529411764705884</v>
       </c>
       <c r="C48" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="B49">
-        <v>38.05882352941177</v>
+        <v>38.1764705882353</v>
       </c>
       <c r="C49" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="B50">
-        <v>37.35294117647059</v>
+        <v>37.647058823529406</v>
       </c>
       <c r="C50" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B51">
-        <v>37.00000000000001</v>
+        <v>37.294117647058826</v>
       </c>
       <c r="C51" t="s">
         <v>225</v>
@@ -2186,55 +2183,55 @@
         <v>67.05882352941175</v>
       </c>
       <c r="D2" s="1">
-        <v>-2.047619047619048</v>
+        <v>-1.9626769626769627</v>
       </c>
       <c r="E2" s="1">
         <v>-2.08</v>
       </c>
       <c r="F2" s="1">
-        <v>0.13172893774885863</v>
+        <v>0.16143519292480366</v>
       </c>
       <c r="G2" s="1">
         <v>0.21</v>
       </c>
       <c r="H2" s="1">
-        <v>50.62</v>
+        <v>49.23</v>
       </c>
       <c r="I2" s="1">
-        <v>9.36</v>
+        <v>8.71</v>
       </c>
       <c r="J2" s="1">
-        <v>0.013554747128503516</v>
+        <v>0.012933248288435392</v>
       </c>
       <c r="K2" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L2" s="1">
-        <v>-457</v>
+        <v>-461</v>
       </c>
       <c r="M2" s="1">
-        <v>0.08888369669755436</v>
+        <v>0.11560387953750073</v>
       </c>
       <c r="N2" s="1">
-        <v>15.38681790409775</v>
+        <v>18.436820028092225</v>
       </c>
       <c r="O2" s="1">
-        <v>69.41176470588235</v>
+        <v>71.76470588235294</v>
       </c>
       <c r="P2" s="1">
         <v>16.29652721982991</v>
       </c>
       <c r="Q2" s="1">
-        <v>50.11764705882352</v>
+        <v>48.58823529411765</v>
       </c>
       <c r="R2" s="1">
-        <v>45.647058823529406</v>
+        <v>46.05882352941177</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>95</v>
       </c>
       <c r="T2" s="1">
-        <v>25.83</v>
+        <v>26.24</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -2248,55 +2245,55 @@
         <v>54.11764705882353</v>
       </c>
       <c r="D3" s="2">
-        <v>26.676923076923075</v>
+        <v>26.810256410256407</v>
       </c>
       <c r="E3" s="2">
         <v>3.59</v>
       </c>
       <c r="F3" s="2">
-        <v>0.037824397126275</v>
+        <v>0.027508228439093035</v>
       </c>
       <c r="G3" s="2">
         <v>2.47</v>
       </c>
       <c r="H3" s="2">
-        <v>69.23</v>
+        <v>74.4</v>
       </c>
       <c r="I3" s="2">
-        <v>67.95</v>
+        <v>76.14</v>
       </c>
       <c r="J3" s="2">
-        <v>0.010272886926532632</v>
+        <v>0.01318482279984989</v>
       </c>
       <c r="K3" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L3" s="2">
-        <v>861</v>
+        <v>850</v>
       </c>
       <c r="M3" s="2">
-        <v>0.11754908617110704</v>
+        <v>0.11278927993192256</v>
       </c>
       <c r="N3" s="2">
-        <v>18.253356851453013</v>
+        <v>18.155360067534403</v>
       </c>
       <c r="O3" s="2">
-        <v>72.94117647058823</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="P3" s="2">
         <v>26.053946839070953</v>
       </c>
       <c r="Q3" s="2">
-        <v>73.29411764705883</v>
+        <v>75.41176470588235</v>
       </c>
       <c r="R3" s="2">
-        <v>56.94117647058823</v>
+        <v>57.1764705882353</v>
       </c>
       <c r="S3" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T3" s="2">
-        <v>-10.13</v>
+        <v>-9.9</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -2316,49 +2313,49 @@
         <v>6.34</v>
       </c>
       <c r="F4" s="2">
-        <v>0.3691387491148527</v>
+        <v>0.3891338292496143</v>
       </c>
       <c r="G4" s="2">
         <v>1.35</v>
       </c>
       <c r="H4" s="2">
-        <v>53.7</v>
+        <v>54.03</v>
       </c>
       <c r="I4" s="2">
-        <v>48.61</v>
+        <v>48.51</v>
       </c>
       <c r="J4" s="2">
-        <v>0.023150448238343307</v>
+        <v>0.02238301397696013</v>
       </c>
       <c r="K4" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L4" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="M4" s="2">
-        <v>0.3881208179350508</v>
+        <v>0.4094388415098118</v>
       </c>
       <c r="N4" s="2">
-        <v>45.310530027847406</v>
+        <v>47.820316225323324</v>
       </c>
       <c r="O4" s="2">
-        <v>89.41176470588236</v>
+        <v>88.23529411764706</v>
       </c>
       <c r="P4" s="2">
         <v>19.349659482175007</v>
       </c>
       <c r="Q4" s="2">
-        <v>58.117647058823536</v>
+        <v>57.76470588235295</v>
       </c>
       <c r="R4" s="2">
-        <v>53.294117647058826</v>
+        <v>52.94117647058824</v>
       </c>
       <c r="S4" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T4" s="2">
-        <v>4.94</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -2372,25 +2369,25 @@
         <v>40</v>
       </c>
       <c r="D5" s="1">
-        <v>30.98148148148148</v>
+        <v>31.47222222222222</v>
       </c>
       <c r="E5" s="1">
         <v>1.69</v>
       </c>
       <c r="F5" s="1">
-        <v>-0.10211514577301976</v>
+        <v>-0.11403973862727687</v>
       </c>
       <c r="G5" s="1">
         <v>1.91</v>
       </c>
       <c r="H5" s="1">
-        <v>60.31</v>
+        <v>60.78</v>
       </c>
       <c r="I5" s="1">
-        <v>-4.11</v>
+        <v>-3.59</v>
       </c>
       <c r="J5" s="1">
-        <v>-0.007650825092846842</v>
+        <v>-0.007016981550023065</v>
       </c>
       <c r="K5" s="1" t="b">
         <v>0</v>
@@ -2399,28 +2396,28 @@
         <v>143</v>
       </c>
       <c r="M5" s="1">
-        <v>-0.05276176684050471</v>
+        <v>-0.06124670675076338</v>
       </c>
       <c r="N5" s="1">
-        <v>1.222271550291836</v>
+        <v>0.7517613992657948</v>
       </c>
       <c r="O5" s="1">
-        <v>48.23529411764706</v>
+        <v>47.05882352941176</v>
       </c>
       <c r="P5" s="1">
         <v>33.002444654975626</v>
       </c>
       <c r="Q5" s="1">
-        <v>54</v>
+        <v>53.411764705882355</v>
       </c>
       <c r="R5" s="1">
-        <v>40.76470588235294</v>
+        <v>40.29411764705881</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T5" s="1">
-        <v>-5.21</v>
+        <v>-5.68</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -2440,19 +2437,19 @@
         <v>-1.88</v>
       </c>
       <c r="F6" s="1">
-        <v>-0.10420662709478996</v>
+        <v>-0.09200733241124384</v>
       </c>
       <c r="G6" s="1">
         <v>1.6</v>
       </c>
       <c r="H6" s="1">
-        <v>37.18</v>
+        <v>37.91</v>
       </c>
       <c r="I6" s="1">
-        <v>-15.85</v>
+        <v>-15.52</v>
       </c>
       <c r="J6" s="1">
-        <v>-0.0020607832537343487</v>
+        <v>-0.002504261176736078</v>
       </c>
       <c r="K6" s="1" t="b">
         <v>1</v>
@@ -2461,28 +2458,28 @@
         <v>-204</v>
       </c>
       <c r="M6" s="1">
-        <v>-0.07166593768873608</v>
+        <v>-0.05719873996519098</v>
       </c>
       <c r="N6" s="1">
-        <v>-0.6681455345312957</v>
+        <v>1.1565580778230509</v>
       </c>
       <c r="O6" s="1">
-        <v>45.88235294117647</v>
+        <v>50.588235294117645</v>
       </c>
       <c r="P6" s="1">
         <v>27.785495103772316</v>
       </c>
       <c r="Q6" s="1">
-        <v>40.117647058823536</v>
+        <v>38.82352941176471</v>
       </c>
       <c r="R6" s="1">
-        <v>35.588235294117645</v>
+        <v>36.352941176470594</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T6" s="1">
-        <v>16.5</v>
+        <v>17.27</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -2502,19 +2499,19 @@
         <v>0.5</v>
       </c>
       <c r="F7" s="2">
-        <v>0.0020655019957711296</v>
+        <v>0.007796491021726998</v>
       </c>
       <c r="G7" s="2">
         <v>2.22</v>
       </c>
       <c r="H7" s="2">
-        <v>54.23</v>
+        <v>55.75</v>
       </c>
       <c r="I7" s="2">
-        <v>12.47</v>
+        <v>13.15</v>
       </c>
       <c r="J7" s="2">
-        <v>0.00844467352025804</v>
+        <v>0.008139036288984727</v>
       </c>
       <c r="K7" s="2" t="b">
         <v>0</v>
@@ -2523,10 +2520,10 @@
         <v>177</v>
       </c>
       <c r="M7" s="2">
-        <v>0.06823157045474737</v>
+        <v>0.07857396232870117</v>
       </c>
       <c r="N7" s="2">
-        <v>13.321605279817053</v>
+        <v>14.733828307212251</v>
       </c>
       <c r="O7" s="2">
         <v>65.88235294117646</v>
@@ -2535,16 +2532,16 @@
         <v>19.398494070050486</v>
       </c>
       <c r="Q7" s="2">
-        <v>67.29411764705883</v>
+        <v>66.70588235294117</v>
       </c>
       <c r="R7" s="2">
-        <v>57.05882352941175</v>
+        <v>56.94117647058822</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T7" s="2">
-        <v>8.64</v>
+        <v>8.53</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -2564,19 +2561,19 @@
         <v>2.63</v>
       </c>
       <c r="F8" s="1">
-        <v>-0.13658805305680174</v>
+        <v>-0.12201349896928142</v>
       </c>
       <c r="G8" s="1">
         <v>0.61</v>
       </c>
       <c r="H8" s="1">
-        <v>33.1</v>
+        <v>38.36</v>
       </c>
       <c r="I8" s="1">
-        <v>4.37</v>
+        <v>5.58</v>
       </c>
       <c r="J8" s="1">
-        <v>-0.012906366634134737</v>
+        <v>-0.012804658339972528</v>
       </c>
       <c r="K8" s="1" t="b">
         <v>0</v>
@@ -2585,28 +2582,28 @@
         <v>364</v>
       </c>
       <c r="M8" s="1">
-        <v>-0.15773950117073676</v>
+        <v>-0.14463908405921577</v>
       </c>
       <c r="N8" s="1">
-        <v>-9.275501882731369</v>
+        <v>-7.587476331579437</v>
       </c>
       <c r="O8" s="1">
-        <v>25.882352941176475</v>
+        <v>31.76470588235294</v>
       </c>
       <c r="P8" s="1">
         <v>14.910048504309984</v>
       </c>
       <c r="Q8" s="1">
-        <v>42.823529411764696</v>
+        <v>44.23529411764706</v>
       </c>
       <c r="R8" s="1">
-        <v>35.76470588235294</v>
+        <v>37.294117647058826</v>
       </c>
       <c r="S8" s="1" t="s">
         <v>101</v>
       </c>
       <c r="T8" s="1">
-        <v>-23.99</v>
+        <v>-22.46</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -2626,19 +2623,19 @@
         <v>2.96</v>
       </c>
       <c r="F9" s="2">
-        <v>0.5922545047803275</v>
+        <v>0.6918032624873154</v>
       </c>
       <c r="G9" s="2">
         <v>1.6</v>
       </c>
       <c r="H9" s="2">
-        <v>65.07</v>
+        <v>66.14</v>
       </c>
       <c r="I9" s="2">
-        <v>25.21</v>
+        <v>26.06</v>
       </c>
       <c r="J9" s="2">
-        <v>0.033494708858078245</v>
+        <v>0.03519040442583034</v>
       </c>
       <c r="K9" s="2" t="b">
         <v>0</v>
@@ -2647,28 +2644,28 @@
         <v>-112</v>
       </c>
       <c r="M9" s="2">
-        <v>0.6247951941863814</v>
+        <v>0.7266118549333682</v>
       </c>
       <c r="N9" s="2">
-        <v>68.97796765298045</v>
+        <v>79.53761756767896</v>
       </c>
       <c r="O9" s="2">
-        <v>95.29411764705881</v>
+        <v>98.82352941176471</v>
       </c>
       <c r="P9" s="2">
         <v>33.227512780245505</v>
       </c>
       <c r="Q9" s="2">
-        <v>72.58823529411765</v>
+        <v>73.05882352941175</v>
       </c>
       <c r="R9" s="2">
-        <v>61.705882352941174</v>
+        <v>62.764705882352935</v>
       </c>
       <c r="S9" s="2" t="s">
         <v>102</v>
       </c>
       <c r="T9" s="2">
-        <v>34.33</v>
+        <v>35.39</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -2688,19 +2685,19 @@
         <v>0.08</v>
       </c>
       <c r="F10" s="1">
-        <v>-0.08843909450990346</v>
+        <v>-0.0492221601054378</v>
       </c>
       <c r="G10" s="1">
         <v>1.42</v>
       </c>
       <c r="H10" s="1">
-        <v>44.57</v>
+        <v>51.6</v>
       </c>
       <c r="I10" s="1">
-        <v>-0.79</v>
+        <v>1.63</v>
       </c>
       <c r="J10" s="1">
-        <v>0.007969366079722411</v>
+        <v>0.007989718611138669</v>
       </c>
       <c r="K10" s="1" t="b">
         <v>1</v>
@@ -2709,28 +2706,28 @@
         <v>-49</v>
       </c>
       <c r="M10" s="1">
-        <v>-0.06566061192566575</v>
+        <v>-0.0248561453932008</v>
       </c>
       <c r="N10" s="1">
-        <v>-0.067612958224256</v>
+        <v>4.390817535022066</v>
       </c>
       <c r="O10" s="1">
-        <v>47.05882352941176</v>
+        <v>56.470588235294116</v>
       </c>
       <c r="P10" s="1">
         <v>14.568379622257217</v>
       </c>
       <c r="Q10" s="1">
-        <v>49.88235294117647</v>
+        <v>51.88235294117647</v>
       </c>
       <c r="R10" s="1">
-        <v>43.41176470588235</v>
+        <v>46.23529411764706</v>
       </c>
       <c r="S10" s="1" t="s">
         <v>103</v>
       </c>
       <c r="T10" s="1">
-        <v>7.86</v>
+        <v>10.69</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -2750,19 +2747,19 @@
         <v>2.19</v>
       </c>
       <c r="F11" s="2">
-        <v>0.5436053945474817</v>
+        <v>0.5340386499796576</v>
       </c>
       <c r="G11" s="2">
         <v>0.71</v>
       </c>
       <c r="H11" s="2">
-        <v>63.53</v>
+        <v>63.83</v>
       </c>
       <c r="I11" s="2">
-        <v>45.88</v>
+        <v>45.78</v>
       </c>
       <c r="J11" s="2">
-        <v>0.025187103761932495</v>
+        <v>0.02412976788980005</v>
       </c>
       <c r="K11" s="2" t="b">
         <v>0</v>
@@ -2771,28 +2768,28 @@
         <v>40</v>
       </c>
       <c r="M11" s="2">
-        <v>0.527877394667889</v>
+        <v>0.5172144969640653</v>
       </c>
       <c r="N11" s="2">
-        <v>59.2861877011312</v>
+        <v>58.59788177074867</v>
       </c>
       <c r="O11" s="2">
-        <v>92.94117647058823</v>
+        <v>91.76470588235294</v>
       </c>
       <c r="P11" s="2">
         <v>21.2185970476566</v>
       </c>
       <c r="Q11" s="2">
-        <v>66.11764705882354</v>
+        <v>66</v>
       </c>
       <c r="R11" s="2">
-        <v>58.05882352941177</v>
+        <v>57.588235294117645</v>
       </c>
       <c r="S11" s="2" t="s">
         <v>104</v>
       </c>
       <c r="T11" s="2">
-        <v>6.41</v>
+        <v>5.94</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -2812,19 +2809,19 @@
         <v>1.33</v>
       </c>
       <c r="F12" s="2">
-        <v>0.7507429854997593</v>
+        <v>0.6516601148093444</v>
       </c>
       <c r="G12" s="2">
         <v>0.99</v>
       </c>
       <c r="H12" s="2">
-        <v>60.07</v>
+        <v>58.62</v>
       </c>
       <c r="I12" s="2">
-        <v>52.13</v>
+        <v>50.88</v>
       </c>
       <c r="J12" s="2">
-        <v>0.04224989986338375</v>
+        <v>0.041632056749910044</v>
       </c>
       <c r="K12" s="2" t="b">
         <v>0</v>
@@ -2833,28 +2830,28 @@
         <v>30</v>
       </c>
       <c r="M12" s="2">
-        <v>0.7502006406763251</v>
+        <v>0.6510799716019102</v>
       </c>
       <c r="N12" s="2">
-        <v>81.51851230197482</v>
+        <v>71.98442923453318</v>
       </c>
       <c r="O12" s="2">
-        <v>100</v>
+        <v>95.29411764705881</v>
       </c>
       <c r="P12" s="2">
         <v>23.557267760130397</v>
       </c>
       <c r="Q12" s="2">
-        <v>69.52941176470588</v>
+        <v>69.05882352941177</v>
       </c>
       <c r="R12" s="2">
-        <v>62.588235294117645</v>
+        <v>61.1764705882353</v>
       </c>
       <c r="S12" s="2" t="s">
         <v>105</v>
       </c>
       <c r="T12" s="2">
-        <v>9.84</v>
+        <v>8.43</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -2874,19 +2871,19 @@
         <v>-1.08</v>
       </c>
       <c r="F13" s="1">
-        <v>0.4230021877811984</v>
+        <v>0.4263643673759915</v>
       </c>
       <c r="G13" s="1">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="H13" s="1">
-        <v>54.15</v>
+        <v>48.57</v>
       </c>
       <c r="I13" s="1">
-        <v>17.49</v>
+        <v>12.06</v>
       </c>
       <c r="J13" s="1">
-        <v>0.0473234816342728</v>
+        <v>0.045699860353661935</v>
       </c>
       <c r="K13" s="1" t="b">
         <v>1</v>
@@ -2895,28 +2892,28 @@
         <v>5</v>
       </c>
       <c r="M13" s="1">
-        <v>0.4539158427169496</v>
+        <v>0.4600126734071759</v>
       </c>
       <c r="N13" s="1">
-        <v>51.89003250603727</v>
+        <v>52.87769941505973</v>
       </c>
       <c r="O13" s="1">
-        <v>90.58823529411765</v>
+        <v>89.41176470588236</v>
       </c>
       <c r="P13" s="1">
         <v>40.13761891809808</v>
       </c>
       <c r="Q13" s="1">
-        <v>42.94117647058824</v>
+        <v>39.529411764705884</v>
       </c>
       <c r="R13" s="1">
-        <v>37.00000000000001</v>
+        <v>36.52941176470589</v>
       </c>
       <c r="S13" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T13" s="1">
-        <v>36.21</v>
+        <v>35.74</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -2936,19 +2933,19 @@
         <v>-1.75</v>
       </c>
       <c r="F14" s="2">
-        <v>0.6865564862931275</v>
+        <v>0.6883602427348451</v>
       </c>
       <c r="G14" s="2">
         <v>0.75</v>
       </c>
       <c r="H14" s="2">
-        <v>70.21</v>
+        <v>72.01</v>
       </c>
       <c r="I14" s="2">
-        <v>87.96</v>
+        <v>89.77</v>
       </c>
       <c r="J14" s="2">
-        <v>0.03120544454354591</v>
+        <v>0.032676254454583886</v>
       </c>
       <c r="K14" s="2" t="b">
         <v>0</v>
@@ -2957,13 +2954,13 @@
         <v>101</v>
       </c>
       <c r="M14" s="2">
-        <v>0.6729978657072717</v>
+        <v>0.6738566625489897</v>
       </c>
       <c r="N14" s="2">
-        <v>73.7982348050695</v>
+        <v>74.26209832924113</v>
       </c>
       <c r="O14" s="2">
-        <v>97.6470588235294</v>
+        <v>96.47058823529412</v>
       </c>
       <c r="P14" s="2">
         <v>19.142997204429033</v>
@@ -2972,13 +2969,13 @@
         <v>68.82352941176471</v>
       </c>
       <c r="R14" s="2">
-        <v>61</v>
+        <v>60.88235294117648</v>
       </c>
       <c r="S14" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T14" s="2">
-        <v>5.09</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -2998,19 +2995,19 @@
         <v>1.49</v>
       </c>
       <c r="F15" s="1">
-        <v>-0.20152043253389712</v>
+        <v>-0.1825255115720157</v>
       </c>
       <c r="G15" s="1">
         <v>2.25</v>
       </c>
       <c r="H15" s="1">
-        <v>67.25</v>
+        <v>74.34</v>
       </c>
       <c r="I15" s="1">
-        <v>53.01</v>
+        <v>63.92</v>
       </c>
       <c r="J15" s="1">
-        <v>0.008670674726406103</v>
+        <v>0.013991626364916392</v>
       </c>
       <c r="K15" s="1" t="b">
         <v>1</v>
@@ -3019,28 +3016,28 @@
         <v>1031</v>
       </c>
       <c r="M15" s="1">
-        <v>-0.1337273296046182</v>
+        <v>-0.1100076106427389</v>
       </c>
       <c r="N15" s="1">
-        <v>-6.874284726119502</v>
+        <v>-4.124328989931748</v>
       </c>
       <c r="O15" s="1">
-        <v>31.76470588235294</v>
+        <v>35.294117647058826</v>
       </c>
       <c r="P15" s="1">
         <v>41.90435941885386</v>
       </c>
       <c r="Q15" s="1">
-        <v>59.76470588235295</v>
+        <v>62.82352941176471</v>
       </c>
       <c r="R15" s="1">
-        <v>30.88235294117647</v>
+        <v>33.235294117647065</v>
       </c>
       <c r="S15" s="1" t="s">
         <v>107</v>
       </c>
       <c r="T15" s="1">
-        <v>-27.53</v>
+        <v>-25.18</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -3060,19 +3057,19 @@
         <v>29.93</v>
       </c>
       <c r="F16" s="3">
-        <v>-0.2998474830571089</v>
+        <v>-0.3306596581502806</v>
       </c>
       <c r="G16" s="3">
         <v>1.8</v>
       </c>
       <c r="H16" s="3">
-        <v>50.07</v>
+        <v>48.8</v>
       </c>
       <c r="I16" s="3">
-        <v>-3.72</v>
+        <v>-4.68</v>
       </c>
       <c r="J16" s="3">
-        <v>-0.02683543490510299</v>
+        <v>-0.019216719442214092</v>
       </c>
       <c r="K16" s="3" t="b">
         <v>1</v>
@@ -3081,28 +3078,28 @@
         <v>27</v>
       </c>
       <c r="M16" s="3">
-        <v>-0.2564598971823704</v>
+        <v>-0.2842482015555434</v>
       </c>
       <c r="N16" s="3">
-        <v>-19.147541483894724</v>
+        <v>-21.548388081212195</v>
       </c>
       <c r="O16" s="3">
-        <v>10.588235294117647</v>
+        <v>9.411764705882353</v>
       </c>
       <c r="P16" s="3">
         <v>40.1905830435425</v>
       </c>
       <c r="Q16" s="3">
-        <v>30.588235294117645</v>
+        <v>30.941176470588236</v>
       </c>
       <c r="R16" s="3">
-        <v>13.058823529411764</v>
+        <v>13.529411764705884</v>
       </c>
       <c r="S16" s="3" t="s">
         <v>108</v>
       </c>
       <c r="T16" s="3">
-        <v>-30.17</v>
+        <v>-29.7</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -3122,19 +3119,19 @@
         <v>-1.64</v>
       </c>
       <c r="F17" s="1">
-        <v>-0.07341890325967368</v>
+        <v>-0.07270578235136307</v>
       </c>
       <c r="G17" s="1">
         <v>1.76</v>
       </c>
       <c r="H17" s="1">
-        <v>51.78</v>
+        <v>51.25</v>
       </c>
       <c r="I17" s="1">
-        <v>4.97</v>
+        <v>4.59</v>
       </c>
       <c r="J17" s="1">
-        <v>-0.00003944970876741593</v>
+        <v>0.0051619944250029266</v>
       </c>
       <c r="K17" s="1" t="b">
         <v>1</v>
@@ -3143,28 +3140,28 @@
         <v>31</v>
       </c>
       <c r="M17" s="1">
-        <v>-0.03220069667867209</v>
+        <v>-0.02861489858636279</v>
       </c>
       <c r="N17" s="1">
-        <v>3.2783785664751077</v>
+        <v>4.014942215705853</v>
       </c>
       <c r="O17" s="1">
-        <v>54.11764705882353</v>
+        <v>55.294117647058826</v>
       </c>
       <c r="P17" s="1">
         <v>24.80206596461608</v>
       </c>
       <c r="Q17" s="1">
-        <v>41.05882352941177</v>
+        <v>41.647058823529406</v>
       </c>
       <c r="R17" s="1">
-        <v>33.294117647058826</v>
+        <v>34.235294117647065</v>
       </c>
       <c r="S17" s="1" t="s">
         <v>102</v>
       </c>
       <c r="T17" s="1">
-        <v>0.12</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -3184,19 +3181,19 @@
         <v>11.08</v>
       </c>
       <c r="F18" s="3">
-        <v>-0.709113646504802</v>
+        <v>-0.7379893423809751</v>
       </c>
       <c r="G18" s="3">
         <v>1.12</v>
       </c>
       <c r="H18" s="3">
-        <v>19.48</v>
+        <v>14.63</v>
       </c>
       <c r="I18" s="3">
-        <v>-55.62</v>
+        <v>-58.58</v>
       </c>
       <c r="J18" s="3">
-        <v>-0.07868279643766589</v>
+        <v>-0.08236145440931923</v>
       </c>
       <c r="K18" s="3" t="b">
         <v>1</v>
@@ -3205,16 +3202,16 @@
         <v>31</v>
       </c>
       <c r="M18" s="3">
-        <v>-0.7026055086235913</v>
+        <v>-0.7310276238917646</v>
       </c>
       <c r="N18" s="3">
-        <v>-63.76210262801681</v>
+        <v>-66.22633031483431</v>
       </c>
       <c r="O18" s="3">
         <v>1.1764705882352942</v>
       </c>
       <c r="P18" s="3">
-        <v>67.99674143147296</v>
+        <v>68.77035731645671</v>
       </c>
       <c r="Q18" s="3">
         <v>39.647058823529406</v>
@@ -3246,19 +3243,19 @@
         <v>3.1</v>
       </c>
       <c r="F19" s="2">
-        <v>0.13823063380827963</v>
+        <v>0.11815369116035443</v>
       </c>
       <c r="G19" s="2">
         <v>0.09</v>
       </c>
       <c r="H19" s="2">
-        <v>63.77</v>
+        <v>62.2</v>
       </c>
       <c r="I19" s="2">
-        <v>17.67</v>
+        <v>17.04</v>
       </c>
       <c r="J19" s="2">
-        <v>0.008014195843523662</v>
+        <v>0.01030310000911132</v>
       </c>
       <c r="K19" s="2" t="b">
         <v>1</v>
@@ -3267,28 +3264,28 @@
         <v>-60</v>
       </c>
       <c r="M19" s="2">
-        <v>0.08887725487576459</v>
+        <v>0.06536065928384094</v>
       </c>
       <c r="N19" s="2">
-        <v>15.386173721918766</v>
+        <v>13.412498002726231</v>
       </c>
       <c r="O19" s="2">
-        <v>68.23529411764706</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="P19" s="2">
         <v>11.392700631623551</v>
       </c>
       <c r="Q19" s="2">
-        <v>64.47058823529412</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="R19" s="2">
-        <v>55.88235294117647</v>
+        <v>55.17647058823529</v>
       </c>
       <c r="S19" s="2" t="s">
         <v>110</v>
       </c>
       <c r="T19" s="2">
-        <v>7.47</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -3308,19 +3305,19 @@
         <v>-5.69</v>
       </c>
       <c r="F20" s="2">
-        <v>0.3328171899283523</v>
+        <v>0.3109990847220883</v>
       </c>
       <c r="G20" s="2">
         <v>1.07</v>
       </c>
       <c r="H20" s="2">
-        <v>57.25</v>
+        <v>63.87</v>
       </c>
       <c r="I20" s="2">
-        <v>24.03</v>
+        <v>26.72</v>
       </c>
       <c r="J20" s="2">
-        <v>0.024704990513418974</v>
+        <v>0.02473565319322041</v>
       </c>
       <c r="K20" s="2" t="b">
         <v>0</v>
@@ -3329,28 +3326,28 @@
         <v>8</v>
       </c>
       <c r="M20" s="2">
-        <v>0.3366136036923919</v>
+        <v>0.3150600871741278</v>
       </c>
       <c r="N20" s="2">
-        <v>40.1598086035815</v>
+        <v>38.382440791754924</v>
       </c>
       <c r="O20" s="2">
-        <v>87.05882352941177</v>
+        <v>84.70588235294117</v>
       </c>
       <c r="P20" s="2">
-        <v>15.865501923269152</v>
+        <v>15.052477440996265</v>
       </c>
       <c r="Q20" s="2">
-        <v>62.23529411764706</v>
+        <v>64.11764705882354</v>
       </c>
       <c r="R20" s="2">
-        <v>57.58823529411765</v>
+        <v>56.88235294117648</v>
       </c>
       <c r="S20" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T20" s="2">
-        <v>21.73</v>
+        <v>21.03</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -3370,19 +3367,19 @@
         <v>-3.44</v>
       </c>
       <c r="F21" s="3">
-        <v>-0.4076005561597832</v>
+        <v>-0.4101216391199482</v>
       </c>
       <c r="G21" s="3">
         <v>1.63</v>
       </c>
       <c r="H21" s="3">
-        <v>34.18</v>
+        <v>35.55</v>
       </c>
       <c r="I21" s="3">
-        <v>-19.74</v>
+        <v>-19.5</v>
       </c>
       <c r="J21" s="3">
-        <v>-0.024514627176096933</v>
+        <v>-0.026776359199948047</v>
       </c>
       <c r="K21" s="3" t="b">
         <v>1</v>
@@ -3391,28 +3388,28 @@
         <v>55</v>
       </c>
       <c r="M21" s="3">
-        <v>-0.3734328322834266</v>
+        <v>-0.3735726170515927</v>
       </c>
       <c r="N21" s="3">
-        <v>-30.844834994000347</v>
+        <v>-30.48082963081713</v>
       </c>
       <c r="O21" s="3">
-        <v>4.705882352941177</v>
+        <v>3.5294117647058822</v>
       </c>
       <c r="P21" s="3">
-        <v>54.27900061157512</v>
+        <v>54.624638650661495</v>
       </c>
       <c r="Q21" s="3">
-        <v>36.352941176470594</v>
+        <v>35.52941176470589</v>
       </c>
       <c r="R21" s="3">
-        <v>20.058823529411768</v>
+        <v>19.11764705882353</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>111</v>
       </c>
       <c r="T21" s="3">
-        <v>-31.16</v>
+        <v>-32.1</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -3432,19 +3429,19 @@
         <v>-0.24</v>
       </c>
       <c r="F22" s="1">
-        <v>-0.18846342966613092</v>
+        <v>-0.21680737246601367</v>
       </c>
       <c r="G22" s="1">
         <v>1.38</v>
       </c>
       <c r="H22" s="1">
-        <v>38.96</v>
+        <v>40.92</v>
       </c>
       <c r="I22" s="1">
-        <v>-1.32</v>
+        <v>-0.74</v>
       </c>
       <c r="J22" s="1">
-        <v>-0.012270105174911727</v>
+        <v>-0.011157217131063461</v>
       </c>
       <c r="K22" s="1" t="b">
         <v>1</v>
@@ -3453,28 +3450,28 @@
         <v>245</v>
       </c>
       <c r="M22" s="1">
-        <v>-0.16785432637563014</v>
+        <v>-0.19476193058351354</v>
       </c>
       <c r="N22" s="1">
-        <v>-10.286984403220702</v>
+        <v>-12.599760984009217</v>
       </c>
       <c r="O22" s="1">
-        <v>23.52941176470588</v>
+        <v>18.823529411764707</v>
       </c>
       <c r="P22" s="1">
         <v>19.455960650079966</v>
       </c>
       <c r="Q22" s="1">
-        <v>44.11764705882352</v>
+        <v>44.35294117647058</v>
       </c>
       <c r="R22" s="1">
-        <v>33.99999999999999</v>
+        <v>32.705882352941174</v>
       </c>
       <c r="S22" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T22" s="1">
-        <v>-19.11</v>
+        <v>-20.4</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -3488,25 +3485,25 @@
         <v>96.47058823529412</v>
       </c>
       <c r="D23" s="2">
-        <v>-0.688512241054614</v>
+        <v>-0.6689265536723165</v>
       </c>
       <c r="E23" s="2">
         <v>0.09</v>
       </c>
       <c r="F23" s="2">
-        <v>0.258470266226973</v>
+        <v>0.35258172772505253</v>
       </c>
       <c r="G23" s="2">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="H23" s="2">
-        <v>73.89</v>
+        <v>80.08</v>
       </c>
       <c r="I23" s="2">
-        <v>17.68</v>
+        <v>23.92</v>
       </c>
       <c r="J23" s="2">
-        <v>0.011516256880881174</v>
+        <v>0.012049575661449066</v>
       </c>
       <c r="K23" s="2" t="b">
         <v>1</v>
@@ -3515,28 +3512,28 @@
         <v>45</v>
       </c>
       <c r="M23" s="2">
-        <v>0.26931716269565764</v>
+        <v>0.3636044486663026</v>
       </c>
       <c r="N23" s="2">
-        <v>33.43016450390807</v>
+        <v>43.2368769409724</v>
       </c>
       <c r="O23" s="2">
-        <v>83.52941176470588</v>
+        <v>87.05882352941177</v>
       </c>
       <c r="P23" s="2">
         <v>20.883293768118005</v>
       </c>
       <c r="Q23" s="2">
-        <v>65.76470588235294</v>
+        <v>65.76470588235293</v>
       </c>
       <c r="R23" s="2">
-        <v>56.411764705882355</v>
+        <v>57.41176470588236</v>
       </c>
       <c r="S23" s="2" t="s">
         <v>110</v>
       </c>
       <c r="T23" s="2">
-        <v>20.62</v>
+        <v>21.62</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -3556,19 +3553,19 @@
         <v>1.58</v>
       </c>
       <c r="F24" s="1">
-        <v>0.5182394077841334</v>
+        <v>0.6754998678271693</v>
       </c>
       <c r="G24" s="1">
         <v>3.58</v>
       </c>
       <c r="H24" s="1">
-        <v>65.82</v>
+        <v>66.05</v>
       </c>
       <c r="I24" s="1">
-        <v>18.27</v>
+        <v>18.78</v>
       </c>
       <c r="J24" s="1">
-        <v>0.05735022450404733</v>
+        <v>0.061648721352105355</v>
       </c>
       <c r="K24" s="1" t="b">
         <v>0</v>
@@ -3577,28 +3574,28 @@
         <v>-69</v>
       </c>
       <c r="M24" s="1">
-        <v>0.6581643722301651</v>
+        <v>0.8251768153451966</v>
       </c>
       <c r="N24" s="1">
-        <v>72.31488545735884</v>
+        <v>89.39411360886179</v>
       </c>
       <c r="O24" s="1">
-        <v>96.47058823529412</v>
+        <v>100</v>
       </c>
       <c r="P24" s="1">
         <v>57.99224429263358</v>
       </c>
       <c r="Q24" s="1">
-        <v>52.58823529411765</v>
+        <v>52.82352941176471</v>
       </c>
       <c r="R24" s="1">
-        <v>42.47058823529412</v>
+        <v>43.64705882352941</v>
       </c>
       <c r="S24" s="1" t="s">
         <v>109</v>
       </c>
       <c r="T24" s="1">
-        <v>46.19</v>
+        <v>47.37</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -3618,19 +3615,19 @@
         <v>15.51</v>
       </c>
       <c r="F25" s="3">
-        <v>-0.28859643682751596</v>
+        <v>-0.3065515304484267</v>
       </c>
       <c r="G25" s="3">
         <v>2.36</v>
       </c>
       <c r="H25" s="3">
-        <v>45.17</v>
+        <v>45.22</v>
       </c>
       <c r="I25" s="3">
-        <v>-30.3</v>
+        <v>-30.09</v>
       </c>
       <c r="J25" s="3">
-        <v>-0.00024310390602355666</v>
+        <v>-0.0006184264868946928</v>
       </c>
       <c r="K25" s="3" t="b">
         <v>0</v>
@@ -3639,28 +3636,28 @@
         <v>34</v>
       </c>
       <c r="M25" s="3">
-        <v>-0.21483754084046047</v>
+        <v>-0.22765205423737356</v>
       </c>
       <c r="N25" s="3">
-        <v>-14.985305849703732</v>
+        <v>-15.888773349395215</v>
       </c>
       <c r="O25" s="3">
-        <v>17.647058823529413</v>
+        <v>16.470588235294116</v>
       </c>
       <c r="P25" s="3">
         <v>45.59139601172712</v>
       </c>
       <c r="Q25" s="3">
-        <v>19.764705882352946</v>
+        <v>18.35294117647059</v>
       </c>
       <c r="R25" s="3">
-        <v>5.705882352941179</v>
+        <v>5.117647058823531</v>
       </c>
       <c r="S25" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T25" s="3">
-        <v>4.3</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -3680,19 +3677,19 @@
         <v>-0.85</v>
       </c>
       <c r="F26" s="3">
-        <v>-0.3998634494049582</v>
+        <v>-0.3166222181737807</v>
       </c>
       <c r="G26" s="3">
         <v>3.37</v>
       </c>
       <c r="H26" s="3">
-        <v>53.2</v>
+        <v>61.89</v>
       </c>
       <c r="I26" s="3">
-        <v>-5.63</v>
+        <v>2.79</v>
       </c>
       <c r="J26" s="3">
-        <v>-0.003862061978036462</v>
+        <v>0.002331961676426706</v>
       </c>
       <c r="K26" s="3" t="b">
         <v>1</v>
@@ -3701,28 +3698,28 @@
         <v>160</v>
       </c>
       <c r="M26" s="3">
-        <v>-0.2713277262510454</v>
+        <v>-0.17912827801187192</v>
       </c>
       <c r="N26" s="3">
-        <v>-20.634324390762227</v>
+        <v>-11.036395726845049</v>
       </c>
       <c r="O26" s="3">
-        <v>8.235294117647058</v>
+        <v>21.176470588235293</v>
       </c>
       <c r="P26" s="3">
         <v>55.61259899184437</v>
       </c>
       <c r="Q26" s="3">
-        <v>24.23529411764706</v>
+        <v>29.176470588235293</v>
       </c>
       <c r="R26" s="3">
-        <v>2.5294117647058822</v>
+        <v>7.588235294117645</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T26" s="3">
-        <v>-26.31</v>
+        <v>-21.25</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -3742,19 +3739,19 @@
         <v>6.87</v>
       </c>
       <c r="F27" s="3">
-        <v>-0.48152232434367737</v>
+        <v>-0.45480876149569793</v>
       </c>
       <c r="G27" s="3">
         <v>2.66</v>
       </c>
       <c r="H27" s="3">
-        <v>37.21</v>
+        <v>40.72</v>
       </c>
       <c r="I27" s="3">
-        <v>-36.84</v>
+        <v>-35.22</v>
       </c>
       <c r="J27" s="3">
-        <v>-0.020644318548790477</v>
+        <v>-0.019978165100761277</v>
       </c>
       <c r="K27" s="3" t="b">
         <v>0</v>
@@ -3763,28 +3760,28 @@
         <v>7</v>
       </c>
       <c r="M27" s="3">
-        <v>-0.3914930836535949</v>
+        <v>-0.3585049890616183</v>
       </c>
       <c r="N27" s="3">
-        <v>-32.650860131017176</v>
+        <v>-28.974066831819695</v>
       </c>
       <c r="O27" s="3">
-        <v>2.3529411764705883</v>
+        <v>4.705882352941177</v>
       </c>
       <c r="P27" s="3">
         <v>50.56910707785277</v>
       </c>
       <c r="Q27" s="3">
-        <v>12.823529411764705</v>
+        <v>13.176470588235295</v>
       </c>
       <c r="R27" s="3">
-        <v>-0.05882352941176627</v>
+        <v>0.7647058823529402</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T27" s="3">
-        <v>-16.22</v>
+        <v>-15.39</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -3804,19 +3801,19 @@
         <v>2.19</v>
       </c>
       <c r="F28" s="1">
-        <v>-0.05686137828423446</v>
+        <v>-0.007809862320691002</v>
       </c>
       <c r="G28" s="1">
         <v>3.26</v>
       </c>
       <c r="H28" s="1">
-        <v>51.74</v>
+        <v>52.95</v>
       </c>
       <c r="I28" s="1">
-        <v>-9.7</v>
+        <v>-8.69</v>
       </c>
       <c r="J28" s="1">
-        <v>0.013389762757673942</v>
+        <v>0.014709630294739586</v>
       </c>
       <c r="K28" s="1" t="b">
         <v>0</v>
@@ -3825,28 +3822,28 @@
         <v>3</v>
       </c>
       <c r="M28" s="1">
-        <v>0.06570855181190183</v>
+        <v>0.12330250255944142</v>
       </c>
       <c r="N28" s="1">
-        <v>13.069303415532502</v>
+        <v>19.206682330286288</v>
       </c>
       <c r="O28" s="1">
-        <v>64.70588235294117</v>
+        <v>72.94117647058823</v>
       </c>
       <c r="P28" s="1">
         <v>35.08771990976345</v>
       </c>
       <c r="Q28" s="1">
-        <v>49.05882352941176</v>
+        <v>49.764705882352935</v>
       </c>
       <c r="R28" s="1">
-        <v>41.05882352941176</v>
+        <v>43.64705882352941</v>
       </c>
       <c r="S28" s="1" t="s">
         <v>112</v>
       </c>
       <c r="T28" s="1">
-        <v>24.05</v>
+        <v>26.63</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -3866,19 +3863,19 @@
         <v>-4.83</v>
       </c>
       <c r="F29" s="1">
-        <v>-0.1804792706906862</v>
+        <v>-0.17424495950336633</v>
       </c>
       <c r="G29" s="1">
         <v>2.32</v>
       </c>
       <c r="H29" s="1">
-        <v>40.82</v>
+        <v>44.24</v>
       </c>
       <c r="I29" s="1">
-        <v>-14.09</v>
+        <v>-12.28</v>
       </c>
       <c r="J29" s="1">
-        <v>-0.008374137523703638</v>
+        <v>-0.008462453192343537</v>
       </c>
       <c r="K29" s="1" t="b">
         <v>1</v>
@@ -3887,28 +3884,28 @@
         <v>11</v>
       </c>
       <c r="M29" s="1">
-        <v>-0.10888975399736767</v>
+        <v>-0.09766605612205004</v>
       </c>
       <c r="N29" s="1">
-        <v>-4.390527165394458</v>
+        <v>-2.8901735378628564</v>
       </c>
       <c r="O29" s="1">
-        <v>35.294117647058826</v>
+        <v>40</v>
       </c>
       <c r="P29" s="1">
-        <v>18.81663456064845</v>
+        <v>18.79659508828292</v>
       </c>
       <c r="Q29" s="1">
-        <v>47.05882352941176</v>
+        <v>47.64705882352941</v>
       </c>
       <c r="R29" s="1">
-        <v>41.23529411764706</v>
+        <v>42.76470588235294</v>
       </c>
       <c r="S29" s="1" t="s">
         <v>110</v>
       </c>
       <c r="T29" s="1">
-        <v>0.99</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -3928,19 +3925,19 @@
         <v>1.22</v>
       </c>
       <c r="F30" s="1">
-        <v>-0.17080193300518698</v>
+        <v>-0.1810122276425397</v>
       </c>
       <c r="G30" s="1">
         <v>1.25</v>
       </c>
       <c r="H30" s="1">
-        <v>40.13</v>
+        <v>36.72</v>
       </c>
       <c r="I30" s="1">
-        <v>-9.17</v>
+        <v>-10.7</v>
       </c>
       <c r="J30" s="1">
-        <v>-0.010028384946304017</v>
+        <v>-0.009442467392974703</v>
       </c>
       <c r="K30" s="1" t="b">
         <v>1</v>
@@ -3949,28 +3946,28 @@
         <v>136</v>
       </c>
       <c r="M30" s="1">
-        <v>-0.1572433124193312</v>
+        <v>-0.16650864745668437</v>
       </c>
       <c r="N30" s="1">
-        <v>-9.225883007590806</v>
+        <v>-9.774432671326291</v>
       </c>
       <c r="O30" s="1">
         <v>27.058823529411764</v>
       </c>
       <c r="P30" s="1">
-        <v>18.121365335609003</v>
+        <v>18.204489584640044</v>
       </c>
       <c r="Q30" s="1">
-        <v>51.882352941176464</v>
+        <v>50.470588235294116</v>
       </c>
       <c r="R30" s="1">
-        <v>43.11764705882353</v>
+        <v>43</v>
       </c>
       <c r="S30" s="1" t="s">
         <v>111</v>
       </c>
       <c r="T30" s="1">
-        <v>-5.36</v>
+        <v>-5.48</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -3990,19 +3987,19 @@
         <v>0.39</v>
       </c>
       <c r="F31" s="1">
-        <v>-0.16135179682802436</v>
+        <v>-0.17137880698784186</v>
       </c>
       <c r="G31" s="1">
         <v>1.47</v>
       </c>
       <c r="H31" s="1">
-        <v>42.32</v>
+        <v>45.36</v>
       </c>
       <c r="I31" s="1">
-        <v>-4.77</v>
+        <v>-3.54</v>
       </c>
       <c r="J31" s="1">
-        <v>-0.009218959447684303</v>
+        <v>-0.009371948354026896</v>
       </c>
       <c r="K31" s="1" t="b">
         <v>0</v>
@@ -4011,28 +4008,28 @@
         <v>209</v>
       </c>
       <c r="M31" s="1">
-        <v>-0.13586159012661547</v>
+        <v>-0.1441120762384338</v>
       </c>
       <c r="N31" s="1">
-        <v>-7.087710778319237</v>
+        <v>-7.534775549501241</v>
       </c>
       <c r="O31" s="1">
-        <v>30.58823529411765</v>
+        <v>32.94117647058823</v>
       </c>
       <c r="P31" s="1">
         <v>29.54918623383928</v>
       </c>
       <c r="Q31" s="1">
-        <v>51.64705882352941</v>
+        <v>52.23529411764706</v>
       </c>
       <c r="R31" s="1">
-        <v>39</v>
+        <v>39.588235294117645</v>
       </c>
       <c r="S31" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T31" s="1">
-        <v>-9.05</v>
+        <v>-8.46</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -4052,19 +4049,19 @@
         <v>3.57</v>
       </c>
       <c r="F32" s="1">
-        <v>-0.07265357003503854</v>
+        <v>-0.0757964354650135</v>
       </c>
       <c r="G32" s="1">
         <v>1.62</v>
       </c>
       <c r="H32" s="1">
-        <v>41.06</v>
+        <v>46.14</v>
       </c>
       <c r="I32" s="1">
-        <v>-7.6</v>
+        <v>-5.29</v>
       </c>
       <c r="J32" s="1">
-        <v>-0.013710073635057411</v>
+        <v>-0.015269334595524313</v>
       </c>
       <c r="K32" s="1" t="b">
         <v>0</v>
@@ -4073,28 +4070,28 @@
         <v>21</v>
       </c>
       <c r="M32" s="1">
-        <v>-0.039028190982116184</v>
+        <v>-0.03982755660409221</v>
       </c>
       <c r="N32" s="1">
-        <v>2.5956291361306865</v>
+        <v>2.8936764139329125</v>
       </c>
       <c r="O32" s="1">
-        <v>51.76470588235295</v>
+        <v>54.11764705882353</v>
       </c>
       <c r="P32" s="1">
         <v>26.613703173358488</v>
       </c>
       <c r="Q32" s="1">
-        <v>34.23529411764706</v>
+        <v>34.470588235294116</v>
       </c>
       <c r="R32" s="1">
-        <v>32.470588235294116</v>
+        <v>32.94117647058823</v>
       </c>
       <c r="S32" s="1" t="s">
         <v>109</v>
       </c>
       <c r="T32" s="1">
-        <v>0.58</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -4114,19 +4111,19 @@
         <v>0.24</v>
       </c>
       <c r="F33" s="2">
-        <v>0.2993452791916342</v>
+        <v>0.3366804893544467</v>
       </c>
       <c r="G33" s="2">
         <v>1.1</v>
       </c>
       <c r="H33" s="2">
-        <v>54.5</v>
+        <v>53.21</v>
       </c>
       <c r="I33" s="2">
-        <v>15.32</v>
+        <v>14.89</v>
       </c>
       <c r="J33" s="2">
-        <v>0.024467845138836035</v>
+        <v>0.023823104227291014</v>
       </c>
       <c r="K33" s="2" t="b">
         <v>1</v>
@@ -4135,10 +4132,10 @@
         <v>81</v>
       </c>
       <c r="M33" s="2">
-        <v>0.3047687274259765</v>
+        <v>0.34248192142878886</v>
       </c>
       <c r="N33" s="2">
-        <v>36.97532097693996</v>
+        <v>41.124624217221026</v>
       </c>
       <c r="O33" s="2">
         <v>85.88235294117646</v>
@@ -4147,7 +4144,7 @@
         <v>23.38443607454554</v>
       </c>
       <c r="Q33" s="2">
-        <v>67.29411764705883</v>
+        <v>66.3529411764706</v>
       </c>
       <c r="R33" s="2">
         <v>60</v>
@@ -4176,19 +4173,19 @@
         <v>2.34</v>
       </c>
       <c r="F34" s="1">
-        <v>-0.0979788143941577</v>
+        <v>-0.08487507572712688</v>
       </c>
       <c r="G34" s="1">
         <v>1.21</v>
       </c>
       <c r="H34" s="1">
-        <v>45.68</v>
+        <v>48.93</v>
       </c>
       <c r="I34" s="1">
-        <v>0.17</v>
+        <v>1.38</v>
       </c>
       <c r="J34" s="1">
-        <v>-0.0028423176498818294</v>
+        <v>-0.003652781588481443</v>
       </c>
       <c r="K34" s="1" t="b">
         <v>1</v>
@@ -4197,28 +4194,28 @@
         <v>210</v>
       </c>
       <c r="M34" s="1">
-        <v>-0.08658957310203885</v>
+        <v>-0.07269206837100839</v>
       </c>
       <c r="N34" s="1">
-        <v>-2.1605090758615764</v>
+        <v>-0.3927747627586982</v>
       </c>
       <c r="O34" s="1">
-        <v>42.35294117647059</v>
+        <v>45.88235294117647</v>
       </c>
       <c r="P34" s="1">
         <v>21.09433056126816</v>
       </c>
       <c r="Q34" s="1">
-        <v>46.470588235294116</v>
+        <v>45.882352941176464</v>
       </c>
       <c r="R34" s="1">
-        <v>37.35294117647059</v>
+        <v>38.1764705882353</v>
       </c>
       <c r="S34" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T34" s="1">
-        <v>-9.48</v>
+        <v>-8.65</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -4238,49 +4235,49 @@
         <v>-0.47</v>
       </c>
       <c r="F35" s="1">
-        <v>-0.014927975149269773</v>
+        <v>-0.047054051288710264</v>
       </c>
       <c r="G35" s="1">
         <v>0.95</v>
       </c>
       <c r="H35" s="1">
-        <v>34.66</v>
+        <v>32.16</v>
       </c>
       <c r="I35" s="1">
-        <v>-16.81</v>
+        <v>-17.93</v>
       </c>
       <c r="J35" s="1">
-        <v>-0.0023912012811345175</v>
+        <v>-0.002689614466869727</v>
       </c>
       <c r="K35" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" s="1">
         <v>-57</v>
       </c>
       <c r="M35" s="1">
-        <v>-0.017639699266440934</v>
+        <v>-0.04995476732588133</v>
       </c>
       <c r="N35" s="1">
-        <v>4.73447830769823</v>
+        <v>1.8809553417540148</v>
       </c>
       <c r="O35" s="1">
-        <v>55.294117647058826</v>
+        <v>51.76470588235295</v>
       </c>
       <c r="P35" s="1">
-        <v>19.973884530776573</v>
+        <v>20.292142946083924</v>
       </c>
       <c r="Q35" s="1">
-        <v>43.05882352941177</v>
+        <v>42</v>
       </c>
       <c r="R35" s="1">
-        <v>43.94117647058824</v>
+        <v>42.41176470588236</v>
       </c>
       <c r="S35" s="1" t="s">
         <v>101</v>
       </c>
       <c r="T35" s="1">
-        <v>21.44</v>
+        <v>19.91</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -4300,19 +4297,19 @@
         <v>-1.3</v>
       </c>
       <c r="F36" s="1">
-        <v>-0.09509953450079849</v>
+        <v>-0.0994227443660013</v>
       </c>
       <c r="G36" s="1">
         <v>1.12</v>
       </c>
       <c r="H36" s="1">
-        <v>44.02</v>
+        <v>42.7</v>
       </c>
       <c r="I36" s="1">
-        <v>-9.19</v>
+        <v>-9.75</v>
       </c>
       <c r="J36" s="1">
-        <v>0.004373412843074677</v>
+        <v>0.0032861538217901338</v>
       </c>
       <c r="K36" s="1" t="b">
         <v>1</v>
@@ -4321,28 +4318,28 @@
         <v>-18</v>
       </c>
       <c r="M36" s="1">
-        <v>-0.0885913966195877</v>
+        <v>-0.09246102587679073</v>
       </c>
       <c r="N36" s="1">
-        <v>-2.3606914276164535</v>
+        <v>-2.3696705133369345</v>
       </c>
       <c r="O36" s="1">
-        <v>40</v>
+        <v>41.17647058823529</v>
       </c>
       <c r="P36" s="1">
         <v>26.730280409441182</v>
       </c>
       <c r="Q36" s="1">
-        <v>48.82352941176472</v>
+        <v>47.1764705882353</v>
       </c>
       <c r="R36" s="1">
-        <v>38.411764705882355</v>
+        <v>38.529411764705884</v>
       </c>
       <c r="S36" s="1" t="s">
         <v>108</v>
       </c>
       <c r="T36" s="1">
-        <v>11.46</v>
+        <v>11.58</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -4362,19 +4359,19 @@
         <v>-3.26</v>
       </c>
       <c r="F37" s="2">
-        <v>0.1559409475199089</v>
+        <v>0.1561430887128934</v>
       </c>
       <c r="G37" s="2">
         <v>1.28</v>
       </c>
       <c r="H37" s="2">
-        <v>40.33</v>
+        <v>41.06</v>
       </c>
       <c r="I37" s="2">
-        <v>4</v>
+        <v>4.36</v>
       </c>
       <c r="J37" s="2">
-        <v>0.011443912733200126</v>
+        <v>0.007392605857651344</v>
       </c>
       <c r="K37" s="2" t="b">
         <v>1</v>
@@ -4383,28 +4380,28 @@
         <v>-108</v>
       </c>
       <c r="M37" s="2">
-        <v>0.17112660257606738</v>
+        <v>0.17238709852105139</v>
       </c>
       <c r="N37" s="2">
-        <v>23.61110849194904</v>
+        <v>24.115141926447272</v>
       </c>
       <c r="O37" s="2">
-        <v>78.82352941176471</v>
+        <v>77.64705882352942</v>
       </c>
       <c r="P37" s="2">
         <v>20.1020772277769</v>
       </c>
       <c r="Q37" s="2">
-        <v>51.76470588235294</v>
+        <v>49.294117647058826</v>
       </c>
       <c r="R37" s="2">
-        <v>51.88235294117647</v>
+        <v>50.588235294117645</v>
       </c>
       <c r="S37" s="2" t="s">
         <v>111</v>
       </c>
       <c r="T37" s="2">
-        <v>22.07</v>
+        <v>20.77</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -4424,19 +4421,19 @@
         <v>3.13</v>
       </c>
       <c r="F38" s="2">
-        <v>0.4655988829695965</v>
+        <v>0.46236494132502365</v>
       </c>
       <c r="G38" s="2">
         <v>1.21</v>
       </c>
       <c r="H38" s="2">
-        <v>67.3</v>
+        <v>66.26</v>
       </c>
       <c r="I38" s="2">
-        <v>73.95</v>
+        <v>72.19</v>
       </c>
       <c r="J38" s="2">
-        <v>0.027151927006933585</v>
+        <v>0.027242657661209382</v>
       </c>
       <c r="K38" s="2" t="b">
         <v>0</v>
@@ -4445,28 +4442,28 @@
         <v>391</v>
       </c>
       <c r="M38" s="2">
-        <v>0.47698812426171533</v>
+        <v>0.47454794868114214</v>
       </c>
       <c r="N38" s="2">
-        <v>54.19726066051385</v>
+        <v>54.331226942456354</v>
       </c>
       <c r="O38" s="2">
-        <v>91.76470588235294</v>
+        <v>90.58823529411765</v>
       </c>
       <c r="P38" s="2">
         <v>17.802507034008837</v>
       </c>
       <c r="Q38" s="2">
-        <v>76.23529411764704</v>
+        <v>76</v>
       </c>
       <c r="R38" s="2">
-        <v>66.58823529411764</v>
+        <v>66.23529411764706</v>
       </c>
       <c r="S38" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T38" s="2">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -4486,19 +4483,19 @@
         <v>-1.29</v>
       </c>
       <c r="F39" s="1">
-        <v>-0.08180180735324165</v>
+        <v>-0.10697600929726371</v>
       </c>
       <c r="G39" s="1">
         <v>1.12</v>
       </c>
       <c r="H39" s="1">
-        <v>36.15</v>
+        <v>37.55</v>
       </c>
       <c r="I39" s="1">
-        <v>-7.93</v>
+        <v>-7.44</v>
       </c>
       <c r="J39" s="1">
-        <v>-0.006090746762965525</v>
+        <v>-0.006455693050868042</v>
       </c>
       <c r="K39" s="1" t="b">
         <v>0</v>
@@ -4507,28 +4504,28 @@
         <v>-1</v>
       </c>
       <c r="M39" s="1">
-        <v>-0.07529366947203087</v>
+        <v>-0.10001429080805313</v>
       </c>
       <c r="N39" s="1">
-        <v>-1.030918712860774</v>
+        <v>-3.1249970064631656</v>
       </c>
       <c r="O39" s="1">
-        <v>44.70588235294118</v>
+        <v>38.82352941176471</v>
       </c>
       <c r="P39" s="1">
         <v>30.28933322215756</v>
       </c>
       <c r="Q39" s="1">
-        <v>42.705882352941174</v>
+        <v>42.11764705882353</v>
       </c>
       <c r="R39" s="1">
-        <v>36.82352941176471</v>
+        <v>34.82352941176471</v>
       </c>
       <c r="S39" s="1" t="s">
         <v>112</v>
       </c>
       <c r="T39" s="1">
-        <v>11.03</v>
+        <v>9.03</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -4548,31 +4545,31 @@
         <v>4.43</v>
       </c>
       <c r="F40" s="1">
-        <v>0.5650719043727077</v>
+        <v>0.6443761270143141</v>
       </c>
       <c r="G40" s="1">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H40" s="1">
-        <v>65.42</v>
+        <v>64.39</v>
       </c>
       <c r="I40" s="1">
-        <v>18.61</v>
+        <v>17.81</v>
       </c>
       <c r="J40" s="1">
-        <v>0.04541650717500069</v>
+        <v>0.051387921921507894</v>
       </c>
       <c r="K40" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" s="1">
         <v>-21</v>
       </c>
       <c r="M40" s="1">
-        <v>0.5439204562587727</v>
+        <v>0.622330685131814</v>
       </c>
       <c r="N40" s="1">
-        <v>60.89049386021957</v>
+        <v>69.10950058752353</v>
       </c>
       <c r="O40" s="1">
         <v>94.11764705882352</v>
@@ -4581,16 +4578,16 @@
         <v>51.940889187924654</v>
       </c>
       <c r="Q40" s="1">
-        <v>58.117647058823536</v>
+        <v>58.00000000000001</v>
       </c>
       <c r="R40" s="1">
-        <v>47.235294117647065</v>
+        <v>47.352941176470594</v>
       </c>
       <c r="S40" s="1" t="s">
         <v>113</v>
       </c>
       <c r="T40" s="1">
-        <v>38.76</v>
+        <v>38.88</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -4610,19 +4607,19 @@
         <v>0.01</v>
       </c>
       <c r="F41" s="3">
-        <v>-0.10056493821438309</v>
+        <v>-0.1031559793739243</v>
       </c>
       <c r="G41" s="3">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="H41" s="3">
-        <v>35.65</v>
+        <v>38.7</v>
       </c>
       <c r="I41" s="3">
-        <v>-15.19</v>
+        <v>-13.92</v>
       </c>
       <c r="J41" s="3">
-        <v>-0.020176778753364773</v>
+        <v>-0.02171290738253668</v>
       </c>
       <c r="K41" s="3" t="b">
         <v>1</v>
@@ -4631,28 +4628,28 @@
         <v>4</v>
       </c>
       <c r="M41" s="3">
-        <v>-0.08809100727539576</v>
+        <v>-0.09039282881037158</v>
       </c>
       <c r="N41" s="3">
-        <v>-2.310652493197266</v>
+        <v>-2.162850806695012</v>
       </c>
       <c r="O41" s="3">
-        <v>41.17647058823529</v>
+        <v>42.35294117647059</v>
       </c>
       <c r="P41" s="3">
         <v>30.769232468942608</v>
       </c>
       <c r="Q41" s="3">
-        <v>20.352941176470587</v>
+        <v>20.47058823529412</v>
       </c>
       <c r="R41" s="3">
-        <v>19.588235294117645</v>
+        <v>19.705882352941174</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>107</v>
       </c>
       <c r="T41" s="3">
-        <v>-17.06</v>
+        <v>-16.94</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -4672,49 +4669,49 @@
         <v>4.33</v>
       </c>
       <c r="F42" s="3">
-        <v>-0.1892512599381852</v>
+        <v>-0.2081042627953599</v>
       </c>
       <c r="G42" s="3">
         <v>0.31</v>
       </c>
       <c r="H42" s="3">
-        <v>44.75</v>
+        <v>58.36</v>
       </c>
       <c r="I42" s="3">
-        <v>-9.07</v>
+        <v>-4.99</v>
       </c>
       <c r="J42" s="3">
-        <v>-0.015165693555448268</v>
+        <v>-0.015573571138320641</v>
       </c>
       <c r="K42" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="3">
         <v>16</v>
       </c>
       <c r="M42" s="3">
-        <v>-0.22667305275514715</v>
+        <v>-0.2481341441083207</v>
       </c>
       <c r="N42" s="3">
-        <v>-16.168857041172398</v>
+        <v>-17.93698233648992</v>
       </c>
       <c r="O42" s="3">
-        <v>15.294117647058824</v>
+        <v>14.117647058823529</v>
       </c>
       <c r="P42" s="3">
-        <v>19.870570381723375</v>
+        <v>20.352744065122756</v>
       </c>
       <c r="Q42" s="3">
-        <v>38.58823529411765</v>
+        <v>42</v>
       </c>
       <c r="R42" s="3">
-        <v>26.58823529411765</v>
+        <v>25.88235294117647</v>
       </c>
       <c r="S42" s="3" t="s">
         <v>111</v>
       </c>
       <c r="T42" s="3">
-        <v>-8.9</v>
+        <v>-9.61</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -4734,19 +4731,19 @@
         <v>8.78</v>
       </c>
       <c r="F43" s="2">
-        <v>0.16499480030957842</v>
+        <v>0.16957343213417514</v>
       </c>
       <c r="G43" s="2">
         <v>1.35</v>
       </c>
       <c r="H43" s="2">
-        <v>48.26</v>
+        <v>50.3</v>
       </c>
       <c r="I43" s="2">
-        <v>14.98</v>
+        <v>16.76</v>
       </c>
       <c r="J43" s="2">
-        <v>0.007307714562346161</v>
+        <v>0.006303173967708992</v>
       </c>
       <c r="K43" s="2" t="b">
         <v>0</v>
@@ -4755,28 +4752,28 @@
         <v>18</v>
       </c>
       <c r="M43" s="2">
-        <v>0.1839768691297765</v>
+        <v>0.18987844439437263</v>
       </c>
       <c r="N43" s="2">
-        <v>24.89613514731997</v>
+        <v>25.864276513779405</v>
       </c>
       <c r="O43" s="2">
-        <v>81.17647058823529</v>
+        <v>80</v>
       </c>
       <c r="P43" s="2">
         <v>24.82490242340647</v>
       </c>
       <c r="Q43" s="2">
-        <v>60.470588235294116</v>
+        <v>61.05882352941177</v>
       </c>
       <c r="R43" s="2">
-        <v>56.17647058823529</v>
+        <v>55.82352941176471</v>
       </c>
       <c r="S43" s="2" t="s">
         <v>114</v>
       </c>
       <c r="T43" s="2">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -4796,19 +4793,19 @@
         <v>-0.69</v>
       </c>
       <c r="F44" s="2">
-        <v>0.09335062089405227</v>
+        <v>0.1371561215211676</v>
       </c>
       <c r="G44" s="2">
         <v>2.63</v>
       </c>
       <c r="H44" s="2">
-        <v>52.42</v>
+        <v>56.32</v>
       </c>
       <c r="I44" s="2">
-        <v>8.16</v>
+        <v>11.72</v>
       </c>
       <c r="J44" s="2">
-        <v>0.010273746718710872</v>
+        <v>0.012058489583432822</v>
       </c>
       <c r="K44" s="2" t="b">
         <v>1</v>
@@ -4817,28 +4814,28 @@
         <v>-6</v>
       </c>
       <c r="M44" s="2">
-        <v>0.181752827113832</v>
+        <v>0.23171946433294455</v>
       </c>
       <c r="N44" s="2">
-        <v>24.673730945725513</v>
+        <v>30.048378507636603</v>
       </c>
       <c r="O44" s="2">
-        <v>80</v>
+        <v>82.35294117647058</v>
       </c>
       <c r="P44" s="2">
         <v>25.276100184761987</v>
       </c>
       <c r="Q44" s="2">
-        <v>62.35294117647059</v>
+        <v>63.647058823529406</v>
       </c>
       <c r="R44" s="2">
-        <v>56.17647058823529</v>
+        <v>57.117647058823536</v>
       </c>
       <c r="S44" s="2" t="s">
         <v>103</v>
       </c>
       <c r="T44" s="2">
-        <v>21.36</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
@@ -4858,19 +4855,19 @@
         <v>1.03</v>
       </c>
       <c r="F45" s="1">
-        <v>-0.025361315714862998</v>
+        <v>0.003671197466789053</v>
       </c>
       <c r="G45" s="1">
         <v>1.45</v>
       </c>
       <c r="H45" s="1">
-        <v>43.13</v>
+        <v>45.67</v>
       </c>
       <c r="I45" s="1">
-        <v>3.09</v>
+        <v>4.07</v>
       </c>
       <c r="J45" s="1">
-        <v>0.002880008894932799</v>
+        <v>0.0018497796267098127</v>
       </c>
       <c r="K45" s="1" t="b">
         <v>1</v>
@@ -4879,28 +4876,28 @@
         <v>196</v>
       </c>
       <c r="M45" s="1">
-        <v>-0.0009557986603225821</v>
+        <v>0.02977764180132869</v>
       </c>
       <c r="N45" s="1">
-        <v>6.402868368310048</v>
+        <v>9.854196254475015</v>
       </c>
       <c r="O45" s="1">
-        <v>58.82352941176471</v>
+        <v>61.1764705882353</v>
       </c>
       <c r="P45" s="1">
         <v>17.57882034058413</v>
       </c>
       <c r="Q45" s="1">
-        <v>44</v>
+        <v>43.882352941176464</v>
       </c>
       <c r="R45" s="1">
-        <v>42.117647058823536</v>
+        <v>42.470588235294116</v>
       </c>
       <c r="S45" s="1" t="s">
         <v>109</v>
       </c>
       <c r="T45" s="1">
-        <v>-2.21</v>
+        <v>-1.86</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
@@ -4920,19 +4917,19 @@
         <v>4.52</v>
       </c>
       <c r="F46" s="3">
-        <v>-0.334412896006272</v>
+        <v>-0.32783442538693164</v>
       </c>
       <c r="G46" s="3">
         <v>1.76</v>
       </c>
       <c r="H46" s="3">
-        <v>35.14</v>
+        <v>34.72</v>
       </c>
       <c r="I46" s="3">
-        <v>-33.04</v>
+        <v>-33.82</v>
       </c>
       <c r="J46" s="3">
-        <v>-0.010102064440776522</v>
+        <v>-0.010403586090275453</v>
       </c>
       <c r="K46" s="3" t="b">
         <v>1</v>
@@ -4941,28 +4938,28 @@
         <v>17</v>
       </c>
       <c r="M46" s="3">
-        <v>-0.2931946894252704</v>
+        <v>-0.2837435416219314</v>
       </c>
       <c r="N46" s="3">
-        <v>-22.82102070818473</v>
+        <v>-21.497922087850995</v>
       </c>
       <c r="O46" s="3">
-        <v>5.88235294117647</v>
+        <v>10.588235294117647</v>
       </c>
       <c r="P46" s="3">
         <v>54.33673655574689</v>
       </c>
       <c r="Q46" s="3">
-        <v>42.11764705882352</v>
+        <v>41.6470588235294</v>
       </c>
       <c r="R46" s="3">
-        <v>24.29411764705882</v>
+        <v>25.823529411764703</v>
       </c>
       <c r="S46" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T46" s="3">
-        <v>3.26</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
@@ -4982,19 +4979,19 @@
         <v>2.57</v>
       </c>
       <c r="F47" s="1">
-        <v>0.08195431159315396</v>
+        <v>0.10384106899887256</v>
       </c>
       <c r="G47" s="1">
         <v>1.42</v>
       </c>
       <c r="H47" s="1">
-        <v>47.74</v>
+        <v>48.74</v>
       </c>
       <c r="I47" s="1">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J47" s="1">
-        <v>0.018669269883780492</v>
+        <v>0.019236496462337747</v>
       </c>
       <c r="K47" s="1" t="b">
         <v>1</v>
@@ -5003,28 +5000,28 @@
         <v>-56</v>
       </c>
       <c r="M47" s="1">
-        <v>0.10473279417739167</v>
+        <v>0.12820708371110956</v>
       </c>
       <c r="N47" s="1">
-        <v>16.97172765208148</v>
+        <v>19.697140445453098</v>
       </c>
       <c r="O47" s="1">
-        <v>71.76470588235294</v>
+        <v>75.29411764705883</v>
       </c>
       <c r="P47" s="1">
-        <v>30.777935412994907</v>
+        <v>28.98612413886803</v>
       </c>
       <c r="Q47" s="1">
-        <v>52.58823529411765</v>
+        <v>52.11764705882353</v>
       </c>
       <c r="R47" s="1">
-        <v>45.352941176470594</v>
+        <v>47.00000000000001</v>
       </c>
       <c r="S47" s="1" t="s">
         <v>109</v>
       </c>
       <c r="T47" s="1">
-        <v>19.5</v>
+        <v>21.15</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
@@ -5044,19 +5041,19 @@
         <v>0.66</v>
       </c>
       <c r="F48" s="2">
-        <v>0.15637147879667657</v>
+        <v>0.16764111920633198</v>
       </c>
       <c r="G48" s="2">
         <v>1.61</v>
       </c>
       <c r="H48" s="2">
-        <v>57.25</v>
+        <v>62.26</v>
       </c>
       <c r="I48" s="2">
-        <v>29.52</v>
+        <v>33.39</v>
       </c>
       <c r="J48" s="2">
-        <v>0.011279799840354104</v>
+        <v>0.01039140142014387</v>
       </c>
       <c r="K48" s="2" t="b">
         <v>1</v>
@@ -5065,28 +5062,28 @@
         <v>243</v>
       </c>
       <c r="M48" s="2">
-        <v>0.18945451302616467</v>
+        <v>0.20302985485981906</v>
       </c>
       <c r="N48" s="2">
-        <v>25.443899536958774</v>
+        <v>27.179417560324055</v>
       </c>
       <c r="O48" s="2">
-        <v>82.35294117647058</v>
+        <v>81.17647058823529</v>
       </c>
       <c r="P48" s="2">
         <v>21.006318468965095</v>
       </c>
       <c r="Q48" s="2">
-        <v>64.58823529411765</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="R48" s="2">
-        <v>56.588235294117645</v>
+        <v>55.764705882352935</v>
       </c>
       <c r="S48" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T48" s="2">
-        <v>7.32</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
@@ -5106,19 +5103,19 @@
         <v>-11.2</v>
       </c>
       <c r="F49" s="2">
-        <v>0.09844711598854143</v>
+        <v>0.1777465237878837</v>
       </c>
       <c r="G49" s="2">
         <v>1.08</v>
       </c>
       <c r="H49" s="2">
-        <v>43.77</v>
+        <v>49.21</v>
       </c>
       <c r="I49" s="2">
-        <v>-8.35</v>
+        <v>-4.2</v>
       </c>
       <c r="J49" s="2">
-        <v>0.01726551784734589</v>
+        <v>0.015841661575346045</v>
       </c>
       <c r="K49" s="2" t="b">
         <v>0</v>
@@ -5127,28 +5124,28 @@
         <v>-7</v>
       </c>
       <c r="M49" s="2">
-        <v>0.10278587457601529</v>
+        <v>0.1823876694473574</v>
       </c>
       <c r="N49" s="2">
-        <v>16.777035691943844</v>
+        <v>25.115199019077885</v>
       </c>
       <c r="O49" s="2">
-        <v>70.58823529411765</v>
+        <v>78.82352941176471</v>
       </c>
       <c r="P49" s="2">
         <v>31.00158698078384</v>
       </c>
       <c r="Q49" s="2">
-        <v>60.94117647058823</v>
+        <v>62.58823529411765</v>
       </c>
       <c r="R49" s="2">
-        <v>54.47058823529412</v>
+        <v>56.94117647058824</v>
       </c>
       <c r="S49" s="2" t="s">
         <v>102</v>
       </c>
       <c r="T49" s="2">
-        <v>23.37</v>
+        <v>25.84</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
@@ -5168,19 +5165,19 @@
         <v>12.86</v>
       </c>
       <c r="F50" s="3">
-        <v>-0.32806768601339753</v>
+        <v>-0.3349742461151789</v>
       </c>
       <c r="G50" s="3">
         <v>3.84</v>
       </c>
       <c r="H50" s="3">
-        <v>56.63</v>
+        <v>57.15</v>
       </c>
       <c r="I50" s="3">
-        <v>13.32</v>
+        <v>14.02</v>
       </c>
       <c r="J50" s="3">
-        <v>0.012732253681764958</v>
+        <v>0.01144684524259245</v>
       </c>
       <c r="K50" s="3" t="b">
         <v>0</v>
@@ -5189,22 +5186,22 @@
         <v>69</v>
       </c>
       <c r="M50" s="3">
-        <v>-0.17404175615807582</v>
+        <v>-0.17021357520386204</v>
       </c>
       <c r="N50" s="3">
-        <v>-10.905727381465272</v>
+        <v>-10.144925446044057</v>
       </c>
       <c r="O50" s="3">
-        <v>22.35294117647059</v>
+        <v>23.52941176470588</v>
       </c>
       <c r="P50" s="3">
         <v>41.201484669672254</v>
       </c>
       <c r="Q50" s="3">
-        <v>54.705882352941174</v>
+        <v>53.05882352941177</v>
       </c>
       <c r="R50" s="3">
-        <v>27.411764705882355</v>
+        <v>26.941176470588232</v>
       </c>
       <c r="S50" s="3" t="s">
         <v>108</v>
@@ -5228,19 +5225,19 @@
         <v>14.41</v>
       </c>
       <c r="F51" s="1">
-        <v>0.25314923951320245</v>
+        <v>0.4958835886672298</v>
       </c>
       <c r="G51" s="1">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="H51" s="1">
-        <v>58.76</v>
+        <v>57.14</v>
       </c>
       <c r="I51" s="1">
-        <v>39.64</v>
+        <v>37.06</v>
       </c>
       <c r="J51" s="1">
-        <v>0.05856227101337115</v>
+        <v>0.05673892083394905</v>
       </c>
       <c r="K51" s="1" t="b">
         <v>0</v>
@@ -5249,22 +5246,22 @@
         <v>14</v>
       </c>
       <c r="M51" s="1">
-        <v>0.29436744609420407</v>
+        <v>0.5405546156396643</v>
       </c>
       <c r="N51" s="1">
-        <v>35.93519284376273</v>
+        <v>60.93189363830859</v>
       </c>
       <c r="O51" s="1">
-        <v>84.70588235294117</v>
+        <v>92.94117647058823</v>
       </c>
       <c r="P51" s="1">
         <v>38.38748944617691</v>
       </c>
       <c r="Q51" s="1">
-        <v>54.470588235294116</v>
+        <v>53.29411764705882</v>
       </c>
       <c r="R51" s="1">
-        <v>42.76470588235294</v>
+        <v>45.117647058823536</v>
       </c>
       <c r="S51" s="1" t="s">
         <v>97</v>
@@ -5288,19 +5285,19 @@
         <v>-5.32</v>
       </c>
       <c r="F52" s="3">
-        <v>-0.1556909455488903</v>
+        <v>-0.15652891797290508</v>
       </c>
       <c r="G52" s="3">
         <v>0.91</v>
       </c>
       <c r="H52" s="3">
-        <v>42.56</v>
+        <v>42.69</v>
       </c>
       <c r="I52" s="3">
-        <v>-31.08</v>
+        <v>-30.88</v>
       </c>
       <c r="J52" s="3">
-        <v>-0.014176342869726724</v>
+        <v>-0.014479006768678072</v>
       </c>
       <c r="K52" s="3" t="b">
         <v>0</v>
@@ -5309,22 +5306,22 @@
         <v>-110</v>
       </c>
       <c r="M52" s="3">
-        <v>-0.16057204895979837</v>
+        <v>-0.161750206839813</v>
       </c>
       <c r="N52" s="3">
-        <v>-9.558756661637522</v>
+        <v>-9.298588609639154</v>
       </c>
       <c r="O52" s="3">
-        <v>24.705882352941178</v>
+        <v>29.411764705882355</v>
       </c>
       <c r="P52" s="3">
-        <v>34.68082090497681</v>
+        <v>32.59357836340351</v>
       </c>
       <c r="Q52" s="3">
-        <v>34</v>
+        <v>33.17647058823529</v>
       </c>
       <c r="R52" s="3">
-        <v>24.117647058823533</v>
+        <v>25.58823529411765</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>114</v>
@@ -5348,19 +5345,19 @@
         <v>-0.87</v>
       </c>
       <c r="F53" s="3">
-        <v>-0.05073960103705262</v>
+        <v>-0.0432336681091708</v>
       </c>
       <c r="G53" s="3">
         <v>0</v>
       </c>
       <c r="H53" s="3">
-        <v>52.32</v>
+        <v>53.15</v>
       </c>
       <c r="I53" s="3">
-        <v>3.52</v>
+        <v>4.07</v>
       </c>
       <c r="J53" s="3">
-        <v>0.00616712984089757</v>
+        <v>0.007089722614657735</v>
       </c>
       <c r="K53" s="3" t="b">
         <v>1</v>
@@ -5369,22 +5366,22 @@
         <v>1748</v>
       </c>
       <c r="M53" s="3">
-        <v>-0.10497408338047576</v>
+        <v>-0.10124798885259223</v>
       </c>
       <c r="N53" s="3">
-        <v>-3.9989601037052673</v>
+        <v>-3.2483668109170747</v>
       </c>
       <c r="O53" s="3">
-        <v>36.470588235294116</v>
+        <v>37.64705882352941</v>
       </c>
       <c r="P53" s="3">
         <v>48.781873808753</v>
       </c>
       <c r="Q53" s="3">
-        <v>39.294117647058826</v>
+        <v>40.117647058823536</v>
       </c>
       <c r="R53" s="3">
-        <v>22.058823529411768</v>
+        <v>22.88235294117647</v>
       </c>
       <c r="S53" s="3" t="s">
         <v>96</v>
@@ -5402,25 +5399,25 @@
         <v>61.1764705882353</v>
       </c>
       <c r="D54" s="1">
-        <v>0.788632326820604</v>
+        <v>0.8348134991119006</v>
       </c>
       <c r="E54" s="1">
         <v>-1.38</v>
       </c>
       <c r="F54" s="1">
-        <v>-0.011625899312348711</v>
+        <v>-0.05789997444780892</v>
       </c>
       <c r="G54" s="1">
         <v>0.98</v>
       </c>
       <c r="H54" s="1">
-        <v>51.46</v>
+        <v>49.19</v>
       </c>
       <c r="I54" s="1">
-        <v>5.85</v>
+        <v>5.07</v>
       </c>
       <c r="J54" s="1">
-        <v>0.00526224159782243</v>
+        <v>0.005991652206331156</v>
       </c>
       <c r="K54" s="1" t="b">
         <v>0</v>
@@ -5429,28 +5426,28 @@
         <v>85</v>
       </c>
       <c r="M54" s="1">
-        <v>-0.012710588959217173</v>
+        <v>-0.05906026086267735</v>
       </c>
       <c r="N54" s="1">
-        <v>5.227389338420602</v>
+        <v>0.970405988074398</v>
       </c>
       <c r="O54" s="1">
-        <v>57.647058823529406</v>
+        <v>48.23529411764706</v>
       </c>
       <c r="P54" s="1">
         <v>11.84024085938085</v>
       </c>
       <c r="Q54" s="1">
-        <v>53.05882352941176</v>
+        <v>52.47058823529412</v>
       </c>
       <c r="R54" s="1">
-        <v>47.529411764705884</v>
+        <v>45.117647058823536</v>
       </c>
       <c r="S54" s="1" t="s">
         <v>115</v>
       </c>
       <c r="T54" s="1">
-        <v>7.1</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
@@ -5470,31 +5467,31 @@
         <v>0.67</v>
       </c>
       <c r="F55" s="3">
-        <v>-0.27141810180094517</v>
+        <v>-0.2926685570723293</v>
       </c>
       <c r="G55" s="3">
         <v>1.58</v>
       </c>
       <c r="H55" s="3">
-        <v>47.65</v>
+        <v>49.39</v>
       </c>
       <c r="I55" s="3">
-        <v>2.48</v>
+        <v>2.92</v>
       </c>
       <c r="J55" s="3">
-        <v>-0.01629632521473801</v>
+        <v>-0.015663846084244742</v>
       </c>
       <c r="K55" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" s="3">
         <v>349</v>
       </c>
       <c r="M55" s="3">
-        <v>-0.23996210204175972</v>
+        <v>-0.2590202510411449</v>
       </c>
       <c r="N55" s="3">
-        <v>-17.49776196983366</v>
+        <v>-19.025593029772352</v>
       </c>
       <c r="O55" s="3">
         <v>12.941176470588237</v>
@@ -5503,16 +5500,16 @@
         <v>26.83257063748809</v>
       </c>
       <c r="Q55" s="3">
-        <v>47.29411764705881</v>
+        <v>47.41176470588235</v>
       </c>
       <c r="R55" s="3">
-        <v>29.235294117647058</v>
+        <v>28.94117647058824</v>
       </c>
       <c r="S55" s="3" t="s">
         <v>96</v>
       </c>
       <c r="T55" s="3">
-        <v>-29.36</v>
+        <v>-29.66</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
@@ -5532,19 +5529,19 @@
         <v>1.76</v>
       </c>
       <c r="F56" s="1">
-        <v>-0.37319162494732894</v>
+        <v>-0.36876182805844937</v>
       </c>
       <c r="G56" s="1">
         <v>3.8</v>
       </c>
       <c r="H56" s="1">
-        <v>57.38</v>
+        <v>58.53</v>
       </c>
       <c r="I56" s="1">
-        <v>33.36</v>
+        <v>34.91</v>
       </c>
       <c r="J56" s="1">
-        <v>0.01229850390500414</v>
+        <v>0.012340627616071714</v>
       </c>
       <c r="K56" s="1" t="b">
         <v>1</v>
@@ -5553,19 +5550,19 @@
         <v>322</v>
       </c>
       <c r="M56" s="1">
-        <v>-0.22133507438574418</v>
+        <v>-0.20632172997686937</v>
       </c>
       <c r="N56" s="1">
-        <v>-15.6350592042321</v>
+        <v>-13.755740923344792</v>
       </c>
       <c r="O56" s="1">
-        <v>16.470588235294116</v>
+        <v>17.647058823529413</v>
       </c>
       <c r="P56" s="1">
         <v>52.65288503392759</v>
       </c>
       <c r="Q56" s="1">
-        <v>69.29411764705883</v>
+        <v>68.58823529411765</v>
       </c>
       <c r="R56" s="1">
         <v>35.05882352941177</v>
@@ -5588,25 +5585,25 @@
         <v>56.470588235294116</v>
       </c>
       <c r="D57" s="3">
-        <v>7.153846153846153</v>
+        <v>7.285067873303166</v>
       </c>
       <c r="E57" s="3">
         <v>-1.31</v>
       </c>
       <c r="F57" s="3">
-        <v>-0.339847777710406</v>
+        <v>-0.35388823959998345</v>
       </c>
       <c r="G57" s="3">
         <v>2.04</v>
       </c>
       <c r="H57" s="3">
-        <v>43.47</v>
+        <v>46.91</v>
       </c>
       <c r="I57" s="3">
-        <v>-6.61</v>
+        <v>-4.36</v>
       </c>
       <c r="J57" s="3">
-        <v>-0.024809220487229364</v>
+        <v>-0.024353914485329434</v>
       </c>
       <c r="K57" s="3" t="b">
         <v>0</v>
@@ -5615,28 +5612,28 @@
         <v>250</v>
       </c>
       <c r="M57" s="3">
-        <v>-0.2834439160732459</v>
+        <v>-0.29355334602682515</v>
       </c>
       <c r="N57" s="3">
-        <v>-21.84594337298228</v>
+        <v>-22.47890252834037</v>
       </c>
       <c r="O57" s="3">
-        <v>7.0588235294117645</v>
+        <v>8.235294117647058</v>
       </c>
       <c r="P57" s="3">
         <v>40.717118046641446</v>
       </c>
       <c r="Q57" s="3">
-        <v>43.88235294117648</v>
+        <v>44.352941176470594</v>
       </c>
       <c r="R57" s="3">
-        <v>24.588235294117645</v>
+        <v>24.941176470588232</v>
       </c>
       <c r="S57" s="3" t="s">
         <v>110</v>
       </c>
       <c r="T57" s="3">
-        <v>-24.38</v>
+        <v>-24.02</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
@@ -5656,19 +5653,19 @@
         <v>1.26</v>
       </c>
       <c r="F58" s="1">
-        <v>-0.07314590368359956</v>
+        <v>-0.04339343945308263</v>
       </c>
       <c r="G58" s="1">
         <v>1.64</v>
       </c>
       <c r="H58" s="1">
-        <v>41.11</v>
+        <v>43.24</v>
       </c>
       <c r="I58" s="1">
-        <v>-19.65</v>
+        <v>-18.42</v>
       </c>
       <c r="J58" s="1">
-        <v>0.010654820733857415</v>
+        <v>0.013127827314443964</v>
       </c>
       <c r="K58" s="1" t="b">
         <v>1</v>
@@ -5677,28 +5674,28 @@
         <v>3</v>
       </c>
       <c r="M58" s="1">
-        <v>-0.03843583498380876</v>
+        <v>-0.006264274177292917</v>
       </c>
       <c r="N58" s="1">
-        <v>2.6548647359614446</v>
+        <v>6.2500046566128535</v>
       </c>
       <c r="O58" s="1">
-        <v>52.94117647058824</v>
+        <v>60</v>
       </c>
       <c r="P58" s="1">
         <v>33.706290307642504</v>
       </c>
       <c r="Q58" s="1">
-        <v>55.1764705882353</v>
+        <v>56.23529411764706</v>
       </c>
       <c r="R58" s="1">
-        <v>46.35294117647059</v>
+        <v>48.94117647058823</v>
       </c>
       <c r="S58" s="1" t="s">
         <v>103</v>
       </c>
       <c r="T58" s="1">
-        <v>24.4</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
@@ -5712,25 +5709,25 @@
         <v>64.70588235294117</v>
       </c>
       <c r="D59" s="3">
-        <v>3.416666666666667</v>
+        <v>3.456597222222223</v>
       </c>
       <c r="E59" s="3">
         <v>0.97</v>
       </c>
       <c r="F59" s="3">
-        <v>-0.2917755267339034</v>
+        <v>-0.35423476095856316</v>
       </c>
       <c r="G59" s="3">
         <v>1.86</v>
       </c>
       <c r="H59" s="3">
-        <v>50.68</v>
+        <v>55.3</v>
       </c>
       <c r="I59" s="3">
-        <v>11.79</v>
+        <v>15.51</v>
       </c>
       <c r="J59" s="3">
-        <v>-0.015145886610036194</v>
+        <v>-0.01290389685791354</v>
       </c>
       <c r="K59" s="3" t="b">
         <v>1</v>
@@ -5739,28 +5736,28 @@
         <v>520</v>
       </c>
       <c r="M59" s="3">
-        <v>-0.2451338719185595</v>
+        <v>-0.3043424451192207</v>
       </c>
       <c r="N59" s="3">
-        <v>-18.014938957513635</v>
+        <v>-23.557812437579926</v>
       </c>
       <c r="O59" s="3">
-        <v>11.76470588235294</v>
+        <v>7.0588235294117645</v>
       </c>
       <c r="P59" s="3">
         <v>41.76493344029593</v>
       </c>
       <c r="Q59" s="3">
-        <v>50.94117647058824</v>
+        <v>52.82352941176471</v>
       </c>
       <c r="R59" s="3">
-        <v>26.70588235294118</v>
+        <v>25.529411764705884</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>110</v>
       </c>
       <c r="T59" s="3">
-        <v>-32.5</v>
+        <v>-33.68</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.25">
@@ -5780,19 +5777,19 @@
         <v>-4.45</v>
       </c>
       <c r="F60" s="3">
-        <v>-0.4746268538055761</v>
+        <v>-0.48208340597451393</v>
       </c>
       <c r="G60" s="3">
         <v>2.83</v>
       </c>
       <c r="H60" s="3">
-        <v>35.66</v>
+        <v>38.72</v>
       </c>
       <c r="I60" s="3">
-        <v>-34.99</v>
+        <v>-33.6</v>
       </c>
       <c r="J60" s="3">
-        <v>-0.02643302661710694</v>
+        <v>-0.026673924128155363</v>
       </c>
       <c r="K60" s="3" t="b">
         <v>0</v>
@@ -5801,28 +5798,28 @@
         <v>21</v>
       </c>
       <c r="M60" s="3">
-        <v>-0.3753777511171118</v>
+        <v>-0.37591719901405274</v>
       </c>
       <c r="N60" s="3">
-        <v>-31.039326877368868</v>
+        <v>-30.715287827063136</v>
       </c>
       <c r="O60" s="3">
-        <v>3.5294117647058822</v>
+        <v>2.3529411764705883</v>
       </c>
       <c r="P60" s="3">
         <v>46.90217032437056</v>
       </c>
       <c r="Q60" s="3">
-        <v>24.11764705882353</v>
+        <v>24.823529411764703</v>
       </c>
       <c r="R60" s="3">
-        <v>10.64705882352941</v>
+        <v>10.294117647058819</v>
       </c>
       <c r="S60" s="3" t="s">
         <v>98</v>
       </c>
       <c r="T60" s="3">
-        <v>-16.24</v>
+        <v>-16.6</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
@@ -5836,25 +5833,25 @@
         <v>55.294117647058826</v>
       </c>
       <c r="D61" s="1">
-        <v>2.1747126436781614</v>
+        <v>2.23448275862069</v>
       </c>
       <c r="E61" s="1">
         <v>-0.52</v>
       </c>
       <c r="F61" s="1">
-        <v>-0.10634080411283578</v>
+        <v>-0.1180671063842687</v>
       </c>
       <c r="G61" s="1">
         <v>1.21</v>
       </c>
       <c r="H61" s="1">
-        <v>25.28</v>
+        <v>26.5</v>
       </c>
       <c r="I61" s="1">
-        <v>1.37</v>
+        <v>1.59</v>
       </c>
       <c r="J61" s="1">
-        <v>-0.003637125376053656</v>
+        <v>-0.005392966599319305</v>
       </c>
       <c r="K61" s="1" t="b">
         <v>0</v>
@@ -5863,28 +5860,28 @@
         <v>170</v>
       </c>
       <c r="M61" s="1">
-        <v>-0.09495156282071693</v>
+        <v>-0.10588409902815021</v>
       </c>
       <c r="N61" s="1">
-        <v>-2.9967080477293764</v>
+        <v>-3.7119778284728775</v>
       </c>
       <c r="O61" s="1">
-        <v>37.64705882352941</v>
+        <v>36.470588235294116</v>
       </c>
       <c r="P61" s="1">
         <v>13.593577982515374</v>
       </c>
       <c r="Q61" s="1">
-        <v>43.1764705882353</v>
+        <v>42.35294117647059</v>
       </c>
       <c r="R61" s="1">
-        <v>39.70588235294118</v>
+        <v>39.00000000000001</v>
       </c>
       <c r="S61" s="1" t="s">
         <v>116</v>
       </c>
       <c r="T61" s="1">
-        <v>-7.49</v>
+        <v>-8.2</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
@@ -5904,19 +5901,19 @@
         <v>0.11</v>
       </c>
       <c r="F62" s="2">
-        <v>0.10426060464486614</v>
+        <v>0.1008006324313209</v>
       </c>
       <c r="G62" s="2">
         <v>0.2</v>
       </c>
       <c r="H62" s="2">
-        <v>52.07</v>
+        <v>56.2</v>
       </c>
       <c r="I62" s="2">
-        <v>11.96</v>
+        <v>12.72</v>
       </c>
       <c r="J62" s="2">
-        <v>0.0031673648005258437</v>
+        <v>0.004444487842905838</v>
       </c>
       <c r="K62" s="2" t="b">
         <v>1</v>
@@ -5925,10 +5922,10 @@
         <v>93</v>
       </c>
       <c r="M62" s="2">
-        <v>0.06087301877012763</v>
+        <v>0.05438917583658376</v>
       </c>
       <c r="N62" s="2">
-        <v>12.585750111355079</v>
+        <v>12.315349658000518</v>
       </c>
       <c r="O62" s="2">
         <v>63.52941176470588</v>
@@ -5937,16 +5934,16 @@
         <v>7.56622762341097</v>
       </c>
       <c r="Q62" s="2">
-        <v>55.05882352941176</v>
+        <v>55.88235294117647</v>
       </c>
       <c r="R62" s="2">
-        <v>50.94117647058823</v>
+        <v>51.05882352941177</v>
       </c>
       <c r="S62" s="2" t="s">
         <v>101</v>
       </c>
       <c r="T62" s="2">
-        <v>4.97</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
@@ -5960,25 +5957,25 @@
         <v>98.82352941176471</v>
       </c>
       <c r="D63" s="1">
-        <v>1.5863708399366083</v>
+        <v>1.5961059542676024</v>
       </c>
       <c r="E63" s="1">
         <v>-1.09</v>
       </c>
       <c r="F63" s="1">
-        <v>-0.10940412880479819</v>
+        <v>-0.24974158560379423</v>
       </c>
       <c r="G63" s="1">
         <v>2.23</v>
       </c>
       <c r="H63" s="1">
-        <v>59.82</v>
+        <v>64.62</v>
       </c>
       <c r="I63" s="1">
-        <v>60.87</v>
+        <v>65.92</v>
       </c>
       <c r="J63" s="1">
-        <v>0.007891169951779037</v>
+        <v>0.01107044650714059</v>
       </c>
       <c r="K63" s="1" t="b">
         <v>0</v>
@@ -5987,28 +5984,28 @@
         <v>936</v>
       </c>
       <c r="M63" s="1">
-        <v>-0.04269571552238771</v>
+        <v>-0.17838397108938586</v>
       </c>
       <c r="N63" s="1">
-        <v>2.2288766821035337</v>
+        <v>-10.961965034596446</v>
       </c>
       <c r="O63" s="1">
-        <v>50.588235294117645</v>
+        <v>22.35294117647059</v>
       </c>
       <c r="P63" s="1">
         <v>39.10478556320163</v>
       </c>
       <c r="Q63" s="1">
-        <v>73.17647058823529</v>
+        <v>76</v>
       </c>
       <c r="R63" s="1">
-        <v>49.882352941176464</v>
+        <v>42.23529411764706</v>
       </c>
       <c r="S63" s="1" t="s">
         <v>117</v>
       </c>
       <c r="T63" s="1">
-        <v>-18.23</v>
+        <v>-25.87</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.25">
@@ -6028,19 +6025,19 @@
         <v>1.52</v>
       </c>
       <c r="F64" s="1">
-        <v>-0.1437068021735461</v>
+        <v>-0.16404090432788793</v>
       </c>
       <c r="G64" s="1">
         <v>0.97</v>
       </c>
       <c r="H64" s="1">
-        <v>48.77</v>
+        <v>52.29</v>
       </c>
       <c r="I64" s="1">
-        <v>3.68</v>
+        <v>5.47</v>
       </c>
       <c r="J64" s="1">
-        <v>-0.013487697999865201</v>
+        <v>-0.012699741311393006</v>
       </c>
       <c r="K64" s="1" t="b">
         <v>1</v>
@@ -6049,90 +6046,90 @@
         <v>366</v>
       </c>
       <c r="M64" s="1">
-        <v>-0.1453338366438488</v>
+        <v>-0.16578133395019057</v>
       </c>
       <c r="N64" s="1">
-        <v>-8.034935430042568</v>
+        <v>-9.701701320676909</v>
       </c>
       <c r="O64" s="1">
-        <v>29.411764705882355</v>
+        <v>28.235294117647058</v>
       </c>
       <c r="P64" s="1">
         <v>25.543467249515373</v>
       </c>
       <c r="Q64" s="1">
-        <v>46.58823529411765</v>
+        <v>47.88235294117647</v>
       </c>
       <c r="R64" s="1">
-        <v>32.882352941176464</v>
+        <v>32.647058823529406</v>
       </c>
       <c r="S64" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T64" s="1">
-        <v>-11.87</v>
+        <v>-12.11</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
+      <c r="A65" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B65" s="1">
+      <c r="B65" s="3">
         <v>7.62</v>
       </c>
-      <c r="C65" s="1">
+      <c r="C65" s="3">
         <v>65.88235294117646</v>
       </c>
-      <c r="D65" s="1">
-        <v>-0.39107611548556437</v>
-      </c>
-      <c r="E65" s="1">
+      <c r="D65" s="3">
+        <v>-0.39370078740157477</v>
+      </c>
+      <c r="E65" s="3">
         <v>0.4</v>
       </c>
-      <c r="F65" s="1">
-        <v>-0.11383661090491344</v>
-      </c>
-      <c r="G65" s="1">
+      <c r="F65" s="3">
+        <v>-0.13088313432433693</v>
+      </c>
+      <c r="G65" s="3">
         <v>0.36</v>
       </c>
-      <c r="H65" s="1">
-        <v>30.07</v>
-      </c>
-      <c r="I65" s="1">
-        <v>-12.06</v>
-      </c>
-      <c r="J65" s="1">
-        <v>-0.006280424808417941</v>
-      </c>
-      <c r="K65" s="1" t="b">
+      <c r="H65" s="3">
+        <v>26.27</v>
+      </c>
+      <c r="I65" s="3">
+        <v>-13.5</v>
+      </c>
+      <c r="J65" s="3">
+        <v>-0.005809294569099313</v>
+      </c>
+      <c r="K65" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L65" s="1">
+      <c r="L65" s="3">
         <v>-101</v>
       </c>
-      <c r="M65" s="1">
-        <v>-0.14854667960470425</v>
-      </c>
-      <c r="N65" s="1">
-        <v>-8.356219726128106</v>
-      </c>
-      <c r="O65" s="1">
-        <v>28.235294117647058</v>
-      </c>
-      <c r="P65" s="1">
-        <v>18.234594077618315</v>
-      </c>
-      <c r="Q65" s="1">
-        <v>34.588235294117645</v>
-      </c>
-      <c r="R65" s="1">
-        <v>30.58823529411765</v>
-      </c>
-      <c r="S65" s="1" t="s">
+      <c r="M65" s="3">
+        <v>-0.16801229960012665</v>
+      </c>
+      <c r="N65" s="3">
+        <v>-9.92479788567052</v>
+      </c>
+      <c r="O65" s="3">
+        <v>25.882352941176475</v>
+      </c>
+      <c r="P65" s="3">
+        <v>19.1431702600252</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>34.470588235294116</v>
+      </c>
+      <c r="R65" s="3">
+        <v>29.64705882352941</v>
+      </c>
+      <c r="S65" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="T65" s="1">
-        <v>4.55</v>
+      <c r="T65" s="3">
+        <v>3.61</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
@@ -6146,25 +6143,25 @@
         <v>89.41176470588236</v>
       </c>
       <c r="D66" s="2">
-        <v>0.3379655364091163</v>
+        <v>0.38021122846025573</v>
       </c>
       <c r="E66" s="2">
         <v>2.08</v>
       </c>
       <c r="F66" s="2">
-        <v>0.14063338479640128</v>
+        <v>0.0955648941640535</v>
       </c>
       <c r="G66" s="2">
         <v>0.87</v>
       </c>
       <c r="H66" s="2">
-        <v>65.86</v>
+        <v>61.01</v>
       </c>
       <c r="I66" s="2">
-        <v>21.31</v>
+        <v>19.46</v>
       </c>
       <c r="J66" s="2">
-        <v>0.014957079449734328</v>
+        <v>0.016351955787534254</v>
       </c>
       <c r="K66" s="2" t="b">
         <v>0</v>
@@ -6173,90 +6170,90 @@
         <v>80</v>
       </c>
       <c r="M66" s="2">
-        <v>0.13358290209175627</v>
+        <v>0.08802303246740872</v>
       </c>
       <c r="N66" s="2">
-        <v>19.85673844351794</v>
+        <v>15.678735321083021</v>
       </c>
       <c r="O66" s="2">
-        <v>75.29411764705883</v>
+        <v>67.05882352941175</v>
       </c>
       <c r="P66" s="2">
         <v>10.56723987277981</v>
       </c>
       <c r="Q66" s="2">
-        <v>70.94117647058823</v>
+        <v>70.11764705882352</v>
       </c>
       <c r="R66" s="2">
-        <v>61.58823529411765</v>
+        <v>59.52941176470588</v>
       </c>
       <c r="S66" s="2" t="s">
         <v>119</v>
       </c>
       <c r="T66" s="2">
-        <v>17.99</v>
+        <v>15.93</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
+      <c r="A67" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B67" s="1">
+      <c r="B67" s="3">
         <v>72.89</v>
       </c>
-      <c r="C67" s="1">
+      <c r="C67" s="3">
         <v>100</v>
       </c>
-      <c r="D67" s="1">
+      <c r="D67" s="3">
         <v>-0.6876114693373577</v>
       </c>
-      <c r="E67" s="1">
+      <c r="E67" s="3">
         <v>1.69</v>
       </c>
-      <c r="F67" s="1">
-        <v>-0.34390122875127477</v>
-      </c>
-      <c r="G67" s="1">
-        <v>5.2</v>
-      </c>
-      <c r="H67" s="1">
-        <v>57.64</v>
-      </c>
-      <c r="I67" s="1">
-        <v>61.62</v>
-      </c>
-      <c r="J67" s="1">
-        <v>-0.0007520970444974813</v>
-      </c>
-      <c r="K67" s="1" t="b">
+      <c r="F67" s="3">
+        <v>-0.5625697670784382</v>
+      </c>
+      <c r="G67" s="3">
+        <v>5.22</v>
+      </c>
+      <c r="H67" s="3">
+        <v>58.2</v>
+      </c>
+      <c r="I67" s="3">
+        <v>62.22</v>
+      </c>
+      <c r="J67" s="3">
+        <v>0.002586596388619295</v>
+      </c>
+      <c r="K67" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L67" s="1">
+      <c r="L67" s="3">
         <v>667</v>
       </c>
-      <c r="M67" s="1">
-        <v>-0.11611640290889758</v>
-      </c>
-      <c r="N67" s="1">
-        <v>-5.113192056547441</v>
-      </c>
-      <c r="O67" s="1">
-        <v>34.11764705882353</v>
-      </c>
-      <c r="P67" s="1">
+      <c r="M67" s="3">
+        <v>-0.31774933354119983</v>
+      </c>
+      <c r="N67" s="3">
+        <v>-24.898501279777836</v>
+      </c>
+      <c r="O67" s="3">
+        <v>5.88235294117647</v>
+      </c>
+      <c r="P67" s="3">
         <v>56.49293299150161</v>
       </c>
-      <c r="Q67" s="1">
-        <v>61.1764705882353</v>
-      </c>
-      <c r="R67" s="1">
-        <v>34.05882352941176</v>
-      </c>
-      <c r="S67" s="1" t="s">
+      <c r="Q67" s="3">
+        <v>60.82352941176471</v>
+      </c>
+      <c r="R67" s="3">
+        <v>25.647058823529413</v>
+      </c>
+      <c r="S67" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="T67" s="1">
-        <v>-35.33</v>
+      <c r="T67" s="3">
+        <v>-43.74</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
@@ -6270,25 +6267,25 @@
         <v>83.52941176470588</v>
       </c>
       <c r="D68" s="1">
-        <v>3.1405912040374915</v>
+        <v>3.1600576784426826</v>
       </c>
       <c r="E68" s="1">
         <v>-2.41</v>
       </c>
       <c r="F68" s="1">
-        <v>-0.2345671284820057</v>
+        <v>-0.21992343107345258</v>
       </c>
       <c r="G68" s="1">
         <v>2.09</v>
       </c>
       <c r="H68" s="1">
-        <v>57.39</v>
+        <v>58.82</v>
       </c>
       <c r="I68" s="1">
-        <v>43.49</v>
+        <v>44.74</v>
       </c>
       <c r="J68" s="1">
-        <v>-0.0024222637003197605</v>
+        <v>-0.0007192091735043825</v>
       </c>
       <c r="K68" s="1" t="b">
         <v>1</v>
@@ -6297,28 +6294,28 @@
         <v>514</v>
       </c>
       <c r="M68" s="1">
-        <v>-0.1754515427276745</v>
+        <v>-0.1566878214631232</v>
       </c>
       <c r="N68" s="1">
-        <v>-11.046706038425134</v>
+        <v>-8.792350071970173</v>
       </c>
       <c r="O68" s="1">
-        <v>21.176470588235293</v>
+        <v>30.58823529411765</v>
       </c>
       <c r="P68" s="1">
         <v>31.85898471566022</v>
       </c>
       <c r="Q68" s="1">
-        <v>65.88235294117648</v>
+        <v>66.3529411764706</v>
       </c>
       <c r="R68" s="1">
-        <v>38.05882352941177</v>
+        <v>41.117647058823536</v>
       </c>
       <c r="S68" s="1" t="s">
         <v>111</v>
       </c>
       <c r="T68" s="1">
-        <v>-27.98</v>
+        <v>-24.92</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
@@ -6332,25 +6329,25 @@
         <v>85.88235294117646</v>
       </c>
       <c r="D69" s="1">
-        <v>-0.18969696969696975</v>
+        <v>-0.15878787878787873</v>
       </c>
       <c r="E69" s="1">
         <v>-1.74</v>
       </c>
       <c r="F69" s="1">
-        <v>0.04697038470444885</v>
+        <v>-0.011984213959823409</v>
       </c>
       <c r="G69" s="1">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="H69" s="1">
-        <v>32.56</v>
+        <v>29.51</v>
       </c>
       <c r="I69" s="1">
-        <v>-29.41</v>
+        <v>-31.69</v>
       </c>
       <c r="J69" s="1">
-        <v>0.008317740820796147</v>
+        <v>0.0056815149485858075</v>
       </c>
       <c r="K69" s="1" t="b">
         <v>0</v>
@@ -6359,28 +6356,28 @@
         <v>-251</v>
       </c>
       <c r="M69" s="1">
-        <v>0.04642803988101463</v>
+        <v>-0.011984213959823409</v>
       </c>
       <c r="N69" s="1">
-        <v>11.141252222443766</v>
+        <v>5.678010678359797</v>
       </c>
       <c r="O69" s="1">
-        <v>62.35294117647059</v>
+        <v>58.82352941176471</v>
       </c>
       <c r="P69" s="1">
         <v>37.32769516583675</v>
       </c>
       <c r="Q69" s="1">
-        <v>46.941176470588225</v>
+        <v>45.05882352941176</v>
       </c>
       <c r="R69" s="1">
-        <v>44.882352941176464</v>
+        <v>43.17647058823529</v>
       </c>
       <c r="S69" s="1" t="s">
         <v>120</v>
       </c>
       <c r="T69" s="1">
-        <v>27.14</v>
+        <v>25.43</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
@@ -6400,19 +6397,19 @@
         <v>-0.54</v>
       </c>
       <c r="F70" s="1">
-        <v>-0.1390719121631107</v>
+        <v>-0.12578574350414173</v>
       </c>
       <c r="G70" s="1">
         <v>1.26</v>
       </c>
       <c r="H70" s="1">
-        <v>36.48</v>
+        <v>37.5</v>
       </c>
       <c r="I70" s="1">
-        <v>-7.97</v>
+        <v>-7.58</v>
       </c>
       <c r="J70" s="1">
-        <v>-0.004690740525377768</v>
+        <v>-0.004889466748683411</v>
       </c>
       <c r="K70" s="1" t="b">
         <v>0</v>
@@ -6421,28 +6418,28 @@
         <v>4</v>
       </c>
       <c r="M70" s="1">
-        <v>-0.1249709467538207</v>
+        <v>-0.11070202011085217</v>
       </c>
       <c r="N70" s="1">
-        <v>-5.998646441039758</v>
+        <v>-4.193769936743079</v>
       </c>
       <c r="O70" s="1">
-        <v>32.94117647058823</v>
+        <v>34.11764705882353</v>
       </c>
       <c r="P70" s="1">
         <v>16.710870321490763</v>
       </c>
       <c r="Q70" s="1">
-        <v>46.82352941176471</v>
+        <v>46.117647058823536</v>
       </c>
       <c r="R70" s="1">
-        <v>40.58823529411765</v>
+        <v>40.94117647058824</v>
       </c>
       <c r="S70" s="1" t="s">
         <v>103</v>
       </c>
       <c r="T70" s="1">
-        <v>-1.12</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.25">
@@ -6462,19 +6459,19 @@
         <v>0.14</v>
       </c>
       <c r="F71" s="2">
-        <v>0.1818283619151045</v>
+        <v>0.1660943925755984</v>
       </c>
       <c r="G71" s="2">
         <v>0.33</v>
       </c>
       <c r="H71" s="2">
-        <v>60.3</v>
+        <v>56.49</v>
       </c>
       <c r="I71" s="2">
-        <v>11.01</v>
+        <v>9.84</v>
       </c>
       <c r="J71" s="2">
-        <v>0.011873694973868707</v>
+        <v>0.013053316165843003</v>
       </c>
       <c r="K71" s="2" t="b">
         <v>1</v>
@@ -6483,28 +6480,28 @@
         <v>-79</v>
       </c>
       <c r="M71" s="2">
-        <v>0.145491258745011</v>
+        <v>0.12722479767750605</v>
       </c>
       <c r="N71" s="2">
-        <v>21.047574108843424</v>
+        <v>19.59891184209275</v>
       </c>
       <c r="O71" s="2">
-        <v>76.47058823529412</v>
+        <v>74.11764705882354</v>
       </c>
       <c r="P71" s="2">
         <v>10.873073633899006</v>
       </c>
       <c r="Q71" s="2">
-        <v>62.58823529411765</v>
+        <v>61.05882352941177</v>
       </c>
       <c r="R71" s="2">
-        <v>57.41176470588236</v>
+        <v>56.70588235294119</v>
       </c>
       <c r="S71" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T71" s="2">
-        <v>9.36</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.25">
@@ -6524,49 +6521,49 @@
         <v>0.2</v>
       </c>
       <c r="F72" s="1">
-        <v>-0.1025784763643005</v>
+        <v>-0.10177974530808893</v>
       </c>
       <c r="G72" s="1">
         <v>1.47</v>
       </c>
       <c r="H72" s="1">
-        <v>60.94</v>
+        <v>62.72</v>
       </c>
       <c r="I72" s="1">
-        <v>-12.09</v>
+        <v>-11.33</v>
       </c>
       <c r="J72" s="1">
-        <v>-0.005793518152722301</v>
+        <v>-0.0023344083426988134</v>
       </c>
       <c r="K72" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" s="1">
         <v>-41</v>
       </c>
       <c r="M72" s="1">
-        <v>-0.07708826966289162</v>
+        <v>-0.07451301455868087</v>
       </c>
       <c r="N72" s="1">
-        <v>-1.210378731946844</v>
+        <v>-0.5748693815259397</v>
       </c>
       <c r="O72" s="1">
-        <v>43.529411764705884</v>
+        <v>44.70588235294118</v>
       </c>
       <c r="P72" s="1">
-        <v>29.505935179545663</v>
+        <v>28.84879594738295</v>
       </c>
       <c r="Q72" s="1">
-        <v>51.17647058823529</v>
+        <v>52.705882352941174</v>
       </c>
       <c r="R72" s="1">
-        <v>39</v>
+        <v>39.88235294117647</v>
       </c>
       <c r="S72" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T72" s="1">
-        <v>9.55</v>
+        <v>10.43</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.25">
@@ -6586,19 +6583,19 @@
         <v>-0.34</v>
       </c>
       <c r="F73" s="2">
-        <v>0.3584735428253212</v>
+        <v>0.3164785798337941</v>
       </c>
       <c r="G73" s="2">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="H73" s="2">
-        <v>72.47</v>
+        <v>75.31</v>
       </c>
       <c r="I73" s="2">
-        <v>23.9</v>
+        <v>25.87</v>
       </c>
       <c r="J73" s="2">
-        <v>0.0231736868851309</v>
+        <v>0.023496730151741075</v>
       </c>
       <c r="K73" s="2" t="b">
         <v>1</v>
@@ -6607,13 +6604,13 @@
         <v>49</v>
       </c>
       <c r="M73" s="2">
-        <v>0.3525077497675446</v>
+        <v>0.30951686134458356</v>
       </c>
       <c r="N73" s="2">
-        <v>41.74922321109678</v>
+        <v>37.82811820880049</v>
       </c>
       <c r="O73" s="2">
-        <v>88.23529411764706</v>
+        <v>83.52941176470588</v>
       </c>
       <c r="P73" s="2">
         <v>8.480874361506512</v>
@@ -6622,13 +6619,13 @@
         <v>67.76470588235294</v>
       </c>
       <c r="R73" s="2">
-        <v>61.94117647058824</v>
+        <v>60.529411764705884</v>
       </c>
       <c r="S73" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T73" s="2">
-        <v>22.06</v>
+        <v>20.65</v>
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.25">
@@ -6642,25 +6639,25 @@
         <v>44.70588235294118</v>
       </c>
       <c r="D74" s="1">
-        <v>11.29047619047619</v>
+        <v>11.195238095238095</v>
       </c>
       <c r="E74" s="1">
         <v>0.44</v>
       </c>
       <c r="F74" s="1">
-        <v>-0.20838020460620804</v>
+        <v>-0.19461464436377918</v>
       </c>
       <c r="G74" s="1">
         <v>1.1</v>
       </c>
       <c r="H74" s="1">
-        <v>36.31</v>
+        <v>37.79</v>
       </c>
       <c r="I74" s="1">
-        <v>-27.47</v>
+        <v>-26.96</v>
       </c>
       <c r="J74" s="1">
-        <v>-0.01794466382043905</v>
+        <v>-0.018125564055936152</v>
       </c>
       <c r="K74" s="1" t="b">
         <v>1</v>
@@ -6669,28 +6666,28 @@
         <v>-169</v>
       </c>
       <c r="M74" s="1">
-        <v>-0.20295675637186572</v>
+        <v>-0.18881321228943704</v>
       </c>
       <c r="N74" s="1">
-        <v>-13.797227402844255</v>
+        <v>-12.00488915460156</v>
       </c>
       <c r="O74" s="1">
-        <v>18.823529411764707</v>
+        <v>20</v>
       </c>
       <c r="P74" s="1">
         <v>25.03694506602277</v>
       </c>
       <c r="Q74" s="1">
-        <v>40.470588235294116</v>
+        <v>40.35294117647059</v>
       </c>
       <c r="R74" s="1">
-        <v>31.29411764705883</v>
+        <v>31.647058823529417</v>
       </c>
       <c r="S74" s="1" t="s">
         <v>121</v>
       </c>
       <c r="T74" s="1">
-        <v>-0.72</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
@@ -6710,19 +6707,19 @@
         <v>-3.72</v>
       </c>
       <c r="F75" s="3">
-        <v>-0.2535075385430039</v>
+        <v>-0.28947864338836166</v>
       </c>
       <c r="G75" s="3">
         <v>1.25</v>
       </c>
       <c r="H75" s="3">
-        <v>33.98</v>
+        <v>31.39</v>
       </c>
       <c r="I75" s="3">
-        <v>-9.54</v>
+        <v>-11.34</v>
       </c>
       <c r="J75" s="3">
-        <v>-0.020526609964835567</v>
+        <v>-0.022121120413911323</v>
       </c>
       <c r="K75" s="3" t="b">
         <v>0</v>
@@ -6731,28 +6728,28 @@
         <v>32</v>
       </c>
       <c r="M75" s="3">
-        <v>-0.23994891795714812</v>
+        <v>-0.2749750632025063</v>
       </c>
       <c r="N75" s="3">
-        <v>-17.4964435613725</v>
+        <v>-20.621074245908485</v>
       </c>
       <c r="O75" s="3">
-        <v>14.117647058823529</v>
+        <v>11.76470588235294</v>
       </c>
       <c r="P75" s="3">
-        <v>30.766929498676355</v>
+        <v>32.10981456426673</v>
       </c>
       <c r="Q75" s="3">
-        <v>41.99999999999999</v>
+        <v>41.05882352941176</v>
       </c>
       <c r="R75" s="3">
-        <v>29.705882352941174</v>
+        <v>28.294117647058822</v>
       </c>
       <c r="S75" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T75" s="3">
-        <v>-28.89</v>
+        <v>-30.3</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
@@ -6772,19 +6769,19 @@
         <v>-0.07</v>
       </c>
       <c r="F76" s="3">
-        <v>-0.3801939058098336</v>
+        <v>-0.3781822075658336</v>
       </c>
       <c r="G76" s="3">
         <v>3.25</v>
       </c>
       <c r="H76" s="3">
-        <v>43.99</v>
+        <v>43.43</v>
       </c>
       <c r="I76" s="3">
-        <v>-30.44</v>
+        <v>-30.59</v>
       </c>
       <c r="J76" s="3">
-        <v>-0.012066563046976795</v>
+        <v>-0.01123969026350234</v>
       </c>
       <c r="K76" s="3" t="b">
         <v>0</v>
@@ -6793,28 +6790,28 @@
         <v>10</v>
       </c>
       <c r="M76" s="3">
-        <v>-0.2581663205371315</v>
+        <v>-0.24764998589313536</v>
       </c>
       <c r="N76" s="3">
-        <v>-19.318183819370834</v>
+        <v>-17.888566514971394</v>
       </c>
       <c r="O76" s="3">
-        <v>9.411764705882353</v>
+        <v>15.294117647058824</v>
       </c>
       <c r="P76" s="3">
         <v>51.49813033405746</v>
       </c>
       <c r="Q76" s="3">
-        <v>44.35294117647059</v>
+        <v>43.411764705882355</v>
       </c>
       <c r="R76" s="3">
-        <v>25.411764705882348</v>
+        <v>27.058823529411768</v>
       </c>
       <c r="S76" s="3" t="s">
         <v>109</v>
       </c>
       <c r="T76" s="3">
-        <v>-0.32</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
@@ -6834,19 +6831,19 @@
         <v>12.83</v>
       </c>
       <c r="F77" s="3">
-        <v>-0.008463843435563806</v>
+        <v>-0.03348036686562583</v>
       </c>
       <c r="G77" s="3">
         <v>0.88</v>
       </c>
       <c r="H77" s="3">
-        <v>47.66</v>
+        <v>45.35</v>
       </c>
       <c r="I77" s="3">
-        <v>46.66</v>
+        <v>42.21</v>
       </c>
       <c r="J77" s="3">
-        <v>-0.02532844109852842</v>
+        <v>-0.02541100767942279</v>
       </c>
       <c r="K77" s="3" t="b">
         <v>1</v>
@@ -6855,28 +6852,28 @@
         <v>42</v>
       </c>
       <c r="M77" s="3">
-        <v>-0.014971981316774574</v>
+        <v>-0.0404420853548364</v>
       </c>
       <c r="N77" s="3">
-        <v>5.00125010266486</v>
+        <v>2.832223538858498</v>
       </c>
       <c r="O77" s="3">
-        <v>56.470588235294116</v>
+        <v>52.94117647058824</v>
       </c>
       <c r="P77" s="3">
         <v>29.799918858582526</v>
       </c>
       <c r="Q77" s="3">
-        <v>31.411764705882355</v>
+        <v>29.882352941176475</v>
       </c>
       <c r="R77" s="3">
-        <v>25.11764705882353</v>
+        <v>23.94117647058824</v>
       </c>
       <c r="S77" s="3" t="s">
         <v>123</v>
       </c>
       <c r="T77" s="3">
-        <v>-48.6</v>
+        <v>-49.78</v>
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
@@ -6896,19 +6893,19 @@
         <v>-9.21</v>
       </c>
       <c r="F78" s="2">
-        <v>0.737380609576443</v>
+        <v>0.687318256940241</v>
       </c>
       <c r="G78" s="2">
         <v>0.92</v>
       </c>
       <c r="H78" s="2">
-        <v>69.02</v>
+        <v>69.3</v>
       </c>
       <c r="I78" s="2">
-        <v>37.22</v>
+        <v>37.23</v>
       </c>
       <c r="J78" s="2">
-        <v>0.03350658862091758</v>
+        <v>0.03175588028881017</v>
       </c>
       <c r="K78" s="2" t="b">
         <v>0</v>
@@ -6917,152 +6914,152 @@
         <v>-5</v>
       </c>
       <c r="M78" s="2">
-        <v>0.7330418509889691</v>
+        <v>0.6826771112807672</v>
       </c>
       <c r="N78" s="2">
-        <v>79.80263333323923</v>
+        <v>75.14414320241887</v>
       </c>
       <c r="O78" s="2">
-        <v>98.82352941176471</v>
+        <v>97.6470588235294</v>
       </c>
       <c r="P78" s="2">
         <v>18.71809072120826</v>
       </c>
       <c r="Q78" s="2">
-        <v>66.23529411764707</v>
+        <v>65.76470588235296</v>
       </c>
       <c r="R78" s="2">
-        <v>60.64705882352942</v>
+        <v>60.176470588235304</v>
       </c>
       <c r="S78" s="2" t="s">
         <v>110</v>
       </c>
       <c r="T78" s="2">
-        <v>12.05</v>
+        <v>11.58</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A79" s="2" t="s">
+      <c r="A79" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B79" s="2">
+      <c r="B79" s="1">
         <v>-0.92</v>
       </c>
-      <c r="C79" s="2">
+      <c r="C79" s="1">
         <v>20</v>
       </c>
-      <c r="D79" s="2">
+      <c r="D79" s="1">
         <v>15.521739130434781</v>
       </c>
-      <c r="E79" s="2">
+      <c r="E79" s="1">
         <v>-3.59</v>
       </c>
-      <c r="F79" s="2">
-        <v>0.15156768438222118</v>
-      </c>
-      <c r="G79" s="2">
+      <c r="F79" s="1">
+        <v>0.09633707540036605</v>
+      </c>
+      <c r="G79" s="1">
         <v>1.12</v>
       </c>
-      <c r="H79" s="2">
-        <v>52.1</v>
-      </c>
-      <c r="I79" s="2">
-        <v>27.39</v>
-      </c>
-      <c r="J79" s="2">
-        <v>0.010105327452156775</v>
-      </c>
-      <c r="K79" s="2" t="b">
+      <c r="H79" s="1">
+        <v>50.66</v>
+      </c>
+      <c r="I79" s="1">
+        <v>26.46</v>
+      </c>
+      <c r="J79" s="1">
+        <v>0.0097321123111172</v>
+      </c>
+      <c r="K79" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L79" s="2">
+      <c r="L79" s="1">
         <v>-2</v>
       </c>
-      <c r="M79" s="2">
-        <v>0.15807582226343198</v>
-      </c>
-      <c r="N79" s="2">
-        <v>22.306030460685516</v>
-      </c>
-      <c r="O79" s="2">
-        <v>77.64705882352942</v>
-      </c>
-      <c r="P79" s="2">
-        <v>16.006637557486414</v>
-      </c>
-      <c r="Q79" s="2">
-        <v>56.35294117647059</v>
-      </c>
-      <c r="R79" s="2">
-        <v>51.94117647058824</v>
-      </c>
-      <c r="S79" s="2" t="s">
+      <c r="M79" s="1">
+        <v>0.10329879388957663</v>
+      </c>
+      <c r="N79" s="1">
+        <v>17.20631146329981</v>
+      </c>
+      <c r="O79" s="1">
+        <v>68.23529411764706</v>
+      </c>
+      <c r="P79" s="1">
+        <v>14.191910385236758</v>
+      </c>
+      <c r="Q79" s="1">
+        <v>55.05882352941177</v>
+      </c>
+      <c r="R79" s="1">
+        <v>49.23529411764706</v>
+      </c>
+      <c r="S79" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="T79" s="2">
-        <v>3.77</v>
+      <c r="T79" s="1">
+        <v>1.06</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A80" s="2" t="s">
+      <c r="A80" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B80" s="2">
+      <c r="B80" s="1">
         <v>5.7</v>
       </c>
-      <c r="C80" s="2">
+      <c r="C80" s="1">
         <v>63.52941176470588</v>
       </c>
-      <c r="D80" s="2">
+      <c r="D80" s="1">
         <v>0.15087719298245603</v>
       </c>
-      <c r="E80" s="2">
+      <c r="E80" s="1">
         <v>0.34</v>
       </c>
-      <c r="F80" s="2">
-        <v>0.14030161636326516</v>
-      </c>
-      <c r="G80" s="2">
+      <c r="F80" s="1">
+        <v>0.11445209148409169</v>
+      </c>
+      <c r="G80" s="1">
         <v>0.83</v>
       </c>
-      <c r="H80" s="2">
-        <v>43.93</v>
-      </c>
-      <c r="I80" s="2">
-        <v>8.74</v>
-      </c>
-      <c r="J80" s="2">
-        <v>0.0077447226379382126</v>
-      </c>
-      <c r="K80" s="2" t="b">
+      <c r="H80" s="1">
+        <v>43.56</v>
+      </c>
+      <c r="I80" s="1">
+        <v>8.4</v>
+      </c>
+      <c r="J80" s="1">
+        <v>0.006523559716235105</v>
+      </c>
+      <c r="K80" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L80" s="2">
+      <c r="L80" s="1">
         <v>6</v>
       </c>
-      <c r="M80" s="2">
-        <v>0.13108175436488323</v>
-      </c>
-      <c r="N80" s="2">
-        <v>19.60662367083064</v>
-      </c>
-      <c r="O80" s="2">
-        <v>74.11764705882354</v>
-      </c>
-      <c r="P80" s="2">
+      <c r="M80" s="1">
+        <v>0.10458965695771005</v>
+      </c>
+      <c r="N80" s="1">
+        <v>17.335397770113147</v>
+      </c>
+      <c r="O80" s="1">
+        <v>69.41176470588235</v>
+      </c>
+      <c r="P80" s="1">
         <v>11.616065285425229</v>
       </c>
-      <c r="Q80" s="2">
-        <v>50.35294117647059</v>
-      </c>
-      <c r="R80" s="2">
-        <v>51.29411764705883</v>
-      </c>
-      <c r="S80" s="2" t="s">
+      <c r="Q80" s="1">
+        <v>49.529411764705884</v>
+      </c>
+      <c r="R80" s="1">
+        <v>49.88235294117647</v>
+      </c>
+      <c r="S80" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="T80" s="2">
-        <v>11.42</v>
+      <c r="T80" s="1">
+        <v>10</v>
       </c>
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.25">
@@ -7082,19 +7079,19 @@
         <v>0.87</v>
       </c>
       <c r="F81" s="2">
-        <v>0.0480738888119855</v>
+        <v>0.05218514591322693</v>
       </c>
       <c r="G81" s="2">
         <v>0.77</v>
       </c>
       <c r="H81" s="2">
-        <v>40.52</v>
+        <v>48.41</v>
       </c>
       <c r="I81" s="2">
-        <v>7.43</v>
+        <v>9.19</v>
       </c>
       <c r="J81" s="2">
-        <v>0.004699661602189917</v>
+        <v>0.004325144399203818</v>
       </c>
       <c r="K81" s="2" t="b">
         <v>1</v>
@@ -7103,28 +7100,28 @@
         <v>158</v>
       </c>
       <c r="M81" s="2">
-        <v>0.03559995787299819</v>
+        <v>0.03884185214224001</v>
       </c>
       <c r="N81" s="2">
-        <v>10.058444021642135</v>
+        <v>10.760617288566136</v>
       </c>
       <c r="O81" s="2">
-        <v>61.1764705882353</v>
+        <v>62.35294117647059</v>
       </c>
       <c r="P81" s="2">
         <v>6.707278396222185</v>
       </c>
       <c r="Q81" s="2">
-        <v>52.8235294117647</v>
+        <v>54</v>
       </c>
       <c r="R81" s="2">
-        <v>51.76470588235294</v>
+        <v>51.88235294117647</v>
       </c>
       <c r="S81" s="2" t="s">
         <v>111</v>
       </c>
       <c r="T81" s="2">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.25">
@@ -7138,25 +7135,25 @@
         <v>95.29411764705881</v>
       </c>
       <c r="D82" s="1">
-        <v>-0.9305912596401028</v>
+        <v>-0.9365895458440445</v>
       </c>
       <c r="E82" s="1">
         <v>-1.14</v>
       </c>
       <c r="F82" s="1">
-        <v>-0.053291150385017916</v>
+        <v>-0.059079476807359976</v>
       </c>
       <c r="G82" s="1">
         <v>1.01</v>
       </c>
       <c r="H82" s="1">
-        <v>33.11</v>
+        <v>36.3</v>
       </c>
       <c r="I82" s="1">
-        <v>4.99</v>
+        <v>5.64</v>
       </c>
       <c r="J82" s="1">
-        <v>0.002755423044509321</v>
+        <v>0.0012201237566719805</v>
       </c>
       <c r="K82" s="1" t="b">
         <v>1</v>
@@ -7165,10 +7162,10 @@
         <v>111</v>
       </c>
       <c r="M82" s="1">
-        <v>-0.05274880556158368</v>
+        <v>-0.05849933359992576</v>
       </c>
       <c r="N82" s="1">
-        <v>1.2235676781839364</v>
+        <v>1.0264987143495636</v>
       </c>
       <c r="O82" s="1">
         <v>49.411764705882355</v>
@@ -7177,16 +7174,16 @@
         <v>7.571607002312677</v>
       </c>
       <c r="Q82" s="1">
-        <v>48.23529411764706</v>
+        <v>48.117647058823536</v>
       </c>
       <c r="R82" s="1">
-        <v>46.35294117647059</v>
+        <v>45.99999999999999</v>
       </c>
       <c r="S82" s="1" t="s">
         <v>101</v>
       </c>
       <c r="T82" s="1">
-        <v>1.05</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.25">
@@ -7206,19 +7203,19 @@
         <v>0.23</v>
       </c>
       <c r="F83" s="2">
-        <v>0.08114405426294356</v>
+        <v>0.14803610104324944</v>
       </c>
       <c r="G83" s="2">
         <v>1.07</v>
       </c>
       <c r="H83" s="2">
-        <v>60.86</v>
+        <v>61.35</v>
       </c>
       <c r="I83" s="2">
         <v>16.75</v>
       </c>
       <c r="J83" s="2">
-        <v>0.007002184284276297</v>
+        <v>0.0060417100649566196</v>
       </c>
       <c r="K83" s="2" t="b">
         <v>0</v>
@@ -7227,28 +7224,28 @@
         <v>90</v>
       </c>
       <c r="M83" s="2">
-        <v>0.08494046802698318</v>
+        <v>0.15209710349528893</v>
       </c>
       <c r="N83" s="2">
-        <v>14.992495037040623</v>
+        <v>22.086142423871035</v>
       </c>
       <c r="O83" s="2">
-        <v>67.05882352941175</v>
+        <v>76.47058823529412</v>
       </c>
       <c r="P83" s="2">
         <v>12.706223591210087</v>
       </c>
       <c r="Q83" s="2">
-        <v>58.47058823529412</v>
+        <v>58.117647058823536</v>
       </c>
       <c r="R83" s="2">
-        <v>51.05882352941176</v>
+        <v>53.88235294117647</v>
       </c>
       <c r="S83" s="2" t="s">
         <v>109</v>
       </c>
       <c r="T83" s="2">
-        <v>-1.08</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.25">
@@ -7268,19 +7265,19 @@
         <v>2.31</v>
       </c>
       <c r="F84" s="1">
-        <v>-0.10498741089377293</v>
+        <v>-0.08966024621211244</v>
       </c>
       <c r="G84" s="1">
         <v>1.2</v>
       </c>
       <c r="H84" s="1">
-        <v>44.8</v>
+        <v>48.53</v>
       </c>
       <c r="I84" s="1">
-        <v>-0.55</v>
+        <v>0.76</v>
       </c>
       <c r="J84" s="1">
-        <v>-0.0032923025525219162</v>
+        <v>-0.004236079974970514</v>
       </c>
       <c r="K84" s="1" t="b">
         <v>1</v>
@@ -7289,28 +7286,28 @@
         <v>175</v>
       </c>
       <c r="M84" s="1">
-        <v>-0.0941405144250883</v>
+        <v>-0.07805738206342816</v>
       </c>
       <c r="N84" s="1">
-        <v>-2.915603208166512</v>
+        <v>-0.9293061320006757</v>
       </c>
       <c r="O84" s="1">
-        <v>38.82352941176471</v>
+        <v>43.529411764705884</v>
       </c>
       <c r="P84" s="1">
         <v>20.22353911360907</v>
       </c>
       <c r="Q84" s="1">
-        <v>45.52941176470588</v>
+        <v>44.705882352941174</v>
       </c>
       <c r="R84" s="1">
-        <v>36.23529411764706</v>
+        <v>37.647058823529406</v>
       </c>
       <c r="S84" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T84" s="1">
-        <v>-10.53</v>
+        <v>-9.12</v>
       </c>
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.25">
@@ -7330,19 +7327,19 @@
         <v>0.23</v>
       </c>
       <c r="F85" s="1">
-        <v>-0.17498308576310917</v>
+        <v>-0.16846979777205007</v>
       </c>
       <c r="G85" s="1">
         <v>0.98</v>
       </c>
       <c r="H85" s="1">
-        <v>39.58</v>
+        <v>42.62</v>
       </c>
       <c r="I85" s="1">
-        <v>9.22</v>
+        <v>10.45</v>
       </c>
       <c r="J85" s="1">
-        <v>-0.008051726536975383</v>
+        <v>-0.008271890563022459</v>
       </c>
       <c r="K85" s="1" t="b">
         <v>1</v>
@@ -7351,28 +7348,28 @@
         <v>378</v>
       </c>
       <c r="M85" s="1">
-        <v>-0.17606777540997764</v>
+        <v>-0.1696300841869185</v>
       </c>
       <c r="N85" s="1">
-        <v>-11.108329306655454</v>
+        <v>-10.086576344349709</v>
       </c>
       <c r="O85" s="1">
-        <v>20</v>
+        <v>24.705882352941178</v>
       </c>
       <c r="P85" s="1">
         <v>18.130768996018627</v>
       </c>
       <c r="Q85" s="1">
-        <v>44</v>
+        <v>44.35294117647059</v>
       </c>
       <c r="R85" s="1">
-        <v>31.235294117647054</v>
+        <v>32.76470588235294</v>
       </c>
       <c r="S85" s="1" t="s">
         <v>132</v>
       </c>
       <c r="T85" s="1">
-        <v>-25.41</v>
+        <v>-23.88</v>
       </c>
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.25">
@@ -7392,19 +7389,19 @@
         <v>0.62</v>
       </c>
       <c r="F86" s="1">
-        <v>0.003154001706210746</v>
+        <v>-0.01158596071125556</v>
       </c>
       <c r="G86" s="1">
         <v>0.95</v>
       </c>
       <c r="H86" s="1">
-        <v>34.69</v>
+        <v>33.44</v>
       </c>
       <c r="I86" s="1">
-        <v>4.49</v>
+        <v>3.96</v>
       </c>
       <c r="J86" s="1">
-        <v>-0.0025285139555875553</v>
+        <v>-0.0033453858309615957</v>
       </c>
       <c r="K86" s="1" t="b">
         <v>1</v>
@@ -7413,28 +7410,28 @@
         <v>131</v>
       </c>
       <c r="M86" s="1">
-        <v>0.0004422775890395858</v>
+        <v>-0.01448667674842663</v>
       </c>
       <c r="N86" s="1">
-        <v>6.54267599324627</v>
+        <v>5.427764399499481</v>
       </c>
       <c r="O86" s="1">
-        <v>60</v>
+        <v>57.647058823529406</v>
       </c>
       <c r="P86" s="1">
         <v>13.196185332148602</v>
       </c>
       <c r="Q86" s="1">
-        <v>45.41176470588236</v>
+        <v>43.99999999999999</v>
       </c>
       <c r="R86" s="1">
-        <v>46.588235294117645</v>
+        <v>45.64705882352941</v>
       </c>
       <c r="S86" s="1" t="s">
         <v>107</v>
       </c>
       <c r="T86" s="1">
-        <v>-0.18</v>
+        <v>-1.12</v>
       </c>
     </row>
   </sheetData>
@@ -7461,7 +7458,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>45.647058823529406</v>
+        <v>46.05882352941177</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -7469,7 +7466,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>56.94117647058823</v>
+        <v>57.1764705882353</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7477,7 +7474,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>53.294117647058826</v>
+        <v>52.94117647058824</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -7485,7 +7482,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>40.76470588235294</v>
+        <v>40.29411764705881</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -7493,7 +7490,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>35.588235294117645</v>
+        <v>36.352941176470594</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7501,7 +7498,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>57.05882352941175</v>
+        <v>56.94117647058822</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -7509,7 +7506,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>35.76470588235294</v>
+        <v>37.294117647058826</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -7517,7 +7514,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>61.705882352941174</v>
+        <v>62.764705882352935</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -7525,7 +7522,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>43.41176470588235</v>
+        <v>46.23529411764706</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -7533,7 +7530,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>58.05882352941177</v>
+        <v>57.588235294117645</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -7541,7 +7538,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>62.588235294117645</v>
+        <v>61.1764705882353</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -7549,7 +7546,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>37.00000000000001</v>
+        <v>36.52941176470589</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -7557,7 +7554,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>61</v>
+        <v>60.88235294117648</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -7565,7 +7562,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>30.88235294117647</v>
+        <v>33.235294117647065</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -7573,7 +7570,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>13.058823529411764</v>
+        <v>13.529411764705884</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -7581,7 +7578,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>33.294117647058826</v>
+        <v>34.235294117647065</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -7597,7 +7594,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>55.88235294117647</v>
+        <v>55.17647058823529</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -7605,7 +7602,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>57.58823529411765</v>
+        <v>56.88235294117648</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -7613,7 +7610,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>20.058823529411768</v>
+        <v>19.11764705882353</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -7621,7 +7618,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>33.99999999999999</v>
+        <v>32.705882352941174</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -7629,7 +7626,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>56.411764705882355</v>
+        <v>57.41176470588236</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -7637,7 +7634,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>42.47058823529412</v>
+        <v>43.64705882352941</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -7645,7 +7642,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>5.705882352941179</v>
+        <v>5.117647058823531</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -7653,7 +7650,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>2.5294117647058822</v>
+        <v>7.588235294117645</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -7661,7 +7658,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>-0.05882352941176627</v>
+        <v>0.7647058823529402</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -7669,7 +7666,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>41.05882352941176</v>
+        <v>43.64705882352941</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -7677,7 +7674,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>41.23529411764706</v>
+        <v>42.76470588235294</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -7685,7 +7682,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>43.11764705882353</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -7693,7 +7690,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>39</v>
+        <v>39.588235294117645</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -7701,7 +7698,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>32.470588235294116</v>
+        <v>32.94117647058823</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -7717,7 +7714,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>37.35294117647059</v>
+        <v>38.1764705882353</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -7725,7 +7722,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>43.94117647058824</v>
+        <v>42.41176470588236</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -7733,7 +7730,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>38.411764705882355</v>
+        <v>38.529411764705884</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -7741,7 +7738,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>51.88235294117647</v>
+        <v>50.588235294117645</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -7749,7 +7746,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>66.58823529411764</v>
+        <v>66.23529411764706</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -7757,7 +7754,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>36.82352941176471</v>
+        <v>34.82352941176471</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -7765,7 +7762,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>47.235294117647065</v>
+        <v>47.352941176470594</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -7773,7 +7770,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>19.588235294117645</v>
+        <v>19.705882352941174</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -7781,7 +7778,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>26.58823529411765</v>
+        <v>25.88235294117647</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -7789,7 +7786,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>56.17647058823529</v>
+        <v>55.82352941176471</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -7797,7 +7794,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>56.17647058823529</v>
+        <v>57.117647058823536</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -7805,7 +7802,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>42.117647058823536</v>
+        <v>42.470588235294116</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -7813,7 +7810,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>24.29411764705882</v>
+        <v>25.823529411764703</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -7821,7 +7818,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>45.352941176470594</v>
+        <v>47.00000000000001</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -7829,7 +7826,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>56.588235294117645</v>
+        <v>55.764705882352935</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -7837,7 +7834,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>54.47058823529412</v>
+        <v>56.94117647058824</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -7845,7 +7842,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>27.411764705882355</v>
+        <v>26.941176470588232</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -7853,7 +7850,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>42.76470588235294</v>
+        <v>45.117647058823536</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -7861,7 +7858,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>24.117647058823533</v>
+        <v>25.58823529411765</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -7869,7 +7866,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>22.058823529411768</v>
+        <v>22.88235294117647</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -7877,7 +7874,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>47.529411764705884</v>
+        <v>45.117647058823536</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -7885,7 +7882,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>29.235294117647058</v>
+        <v>28.94117647058824</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -7901,7 +7898,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>24.588235294117645</v>
+        <v>24.941176470588232</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -7909,7 +7906,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>46.35294117647059</v>
+        <v>48.94117647058823</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -7917,7 +7914,7 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>26.70588235294118</v>
+        <v>25.529411764705884</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -7925,7 +7922,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>10.64705882352941</v>
+        <v>10.294117647058819</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -7933,7 +7930,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>39.70588235294118</v>
+        <v>39.00000000000001</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -7941,7 +7938,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>50.94117647058823</v>
+        <v>51.05882352941177</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -7949,7 +7946,7 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>49.882352941176464</v>
+        <v>42.23529411764706</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -7957,7 +7954,7 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>32.882352941176464</v>
+        <v>32.647058823529406</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -7965,7 +7962,7 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>30.58823529411765</v>
+        <v>29.64705882352941</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -7973,7 +7970,7 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>61.58823529411765</v>
+        <v>59.52941176470588</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -7981,7 +7978,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>34.05882352941176</v>
+        <v>25.647058823529413</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -7989,7 +7986,7 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>38.05882352941177</v>
+        <v>41.117647058823536</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -7997,7 +7994,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>44.882352941176464</v>
+        <v>43.17647058823529</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -8005,7 +8002,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>40.58823529411765</v>
+        <v>40.94117647058824</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -8013,7 +8010,7 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>57.41176470588236</v>
+        <v>56.70588235294119</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -8021,7 +8018,7 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>39</v>
+        <v>39.88235294117647</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -8029,7 +8026,7 @@
         <v>72</v>
       </c>
       <c r="B73">
-        <v>61.94117647058824</v>
+        <v>60.529411764705884</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -8037,7 +8034,7 @@
         <v>73</v>
       </c>
       <c r="B74">
-        <v>31.29411764705883</v>
+        <v>31.647058823529417</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -8045,7 +8042,7 @@
         <v>74</v>
       </c>
       <c r="B75">
-        <v>29.705882352941174</v>
+        <v>28.294117647058822</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -8053,7 +8050,7 @@
         <v>75</v>
       </c>
       <c r="B76">
-        <v>25.411764705882348</v>
+        <v>27.058823529411768</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -8061,7 +8058,7 @@
         <v>122</v>
       </c>
       <c r="B77">
-        <v>25.11764705882353</v>
+        <v>23.94117647058824</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -8069,7 +8066,7 @@
         <v>124</v>
       </c>
       <c r="B78">
-        <v>60.64705882352942</v>
+        <v>60.176470588235304</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -8077,7 +8074,7 @@
         <v>125</v>
       </c>
       <c r="B79">
-        <v>51.94117647058824</v>
+        <v>49.23529411764706</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -8085,7 +8082,7 @@
         <v>126</v>
       </c>
       <c r="B80">
-        <v>51.29411764705883</v>
+        <v>49.88235294117647</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -8093,7 +8090,7 @@
         <v>127</v>
       </c>
       <c r="B81">
-        <v>51.76470588235294</v>
+        <v>51.88235294117647</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -8101,7 +8098,7 @@
         <v>128</v>
       </c>
       <c r="B82">
-        <v>46.35294117647059</v>
+        <v>45.99999999999999</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -8109,7 +8106,7 @@
         <v>129</v>
       </c>
       <c r="B83">
-        <v>51.05882352941176</v>
+        <v>53.88235294117647</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -8117,7 +8114,7 @@
         <v>130</v>
       </c>
       <c r="B84">
-        <v>36.23529411764706</v>
+        <v>37.647058823529406</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -8125,7 +8122,7 @@
         <v>131</v>
       </c>
       <c r="B85">
-        <v>31.235294117647054</v>
+        <v>32.76470588235294</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
@@ -8133,7 +8130,7 @@
         <v>133</v>
       </c>
       <c r="B86">
-        <v>46.588235294117645</v>
+        <v>45.64705882352941</v>
       </c>
     </row>
   </sheetData>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="234">
   <si>
     <t>Ticker</t>
   </si>
@@ -319,7 +319,7 @@
     <t>2027-07-22</t>
   </si>
   <si>
-    <t>2027-07-16</t>
+    <t>2026-10-20</t>
   </si>
   <si>
     <t>2027-08-26</t>
@@ -334,7 +334,7 @@
     <t>2027-08-05</t>
   </si>
   <si>
-    <t>2026-08-27</t>
+    <t>2027-08-27</t>
   </si>
   <si>
     <t>2026-09-01</t>
@@ -424,10 +424,13 @@
     <t>UNP</t>
   </si>
   <si>
+    <t>2026-10-22</t>
+  </si>
+  <si>
     <t>_date_</t>
   </si>
   <si>
-    <t>2026-09-25</t>
+    <t>2026-09-28</t>
   </si>
   <si>
     <t>Criteria</t>
@@ -691,31 +694,31 @@
     <t>Momentum Breakout, Market Leader</t>
   </si>
   <si>
-    <t>Momentum Breakout, Stable Uptrend, Volume Spike, Institutional Buying</t>
+    <t>Momentum Breakout, Stable Uptrend, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Institutional Buying</t>
   </si>
   <si>
     <t>Momentum Breakout, Market Leader, Volume Spike, Institutional Buying</t>
   </si>
   <si>
-    <t>Institutional Buying</t>
+    <t>Momentum Breakout, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Volume Spike</t>
+  </si>
+  <si>
+    <t>Volume Spike</t>
   </si>
   <si>
     <t>Volume Spike, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Volume Spike</t>
-  </si>
-  <si>
-    <t>Momentum Breakout</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Volume Spike</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Volume Spike, Institutional Buying</t>
   </si>
   <si>
     <t>Earnings Upcoming, Institutional Buying</t>
@@ -1402,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -1413,10 +1416,10 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>66.23529411764706</v>
+        <v>66.11764705882354</v>
       </c>
       <c r="C2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1424,10 +1427,10 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>62.764705882352935</v>
+        <v>62.41176470588234</v>
       </c>
       <c r="C3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1435,32 +1438,32 @@
         <v>11</v>
       </c>
       <c r="B4">
-        <v>61.1764705882353</v>
+        <v>61.05882352941177</v>
       </c>
       <c r="C4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="B5">
-        <v>60.88235294117648</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="B6">
-        <v>60.529411764705884</v>
+        <v>60.52941176470589</v>
       </c>
       <c r="C6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1468,29 +1471,29 @@
         <v>124</v>
       </c>
       <c r="B7">
-        <v>60.176470588235304</v>
+        <v>60.294117647058826</v>
       </c>
       <c r="C7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="B8">
-        <v>60</v>
+        <v>59.58823529411765</v>
       </c>
       <c r="C8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="B9">
-        <v>59.52941176470588</v>
+        <v>58.70588235294118</v>
       </c>
       <c r="C9" t="s">
         <v>225</v>
@@ -1498,51 +1501,51 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="B10">
-        <v>57.588235294117645</v>
+        <v>58.705882352941174</v>
       </c>
       <c r="C10" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B11">
-        <v>57.41176470588236</v>
+        <v>57.647058823529406</v>
       </c>
       <c r="C11" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="B12">
-        <v>57.1764705882353</v>
+        <v>57.29411764705883</v>
       </c>
       <c r="C12" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="B13">
         <v>57.117647058823536</v>
       </c>
       <c r="C13" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B14">
         <v>56.94117647058824</v>
@@ -1553,21 +1556,21 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B15">
-        <v>56.94117647058822</v>
+        <v>56.529411764705884</v>
       </c>
       <c r="C15" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="B16">
-        <v>56.88235294117648</v>
+        <v>56.47058823529412</v>
       </c>
       <c r="C16" t="s">
         <v>229</v>
@@ -1575,10 +1578,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="B17">
-        <v>56.70588235294119</v>
+        <v>55.58823529411765</v>
       </c>
       <c r="C17" t="s">
         <v>230</v>
@@ -1589,18 +1592,18 @@
         <v>42</v>
       </c>
       <c r="B18">
-        <v>55.82352941176471</v>
+        <v>54.76470588235294</v>
       </c>
       <c r="C18" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="B19">
-        <v>55.764705882352935</v>
+        <v>53.64705882352941</v>
       </c>
       <c r="C19" t="s">
         <v>231</v>
@@ -1608,76 +1611,76 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>129</v>
       </c>
       <c r="B20">
-        <v>55.17647058823529</v>
+        <v>52.117647058823536</v>
       </c>
       <c r="C20" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>129</v>
+        <v>3</v>
       </c>
       <c r="B21">
-        <v>53.88235294117647</v>
+        <v>52</v>
       </c>
       <c r="C21" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>3</v>
+        <v>127</v>
       </c>
       <c r="B22">
-        <v>52.94117647058824</v>
+        <v>51.764705882352935</v>
       </c>
       <c r="C22" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>127</v>
+        <v>46</v>
       </c>
       <c r="B23">
-        <v>51.88235294117647</v>
+        <v>51.70588235294118</v>
       </c>
       <c r="C23" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="B24">
-        <v>51.05882352941177</v>
+        <v>50.823529411764696</v>
       </c>
       <c r="C24" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="B25">
-        <v>50.588235294117645</v>
+        <v>50.70588235294117</v>
       </c>
       <c r="C25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>126</v>
+        <v>61</v>
       </c>
       <c r="B26">
-        <v>49.88235294117647</v>
+        <v>50.352941176470594</v>
       </c>
       <c r="C26" t="s">
         <v>226</v>
@@ -1685,142 +1688,142 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B27">
-        <v>49.23529411764706</v>
+        <v>48.94117647058823</v>
       </c>
       <c r="C27" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="B28">
-        <v>48.94117647058823</v>
+        <v>48.1764705882353</v>
       </c>
       <c r="C28" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="B29">
-        <v>47.352941176470594</v>
+        <v>48.17647058823529</v>
       </c>
       <c r="C29" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="B30">
-        <v>47.00000000000001</v>
+        <v>48.11764705882353</v>
       </c>
       <c r="C30" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="B31">
-        <v>46.23529411764706</v>
+        <v>47.47058823529412</v>
       </c>
       <c r="C31" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="B32">
-        <v>46.05882352941177</v>
+        <v>46.47058823529412</v>
       </c>
       <c r="C32" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c r="B33">
-        <v>45.99999999999999</v>
+        <v>45.352941176470594</v>
       </c>
       <c r="C33" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>133</v>
+        <v>23</v>
       </c>
       <c r="B34">
-        <v>45.64705882352941</v>
+        <v>43.64705882352941</v>
       </c>
       <c r="C34" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>50</v>
+        <v>133</v>
       </c>
       <c r="B35">
-        <v>45.117647058823536</v>
+        <v>43.529411764705884</v>
       </c>
       <c r="C35" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B36">
-        <v>45.117647058823536</v>
+        <v>42.94117647058823</v>
       </c>
       <c r="C36" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="B37">
-        <v>43.64705882352941</v>
+        <v>42.23529411764706</v>
       </c>
       <c r="C37" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B38">
-        <v>43.64705882352941</v>
+        <v>42.1764705882353</v>
       </c>
       <c r="C38" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B39">
-        <v>43</v>
+        <v>42.117647058823536</v>
       </c>
       <c r="C39" t="s">
         <v>226</v>
@@ -1828,10 +1831,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B40">
-        <v>42.76470588235294</v>
+        <v>40.64705882352941</v>
       </c>
       <c r="C40" t="s">
         <v>226</v>
@@ -1839,10 +1842,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="B41">
-        <v>42.470588235294116</v>
+        <v>40.058823529411775</v>
       </c>
       <c r="C41" t="s">
         <v>226</v>
@@ -1850,21 +1853,21 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B42">
-        <v>42.23529411764706</v>
+        <v>40.05882352941177</v>
       </c>
       <c r="C42" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="B43">
-        <v>41.117647058823536</v>
+        <v>39.882352941176464</v>
       </c>
       <c r="C43" t="s">
         <v>226</v>
@@ -1872,13 +1875,13 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="B44">
-        <v>40.94117647058824</v>
+        <v>39.705882352941174</v>
       </c>
       <c r="C44" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -1886,51 +1889,51 @@
         <v>4</v>
       </c>
       <c r="B45">
-        <v>40.29411764705881</v>
+        <v>39.588235294117645</v>
       </c>
       <c r="C45" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="B46">
-        <v>39.588235294117645</v>
+        <v>38.94117647058823</v>
       </c>
       <c r="C46" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="B47">
-        <v>39.00000000000001</v>
+        <v>37.235294117647065</v>
       </c>
       <c r="C47" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>35</v>
+        <v>131</v>
       </c>
       <c r="B48">
-        <v>38.529411764705884</v>
+        <v>35.11764705882353</v>
       </c>
       <c r="C48" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B49">
-        <v>38.1764705882353</v>
+        <v>33.76470588235294</v>
       </c>
       <c r="C49" t="s">
         <v>226</v>
@@ -1938,24 +1941,24 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>130</v>
+        <v>14</v>
       </c>
       <c r="B50">
-        <v>37.647058823529406</v>
+        <v>33.58823529411765</v>
       </c>
       <c r="C50" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B51">
-        <v>37.294117647058826</v>
+        <v>33.17647058823529</v>
       </c>
       <c r="C51" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -2183,37 +2186,37 @@
         <v>67.05882352941175</v>
       </c>
       <c r="D2" s="1">
-        <v>-1.9626769626769627</v>
+        <v>-2.036036036036036</v>
       </c>
       <c r="E2" s="1">
         <v>-2.08</v>
       </c>
       <c r="F2" s="1">
-        <v>0.16143519292480366</v>
+        <v>0.15132359060100226</v>
       </c>
       <c r="G2" s="1">
         <v>0.21</v>
       </c>
       <c r="H2" s="1">
-        <v>49.23</v>
+        <v>53.62</v>
       </c>
       <c r="I2" s="1">
-        <v>8.71</v>
+        <v>10.2</v>
       </c>
       <c r="J2" s="1">
-        <v>0.012933248288435392</v>
+        <v>0.010397694802518957</v>
       </c>
       <c r="K2" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>-461</v>
+        <v>-457</v>
       </c>
       <c r="M2" s="1">
-        <v>0.11560387953750073</v>
+        <v>0.09841126847668624</v>
       </c>
       <c r="N2" s="1">
-        <v>18.436820028092225</v>
+        <v>17.613889141885846</v>
       </c>
       <c r="O2" s="1">
         <v>71.76470588235294</v>
@@ -2222,16 +2225,16 @@
         <v>16.29652721982991</v>
       </c>
       <c r="Q2" s="1">
-        <v>48.58823529411765</v>
+        <v>48.8235294117647</v>
       </c>
       <c r="R2" s="1">
-        <v>46.05882352941177</v>
+        <v>44.588235294117645</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>95</v>
       </c>
       <c r="T2" s="1">
-        <v>26.24</v>
+        <v>24.77</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -2248,52 +2251,52 @@
         <v>26.810256410256407</v>
       </c>
       <c r="E3" s="2">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="F3" s="2">
-        <v>0.027508228439093035</v>
+        <v>0.03222173311079152</v>
       </c>
       <c r="G3" s="2">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="H3" s="2">
-        <v>74.4</v>
+        <v>67.04</v>
       </c>
       <c r="I3" s="2">
-        <v>76.14</v>
+        <v>67.07</v>
       </c>
       <c r="J3" s="2">
-        <v>0.01318482279984989</v>
+        <v>0.01788051495543927</v>
       </c>
       <c r="K3" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L3" s="2">
-        <v>850</v>
+        <v>860</v>
       </c>
       <c r="M3" s="2">
-        <v>0.11278927993192256</v>
+        <v>0.13134861506520634</v>
       </c>
       <c r="N3" s="2">
-        <v>18.155360067534403</v>
+        <v>20.907623800737856</v>
       </c>
       <c r="O3" s="2">
-        <v>70.58823529411765</v>
+        <v>75.29411764705883</v>
       </c>
       <c r="P3" s="2">
         <v>26.053946839070953</v>
       </c>
       <c r="Q3" s="2">
-        <v>75.41176470588235</v>
+        <v>75.88235294117646</v>
       </c>
       <c r="R3" s="2">
-        <v>57.1764705882353</v>
+        <v>58.70588235294118</v>
       </c>
       <c r="S3" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T3" s="2">
-        <v>-9.9</v>
+        <v>-8.37</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -2307,55 +2310,55 @@
         <v>10.588235294117647</v>
       </c>
       <c r="D4" s="2">
-        <v>12.511041009463725</v>
+        <v>12.47634069400631</v>
       </c>
       <c r="E4" s="2">
-        <v>6.34</v>
+        <v>6.39</v>
       </c>
       <c r="F4" s="2">
-        <v>0.3891338292496143</v>
+        <v>0.24753379953182647</v>
       </c>
       <c r="G4" s="2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="H4" s="2">
-        <v>54.03</v>
+        <v>52.26</v>
       </c>
       <c r="I4" s="2">
-        <v>48.51</v>
+        <v>47.08</v>
       </c>
       <c r="J4" s="2">
-        <v>0.02238301397696013</v>
+        <v>0.02144487541476158</v>
       </c>
       <c r="K4" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L4" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M4" s="2">
-        <v>0.4094388415098118</v>
+        <v>0.2716457437910085</v>
       </c>
       <c r="N4" s="2">
-        <v>47.820316225323324</v>
+        <v>34.93733667331808</v>
       </c>
       <c r="O4" s="2">
-        <v>88.23529411764706</v>
+        <v>85.88235294117646</v>
       </c>
       <c r="P4" s="2">
         <v>19.349659482175007</v>
       </c>
       <c r="Q4" s="2">
-        <v>57.76470588235295</v>
+        <v>57.88235294117648</v>
       </c>
       <c r="R4" s="2">
-        <v>52.94117647058824</v>
+        <v>52</v>
       </c>
       <c r="S4" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T4" s="2">
-        <v>4.59</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -2369,55 +2372,55 @@
         <v>40</v>
       </c>
       <c r="D5" s="1">
-        <v>31.47222222222222</v>
+        <v>30.694444444444443</v>
       </c>
       <c r="E5" s="1">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="F5" s="1">
-        <v>-0.11403973862727687</v>
+        <v>-0.1586925511591099</v>
       </c>
       <c r="G5" s="1">
         <v>1.91</v>
       </c>
       <c r="H5" s="1">
-        <v>60.78</v>
+        <v>52.81</v>
       </c>
       <c r="I5" s="1">
-        <v>-3.59</v>
+        <v>-6.85</v>
       </c>
       <c r="J5" s="1">
-        <v>-0.007016981550023065</v>
+        <v>-0.005701715423466112</v>
       </c>
       <c r="K5" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L5" s="1">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="M5" s="1">
-        <v>-0.06124670675076338</v>
+        <v>-0.0977429142817332</v>
       </c>
       <c r="N5" s="1">
-        <v>0.7517613992657948</v>
+        <v>-2.0015291339561045</v>
       </c>
       <c r="O5" s="1">
-        <v>47.05882352941176</v>
+        <v>43.529411764705884</v>
       </c>
       <c r="P5" s="1">
         <v>33.002444654975626</v>
       </c>
       <c r="Q5" s="1">
-        <v>53.411764705882355</v>
+        <v>52.705882352941174</v>
       </c>
       <c r="R5" s="1">
-        <v>40.29411764705881</v>
+        <v>39.588235294117645</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T5" s="1">
-        <v>-5.68</v>
+        <v>-6.39</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -2434,52 +2437,52 @@
         <v>0.8264984227129338</v>
       </c>
       <c r="E6" s="1">
-        <v>-1.88</v>
+        <v>-1.85</v>
       </c>
       <c r="F6" s="1">
-        <v>-0.09200733241124384</v>
+        <v>-0.1539526213206618</v>
       </c>
       <c r="G6" s="1">
         <v>1.6</v>
       </c>
       <c r="H6" s="1">
-        <v>37.91</v>
+        <v>38.34</v>
       </c>
       <c r="I6" s="1">
-        <v>-15.52</v>
+        <v>-15.46</v>
       </c>
       <c r="J6" s="1">
-        <v>-0.002504261176736078</v>
+        <v>-0.002379906954218569</v>
       </c>
       <c r="K6" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" s="1">
-        <v>-204</v>
+        <v>-205</v>
       </c>
       <c r="M6" s="1">
-        <v>-0.05719873996519098</v>
+        <v>-0.11376604755535846</v>
       </c>
       <c r="N6" s="1">
-        <v>1.1565580778230509</v>
+        <v>-3.603842461318627</v>
       </c>
       <c r="O6" s="1">
-        <v>50.588235294117645</v>
+        <v>36.470588235294116</v>
       </c>
       <c r="P6" s="1">
-        <v>27.785495103772316</v>
+        <v>26.56962821327962</v>
       </c>
       <c r="Q6" s="1">
-        <v>38.82352941176471</v>
+        <v>39.05882352941177</v>
       </c>
       <c r="R6" s="1">
-        <v>36.352941176470594</v>
+        <v>32.35294117647059</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T6" s="1">
-        <v>17.27</v>
+        <v>13.27</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -2496,52 +2499,52 @@
         <v>7.8103666245259165</v>
       </c>
       <c r="E7" s="2">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="F7" s="2">
-        <v>0.007796491021726998</v>
+        <v>0.009572343931911642</v>
       </c>
       <c r="G7" s="2">
         <v>2.22</v>
       </c>
       <c r="H7" s="2">
-        <v>55.75</v>
+        <v>53.78</v>
       </c>
       <c r="I7" s="2">
-        <v>13.15</v>
+        <v>12.14</v>
       </c>
       <c r="J7" s="2">
-        <v>0.008139036288984727</v>
+        <v>0.007954353606071099</v>
       </c>
       <c r="K7" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L7" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M7" s="2">
-        <v>0.07857396232870117</v>
+        <v>0.09128504392136172</v>
       </c>
       <c r="N7" s="2">
-        <v>14.733828307212251</v>
+        <v>16.90126668635338</v>
       </c>
       <c r="O7" s="2">
-        <v>65.88235294117646</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="P7" s="2">
         <v>19.398494070050486</v>
       </c>
       <c r="Q7" s="2">
-        <v>66.70588235294117</v>
+        <v>66.58823529411765</v>
       </c>
       <c r="R7" s="2">
-        <v>56.94117647058822</v>
+        <v>57.647058823529406</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T7" s="2">
-        <v>8.53</v>
+        <v>9.23</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -2555,55 +2558,55 @@
         <v>84.70588235294117</v>
       </c>
       <c r="D8" s="1">
-        <v>-0.11961414790996792</v>
+        <v>-0.13762057877813508</v>
       </c>
       <c r="E8" s="1">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="F8" s="1">
-        <v>-0.12201349896928142</v>
+        <v>-0.1714970147785152</v>
       </c>
       <c r="G8" s="1">
         <v>0.61</v>
       </c>
       <c r="H8" s="1">
-        <v>38.36</v>
+        <v>41.16</v>
       </c>
       <c r="I8" s="1">
-        <v>5.58</v>
+        <v>6.16</v>
       </c>
       <c r="J8" s="1">
-        <v>-0.012804658339972528</v>
+        <v>-0.012237623850019754</v>
       </c>
       <c r="K8" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L8" s="1">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="M8" s="1">
-        <v>-0.14463908405921577</v>
+        <v>-0.19761828772596235</v>
       </c>
       <c r="N8" s="1">
-        <v>-7.587476331579437</v>
+        <v>-11.989066478379014</v>
       </c>
       <c r="O8" s="1">
-        <v>31.76470588235294</v>
+        <v>21.176470588235293</v>
       </c>
       <c r="P8" s="1">
         <v>14.910048504309984</v>
       </c>
       <c r="Q8" s="1">
-        <v>44.23529411764706</v>
+        <v>44.470588235294116</v>
       </c>
       <c r="R8" s="1">
-        <v>37.294117647058826</v>
+        <v>33.76470588235294</v>
       </c>
       <c r="S8" s="1" t="s">
         <v>101</v>
       </c>
       <c r="T8" s="1">
-        <v>-22.46</v>
+        <v>-25.99</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -2620,52 +2623,52 @@
         <v>36.128205128205124</v>
       </c>
       <c r="E9" s="2">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="F9" s="2">
-        <v>0.6918032624873154</v>
+        <v>0.5616217782893509</v>
       </c>
       <c r="G9" s="2">
         <v>1.6</v>
       </c>
       <c r="H9" s="2">
-        <v>66.14</v>
+        <v>61.48</v>
       </c>
       <c r="I9" s="2">
-        <v>26.06</v>
+        <v>23.56</v>
       </c>
       <c r="J9" s="2">
-        <v>0.03519040442583034</v>
+        <v>0.035812135835275885</v>
       </c>
       <c r="K9" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L9" s="2">
-        <v>-112</v>
+        <v>-113</v>
       </c>
       <c r="M9" s="2">
-        <v>0.7266118549333682</v>
+        <v>0.6018083520546542</v>
       </c>
       <c r="N9" s="2">
-        <v>79.53761756767896</v>
+        <v>67.95359749968264</v>
       </c>
       <c r="O9" s="2">
-        <v>98.82352941176471</v>
+        <v>97.6470588235294</v>
       </c>
       <c r="P9" s="2">
         <v>33.227512780245505</v>
       </c>
       <c r="Q9" s="2">
-        <v>73.05882352941175</v>
+        <v>73.05882352941177</v>
       </c>
       <c r="R9" s="2">
-        <v>62.764705882352935</v>
+        <v>62.41176470588234</v>
       </c>
       <c r="S9" s="2" t="s">
         <v>102</v>
       </c>
       <c r="T9" s="2">
-        <v>35.39</v>
+        <v>35.03</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -2682,52 +2685,52 @@
         <v>0.7484536082474229</v>
       </c>
       <c r="E10" s="1">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="F10" s="1">
-        <v>-0.0492221601054378</v>
+        <v>-0.03135675133015266</v>
       </c>
       <c r="G10" s="1">
         <v>1.42</v>
       </c>
       <c r="H10" s="1">
-        <v>51.6</v>
+        <v>52.59</v>
       </c>
       <c r="I10" s="1">
-        <v>1.63</v>
+        <v>2.01</v>
       </c>
       <c r="J10" s="1">
-        <v>0.007989718611138669</v>
+        <v>0.007568911762150084</v>
       </c>
       <c r="K10" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="1">
-        <v>-49</v>
+        <v>-50</v>
       </c>
       <c r="M10" s="1">
-        <v>-0.0248561453932008</v>
+        <v>-0.00322614969444035</v>
       </c>
       <c r="N10" s="1">
-        <v>4.390817535022066</v>
+        <v>7.450147324773182</v>
       </c>
       <c r="O10" s="1">
-        <v>56.470588235294116</v>
+        <v>62.35294117647059</v>
       </c>
       <c r="P10" s="1">
         <v>14.568379622257217</v>
       </c>
       <c r="Q10" s="1">
-        <v>51.88235294117647</v>
+        <v>51.76470588235294</v>
       </c>
       <c r="R10" s="1">
-        <v>46.23529411764706</v>
+        <v>47.294117647058826</v>
       </c>
       <c r="S10" s="1" t="s">
         <v>103</v>
       </c>
       <c r="T10" s="1">
-        <v>10.69</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -2744,22 +2747,22 @@
         <v>46.68316831683168</v>
       </c>
       <c r="E11" s="2">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
       <c r="F11" s="2">
-        <v>0.5340386499796576</v>
+        <v>0.3476885486536194</v>
       </c>
       <c r="G11" s="2">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="H11" s="2">
-        <v>63.83</v>
+        <v>50.99</v>
       </c>
       <c r="I11" s="2">
-        <v>45.78</v>
+        <v>33.95</v>
       </c>
       <c r="J11" s="2">
-        <v>0.02412976788980005</v>
+        <v>0.021960151707457486</v>
       </c>
       <c r="K11" s="2" t="b">
         <v>0</v>
@@ -2768,28 +2771,28 @@
         <v>40</v>
       </c>
       <c r="M11" s="2">
-        <v>0.5172144969640653</v>
+        <v>0.3289348142298112</v>
       </c>
       <c r="N11" s="2">
-        <v>58.59788177074867</v>
+        <v>40.666243717198334</v>
       </c>
       <c r="O11" s="2">
-        <v>91.76470588235294</v>
+        <v>89.41176470588236</v>
       </c>
       <c r="P11" s="2">
         <v>21.2185970476566</v>
       </c>
       <c r="Q11" s="2">
-        <v>66</v>
+        <v>62.11764705882352</v>
       </c>
       <c r="R11" s="2">
-        <v>57.588235294117645</v>
+        <v>56.529411764705884</v>
       </c>
       <c r="S11" s="2" t="s">
         <v>104</v>
       </c>
       <c r="T11" s="2">
-        <v>5.94</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -2806,22 +2809,22 @@
         <v>65.16129032258064</v>
       </c>
       <c r="E12" s="2">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="F12" s="2">
-        <v>0.6516601148093444</v>
+        <v>0.5343973205552309</v>
       </c>
       <c r="G12" s="2">
         <v>0.99</v>
       </c>
       <c r="H12" s="2">
-        <v>58.62</v>
+        <v>51.41</v>
       </c>
       <c r="I12" s="2">
-        <v>50.88</v>
+        <v>45.08</v>
       </c>
       <c r="J12" s="2">
-        <v>0.041632056749910044</v>
+        <v>0.03953146008340663</v>
       </c>
       <c r="K12" s="2" t="b">
         <v>0</v>
@@ -2830,10 +2833,10 @@
         <v>30</v>
       </c>
       <c r="M12" s="2">
-        <v>0.6510799716019102</v>
+        <v>0.5337275443258092</v>
       </c>
       <c r="N12" s="2">
-        <v>71.98442923453318</v>
+        <v>61.14551672679812</v>
       </c>
       <c r="O12" s="2">
         <v>95.29411764705881</v>
@@ -2842,16 +2845,16 @@
         <v>23.557267760130397</v>
       </c>
       <c r="Q12" s="2">
-        <v>69.05882352941177</v>
+        <v>67.41176470588235</v>
       </c>
       <c r="R12" s="2">
-        <v>61.1764705882353</v>
+        <v>61.05882352941177</v>
       </c>
       <c r="S12" s="2" t="s">
         <v>105</v>
       </c>
       <c r="T12" s="2">
-        <v>8.43</v>
+        <v>8.31</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -2868,52 +2871,52 @@
         <v>-4529.499999999999</v>
       </c>
       <c r="E13" s="1">
-        <v>-1.08</v>
+        <v>0.14</v>
       </c>
       <c r="F13" s="1">
-        <v>0.4263643673759915</v>
+        <v>0.37801015538766347</v>
       </c>
       <c r="G13" s="1">
         <v>1.58</v>
       </c>
       <c r="H13" s="1">
-        <v>48.57</v>
+        <v>45.24</v>
       </c>
       <c r="I13" s="1">
-        <v>12.06</v>
+        <v>8.58</v>
       </c>
       <c r="J13" s="1">
-        <v>0.045699860353661935</v>
+        <v>0.04243333562607788</v>
       </c>
       <c r="K13" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
       </c>
       <c r="M13" s="1">
-        <v>0.4600126734071759</v>
+        <v>0.41685717669412337</v>
       </c>
       <c r="N13" s="1">
-        <v>52.87769941505973</v>
+        <v>49.45847996362955</v>
       </c>
       <c r="O13" s="1">
-        <v>89.41176470588236</v>
+        <v>91.76470588235294</v>
       </c>
       <c r="P13" s="1">
         <v>40.13761891809808</v>
       </c>
       <c r="Q13" s="1">
-        <v>39.529411764705884</v>
+        <v>38.58823529411765</v>
       </c>
       <c r="R13" s="1">
-        <v>36.52941176470589</v>
+        <v>37.235294117647065</v>
       </c>
       <c r="S13" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T13" s="1">
-        <v>35.74</v>
+        <v>36.44</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -2930,22 +2933,22 @@
         <v>5.385542168674699</v>
       </c>
       <c r="E14" s="2">
-        <v>-1.75</v>
+        <v>-1.81</v>
       </c>
       <c r="F14" s="2">
-        <v>0.6883602427348451</v>
+        <v>0.5089135044606476</v>
       </c>
       <c r="G14" s="2">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="H14" s="2">
-        <v>72.01</v>
+        <v>60.27</v>
       </c>
       <c r="I14" s="2">
-        <v>89.77</v>
+        <v>75.78</v>
       </c>
       <c r="J14" s="2">
-        <v>0.032676254454583886</v>
+        <v>0.034496986763934985</v>
       </c>
       <c r="K14" s="2" t="b">
         <v>0</v>
@@ -2954,28 +2957,28 @@
         <v>101</v>
       </c>
       <c r="M14" s="2">
-        <v>0.6738566625489897</v>
+        <v>0.4928388749545263</v>
       </c>
       <c r="N14" s="2">
-        <v>74.26209832924113</v>
+        <v>57.05664978966985</v>
       </c>
       <c r="O14" s="2">
-        <v>96.47058823529412</v>
+        <v>92.94117647058823</v>
       </c>
       <c r="P14" s="2">
         <v>19.142997204429033</v>
       </c>
       <c r="Q14" s="2">
-        <v>68.82352941176471</v>
+        <v>68.11764705882354</v>
       </c>
       <c r="R14" s="2">
-        <v>60.88235294117648</v>
+        <v>59.58823529411765</v>
       </c>
       <c r="S14" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T14" s="2">
-        <v>4.97</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -2992,34 +2995,34 @@
         <v>18.990566037735846</v>
       </c>
       <c r="E15" s="1">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="F15" s="1">
-        <v>-0.1825255115720157</v>
+        <v>-0.20357833542852233</v>
       </c>
       <c r="G15" s="1">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="H15" s="1">
-        <v>74.34</v>
+        <v>60.55</v>
       </c>
       <c r="I15" s="1">
-        <v>63.92</v>
+        <v>48.12</v>
       </c>
       <c r="J15" s="1">
-        <v>0.013991626364916392</v>
+        <v>0.020174346157904356</v>
       </c>
       <c r="K15" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L15" s="1">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="M15" s="1">
-        <v>-0.1100076106427389</v>
+        <v>-0.11918653052138539</v>
       </c>
       <c r="N15" s="1">
-        <v>-4.124328989931748</v>
+        <v>-4.145890757921323</v>
       </c>
       <c r="O15" s="1">
         <v>35.294117647058826</v>
@@ -3031,13 +3034,13 @@
         <v>62.82352941176471</v>
       </c>
       <c r="R15" s="1">
-        <v>33.235294117647065</v>
+        <v>33.58823529411765</v>
       </c>
       <c r="S15" s="1" t="s">
         <v>107</v>
       </c>
       <c r="T15" s="1">
-        <v>-25.18</v>
+        <v>-24.83</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -3054,52 +3057,52 @@
         <v>6.092261904761904</v>
       </c>
       <c r="E16" s="3">
-        <v>29.93</v>
+        <v>29.77</v>
       </c>
       <c r="F16" s="3">
-        <v>-0.3306596581502806</v>
+        <v>-0.42687328334488717</v>
       </c>
       <c r="G16" s="3">
         <v>1.8</v>
       </c>
       <c r="H16" s="3">
-        <v>48.8</v>
+        <v>42.74</v>
       </c>
       <c r="I16" s="3">
-        <v>-4.68</v>
+        <v>-8.97</v>
       </c>
       <c r="J16" s="3">
-        <v>-0.019216719442214092</v>
+        <v>-0.007127116777868138</v>
       </c>
       <c r="K16" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="3">
         <v>27</v>
       </c>
       <c r="M16" s="3">
-        <v>-0.2842482015555434</v>
+        <v>-0.37329118499114944</v>
       </c>
       <c r="N16" s="3">
-        <v>-21.548388081212195</v>
+        <v>-29.55635620489772</v>
       </c>
       <c r="O16" s="3">
-        <v>9.411764705882353</v>
+        <v>4.705882352941177</v>
       </c>
       <c r="P16" s="3">
         <v>40.1905830435425</v>
       </c>
       <c r="Q16" s="3">
-        <v>30.941176470588236</v>
+        <v>33.05882352941176</v>
       </c>
       <c r="R16" s="3">
-        <v>13.529411764705884</v>
+        <v>14</v>
       </c>
       <c r="S16" s="3" t="s">
         <v>108</v>
       </c>
       <c r="T16" s="3">
-        <v>-29.7</v>
+        <v>-29.23</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -3116,52 +3119,52 @@
         <v>6.226890756302521</v>
       </c>
       <c r="E17" s="1">
-        <v>-1.64</v>
+        <v>-1.63</v>
       </c>
       <c r="F17" s="1">
-        <v>-0.07270578235136307</v>
+        <v>-0.14119432085225458</v>
       </c>
       <c r="G17" s="1">
         <v>1.76</v>
       </c>
       <c r="H17" s="1">
-        <v>51.25</v>
+        <v>46.34</v>
       </c>
       <c r="I17" s="1">
-        <v>4.59</v>
+        <v>1.17</v>
       </c>
       <c r="J17" s="1">
-        <v>0.0051619944250029266</v>
+        <v>0.010813196832225178</v>
       </c>
       <c r="K17" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="1">
         <v>31</v>
       </c>
       <c r="M17" s="1">
-        <v>-0.02861489858636279</v>
+        <v>-0.09029132741620371</v>
       </c>
       <c r="N17" s="1">
-        <v>4.014942215705853</v>
+        <v>-1.256370447403158</v>
       </c>
       <c r="O17" s="1">
-        <v>55.294117647058826</v>
+        <v>44.70588235294118</v>
       </c>
       <c r="P17" s="1">
         <v>24.80206596461608</v>
       </c>
       <c r="Q17" s="1">
-        <v>41.647058823529406</v>
+        <v>42.35294117647058</v>
       </c>
       <c r="R17" s="1">
-        <v>34.235294117647065</v>
+        <v>32.352941176470594</v>
       </c>
       <c r="S17" s="1" t="s">
         <v>102</v>
       </c>
       <c r="T17" s="1">
-        <v>1.06</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -3178,22 +3181,22 @@
         <v>664</v>
       </c>
       <c r="E18" s="3">
-        <v>11.08</v>
+        <v>10.92</v>
       </c>
       <c r="F18" s="3">
-        <v>-0.7379893423809751</v>
+        <v>-0.7303934814384792</v>
       </c>
       <c r="G18" s="3">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="H18" s="3">
-        <v>14.63</v>
+        <v>22.55</v>
       </c>
       <c r="I18" s="3">
-        <v>-58.58</v>
+        <v>-55.15</v>
       </c>
       <c r="J18" s="3">
-        <v>-0.08236145440931923</v>
+        <v>-0.0826058430970883</v>
       </c>
       <c r="K18" s="3" t="b">
         <v>1</v>
@@ -3202,10 +3205,10 @@
         <v>31</v>
       </c>
       <c r="M18" s="3">
-        <v>-0.7310276238917646</v>
+        <v>-0.7236957191442619</v>
       </c>
       <c r="N18" s="3">
-        <v>-66.22633031483431</v>
+        <v>-64.59680962020899</v>
       </c>
       <c r="O18" s="3">
         <v>1.1764705882352942</v>
@@ -3240,22 +3243,22 @@
         <v>4.892035398230088</v>
       </c>
       <c r="E19" s="2">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="F19" s="2">
-        <v>0.11815369116035443</v>
+        <v>0.03610964820245662</v>
       </c>
       <c r="G19" s="2">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="H19" s="2">
-        <v>62.2</v>
+        <v>59.42</v>
       </c>
       <c r="I19" s="2">
-        <v>17.04</v>
+        <v>16.15</v>
       </c>
       <c r="J19" s="2">
-        <v>0.01030310000911132</v>
+        <v>0.011362774841695403</v>
       </c>
       <c r="K19" s="2" t="b">
         <v>1</v>
@@ -3264,28 +3267,28 @@
         <v>-60</v>
       </c>
       <c r="M19" s="2">
-        <v>0.06536065928384094</v>
+        <v>-0.02417021244549833</v>
       </c>
       <c r="N19" s="2">
-        <v>13.412498002726231</v>
+        <v>5.355741049667383</v>
       </c>
       <c r="O19" s="2">
-        <v>64.70588235294117</v>
+        <v>58.82352941176471</v>
       </c>
       <c r="P19" s="2">
         <v>11.392700631623551</v>
       </c>
       <c r="Q19" s="2">
-        <v>64.70588235294117</v>
+        <v>65.52941176470588</v>
       </c>
       <c r="R19" s="2">
-        <v>55.17647058823529</v>
+        <v>53.64705882352941</v>
       </c>
       <c r="S19" s="2" t="s">
         <v>110</v>
       </c>
       <c r="T19" s="2">
-        <v>6.76</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -3299,25 +3302,25 @@
         <v>70.58823529411765</v>
       </c>
       <c r="D20" s="2">
-        <v>-0.11030303030303032</v>
+        <v>0.08121212121212121</v>
       </c>
       <c r="E20" s="2">
-        <v>-5.69</v>
+        <v>-5.75</v>
       </c>
       <c r="F20" s="2">
-        <v>0.3109990847220883</v>
+        <v>0.184248357749065</v>
       </c>
       <c r="G20" s="2">
         <v>1.07</v>
       </c>
       <c r="H20" s="2">
-        <v>63.87</v>
+        <v>56.72</v>
       </c>
       <c r="I20" s="2">
-        <v>26.72</v>
+        <v>24.43</v>
       </c>
       <c r="J20" s="2">
-        <v>0.02473565319322041</v>
+        <v>0.023697002340234787</v>
       </c>
       <c r="K20" s="2" t="b">
         <v>0</v>
@@ -3326,13 +3329,13 @@
         <v>8</v>
       </c>
       <c r="M20" s="2">
-        <v>0.3150600871741278</v>
+        <v>0.18893679135501706</v>
       </c>
       <c r="N20" s="2">
-        <v>38.382440791754924</v>
+        <v>26.66644142971892</v>
       </c>
       <c r="O20" s="2">
-        <v>84.70588235294117</v>
+        <v>82.35294117647058</v>
       </c>
       <c r="P20" s="2">
         <v>15.052477440996265</v>
@@ -3341,13 +3344,13 @@
         <v>64.11764705882354</v>
       </c>
       <c r="R20" s="2">
-        <v>56.88235294117648</v>
+        <v>57.117647058823536</v>
       </c>
       <c r="S20" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T20" s="2">
-        <v>21.03</v>
+        <v>21.26</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -3361,55 +3364,55 @@
         <v>38.82352941176471</v>
       </c>
       <c r="D21" s="3">
-        <v>9.623762376237623</v>
+        <v>9.584158415841584</v>
       </c>
       <c r="E21" s="3">
         <v>-3.44</v>
       </c>
       <c r="F21" s="3">
-        <v>-0.4101216391199482</v>
+        <v>-0.43896513365536965</v>
       </c>
       <c r="G21" s="3">
         <v>1.63</v>
       </c>
       <c r="H21" s="3">
-        <v>35.55</v>
+        <v>31.04</v>
       </c>
       <c r="I21" s="3">
-        <v>-19.5</v>
+        <v>-22.37</v>
       </c>
       <c r="J21" s="3">
-        <v>-0.026776359199948047</v>
+        <v>-0.026107129338858687</v>
       </c>
       <c r="K21" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" s="3">
         <v>55</v>
       </c>
       <c r="M21" s="3">
-        <v>-0.3735726170515927</v>
+        <v>-0.3967692312018012</v>
       </c>
       <c r="N21" s="3">
-        <v>-30.48082963081713</v>
+        <v>-31.9041608259629</v>
       </c>
       <c r="O21" s="3">
-        <v>3.5294117647058822</v>
+        <v>2.3529411764705883</v>
       </c>
       <c r="P21" s="3">
-        <v>54.624638650661495</v>
+        <v>55.20530802479801</v>
       </c>
       <c r="Q21" s="3">
-        <v>35.52941176470589</v>
+        <v>35.1764705882353</v>
       </c>
       <c r="R21" s="3">
-        <v>19.11764705882353</v>
+        <v>18.764705882352942</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>111</v>
       </c>
       <c r="T21" s="3">
-        <v>-32.1</v>
+        <v>-32.45</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -3426,52 +3429,52 @@
         <v>0.7558962264150944</v>
       </c>
       <c r="E22" s="1">
-        <v>-0.24</v>
+        <v>-0.25</v>
       </c>
       <c r="F22" s="1">
-        <v>-0.21680737246601367</v>
+        <v>-0.21675636535697101</v>
       </c>
       <c r="G22" s="1">
         <v>1.38</v>
       </c>
       <c r="H22" s="1">
-        <v>40.92</v>
+        <v>47.26</v>
       </c>
       <c r="I22" s="1">
-        <v>-0.74</v>
+        <v>1.09</v>
       </c>
       <c r="J22" s="1">
-        <v>-0.011157217131063461</v>
+        <v>-0.009629701095594167</v>
       </c>
       <c r="K22" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" s="1">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="M22" s="1">
-        <v>-0.19476193058351354</v>
+        <v>-0.19130486863894558</v>
       </c>
       <c r="N22" s="1">
-        <v>-12.599760984009217</v>
+        <v>-11.357724569677337</v>
       </c>
       <c r="O22" s="1">
-        <v>18.823529411764707</v>
+        <v>22.35294117647059</v>
       </c>
       <c r="P22" s="1">
         <v>19.455960650079966</v>
       </c>
       <c r="Q22" s="1">
-        <v>44.35294117647058</v>
+        <v>46.23529411764705</v>
       </c>
       <c r="R22" s="1">
-        <v>32.705882352941174</v>
+        <v>33.17647058823529</v>
       </c>
       <c r="S22" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T22" s="1">
-        <v>-20.4</v>
+        <v>-19.93</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -3485,37 +3488,37 @@
         <v>96.47058823529412</v>
       </c>
       <c r="D23" s="2">
-        <v>-0.6689265536723165</v>
+        <v>-0.6681732580037666</v>
       </c>
       <c r="E23" s="2">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="F23" s="2">
-        <v>0.35258172772505253</v>
+        <v>0.2742406485153579</v>
       </c>
       <c r="G23" s="2">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="H23" s="2">
-        <v>80.08</v>
+        <v>63.56</v>
       </c>
       <c r="I23" s="2">
-        <v>23.92</v>
+        <v>15.8</v>
       </c>
       <c r="J23" s="2">
-        <v>0.012049575661449066</v>
+        <v>0.013776241769028136</v>
       </c>
       <c r="K23" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L23" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M23" s="2">
-        <v>0.3636044486663026</v>
+        <v>0.2883059493332141</v>
       </c>
       <c r="N23" s="2">
-        <v>43.2368769409724</v>
+        <v>36.603357227538616</v>
       </c>
       <c r="O23" s="2">
         <v>87.05882352941177</v>
@@ -3524,16 +3527,16 @@
         <v>20.883293768118005</v>
       </c>
       <c r="Q23" s="2">
-        <v>65.76470588235293</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="R23" s="2">
-        <v>57.41176470588236</v>
+        <v>57.29411764705883</v>
       </c>
       <c r="S23" s="2" t="s">
         <v>110</v>
       </c>
       <c r="T23" s="2">
-        <v>21.62</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -3550,22 +3553,22 @@
         <v>2.6549737681308505</v>
       </c>
       <c r="E24" s="1">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="F24" s="1">
-        <v>0.6754998678271693</v>
+        <v>0.6757837538162064</v>
       </c>
       <c r="G24" s="1">
-        <v>3.58</v>
+        <v>3.59</v>
       </c>
       <c r="H24" s="1">
-        <v>66.05</v>
+        <v>60.5</v>
       </c>
       <c r="I24" s="1">
-        <v>18.78</v>
+        <v>13.44</v>
       </c>
       <c r="J24" s="1">
-        <v>0.061648721352105355</v>
+        <v>0.06180199100874978</v>
       </c>
       <c r="K24" s="1" t="b">
         <v>0</v>
@@ -3574,10 +3577,10 @@
         <v>-69</v>
       </c>
       <c r="M24" s="1">
-        <v>0.8251768153451966</v>
+        <v>0.8492557972364323</v>
       </c>
       <c r="N24" s="1">
-        <v>89.39411360886179</v>
+        <v>92.69834201786044</v>
       </c>
       <c r="O24" s="1">
         <v>100</v>
@@ -3586,7 +3589,7 @@
         <v>57.99224429263358</v>
       </c>
       <c r="Q24" s="1">
-        <v>52.82352941176471</v>
+        <v>52.352941176470594</v>
       </c>
       <c r="R24" s="1">
         <v>43.64705882352941</v>
@@ -3615,19 +3618,19 @@
         <v>15.51</v>
       </c>
       <c r="F25" s="3">
-        <v>-0.3065515304484267</v>
+        <v>-0.33515384773990087</v>
       </c>
       <c r="G25" s="3">
         <v>2.36</v>
       </c>
       <c r="H25" s="3">
-        <v>45.22</v>
+        <v>42.67</v>
       </c>
       <c r="I25" s="3">
-        <v>-30.09</v>
+        <v>-32.09</v>
       </c>
       <c r="J25" s="3">
-        <v>-0.0006184264868946928</v>
+        <v>0.0027876121455046453</v>
       </c>
       <c r="K25" s="3" t="b">
         <v>0</v>
@@ -3636,13 +3639,13 @@
         <v>34</v>
       </c>
       <c r="M25" s="3">
-        <v>-0.22765205423737356</v>
+        <v>-0.24406428053854667</v>
       </c>
       <c r="N25" s="3">
-        <v>-15.888773349395215</v>
+        <v>-16.633665759637445</v>
       </c>
       <c r="O25" s="3">
-        <v>16.470588235294116</v>
+        <v>15.294117647058824</v>
       </c>
       <c r="P25" s="3">
         <v>45.59139601172712</v>
@@ -3674,22 +3677,22 @@
         <v>-0.6021978021978023</v>
       </c>
       <c r="E26" s="3">
-        <v>-0.85</v>
+        <v>-0.83</v>
       </c>
       <c r="F26" s="3">
-        <v>-0.3166222181737807</v>
+        <v>-0.31413649611675387</v>
       </c>
       <c r="G26" s="3">
         <v>3.37</v>
       </c>
       <c r="H26" s="3">
-        <v>61.89</v>
+        <v>58.32</v>
       </c>
       <c r="I26" s="3">
-        <v>2.79</v>
+        <v>0.83</v>
       </c>
       <c r="J26" s="3">
-        <v>0.002331961676426706</v>
+        <v>0.010501055033496057</v>
       </c>
       <c r="K26" s="3" t="b">
         <v>1</v>
@@ -3698,28 +3701,28 @@
         <v>160</v>
       </c>
       <c r="M26" s="3">
-        <v>-0.17912827801187192</v>
+        <v>-0.15539952974380578</v>
       </c>
       <c r="N26" s="3">
-        <v>-11.036395726845049</v>
+        <v>-7.767190680163366</v>
       </c>
       <c r="O26" s="3">
-        <v>21.176470588235293</v>
+        <v>29.411764705882355</v>
       </c>
       <c r="P26" s="3">
         <v>55.61259899184437</v>
       </c>
       <c r="Q26" s="3">
-        <v>29.176470588235293</v>
+        <v>32.23529411764706</v>
       </c>
       <c r="R26" s="3">
-        <v>7.588235294117645</v>
+        <v>11.823529411764703</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T26" s="3">
-        <v>-21.25</v>
+        <v>-17.02</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -3736,22 +3739,22 @@
         <v>-1.7653061224489797</v>
       </c>
       <c r="E27" s="3">
-        <v>6.87</v>
+        <v>6.8</v>
       </c>
       <c r="F27" s="3">
-        <v>-0.45480876149569793</v>
+        <v>-0.47249888581735155</v>
       </c>
       <c r="G27" s="3">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="H27" s="3">
-        <v>40.72</v>
+        <v>37.59</v>
       </c>
       <c r="I27" s="3">
-        <v>-35.22</v>
+        <v>-36.34</v>
       </c>
       <c r="J27" s="3">
-        <v>-0.019978165100761277</v>
+        <v>-0.017748881536410743</v>
       </c>
       <c r="K27" s="3" t="b">
         <v>0</v>
@@ -3760,28 +3763,28 @@
         <v>7</v>
       </c>
       <c r="M27" s="3">
-        <v>-0.3585049890616183</v>
+        <v>-0.36198580796276747</v>
       </c>
       <c r="N27" s="3">
-        <v>-28.974066831819695</v>
+        <v>-28.425818502059524</v>
       </c>
       <c r="O27" s="3">
-        <v>4.705882352941177</v>
+        <v>5.88235294117647</v>
       </c>
       <c r="P27" s="3">
         <v>50.56910707785277</v>
       </c>
       <c r="Q27" s="3">
-        <v>13.176470588235295</v>
+        <v>12.941176470588236</v>
       </c>
       <c r="R27" s="3">
-        <v>0.7647058823529402</v>
+        <v>1.2352941176470562</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T27" s="3">
-        <v>-15.39</v>
+        <v>-14.92</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -3798,22 +3801,22 @@
         <v>8.555555555555555</v>
       </c>
       <c r="E28" s="1">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="F28" s="1">
-        <v>-0.007809862320691002</v>
+        <v>-0.07714627762008325</v>
       </c>
       <c r="G28" s="1">
         <v>3.26</v>
       </c>
       <c r="H28" s="1">
-        <v>52.95</v>
+        <v>48.22</v>
       </c>
       <c r="I28" s="1">
-        <v>-8.69</v>
+        <v>-11.49</v>
       </c>
       <c r="J28" s="1">
-        <v>0.014709630294739586</v>
+        <v>0.01726895947340087</v>
       </c>
       <c r="K28" s="1" t="b">
         <v>0</v>
@@ -3822,28 +3825,28 @@
         <v>3</v>
       </c>
       <c r="M28" s="1">
-        <v>0.12330250255944142</v>
+        <v>0.07422315022922588</v>
       </c>
       <c r="N28" s="1">
-        <v>19.206682330286288</v>
+        <v>15.195077317139798</v>
       </c>
       <c r="O28" s="1">
-        <v>72.94117647058823</v>
+        <v>68.23529411764706</v>
       </c>
       <c r="P28" s="1">
         <v>35.08771990976345</v>
       </c>
       <c r="Q28" s="1">
-        <v>49.764705882352935</v>
+        <v>48.705882352941174</v>
       </c>
       <c r="R28" s="1">
-        <v>43.64705882352941</v>
+        <v>42.117647058823536</v>
       </c>
       <c r="S28" s="1" t="s">
         <v>112</v>
       </c>
       <c r="T28" s="1">
-        <v>26.63</v>
+        <v>25.11</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -3860,22 +3863,22 @@
         <v>81.95744680851065</v>
       </c>
       <c r="E29" s="1">
-        <v>-4.83</v>
+        <v>-4.82</v>
       </c>
       <c r="F29" s="1">
-        <v>-0.17424495950336633</v>
+        <v>-0.23884498109153313</v>
       </c>
       <c r="G29" s="1">
         <v>2.32</v>
       </c>
       <c r="H29" s="1">
-        <v>44.24</v>
+        <v>39.45</v>
       </c>
       <c r="I29" s="1">
-        <v>-12.28</v>
+        <v>-14.9</v>
       </c>
       <c r="J29" s="1">
-        <v>-0.008462453192343537</v>
+        <v>-0.007439688989360435</v>
       </c>
       <c r="K29" s="1" t="b">
         <v>1</v>
@@ -3884,28 +3887,28 @@
         <v>11</v>
       </c>
       <c r="M29" s="1">
-        <v>-0.09766605612205004</v>
+        <v>-0.15043451880786585</v>
       </c>
       <c r="N29" s="1">
-        <v>-2.8901735378628564</v>
+        <v>-7.270689586569364</v>
       </c>
       <c r="O29" s="1">
-        <v>40</v>
+        <v>30.58823529411765</v>
       </c>
       <c r="P29" s="1">
         <v>18.79659508828292</v>
       </c>
       <c r="Q29" s="1">
-        <v>47.64705882352941</v>
+        <v>46.23529411764706</v>
       </c>
       <c r="R29" s="1">
-        <v>42.76470588235294</v>
+        <v>39.705882352941174</v>
       </c>
       <c r="S29" s="1" t="s">
         <v>110</v>
       </c>
       <c r="T29" s="1">
-        <v>2.52</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -3922,52 +3925,52 @@
         <v>224.99545454545452</v>
       </c>
       <c r="E30" s="1">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="F30" s="1">
-        <v>-0.1810122276425397</v>
+        <v>-0.1827573804649707</v>
       </c>
       <c r="G30" s="1">
         <v>1.25</v>
       </c>
       <c r="H30" s="1">
-        <v>36.72</v>
+        <v>35.14</v>
       </c>
       <c r="I30" s="1">
-        <v>-10.7</v>
+        <v>-11.62</v>
       </c>
       <c r="J30" s="1">
-        <v>-0.009442467392974703</v>
+        <v>-0.00866513021471953</v>
       </c>
       <c r="K30" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L30" s="1">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M30" s="1">
-        <v>-0.16650864745668437</v>
+        <v>-0.16601297472942766</v>
       </c>
       <c r="N30" s="1">
-        <v>-9.774432671326291</v>
+        <v>-8.828535178725547</v>
       </c>
       <c r="O30" s="1">
-        <v>27.058823529411764</v>
+        <v>25.882352941176475</v>
       </c>
       <c r="P30" s="1">
         <v>18.204489584640044</v>
       </c>
       <c r="Q30" s="1">
-        <v>50.470588235294116</v>
+        <v>49.882352941176464</v>
       </c>
       <c r="R30" s="1">
-        <v>43</v>
+        <v>42.1764705882353</v>
       </c>
       <c r="S30" s="1" t="s">
         <v>111</v>
       </c>
       <c r="T30" s="1">
-        <v>-5.48</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -3984,52 +3987,52 @@
         <v>7.286079182630906</v>
       </c>
       <c r="E31" s="1">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="F31" s="1">
-        <v>-0.17137880698784186</v>
+        <v>-0.14265730522796</v>
       </c>
       <c r="G31" s="1">
         <v>1.47</v>
       </c>
       <c r="H31" s="1">
-        <v>45.36</v>
+        <v>41.14</v>
       </c>
       <c r="I31" s="1">
-        <v>-3.54</v>
+        <v>-5.45</v>
       </c>
       <c r="J31" s="1">
-        <v>-0.009371948354026896</v>
+        <v>-0.008242151808458241</v>
       </c>
       <c r="K31" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L31" s="1">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="M31" s="1">
-        <v>-0.1441120762384338</v>
+        <v>-0.11117782244513907</v>
       </c>
       <c r="N31" s="1">
-        <v>-7.534775549501241</v>
+        <v>-3.345019950296694</v>
       </c>
       <c r="O31" s="1">
-        <v>32.94117647058823</v>
+        <v>37.64705882352941</v>
       </c>
       <c r="P31" s="1">
         <v>29.54918623383928</v>
       </c>
       <c r="Q31" s="1">
-        <v>52.23529411764706</v>
+        <v>50.47058823529411</v>
       </c>
       <c r="R31" s="1">
-        <v>39.588235294117645</v>
+        <v>40.64705882352941</v>
       </c>
       <c r="S31" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T31" s="1">
-        <v>-8.46</v>
+        <v>-7.4</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -4046,22 +4049,22 @@
         <v>8.848837209302324</v>
       </c>
       <c r="E32" s="1">
-        <v>3.57</v>
+        <v>3.6</v>
       </c>
       <c r="F32" s="1">
-        <v>-0.0757964354650135</v>
+        <v>-0.12949046357710658</v>
       </c>
       <c r="G32" s="1">
         <v>1.62</v>
       </c>
       <c r="H32" s="1">
-        <v>46.14</v>
+        <v>46.15</v>
       </c>
       <c r="I32" s="1">
-        <v>-5.29</v>
+        <v>-5.27</v>
       </c>
       <c r="J32" s="1">
-        <v>-0.015269334595524313</v>
+        <v>-0.013463269745334855</v>
       </c>
       <c r="K32" s="1" t="b">
         <v>0</v>
@@ -4070,28 +4073,28 @@
         <v>21</v>
       </c>
       <c r="M32" s="1">
-        <v>-0.03982755660409221</v>
+        <v>-0.08796433735295983</v>
       </c>
       <c r="N32" s="1">
-        <v>2.8936764139329125</v>
+        <v>-1.0236714410787613</v>
       </c>
       <c r="O32" s="1">
-        <v>54.11764705882353</v>
+        <v>45.88235294117647</v>
       </c>
       <c r="P32" s="1">
         <v>26.613703173358488</v>
       </c>
       <c r="Q32" s="1">
-        <v>34.470588235294116</v>
+        <v>35.17647058823529</v>
       </c>
       <c r="R32" s="1">
-        <v>32.94117647058823</v>
+        <v>30.11764705882353</v>
       </c>
       <c r="S32" s="1" t="s">
         <v>109</v>
       </c>
       <c r="T32" s="1">
-        <v>1.05</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -4108,52 +4111,52 @@
         <v>0.0579387186629526</v>
       </c>
       <c r="E33" s="2">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="F33" s="2">
-        <v>0.3366804893544467</v>
+        <v>0.29951965383047985</v>
       </c>
       <c r="G33" s="2">
         <v>1.1</v>
       </c>
       <c r="H33" s="2">
-        <v>53.21</v>
+        <v>61.24</v>
       </c>
       <c r="I33" s="2">
-        <v>14.89</v>
+        <v>18.78</v>
       </c>
       <c r="J33" s="2">
-        <v>0.023823104227291014</v>
+        <v>0.02395408619617998</v>
       </c>
       <c r="K33" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M33" s="2">
-        <v>0.34248192142878886</v>
+        <v>0.3062174161246971</v>
       </c>
       <c r="N33" s="2">
-        <v>41.124624217221026</v>
+        <v>38.39450390668692</v>
       </c>
       <c r="O33" s="2">
-        <v>85.88235294117646</v>
+        <v>88.23529411764706</v>
       </c>
       <c r="P33" s="2">
         <v>23.38443607454554</v>
       </c>
       <c r="Q33" s="2">
-        <v>66.3529411764706</v>
+        <v>70.47058823529412</v>
       </c>
       <c r="R33" s="2">
-        <v>60</v>
+        <v>60.52941176470589</v>
       </c>
       <c r="S33" s="2" t="s">
         <v>110</v>
       </c>
       <c r="T33" s="2">
-        <v>24.21</v>
+        <v>24.74</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -4170,52 +4173,52 @@
         <v>-2.3345052737317933</v>
       </c>
       <c r="E34" s="1">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="F34" s="1">
-        <v>-0.08487507572712688</v>
+        <v>-0.07243847195118878</v>
       </c>
       <c r="G34" s="1">
         <v>1.21</v>
       </c>
       <c r="H34" s="1">
-        <v>48.93</v>
+        <v>46.99</v>
       </c>
       <c r="I34" s="1">
-        <v>1.38</v>
+        <v>0.57</v>
       </c>
       <c r="J34" s="1">
-        <v>-0.003652781588481443</v>
+        <v>-0.003723626856012923</v>
       </c>
       <c r="K34" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" s="1">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="M34" s="1">
-        <v>-0.07269206837100839</v>
+        <v>-0.058373171133332624</v>
       </c>
       <c r="N34" s="1">
-        <v>-0.3927747627586982</v>
+        <v>1.9354451808839614</v>
       </c>
       <c r="O34" s="1">
-        <v>45.88235294117647</v>
+        <v>51.76470588235295</v>
       </c>
       <c r="P34" s="1">
         <v>21.09433056126816</v>
       </c>
       <c r="Q34" s="1">
-        <v>45.882352941176464</v>
+        <v>46</v>
       </c>
       <c r="R34" s="1">
-        <v>38.1764705882353</v>
+        <v>40.058823529411775</v>
       </c>
       <c r="S34" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T34" s="1">
-        <v>-8.65</v>
+        <v>-6.77</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -4229,25 +4232,25 @@
         <v>87.05882352941177</v>
       </c>
       <c r="D35" s="1">
-        <v>-0.4631519274376417</v>
+        <v>-0.4535147392290249</v>
       </c>
       <c r="E35" s="1">
-        <v>-0.47</v>
+        <v>-0.5</v>
       </c>
       <c r="F35" s="1">
-        <v>-0.047054051288710264</v>
+        <v>-0.09396511344847842</v>
       </c>
       <c r="G35" s="1">
-        <v>0.95</v>
+        <v>0.94</v>
       </c>
       <c r="H35" s="1">
-        <v>32.16</v>
+        <v>32.63</v>
       </c>
       <c r="I35" s="1">
-        <v>-17.93</v>
+        <v>-17.8</v>
       </c>
       <c r="J35" s="1">
-        <v>-0.002689614466869727</v>
+        <v>-0.005070446573245401</v>
       </c>
       <c r="K35" s="1" t="b">
         <v>0</v>
@@ -4256,28 +4259,28 @@
         <v>-57</v>
       </c>
       <c r="M35" s="1">
-        <v>-0.04995476732588133</v>
+        <v>-0.09798377082500875</v>
       </c>
       <c r="N35" s="1">
-        <v>1.8809553417540148</v>
+        <v>-2.025614788283657</v>
       </c>
       <c r="O35" s="1">
-        <v>51.76470588235295</v>
+        <v>42.35294117647059</v>
       </c>
       <c r="P35" s="1">
-        <v>20.292142946083924</v>
+        <v>20.53422985929523</v>
       </c>
       <c r="Q35" s="1">
-        <v>42</v>
+        <v>41.294117647058826</v>
       </c>
       <c r="R35" s="1">
-        <v>42.41176470588236</v>
+        <v>39</v>
       </c>
       <c r="S35" s="1" t="s">
         <v>101</v>
       </c>
       <c r="T35" s="1">
-        <v>19.91</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -4294,52 +4297,52 @@
         <v>0.009737098344693247</v>
       </c>
       <c r="E36" s="1">
-        <v>-1.3</v>
+        <v>-1.31</v>
       </c>
       <c r="F36" s="1">
-        <v>-0.0994227443660013</v>
+        <v>-0.0886056317002658</v>
       </c>
       <c r="G36" s="1">
         <v>1.12</v>
       </c>
       <c r="H36" s="1">
-        <v>42.7</v>
+        <v>42.74</v>
       </c>
       <c r="I36" s="1">
-        <v>-9.75</v>
+        <v>-9.69</v>
       </c>
       <c r="J36" s="1">
-        <v>0.0032861538217901338</v>
+        <v>0.002882098033871043</v>
       </c>
       <c r="K36" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" s="1">
         <v>-18</v>
       </c>
       <c r="M36" s="1">
-        <v>-0.09246102587679073</v>
+        <v>-0.08056831694720512</v>
       </c>
       <c r="N36" s="1">
-        <v>-2.3696705133369345</v>
+        <v>-0.2840694005032938</v>
       </c>
       <c r="O36" s="1">
-        <v>41.17647058823529</v>
+        <v>47.05882352941176</v>
       </c>
       <c r="P36" s="1">
         <v>26.730280409441182</v>
       </c>
       <c r="Q36" s="1">
-        <v>47.1764705882353</v>
+        <v>47.64705882352942</v>
       </c>
       <c r="R36" s="1">
-        <v>38.529411764705884</v>
+        <v>39.94117647058823</v>
       </c>
       <c r="S36" s="1" t="s">
         <v>108</v>
       </c>
       <c r="T36" s="1">
-        <v>11.58</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -4356,52 +4359,52 @@
         <v>0.42155009451795833</v>
       </c>
       <c r="E37" s="2">
-        <v>-3.26</v>
+        <v>-3.28</v>
       </c>
       <c r="F37" s="2">
-        <v>0.1561430887128934</v>
+        <v>0.14623708421868045</v>
       </c>
       <c r="G37" s="2">
         <v>1.28</v>
       </c>
       <c r="H37" s="2">
-        <v>41.06</v>
+        <v>50.84</v>
       </c>
       <c r="I37" s="2">
-        <v>4.36</v>
+        <v>8.62</v>
       </c>
       <c r="J37" s="2">
-        <v>0.007392605857651344</v>
+        <v>0.004268824971623391</v>
       </c>
       <c r="K37" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2">
         <v>-108</v>
       </c>
       <c r="M37" s="2">
-        <v>0.17238709852105139</v>
+        <v>0.16499081864248866</v>
       </c>
       <c r="N37" s="2">
-        <v>24.115141926447272</v>
+        <v>24.271844158466088</v>
       </c>
       <c r="O37" s="2">
-        <v>77.64705882352942</v>
+        <v>81.17647058823529</v>
       </c>
       <c r="P37" s="2">
-        <v>20.1020772277769</v>
+        <v>19.310067662476122</v>
       </c>
       <c r="Q37" s="2">
-        <v>49.294117647058826</v>
+        <v>51.294117647058826</v>
       </c>
       <c r="R37" s="2">
-        <v>50.588235294117645</v>
+        <v>50.823529411764696</v>
       </c>
       <c r="S37" s="2" t="s">
         <v>111</v>
       </c>
       <c r="T37" s="2">
-        <v>20.77</v>
+        <v>21.01</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -4418,34 +4421,34 @@
         <v>689</v>
       </c>
       <c r="E38" s="2">
-        <v>3.13</v>
+        <v>3.02</v>
       </c>
       <c r="F38" s="2">
-        <v>0.46236494132502365</v>
+        <v>0.34670995161913987</v>
       </c>
       <c r="G38" s="2">
         <v>1.21</v>
       </c>
       <c r="H38" s="2">
-        <v>66.26</v>
+        <v>60.16</v>
       </c>
       <c r="I38" s="2">
-        <v>72.19</v>
+        <v>65.21</v>
       </c>
       <c r="J38" s="2">
-        <v>0.027242657661209382</v>
+        <v>0.02678620788946634</v>
       </c>
       <c r="K38" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L38" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="M38" s="2">
-        <v>0.47454794868114214</v>
+        <v>0.36077525243699604</v>
       </c>
       <c r="N38" s="2">
-        <v>54.331226942456354</v>
+        <v>43.85028753791681</v>
       </c>
       <c r="O38" s="2">
         <v>90.58823529411765</v>
@@ -4454,16 +4457,16 @@
         <v>17.802507034008837</v>
       </c>
       <c r="Q38" s="2">
-        <v>76</v>
+        <v>75.41176470588235</v>
       </c>
       <c r="R38" s="2">
-        <v>66.23529411764706</v>
+        <v>66.11764705882354</v>
       </c>
       <c r="S38" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T38" s="2">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -4483,19 +4486,19 @@
         <v>-1.29</v>
       </c>
       <c r="F39" s="1">
-        <v>-0.10697600929726371</v>
+        <v>-0.15308305745539563</v>
       </c>
       <c r="G39" s="1">
         <v>1.12</v>
       </c>
       <c r="H39" s="1">
-        <v>37.55</v>
+        <v>34.4</v>
       </c>
       <c r="I39" s="1">
-        <v>-7.44</v>
+        <v>-8.88</v>
       </c>
       <c r="J39" s="1">
-        <v>-0.006455693050868042</v>
+        <v>-0.008141943524639835</v>
       </c>
       <c r="K39" s="1" t="b">
         <v>0</v>
@@ -4504,28 +4507,28 @@
         <v>-1</v>
       </c>
       <c r="M39" s="1">
-        <v>-0.10001429080805313</v>
+        <v>-0.14504574270233495</v>
       </c>
       <c r="N39" s="1">
-        <v>-3.1249970064631656</v>
+        <v>-6.731811976016282</v>
       </c>
       <c r="O39" s="1">
-        <v>38.82352941176471</v>
+        <v>31.76470588235294</v>
       </c>
       <c r="P39" s="1">
         <v>30.28933322215756</v>
       </c>
       <c r="Q39" s="1">
-        <v>42.11764705882353</v>
+        <v>41.05882352941177</v>
       </c>
       <c r="R39" s="1">
-        <v>34.82352941176471</v>
+        <v>32.117647058823536</v>
       </c>
       <c r="S39" s="1" t="s">
         <v>112</v>
       </c>
       <c r="T39" s="1">
-        <v>9.03</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -4542,22 +4545,22 @@
         <v>10.75575027382256</v>
       </c>
       <c r="E40" s="1">
-        <v>4.43</v>
+        <v>4.41</v>
       </c>
       <c r="F40" s="1">
-        <v>0.6443761270143141</v>
+        <v>0.5552639578608645</v>
       </c>
       <c r="G40" s="1">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="H40" s="1">
-        <v>64.39</v>
+        <v>54.6</v>
       </c>
       <c r="I40" s="1">
-        <v>17.81</v>
+        <v>8.5</v>
       </c>
       <c r="J40" s="1">
-        <v>0.051387921921507894</v>
+        <v>0.05542848641340796</v>
       </c>
       <c r="K40" s="1" t="b">
         <v>0</v>
@@ -4566,28 +4569,28 @@
         <v>-21</v>
       </c>
       <c r="M40" s="1">
-        <v>0.622330685131814</v>
+        <v>0.5358404472076346</v>
       </c>
       <c r="N40" s="1">
-        <v>69.10950058752353</v>
+        <v>61.356807014980674</v>
       </c>
       <c r="O40" s="1">
-        <v>94.11764705882352</v>
+        <v>96.47058823529412</v>
       </c>
       <c r="P40" s="1">
         <v>51.940889187924654</v>
       </c>
       <c r="Q40" s="1">
-        <v>58.00000000000001</v>
+        <v>55.1764705882353</v>
       </c>
       <c r="R40" s="1">
-        <v>47.352941176470594</v>
+        <v>48.1764705882353</v>
       </c>
       <c r="S40" s="1" t="s">
         <v>113</v>
       </c>
       <c r="T40" s="1">
-        <v>38.88</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -4604,22 +4607,22 @@
         <v>1.5553319919517103</v>
       </c>
       <c r="E41" s="3">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="F41" s="3">
-        <v>-0.1031559793739243</v>
+        <v>-0.06362393633320472</v>
       </c>
       <c r="G41" s="3">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="H41" s="3">
-        <v>38.7</v>
+        <v>43.45</v>
       </c>
       <c r="I41" s="3">
-        <v>-13.92</v>
+        <v>-12.09</v>
       </c>
       <c r="J41" s="3">
-        <v>-0.02171290738253668</v>
+        <v>-0.020462325952884004</v>
       </c>
       <c r="K41" s="3" t="b">
         <v>1</v>
@@ -4628,28 +4631,28 @@
         <v>4</v>
       </c>
       <c r="M41" s="3">
-        <v>-0.09039282881037158</v>
+        <v>-0.04955863551534856</v>
       </c>
       <c r="N41" s="3">
-        <v>-2.162850806695012</v>
+        <v>2.816898742682366</v>
       </c>
       <c r="O41" s="3">
-        <v>42.35294117647059</v>
+        <v>54.11764705882353</v>
       </c>
       <c r="P41" s="3">
         <v>30.769232468942608</v>
       </c>
       <c r="Q41" s="3">
-        <v>20.47058823529412</v>
+        <v>21.88235294117647</v>
       </c>
       <c r="R41" s="3">
-        <v>19.705882352941174</v>
+        <v>22.88235294117647</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>107</v>
       </c>
       <c r="T41" s="3">
-        <v>-16.94</v>
+        <v>-13.76</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -4666,22 +4669,22 @@
         <v>1.2252252252252251</v>
       </c>
       <c r="E42" s="3">
-        <v>4.33</v>
+        <v>4.78</v>
       </c>
       <c r="F42" s="3">
-        <v>-0.2081042627953599</v>
+        <v>-0.23275652570528926</v>
       </c>
       <c r="G42" s="3">
         <v>0.31</v>
       </c>
       <c r="H42" s="3">
-        <v>58.36</v>
+        <v>28.95</v>
       </c>
       <c r="I42" s="3">
-        <v>-4.99</v>
+        <v>-12.56</v>
       </c>
       <c r="J42" s="3">
-        <v>-0.015573571138320641</v>
+        <v>-0.016096717338958923</v>
       </c>
       <c r="K42" s="3" t="b">
         <v>1</v>
@@ -4690,28 +4693,28 @@
         <v>16</v>
       </c>
       <c r="M42" s="3">
-        <v>-0.2481341441083207</v>
+        <v>-0.2789710855353881</v>
       </c>
       <c r="N42" s="3">
-        <v>-17.93698233648992</v>
+        <v>-20.124346259321587</v>
       </c>
       <c r="O42" s="3">
-        <v>14.117647058823529</v>
+        <v>9.411764705882353</v>
       </c>
       <c r="P42" s="3">
         <v>20.352744065122756</v>
       </c>
       <c r="Q42" s="3">
-        <v>42</v>
+        <v>33.529411764705884</v>
       </c>
       <c r="R42" s="3">
-        <v>25.88235294117647</v>
+        <v>24.23529411764706</v>
       </c>
       <c r="S42" s="3" t="s">
         <v>111</v>
       </c>
       <c r="T42" s="3">
-        <v>-9.61</v>
+        <v>-11.25</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -4728,22 +4731,22 @@
         <v>150.93333333333334</v>
       </c>
       <c r="E43" s="2">
-        <v>8.78</v>
+        <v>8.46</v>
       </c>
       <c r="F43" s="2">
-        <v>0.16957343213417514</v>
+        <v>0.11784112195349697</v>
       </c>
       <c r="G43" s="2">
         <v>1.35</v>
       </c>
       <c r="H43" s="2">
-        <v>50.3</v>
+        <v>45.26</v>
       </c>
       <c r="I43" s="2">
-        <v>16.76</v>
+        <v>12.53</v>
       </c>
       <c r="J43" s="2">
-        <v>0.006303173967708992</v>
+        <v>0.004318386150027533</v>
       </c>
       <c r="K43" s="2" t="b">
         <v>0</v>
@@ -4752,28 +4755,28 @@
         <v>18</v>
       </c>
       <c r="M43" s="2">
-        <v>0.18987844439437263</v>
+        <v>0.14128328998325723</v>
       </c>
       <c r="N43" s="2">
-        <v>25.864276513779405</v>
+        <v>21.90109129254294</v>
       </c>
       <c r="O43" s="2">
-        <v>80</v>
+        <v>78.82352941176471</v>
       </c>
       <c r="P43" s="2">
         <v>24.82490242340647</v>
       </c>
       <c r="Q43" s="2">
-        <v>61.05882352941177</v>
+        <v>58.470588235294116</v>
       </c>
       <c r="R43" s="2">
-        <v>55.82352941176471</v>
+        <v>54.76470588235294</v>
       </c>
       <c r="S43" s="2" t="s">
         <v>114</v>
       </c>
       <c r="T43" s="2">
-        <v>3.45</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -4790,22 +4793,22 @@
         <v>19.054054054054053</v>
       </c>
       <c r="E44" s="2">
-        <v>-0.69</v>
+        <v>-0.66</v>
       </c>
       <c r="F44" s="2">
-        <v>0.1371561215211676</v>
+        <v>0.030367371746275573</v>
       </c>
       <c r="G44" s="2">
         <v>2.63</v>
       </c>
       <c r="H44" s="2">
-        <v>56.32</v>
+        <v>52.35</v>
       </c>
       <c r="I44" s="2">
-        <v>11.72</v>
+        <v>8.72</v>
       </c>
       <c r="J44" s="2">
-        <v>0.012058489583432822</v>
+        <v>0.013792171465670125</v>
       </c>
       <c r="K44" s="2" t="b">
         <v>1</v>
@@ -4814,28 +4817,28 @@
         <v>-6</v>
       </c>
       <c r="M44" s="2">
-        <v>0.23171946433294455</v>
+        <v>0.13954089714201623</v>
       </c>
       <c r="N44" s="2">
-        <v>30.048378507636603</v>
+        <v>21.726852008418838</v>
       </c>
       <c r="O44" s="2">
-        <v>82.35294117647058</v>
+        <v>77.64705882352942</v>
       </c>
       <c r="P44" s="2">
         <v>25.276100184761987</v>
       </c>
       <c r="Q44" s="2">
-        <v>63.647058823529406</v>
+        <v>63.17647058823529</v>
       </c>
       <c r="R44" s="2">
-        <v>57.117647058823536</v>
+        <v>55.58823529411765</v>
       </c>
       <c r="S44" s="2" t="s">
         <v>103</v>
       </c>
       <c r="T44" s="2">
-        <v>22.3</v>
+        <v>20.77</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
@@ -4852,34 +4855,34 @@
         <v>-2.352373290426388</v>
       </c>
       <c r="E45" s="1">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="F45" s="1">
-        <v>0.003671197466789053</v>
+        <v>-0.03489494787106044</v>
       </c>
       <c r="G45" s="1">
         <v>1.45</v>
       </c>
       <c r="H45" s="1">
-        <v>45.67</v>
+        <v>43.22</v>
       </c>
       <c r="I45" s="1">
-        <v>4.07</v>
+        <v>3.06</v>
       </c>
       <c r="J45" s="1">
-        <v>0.0018497796267098127</v>
+        <v>0.0013101956598168911</v>
       </c>
       <c r="K45" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" s="1">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M45" s="1">
-        <v>0.02977764180132869</v>
+        <v>-0.0047550175470829625</v>
       </c>
       <c r="N45" s="1">
-        <v>9.854196254475015</v>
+        <v>7.297260539508913</v>
       </c>
       <c r="O45" s="1">
         <v>61.1764705882353</v>
@@ -4888,16 +4891,16 @@
         <v>17.57882034058413</v>
       </c>
       <c r="Q45" s="1">
-        <v>43.882352941176464</v>
+        <v>43.17647058823529</v>
       </c>
       <c r="R45" s="1">
-        <v>42.470588235294116</v>
+        <v>42.23529411764706</v>
       </c>
       <c r="S45" s="1" t="s">
         <v>109</v>
       </c>
       <c r="T45" s="1">
-        <v>-1.86</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
@@ -4914,114 +4917,114 @@
         <v>473.05882352941177</v>
       </c>
       <c r="E46" s="3">
-        <v>4.52</v>
+        <v>5.18</v>
       </c>
       <c r="F46" s="3">
-        <v>-0.32783442538693164</v>
+        <v>-0.3516270186498901</v>
       </c>
       <c r="G46" s="3">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H46" s="3">
-        <v>34.72</v>
+        <v>33.18</v>
       </c>
       <c r="I46" s="3">
-        <v>-33.82</v>
+        <v>-34.85</v>
       </c>
       <c r="J46" s="3">
-        <v>-0.010403586090275453</v>
+        <v>-0.00822829217933939</v>
       </c>
       <c r="K46" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="3">
         <v>17</v>
       </c>
       <c r="M46" s="3">
-        <v>-0.2837435416219314</v>
+        <v>-0.301393801443261</v>
       </c>
       <c r="N46" s="3">
-        <v>-21.497922087850995</v>
+        <v>-22.36661785010888</v>
       </c>
       <c r="O46" s="3">
-        <v>10.588235294117647</v>
+        <v>8.235294117647058</v>
       </c>
       <c r="P46" s="3">
         <v>54.33673655574689</v>
       </c>
       <c r="Q46" s="3">
-        <v>41.6470588235294</v>
+        <v>42.11764705882352</v>
       </c>
       <c r="R46" s="3">
-        <v>25.823529411764703</v>
+        <v>25.23529411764705</v>
       </c>
       <c r="S46" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T46" s="3">
-        <v>4.79</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B47" s="1">
+      <c r="B47" s="2">
         <v>8.67</v>
       </c>
-      <c r="C47" s="1">
+      <c r="C47" s="2">
         <v>74.11764705882354</v>
       </c>
-      <c r="D47" s="1">
+      <c r="D47" s="2">
         <v>-0.7716262975778546</v>
       </c>
-      <c r="E47" s="1">
-        <v>2.57</v>
-      </c>
-      <c r="F47" s="1">
-        <v>0.10384106899887256</v>
-      </c>
-      <c r="G47" s="1">
-        <v>1.42</v>
-      </c>
-      <c r="H47" s="1">
-        <v>48.74</v>
-      </c>
-      <c r="I47" s="1">
-        <v>3.1</v>
-      </c>
-      <c r="J47" s="1">
-        <v>0.019236496462337747</v>
-      </c>
-      <c r="K47" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L47" s="1">
+      <c r="E47" s="2">
+        <v>2.6</v>
+      </c>
+      <c r="F47" s="2">
+        <v>0.10633192141141011</v>
+      </c>
+      <c r="G47" s="2">
+        <v>1.41</v>
+      </c>
+      <c r="H47" s="2">
+        <v>52.83</v>
+      </c>
+      <c r="I47" s="2">
+        <v>5.09</v>
+      </c>
+      <c r="J47" s="2">
+        <v>0.020450294930138033</v>
+      </c>
+      <c r="K47" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L47" s="2">
         <v>-56</v>
       </c>
-      <c r="M47" s="1">
-        <v>0.12820708371110956</v>
-      </c>
-      <c r="N47" s="1">
-        <v>19.697140445453098</v>
-      </c>
-      <c r="O47" s="1">
-        <v>75.29411764705883</v>
-      </c>
-      <c r="P47" s="1">
-        <v>28.98612413886803</v>
-      </c>
-      <c r="Q47" s="1">
-        <v>52.11764705882353</v>
-      </c>
-      <c r="R47" s="1">
-        <v>47.00000000000001</v>
-      </c>
-      <c r="S47" s="1" t="s">
+      <c r="M47" s="2">
+        <v>0.1337927468177007</v>
+      </c>
+      <c r="N47" s="2">
+        <v>21.15203697598729</v>
+      </c>
+      <c r="O47" s="2">
+        <v>76.47058823529412</v>
+      </c>
+      <c r="P47" s="2">
+        <v>14.027665623490911</v>
+      </c>
+      <c r="Q47" s="2">
+        <v>55.29411764705883</v>
+      </c>
+      <c r="R47" s="2">
+        <v>51.70588235294118</v>
+      </c>
+      <c r="S47" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="T47" s="1">
-        <v>21.15</v>
+      <c r="T47" s="2">
+        <v>25.85</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
@@ -5041,49 +5044,49 @@
         <v>0.66</v>
       </c>
       <c r="F48" s="2">
-        <v>0.16764111920633198</v>
+        <v>0.1920124423709208</v>
       </c>
       <c r="G48" s="2">
         <v>1.61</v>
       </c>
       <c r="H48" s="2">
-        <v>62.26</v>
+        <v>55.76</v>
       </c>
       <c r="I48" s="2">
-        <v>33.39</v>
+        <v>28.73</v>
       </c>
       <c r="J48" s="2">
-        <v>0.01039140142014387</v>
+        <v>0.014415857337782155</v>
       </c>
       <c r="K48" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M48" s="2">
-        <v>0.20302985485981906</v>
+        <v>0.23286879236564584</v>
       </c>
       <c r="N48" s="2">
-        <v>27.179417560324055</v>
+        <v>31.059641530781796</v>
       </c>
       <c r="O48" s="2">
-        <v>81.17647058823529</v>
+        <v>83.52941176470588</v>
       </c>
       <c r="P48" s="2">
-        <v>21.006318468965095</v>
+        <v>21.001739961426274</v>
       </c>
       <c r="Q48" s="2">
-        <v>64.70588235294117</v>
+        <v>65.05882352941177</v>
       </c>
       <c r="R48" s="2">
-        <v>55.764705882352935</v>
+        <v>56.94117647058824</v>
       </c>
       <c r="S48" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T48" s="2">
-        <v>6.5</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
@@ -5100,22 +5103,22 @@
         <v>2104.736842105263</v>
       </c>
       <c r="E49" s="2">
-        <v>-11.2</v>
+        <v>-11.3</v>
       </c>
       <c r="F49" s="2">
-        <v>0.1777465237878837</v>
+        <v>0.14593917035811804</v>
       </c>
       <c r="G49" s="2">
         <v>1.08</v>
       </c>
       <c r="H49" s="2">
-        <v>49.21</v>
+        <v>47.57</v>
       </c>
       <c r="I49" s="2">
-        <v>-4.2</v>
+        <v>-5.13</v>
       </c>
       <c r="J49" s="2">
-        <v>0.015841661575346045</v>
+        <v>0.015404809841220791</v>
       </c>
       <c r="K49" s="2" t="b">
         <v>0</v>
@@ -5124,28 +5127,28 @@
         <v>-7</v>
       </c>
       <c r="M49" s="2">
-        <v>0.1823876694473574</v>
+        <v>0.15129738019349181</v>
       </c>
       <c r="N49" s="2">
-        <v>25.115199019077885</v>
+        <v>22.902500313566396</v>
       </c>
       <c r="O49" s="2">
-        <v>78.82352941176471</v>
+        <v>80</v>
       </c>
       <c r="P49" s="2">
         <v>31.00158698078384</v>
       </c>
       <c r="Q49" s="2">
-        <v>62.58823529411765</v>
+        <v>61.41176470588236</v>
       </c>
       <c r="R49" s="2">
-        <v>56.94117647058824</v>
+        <v>56.47058823529412</v>
       </c>
       <c r="S49" s="2" t="s">
         <v>102</v>
       </c>
       <c r="T49" s="2">
-        <v>25.84</v>
+        <v>25.37</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
@@ -5159,25 +5162,25 @@
         <v>8.235294117647058</v>
       </c>
       <c r="D50" s="3">
-        <v>15.862068965517242</v>
+        <v>16.137931034482758</v>
       </c>
       <c r="E50" s="3">
-        <v>12.86</v>
+        <v>12.72</v>
       </c>
       <c r="F50" s="3">
-        <v>-0.3349742461151789</v>
+        <v>-0.41435788541005153</v>
       </c>
       <c r="G50" s="3">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="H50" s="3">
-        <v>57.15</v>
+        <v>51.73</v>
       </c>
       <c r="I50" s="3">
-        <v>14.02</v>
+        <v>8.21</v>
       </c>
       <c r="J50" s="3">
-        <v>0.01144684524259245</v>
+        <v>0.010602233044606965</v>
       </c>
       <c r="K50" s="3" t="b">
         <v>0</v>
@@ -5186,22 +5189,22 @@
         <v>69</v>
       </c>
       <c r="M50" s="3">
-        <v>-0.17021357520386204</v>
+        <v>-0.22347166002486085</v>
       </c>
       <c r="N50" s="3">
-        <v>-10.144925446044057</v>
+        <v>-14.574403708268866</v>
       </c>
       <c r="O50" s="3">
-        <v>23.52941176470588</v>
+        <v>17.647058823529413</v>
       </c>
       <c r="P50" s="3">
         <v>41.201484669672254</v>
       </c>
       <c r="Q50" s="3">
-        <v>53.05882352941177</v>
+        <v>50.35294117647059</v>
       </c>
       <c r="R50" s="3">
-        <v>26.941176470588232</v>
+        <v>24.82352941176471</v>
       </c>
       <c r="S50" s="3" t="s">
         <v>108</v>
@@ -5222,22 +5225,22 @@
         <v>4.831710709318498</v>
       </c>
       <c r="E51" s="1">
-        <v>14.41</v>
+        <v>14.39</v>
       </c>
       <c r="F51" s="1">
-        <v>0.4958835886672298</v>
+        <v>0.47192188192901596</v>
       </c>
       <c r="G51" s="1">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="H51" s="1">
-        <v>57.14</v>
+        <v>56.6</v>
       </c>
       <c r="I51" s="1">
-        <v>37.06</v>
+        <v>36.35</v>
       </c>
       <c r="J51" s="1">
-        <v>0.05673892083394905</v>
+        <v>0.05016814238874764</v>
       </c>
       <c r="K51" s="1" t="b">
         <v>0</v>
@@ -5246,22 +5249,22 @@
         <v>14</v>
       </c>
       <c r="M51" s="1">
-        <v>0.5405546156396643</v>
+        <v>0.5255039802827537</v>
       </c>
       <c r="N51" s="1">
-        <v>60.93189363830859</v>
+        <v>60.323160322492576</v>
       </c>
       <c r="O51" s="1">
-        <v>92.94117647058823</v>
+        <v>94.11764705882352</v>
       </c>
       <c r="P51" s="1">
         <v>38.38748944617691</v>
       </c>
       <c r="Q51" s="1">
-        <v>53.29411764705882</v>
+        <v>53.88235294117648</v>
       </c>
       <c r="R51" s="1">
-        <v>45.117647058823536</v>
+        <v>45.352941176470594</v>
       </c>
       <c r="S51" s="1" t="s">
         <v>97</v>
@@ -5282,22 +5285,22 @@
         <v>-1.9934426229508198</v>
       </c>
       <c r="E52" s="3">
-        <v>-5.32</v>
+        <v>-5.41</v>
       </c>
       <c r="F52" s="3">
-        <v>-0.15652891797290508</v>
+        <v>-0.20941547505042452</v>
       </c>
       <c r="G52" s="3">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="H52" s="3">
-        <v>42.69</v>
+        <v>41.43</v>
       </c>
       <c r="I52" s="3">
-        <v>-30.88</v>
+        <v>-31.35</v>
       </c>
       <c r="J52" s="3">
-        <v>-0.014479006768678072</v>
+        <v>-0.014358909672663164</v>
       </c>
       <c r="K52" s="3" t="b">
         <v>0</v>
@@ -5306,22 +5309,22 @@
         <v>-110</v>
       </c>
       <c r="M52" s="3">
-        <v>-0.161750206839813</v>
+        <v>-0.21611323734464172</v>
       </c>
       <c r="N52" s="3">
-        <v>-9.298588609639154</v>
+        <v>-13.838561440246956</v>
       </c>
       <c r="O52" s="3">
-        <v>29.411764705882355</v>
+        <v>18.823529411764707</v>
       </c>
       <c r="P52" s="3">
-        <v>32.59357836340351</v>
+        <v>28.153300405690313</v>
       </c>
       <c r="Q52" s="3">
-        <v>33.17647058823529</v>
+        <v>33.294117647058826</v>
       </c>
       <c r="R52" s="3">
-        <v>25.58823529411765</v>
+        <v>23.176470588235293</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>114</v>
@@ -5345,43 +5348,43 @@
         <v>-0.87</v>
       </c>
       <c r="F53" s="3">
-        <v>-0.0432336681091708</v>
+        <v>-0.04044394491042243</v>
       </c>
       <c r="G53" s="3">
         <v>0</v>
       </c>
       <c r="H53" s="3">
-        <v>53.15</v>
+        <v>52.42</v>
       </c>
       <c r="I53" s="3">
-        <v>4.07</v>
+        <v>3.54</v>
       </c>
       <c r="J53" s="3">
-        <v>0.007089722614657735</v>
+        <v>0.009617582954560154</v>
       </c>
       <c r="K53" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" s="3">
         <v>1748</v>
       </c>
       <c r="M53" s="3">
-        <v>-0.10124798885259223</v>
+        <v>-0.1074215678525946</v>
       </c>
       <c r="N53" s="3">
-        <v>-3.2483668109170747</v>
+        <v>-2.9693944910422454</v>
       </c>
       <c r="O53" s="3">
-        <v>37.64705882352941</v>
+        <v>38.82352941176471</v>
       </c>
       <c r="P53" s="3">
         <v>48.781873808753</v>
       </c>
       <c r="Q53" s="3">
-        <v>40.117647058823536</v>
+        <v>40.705882352941174</v>
       </c>
       <c r="R53" s="3">
-        <v>22.88235294117647</v>
+        <v>23.176470588235293</v>
       </c>
       <c r="S53" s="3" t="s">
         <v>96</v>
@@ -5402,22 +5405,22 @@
         <v>0.8348134991119006</v>
       </c>
       <c r="E54" s="1">
-        <v>-1.38</v>
+        <v>-1.39</v>
       </c>
       <c r="F54" s="1">
-        <v>-0.05789997444780892</v>
+        <v>-0.04260958910736</v>
       </c>
       <c r="G54" s="1">
         <v>0.98</v>
       </c>
       <c r="H54" s="1">
-        <v>49.19</v>
+        <v>48.71</v>
       </c>
       <c r="I54" s="1">
-        <v>5.07</v>
+        <v>4.91</v>
       </c>
       <c r="J54" s="1">
-        <v>0.005991652206331156</v>
+        <v>0.005512396364876555</v>
       </c>
       <c r="K54" s="1" t="b">
         <v>0</v>
@@ -5426,28 +5429,28 @@
         <v>85</v>
       </c>
       <c r="M54" s="1">
-        <v>-0.05906026086267735</v>
+        <v>-0.04394914156620344</v>
       </c>
       <c r="N54" s="1">
-        <v>0.970405988074398</v>
+        <v>3.377848137596863</v>
       </c>
       <c r="O54" s="1">
-        <v>48.23529411764706</v>
+        <v>56.470588235294116</v>
       </c>
       <c r="P54" s="1">
         <v>11.84024085938085</v>
       </c>
       <c r="Q54" s="1">
-        <v>52.47058823529412</v>
+        <v>52.705882352941174</v>
       </c>
       <c r="R54" s="1">
-        <v>45.117647058823536</v>
+        <v>47.47058823529412</v>
       </c>
       <c r="S54" s="1" t="s">
         <v>115</v>
       </c>
       <c r="T54" s="1">
-        <v>4.69</v>
+        <v>7.04</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
@@ -5464,114 +5467,114 @@
         <v>-0.1840860215053764</v>
       </c>
       <c r="E55" s="3">
-        <v>0.67</v>
+        <v>0.69</v>
       </c>
       <c r="F55" s="3">
-        <v>-0.2926685570723293</v>
+        <v>-0.2929107333333941</v>
       </c>
       <c r="G55" s="3">
         <v>1.58</v>
       </c>
       <c r="H55" s="3">
-        <v>49.39</v>
+        <v>47.56</v>
       </c>
       <c r="I55" s="3">
-        <v>2.92</v>
+        <v>2.07</v>
       </c>
       <c r="J55" s="3">
-        <v>-0.015663846084244742</v>
+        <v>-0.01298188149146299</v>
       </c>
       <c r="K55" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L55" s="3">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="M55" s="3">
-        <v>-0.2590202510411449</v>
+        <v>-0.25406371202693423</v>
       </c>
       <c r="N55" s="3">
-        <v>-19.025593029772352</v>
+        <v>-17.633608908476205</v>
       </c>
       <c r="O55" s="3">
-        <v>12.941176470588237</v>
+        <v>11.76470588235294</v>
       </c>
       <c r="P55" s="3">
         <v>26.83257063748809</v>
       </c>
       <c r="Q55" s="3">
-        <v>47.41176470588235</v>
+        <v>47.52941176470588</v>
       </c>
       <c r="R55" s="3">
-        <v>28.94117647058824</v>
+        <v>28.588235294117645</v>
       </c>
       <c r="S55" s="3" t="s">
         <v>96</v>
       </c>
       <c r="T55" s="3">
-        <v>-29.66</v>
+        <v>-30.01</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
+      <c r="A56" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B56" s="1">
+      <c r="B56" s="2">
         <v>0.73</v>
       </c>
-      <c r="C56" s="1">
+      <c r="C56" s="2">
         <v>37.64705882352941</v>
       </c>
-      <c r="D56" s="1">
+      <c r="D56" s="2">
         <v>113.35616438356165</v>
       </c>
-      <c r="E56" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="F56" s="1">
-        <v>-0.36876182805844937</v>
-      </c>
-      <c r="G56" s="1">
-        <v>3.8</v>
-      </c>
-      <c r="H56" s="1">
-        <v>58.53</v>
-      </c>
-      <c r="I56" s="1">
-        <v>34.91</v>
-      </c>
-      <c r="J56" s="1">
-        <v>0.012340627616071714</v>
-      </c>
-      <c r="K56" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L56" s="1">
-        <v>322</v>
-      </c>
-      <c r="M56" s="1">
-        <v>-0.20632172997686937</v>
-      </c>
-      <c r="N56" s="1">
-        <v>-13.755740923344792</v>
-      </c>
-      <c r="O56" s="1">
-        <v>17.647058823529413</v>
-      </c>
-      <c r="P56" s="1">
+      <c r="E56" s="2">
+        <v>2.08</v>
+      </c>
+      <c r="F56" s="2">
+        <v>-0.12039070994908113</v>
+      </c>
+      <c r="G56" s="2">
+        <v>3.81</v>
+      </c>
+      <c r="H56" s="2">
+        <v>57.48</v>
+      </c>
+      <c r="I56" s="2">
+        <v>35.53</v>
+      </c>
+      <c r="J56" s="2">
+        <v>0.01883970337392056</v>
+      </c>
+      <c r="K56" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L56" s="2">
+        <v>323</v>
+      </c>
+      <c r="M56" s="2">
+        <v>0.06781641051842269</v>
+      </c>
+      <c r="N56" s="2">
+        <v>14.554403346059486</v>
+      </c>
+      <c r="O56" s="2">
+        <v>67.05882352941175</v>
+      </c>
+      <c r="P56" s="2">
         <v>52.65288503392759</v>
       </c>
-      <c r="Q56" s="1">
-        <v>68.58823529411765</v>
-      </c>
-      <c r="R56" s="1">
-        <v>35.05882352941177</v>
-      </c>
-      <c r="S56" s="1" t="s">
+      <c r="Q56" s="2">
+        <v>70.82352941176471</v>
+      </c>
+      <c r="R56" s="2">
+        <v>50.70588235294117</v>
+      </c>
+      <c r="S56" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="T56" s="1">
-        <v>-24.94</v>
+      <c r="T56" s="2">
+        <v>-9.29</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
@@ -5588,22 +5591,22 @@
         <v>7.285067873303166</v>
       </c>
       <c r="E57" s="3">
-        <v>-1.31</v>
+        <v>-1.36</v>
       </c>
       <c r="F57" s="3">
-        <v>-0.35388823959998345</v>
+        <v>-0.3140894384571067</v>
       </c>
       <c r="G57" s="3">
         <v>2.04</v>
       </c>
       <c r="H57" s="3">
-        <v>46.91</v>
+        <v>44.86</v>
       </c>
       <c r="I57" s="3">
-        <v>-4.36</v>
+        <v>-6.23</v>
       </c>
       <c r="J57" s="3">
-        <v>-0.024353914485329434</v>
+        <v>-0.020284230696150034</v>
       </c>
       <c r="K57" s="3" t="b">
         <v>0</v>
@@ -5612,28 +5615,28 @@
         <v>250</v>
       </c>
       <c r="M57" s="3">
-        <v>-0.29355334602682515</v>
+        <v>-0.24443271059724758</v>
       </c>
       <c r="N57" s="3">
-        <v>-22.47890252834037</v>
+        <v>-16.670508765507538</v>
       </c>
       <c r="O57" s="3">
-        <v>8.235294117647058</v>
+        <v>14.117647058823529</v>
       </c>
       <c r="P57" s="3">
         <v>40.717118046641446</v>
       </c>
       <c r="Q57" s="3">
-        <v>44.352941176470594</v>
+        <v>44.58823529411765</v>
       </c>
       <c r="R57" s="3">
-        <v>24.941176470588232</v>
+        <v>26.941176470588232</v>
       </c>
       <c r="S57" s="3" t="s">
         <v>110</v>
       </c>
       <c r="T57" s="3">
-        <v>-24.02</v>
+        <v>-22.02</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
@@ -5653,49 +5656,49 @@
         <v>1.26</v>
       </c>
       <c r="F58" s="1">
-        <v>-0.04339343945308263</v>
+        <v>-0.1451834415319172</v>
       </c>
       <c r="G58" s="1">
         <v>1.64</v>
       </c>
       <c r="H58" s="1">
-        <v>43.24</v>
+        <v>45.25</v>
       </c>
       <c r="I58" s="1">
-        <v>-18.42</v>
+        <v>-17.15</v>
       </c>
       <c r="J58" s="1">
-        <v>0.013127827314443964</v>
+        <v>0.016426117028996167</v>
       </c>
       <c r="K58" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" s="1">
         <v>3</v>
       </c>
       <c r="M58" s="1">
-        <v>-0.006264274177292917</v>
+        <v>-0.10231776284892702</v>
       </c>
       <c r="N58" s="1">
-        <v>6.2500046566128535</v>
+        <v>-2.459013990675489</v>
       </c>
       <c r="O58" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="P58" s="1">
         <v>33.706290307642504</v>
       </c>
       <c r="Q58" s="1">
-        <v>56.23529411764706</v>
+        <v>57.411764705882355</v>
       </c>
       <c r="R58" s="1">
-        <v>48.94117647058823</v>
+        <v>42.94117647058823</v>
       </c>
       <c r="S58" s="1" t="s">
         <v>103</v>
       </c>
       <c r="T58" s="1">
-        <v>26.99</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
@@ -5712,52 +5715,52 @@
         <v>3.456597222222223</v>
       </c>
       <c r="E59" s="3">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="F59" s="3">
-        <v>-0.35423476095856316</v>
+        <v>-0.30383719056383857</v>
       </c>
       <c r="G59" s="3">
         <v>1.86</v>
       </c>
       <c r="H59" s="3">
-        <v>55.3</v>
+        <v>51.26</v>
       </c>
       <c r="I59" s="3">
-        <v>15.51</v>
+        <v>12.23</v>
       </c>
       <c r="J59" s="3">
-        <v>-0.01290389685791354</v>
+        <v>-0.009099462723836231</v>
       </c>
       <c r="K59" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" s="3">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="M59" s="3">
-        <v>-0.3043424451192207</v>
+        <v>-0.2462364348335705</v>
       </c>
       <c r="N59" s="3">
-        <v>-23.557812437579926</v>
+        <v>-16.850881189139834</v>
       </c>
       <c r="O59" s="3">
-        <v>7.0588235294117645</v>
+        <v>12.941176470588237</v>
       </c>
       <c r="P59" s="3">
         <v>41.76493344029593</v>
       </c>
       <c r="Q59" s="3">
-        <v>52.82352941176471</v>
+        <v>52.705882352941174</v>
       </c>
       <c r="R59" s="3">
-        <v>25.529411764705884</v>
+        <v>27.529411764705884</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>110</v>
       </c>
       <c r="T59" s="3">
-        <v>-33.68</v>
+        <v>-31.68</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.25">
@@ -5774,22 +5777,22 @@
         <v>2.417910447761194</v>
       </c>
       <c r="E60" s="3">
-        <v>-4.45</v>
+        <v>-4.42</v>
       </c>
       <c r="F60" s="3">
-        <v>-0.48208340597451393</v>
+        <v>-0.5138727134497337</v>
       </c>
       <c r="G60" s="3">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="H60" s="3">
-        <v>38.72</v>
+        <v>34.49</v>
       </c>
       <c r="I60" s="3">
-        <v>-33.6</v>
+        <v>-35.25</v>
       </c>
       <c r="J60" s="3">
-        <v>-0.026673924128155363</v>
+        <v>-0.02370514545342214</v>
       </c>
       <c r="K60" s="3" t="b">
         <v>0</v>
@@ -5798,28 +5801,28 @@
         <v>21</v>
       </c>
       <c r="M60" s="3">
-        <v>-0.37591719901405274</v>
+        <v>-0.39197343969498033</v>
       </c>
       <c r="N60" s="3">
-        <v>-30.715287827063136</v>
+        <v>-31.424581675280816</v>
       </c>
       <c r="O60" s="3">
-        <v>2.3529411764705883</v>
+        <v>3.5294117647058822</v>
       </c>
       <c r="P60" s="3">
         <v>46.90217032437056</v>
       </c>
       <c r="Q60" s="3">
-        <v>24.823529411764703</v>
+        <v>24.235294117647054</v>
       </c>
       <c r="R60" s="3">
-        <v>10.294117647058819</v>
+        <v>10.764705882352938</v>
       </c>
       <c r="S60" s="3" t="s">
         <v>98</v>
       </c>
       <c r="T60" s="3">
-        <v>-16.6</v>
+        <v>-16.13</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
@@ -5833,55 +5836,55 @@
         <v>55.294117647058826</v>
       </c>
       <c r="D61" s="1">
-        <v>2.23448275862069</v>
+        <v>2.2689655172413796</v>
       </c>
       <c r="E61" s="1">
         <v>-0.52</v>
       </c>
       <c r="F61" s="1">
-        <v>-0.1180671063842687</v>
+        <v>-0.11151016002888062</v>
       </c>
       <c r="G61" s="1">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="H61" s="1">
-        <v>26.5</v>
+        <v>30.62</v>
       </c>
       <c r="I61" s="1">
-        <v>1.59</v>
+        <v>2.33</v>
       </c>
       <c r="J61" s="1">
-        <v>-0.005392966599319305</v>
+        <v>-0.006451487788661882</v>
       </c>
       <c r="K61" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L61" s="1">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M61" s="1">
-        <v>-0.10588409902815021</v>
+        <v>-0.09811463544044619</v>
       </c>
       <c r="N61" s="1">
-        <v>-3.7119778284728775</v>
+        <v>-2.038701249827406</v>
       </c>
       <c r="O61" s="1">
-        <v>36.470588235294116</v>
+        <v>41.17647058823529</v>
       </c>
       <c r="P61" s="1">
         <v>13.593577982515374</v>
       </c>
       <c r="Q61" s="1">
-        <v>42.35294117647059</v>
+        <v>42.588235294117645</v>
       </c>
       <c r="R61" s="1">
-        <v>39.00000000000001</v>
+        <v>40.05882352941177</v>
       </c>
       <c r="S61" s="1" t="s">
         <v>116</v>
       </c>
       <c r="T61" s="1">
-        <v>-8.2</v>
+        <v>-7.14</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
@@ -5898,52 +5901,52 @@
         <v>0.1888760139049825</v>
       </c>
       <c r="E62" s="2">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="F62" s="2">
-        <v>0.1008006324313209</v>
+        <v>0.04088234520051771</v>
       </c>
       <c r="G62" s="2">
         <v>0.2</v>
       </c>
       <c r="H62" s="2">
-        <v>56.2</v>
+        <v>58.94</v>
       </c>
       <c r="I62" s="2">
-        <v>12.72</v>
+        <v>13.19</v>
       </c>
       <c r="J62" s="2">
-        <v>0.004444487842905838</v>
+        <v>0.006391514005877937</v>
       </c>
       <c r="K62" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M62" s="2">
-        <v>0.05438917583658376</v>
+        <v>-0.012699753153220028</v>
       </c>
       <c r="N62" s="2">
-        <v>12.315349658000518</v>
+        <v>6.502786978895224</v>
       </c>
       <c r="O62" s="2">
-        <v>63.52941176470588</v>
+        <v>60</v>
       </c>
       <c r="P62" s="2">
         <v>7.56622762341097</v>
       </c>
       <c r="Q62" s="2">
-        <v>55.88235294117647</v>
+        <v>58.94117647058824</v>
       </c>
       <c r="R62" s="2">
-        <v>51.05882352941177</v>
+        <v>50.352941176470594</v>
       </c>
       <c r="S62" s="2" t="s">
         <v>101</v>
       </c>
       <c r="T62" s="2">
-        <v>5.08</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
@@ -5957,55 +5960,55 @@
         <v>98.82352941176471</v>
       </c>
       <c r="D63" s="1">
-        <v>1.5961059542676024</v>
+        <v>1.6126330088295224</v>
       </c>
       <c r="E63" s="1">
-        <v>-1.09</v>
+        <v>-1.05</v>
       </c>
       <c r="F63" s="1">
-        <v>-0.24974158560379423</v>
+        <v>-0.20498070792182313</v>
       </c>
       <c r="G63" s="1">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="H63" s="1">
-        <v>64.62</v>
+        <v>58.35</v>
       </c>
       <c r="I63" s="1">
-        <v>65.92</v>
+        <v>58.47</v>
       </c>
       <c r="J63" s="1">
-        <v>0.01107044650714059</v>
+        <v>0.015484596668831169</v>
       </c>
       <c r="K63" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L63" s="1">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="M63" s="1">
-        <v>-0.17838397108938586</v>
+        <v>-0.1219284554735296</v>
       </c>
       <c r="N63" s="1">
-        <v>-10.961965034596446</v>
+        <v>-4.420083253135738</v>
       </c>
       <c r="O63" s="1">
-        <v>22.35294117647059</v>
+        <v>34.11764705882353</v>
       </c>
       <c r="P63" s="1">
         <v>39.10478556320163</v>
       </c>
       <c r="Q63" s="1">
-        <v>76</v>
+        <v>76.58823529411765</v>
       </c>
       <c r="R63" s="1">
-        <v>42.23529411764706</v>
+        <v>46.47058823529412</v>
       </c>
       <c r="S63" s="1" t="s">
         <v>117</v>
       </c>
       <c r="T63" s="1">
-        <v>-25.87</v>
+        <v>-21.64</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.25">
@@ -6022,34 +6025,34 @@
         <v>-1.5699971371314059</v>
       </c>
       <c r="E64" s="1">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="F64" s="1">
-        <v>-0.16404090432788793</v>
+        <v>-0.15947503754139494</v>
       </c>
       <c r="G64" s="1">
         <v>0.97</v>
       </c>
       <c r="H64" s="1">
-        <v>52.29</v>
+        <v>47.63</v>
       </c>
       <c r="I64" s="1">
-        <v>5.47</v>
+        <v>2.86</v>
       </c>
       <c r="J64" s="1">
-        <v>-0.012699741311393006</v>
+        <v>-0.010791662646189238</v>
       </c>
       <c r="K64" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" s="1">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="M64" s="1">
-        <v>-0.16578133395019057</v>
+        <v>-0.16148436622966011</v>
       </c>
       <c r="N64" s="1">
-        <v>-9.701701320676909</v>
+        <v>-8.375674328748792</v>
       </c>
       <c r="O64" s="1">
         <v>28.235294117647058</v>
@@ -6058,16 +6061,16 @@
         <v>25.543467249515373</v>
       </c>
       <c r="Q64" s="1">
-        <v>47.88235294117647</v>
+        <v>45.99999999999999</v>
       </c>
       <c r="R64" s="1">
-        <v>32.647058823529406</v>
+        <v>32.29411764705882</v>
       </c>
       <c r="S64" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T64" s="1">
-        <v>-12.11</v>
+        <v>-12.46</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.25">
@@ -6081,55 +6084,55 @@
         <v>65.88235294117646</v>
       </c>
       <c r="D65" s="3">
-        <v>-0.39370078740157477</v>
+        <v>-0.410761154855643</v>
       </c>
       <c r="E65" s="3">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="F65" s="3">
-        <v>-0.13088313432433693</v>
+        <v>-0.12510874079301193</v>
       </c>
       <c r="G65" s="3">
         <v>0.36</v>
       </c>
       <c r="H65" s="3">
-        <v>26.27</v>
+        <v>28.86</v>
       </c>
       <c r="I65" s="3">
-        <v>-13.5</v>
+        <v>-12.93</v>
       </c>
       <c r="J65" s="3">
-        <v>-0.005809294569099313</v>
+        <v>-0.005542145213839998</v>
       </c>
       <c r="K65" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" s="3">
-        <v>-101</v>
+        <v>-102</v>
       </c>
       <c r="M65" s="3">
-        <v>-0.16801229960012665</v>
+        <v>-0.1679744194760021</v>
       </c>
       <c r="N65" s="3">
-        <v>-9.92479788567052</v>
+        <v>-9.024679653382991</v>
       </c>
       <c r="O65" s="3">
-        <v>25.882352941176475</v>
+        <v>24.705882352941178</v>
       </c>
       <c r="P65" s="3">
-        <v>19.1431702600252</v>
+        <v>18.58840549196192</v>
       </c>
       <c r="Q65" s="3">
-        <v>34.470588235294116</v>
+        <v>34.94117647058823</v>
       </c>
       <c r="R65" s="3">
-        <v>29.64705882352941</v>
+        <v>29.76470588235294</v>
       </c>
       <c r="S65" s="3" t="s">
         <v>118</v>
       </c>
       <c r="T65" s="3">
-        <v>3.61</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
@@ -6149,111 +6152,111 @@
         <v>2.08</v>
       </c>
       <c r="F66" s="2">
-        <v>0.0955648941640535</v>
+        <v>0.05690085765609246</v>
       </c>
       <c r="G66" s="2">
         <v>0.87</v>
       </c>
       <c r="H66" s="2">
-        <v>61.01</v>
+        <v>58.86</v>
       </c>
       <c r="I66" s="2">
-        <v>19.46</v>
+        <v>18.42</v>
       </c>
       <c r="J66" s="2">
-        <v>0.016351955787534254</v>
+        <v>0.01705682369638478</v>
       </c>
       <c r="K66" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L66" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M66" s="2">
-        <v>0.08802303246740872</v>
+        <v>0.04819376667361008</v>
       </c>
       <c r="N66" s="2">
-        <v>15.678735321083021</v>
+        <v>12.592138961578229</v>
       </c>
       <c r="O66" s="2">
-        <v>67.05882352941175</v>
+        <v>65.88235294117646</v>
       </c>
       <c r="P66" s="2">
         <v>10.56723987277981</v>
       </c>
       <c r="Q66" s="2">
-        <v>70.11764705882352</v>
+        <v>69.52941176470588</v>
       </c>
       <c r="R66" s="2">
-        <v>59.52941176470588</v>
+        <v>58.705882352941174</v>
       </c>
       <c r="S66" s="2" t="s">
         <v>119</v>
       </c>
       <c r="T66" s="2">
-        <v>15.93</v>
+        <v>15.11</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A67" s="3" t="s">
+      <c r="A67" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B67" s="3">
+      <c r="B67" s="1">
         <v>72.89</v>
       </c>
-      <c r="C67" s="3">
+      <c r="C67" s="1">
         <v>100</v>
       </c>
-      <c r="D67" s="3">
+      <c r="D67" s="1">
         <v>-0.6876114693373577</v>
       </c>
-      <c r="E67" s="3">
-        <v>1.69</v>
-      </c>
-      <c r="F67" s="3">
-        <v>-0.5625697670784382</v>
-      </c>
-      <c r="G67" s="3">
-        <v>5.22</v>
-      </c>
-      <c r="H67" s="3">
-        <v>58.2</v>
-      </c>
-      <c r="I67" s="3">
-        <v>62.22</v>
-      </c>
-      <c r="J67" s="3">
-        <v>0.002586596388619295</v>
-      </c>
-      <c r="K67" s="3" t="b">
+      <c r="E67" s="1">
+        <v>1.77</v>
+      </c>
+      <c r="F67" s="1">
+        <v>-0.5087004596405837</v>
+      </c>
+      <c r="G67" s="1">
+        <v>5.2</v>
+      </c>
+      <c r="H67" s="1">
+        <v>52.83</v>
+      </c>
+      <c r="I67" s="1">
+        <v>52.8</v>
+      </c>
+      <c r="J67" s="1">
+        <v>0.008348352451224951</v>
+      </c>
+      <c r="K67" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L67" s="3">
-        <v>667</v>
-      </c>
-      <c r="M67" s="3">
-        <v>-0.31774933354119983</v>
-      </c>
-      <c r="N67" s="3">
-        <v>-24.898501279777836</v>
-      </c>
-      <c r="O67" s="3">
-        <v>5.88235294117647</v>
-      </c>
-      <c r="P67" s="3">
+      <c r="L67" s="1">
+        <v>668</v>
+      </c>
+      <c r="M67" s="1">
+        <v>-0.2273944432834606</v>
+      </c>
+      <c r="N67" s="1">
+        <v>-14.966682034128844</v>
+      </c>
+      <c r="O67" s="1">
+        <v>16.470588235294116</v>
+      </c>
+      <c r="P67" s="1">
         <v>56.49293299150161</v>
       </c>
-      <c r="Q67" s="3">
-        <v>60.82352941176471</v>
-      </c>
-      <c r="R67" s="3">
-        <v>25.647058823529413</v>
-      </c>
-      <c r="S67" s="3" t="s">
+      <c r="Q67" s="1">
+        <v>63.05882352941177</v>
+      </c>
+      <c r="R67" s="1">
+        <v>30</v>
+      </c>
+      <c r="S67" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="T67" s="3">
-        <v>-43.74</v>
+      <c r="T67" s="1">
+        <v>-39.39</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
@@ -6270,52 +6273,52 @@
         <v>3.1600576784426826</v>
       </c>
       <c r="E68" s="1">
-        <v>-2.41</v>
+        <v>-2.4</v>
       </c>
       <c r="F68" s="1">
-        <v>-0.21992343107345258</v>
+        <v>-0.13192003913163258</v>
       </c>
       <c r="G68" s="1">
         <v>2.09</v>
       </c>
       <c r="H68" s="1">
-        <v>58.82</v>
+        <v>54.2</v>
       </c>
       <c r="I68" s="1">
-        <v>44.74</v>
+        <v>39.43</v>
       </c>
       <c r="J68" s="1">
-        <v>-0.0007192091735043825</v>
+        <v>0.007605061791555833</v>
       </c>
       <c r="K68" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" s="1">
         <v>514</v>
       </c>
       <c r="M68" s="1">
-        <v>-0.1566878214631232</v>
+        <v>-0.05891443012466491</v>
       </c>
       <c r="N68" s="1">
-        <v>-8.792350071970173</v>
+        <v>1.8813192817507263</v>
       </c>
       <c r="O68" s="1">
-        <v>30.58823529411765</v>
+        <v>49.411764705882355</v>
       </c>
       <c r="P68" s="1">
         <v>31.85898471566022</v>
       </c>
       <c r="Q68" s="1">
-        <v>66.3529411764706</v>
+        <v>69.05882352941177</v>
       </c>
       <c r="R68" s="1">
-        <v>41.117647058823536</v>
+        <v>48.17647058823529</v>
       </c>
       <c r="S68" s="1" t="s">
         <v>111</v>
       </c>
       <c r="T68" s="1">
-        <v>-24.92</v>
+        <v>-17.86</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
@@ -6332,52 +6335,52 @@
         <v>-0.15878787878787873</v>
       </c>
       <c r="E69" s="1">
-        <v>-1.74</v>
+        <v>-1.89</v>
       </c>
       <c r="F69" s="1">
-        <v>-0.011984213959823409</v>
+        <v>-0.046914386054515964</v>
       </c>
       <c r="G69" s="1">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="H69" s="1">
-        <v>29.51</v>
+        <v>29.48</v>
       </c>
       <c r="I69" s="1">
-        <v>-31.69</v>
+        <v>-31.39</v>
       </c>
       <c r="J69" s="1">
-        <v>0.0056815149485858075</v>
+        <v>0.0008971538779524497</v>
       </c>
       <c r="K69" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L69" s="1">
-        <v>-251</v>
+        <v>-252</v>
       </c>
       <c r="M69" s="1">
-        <v>-0.011984213959823409</v>
+        <v>-0.04758416228393769</v>
       </c>
       <c r="N69" s="1">
-        <v>5.678010678359797</v>
+        <v>3.0143460658234473</v>
       </c>
       <c r="O69" s="1">
-        <v>58.82352941176471</v>
+        <v>55.294117647058826</v>
       </c>
       <c r="P69" s="1">
         <v>37.32769516583675</v>
       </c>
       <c r="Q69" s="1">
-        <v>45.05882352941176</v>
+        <v>42.941176470588225</v>
       </c>
       <c r="R69" s="1">
-        <v>43.17647058823529</v>
+        <v>40.94117647058823</v>
       </c>
       <c r="S69" s="1" t="s">
         <v>120</v>
       </c>
       <c r="T69" s="1">
-        <v>25.43</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
@@ -6394,52 +6397,52 @@
         <v>5.923076923076923</v>
       </c>
       <c r="E70" s="1">
-        <v>-0.54</v>
+        <v>-0.55</v>
       </c>
       <c r="F70" s="1">
-        <v>-0.12578574350414173</v>
+        <v>-0.18149343830850734</v>
       </c>
       <c r="G70" s="1">
         <v>1.26</v>
       </c>
       <c r="H70" s="1">
-        <v>37.5</v>
+        <v>38.21</v>
       </c>
       <c r="I70" s="1">
-        <v>-7.58</v>
+        <v>-7.28</v>
       </c>
       <c r="J70" s="1">
-        <v>-0.004889466748683411</v>
+        <v>-0.0050493138942308835</v>
       </c>
       <c r="K70" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L70" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M70" s="1">
-        <v>-0.11070202011085217</v>
+        <v>-0.1640792563435426</v>
       </c>
       <c r="N70" s="1">
-        <v>-4.193769936743079</v>
+        <v>-8.635163340137044</v>
       </c>
       <c r="O70" s="1">
-        <v>34.11764705882353</v>
+        <v>27.058823529411764</v>
       </c>
       <c r="P70" s="1">
         <v>16.710870321490763</v>
       </c>
       <c r="Q70" s="1">
-        <v>46.117647058823536</v>
+        <v>47.41176470588236</v>
       </c>
       <c r="R70" s="1">
-        <v>40.94117647058824</v>
+        <v>38.94117647058823</v>
       </c>
       <c r="S70" s="1" t="s">
         <v>103</v>
       </c>
       <c r="T70" s="1">
-        <v>-0.77</v>
+        <v>-2.77</v>
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.25">
@@ -6456,52 +6459,52 @@
         <v>886.3947368421052</v>
       </c>
       <c r="E71" s="2">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="F71" s="2">
-        <v>0.1660943925755984</v>
+        <v>0.14739445916654523</v>
       </c>
       <c r="G71" s="2">
         <v>0.33</v>
       </c>
       <c r="H71" s="2">
-        <v>56.49</v>
+        <v>60.1</v>
       </c>
       <c r="I71" s="2">
-        <v>9.84</v>
+        <v>11.01</v>
       </c>
       <c r="J71" s="2">
-        <v>0.013053316165843003</v>
+        <v>0.01375035786157295</v>
       </c>
       <c r="K71" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L71" s="2">
-        <v>-79</v>
+        <v>-80</v>
       </c>
       <c r="M71" s="2">
-        <v>0.12722479767750605</v>
+        <v>0.10251945179528987</v>
       </c>
       <c r="N71" s="2">
-        <v>19.59891184209275</v>
+        <v>18.02470747374621</v>
       </c>
       <c r="O71" s="2">
-        <v>74.11764705882354</v>
+        <v>72.94117647058823</v>
       </c>
       <c r="P71" s="2">
         <v>10.873073633899006</v>
       </c>
       <c r="Q71" s="2">
-        <v>61.05882352941177</v>
+        <v>62.23529411764706</v>
       </c>
       <c r="R71" s="2">
-        <v>56.70588235294119</v>
+        <v>55.76470588235294</v>
       </c>
       <c r="S71" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T71" s="2">
-        <v>8.66</v>
+        <v>7.72</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.25">
@@ -6518,52 +6521,52 @@
         <v>0.3596792668957616</v>
       </c>
       <c r="E72" s="1">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="F72" s="1">
-        <v>-0.10177974530808893</v>
+        <v>-0.10802109027089807</v>
       </c>
       <c r="G72" s="1">
         <v>1.47</v>
       </c>
       <c r="H72" s="1">
-        <v>62.72</v>
+        <v>64.22</v>
       </c>
       <c r="I72" s="1">
-        <v>-11.33</v>
+        <v>-10.27</v>
       </c>
       <c r="J72" s="1">
-        <v>-0.0023344083426988134</v>
+        <v>0.001180220369073315</v>
       </c>
       <c r="K72" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L72" s="1">
-        <v>-41</v>
+        <v>-42</v>
       </c>
       <c r="M72" s="1">
-        <v>-0.07451301455868087</v>
+        <v>-0.07654160748807715</v>
       </c>
       <c r="N72" s="1">
-        <v>-0.5748693815259397</v>
+        <v>0.11860154540950638</v>
       </c>
       <c r="O72" s="1">
-        <v>44.70588235294118</v>
+        <v>48.23529411764706</v>
       </c>
       <c r="P72" s="1">
-        <v>28.84879594738295</v>
+        <v>27.47171350888485</v>
       </c>
       <c r="Q72" s="1">
-        <v>52.705882352941174</v>
+        <v>54.58823529411765</v>
       </c>
       <c r="R72" s="1">
-        <v>39.88235294117647</v>
+        <v>41.05882352941176</v>
       </c>
       <c r="S72" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T72" s="1">
-        <v>10.43</v>
+        <v>11.61</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.25">
@@ -6580,52 +6583,52 @@
         <v>-0.5045723507261969</v>
       </c>
       <c r="E73" s="2">
-        <v>-0.34</v>
+        <v>-0.31</v>
       </c>
       <c r="F73" s="2">
-        <v>0.3164785798337941</v>
+        <v>0.24535237187785608</v>
       </c>
       <c r="G73" s="2">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="H73" s="2">
-        <v>75.31</v>
+        <v>73.59</v>
       </c>
       <c r="I73" s="2">
-        <v>25.87</v>
+        <v>25.55</v>
       </c>
       <c r="J73" s="2">
-        <v>0.023496730151741075</v>
+        <v>0.02260487213828174</v>
       </c>
       <c r="K73" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M73" s="2">
-        <v>0.30951686134458356</v>
+        <v>0.23798483335421716</v>
       </c>
       <c r="N73" s="2">
-        <v>37.82811820880049</v>
+        <v>31.571245629638934</v>
       </c>
       <c r="O73" s="2">
-        <v>83.52941176470588</v>
+        <v>84.70588235294117</v>
       </c>
       <c r="P73" s="2">
-        <v>8.480874361506512</v>
+        <v>7.6128642599377825</v>
       </c>
       <c r="Q73" s="2">
-        <v>67.76470588235294</v>
+        <v>68.35294117647058</v>
       </c>
       <c r="R73" s="2">
-        <v>60.529411764705884</v>
+        <v>61</v>
       </c>
       <c r="S73" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T73" s="2">
-        <v>20.65</v>
+        <v>21.12</v>
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.25">
@@ -6639,37 +6642,37 @@
         <v>44.70588235294118</v>
       </c>
       <c r="D74" s="1">
-        <v>11.195238095238095</v>
+        <v>11.06190476190476</v>
       </c>
       <c r="E74" s="1">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="F74" s="1">
-        <v>-0.19461464436377918</v>
+        <v>-0.2064549955100351</v>
       </c>
       <c r="G74" s="1">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="H74" s="1">
-        <v>37.79</v>
+        <v>34.16</v>
       </c>
       <c r="I74" s="1">
-        <v>-26.96</v>
+        <v>-27.87</v>
       </c>
       <c r="J74" s="1">
-        <v>-0.018125564055936152</v>
+        <v>-0.01895711182762106</v>
       </c>
       <c r="K74" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L74" s="1">
-        <v>-169</v>
+        <v>-170</v>
       </c>
       <c r="M74" s="1">
-        <v>-0.18881321228943704</v>
+        <v>-0.2004270094452396</v>
       </c>
       <c r="N74" s="1">
-        <v>-12.00488915460156</v>
+        <v>-12.269938650306749</v>
       </c>
       <c r="O74" s="1">
         <v>20</v>
@@ -6678,16 +6681,16 @@
         <v>25.03694506602277</v>
       </c>
       <c r="Q74" s="1">
-        <v>40.35294117647059</v>
+        <v>39.411764705882355</v>
       </c>
       <c r="R74" s="1">
-        <v>31.647058823529417</v>
+        <v>31.294117647058822</v>
       </c>
       <c r="S74" s="1" t="s">
         <v>121</v>
       </c>
       <c r="T74" s="1">
-        <v>-0.37</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
@@ -6704,22 +6707,22 @@
         <v>97.42857142857143</v>
       </c>
       <c r="E75" s="3">
-        <v>-3.72</v>
+        <v>-3.81</v>
       </c>
       <c r="F75" s="3">
-        <v>-0.28947864338836166</v>
+        <v>-0.3671408209034849</v>
       </c>
       <c r="G75" s="3">
         <v>1.25</v>
       </c>
       <c r="H75" s="3">
-        <v>31.39</v>
+        <v>32.85</v>
       </c>
       <c r="I75" s="3">
-        <v>-11.34</v>
+        <v>-11.31</v>
       </c>
       <c r="J75" s="3">
-        <v>-0.022121120413911323</v>
+        <v>-0.024223150384342633</v>
       </c>
       <c r="K75" s="3" t="b">
         <v>0</v>
@@ -6728,28 +6731,28 @@
         <v>32</v>
       </c>
       <c r="M75" s="3">
-        <v>-0.2749750632025063</v>
+        <v>-0.35039641516794184</v>
       </c>
       <c r="N75" s="3">
-        <v>-20.621074245908485</v>
+        <v>-27.26687922257697</v>
       </c>
       <c r="O75" s="3">
-        <v>11.76470588235294</v>
+        <v>7.0588235294117645</v>
       </c>
       <c r="P75" s="3">
-        <v>32.10981456426673</v>
+        <v>32.49775597661548</v>
       </c>
       <c r="Q75" s="3">
-        <v>41.05882352941176</v>
+        <v>41.058823529411754</v>
       </c>
       <c r="R75" s="3">
-        <v>28.294117647058822</v>
+        <v>26.41176470588235</v>
       </c>
       <c r="S75" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T75" s="3">
-        <v>-30.3</v>
+        <v>-32.19</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
@@ -6766,22 +6769,22 @@
         <v>162.09090909090907</v>
       </c>
       <c r="E76" s="3">
-        <v>-0.07</v>
+        <v>-0.08</v>
       </c>
       <c r="F76" s="3">
-        <v>-0.3781822075658336</v>
+        <v>-0.4238295915247604</v>
       </c>
       <c r="G76" s="3">
         <v>3.25</v>
       </c>
       <c r="H76" s="3">
-        <v>43.43</v>
+        <v>40.67</v>
       </c>
       <c r="I76" s="3">
-        <v>-30.59</v>
+        <v>-31.46</v>
       </c>
       <c r="J76" s="3">
-        <v>-0.01123969026350234</v>
+        <v>-0.008609182920113043</v>
       </c>
       <c r="K76" s="3" t="b">
         <v>0</v>
@@ -6790,28 +6793,28 @@
         <v>10</v>
       </c>
       <c r="M76" s="3">
-        <v>-0.24764998589313536</v>
+        <v>-0.273129939904873</v>
       </c>
       <c r="N76" s="3">
-        <v>-17.888566514971394</v>
+        <v>-19.540231696270077</v>
       </c>
       <c r="O76" s="3">
-        <v>15.294117647058824</v>
+        <v>10.588235294117647</v>
       </c>
       <c r="P76" s="3">
         <v>51.49813033405746</v>
       </c>
       <c r="Q76" s="3">
-        <v>43.411764705882355</v>
+        <v>42.94117647058823</v>
       </c>
       <c r="R76" s="3">
-        <v>27.058823529411768</v>
+        <v>25.764705882352942</v>
       </c>
       <c r="S76" s="3" t="s">
         <v>109</v>
       </c>
       <c r="T76" s="3">
-        <v>1.33</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
@@ -6828,52 +6831,52 @@
         <v>-22.482857142857142</v>
       </c>
       <c r="E77" s="3">
-        <v>12.83</v>
+        <v>12.8</v>
       </c>
       <c r="F77" s="3">
-        <v>-0.03348036686562583</v>
+        <v>-0.16102454855904733</v>
       </c>
       <c r="G77" s="3">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="H77" s="3">
-        <v>45.35</v>
+        <v>43.62</v>
       </c>
       <c r="I77" s="3">
-        <v>42.21</v>
+        <v>40.7</v>
       </c>
       <c r="J77" s="3">
-        <v>-0.02541100767942279</v>
+        <v>-0.0203614235520299</v>
       </c>
       <c r="K77" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" s="3">
         <v>42</v>
       </c>
       <c r="M77" s="3">
-        <v>-0.0404420853548364</v>
+        <v>-0.1697316395415297</v>
       </c>
       <c r="N77" s="3">
-        <v>2.832223538858498</v>
+        <v>-9.200401659935748</v>
       </c>
       <c r="O77" s="3">
-        <v>52.94117647058824</v>
+        <v>23.52941176470588</v>
       </c>
       <c r="P77" s="3">
         <v>29.799918858582526</v>
       </c>
       <c r="Q77" s="3">
-        <v>29.882352941176475</v>
+        <v>30.70588235294118</v>
       </c>
       <c r="R77" s="3">
-        <v>23.94117647058824</v>
+        <v>15.235294117647062</v>
       </c>
       <c r="S77" s="3" t="s">
         <v>123</v>
       </c>
       <c r="T77" s="3">
-        <v>-49.78</v>
+        <v>-58.48</v>
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
@@ -6890,10 +6893,10 @@
         <v>2.5233644859813085</v>
       </c>
       <c r="E78" s="2">
-        <v>-9.21</v>
+        <v>-9.42</v>
       </c>
       <c r="F78" s="2">
-        <v>0.687318256940241</v>
+        <v>0.6602035029410325</v>
       </c>
       <c r="G78" s="2">
         <v>0.92</v>
@@ -6902,10 +6905,10 @@
         <v>69.3</v>
       </c>
       <c r="I78" s="2">
-        <v>37.23</v>
+        <v>37.17</v>
       </c>
       <c r="J78" s="2">
-        <v>0.03175588028881017</v>
+        <v>0.027637143117154688</v>
       </c>
       <c r="K78" s="2" t="b">
         <v>0</v>
@@ -6914,28 +6917,28 @@
         <v>-5</v>
       </c>
       <c r="M78" s="2">
-        <v>0.6826771112807672</v>
+        <v>0.6548452931056588</v>
       </c>
       <c r="N78" s="2">
-        <v>75.14414320241887</v>
+        <v>73.25729160478309</v>
       </c>
       <c r="O78" s="2">
-        <v>97.6470588235294</v>
+        <v>98.82352941176471</v>
       </c>
       <c r="P78" s="2">
         <v>18.71809072120826</v>
       </c>
       <c r="Q78" s="2">
-        <v>65.76470588235296</v>
+        <v>66.3529411764706</v>
       </c>
       <c r="R78" s="2">
-        <v>60.176470588235304</v>
+        <v>60.294117647058826</v>
       </c>
       <c r="S78" s="2" t="s">
         <v>110</v>
       </c>
       <c r="T78" s="2">
-        <v>11.58</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.25">
@@ -6952,52 +6955,52 @@
         <v>15.521739130434781</v>
       </c>
       <c r="E79" s="1">
-        <v>-3.59</v>
+        <v>-3.58</v>
       </c>
       <c r="F79" s="1">
-        <v>0.09633707540036605</v>
+        <v>0.035020472335560174</v>
       </c>
       <c r="G79" s="1">
         <v>1.12</v>
       </c>
       <c r="H79" s="1">
-        <v>50.66</v>
+        <v>50.87</v>
       </c>
       <c r="I79" s="1">
-        <v>26.46</v>
+        <v>26.23</v>
       </c>
       <c r="J79" s="1">
-        <v>0.0097321123111172</v>
+        <v>0.008665519072377836</v>
       </c>
       <c r="K79" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L79" s="1">
         <v>-2</v>
       </c>
       <c r="M79" s="1">
-        <v>0.10329879388957663</v>
+        <v>0.04305778708862085</v>
       </c>
       <c r="N79" s="1">
-        <v>17.20631146329981</v>
+        <v>12.078541003079298</v>
       </c>
       <c r="O79" s="1">
-        <v>68.23529411764706</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="P79" s="1">
-        <v>14.191910385236758</v>
+        <v>12.125814181373388</v>
       </c>
       <c r="Q79" s="1">
-        <v>55.05882352941177</v>
+        <v>54.70588235294118</v>
       </c>
       <c r="R79" s="1">
-        <v>49.23529411764706</v>
+        <v>48.17647058823529</v>
       </c>
       <c r="S79" s="1" t="s">
         <v>108</v>
       </c>
       <c r="T79" s="1">
-        <v>1.06</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.25">
@@ -7014,34 +7017,34 @@
         <v>0.15087719298245603</v>
       </c>
       <c r="E80" s="1">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="F80" s="1">
-        <v>0.11445209148409169</v>
+        <v>0.10116766016131047</v>
       </c>
       <c r="G80" s="1">
         <v>0.83</v>
       </c>
       <c r="H80" s="1">
-        <v>43.56</v>
+        <v>40.07</v>
       </c>
       <c r="I80" s="1">
-        <v>8.4</v>
+        <v>7.27</v>
       </c>
       <c r="J80" s="1">
-        <v>0.006523559716235105</v>
+        <v>0.003814402461251358</v>
       </c>
       <c r="K80" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L80" s="1">
         <v>6</v>
       </c>
       <c r="M80" s="1">
-        <v>0.10458965695771005</v>
+        <v>0.0897814642611412</v>
       </c>
       <c r="N80" s="1">
-        <v>17.335397770113147</v>
+        <v>16.750908720331335</v>
       </c>
       <c r="O80" s="1">
         <v>69.41176470588235</v>
@@ -7050,16 +7053,16 @@
         <v>11.616065285425229</v>
       </c>
       <c r="Q80" s="1">
-        <v>49.529411764705884</v>
+        <v>46.588235294117645</v>
       </c>
       <c r="R80" s="1">
-        <v>49.88235294117647</v>
+        <v>48.94117647058823</v>
       </c>
       <c r="S80" s="1" t="s">
         <v>102</v>
       </c>
       <c r="T80" s="1">
-        <v>10</v>
+        <v>9.06</v>
       </c>
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.25">
@@ -7079,49 +7082,49 @@
         <v>0.87</v>
       </c>
       <c r="F81" s="2">
-        <v>0.05218514591322693</v>
+        <v>0.030322124837270134</v>
       </c>
       <c r="G81" s="2">
         <v>0.77</v>
       </c>
       <c r="H81" s="2">
-        <v>48.41</v>
+        <v>47.97</v>
       </c>
       <c r="I81" s="2">
-        <v>9.19</v>
+        <v>9</v>
       </c>
       <c r="J81" s="2">
-        <v>0.004325144399203818</v>
+        <v>0.002498090645730258</v>
       </c>
       <c r="K81" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M81" s="2">
-        <v>0.03884185214224001</v>
+        <v>0.014917271560570544</v>
       </c>
       <c r="N81" s="2">
-        <v>10.760617288566136</v>
+        <v>9.264489450274265</v>
       </c>
       <c r="O81" s="2">
-        <v>62.35294117647059</v>
+        <v>63.52941176470588</v>
       </c>
       <c r="P81" s="2">
-        <v>6.707278396222185</v>
+        <v>6.084662055268521</v>
       </c>
       <c r="Q81" s="2">
-        <v>54</v>
+        <v>54.47058823529412</v>
       </c>
       <c r="R81" s="2">
-        <v>51.88235294117647</v>
+        <v>51.764705882352935</v>
       </c>
       <c r="S81" s="2" t="s">
         <v>111</v>
       </c>
       <c r="T81" s="2">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.25">
@@ -7135,55 +7138,55 @@
         <v>95.29411764705881</v>
       </c>
       <c r="D82" s="1">
-        <v>-0.9365895458440445</v>
+        <v>-0.9361610968294773</v>
       </c>
       <c r="E82" s="1">
-        <v>-1.14</v>
+        <v>-1.15</v>
       </c>
       <c r="F82" s="1">
-        <v>-0.059079476807359976</v>
+        <v>-0.035820251974008135</v>
       </c>
       <c r="G82" s="1">
         <v>1.01</v>
       </c>
       <c r="H82" s="1">
-        <v>36.3</v>
+        <v>41.27</v>
       </c>
       <c r="I82" s="1">
-        <v>5.64</v>
+        <v>6.59</v>
       </c>
       <c r="J82" s="1">
-        <v>0.0012201237566719805</v>
+        <v>0.0004099666323727792</v>
       </c>
       <c r="K82" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L82" s="1">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M82" s="1">
-        <v>-0.05849933359992576</v>
+        <v>-0.03515047574458641</v>
       </c>
       <c r="N82" s="1">
-        <v>1.0264987143495636</v>
+        <v>4.257714719758567</v>
       </c>
       <c r="O82" s="1">
-        <v>49.411764705882355</v>
+        <v>57.647058823529406</v>
       </c>
       <c r="P82" s="1">
         <v>7.571607002312677</v>
       </c>
       <c r="Q82" s="1">
-        <v>48.117647058823536</v>
+        <v>48.94117647058823</v>
       </c>
       <c r="R82" s="1">
-        <v>45.99999999999999</v>
+        <v>48.11764705882353</v>
       </c>
       <c r="S82" s="1" t="s">
         <v>101</v>
       </c>
       <c r="T82" s="1">
-        <v>0.7</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.25">
@@ -7197,55 +7200,55 @@
         <v>75.29411764705883</v>
       </c>
       <c r="D83" s="2">
-        <v>0.010321100917431176</v>
+        <v>0.0057339449541283175</v>
       </c>
       <c r="E83" s="2">
         <v>0.23</v>
       </c>
       <c r="F83" s="2">
-        <v>0.14803610104324944</v>
+        <v>0.11946571380693816</v>
       </c>
       <c r="G83" s="2">
         <v>1.07</v>
       </c>
       <c r="H83" s="2">
-        <v>61.35</v>
+        <v>65.55</v>
       </c>
       <c r="I83" s="2">
-        <v>16.75</v>
+        <v>18.36</v>
       </c>
       <c r="J83" s="2">
-        <v>0.0060417100649566196</v>
+        <v>0.0052782807758773</v>
       </c>
       <c r="K83" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L83" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M83" s="2">
-        <v>0.15209710349528893</v>
+        <v>0.12415414741289021</v>
       </c>
       <c r="N83" s="2">
-        <v>22.086142423871035</v>
+        <v>20.18817703550623</v>
       </c>
       <c r="O83" s="2">
-        <v>76.47058823529412</v>
+        <v>74.11764705882354</v>
       </c>
       <c r="P83" s="2">
         <v>12.706223591210087</v>
       </c>
       <c r="Q83" s="2">
-        <v>58.117647058823536</v>
+        <v>58.82352941176472</v>
       </c>
       <c r="R83" s="2">
-        <v>53.88235294117647</v>
+        <v>52.117647058823536</v>
       </c>
       <c r="S83" s="2" t="s">
         <v>109</v>
       </c>
       <c r="T83" s="2">
-        <v>1.75</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.25">
@@ -7262,52 +7265,52 @@
         <v>-2.336514314414867</v>
       </c>
       <c r="E84" s="1">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="F84" s="1">
-        <v>-0.08966024621211244</v>
+        <v>-0.07203090072237375</v>
       </c>
       <c r="G84" s="1">
         <v>1.2</v>
       </c>
       <c r="H84" s="1">
-        <v>48.53</v>
+        <v>47.37</v>
       </c>
       <c r="I84" s="1">
-        <v>0.76</v>
+        <v>0.29</v>
       </c>
       <c r="J84" s="1">
-        <v>-0.004236079974970514</v>
+        <v>-0.004291404589378948</v>
       </c>
       <c r="K84" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L84" s="1">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M84" s="1">
-        <v>-0.07805738206342816</v>
+        <v>-0.05863537613393932</v>
       </c>
       <c r="N84" s="1">
-        <v>-0.9293061320006757</v>
+        <v>1.9092246808232824</v>
       </c>
       <c r="O84" s="1">
-        <v>43.529411764705884</v>
+        <v>50.588235294117645</v>
       </c>
       <c r="P84" s="1">
         <v>20.22353911360907</v>
       </c>
       <c r="Q84" s="1">
-        <v>44.705882352941174</v>
+        <v>45.52941176470588</v>
       </c>
       <c r="R84" s="1">
-        <v>37.647058823529406</v>
+        <v>39.882352941176464</v>
       </c>
       <c r="S84" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T84" s="1">
-        <v>-9.12</v>
+        <v>-6.89</v>
       </c>
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.25">
@@ -7324,37 +7327,37 @@
         <v>1.6186186186186187</v>
       </c>
       <c r="E85" s="1">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="F85" s="1">
-        <v>-0.16846979777205007</v>
+        <v>-0.13853098956071186</v>
       </c>
       <c r="G85" s="1">
         <v>0.98</v>
       </c>
       <c r="H85" s="1">
-        <v>42.62</v>
+        <v>40.58</v>
       </c>
       <c r="I85" s="1">
-        <v>10.45</v>
+        <v>9.33</v>
       </c>
       <c r="J85" s="1">
-        <v>-0.008271890563022459</v>
+        <v>-0.007253566630343955</v>
       </c>
       <c r="K85" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L85" s="1">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="M85" s="1">
-        <v>-0.1696300841869185</v>
+        <v>-0.1398705420195553</v>
       </c>
       <c r="N85" s="1">
-        <v>-10.086576344349709</v>
+        <v>-6.214291907738306</v>
       </c>
       <c r="O85" s="1">
-        <v>24.705882352941178</v>
+        <v>32.94117647058823</v>
       </c>
       <c r="P85" s="1">
         <v>18.130768996018627</v>
@@ -7363,13 +7366,13 @@
         <v>44.35294117647059</v>
       </c>
       <c r="R85" s="1">
-        <v>32.76470588235294</v>
+        <v>35.11764705882353</v>
       </c>
       <c r="S85" s="1" t="s">
         <v>132</v>
       </c>
       <c r="T85" s="1">
-        <v>-23.88</v>
+        <v>-21.53</v>
       </c>
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.25">
@@ -7386,52 +7389,52 @@
         <v>-0.3141700404858299</v>
       </c>
       <c r="E86" s="1">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="F86" s="1">
-        <v>-0.01158596071125556</v>
+        <v>-0.05410670036530564</v>
       </c>
       <c r="G86" s="1">
         <v>0.95</v>
       </c>
       <c r="H86" s="1">
-        <v>33.44</v>
+        <v>35.49</v>
       </c>
       <c r="I86" s="1">
-        <v>3.96</v>
+        <v>4.15</v>
       </c>
       <c r="J86" s="1">
-        <v>-0.0033453858309615957</v>
+        <v>-0.005753042678949898</v>
       </c>
       <c r="K86" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L86" s="1">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M86" s="1">
-        <v>-0.01448667674842663</v>
+        <v>-0.057455581512414255</v>
       </c>
       <c r="N86" s="1">
-        <v>5.427764399499481</v>
+        <v>2.0272041429757883</v>
       </c>
       <c r="O86" s="1">
-        <v>57.647058823529406</v>
+        <v>52.94117647058824</v>
       </c>
       <c r="P86" s="1">
         <v>13.196185332148602</v>
       </c>
       <c r="Q86" s="1">
-        <v>43.99999999999999</v>
+        <v>44</v>
       </c>
       <c r="R86" s="1">
-        <v>45.64705882352941</v>
+        <v>43.529411764705884</v>
       </c>
       <c r="S86" s="1" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="T86" s="1">
-        <v>-1.12</v>
+        <v>-3.24</v>
       </c>
     </row>
   </sheetData>
@@ -7447,10 +7450,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -7458,7 +7461,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>46.05882352941177</v>
+        <v>44.588235294117645</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -7466,7 +7469,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>57.1764705882353</v>
+        <v>58.70588235294118</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7474,7 +7477,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>52.94117647058824</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -7482,7 +7485,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>40.29411764705881</v>
+        <v>39.588235294117645</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -7490,7 +7493,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>36.352941176470594</v>
+        <v>32.35294117647059</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7498,7 +7501,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>56.94117647058822</v>
+        <v>57.647058823529406</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -7506,7 +7509,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>37.294117647058826</v>
+        <v>33.76470588235294</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -7514,7 +7517,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>62.764705882352935</v>
+        <v>62.41176470588234</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -7522,7 +7525,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>46.23529411764706</v>
+        <v>47.294117647058826</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -7530,7 +7533,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>57.588235294117645</v>
+        <v>56.529411764705884</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -7538,7 +7541,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>61.1764705882353</v>
+        <v>61.05882352941177</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -7546,7 +7549,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>36.52941176470589</v>
+        <v>37.235294117647065</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -7554,7 +7557,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>60.88235294117648</v>
+        <v>59.58823529411765</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -7562,7 +7565,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>33.235294117647065</v>
+        <v>33.58823529411765</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -7570,7 +7573,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>13.529411764705884</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -7578,7 +7581,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>34.235294117647065</v>
+        <v>32.352941176470594</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -7594,7 +7597,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>55.17647058823529</v>
+        <v>53.64705882352941</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -7602,7 +7605,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>56.88235294117648</v>
+        <v>57.117647058823536</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -7610,7 +7613,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>19.11764705882353</v>
+        <v>18.764705882352942</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -7618,7 +7621,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>32.705882352941174</v>
+        <v>33.17647058823529</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -7626,7 +7629,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>57.41176470588236</v>
+        <v>57.29411764705883</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -7650,7 +7653,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>7.588235294117645</v>
+        <v>11.823529411764703</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -7658,7 +7661,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>0.7647058823529402</v>
+        <v>1.2352941176470562</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -7666,7 +7669,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>43.64705882352941</v>
+        <v>42.117647058823536</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -7674,7 +7677,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>42.76470588235294</v>
+        <v>39.705882352941174</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -7682,7 +7685,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>43</v>
+        <v>42.1764705882353</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -7690,7 +7693,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>39.588235294117645</v>
+        <v>40.64705882352941</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -7698,7 +7701,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>32.94117647058823</v>
+        <v>30.11764705882353</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -7706,7 +7709,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>60</v>
+        <v>60.52941176470589</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -7714,7 +7717,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>38.1764705882353</v>
+        <v>40.058823529411775</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -7722,7 +7725,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>42.41176470588236</v>
+        <v>39</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -7730,7 +7733,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>38.529411764705884</v>
+        <v>39.94117647058823</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -7738,7 +7741,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>50.588235294117645</v>
+        <v>50.823529411764696</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -7746,7 +7749,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>66.23529411764706</v>
+        <v>66.11764705882354</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -7754,7 +7757,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>34.82352941176471</v>
+        <v>32.117647058823536</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -7762,7 +7765,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>47.352941176470594</v>
+        <v>48.1764705882353</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -7770,7 +7773,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>19.705882352941174</v>
+        <v>22.88235294117647</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -7778,7 +7781,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>25.88235294117647</v>
+        <v>24.23529411764706</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -7786,7 +7789,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>55.82352941176471</v>
+        <v>54.76470588235294</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -7794,7 +7797,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>57.117647058823536</v>
+        <v>55.58823529411765</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -7802,7 +7805,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>42.470588235294116</v>
+        <v>42.23529411764706</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -7810,7 +7813,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>25.823529411764703</v>
+        <v>25.23529411764705</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -7818,7 +7821,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>47.00000000000001</v>
+        <v>51.70588235294118</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -7826,7 +7829,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>55.764705882352935</v>
+        <v>56.94117647058824</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -7834,7 +7837,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>56.94117647058824</v>
+        <v>56.47058823529412</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -7842,7 +7845,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>26.941176470588232</v>
+        <v>24.82352941176471</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -7850,7 +7853,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>45.117647058823536</v>
+        <v>45.352941176470594</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -7858,7 +7861,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>25.58823529411765</v>
+        <v>23.176470588235293</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -7866,7 +7869,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>22.88235294117647</v>
+        <v>23.176470588235293</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -7874,7 +7877,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>45.117647058823536</v>
+        <v>47.47058823529412</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -7882,7 +7885,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>28.94117647058824</v>
+        <v>28.588235294117645</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -7890,7 +7893,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>35.05882352941177</v>
+        <v>50.70588235294117</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -7898,7 +7901,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>24.941176470588232</v>
+        <v>26.941176470588232</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -7906,7 +7909,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>48.94117647058823</v>
+        <v>42.94117647058823</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -7914,7 +7917,7 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>25.529411764705884</v>
+        <v>27.529411764705884</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -7922,7 +7925,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>10.294117647058819</v>
+        <v>10.764705882352938</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -7930,7 +7933,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>39.00000000000001</v>
+        <v>40.05882352941177</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -7938,7 +7941,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>51.05882352941177</v>
+        <v>50.352941176470594</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -7946,7 +7949,7 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>42.23529411764706</v>
+        <v>46.47058823529412</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -7954,7 +7957,7 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>32.647058823529406</v>
+        <v>32.29411764705882</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -7962,7 +7965,7 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>29.64705882352941</v>
+        <v>29.76470588235294</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -7970,7 +7973,7 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>59.52941176470588</v>
+        <v>58.705882352941174</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -7978,7 +7981,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>25.647058823529413</v>
+        <v>30</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -7986,7 +7989,7 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>41.117647058823536</v>
+        <v>48.17647058823529</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -7994,7 +7997,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>43.17647058823529</v>
+        <v>40.94117647058823</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -8002,7 +8005,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>40.94117647058824</v>
+        <v>38.94117647058823</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -8010,7 +8013,7 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>56.70588235294119</v>
+        <v>55.76470588235294</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -8018,7 +8021,7 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>39.88235294117647</v>
+        <v>41.05882352941176</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -8026,7 +8029,7 @@
         <v>72</v>
       </c>
       <c r="B73">
-        <v>60.529411764705884</v>
+        <v>61</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -8034,7 +8037,7 @@
         <v>73</v>
       </c>
       <c r="B74">
-        <v>31.647058823529417</v>
+        <v>31.294117647058822</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -8042,7 +8045,7 @@
         <v>74</v>
       </c>
       <c r="B75">
-        <v>28.294117647058822</v>
+        <v>26.41176470588235</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -8050,7 +8053,7 @@
         <v>75</v>
       </c>
       <c r="B76">
-        <v>27.058823529411768</v>
+        <v>25.764705882352942</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -8058,7 +8061,7 @@
         <v>122</v>
       </c>
       <c r="B77">
-        <v>23.94117647058824</v>
+        <v>15.235294117647062</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -8066,7 +8069,7 @@
         <v>124</v>
       </c>
       <c r="B78">
-        <v>60.176470588235304</v>
+        <v>60.294117647058826</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -8074,7 +8077,7 @@
         <v>125</v>
       </c>
       <c r="B79">
-        <v>49.23529411764706</v>
+        <v>48.17647058823529</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -8082,7 +8085,7 @@
         <v>126</v>
       </c>
       <c r="B80">
-        <v>49.88235294117647</v>
+        <v>48.94117647058823</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -8090,7 +8093,7 @@
         <v>127</v>
       </c>
       <c r="B81">
-        <v>51.88235294117647</v>
+        <v>51.764705882352935</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -8098,7 +8101,7 @@
         <v>128</v>
       </c>
       <c r="B82">
-        <v>45.99999999999999</v>
+        <v>48.11764705882353</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -8106,7 +8109,7 @@
         <v>129</v>
       </c>
       <c r="B83">
-        <v>53.88235294117647</v>
+        <v>52.117647058823536</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -8114,7 +8117,7 @@
         <v>130</v>
       </c>
       <c r="B84">
-        <v>37.647058823529406</v>
+        <v>39.882352941176464</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -8122,7 +8125,7 @@
         <v>131</v>
       </c>
       <c r="B85">
-        <v>32.76470588235294</v>
+        <v>35.11764705882353</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
@@ -8130,7 +8133,7 @@
         <v>133</v>
       </c>
       <c r="B86">
-        <v>45.64705882352941</v>
+        <v>43.529411764705884</v>
       </c>
     </row>
   </sheetData>
@@ -8149,10 +8152,10 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -8160,10 +8163,10 @@
         <v>122</v>
       </c>
       <c r="C2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -8171,10 +8174,10 @@
         <v>124</v>
       </c>
       <c r="C3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -8182,21 +8185,21 @@
         <v>125</v>
       </c>
       <c r="C4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -8204,82 +8207,82 @@
         <v>126</v>
       </c>
       <c r="C6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D15" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -8298,10 +8301,10 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -8309,10 +8312,10 @@
         <v>127</v>
       </c>
       <c r="C2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -8320,98 +8323,98 @@
         <v>128</v>
       </c>
       <c r="C3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D14" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -8430,10 +8433,10 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -8441,10 +8444,10 @@
         <v>129</v>
       </c>
       <c r="C2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -8452,10 +8455,10 @@
         <v>130</v>
       </c>
       <c r="C3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -8463,90 +8466,90 @@
         <v>131</v>
       </c>
       <c r="C4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D14" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -8565,10 +8568,10 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -8576,114 +8579,114 @@
         <v>133</v>
       </c>
       <c r="C2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D15" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -8699,212 +8702,212 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D3" t="s">
         <v>190</v>
-      </c>
-      <c r="B3" t="s">
-        <v>187</v>
-      </c>
-      <c r="C3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D3" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>201</v>
+      </c>
+      <c r="B6" t="s">
+        <v>198</v>
+      </c>
+      <c r="C6" t="s">
+        <v>202</v>
+      </c>
+      <c r="D6" t="s">
         <v>200</v>
-      </c>
-      <c r="B6" t="s">
-        <v>197</v>
-      </c>
-      <c r="C6" t="s">
-        <v>201</v>
-      </c>
-      <c r="D6" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>208</v>
+      </c>
+      <c r="B9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C9" t="s">
         <v>207</v>
       </c>
-      <c r="B9" t="s">
-        <v>208</v>
-      </c>
-      <c r="C9" t="s">
-        <v>206</v>
-      </c>
       <c r="D9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B12" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C12" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D12" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C13" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D13" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B14" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C14" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D14" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C15" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D15" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -430,7 +430,7 @@
     <t>_date_</t>
   </si>
   <si>
-    <t>2026-09-28</t>
+    <t>2026-09-29</t>
   </si>
   <si>
     <t>Criteria</t>
@@ -694,34 +694,34 @@
     <t>Momentum Breakout, Market Leader</t>
   </si>
   <si>
-    <t>Momentum Breakout, Stable Uptrend, Institutional Buying</t>
+    <t>Momentum Breakout, Market Leader, Stable Uptrend, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Volume Spike</t>
   </si>
   <si>
     <t>Momentum Breakout, Volume Spike, Institutional Buying</t>
   </si>
   <si>
-    <t>Institutional Buying</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Market Leader, Volume Spike, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Momentum Breakout</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Volume Spike</t>
-  </si>
-  <si>
     <t>Volume Spike</t>
   </si>
   <si>
+    <t>Earnings Upcoming, Institutional Buying</t>
+  </si>
+  <si>
     <t>Volume Spike, Institutional Buying</t>
   </si>
   <si>
-    <t>Earnings Upcoming, Institutional Buying</t>
+    <t>Earnings Upcoming</t>
   </si>
 </sst>
 </file>
@@ -1416,7 +1416,7 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>66.11764705882354</v>
+        <v>66.23529411764706</v>
       </c>
       <c r="C2" t="s">
         <v>222</v>
@@ -1435,24 +1435,24 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="B4">
-        <v>61.05882352941177</v>
+        <v>61.52941176470589</v>
       </c>
       <c r="C4" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="B5">
-        <v>61</v>
+        <v>61.41176470588235</v>
       </c>
       <c r="C5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1460,7 +1460,7 @@
         <v>32</v>
       </c>
       <c r="B6">
-        <v>60.52941176470589</v>
+        <v>60.882352941176485</v>
       </c>
       <c r="C6" t="s">
         <v>222</v>
@@ -1468,32 +1468,32 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>124</v>
+        <v>13</v>
       </c>
       <c r="B7">
-        <v>60.294117647058826</v>
+        <v>60.411764705882355</v>
       </c>
       <c r="C7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>124</v>
       </c>
       <c r="B8">
-        <v>59.58823529411765</v>
+        <v>60.29411764705883</v>
       </c>
       <c r="C8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="B9">
-        <v>58.70588235294118</v>
+        <v>58.8235294117647</v>
       </c>
       <c r="C9" t="s">
         <v>225</v>
@@ -1501,21 +1501,21 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="B10">
-        <v>58.705882352941174</v>
+        <v>58.23529411764705</v>
       </c>
       <c r="C10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B11">
-        <v>57.647058823529406</v>
+        <v>57.82352941176471</v>
       </c>
       <c r="C11" t="s">
         <v>226</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="B12">
-        <v>57.29411764705883</v>
+        <v>57.294117647058826</v>
       </c>
       <c r="C12" t="s">
         <v>227</v>
@@ -1534,21 +1534,21 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B13">
-        <v>57.117647058823536</v>
+        <v>56.94117647058824</v>
       </c>
       <c r="C13" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B14">
-        <v>56.94117647058824</v>
+        <v>56.88235294117647</v>
       </c>
       <c r="C14" t="s">
         <v>228</v>
@@ -1556,21 +1556,21 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="B15">
-        <v>56.529411764705884</v>
+        <v>56.35294117647059</v>
       </c>
       <c r="C15" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="B16">
-        <v>56.47058823529412</v>
+        <v>56.11764705882352</v>
       </c>
       <c r="C16" t="s">
         <v>229</v>
@@ -1578,35 +1578,35 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="B17">
-        <v>55.58823529411765</v>
+        <v>55.70588235294118</v>
       </c>
       <c r="C17" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="B18">
-        <v>54.76470588235294</v>
+        <v>54.35294117647059</v>
       </c>
       <c r="C18" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="B19">
-        <v>53.64705882352941</v>
+        <v>53.47058823529413</v>
       </c>
       <c r="C19" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -1614,43 +1614,43 @@
         <v>129</v>
       </c>
       <c r="B20">
-        <v>52.117647058823536</v>
+        <v>53.05882352941177</v>
       </c>
       <c r="C20" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>3</v>
+        <v>127</v>
       </c>
       <c r="B21">
-        <v>52</v>
+        <v>52.764705882352935</v>
       </c>
       <c r="C21" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>127</v>
+        <v>3</v>
       </c>
       <c r="B22">
-        <v>51.764705882352935</v>
+        <v>51.88235294117647</v>
       </c>
       <c r="C22" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="B23">
-        <v>51.70588235294118</v>
+        <v>50.411764705882355</v>
       </c>
       <c r="C23" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -1658,109 +1658,109 @@
         <v>36</v>
       </c>
       <c r="B24">
-        <v>50.823529411764696</v>
+        <v>49.99999999999999</v>
       </c>
       <c r="C24" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>55</v>
+        <v>126</v>
       </c>
       <c r="B25">
-        <v>50.70588235294117</v>
+        <v>48.94117647058823</v>
       </c>
       <c r="C25" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B26">
-        <v>50.352941176470594</v>
+        <v>48.1764705882353</v>
       </c>
       <c r="C26" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>126</v>
+        <v>53</v>
       </c>
       <c r="B27">
-        <v>48.94117647058823</v>
+        <v>48.11764705882353</v>
       </c>
       <c r="C27" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="B28">
-        <v>48.1764705882353</v>
+        <v>48.11764705882353</v>
       </c>
       <c r="C28" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="B29">
-        <v>48.17647058823529</v>
+        <v>47.47058823529412</v>
       </c>
       <c r="C29" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>128</v>
+        <v>67</v>
       </c>
       <c r="B30">
-        <v>48.11764705882353</v>
+        <v>47</v>
       </c>
       <c r="C30" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B31">
-        <v>47.47058823529412</v>
+        <v>46.23529411764706</v>
       </c>
       <c r="C31" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="B32">
-        <v>46.47058823529412</v>
+        <v>45.00000000000001</v>
       </c>
       <c r="C32" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B33">
-        <v>45.352941176470594</v>
+        <v>44.23529411764706</v>
       </c>
       <c r="C33" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -1779,65 +1779,65 @@
         <v>133</v>
       </c>
       <c r="B35">
-        <v>43.529411764705884</v>
+        <v>43.64705882352941</v>
       </c>
       <c r="C35" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="B36">
-        <v>42.94117647058823</v>
+        <v>41.88235294117648</v>
       </c>
       <c r="C36" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="B37">
-        <v>42.23529411764706</v>
+        <v>41.705882352941174</v>
       </c>
       <c r="C37" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="B38">
-        <v>42.1764705882353</v>
+        <v>41.411764705882355</v>
       </c>
       <c r="C38" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="B39">
-        <v>42.117647058823536</v>
+        <v>41.1764705882353</v>
       </c>
       <c r="C39" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="B40">
-        <v>40.64705882352941</v>
+        <v>40.529411764705884</v>
       </c>
       <c r="C40" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -1845,32 +1845,32 @@
         <v>33</v>
       </c>
       <c r="B41">
-        <v>40.058823529411775</v>
+        <v>39.352941176470594</v>
       </c>
       <c r="C41" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="B42">
-        <v>40.05882352941177</v>
+        <v>39.17647058823529</v>
       </c>
       <c r="C42" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>130</v>
+        <v>29</v>
       </c>
       <c r="B43">
-        <v>39.882352941176464</v>
+        <v>38.76470588235294</v>
       </c>
       <c r="C43" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -1878,7 +1878,7 @@
         <v>28</v>
       </c>
       <c r="B44">
-        <v>39.705882352941174</v>
+        <v>38.41176470588235</v>
       </c>
       <c r="C44" t="s">
         <v>232</v>
@@ -1886,79 +1886,79 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B45">
-        <v>39.588235294117645</v>
+        <v>37.529411764705884</v>
       </c>
       <c r="C45" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="B46">
-        <v>38.94117647058823</v>
+        <v>37.235294117647065</v>
       </c>
       <c r="C46" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>12</v>
+        <v>131</v>
       </c>
       <c r="B47">
-        <v>37.235294117647065</v>
+        <v>36.00000000000001</v>
       </c>
       <c r="C47" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>131</v>
+        <v>4</v>
       </c>
       <c r="B48">
-        <v>35.11764705882353</v>
+        <v>34.294117647058826</v>
       </c>
       <c r="C48" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="B49">
-        <v>33.76470588235294</v>
+        <v>33.41176470588235</v>
       </c>
       <c r="C49" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B50">
-        <v>33.58823529411765</v>
+        <v>32.58823529411765</v>
       </c>
       <c r="C50" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B51">
-        <v>33.17647058823529</v>
+        <v>32.529411764705884</v>
       </c>
       <c r="C51" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -2192,19 +2192,19 @@
         <v>-2.08</v>
       </c>
       <c r="F2" s="1">
-        <v>0.15132359060100226</v>
+        <v>0.1744031139026391</v>
       </c>
       <c r="G2" s="1">
         <v>0.21</v>
       </c>
       <c r="H2" s="1">
-        <v>53.62</v>
+        <v>50.64</v>
       </c>
       <c r="I2" s="1">
-        <v>10.2</v>
+        <v>8.94</v>
       </c>
       <c r="J2" s="1">
-        <v>0.010397694802518957</v>
+        <v>0.009833514263353984</v>
       </c>
       <c r="K2" s="1" t="b">
         <v>0</v>
@@ -2213,28 +2213,28 @@
         <v>-457</v>
       </c>
       <c r="M2" s="1">
-        <v>0.09841126847668624</v>
+        <v>0.13934229116550956</v>
       </c>
       <c r="N2" s="1">
-        <v>17.613889141885846</v>
+        <v>19.447307944035703</v>
       </c>
       <c r="O2" s="1">
-        <v>71.76470588235294</v>
+        <v>76.47058823529412</v>
       </c>
       <c r="P2" s="1">
         <v>16.29652721982991</v>
       </c>
       <c r="Q2" s="1">
-        <v>48.8235294117647</v>
+        <v>47.41176470588235</v>
       </c>
       <c r="R2" s="1">
-        <v>44.588235294117645</v>
+        <v>45.76470588235294</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>95</v>
       </c>
       <c r="T2" s="1">
-        <v>24.77</v>
+        <v>25.95</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -2254,49 +2254,49 @@
         <v>3.6</v>
       </c>
       <c r="F3" s="2">
-        <v>0.03222173311079152</v>
+        <v>0.006378801643399004</v>
       </c>
       <c r="G3" s="2">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="H3" s="2">
-        <v>67.04</v>
+        <v>66.14</v>
       </c>
       <c r="I3" s="2">
-        <v>67.07</v>
+        <v>65.77</v>
       </c>
       <c r="J3" s="2">
-        <v>0.01788051495543927</v>
+        <v>0.020031403042783044</v>
       </c>
       <c r="K3" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="2">
         <v>860</v>
       </c>
       <c r="M3" s="2">
-        <v>0.13134861506520634</v>
+        <v>0.07161856040742487</v>
       </c>
       <c r="N3" s="2">
-        <v>20.907623800737856</v>
+        <v>12.674934868227233</v>
       </c>
       <c r="O3" s="2">
-        <v>75.29411764705883</v>
+        <v>69.41176470588235</v>
       </c>
       <c r="P3" s="2">
         <v>26.053946839070953</v>
       </c>
       <c r="Q3" s="2">
-        <v>75.88235294117646</v>
+        <v>75.88235294117648</v>
       </c>
       <c r="R3" s="2">
-        <v>58.70588235294118</v>
+        <v>56.94117647058824</v>
       </c>
       <c r="S3" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T3" s="2">
-        <v>-8.37</v>
+        <v>-10.13</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -2310,25 +2310,25 @@
         <v>10.588235294117647</v>
       </c>
       <c r="D4" s="2">
-        <v>12.47634069400631</v>
+        <v>12.608832807570979</v>
       </c>
       <c r="E4" s="2">
         <v>6.39</v>
       </c>
       <c r="F4" s="2">
-        <v>0.24753379953182647</v>
+        <v>0.2327665689372883</v>
       </c>
       <c r="G4" s="2">
         <v>1.36</v>
       </c>
       <c r="H4" s="2">
-        <v>52.26</v>
+        <v>50.33</v>
       </c>
       <c r="I4" s="2">
-        <v>47.08</v>
+        <v>45.28</v>
       </c>
       <c r="J4" s="2">
-        <v>0.02144487541476158</v>
+        <v>0.020137465246089566</v>
       </c>
       <c r="K4" s="2" t="b">
         <v>0</v>
@@ -2337,10 +2337,10 @@
         <v>181</v>
       </c>
       <c r="M4" s="2">
-        <v>0.2716457437910085</v>
+        <v>0.24874365271623344</v>
       </c>
       <c r="N4" s="2">
-        <v>34.93733667331808</v>
+        <v>30.387444099108095</v>
       </c>
       <c r="O4" s="2">
         <v>85.88235294117646</v>
@@ -2349,16 +2349,16 @@
         <v>19.349659482175007</v>
       </c>
       <c r="Q4" s="2">
-        <v>57.88235294117648</v>
+        <v>57.05882352941177</v>
       </c>
       <c r="R4" s="2">
-        <v>52</v>
+        <v>51.88235294117647</v>
       </c>
       <c r="S4" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T4" s="2">
-        <v>3.65</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -2372,25 +2372,25 @@
         <v>40</v>
       </c>
       <c r="D5" s="1">
-        <v>30.694444444444443</v>
+        <v>30.666666666666668</v>
       </c>
       <c r="E5" s="1">
         <v>1.7</v>
       </c>
       <c r="F5" s="1">
-        <v>-0.1586925511591099</v>
+        <v>-0.22758311906285222</v>
       </c>
       <c r="G5" s="1">
         <v>1.91</v>
       </c>
       <c r="H5" s="1">
-        <v>52.81</v>
+        <v>47.48</v>
       </c>
       <c r="I5" s="1">
-        <v>-6.85</v>
+        <v>-9.26</v>
       </c>
       <c r="J5" s="1">
-        <v>-0.005701715423466112</v>
+        <v>-0.005193417278709439</v>
       </c>
       <c r="K5" s="1" t="b">
         <v>0</v>
@@ -2399,28 +2399,28 @@
         <v>142</v>
       </c>
       <c r="M5" s="1">
-        <v>-0.0977429142817332</v>
+        <v>-0.187196601732741</v>
       </c>
       <c r="N5" s="1">
-        <v>-2.0015291339561045</v>
+        <v>-13.206581345789342</v>
       </c>
       <c r="O5" s="1">
-        <v>43.529411764705884</v>
+        <v>24.705882352941178</v>
       </c>
       <c r="P5" s="1">
         <v>33.002444654975626</v>
       </c>
       <c r="Q5" s="1">
-        <v>52.705882352941174</v>
+        <v>51.1764705882353</v>
       </c>
       <c r="R5" s="1">
-        <v>39.588235294117645</v>
+        <v>34.294117647058826</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T5" s="1">
-        <v>-6.39</v>
+        <v>-11.68</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -2440,19 +2440,19 @@
         <v>-1.85</v>
       </c>
       <c r="F6" s="1">
-        <v>-0.1539526213206618</v>
+        <v>-0.1438728373204411</v>
       </c>
       <c r="G6" s="1">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="H6" s="1">
-        <v>38.34</v>
+        <v>33.2</v>
       </c>
       <c r="I6" s="1">
-        <v>-15.46</v>
+        <v>-18.18</v>
       </c>
       <c r="J6" s="1">
-        <v>-0.002379906954218569</v>
+        <v>-0.0023033099569645726</v>
       </c>
       <c r="K6" s="1" t="b">
         <v>0</v>
@@ -2461,28 +2461,28 @@
         <v>-205</v>
       </c>
       <c r="M6" s="1">
-        <v>-0.11376604755535846</v>
+        <v>-0.11680055647278409</v>
       </c>
       <c r="N6" s="1">
-        <v>-3.603842461318627</v>
+        <v>-6.166976819793657</v>
       </c>
       <c r="O6" s="1">
-        <v>36.470588235294116</v>
+        <v>40</v>
       </c>
       <c r="P6" s="1">
-        <v>26.56962821327962</v>
+        <v>25.73060759470965</v>
       </c>
       <c r="Q6" s="1">
-        <v>39.05882352941177</v>
+        <v>38.70588235294118</v>
       </c>
       <c r="R6" s="1">
-        <v>32.35294117647059</v>
+        <v>33.8235294117647</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T6" s="1">
-        <v>13.27</v>
+        <v>14.74</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -2496,25 +2496,25 @@
         <v>69.41176470588235</v>
       </c>
       <c r="D7" s="2">
-        <v>7.8103666245259165</v>
+        <v>7.811630847029078</v>
       </c>
       <c r="E7" s="2">
         <v>0.49</v>
       </c>
       <c r="F7" s="2">
-        <v>0.009572343931911642</v>
+        <v>0.06454625939263205</v>
       </c>
       <c r="G7" s="2">
         <v>2.22</v>
       </c>
       <c r="H7" s="2">
-        <v>53.78</v>
+        <v>60.01</v>
       </c>
       <c r="I7" s="2">
-        <v>12.14</v>
+        <v>15.25</v>
       </c>
       <c r="J7" s="2">
-        <v>0.007954353606071099</v>
+        <v>0.008839661170852395</v>
       </c>
       <c r="K7" s="2" t="b">
         <v>0</v>
@@ -2523,28 +2523,28 @@
         <v>176</v>
       </c>
       <c r="M7" s="2">
-        <v>0.09128504392136172</v>
+        <v>0.11869082108794604</v>
       </c>
       <c r="N7" s="2">
-        <v>16.90126668635338</v>
+        <v>17.38216093627935</v>
       </c>
       <c r="O7" s="2">
-        <v>70.58823529411765</v>
+        <v>71.76470588235294</v>
       </c>
       <c r="P7" s="2">
         <v>19.398494070050486</v>
       </c>
       <c r="Q7" s="2">
-        <v>66.58823529411765</v>
+        <v>68.47058823529412</v>
       </c>
       <c r="R7" s="2">
-        <v>57.647058823529406</v>
+        <v>58.23529411764705</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T7" s="2">
-        <v>9.23</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -2564,19 +2564,19 @@
         <v>2.62</v>
       </c>
       <c r="F8" s="1">
-        <v>-0.1714970147785152</v>
+        <v>-0.13784138431912413</v>
       </c>
       <c r="G8" s="1">
         <v>0.61</v>
       </c>
       <c r="H8" s="1">
-        <v>41.16</v>
+        <v>41.32</v>
       </c>
       <c r="I8" s="1">
-        <v>6.16</v>
+        <v>6.11</v>
       </c>
       <c r="J8" s="1">
-        <v>-0.012237623850019754</v>
+        <v>-0.012325674328951283</v>
       </c>
       <c r="K8" s="1" t="b">
         <v>0</v>
@@ -2585,28 +2585,28 @@
         <v>363</v>
       </c>
       <c r="M8" s="1">
-        <v>-0.19761828772596235</v>
+        <v>-0.15514989174631466</v>
       </c>
       <c r="N8" s="1">
-        <v>-11.989066478379014</v>
+        <v>-10.001910347146712</v>
       </c>
       <c r="O8" s="1">
-        <v>21.176470588235293</v>
+        <v>34.11764705882353</v>
       </c>
       <c r="P8" s="1">
         <v>14.910048504309984</v>
       </c>
       <c r="Q8" s="1">
-        <v>44.470588235294116</v>
+        <v>44.94117647058824</v>
       </c>
       <c r="R8" s="1">
-        <v>33.76470588235294</v>
+        <v>37.529411764705884</v>
       </c>
       <c r="S8" s="1" t="s">
         <v>101</v>
       </c>
       <c r="T8" s="1">
-        <v>-25.99</v>
+        <v>-22.23</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -2626,19 +2626,19 @@
         <v>2.97</v>
       </c>
       <c r="F9" s="2">
-        <v>0.5616217782893509</v>
+        <v>0.5386383245216965</v>
       </c>
       <c r="G9" s="2">
         <v>1.6</v>
       </c>
       <c r="H9" s="2">
-        <v>61.48</v>
+        <v>60.16</v>
       </c>
       <c r="I9" s="2">
-        <v>23.56</v>
+        <v>22.86</v>
       </c>
       <c r="J9" s="2">
-        <v>0.035812135835275885</v>
+        <v>0.03540855662268145</v>
       </c>
       <c r="K9" s="2" t="b">
         <v>0</v>
@@ -2647,10 +2647,10 @@
         <v>-113</v>
       </c>
       <c r="M9" s="2">
-        <v>0.6018083520546542</v>
+        <v>0.565266797486605</v>
       </c>
       <c r="N9" s="2">
-        <v>67.95359749968264</v>
+        <v>62.03975857614525</v>
       </c>
       <c r="O9" s="2">
         <v>97.6470588235294</v>
@@ -2659,7 +2659,7 @@
         <v>33.227512780245505</v>
       </c>
       <c r="Q9" s="2">
-        <v>73.05882352941177</v>
+        <v>72.47058823529412</v>
       </c>
       <c r="R9" s="2">
         <v>62.41176470588234</v>
@@ -2682,25 +2682,25 @@
         <v>58.82352941176471</v>
       </c>
       <c r="D10" s="1">
-        <v>0.7484536082474229</v>
+        <v>0.754639175257732</v>
       </c>
       <c r="E10" s="1">
         <v>0.02</v>
       </c>
       <c r="F10" s="1">
-        <v>-0.03135675133015266</v>
+        <v>-0.003203961991568721</v>
       </c>
       <c r="G10" s="1">
         <v>1.42</v>
       </c>
       <c r="H10" s="1">
-        <v>52.59</v>
+        <v>50.53</v>
       </c>
       <c r="I10" s="1">
-        <v>2.01</v>
+        <v>1.37</v>
       </c>
       <c r="J10" s="1">
-        <v>0.007568911762150084</v>
+        <v>0.007422108192718916</v>
       </c>
       <c r="K10" s="1" t="b">
         <v>0</v>
@@ -2709,28 +2709,28 @@
         <v>-50</v>
       </c>
       <c r="M10" s="1">
-        <v>-0.00322614969444035</v>
+        <v>0.01543596908386724</v>
       </c>
       <c r="N10" s="1">
-        <v>7.450147324773182</v>
+        <v>7.056675735871483</v>
       </c>
       <c r="O10" s="1">
-        <v>62.35294117647059</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="P10" s="1">
         <v>14.568379622257217</v>
       </c>
       <c r="Q10" s="1">
-        <v>51.76470588235294</v>
+        <v>51.64705882352941</v>
       </c>
       <c r="R10" s="1">
-        <v>47.294117647058826</v>
+        <v>48.41176470588235</v>
       </c>
       <c r="S10" s="1" t="s">
         <v>103</v>
       </c>
       <c r="T10" s="1">
-        <v>11.75</v>
+        <v>12.86</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -2750,19 +2750,19 @@
         <v>2.26</v>
       </c>
       <c r="F11" s="2">
-        <v>0.3476885486536194</v>
+        <v>0.31697457118717376</v>
       </c>
       <c r="G11" s="2">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="H11" s="2">
-        <v>50.99</v>
+        <v>54.84</v>
       </c>
       <c r="I11" s="2">
-        <v>33.95</v>
+        <v>37.79</v>
       </c>
       <c r="J11" s="2">
-        <v>0.021960151707457486</v>
+        <v>0.01917155768958174</v>
       </c>
       <c r="K11" s="2" t="b">
         <v>0</v>
@@ -2771,28 +2771,28 @@
         <v>40</v>
       </c>
       <c r="M11" s="2">
-        <v>0.3289348142298112</v>
+        <v>0.304104142587468</v>
       </c>
       <c r="N11" s="2">
-        <v>40.666243717198334</v>
+        <v>35.92349308623154</v>
       </c>
       <c r="O11" s="2">
-        <v>89.41176470588236</v>
+        <v>88.23529411764706</v>
       </c>
       <c r="P11" s="2">
         <v>21.2185970476566</v>
       </c>
       <c r="Q11" s="2">
-        <v>62.11764705882352</v>
+        <v>63.05882352941177</v>
       </c>
       <c r="R11" s="2">
-        <v>56.529411764705884</v>
+        <v>55.70588235294118</v>
       </c>
       <c r="S11" s="2" t="s">
         <v>104</v>
       </c>
       <c r="T11" s="2">
-        <v>4.88</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -2812,19 +2812,19 @@
         <v>1.34</v>
       </c>
       <c r="F12" s="2">
-        <v>0.5343973205552309</v>
+        <v>0.49338667099582123</v>
       </c>
       <c r="G12" s="2">
         <v>0.99</v>
       </c>
       <c r="H12" s="2">
-        <v>51.41</v>
+        <v>48.3</v>
       </c>
       <c r="I12" s="2">
-        <v>45.08</v>
+        <v>42.3</v>
       </c>
       <c r="J12" s="2">
-        <v>0.03953146008340663</v>
+        <v>0.03728376961720136</v>
       </c>
       <c r="K12" s="2" t="b">
         <v>0</v>
@@ -2833,28 +2833,28 @@
         <v>30</v>
       </c>
       <c r="M12" s="2">
-        <v>0.5337275443258092</v>
+        <v>0.4929428631130728</v>
       </c>
       <c r="N12" s="2">
-        <v>61.14551672679812</v>
+        <v>54.80736513879204</v>
       </c>
       <c r="O12" s="2">
-        <v>95.29411764705881</v>
+        <v>96.47058823529412</v>
       </c>
       <c r="P12" s="2">
         <v>23.557267760130397</v>
       </c>
       <c r="Q12" s="2">
-        <v>67.41176470588235</v>
+        <v>66.94117647058823</v>
       </c>
       <c r="R12" s="2">
-        <v>61.05882352941177</v>
+        <v>61.41176470588235</v>
       </c>
       <c r="S12" s="2" t="s">
         <v>105</v>
       </c>
       <c r="T12" s="2">
-        <v>8.31</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -2874,19 +2874,19 @@
         <v>0.14</v>
       </c>
       <c r="F13" s="1">
-        <v>0.37801015538766347</v>
+        <v>0.3375681044161909</v>
       </c>
       <c r="G13" s="1">
         <v>1.58</v>
       </c>
       <c r="H13" s="1">
-        <v>45.24</v>
+        <v>42.15</v>
       </c>
       <c r="I13" s="1">
-        <v>8.58</v>
+        <v>5.1</v>
       </c>
       <c r="J13" s="1">
-        <v>0.04243333562607788</v>
+        <v>0.040535953358588145</v>
       </c>
       <c r="K13" s="1" t="b">
         <v>0</v>
@@ -2895,10 +2895,10 @@
         <v>5</v>
       </c>
       <c r="M13" s="1">
-        <v>0.41685717669412337</v>
+        <v>0.36330896161560244</v>
       </c>
       <c r="N13" s="1">
-        <v>49.45847996362955</v>
+        <v>41.843974989045</v>
       </c>
       <c r="O13" s="1">
         <v>91.76470588235294</v>
@@ -2907,7 +2907,7 @@
         <v>40.13761891809808</v>
       </c>
       <c r="Q13" s="1">
-        <v>38.58823529411765</v>
+        <v>37.88235294117648</v>
       </c>
       <c r="R13" s="1">
         <v>37.235294117647065</v>
@@ -2936,19 +2936,19 @@
         <v>-1.81</v>
       </c>
       <c r="F14" s="2">
-        <v>0.5089135044606476</v>
+        <v>0.49612336734945917</v>
       </c>
       <c r="G14" s="2">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="H14" s="2">
-        <v>60.27</v>
+        <v>65.9</v>
       </c>
       <c r="I14" s="2">
-        <v>75.78</v>
+        <v>84.83</v>
       </c>
       <c r="J14" s="2">
-        <v>0.034496986763934985</v>
+        <v>0.034277725501204094</v>
       </c>
       <c r="K14" s="2" t="b">
         <v>0</v>
@@ -2957,28 +2957,28 @@
         <v>101</v>
       </c>
       <c r="M14" s="2">
-        <v>0.4928388749545263</v>
+        <v>0.48458436239799885</v>
       </c>
       <c r="N14" s="2">
-        <v>57.05664978966985</v>
+        <v>53.97151506728463</v>
       </c>
       <c r="O14" s="2">
-        <v>92.94117647058823</v>
+        <v>95.29411764705881</v>
       </c>
       <c r="P14" s="2">
         <v>19.142997204429033</v>
       </c>
       <c r="Q14" s="2">
-        <v>68.11764705882354</v>
+        <v>68.82352941176471</v>
       </c>
       <c r="R14" s="2">
-        <v>59.58823529411765</v>
+        <v>60.411764705882355</v>
       </c>
       <c r="S14" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T14" s="2">
-        <v>3.67</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -2998,49 +2998,49 @@
         <v>1.51</v>
       </c>
       <c r="F15" s="1">
-        <v>-0.20357833542852233</v>
+        <v>-0.2297230983678799</v>
       </c>
       <c r="G15" s="1">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="H15" s="1">
-        <v>60.55</v>
+        <v>58.03</v>
       </c>
       <c r="I15" s="1">
-        <v>48.12</v>
+        <v>44.57</v>
       </c>
       <c r="J15" s="1">
-        <v>0.020174346157904356</v>
+        <v>0.021984455366145874</v>
       </c>
       <c r="K15" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" s="1">
         <v>1030</v>
       </c>
       <c r="M15" s="1">
-        <v>-0.11918653052138539</v>
+        <v>-0.1742471130243205</v>
       </c>
       <c r="N15" s="1">
-        <v>-4.145890757921323</v>
+        <v>-11.911632474947298</v>
       </c>
       <c r="O15" s="1">
-        <v>35.294117647058826</v>
+        <v>30.58823529411765</v>
       </c>
       <c r="P15" s="1">
         <v>41.90435941885386</v>
       </c>
       <c r="Q15" s="1">
-        <v>62.82352941176471</v>
+        <v>62.235294117647065</v>
       </c>
       <c r="R15" s="1">
-        <v>33.58823529411765</v>
+        <v>32.529411764705884</v>
       </c>
       <c r="S15" s="1" t="s">
         <v>107</v>
       </c>
       <c r="T15" s="1">
-        <v>-24.83</v>
+        <v>-25.89</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -3060,19 +3060,19 @@
         <v>29.77</v>
       </c>
       <c r="F16" s="3">
-        <v>-0.42687328334488717</v>
+        <v>-0.4035416195135191</v>
       </c>
       <c r="G16" s="3">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="H16" s="3">
-        <v>42.74</v>
+        <v>43.29</v>
       </c>
       <c r="I16" s="3">
-        <v>-8.97</v>
+        <v>-9.28</v>
       </c>
       <c r="J16" s="3">
-        <v>-0.007127116777868138</v>
+        <v>-0.0037464760279519527</v>
       </c>
       <c r="K16" s="3" t="b">
         <v>0</v>
@@ -3081,10 +3081,10 @@
         <v>27</v>
       </c>
       <c r="M16" s="3">
-        <v>-0.37329118499114944</v>
+        <v>-0.36759318101089256</v>
       </c>
       <c r="N16" s="3">
-        <v>-29.55635620489772</v>
+        <v>-31.2462392736045</v>
       </c>
       <c r="O16" s="3">
         <v>4.705882352941177</v>
@@ -3093,16 +3093,16 @@
         <v>40.1905830435425</v>
       </c>
       <c r="Q16" s="3">
-        <v>33.05882352941176</v>
+        <v>35.76470588235294</v>
       </c>
       <c r="R16" s="3">
-        <v>14</v>
+        <v>14.941176470588236</v>
       </c>
       <c r="S16" s="3" t="s">
         <v>108</v>
       </c>
       <c r="T16" s="3">
-        <v>-29.23</v>
+        <v>-28.29</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -3122,19 +3122,19 @@
         <v>-1.63</v>
       </c>
       <c r="F17" s="1">
-        <v>-0.14119432085225458</v>
+        <v>-0.12896663603686004</v>
       </c>
       <c r="G17" s="1">
         <v>1.76</v>
       </c>
       <c r="H17" s="1">
-        <v>46.34</v>
+        <v>46.89</v>
       </c>
       <c r="I17" s="1">
-        <v>1.17</v>
+        <v>1.58</v>
       </c>
       <c r="J17" s="1">
-        <v>0.010813196832225178</v>
+        <v>0.011293607413839021</v>
       </c>
       <c r="K17" s="1" t="b">
         <v>0</v>
@@ -3143,28 +3143,28 @@
         <v>31</v>
       </c>
       <c r="M17" s="1">
-        <v>-0.09029132741620371</v>
+        <v>-0.09523723694797592</v>
       </c>
       <c r="N17" s="1">
-        <v>-1.256370447403158</v>
+        <v>-4.010644867312843</v>
       </c>
       <c r="O17" s="1">
-        <v>44.70588235294118</v>
+        <v>47.05882352941176</v>
       </c>
       <c r="P17" s="1">
         <v>24.80206596461608</v>
       </c>
       <c r="Q17" s="1">
-        <v>42.35294117647058</v>
+        <v>42</v>
       </c>
       <c r="R17" s="1">
-        <v>32.352941176470594</v>
+        <v>32.58823529411765</v>
       </c>
       <c r="S17" s="1" t="s">
         <v>102</v>
       </c>
       <c r="T17" s="1">
-        <v>-0.82</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -3184,19 +3184,19 @@
         <v>10.92</v>
       </c>
       <c r="F18" s="3">
-        <v>-0.7303934814384792</v>
+        <v>-0.7199716686393888</v>
       </c>
       <c r="G18" s="3">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="H18" s="3">
-        <v>22.55</v>
+        <v>21.47</v>
       </c>
       <c r="I18" s="3">
-        <v>-55.15</v>
+        <v>-56.54</v>
       </c>
       <c r="J18" s="3">
-        <v>-0.0826058430970883</v>
+        <v>-0.0854598461453549</v>
       </c>
       <c r="K18" s="3" t="b">
         <v>1</v>
@@ -3205,10 +3205,10 @@
         <v>31</v>
       </c>
       <c r="M18" s="3">
-        <v>-0.7236957191442619</v>
+        <v>-0.7142021661636586</v>
       </c>
       <c r="N18" s="3">
-        <v>-64.59680962020899</v>
+        <v>-65.90713778888112</v>
       </c>
       <c r="O18" s="3">
         <v>1.1764705882352942</v>
@@ -3217,7 +3217,7 @@
         <v>68.77035731645671</v>
       </c>
       <c r="Q18" s="3">
-        <v>39.647058823529406</v>
+        <v>39.764705882352935</v>
       </c>
       <c r="R18" s="3">
         <v>23.11764705882353</v>
@@ -3246,19 +3246,19 @@
         <v>3.12</v>
       </c>
       <c r="F19" s="2">
-        <v>0.03610964820245662</v>
+        <v>0.04092667623138403</v>
       </c>
       <c r="G19" s="2">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H19" s="2">
-        <v>59.42</v>
+        <v>61.5</v>
       </c>
       <c r="I19" s="2">
-        <v>16.15</v>
+        <v>16.92</v>
       </c>
       <c r="J19" s="2">
-        <v>0.011362774841695403</v>
+        <v>0.011604867955526245</v>
       </c>
       <c r="K19" s="2" t="b">
         <v>1</v>
@@ -3267,28 +3267,28 @@
         <v>-60</v>
       </c>
       <c r="M19" s="2">
-        <v>-0.02417021244549833</v>
+        <v>0.0005401589012727914</v>
       </c>
       <c r="N19" s="2">
-        <v>5.355741049667383</v>
+        <v>5.567094717612036</v>
       </c>
       <c r="O19" s="2">
-        <v>58.82352941176471</v>
+        <v>62.35294117647059</v>
       </c>
       <c r="P19" s="2">
         <v>11.392700631623551</v>
       </c>
       <c r="Q19" s="2">
-        <v>65.52941176470588</v>
+        <v>65.6470588235294</v>
       </c>
       <c r="R19" s="2">
-        <v>53.64705882352941</v>
+        <v>54.35294117647059</v>
       </c>
       <c r="S19" s="2" t="s">
         <v>110</v>
       </c>
       <c r="T19" s="2">
-        <v>5.23</v>
+        <v>5.94</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -3308,19 +3308,19 @@
         <v>-5.75</v>
       </c>
       <c r="F20" s="2">
-        <v>0.184248357749065</v>
+        <v>0.2207670199873413</v>
       </c>
       <c r="G20" s="2">
         <v>1.07</v>
       </c>
       <c r="H20" s="2">
-        <v>56.72</v>
+        <v>53.46</v>
       </c>
       <c r="I20" s="2">
-        <v>24.43</v>
+        <v>23.21</v>
       </c>
       <c r="J20" s="2">
-        <v>0.023697002340234787</v>
+        <v>0.023139935792158547</v>
       </c>
       <c r="K20" s="2" t="b">
         <v>0</v>
@@ -3329,28 +3329,28 @@
         <v>8</v>
       </c>
       <c r="M20" s="2">
-        <v>0.18893679135501706</v>
+        <v>0.22387367516658063</v>
       </c>
       <c r="N20" s="2">
-        <v>26.66644142971892</v>
+        <v>27.900446344142804</v>
       </c>
       <c r="O20" s="2">
-        <v>82.35294117647058</v>
+        <v>84.70588235294117</v>
       </c>
       <c r="P20" s="2">
         <v>15.052477440996265</v>
       </c>
       <c r="Q20" s="2">
-        <v>64.11764705882354</v>
+        <v>63.05882352941176</v>
       </c>
       <c r="R20" s="2">
-        <v>57.117647058823536</v>
+        <v>57.82352941176471</v>
       </c>
       <c r="S20" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T20" s="2">
-        <v>21.26</v>
+        <v>21.97</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -3364,25 +3364,25 @@
         <v>38.82352941176471</v>
       </c>
       <c r="D21" s="3">
-        <v>9.584158415841584</v>
+        <v>8.722772277227723</v>
       </c>
       <c r="E21" s="3">
         <v>-3.44</v>
       </c>
       <c r="F21" s="3">
-        <v>-0.43896513365536965</v>
+        <v>-0.44410545367594273</v>
       </c>
       <c r="G21" s="3">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="H21" s="3">
-        <v>31.04</v>
+        <v>28.22</v>
       </c>
       <c r="I21" s="3">
-        <v>-22.37</v>
+        <v>-25.02</v>
       </c>
       <c r="J21" s="3">
-        <v>-0.026107129338858687</v>
+        <v>-0.026550007738637776</v>
       </c>
       <c r="K21" s="3" t="b">
         <v>0</v>
@@ -3391,28 +3391,28 @@
         <v>55</v>
       </c>
       <c r="M21" s="3">
-        <v>-0.3967692312018012</v>
+        <v>-0.4157017491800403</v>
       </c>
       <c r="N21" s="3">
-        <v>-31.9041608259629</v>
+        <v>-36.05709609051928</v>
       </c>
       <c r="O21" s="3">
-        <v>2.3529411764705883</v>
+        <v>3.5294117647058822</v>
       </c>
       <c r="P21" s="3">
-        <v>55.20530802479801</v>
+        <v>57.26531305832072</v>
       </c>
       <c r="Q21" s="3">
-        <v>35.1764705882353</v>
+        <v>34.94117647058823</v>
       </c>
       <c r="R21" s="3">
-        <v>18.764705882352942</v>
+        <v>18.588235294117645</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>111</v>
       </c>
       <c r="T21" s="3">
-        <v>-32.45</v>
+        <v>-32.63</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -3426,25 +3426,25 @@
         <v>71.76470588235294</v>
       </c>
       <c r="D22" s="1">
-        <v>0.7558962264150944</v>
+        <v>0.7464622641509434</v>
       </c>
       <c r="E22" s="1">
         <v>-0.25</v>
       </c>
       <c r="F22" s="1">
-        <v>-0.21675636535697101</v>
+        <v>-0.22042609574798047</v>
       </c>
       <c r="G22" s="1">
         <v>1.38</v>
       </c>
       <c r="H22" s="1">
-        <v>47.26</v>
+        <v>39.89</v>
       </c>
       <c r="I22" s="1">
-        <v>1.09</v>
+        <v>-1.98</v>
       </c>
       <c r="J22" s="1">
-        <v>-0.009629701095594167</v>
+        <v>-0.009095137148808514</v>
       </c>
       <c r="K22" s="1" t="b">
         <v>0</v>
@@ -3453,28 +3453,28 @@
         <v>244</v>
       </c>
       <c r="M22" s="1">
-        <v>-0.19130486863894558</v>
+        <v>-0.20356139620353841</v>
       </c>
       <c r="N22" s="1">
-        <v>-11.357724569677337</v>
+        <v>-14.843060792869089</v>
       </c>
       <c r="O22" s="1">
-        <v>22.35294117647059</v>
+        <v>20</v>
       </c>
       <c r="P22" s="1">
         <v>19.455960650079966</v>
       </c>
       <c r="Q22" s="1">
-        <v>46.23529411764705</v>
+        <v>43.76470588235294</v>
       </c>
       <c r="R22" s="1">
-        <v>33.17647058823529</v>
+        <v>32.41176470588235</v>
       </c>
       <c r="S22" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T22" s="1">
-        <v>-19.93</v>
+        <v>-20.7</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -3488,25 +3488,25 @@
         <v>96.47058823529412</v>
       </c>
       <c r="D23" s="2">
-        <v>-0.6681732580037666</v>
+        <v>-0.6576271186440679</v>
       </c>
       <c r="E23" s="2">
         <v>0.1</v>
       </c>
       <c r="F23" s="2">
-        <v>0.2742406485153579</v>
+        <v>0.20798030286428826</v>
       </c>
       <c r="G23" s="2">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="H23" s="2">
-        <v>63.56</v>
+        <v>61.35</v>
       </c>
       <c r="I23" s="2">
-        <v>15.8</v>
+        <v>14.51</v>
       </c>
       <c r="J23" s="2">
-        <v>0.013776241769028136</v>
+        <v>0.013663813334479693</v>
       </c>
       <c r="K23" s="2" t="b">
         <v>1</v>
@@ -3515,28 +3515,28 @@
         <v>44</v>
       </c>
       <c r="M23" s="2">
-        <v>0.2883059493332141</v>
+        <v>0.21685646051925778</v>
       </c>
       <c r="N23" s="2">
-        <v>36.603357227538616</v>
+        <v>27.19872487941054</v>
       </c>
       <c r="O23" s="2">
-        <v>87.05882352941177</v>
+        <v>83.52941176470588</v>
       </c>
       <c r="P23" s="2">
         <v>20.883293768118005</v>
       </c>
       <c r="Q23" s="2">
-        <v>64.70588235294117</v>
+        <v>63.529411764705884</v>
       </c>
       <c r="R23" s="2">
-        <v>57.29411764705883</v>
+        <v>56.11764705882352</v>
       </c>
       <c r="S23" s="2" t="s">
         <v>110</v>
       </c>
       <c r="T23" s="2">
-        <v>21.5</v>
+        <v>20.32</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -3550,25 +3550,25 @@
         <v>1.1764705882352942</v>
       </c>
       <c r="D24" s="1">
-        <v>2.6549737681308505</v>
+        <v>2.6322394815348216</v>
       </c>
       <c r="E24" s="1">
         <v>1.53</v>
       </c>
       <c r="F24" s="1">
-        <v>0.6757837538162064</v>
+        <v>0.5263220108935313</v>
       </c>
       <c r="G24" s="1">
-        <v>3.59</v>
+        <v>3.57</v>
       </c>
       <c r="H24" s="1">
-        <v>60.5</v>
+        <v>63.13</v>
       </c>
       <c r="I24" s="1">
-        <v>13.44</v>
+        <v>16.52</v>
       </c>
       <c r="J24" s="1">
-        <v>0.06180199100874978</v>
+        <v>0.05892829790776801</v>
       </c>
       <c r="K24" s="1" t="b">
         <v>0</v>
@@ -3577,10 +3577,10 @@
         <v>-69</v>
       </c>
       <c r="M24" s="1">
-        <v>0.8492557972364323</v>
+        <v>0.6403806367598894</v>
       </c>
       <c r="N24" s="1">
-        <v>92.69834201786044</v>
+        <v>69.55114250347368</v>
       </c>
       <c r="O24" s="1">
         <v>100</v>
@@ -3589,7 +3589,7 @@
         <v>57.99224429263358</v>
       </c>
       <c r="Q24" s="1">
-        <v>52.352941176470594</v>
+        <v>52.94117647058824</v>
       </c>
       <c r="R24" s="1">
         <v>43.64705882352941</v>
@@ -3618,19 +3618,19 @@
         <v>15.51</v>
       </c>
       <c r="F25" s="3">
-        <v>-0.33515384773990087</v>
+        <v>-0.344977334590094</v>
       </c>
       <c r="G25" s="3">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="H25" s="3">
-        <v>42.67</v>
+        <v>40.74</v>
       </c>
       <c r="I25" s="3">
-        <v>-32.09</v>
+        <v>-34.13</v>
       </c>
       <c r="J25" s="3">
-        <v>0.0027876121455046453</v>
+        <v>0.0037631449726765603</v>
       </c>
       <c r="K25" s="3" t="b">
         <v>0</v>
@@ -3639,28 +3639,28 @@
         <v>34</v>
       </c>
       <c r="M25" s="3">
-        <v>-0.24406428053854667</v>
+        <v>-0.2841756546535529</v>
       </c>
       <c r="N25" s="3">
-        <v>-16.633665759637445</v>
+        <v>-22.904486637870537</v>
       </c>
       <c r="O25" s="3">
-        <v>15.294117647058824</v>
+        <v>11.76470588235294</v>
       </c>
       <c r="P25" s="3">
         <v>45.59139601172712</v>
       </c>
       <c r="Q25" s="3">
-        <v>18.35294117647059</v>
+        <v>18.941176470588236</v>
       </c>
       <c r="R25" s="3">
-        <v>5.117647058823531</v>
+        <v>4.411764705882353</v>
       </c>
       <c r="S25" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T25" s="3">
-        <v>3.72</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -3674,25 +3674,25 @@
         <v>7.0588235294117645</v>
       </c>
       <c r="D26" s="3">
-        <v>-0.6021978021978023</v>
+        <v>-0.41318681318681316</v>
       </c>
       <c r="E26" s="3">
         <v>-0.83</v>
       </c>
       <c r="F26" s="3">
-        <v>-0.31413649611675387</v>
+        <v>-0.3324752216676616</v>
       </c>
       <c r="G26" s="3">
+        <v>3.36</v>
+      </c>
+      <c r="H26" s="3">
+        <v>61.25</v>
+      </c>
+      <c r="I26" s="3">
         <v>3.37</v>
       </c>
-      <c r="H26" s="3">
-        <v>58.32</v>
-      </c>
-      <c r="I26" s="3">
-        <v>0.83</v>
-      </c>
       <c r="J26" s="3">
-        <v>0.010501055033496057</v>
+        <v>0.016711645651632814</v>
       </c>
       <c r="K26" s="3" t="b">
         <v>1</v>
@@ -3701,28 +3701,28 @@
         <v>160</v>
       </c>
       <c r="M26" s="3">
-        <v>-0.15539952974380578</v>
+        <v>-0.22773656133902143</v>
       </c>
       <c r="N26" s="3">
-        <v>-7.767190680163366</v>
+        <v>-17.260577306417392</v>
       </c>
       <c r="O26" s="3">
-        <v>29.411764705882355</v>
+        <v>16.470588235294116</v>
       </c>
       <c r="P26" s="3">
         <v>55.61259899184437</v>
       </c>
       <c r="Q26" s="3">
-        <v>32.23529411764706</v>
+        <v>36.94117647058824</v>
       </c>
       <c r="R26" s="3">
-        <v>11.823529411764703</v>
+        <v>9.88235294117647</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T26" s="3">
-        <v>-17.02</v>
+        <v>-18.96</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -3742,19 +3742,19 @@
         <v>6.8</v>
       </c>
       <c r="F27" s="3">
-        <v>-0.47249888581735155</v>
+        <v>-0.42080752572294094</v>
       </c>
       <c r="G27" s="3">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="H27" s="3">
-        <v>37.59</v>
+        <v>36.73</v>
       </c>
       <c r="I27" s="3">
-        <v>-36.34</v>
+        <v>-36.78</v>
       </c>
       <c r="J27" s="3">
-        <v>-0.017748881536410743</v>
+        <v>-0.017289796069473878</v>
       </c>
       <c r="K27" s="3" t="b">
         <v>0</v>
@@ -3763,10 +3763,10 @@
         <v>7</v>
       </c>
       <c r="M27" s="3">
-        <v>-0.36198580796276747</v>
+        <v>-0.34713541718669405</v>
       </c>
       <c r="N27" s="3">
-        <v>-28.425818502059524</v>
+        <v>-29.20046289118466</v>
       </c>
       <c r="O27" s="3">
         <v>5.88235294117647</v>
@@ -3775,7 +3775,7 @@
         <v>50.56910707785277</v>
       </c>
       <c r="Q27" s="3">
-        <v>12.941176470588236</v>
+        <v>13.294117647058824</v>
       </c>
       <c r="R27" s="3">
         <v>1.2352941176470562</v>
@@ -3804,19 +3804,19 @@
         <v>2.08</v>
       </c>
       <c r="F28" s="1">
-        <v>-0.07714627762008325</v>
+        <v>-0.04432025866489178</v>
       </c>
       <c r="G28" s="1">
         <v>3.26</v>
       </c>
       <c r="H28" s="1">
-        <v>48.22</v>
+        <v>41.81</v>
       </c>
       <c r="I28" s="1">
-        <v>-11.49</v>
+        <v>-16.37</v>
       </c>
       <c r="J28" s="1">
-        <v>0.01726895947340087</v>
+        <v>0.01744270357842766</v>
       </c>
       <c r="K28" s="1" t="b">
         <v>0</v>
@@ -3825,10 +3825,10 @@
         <v>3</v>
       </c>
       <c r="M28" s="1">
-        <v>0.07422315022922588</v>
+        <v>0.05598032283626364</v>
       </c>
       <c r="N28" s="1">
-        <v>15.195077317139798</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="O28" s="1">
         <v>68.23529411764706</v>
@@ -3837,16 +3837,16 @@
         <v>35.08771990976345</v>
       </c>
       <c r="Q28" s="1">
-        <v>48.705882352941174</v>
+        <v>46.11764705882353</v>
       </c>
       <c r="R28" s="1">
-        <v>42.117647058823536</v>
+        <v>41.88235294117648</v>
       </c>
       <c r="S28" s="1" t="s">
         <v>112</v>
       </c>
       <c r="T28" s="1">
-        <v>25.11</v>
+        <v>24.87</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -3866,19 +3866,19 @@
         <v>-4.82</v>
       </c>
       <c r="F29" s="1">
-        <v>-0.23884498109153313</v>
+        <v>-0.23840133577486028</v>
       </c>
       <c r="G29" s="1">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="H29" s="1">
-        <v>39.45</v>
+        <v>36.93</v>
       </c>
       <c r="I29" s="1">
-        <v>-14.9</v>
+        <v>-16.53</v>
       </c>
       <c r="J29" s="1">
-        <v>-0.007439688989360435</v>
+        <v>-0.006934547302196772</v>
       </c>
       <c r="K29" s="1" t="b">
         <v>1</v>
@@ -3887,13 +3887,13 @@
         <v>11</v>
       </c>
       <c r="M29" s="1">
-        <v>-0.15043451880786585</v>
+        <v>-0.17937488736931306</v>
       </c>
       <c r="N29" s="1">
-        <v>-7.270689586569364</v>
+        <v>-12.424409909446556</v>
       </c>
       <c r="O29" s="1">
-        <v>30.58823529411765</v>
+        <v>25.882352941176475</v>
       </c>
       <c r="P29" s="1">
         <v>18.79659508828292</v>
@@ -3902,13 +3902,13 @@
         <v>46.23529411764706</v>
       </c>
       <c r="R29" s="1">
-        <v>39.705882352941174</v>
+        <v>38.41176470588235</v>
       </c>
       <c r="S29" s="1" t="s">
         <v>110</v>
       </c>
       <c r="T29" s="1">
-        <v>-0.54</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -3922,25 +3922,25 @@
         <v>47.05882352941176</v>
       </c>
       <c r="D30" s="1">
-        <v>224.99545454545452</v>
+        <v>223.06363636363636</v>
       </c>
       <c r="E30" s="1">
         <v>1.26</v>
       </c>
       <c r="F30" s="1">
-        <v>-0.1827573804649707</v>
+        <v>-0.20780353353649011</v>
       </c>
       <c r="G30" s="1">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="H30" s="1">
-        <v>35.14</v>
+        <v>27.62</v>
       </c>
       <c r="I30" s="1">
-        <v>-11.62</v>
+        <v>-16.49</v>
       </c>
       <c r="J30" s="1">
-        <v>-0.00866513021471953</v>
+        <v>-0.009470704473733419</v>
       </c>
       <c r="K30" s="1" t="b">
         <v>1</v>
@@ -3949,28 +3949,28 @@
         <v>135</v>
       </c>
       <c r="M30" s="1">
-        <v>-0.16601297472942766</v>
+        <v>-0.19626452858502974</v>
       </c>
       <c r="N30" s="1">
-        <v>-8.828535178725547</v>
+        <v>-14.11337403101822</v>
       </c>
       <c r="O30" s="1">
-        <v>25.882352941176475</v>
+        <v>21.176470588235293</v>
       </c>
       <c r="P30" s="1">
-        <v>18.204489584640044</v>
+        <v>23.36242946298323</v>
       </c>
       <c r="Q30" s="1">
-        <v>49.882352941176464</v>
+        <v>48.11764705882352</v>
       </c>
       <c r="R30" s="1">
-        <v>42.1764705882353</v>
+        <v>38.76470588235294</v>
       </c>
       <c r="S30" s="1" t="s">
         <v>111</v>
       </c>
       <c r="T30" s="1">
-        <v>-6.3</v>
+        <v>-9.71</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -3990,19 +3990,19 @@
         <v>0.38</v>
       </c>
       <c r="F31" s="1">
-        <v>-0.14265730522796</v>
+        <v>-0.13742083443303227</v>
       </c>
       <c r="G31" s="1">
         <v>1.47</v>
       </c>
       <c r="H31" s="1">
-        <v>41.14</v>
+        <v>42.88</v>
       </c>
       <c r="I31" s="1">
-        <v>-5.45</v>
+        <v>-4.61</v>
       </c>
       <c r="J31" s="1">
-        <v>-0.008242151808458241</v>
+        <v>-0.007411432554442802</v>
       </c>
       <c r="K31" s="1" t="b">
         <v>0</v>
@@ -4011,90 +4011,90 @@
         <v>208</v>
       </c>
       <c r="M31" s="1">
-        <v>-0.11117782244513907</v>
+        <v>-0.11656186394385393</v>
       </c>
       <c r="N31" s="1">
-        <v>-3.345019950296694</v>
+        <v>-6.143107566900642</v>
       </c>
       <c r="O31" s="1">
-        <v>37.64705882352941</v>
+        <v>41.17647058823529</v>
       </c>
       <c r="P31" s="1">
         <v>29.54918623383928</v>
       </c>
       <c r="Q31" s="1">
-        <v>50.47058823529411</v>
+        <v>51.99999999999999</v>
       </c>
       <c r="R31" s="1">
-        <v>40.64705882352941</v>
+        <v>41.705882352941174</v>
       </c>
       <c r="S31" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T31" s="1">
-        <v>-7.4</v>
+        <v>-6.34</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32" s="3">
         <v>-2.58</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C32" s="3">
         <v>12.941176470588237</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D32" s="3">
         <v>8.848837209302324</v>
       </c>
-      <c r="E32" s="1">
+      <c r="E32" s="3">
         <v>3.6</v>
       </c>
-      <c r="F32" s="1">
-        <v>-0.12949046357710658</v>
-      </c>
-      <c r="G32" s="1">
+      <c r="F32" s="3">
+        <v>-0.20281341884137505</v>
+      </c>
+      <c r="G32" s="3">
         <v>1.62</v>
       </c>
-      <c r="H32" s="1">
-        <v>46.15</v>
-      </c>
-      <c r="I32" s="1">
-        <v>-5.27</v>
-      </c>
-      <c r="J32" s="1">
-        <v>-0.013463269745334855</v>
-      </c>
-      <c r="K32" s="1" t="b">
+      <c r="H32" s="3">
+        <v>40.74</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-8.5</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-0.014173547534774721</v>
+      </c>
+      <c r="K32" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L32" s="1">
+      <c r="L32" s="3">
         <v>21</v>
       </c>
-      <c r="M32" s="1">
-        <v>-0.08796433735295983</v>
-      </c>
-      <c r="N32" s="1">
-        <v>-1.0236714410787613</v>
-      </c>
-      <c r="O32" s="1">
-        <v>45.88235294117647</v>
-      </c>
-      <c r="P32" s="1">
+      <c r="M32" s="3">
+        <v>-0.1752973301109696</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-12.01665418361221</v>
+      </c>
+      <c r="O32" s="3">
+        <v>28.235294117647058</v>
+      </c>
+      <c r="P32" s="3">
         <v>26.613703173358488</v>
       </c>
-      <c r="Q32" s="1">
-        <v>35.17647058823529</v>
-      </c>
-      <c r="R32" s="1">
-        <v>30.11764705882353</v>
-      </c>
-      <c r="S32" s="1" t="s">
+      <c r="Q32" s="3">
+        <v>33.64705882352941</v>
+      </c>
+      <c r="R32" s="3">
+        <v>25</v>
+      </c>
+      <c r="S32" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="T32" s="1">
-        <v>-1.77</v>
+      <c r="T32" s="3">
+        <v>-6.89</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -4114,19 +4114,19 @@
         <v>0.23</v>
       </c>
       <c r="F33" s="2">
-        <v>0.29951965383047985</v>
+        <v>0.32204111499466265</v>
       </c>
       <c r="G33" s="2">
         <v>1.1</v>
       </c>
       <c r="H33" s="2">
-        <v>61.24</v>
+        <v>57.63</v>
       </c>
       <c r="I33" s="2">
-        <v>18.78</v>
+        <v>17.47</v>
       </c>
       <c r="J33" s="2">
-        <v>0.02395408619617998</v>
+        <v>0.02378702901288323</v>
       </c>
       <c r="K33" s="2" t="b">
         <v>0</v>
@@ -4135,28 +4135,28 @@
         <v>80</v>
       </c>
       <c r="M33" s="2">
-        <v>0.3062174161246971</v>
+        <v>0.3264791938221474</v>
       </c>
       <c r="N33" s="2">
-        <v>38.39450390668692</v>
+        <v>38.16099820969948</v>
       </c>
       <c r="O33" s="2">
-        <v>88.23529411764706</v>
+        <v>89.41176470588236</v>
       </c>
       <c r="P33" s="2">
         <v>23.38443607454554</v>
       </c>
       <c r="Q33" s="2">
-        <v>70.47058823529412</v>
+        <v>69.1764705882353</v>
       </c>
       <c r="R33" s="2">
-        <v>60.52941176470589</v>
+        <v>60.882352941176485</v>
       </c>
       <c r="S33" s="2" t="s">
         <v>110</v>
       </c>
       <c r="T33" s="2">
-        <v>24.74</v>
+        <v>25.09</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -4170,25 +4170,25 @@
         <v>92.94117647058823</v>
       </c>
       <c r="D34" s="1">
-        <v>-2.3345052737317933</v>
+        <v>-2.3294826720241084</v>
       </c>
       <c r="E34" s="1">
         <v>2.36</v>
       </c>
       <c r="F34" s="1">
-        <v>-0.07243847195118878</v>
+        <v>-0.09527217070667938</v>
       </c>
       <c r="G34" s="1">
         <v>1.21</v>
       </c>
       <c r="H34" s="1">
-        <v>46.99</v>
+        <v>47.99</v>
       </c>
       <c r="I34" s="1">
-        <v>0.57</v>
+        <v>0.97</v>
       </c>
       <c r="J34" s="1">
-        <v>-0.003723626856012923</v>
+        <v>-0.003828868714196778</v>
       </c>
       <c r="K34" s="1" t="b">
         <v>0</v>
@@ -4197,28 +4197,28 @@
         <v>209</v>
       </c>
       <c r="M34" s="1">
-        <v>-0.058373171133332624</v>
+        <v>-0.0859522051689614</v>
       </c>
       <c r="N34" s="1">
-        <v>1.9354451808839614</v>
+        <v>-3.082141689411388</v>
       </c>
       <c r="O34" s="1">
-        <v>51.76470588235295</v>
+        <v>49.411764705882355</v>
       </c>
       <c r="P34" s="1">
         <v>21.09433056126816</v>
       </c>
       <c r="Q34" s="1">
-        <v>46</v>
+        <v>46.8235294117647</v>
       </c>
       <c r="R34" s="1">
-        <v>40.058823529411775</v>
+        <v>39.352941176470594</v>
       </c>
       <c r="S34" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T34" s="1">
-        <v>-6.77</v>
+        <v>-7.48</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -4238,19 +4238,19 @@
         <v>-0.5</v>
       </c>
       <c r="F35" s="1">
-        <v>-0.09396511344847842</v>
+        <v>-0.058965137241281246</v>
       </c>
       <c r="G35" s="1">
-        <v>0.94</v>
+        <v>0.95</v>
       </c>
       <c r="H35" s="1">
-        <v>32.63</v>
+        <v>32.26</v>
       </c>
       <c r="I35" s="1">
-        <v>-17.8</v>
+        <v>-17.76</v>
       </c>
       <c r="J35" s="1">
-        <v>-0.005070446573245401</v>
+        <v>-0.0066453260547554615</v>
       </c>
       <c r="K35" s="1" t="b">
         <v>0</v>
@@ -4259,28 +4259,28 @@
         <v>-57</v>
       </c>
       <c r="M35" s="1">
-        <v>-0.09798377082500875</v>
+        <v>-0.061184176655023625</v>
       </c>
       <c r="N35" s="1">
-        <v>-2.025614788283657</v>
+        <v>-0.605338838017608</v>
       </c>
       <c r="O35" s="1">
-        <v>42.35294117647059</v>
+        <v>51.76470588235295</v>
       </c>
       <c r="P35" s="1">
         <v>20.53422985929523</v>
       </c>
       <c r="Q35" s="1">
-        <v>41.294117647058826</v>
+        <v>40.117647058823536</v>
       </c>
       <c r="R35" s="1">
-        <v>39</v>
+        <v>41.05882352941177</v>
       </c>
       <c r="S35" s="1" t="s">
         <v>101</v>
       </c>
       <c r="T35" s="1">
-        <v>16.5</v>
+        <v>18.56</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -4300,19 +4300,19 @@
         <v>-1.31</v>
       </c>
       <c r="F36" s="1">
-        <v>-0.0886056317002658</v>
+        <v>-0.0561761137477762</v>
       </c>
       <c r="G36" s="1">
         <v>1.12</v>
       </c>
       <c r="H36" s="1">
-        <v>42.74</v>
+        <v>41.55</v>
       </c>
       <c r="I36" s="1">
-        <v>-9.69</v>
+        <v>-10.12</v>
       </c>
       <c r="J36" s="1">
-        <v>0.002882098033871043</v>
+        <v>0.0026815672448318385</v>
       </c>
       <c r="K36" s="1" t="b">
         <v>0</v>
@@ -4321,90 +4321,90 @@
         <v>-18</v>
       </c>
       <c r="M36" s="1">
-        <v>-0.08056831694720512</v>
+        <v>-0.05085041915479449</v>
       </c>
       <c r="N36" s="1">
-        <v>-0.2840694005032938</v>
+        <v>0.4280369120052986</v>
       </c>
       <c r="O36" s="1">
-        <v>47.05882352941176</v>
+        <v>52.94117647058824</v>
       </c>
       <c r="P36" s="1">
         <v>26.730280409441182</v>
       </c>
       <c r="Q36" s="1">
-        <v>47.64705882352942</v>
+        <v>47.41176470588236</v>
       </c>
       <c r="R36" s="1">
-        <v>39.94117647058823</v>
+        <v>41.70588235294119</v>
       </c>
       <c r="S36" s="1" t="s">
         <v>108</v>
       </c>
       <c r="T36" s="1">
-        <v>12.99</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B37" s="1">
         <v>5.29</v>
       </c>
-      <c r="C37" s="2">
+      <c r="C37" s="1">
         <v>60</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37" s="1">
         <v>0.42155009451795833</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E37" s="1">
         <v>-3.28</v>
       </c>
-      <c r="F37" s="2">
-        <v>0.14623708421868045</v>
-      </c>
-      <c r="G37" s="2">
+      <c r="F37" s="1">
+        <v>0.15551599057812637</v>
+      </c>
+      <c r="G37" s="1">
         <v>1.28</v>
       </c>
-      <c r="H37" s="2">
-        <v>50.84</v>
-      </c>
-      <c r="I37" s="2">
-        <v>8.62</v>
-      </c>
-      <c r="J37" s="2">
-        <v>0.004268824971623391</v>
-      </c>
-      <c r="K37" s="2" t="b">
+      <c r="H37" s="1">
+        <v>48.2</v>
+      </c>
+      <c r="I37" s="1">
+        <v>7.39</v>
+      </c>
+      <c r="J37" s="1">
+        <v>0.0012315706264228127</v>
+      </c>
+      <c r="K37" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L37" s="2">
+      <c r="L37" s="1">
         <v>-108</v>
       </c>
-      <c r="M37" s="2">
-        <v>0.16499081864248866</v>
-      </c>
-      <c r="N37" s="2">
-        <v>24.271844158466088</v>
-      </c>
-      <c r="O37" s="2">
-        <v>81.17647058823529</v>
-      </c>
-      <c r="P37" s="2">
-        <v>19.310067662476122</v>
-      </c>
-      <c r="Q37" s="2">
-        <v>51.294117647058826</v>
-      </c>
-      <c r="R37" s="2">
-        <v>50.823529411764696</v>
-      </c>
-      <c r="S37" s="2" t="s">
+      <c r="M37" s="1">
+        <v>0.1679426112950837</v>
+      </c>
+      <c r="N37" s="1">
+        <v>22.307339956993115</v>
+      </c>
+      <c r="O37" s="1">
+        <v>80</v>
+      </c>
+      <c r="P37" s="1">
+        <v>19.230003461162156</v>
+      </c>
+      <c r="Q37" s="1">
+        <v>50.00000000000001</v>
+      </c>
+      <c r="R37" s="1">
+        <v>49.99999999999999</v>
+      </c>
+      <c r="S37" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="T37" s="2">
-        <v>21.01</v>
+      <c r="T37" s="1">
+        <v>20.18</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -4424,19 +4424,19 @@
         <v>3.02</v>
       </c>
       <c r="F38" s="2">
-        <v>0.34670995161913987</v>
+        <v>0.33185532202529944</v>
       </c>
       <c r="G38" s="2">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="H38" s="2">
-        <v>60.16</v>
+        <v>64.84</v>
       </c>
       <c r="I38" s="2">
-        <v>65.21</v>
+        <v>71.37</v>
       </c>
       <c r="J38" s="2">
-        <v>0.02678620788946634</v>
+        <v>0.02605031747846348</v>
       </c>
       <c r="K38" s="2" t="b">
         <v>0</v>
@@ -4445,10 +4445,10 @@
         <v>390</v>
       </c>
       <c r="M38" s="2">
-        <v>0.36077525243699604</v>
+        <v>0.34073147968026896</v>
       </c>
       <c r="N38" s="2">
-        <v>43.85028753791681</v>
+        <v>39.586226795511635</v>
       </c>
       <c r="O38" s="2">
         <v>90.58823529411765</v>
@@ -4457,16 +4457,16 @@
         <v>17.802507034008837</v>
       </c>
       <c r="Q38" s="2">
-        <v>75.41176470588235</v>
+        <v>76.47058823529412</v>
       </c>
       <c r="R38" s="2">
-        <v>66.11764705882354</v>
+        <v>66.23529411764706</v>
       </c>
       <c r="S38" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T38" s="2">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -4486,19 +4486,19 @@
         <v>-1.29</v>
       </c>
       <c r="F39" s="1">
-        <v>-0.15308305745539563</v>
+        <v>-0.1668324988491925</v>
       </c>
       <c r="G39" s="1">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="H39" s="1">
-        <v>34.4</v>
+        <v>32.69</v>
       </c>
       <c r="I39" s="1">
-        <v>-8.88</v>
+        <v>-9.84</v>
       </c>
       <c r="J39" s="1">
-        <v>-0.008141943524639835</v>
+        <v>-0.008914014739852531</v>
       </c>
       <c r="K39" s="1" t="b">
         <v>0</v>
@@ -4507,28 +4507,28 @@
         <v>-1</v>
       </c>
       <c r="M39" s="1">
-        <v>-0.14504574270233495</v>
+        <v>-0.16106299637346233</v>
       </c>
       <c r="N39" s="1">
-        <v>-6.731811976016282</v>
+        <v>-10.593220809861478</v>
       </c>
       <c r="O39" s="1">
-        <v>31.76470588235294</v>
+        <v>32.94117647058823</v>
       </c>
       <c r="P39" s="1">
         <v>30.28933322215756</v>
       </c>
       <c r="Q39" s="1">
-        <v>41.05882352941177</v>
+        <v>39.88235294117647</v>
       </c>
       <c r="R39" s="1">
-        <v>32.117647058823536</v>
+        <v>31.882352941176478</v>
       </c>
       <c r="S39" s="1" t="s">
         <v>112</v>
       </c>
       <c r="T39" s="1">
-        <v>6.32</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -4548,19 +4548,19 @@
         <v>4.41</v>
       </c>
       <c r="F40" s="1">
-        <v>0.5552639578608645</v>
+        <v>0.4782775167853881</v>
       </c>
       <c r="G40" s="1">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="H40" s="1">
-        <v>54.6</v>
+        <v>54.68</v>
       </c>
       <c r="I40" s="1">
-        <v>8.5</v>
+        <v>8.93</v>
       </c>
       <c r="J40" s="1">
-        <v>0.05542848641340796</v>
+        <v>0.05316555771573186</v>
       </c>
       <c r="K40" s="1" t="b">
         <v>0</v>
@@ -4569,28 +4569,28 @@
         <v>-21</v>
       </c>
       <c r="M40" s="1">
-        <v>0.5358404472076346</v>
+        <v>0.46407566453743687</v>
       </c>
       <c r="N40" s="1">
-        <v>61.356807014980674</v>
+        <v>51.92064528122845</v>
       </c>
       <c r="O40" s="1">
-        <v>96.47058823529412</v>
+        <v>94.11764705882352</v>
       </c>
       <c r="P40" s="1">
         <v>51.940889187924654</v>
       </c>
       <c r="Q40" s="1">
-        <v>55.1764705882353</v>
+        <v>55.411764705882355</v>
       </c>
       <c r="R40" s="1">
-        <v>48.1764705882353</v>
+        <v>47.47058823529412</v>
       </c>
       <c r="S40" s="1" t="s">
         <v>113</v>
       </c>
       <c r="T40" s="1">
-        <v>39.7</v>
+        <v>38.99</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -4610,19 +4610,19 @@
         <v>-0.03</v>
       </c>
       <c r="F41" s="3">
-        <v>-0.06362393633320472</v>
+        <v>-0.12513552416639212</v>
       </c>
       <c r="G41" s="3">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="H41" s="3">
-        <v>43.45</v>
+        <v>42.96</v>
       </c>
       <c r="I41" s="3">
-        <v>-12.09</v>
+        <v>-12.45</v>
       </c>
       <c r="J41" s="3">
-        <v>-0.020462325952884004</v>
+        <v>-0.020209810577188635</v>
       </c>
       <c r="K41" s="3" t="b">
         <v>1</v>
@@ -4631,28 +4631,28 @@
         <v>4</v>
       </c>
       <c r="M41" s="3">
-        <v>-0.04955863551534856</v>
+        <v>-0.11537175074592565</v>
       </c>
       <c r="N41" s="3">
-        <v>2.816898742682366</v>
+        <v>-6.02409624710781</v>
       </c>
       <c r="O41" s="3">
-        <v>54.11764705882353</v>
+        <v>42.35294117647059</v>
       </c>
       <c r="P41" s="3">
         <v>30.769232468942608</v>
       </c>
       <c r="Q41" s="3">
-        <v>21.88235294117647</v>
+        <v>22.941176470588232</v>
       </c>
       <c r="R41" s="3">
-        <v>22.88235294117647</v>
+        <v>19.352941176470587</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>107</v>
       </c>
       <c r="T41" s="3">
-        <v>-13.76</v>
+        <v>-17.29</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -4672,19 +4672,19 @@
         <v>4.78</v>
       </c>
       <c r="F42" s="3">
-        <v>-0.23275652570528926</v>
+        <v>-0.22122306773260972</v>
       </c>
       <c r="G42" s="3">
         <v>0.31</v>
       </c>
       <c r="H42" s="3">
-        <v>28.95</v>
+        <v>17.03</v>
       </c>
       <c r="I42" s="3">
-        <v>-12.56</v>
+        <v>-14.91</v>
       </c>
       <c r="J42" s="3">
-        <v>-0.016096717338958923</v>
+        <v>-0.016245164718787203</v>
       </c>
       <c r="K42" s="3" t="b">
         <v>1</v>
@@ -4693,28 +4693,28 @@
         <v>16</v>
       </c>
       <c r="M42" s="3">
-        <v>-0.2789710855353881</v>
+        <v>-0.2518458116422545</v>
       </c>
       <c r="N42" s="3">
-        <v>-20.124346259321587</v>
+        <v>-19.671502336740698</v>
       </c>
       <c r="O42" s="3">
-        <v>9.411764705882353</v>
+        <v>15.294117647058824</v>
       </c>
       <c r="P42" s="3">
-        <v>20.352744065122756</v>
+        <v>20.568455255211532</v>
       </c>
       <c r="Q42" s="3">
-        <v>33.529411764705884</v>
+        <v>33.411764705882355</v>
       </c>
       <c r="R42" s="3">
-        <v>24.23529411764706</v>
+        <v>26.000000000000004</v>
       </c>
       <c r="S42" s="3" t="s">
         <v>111</v>
       </c>
       <c r="T42" s="3">
-        <v>-11.25</v>
+        <v>-9.49</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -4734,19 +4734,19 @@
         <v>8.46</v>
       </c>
       <c r="F43" s="2">
-        <v>0.11784112195349697</v>
+        <v>0.11095593919919937</v>
       </c>
       <c r="G43" s="2">
         <v>1.35</v>
       </c>
       <c r="H43" s="2">
-        <v>45.26</v>
+        <v>45.29</v>
       </c>
       <c r="I43" s="2">
-        <v>12.53</v>
+        <v>12.55</v>
       </c>
       <c r="J43" s="2">
-        <v>0.004318386150027533</v>
+        <v>0.0034243542472177785</v>
       </c>
       <c r="K43" s="2" t="b">
         <v>0</v>
@@ -4755,28 +4755,28 @@
         <v>18</v>
       </c>
       <c r="M43" s="2">
-        <v>0.14128328998325723</v>
+        <v>0.126489215095396</v>
       </c>
       <c r="N43" s="2">
-        <v>21.90109129254294</v>
+        <v>18.16200033702436</v>
       </c>
       <c r="O43" s="2">
-        <v>78.82352941176471</v>
+        <v>75.29411764705883</v>
       </c>
       <c r="P43" s="2">
         <v>24.82490242340647</v>
       </c>
       <c r="Q43" s="2">
-        <v>58.470588235294116</v>
+        <v>58.11764705882352</v>
       </c>
       <c r="R43" s="2">
-        <v>54.76470588235294</v>
+        <v>53.47058823529413</v>
       </c>
       <c r="S43" s="2" t="s">
         <v>114</v>
       </c>
       <c r="T43" s="2">
-        <v>2.39</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -4790,25 +4790,25 @@
         <v>42.35294117647059</v>
       </c>
       <c r="D44" s="2">
-        <v>19.054054054054053</v>
+        <v>19.006756756756758</v>
       </c>
       <c r="E44" s="2">
         <v>-0.66</v>
       </c>
       <c r="F44" s="2">
-        <v>0.030367371746275573</v>
+        <v>0.13345135024355373</v>
       </c>
       <c r="G44" s="2">
         <v>2.63</v>
       </c>
       <c r="H44" s="2">
-        <v>52.35</v>
+        <v>53.49</v>
       </c>
       <c r="I44" s="2">
-        <v>8.72</v>
+        <v>9.97</v>
       </c>
       <c r="J44" s="2">
-        <v>0.013792171465670125</v>
+        <v>0.01450454940312598</v>
       </c>
       <c r="K44" s="2" t="b">
         <v>1</v>
@@ -4817,28 +4817,28 @@
         <v>-6</v>
       </c>
       <c r="M44" s="2">
-        <v>0.13954089714201623</v>
+        <v>0.2057920351315552</v>
       </c>
       <c r="N44" s="2">
-        <v>21.726852008418838</v>
+        <v>26.092282340640278</v>
       </c>
       <c r="O44" s="2">
-        <v>77.64705882352942</v>
+        <v>82.35294117647058</v>
       </c>
       <c r="P44" s="2">
-        <v>25.276100184761987</v>
+        <v>25.20580223963847</v>
       </c>
       <c r="Q44" s="2">
-        <v>63.17647058823529</v>
+        <v>63.76470588235294</v>
       </c>
       <c r="R44" s="2">
-        <v>55.58823529411765</v>
+        <v>56.88235294117647</v>
       </c>
       <c r="S44" s="2" t="s">
         <v>103</v>
       </c>
       <c r="T44" s="2">
-        <v>20.77</v>
+        <v>22.07</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
@@ -4858,19 +4858,19 @@
         <v>1.02</v>
       </c>
       <c r="F45" s="1">
-        <v>-0.03489494787106044</v>
+        <v>-0.0505189061485746</v>
       </c>
       <c r="G45" s="1">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="H45" s="1">
-        <v>43.22</v>
+        <v>41.68</v>
       </c>
       <c r="I45" s="1">
-        <v>3.06</v>
+        <v>2.27</v>
       </c>
       <c r="J45" s="1">
-        <v>0.0013101956598168911</v>
+        <v>0.00020070066334538784</v>
       </c>
       <c r="K45" s="1" t="b">
         <v>0</v>
@@ -4879,28 +4879,28 @@
         <v>195</v>
       </c>
       <c r="M45" s="1">
-        <v>-0.0047550175470829625</v>
+        <v>-0.030103743542144734</v>
       </c>
       <c r="N45" s="1">
-        <v>7.297260539508913</v>
+        <v>2.5027044732702732</v>
       </c>
       <c r="O45" s="1">
-        <v>61.1764705882353</v>
+        <v>58.82352941176471</v>
       </c>
       <c r="P45" s="1">
         <v>17.57882034058413</v>
       </c>
       <c r="Q45" s="1">
-        <v>43.17647058823529</v>
+        <v>42.470588235294116</v>
       </c>
       <c r="R45" s="1">
-        <v>42.23529411764706</v>
+        <v>41.411764705882355</v>
       </c>
       <c r="S45" s="1" t="s">
         <v>109</v>
       </c>
       <c r="T45" s="1">
-        <v>-2.09</v>
+        <v>-2.92</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
@@ -4920,19 +4920,19 @@
         <v>5.18</v>
       </c>
       <c r="F46" s="3">
-        <v>-0.3516270186498901</v>
+        <v>-0.3333067630590114</v>
       </c>
       <c r="G46" s="3">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="H46" s="3">
-        <v>33.18</v>
+        <v>33.28</v>
       </c>
       <c r="I46" s="3">
-        <v>-34.85</v>
+        <v>-35.29</v>
       </c>
       <c r="J46" s="3">
-        <v>-0.00822829217933939</v>
+        <v>-0.007012747777044744</v>
       </c>
       <c r="K46" s="3" t="b">
         <v>0</v>
@@ -4941,28 +4941,28 @@
         <v>17</v>
       </c>
       <c r="M46" s="3">
-        <v>-0.301393801443261</v>
+        <v>-0.2991335560873788</v>
       </c>
       <c r="N46" s="3">
-        <v>-22.36661785010888</v>
+        <v>-24.40027678125313</v>
       </c>
       <c r="O46" s="3">
-        <v>8.235294117647058</v>
+        <v>9.411764705882353</v>
       </c>
       <c r="P46" s="3">
         <v>54.33673655574689</v>
       </c>
       <c r="Q46" s="3">
-        <v>42.11764705882352</v>
+        <v>42.8235294117647</v>
       </c>
       <c r="R46" s="3">
-        <v>25.23529411764705</v>
+        <v>25.705882352941167</v>
       </c>
       <c r="S46" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T46" s="3">
-        <v>4.2</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
@@ -4982,19 +4982,19 @@
         <v>2.6</v>
       </c>
       <c r="F47" s="2">
-        <v>0.10633192141141011</v>
+        <v>0.10694175764340416</v>
       </c>
       <c r="G47" s="2">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="H47" s="2">
-        <v>52.83</v>
+        <v>48.01</v>
       </c>
       <c r="I47" s="2">
-        <v>5.09</v>
+        <v>2.93</v>
       </c>
       <c r="J47" s="2">
-        <v>0.020450294930138033</v>
+        <v>0.020678712732062017</v>
       </c>
       <c r="K47" s="2" t="b">
         <v>0</v>
@@ -5003,28 +5003,28 @@
         <v>-56</v>
       </c>
       <c r="M47" s="2">
-        <v>0.1337927468177007</v>
+        <v>0.12558168871884012</v>
       </c>
       <c r="N47" s="2">
-        <v>21.15203697598729</v>
+        <v>18.071247699368765</v>
       </c>
       <c r="O47" s="2">
-        <v>76.47058823529412</v>
+        <v>72.94117647058823</v>
       </c>
       <c r="P47" s="2">
         <v>14.027665623490911</v>
       </c>
       <c r="Q47" s="2">
-        <v>55.29411764705883</v>
+        <v>53.411764705882355</v>
       </c>
       <c r="R47" s="2">
-        <v>51.70588235294118</v>
+        <v>50.88235294117647</v>
       </c>
       <c r="S47" s="2" t="s">
         <v>109</v>
       </c>
       <c r="T47" s="2">
-        <v>25.85</v>
+        <v>25.03</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
@@ -5044,19 +5044,19 @@
         <v>0.66</v>
       </c>
       <c r="F48" s="2">
-        <v>0.1920124423709208</v>
+        <v>0.16699144288684903</v>
       </c>
       <c r="G48" s="2">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H48" s="2">
-        <v>55.76</v>
+        <v>58.52</v>
       </c>
       <c r="I48" s="2">
-        <v>28.73</v>
+        <v>30.06</v>
       </c>
       <c r="J48" s="2">
-        <v>0.014415857337782155</v>
+        <v>0.016287491376495985</v>
       </c>
       <c r="K48" s="2" t="b">
         <v>0</v>
@@ -5065,28 +5065,28 @@
         <v>242</v>
       </c>
       <c r="M48" s="2">
-        <v>0.23286879236564584</v>
+        <v>0.19361991585175753</v>
       </c>
       <c r="N48" s="2">
-        <v>31.059641530781796</v>
+        <v>24.8750704126605</v>
       </c>
       <c r="O48" s="2">
-        <v>83.52941176470588</v>
+        <v>81.17647058823529</v>
       </c>
       <c r="P48" s="2">
-        <v>21.001739961426274</v>
+        <v>20.965127717005057</v>
       </c>
       <c r="Q48" s="2">
-        <v>65.05882352941177</v>
+        <v>65.6470588235294</v>
       </c>
       <c r="R48" s="2">
-        <v>56.94117647058824</v>
+        <v>56.35294117647059</v>
       </c>
       <c r="S48" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T48" s="2">
-        <v>7.67</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
@@ -5106,19 +5106,19 @@
         <v>-11.3</v>
       </c>
       <c r="F49" s="2">
-        <v>0.14593917035811804</v>
+        <v>0.12231415592308581</v>
       </c>
       <c r="G49" s="2">
         <v>1.08</v>
       </c>
       <c r="H49" s="2">
-        <v>47.57</v>
+        <v>44.14</v>
       </c>
       <c r="I49" s="2">
-        <v>-5.13</v>
+        <v>-7.58</v>
       </c>
       <c r="J49" s="2">
-        <v>0.015404809841220791</v>
+        <v>0.014075296675261834</v>
       </c>
       <c r="K49" s="2" t="b">
         <v>0</v>
@@ -5127,28 +5127,28 @@
         <v>-7</v>
       </c>
       <c r="M49" s="2">
-        <v>0.15129738019349181</v>
+        <v>0.12586461898507362</v>
       </c>
       <c r="N49" s="2">
-        <v>22.902500313566396</v>
+        <v>18.099540725992114</v>
       </c>
       <c r="O49" s="2">
-        <v>80</v>
+        <v>74.11764705882354</v>
       </c>
       <c r="P49" s="2">
-        <v>31.00158698078384</v>
+        <v>29.65964183269925</v>
       </c>
       <c r="Q49" s="2">
-        <v>61.41176470588236</v>
+        <v>59.529411764705884</v>
       </c>
       <c r="R49" s="2">
-        <v>56.47058823529412</v>
+        <v>54.58823529411766</v>
       </c>
       <c r="S49" s="2" t="s">
         <v>102</v>
       </c>
       <c r="T49" s="2">
-        <v>25.37</v>
+        <v>23.49</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
@@ -5168,19 +5168,19 @@
         <v>12.72</v>
       </c>
       <c r="F50" s="3">
-        <v>-0.41435788541005153</v>
+        <v>-0.3136914901662976</v>
       </c>
       <c r="G50" s="3">
         <v>3.85</v>
       </c>
       <c r="H50" s="3">
-        <v>51.73</v>
+        <v>50.58</v>
       </c>
       <c r="I50" s="3">
-        <v>8.21</v>
+        <v>6.92</v>
       </c>
       <c r="J50" s="3">
-        <v>0.010602233044606965</v>
+        <v>0.008112720128050002</v>
       </c>
       <c r="K50" s="3" t="b">
         <v>0</v>
@@ -5189,22 +5189,22 @@
         <v>69</v>
       </c>
       <c r="M50" s="3">
-        <v>-0.22347166002486085</v>
+        <v>-0.1872062435829821</v>
       </c>
       <c r="N50" s="3">
-        <v>-14.574403708268866</v>
+        <v>-13.207545530813453</v>
       </c>
       <c r="O50" s="3">
-        <v>17.647058823529413</v>
+        <v>23.52941176470588</v>
       </c>
       <c r="P50" s="3">
         <v>41.201484669672254</v>
       </c>
       <c r="Q50" s="3">
-        <v>50.35294117647059</v>
+        <v>49.05882352941176</v>
       </c>
       <c r="R50" s="3">
-        <v>24.82352941176471</v>
+        <v>25.88235294117647</v>
       </c>
       <c r="S50" s="3" t="s">
         <v>108</v>
@@ -5228,19 +5228,19 @@
         <v>14.39</v>
       </c>
       <c r="F51" s="1">
-        <v>0.47192188192901596</v>
+        <v>0.34437049064350345</v>
       </c>
       <c r="G51" s="1">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="H51" s="1">
-        <v>56.6</v>
+        <v>54.7</v>
       </c>
       <c r="I51" s="1">
-        <v>36.35</v>
+        <v>33.53</v>
       </c>
       <c r="J51" s="1">
-        <v>0.05016814238874764</v>
+        <v>0.04871111869746869</v>
       </c>
       <c r="K51" s="1" t="b">
         <v>0</v>
@@ -5249,22 +5249,22 @@
         <v>14</v>
       </c>
       <c r="M51" s="1">
-        <v>0.5255039802827537</v>
+        <v>0.37765608184963906</v>
       </c>
       <c r="N51" s="1">
-        <v>60.323160322492576</v>
+        <v>43.27868701244865</v>
       </c>
       <c r="O51" s="1">
-        <v>94.11764705882352</v>
+        <v>92.94117647058823</v>
       </c>
       <c r="P51" s="1">
         <v>38.38748944617691</v>
       </c>
       <c r="Q51" s="1">
-        <v>53.88235294117648</v>
+        <v>53.529411764705884</v>
       </c>
       <c r="R51" s="1">
-        <v>45.352941176470594</v>
+        <v>45.00000000000001</v>
       </c>
       <c r="S51" s="1" t="s">
         <v>97</v>
@@ -5288,19 +5288,19 @@
         <v>-5.41</v>
       </c>
       <c r="F52" s="3">
-        <v>-0.20941547505042452</v>
+        <v>-0.17109450993355713</v>
       </c>
       <c r="G52" s="3">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="H52" s="3">
-        <v>41.43</v>
+        <v>40.45</v>
       </c>
       <c r="I52" s="3">
-        <v>-31.35</v>
+        <v>-31.67</v>
       </c>
       <c r="J52" s="3">
-        <v>-0.014358909672663164</v>
+        <v>-0.014019487305373885</v>
       </c>
       <c r="K52" s="3" t="b">
         <v>0</v>
@@ -5309,22 +5309,22 @@
         <v>-110</v>
       </c>
       <c r="M52" s="3">
-        <v>-0.21611323734464172</v>
+        <v>-0.17508878087829338</v>
       </c>
       <c r="N52" s="3">
-        <v>-13.838561440246956</v>
+        <v>-11.995799260344592</v>
       </c>
       <c r="O52" s="3">
-        <v>18.823529411764707</v>
+        <v>29.411764705882355</v>
       </c>
       <c r="P52" s="3">
         <v>28.153300405690313</v>
       </c>
       <c r="Q52" s="3">
-        <v>33.294117647058826</v>
+        <v>33.29411764705882</v>
       </c>
       <c r="R52" s="3">
-        <v>23.176470588235293</v>
+        <v>26.470588235294116</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>114</v>
@@ -5348,19 +5348,19 @@
         <v>-0.87</v>
       </c>
       <c r="F53" s="3">
-        <v>-0.04044394491042243</v>
+        <v>-0.12476425752084781</v>
       </c>
       <c r="G53" s="3">
         <v>0</v>
       </c>
       <c r="H53" s="3">
-        <v>52.42</v>
+        <v>50.61</v>
       </c>
       <c r="I53" s="3">
-        <v>3.54</v>
+        <v>2.34</v>
       </c>
       <c r="J53" s="3">
-        <v>0.009617582954560154</v>
+        <v>0.011824034616526598</v>
       </c>
       <c r="K53" s="3" t="b">
         <v>0</v>
@@ -5369,22 +5369,22 @@
         <v>1748</v>
       </c>
       <c r="M53" s="3">
-        <v>-0.1074215678525946</v>
+        <v>-0.16914504579569534</v>
       </c>
       <c r="N53" s="3">
-        <v>-2.9693944910422454</v>
+        <v>-11.401425752084782</v>
       </c>
       <c r="O53" s="3">
-        <v>38.82352941176471</v>
+        <v>31.76470588235294</v>
       </c>
       <c r="P53" s="3">
         <v>48.781873808753</v>
       </c>
       <c r="Q53" s="3">
-        <v>40.705882352941174</v>
+        <v>40.8235294117647</v>
       </c>
       <c r="R53" s="3">
-        <v>23.176470588235293</v>
+        <v>21.52941176470588</v>
       </c>
       <c r="S53" s="3" t="s">
         <v>96</v>
@@ -5402,25 +5402,25 @@
         <v>61.1764705882353</v>
       </c>
       <c r="D54" s="1">
-        <v>0.8348134991119006</v>
+        <v>0.7904085257548846</v>
       </c>
       <c r="E54" s="1">
         <v>-1.39</v>
       </c>
       <c r="F54" s="1">
-        <v>-0.04260958910736</v>
+        <v>-0.010839839568063059</v>
       </c>
       <c r="G54" s="1">
         <v>0.98</v>
       </c>
       <c r="H54" s="1">
-        <v>48.71</v>
+        <v>50.48</v>
       </c>
       <c r="I54" s="1">
-        <v>4.91</v>
+        <v>5.46</v>
       </c>
       <c r="J54" s="1">
-        <v>0.005512396364876555</v>
+        <v>0.005761356310475363</v>
       </c>
       <c r="K54" s="1" t="b">
         <v>0</v>
@@ -5429,28 +5429,28 @@
         <v>85</v>
       </c>
       <c r="M54" s="1">
-        <v>-0.04394914156620344</v>
+        <v>-0.01172745533356001</v>
       </c>
       <c r="N54" s="1">
-        <v>3.377848137596863</v>
+        <v>4.340333294128743</v>
       </c>
       <c r="O54" s="1">
-        <v>56.470588235294116</v>
+        <v>60</v>
       </c>
       <c r="P54" s="1">
         <v>11.84024085938085</v>
       </c>
       <c r="Q54" s="1">
-        <v>52.705882352941174</v>
+        <v>53.17647058823529</v>
       </c>
       <c r="R54" s="1">
-        <v>47.47058823529412</v>
+        <v>48.11764705882353</v>
       </c>
       <c r="S54" s="1" t="s">
         <v>115</v>
       </c>
       <c r="T54" s="1">
-        <v>7.04</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
@@ -5470,19 +5470,19 @@
         <v>0.69</v>
       </c>
       <c r="F55" s="3">
-        <v>-0.2929107333333941</v>
+        <v>-0.2872615072541589</v>
       </c>
       <c r="G55" s="3">
         <v>1.58</v>
       </c>
       <c r="H55" s="3">
-        <v>47.56</v>
+        <v>52.39</v>
       </c>
       <c r="I55" s="3">
-        <v>2.07</v>
+        <v>3.83</v>
       </c>
       <c r="J55" s="3">
-        <v>-0.01298188149146299</v>
+        <v>-0.011218956548499326</v>
       </c>
       <c r="K55" s="3" t="b">
         <v>0</v>
@@ -5491,90 +5491,90 @@
         <v>348</v>
       </c>
       <c r="M55" s="3">
-        <v>-0.25406371202693423</v>
+        <v>-0.26152065005474734</v>
       </c>
       <c r="N55" s="3">
-        <v>-17.633608908476205</v>
+        <v>-20.638986177989985</v>
       </c>
       <c r="O55" s="3">
-        <v>11.76470588235294</v>
+        <v>12.941176470588237</v>
       </c>
       <c r="P55" s="3">
         <v>26.83257063748809</v>
       </c>
       <c r="Q55" s="3">
-        <v>47.52941176470588</v>
+        <v>50.11764705882352</v>
       </c>
       <c r="R55" s="3">
-        <v>28.588235294117645</v>
+        <v>28.94117647058824</v>
       </c>
       <c r="S55" s="3" t="s">
         <v>96</v>
       </c>
       <c r="T55" s="3">
-        <v>-30.01</v>
+        <v>-29.66</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
+      <c r="A56" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B56" s="2">
+      <c r="B56" s="1">
         <v>0.73</v>
       </c>
-      <c r="C56" s="2">
+      <c r="C56" s="1">
         <v>37.64705882352941</v>
       </c>
-      <c r="D56" s="2">
+      <c r="D56" s="1">
         <v>113.35616438356165</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E56" s="1">
         <v>2.08</v>
       </c>
-      <c r="F56" s="2">
-        <v>-0.12039070994908113</v>
-      </c>
-      <c r="G56" s="2">
-        <v>3.81</v>
-      </c>
-      <c r="H56" s="2">
-        <v>57.48</v>
-      </c>
-      <c r="I56" s="2">
-        <v>35.53</v>
-      </c>
-      <c r="J56" s="2">
-        <v>0.01883970337392056</v>
-      </c>
-      <c r="K56" s="2" t="b">
+      <c r="F56" s="1">
+        <v>-0.22309708857379798</v>
+      </c>
+      <c r="G56" s="1">
+        <v>3.79</v>
+      </c>
+      <c r="H56" s="1">
+        <v>53.99</v>
+      </c>
+      <c r="I56" s="1">
+        <v>30.53</v>
+      </c>
+      <c r="J56" s="1">
+        <v>0.020529766307827702</v>
+      </c>
+      <c r="K56" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L56" s="2">
+      <c r="L56" s="1">
         <v>323</v>
       </c>
-      <c r="M56" s="2">
-        <v>0.06781641051842269</v>
-      </c>
-      <c r="N56" s="2">
-        <v>14.554403346059486</v>
-      </c>
-      <c r="O56" s="2">
-        <v>67.05882352941175</v>
-      </c>
-      <c r="P56" s="2">
+      <c r="M56" s="1">
+        <v>-0.09927468928697336</v>
+      </c>
+      <c r="N56" s="1">
+        <v>-4.41439010121258</v>
+      </c>
+      <c r="O56" s="1">
+        <v>44.70588235294118</v>
+      </c>
+      <c r="P56" s="1">
         <v>52.65288503392759</v>
       </c>
-      <c r="Q56" s="2">
-        <v>70.82352941176471</v>
-      </c>
-      <c r="R56" s="2">
-        <v>50.70588235294117</v>
-      </c>
-      <c r="S56" s="2" t="s">
+      <c r="Q56" s="1">
+        <v>70.3529411764706</v>
+      </c>
+      <c r="R56" s="1">
+        <v>44.23529411764706</v>
+      </c>
+      <c r="S56" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="T56" s="2">
-        <v>-9.29</v>
+      <c r="T56" s="1">
+        <v>-15.76</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
@@ -5594,19 +5594,19 @@
         <v>-1.36</v>
       </c>
       <c r="F57" s="3">
-        <v>-0.3140894384571067</v>
+        <v>-0.30629057940792476</v>
       </c>
       <c r="G57" s="3">
         <v>2.04</v>
       </c>
       <c r="H57" s="3">
-        <v>44.86</v>
+        <v>45.65</v>
       </c>
       <c r="I57" s="3">
-        <v>-6.23</v>
+        <v>-6.04</v>
       </c>
       <c r="J57" s="3">
-        <v>-0.020284230696150034</v>
+        <v>-0.01872175291161453</v>
       </c>
       <c r="K57" s="3" t="b">
         <v>0</v>
@@ -5615,10 +5615,10 @@
         <v>250</v>
       </c>
       <c r="M57" s="3">
-        <v>-0.24443271059724758</v>
+        <v>-0.2601345596020833</v>
       </c>
       <c r="N57" s="3">
-        <v>-16.670508765507538</v>
+        <v>-20.500377132723578</v>
       </c>
       <c r="O57" s="3">
         <v>14.117647058823529</v>
@@ -5627,7 +5627,7 @@
         <v>40.717118046641446</v>
       </c>
       <c r="Q57" s="3">
-        <v>44.58823529411765</v>
+        <v>45.64705882352941</v>
       </c>
       <c r="R57" s="3">
         <v>26.941176470588232</v>
@@ -5656,19 +5656,19 @@
         <v>1.26</v>
       </c>
       <c r="F58" s="1">
-        <v>-0.1451834415319172</v>
+        <v>-0.10812463267750477</v>
       </c>
       <c r="G58" s="1">
         <v>1.64</v>
       </c>
       <c r="H58" s="1">
-        <v>45.25</v>
+        <v>39.47</v>
       </c>
       <c r="I58" s="1">
-        <v>-17.15</v>
+        <v>-20.16</v>
       </c>
       <c r="J58" s="1">
-        <v>0.016426117028996167</v>
+        <v>0.017981739098306974</v>
       </c>
       <c r="K58" s="1" t="b">
         <v>0</v>
@@ -5677,28 +5677,28 @@
         <v>3</v>
       </c>
       <c r="M58" s="1">
-        <v>-0.10231776284892702</v>
+        <v>-0.07972092818160237</v>
       </c>
       <c r="N58" s="1">
         <v>-2.459013990675489</v>
       </c>
       <c r="O58" s="1">
-        <v>40</v>
+        <v>50.588235294117645</v>
       </c>
       <c r="P58" s="1">
         <v>33.706290307642504</v>
       </c>
       <c r="Q58" s="1">
-        <v>57.411764705882355</v>
+        <v>56</v>
       </c>
       <c r="R58" s="1">
-        <v>42.94117647058823</v>
+        <v>46.23529411764706</v>
       </c>
       <c r="S58" s="1" t="s">
         <v>103</v>
       </c>
       <c r="T58" s="1">
-        <v>20.99</v>
+        <v>24.28</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
@@ -5718,19 +5718,19 @@
         <v>0.96</v>
       </c>
       <c r="F59" s="3">
-        <v>-0.30383719056383857</v>
+        <v>-0.3279968658405662</v>
       </c>
       <c r="G59" s="3">
         <v>1.86</v>
       </c>
       <c r="H59" s="3">
-        <v>51.26</v>
+        <v>56.46</v>
       </c>
       <c r="I59" s="3">
-        <v>12.23</v>
+        <v>16.01</v>
       </c>
       <c r="J59" s="3">
-        <v>-0.009099462723836231</v>
+        <v>-0.005915414416503513</v>
       </c>
       <c r="K59" s="3" t="b">
         <v>0</v>
@@ -5739,28 +5739,28 @@
         <v>519</v>
       </c>
       <c r="M59" s="3">
-        <v>-0.2462364348335705</v>
+        <v>-0.2898293879241973</v>
       </c>
       <c r="N59" s="3">
-        <v>-16.850881189139834</v>
+        <v>-23.469859964934976</v>
       </c>
       <c r="O59" s="3">
-        <v>12.941176470588237</v>
+        <v>10.588235294117647</v>
       </c>
       <c r="P59" s="3">
         <v>41.76493344029593</v>
       </c>
       <c r="Q59" s="3">
-        <v>52.705882352941174</v>
+        <v>57.1764705882353</v>
       </c>
       <c r="R59" s="3">
-        <v>27.529411764705884</v>
+        <v>28.000000000000007</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>110</v>
       </c>
       <c r="T59" s="3">
-        <v>-31.68</v>
+        <v>-31.21</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.25">
@@ -5780,19 +5780,19 @@
         <v>-4.42</v>
       </c>
       <c r="F60" s="3">
-        <v>-0.5138727134497337</v>
+        <v>-0.5360009444836781</v>
       </c>
       <c r="G60" s="3">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="H60" s="3">
-        <v>34.49</v>
+        <v>29.68</v>
       </c>
       <c r="I60" s="3">
-        <v>-35.25</v>
+        <v>-38.53</v>
       </c>
       <c r="J60" s="3">
-        <v>-0.02370514545342214</v>
+        <v>-0.023190107558732517</v>
       </c>
       <c r="K60" s="3" t="b">
         <v>0</v>
@@ -5801,28 +5801,28 @@
         <v>21</v>
       </c>
       <c r="M60" s="3">
-        <v>-0.39197343969498033</v>
+        <v>-0.4543402940579586</v>
       </c>
       <c r="N60" s="3">
-        <v>-31.424581675280816</v>
+        <v>-39.92095057831111</v>
       </c>
       <c r="O60" s="3">
-        <v>3.5294117647058822</v>
+        <v>2.3529411764705883</v>
       </c>
       <c r="P60" s="3">
-        <v>46.90217032437056</v>
+        <v>50.43478220306857</v>
       </c>
       <c r="Q60" s="3">
-        <v>24.235294117647054</v>
+        <v>23.76470588235294</v>
       </c>
       <c r="R60" s="3">
-        <v>10.764705882352938</v>
+        <v>10.294117647058819</v>
       </c>
       <c r="S60" s="3" t="s">
         <v>98</v>
       </c>
       <c r="T60" s="3">
-        <v>-16.13</v>
+        <v>-16.6</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
@@ -5836,25 +5836,25 @@
         <v>55.294117647058826</v>
       </c>
       <c r="D61" s="1">
-        <v>2.2689655172413796</v>
+        <v>2.285057471264368</v>
       </c>
       <c r="E61" s="1">
         <v>-0.52</v>
       </c>
       <c r="F61" s="1">
-        <v>-0.11151016002888062</v>
+        <v>-0.10608862186609126</v>
       </c>
       <c r="G61" s="1">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="H61" s="1">
-        <v>30.62</v>
+        <v>29.46</v>
       </c>
       <c r="I61" s="1">
-        <v>2.33</v>
+        <v>0.84</v>
       </c>
       <c r="J61" s="1">
-        <v>-0.006451487788661882</v>
+        <v>-0.007776431559266056</v>
       </c>
       <c r="K61" s="1" t="b">
         <v>0</v>
@@ -5863,28 +5863,28 @@
         <v>169</v>
       </c>
       <c r="M61" s="1">
-        <v>-0.09811463544044619</v>
+        <v>-0.09676865632837328</v>
       </c>
       <c r="N61" s="1">
-        <v>-2.038701249827406</v>
+        <v>-4.163786805352571</v>
       </c>
       <c r="O61" s="1">
-        <v>41.17647058823529</v>
+        <v>45.88235294117647</v>
       </c>
       <c r="P61" s="1">
-        <v>13.593577982515374</v>
+        <v>14.411351164527469</v>
       </c>
       <c r="Q61" s="1">
-        <v>42.588235294117645</v>
+        <v>40.705882352941174</v>
       </c>
       <c r="R61" s="1">
-        <v>40.05882352941177</v>
+        <v>40.529411764705884</v>
       </c>
       <c r="S61" s="1" t="s">
         <v>116</v>
       </c>
       <c r="T61" s="1">
-        <v>-7.14</v>
+        <v>-6.67</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
@@ -5898,25 +5898,25 @@
         <v>72.94117647058823</v>
       </c>
       <c r="D62" s="2">
-        <v>0.1888760139049825</v>
+        <v>0.1622247972190033</v>
       </c>
       <c r="E62" s="2">
         <v>0.09</v>
       </c>
       <c r="F62" s="2">
-        <v>0.04088234520051771</v>
+        <v>0.03236410165294451</v>
       </c>
       <c r="G62" s="2">
         <v>0.2</v>
       </c>
       <c r="H62" s="2">
-        <v>58.94</v>
+        <v>56.92</v>
       </c>
       <c r="I62" s="2">
-        <v>13.19</v>
+        <v>12.65</v>
       </c>
       <c r="J62" s="2">
-        <v>0.006391514005877937</v>
+        <v>0.00687267704502611</v>
       </c>
       <c r="K62" s="2" t="b">
         <v>0</v>
@@ -5925,28 +5925,28 @@
         <v>92</v>
       </c>
       <c r="M62" s="2">
-        <v>-0.012699753153220028</v>
+        <v>-0.003140528966933509</v>
       </c>
       <c r="N62" s="2">
-        <v>6.502786978895224</v>
+        <v>5.19902593079141</v>
       </c>
       <c r="O62" s="2">
-        <v>60</v>
+        <v>61.1764705882353</v>
       </c>
       <c r="P62" s="2">
         <v>7.56622762341097</v>
       </c>
       <c r="Q62" s="2">
-        <v>58.94117647058824</v>
+        <v>57.76470588235294</v>
       </c>
       <c r="R62" s="2">
-        <v>50.352941176470594</v>
+        <v>50.411764705882355</v>
       </c>
       <c r="S62" s="2" t="s">
         <v>101</v>
       </c>
       <c r="T62" s="2">
-        <v>4.38</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
@@ -5960,25 +5960,25 @@
         <v>98.82352941176471</v>
       </c>
       <c r="D63" s="1">
-        <v>1.6126330088295224</v>
+        <v>1.6422911478378988</v>
       </c>
       <c r="E63" s="1">
         <v>-1.05</v>
       </c>
       <c r="F63" s="1">
-        <v>-0.20498070792182313</v>
+        <v>-0.18943769523470388</v>
       </c>
       <c r="G63" s="1">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="H63" s="1">
-        <v>58.35</v>
+        <v>59.81</v>
       </c>
       <c r="I63" s="1">
-        <v>58.47</v>
+        <v>59.38</v>
       </c>
       <c r="J63" s="1">
-        <v>0.015484596668831169</v>
+        <v>0.01848645400082876</v>
       </c>
       <c r="K63" s="1" t="b">
         <v>0</v>
@@ -5987,28 +5987,28 @@
         <v>935</v>
       </c>
       <c r="M63" s="1">
-        <v>-0.1219284554735296</v>
+        <v>-0.13484932565664143</v>
       </c>
       <c r="N63" s="1">
-        <v>-4.420083253135738</v>
+        <v>-7.971853738179395</v>
       </c>
       <c r="O63" s="1">
-        <v>34.11764705882353</v>
+        <v>37.64705882352941</v>
       </c>
       <c r="P63" s="1">
         <v>39.10478556320163</v>
       </c>
       <c r="Q63" s="1">
-        <v>76.58823529411765</v>
+        <v>77.76470588235296</v>
       </c>
       <c r="R63" s="1">
-        <v>46.47058823529412</v>
+        <v>48.1764705882353</v>
       </c>
       <c r="S63" s="1" t="s">
         <v>117</v>
       </c>
       <c r="T63" s="1">
-        <v>-21.64</v>
+        <v>-19.93</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.25">
@@ -6028,19 +6028,19 @@
         <v>1.48</v>
       </c>
       <c r="F64" s="1">
-        <v>-0.15947503754139494</v>
+        <v>-0.1923377804971709</v>
       </c>
       <c r="G64" s="1">
         <v>0.97</v>
       </c>
       <c r="H64" s="1">
-        <v>47.63</v>
+        <v>50.79</v>
       </c>
       <c r="I64" s="1">
-        <v>2.86</v>
+        <v>4.37</v>
       </c>
       <c r="J64" s="1">
-        <v>-0.010791662646189238</v>
+        <v>-0.010063311717134994</v>
       </c>
       <c r="K64" s="1" t="b">
         <v>0</v>
@@ -6049,90 +6049,90 @@
         <v>365</v>
       </c>
       <c r="M64" s="1">
-        <v>-0.16148436622966011</v>
+        <v>-0.19366920414541633</v>
       </c>
       <c r="N64" s="1">
-        <v>-8.375674328748792</v>
+        <v>-13.853841587056879</v>
       </c>
       <c r="O64" s="1">
-        <v>28.235294117647058</v>
+        <v>22.35294117647059</v>
       </c>
       <c r="P64" s="1">
         <v>25.543467249515373</v>
       </c>
       <c r="Q64" s="1">
-        <v>45.99999999999999</v>
+        <v>47.882352941176464</v>
       </c>
       <c r="R64" s="1">
-        <v>32.29411764705882</v>
+        <v>30.529411764705884</v>
       </c>
       <c r="S64" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T64" s="1">
-        <v>-12.46</v>
+        <v>-14.23</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A65" s="3" t="s">
+      <c r="A65" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B65" s="3">
+      <c r="B65" s="1">
         <v>7.62</v>
       </c>
-      <c r="C65" s="3">
+      <c r="C65" s="1">
         <v>65.88235294117646</v>
       </c>
-      <c r="D65" s="3">
-        <v>-0.410761154855643</v>
-      </c>
-      <c r="E65" s="3">
+      <c r="D65" s="1">
+        <v>-0.431758530183727</v>
+      </c>
+      <c r="E65" s="1">
         <v>0.42</v>
       </c>
-      <c r="F65" s="3">
-        <v>-0.12510874079301193</v>
-      </c>
-      <c r="G65" s="3">
+      <c r="F65" s="1">
+        <v>-0.10013343807246583</v>
+      </c>
+      <c r="G65" s="1">
         <v>0.36</v>
       </c>
-      <c r="H65" s="3">
-        <v>28.86</v>
-      </c>
-      <c r="I65" s="3">
-        <v>-12.93</v>
-      </c>
-      <c r="J65" s="3">
-        <v>-0.005542145213839998</v>
-      </c>
-      <c r="K65" s="3" t="b">
+      <c r="H65" s="1">
+        <v>26.58</v>
+      </c>
+      <c r="I65" s="1">
+        <v>-13.71</v>
+      </c>
+      <c r="J65" s="1">
+        <v>-0.0056682744534288015</v>
+      </c>
+      <c r="K65" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L65" s="3">
+      <c r="L65" s="1">
         <v>-102</v>
       </c>
-      <c r="M65" s="3">
-        <v>-0.1679744194760021</v>
-      </c>
-      <c r="N65" s="3">
-        <v>-9.024679653382991</v>
-      </c>
-      <c r="O65" s="3">
-        <v>24.705882352941178</v>
-      </c>
-      <c r="P65" s="3">
-        <v>18.58840549196192</v>
-      </c>
-      <c r="Q65" s="3">
+      <c r="M65" s="1">
+        <v>-0.12853714256836823</v>
+      </c>
+      <c r="N65" s="1">
+        <v>-7.3406354293520675</v>
+      </c>
+      <c r="O65" s="1">
+        <v>38.82352941176471</v>
+      </c>
+      <c r="P65" s="1">
+        <v>18.004991105304</v>
+      </c>
+      <c r="Q65" s="1">
         <v>34.94117647058823</v>
       </c>
-      <c r="R65" s="3">
-        <v>29.76470588235294</v>
-      </c>
-      <c r="S65" s="3" t="s">
+      <c r="R65" s="1">
+        <v>33.82352941176471</v>
+      </c>
+      <c r="S65" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="T65" s="3">
-        <v>3.73</v>
+      <c r="T65" s="1">
+        <v>7.79</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
@@ -6152,19 +6152,19 @@
         <v>2.08</v>
       </c>
       <c r="F66" s="2">
-        <v>0.05690085765609246</v>
+        <v>0.05111271238491567</v>
       </c>
       <c r="G66" s="2">
         <v>0.87</v>
       </c>
       <c r="H66" s="2">
-        <v>58.86</v>
+        <v>54.08</v>
       </c>
       <c r="I66" s="2">
-        <v>18.42</v>
+        <v>16.45</v>
       </c>
       <c r="J66" s="2">
-        <v>0.01705682369638478</v>
+        <v>0.01682933657025359</v>
       </c>
       <c r="K66" s="2" t="b">
         <v>0</v>
@@ -6173,28 +6173,28 @@
         <v>79</v>
       </c>
       <c r="M66" s="2">
-        <v>0.04819376667361008</v>
+        <v>0.0453432099091855</v>
       </c>
       <c r="N66" s="2">
-        <v>12.592138961578229</v>
+        <v>10.047399818403294</v>
       </c>
       <c r="O66" s="2">
-        <v>65.88235294117646</v>
+        <v>67.05882352941175</v>
       </c>
       <c r="P66" s="2">
         <v>10.56723987277981</v>
       </c>
       <c r="Q66" s="2">
-        <v>69.52941176470588</v>
+        <v>67.64705882352942</v>
       </c>
       <c r="R66" s="2">
-        <v>58.705882352941174</v>
+        <v>58.8235294117647</v>
       </c>
       <c r="S66" s="2" t="s">
         <v>119</v>
       </c>
       <c r="T66" s="2">
-        <v>15.11</v>
+        <v>15.23</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
@@ -6214,19 +6214,19 @@
         <v>1.77</v>
       </c>
       <c r="F67" s="1">
-        <v>-0.5087004596405837</v>
+        <v>-0.4074643034223971</v>
       </c>
       <c r="G67" s="1">
-        <v>5.2</v>
+        <v>5.23</v>
       </c>
       <c r="H67" s="1">
-        <v>52.83</v>
+        <v>53.94</v>
       </c>
       <c r="I67" s="1">
-        <v>52.8</v>
+        <v>53.58</v>
       </c>
       <c r="J67" s="1">
-        <v>0.008348352451224951</v>
+        <v>0.01512414547059799</v>
       </c>
       <c r="K67" s="1" t="b">
         <v>0</v>
@@ -6235,28 +6235,28 @@
         <v>668</v>
       </c>
       <c r="M67" s="1">
-        <v>-0.2273944432834606</v>
+        <v>-0.21973356901979202</v>
       </c>
       <c r="N67" s="1">
-        <v>-14.966682034128844</v>
+        <v>-16.460278074494454</v>
       </c>
       <c r="O67" s="1">
-        <v>16.470588235294116</v>
+        <v>18.823529411764707</v>
       </c>
       <c r="P67" s="1">
         <v>56.49293299150161</v>
       </c>
       <c r="Q67" s="1">
-        <v>63.05882352941177</v>
+        <v>65.41176470588235</v>
       </c>
       <c r="R67" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S67" s="1" t="s">
         <v>103</v>
       </c>
       <c r="T67" s="1">
-        <v>-39.39</v>
+        <v>-37.39</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
@@ -6276,19 +6276,19 @@
         <v>-2.4</v>
       </c>
       <c r="F68" s="1">
-        <v>-0.13192003913163258</v>
+        <v>-0.15205366543393822</v>
       </c>
       <c r="G68" s="1">
         <v>2.09</v>
       </c>
       <c r="H68" s="1">
-        <v>54.2</v>
+        <v>59.86</v>
       </c>
       <c r="I68" s="1">
-        <v>39.43</v>
+        <v>44.58</v>
       </c>
       <c r="J68" s="1">
-        <v>0.007605061791555833</v>
+        <v>0.011571276211149863</v>
       </c>
       <c r="K68" s="1" t="b">
         <v>0</v>
@@ -6297,28 +6297,28 @@
         <v>514</v>
       </c>
       <c r="M68" s="1">
-        <v>-0.05891443012466491</v>
+        <v>-0.10367860621435443</v>
       </c>
       <c r="N68" s="1">
-        <v>1.8813192817507263</v>
+        <v>-4.854781793950693</v>
       </c>
       <c r="O68" s="1">
-        <v>49.411764705882355</v>
+        <v>43.529411764705884</v>
       </c>
       <c r="P68" s="1">
         <v>31.85898471566022</v>
       </c>
       <c r="Q68" s="1">
-        <v>69.05882352941177</v>
+        <v>71.6470588235294</v>
       </c>
       <c r="R68" s="1">
-        <v>48.17647058823529</v>
+        <v>47</v>
       </c>
       <c r="S68" s="1" t="s">
         <v>111</v>
       </c>
       <c r="T68" s="1">
-        <v>-17.86</v>
+        <v>-19.04</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
@@ -6338,19 +6338,19 @@
         <v>-1.89</v>
       </c>
       <c r="F69" s="1">
-        <v>-0.046914386054515964</v>
+        <v>-0.043869526755578425</v>
       </c>
       <c r="G69" s="1">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="H69" s="1">
-        <v>29.48</v>
+        <v>28.2</v>
       </c>
       <c r="I69" s="1">
-        <v>-31.39</v>
+        <v>-32.42</v>
       </c>
       <c r="J69" s="1">
-        <v>0.0008971538779524497</v>
+        <v>-0.00223424600259286</v>
       </c>
       <c r="K69" s="1" t="b">
         <v>0</v>
@@ -6359,10 +6359,10 @@
         <v>-252</v>
       </c>
       <c r="M69" s="1">
-        <v>-0.04758416228393769</v>
+        <v>-0.043869526755578425</v>
       </c>
       <c r="N69" s="1">
-        <v>3.0143460658234473</v>
+        <v>1.126126151926909</v>
       </c>
       <c r="O69" s="1">
         <v>55.294117647058826</v>
@@ -6374,13 +6374,13 @@
         <v>42.941176470588225</v>
       </c>
       <c r="R69" s="1">
-        <v>40.94117647058823</v>
+        <v>40.8235294117647</v>
       </c>
       <c r="S69" s="1" t="s">
         <v>120</v>
       </c>
       <c r="T69" s="1">
-        <v>23.2</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
@@ -6394,25 +6394,25 @@
         <v>57.647058823529406</v>
       </c>
       <c r="D70" s="1">
-        <v>5.923076923076923</v>
+        <v>6.004395604395604</v>
       </c>
       <c r="E70" s="1">
         <v>-0.55</v>
       </c>
       <c r="F70" s="1">
-        <v>-0.18149343830850734</v>
+        <v>-0.1638882877679056</v>
       </c>
       <c r="G70" s="1">
         <v>1.26</v>
       </c>
       <c r="H70" s="1">
-        <v>38.21</v>
+        <v>35.32</v>
       </c>
       <c r="I70" s="1">
-        <v>-7.28</v>
+        <v>-8.79</v>
       </c>
       <c r="J70" s="1">
-        <v>-0.0050493138942308835</v>
+        <v>-0.005217433017573139</v>
       </c>
       <c r="K70" s="1" t="b">
         <v>0</v>
@@ -6421,28 +6421,28 @@
         <v>3</v>
       </c>
       <c r="M70" s="1">
-        <v>-0.1640792563435426</v>
+        <v>-0.15234928281644522</v>
       </c>
       <c r="N70" s="1">
-        <v>-8.635163340137044</v>
+        <v>-9.721849454159768</v>
       </c>
       <c r="O70" s="1">
-        <v>27.058823529411764</v>
+        <v>35.294117647058826</v>
       </c>
       <c r="P70" s="1">
         <v>16.710870321490763</v>
       </c>
       <c r="Q70" s="1">
-        <v>47.41176470588236</v>
+        <v>46.82352941176471</v>
       </c>
       <c r="R70" s="1">
-        <v>38.94117647058823</v>
+        <v>41.1764705882353</v>
       </c>
       <c r="S70" s="1" t="s">
         <v>103</v>
       </c>
       <c r="T70" s="1">
-        <v>-2.77</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.25">
@@ -6462,19 +6462,19 @@
         <v>0.15</v>
       </c>
       <c r="F71" s="2">
-        <v>0.14739445916654523</v>
+        <v>0.17946466210235704</v>
       </c>
       <c r="G71" s="2">
         <v>0.33</v>
       </c>
       <c r="H71" s="2">
-        <v>60.1</v>
+        <v>60.96</v>
       </c>
       <c r="I71" s="2">
-        <v>11.01</v>
+        <v>11.4</v>
       </c>
       <c r="J71" s="2">
-        <v>0.01375035786157295</v>
+        <v>0.0133095589364393</v>
       </c>
       <c r="K71" s="2" t="b">
         <v>0</v>
@@ -6483,28 +6483,28 @@
         <v>-80</v>
       </c>
       <c r="M71" s="2">
-        <v>0.10251945179528987</v>
+        <v>0.1497295339582092</v>
       </c>
       <c r="N71" s="2">
-        <v>18.02470747374621</v>
+        <v>20.486032223305664</v>
       </c>
       <c r="O71" s="2">
-        <v>72.94117647058823</v>
+        <v>78.82352941176471</v>
       </c>
       <c r="P71" s="2">
         <v>10.873073633899006</v>
       </c>
       <c r="Q71" s="2">
-        <v>62.23529411764706</v>
+        <v>62.00000000000001</v>
       </c>
       <c r="R71" s="2">
-        <v>55.76470588235294</v>
+        <v>57.294117647058826</v>
       </c>
       <c r="S71" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T71" s="2">
-        <v>7.72</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.25">
@@ -6524,19 +6524,19 @@
         <v>0.23</v>
       </c>
       <c r="F72" s="1">
-        <v>-0.10802109027089807</v>
+        <v>-0.05426399750654859</v>
       </c>
       <c r="G72" s="1">
         <v>1.47</v>
       </c>
       <c r="H72" s="1">
-        <v>64.22</v>
+        <v>67.67</v>
       </c>
       <c r="I72" s="1">
-        <v>-10.27</v>
+        <v>-8.18</v>
       </c>
       <c r="J72" s="1">
-        <v>0.001180220369073315</v>
+        <v>0.005171046751789497</v>
       </c>
       <c r="K72" s="1" t="b">
         <v>0</v>
@@ -6545,28 +6545,28 @@
         <v>-42</v>
       </c>
       <c r="M72" s="1">
-        <v>-0.07654160748807715</v>
+        <v>-0.03340502701737025</v>
       </c>
       <c r="N72" s="1">
-        <v>0.11860154540950638</v>
+        <v>2.1725761257477263</v>
       </c>
       <c r="O72" s="1">
-        <v>48.23529411764706</v>
+        <v>56.470588235294116</v>
       </c>
       <c r="P72" s="1">
-        <v>27.47171350888485</v>
+        <v>26.785597000261102</v>
       </c>
       <c r="Q72" s="1">
-        <v>54.58823529411765</v>
+        <v>57.411764705882355</v>
       </c>
       <c r="R72" s="1">
-        <v>41.05882352941176</v>
+        <v>44.58823529411765</v>
       </c>
       <c r="S72" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T72" s="1">
-        <v>11.61</v>
+        <v>15.14</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.25">
@@ -6586,19 +6586,19 @@
         <v>-0.31</v>
       </c>
       <c r="F73" s="2">
-        <v>0.24535237187785608</v>
+        <v>0.2901892935714986</v>
       </c>
       <c r="G73" s="2">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="H73" s="2">
         <v>73.59</v>
       </c>
       <c r="I73" s="2">
-        <v>25.55</v>
+        <v>25.43</v>
       </c>
       <c r="J73" s="2">
-        <v>0.02260487213828174</v>
+        <v>0.02299011363857645</v>
       </c>
       <c r="K73" s="2" t="b">
         <v>0</v>
@@ -6607,28 +6607,28 @@
         <v>48</v>
       </c>
       <c r="M73" s="2">
-        <v>0.23798483335421716</v>
+        <v>0.2848635989785169</v>
       </c>
       <c r="N73" s="2">
-        <v>31.571245629638934</v>
+        <v>33.99943872533644</v>
       </c>
       <c r="O73" s="2">
-        <v>84.70588235294117</v>
+        <v>87.05882352941177</v>
       </c>
       <c r="P73" s="2">
         <v>7.6128642599377825</v>
       </c>
       <c r="Q73" s="2">
-        <v>68.35294117647058</v>
+        <v>68.11764705882354</v>
       </c>
       <c r="R73" s="2">
-        <v>61</v>
+        <v>61.52941176470589</v>
       </c>
       <c r="S73" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T73" s="2">
-        <v>21.12</v>
+        <v>21.65</v>
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.25">
@@ -6642,55 +6642,55 @@
         <v>44.70588235294118</v>
       </c>
       <c r="D74" s="1">
-        <v>11.06190476190476</v>
+        <v>10.847619047619046</v>
       </c>
       <c r="E74" s="1">
         <v>0.38</v>
       </c>
       <c r="F74" s="1">
-        <v>-0.2064549955100351</v>
+        <v>-0.18227861176867638</v>
       </c>
       <c r="G74" s="1">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="H74" s="1">
-        <v>34.16</v>
+        <v>41.87</v>
       </c>
       <c r="I74" s="1">
-        <v>-27.87</v>
+        <v>-25.85</v>
       </c>
       <c r="J74" s="1">
-        <v>-0.01895711182762106</v>
+        <v>-0.018588116744180032</v>
       </c>
       <c r="K74" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" s="1">
         <v>-170</v>
       </c>
       <c r="M74" s="1">
-        <v>-0.2004270094452396</v>
+        <v>-0.17784053294119162</v>
       </c>
       <c r="N74" s="1">
-        <v>-12.269938650306749</v>
+        <v>-12.270974466634412</v>
       </c>
       <c r="O74" s="1">
-        <v>20</v>
+        <v>27.058823529411764</v>
       </c>
       <c r="P74" s="1">
         <v>25.03694506602277</v>
       </c>
       <c r="Q74" s="1">
-        <v>39.411764705882355</v>
+        <v>41.88235294117647</v>
       </c>
       <c r="R74" s="1">
-        <v>31.294117647058822</v>
+        <v>33.41176470588235</v>
       </c>
       <c r="S74" s="1" t="s">
         <v>121</v>
       </c>
       <c r="T74" s="1">
-        <v>-0.72</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
@@ -6710,19 +6710,19 @@
         <v>-3.81</v>
       </c>
       <c r="F75" s="3">
-        <v>-0.3671408209034849</v>
+        <v>-0.35041901825152716</v>
       </c>
       <c r="G75" s="3">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="H75" s="3">
-        <v>32.85</v>
+        <v>27.51</v>
       </c>
       <c r="I75" s="3">
-        <v>-11.31</v>
+        <v>-14.26</v>
       </c>
       <c r="J75" s="3">
-        <v>-0.024223150384342633</v>
+        <v>-0.024933746030294558</v>
       </c>
       <c r="K75" s="3" t="b">
         <v>0</v>
@@ -6731,28 +6731,28 @@
         <v>32</v>
       </c>
       <c r="M75" s="3">
-        <v>-0.35039641516794184</v>
+        <v>-0.3388800133000668</v>
       </c>
       <c r="N75" s="3">
-        <v>-27.26687922257697</v>
+        <v>-28.374922502521926</v>
       </c>
       <c r="O75" s="3">
         <v>7.0588235294117645</v>
       </c>
       <c r="P75" s="3">
-        <v>32.49775597661548</v>
+        <v>33.18412261673902</v>
       </c>
       <c r="Q75" s="3">
-        <v>41.058823529411754</v>
+        <v>40.35294117647058</v>
       </c>
       <c r="R75" s="3">
-        <v>26.41176470588235</v>
+        <v>26.294117647058822</v>
       </c>
       <c r="S75" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T75" s="3">
-        <v>-32.19</v>
+        <v>-32.3</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
@@ -6772,19 +6772,19 @@
         <v>-0.08</v>
       </c>
       <c r="F76" s="3">
-        <v>-0.4238295915247604</v>
+        <v>-0.416542437471384</v>
       </c>
       <c r="G76" s="3">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="H76" s="3">
-        <v>40.67</v>
+        <v>37.9</v>
       </c>
       <c r="I76" s="3">
-        <v>-31.46</v>
+        <v>-33.17</v>
       </c>
       <c r="J76" s="3">
-        <v>-0.008609182920113043</v>
+        <v>-0.00735933571744042</v>
       </c>
       <c r="K76" s="3" t="b">
         <v>0</v>
@@ -6793,28 +6793,28 @@
         <v>10</v>
       </c>
       <c r="M76" s="3">
-        <v>-0.273129939904873</v>
+        <v>-0.3162418559702286</v>
       </c>
       <c r="N76" s="3">
-        <v>-19.540231696270077</v>
+        <v>-26.111106769538107</v>
       </c>
       <c r="O76" s="3">
-        <v>10.588235294117647</v>
+        <v>8.235294117647058</v>
       </c>
       <c r="P76" s="3">
         <v>51.49813033405746</v>
       </c>
       <c r="Q76" s="3">
-        <v>42.94117647058823</v>
+        <v>43.29411764705882</v>
       </c>
       <c r="R76" s="3">
-        <v>25.764705882352942</v>
+        <v>25.294117647058826</v>
       </c>
       <c r="S76" s="3" t="s">
         <v>109</v>
       </c>
       <c r="T76" s="3">
-        <v>0.03</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
@@ -6834,19 +6834,19 @@
         <v>12.8</v>
       </c>
       <c r="F77" s="3">
-        <v>-0.16102454855904733</v>
+        <v>-0.21765931011452888</v>
       </c>
       <c r="G77" s="3">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="H77" s="3">
-        <v>43.62</v>
+        <v>44.33</v>
       </c>
       <c r="I77" s="3">
-        <v>40.7</v>
+        <v>40.54</v>
       </c>
       <c r="J77" s="3">
-        <v>-0.0203614235520299</v>
+        <v>-0.02071289991771768</v>
       </c>
       <c r="K77" s="3" t="b">
         <v>0</v>
@@ -6855,28 +6855,28 @@
         <v>42</v>
       </c>
       <c r="M77" s="3">
-        <v>-0.1697316395415297</v>
+        <v>-0.2229850047075106</v>
       </c>
       <c r="N77" s="3">
-        <v>-9.200401659935748</v>
+        <v>-16.78542164326631</v>
       </c>
       <c r="O77" s="3">
-        <v>23.52941176470588</v>
+        <v>17.647058823529413</v>
       </c>
       <c r="P77" s="3">
         <v>29.799918858582526</v>
       </c>
       <c r="Q77" s="3">
-        <v>30.70588235294118</v>
+        <v>31.058823529411768</v>
       </c>
       <c r="R77" s="3">
-        <v>15.235294117647062</v>
+        <v>13.235294117647063</v>
       </c>
       <c r="S77" s="3" t="s">
         <v>123</v>
       </c>
       <c r="T77" s="3">
-        <v>-58.48</v>
+        <v>-60.48</v>
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
@@ -6896,19 +6896,19 @@
         <v>-9.42</v>
       </c>
       <c r="F78" s="2">
-        <v>0.6602035029410325</v>
+        <v>0.640655863648744</v>
       </c>
       <c r="G78" s="2">
         <v>0.92</v>
       </c>
       <c r="H78" s="2">
-        <v>69.3</v>
+        <v>69.79</v>
       </c>
       <c r="I78" s="2">
         <v>37.17</v>
       </c>
       <c r="J78" s="2">
-        <v>0.027637143117154688</v>
+        <v>0.025675278585829048</v>
       </c>
       <c r="K78" s="2" t="b">
         <v>0</v>
@@ -6917,10 +6917,10 @@
         <v>-5</v>
       </c>
       <c r="M78" s="2">
-        <v>0.6548452931056588</v>
+        <v>0.6371054005867562</v>
       </c>
       <c r="N78" s="2">
-        <v>73.25729160478309</v>
+        <v>69.22361888616038</v>
       </c>
       <c r="O78" s="2">
         <v>98.82352941176471</v>
@@ -6929,10 +6929,10 @@
         <v>18.71809072120826</v>
       </c>
       <c r="Q78" s="2">
-        <v>66.3529411764706</v>
+        <v>66.00000000000001</v>
       </c>
       <c r="R78" s="2">
-        <v>60.294117647058826</v>
+        <v>60.29411764705883</v>
       </c>
       <c r="S78" s="2" t="s">
         <v>110</v>
@@ -6958,19 +6958,19 @@
         <v>-3.58</v>
       </c>
       <c r="F79" s="1">
-        <v>0.035020472335560174</v>
+        <v>0.006210174055038764</v>
       </c>
       <c r="G79" s="1">
         <v>1.12</v>
       </c>
       <c r="H79" s="1">
-        <v>50.87</v>
+        <v>46.46</v>
       </c>
       <c r="I79" s="1">
-        <v>26.23</v>
+        <v>24.09</v>
       </c>
       <c r="J79" s="1">
-        <v>0.008665519072377836</v>
+        <v>0.007337581214495477</v>
       </c>
       <c r="K79" s="1" t="b">
         <v>0</v>
@@ -6979,28 +6979,28 @@
         <v>-2</v>
       </c>
       <c r="M79" s="1">
-        <v>0.04305778708862085</v>
+        <v>0.011535868648020475</v>
       </c>
       <c r="N79" s="1">
-        <v>12.078541003079298</v>
+        <v>6.6666656922867915</v>
       </c>
       <c r="O79" s="1">
-        <v>64.70588235294117</v>
+        <v>63.52941176470588</v>
       </c>
       <c r="P79" s="1">
-        <v>12.125814181373388</v>
+        <v>11.588828914572927</v>
       </c>
       <c r="Q79" s="1">
-        <v>54.70588235294118</v>
+        <v>52.705882352941174</v>
       </c>
       <c r="R79" s="1">
-        <v>48.17647058823529</v>
+        <v>47.58823529411765</v>
       </c>
       <c r="S79" s="1" t="s">
         <v>108</v>
       </c>
       <c r="T79" s="1">
-        <v>0.01</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.25">
@@ -7020,19 +7020,19 @@
         <v>0.33</v>
       </c>
       <c r="F80" s="1">
-        <v>0.10116766016131047</v>
+        <v>0.0937703983475411</v>
       </c>
       <c r="G80" s="1">
         <v>0.83</v>
       </c>
       <c r="H80" s="1">
-        <v>40.07</v>
+        <v>35.51</v>
       </c>
       <c r="I80" s="1">
-        <v>7.27</v>
+        <v>5.69</v>
       </c>
       <c r="J80" s="1">
-        <v>0.003814402461251358</v>
+        <v>0.0021355740383526213</v>
       </c>
       <c r="K80" s="1" t="b">
         <v>0</v>
@@ -7041,19 +7041,19 @@
         <v>6</v>
       </c>
       <c r="M80" s="1">
-        <v>0.0897814642611412</v>
+        <v>0.08622566434081702</v>
       </c>
       <c r="N80" s="1">
-        <v>16.750908720331335</v>
+        <v>14.135645261566449</v>
       </c>
       <c r="O80" s="1">
-        <v>69.41176470588235</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="P80" s="1">
         <v>11.616065285425229</v>
       </c>
       <c r="Q80" s="1">
-        <v>46.588235294117645</v>
+        <v>45.76470588235294</v>
       </c>
       <c r="R80" s="1">
         <v>48.94117647058823</v>
@@ -7082,19 +7082,19 @@
         <v>0.87</v>
       </c>
       <c r="F81" s="2">
-        <v>0.030322124837270134</v>
+        <v>0.03144148439082524</v>
       </c>
       <c r="G81" s="2">
         <v>0.77</v>
       </c>
       <c r="H81" s="2">
-        <v>47.97</v>
+        <v>47.74</v>
       </c>
       <c r="I81" s="2">
-        <v>9</v>
+        <v>8.88</v>
       </c>
       <c r="J81" s="2">
-        <v>0.002498090645730258</v>
+        <v>0.0018530605416959582</v>
       </c>
       <c r="K81" s="2" t="b">
         <v>0</v>
@@ -7103,28 +7103,28 @@
         <v>157</v>
       </c>
       <c r="M81" s="2">
-        <v>0.014917271560570544</v>
+        <v>0.021233903087610306</v>
       </c>
       <c r="N81" s="2">
-        <v>9.264489450274265</v>
+        <v>7.636469136245781</v>
       </c>
       <c r="O81" s="2">
-        <v>63.52941176470588</v>
+        <v>65.88235294117646</v>
       </c>
       <c r="P81" s="2">
         <v>6.084662055268521</v>
       </c>
       <c r="Q81" s="2">
-        <v>54.47058823529412</v>
+        <v>54.470588235294116</v>
       </c>
       <c r="R81" s="2">
-        <v>51.764705882352935</v>
+        <v>52.764705882352935</v>
       </c>
       <c r="S81" s="2" t="s">
         <v>111</v>
       </c>
       <c r="T81" s="2">
-        <v>1.34</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.25">
@@ -7138,25 +7138,25 @@
         <v>95.29411764705881</v>
       </c>
       <c r="D82" s="1">
-        <v>-0.9361610968294773</v>
+        <v>-0.9365895458440445</v>
       </c>
       <c r="E82" s="1">
         <v>-1.15</v>
       </c>
       <c r="F82" s="1">
-        <v>-0.035820251974008135</v>
+        <v>-0.03371606563371901</v>
       </c>
       <c r="G82" s="1">
         <v>1.01</v>
       </c>
       <c r="H82" s="1">
-        <v>41.27</v>
+        <v>37.04</v>
       </c>
       <c r="I82" s="1">
-        <v>6.59</v>
+        <v>4.9</v>
       </c>
       <c r="J82" s="1">
-        <v>0.0004099666323727792</v>
+        <v>-0.0007264299348070346</v>
       </c>
       <c r="K82" s="1" t="b">
         <v>1</v>
@@ -7165,19 +7165,19 @@
         <v>110</v>
       </c>
       <c r="M82" s="1">
-        <v>-0.03515047574458641</v>
+        <v>-0.033272257750970535</v>
       </c>
       <c r="N82" s="1">
-        <v>4.257714719758567</v>
+        <v>2.1858530523876882</v>
       </c>
       <c r="O82" s="1">
         <v>57.647058823529406</v>
       </c>
       <c r="P82" s="1">
-        <v>7.571607002312677</v>
+        <v>7.8290149820101895</v>
       </c>
       <c r="Q82" s="1">
-        <v>48.94117647058823</v>
+        <v>48.35294117647059</v>
       </c>
       <c r="R82" s="1">
         <v>48.11764705882353</v>
@@ -7206,19 +7206,19 @@
         <v>0.23</v>
       </c>
       <c r="F83" s="2">
-        <v>0.11946571380693816</v>
+        <v>0.14286998050434677</v>
       </c>
       <c r="G83" s="2">
         <v>1.07</v>
       </c>
       <c r="H83" s="2">
-        <v>65.55</v>
+        <v>60.07</v>
       </c>
       <c r="I83" s="2">
-        <v>18.36</v>
+        <v>16.94</v>
       </c>
       <c r="J83" s="2">
-        <v>0.0052782807758773</v>
+        <v>0.004085269823065668</v>
       </c>
       <c r="K83" s="2" t="b">
         <v>0</v>
@@ -7227,28 +7227,28 @@
         <v>89</v>
       </c>
       <c r="M83" s="2">
-        <v>0.12415414741289021</v>
+        <v>0.1459766356835861</v>
       </c>
       <c r="N83" s="2">
-        <v>20.18817703550623</v>
+        <v>20.110742395843353</v>
       </c>
       <c r="O83" s="2">
-        <v>74.11764705882354</v>
+        <v>77.64705882352942</v>
       </c>
       <c r="P83" s="2">
         <v>12.706223591210087</v>
       </c>
       <c r="Q83" s="2">
-        <v>58.82352941176472</v>
+        <v>57.64705882352942</v>
       </c>
       <c r="R83" s="2">
-        <v>52.117647058823536</v>
+        <v>53.05882352941177</v>
       </c>
       <c r="S83" s="2" t="s">
         <v>109</v>
       </c>
       <c r="T83" s="2">
-        <v>-0.02</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.25">
@@ -7262,25 +7262,25 @@
         <v>92.94117647058823</v>
       </c>
       <c r="D84" s="1">
-        <v>-2.336514314414867</v>
+        <v>-2.3314917127071824</v>
       </c>
       <c r="E84" s="1">
         <v>2.34</v>
       </c>
       <c r="F84" s="1">
-        <v>-0.07203090072237375</v>
+        <v>-0.09850932340449435</v>
       </c>
       <c r="G84" s="1">
         <v>1.2</v>
       </c>
       <c r="H84" s="1">
-        <v>47.37</v>
+        <v>47.81</v>
       </c>
       <c r="I84" s="1">
-        <v>0.29</v>
+        <v>0.45</v>
       </c>
       <c r="J84" s="1">
-        <v>-0.004291404589378948</v>
+        <v>-0.004455521612377182</v>
       </c>
       <c r="K84" s="1" t="b">
         <v>0</v>
@@ -7289,28 +7289,28 @@
         <v>176</v>
       </c>
       <c r="M84" s="1">
-        <v>-0.05863537613393932</v>
+        <v>-0.08963316574952485</v>
       </c>
       <c r="N84" s="1">
-        <v>1.9092246808232824</v>
+        <v>-3.4502377474677353</v>
       </c>
       <c r="O84" s="1">
-        <v>50.588235294117645</v>
+        <v>48.23529411764706</v>
       </c>
       <c r="P84" s="1">
         <v>20.22353911360907</v>
       </c>
       <c r="Q84" s="1">
-        <v>45.52941176470588</v>
+        <v>45.88235294117647</v>
       </c>
       <c r="R84" s="1">
-        <v>39.882352941176464</v>
+        <v>39.17647058823529</v>
       </c>
       <c r="S84" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T84" s="1">
-        <v>-6.89</v>
+        <v>-7.59</v>
       </c>
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.25">
@@ -7330,19 +7330,19 @@
         <v>0.24</v>
       </c>
       <c r="F85" s="1">
-        <v>-0.13853098956071186</v>
+        <v>-0.14736126400167443</v>
       </c>
       <c r="G85" s="1">
         <v>0.98</v>
       </c>
       <c r="H85" s="1">
-        <v>40.58</v>
+        <v>41.76</v>
       </c>
       <c r="I85" s="1">
-        <v>9.33</v>
+        <v>9.75</v>
       </c>
       <c r="J85" s="1">
-        <v>-0.007253566630343955</v>
+        <v>-0.006443716166150902</v>
       </c>
       <c r="K85" s="1" t="b">
         <v>1</v>
@@ -7351,28 +7351,28 @@
         <v>377</v>
       </c>
       <c r="M85" s="1">
-        <v>-0.1398705420195553</v>
+        <v>-0.14824887976717138</v>
       </c>
       <c r="N85" s="1">
-        <v>-6.214291907738306</v>
+        <v>-9.311809149232388</v>
       </c>
       <c r="O85" s="1">
-        <v>32.94117647058823</v>
+        <v>36.470588235294116</v>
       </c>
       <c r="P85" s="1">
         <v>18.130768996018627</v>
       </c>
       <c r="Q85" s="1">
-        <v>44.35294117647059</v>
+        <v>45.529411764705884</v>
       </c>
       <c r="R85" s="1">
-        <v>35.11764705882353</v>
+        <v>36.00000000000001</v>
       </c>
       <c r="S85" s="1" t="s">
         <v>132</v>
       </c>
       <c r="T85" s="1">
-        <v>-21.53</v>
+        <v>-20.65</v>
       </c>
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.25">
@@ -7386,55 +7386,55 @@
         <v>81.17647058823529</v>
       </c>
       <c r="D86" s="1">
-        <v>-0.3141700404858299</v>
+        <v>-0.3052631578947368</v>
       </c>
       <c r="E86" s="1">
         <v>0.61</v>
       </c>
       <c r="F86" s="1">
-        <v>-0.05410670036530564</v>
+        <v>-0.047777924754703965</v>
       </c>
       <c r="G86" s="1">
         <v>0.95</v>
       </c>
       <c r="H86" s="1">
-        <v>35.49</v>
+        <v>33.76</v>
       </c>
       <c r="I86" s="1">
-        <v>4.15</v>
+        <v>3.72</v>
       </c>
       <c r="J86" s="1">
-        <v>-0.005753042678949898</v>
+        <v>-0.006461275641886408</v>
       </c>
       <c r="K86" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L86" s="1">
         <v>130</v>
       </c>
       <c r="M86" s="1">
-        <v>-0.057455581512414255</v>
+        <v>-0.049996964168446345</v>
       </c>
       <c r="N86" s="1">
-        <v>2.0272041429757883</v>
+        <v>0.513382410640126</v>
       </c>
       <c r="O86" s="1">
-        <v>52.94117647058824</v>
+        <v>54.11764705882353</v>
       </c>
       <c r="P86" s="1">
         <v>13.196185332148602</v>
       </c>
       <c r="Q86" s="1">
-        <v>44</v>
+        <v>43.41176470588235</v>
       </c>
       <c r="R86" s="1">
-        <v>43.529411764705884</v>
+        <v>43.64705882352941</v>
       </c>
       <c r="S86" s="1" t="s">
         <v>134</v>
       </c>
       <c r="T86" s="1">
-        <v>-3.24</v>
+        <v>-3.12</v>
       </c>
     </row>
   </sheetData>
@@ -7461,7 +7461,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>44.588235294117645</v>
+        <v>45.76470588235294</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -7469,7 +7469,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>58.70588235294118</v>
+        <v>56.94117647058824</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7477,7 +7477,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>52</v>
+        <v>51.88235294117647</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -7485,7 +7485,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>39.588235294117645</v>
+        <v>34.294117647058826</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -7493,7 +7493,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>32.35294117647059</v>
+        <v>33.8235294117647</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7501,7 +7501,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>57.647058823529406</v>
+        <v>58.23529411764705</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -7509,7 +7509,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>33.76470588235294</v>
+        <v>37.529411764705884</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -7525,7 +7525,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>47.294117647058826</v>
+        <v>48.41176470588235</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -7533,7 +7533,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>56.529411764705884</v>
+        <v>55.70588235294118</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -7541,7 +7541,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>61.05882352941177</v>
+        <v>61.41176470588235</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -7557,7 +7557,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>59.58823529411765</v>
+        <v>60.411764705882355</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -7565,7 +7565,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>33.58823529411765</v>
+        <v>32.529411764705884</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -7573,7 +7573,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>14</v>
+        <v>14.941176470588236</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -7581,7 +7581,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>32.352941176470594</v>
+        <v>32.58823529411765</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -7597,7 +7597,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>53.64705882352941</v>
+        <v>54.35294117647059</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -7605,7 +7605,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>57.117647058823536</v>
+        <v>57.82352941176471</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -7613,7 +7613,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>18.764705882352942</v>
+        <v>18.588235294117645</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -7621,7 +7621,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>33.17647058823529</v>
+        <v>32.41176470588235</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -7629,7 +7629,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>57.29411764705883</v>
+        <v>56.11764705882352</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -7645,7 +7645,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>5.117647058823531</v>
+        <v>4.411764705882353</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -7653,7 +7653,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>11.823529411764703</v>
+        <v>9.88235294117647</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -7669,7 +7669,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>42.117647058823536</v>
+        <v>41.88235294117648</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -7677,7 +7677,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>39.705882352941174</v>
+        <v>38.41176470588235</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -7685,7 +7685,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>42.1764705882353</v>
+        <v>38.76470588235294</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -7693,7 +7693,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>40.64705882352941</v>
+        <v>41.705882352941174</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -7701,7 +7701,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>30.11764705882353</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -7709,7 +7709,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>60.52941176470589</v>
+        <v>60.882352941176485</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -7717,7 +7717,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>40.058823529411775</v>
+        <v>39.352941176470594</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -7725,7 +7725,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>39</v>
+        <v>41.05882352941177</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -7733,7 +7733,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>39.94117647058823</v>
+        <v>41.70588235294119</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -7741,7 +7741,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>50.823529411764696</v>
+        <v>49.99999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -7749,7 +7749,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>66.11764705882354</v>
+        <v>66.23529411764706</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -7757,7 +7757,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>32.117647058823536</v>
+        <v>31.882352941176478</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -7765,7 +7765,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>48.1764705882353</v>
+        <v>47.47058823529412</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -7773,7 +7773,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>22.88235294117647</v>
+        <v>19.352941176470587</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -7781,7 +7781,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>24.23529411764706</v>
+        <v>26.000000000000004</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -7789,7 +7789,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>54.76470588235294</v>
+        <v>53.47058823529413</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -7797,7 +7797,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>55.58823529411765</v>
+        <v>56.88235294117647</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -7805,7 +7805,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>42.23529411764706</v>
+        <v>41.411764705882355</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -7813,7 +7813,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>25.23529411764705</v>
+        <v>25.705882352941167</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -7821,7 +7821,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>51.70588235294118</v>
+        <v>50.88235294117647</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -7829,7 +7829,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>56.94117647058824</v>
+        <v>56.35294117647059</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -7837,7 +7837,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>56.47058823529412</v>
+        <v>54.58823529411766</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -7845,7 +7845,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>24.82352941176471</v>
+        <v>25.88235294117647</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -7853,7 +7853,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>45.352941176470594</v>
+        <v>45.00000000000001</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -7861,7 +7861,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>23.176470588235293</v>
+        <v>26.470588235294116</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -7869,7 +7869,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>23.176470588235293</v>
+        <v>21.52941176470588</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -7877,7 +7877,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>47.47058823529412</v>
+        <v>48.11764705882353</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -7885,7 +7885,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>28.588235294117645</v>
+        <v>28.94117647058824</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -7893,7 +7893,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>50.70588235294117</v>
+        <v>44.23529411764706</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -7909,7 +7909,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>42.94117647058823</v>
+        <v>46.23529411764706</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -7917,7 +7917,7 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>27.529411764705884</v>
+        <v>28.000000000000007</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -7925,7 +7925,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>10.764705882352938</v>
+        <v>10.294117647058819</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -7933,7 +7933,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>40.05882352941177</v>
+        <v>40.529411764705884</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -7941,7 +7941,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>50.352941176470594</v>
+        <v>50.411764705882355</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -7949,7 +7949,7 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>46.47058823529412</v>
+        <v>48.1764705882353</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -7957,7 +7957,7 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>32.29411764705882</v>
+        <v>30.529411764705884</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -7965,7 +7965,7 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>29.76470588235294</v>
+        <v>33.82352941176471</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -7973,7 +7973,7 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>58.705882352941174</v>
+        <v>58.8235294117647</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -7981,7 +7981,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -7989,7 +7989,7 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>48.17647058823529</v>
+        <v>47</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -7997,7 +7997,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>40.94117647058823</v>
+        <v>40.8235294117647</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -8005,7 +8005,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>38.94117647058823</v>
+        <v>41.1764705882353</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -8013,7 +8013,7 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>55.76470588235294</v>
+        <v>57.294117647058826</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -8021,7 +8021,7 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>41.05882352941176</v>
+        <v>44.58823529411765</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -8029,7 +8029,7 @@
         <v>72</v>
       </c>
       <c r="B73">
-        <v>61</v>
+        <v>61.52941176470589</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -8037,7 +8037,7 @@
         <v>73</v>
       </c>
       <c r="B74">
-        <v>31.294117647058822</v>
+        <v>33.41176470588235</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -8045,7 +8045,7 @@
         <v>74</v>
       </c>
       <c r="B75">
-        <v>26.41176470588235</v>
+        <v>26.294117647058822</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -8053,7 +8053,7 @@
         <v>75</v>
       </c>
       <c r="B76">
-        <v>25.764705882352942</v>
+        <v>25.294117647058826</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -8061,7 +8061,7 @@
         <v>122</v>
       </c>
       <c r="B77">
-        <v>15.235294117647062</v>
+        <v>13.235294117647063</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -8069,7 +8069,7 @@
         <v>124</v>
       </c>
       <c r="B78">
-        <v>60.294117647058826</v>
+        <v>60.29411764705883</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -8077,7 +8077,7 @@
         <v>125</v>
       </c>
       <c r="B79">
-        <v>48.17647058823529</v>
+        <v>47.58823529411765</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -8093,7 +8093,7 @@
         <v>127</v>
       </c>
       <c r="B81">
-        <v>51.764705882352935</v>
+        <v>52.764705882352935</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -8109,7 +8109,7 @@
         <v>129</v>
       </c>
       <c r="B83">
-        <v>52.117647058823536</v>
+        <v>53.05882352941177</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -8117,7 +8117,7 @@
         <v>130</v>
       </c>
       <c r="B84">
-        <v>39.882352941176464</v>
+        <v>39.17647058823529</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -8125,7 +8125,7 @@
         <v>131</v>
       </c>
       <c r="B85">
-        <v>35.11764705882353</v>
+        <v>36.00000000000001</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
@@ -8133,7 +8133,7 @@
         <v>133</v>
       </c>
       <c r="B86">
-        <v>43.529411764705884</v>
+        <v>43.64705882352941</v>
       </c>
     </row>
   </sheetData>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="231">
   <si>
     <t>Ticker</t>
   </si>
@@ -430,9 +430,6 @@
     <t>_date_</t>
   </si>
   <si>
-    <t>2026-09-29</t>
-  </si>
-  <si>
     <t>Criteria</t>
   </si>
   <si>
@@ -700,22 +697,16 @@
     <t>Institutional Buying</t>
   </si>
   <si>
+    <t>Momentum Breakout</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Market Leader, Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
     <t>Momentum Breakout, Institutional Buying</t>
   </si>
   <si>
-    <t>Momentum Breakout</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Volume Spike</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Volume Spike, Institutional Buying</t>
-  </si>
-  <si>
     <t>Volume Spike</t>
-  </si>
-  <si>
-    <t>Earnings Upcoming, Institutional Buying</t>
   </si>
   <si>
     <t>Volume Spike, Institutional Buying</t>
@@ -1405,10 +1396,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C1" t="s">
         <v>220</v>
-      </c>
-      <c r="C1" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -1419,7 +1410,7 @@
         <v>66.23529411764706</v>
       </c>
       <c r="C2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1427,10 +1418,10 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>62.41176470588234</v>
+        <v>62.17647058823529</v>
       </c>
       <c r="C3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1438,10 +1429,10 @@
         <v>72</v>
       </c>
       <c r="B4">
-        <v>61.52941176470589</v>
+        <v>61.64705882352943</v>
       </c>
       <c r="C4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1449,10 +1440,10 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>61.41176470588235</v>
+        <v>61.05882352941177</v>
       </c>
       <c r="C5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1460,18 +1451,18 @@
         <v>32</v>
       </c>
       <c r="B6">
-        <v>60.882352941176485</v>
+        <v>60.29411764705883</v>
       </c>
       <c r="C6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>124</v>
       </c>
       <c r="B7">
-        <v>60.411764705882355</v>
+        <v>60.29411764705883</v>
       </c>
       <c r="C7" t="s">
         <v>222</v>
@@ -1479,13 +1470,13 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>124</v>
+        <v>13</v>
       </c>
       <c r="B8">
-        <v>60.29411764705883</v>
+        <v>59.70588235294118</v>
       </c>
       <c r="C8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1493,10 +1484,10 @@
         <v>65</v>
       </c>
       <c r="B9">
-        <v>58.8235294117647</v>
+        <v>58.588235294117645</v>
       </c>
       <c r="C9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1507,84 +1498,84 @@
         <v>58.23529411764705</v>
       </c>
       <c r="C10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="B11">
-        <v>57.82352941176471</v>
+        <v>57.705882352941174</v>
       </c>
       <c r="C11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="B12">
-        <v>57.294117647058826</v>
+        <v>57.05882352941176</v>
       </c>
       <c r="C12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="B13">
-        <v>56.94117647058824</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B14">
-        <v>56.88235294117647</v>
+        <v>56.235294117647065</v>
       </c>
       <c r="C14" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="B15">
-        <v>56.35294117647059</v>
+        <v>55.82352941176471</v>
       </c>
       <c r="C15" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="B16">
-        <v>56.11764705882352</v>
+        <v>55.529411764705884</v>
       </c>
       <c r="C16" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B17">
-        <v>55.70588235294118</v>
+        <v>54.23529411764706</v>
       </c>
       <c r="C17" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -1592,10 +1583,10 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>54.35294117647059</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -1603,32 +1594,32 @@
         <v>42</v>
       </c>
       <c r="B19">
-        <v>53.47058823529413</v>
+        <v>53.58823529411765</v>
       </c>
       <c r="C19" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B20">
-        <v>53.05882352941177</v>
+        <v>52.52941176470588</v>
       </c>
       <c r="C20" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B21">
-        <v>52.764705882352935</v>
+        <v>51.64705882352941</v>
       </c>
       <c r="C21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -1636,10 +1627,10 @@
         <v>3</v>
       </c>
       <c r="B22">
-        <v>51.88235294117647</v>
+        <v>50.82352941176471</v>
       </c>
       <c r="C22" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1647,10 +1638,10 @@
         <v>61</v>
       </c>
       <c r="B23">
-        <v>50.411764705882355</v>
+        <v>50.588235294117645</v>
       </c>
       <c r="C23" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -1658,10 +1649,10 @@
         <v>36</v>
       </c>
       <c r="B24">
-        <v>49.99999999999999</v>
+        <v>49.882352941176464</v>
       </c>
       <c r="C24" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -1669,10 +1660,10 @@
         <v>126</v>
       </c>
       <c r="B25">
-        <v>48.94117647058823</v>
+        <v>49.11764705882353</v>
       </c>
       <c r="C25" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -1680,10 +1671,10 @@
         <v>62</v>
       </c>
       <c r="B26">
-        <v>48.1764705882353</v>
+        <v>48.294117647058826</v>
       </c>
       <c r="C26" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -1691,65 +1682,65 @@
         <v>53</v>
       </c>
       <c r="B27">
-        <v>48.11764705882353</v>
+        <v>48.05882352941177</v>
       </c>
       <c r="C27" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>128</v>
+        <v>39</v>
       </c>
       <c r="B28">
-        <v>48.11764705882353</v>
+        <v>47.76470588235294</v>
       </c>
       <c r="C28" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="B29">
-        <v>47.47058823529412</v>
+        <v>46.705882352941174</v>
       </c>
       <c r="C29" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="B30">
-        <v>47</v>
+        <v>46.411764705882355</v>
       </c>
       <c r="C30" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="B31">
-        <v>46.23529411764706</v>
+        <v>46.17647058823529</v>
       </c>
       <c r="C31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B32">
-        <v>45.00000000000001</v>
+        <v>45.882352941176464</v>
       </c>
       <c r="C32" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -1757,153 +1748,153 @@
         <v>55</v>
       </c>
       <c r="B33">
-        <v>44.23529411764706</v>
+        <v>45.1764705882353</v>
       </c>
       <c r="C33" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="B34">
-        <v>43.64705882352941</v>
+        <v>44.11764705882353</v>
       </c>
       <c r="C34" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>133</v>
+        <v>23</v>
       </c>
       <c r="B35">
         <v>43.64705882352941</v>
       </c>
       <c r="C35" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>27</v>
+        <v>133</v>
       </c>
       <c r="B36">
-        <v>41.88235294117648</v>
+        <v>42.470588235294116</v>
       </c>
       <c r="C36" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="B37">
-        <v>41.705882352941174</v>
+        <v>40.8235294117647</v>
       </c>
       <c r="C37" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="B38">
-        <v>41.411764705882355</v>
+        <v>40.76470588235294</v>
       </c>
       <c r="C38" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="B39">
-        <v>41.1764705882353</v>
+        <v>40.705882352941174</v>
       </c>
       <c r="C39" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="B40">
         <v>40.529411764705884</v>
       </c>
       <c r="C40" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="B41">
-        <v>39.352941176470594</v>
+        <v>40.529411764705884</v>
       </c>
       <c r="C41" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>130</v>
+        <v>27</v>
       </c>
       <c r="B42">
-        <v>39.17647058823529</v>
+        <v>39.882352941176464</v>
       </c>
       <c r="C42" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="B43">
-        <v>38.76470588235294</v>
+        <v>37.64705882352941</v>
       </c>
       <c r="C43" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="B44">
-        <v>38.41176470588235</v>
+        <v>37.41176470588235</v>
       </c>
       <c r="C44" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B45">
-        <v>37.529411764705884</v>
+        <v>37.235294117647065</v>
       </c>
       <c r="C45" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B46">
-        <v>37.235294117647065</v>
+        <v>37.11764705882353</v>
       </c>
       <c r="C46" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -1914,51 +1905,51 @@
         <v>36.00000000000001</v>
       </c>
       <c r="C47" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B48">
-        <v>34.294117647058826</v>
+        <v>34.705882352941174</v>
       </c>
       <c r="C48" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="B49">
-        <v>33.41176470588235</v>
+        <v>34.588235294117645</v>
       </c>
       <c r="C49" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="B50">
-        <v>32.58823529411765</v>
+        <v>33.705882352941174</v>
       </c>
       <c r="C50" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B51">
-        <v>32.529411764705884</v>
+        <v>33.58823529411765</v>
       </c>
       <c r="C51" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -2192,31 +2183,31 @@
         <v>-2.08</v>
       </c>
       <c r="F2" s="1">
-        <v>0.1744031139026391</v>
+        <v>0.1625999849549492</v>
       </c>
       <c r="G2" s="1">
         <v>0.21</v>
       </c>
       <c r="H2" s="1">
-        <v>50.64</v>
+        <v>50.85</v>
       </c>
       <c r="I2" s="1">
-        <v>8.94</v>
+        <v>8.84</v>
       </c>
       <c r="J2" s="1">
-        <v>0.009833514263353984</v>
+        <v>0.009663166557348756</v>
       </c>
       <c r="K2" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>-457</v>
+        <v>-458</v>
       </c>
       <c r="M2" s="1">
-        <v>0.13934229116550956</v>
+        <v>0.13702181933693813</v>
       </c>
       <c r="N2" s="1">
-        <v>19.447307944035703</v>
+        <v>18.014924416986364</v>
       </c>
       <c r="O2" s="1">
         <v>76.47058823529412</v>
@@ -2225,7 +2216,7 @@
         <v>16.29652721982991</v>
       </c>
       <c r="Q2" s="1">
-        <v>47.41176470588235</v>
+        <v>46.94117647058823</v>
       </c>
       <c r="R2" s="1">
         <v>45.76470588235294</v>
@@ -2248,55 +2239,55 @@
         <v>54.11764705882353</v>
       </c>
       <c r="D3" s="2">
-        <v>26.810256410256407</v>
+        <v>26.74102564102564</v>
       </c>
       <c r="E3" s="2">
         <v>3.6</v>
       </c>
       <c r="F3" s="2">
-        <v>0.006378801643399004</v>
+        <v>-0.044504892225418896</v>
       </c>
       <c r="G3" s="2">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="H3" s="2">
-        <v>66.14</v>
+        <v>65.53</v>
       </c>
       <c r="I3" s="2">
-        <v>65.77</v>
+        <v>63.98</v>
       </c>
       <c r="J3" s="2">
-        <v>0.020031403042783044</v>
+        <v>0.020545834372566706</v>
       </c>
       <c r="K3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L3" s="2">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="M3" s="2">
-        <v>0.07161856040742487</v>
+        <v>0.002766148030652227</v>
       </c>
       <c r="N3" s="2">
-        <v>12.674934868227233</v>
+        <v>4.589357286357768</v>
       </c>
       <c r="O3" s="2">
-        <v>69.41176470588235</v>
+        <v>60</v>
       </c>
       <c r="P3" s="2">
         <v>26.053946839070953</v>
       </c>
       <c r="Q3" s="2">
-        <v>75.88235294117648</v>
+        <v>75.88235294117646</v>
       </c>
       <c r="R3" s="2">
-        <v>56.94117647058824</v>
+        <v>54.23529411764706</v>
       </c>
       <c r="S3" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T3" s="2">
-        <v>-10.13</v>
+        <v>-12.84</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -2310,55 +2301,55 @@
         <v>10.588235294117647</v>
       </c>
       <c r="D4" s="2">
-        <v>12.608832807570979</v>
+        <v>12.479495268138802</v>
       </c>
       <c r="E4" s="2">
         <v>6.39</v>
       </c>
       <c r="F4" s="2">
-        <v>0.2327665689372883</v>
+        <v>0.24309488516865063</v>
       </c>
       <c r="G4" s="2">
         <v>1.36</v>
       </c>
       <c r="H4" s="2">
-        <v>50.33</v>
+        <v>51.08</v>
       </c>
       <c r="I4" s="2">
-        <v>45.28</v>
+        <v>45.5</v>
       </c>
       <c r="J4" s="2">
-        <v>0.020137465246089566</v>
+        <v>0.019285989850201312</v>
       </c>
       <c r="K4" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L4" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="M4" s="2">
-        <v>0.24874365271623344</v>
+        <v>0.2547507581085038</v>
       </c>
       <c r="N4" s="2">
-        <v>30.387444099108095</v>
+        <v>29.787818294142927</v>
       </c>
       <c r="O4" s="2">
-        <v>85.88235294117646</v>
+        <v>83.52941176470588</v>
       </c>
       <c r="P4" s="2">
         <v>19.349659482175007</v>
       </c>
       <c r="Q4" s="2">
-        <v>57.05882352941177</v>
+        <v>56.58823529411765</v>
       </c>
       <c r="R4" s="2">
-        <v>51.88235294117647</v>
+        <v>50.82352941176471</v>
       </c>
       <c r="S4" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T4" s="2">
-        <v>3.53</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -2378,49 +2369,49 @@
         <v>1.7</v>
       </c>
       <c r="F5" s="1">
-        <v>-0.22758311906285222</v>
+        <v>-0.2340178624845641</v>
       </c>
       <c r="G5" s="1">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="H5" s="1">
-        <v>47.48</v>
+        <v>45.38</v>
       </c>
       <c r="I5" s="1">
-        <v>-9.26</v>
+        <v>-10.26</v>
       </c>
       <c r="J5" s="1">
-        <v>-0.005193417278709439</v>
+        <v>-0.005247950317212834</v>
       </c>
       <c r="K5" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L5" s="1">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="M5" s="1">
-        <v>-0.187196601732741</v>
+        <v>-0.2042306316382727</v>
       </c>
       <c r="N5" s="1">
-        <v>-13.206581345789342</v>
+        <v>-16.110320680534727</v>
       </c>
       <c r="O5" s="1">
-        <v>24.705882352941178</v>
+        <v>23.52941176470588</v>
       </c>
       <c r="P5" s="1">
         <v>33.002444654975626</v>
       </c>
       <c r="Q5" s="1">
-        <v>51.1764705882353</v>
+        <v>49.05882352941176</v>
       </c>
       <c r="R5" s="1">
-        <v>34.294117647058826</v>
+        <v>33.58823529411765</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T5" s="1">
-        <v>-11.68</v>
+        <v>-12.39</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -2434,25 +2425,25 @@
         <v>49.411764705882355</v>
       </c>
       <c r="D6" s="1">
-        <v>0.8264984227129338</v>
+        <v>0.8233438485804417</v>
       </c>
       <c r="E6" s="1">
         <v>-1.85</v>
       </c>
       <c r="F6" s="1">
-        <v>-0.1438728373204411</v>
+        <v>-0.07828379474590048</v>
       </c>
       <c r="G6" s="1">
         <v>1.61</v>
       </c>
       <c r="H6" s="1">
-        <v>33.2</v>
+        <v>37.77</v>
       </c>
       <c r="I6" s="1">
-        <v>-18.18</v>
+        <v>-16.44</v>
       </c>
       <c r="J6" s="1">
-        <v>-0.0023033099569645726</v>
+        <v>-0.0011495180547756781</v>
       </c>
       <c r="K6" s="1" t="b">
         <v>0</v>
@@ -2461,28 +2452,28 @@
         <v>-205</v>
       </c>
       <c r="M6" s="1">
-        <v>-0.11680055647278409</v>
+        <v>-0.05853356559781597</v>
       </c>
       <c r="N6" s="1">
-        <v>-6.166976819793657</v>
+        <v>-1.5406140764890597</v>
       </c>
       <c r="O6" s="1">
-        <v>40</v>
+        <v>48.23529411764706</v>
       </c>
       <c r="P6" s="1">
         <v>25.73060759470965</v>
       </c>
       <c r="Q6" s="1">
-        <v>38.70588235294118</v>
+        <v>40</v>
       </c>
       <c r="R6" s="1">
-        <v>33.8235294117647</v>
+        <v>36.352941176470594</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T6" s="1">
-        <v>14.74</v>
+        <v>17.27</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -2502,31 +2493,31 @@
         <v>0.49</v>
       </c>
       <c r="F7" s="2">
-        <v>0.06454625939263205</v>
+        <v>0.05291117865477987</v>
       </c>
       <c r="G7" s="2">
         <v>2.22</v>
       </c>
       <c r="H7" s="2">
-        <v>60.01</v>
+        <v>57.51</v>
       </c>
       <c r="I7" s="2">
-        <v>15.25</v>
+        <v>13.99</v>
       </c>
       <c r="J7" s="2">
-        <v>0.008839661170852395</v>
+        <v>0.008687738703164279</v>
       </c>
       <c r="K7" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L7" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="M7" s="2">
-        <v>0.11869082108794604</v>
+        <v>0.0924116369509489</v>
       </c>
       <c r="N7" s="2">
-        <v>17.38216093627935</v>
+        <v>13.553906178387443</v>
       </c>
       <c r="O7" s="2">
         <v>71.76470588235294</v>
@@ -2535,7 +2526,7 @@
         <v>19.398494070050486</v>
       </c>
       <c r="Q7" s="2">
-        <v>68.47058823529412</v>
+        <v>67.52941176470588</v>
       </c>
       <c r="R7" s="2">
         <v>58.23529411764705</v>
@@ -2564,31 +2555,31 @@
         <v>2.62</v>
       </c>
       <c r="F8" s="1">
-        <v>-0.13784138431912413</v>
+        <v>-0.12839980801241327</v>
       </c>
       <c r="G8" s="1">
         <v>0.61</v>
       </c>
       <c r="H8" s="1">
-        <v>41.32</v>
+        <v>39.73</v>
       </c>
       <c r="I8" s="1">
-        <v>6.11</v>
+        <v>5.44</v>
       </c>
       <c r="J8" s="1">
-        <v>-0.012325674328951283</v>
+        <v>-0.011886258322705729</v>
       </c>
       <c r="K8" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L8" s="1">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="M8" s="1">
-        <v>-0.15514989174631466</v>
+        <v>-0.14102700369725418</v>
       </c>
       <c r="N8" s="1">
-        <v>-10.001910347146712</v>
+        <v>-9.789957886432877</v>
       </c>
       <c r="O8" s="1">
         <v>34.11764705882353</v>
@@ -2597,16 +2588,16 @@
         <v>14.910048504309984</v>
       </c>
       <c r="Q8" s="1">
-        <v>44.94117647058824</v>
+        <v>44.11764705882353</v>
       </c>
       <c r="R8" s="1">
-        <v>37.529411764705884</v>
+        <v>37.64705882352941</v>
       </c>
       <c r="S8" s="1" t="s">
         <v>101</v>
       </c>
       <c r="T8" s="1">
-        <v>-22.23</v>
+        <v>-22.11</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -2620,25 +2611,25 @@
         <v>41.17647058823529</v>
       </c>
       <c r="D9" s="2">
-        <v>36.128205128205124</v>
+        <v>35.98290598290598</v>
       </c>
       <c r="E9" s="2">
         <v>2.97</v>
       </c>
       <c r="F9" s="2">
-        <v>0.5386383245216965</v>
+        <v>0.5400003686179459</v>
       </c>
       <c r="G9" s="2">
         <v>1.6</v>
       </c>
       <c r="H9" s="2">
-        <v>60.16</v>
+        <v>59.79</v>
       </c>
       <c r="I9" s="2">
-        <v>22.86</v>
+        <v>22.68</v>
       </c>
       <c r="J9" s="2">
-        <v>0.03540855662268145</v>
+        <v>0.03481339302119774</v>
       </c>
       <c r="K9" s="2" t="b">
         <v>0</v>
@@ -2647,28 +2638,28 @@
         <v>-113</v>
       </c>
       <c r="M9" s="2">
-        <v>0.565266797486605</v>
+        <v>0.5594268235177011</v>
       </c>
       <c r="N9" s="2">
-        <v>62.03975857614525</v>
+        <v>60.255424835062655</v>
       </c>
       <c r="O9" s="2">
-        <v>97.6470588235294</v>
+        <v>96.47058823529412</v>
       </c>
       <c r="P9" s="2">
         <v>33.227512780245505</v>
       </c>
       <c r="Q9" s="2">
-        <v>72.47058823529412</v>
+        <v>72.35294117647058</v>
       </c>
       <c r="R9" s="2">
-        <v>62.41176470588234</v>
+        <v>62.17647058823529</v>
       </c>
       <c r="S9" s="2" t="s">
         <v>102</v>
       </c>
       <c r="T9" s="2">
-        <v>35.03</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -2682,25 +2673,25 @@
         <v>58.82352941176471</v>
       </c>
       <c r="D10" s="1">
-        <v>0.754639175257732</v>
+        <v>0.7402061855670103</v>
       </c>
       <c r="E10" s="1">
         <v>0.02</v>
       </c>
       <c r="F10" s="1">
-        <v>-0.003203961991568721</v>
+        <v>0.038442925953966645</v>
       </c>
       <c r="G10" s="1">
         <v>1.42</v>
       </c>
       <c r="H10" s="1">
-        <v>50.53</v>
+        <v>51.2</v>
       </c>
       <c r="I10" s="1">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="J10" s="1">
-        <v>0.007422108192718916</v>
+        <v>0.0076398836230453055</v>
       </c>
       <c r="K10" s="1" t="b">
         <v>0</v>
@@ -2709,28 +2700,28 @@
         <v>-50</v>
       </c>
       <c r="M10" s="1">
-        <v>0.01543596908386724</v>
+        <v>0.05204144438379532</v>
       </c>
       <c r="N10" s="1">
-        <v>7.056675735871483</v>
+        <v>9.516886921672079</v>
       </c>
       <c r="O10" s="1">
-        <v>64.70588235294117</v>
+        <v>69.41176470588235</v>
       </c>
       <c r="P10" s="1">
         <v>14.568379622257217</v>
       </c>
       <c r="Q10" s="1">
-        <v>51.64705882352941</v>
+        <v>51.411764705882355</v>
       </c>
       <c r="R10" s="1">
-        <v>48.41176470588235</v>
+        <v>49.64705882352941</v>
       </c>
       <c r="S10" s="1" t="s">
         <v>103</v>
       </c>
       <c r="T10" s="1">
-        <v>12.86</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -2750,49 +2741,49 @@
         <v>2.26</v>
       </c>
       <c r="F11" s="2">
-        <v>0.31697457118717376</v>
+        <v>0.33986252389714355</v>
       </c>
       <c r="G11" s="2">
         <v>0.71</v>
       </c>
       <c r="H11" s="2">
-        <v>54.84</v>
+        <v>57.69</v>
       </c>
       <c r="I11" s="2">
-        <v>37.79</v>
+        <v>40.8</v>
       </c>
       <c r="J11" s="2">
-        <v>0.01917155768958174</v>
+        <v>0.017676865512675343</v>
       </c>
       <c r="K11" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L11" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M11" s="2">
-        <v>0.304104142587468</v>
+        <v>0.3304730706955952</v>
       </c>
       <c r="N11" s="2">
-        <v>35.92349308623154</v>
+        <v>37.36004955285205</v>
       </c>
       <c r="O11" s="2">
-        <v>88.23529411764706</v>
+        <v>89.41176470588236</v>
       </c>
       <c r="P11" s="2">
         <v>21.2185970476566</v>
       </c>
       <c r="Q11" s="2">
-        <v>63.05882352941177</v>
+        <v>62.705882352941174</v>
       </c>
       <c r="R11" s="2">
-        <v>55.70588235294118</v>
+        <v>55.82352941176471</v>
       </c>
       <c r="S11" s="2" t="s">
         <v>104</v>
       </c>
       <c r="T11" s="2">
-        <v>4.06</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -2812,19 +2803,19 @@
         <v>1.34</v>
       </c>
       <c r="F12" s="2">
-        <v>0.49338667099582123</v>
+        <v>0.487166805816495</v>
       </c>
       <c r="G12" s="2">
         <v>0.99</v>
       </c>
       <c r="H12" s="2">
-        <v>48.3</v>
+        <v>51.69</v>
       </c>
       <c r="I12" s="2">
-        <v>42.3</v>
+        <v>45.03</v>
       </c>
       <c r="J12" s="2">
-        <v>0.03728376961720136</v>
+        <v>0.03568034965683133</v>
       </c>
       <c r="K12" s="2" t="b">
         <v>0</v>
@@ -2833,28 +2824,28 @@
         <v>30</v>
       </c>
       <c r="M12" s="2">
-        <v>0.4929428631130728</v>
+        <v>0.4868430315681658</v>
       </c>
       <c r="N12" s="2">
-        <v>54.80736513879204</v>
+        <v>52.99704564010912</v>
       </c>
       <c r="O12" s="2">
-        <v>96.47058823529412</v>
+        <v>95.29411764705881</v>
       </c>
       <c r="P12" s="2">
         <v>23.557267760130397</v>
       </c>
       <c r="Q12" s="2">
-        <v>66.94117647058823</v>
+        <v>67.88235294117646</v>
       </c>
       <c r="R12" s="2">
-        <v>61.41176470588235</v>
+        <v>61.05882352941177</v>
       </c>
       <c r="S12" s="2" t="s">
         <v>105</v>
       </c>
       <c r="T12" s="2">
-        <v>8.67</v>
+        <v>8.31</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -2874,19 +2865,19 @@
         <v>0.14</v>
       </c>
       <c r="F13" s="1">
-        <v>0.3375681044161909</v>
+        <v>0.40571955570468576</v>
       </c>
       <c r="G13" s="1">
         <v>1.58</v>
       </c>
       <c r="H13" s="1">
-        <v>42.15</v>
+        <v>45.56</v>
       </c>
       <c r="I13" s="1">
-        <v>5.1</v>
+        <v>8.27</v>
       </c>
       <c r="J13" s="1">
-        <v>0.040535953358588145</v>
+        <v>0.03735223376580087</v>
       </c>
       <c r="K13" s="1" t="b">
         <v>0</v>
@@ -2895,10 +2886,10 @@
         <v>5</v>
       </c>
       <c r="M13" s="1">
-        <v>0.36330896161560244</v>
+        <v>0.4244984621077825</v>
       </c>
       <c r="N13" s="1">
-        <v>41.843974989045</v>
+        <v>46.76258869407079</v>
       </c>
       <c r="O13" s="1">
         <v>91.76470588235294</v>
@@ -2907,7 +2898,7 @@
         <v>40.13761891809808</v>
       </c>
       <c r="Q13" s="1">
-        <v>37.88235294117648</v>
+        <v>38.94117647058824</v>
       </c>
       <c r="R13" s="1">
         <v>37.235294117647065</v>
@@ -2930,117 +2921,117 @@
         <v>43.529411764705884</v>
       </c>
       <c r="D14" s="2">
-        <v>5.385542168674699</v>
+        <v>5.397590361445783</v>
       </c>
       <c r="E14" s="2">
         <v>-1.81</v>
       </c>
       <c r="F14" s="2">
-        <v>0.49612336734945917</v>
+        <v>0.46679315681479927</v>
       </c>
       <c r="G14" s="2">
         <v>0.74</v>
       </c>
       <c r="H14" s="2">
-        <v>65.9</v>
+        <v>66.41</v>
       </c>
       <c r="I14" s="2">
-        <v>84.83</v>
+        <v>84.95</v>
       </c>
       <c r="J14" s="2">
-        <v>0.034277725501204094</v>
+        <v>0.03394546424290756</v>
       </c>
       <c r="K14" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L14" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M14" s="2">
-        <v>0.48458436239799885</v>
+        <v>0.4583750263582387</v>
       </c>
       <c r="N14" s="2">
-        <v>53.97151506728463</v>
+        <v>50.15024511911641</v>
       </c>
       <c r="O14" s="2">
-        <v>95.29411764705881</v>
+        <v>92.94117647058823</v>
       </c>
       <c r="P14" s="2">
         <v>19.142997204429033</v>
       </c>
       <c r="Q14" s="2">
-        <v>68.82352941176471</v>
+        <v>69.05882352941177</v>
       </c>
       <c r="R14" s="2">
-        <v>60.411764705882355</v>
+        <v>59.70588235294118</v>
       </c>
       <c r="S14" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T14" s="2">
-        <v>4.5</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="3">
         <v>-2.12</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="3">
         <v>15.294117647058824</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="3">
         <v>18.990566037735846</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="3">
         <v>1.51</v>
       </c>
-      <c r="F15" s="1">
-        <v>-0.2297230983678799</v>
-      </c>
-      <c r="G15" s="1">
-        <v>2.25</v>
-      </c>
-      <c r="H15" s="1">
-        <v>58.03</v>
-      </c>
-      <c r="I15" s="1">
-        <v>44.57</v>
-      </c>
-      <c r="J15" s="1">
-        <v>0.021984455366145874</v>
-      </c>
-      <c r="K15" s="1" t="b">
+      <c r="F15" s="3">
+        <v>-0.25300975626125993</v>
+      </c>
+      <c r="G15" s="3">
+        <v>2.24</v>
+      </c>
+      <c r="H15" s="3">
+        <v>58.36</v>
+      </c>
+      <c r="I15" s="3">
+        <v>44.25</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0.021508543488521336</v>
+      </c>
+      <c r="K15" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L15" s="1">
-        <v>1030</v>
-      </c>
-      <c r="M15" s="1">
-        <v>-0.1742471130243205</v>
-      </c>
-      <c r="N15" s="1">
-        <v>-11.911632474947298</v>
-      </c>
-      <c r="O15" s="1">
-        <v>30.58823529411765</v>
-      </c>
-      <c r="P15" s="1">
+      <c r="L15" s="3">
+        <v>1029</v>
+      </c>
+      <c r="M15" s="3">
+        <v>-0.2128617494684324</v>
+      </c>
+      <c r="N15" s="3">
+        <v>-16.973432463550697</v>
+      </c>
+      <c r="O15" s="3">
+        <v>22.35294117647059</v>
+      </c>
+      <c r="P15" s="3">
         <v>41.90435941885386</v>
       </c>
-      <c r="Q15" s="1">
-        <v>62.235294117647065</v>
-      </c>
-      <c r="R15" s="1">
-        <v>32.529411764705884</v>
-      </c>
-      <c r="S15" s="1" t="s">
+      <c r="Q15" s="3">
+        <v>61.88235294117648</v>
+      </c>
+      <c r="R15" s="3">
+        <v>29.94117647058824</v>
+      </c>
+      <c r="S15" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="T15" s="1">
-        <v>-25.89</v>
+      <c r="T15" s="3">
+        <v>-28.47</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -3060,19 +3051,19 @@
         <v>29.77</v>
       </c>
       <c r="F16" s="3">
-        <v>-0.4035416195135191</v>
+        <v>-0.3580364758856287</v>
       </c>
       <c r="G16" s="3">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H16" s="3">
-        <v>43.29</v>
+        <v>47.86</v>
       </c>
       <c r="I16" s="3">
-        <v>-9.28</v>
+        <v>-6.49</v>
       </c>
       <c r="J16" s="3">
-        <v>-0.0037464760279519527</v>
+        <v>-0.001344131412798135</v>
       </c>
       <c r="K16" s="3" t="b">
         <v>0</v>
@@ -3081,28 +3072,28 @@
         <v>27</v>
       </c>
       <c r="M16" s="3">
-        <v>-0.36759318101089256</v>
+        <v>-0.33213453601928833</v>
       </c>
       <c r="N16" s="3">
-        <v>-31.2462392736045</v>
+        <v>-28.900711118636295</v>
       </c>
       <c r="O16" s="3">
-        <v>4.705882352941177</v>
+        <v>7.0588235294117645</v>
       </c>
       <c r="P16" s="3">
         <v>40.1905830435425</v>
       </c>
       <c r="Q16" s="3">
-        <v>35.76470588235294</v>
+        <v>37.529411764705884</v>
       </c>
       <c r="R16" s="3">
-        <v>14.941176470588236</v>
+        <v>15.882352941176471</v>
       </c>
       <c r="S16" s="3" t="s">
         <v>108</v>
       </c>
       <c r="T16" s="3">
-        <v>-28.29</v>
+        <v>-27.35</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -3122,19 +3113,19 @@
         <v>-1.63</v>
       </c>
       <c r="F17" s="1">
-        <v>-0.12896663603686004</v>
+        <v>-0.04096494134062771</v>
       </c>
       <c r="G17" s="1">
         <v>1.76</v>
       </c>
       <c r="H17" s="1">
-        <v>46.89</v>
+        <v>51.76</v>
       </c>
       <c r="I17" s="1">
-        <v>1.58</v>
+        <v>4.79</v>
       </c>
       <c r="J17" s="1">
-        <v>0.011293607413839021</v>
+        <v>0.01148692028252879</v>
       </c>
       <c r="K17" s="1" t="b">
         <v>0</v>
@@ -3143,28 +3134,28 @@
         <v>31</v>
       </c>
       <c r="M17" s="1">
-        <v>-0.09523723694797592</v>
+        <v>-0.016358098467604387</v>
       </c>
       <c r="N17" s="1">
-        <v>-4.010644867312843</v>
+        <v>2.6769326365320976</v>
       </c>
       <c r="O17" s="1">
-        <v>47.05882352941176</v>
+        <v>54.11764705882353</v>
       </c>
       <c r="P17" s="1">
         <v>24.80206596461608</v>
       </c>
       <c r="Q17" s="1">
-        <v>42</v>
+        <v>44.470588235294116</v>
       </c>
       <c r="R17" s="1">
-        <v>32.58823529411765</v>
+        <v>34.705882352941174</v>
       </c>
       <c r="S17" s="1" t="s">
         <v>102</v>
       </c>
       <c r="T17" s="1">
-        <v>-0.58</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -3184,31 +3175,31 @@
         <v>10.92</v>
       </c>
       <c r="F18" s="3">
-        <v>-0.7199716686393888</v>
+        <v>-0.7151231332853476</v>
       </c>
       <c r="G18" s="3">
         <v>1.13</v>
       </c>
       <c r="H18" s="3">
-        <v>21.47</v>
+        <v>21.39</v>
       </c>
       <c r="I18" s="3">
-        <v>-56.54</v>
+        <v>-56.52</v>
       </c>
       <c r="J18" s="3">
-        <v>-0.0854598461453549</v>
+        <v>-0.08800476728131815</v>
       </c>
       <c r="K18" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" s="3">
         <v>31</v>
       </c>
       <c r="M18" s="3">
-        <v>-0.7142021661636586</v>
+        <v>-0.7109140680570672</v>
       </c>
       <c r="N18" s="3">
-        <v>-65.90713778888112</v>
+        <v>-66.77866432241419</v>
       </c>
       <c r="O18" s="3">
         <v>1.1764705882352942</v>
@@ -3217,7 +3208,7 @@
         <v>68.77035731645671</v>
       </c>
       <c r="Q18" s="3">
-        <v>39.764705882352935</v>
+        <v>39.647058823529406</v>
       </c>
       <c r="R18" s="3">
         <v>23.11764705882353</v>
@@ -3246,19 +3237,19 @@
         <v>3.12</v>
       </c>
       <c r="F19" s="2">
-        <v>0.04092667623138403</v>
+        <v>0.03729414474307281</v>
       </c>
       <c r="G19" s="2">
         <v>0.09</v>
       </c>
       <c r="H19" s="2">
-        <v>61.5</v>
+        <v>60.83</v>
       </c>
       <c r="I19" s="2">
-        <v>16.92</v>
+        <v>16.55</v>
       </c>
       <c r="J19" s="2">
-        <v>0.011604867955526245</v>
+        <v>0.012608276643978641</v>
       </c>
       <c r="K19" s="2" t="b">
         <v>1</v>
@@ -3267,28 +3258,28 @@
         <v>-60</v>
       </c>
       <c r="M19" s="2">
-        <v>0.0005401589012727914</v>
+        <v>0.007830688145110676</v>
       </c>
       <c r="N19" s="2">
-        <v>5.567094717612036</v>
+        <v>5.095811297803598</v>
       </c>
       <c r="O19" s="2">
-        <v>62.35294117647059</v>
+        <v>61.1764705882353</v>
       </c>
       <c r="P19" s="2">
         <v>11.392700631623551</v>
       </c>
       <c r="Q19" s="2">
-        <v>65.6470588235294</v>
+        <v>65.41176470588235</v>
       </c>
       <c r="R19" s="2">
-        <v>54.35294117647059</v>
+        <v>54</v>
       </c>
       <c r="S19" s="2" t="s">
         <v>110</v>
       </c>
       <c r="T19" s="2">
-        <v>5.94</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -3308,19 +3299,19 @@
         <v>-5.75</v>
       </c>
       <c r="F20" s="2">
-        <v>0.2207670199873413</v>
+        <v>0.24730738062212787</v>
       </c>
       <c r="G20" s="2">
         <v>1.07</v>
       </c>
       <c r="H20" s="2">
-        <v>53.46</v>
+        <v>55.03</v>
       </c>
       <c r="I20" s="2">
-        <v>23.21</v>
+        <v>23.69</v>
       </c>
       <c r="J20" s="2">
-        <v>0.023139935792158547</v>
+        <v>0.022787556577677323</v>
       </c>
       <c r="K20" s="2" t="b">
         <v>0</v>
@@ -3329,13 +3320,13 @@
         <v>8</v>
       </c>
       <c r="M20" s="2">
-        <v>0.22387367516658063</v>
+        <v>0.24957380036043264</v>
       </c>
       <c r="N20" s="2">
-        <v>27.900446344142804</v>
+        <v>29.270122519335807</v>
       </c>
       <c r="O20" s="2">
-        <v>84.70588235294117</v>
+        <v>82.35294117647058</v>
       </c>
       <c r="P20" s="2">
         <v>15.052477440996265</v>
@@ -3344,13 +3335,13 @@
         <v>63.05882352941176</v>
       </c>
       <c r="R20" s="2">
-        <v>57.82352941176471</v>
+        <v>57</v>
       </c>
       <c r="S20" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T20" s="2">
-        <v>21.97</v>
+        <v>21.15</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -3370,31 +3361,31 @@
         <v>-3.44</v>
       </c>
       <c r="F21" s="3">
-        <v>-0.44410545367594273</v>
+        <v>-0.41742333012359983</v>
       </c>
       <c r="G21" s="3">
         <v>1.64</v>
       </c>
       <c r="H21" s="3">
-        <v>28.22</v>
+        <v>34.11</v>
       </c>
       <c r="I21" s="3">
-        <v>-25.02</v>
+        <v>-22.57</v>
       </c>
       <c r="J21" s="3">
-        <v>-0.026550007738637776</v>
+        <v>-0.02614283677050927</v>
       </c>
       <c r="K21" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="3">
         <v>55</v>
       </c>
       <c r="M21" s="3">
-        <v>-0.4157017491800403</v>
+        <v>-0.39670177823052755</v>
       </c>
       <c r="N21" s="3">
-        <v>-36.05709609051928</v>
+        <v>-35.357435339760215</v>
       </c>
       <c r="O21" s="3">
         <v>3.5294117647058822</v>
@@ -3403,16 +3394,16 @@
         <v>57.26531305832072</v>
       </c>
       <c r="Q21" s="3">
-        <v>34.94117647058823</v>
+        <v>35.411764705882355</v>
       </c>
       <c r="R21" s="3">
-        <v>18.588235294117645</v>
+        <v>18.705882352941174</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>111</v>
       </c>
       <c r="T21" s="3">
-        <v>-32.63</v>
+        <v>-32.51</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -3432,19 +3423,19 @@
         <v>-0.25</v>
       </c>
       <c r="F22" s="1">
-        <v>-0.22042609574798047</v>
+        <v>-0.20484350967990472</v>
       </c>
       <c r="G22" s="1">
         <v>1.38</v>
       </c>
       <c r="H22" s="1">
-        <v>39.89</v>
+        <v>41.92</v>
       </c>
       <c r="I22" s="1">
-        <v>-1.98</v>
+        <v>-1.37</v>
       </c>
       <c r="J22" s="1">
-        <v>-0.009095137148808514</v>
+        <v>-0.008490465071306451</v>
       </c>
       <c r="K22" s="1" t="b">
         <v>0</v>
@@ -3453,28 +3444,28 @@
         <v>244</v>
       </c>
       <c r="M22" s="1">
-        <v>-0.20356139620353841</v>
+        <v>-0.19254008824339308</v>
       </c>
       <c r="N22" s="1">
-        <v>-14.843060792869089</v>
+        <v>-14.941266341046767</v>
       </c>
       <c r="O22" s="1">
-        <v>20</v>
+        <v>25.882352941176475</v>
       </c>
       <c r="P22" s="1">
         <v>19.455960650079966</v>
       </c>
       <c r="Q22" s="1">
-        <v>43.76470588235294</v>
+        <v>45.05882352941176</v>
       </c>
       <c r="R22" s="1">
-        <v>32.41176470588235</v>
+        <v>34.588235294117645</v>
       </c>
       <c r="S22" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T22" s="1">
-        <v>-20.7</v>
+        <v>-18.52</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -3494,49 +3485,49 @@
         <v>0.1</v>
       </c>
       <c r="F23" s="2">
-        <v>0.20798030286428826</v>
+        <v>0.2622833044812256</v>
       </c>
       <c r="G23" s="2">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="H23" s="2">
-        <v>61.35</v>
+        <v>63.76</v>
       </c>
       <c r="I23" s="2">
-        <v>14.51</v>
+        <v>17.27</v>
       </c>
       <c r="J23" s="2">
-        <v>0.013663813334479693</v>
+        <v>0.014056288471075552</v>
       </c>
       <c r="K23" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L23" s="2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M23" s="2">
-        <v>0.21685646051925778</v>
+        <v>0.26843501519948143</v>
       </c>
       <c r="N23" s="2">
-        <v>27.19872487941054</v>
+        <v>31.156244003240673</v>
       </c>
       <c r="O23" s="2">
-        <v>83.52941176470588</v>
+        <v>85.88235294117646</v>
       </c>
       <c r="P23" s="2">
         <v>20.883293768118005</v>
       </c>
       <c r="Q23" s="2">
-        <v>63.529411764705884</v>
+        <v>64.8235294117647</v>
       </c>
       <c r="R23" s="2">
-        <v>56.11764705882352</v>
+        <v>57.05882352941176</v>
       </c>
       <c r="S23" s="2" t="s">
         <v>110</v>
       </c>
       <c r="T23" s="2">
-        <v>20.32</v>
+        <v>21.27</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -3556,19 +3547,19 @@
         <v>1.53</v>
       </c>
       <c r="F24" s="1">
-        <v>0.5263220108935313</v>
+        <v>0.6529102365762046</v>
       </c>
       <c r="G24" s="1">
         <v>3.57</v>
       </c>
       <c r="H24" s="1">
-        <v>63.13</v>
+        <v>60.48</v>
       </c>
       <c r="I24" s="1">
-        <v>16.52</v>
+        <v>13.84</v>
       </c>
       <c r="J24" s="1">
-        <v>0.05892829790776801</v>
+        <v>0.05491884583483637</v>
       </c>
       <c r="K24" s="1" t="b">
         <v>0</v>
@@ -3577,10 +3568,10 @@
         <v>-69</v>
       </c>
       <c r="M24" s="1">
-        <v>0.6403806367598894</v>
+        <v>0.736120218396823</v>
       </c>
       <c r="N24" s="1">
-        <v>69.55114250347368</v>
+        <v>77.92476432297484</v>
       </c>
       <c r="O24" s="1">
         <v>100</v>
@@ -3589,7 +3580,7 @@
         <v>57.99224429263358</v>
       </c>
       <c r="Q24" s="1">
-        <v>52.94117647058824</v>
+        <v>52</v>
       </c>
       <c r="R24" s="1">
         <v>43.64705882352941</v>
@@ -3618,49 +3609,49 @@
         <v>15.51</v>
       </c>
       <c r="F25" s="3">
-        <v>-0.344977334590094</v>
+        <v>-0.3138054903259755</v>
       </c>
       <c r="G25" s="3">
         <v>2.37</v>
       </c>
       <c r="H25" s="3">
-        <v>40.74</v>
+        <v>39.56</v>
       </c>
       <c r="I25" s="3">
-        <v>-34.13</v>
+        <v>-35.09</v>
       </c>
       <c r="J25" s="3">
-        <v>0.0037631449726765603</v>
+        <v>0.0021225341700170357</v>
       </c>
       <c r="K25" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L25" s="3">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M25" s="3">
-        <v>-0.2841756546535529</v>
+        <v>-0.26944841830486765</v>
       </c>
       <c r="N25" s="3">
-        <v>-22.904486637870537</v>
+        <v>-22.632099347194224</v>
       </c>
       <c r="O25" s="3">
-        <v>11.76470588235294</v>
+        <v>15.294117647058824</v>
       </c>
       <c r="P25" s="3">
         <v>45.59139601172712</v>
       </c>
       <c r="Q25" s="3">
-        <v>18.941176470588236</v>
+        <v>17.764705882352942</v>
       </c>
       <c r="R25" s="3">
-        <v>4.411764705882353</v>
+        <v>5.23529411764706</v>
       </c>
       <c r="S25" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T25" s="3">
-        <v>3.01</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -3680,19 +3671,19 @@
         <v>-0.83</v>
       </c>
       <c r="F26" s="3">
-        <v>-0.3324752216676616</v>
+        <v>-0.2950920109155807</v>
       </c>
       <c r="G26" s="3">
         <v>3.36</v>
       </c>
       <c r="H26" s="3">
-        <v>61.25</v>
+        <v>58.43</v>
       </c>
       <c r="I26" s="3">
-        <v>3.37</v>
+        <v>1.28</v>
       </c>
       <c r="J26" s="3">
-        <v>0.016711645651632814</v>
+        <v>0.020676090076644785</v>
       </c>
       <c r="K26" s="3" t="b">
         <v>1</v>
@@ -3701,28 +3692,28 @@
         <v>160</v>
       </c>
       <c r="M26" s="3">
-        <v>-0.22773656133902143</v>
+        <v>-0.21868128830987665</v>
       </c>
       <c r="N26" s="3">
-        <v>-17.260577306417392</v>
+        <v>-17.555386347695126</v>
       </c>
       <c r="O26" s="3">
-        <v>16.470588235294116</v>
+        <v>20</v>
       </c>
       <c r="P26" s="3">
         <v>55.61259899184437</v>
       </c>
       <c r="Q26" s="3">
-        <v>36.94117647058824</v>
+        <v>37.294117647058826</v>
       </c>
       <c r="R26" s="3">
-        <v>9.88235294117647</v>
+        <v>11.882352941176473</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T26" s="3">
-        <v>-18.96</v>
+        <v>-16.96</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -3742,19 +3733,19 @@
         <v>6.8</v>
       </c>
       <c r="F27" s="3">
-        <v>-0.42080752572294094</v>
+        <v>-0.42534931778148966</v>
       </c>
       <c r="G27" s="3">
         <v>2.66</v>
       </c>
       <c r="H27" s="3">
-        <v>36.73</v>
+        <v>33.98</v>
       </c>
       <c r="I27" s="3">
-        <v>-36.78</v>
+        <v>-37.9</v>
       </c>
       <c r="J27" s="3">
-        <v>-0.017289796069473878</v>
+        <v>-0.018554309416669447</v>
       </c>
       <c r="K27" s="3" t="b">
         <v>0</v>
@@ -3763,28 +3754,28 @@
         <v>7</v>
       </c>
       <c r="M27" s="3">
-        <v>-0.34713541718669405</v>
+        <v>-0.37160279255883344</v>
       </c>
       <c r="N27" s="3">
-        <v>-29.20046289118466</v>
+        <v>-32.8475367725908</v>
       </c>
       <c r="O27" s="3">
-        <v>5.88235294117647</v>
+        <v>4.705882352941177</v>
       </c>
       <c r="P27" s="3">
-        <v>50.56910707785277</v>
+        <v>51.30081562413137</v>
       </c>
       <c r="Q27" s="3">
-        <v>13.294117647058824</v>
+        <v>12.000000000000002</v>
       </c>
       <c r="R27" s="3">
-        <v>1.2352941176470562</v>
+        <v>0.7647058823529402</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T27" s="3">
-        <v>-14.92</v>
+        <v>-15.39</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -3804,19 +3795,19 @@
         <v>2.08</v>
       </c>
       <c r="F28" s="1">
-        <v>-0.04432025866489178</v>
+        <v>-0.0468567537543329</v>
       </c>
       <c r="G28" s="1">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="H28" s="1">
-        <v>41.81</v>
+        <v>39.64</v>
       </c>
       <c r="I28" s="1">
-        <v>-16.37</v>
+        <v>-18.21</v>
       </c>
       <c r="J28" s="1">
-        <v>0.01744270357842766</v>
+        <v>0.012351029523712843</v>
       </c>
       <c r="K28" s="1" t="b">
         <v>0</v>
@@ -3825,28 +3816,28 @@
         <v>3</v>
       </c>
       <c r="M28" s="1">
-        <v>0.05598032283626364</v>
+        <v>0.02664000061640781</v>
       </c>
       <c r="N28" s="1">
-        <v>11.11111111111111</v>
+        <v>6.976742544933333</v>
       </c>
       <c r="O28" s="1">
-        <v>68.23529411764706</v>
+        <v>65.88235294117646</v>
       </c>
       <c r="P28" s="1">
         <v>35.08771990976345</v>
       </c>
       <c r="Q28" s="1">
-        <v>46.11764705882353</v>
+        <v>41.88235294117647</v>
       </c>
       <c r="R28" s="1">
-        <v>41.88235294117648</v>
+        <v>39.882352941176464</v>
       </c>
       <c r="S28" s="1" t="s">
         <v>112</v>
       </c>
       <c r="T28" s="1">
-        <v>24.87</v>
+        <v>22.87</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -3860,55 +3851,55 @@
         <v>36.470588235294116</v>
       </c>
       <c r="D29" s="1">
-        <v>81.95744680851065</v>
+        <v>81.97872340425532</v>
       </c>
       <c r="E29" s="1">
         <v>-4.82</v>
       </c>
       <c r="F29" s="1">
-        <v>-0.23840133577486028</v>
+        <v>-0.19884976926297254</v>
       </c>
       <c r="G29" s="1">
         <v>2.33</v>
       </c>
       <c r="H29" s="1">
-        <v>36.93</v>
+        <v>35.47</v>
       </c>
       <c r="I29" s="1">
-        <v>-16.53</v>
+        <v>-17.22</v>
       </c>
       <c r="J29" s="1">
-        <v>-0.006934547302196772</v>
+        <v>-0.007089389914831643</v>
       </c>
       <c r="K29" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M29" s="1">
-        <v>-0.17937488736931306</v>
+        <v>-0.15578779423518174</v>
       </c>
       <c r="N29" s="1">
-        <v>-12.424409909446556</v>
+        <v>-11.26603694022563</v>
       </c>
       <c r="O29" s="1">
-        <v>25.882352941176475</v>
+        <v>32.94117647058823</v>
       </c>
       <c r="P29" s="1">
         <v>18.79659508828292</v>
       </c>
       <c r="Q29" s="1">
-        <v>46.23529411764706</v>
+        <v>45.294117647058826</v>
       </c>
       <c r="R29" s="1">
-        <v>38.41176470588235</v>
+        <v>40.529411764705884</v>
       </c>
       <c r="S29" s="1" t="s">
         <v>110</v>
       </c>
       <c r="T29" s="1">
-        <v>-1.83</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -3922,55 +3913,55 @@
         <v>47.05882352941176</v>
       </c>
       <c r="D30" s="1">
-        <v>223.06363636363636</v>
+        <v>221.11363636363635</v>
       </c>
       <c r="E30" s="1">
         <v>1.26</v>
       </c>
       <c r="F30" s="1">
-        <v>-0.20780353353649011</v>
+        <v>-0.18421946378043325</v>
       </c>
       <c r="G30" s="1">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="H30" s="1">
-        <v>27.62</v>
+        <v>39.64</v>
       </c>
       <c r="I30" s="1">
-        <v>-16.49</v>
+        <v>-12.48</v>
       </c>
       <c r="J30" s="1">
-        <v>-0.009470704473733419</v>
+        <v>-0.009858558011301964</v>
       </c>
       <c r="K30" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L30" s="1">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M30" s="1">
-        <v>-0.19626452858502974</v>
+        <v>-0.1761251075722019</v>
       </c>
       <c r="N30" s="1">
-        <v>-14.11337403101822</v>
+        <v>-13.29976827392765</v>
       </c>
       <c r="O30" s="1">
-        <v>21.176470588235293</v>
+        <v>28.235294117647058</v>
       </c>
       <c r="P30" s="1">
         <v>23.36242946298323</v>
       </c>
       <c r="Q30" s="1">
-        <v>48.11764705882352</v>
+        <v>50.23529411764705</v>
       </c>
       <c r="R30" s="1">
-        <v>38.76470588235294</v>
+        <v>40.76470588235294</v>
       </c>
       <c r="S30" s="1" t="s">
         <v>111</v>
       </c>
       <c r="T30" s="1">
-        <v>-9.71</v>
+        <v>-7.71</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -3990,49 +3981,49 @@
         <v>0.38</v>
       </c>
       <c r="F31" s="1">
-        <v>-0.13742083443303227</v>
+        <v>-0.11830508954472968</v>
       </c>
       <c r="G31" s="1">
         <v>1.47</v>
       </c>
       <c r="H31" s="1">
-        <v>42.88</v>
+        <v>46.6</v>
       </c>
       <c r="I31" s="1">
-        <v>-4.61</v>
+        <v>-3.14</v>
       </c>
       <c r="J31" s="1">
-        <v>-0.007411432554442802</v>
+        <v>-0.007606595352030266</v>
       </c>
       <c r="K31" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L31" s="1">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M31" s="1">
-        <v>-0.11656186394385393</v>
+        <v>-0.10308769987325472</v>
       </c>
       <c r="N31" s="1">
-        <v>-6.143107566900642</v>
+        <v>-5.996027504032925</v>
       </c>
       <c r="O31" s="1">
-        <v>41.17647058823529</v>
+        <v>38.82352941176471</v>
       </c>
       <c r="P31" s="1">
         <v>29.54918623383928</v>
       </c>
       <c r="Q31" s="1">
-        <v>51.99999999999999</v>
+        <v>52.23529411764705</v>
       </c>
       <c r="R31" s="1">
-        <v>41.705882352941174</v>
+        <v>40.705882352941174</v>
       </c>
       <c r="S31" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T31" s="1">
-        <v>-6.34</v>
+        <v>-7.34</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -4052,19 +4043,19 @@
         <v>3.6</v>
       </c>
       <c r="F32" s="3">
-        <v>-0.20281341884137505</v>
+        <v>-0.2003772243165152</v>
       </c>
       <c r="G32" s="3">
         <v>1.62</v>
       </c>
       <c r="H32" s="3">
-        <v>40.74</v>
+        <v>43.36</v>
       </c>
       <c r="I32" s="3">
-        <v>-8.5</v>
+        <v>-7.29</v>
       </c>
       <c r="J32" s="3">
-        <v>-0.014173547534774721</v>
+        <v>-0.014335914008124527</v>
       </c>
       <c r="K32" s="3" t="b">
         <v>0</v>
@@ -4073,28 +4064,28 @@
         <v>21</v>
       </c>
       <c r="M32" s="3">
-        <v>-0.1752973301109696</v>
+        <v>-0.18030322092010143</v>
       </c>
       <c r="N32" s="3">
-        <v>-12.01665418361221</v>
+        <v>-13.717579608717607</v>
       </c>
       <c r="O32" s="3">
-        <v>28.235294117647058</v>
+        <v>27.058823529411764</v>
       </c>
       <c r="P32" s="3">
         <v>26.613703173358488</v>
       </c>
       <c r="Q32" s="3">
-        <v>33.64705882352941</v>
+        <v>34.352941176470594</v>
       </c>
       <c r="R32" s="3">
-        <v>25</v>
+        <v>24.764705882352942</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>109</v>
       </c>
       <c r="T32" s="3">
-        <v>-6.89</v>
+        <v>-7.13</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -4114,49 +4105,49 @@
         <v>0.23</v>
       </c>
       <c r="F33" s="2">
-        <v>0.32204111499466265</v>
+        <v>0.31806571157811336</v>
       </c>
       <c r="G33" s="2">
         <v>1.1</v>
       </c>
       <c r="H33" s="2">
-        <v>57.63</v>
+        <v>57.83</v>
       </c>
       <c r="I33" s="2">
-        <v>17.47</v>
+        <v>17.52</v>
       </c>
       <c r="J33" s="2">
-        <v>0.02378702901288323</v>
+        <v>0.02366402055445795</v>
       </c>
       <c r="K33" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L33" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M33" s="2">
-        <v>0.3264791938221474</v>
+        <v>0.3213034540614059</v>
       </c>
       <c r="N33" s="2">
-        <v>38.16099820969948</v>
+        <v>36.44308788943313</v>
       </c>
       <c r="O33" s="2">
-        <v>89.41176470588236</v>
+        <v>88.23529411764706</v>
       </c>
       <c r="P33" s="2">
         <v>23.38443607454554</v>
       </c>
       <c r="Q33" s="2">
-        <v>69.1764705882353</v>
+        <v>68.58823529411764</v>
       </c>
       <c r="R33" s="2">
-        <v>60.882352941176485</v>
+        <v>60.29411764705883</v>
       </c>
       <c r="S33" s="2" t="s">
         <v>110</v>
       </c>
       <c r="T33" s="2">
-        <v>25.09</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -4170,55 +4161,55 @@
         <v>92.94117647058823</v>
       </c>
       <c r="D34" s="1">
-        <v>-2.3294826720241084</v>
+        <v>-2.3284781516825714</v>
       </c>
       <c r="E34" s="1">
         <v>2.36</v>
       </c>
       <c r="F34" s="1">
-        <v>-0.09527217070667938</v>
+        <v>-0.0959573578990647</v>
       </c>
       <c r="G34" s="1">
         <v>1.21</v>
       </c>
       <c r="H34" s="1">
-        <v>47.99</v>
+        <v>50.34</v>
       </c>
       <c r="I34" s="1">
-        <v>0.97</v>
+        <v>1.7</v>
       </c>
       <c r="J34" s="1">
-        <v>-0.003828868714196778</v>
+        <v>-0.004391819270221309</v>
       </c>
       <c r="K34" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L34" s="1">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="M34" s="1">
-        <v>-0.0859522051689614</v>
+        <v>-0.08915809868415037</v>
       </c>
       <c r="N34" s="1">
-        <v>-3.082141689411388</v>
+        <v>-4.603067385122499</v>
       </c>
       <c r="O34" s="1">
-        <v>49.411764705882355</v>
+        <v>42.35294117647059</v>
       </c>
       <c r="P34" s="1">
         <v>21.09433056126816</v>
       </c>
       <c r="Q34" s="1">
-        <v>46.8235294117647</v>
+        <v>47.17647058823529</v>
       </c>
       <c r="R34" s="1">
-        <v>39.352941176470594</v>
+        <v>37.11764705882353</v>
       </c>
       <c r="S34" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T34" s="1">
-        <v>-7.48</v>
+        <v>-9.71</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -4232,37 +4223,37 @@
         <v>87.05882352941177</v>
       </c>
       <c r="D35" s="1">
-        <v>-0.4535147392290249</v>
+        <v>-0.4614512471655329</v>
       </c>
       <c r="E35" s="1">
         <v>-0.5</v>
       </c>
       <c r="F35" s="1">
-        <v>-0.058965137241281246</v>
+        <v>-0.022017981887703778</v>
       </c>
       <c r="G35" s="1">
         <v>0.95</v>
       </c>
       <c r="H35" s="1">
-        <v>32.26</v>
+        <v>41.03</v>
       </c>
       <c r="I35" s="1">
-        <v>-17.76</v>
+        <v>-14.97</v>
       </c>
       <c r="J35" s="1">
-        <v>-0.0066453260547554615</v>
+        <v>-0.007511586751529567</v>
       </c>
       <c r="K35" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L35" s="1">
-        <v>-57</v>
+        <v>-58</v>
       </c>
       <c r="M35" s="1">
-        <v>-0.061184176655023625</v>
+        <v>-0.023636853129350044</v>
       </c>
       <c r="N35" s="1">
-        <v>-0.605338838017608</v>
+        <v>1.9490571703575403</v>
       </c>
       <c r="O35" s="1">
         <v>51.76470588235295</v>
@@ -4271,16 +4262,16 @@
         <v>20.53422985929523</v>
       </c>
       <c r="Q35" s="1">
-        <v>40.117647058823536</v>
+        <v>41.52941176470588</v>
       </c>
       <c r="R35" s="1">
-        <v>41.05882352941177</v>
+        <v>40.70588235294118</v>
       </c>
       <c r="S35" s="1" t="s">
         <v>101</v>
       </c>
       <c r="T35" s="1">
-        <v>18.56</v>
+        <v>18.21</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -4300,49 +4291,49 @@
         <v>-1.31</v>
       </c>
       <c r="F36" s="1">
-        <v>-0.0561761137477762</v>
+        <v>0.018252782330044556</v>
       </c>
       <c r="G36" s="1">
         <v>1.12</v>
       </c>
       <c r="H36" s="1">
-        <v>41.55</v>
+        <v>46.63</v>
       </c>
       <c r="I36" s="1">
-        <v>-10.12</v>
+        <v>-8.06</v>
       </c>
       <c r="J36" s="1">
-        <v>0.0026815672448318385</v>
+        <v>0.003062740100417369</v>
       </c>
       <c r="K36" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L36" s="1">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="M36" s="1">
-        <v>-0.05085041915479449</v>
+        <v>0.02213807330999562</v>
       </c>
       <c r="N36" s="1">
-        <v>0.4280369120052986</v>
+        <v>6.526549814292111</v>
       </c>
       <c r="O36" s="1">
-        <v>52.94117647058824</v>
+        <v>63.52941176470588</v>
       </c>
       <c r="P36" s="1">
         <v>26.730280409441182</v>
       </c>
       <c r="Q36" s="1">
-        <v>47.41176470588236</v>
+        <v>50.117647058823536</v>
       </c>
       <c r="R36" s="1">
-        <v>41.70588235294119</v>
+        <v>45.35294117647059</v>
       </c>
       <c r="S36" s="1" t="s">
         <v>108</v>
       </c>
       <c r="T36" s="1">
-        <v>14.75</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -4362,49 +4353,49 @@
         <v>-3.28</v>
       </c>
       <c r="F37" s="1">
-        <v>0.15551599057812637</v>
+        <v>0.1958383693213001</v>
       </c>
       <c r="G37" s="1">
         <v>1.28</v>
       </c>
       <c r="H37" s="1">
-        <v>48.2</v>
+        <v>47.47</v>
       </c>
       <c r="I37" s="1">
-        <v>7.39</v>
+        <v>7.1</v>
       </c>
       <c r="J37" s="1">
-        <v>0.0012315706264228127</v>
+        <v>-0.0016484605143570652</v>
       </c>
       <c r="K37" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L37" s="1">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="M37" s="1">
-        <v>0.1679426112950837</v>
+        <v>0.20490404827451925</v>
       </c>
       <c r="N37" s="1">
-        <v>22.307339956993115</v>
+        <v>24.803147310744457</v>
       </c>
       <c r="O37" s="1">
-        <v>80</v>
+        <v>81.17647058823529</v>
       </c>
       <c r="P37" s="1">
         <v>19.230003461162156</v>
       </c>
       <c r="Q37" s="1">
-        <v>50.00000000000001</v>
+        <v>48.23529411764706</v>
       </c>
       <c r="R37" s="1">
-        <v>49.99999999999999</v>
+        <v>49.882352941176464</v>
       </c>
       <c r="S37" s="1" t="s">
         <v>111</v>
       </c>
       <c r="T37" s="1">
-        <v>20.18</v>
+        <v>20.07</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -4424,31 +4415,31 @@
         <v>3.02</v>
       </c>
       <c r="F38" s="2">
-        <v>0.33185532202529944</v>
+        <v>0.3275493044264137</v>
       </c>
       <c r="G38" s="2">
         <v>1.2</v>
       </c>
       <c r="H38" s="2">
-        <v>64.84</v>
+        <v>66.23</v>
       </c>
       <c r="I38" s="2">
-        <v>71.37</v>
+        <v>73.15</v>
       </c>
       <c r="J38" s="2">
-        <v>0.02605031747846348</v>
+        <v>0.02609621740645859</v>
       </c>
       <c r="K38" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L38" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M38" s="2">
-        <v>0.34073147968026896</v>
+        <v>0.33402478939299884</v>
       </c>
       <c r="N38" s="2">
-        <v>39.586226795511635</v>
+        <v>37.71522142259243</v>
       </c>
       <c r="O38" s="2">
         <v>90.58823529411765</v>
@@ -4457,7 +4448,7 @@
         <v>17.802507034008837</v>
       </c>
       <c r="Q38" s="2">
-        <v>76.47058823529412</v>
+        <v>76.58823529411765</v>
       </c>
       <c r="R38" s="2">
         <v>66.23529411764706</v>
@@ -4486,19 +4477,19 @@
         <v>-1.29</v>
       </c>
       <c r="F39" s="1">
-        <v>-0.1668324988491925</v>
+        <v>-0.16165159328638296</v>
       </c>
       <c r="G39" s="1">
         <v>1.13</v>
       </c>
       <c r="H39" s="1">
-        <v>32.69</v>
+        <v>38.56</v>
       </c>
       <c r="I39" s="1">
-        <v>-9.84</v>
+        <v>-8.06</v>
       </c>
       <c r="J39" s="1">
-        <v>-0.008914014739852531</v>
+        <v>-0.009836967870876337</v>
       </c>
       <c r="K39" s="1" t="b">
         <v>0</v>
@@ -4507,28 +4498,28 @@
         <v>-1</v>
       </c>
       <c r="M39" s="1">
-        <v>-0.16106299637346233</v>
+        <v>-0.15744252805810266</v>
       </c>
       <c r="N39" s="1">
-        <v>-10.593220809861478</v>
+        <v>-11.431510322517724</v>
       </c>
       <c r="O39" s="1">
-        <v>32.94117647058823</v>
+        <v>31.76470588235294</v>
       </c>
       <c r="P39" s="1">
         <v>30.28933322215756</v>
       </c>
       <c r="Q39" s="1">
-        <v>39.88235294117647</v>
+        <v>40.470588235294116</v>
       </c>
       <c r="R39" s="1">
-        <v>31.882352941176478</v>
+        <v>31.294117647058833</v>
       </c>
       <c r="S39" s="1" t="s">
         <v>112</v>
       </c>
       <c r="T39" s="1">
-        <v>6.09</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -4548,19 +4539,19 @@
         <v>4.41</v>
       </c>
       <c r="F40" s="1">
-        <v>0.4782775167853881</v>
+        <v>0.49006731784189644</v>
       </c>
       <c r="G40" s="1">
         <v>0.68</v>
       </c>
       <c r="H40" s="1">
-        <v>54.68</v>
+        <v>52.43</v>
       </c>
       <c r="I40" s="1">
-        <v>8.93</v>
+        <v>6.26</v>
       </c>
       <c r="J40" s="1">
-        <v>0.05316555771573186</v>
+        <v>0.04913823872985493</v>
       </c>
       <c r="K40" s="1" t="b">
         <v>0</v>
@@ -4569,10 +4560,10 @@
         <v>-21</v>
       </c>
       <c r="M40" s="1">
-        <v>0.46407566453743687</v>
+        <v>0.4797065418953603</v>
       </c>
       <c r="N40" s="1">
-        <v>51.92064528122845</v>
+        <v>52.28339667282857</v>
       </c>
       <c r="O40" s="1">
         <v>94.11764705882352</v>
@@ -4581,16 +4572,16 @@
         <v>51.940889187924654</v>
       </c>
       <c r="Q40" s="1">
-        <v>55.411764705882355</v>
+        <v>54.588235294117645</v>
       </c>
       <c r="R40" s="1">
-        <v>47.47058823529412</v>
+        <v>47.76470588235294</v>
       </c>
       <c r="S40" s="1" t="s">
         <v>113</v>
       </c>
       <c r="T40" s="1">
-        <v>38.99</v>
+        <v>39.29</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -4604,25 +4595,25 @@
         <v>4.705882352941177</v>
       </c>
       <c r="D41" s="3">
-        <v>1.5553319919517103</v>
+        <v>1.4768611670020122</v>
       </c>
       <c r="E41" s="3">
         <v>-0.03</v>
       </c>
       <c r="F41" s="3">
-        <v>-0.12513552416639212</v>
+        <v>-0.26854944607689996</v>
       </c>
       <c r="G41" s="3">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="H41" s="3">
-        <v>42.96</v>
+        <v>34.84</v>
       </c>
       <c r="I41" s="3">
-        <v>-12.45</v>
+        <v>-17.49</v>
       </c>
       <c r="J41" s="3">
-        <v>-0.020209810577188635</v>
+        <v>-0.018688079297770752</v>
       </c>
       <c r="K41" s="3" t="b">
         <v>1</v>
@@ -4631,28 +4622,28 @@
         <v>4</v>
       </c>
       <c r="M41" s="3">
-        <v>-0.11537175074592565</v>
+        <v>-0.2611026383653271</v>
       </c>
       <c r="N41" s="3">
-        <v>-6.02409624710781</v>
+        <v>-21.797521353240167</v>
       </c>
       <c r="O41" s="3">
-        <v>42.35294117647059</v>
+        <v>17.647058823529413</v>
       </c>
       <c r="P41" s="3">
         <v>30.769232468942608</v>
       </c>
       <c r="Q41" s="3">
-        <v>22.941176470588232</v>
+        <v>19.17647058823529</v>
       </c>
       <c r="R41" s="3">
-        <v>19.352941176470587</v>
+        <v>11.941176470588237</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>107</v>
       </c>
       <c r="T41" s="3">
-        <v>-17.29</v>
+        <v>-24.71</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -4672,49 +4663,49 @@
         <v>4.78</v>
       </c>
       <c r="F42" s="3">
-        <v>-0.22122306773260972</v>
+        <v>-0.19137522701925977</v>
       </c>
       <c r="G42" s="3">
         <v>0.31</v>
       </c>
       <c r="H42" s="3">
-        <v>17.03</v>
+        <v>44.37</v>
       </c>
       <c r="I42" s="3">
-        <v>-14.91</v>
+        <v>-10.34</v>
       </c>
       <c r="J42" s="3">
-        <v>-0.016245164718787203</v>
+        <v>-0.01571371807489029</v>
       </c>
       <c r="K42" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L42" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M42" s="3">
-        <v>-0.2518458116422545</v>
+        <v>-0.2137156501539783</v>
       </c>
       <c r="N42" s="3">
-        <v>-19.671502336740698</v>
+        <v>-17.05882253210529</v>
       </c>
       <c r="O42" s="3">
-        <v>15.294117647058824</v>
+        <v>21.176470588235293</v>
       </c>
       <c r="P42" s="3">
         <v>20.568455255211532</v>
       </c>
       <c r="Q42" s="3">
-        <v>33.411764705882355</v>
+        <v>37.411764705882355</v>
       </c>
       <c r="R42" s="3">
-        <v>26.000000000000004</v>
+        <v>27.764705882352942</v>
       </c>
       <c r="S42" s="3" t="s">
         <v>111</v>
       </c>
       <c r="T42" s="3">
-        <v>-9.49</v>
+        <v>-7.72</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -4734,31 +4725,31 @@
         <v>8.46</v>
       </c>
       <c r="F43" s="2">
-        <v>0.11095593919919937</v>
+        <v>0.1163699819764546</v>
       </c>
       <c r="G43" s="2">
         <v>1.35</v>
       </c>
       <c r="H43" s="2">
-        <v>45.29</v>
+        <v>45.47</v>
       </c>
       <c r="I43" s="2">
-        <v>12.55</v>
+        <v>12.79</v>
       </c>
       <c r="J43" s="2">
-        <v>0.0034243542472177785</v>
+        <v>0.002381298672833308</v>
       </c>
       <c r="K43" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L43" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M43" s="2">
-        <v>0.126489215095396</v>
+        <v>0.1277020806679785</v>
       </c>
       <c r="N43" s="2">
-        <v>18.16200033702436</v>
+        <v>17.0829505500904</v>
       </c>
       <c r="O43" s="2">
         <v>75.29411764705883</v>
@@ -4767,16 +4758,16 @@
         <v>24.82490242340647</v>
       </c>
       <c r="Q43" s="2">
-        <v>58.11764705882352</v>
+        <v>57.882352941176464</v>
       </c>
       <c r="R43" s="2">
-        <v>53.47058823529413</v>
+        <v>53.58823529411765</v>
       </c>
       <c r="S43" s="2" t="s">
         <v>114</v>
       </c>
       <c r="T43" s="2">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -4796,49 +4787,49 @@
         <v>-0.66</v>
       </c>
       <c r="F44" s="2">
-        <v>0.13345135024355373</v>
+        <v>0.2025734114928086</v>
       </c>
       <c r="G44" s="2">
         <v>2.63</v>
       </c>
       <c r="H44" s="2">
-        <v>53.49</v>
+        <v>58.47</v>
       </c>
       <c r="I44" s="2">
-        <v>9.97</v>
+        <v>14.39</v>
       </c>
       <c r="J44" s="2">
-        <v>0.01450454940312598</v>
+        <v>0.014569788092827165</v>
       </c>
       <c r="K44" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="2">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="M44" s="2">
-        <v>0.2057920351315552</v>
+        <v>0.25534861397047703</v>
       </c>
       <c r="N44" s="2">
-        <v>26.092282340640278</v>
+        <v>29.84760388034025</v>
       </c>
       <c r="O44" s="2">
-        <v>82.35294117647058</v>
+        <v>84.70588235294117</v>
       </c>
       <c r="P44" s="2">
         <v>25.20580223963847</v>
       </c>
       <c r="Q44" s="2">
-        <v>63.76470588235294</v>
+        <v>66.23529411764706</v>
       </c>
       <c r="R44" s="2">
-        <v>56.88235294117647</v>
+        <v>57.705882352941174</v>
       </c>
       <c r="S44" s="2" t="s">
         <v>103</v>
       </c>
       <c r="T44" s="2">
-        <v>22.07</v>
+        <v>22.89</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
@@ -4858,19 +4849,19 @@
         <v>1.02</v>
       </c>
       <c r="F45" s="1">
-        <v>-0.0505189061485746</v>
+        <v>-0.02307096070985258</v>
       </c>
       <c r="G45" s="1">
         <v>1.46</v>
       </c>
       <c r="H45" s="1">
-        <v>41.68</v>
+        <v>42.45</v>
       </c>
       <c r="I45" s="1">
-        <v>2.27</v>
+        <v>2.47</v>
       </c>
       <c r="J45" s="1">
-        <v>0.00020070066334538784</v>
+        <v>-0.000657157931105043</v>
       </c>
       <c r="K45" s="1" t="b">
         <v>0</v>
@@ -4879,28 +4870,28 @@
         <v>195</v>
       </c>
       <c r="M45" s="1">
-        <v>-0.030103743542144734</v>
+        <v>-0.008177345286706883</v>
       </c>
       <c r="N45" s="1">
-        <v>2.5027044732702732</v>
+        <v>3.4950079546218435</v>
       </c>
       <c r="O45" s="1">
-        <v>58.82352941176471</v>
+        <v>56.470588235294116</v>
       </c>
       <c r="P45" s="1">
         <v>17.57882034058413</v>
       </c>
       <c r="Q45" s="1">
-        <v>42.470588235294116</v>
+        <v>42.94117647058823</v>
       </c>
       <c r="R45" s="1">
-        <v>41.411764705882355</v>
+        <v>40.8235294117647</v>
       </c>
       <c r="S45" s="1" t="s">
         <v>109</v>
       </c>
       <c r="T45" s="1">
-        <v>-2.92</v>
+        <v>-3.51</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
@@ -4920,19 +4911,19 @@
         <v>5.18</v>
       </c>
       <c r="F46" s="3">
-        <v>-0.3333067630590114</v>
+        <v>-0.31012702325647357</v>
       </c>
       <c r="G46" s="3">
         <v>1.77</v>
       </c>
       <c r="H46" s="3">
-        <v>33.28</v>
+        <v>32.82</v>
       </c>
       <c r="I46" s="3">
-        <v>-35.29</v>
+        <v>-35.55</v>
       </c>
       <c r="J46" s="3">
-        <v>-0.007012747777044744</v>
+        <v>-0.006781749839960764</v>
       </c>
       <c r="K46" s="3" t="b">
         <v>0</v>
@@ -4941,28 +4932,28 @@
         <v>17</v>
       </c>
       <c r="M46" s="3">
-        <v>-0.2991335560873788</v>
+        <v>-0.285196406135121</v>
       </c>
       <c r="N46" s="3">
-        <v>-24.40027678125313</v>
+        <v>-24.20689813021956</v>
       </c>
       <c r="O46" s="3">
-        <v>9.411764705882353</v>
+        <v>11.76470588235294</v>
       </c>
       <c r="P46" s="3">
         <v>54.33673655574689</v>
       </c>
       <c r="Q46" s="3">
-        <v>42.8235294117647</v>
+        <v>42.823529411764696</v>
       </c>
       <c r="R46" s="3">
-        <v>25.705882352941167</v>
+        <v>26.764705882352935</v>
       </c>
       <c r="S46" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T46" s="3">
-        <v>4.67</v>
+        <v>5.73</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
@@ -4982,19 +4973,19 @@
         <v>2.6</v>
       </c>
       <c r="F47" s="2">
-        <v>0.10694175764340416</v>
+        <v>0.08868422944994209</v>
       </c>
       <c r="G47" s="2">
         <v>1.42</v>
       </c>
       <c r="H47" s="2">
-        <v>48.01</v>
+        <v>46.31</v>
       </c>
       <c r="I47" s="2">
-        <v>2.93</v>
+        <v>2.09</v>
       </c>
       <c r="J47" s="2">
-        <v>0.020678712732062017</v>
+        <v>0.02019858679799019</v>
       </c>
       <c r="K47" s="2" t="b">
         <v>0</v>
@@ -5003,22 +4994,22 @@
         <v>-56</v>
       </c>
       <c r="M47" s="2">
-        <v>0.12558168871884012</v>
+        <v>0.10228274787977076</v>
       </c>
       <c r="N47" s="2">
-        <v>18.071247699368765</v>
+        <v>14.541017271269608</v>
       </c>
       <c r="O47" s="2">
-        <v>72.94117647058823</v>
+        <v>74.11764705882354</v>
       </c>
       <c r="P47" s="2">
         <v>14.027665623490911</v>
       </c>
       <c r="Q47" s="2">
-        <v>53.411764705882355</v>
+        <v>51.41176470588235</v>
       </c>
       <c r="R47" s="2">
-        <v>50.88235294117647</v>
+        <v>50.88235294117648</v>
       </c>
       <c r="S47" s="2" t="s">
         <v>109</v>
@@ -5038,25 +5029,25 @@
         <v>49.411764705882355</v>
       </c>
       <c r="D48" s="2">
-        <v>7.596214511041009</v>
+        <v>7.690851735015774</v>
       </c>
       <c r="E48" s="2">
         <v>0.66</v>
       </c>
       <c r="F48" s="2">
-        <v>0.16699144288684903</v>
+        <v>0.13125935319820153</v>
       </c>
       <c r="G48" s="2">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="H48" s="2">
-        <v>58.52</v>
+        <v>56.48</v>
       </c>
       <c r="I48" s="2">
-        <v>30.06</v>
+        <v>28.73</v>
       </c>
       <c r="J48" s="2">
-        <v>0.016287491376495985</v>
+        <v>0.017251336136699023</v>
       </c>
       <c r="K48" s="2" t="b">
         <v>0</v>
@@ -5065,28 +5056,28 @@
         <v>242</v>
       </c>
       <c r="M48" s="2">
-        <v>0.19361991585175753</v>
+        <v>0.15100958234628603</v>
       </c>
       <c r="N48" s="2">
-        <v>24.8750704126605</v>
+        <v>19.413700717921152</v>
       </c>
       <c r="O48" s="2">
-        <v>81.17647058823529</v>
+        <v>77.64705882352942</v>
       </c>
       <c r="P48" s="2">
         <v>20.965127717005057</v>
       </c>
       <c r="Q48" s="2">
-        <v>65.6470588235294</v>
+        <v>65.41176470588236</v>
       </c>
       <c r="R48" s="2">
-        <v>56.35294117647059</v>
+        <v>55.529411764705884</v>
       </c>
       <c r="S48" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T48" s="2">
-        <v>7.08</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
@@ -5106,49 +5097,49 @@
         <v>-11.3</v>
       </c>
       <c r="F49" s="2">
-        <v>0.12231415592308581</v>
+        <v>0.15698510274996505</v>
       </c>
       <c r="G49" s="2">
         <v>1.08</v>
       </c>
       <c r="H49" s="2">
-        <v>44.14</v>
+        <v>50.37</v>
       </c>
       <c r="I49" s="2">
-        <v>-7.58</v>
+        <v>-3.28</v>
       </c>
       <c r="J49" s="2">
-        <v>0.014075296675261834</v>
+        <v>0.013333842539416883</v>
       </c>
       <c r="K49" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L49" s="2">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="M49" s="2">
-        <v>0.12586461898507362</v>
+        <v>0.1595752967365991</v>
       </c>
       <c r="N49" s="2">
-        <v>18.099540725992114</v>
+        <v>20.27027215695245</v>
       </c>
       <c r="O49" s="2">
-        <v>74.11764705882354</v>
+        <v>80</v>
       </c>
       <c r="P49" s="2">
         <v>29.65964183269925</v>
       </c>
       <c r="Q49" s="2">
-        <v>59.529411764705884</v>
+        <v>60.94117647058824</v>
       </c>
       <c r="R49" s="2">
-        <v>54.58823529411766</v>
+        <v>56.235294117647065</v>
       </c>
       <c r="S49" s="2" t="s">
         <v>102</v>
       </c>
       <c r="T49" s="2">
-        <v>23.49</v>
+        <v>25.14</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
@@ -5162,49 +5153,49 @@
         <v>8.235294117647058</v>
       </c>
       <c r="D50" s="3">
-        <v>16.137931034482758</v>
+        <v>15.588859416445624</v>
       </c>
       <c r="E50" s="3">
         <v>12.72</v>
       </c>
       <c r="F50" s="3">
-        <v>-0.3136914901662976</v>
+        <v>-0.2203026622081312</v>
       </c>
       <c r="G50" s="3">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="H50" s="3">
-        <v>50.58</v>
+        <v>49.36</v>
       </c>
       <c r="I50" s="3">
-        <v>6.92</v>
+        <v>5.64</v>
       </c>
       <c r="J50" s="3">
-        <v>0.008112720128050002</v>
+        <v>0.0021266524314180147</v>
       </c>
       <c r="K50" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L50" s="3">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M50" s="3">
-        <v>-0.1872062435829821</v>
+        <v>-0.128350775682623</v>
       </c>
       <c r="N50" s="3">
-        <v>-13.207545530813453</v>
+        <v>-8.52233508496976</v>
       </c>
       <c r="O50" s="3">
-        <v>23.52941176470588</v>
+        <v>36.470588235294116</v>
       </c>
       <c r="P50" s="3">
         <v>41.201484669672254</v>
       </c>
       <c r="Q50" s="3">
-        <v>49.05882352941176</v>
+        <v>45.88235294117648</v>
       </c>
       <c r="R50" s="3">
-        <v>25.88235294117647</v>
+        <v>28.82352941176471</v>
       </c>
       <c r="S50" s="3" t="s">
         <v>108</v>
@@ -5228,19 +5219,19 @@
         <v>14.39</v>
       </c>
       <c r="F51" s="1">
-        <v>0.34437049064350345</v>
+        <v>0.5440662772990568</v>
       </c>
       <c r="G51" s="1">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="H51" s="1">
-        <v>54.7</v>
+        <v>60.12</v>
       </c>
       <c r="I51" s="1">
-        <v>33.53</v>
+        <v>44.64</v>
       </c>
       <c r="J51" s="1">
-        <v>0.04871111869746869</v>
+        <v>0.04881842419585913</v>
       </c>
       <c r="K51" s="1" t="b">
         <v>0</v>
@@ -5249,22 +5240,22 @@
         <v>14</v>
       </c>
       <c r="M51" s="1">
-        <v>0.37765608184963906</v>
+        <v>0.5677017974270924</v>
       </c>
       <c r="N51" s="1">
-        <v>43.27868701244865</v>
+        <v>61.08292222600178</v>
       </c>
       <c r="O51" s="1">
-        <v>92.94117647058823</v>
+        <v>97.6470588235294</v>
       </c>
       <c r="P51" s="1">
         <v>38.38748944617691</v>
       </c>
       <c r="Q51" s="1">
-        <v>53.529411764705884</v>
+        <v>55.52941176470589</v>
       </c>
       <c r="R51" s="1">
-        <v>45.00000000000001</v>
+        <v>46.411764705882355</v>
       </c>
       <c r="S51" s="1" t="s">
         <v>97</v>
@@ -5288,43 +5279,43 @@
         <v>-5.41</v>
       </c>
       <c r="F52" s="3">
-        <v>-0.17109450993355713</v>
+        <v>-0.19213994158659858</v>
       </c>
       <c r="G52" s="3">
-        <v>